--- a/data/arsenal_stats.xlsx
+++ b/data/arsenal_stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bungeltd-my.sharepoint.com/personal/przemyslaw_iskra_bunge_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8141" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8FCD32E-9BEF-4135-9A18-E8DB583F1F57}"/>
+  <xr:revisionPtr revIDLastSave="8244" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{081A4EE6-617B-4068-A6F2-68A91462960B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="799" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="799" firstSheet="1" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="19" state="hidden" r:id="rId1"/>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2255" uniqueCount="479">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2257" uniqueCount="480">
   <si>
     <t>Arsenal FC squad statistics</t>
   </si>
@@ -1381,16 +1381,7 @@
     <t>−1</t>
   </si>
   <si>
-    <t>−2</t>
-  </si>
-  <si>
     <t>−4</t>
-  </si>
-  <si>
-    <t>31.08.2026</t>
-  </si>
-  <si>
-    <t>Villa Park (A)</t>
   </si>
   <si>
     <t>KONSA Ezri</t>
@@ -1400,9 +1391,6 @@
   </si>
   <si>
     <t>−5</t>
-  </si>
-  <si>
-    <t>1-0</t>
   </si>
   <si>
     <t>06.09.2026</t>
@@ -1465,9 +1453,6 @@
     <t>Gabriel</t>
   </si>
   <si>
-    <t>Mosquera</t>
-  </si>
-  <si>
     <t>White</t>
   </si>
   <si>
@@ -1492,16 +1477,10 @@
     <t>Sub</t>
   </si>
   <si>
-    <t>Eze</t>
-  </si>
-  <si>
     <t>Subbed</t>
   </si>
   <si>
     <t>Merino</t>
-  </si>
-  <si>
-    <t>Guimares</t>
   </si>
   <si>
     <t>Konsa</t>
@@ -1517,6 +1496,30 @@
   </si>
   <si>
     <t>A</t>
+  </si>
+  <si>
+    <t>Hincapie</t>
+  </si>
+  <si>
+    <t>Gyokeres</t>
+  </si>
+  <si>
+    <t>Madueke</t>
+  </si>
+  <si>
+    <t>2-1</t>
+  </si>
+  <si>
+    <t>−3</t>
+  </si>
+  <si>
+    <t>09.09.2026</t>
+  </si>
+  <si>
+    <t>SSC Napoli</t>
+  </si>
+  <si>
+    <t>Stadio Diego Armando Maradona (A)</t>
   </si>
 </sst>
 </file>
@@ -3035,18 +3038,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3071,13 +3062,16 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3089,23 +3083,32 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="54" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3143,15 +3146,6 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="28" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3159,27 +3153,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="61" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="10" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="37" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="11" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3272,67 +3245,31 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="61" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="10" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="37" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="11" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="54" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3410,6 +3347,63 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3420,6 +3414,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
@@ -4623,7 +4624,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="32"/>
                 <c:pt idx="0">
-                  <c:v>3</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -4632,19 +4633,19 @@
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>2</c:v>
-                </c:pt>
                 <c:pt idx="5">
-                  <c:v>3</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>3</c:v>
@@ -4656,37 +4657,37 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="13">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>3</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>3</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>3</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>2</c:v>
@@ -4695,7 +4696,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>3</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>0</c:v>
@@ -4707,7 +4708,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>3</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>0</c:v>
@@ -4874,7 +4875,7 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -4904,7 +4905,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>0</c:v>
@@ -6463,7 +6464,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{17A5E28A-E463-4C40-A63A-BEB078719740}" type="CELLRANGE">
+                    <a:fld id="{BBD2B189-A30D-46C5-BA22-BABC4E570F61}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6497,7 +6498,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{13C187B5-7472-4732-835F-86471B762933}" type="CELLRANGE">
+                    <a:fld id="{867B5695-9842-4520-A406-ABF7043751F9}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6531,7 +6532,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C5EE53E9-36DD-4297-8848-0ACFD4A419E3}" type="CELLRANGE">
+                    <a:fld id="{CD184A09-31FD-4705-A0B6-B34E9815EE9C}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6565,7 +6566,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{AB209AE1-B687-4F0E-AEBB-B4B5375F1361}" type="CELLRANGE">
+                    <a:fld id="{F51BB28D-FE82-43CB-8492-66DA0EB1C159}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6599,7 +6600,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{4B0D3003-19DC-4D3B-88E1-65E8814380E1}" type="CELLRANGE">
+                    <a:fld id="{8130226E-9E9B-4C6D-AD60-9FB007F60840}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6633,7 +6634,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{354D48AD-2193-4027-87D1-98A35DAADE32}" type="CELLRANGE">
+                    <a:fld id="{FCFD2949-E0EE-4C28-AAF7-64677AE85E23}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6667,7 +6668,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{40014D28-61AC-4045-BB50-ACB1AF492329}" type="CELLRANGE">
+                    <a:fld id="{F34007A7-824C-4A7B-8485-AE2E27D134B7}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6701,7 +6702,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{0D1FE37A-BA8D-4640-ABA0-3133C666A140}" type="CELLRANGE">
+                    <a:fld id="{F3BF0278-F322-4197-9378-895D1C2BDC7B}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6735,7 +6736,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A704AE04-F2E7-4EB2-AA11-583CDB7CF41A}" type="CELLRANGE">
+                    <a:fld id="{22D83495-8E80-4D15-AE2C-682325F7CBAA}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6769,7 +6770,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2EFA9555-2E10-4B83-A22A-3C8818BC45AF}" type="CELLRANGE">
+                    <a:fld id="{DBF8691F-6A1B-444B-B28B-F5AC8C275F36}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6803,7 +6804,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8299E1A9-5ABC-442F-A0AF-60B6D719A013}" type="CELLRANGE">
+                    <a:fld id="{E10B2AB4-7FDA-4D57-B95F-48656F926D1A}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6837,7 +6838,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D5ACC964-D12A-4C04-AA3D-AE5D7CA61D41}" type="CELLRANGE">
+                    <a:fld id="{C58472E1-2634-4C6B-92F2-758C6F4F79CB}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6886,7 +6887,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{E066D06C-DD71-47EB-B6B6-BC37C07B855C}" type="CELLRANGE">
+                    <a:fld id="{B203CEB0-15E7-4E72-9556-673B2EA6EC56}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr>
                         <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
@@ -6945,7 +6946,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{1CB60E55-B1DB-4B73-8E21-159BE9B35D96}" type="CELLRANGE">
+                    <a:fld id="{A53CD454-C59B-4F46-B29C-0756287872AE}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6979,7 +6980,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9B4B8748-539E-4BFE-9A58-25FD825C95C2}" type="CELLRANGE">
+                    <a:fld id="{2C74B345-F96E-4093-91FF-566EEFFC679A}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7013,7 +7014,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6CF0C524-95DE-496B-8432-6E1A6177F001}" type="CELLRANGE">
+                    <a:fld id="{E51F1051-D723-4A91-9ED6-2AEE3CEEC3EC}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7047,7 +7048,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6227454D-25FC-4DDC-9FC7-ACCC06475492}" type="CELLRANGE">
+                    <a:fld id="{28DA3CCE-E8CE-4EF9-B6B0-B1D523F50408}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7225,19 +7226,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>193</c:v>
+                  <c:v>194</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>41</c:v>
+                  <c:v>42</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>264</c:v>
+                  <c:v>265</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>315</c:v>
+                  <c:v>316</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>237</c:v>
+                  <c:v>238</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>55</c:v>
@@ -7249,31 +7250,31 @@
                   <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>56</c:v>
+                  <c:v>57</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>44</c:v>
+                  <c:v>45</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>51</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>80</c:v>
+                  <c:v>81</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>114</c:v>
+                  <c:v>115</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>68</c:v>
+                  <c:v>69</c:v>
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>2</c:v>
@@ -7300,7 +7301,7 @@
                   <c:v>83</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>44</c:v>
+                  <c:v>45</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>10</c:v>
@@ -7330,7 +7331,7 @@
                   <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>38</c:v>
+                  <c:v>39</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>0</c:v>
@@ -7527,7 +7528,7 @@
                         <c:v>83</c:v>
                       </c:pt>
                       <c:pt idx="4">
-                        <c:v>44</c:v>
+                        <c:v>45</c:v>
                       </c:pt>
                       <c:pt idx="5">
                         <c:v>10</c:v>
@@ -7557,7 +7558,7 @@
                         <c:v>15</c:v>
                       </c:pt>
                       <c:pt idx="14">
-                        <c:v>38</c:v>
+                        <c:v>39</c:v>
                       </c:pt>
                       <c:pt idx="15">
                         <c:v>0</c:v>
@@ -14183,30 +14184,30 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
       <c r="B1" s="5"/>
-      <c r="C1" s="204" t="s">
+      <c r="C1" s="212" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="204"/>
-      <c r="E1" s="205" t="s">
+      <c r="D1" s="212"/>
+      <c r="E1" s="213" t="s">
         <v>120</v>
       </c>
-      <c r="F1" s="205"/>
-      <c r="G1" s="204" t="s">
+      <c r="F1" s="213"/>
+      <c r="G1" s="212" t="s">
         <v>108</v>
       </c>
-      <c r="H1" s="204"/>
-      <c r="I1" s="205" t="s">
+      <c r="H1" s="212"/>
+      <c r="I1" s="213" t="s">
         <v>110</v>
       </c>
-      <c r="J1" s="205"/>
-      <c r="K1" s="204" t="s">
+      <c r="J1" s="213"/>
+      <c r="K1" s="212" t="s">
         <v>39</v>
       </c>
-      <c r="L1" s="204"/>
-      <c r="M1" s="202" t="s">
+      <c r="L1" s="212"/>
+      <c r="M1" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="203"/>
+      <c r="N1" s="211"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -15913,30 +15914,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="204" t="s">
+      <c r="C2" s="212" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="204"/>
-      <c r="E2" s="205" t="s">
+      <c r="D2" s="212"/>
+      <c r="E2" s="213" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="205"/>
-      <c r="G2" s="204" t="s">
+      <c r="F2" s="213"/>
+      <c r="G2" s="212" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="204"/>
-      <c r="I2" s="205" t="s">
+      <c r="H2" s="212"/>
+      <c r="I2" s="213" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="205"/>
-      <c r="K2" s="204" t="s">
+      <c r="J2" s="213"/>
+      <c r="K2" s="212" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="204"/>
-      <c r="M2" s="209" t="s">
+      <c r="L2" s="212"/>
+      <c r="M2" s="205" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="209"/>
+      <c r="N2" s="205"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -17740,30 +17741,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="204" t="s">
+      <c r="C2" s="212" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="204"/>
-      <c r="E2" s="205" t="s">
+      <c r="D2" s="212"/>
+      <c r="E2" s="213" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="205"/>
-      <c r="G2" s="204" t="s">
+      <c r="F2" s="213"/>
+      <c r="G2" s="212" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="204"/>
-      <c r="I2" s="205" t="s">
+      <c r="H2" s="212"/>
+      <c r="I2" s="213" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="205"/>
-      <c r="K2" s="204" t="s">
+      <c r="J2" s="213"/>
+      <c r="K2" s="212" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="204"/>
-      <c r="M2" s="209" t="s">
+      <c r="L2" s="212"/>
+      <c r="M2" s="205" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="209"/>
+      <c r="N2" s="205"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -19430,30 +19431,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="204" t="s">
+      <c r="C2" s="212" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="204"/>
-      <c r="E2" s="205" t="s">
+      <c r="D2" s="212"/>
+      <c r="E2" s="213" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="205"/>
-      <c r="G2" s="204" t="s">
+      <c r="F2" s="213"/>
+      <c r="G2" s="212" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="204"/>
-      <c r="I2" s="205" t="s">
+      <c r="H2" s="212"/>
+      <c r="I2" s="213" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="205"/>
-      <c r="K2" s="204" t="s">
+      <c r="J2" s="213"/>
+      <c r="K2" s="212" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="204"/>
-      <c r="M2" s="209" t="s">
+      <c r="L2" s="212"/>
+      <c r="M2" s="205" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="209"/>
+      <c r="N2" s="205"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -21256,30 +21257,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="204" t="s">
+      <c r="C2" s="212" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="204"/>
-      <c r="E2" s="205" t="s">
+      <c r="D2" s="212"/>
+      <c r="E2" s="213" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="205"/>
-      <c r="G2" s="204" t="s">
+      <c r="F2" s="213"/>
+      <c r="G2" s="212" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="204"/>
-      <c r="I2" s="205" t="s">
+      <c r="H2" s="212"/>
+      <c r="I2" s="213" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="205"/>
-      <c r="K2" s="204" t="s">
+      <c r="J2" s="213"/>
+      <c r="K2" s="212" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="204"/>
-      <c r="M2" s="209" t="s">
+      <c r="L2" s="212"/>
+      <c r="M2" s="205" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="209"/>
+      <c r="N2" s="205"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -23128,36 +23129,36 @@
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="206" t="s">
+      <c r="C2" s="202" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="207"/>
-      <c r="E2" s="208"/>
-      <c r="F2" s="211" t="s">
+      <c r="D2" s="203"/>
+      <c r="E2" s="204"/>
+      <c r="F2" s="207" t="s">
         <v>120</v>
       </c>
-      <c r="G2" s="212"/>
-      <c r="H2" s="213"/>
-      <c r="I2" s="206" t="s">
+      <c r="G2" s="208"/>
+      <c r="H2" s="209"/>
+      <c r="I2" s="202" t="s">
         <v>108</v>
       </c>
-      <c r="J2" s="207"/>
-      <c r="K2" s="208"/>
-      <c r="L2" s="211" t="s">
+      <c r="J2" s="203"/>
+      <c r="K2" s="204"/>
+      <c r="L2" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="M2" s="212"/>
-      <c r="N2" s="213"/>
-      <c r="O2" s="206" t="s">
+      <c r="M2" s="208"/>
+      <c r="N2" s="209"/>
+      <c r="O2" s="202" t="s">
         <v>39</v>
       </c>
-      <c r="P2" s="207"/>
-      <c r="Q2" s="208"/>
-      <c r="R2" s="209" t="s">
+      <c r="P2" s="203"/>
+      <c r="Q2" s="204"/>
+      <c r="R2" s="205" t="s">
         <v>7</v>
       </c>
-      <c r="S2" s="209"/>
-      <c r="T2" s="209"/>
+      <c r="S2" s="205"/>
+      <c r="T2" s="205"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -23230,7 +23231,7 @@
       </c>
       <c r="C4" s="6">
         <f>'Premier League'!C4</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="6">
         <f>'Premier League'!D4</f>
@@ -23290,7 +23291,7 @@
       </c>
       <c r="R4" s="2">
         <f>SUM(C4,F4,I4,L4,O4)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S4" s="2">
         <f t="shared" ref="S4:T4" si="0">SUM(D4,G4,J4,M4,P4)</f>
@@ -23472,7 +23473,7 @@
       </c>
       <c r="C7" s="6">
         <f>'Premier League'!C7</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" s="6">
         <f>'Premier League'!D7</f>
@@ -23532,7 +23533,7 @@
       </c>
       <c r="R7" s="2">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S7" s="2">
         <f t="shared" si="2"/>
@@ -23553,7 +23554,7 @@
       </c>
       <c r="C8" s="6">
         <f>'Premier League'!C8</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" s="6">
         <f>'Premier League'!D8</f>
@@ -23613,7 +23614,7 @@
       </c>
       <c r="R8" s="2">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S8" s="2">
         <f t="shared" si="2"/>
@@ -23634,7 +23635,7 @@
       </c>
       <c r="C9" s="6">
         <f>'Premier League'!C9</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" s="6">
         <f>'Premier League'!D9</f>
@@ -23694,7 +23695,7 @@
       </c>
       <c r="R9" s="2">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S9" s="2">
         <f t="shared" si="2"/>
@@ -23715,7 +23716,7 @@
       </c>
       <c r="C10" s="6">
         <f>'Premier League'!C10</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" s="6">
         <f>'Premier League'!D10</f>
@@ -23775,7 +23776,7 @@
       </c>
       <c r="R10" s="2">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S10" s="2">
         <f t="shared" si="2"/>
@@ -23796,11 +23797,11 @@
       </c>
       <c r="C11" s="6">
         <f>'Premier League'!C11</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" s="6">
         <f>'Premier League'!D11</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" s="6">
         <f>'Premier League'!E11</f>
@@ -23856,11 +23857,11 @@
       </c>
       <c r="R11" s="2">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S11" s="2">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T11" s="2">
         <f t="shared" si="3"/>
@@ -24120,7 +24121,7 @@
       </c>
       <c r="C15" s="6">
         <f>'Premier League'!C15</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" s="6">
         <f>'Premier League'!D15</f>
@@ -24180,7 +24181,7 @@
       </c>
       <c r="R15" s="2">
         <f>SUM(C15,F15,I15,L15,O15)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S15" s="2">
         <f>SUM(D15,G15,J15,M15,P15)</f>
@@ -24197,11 +24198,11 @@
         <v>15</v>
       </c>
       <c r="B16" s="149" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C16" s="6">
         <f>'Premier League'!C16</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="6">
         <f>'Premier League'!D16</f>
@@ -24261,7 +24262,7 @@
       </c>
       <c r="R16" s="2">
         <f t="shared" ref="R16:R37" si="4">SUM(C16,F16,I16,L16,O16)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S16" s="2">
         <f t="shared" ref="S16:S37" si="5">SUM(D16,G16,J16,M16,P16)</f>
@@ -24282,7 +24283,7 @@
       </c>
       <c r="C17" s="6">
         <f>'Premier League'!C17</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" s="6">
         <f>'Premier League'!D17</f>
@@ -24290,7 +24291,7 @@
       </c>
       <c r="E17" s="6">
         <f>'Premier League'!E17</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="4">
         <f>Europe!C17</f>
@@ -24342,7 +24343,7 @@
       </c>
       <c r="R17" s="2">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S17" s="2">
         <f t="shared" si="5"/>
@@ -24350,7 +24351,7 @@
       </c>
       <c r="T17" s="2">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V17" s="55"/>
     </row>
@@ -24363,7 +24364,7 @@
       </c>
       <c r="C18" s="6">
         <f>'Premier League'!C18</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="6">
         <f>'Premier League'!D18</f>
@@ -24423,7 +24424,7 @@
       </c>
       <c r="R18" s="2">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S18" s="2">
         <f t="shared" si="5"/>
@@ -24523,7 +24524,7 @@
       </c>
       <c r="C20" s="6">
         <f>'Premier League'!C20</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" s="6">
         <f>'Premier League'!D20</f>
@@ -24583,7 +24584,7 @@
       </c>
       <c r="R20" s="2">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S20" s="2">
         <f t="shared" si="5"/>
@@ -24603,11 +24604,11 @@
       </c>
       <c r="C21" s="6">
         <f>'Premier League'!C21</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D21" s="6">
         <f>'Premier League'!D21</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" s="6">
         <f>'Premier League'!E21</f>
@@ -24663,11 +24664,11 @@
       </c>
       <c r="R21" s="2">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S21" s="2">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T21" s="2">
         <f t="shared" si="6"/>
@@ -24765,7 +24766,7 @@
       </c>
       <c r="C23" s="6">
         <f>'Premier League'!C23</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D23" s="6">
         <f>'Premier League'!D23</f>
@@ -24825,7 +24826,7 @@
       </c>
       <c r="R23" s="2">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S23" s="2">
         <f t="shared" si="5"/>
@@ -24927,7 +24928,7 @@
       </c>
       <c r="C25" s="6">
         <f>'Premier League'!C25</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25" s="6">
         <f>'Premier League'!D25</f>
@@ -24987,7 +24988,7 @@
       </c>
       <c r="R25" s="2">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S25" s="2">
         <f t="shared" si="5"/>
@@ -25169,7 +25170,7 @@
       </c>
       <c r="C28" s="6">
         <f>'Premier League'!C28</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D28" s="6">
         <f>'Premier League'!D28</f>
@@ -25177,7 +25178,7 @@
       </c>
       <c r="E28" s="6">
         <f>'Premier League'!E28</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" s="4">
         <f>Europe!C28</f>
@@ -25229,7 +25230,7 @@
       </c>
       <c r="R28" s="2">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S28" s="2">
         <f t="shared" si="5"/>
@@ -25237,7 +25238,7 @@
       </c>
       <c r="T28" s="2">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" s="55"/>
     </row>
@@ -25491,7 +25492,7 @@
       </c>
       <c r="C32" s="6">
         <f>'Premier League'!C32</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D32" s="6">
         <f>'Premier League'!D32</f>
@@ -25551,7 +25552,7 @@
       </c>
       <c r="R32" s="2">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S32" s="2">
         <f t="shared" si="5"/>
@@ -26016,36 +26017,36 @@
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
       <c r="D1" s="5"/>
-      <c r="E1" s="206" t="s">
+      <c r="E1" s="202" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="207"/>
-      <c r="G1" s="208"/>
-      <c r="H1" s="211" t="s">
+      <c r="F1" s="203"/>
+      <c r="G1" s="204"/>
+      <c r="H1" s="207" t="s">
         <v>120</v>
       </c>
-      <c r="I1" s="212"/>
-      <c r="J1" s="213"/>
-      <c r="K1" s="206" t="s">
+      <c r="I1" s="208"/>
+      <c r="J1" s="209"/>
+      <c r="K1" s="202" t="s">
         <v>108</v>
       </c>
-      <c r="L1" s="207"/>
-      <c r="M1" s="208"/>
-      <c r="N1" s="211" t="s">
+      <c r="L1" s="203"/>
+      <c r="M1" s="204"/>
+      <c r="N1" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="O1" s="212"/>
-      <c r="P1" s="213"/>
-      <c r="Q1" s="206" t="s">
+      <c r="O1" s="208"/>
+      <c r="P1" s="209"/>
+      <c r="Q1" s="202" t="s">
         <v>39</v>
       </c>
-      <c r="R1" s="207"/>
-      <c r="S1" s="208"/>
-      <c r="T1" s="209" t="s">
+      <c r="R1" s="203"/>
+      <c r="S1" s="204"/>
+      <c r="T1" s="205" t="s">
         <v>7</v>
       </c>
-      <c r="U1" s="209"/>
-      <c r="V1" s="209"/>
+      <c r="U1" s="205"/>
+      <c r="V1" s="205"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -37619,196 +37620,196 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F1" s="214">
-        <v>1</v>
-      </c>
-      <c r="G1" s="215"/>
-      <c r="H1" s="216"/>
-      <c r="I1" s="214">
+      <c r="F1" s="217">
+        <v>1</v>
+      </c>
+      <c r="G1" s="218"/>
+      <c r="H1" s="219"/>
+      <c r="I1" s="217">
         <v>2</v>
       </c>
-      <c r="J1" s="215"/>
-      <c r="K1" s="216"/>
-      <c r="L1" s="214">
-        <v>3</v>
-      </c>
-      <c r="M1" s="215"/>
-      <c r="N1" s="216"/>
-      <c r="O1" s="214">
+      <c r="J1" s="218"/>
+      <c r="K1" s="219"/>
+      <c r="L1" s="217">
+        <v>3</v>
+      </c>
+      <c r="M1" s="218"/>
+      <c r="N1" s="219"/>
+      <c r="O1" s="217">
         <v>4</v>
       </c>
-      <c r="P1" s="215"/>
-      <c r="Q1" s="216"/>
-      <c r="R1" s="214">
+      <c r="P1" s="218"/>
+      <c r="Q1" s="219"/>
+      <c r="R1" s="217">
         <v>5</v>
       </c>
-      <c r="S1" s="215"/>
-      <c r="T1" s="216"/>
-      <c r="U1" s="214">
+      <c r="S1" s="218"/>
+      <c r="T1" s="219"/>
+      <c r="U1" s="217">
         <v>6</v>
       </c>
-      <c r="V1" s="215"/>
-      <c r="W1" s="216"/>
-      <c r="X1" s="214">
+      <c r="V1" s="218"/>
+      <c r="W1" s="219"/>
+      <c r="X1" s="217">
         <v>7</v>
       </c>
-      <c r="Y1" s="215"/>
-      <c r="Z1" s="216"/>
-      <c r="AA1" s="214">
+      <c r="Y1" s="218"/>
+      <c r="Z1" s="219"/>
+      <c r="AA1" s="217">
         <v>8</v>
       </c>
-      <c r="AB1" s="215"/>
-      <c r="AC1" s="216"/>
-      <c r="AD1" s="214">
+      <c r="AB1" s="218"/>
+      <c r="AC1" s="219"/>
+      <c r="AD1" s="217">
         <v>9</v>
       </c>
-      <c r="AE1" s="215"/>
-      <c r="AF1" s="216"/>
-      <c r="AG1" s="214">
+      <c r="AE1" s="218"/>
+      <c r="AF1" s="219"/>
+      <c r="AG1" s="217">
         <v>10</v>
       </c>
-      <c r="AH1" s="215"/>
-      <c r="AI1" s="216"/>
-      <c r="AJ1" s="214">
+      <c r="AH1" s="218"/>
+      <c r="AI1" s="219"/>
+      <c r="AJ1" s="217">
         <v>11</v>
       </c>
-      <c r="AK1" s="215"/>
-      <c r="AL1" s="216"/>
-      <c r="AM1" s="214">
+      <c r="AK1" s="218"/>
+      <c r="AL1" s="219"/>
+      <c r="AM1" s="217">
         <v>12</v>
       </c>
-      <c r="AN1" s="215"/>
-      <c r="AO1" s="216"/>
-      <c r="AP1" s="214">
+      <c r="AN1" s="218"/>
+      <c r="AO1" s="219"/>
+      <c r="AP1" s="217">
         <v>13</v>
       </c>
-      <c r="AQ1" s="215"/>
-      <c r="AR1" s="216"/>
-      <c r="AS1" s="214">
+      <c r="AQ1" s="218"/>
+      <c r="AR1" s="219"/>
+      <c r="AS1" s="217">
         <v>14</v>
       </c>
-      <c r="AT1" s="215"/>
-      <c r="AU1" s="216"/>
-      <c r="AV1" s="214">
+      <c r="AT1" s="218"/>
+      <c r="AU1" s="219"/>
+      <c r="AV1" s="217">
         <v>15</v>
       </c>
-      <c r="AW1" s="215"/>
-      <c r="AX1" s="216"/>
-      <c r="AY1" s="214">
+      <c r="AW1" s="218"/>
+      <c r="AX1" s="219"/>
+      <c r="AY1" s="217">
         <v>16</v>
       </c>
-      <c r="AZ1" s="215"/>
-      <c r="BA1" s="216"/>
-      <c r="BB1" s="214">
+      <c r="AZ1" s="218"/>
+      <c r="BA1" s="219"/>
+      <c r="BB1" s="217">
         <v>17</v>
       </c>
-      <c r="BC1" s="215"/>
-      <c r="BD1" s="216"/>
-      <c r="BE1" s="214">
+      <c r="BC1" s="218"/>
+      <c r="BD1" s="219"/>
+      <c r="BE1" s="217">
         <v>18</v>
       </c>
-      <c r="BF1" s="215"/>
-      <c r="BG1" s="216"/>
-      <c r="BH1" s="214">
+      <c r="BF1" s="218"/>
+      <c r="BG1" s="219"/>
+      <c r="BH1" s="217">
         <v>19</v>
       </c>
-      <c r="BI1" s="215"/>
-      <c r="BJ1" s="216"/>
-      <c r="BK1" s="214">
+      <c r="BI1" s="218"/>
+      <c r="BJ1" s="219"/>
+      <c r="BK1" s="217">
         <v>20</v>
       </c>
-      <c r="BL1" s="215"/>
-      <c r="BM1" s="216"/>
-      <c r="BN1" s="214">
+      <c r="BL1" s="218"/>
+      <c r="BM1" s="219"/>
+      <c r="BN1" s="217">
         <v>21</v>
       </c>
-      <c r="BO1" s="215"/>
-      <c r="BP1" s="216"/>
-      <c r="BQ1" s="214">
+      <c r="BO1" s="218"/>
+      <c r="BP1" s="219"/>
+      <c r="BQ1" s="217">
         <v>22</v>
       </c>
-      <c r="BR1" s="215"/>
-      <c r="BS1" s="216"/>
-      <c r="BT1" s="214">
+      <c r="BR1" s="218"/>
+      <c r="BS1" s="219"/>
+      <c r="BT1" s="217">
         <v>23</v>
       </c>
-      <c r="BU1" s="215"/>
-      <c r="BV1" s="216"/>
-      <c r="BW1" s="214">
+      <c r="BU1" s="218"/>
+      <c r="BV1" s="219"/>
+      <c r="BW1" s="217">
         <v>24</v>
       </c>
-      <c r="BX1" s="215"/>
-      <c r="BY1" s="216"/>
-      <c r="BZ1" s="214">
+      <c r="BX1" s="218"/>
+      <c r="BY1" s="219"/>
+      <c r="BZ1" s="217">
         <v>25</v>
       </c>
-      <c r="CA1" s="215"/>
-      <c r="CB1" s="216"/>
-      <c r="CC1" s="214">
+      <c r="CA1" s="218"/>
+      <c r="CB1" s="219"/>
+      <c r="CC1" s="217">
         <v>26</v>
       </c>
-      <c r="CD1" s="215"/>
-      <c r="CE1" s="216"/>
-      <c r="CF1" s="214">
+      <c r="CD1" s="218"/>
+      <c r="CE1" s="219"/>
+      <c r="CF1" s="217">
         <v>27</v>
       </c>
-      <c r="CG1" s="215"/>
-      <c r="CH1" s="216"/>
-      <c r="CI1" s="214">
+      <c r="CG1" s="218"/>
+      <c r="CH1" s="219"/>
+      <c r="CI1" s="217">
         <v>28</v>
       </c>
-      <c r="CJ1" s="215"/>
-      <c r="CK1" s="216"/>
-      <c r="CL1" s="214">
+      <c r="CJ1" s="218"/>
+      <c r="CK1" s="219"/>
+      <c r="CL1" s="217">
         <v>29</v>
       </c>
-      <c r="CM1" s="215"/>
-      <c r="CN1" s="216"/>
-      <c r="CO1" s="214">
+      <c r="CM1" s="218"/>
+      <c r="CN1" s="219"/>
+      <c r="CO1" s="217">
         <v>30</v>
       </c>
-      <c r="CP1" s="215"/>
-      <c r="CQ1" s="216"/>
-      <c r="CR1" s="214">
+      <c r="CP1" s="218"/>
+      <c r="CQ1" s="219"/>
+      <c r="CR1" s="217">
         <v>31</v>
       </c>
-      <c r="CS1" s="215"/>
-      <c r="CT1" s="216"/>
-      <c r="CU1" s="214">
+      <c r="CS1" s="218"/>
+      <c r="CT1" s="219"/>
+      <c r="CU1" s="217">
         <v>32</v>
       </c>
-      <c r="CV1" s="215"/>
-      <c r="CW1" s="216"/>
-      <c r="CX1" s="214">
+      <c r="CV1" s="218"/>
+      <c r="CW1" s="219"/>
+      <c r="CX1" s="217">
         <v>33</v>
       </c>
-      <c r="CY1" s="215"/>
-      <c r="CZ1" s="216"/>
-      <c r="DA1" s="214">
+      <c r="CY1" s="218"/>
+      <c r="CZ1" s="219"/>
+      <c r="DA1" s="217">
         <v>34</v>
       </c>
-      <c r="DB1" s="215"/>
-      <c r="DC1" s="216"/>
-      <c r="DD1" s="214">
+      <c r="DB1" s="218"/>
+      <c r="DC1" s="219"/>
+      <c r="DD1" s="217">
         <v>35</v>
       </c>
-      <c r="DE1" s="215"/>
-      <c r="DF1" s="216"/>
-      <c r="DG1" s="214">
+      <c r="DE1" s="218"/>
+      <c r="DF1" s="219"/>
+      <c r="DG1" s="217">
         <v>36</v>
       </c>
-      <c r="DH1" s="215"/>
-      <c r="DI1" s="216"/>
-      <c r="DJ1" s="214">
+      <c r="DH1" s="218"/>
+      <c r="DI1" s="219"/>
+      <c r="DJ1" s="217">
         <v>37</v>
       </c>
-      <c r="DK1" s="215"/>
-      <c r="DL1" s="216"/>
-      <c r="DM1" s="214">
+      <c r="DK1" s="218"/>
+      <c r="DL1" s="219"/>
+      <c r="DM1" s="217">
         <v>38</v>
       </c>
-      <c r="DN1" s="215"/>
-      <c r="DO1" s="216"/>
+      <c r="DN1" s="218"/>
+      <c r="DO1" s="219"/>
     </row>
     <row r="2" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
@@ -37822,196 +37823,196 @@
       <c r="E2" s="220" t="s">
         <v>398</v>
       </c>
-      <c r="F2" s="217" t="s">
+      <c r="F2" s="214" t="s">
         <v>346</v>
       </c>
-      <c r="G2" s="218"/>
-      <c r="H2" s="219"/>
-      <c r="I2" s="222" t="s">
+      <c r="G2" s="215"/>
+      <c r="H2" s="216"/>
+      <c r="I2" s="214" t="s">
         <v>331</v>
       </c>
-      <c r="J2" s="223"/>
-      <c r="K2" s="224"/>
-      <c r="L2" s="217" t="s">
+      <c r="J2" s="215"/>
+      <c r="K2" s="216"/>
+      <c r="L2" s="214" t="s">
         <v>330</v>
       </c>
-      <c r="M2" s="218"/>
-      <c r="N2" s="219"/>
-      <c r="O2" s="217" t="s">
+      <c r="M2" s="215"/>
+      <c r="N2" s="216"/>
+      <c r="O2" s="214" t="s">
         <v>328</v>
       </c>
-      <c r="P2" s="218"/>
-      <c r="Q2" s="219"/>
-      <c r="R2" s="217" t="s">
+      <c r="P2" s="215"/>
+      <c r="Q2" s="216"/>
+      <c r="R2" s="214" t="s">
         <v>335</v>
       </c>
-      <c r="S2" s="218"/>
-      <c r="T2" s="219"/>
-      <c r="U2" s="217" t="s">
+      <c r="S2" s="215"/>
+      <c r="T2" s="216"/>
+      <c r="U2" s="214" t="s">
         <v>320</v>
       </c>
-      <c r="V2" s="218"/>
-      <c r="W2" s="219"/>
-      <c r="X2" s="217" t="s">
+      <c r="V2" s="215"/>
+      <c r="W2" s="216"/>
+      <c r="X2" s="214" t="s">
         <v>337</v>
       </c>
-      <c r="Y2" s="218"/>
-      <c r="Z2" s="219"/>
-      <c r="AA2" s="217" t="s">
+      <c r="Y2" s="215"/>
+      <c r="Z2" s="216"/>
+      <c r="AA2" s="214" t="s">
         <v>334</v>
       </c>
-      <c r="AB2" s="218"/>
-      <c r="AC2" s="219"/>
-      <c r="AD2" s="217" t="s">
+      <c r="AB2" s="215"/>
+      <c r="AC2" s="216"/>
+      <c r="AD2" s="214" t="s">
         <v>321</v>
       </c>
-      <c r="AE2" s="218"/>
-      <c r="AF2" s="219"/>
-      <c r="AG2" s="217" t="s">
+      <c r="AE2" s="215"/>
+      <c r="AF2" s="216"/>
+      <c r="AG2" s="214" t="s">
         <v>347</v>
       </c>
-      <c r="AH2" s="218"/>
-      <c r="AI2" s="219"/>
-      <c r="AJ2" s="217" t="s">
+      <c r="AH2" s="215"/>
+      <c r="AI2" s="216"/>
+      <c r="AJ2" s="214" t="s">
         <v>324</v>
       </c>
-      <c r="AK2" s="218"/>
-      <c r="AL2" s="219"/>
-      <c r="AM2" s="217" t="s">
+      <c r="AK2" s="215"/>
+      <c r="AL2" s="216"/>
+      <c r="AM2" s="214" t="s">
         <v>323</v>
       </c>
-      <c r="AN2" s="218"/>
-      <c r="AO2" s="219"/>
-      <c r="AP2" s="217" t="s">
+      <c r="AN2" s="215"/>
+      <c r="AO2" s="216"/>
+      <c r="AP2" s="214" t="s">
         <v>332</v>
       </c>
-      <c r="AQ2" s="218"/>
-      <c r="AR2" s="219"/>
-      <c r="AS2" s="217" t="s">
+      <c r="AQ2" s="215"/>
+      <c r="AR2" s="216"/>
+      <c r="AS2" s="214" t="s">
         <v>329</v>
       </c>
-      <c r="AT2" s="218"/>
-      <c r="AU2" s="219"/>
-      <c r="AV2" s="217" t="s">
+      <c r="AT2" s="215"/>
+      <c r="AU2" s="216"/>
+      <c r="AV2" s="214" t="s">
         <v>336</v>
       </c>
-      <c r="AW2" s="218"/>
-      <c r="AX2" s="219"/>
-      <c r="AY2" s="217" t="s">
+      <c r="AW2" s="215"/>
+      <c r="AX2" s="216"/>
+      <c r="AY2" s="214" t="s">
         <v>305</v>
       </c>
-      <c r="AZ2" s="218"/>
-      <c r="BA2" s="219"/>
-      <c r="BB2" s="217" t="s">
+      <c r="AZ2" s="215"/>
+      <c r="BA2" s="216"/>
+      <c r="BB2" s="214" t="s">
         <v>326</v>
       </c>
-      <c r="BC2" s="218"/>
-      <c r="BD2" s="219"/>
-      <c r="BE2" s="217" t="s">
+      <c r="BC2" s="215"/>
+      <c r="BD2" s="216"/>
+      <c r="BE2" s="214" t="s">
         <v>325</v>
       </c>
-      <c r="BF2" s="218"/>
-      <c r="BG2" s="219"/>
-      <c r="BH2" s="217" t="s">
+      <c r="BF2" s="215"/>
+      <c r="BG2" s="216"/>
+      <c r="BH2" s="214" t="s">
         <v>348</v>
       </c>
-      <c r="BI2" s="218"/>
-      <c r="BJ2" s="219"/>
-      <c r="BK2" s="217" t="s">
+      <c r="BI2" s="215"/>
+      <c r="BJ2" s="216"/>
+      <c r="BK2" s="214" t="s">
         <v>332</v>
       </c>
-      <c r="BL2" s="218"/>
-      <c r="BM2" s="219"/>
-      <c r="BN2" s="217" t="s">
+      <c r="BL2" s="215"/>
+      <c r="BM2" s="216"/>
+      <c r="BN2" s="214" t="s">
         <v>347</v>
       </c>
-      <c r="BO2" s="218"/>
-      <c r="BP2" s="219"/>
-      <c r="BQ2" s="217" t="s">
+      <c r="BO2" s="215"/>
+      <c r="BP2" s="216"/>
+      <c r="BQ2" s="214" t="s">
         <v>324</v>
       </c>
-      <c r="BR2" s="218"/>
-      <c r="BS2" s="219"/>
-      <c r="BT2" s="217" t="s">
+      <c r="BR2" s="215"/>
+      <c r="BS2" s="216"/>
+      <c r="BT2" s="214" t="s">
         <v>323</v>
       </c>
-      <c r="BU2" s="218"/>
-      <c r="BV2" s="219"/>
-      <c r="BW2" s="217" t="s">
+      <c r="BU2" s="215"/>
+      <c r="BV2" s="216"/>
+      <c r="BW2" s="214" t="s">
         <v>321</v>
       </c>
-      <c r="BX2" s="218"/>
-      <c r="BY2" s="219"/>
-      <c r="BZ2" s="217" t="s">
+      <c r="BX2" s="215"/>
+      <c r="BY2" s="216"/>
+      <c r="BZ2" s="214" t="s">
         <v>348</v>
       </c>
-      <c r="CA2" s="218"/>
-      <c r="CB2" s="219"/>
-      <c r="CC2" s="217" t="s">
+      <c r="CA2" s="215"/>
+      <c r="CB2" s="216"/>
+      <c r="CC2" s="214" t="s">
         <v>325</v>
       </c>
-      <c r="CD2" s="218"/>
-      <c r="CE2" s="219"/>
-      <c r="CF2" s="217" t="s">
+      <c r="CD2" s="215"/>
+      <c r="CE2" s="216"/>
+      <c r="CF2" s="214" t="s">
         <v>305</v>
       </c>
-      <c r="CG2" s="218"/>
-      <c r="CH2" s="219"/>
-      <c r="CI2" s="217" t="s">
+      <c r="CG2" s="215"/>
+      <c r="CH2" s="216"/>
+      <c r="CI2" s="214" t="s">
         <v>326</v>
       </c>
-      <c r="CJ2" s="218"/>
-      <c r="CK2" s="219"/>
-      <c r="CL2" s="217" t="s">
+      <c r="CJ2" s="215"/>
+      <c r="CK2" s="216"/>
+      <c r="CL2" s="214" t="s">
         <v>330</v>
       </c>
-      <c r="CM2" s="218"/>
-      <c r="CN2" s="219"/>
-      <c r="CO2" s="217" t="s">
+      <c r="CM2" s="215"/>
+      <c r="CN2" s="216"/>
+      <c r="CO2" s="214" t="s">
         <v>328</v>
       </c>
-      <c r="CP2" s="218"/>
-      <c r="CQ2" s="219"/>
-      <c r="CR2" s="217" t="s">
+      <c r="CP2" s="215"/>
+      <c r="CQ2" s="216"/>
+      <c r="CR2" s="214" t="s">
         <v>346</v>
       </c>
-      <c r="CS2" s="218"/>
-      <c r="CT2" s="219"/>
-      <c r="CU2" s="217" t="s">
+      <c r="CS2" s="215"/>
+      <c r="CT2" s="216"/>
+      <c r="CU2" s="214" t="s">
         <v>331</v>
       </c>
-      <c r="CV2" s="218"/>
-      <c r="CW2" s="219"/>
-      <c r="CX2" s="217" t="s">
+      <c r="CV2" s="215"/>
+      <c r="CW2" s="216"/>
+      <c r="CX2" s="214" t="s">
         <v>336</v>
       </c>
-      <c r="CY2" s="218"/>
-      <c r="CZ2" s="219"/>
-      <c r="DA2" s="217" t="s">
+      <c r="CY2" s="215"/>
+      <c r="CZ2" s="216"/>
+      <c r="DA2" s="214" t="s">
         <v>329</v>
       </c>
-      <c r="DB2" s="218"/>
-      <c r="DC2" s="219"/>
-      <c r="DD2" s="217" t="s">
+      <c r="DB2" s="215"/>
+      <c r="DC2" s="216"/>
+      <c r="DD2" s="214" t="s">
         <v>320</v>
       </c>
-      <c r="DE2" s="218"/>
-      <c r="DF2" s="219"/>
-      <c r="DG2" s="217" t="s">
+      <c r="DE2" s="215"/>
+      <c r="DF2" s="216"/>
+      <c r="DG2" s="214" t="s">
         <v>337</v>
       </c>
-      <c r="DH2" s="218"/>
-      <c r="DI2" s="219"/>
-      <c r="DJ2" s="217" t="s">
+      <c r="DH2" s="215"/>
+      <c r="DI2" s="216"/>
+      <c r="DJ2" s="214" t="s">
         <v>334</v>
       </c>
-      <c r="DK2" s="218"/>
-      <c r="DL2" s="219"/>
-      <c r="DM2" s="217" t="s">
+      <c r="DK2" s="215"/>
+      <c r="DL2" s="216"/>
+      <c r="DM2" s="214" t="s">
         <v>335</v>
       </c>
-      <c r="DN2" s="218"/>
-      <c r="DO2" s="219"/>
+      <c r="DN2" s="215"/>
+      <c r="DO2" s="216"/>
     </row>
     <row r="3" spans="1:119" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -38020,16 +38021,16 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="225"/>
-      <c r="D3" s="225"/>
-      <c r="E3" s="221"/>
+      <c r="C3" s="221"/>
+      <c r="D3" s="221"/>
+      <c r="E3" s="222"/>
       <c r="F3" s="160" t="s">
         <v>393</v>
       </c>
       <c r="G3" s="161" t="s">
         <v>394</v>
       </c>
-      <c r="H3" s="162" t="s">
+      <c r="H3" s="328" t="s">
         <v>395</v>
       </c>
       <c r="I3" s="160" t="s">
@@ -38047,7 +38048,7 @@
       <c r="M3" s="161" t="s">
         <v>394</v>
       </c>
-      <c r="N3" s="162" t="s">
+      <c r="N3" s="328" t="s">
         <v>395</v>
       </c>
       <c r="O3" s="160" t="s">
@@ -38375,13 +38376,13 @@
       </c>
       <c r="C4" s="58">
         <f>SUM(F4,I4,L4,O4,R4,U4,X4,AA4,AD4,AG4,AJ4,AM4,AP4,AS4,AV4,AY4,BB4,BE4,BH4,BK4,BN4,BQ4,BT4,BW4,BZ4,CC4,CF4,CI4,CL4,CO4,CR4,CU4,CX4,DA4,DD4,DG4,DJ4,DM4)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="58">
         <f t="shared" ref="D4:E4" si="0">SUM(G4,J4,M4,P4,S4,V4,Y4,AB4,AE4,AH4,AK4,AN4,AQ4,AT4,AW4,AZ4,BC4,BF4,BI4,BL4,BO4,BR4,BU4,BX4,CA4,CD4,CG4,CJ4,CM4,CP4,CS4,CV4,CY4,DB4,DE4,DH4,DK4,DN4)</f>
         <v>0</v>
       </c>
-      <c r="E4" s="58">
+      <c r="E4" s="51">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -38389,15 +38390,17 @@
         <v>1</v>
       </c>
       <c r="G4" s="36"/>
-      <c r="H4" s="53"/>
+      <c r="H4" s="168"/>
       <c r="I4" s="52">
         <v>1</v>
       </c>
       <c r="J4" s="36"/>
       <c r="K4" s="53"/>
-      <c r="L4" s="52"/>
+      <c r="L4" s="52">
+        <v>1</v>
+      </c>
       <c r="M4" s="36"/>
-      <c r="N4" s="53"/>
+      <c r="N4" s="168"/>
       <c r="O4" s="52"/>
       <c r="P4" s="36"/>
       <c r="Q4" s="53"/>
@@ -38519,19 +38522,19 @@
         <f t="shared" ref="D5:D15" si="2">SUM(G5,J5,M5,P5,S5,V5,Y5,AB5,AE5,AH5,AK5,AN5,AQ5,AT5,AW5,AZ5,BC5,BF5,BI5,BL5,BO5,BR5,BU5,BX5,CA5,CD5,CG5,CJ5,CM5,CP5,CS5,CV5,CY5,DB5,DE5,DH5,DK5,DN5)</f>
         <v>0</v>
       </c>
-      <c r="E5" s="58">
+      <c r="E5" s="51">
         <f t="shared" ref="E5:E15" si="3">SUM(H5,K5,N5,Q5,T5,W5,Z5,AC5,AF5,AI5,AL5,AO5,AR5,AU5,AX5,BA5,BD5,BG5,BJ5,BM5,BP5,BS5,BV5,BY5,CB5,CE5,CH5,CK5,CN5,CQ5,CT5,CW5,CZ5,DC5,DF5,DI5,DL5,DO5)</f>
         <v>0</v>
       </c>
       <c r="F5" s="52"/>
       <c r="G5" s="36"/>
-      <c r="H5" s="53"/>
+      <c r="H5" s="168"/>
       <c r="I5" s="52"/>
       <c r="J5" s="36"/>
       <c r="K5" s="53"/>
       <c r="L5" s="52"/>
       <c r="M5" s="36"/>
-      <c r="N5" s="53"/>
+      <c r="N5" s="168"/>
       <c r="O5" s="52"/>
       <c r="P5" s="36"/>
       <c r="Q5" s="53"/>
@@ -38653,7 +38656,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E6" s="58">
+      <c r="E6" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -38661,7 +38664,7 @@
         <v>1</v>
       </c>
       <c r="G6" s="36"/>
-      <c r="H6" s="53"/>
+      <c r="H6" s="168"/>
       <c r="I6" s="52">
         <v>1</v>
       </c>
@@ -38669,7 +38672,7 @@
       <c r="K6" s="53"/>
       <c r="L6" s="52"/>
       <c r="M6" s="36"/>
-      <c r="N6" s="53"/>
+      <c r="N6" s="168"/>
       <c r="O6" s="52"/>
       <c r="P6" s="36"/>
       <c r="Q6" s="53"/>
@@ -38785,13 +38788,13 @@
       </c>
       <c r="C7" s="58">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" s="58">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E7" s="58">
+      <c r="E7" s="51">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -38799,7 +38802,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="36"/>
-      <c r="H7" s="53">
+      <c r="H7" s="168">
         <v>1</v>
       </c>
       <c r="I7" s="52">
@@ -38807,9 +38810,11 @@
       </c>
       <c r="J7" s="36"/>
       <c r="K7" s="53"/>
-      <c r="L7" s="52"/>
+      <c r="L7" s="52">
+        <v>1</v>
+      </c>
       <c r="M7" s="36"/>
-      <c r="N7" s="53"/>
+      <c r="N7" s="168"/>
       <c r="O7" s="52"/>
       <c r="P7" s="36"/>
       <c r="Q7" s="53"/>
@@ -38925,13 +38930,13 @@
       </c>
       <c r="C8" s="58">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" s="58">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E8" s="58">
+      <c r="E8" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -38939,13 +38944,15 @@
         <v>1</v>
       </c>
       <c r="G8" s="36"/>
-      <c r="H8" s="53"/>
+      <c r="H8" s="168"/>
       <c r="I8" s="52"/>
       <c r="J8" s="36"/>
       <c r="K8" s="53"/>
-      <c r="L8" s="52"/>
+      <c r="L8" s="52">
+        <v>1</v>
+      </c>
       <c r="M8" s="36"/>
-      <c r="N8" s="53"/>
+      <c r="N8" s="168"/>
       <c r="O8" s="52"/>
       <c r="P8" s="36"/>
       <c r="Q8" s="53"/>
@@ -39061,13 +39068,13 @@
       </c>
       <c r="C9" s="58">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" s="58">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E9" s="58">
+      <c r="E9" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -39075,15 +39082,17 @@
         <v>1</v>
       </c>
       <c r="G9" s="36"/>
-      <c r="H9" s="53"/>
+      <c r="H9" s="168"/>
       <c r="I9" s="52">
         <v>1</v>
       </c>
       <c r="J9" s="36"/>
       <c r="K9" s="53"/>
-      <c r="L9" s="52"/>
+      <c r="L9" s="52">
+        <v>1</v>
+      </c>
       <c r="M9" s="36"/>
-      <c r="N9" s="53"/>
+      <c r="N9" s="168"/>
       <c r="O9" s="52"/>
       <c r="P9" s="36"/>
       <c r="Q9" s="53"/>
@@ -39199,13 +39208,13 @@
       </c>
       <c r="C10" s="58">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" s="58">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="E10" s="58">
+      <c r="E10" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -39215,7 +39224,7 @@
       <c r="G10" s="36">
         <v>1</v>
       </c>
-      <c r="H10" s="53"/>
+      <c r="H10" s="168"/>
       <c r="I10" s="52">
         <v>1</v>
       </c>
@@ -39223,9 +39232,11 @@
         <v>1</v>
       </c>
       <c r="K10" s="53"/>
-      <c r="L10" s="52"/>
+      <c r="L10" s="52">
+        <v>1</v>
+      </c>
       <c r="M10" s="36"/>
-      <c r="N10" s="53"/>
+      <c r="N10" s="168"/>
       <c r="O10" s="52"/>
       <c r="P10" s="36"/>
       <c r="Q10" s="53"/>
@@ -39341,13 +39352,13 @@
       </c>
       <c r="C11" s="58">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" s="58">
         <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="E11" s="58">
+        <v>2</v>
+      </c>
+      <c r="E11" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -39357,15 +39368,19 @@
       <c r="G11" s="36">
         <v>1</v>
       </c>
-      <c r="H11" s="53"/>
+      <c r="H11" s="168"/>
       <c r="I11" s="52">
         <v>1</v>
       </c>
       <c r="J11" s="36"/>
       <c r="K11" s="53"/>
-      <c r="L11" s="52"/>
-      <c r="M11" s="36"/>
-      <c r="N11" s="53"/>
+      <c r="L11" s="52">
+        <v>1</v>
+      </c>
+      <c r="M11" s="36">
+        <v>1</v>
+      </c>
+      <c r="N11" s="168"/>
       <c r="O11" s="52"/>
       <c r="P11" s="36"/>
       <c r="Q11" s="53"/>
@@ -39487,7 +39502,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E12" s="58">
+      <c r="E12" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -39495,7 +39510,7 @@
         <v>1</v>
       </c>
       <c r="G12" s="36"/>
-      <c r="H12" s="53"/>
+      <c r="H12" s="168"/>
       <c r="I12" s="52">
         <v>1</v>
       </c>
@@ -39503,7 +39518,7 @@
       <c r="K12" s="53"/>
       <c r="L12" s="52"/>
       <c r="M12" s="36"/>
-      <c r="N12" s="53"/>
+      <c r="N12" s="168"/>
       <c r="O12" s="52"/>
       <c r="P12" s="36"/>
       <c r="Q12" s="53"/>
@@ -39625,19 +39640,19 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E13" s="58">
+      <c r="E13" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F13" s="52"/>
       <c r="G13" s="36"/>
-      <c r="H13" s="53"/>
+      <c r="H13" s="168"/>
       <c r="I13" s="52"/>
       <c r="J13" s="36"/>
       <c r="K13" s="53"/>
       <c r="L13" s="52"/>
       <c r="M13" s="36"/>
-      <c r="N13" s="53"/>
+      <c r="N13" s="168"/>
       <c r="O13" s="52"/>
       <c r="P13" s="36"/>
       <c r="Q13" s="53"/>
@@ -39759,19 +39774,19 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E14" s="58">
+      <c r="E14" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F14" s="52"/>
       <c r="G14" s="36"/>
-      <c r="H14" s="53"/>
+      <c r="H14" s="168"/>
       <c r="I14" s="52"/>
       <c r="J14" s="36"/>
       <c r="K14" s="53"/>
       <c r="L14" s="52"/>
       <c r="M14" s="36"/>
-      <c r="N14" s="53"/>
+      <c r="N14" s="168"/>
       <c r="O14" s="52"/>
       <c r="P14" s="36"/>
       <c r="Q14" s="53"/>
@@ -39887,25 +39902,27 @@
       </c>
       <c r="C15" s="58">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" s="58">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E15" s="58">
+      <c r="E15" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F15" s="52"/>
       <c r="G15" s="36"/>
-      <c r="H15" s="53"/>
+      <c r="H15" s="168"/>
       <c r="I15" s="52"/>
       <c r="J15" s="36"/>
       <c r="K15" s="53"/>
-      <c r="L15" s="52"/>
+      <c r="L15" s="52">
+        <v>1</v>
+      </c>
       <c r="M15" s="36"/>
-      <c r="N15" s="53"/>
+      <c r="N15" s="168"/>
       <c r="O15" s="52"/>
       <c r="P15" s="36"/>
       <c r="Q15" s="53"/>
@@ -40017,31 +40034,33 @@
         <v>15</v>
       </c>
       <c r="B16" s="149" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C16" s="58">
         <f t="shared" ref="C16:C37" si="4">SUM(F16,I16,L16,O16,R16,U16,X16,AA16,AD16,AG16,AJ16,AM16,AP16,AS16,AV16,AY16,BB16,BE16,BH16,BK16,BN16,BQ16,BT16,BW16,BZ16,CC16,CF16,CI16,CL16,CO16,CR16,CU16,CX16,DA16,DD16,DG16,DJ16,DM16)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="58">
         <f t="shared" ref="D16:D37" si="5">SUM(G16,J16,M16,P16,S16,V16,Y16,AB16,AE16,AH16,AK16,AN16,AQ16,AT16,AW16,AZ16,BC16,BF16,BI16,BL16,BO16,BR16,BU16,BX16,CA16,CD16,CG16,CJ16,CM16,CP16,CS16,CV16,CY16,DB16,DE16,DH16,DK16,DN16)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="58">
+      <c r="E16" s="51">
         <f t="shared" ref="E16:E37" si="6">SUM(H16,K16,N16,Q16,T16,W16,Z16,AC16,AF16,AI16,AL16,AO16,AR16,AU16,AX16,BA16,BD16,BG16,BJ16,BM16,BP16,BS16,BV16,BY16,CB16,CE16,CH16,CK16,CN16,CQ16,CT16,CW16,CZ16,DC16,DF16,DI16,DL16,DO16)</f>
         <v>0</v>
       </c>
       <c r="F16" s="52"/>
       <c r="G16" s="36"/>
-      <c r="H16" s="53"/>
+      <c r="H16" s="168"/>
       <c r="I16" s="52">
         <v>1</v>
       </c>
       <c r="J16" s="36"/>
       <c r="K16" s="53"/>
-      <c r="L16" s="52"/>
+      <c r="L16" s="52">
+        <v>1</v>
+      </c>
       <c r="M16" s="36"/>
-      <c r="N16" s="53"/>
+      <c r="N16" s="168"/>
       <c r="O16" s="52"/>
       <c r="P16" s="36"/>
       <c r="Q16" s="53"/>
@@ -40157,29 +40176,33 @@
       </c>
       <c r="C17" s="58">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" s="58">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="E17" s="58">
+      <c r="E17" s="51">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="52">
         <v>1</v>
       </c>
       <c r="G17" s="36"/>
-      <c r="H17" s="53"/>
+      <c r="H17" s="168"/>
       <c r="I17" s="52">
         <v>1</v>
       </c>
       <c r="J17" s="36"/>
       <c r="K17" s="53"/>
-      <c r="L17" s="52"/>
+      <c r="L17" s="52">
+        <v>1</v>
+      </c>
       <c r="M17" s="36"/>
-      <c r="N17" s="53"/>
+      <c r="N17" s="168">
+        <v>1</v>
+      </c>
       <c r="O17" s="52"/>
       <c r="P17" s="36"/>
       <c r="Q17" s="53"/>
@@ -40295,13 +40318,13 @@
       </c>
       <c r="C18" s="58">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="58">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="E18" s="58">
+      <c r="E18" s="51">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -40309,13 +40332,15 @@
         <v>1</v>
       </c>
       <c r="G18" s="36"/>
-      <c r="H18" s="53"/>
+      <c r="H18" s="168"/>
       <c r="I18" s="52"/>
       <c r="J18" s="36"/>
       <c r="K18" s="53"/>
-      <c r="L18" s="52"/>
+      <c r="L18" s="52">
+        <v>1</v>
+      </c>
       <c r="M18" s="36"/>
-      <c r="N18" s="53"/>
+      <c r="N18" s="168"/>
       <c r="O18" s="52"/>
       <c r="P18" s="36"/>
       <c r="Q18" s="53"/>
@@ -40437,19 +40462,19 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="E19" s="58">
+      <c r="E19" s="51">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F19" s="52"/>
       <c r="G19" s="36"/>
-      <c r="H19" s="53"/>
+      <c r="H19" s="168"/>
       <c r="I19" s="52"/>
       <c r="J19" s="36"/>
       <c r="K19" s="53"/>
       <c r="L19" s="52"/>
       <c r="M19" s="36"/>
-      <c r="N19" s="53"/>
+      <c r="N19" s="168"/>
       <c r="O19" s="52"/>
       <c r="P19" s="36"/>
       <c r="Q19" s="53"/>
@@ -40565,13 +40590,13 @@
       </c>
       <c r="C20" s="58">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" s="58">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="E20" s="58">
+      <c r="E20" s="51">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -40579,15 +40604,17 @@
         <v>1</v>
       </c>
       <c r="G20" s="36"/>
-      <c r="H20" s="53"/>
+      <c r="H20" s="168"/>
       <c r="I20" s="52">
         <v>1</v>
       </c>
       <c r="J20" s="36"/>
       <c r="K20" s="53"/>
-      <c r="L20" s="52"/>
+      <c r="L20" s="52">
+        <v>1</v>
+      </c>
       <c r="M20" s="36"/>
-      <c r="N20" s="53"/>
+      <c r="N20" s="168"/>
       <c r="O20" s="52"/>
       <c r="P20" s="36"/>
       <c r="Q20" s="53"/>
@@ -40703,13 +40730,13 @@
       </c>
       <c r="C21" s="58">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D21" s="58">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="E21" s="58">
+        <v>2</v>
+      </c>
+      <c r="E21" s="51">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -40719,15 +40746,19 @@
       <c r="G21" s="36">
         <v>1</v>
       </c>
-      <c r="H21" s="53"/>
+      <c r="H21" s="168"/>
       <c r="I21" s="52">
         <v>1</v>
       </c>
       <c r="J21" s="36"/>
       <c r="K21" s="53"/>
-      <c r="L21" s="52"/>
-      <c r="M21" s="36"/>
-      <c r="N21" s="53"/>
+      <c r="L21" s="52">
+        <v>1</v>
+      </c>
+      <c r="M21" s="36">
+        <v>1</v>
+      </c>
+      <c r="N21" s="168"/>
       <c r="O21" s="52"/>
       <c r="P21" s="36"/>
       <c r="Q21" s="53"/>
@@ -40849,19 +40880,19 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="E22" s="58">
+      <c r="E22" s="51">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F22" s="52"/>
       <c r="G22" s="36"/>
-      <c r="H22" s="53"/>
+      <c r="H22" s="168"/>
       <c r="I22" s="52"/>
       <c r="J22" s="36"/>
       <c r="K22" s="53"/>
       <c r="L22" s="52"/>
       <c r="M22" s="36"/>
-      <c r="N22" s="53"/>
+      <c r="N22" s="168"/>
       <c r="O22" s="52"/>
       <c r="P22" s="36"/>
       <c r="Q22" s="53"/>
@@ -40977,13 +41008,13 @@
       </c>
       <c r="C23" s="58">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D23" s="58">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="E23" s="58">
+      <c r="E23" s="51">
         <f t="shared" si="6"/>
         <v>2</v>
       </c>
@@ -40991,7 +41022,7 @@
         <v>1</v>
       </c>
       <c r="G23" s="36"/>
-      <c r="H23" s="53">
+      <c r="H23" s="168">
         <v>1</v>
       </c>
       <c r="I23" s="52">
@@ -41001,9 +41032,11 @@
       <c r="K23" s="53">
         <v>1</v>
       </c>
-      <c r="L23" s="52"/>
+      <c r="L23" s="52">
+        <v>1</v>
+      </c>
       <c r="M23" s="36"/>
-      <c r="N23" s="53"/>
+      <c r="N23" s="168"/>
       <c r="O23" s="52"/>
       <c r="P23" s="36"/>
       <c r="Q23" s="53"/>
@@ -41125,19 +41158,19 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="E24" s="58">
+      <c r="E24" s="51">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F24" s="52"/>
       <c r="G24" s="36"/>
-      <c r="H24" s="53"/>
+      <c r="H24" s="168"/>
       <c r="I24" s="52"/>
       <c r="J24" s="36"/>
       <c r="K24" s="53"/>
       <c r="L24" s="52"/>
       <c r="M24" s="36"/>
-      <c r="N24" s="53"/>
+      <c r="N24" s="168"/>
       <c r="O24" s="52"/>
       <c r="P24" s="36"/>
       <c r="Q24" s="53"/>
@@ -41253,13 +41286,13 @@
       </c>
       <c r="C25" s="58">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25" s="58">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="E25" s="58">
+      <c r="E25" s="51">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -41267,15 +41300,17 @@
         <v>1</v>
       </c>
       <c r="G25" s="36"/>
-      <c r="H25" s="53"/>
+      <c r="H25" s="168"/>
       <c r="I25" s="52">
         <v>1</v>
       </c>
       <c r="J25" s="36"/>
       <c r="K25" s="53"/>
-      <c r="L25" s="52"/>
+      <c r="L25" s="52">
+        <v>1</v>
+      </c>
       <c r="M25" s="36"/>
-      <c r="N25" s="53"/>
+      <c r="N25" s="168"/>
       <c r="O25" s="52"/>
       <c r="P25" s="36"/>
       <c r="Q25" s="53"/>
@@ -41397,13 +41432,13 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="E26" s="58">
+      <c r="E26" s="51">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F26" s="52"/>
       <c r="G26" s="36"/>
-      <c r="H26" s="53"/>
+      <c r="H26" s="168"/>
       <c r="I26" s="52">
         <v>1</v>
       </c>
@@ -41411,7 +41446,7 @@
       <c r="K26" s="53"/>
       <c r="L26" s="52"/>
       <c r="M26" s="36"/>
-      <c r="N26" s="53"/>
+      <c r="N26" s="168"/>
       <c r="O26" s="52"/>
       <c r="P26" s="36"/>
       <c r="Q26" s="53"/>
@@ -41533,19 +41568,19 @@
         <f>SUM(G27,J27,M27,P27,S27,V27,Y27,AB27,AE27,AH27,AK27,AN27,AQ27,AT27,AW27,AZ27,BC27,BF27,BI27,BL27,BO27,BR27,BU27,BX27,CA27,CD27,CG27,CJ27,CM27,CP27,CS27,CV27,CY27,DB27,DE27,DH27,DK27,DN27)</f>
         <v>0</v>
       </c>
-      <c r="E27" s="58">
+      <c r="E27" s="51">
         <f>SUM(H27,K27,N27,Q27,T27,W27,Z27,AC27,AF27,AI27,AL27,AO27,AR27,AU27,AX27,BA27,BD27,BG27,BJ27,BM27,BP27,BS27,BV27,BY27,CB27,CE27,CH27,CK27,CN27,CQ27,CT27,CW27,CZ27,DC27,DF27,DI27,DL27,DO27)</f>
         <v>0</v>
       </c>
       <c r="F27" s="52"/>
       <c r="G27" s="36"/>
-      <c r="H27" s="53"/>
+      <c r="H27" s="168"/>
       <c r="I27" s="52"/>
       <c r="J27" s="36"/>
       <c r="K27" s="53"/>
       <c r="L27" s="52"/>
       <c r="M27" s="36"/>
-      <c r="N27" s="53"/>
+      <c r="N27" s="168"/>
       <c r="O27" s="52"/>
       <c r="P27" s="36"/>
       <c r="Q27" s="53"/>
@@ -41661,29 +41696,33 @@
       </c>
       <c r="C28" s="58">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D28" s="58">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="E28" s="58">
+      <c r="E28" s="51">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" s="52">
         <v>1</v>
       </c>
       <c r="G28" s="36"/>
-      <c r="H28" s="53"/>
+      <c r="H28" s="168"/>
       <c r="I28" s="52">
         <v>1</v>
       </c>
       <c r="J28" s="36"/>
       <c r="K28" s="53"/>
-      <c r="L28" s="52"/>
+      <c r="L28" s="52">
+        <v>1</v>
+      </c>
       <c r="M28" s="36"/>
-      <c r="N28" s="53"/>
+      <c r="N28" s="168">
+        <v>1</v>
+      </c>
       <c r="O28" s="52"/>
       <c r="P28" s="36"/>
       <c r="Q28" s="53"/>
@@ -41805,19 +41844,19 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="E29" s="58">
+      <c r="E29" s="51">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F29" s="52"/>
       <c r="G29" s="36"/>
-      <c r="H29" s="53"/>
+      <c r="H29" s="168"/>
       <c r="I29" s="52"/>
       <c r="J29" s="36"/>
       <c r="K29" s="53"/>
       <c r="L29" s="52"/>
       <c r="M29" s="36"/>
-      <c r="N29" s="53"/>
+      <c r="N29" s="168"/>
       <c r="O29" s="52"/>
       <c r="P29" s="36"/>
       <c r="Q29" s="53"/>
@@ -41939,19 +41978,19 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="E30" s="58">
+      <c r="E30" s="51">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="F30" s="52"/>
       <c r="G30" s="36"/>
-      <c r="H30" s="53"/>
+      <c r="H30" s="168"/>
       <c r="I30" s="52"/>
       <c r="J30" s="36"/>
       <c r="K30" s="53"/>
       <c r="L30" s="52"/>
       <c r="M30" s="36"/>
-      <c r="N30" s="53"/>
+      <c r="N30" s="168"/>
       <c r="O30" s="52"/>
       <c r="P30" s="36"/>
       <c r="Q30" s="53"/>
@@ -42073,19 +42112,19 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="E31" s="58">
+      <c r="E31" s="51">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F31" s="52"/>
       <c r="G31" s="36"/>
-      <c r="H31" s="53"/>
+      <c r="H31" s="168"/>
       <c r="I31" s="52"/>
       <c r="J31" s="36"/>
       <c r="K31" s="53"/>
       <c r="L31" s="52"/>
       <c r="M31" s="36"/>
-      <c r="N31" s="53"/>
+      <c r="N31" s="168"/>
       <c r="O31" s="52"/>
       <c r="P31" s="36"/>
       <c r="Q31" s="53"/>
@@ -42201,13 +42240,13 @@
       </c>
       <c r="C32" s="58">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D32" s="58">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="E32" s="58">
+      <c r="E32" s="51">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -42215,15 +42254,17 @@
         <v>1</v>
       </c>
       <c r="G32" s="36"/>
-      <c r="H32" s="53"/>
+      <c r="H32" s="168"/>
       <c r="I32" s="52">
         <v>1</v>
       </c>
       <c r="J32" s="36"/>
       <c r="K32" s="53"/>
-      <c r="L32" s="52"/>
+      <c r="L32" s="52">
+        <v>1</v>
+      </c>
       <c r="M32" s="36"/>
-      <c r="N32" s="53"/>
+      <c r="N32" s="168"/>
       <c r="O32" s="52"/>
       <c r="P32" s="36"/>
       <c r="Q32" s="53"/>
@@ -42345,19 +42386,19 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="E33" s="58">
+      <c r="E33" s="51">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F33" s="52"/>
       <c r="G33" s="36"/>
-      <c r="H33" s="53"/>
+      <c r="H33" s="168"/>
       <c r="I33" s="52"/>
       <c r="J33" s="36"/>
       <c r="K33" s="53"/>
       <c r="L33" s="52"/>
       <c r="M33" s="36"/>
-      <c r="N33" s="53"/>
+      <c r="N33" s="168"/>
       <c r="O33" s="52"/>
       <c r="P33" s="36"/>
       <c r="Q33" s="53"/>
@@ -42464,7 +42505,7 @@
       <c r="DN33" s="36"/>
       <c r="DO33" s="53"/>
     </row>
-    <row r="34" spans="1:119" s="54" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:119" s="54" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="28">
         <v>55</v>
       </c>
@@ -42479,124 +42520,124 @@
         <f>SUM(G34,J34,M34,P34,S34,V34,Y34,AB34,AE34,AH34,AK34,AN34,AQ34,AT34,AW34,AZ34,BC34,BF34,BI34,BL34,BO34,BR34,BU34,BX34,CA34,CD34,CG34,CJ34,CM34,CP34,CS34,CV34,CY34,DB34,DE34,DH34,DK34,DN34)</f>
         <v>0</v>
       </c>
-      <c r="E34" s="58">
+      <c r="E34" s="51">
         <f>SUM(H34,K34,N34,Q34,T34,W34,Z34,AC34,AF34,AI34,AL34,AO34,AR34,AU34,AX34,BA34,BD34,BG34,BJ34,BM34,BP34,BS34,BV34,BY34,CB34,CE34,CH34,CK34,CN34,CQ34,CT34,CW34,CZ34,DC34,DF34,DI34,DL34,DO34)</f>
         <v>0</v>
       </c>
-      <c r="F34" s="146"/>
-      <c r="G34" s="163"/>
-      <c r="H34" s="147"/>
-      <c r="I34" s="146"/>
-      <c r="J34" s="163"/>
-      <c r="K34" s="147"/>
-      <c r="L34" s="146"/>
-      <c r="M34" s="163"/>
-      <c r="N34" s="147"/>
-      <c r="O34" s="146"/>
-      <c r="P34" s="163"/>
-      <c r="Q34" s="147"/>
-      <c r="R34" s="146"/>
-      <c r="S34" s="163"/>
-      <c r="T34" s="147"/>
-      <c r="U34" s="146"/>
-      <c r="V34" s="163"/>
-      <c r="W34" s="147"/>
-      <c r="X34" s="146"/>
-      <c r="Y34" s="163"/>
-      <c r="Z34" s="147"/>
-      <c r="AA34" s="146"/>
-      <c r="AB34" s="163"/>
-      <c r="AC34" s="147"/>
-      <c r="AD34" s="146"/>
-      <c r="AE34" s="163"/>
-      <c r="AF34" s="147"/>
-      <c r="AG34" s="146"/>
-      <c r="AH34" s="163"/>
-      <c r="AI34" s="147"/>
-      <c r="AJ34" s="146"/>
-      <c r="AK34" s="163"/>
-      <c r="AL34" s="147"/>
-      <c r="AM34" s="146"/>
-      <c r="AN34" s="163"/>
-      <c r="AO34" s="147"/>
-      <c r="AP34" s="146"/>
-      <c r="AQ34" s="163"/>
-      <c r="AR34" s="147"/>
-      <c r="AS34" s="146"/>
-      <c r="AT34" s="163"/>
-      <c r="AU34" s="147"/>
-      <c r="AV34" s="146"/>
-      <c r="AW34" s="163"/>
-      <c r="AX34" s="147"/>
-      <c r="AY34" s="146"/>
-      <c r="AZ34" s="163"/>
-      <c r="BA34" s="147"/>
-      <c r="BB34" s="146"/>
-      <c r="BC34" s="163"/>
-      <c r="BD34" s="147"/>
-      <c r="BE34" s="146"/>
-      <c r="BF34" s="163"/>
-      <c r="BG34" s="147"/>
-      <c r="BH34" s="146"/>
-      <c r="BI34" s="163"/>
-      <c r="BJ34" s="147"/>
-      <c r="BK34" s="146"/>
-      <c r="BL34" s="163"/>
-      <c r="BM34" s="147"/>
-      <c r="BN34" s="146"/>
-      <c r="BO34" s="163"/>
-      <c r="BP34" s="147"/>
-      <c r="BQ34" s="146"/>
-      <c r="BR34" s="163"/>
-      <c r="BS34" s="147"/>
-      <c r="BT34" s="146"/>
-      <c r="BU34" s="163"/>
-      <c r="BV34" s="147"/>
-      <c r="BW34" s="146"/>
-      <c r="BX34" s="163"/>
-      <c r="BY34" s="147"/>
-      <c r="BZ34" s="146"/>
-      <c r="CA34" s="163"/>
-      <c r="CB34" s="147"/>
-      <c r="CC34" s="146"/>
-      <c r="CD34" s="163"/>
-      <c r="CE34" s="147"/>
-      <c r="CF34" s="146"/>
-      <c r="CG34" s="163"/>
-      <c r="CH34" s="147"/>
-      <c r="CI34" s="146"/>
-      <c r="CJ34" s="163"/>
-      <c r="CK34" s="147"/>
-      <c r="CL34" s="146"/>
-      <c r="CM34" s="163"/>
-      <c r="CN34" s="147"/>
-      <c r="CO34" s="146"/>
-      <c r="CP34" s="163"/>
-      <c r="CQ34" s="147"/>
-      <c r="CR34" s="146"/>
-      <c r="CS34" s="163"/>
-      <c r="CT34" s="147"/>
-      <c r="CU34" s="146"/>
-      <c r="CV34" s="163"/>
-      <c r="CW34" s="147"/>
-      <c r="CX34" s="146"/>
-      <c r="CY34" s="163"/>
-      <c r="CZ34" s="147"/>
-      <c r="DA34" s="146"/>
-      <c r="DB34" s="163"/>
-      <c r="DC34" s="147"/>
-      <c r="DD34" s="146"/>
-      <c r="DE34" s="163"/>
-      <c r="DF34" s="147"/>
-      <c r="DG34" s="146"/>
-      <c r="DH34" s="163"/>
-      <c r="DI34" s="147"/>
-      <c r="DJ34" s="146"/>
-      <c r="DK34" s="163"/>
-      <c r="DL34" s="147"/>
-      <c r="DM34" s="146"/>
-      <c r="DN34" s="163"/>
-      <c r="DO34" s="147"/>
+      <c r="F34" s="52"/>
+      <c r="G34" s="36"/>
+      <c r="H34" s="168"/>
+      <c r="I34" s="52"/>
+      <c r="J34" s="36"/>
+      <c r="K34" s="53"/>
+      <c r="L34" s="52"/>
+      <c r="M34" s="36"/>
+      <c r="N34" s="168"/>
+      <c r="O34" s="52"/>
+      <c r="P34" s="36"/>
+      <c r="Q34" s="53"/>
+      <c r="R34" s="52"/>
+      <c r="S34" s="36"/>
+      <c r="T34" s="53"/>
+      <c r="U34" s="52"/>
+      <c r="V34" s="36"/>
+      <c r="W34" s="53"/>
+      <c r="X34" s="52"/>
+      <c r="Y34" s="36"/>
+      <c r="Z34" s="53"/>
+      <c r="AA34" s="52"/>
+      <c r="AB34" s="36"/>
+      <c r="AC34" s="53"/>
+      <c r="AD34" s="52"/>
+      <c r="AE34" s="36"/>
+      <c r="AF34" s="53"/>
+      <c r="AG34" s="52"/>
+      <c r="AH34" s="36"/>
+      <c r="AI34" s="53"/>
+      <c r="AJ34" s="52"/>
+      <c r="AK34" s="36"/>
+      <c r="AL34" s="53"/>
+      <c r="AM34" s="52"/>
+      <c r="AN34" s="36"/>
+      <c r="AO34" s="53"/>
+      <c r="AP34" s="52"/>
+      <c r="AQ34" s="36"/>
+      <c r="AR34" s="53"/>
+      <c r="AS34" s="52"/>
+      <c r="AT34" s="36"/>
+      <c r="AU34" s="53"/>
+      <c r="AV34" s="52"/>
+      <c r="AW34" s="36"/>
+      <c r="AX34" s="53"/>
+      <c r="AY34" s="52"/>
+      <c r="AZ34" s="36"/>
+      <c r="BA34" s="53"/>
+      <c r="BB34" s="52"/>
+      <c r="BC34" s="36"/>
+      <c r="BD34" s="53"/>
+      <c r="BE34" s="52"/>
+      <c r="BF34" s="36"/>
+      <c r="BG34" s="53"/>
+      <c r="BH34" s="52"/>
+      <c r="BI34" s="36"/>
+      <c r="BJ34" s="53"/>
+      <c r="BK34" s="52"/>
+      <c r="BL34" s="36"/>
+      <c r="BM34" s="53"/>
+      <c r="BN34" s="52"/>
+      <c r="BO34" s="36"/>
+      <c r="BP34" s="53"/>
+      <c r="BQ34" s="52"/>
+      <c r="BR34" s="36"/>
+      <c r="BS34" s="53"/>
+      <c r="BT34" s="52"/>
+      <c r="BU34" s="36"/>
+      <c r="BV34" s="53"/>
+      <c r="BW34" s="52"/>
+      <c r="BX34" s="36"/>
+      <c r="BY34" s="53"/>
+      <c r="BZ34" s="52"/>
+      <c r="CA34" s="36"/>
+      <c r="CB34" s="53"/>
+      <c r="CC34" s="52"/>
+      <c r="CD34" s="36"/>
+      <c r="CE34" s="53"/>
+      <c r="CF34" s="52"/>
+      <c r="CG34" s="36"/>
+      <c r="CH34" s="53"/>
+      <c r="CI34" s="52"/>
+      <c r="CJ34" s="36"/>
+      <c r="CK34" s="53"/>
+      <c r="CL34" s="52"/>
+      <c r="CM34" s="36"/>
+      <c r="CN34" s="53"/>
+      <c r="CO34" s="52"/>
+      <c r="CP34" s="36"/>
+      <c r="CQ34" s="53"/>
+      <c r="CR34" s="52"/>
+      <c r="CS34" s="36"/>
+      <c r="CT34" s="53"/>
+      <c r="CU34" s="52"/>
+      <c r="CV34" s="36"/>
+      <c r="CW34" s="53"/>
+      <c r="CX34" s="52"/>
+      <c r="CY34" s="36"/>
+      <c r="CZ34" s="53"/>
+      <c r="DA34" s="52"/>
+      <c r="DB34" s="36"/>
+      <c r="DC34" s="53"/>
+      <c r="DD34" s="52"/>
+      <c r="DE34" s="36"/>
+      <c r="DF34" s="53"/>
+      <c r="DG34" s="52"/>
+      <c r="DH34" s="36"/>
+      <c r="DI34" s="53"/>
+      <c r="DJ34" s="52"/>
+      <c r="DK34" s="36"/>
+      <c r="DL34" s="53"/>
+      <c r="DM34" s="52"/>
+      <c r="DN34" s="36"/>
+      <c r="DO34" s="53"/>
     </row>
     <row r="35" spans="1:119" s="54" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="27">
@@ -42613,19 +42654,19 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="E35" s="58">
+      <c r="E35" s="51">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F35" s="52"/>
       <c r="G35" s="36"/>
-      <c r="H35" s="53"/>
+      <c r="H35" s="168"/>
       <c r="I35" s="52"/>
       <c r="J35" s="36"/>
       <c r="K35" s="53"/>
       <c r="L35" s="52"/>
       <c r="M35" s="36"/>
-      <c r="N35" s="53"/>
+      <c r="N35" s="168"/>
       <c r="O35" s="52"/>
       <c r="P35" s="36"/>
       <c r="Q35" s="53"/>
@@ -42747,19 +42788,19 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="E36" s="58">
+      <c r="E36" s="51">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F36" s="52"/>
       <c r="G36" s="36"/>
-      <c r="H36" s="53"/>
+      <c r="H36" s="168"/>
       <c r="I36" s="52"/>
       <c r="J36" s="36"/>
       <c r="K36" s="53"/>
       <c r="L36" s="52"/>
       <c r="M36" s="36"/>
-      <c r="N36" s="53"/>
+      <c r="N36" s="168"/>
       <c r="O36" s="52"/>
       <c r="P36" s="36"/>
       <c r="Q36" s="53"/>
@@ -42866,7 +42907,7 @@
       <c r="DN36" s="36"/>
       <c r="DO36" s="53"/>
     </row>
-    <row r="37" spans="1:119" s="54" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:119" s="54" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="28">
         <v>89</v>
       </c>
@@ -42881,124 +42922,124 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="E37" s="58">
+      <c r="E37" s="51">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F37" s="52"/>
-      <c r="G37" s="36"/>
-      <c r="H37" s="53"/>
-      <c r="I37" s="52"/>
-      <c r="J37" s="36"/>
-      <c r="K37" s="53"/>
-      <c r="L37" s="52"/>
-      <c r="M37" s="36"/>
-      <c r="N37" s="53"/>
-      <c r="O37" s="52"/>
-      <c r="P37" s="36"/>
-      <c r="Q37" s="53"/>
-      <c r="R37" s="52"/>
-      <c r="S37" s="36"/>
-      <c r="T37" s="53"/>
-      <c r="U37" s="52"/>
-      <c r="V37" s="36"/>
-      <c r="W37" s="53"/>
-      <c r="X37" s="52"/>
-      <c r="Y37" s="36"/>
-      <c r="Z37" s="53"/>
-      <c r="AA37" s="52"/>
-      <c r="AB37" s="36"/>
-      <c r="AC37" s="53"/>
-      <c r="AD37" s="52"/>
-      <c r="AE37" s="36"/>
-      <c r="AF37" s="53"/>
-      <c r="AG37" s="52"/>
-      <c r="AH37" s="36"/>
-      <c r="AI37" s="53"/>
-      <c r="AJ37" s="52"/>
-      <c r="AK37" s="36"/>
-      <c r="AL37" s="53"/>
-      <c r="AM37" s="52"/>
-      <c r="AN37" s="36"/>
-      <c r="AO37" s="53"/>
-      <c r="AP37" s="52"/>
-      <c r="AQ37" s="36"/>
-      <c r="AR37" s="53"/>
-      <c r="AS37" s="52"/>
-      <c r="AT37" s="36"/>
-      <c r="AU37" s="53"/>
-      <c r="AV37" s="52"/>
-      <c r="AW37" s="36"/>
-      <c r="AX37" s="53"/>
-      <c r="AY37" s="52"/>
-      <c r="AZ37" s="36"/>
-      <c r="BA37" s="53"/>
-      <c r="BB37" s="52"/>
-      <c r="BC37" s="36"/>
-      <c r="BD37" s="53"/>
-      <c r="BE37" s="52"/>
-      <c r="BF37" s="36"/>
-      <c r="BG37" s="53"/>
-      <c r="BH37" s="52"/>
-      <c r="BI37" s="36"/>
-      <c r="BJ37" s="53"/>
-      <c r="BK37" s="52"/>
-      <c r="BL37" s="36"/>
-      <c r="BM37" s="53"/>
-      <c r="BN37" s="52"/>
-      <c r="BO37" s="36"/>
-      <c r="BP37" s="53"/>
-      <c r="BQ37" s="52"/>
-      <c r="BR37" s="36"/>
-      <c r="BS37" s="53"/>
-      <c r="BT37" s="52"/>
-      <c r="BU37" s="36"/>
-      <c r="BV37" s="53"/>
-      <c r="BW37" s="52"/>
-      <c r="BX37" s="36"/>
-      <c r="BY37" s="53"/>
-      <c r="BZ37" s="52"/>
-      <c r="CA37" s="36"/>
-      <c r="CB37" s="53"/>
-      <c r="CC37" s="52"/>
-      <c r="CD37" s="36"/>
-      <c r="CE37" s="53"/>
-      <c r="CF37" s="52"/>
-      <c r="CG37" s="36"/>
-      <c r="CH37" s="53"/>
-      <c r="CI37" s="52"/>
-      <c r="CJ37" s="36"/>
-      <c r="CK37" s="53"/>
-      <c r="CL37" s="52"/>
-      <c r="CM37" s="36"/>
-      <c r="CN37" s="53"/>
-      <c r="CO37" s="52"/>
-      <c r="CP37" s="36"/>
-      <c r="CQ37" s="53"/>
-      <c r="CR37" s="52"/>
-      <c r="CS37" s="36"/>
-      <c r="CT37" s="53"/>
-      <c r="CU37" s="52"/>
-      <c r="CV37" s="36"/>
-      <c r="CW37" s="53"/>
-      <c r="CX37" s="52"/>
-      <c r="CY37" s="36"/>
-      <c r="CZ37" s="53"/>
-      <c r="DA37" s="52"/>
-      <c r="DB37" s="36"/>
-      <c r="DC37" s="53"/>
-      <c r="DD37" s="52"/>
-      <c r="DE37" s="36"/>
-      <c r="DF37" s="53"/>
-      <c r="DG37" s="52"/>
-      <c r="DH37" s="36"/>
-      <c r="DI37" s="53"/>
-      <c r="DJ37" s="52"/>
-      <c r="DK37" s="36"/>
-      <c r="DL37" s="53"/>
-      <c r="DM37" s="52"/>
-      <c r="DN37" s="36"/>
-      <c r="DO37" s="53"/>
+      <c r="F37" s="146"/>
+      <c r="G37" s="163"/>
+      <c r="H37" s="329"/>
+      <c r="I37" s="146"/>
+      <c r="J37" s="163"/>
+      <c r="K37" s="147"/>
+      <c r="L37" s="146"/>
+      <c r="M37" s="163"/>
+      <c r="N37" s="329"/>
+      <c r="O37" s="146"/>
+      <c r="P37" s="163"/>
+      <c r="Q37" s="147"/>
+      <c r="R37" s="146"/>
+      <c r="S37" s="163"/>
+      <c r="T37" s="147"/>
+      <c r="U37" s="146"/>
+      <c r="V37" s="163"/>
+      <c r="W37" s="147"/>
+      <c r="X37" s="146"/>
+      <c r="Y37" s="163"/>
+      <c r="Z37" s="147"/>
+      <c r="AA37" s="146"/>
+      <c r="AB37" s="163"/>
+      <c r="AC37" s="147"/>
+      <c r="AD37" s="146"/>
+      <c r="AE37" s="163"/>
+      <c r="AF37" s="147"/>
+      <c r="AG37" s="146"/>
+      <c r="AH37" s="163"/>
+      <c r="AI37" s="147"/>
+      <c r="AJ37" s="146"/>
+      <c r="AK37" s="163"/>
+      <c r="AL37" s="147"/>
+      <c r="AM37" s="146"/>
+      <c r="AN37" s="163"/>
+      <c r="AO37" s="147"/>
+      <c r="AP37" s="146"/>
+      <c r="AQ37" s="163"/>
+      <c r="AR37" s="147"/>
+      <c r="AS37" s="146"/>
+      <c r="AT37" s="163"/>
+      <c r="AU37" s="147"/>
+      <c r="AV37" s="146"/>
+      <c r="AW37" s="163"/>
+      <c r="AX37" s="147"/>
+      <c r="AY37" s="146"/>
+      <c r="AZ37" s="163"/>
+      <c r="BA37" s="147"/>
+      <c r="BB37" s="146"/>
+      <c r="BC37" s="163"/>
+      <c r="BD37" s="147"/>
+      <c r="BE37" s="146"/>
+      <c r="BF37" s="163"/>
+      <c r="BG37" s="147"/>
+      <c r="BH37" s="146"/>
+      <c r="BI37" s="163"/>
+      <c r="BJ37" s="147"/>
+      <c r="BK37" s="146"/>
+      <c r="BL37" s="163"/>
+      <c r="BM37" s="147"/>
+      <c r="BN37" s="146"/>
+      <c r="BO37" s="163"/>
+      <c r="BP37" s="147"/>
+      <c r="BQ37" s="146"/>
+      <c r="BR37" s="163"/>
+      <c r="BS37" s="147"/>
+      <c r="BT37" s="146"/>
+      <c r="BU37" s="163"/>
+      <c r="BV37" s="147"/>
+      <c r="BW37" s="146"/>
+      <c r="BX37" s="163"/>
+      <c r="BY37" s="147"/>
+      <c r="BZ37" s="146"/>
+      <c r="CA37" s="163"/>
+      <c r="CB37" s="147"/>
+      <c r="CC37" s="146"/>
+      <c r="CD37" s="163"/>
+      <c r="CE37" s="147"/>
+      <c r="CF37" s="146"/>
+      <c r="CG37" s="163"/>
+      <c r="CH37" s="147"/>
+      <c r="CI37" s="146"/>
+      <c r="CJ37" s="163"/>
+      <c r="CK37" s="147"/>
+      <c r="CL37" s="146"/>
+      <c r="CM37" s="163"/>
+      <c r="CN37" s="147"/>
+      <c r="CO37" s="146"/>
+      <c r="CP37" s="163"/>
+      <c r="CQ37" s="147"/>
+      <c r="CR37" s="146"/>
+      <c r="CS37" s="163"/>
+      <c r="CT37" s="147"/>
+      <c r="CU37" s="146"/>
+      <c r="CV37" s="163"/>
+      <c r="CW37" s="147"/>
+      <c r="CX37" s="146"/>
+      <c r="CY37" s="163"/>
+      <c r="CZ37" s="147"/>
+      <c r="DA37" s="146"/>
+      <c r="DB37" s="163"/>
+      <c r="DC37" s="147"/>
+      <c r="DD37" s="146"/>
+      <c r="DE37" s="163"/>
+      <c r="DF37" s="147"/>
+      <c r="DG37" s="146"/>
+      <c r="DH37" s="163"/>
+      <c r="DI37" s="147"/>
+      <c r="DJ37" s="146"/>
+      <c r="DK37" s="163"/>
+      <c r="DL37" s="147"/>
+      <c r="DM37" s="146"/>
+      <c r="DN37" s="163"/>
+      <c r="DO37" s="147"/>
     </row>
     <row r="38" spans="1:119" s="54" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38"/>
@@ -43007,464 +43048,527 @@
       <c r="D38"/>
       <c r="E38"/>
       <c r="F38" s="73">
-        <f>SUM(F4:F37)</f>
+        <f t="shared" ref="F38:AK38" si="8">SUM(F4:F37)</f>
         <v>16</v>
       </c>
       <c r="G38" s="73">
-        <f>SUM(G4:G37)</f>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
       <c r="H38" s="73">
-        <f>SUM(H4:H37)</f>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="I38" s="73">
-        <f>SUM(I4:I37)</f>
+        <f t="shared" si="8"/>
         <v>16</v>
       </c>
       <c r="J38" s="73">
-        <f>SUM(J4:J37)</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="K38" s="73">
-        <f>SUM(K4:K37)</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="L38" s="73">
-        <f>SUM(L4:L37)</f>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>16</v>
       </c>
       <c r="M38" s="73">
-        <f>SUM(M4:M37)</f>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>2</v>
       </c>
       <c r="N38" s="73">
-        <f>SUM(N4:N37)</f>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>2</v>
       </c>
       <c r="O38" s="73">
-        <f>SUM(O4:O37)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="P38" s="73">
-        <f>SUM(P4:P37)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q38" s="73">
-        <f>SUM(Q4:Q37)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R38" s="73">
-        <f>SUM(R4:R37)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="S38" s="73">
-        <f>SUM(S4:S37)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="T38" s="73">
-        <f>SUM(T4:T37)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U38" s="73">
-        <f>SUM(U4:U37)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V38" s="73">
-        <f>SUM(V4:V37)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="W38" s="73">
-        <f>SUM(W4:W37)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="X38" s="73">
-        <f>SUM(X4:X37)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Y38" s="73">
-        <f>SUM(Y4:Y37)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Z38" s="73">
-        <f>SUM(Z4:Z37)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AA38" s="73">
-        <f>SUM(AA4:AA37)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AB38" s="73">
-        <f>SUM(AB4:AB37)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AC38" s="73">
-        <f>SUM(AC4:AC37)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AD38" s="73">
-        <f>SUM(AD4:AD37)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE38" s="73">
-        <f>SUM(AE4:AE37)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AF38" s="73">
-        <f>SUM(AF4:AF37)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AG38" s="73">
-        <f>SUM(AG4:AG37)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AH38" s="73">
-        <f>SUM(AH4:AH37)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AI38" s="73">
-        <f>SUM(AI4:AI37)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AJ38" s="73">
-        <f>SUM(AJ4:AJ37)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AK38" s="73">
-        <f>SUM(AK4:AK37)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AL38" s="73">
-        <f>SUM(AL4:AL37)</f>
+        <f t="shared" ref="AL38:BQ38" si="9">SUM(AL4:AL37)</f>
         <v>0</v>
       </c>
       <c r="AM38" s="73">
-        <f>SUM(AM4:AM37)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AN38" s="73">
-        <f>SUM(AN4:AN37)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AO38" s="73">
-        <f>SUM(AO4:AO37)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AP38" s="73">
-        <f>SUM(AP4:AP37)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AQ38" s="73">
-        <f>SUM(AQ4:AQ37)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AR38" s="73">
-        <f>SUM(AR4:AR37)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AS38" s="73">
-        <f>SUM(AS4:AS37)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AT38" s="73">
-        <f>SUM(AT4:AT37)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AU38" s="73">
-        <f>SUM(AU4:AU37)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AV38" s="73">
-        <f>SUM(AV4:AV37)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AW38" s="73">
-        <f>SUM(AW4:AW37)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AX38" s="73">
-        <f>SUM(AX4:AX37)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AY38" s="73">
-        <f>SUM(AY4:AY37)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AZ38" s="73">
-        <f>SUM(AZ4:AZ37)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BA38" s="73">
-        <f>SUM(BA4:BA37)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BB38" s="73">
-        <f>SUM(BB4:BB37)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BC38" s="73">
-        <f>SUM(BC4:BC37)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BD38" s="73">
-        <f>SUM(BD4:BD37)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BE38" s="73">
-        <f>SUM(BE4:BE37)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BF38" s="73">
-        <f>SUM(BF4:BF37)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BG38" s="73">
-        <f>SUM(BG4:BG37)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BH38" s="73">
-        <f>SUM(BH4:BH37)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BI38" s="73">
-        <f>SUM(BI4:BI37)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BJ38" s="73">
-        <f>SUM(BJ4:BJ37)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BK38" s="73">
-        <f>SUM(BK4:BK37)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BL38" s="73">
-        <f>SUM(BL4:BL37)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BM38" s="73">
-        <f>SUM(BM4:BM37)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BN38" s="73">
-        <f>SUM(BN4:BN37)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BO38" s="73">
-        <f>SUM(BO4:BO37)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BP38" s="73">
-        <f>SUM(BP4:BP37)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BQ38" s="73">
-        <f>SUM(BQ4:BQ37)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="BR38" s="73">
-        <f>SUM(BR4:BR37)</f>
+        <f t="shared" ref="BR38:CW38" si="10">SUM(BR4:BR37)</f>
         <v>0</v>
       </c>
       <c r="BS38" s="73">
-        <f>SUM(BS4:BS37)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BT38" s="73">
-        <f>SUM(BT4:BT37)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BU38" s="73">
-        <f>SUM(BU4:BU37)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BV38" s="73">
-        <f>SUM(BV4:BV37)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BW38" s="73">
-        <f>SUM(BW4:BW37)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BX38" s="73">
-        <f>SUM(BX4:BX37)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BY38" s="73">
-        <f>SUM(BY4:BY37)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="BZ38" s="73">
-        <f>SUM(BZ4:BZ37)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="CA38" s="73">
-        <f>SUM(CA4:CA37)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="CB38" s="73">
-        <f>SUM(CB4:CB37)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="CC38" s="73">
-        <f>SUM(CC4:CC37)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="CD38" s="73">
-        <f>SUM(CD4:CD37)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="CE38" s="73">
-        <f>SUM(CE4:CE37)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="CF38" s="73">
-        <f>SUM(CF4:CF37)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="CG38" s="73">
-        <f>SUM(CG4:CG37)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="CH38" s="73">
-        <f>SUM(CH4:CH37)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="CI38" s="73">
-        <f>SUM(CI4:CI37)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="CJ38" s="73">
-        <f>SUM(CJ4:CJ37)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="CK38" s="73">
-        <f>SUM(CK4:CK37)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="CL38" s="73">
-        <f>SUM(CL4:CL37)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="CM38" s="73">
-        <f>SUM(CM4:CM37)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="CN38" s="73">
-        <f>SUM(CN4:CN37)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="CO38" s="73">
-        <f>SUM(CO4:CO37)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="CP38" s="73">
-        <f>SUM(CP4:CP37)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="CQ38" s="73">
-        <f>SUM(CQ4:CQ37)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="CR38" s="73">
-        <f>SUM(CR4:CR37)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="CS38" s="73">
-        <f>SUM(CS4:CS37)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="CT38" s="73">
-        <f>SUM(CT4:CT37)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="CU38" s="73">
-        <f>SUM(CU4:CU37)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="CV38" s="73">
-        <f>SUM(CV4:CV37)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="CW38" s="73">
-        <f>SUM(CW4:CW37)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="CX38" s="73">
-        <f t="shared" ref="CX38:DO38" si="8">SUM(CX4:CX37)</f>
+        <f t="shared" ref="CX38:DO38" si="11">SUM(CX4:CX37)</f>
         <v>0</v>
       </c>
       <c r="CY38" s="73">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="CZ38" s="73">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="DA38" s="73">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="DB38" s="73">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="DC38" s="73">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="DD38" s="73">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="DE38" s="73">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="DF38" s="73">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="DG38" s="73">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="DH38" s="73">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="DI38" s="73">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="DJ38" s="73">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="DK38" s="73">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="DL38" s="73">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="DM38" s="73">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="DN38" s="73">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="DO38" s="73">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="79">
+    <mergeCell ref="DM1:DO1"/>
+    <mergeCell ref="DM2:DO2"/>
+    <mergeCell ref="DA1:DC1"/>
+    <mergeCell ref="DA2:DC2"/>
+    <mergeCell ref="DD1:DF1"/>
+    <mergeCell ref="DD2:DF2"/>
+    <mergeCell ref="DG1:DI1"/>
+    <mergeCell ref="DG2:DI2"/>
+    <mergeCell ref="CU1:CW1"/>
+    <mergeCell ref="CU2:CW2"/>
+    <mergeCell ref="CX1:CZ1"/>
+    <mergeCell ref="CX2:CZ2"/>
+    <mergeCell ref="DJ1:DL1"/>
+    <mergeCell ref="DJ2:DL2"/>
+    <mergeCell ref="CL1:CN1"/>
+    <mergeCell ref="CL2:CN2"/>
+    <mergeCell ref="CO1:CQ1"/>
+    <mergeCell ref="CO2:CQ2"/>
+    <mergeCell ref="CR1:CT1"/>
+    <mergeCell ref="CR2:CT2"/>
+    <mergeCell ref="CC1:CE1"/>
+    <mergeCell ref="CC2:CE2"/>
+    <mergeCell ref="CF1:CH1"/>
+    <mergeCell ref="CF2:CH2"/>
+    <mergeCell ref="CI1:CK1"/>
+    <mergeCell ref="CI2:CK2"/>
+    <mergeCell ref="BT1:BV1"/>
+    <mergeCell ref="BT2:BV2"/>
+    <mergeCell ref="BW1:BY1"/>
+    <mergeCell ref="BW2:BY2"/>
+    <mergeCell ref="BZ1:CB1"/>
+    <mergeCell ref="BZ2:CB2"/>
+    <mergeCell ref="BK1:BM1"/>
+    <mergeCell ref="BK2:BM2"/>
+    <mergeCell ref="BN1:BP1"/>
+    <mergeCell ref="BN2:BP2"/>
+    <mergeCell ref="BQ1:BS1"/>
+    <mergeCell ref="BQ2:BS2"/>
+    <mergeCell ref="AS1:AU1"/>
+    <mergeCell ref="AS2:AU2"/>
+    <mergeCell ref="AV1:AX1"/>
+    <mergeCell ref="AV2:AX2"/>
+    <mergeCell ref="BH1:BJ1"/>
+    <mergeCell ref="BH2:BJ2"/>
+    <mergeCell ref="AY2:BA2"/>
+    <mergeCell ref="BB2:BD2"/>
+    <mergeCell ref="BE2:BG2"/>
+    <mergeCell ref="AJ1:AL1"/>
+    <mergeCell ref="AJ2:AL2"/>
+    <mergeCell ref="AM1:AO1"/>
+    <mergeCell ref="AM2:AO2"/>
+    <mergeCell ref="AP2:AR2"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
     <mergeCell ref="AD2:AF2"/>
     <mergeCell ref="AG2:AI2"/>
     <mergeCell ref="BB1:BD1"/>
@@ -43481,69 +43585,6 @@
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="X1:Z1"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="AJ1:AL1"/>
-    <mergeCell ref="AJ2:AL2"/>
-    <mergeCell ref="AM1:AO1"/>
-    <mergeCell ref="AM2:AO2"/>
-    <mergeCell ref="AP2:AR2"/>
-    <mergeCell ref="AS1:AU1"/>
-    <mergeCell ref="AS2:AU2"/>
-    <mergeCell ref="AV1:AX1"/>
-    <mergeCell ref="AV2:AX2"/>
-    <mergeCell ref="BH1:BJ1"/>
-    <mergeCell ref="BH2:BJ2"/>
-    <mergeCell ref="AY2:BA2"/>
-    <mergeCell ref="BB2:BD2"/>
-    <mergeCell ref="BE2:BG2"/>
-    <mergeCell ref="BK1:BM1"/>
-    <mergeCell ref="BK2:BM2"/>
-    <mergeCell ref="BN1:BP1"/>
-    <mergeCell ref="BN2:BP2"/>
-    <mergeCell ref="BQ1:BS1"/>
-    <mergeCell ref="BQ2:BS2"/>
-    <mergeCell ref="BT1:BV1"/>
-    <mergeCell ref="BT2:BV2"/>
-    <mergeCell ref="BW1:BY1"/>
-    <mergeCell ref="BW2:BY2"/>
-    <mergeCell ref="BZ1:CB1"/>
-    <mergeCell ref="BZ2:CB2"/>
-    <mergeCell ref="CC1:CE1"/>
-    <mergeCell ref="CC2:CE2"/>
-    <mergeCell ref="CF1:CH1"/>
-    <mergeCell ref="CF2:CH2"/>
-    <mergeCell ref="CI1:CK1"/>
-    <mergeCell ref="CI2:CK2"/>
-    <mergeCell ref="CL1:CN1"/>
-    <mergeCell ref="CL2:CN2"/>
-    <mergeCell ref="CO1:CQ1"/>
-    <mergeCell ref="CO2:CQ2"/>
-    <mergeCell ref="CR1:CT1"/>
-    <mergeCell ref="CR2:CT2"/>
-    <mergeCell ref="CU1:CW1"/>
-    <mergeCell ref="CU2:CW2"/>
-    <mergeCell ref="CX1:CZ1"/>
-    <mergeCell ref="CX2:CZ2"/>
-    <mergeCell ref="DJ1:DL1"/>
-    <mergeCell ref="DJ2:DL2"/>
-    <mergeCell ref="DM1:DO1"/>
-    <mergeCell ref="DM2:DO2"/>
-    <mergeCell ref="DA1:DC1"/>
-    <mergeCell ref="DA2:DC2"/>
-    <mergeCell ref="DD1:DF1"/>
-    <mergeCell ref="DD2:DF2"/>
-    <mergeCell ref="DG1:DI1"/>
-    <mergeCell ref="DG2:DI2"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:DO37">
     <cfRule type="cellIs" dxfId="18" priority="1" operator="between">
@@ -43614,14 +43655,14 @@
       <c r="AA1" s="227"/>
       <c r="AB1" s="227"/>
       <c r="AC1" s="228"/>
-      <c r="AD1" s="241" t="s">
+      <c r="AD1" s="238" t="s">
         <v>281</v>
       </c>
-      <c r="AE1" s="242"/>
-      <c r="AF1" s="242"/>
-      <c r="AG1" s="242"/>
-      <c r="AH1" s="242"/>
-      <c r="AI1" s="243"/>
+      <c r="AE1" s="239"/>
+      <c r="AF1" s="239"/>
+      <c r="AG1" s="239"/>
+      <c r="AH1" s="239"/>
+      <c r="AI1" s="240"/>
       <c r="AJ1" s="226" t="s">
         <v>282</v>
       </c>
@@ -43650,51 +43691,51 @@
       <c r="C2" s="236"/>
       <c r="D2" s="236"/>
       <c r="E2" s="236"/>
-      <c r="F2" s="238"/>
-      <c r="G2" s="239"/>
-      <c r="H2" s="240"/>
-      <c r="I2" s="238"/>
-      <c r="J2" s="239"/>
-      <c r="K2" s="240"/>
-      <c r="L2" s="238"/>
-      <c r="M2" s="239"/>
-      <c r="N2" s="240"/>
-      <c r="O2" s="238"/>
-      <c r="P2" s="239"/>
-      <c r="Q2" s="240"/>
-      <c r="R2" s="238"/>
-      <c r="S2" s="239"/>
-      <c r="T2" s="240"/>
-      <c r="U2" s="238"/>
-      <c r="V2" s="239"/>
-      <c r="W2" s="240"/>
-      <c r="X2" s="238"/>
-      <c r="Y2" s="239"/>
-      <c r="Z2" s="240"/>
-      <c r="AA2" s="238"/>
-      <c r="AB2" s="239"/>
-      <c r="AC2" s="239"/>
-      <c r="AD2" s="238"/>
-      <c r="AE2" s="239"/>
-      <c r="AF2" s="240"/>
-      <c r="AG2" s="238"/>
-      <c r="AH2" s="239"/>
-      <c r="AI2" s="240"/>
-      <c r="AJ2" s="238"/>
-      <c r="AK2" s="239"/>
-      <c r="AL2" s="240"/>
-      <c r="AM2" s="238"/>
-      <c r="AN2" s="239"/>
-      <c r="AO2" s="240"/>
-      <c r="AP2" s="238"/>
-      <c r="AQ2" s="239"/>
-      <c r="AR2" s="240"/>
-      <c r="AS2" s="238"/>
-      <c r="AT2" s="239"/>
-      <c r="AU2" s="240"/>
-      <c r="AV2" s="238"/>
-      <c r="AW2" s="239"/>
-      <c r="AX2" s="240"/>
+      <c r="F2" s="223"/>
+      <c r="G2" s="224"/>
+      <c r="H2" s="225"/>
+      <c r="I2" s="223"/>
+      <c r="J2" s="224"/>
+      <c r="K2" s="225"/>
+      <c r="L2" s="223"/>
+      <c r="M2" s="224"/>
+      <c r="N2" s="225"/>
+      <c r="O2" s="223"/>
+      <c r="P2" s="224"/>
+      <c r="Q2" s="225"/>
+      <c r="R2" s="223"/>
+      <c r="S2" s="224"/>
+      <c r="T2" s="225"/>
+      <c r="U2" s="223"/>
+      <c r="V2" s="224"/>
+      <c r="W2" s="225"/>
+      <c r="X2" s="223"/>
+      <c r="Y2" s="224"/>
+      <c r="Z2" s="225"/>
+      <c r="AA2" s="223"/>
+      <c r="AB2" s="224"/>
+      <c r="AC2" s="224"/>
+      <c r="AD2" s="223"/>
+      <c r="AE2" s="224"/>
+      <c r="AF2" s="225"/>
+      <c r="AG2" s="223"/>
+      <c r="AH2" s="224"/>
+      <c r="AI2" s="225"/>
+      <c r="AJ2" s="223"/>
+      <c r="AK2" s="224"/>
+      <c r="AL2" s="225"/>
+      <c r="AM2" s="223"/>
+      <c r="AN2" s="224"/>
+      <c r="AO2" s="225"/>
+      <c r="AP2" s="223"/>
+      <c r="AQ2" s="224"/>
+      <c r="AR2" s="225"/>
+      <c r="AS2" s="223"/>
+      <c r="AT2" s="224"/>
+      <c r="AU2" s="225"/>
+      <c r="AV2" s="223"/>
+      <c r="AW2" s="224"/>
+      <c r="AX2" s="225"/>
     </row>
     <row r="3" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -44627,7 +44668,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="149" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C16" s="58">
         <f t="shared" ref="C16:C37" si="4">SUM(F16,I16,L16,O16,R16,X16,AA16,AD16,U16,AG16,AJ16,AM16,AP16,AS16,AV16)</f>
@@ -46236,13 +46277,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="F1:AC1"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="AJ1:AO1"/>
     <mergeCell ref="AP1:AU1"/>
     <mergeCell ref="AV1:AX1"/>
@@ -46259,6 +46293,13 @@
     <mergeCell ref="AD1:AI1"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="I2:K2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="F1:AC1"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
+    <mergeCell ref="AA2:AC2"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:AW31">
     <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
@@ -46302,36 +46343,36 @@
       <c r="E1" s="235" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="275" t="s">
+      <c r="F1" s="265" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="276"/>
-      <c r="H1" s="277"/>
-      <c r="I1" s="278" t="s">
+      <c r="G1" s="266"/>
+      <c r="H1" s="267"/>
+      <c r="I1" s="268" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="279"/>
-      <c r="K1" s="280"/>
-      <c r="L1" s="245" t="s">
+      <c r="J1" s="269"/>
+      <c r="K1" s="270"/>
+      <c r="L1" s="272" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="246"/>
-      <c r="N1" s="247"/>
-      <c r="O1" s="248" t="s">
+      <c r="M1" s="273"/>
+      <c r="N1" s="274"/>
+      <c r="O1" s="275" t="s">
         <v>199</v>
       </c>
-      <c r="P1" s="249"/>
-      <c r="Q1" s="250"/>
-      <c r="R1" s="251" t="s">
+      <c r="P1" s="276"/>
+      <c r="Q1" s="277"/>
+      <c r="R1" s="241" t="s">
         <v>200</v>
       </c>
-      <c r="S1" s="252"/>
-      <c r="T1" s="253"/>
-      <c r="U1" s="254" t="s">
+      <c r="S1" s="242"/>
+      <c r="T1" s="243"/>
+      <c r="U1" s="244" t="s">
         <v>306</v>
       </c>
-      <c r="V1" s="255"/>
-      <c r="W1" s="256"/>
+      <c r="V1" s="245"/>
+      <c r="W1" s="246"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
@@ -46339,24 +46380,24 @@
       <c r="C2" s="236"/>
       <c r="D2" s="236"/>
       <c r="E2" s="236"/>
-      <c r="F2" s="257"/>
-      <c r="G2" s="258"/>
-      <c r="H2" s="259"/>
-      <c r="I2" s="272"/>
-      <c r="J2" s="273"/>
-      <c r="K2" s="274"/>
-      <c r="L2" s="269"/>
-      <c r="M2" s="270"/>
-      <c r="N2" s="271"/>
-      <c r="O2" s="266"/>
-      <c r="P2" s="267"/>
-      <c r="Q2" s="268"/>
-      <c r="R2" s="263"/>
-      <c r="S2" s="264"/>
-      <c r="T2" s="265"/>
-      <c r="U2" s="260"/>
-      <c r="V2" s="261"/>
-      <c r="W2" s="262"/>
+      <c r="F2" s="247"/>
+      <c r="G2" s="248"/>
+      <c r="H2" s="249"/>
+      <c r="I2" s="262"/>
+      <c r="J2" s="263"/>
+      <c r="K2" s="264"/>
+      <c r="L2" s="259"/>
+      <c r="M2" s="260"/>
+      <c r="N2" s="261"/>
+      <c r="O2" s="256"/>
+      <c r="P2" s="257"/>
+      <c r="Q2" s="258"/>
+      <c r="R2" s="253"/>
+      <c r="S2" s="254"/>
+      <c r="T2" s="255"/>
+      <c r="U2" s="250"/>
+      <c r="V2" s="251"/>
+      <c r="W2" s="252"/>
     </row>
     <row r="3" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -46365,9 +46406,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="244"/>
-      <c r="D3" s="244"/>
-      <c r="E3" s="244"/>
+      <c r="C3" s="271"/>
+      <c r="D3" s="271"/>
+      <c r="E3" s="271"/>
       <c r="F3" s="189" t="s">
         <v>393</v>
       </c>
@@ -46884,7 +46925,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="149" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C16" s="58">
         <f t="shared" si="2"/>
@@ -47791,6 +47832,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="O1:Q1"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="F2:H2"/>
@@ -47801,11 +47847,6 @@
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="O1:Q1"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:W31">
     <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
@@ -48045,7 +48086,7 @@
       <c r="F6" s="25"/>
       <c r="G6" s="21">
         <f>'Apps &amp; Goals 26-27'!C4</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H6" s="21">
         <f>'Apps &amp; Goals 26-27'!D4</f>
@@ -48057,7 +48098,7 @@
       </c>
       <c r="J6" s="25">
         <f>G6+C6</f>
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K6" s="25">
         <f>H6+D6</f>
@@ -48624,7 +48665,7 @@
       <c r="F9" s="25"/>
       <c r="G9" s="21">
         <f>'Apps &amp; Goals 26-27'!C7</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H9" s="21">
         <f>'Apps &amp; Goals 26-27'!D7</f>
@@ -48636,7 +48677,7 @@
       </c>
       <c r="J9" s="25">
         <f t="shared" si="0"/>
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K9" s="25">
         <f t="shared" si="1"/>
@@ -48817,7 +48858,7 @@
       <c r="F10" s="25"/>
       <c r="G10" s="21">
         <f>'Apps &amp; Goals 26-27'!C8</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" s="21">
         <f>'Apps &amp; Goals 26-27'!D8</f>
@@ -48829,7 +48870,7 @@
       </c>
       <c r="J10" s="25">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K10" s="25">
         <f t="shared" si="1"/>
@@ -49010,7 +49051,7 @@
       <c r="F11" s="25"/>
       <c r="G11" s="21">
         <f>'Apps &amp; Goals 26-27'!C9</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H11" s="21">
         <f>'Apps &amp; Goals 26-27'!D9</f>
@@ -49022,7 +49063,7 @@
       </c>
       <c r="J11" s="25">
         <f t="shared" si="0"/>
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K11" s="25">
         <f t="shared" si="1"/>
@@ -49203,7 +49244,7 @@
       <c r="F12" s="25"/>
       <c r="G12" s="21">
         <f>'Apps &amp; Goals 26-27'!C10</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H12" s="21">
         <f>'Apps &amp; Goals 26-27'!D10</f>
@@ -49215,7 +49256,7 @@
       </c>
       <c r="J12" s="25">
         <f t="shared" si="0"/>
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K12" s="25">
         <f t="shared" si="1"/>
@@ -49396,11 +49437,11 @@
       <c r="F13" s="25"/>
       <c r="G13" s="21">
         <f>'Apps &amp; Goals 26-27'!C11</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H13" s="21">
         <f>'Apps &amp; Goals 26-27'!D11</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I13" s="21">
         <f>'Apps &amp; Goals 26-27'!E11</f>
@@ -49408,11 +49449,11 @@
       </c>
       <c r="J13" s="25">
         <f t="shared" si="0"/>
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K13" s="25">
         <f t="shared" si="1"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L13" s="25">
         <f t="shared" si="2"/>
@@ -50168,7 +50209,7 @@
       <c r="F17" s="25"/>
       <c r="G17" s="21">
         <f>'Apps &amp; Goals 26-27'!C15</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" s="21">
         <f>'Apps &amp; Goals 26-27'!D15</f>
@@ -50180,7 +50221,7 @@
       </c>
       <c r="J17" s="25">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K17" s="25">
         <f t="shared" si="1"/>
@@ -50347,7 +50388,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C18" s="25">
         <v>0</v>
@@ -50361,7 +50402,7 @@
       <c r="F18" s="25"/>
       <c r="G18" s="21">
         <f>'Apps &amp; Goals 26-27'!C16</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18" s="21">
         <f>'Apps &amp; Goals 26-27'!D16</f>
@@ -50373,7 +50414,7 @@
       </c>
       <c r="J18" s="25">
         <f t="shared" ref="J18:J39" si="15">G18+C18</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K18" s="25">
         <f t="shared" ref="K18:K39" si="16">H18+D18</f>
@@ -50387,7 +50428,7 @@
         <v>15</v>
       </c>
       <c r="N18" s="45" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="O18" s="26">
         <v>0</v>
@@ -50424,7 +50465,7 @@
         <v>0</v>
       </c>
       <c r="Z18" s="57" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="AA18" s="24">
         <v>0</v>
@@ -50461,7 +50502,7 @@
         <v>0</v>
       </c>
       <c r="AL18" s="63" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="AM18" s="18">
         <v>0</v>
@@ -50498,7 +50539,7 @@
         <v>0</v>
       </c>
       <c r="AX18" s="32" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="AY18" s="33">
         <v>0</v>
@@ -50554,7 +50595,7 @@
       <c r="F19" s="25"/>
       <c r="G19" s="21">
         <f>'Apps &amp; Goals 26-27'!C17</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H19" s="21">
         <f>'Apps &amp; Goals 26-27'!D17</f>
@@ -50562,11 +50603,11 @@
       </c>
       <c r="I19" s="21">
         <f>'Apps &amp; Goals 26-27'!E17</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" s="25">
         <f t="shared" si="15"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K19" s="25">
         <f t="shared" si="16"/>
@@ -50574,7 +50615,7 @@
       </c>
       <c r="L19" s="25">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19">
         <v>17</v>
@@ -50747,7 +50788,7 @@
       <c r="F20" s="25"/>
       <c r="G20" s="21">
         <f>'Apps &amp; Goals 26-27'!C18</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" s="21">
         <f>'Apps &amp; Goals 26-27'!D18</f>
@@ -50759,7 +50800,7 @@
       </c>
       <c r="J20" s="25">
         <f t="shared" si="15"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K20" s="25">
         <f t="shared" si="16"/>
@@ -51133,7 +51174,7 @@
       <c r="F22" s="25"/>
       <c r="G22" s="21">
         <f>'Apps &amp; Goals 26-27'!C20</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H22" s="21">
         <f>'Apps &amp; Goals 26-27'!D20</f>
@@ -51145,7 +51186,7 @@
       </c>
       <c r="J22" s="25">
         <f t="shared" si="15"/>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K22" s="25">
         <f t="shared" si="16"/>
@@ -51326,11 +51367,11 @@
       <c r="F23" s="25"/>
       <c r="G23" s="21">
         <f>'Apps &amp; Goals 26-27'!C21</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H23" s="21">
         <f>'Apps &amp; Goals 26-27'!D21</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I23" s="21">
         <f>'Apps &amp; Goals 26-27'!E21</f>
@@ -51338,11 +51379,11 @@
       </c>
       <c r="J23" s="25">
         <f t="shared" si="15"/>
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K23" s="25">
         <f t="shared" si="16"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L23" s="25">
         <f t="shared" si="17"/>
@@ -51712,7 +51753,7 @@
       <c r="F25" s="25"/>
       <c r="G25" s="21">
         <f>'Apps &amp; Goals 26-27'!C23</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H25" s="21">
         <f>'Apps &amp; Goals 26-27'!D23</f>
@@ -51724,7 +51765,7 @@
       </c>
       <c r="J25" s="25">
         <f t="shared" si="15"/>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K25" s="25">
         <f t="shared" si="16"/>
@@ -52098,7 +52139,7 @@
       <c r="F27" s="25"/>
       <c r="G27" s="21">
         <f>'Apps &amp; Goals 26-27'!C25</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" s="21">
         <f>'Apps &amp; Goals 26-27'!D25</f>
@@ -52110,7 +52151,7 @@
       </c>
       <c r="J27" s="25">
         <f t="shared" si="15"/>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K27" s="25">
         <f t="shared" si="16"/>
@@ -52677,7 +52718,7 @@
       <c r="F30" s="25"/>
       <c r="G30" s="21">
         <f>'Apps &amp; Goals 26-27'!C28</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H30" s="21">
         <f>'Apps &amp; Goals 26-27'!D28</f>
@@ -52685,11 +52726,11 @@
       </c>
       <c r="I30" s="21">
         <f>'Apps &amp; Goals 26-27'!E28</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" s="25">
         <f t="shared" si="15"/>
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K30" s="25">
         <f t="shared" si="16"/>
@@ -52697,7 +52738,7 @@
       </c>
       <c r="L30" s="25">
         <f t="shared" si="17"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M30">
         <v>41</v>
@@ -53449,7 +53490,7 @@
       <c r="F34" s="25"/>
       <c r="G34" s="21">
         <f>'Apps &amp; Goals 26-27'!C32</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H34" s="21">
         <f>'Apps &amp; Goals 26-27'!D32</f>
@@ -53461,7 +53502,7 @@
       </c>
       <c r="J34" s="25">
         <f t="shared" si="15"/>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K34" s="25">
         <f t="shared" si="16"/>
@@ -54628,36 +54669,36 @@
       <c r="E1" s="235" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="275" t="s">
+      <c r="F1" s="265" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="276"/>
-      <c r="H1" s="277"/>
-      <c r="I1" s="278" t="s">
+      <c r="G1" s="266"/>
+      <c r="H1" s="267"/>
+      <c r="I1" s="268" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="279"/>
-      <c r="K1" s="280"/>
-      <c r="L1" s="245" t="s">
+      <c r="J1" s="269"/>
+      <c r="K1" s="270"/>
+      <c r="L1" s="272" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="246"/>
-      <c r="N1" s="247"/>
-      <c r="O1" s="248" t="s">
+      <c r="M1" s="273"/>
+      <c r="N1" s="274"/>
+      <c r="O1" s="275" t="s">
         <v>199</v>
       </c>
-      <c r="P1" s="249"/>
-      <c r="Q1" s="250"/>
-      <c r="R1" s="251" t="s">
+      <c r="P1" s="276"/>
+      <c r="Q1" s="277"/>
+      <c r="R1" s="241" t="s">
         <v>200</v>
       </c>
-      <c r="S1" s="252"/>
-      <c r="T1" s="253"/>
-      <c r="U1" s="254" t="s">
+      <c r="S1" s="242"/>
+      <c r="T1" s="243"/>
+      <c r="U1" s="244" t="s">
         <v>306</v>
       </c>
-      <c r="V1" s="255"/>
-      <c r="W1" s="256"/>
+      <c r="V1" s="245"/>
+      <c r="W1" s="246"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
@@ -54665,26 +54706,26 @@
       <c r="C2" s="236"/>
       <c r="D2" s="236"/>
       <c r="E2" s="236"/>
-      <c r="F2" s="257" t="s">
-        <v>438</v>
-      </c>
-      <c r="G2" s="258"/>
-      <c r="H2" s="259"/>
-      <c r="I2" s="272"/>
-      <c r="J2" s="273"/>
-      <c r="K2" s="274"/>
-      <c r="L2" s="269"/>
-      <c r="M2" s="270"/>
-      <c r="N2" s="271"/>
-      <c r="O2" s="266"/>
-      <c r="P2" s="267"/>
-      <c r="Q2" s="268"/>
-      <c r="R2" s="263"/>
-      <c r="S2" s="264"/>
-      <c r="T2" s="265"/>
-      <c r="U2" s="260"/>
-      <c r="V2" s="261"/>
-      <c r="W2" s="262"/>
+      <c r="F2" s="247" t="s">
+        <v>435</v>
+      </c>
+      <c r="G2" s="248"/>
+      <c r="H2" s="249"/>
+      <c r="I2" s="262"/>
+      <c r="J2" s="263"/>
+      <c r="K2" s="264"/>
+      <c r="L2" s="259"/>
+      <c r="M2" s="260"/>
+      <c r="N2" s="261"/>
+      <c r="O2" s="256"/>
+      <c r="P2" s="257"/>
+      <c r="Q2" s="258"/>
+      <c r="R2" s="253"/>
+      <c r="S2" s="254"/>
+      <c r="T2" s="255"/>
+      <c r="U2" s="250"/>
+      <c r="V2" s="251"/>
+      <c r="W2" s="252"/>
     </row>
     <row r="3" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -54693,9 +54734,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="244"/>
-      <c r="D3" s="244"/>
-      <c r="E3" s="244"/>
+      <c r="C3" s="271"/>
+      <c r="D3" s="271"/>
+      <c r="E3" s="271"/>
       <c r="F3" s="189" t="s">
         <v>393</v>
       </c>
@@ -55212,7 +55253,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="149" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C16" s="58">
         <f t="shared" ref="C16:C37" si="2">SUM(F16,I16,L16,O16,R16,U16)</f>
@@ -56119,11 +56160,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="F2:H2"/>
@@ -56134,6 +56170,11 @@
     <mergeCell ref="U2:W2"/>
     <mergeCell ref="L1:N1"/>
     <mergeCell ref="O1:Q1"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:W31">
     <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
@@ -56161,11 +56202,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C1" s="281" t="s">
+      <c r="C1" s="278" t="s">
         <v>340</v>
       </c>
-      <c r="D1" s="282"/>
-      <c r="E1" s="282"/>
+      <c r="D1" s="279"/>
+      <c r="E1" s="279"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -56341,7 +56382,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="149" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="20"/>
@@ -56629,51 +56670,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="303" t="s">
+      <c r="C1" s="281" t="s">
         <v>202</v>
       </c>
-      <c r="D1" s="304"/>
-      <c r="E1" s="304"/>
-      <c r="F1" s="304"/>
-      <c r="G1" s="304"/>
-      <c r="H1" s="304"/>
-      <c r="I1" s="305"/>
+      <c r="D1" s="282"/>
+      <c r="E1" s="282"/>
+      <c r="F1" s="282"/>
+      <c r="G1" s="282"/>
+      <c r="H1" s="282"/>
+      <c r="I1" s="283"/>
       <c r="J1" s="114" t="s">
         <v>195</v>
       </c>
       <c r="K1" s="115" t="s">
         <v>194</v>
       </c>
-      <c r="L1" s="283" t="s">
+      <c r="L1" s="305" t="s">
         <v>287</v>
       </c>
-      <c r="M1" s="288"/>
-      <c r="N1" s="288"/>
-      <c r="O1" s="288"/>
-      <c r="P1" s="288"/>
-      <c r="Q1" s="288"/>
-      <c r="R1" s="288"/>
-      <c r="S1" s="288"/>
-      <c r="T1" s="288"/>
-      <c r="U1" s="288"/>
-      <c r="V1" s="288"/>
-      <c r="W1" s="288"/>
-      <c r="X1" s="288"/>
-      <c r="Y1" s="288"/>
-      <c r="Z1" s="288"/>
-      <c r="AA1" s="288"/>
-      <c r="AB1" s="288"/>
-      <c r="AC1" s="288"/>
-      <c r="AD1" s="288"/>
-      <c r="AE1" s="288"/>
-      <c r="AF1" s="288"/>
-      <c r="AG1" s="289"/>
-      <c r="AH1" s="283" t="s">
+      <c r="M1" s="310"/>
+      <c r="N1" s="310"/>
+      <c r="O1" s="310"/>
+      <c r="P1" s="310"/>
+      <c r="Q1" s="310"/>
+      <c r="R1" s="310"/>
+      <c r="S1" s="310"/>
+      <c r="T1" s="310"/>
+      <c r="U1" s="310"/>
+      <c r="V1" s="310"/>
+      <c r="W1" s="310"/>
+      <c r="X1" s="310"/>
+      <c r="Y1" s="310"/>
+      <c r="Z1" s="310"/>
+      <c r="AA1" s="310"/>
+      <c r="AB1" s="310"/>
+      <c r="AC1" s="310"/>
+      <c r="AD1" s="310"/>
+      <c r="AE1" s="310"/>
+      <c r="AF1" s="310"/>
+      <c r="AG1" s="311"/>
+      <c r="AH1" s="305" t="s">
         <v>175</v>
       </c>
-      <c r="AI1" s="284"/>
-      <c r="AJ1" s="284"/>
-      <c r="AK1" s="285"/>
+      <c r="AI1" s="306"/>
+      <c r="AJ1" s="306"/>
+      <c r="AK1" s="307"/>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B2" s="111"/>
@@ -61873,15 +61914,15 @@
         <f t="shared" ref="J80:J111" si="2">H80-I80</f>
         <v>2</v>
       </c>
-      <c r="K80" s="290" t="s">
-        <v>442</v>
-      </c>
-      <c r="L80" s="291"/>
-      <c r="M80" s="292"/>
+      <c r="K80" s="312" t="s">
+        <v>438</v>
+      </c>
+      <c r="L80" s="313"/>
+      <c r="M80" s="314"/>
       <c r="O80" s="133"/>
       <c r="P80" s="133"/>
-      <c r="W80" s="286"/>
-      <c r="X80" s="286"/>
+      <c r="W80" s="308"/>
+      <c r="X80" s="308"/>
       <c r="Y80" s="70" t="s">
         <v>211</v>
       </c>
@@ -61931,15 +61972,15 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K81" s="293"/>
-      <c r="L81" s="294"/>
-      <c r="M81" s="295"/>
+      <c r="K81" s="315"/>
+      <c r="L81" s="316"/>
+      <c r="M81" s="317"/>
       <c r="O81" s="133"/>
       <c r="P81" s="133"/>
-      <c r="W81" s="286" t="s">
+      <c r="W81" s="308" t="s">
         <v>209</v>
       </c>
-      <c r="X81" s="286"/>
+      <c r="X81" s="308"/>
       <c r="Y81" s="70">
         <f>COUNTIF(L3:AG40,3)</f>
         <v>481</v>
@@ -61995,17 +62036,17 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K82" s="296" t="s">
-        <v>443</v>
-      </c>
-      <c r="L82" s="297"/>
-      <c r="M82" s="298"/>
+      <c r="K82" s="318" t="s">
+        <v>439</v>
+      </c>
+      <c r="L82" s="319"/>
+      <c r="M82" s="320"/>
       <c r="O82" s="133"/>
       <c r="P82" s="133"/>
-      <c r="W82" s="286" t="s">
+      <c r="W82" s="308" t="s">
         <v>210</v>
       </c>
-      <c r="X82" s="286"/>
+      <c r="X82" s="308"/>
       <c r="Y82" s="70">
         <f>COUNTIF(K3:K40,3)+COUNTIF(J3:J15,3)</f>
         <v>25</v>
@@ -62061,17 +62102,17 @@
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="K83" s="299" t="s">
-        <v>444</v>
-      </c>
-      <c r="L83" s="300"/>
-      <c r="M83" s="301"/>
+      <c r="K83" s="321" t="s">
+        <v>440</v>
+      </c>
+      <c r="L83" s="322"/>
+      <c r="M83" s="323"/>
       <c r="O83" s="133"/>
       <c r="P83" s="133"/>
-      <c r="W83" s="287" t="s">
+      <c r="W83" s="309" t="s">
         <v>97</v>
       </c>
-      <c r="X83" s="287"/>
+      <c r="X83" s="309"/>
       <c r="Y83" s="196">
         <v>220</v>
       </c>
@@ -62124,15 +62165,15 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="K84" s="318" t="s">
+      <c r="K84" s="296" t="s">
         <v>284</v>
       </c>
-      <c r="L84" s="319"/>
-      <c r="M84" s="320"/>
+      <c r="L84" s="297"/>
+      <c r="M84" s="298"/>
       <c r="O84" s="141"/>
       <c r="P84" s="141"/>
-      <c r="W84" s="302"/>
-      <c r="X84" s="302"/>
+      <c r="W84" s="280"/>
+      <c r="X84" s="280"/>
       <c r="Y84" s="198"/>
       <c r="Z84" s="198"/>
       <c r="AA84" s="198"/>
@@ -62170,9 +62211,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K85" s="321"/>
-      <c r="L85" s="322"/>
-      <c r="M85" s="323"/>
+      <c r="K85" s="299"/>
+      <c r="L85" s="300"/>
+      <c r="M85" s="301"/>
       <c r="O85" s="141"/>
       <c r="P85" s="141"/>
     </row>
@@ -62206,9 +62247,9 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="K86" s="321"/>
-      <c r="L86" s="322"/>
-      <c r="M86" s="323"/>
+      <c r="K86" s="299"/>
+      <c r="L86" s="300"/>
+      <c r="M86" s="301"/>
       <c r="O86" s="141"/>
       <c r="P86" s="141"/>
     </row>
@@ -62242,9 +62283,9 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="K87" s="321"/>
-      <c r="L87" s="322"/>
-      <c r="M87" s="323"/>
+      <c r="K87" s="299"/>
+      <c r="L87" s="300"/>
+      <c r="M87" s="301"/>
       <c r="O87" s="141"/>
       <c r="P87" s="141"/>
     </row>
@@ -62278,9 +62319,9 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K88" s="321"/>
-      <c r="L88" s="322"/>
-      <c r="M88" s="323"/>
+      <c r="K88" s="299"/>
+      <c r="L88" s="300"/>
+      <c r="M88" s="301"/>
       <c r="O88" s="141"/>
       <c r="P88" s="141"/>
     </row>
@@ -62314,9 +62355,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K89" s="321"/>
-      <c r="L89" s="322"/>
-      <c r="M89" s="323"/>
+      <c r="K89" s="299"/>
+      <c r="L89" s="300"/>
+      <c r="M89" s="301"/>
       <c r="O89" s="141"/>
       <c r="P89" s="141"/>
     </row>
@@ -62350,9 +62391,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K90" s="321"/>
-      <c r="L90" s="322"/>
-      <c r="M90" s="323"/>
+      <c r="K90" s="299"/>
+      <c r="L90" s="300"/>
+      <c r="M90" s="301"/>
       <c r="O90" s="141"/>
       <c r="P90" s="141"/>
     </row>
@@ -62386,9 +62427,9 @@
         <f t="shared" si="2"/>
         <v>47</v>
       </c>
-      <c r="K91" s="321"/>
-      <c r="L91" s="322"/>
-      <c r="M91" s="323"/>
+      <c r="K91" s="299"/>
+      <c r="L91" s="300"/>
+      <c r="M91" s="301"/>
       <c r="O91" s="141"/>
       <c r="P91" s="141"/>
     </row>
@@ -62422,9 +62463,9 @@
         <f t="shared" si="2"/>
         <v>51</v>
       </c>
-      <c r="K92" s="321"/>
-      <c r="L92" s="322"/>
-      <c r="M92" s="323"/>
+      <c r="K92" s="299"/>
+      <c r="L92" s="300"/>
+      <c r="M92" s="301"/>
       <c r="O92" s="141"/>
       <c r="P92" s="141"/>
     </row>
@@ -62458,9 +62499,9 @@
         <f t="shared" si="2"/>
         <v>37</v>
       </c>
-      <c r="K93" s="321"/>
-      <c r="L93" s="322"/>
-      <c r="M93" s="323"/>
+      <c r="K93" s="299"/>
+      <c r="L93" s="300"/>
+      <c r="M93" s="301"/>
       <c r="O93" s="141"/>
       <c r="P93" s="141"/>
     </row>
@@ -62494,9 +62535,9 @@
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="K94" s="321"/>
-      <c r="L94" s="322"/>
-      <c r="M94" s="323"/>
+      <c r="K94" s="299"/>
+      <c r="L94" s="300"/>
+      <c r="M94" s="301"/>
       <c r="O94" s="141"/>
       <c r="P94" s="141"/>
     </row>
@@ -62530,9 +62571,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K95" s="321"/>
-      <c r="L95" s="322"/>
-      <c r="M95" s="323"/>
+      <c r="K95" s="299"/>
+      <c r="L95" s="300"/>
+      <c r="M95" s="301"/>
       <c r="O95" s="141"/>
       <c r="P95" s="141"/>
     </row>
@@ -62566,9 +62607,9 @@
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="K96" s="321"/>
-      <c r="L96" s="322"/>
-      <c r="M96" s="323"/>
+      <c r="K96" s="299"/>
+      <c r="L96" s="300"/>
+      <c r="M96" s="301"/>
       <c r="O96" s="141"/>
       <c r="P96" s="141"/>
     </row>
@@ -62602,9 +62643,9 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="K97" s="321"/>
-      <c r="L97" s="322"/>
-      <c r="M97" s="323"/>
+      <c r="K97" s="299"/>
+      <c r="L97" s="300"/>
+      <c r="M97" s="301"/>
       <c r="O97" s="141"/>
       <c r="P97" s="141"/>
     </row>
@@ -62638,9 +62679,9 @@
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="K98" s="321"/>
-      <c r="L98" s="322"/>
-      <c r="M98" s="323"/>
+      <c r="K98" s="299"/>
+      <c r="L98" s="300"/>
+      <c r="M98" s="301"/>
       <c r="O98" s="141"/>
       <c r="P98" s="141"/>
     </row>
@@ -62674,9 +62715,9 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K99" s="321"/>
-      <c r="L99" s="322"/>
-      <c r="M99" s="323"/>
+      <c r="K99" s="299"/>
+      <c r="L99" s="300"/>
+      <c r="M99" s="301"/>
       <c r="O99" s="141"/>
       <c r="P99" s="141"/>
     </row>
@@ -62710,9 +62751,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K100" s="321"/>
-      <c r="L100" s="322"/>
-      <c r="M100" s="323"/>
+      <c r="K100" s="299"/>
+      <c r="L100" s="300"/>
+      <c r="M100" s="301"/>
       <c r="O100" s="141"/>
       <c r="P100" s="141"/>
     </row>
@@ -62746,9 +62787,9 @@
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="K101" s="321"/>
-      <c r="L101" s="322"/>
-      <c r="M101" s="323"/>
+      <c r="K101" s="299"/>
+      <c r="L101" s="300"/>
+      <c r="M101" s="301"/>
       <c r="O101" s="141"/>
       <c r="P101" s="141"/>
     </row>
@@ -62782,9 +62823,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K102" s="321"/>
-      <c r="L102" s="322"/>
-      <c r="M102" s="323"/>
+      <c r="K102" s="299"/>
+      <c r="L102" s="300"/>
+      <c r="M102" s="301"/>
       <c r="O102" s="141"/>
       <c r="P102" s="141"/>
     </row>
@@ -62818,9 +62859,9 @@
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="K103" s="321"/>
-      <c r="L103" s="322"/>
-      <c r="M103" s="323"/>
+      <c r="K103" s="299"/>
+      <c r="L103" s="300"/>
+      <c r="M103" s="301"/>
       <c r="O103" s="141"/>
       <c r="P103" s="141"/>
     </row>
@@ -62854,9 +62895,9 @@
         <f t="shared" si="2"/>
         <v>33</v>
       </c>
-      <c r="K104" s="321"/>
-      <c r="L104" s="322"/>
-      <c r="M104" s="323"/>
+      <c r="K104" s="299"/>
+      <c r="L104" s="300"/>
+      <c r="M104" s="301"/>
       <c r="O104" s="141"/>
       <c r="P104" s="141"/>
     </row>
@@ -62890,9 +62931,9 @@
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="K105" s="324"/>
-      <c r="L105" s="325"/>
-      <c r="M105" s="326"/>
+      <c r="K105" s="302"/>
+      <c r="L105" s="303"/>
+      <c r="M105" s="304"/>
       <c r="O105" s="141"/>
       <c r="P105" s="141"/>
     </row>
@@ -62926,11 +62967,11 @@
         <f t="shared" si="2"/>
         <v>21</v>
       </c>
-      <c r="K106" s="315" t="s">
+      <c r="K106" s="293" t="s">
         <v>286</v>
       </c>
-      <c r="L106" s="316"/>
-      <c r="M106" s="317"/>
+      <c r="L106" s="294"/>
+      <c r="M106" s="295"/>
       <c r="O106" s="126"/>
       <c r="P106" s="126"/>
     </row>
@@ -62964,11 +63005,11 @@
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="K107" s="315" t="s">
+      <c r="K107" s="293" t="s">
         <v>288</v>
       </c>
-      <c r="L107" s="316"/>
-      <c r="M107" s="317"/>
+      <c r="L107" s="294"/>
+      <c r="M107" s="295"/>
       <c r="O107" s="126"/>
       <c r="P107" s="126"/>
     </row>
@@ -63002,11 +63043,11 @@
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="K108" s="306" t="s">
+      <c r="K108" s="284" t="s">
         <v>289</v>
       </c>
-      <c r="L108" s="307"/>
-      <c r="M108" s="308"/>
+      <c r="L108" s="285"/>
+      <c r="M108" s="286"/>
       <c r="O108" s="126"/>
       <c r="P108" s="126"/>
     </row>
@@ -63040,9 +63081,9 @@
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="K109" s="309"/>
-      <c r="L109" s="310"/>
-      <c r="M109" s="311"/>
+      <c r="K109" s="287"/>
+      <c r="L109" s="288"/>
+      <c r="M109" s="289"/>
       <c r="O109" s="126"/>
       <c r="P109" s="126"/>
     </row>
@@ -63076,9 +63117,9 @@
         <f t="shared" si="2"/>
         <v>45</v>
       </c>
-      <c r="K110" s="309"/>
-      <c r="L110" s="310"/>
-      <c r="M110" s="311"/>
+      <c r="K110" s="287"/>
+      <c r="L110" s="288"/>
+      <c r="M110" s="289"/>
       <c r="O110" s="126"/>
       <c r="P110" s="126"/>
     </row>
@@ -63112,9 +63153,9 @@
         <f t="shared" si="2"/>
         <v>62</v>
       </c>
-      <c r="K111" s="309"/>
-      <c r="L111" s="310"/>
-      <c r="M111" s="311"/>
+      <c r="K111" s="287"/>
+      <c r="L111" s="288"/>
+      <c r="M111" s="289"/>
       <c r="O111" s="126"/>
       <c r="P111" s="126"/>
     </row>
@@ -63152,9 +63193,9 @@
         <f t="shared" ref="J112:J114" si="6">H112-I112</f>
         <v>34</v>
       </c>
-      <c r="K112" s="309"/>
-      <c r="L112" s="310"/>
-      <c r="M112" s="311"/>
+      <c r="K112" s="287"/>
+      <c r="L112" s="288"/>
+      <c r="M112" s="289"/>
     </row>
     <row r="113" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="156" t="s">
@@ -63190,13 +63231,13 @@
         <f t="shared" si="6"/>
         <v>43</v>
       </c>
-      <c r="K113" s="312"/>
-      <c r="L113" s="313"/>
-      <c r="M113" s="314"/>
+      <c r="K113" s="290"/>
+      <c r="L113" s="291"/>
+      <c r="M113" s="292"/>
     </row>
     <row r="114" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" s="93" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="B114" s="122"/>
       <c r="C114" s="122"/>
@@ -63218,26 +63259,20 @@
       </c>
       <c r="H114" s="122">
         <f>Match!R4</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I114" s="122">
         <f>Match!S4</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J114" s="122">
         <f t="shared" si="6"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A79:J112" xr:uid="{9C81160F-C24B-449F-8F5A-CB622AB71070}"/>
   <mergeCells count="15">
-    <mergeCell ref="W84:X84"/>
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="K108:M113"/>
-    <mergeCell ref="K106:M106"/>
-    <mergeCell ref="K107:M107"/>
-    <mergeCell ref="K84:M105"/>
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="W80:X80"/>
     <mergeCell ref="W81:X81"/>
@@ -63247,6 +63282,12 @@
     <mergeCell ref="K80:M81"/>
     <mergeCell ref="K82:M82"/>
     <mergeCell ref="K83:M83"/>
+    <mergeCell ref="W84:X84"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="K108:M113"/>
+    <mergeCell ref="K106:M106"/>
+    <mergeCell ref="K107:M107"/>
+    <mergeCell ref="K84:M105"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <conditionalFormatting sqref="A3:A40">
@@ -63318,9 +63359,9 @@
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19.85546875" bestFit="1" customWidth="1"/>
@@ -63328,35 +63369,42 @@
     <col min="10" max="10" width="26.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="4.140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="2.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="2.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="3.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="327" t="s">
+      <c r="A1" s="324" t="s">
         <v>406</v>
       </c>
-      <c r="B1" s="327"/>
-      <c r="C1" s="327"/>
-      <c r="D1" s="327"/>
-      <c r="E1" s="327"/>
-      <c r="F1" s="327" t="s">
+      <c r="B1" s="324"/>
+      <c r="C1" s="324"/>
+      <c r="D1" s="324"/>
+      <c r="E1" s="324"/>
+      <c r="F1" s="324" t="s">
         <v>407</v>
       </c>
-      <c r="G1" s="327"/>
-      <c r="H1" s="327"/>
-      <c r="I1" s="327"/>
-      <c r="J1" s="327"/>
+      <c r="G1" s="324"/>
+      <c r="H1" s="324"/>
+      <c r="I1" s="324"/>
+      <c r="J1" s="324"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2" s="327"/>
-      <c r="B2" s="327"/>
-      <c r="C2" s="327"/>
-      <c r="D2" s="327"/>
-      <c r="E2" s="327"/>
-      <c r="F2" s="327"/>
-      <c r="G2" s="327"/>
-      <c r="H2" s="327"/>
-      <c r="I2" s="327"/>
-      <c r="J2" s="327"/>
+      <c r="A2" s="324"/>
+      <c r="B2" s="324"/>
+      <c r="C2" s="324"/>
+      <c r="D2" s="324"/>
+      <c r="E2" s="324"/>
+      <c r="F2" s="324"/>
+      <c r="G2" s="324"/>
+      <c r="H2" s="324"/>
+      <c r="I2" s="324"/>
+      <c r="J2" s="324"/>
       <c r="L2" t="s">
         <v>410</v>
       </c>
@@ -63426,10 +63474,10 @@
         <v>409</v>
       </c>
       <c r="N3" s="195">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O3" s="195">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P3" s="195">
         <v>0</v>
@@ -63438,48 +63486,48 @@
         <v>0</v>
       </c>
       <c r="R3" s="195">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S3" s="195">
         <v>2</v>
       </c>
       <c r="T3" s="195">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U3" s="195">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>441</v>
+        <v>477</v>
       </c>
       <c r="B4" s="194">
-        <v>0.72916666666666663</v>
+        <v>0.875</v>
       </c>
       <c r="C4" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>419</v>
+        <v>478</v>
       </c>
       <c r="E4" t="s">
-        <v>404</v>
+        <v>479</v>
       </c>
       <c r="F4" t="s">
-        <v>435</v>
-      </c>
-      <c r="G4" s="194" t="s">
-        <v>440</v>
+        <v>437</v>
+      </c>
+      <c r="G4" s="330" t="s">
+        <v>475</v>
       </c>
       <c r="H4" t="s">
         <v>4</v>
       </c>
       <c r="I4" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="J4" t="s">
-        <v>436</v>
+        <v>404</v>
       </c>
       <c r="L4">
         <v>2</v>
@@ -63488,10 +63536,10 @@
         <v>414</v>
       </c>
       <c r="N4" s="195">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O4" s="195">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P4" s="195">
         <v>0</v>
@@ -63500,16 +63548,16 @@
         <v>0</v>
       </c>
       <c r="R4" s="195">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S4" s="195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" s="195">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U4" s="195">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
@@ -63520,13 +63568,13 @@
         <v>423</v>
       </c>
       <c r="N5" s="195">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O5" s="195">
         <v>2</v>
       </c>
       <c r="P5" s="195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" s="195">
         <v>0</v>
@@ -63541,7 +63589,7 @@
         <v>3</v>
       </c>
       <c r="U5" s="195">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
@@ -63552,7 +63600,7 @@
         <v>419</v>
       </c>
       <c r="N6" s="195">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O6" s="195">
         <v>2</v>
@@ -63561,16 +63609,16 @@
         <v>0</v>
       </c>
       <c r="Q6" s="195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" s="195">
+        <v>8</v>
+      </c>
+      <c r="S6" s="195">
         <v>7</v>
       </c>
-      <c r="S6" s="195">
-        <v>5</v>
-      </c>
       <c r="T6" s="195">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U6" s="195">
         <v>6</v>
@@ -63584,28 +63632,28 @@
         <v>417</v>
       </c>
       <c r="N7" s="195">
+        <v>3</v>
+      </c>
+      <c r="O7" s="195">
+        <v>1</v>
+      </c>
+      <c r="P7" s="195">
         <v>2</v>
       </c>
-      <c r="O7" s="195">
-        <v>1</v>
-      </c>
-      <c r="P7" s="195">
-        <v>1</v>
-      </c>
       <c r="Q7" s="195">
         <v>0</v>
       </c>
       <c r="R7" s="195">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S7" s="195">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T7" s="195">
         <v>3</v>
       </c>
       <c r="U7" s="195">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
@@ -63613,31 +63661,31 @@
         <v>6</v>
       </c>
       <c r="M8" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="N8" s="195">
+        <v>3</v>
+      </c>
+      <c r="O8" s="195">
+        <v>1</v>
+      </c>
+      <c r="P8" s="195">
         <v>2</v>
       </c>
-      <c r="O8" s="195">
-        <v>1</v>
-      </c>
-      <c r="P8" s="195">
-        <v>1</v>
-      </c>
       <c r="Q8" s="195">
         <v>0</v>
       </c>
       <c r="R8" s="195">
+        <v>6</v>
+      </c>
+      <c r="S8" s="195">
         <v>4</v>
-      </c>
-      <c r="S8" s="195">
-        <v>2</v>
       </c>
       <c r="T8" s="195">
         <v>2</v>
       </c>
       <c r="U8" s="195">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
@@ -63645,31 +63693,31 @@
         <v>7</v>
       </c>
       <c r="M9" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="N9" s="195">
+        <v>3</v>
+      </c>
+      <c r="O9" s="195">
+        <v>1</v>
+      </c>
+      <c r="P9" s="195">
         <v>2</v>
       </c>
-      <c r="O9" s="195">
-        <v>1</v>
-      </c>
-      <c r="P9" s="195">
-        <v>1</v>
-      </c>
       <c r="Q9" s="195">
         <v>0</v>
       </c>
       <c r="R9" s="195">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S9" s="195">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T9" s="195">
         <v>2</v>
       </c>
       <c r="U9" s="195">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
@@ -63677,31 +63725,31 @@
         <v>8</v>
       </c>
       <c r="M10" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="N10" s="195">
+        <v>3</v>
+      </c>
+      <c r="O10" s="195">
+        <v>1</v>
+      </c>
+      <c r="P10" s="195">
         <v>2</v>
       </c>
-      <c r="O10" s="195">
-        <v>1</v>
-      </c>
-      <c r="P10" s="195">
-        <v>1</v>
-      </c>
       <c r="Q10" s="195">
         <v>0</v>
       </c>
       <c r="R10" s="195">
+        <v>5</v>
+      </c>
+      <c r="S10" s="195">
+        <v>3</v>
+      </c>
+      <c r="T10" s="195">
         <v>2</v>
       </c>
-      <c r="S10" s="195">
-        <v>1</v>
-      </c>
-      <c r="T10" s="195">
-        <v>1</v>
-      </c>
       <c r="U10" s="195">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
@@ -63709,31 +63757,31 @@
         <v>9</v>
       </c>
       <c r="M11" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="N11" s="195">
+        <v>3</v>
+      </c>
+      <c r="O11" s="195">
+        <v>1</v>
+      </c>
+      <c r="P11" s="195">
         <v>2</v>
       </c>
-      <c r="O11" s="195">
-        <v>1</v>
-      </c>
-      <c r="P11" s="195">
-        <v>0</v>
-      </c>
       <c r="Q11" s="195">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" s="195">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="S11" s="195">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T11" s="195">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U11" s="195">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
@@ -63741,31 +63789,31 @@
         <v>10</v>
       </c>
       <c r="M12" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="N12" s="195">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O12" s="195">
         <v>1</v>
       </c>
       <c r="P12" s="195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q12" s="195">
         <v>1</v>
       </c>
       <c r="R12" s="195">
+        <v>8</v>
+      </c>
+      <c r="S12" s="195">
         <v>5</v>
       </c>
-      <c r="S12" s="195">
+      <c r="T12" s="195">
+        <v>3</v>
+      </c>
+      <c r="U12" s="195">
         <v>4</v>
-      </c>
-      <c r="T12" s="195">
-        <v>1</v>
-      </c>
-      <c r="U12" s="195">
-        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
@@ -63773,31 +63821,31 @@
         <v>11</v>
       </c>
       <c r="M13" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="N13" s="195">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O13" s="195">
         <v>1</v>
       </c>
       <c r="P13" s="195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13" s="195">
         <v>1</v>
       </c>
       <c r="R13" s="195">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="S13" s="195">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T13" s="195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U13" s="195">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
@@ -63805,31 +63853,31 @@
         <v>12</v>
       </c>
       <c r="M14" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="N14" s="195">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O14" s="195">
         <v>1</v>
       </c>
       <c r="P14" s="195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q14" s="195">
         <v>1</v>
       </c>
       <c r="R14" s="195">
+        <v>3</v>
+      </c>
+      <c r="S14" s="195">
+        <v>3</v>
+      </c>
+      <c r="T14" s="195">
+        <v>0</v>
+      </c>
+      <c r="U14" s="195">
         <v>4</v>
-      </c>
-      <c r="S14" s="195">
-        <v>6</v>
-      </c>
-      <c r="T14" s="195" t="s">
-        <v>433</v>
-      </c>
-      <c r="U14" s="195">
-        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
@@ -63837,31 +63885,31 @@
         <v>13</v>
       </c>
       <c r="M15" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="N15" s="195">
+        <v>3</v>
+      </c>
+      <c r="O15" s="195">
+        <v>1</v>
+      </c>
+      <c r="P15" s="195">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="195">
         <v>2</v>
-      </c>
-      <c r="O15" s="195">
-        <v>0</v>
-      </c>
-      <c r="P15" s="195">
-        <v>2</v>
-      </c>
-      <c r="Q15" s="195">
-        <v>0</v>
       </c>
       <c r="R15" s="195">
         <v>4</v>
       </c>
       <c r="S15" s="195">
-        <v>4</v>
-      </c>
-      <c r="T15" s="195">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="T15" s="195" t="s">
+        <v>433</v>
       </c>
       <c r="U15" s="195">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
@@ -63869,31 +63917,31 @@
         <v>14</v>
       </c>
       <c r="M16" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="N16" s="195">
+        <v>3</v>
+      </c>
+      <c r="O16" s="195">
+        <v>1</v>
+      </c>
+      <c r="P16" s="195">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="195">
         <v>2</v>
       </c>
-      <c r="O16" s="195">
-        <v>0</v>
-      </c>
-      <c r="P16" s="195">
-        <v>1</v>
-      </c>
-      <c r="Q16" s="195">
-        <v>1</v>
-      </c>
       <c r="R16" s="195">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S16" s="195">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T16" s="195" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="U16" s="195">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="12:21" x14ac:dyDescent="0.25">
@@ -63901,31 +63949,31 @@
         <v>15</v>
       </c>
       <c r="M17" t="s">
-        <v>429</v>
+        <v>416</v>
       </c>
       <c r="N17" s="195">
+        <v>3</v>
+      </c>
+      <c r="O17" s="195">
+        <v>0</v>
+      </c>
+      <c r="P17" s="195">
         <v>2</v>
       </c>
-      <c r="O17" s="195">
-        <v>0</v>
-      </c>
-      <c r="P17" s="195">
-        <v>1</v>
-      </c>
       <c r="Q17" s="195">
         <v>1</v>
       </c>
       <c r="R17" s="195">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S17" s="195">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T17" s="195" t="s">
         <v>432</v>
       </c>
       <c r="U17" s="195">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="12:21" x14ac:dyDescent="0.25">
@@ -63933,31 +63981,31 @@
         <v>16</v>
       </c>
       <c r="M18" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="N18" s="195">
+        <v>3</v>
+      </c>
+      <c r="O18" s="195">
+        <v>0</v>
+      </c>
+      <c r="P18" s="195">
         <v>2</v>
       </c>
-      <c r="O18" s="195">
-        <v>0</v>
-      </c>
-      <c r="P18" s="195">
-        <v>0</v>
-      </c>
       <c r="Q18" s="195">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R18" s="195">
         <v>2</v>
       </c>
       <c r="S18" s="195">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T18" s="195" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="U18" s="195">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="12:21" x14ac:dyDescent="0.25">
@@ -63965,16 +64013,16 @@
         <v>17</v>
       </c>
       <c r="M19" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="N19" s="195">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O19" s="195">
         <v>0</v>
       </c>
       <c r="P19" s="195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="195">
         <v>2</v>
@@ -63983,13 +64031,13 @@
         <v>0</v>
       </c>
       <c r="S19" s="195">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T19" s="195" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="U19" s="195">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="12:21" x14ac:dyDescent="0.25">
@@ -63997,31 +64045,31 @@
         <v>18</v>
       </c>
       <c r="M20" t="s">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="N20" s="195">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O20" s="195">
         <v>0</v>
       </c>
       <c r="P20" s="195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q20" s="195">
         <v>2</v>
       </c>
       <c r="R20" s="195">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" s="195">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T20" s="195" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="U20" s="195">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="12:21" x14ac:dyDescent="0.25">
@@ -64029,10 +64077,10 @@
         <v>19</v>
       </c>
       <c r="M21" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="N21" s="195">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O21" s="195">
         <v>0</v>
@@ -64041,16 +64089,16 @@
         <v>0</v>
       </c>
       <c r="Q21" s="195">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R21" s="195">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S21" s="195">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T21" s="195" t="s">
-        <v>439</v>
+        <v>476</v>
       </c>
       <c r="U21" s="195">
         <v>0</v>
@@ -64061,10 +64109,10 @@
         <v>20</v>
       </c>
       <c r="M22" t="s">
-        <v>431</v>
+        <v>405</v>
       </c>
       <c r="N22" s="195">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O22" s="195">
         <v>0</v>
@@ -64073,7 +64121,7 @@
         <v>0</v>
       </c>
       <c r="Q22" s="195">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R22" s="195">
         <v>0</v>
@@ -64082,7 +64130,7 @@
         <v>5</v>
       </c>
       <c r="T22" s="195" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="U22" s="195">
         <v>0</v>
@@ -64114,13 +64162,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="D1" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="E1" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -64128,10 +64176,10 @@
         <v>350</v>
       </c>
       <c r="B2" t="s">
-        <v>458</v>
-      </c>
-      <c r="C2">
-        <v>6.6</v>
+        <v>454</v>
+      </c>
+      <c r="C2" s="201">
+        <v>6.7</v>
       </c>
       <c r="D2">
         <v>90</v>
@@ -64139,30 +64187,27 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="B3" t="s">
-        <v>459</v>
-      </c>
-      <c r="C3">
-        <v>7.4</v>
-      </c>
-      <c r="D3">
-        <v>90</v>
-      </c>
-      <c r="E3" t="s">
-        <v>478</v>
+        <v>455</v>
+      </c>
+      <c r="C3" s="201">
+        <v>6.4</v>
+      </c>
+      <c r="D3" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="B4" t="s">
-        <v>460</v>
-      </c>
-      <c r="C4">
-        <v>7.2</v>
+        <v>456</v>
+      </c>
+      <c r="C4" s="201">
+        <v>6.9</v>
       </c>
       <c r="D4">
         <v>90</v>
@@ -64170,27 +64215,27 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="B5" t="s">
-        <v>461</v>
-      </c>
-      <c r="C5">
-        <v>6.6</v>
-      </c>
-      <c r="D5" t="s">
-        <v>471</v>
+        <v>467</v>
+      </c>
+      <c r="C5" s="201">
+        <v>8</v>
+      </c>
+      <c r="D5">
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="B6" t="s">
-        <v>462</v>
-      </c>
-      <c r="C6">
-        <v>7.2</v>
+        <v>457</v>
+      </c>
+      <c r="C6" s="201">
+        <v>7.1</v>
       </c>
       <c r="D6">
         <v>90</v>
@@ -64198,117 +64243,124 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="B7" t="s">
-        <v>463</v>
-      </c>
-      <c r="C7">
-        <v>6.7</v>
+        <v>458</v>
+      </c>
+      <c r="C7" s="201">
+        <v>6.3</v>
       </c>
       <c r="D7" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="B8" t="s">
-        <v>464</v>
-      </c>
-      <c r="C8">
-        <v>7.2</v>
-      </c>
-      <c r="D8" t="s">
+        <v>459</v>
+      </c>
+      <c r="C8" s="201">
+        <v>8.1</v>
+      </c>
+      <c r="D8">
+        <v>90</v>
+      </c>
+      <c r="E8" t="s">
         <v>471</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="B9" t="s">
+        <v>460</v>
+      </c>
+      <c r="C9" s="201">
+        <v>9.1</v>
+      </c>
+      <c r="D9" t="s">
         <v>465</v>
       </c>
-      <c r="C9">
-        <v>6.6</v>
-      </c>
-      <c r="D9" t="s">
-        <v>471</v>
+      <c r="E9" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="B10" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="C10" s="201">
-        <v>6</v>
-      </c>
-      <c r="D10" t="s">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="D10">
+        <v>90</v>
+      </c>
+      <c r="E10" t="s">
         <v>471</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="B11" t="s">
-        <v>467</v>
-      </c>
-      <c r="C11">
-        <v>8.1</v>
-      </c>
-      <c r="D11">
-        <v>90</v>
-      </c>
-      <c r="E11" t="s">
-        <v>477</v>
+        <v>462</v>
+      </c>
+      <c r="C11" s="201">
+        <v>6.5</v>
+      </c>
+      <c r="D11" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B12" t="s">
-        <v>468</v>
-      </c>
-      <c r="C12">
-        <v>6.3</v>
-      </c>
-      <c r="D12">
-        <v>90</v>
+        <v>463</v>
+      </c>
+      <c r="C12" s="201">
+        <v>8.4</v>
+      </c>
+      <c r="D12" t="s">
+        <v>465</v>
+      </c>
+      <c r="E12" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="B13" t="s">
-        <v>470</v>
-      </c>
-      <c r="C13">
-        <v>6.3</v>
-      </c>
+        <v>474</v>
+      </c>
+      <c r="C13" s="201"/>
       <c r="D13" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="B14" t="s">
-        <v>472</v>
-      </c>
-      <c r="C14">
-        <v>6.7</v>
+        <v>466</v>
+      </c>
+      <c r="C14" s="201">
+        <v>6.3</v>
       </c>
       <c r="D14" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -64318,39 +64370,39 @@
       <c r="B15" t="s">
         <v>473</v>
       </c>
-      <c r="C15">
-        <v>6</v>
+      <c r="C15" s="201">
+        <v>6.3</v>
       </c>
       <c r="D15" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="B16" t="s">
-        <v>474</v>
-      </c>
-      <c r="C16">
-        <v>6.2</v>
+        <v>472</v>
+      </c>
+      <c r="C16" s="201">
+        <v>6.6</v>
       </c>
       <c r="D16" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="B17" t="s">
-        <v>475</v>
-      </c>
-      <c r="C17">
-        <v>6.3</v>
+        <v>468</v>
+      </c>
+      <c r="C17" s="201">
+        <v>6.7</v>
       </c>
       <c r="D17" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
     </row>
   </sheetData>
@@ -64377,24 +64429,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="206" t="s">
+      <c r="A1" s="202" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="328"/>
-      <c r="C1" s="329" t="s">
+      <c r="B1" s="325"/>
+      <c r="C1" s="326" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="209"/>
-      <c r="E1" s="330"/>
-      <c r="H1" s="206" t="s">
+      <c r="D1" s="205"/>
+      <c r="E1" s="327"/>
+      <c r="H1" s="202" t="s">
         <v>47</v>
       </c>
-      <c r="I1" s="328"/>
-      <c r="J1" s="329" t="s">
+      <c r="I1" s="325"/>
+      <c r="J1" s="326" t="s">
         <v>44</v>
       </c>
-      <c r="K1" s="209"/>
-      <c r="L1" s="330"/>
+      <c r="K1" s="205"/>
+      <c r="L1" s="327"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -65374,11 +65426,11 @@
       </c>
       <c r="K30" s="9">
         <f>'Apps &amp; Goals'!T10</f>
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L30" s="14">
         <f>J30/K30</f>
-        <v>0.2634920634920635</v>
+        <v>0.26265822784810128</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
@@ -65482,9 +65534,9 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="210"/>
-      <c r="G1" s="210"/>
-      <c r="H1" s="210"/>
+      <c r="F1" s="206"/>
+      <c r="G1" s="206"/>
+      <c r="H1" s="206"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -65508,36 +65560,36 @@
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="5"/>
-      <c r="E2" s="206" t="s">
+      <c r="E2" s="202" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="207"/>
-      <c r="G2" s="208"/>
-      <c r="H2" s="211" t="s">
+      <c r="F2" s="203"/>
+      <c r="G2" s="204"/>
+      <c r="H2" s="207" t="s">
         <v>120</v>
       </c>
-      <c r="I2" s="212"/>
-      <c r="J2" s="213"/>
-      <c r="K2" s="206" t="s">
+      <c r="I2" s="208"/>
+      <c r="J2" s="209"/>
+      <c r="K2" s="202" t="s">
         <v>108</v>
       </c>
-      <c r="L2" s="207"/>
-      <c r="M2" s="208"/>
-      <c r="N2" s="211" t="s">
+      <c r="L2" s="203"/>
+      <c r="M2" s="204"/>
+      <c r="N2" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="O2" s="212"/>
-      <c r="P2" s="213"/>
-      <c r="Q2" s="206" t="s">
+      <c r="O2" s="208"/>
+      <c r="P2" s="209"/>
+      <c r="Q2" s="202" t="s">
         <v>39</v>
       </c>
-      <c r="R2" s="207"/>
-      <c r="S2" s="208"/>
-      <c r="T2" s="209" t="s">
+      <c r="R2" s="203"/>
+      <c r="S2" s="204"/>
+      <c r="T2" s="205" t="s">
         <v>7</v>
       </c>
-      <c r="U2" s="209"/>
-      <c r="V2" s="209"/>
+      <c r="U2" s="205"/>
+      <c r="V2" s="205"/>
       <c r="Z2" s="125">
         <v>46269</v>
       </c>
@@ -65606,7 +65658,7 @@
         <v>395</v>
       </c>
       <c r="W3" s="200" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
@@ -65624,7 +65676,7 @@
       </c>
       <c r="E4" s="6">
         <f>'#'!J6</f>
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F4" s="6">
         <f>'#'!K6</f>
@@ -65684,7 +65736,7 @@
       </c>
       <c r="T4" s="2">
         <f t="shared" ref="T4:V4" si="0">SUM(E4,H4,K4,N4,Q4)</f>
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="U4" s="2">
         <f t="shared" ref="U4" si="1">SUM(F4,I4,L4,O4,R4)</f>
@@ -65882,7 +65934,7 @@
       </c>
       <c r="E7" s="6">
         <f>'#'!J9</f>
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F7" s="6">
         <f>'#'!K9</f>
@@ -65942,7 +65994,7 @@
       </c>
       <c r="T7" s="2">
         <f t="shared" si="2"/>
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="U7" s="2">
         <f t="shared" si="3"/>
@@ -65968,7 +66020,7 @@
       </c>
       <c r="E8" s="6">
         <f>'#'!J10</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F8" s="6">
         <f>'#'!K10</f>
@@ -66028,7 +66080,7 @@
       </c>
       <c r="T8" s="2">
         <f t="shared" si="2"/>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="U8" s="2">
         <f t="shared" si="3"/>
@@ -66054,7 +66106,7 @@
       </c>
       <c r="E9" s="6">
         <f>'#'!J11</f>
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F9" s="6">
         <f>'#'!K11</f>
@@ -66114,7 +66166,7 @@
       </c>
       <c r="T9" s="2">
         <f t="shared" si="2"/>
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="U9" s="2">
         <f t="shared" si="3"/>
@@ -66140,7 +66192,7 @@
       </c>
       <c r="E10" s="6">
         <f>'#'!J12</f>
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F10" s="6">
         <f>'#'!K12</f>
@@ -66200,7 +66252,7 @@
       </c>
       <c r="T10" s="2">
         <f t="shared" si="2"/>
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="U10" s="2">
         <f t="shared" si="3"/>
@@ -66226,11 +66278,11 @@
       </c>
       <c r="E11" s="6">
         <f>'#'!J13</f>
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F11" s="6">
         <f>'#'!K13</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G11" s="6">
         <f>'#'!L13</f>
@@ -66286,11 +66338,11 @@
       </c>
       <c r="T11" s="2">
         <f t="shared" si="2"/>
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="U11" s="2">
         <f t="shared" si="3"/>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="V11" s="2">
         <f t="shared" si="4"/>
@@ -66570,7 +66622,7 @@
       </c>
       <c r="E15" s="6">
         <f>'#'!J17</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F15" s="6">
         <f>'#'!K17</f>
@@ -66630,7 +66682,7 @@
       </c>
       <c r="T15" s="2">
         <f t="shared" si="2"/>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="U15" s="2">
         <f t="shared" si="3"/>
@@ -66652,11 +66704,11 @@
         <v>352</v>
       </c>
       <c r="D16" s="149" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="E16" s="6">
         <f>'#'!J18</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" s="6">
         <f>'#'!K18</f>
@@ -66716,7 +66768,7 @@
       </c>
       <c r="T16" s="2">
         <f t="shared" ref="T16:T37" si="5">SUM(E16,H16,K16,N16,Q16)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U16" s="2">
         <f t="shared" ref="U16:U37" si="6">SUM(F16,I16,L16,O16,R16)</f>
@@ -66742,7 +66794,7 @@
       </c>
       <c r="E17" s="6">
         <f>'#'!J19</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17" s="6">
         <f>'#'!K19</f>
@@ -66750,7 +66802,7 @@
       </c>
       <c r="G17" s="6">
         <f>'#'!L19</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" s="4">
         <f>'#'!V19</f>
@@ -66802,7 +66854,7 @@
       </c>
       <c r="T17" s="2">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U17" s="2">
         <f t="shared" si="6"/>
@@ -66810,7 +66862,7 @@
       </c>
       <c r="V17" s="2">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.25">
@@ -66828,7 +66880,7 @@
       </c>
       <c r="E18" s="6">
         <f>'#'!J20</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F18" s="6">
         <f>'#'!K20</f>
@@ -66888,7 +66940,7 @@
       </c>
       <c r="T18" s="2">
         <f t="shared" si="5"/>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="U18" s="2">
         <f t="shared" si="6"/>
@@ -66985,7 +67037,7 @@
         <v>2</v>
       </c>
       <c r="W19" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.25">
@@ -67003,7 +67055,7 @@
       </c>
       <c r="E20" s="6">
         <f>'#'!J22</f>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F20" s="6">
         <f>'#'!K22</f>
@@ -67063,7 +67115,7 @@
       </c>
       <c r="T20" s="2">
         <f t="shared" si="5"/>
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="U20" s="2">
         <f t="shared" si="6"/>
@@ -67089,11 +67141,11 @@
       </c>
       <c r="E21" s="6">
         <f>'#'!J23</f>
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F21" s="6">
         <f>'#'!K23</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G21" s="6">
         <f>'#'!L23</f>
@@ -67149,11 +67201,11 @@
       </c>
       <c r="T21" s="2">
         <f t="shared" si="5"/>
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="U21" s="2">
         <f t="shared" si="6"/>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="V21" s="2">
         <f t="shared" si="7"/>
@@ -67261,7 +67313,7 @@
       </c>
       <c r="E23" s="6">
         <f>'#'!J25</f>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F23" s="6">
         <f>'#'!K25</f>
@@ -67321,7 +67373,7 @@
       </c>
       <c r="T23" s="2">
         <f t="shared" si="5"/>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="U23" s="2">
         <f t="shared" si="6"/>
@@ -67418,7 +67470,7 @@
         <v>0</v>
       </c>
       <c r="W24" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.25">
@@ -67436,7 +67488,7 @@
       </c>
       <c r="E25" s="6">
         <f>'#'!J27</f>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F25" s="6">
         <f>'#'!K27</f>
@@ -67496,7 +67548,7 @@
       </c>
       <c r="T25" s="2">
         <f t="shared" si="5"/>
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="U25" s="2">
         <f t="shared" si="6"/>
@@ -67694,7 +67746,7 @@
       </c>
       <c r="E28" s="6">
         <f>'#'!J30</f>
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F28" s="6">
         <f>'#'!K30</f>
@@ -67702,7 +67754,7 @@
       </c>
       <c r="G28" s="6">
         <f>'#'!L30</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H28" s="4">
         <f>'#'!V30</f>
@@ -67754,7 +67806,7 @@
       </c>
       <c r="T28" s="2">
         <f t="shared" si="5"/>
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="U28" s="2">
         <f t="shared" si="6"/>
@@ -67762,7 +67814,7 @@
       </c>
       <c r="V28" s="2">
         <f t="shared" si="7"/>
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.25">
@@ -68023,7 +68075,7 @@
         <v>0</v>
       </c>
       <c r="W31" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
     </row>
     <row r="32" spans="1:23" x14ac:dyDescent="0.25">
@@ -68041,7 +68093,7 @@
       </c>
       <c r="E32" s="6">
         <f>'#'!J34</f>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F32" s="6">
         <f>'#'!K34</f>
@@ -68101,7 +68153,7 @@
       </c>
       <c r="T32" s="2">
         <f t="shared" si="5"/>
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="U32" s="2">
         <f t="shared" si="6"/>
@@ -68198,7 +68250,7 @@
         <v>0</v>
       </c>
       <c r="W33" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.25">
@@ -68635,30 +68687,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="204" t="s">
+      <c r="D2" s="212" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="204"/>
-      <c r="F2" s="205" t="s">
+      <c r="E2" s="212"/>
+      <c r="F2" s="213" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="205"/>
-      <c r="H2" s="204" t="s">
+      <c r="G2" s="213"/>
+      <c r="H2" s="212" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="204"/>
-      <c r="J2" s="205" t="s">
+      <c r="I2" s="212"/>
+      <c r="J2" s="213" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="205"/>
-      <c r="L2" s="204" t="s">
+      <c r="K2" s="213"/>
+      <c r="L2" s="212" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="204"/>
-      <c r="N2" s="209" t="s">
+      <c r="M2" s="212"/>
+      <c r="N2" s="205" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="209"/>
+      <c r="O2" s="205"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -70655,30 +70707,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="204" t="s">
+      <c r="D2" s="212" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="204"/>
-      <c r="F2" s="205" t="s">
+      <c r="E2" s="212"/>
+      <c r="F2" s="213" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="205"/>
-      <c r="H2" s="204" t="s">
+      <c r="G2" s="213"/>
+      <c r="H2" s="212" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="204"/>
-      <c r="J2" s="205" t="s">
+      <c r="I2" s="212"/>
+      <c r="J2" s="213" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="205"/>
-      <c r="L2" s="204" t="s">
+      <c r="K2" s="213"/>
+      <c r="L2" s="212" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="204"/>
-      <c r="N2" s="209" t="s">
+      <c r="M2" s="212"/>
+      <c r="N2" s="205" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="209"/>
+      <c r="O2" s="205"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -72612,30 +72664,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="204" t="s">
+      <c r="D2" s="212" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="204"/>
-      <c r="F2" s="205" t="s">
+      <c r="E2" s="212"/>
+      <c r="F2" s="213" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="205"/>
-      <c r="H2" s="204" t="s">
+      <c r="G2" s="213"/>
+      <c r="H2" s="212" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="204"/>
-      <c r="J2" s="205" t="s">
+      <c r="I2" s="212"/>
+      <c r="J2" s="213" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="205"/>
-      <c r="L2" s="204" t="s">
+      <c r="K2" s="213"/>
+      <c r="L2" s="212" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="204"/>
-      <c r="N2" s="209" t="s">
+      <c r="M2" s="212"/>
+      <c r="N2" s="205" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="209"/>
+      <c r="O2" s="205"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -74660,30 +74712,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="204" t="s">
+      <c r="D2" s="212" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="204"/>
-      <c r="F2" s="205" t="s">
+      <c r="E2" s="212"/>
+      <c r="F2" s="213" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="205"/>
-      <c r="H2" s="204" t="s">
+      <c r="G2" s="213"/>
+      <c r="H2" s="212" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="204"/>
-      <c r="J2" s="205" t="s">
+      <c r="I2" s="212"/>
+      <c r="J2" s="213" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="205"/>
-      <c r="L2" s="204" t="s">
+      <c r="K2" s="213"/>
+      <c r="L2" s="212" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="204"/>
-      <c r="N2" s="209" t="s">
+      <c r="M2" s="212"/>
+      <c r="N2" s="205" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="209"/>
+      <c r="O2" s="205"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -76368,30 +76420,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="204" t="s">
+      <c r="C2" s="212" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="204"/>
-      <c r="E2" s="205" t="s">
+      <c r="D2" s="212"/>
+      <c r="E2" s="213" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="205"/>
-      <c r="G2" s="204" t="s">
+      <c r="F2" s="213"/>
+      <c r="G2" s="212" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="204"/>
-      <c r="I2" s="205" t="s">
+      <c r="H2" s="212"/>
+      <c r="I2" s="213" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="205"/>
-      <c r="K2" s="204" t="s">
+      <c r="J2" s="213"/>
+      <c r="K2" s="212" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="204"/>
-      <c r="M2" s="209" t="s">
+      <c r="L2" s="212"/>
+      <c r="M2" s="205" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="209"/>
+      <c r="N2" s="205"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -78153,30 +78205,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="204" t="s">
+      <c r="C2" s="212" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="204"/>
-      <c r="E2" s="205" t="s">
+      <c r="D2" s="212"/>
+      <c r="E2" s="213" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="205"/>
-      <c r="G2" s="204" t="s">
+      <c r="F2" s="213"/>
+      <c r="G2" s="212" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="204"/>
-      <c r="I2" s="205" t="s">
+      <c r="H2" s="212"/>
+      <c r="I2" s="213" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="205"/>
-      <c r="K2" s="204" t="s">
+      <c r="J2" s="213"/>
+      <c r="K2" s="212" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="204"/>
-      <c r="M2" s="209" t="s">
+      <c r="L2" s="212"/>
+      <c r="M2" s="205" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="209"/>
+      <c r="N2" s="205"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">

--- a/data/arsenal_stats.xlsx
+++ b/data/arsenal_stats.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bungeltd-my.sharepoint.com/personal/przemyslaw_iskra_bunge_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8244" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{081A4EE6-617B-4068-A6F2-68A91462960B}"/>
+  <xr:revisionPtr revIDLastSave="8311" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E05B72E1-9ECF-43E4-9295-08ACD808352C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="799" firstSheet="1" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2257" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2256" uniqueCount="480">
   <si>
     <t>Arsenal FC squad statistics</t>
   </si>
@@ -1294,9 +1294,6 @@
     <t>H/A</t>
   </si>
   <si>
-    <t>Emirates Stadium (H)</t>
-  </si>
-  <si>
     <t>Coventry City</t>
   </si>
   <si>
@@ -1393,9 +1390,6 @@
     <t>−5</t>
   </si>
   <si>
-    <t>06.09.2026</t>
-  </si>
-  <si>
     <t>GEORGE GRAHAM</t>
   </si>
   <si>
@@ -1447,16 +1441,10 @@
     <t>Raya</t>
   </si>
   <si>
-    <t>Calafiori</t>
-  </si>
-  <si>
     <t>Gabriel</t>
   </si>
   <si>
     <t>White</t>
-  </si>
-  <si>
-    <t>Lewis-Skelly</t>
   </si>
   <si>
     <t>Rice</t>
@@ -1507,9 +1495,6 @@
     <t>Madueke</t>
   </si>
   <si>
-    <t>2-1</t>
-  </si>
-  <si>
     <t>−3</t>
   </si>
   <si>
@@ -1520,6 +1505,21 @@
   </si>
   <si>
     <t>Stadio Diego Armando Maradona (A)</t>
+  </si>
+  <si>
+    <t>1-0</t>
+  </si>
+  <si>
+    <t>12.09.2026</t>
+  </si>
+  <si>
+    <t>Stadium of Light (A)</t>
+  </si>
+  <si>
+    <t>Eze</t>
+  </si>
+  <si>
+    <t>Bruno</t>
   </si>
 </sst>
 </file>
@@ -2649,7 +2649,7 @@
     <xf numFmtId="0" fontId="7" fillId="9" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="17" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="331">
+  <cellXfs count="330">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3038,6 +3038,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3047,12 +3053,6 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3060,6 +3060,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3074,14 +3077,8 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3092,23 +3089,23 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="54" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3146,6 +3143,15 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="28" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3153,6 +3159,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="61" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="10" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="37" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="11" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3245,31 +3272,67 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="61" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="10" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="37" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="11" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="54" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3347,63 +3410,6 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3414,13 +3420,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
@@ -4624,7 +4623,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="32"/>
                 <c:pt idx="0">
-                  <c:v>4</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -4633,22 +4632,22 @@
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>3</c:v>
-                </c:pt>
                 <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -4657,25 +4656,25 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="13">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>3</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>4</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>0</c:v>
@@ -4687,16 +4686,16 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>4</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>2</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>4</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>0</c:v>
@@ -4875,7 +4874,7 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -6464,7 +6463,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{BBD2B189-A30D-46C5-BA22-BABC4E570F61}" type="CELLRANGE">
+                    <a:fld id="{D109F790-1F09-405B-AFA5-DA6C0DE92235}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6498,7 +6497,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{867B5695-9842-4520-A406-ABF7043751F9}" type="CELLRANGE">
+                    <a:fld id="{AEFDBFE5-07DF-4F9E-B05D-BECF46F7AA36}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6532,7 +6531,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{CD184A09-31FD-4705-A0B6-B34E9815EE9C}" type="CELLRANGE">
+                    <a:fld id="{9A3CC0EC-D1CA-42E9-96CF-075A03F56F48}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6566,7 +6565,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F51BB28D-FE82-43CB-8492-66DA0EB1C159}" type="CELLRANGE">
+                    <a:fld id="{C82B796E-DBE7-48BC-A6BB-71704D467F70}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6600,7 +6599,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8130226E-9E9B-4C6D-AD60-9FB007F60840}" type="CELLRANGE">
+                    <a:fld id="{1926E432-A605-43C8-9C13-34F50B46F216}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6634,7 +6633,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{FCFD2949-E0EE-4C28-AAF7-64677AE85E23}" type="CELLRANGE">
+                    <a:fld id="{16357A7A-F1F2-41A9-93D8-0A123DABD418}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6668,7 +6667,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F34007A7-824C-4A7B-8485-AE2E27D134B7}" type="CELLRANGE">
+                    <a:fld id="{C5CE56F8-B006-4DC0-AA9D-B58D7670F66E}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6702,7 +6701,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F3BF0278-F322-4197-9378-895D1C2BDC7B}" type="CELLRANGE">
+                    <a:fld id="{CD18CBE0-548D-4D6A-A551-F46BE8822137}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6736,7 +6735,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{22D83495-8E80-4D15-AE2C-682325F7CBAA}" type="CELLRANGE">
+                    <a:fld id="{83956FB6-3A7F-4889-A43B-1D4F67ED0732}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6770,7 +6769,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{DBF8691F-6A1B-444B-B28B-F5AC8C275F36}" type="CELLRANGE">
+                    <a:fld id="{446B1998-46B8-453F-8307-A3461DA49DDD}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6804,7 +6803,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E10B2AB4-7FDA-4D57-B95F-48656F926D1A}" type="CELLRANGE">
+                    <a:fld id="{30937C9F-DD94-4948-87F8-D5EFF7039B90}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6838,7 +6837,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C58472E1-2634-4C6B-92F2-758C6F4F79CB}" type="CELLRANGE">
+                    <a:fld id="{48A4A887-B10C-4FE4-A3B7-291C007794EE}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6887,7 +6886,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{B203CEB0-15E7-4E72-9556-673B2EA6EC56}" type="CELLRANGE">
+                    <a:fld id="{B27544F2-822D-4388-B063-2452C038185F}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr>
                         <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
@@ -6946,7 +6945,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A53CD454-C59B-4F46-B29C-0756287872AE}" type="CELLRANGE">
+                    <a:fld id="{C6FFDFA5-FA6C-4E59-B840-9147BB498B81}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6980,7 +6979,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2C74B345-F96E-4093-91FF-566EEFFC679A}" type="CELLRANGE">
+                    <a:fld id="{6525DAAB-E3BE-4BDE-BD89-AC5B87A9A731}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7014,7 +7013,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E51F1051-D723-4A91-9ED6-2AEE3CEEC3EC}" type="CELLRANGE">
+                    <a:fld id="{7832C286-51F3-4E55-9273-6229D17C05B9}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7048,7 +7047,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{28DA3CCE-E8CE-4EF9-B6B0-B1D523F50408}" type="CELLRANGE">
+                    <a:fld id="{5805233C-FB9E-4F5C-BBCA-34CCF8E39D3D}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7226,22 +7225,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>194</c:v>
+                  <c:v>195</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>42</c:v>
+                  <c:v>43</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>265</c:v>
+                  <c:v>266</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>316</c:v>
+                  <c:v>317</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>238</c:v>
+                  <c:v>239</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>55</c:v>
+                  <c:v>56</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>95</c:v>
@@ -7250,25 +7249,25 @@
                   <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>57</c:v>
+                  <c:v>58</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>4</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>45</c:v>
+                  <c:v>46</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>51</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>81</c:v>
+                  <c:v>82</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>115</c:v>
+                  <c:v>116</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>0</c:v>
@@ -7301,7 +7300,7 @@
                   <c:v>83</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>45</c:v>
+                  <c:v>46</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>10</c:v>
@@ -7528,7 +7527,7 @@
                         <c:v>83</c:v>
                       </c:pt>
                       <c:pt idx="4">
-                        <c:v>45</c:v>
+                        <c:v>46</c:v>
                       </c:pt>
                       <c:pt idx="5">
                         <c:v>10</c:v>
@@ -14184,30 +14183,30 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
       <c r="B1" s="5"/>
-      <c r="C1" s="212" t="s">
+      <c r="C1" s="213" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="212"/>
-      <c r="E1" s="213" t="s">
+      <c r="D1" s="213"/>
+      <c r="E1" s="214" t="s">
         <v>120</v>
       </c>
-      <c r="F1" s="213"/>
-      <c r="G1" s="212" t="s">
+      <c r="F1" s="214"/>
+      <c r="G1" s="213" t="s">
         <v>108</v>
       </c>
-      <c r="H1" s="212"/>
-      <c r="I1" s="213" t="s">
+      <c r="H1" s="213"/>
+      <c r="I1" s="214" t="s">
         <v>110</v>
       </c>
-      <c r="J1" s="213"/>
-      <c r="K1" s="212" t="s">
+      <c r="J1" s="214"/>
+      <c r="K1" s="213" t="s">
         <v>39</v>
       </c>
-      <c r="L1" s="212"/>
-      <c r="M1" s="210" t="s">
+      <c r="L1" s="213"/>
+      <c r="M1" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="211"/>
+      <c r="N1" s="212"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -15914,30 +15913,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="212" t="s">
+      <c r="C2" s="213" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="212"/>
-      <c r="E2" s="213" t="s">
+      <c r="D2" s="213"/>
+      <c r="E2" s="214" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="213"/>
-      <c r="G2" s="212" t="s">
+      <c r="F2" s="214"/>
+      <c r="G2" s="213" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="212"/>
-      <c r="I2" s="213" t="s">
+      <c r="H2" s="213"/>
+      <c r="I2" s="214" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="213"/>
-      <c r="K2" s="212" t="s">
+      <c r="J2" s="214"/>
+      <c r="K2" s="213" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="212"/>
-      <c r="M2" s="205" t="s">
+      <c r="L2" s="213"/>
+      <c r="M2" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="205"/>
+      <c r="N2" s="210"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -17741,30 +17740,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="212" t="s">
+      <c r="C2" s="213" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="212"/>
-      <c r="E2" s="213" t="s">
+      <c r="D2" s="213"/>
+      <c r="E2" s="214" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="213"/>
-      <c r="G2" s="212" t="s">
+      <c r="F2" s="214"/>
+      <c r="G2" s="213" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="212"/>
-      <c r="I2" s="213" t="s">
+      <c r="H2" s="213"/>
+      <c r="I2" s="214" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="213"/>
-      <c r="K2" s="212" t="s">
+      <c r="J2" s="214"/>
+      <c r="K2" s="213" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="212"/>
-      <c r="M2" s="205" t="s">
+      <c r="L2" s="213"/>
+      <c r="M2" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="205"/>
+      <c r="N2" s="210"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -19431,30 +19430,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="212" t="s">
+      <c r="C2" s="213" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="212"/>
-      <c r="E2" s="213" t="s">
+      <c r="D2" s="213"/>
+      <c r="E2" s="214" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="213"/>
-      <c r="G2" s="212" t="s">
+      <c r="F2" s="214"/>
+      <c r="G2" s="213" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="212"/>
-      <c r="I2" s="213" t="s">
+      <c r="H2" s="213"/>
+      <c r="I2" s="214" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="213"/>
-      <c r="K2" s="212" t="s">
+      <c r="J2" s="214"/>
+      <c r="K2" s="213" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="212"/>
-      <c r="M2" s="205" t="s">
+      <c r="L2" s="213"/>
+      <c r="M2" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="205"/>
+      <c r="N2" s="210"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -21257,30 +21256,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="212" t="s">
+      <c r="C2" s="213" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="212"/>
-      <c r="E2" s="213" t="s">
+      <c r="D2" s="213"/>
+      <c r="E2" s="214" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="213"/>
-      <c r="G2" s="212" t="s">
+      <c r="F2" s="214"/>
+      <c r="G2" s="213" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="212"/>
-      <c r="I2" s="213" t="s">
+      <c r="H2" s="213"/>
+      <c r="I2" s="214" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="213"/>
-      <c r="K2" s="212" t="s">
+      <c r="J2" s="214"/>
+      <c r="K2" s="213" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="212"/>
-      <c r="M2" s="205" t="s">
+      <c r="L2" s="213"/>
+      <c r="M2" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="205"/>
+      <c r="N2" s="210"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -23129,36 +23128,36 @@
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="202" t="s">
+      <c r="C2" s="204" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="203"/>
-      <c r="E2" s="204"/>
+      <c r="D2" s="205"/>
+      <c r="E2" s="206"/>
       <c r="F2" s="207" t="s">
         <v>120</v>
       </c>
       <c r="G2" s="208"/>
       <c r="H2" s="209"/>
-      <c r="I2" s="202" t="s">
+      <c r="I2" s="204" t="s">
         <v>108</v>
       </c>
-      <c r="J2" s="203"/>
-      <c r="K2" s="204"/>
+      <c r="J2" s="205"/>
+      <c r="K2" s="206"/>
       <c r="L2" s="207" t="s">
         <v>110</v>
       </c>
       <c r="M2" s="208"/>
       <c r="N2" s="209"/>
-      <c r="O2" s="202" t="s">
+      <c r="O2" s="204" t="s">
         <v>39</v>
       </c>
-      <c r="P2" s="203"/>
-      <c r="Q2" s="204"/>
-      <c r="R2" s="205" t="s">
+      <c r="P2" s="205"/>
+      <c r="Q2" s="206"/>
+      <c r="R2" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="S2" s="205"/>
-      <c r="T2" s="205"/>
+      <c r="S2" s="210"/>
+      <c r="T2" s="210"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -23243,7 +23242,7 @@
       </c>
       <c r="F4" s="4">
         <f>Europe!C4</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="4">
         <f>Europe!D4</f>
@@ -23291,7 +23290,7 @@
       </c>
       <c r="R4" s="2">
         <f>SUM(C4,F4,I4,L4,O4)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S4" s="2">
         <f t="shared" ref="S4:T4" si="0">SUM(D4,G4,J4,M4,P4)</f>
@@ -23485,7 +23484,7 @@
       </c>
       <c r="F7" s="4">
         <f>Europe!C7</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="4">
         <f>Europe!D7</f>
@@ -23533,7 +23532,7 @@
       </c>
       <c r="R7" s="2">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S7" s="2">
         <f t="shared" si="2"/>
@@ -23566,7 +23565,7 @@
       </c>
       <c r="F8" s="4">
         <f>Europe!C8</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" s="4">
         <f>Europe!D8</f>
@@ -23614,7 +23613,7 @@
       </c>
       <c r="R8" s="2">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S8" s="2">
         <f t="shared" si="2"/>
@@ -23647,7 +23646,7 @@
       </c>
       <c r="F9" s="4">
         <f>Europe!C9</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" s="4">
         <f>Europe!D9</f>
@@ -23695,7 +23694,7 @@
       </c>
       <c r="R9" s="2">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S9" s="2">
         <f t="shared" si="2"/>
@@ -23728,7 +23727,7 @@
       </c>
       <c r="F10" s="4">
         <f>Europe!C10</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="4">
         <f>Europe!D10</f>
@@ -23776,7 +23775,7 @@
       </c>
       <c r="R10" s="2">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S10" s="2">
         <f t="shared" si="2"/>
@@ -23809,11 +23808,11 @@
       </c>
       <c r="F11" s="4">
         <f>Europe!C11</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="4">
         <f>Europe!D11</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="4">
         <f>Europe!E11</f>
@@ -23857,11 +23856,11 @@
       </c>
       <c r="R11" s="2">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S11" s="2">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T11" s="2">
         <f t="shared" si="3"/>
@@ -23890,7 +23889,7 @@
       </c>
       <c r="F12" s="4">
         <f>Europe!C12</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" s="4">
         <f>Europe!D12</f>
@@ -23938,7 +23937,7 @@
       </c>
       <c r="R12" s="2">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S12" s="2">
         <f t="shared" si="2"/>
@@ -24133,7 +24132,7 @@
       </c>
       <c r="F15" s="4">
         <f>Europe!C15</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" s="4">
         <f>Europe!D15</f>
@@ -24181,7 +24180,7 @@
       </c>
       <c r="R15" s="2">
         <f>SUM(C15,F15,I15,L15,O15)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S15" s="2">
         <f>SUM(D15,G15,J15,M15,P15)</f>
@@ -24198,7 +24197,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="149" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C16" s="6">
         <f>'Premier League'!C16</f>
@@ -24214,7 +24213,7 @@
       </c>
       <c r="F16" s="4">
         <f>Europe!C16</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" s="4">
         <f>Europe!D16</f>
@@ -24262,7 +24261,7 @@
       </c>
       <c r="R16" s="2">
         <f t="shared" ref="R16:R37" si="4">SUM(C16,F16,I16,L16,O16)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S16" s="2">
         <f t="shared" ref="S16:S37" si="5">SUM(D16,G16,J16,M16,P16)</f>
@@ -24295,7 +24294,7 @@
       </c>
       <c r="F17" s="4">
         <f>Europe!C17</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" s="4">
         <f>Europe!D17</f>
@@ -24303,7 +24302,7 @@
       </c>
       <c r="H17" s="4">
         <f>Europe!E17</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" s="6">
         <f>'FA Cup'!C17</f>
@@ -24343,7 +24342,7 @@
       </c>
       <c r="R17" s="2">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S17" s="2">
         <f t="shared" si="5"/>
@@ -24351,7 +24350,7 @@
       </c>
       <c r="T17" s="2">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V17" s="55"/>
     </row>
@@ -24376,7 +24375,7 @@
       </c>
       <c r="F18" s="4">
         <f>Europe!C18</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" s="4">
         <f>Europe!D18</f>
@@ -24424,7 +24423,7 @@
       </c>
       <c r="R18" s="2">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S18" s="2">
         <f t="shared" si="5"/>
@@ -24536,7 +24535,7 @@
       </c>
       <c r="F20" s="4">
         <f>Europe!C20</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" s="4">
         <f>Europe!D20</f>
@@ -24584,7 +24583,7 @@
       </c>
       <c r="R20" s="2">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S20" s="2">
         <f t="shared" si="5"/>
@@ -24616,7 +24615,7 @@
       </c>
       <c r="F21" s="4">
         <f>Europe!C21</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" s="4">
         <f>Europe!D21</f>
@@ -24664,7 +24663,7 @@
       </c>
       <c r="R21" s="2">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S21" s="2">
         <f t="shared" si="5"/>
@@ -24940,7 +24939,7 @@
       </c>
       <c r="F25" s="4">
         <f>Europe!C25</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" s="4">
         <f>Europe!D25</f>
@@ -24988,7 +24987,7 @@
       </c>
       <c r="R25" s="2">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S25" s="2">
         <f t="shared" si="5"/>
@@ -25021,7 +25020,7 @@
       </c>
       <c r="F26" s="4">
         <f>Europe!C26</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" s="4">
         <f>Europe!D26</f>
@@ -25069,7 +25068,7 @@
       </c>
       <c r="R26" s="2">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S26" s="2">
         <f t="shared" si="5"/>
@@ -25182,7 +25181,7 @@
       </c>
       <c r="F28" s="4">
         <f>Europe!C28</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" s="4">
         <f>Europe!D28</f>
@@ -25230,7 +25229,7 @@
       </c>
       <c r="R28" s="2">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S28" s="2">
         <f t="shared" si="5"/>
@@ -26017,36 +26016,36 @@
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
       <c r="D1" s="5"/>
-      <c r="E1" s="202" t="s">
+      <c r="E1" s="204" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="203"/>
-      <c r="G1" s="204"/>
+      <c r="F1" s="205"/>
+      <c r="G1" s="206"/>
       <c r="H1" s="207" t="s">
         <v>120</v>
       </c>
       <c r="I1" s="208"/>
       <c r="J1" s="209"/>
-      <c r="K1" s="202" t="s">
+      <c r="K1" s="204" t="s">
         <v>108</v>
       </c>
-      <c r="L1" s="203"/>
-      <c r="M1" s="204"/>
+      <c r="L1" s="205"/>
+      <c r="M1" s="206"/>
       <c r="N1" s="207" t="s">
         <v>110</v>
       </c>
       <c r="O1" s="208"/>
       <c r="P1" s="209"/>
-      <c r="Q1" s="202" t="s">
+      <c r="Q1" s="204" t="s">
         <v>39</v>
       </c>
-      <c r="R1" s="203"/>
-      <c r="S1" s="204"/>
-      <c r="T1" s="205" t="s">
+      <c r="R1" s="205"/>
+      <c r="S1" s="206"/>
+      <c r="T1" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="U1" s="205"/>
-      <c r="V1" s="205"/>
+      <c r="U1" s="210"/>
+      <c r="V1" s="210"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -37620,399 +37619,399 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F1" s="217">
-        <v>1</v>
-      </c>
-      <c r="G1" s="218"/>
-      <c r="H1" s="219"/>
-      <c r="I1" s="217">
+      <c r="F1" s="216">
+        <v>1</v>
+      </c>
+      <c r="G1" s="217"/>
+      <c r="H1" s="218"/>
+      <c r="I1" s="216">
         <v>2</v>
       </c>
-      <c r="J1" s="218"/>
-      <c r="K1" s="219"/>
-      <c r="L1" s="217">
-        <v>3</v>
-      </c>
-      <c r="M1" s="218"/>
-      <c r="N1" s="219"/>
-      <c r="O1" s="217">
+      <c r="J1" s="217"/>
+      <c r="K1" s="218"/>
+      <c r="L1" s="216">
+        <v>3</v>
+      </c>
+      <c r="M1" s="217"/>
+      <c r="N1" s="218"/>
+      <c r="O1" s="216">
         <v>4</v>
       </c>
-      <c r="P1" s="218"/>
-      <c r="Q1" s="219"/>
-      <c r="R1" s="217">
+      <c r="P1" s="217"/>
+      <c r="Q1" s="218"/>
+      <c r="R1" s="216">
         <v>5</v>
       </c>
-      <c r="S1" s="218"/>
-      <c r="T1" s="219"/>
-      <c r="U1" s="217">
+      <c r="S1" s="217"/>
+      <c r="T1" s="218"/>
+      <c r="U1" s="216">
         <v>6</v>
       </c>
-      <c r="V1" s="218"/>
-      <c r="W1" s="219"/>
-      <c r="X1" s="217">
+      <c r="V1" s="217"/>
+      <c r="W1" s="218"/>
+      <c r="X1" s="216">
         <v>7</v>
       </c>
-      <c r="Y1" s="218"/>
-      <c r="Z1" s="219"/>
-      <c r="AA1" s="217">
+      <c r="Y1" s="217"/>
+      <c r="Z1" s="218"/>
+      <c r="AA1" s="216">
         <v>8</v>
       </c>
-      <c r="AB1" s="218"/>
-      <c r="AC1" s="219"/>
-      <c r="AD1" s="217">
+      <c r="AB1" s="217"/>
+      <c r="AC1" s="218"/>
+      <c r="AD1" s="216">
         <v>9</v>
       </c>
-      <c r="AE1" s="218"/>
-      <c r="AF1" s="219"/>
-      <c r="AG1" s="217">
+      <c r="AE1" s="217"/>
+      <c r="AF1" s="218"/>
+      <c r="AG1" s="216">
         <v>10</v>
       </c>
-      <c r="AH1" s="218"/>
-      <c r="AI1" s="219"/>
-      <c r="AJ1" s="217">
+      <c r="AH1" s="217"/>
+      <c r="AI1" s="218"/>
+      <c r="AJ1" s="216">
         <v>11</v>
       </c>
-      <c r="AK1" s="218"/>
-      <c r="AL1" s="219"/>
-      <c r="AM1" s="217">
+      <c r="AK1" s="217"/>
+      <c r="AL1" s="218"/>
+      <c r="AM1" s="216">
         <v>12</v>
       </c>
-      <c r="AN1" s="218"/>
-      <c r="AO1" s="219"/>
-      <c r="AP1" s="217">
+      <c r="AN1" s="217"/>
+      <c r="AO1" s="218"/>
+      <c r="AP1" s="216">
         <v>13</v>
       </c>
-      <c r="AQ1" s="218"/>
-      <c r="AR1" s="219"/>
-      <c r="AS1" s="217">
+      <c r="AQ1" s="217"/>
+      <c r="AR1" s="218"/>
+      <c r="AS1" s="216">
         <v>14</v>
       </c>
-      <c r="AT1" s="218"/>
-      <c r="AU1" s="219"/>
-      <c r="AV1" s="217">
+      <c r="AT1" s="217"/>
+      <c r="AU1" s="218"/>
+      <c r="AV1" s="216">
         <v>15</v>
       </c>
-      <c r="AW1" s="218"/>
-      <c r="AX1" s="219"/>
-      <c r="AY1" s="217">
+      <c r="AW1" s="217"/>
+      <c r="AX1" s="218"/>
+      <c r="AY1" s="216">
         <v>16</v>
       </c>
-      <c r="AZ1" s="218"/>
-      <c r="BA1" s="219"/>
-      <c r="BB1" s="217">
+      <c r="AZ1" s="217"/>
+      <c r="BA1" s="218"/>
+      <c r="BB1" s="216">
         <v>17</v>
       </c>
-      <c r="BC1" s="218"/>
-      <c r="BD1" s="219"/>
-      <c r="BE1" s="217">
+      <c r="BC1" s="217"/>
+      <c r="BD1" s="218"/>
+      <c r="BE1" s="216">
         <v>18</v>
       </c>
-      <c r="BF1" s="218"/>
-      <c r="BG1" s="219"/>
-      <c r="BH1" s="217">
+      <c r="BF1" s="217"/>
+      <c r="BG1" s="218"/>
+      <c r="BH1" s="216">
         <v>19</v>
       </c>
-      <c r="BI1" s="218"/>
-      <c r="BJ1" s="219"/>
-      <c r="BK1" s="217">
+      <c r="BI1" s="217"/>
+      <c r="BJ1" s="218"/>
+      <c r="BK1" s="216">
         <v>20</v>
       </c>
-      <c r="BL1" s="218"/>
-      <c r="BM1" s="219"/>
-      <c r="BN1" s="217">
+      <c r="BL1" s="217"/>
+      <c r="BM1" s="218"/>
+      <c r="BN1" s="216">
         <v>21</v>
       </c>
-      <c r="BO1" s="218"/>
-      <c r="BP1" s="219"/>
-      <c r="BQ1" s="217">
+      <c r="BO1" s="217"/>
+      <c r="BP1" s="218"/>
+      <c r="BQ1" s="216">
         <v>22</v>
       </c>
-      <c r="BR1" s="218"/>
-      <c r="BS1" s="219"/>
-      <c r="BT1" s="217">
+      <c r="BR1" s="217"/>
+      <c r="BS1" s="218"/>
+      <c r="BT1" s="216">
         <v>23</v>
       </c>
-      <c r="BU1" s="218"/>
-      <c r="BV1" s="219"/>
-      <c r="BW1" s="217">
+      <c r="BU1" s="217"/>
+      <c r="BV1" s="218"/>
+      <c r="BW1" s="216">
         <v>24</v>
       </c>
-      <c r="BX1" s="218"/>
-      <c r="BY1" s="219"/>
-      <c r="BZ1" s="217">
+      <c r="BX1" s="217"/>
+      <c r="BY1" s="218"/>
+      <c r="BZ1" s="216">
         <v>25</v>
       </c>
-      <c r="CA1" s="218"/>
-      <c r="CB1" s="219"/>
-      <c r="CC1" s="217">
+      <c r="CA1" s="217"/>
+      <c r="CB1" s="218"/>
+      <c r="CC1" s="216">
         <v>26</v>
       </c>
-      <c r="CD1" s="218"/>
-      <c r="CE1" s="219"/>
-      <c r="CF1" s="217">
+      <c r="CD1" s="217"/>
+      <c r="CE1" s="218"/>
+      <c r="CF1" s="216">
         <v>27</v>
       </c>
-      <c r="CG1" s="218"/>
-      <c r="CH1" s="219"/>
-      <c r="CI1" s="217">
+      <c r="CG1" s="217"/>
+      <c r="CH1" s="218"/>
+      <c r="CI1" s="216">
         <v>28</v>
       </c>
-      <c r="CJ1" s="218"/>
-      <c r="CK1" s="219"/>
-      <c r="CL1" s="217">
+      <c r="CJ1" s="217"/>
+      <c r="CK1" s="218"/>
+      <c r="CL1" s="216">
         <v>29</v>
       </c>
-      <c r="CM1" s="218"/>
-      <c r="CN1" s="219"/>
-      <c r="CO1" s="217">
+      <c r="CM1" s="217"/>
+      <c r="CN1" s="218"/>
+      <c r="CO1" s="216">
         <v>30</v>
       </c>
-      <c r="CP1" s="218"/>
-      <c r="CQ1" s="219"/>
-      <c r="CR1" s="217">
+      <c r="CP1" s="217"/>
+      <c r="CQ1" s="218"/>
+      <c r="CR1" s="216">
         <v>31</v>
       </c>
-      <c r="CS1" s="218"/>
-      <c r="CT1" s="219"/>
-      <c r="CU1" s="217">
+      <c r="CS1" s="217"/>
+      <c r="CT1" s="218"/>
+      <c r="CU1" s="216">
         <v>32</v>
       </c>
-      <c r="CV1" s="218"/>
-      <c r="CW1" s="219"/>
-      <c r="CX1" s="217">
+      <c r="CV1" s="217"/>
+      <c r="CW1" s="218"/>
+      <c r="CX1" s="216">
         <v>33</v>
       </c>
-      <c r="CY1" s="218"/>
-      <c r="CZ1" s="219"/>
-      <c r="DA1" s="217">
+      <c r="CY1" s="217"/>
+      <c r="CZ1" s="218"/>
+      <c r="DA1" s="216">
         <v>34</v>
       </c>
-      <c r="DB1" s="218"/>
-      <c r="DC1" s="219"/>
-      <c r="DD1" s="217">
+      <c r="DB1" s="217"/>
+      <c r="DC1" s="218"/>
+      <c r="DD1" s="216">
         <v>35</v>
       </c>
-      <c r="DE1" s="218"/>
-      <c r="DF1" s="219"/>
-      <c r="DG1" s="217">
+      <c r="DE1" s="217"/>
+      <c r="DF1" s="218"/>
+      <c r="DG1" s="216">
         <v>36</v>
       </c>
-      <c r="DH1" s="218"/>
-      <c r="DI1" s="219"/>
-      <c r="DJ1" s="217">
+      <c r="DH1" s="217"/>
+      <c r="DI1" s="218"/>
+      <c r="DJ1" s="216">
         <v>37</v>
       </c>
-      <c r="DK1" s="218"/>
-      <c r="DL1" s="219"/>
-      <c r="DM1" s="217">
+      <c r="DK1" s="217"/>
+      <c r="DL1" s="218"/>
+      <c r="DM1" s="216">
         <v>38</v>
       </c>
-      <c r="DN1" s="218"/>
-      <c r="DO1" s="219"/>
+      <c r="DN1" s="217"/>
+      <c r="DO1" s="218"/>
     </row>
     <row r="2" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="220" t="s">
+      <c r="C2" s="222" t="s">
         <v>396</v>
       </c>
-      <c r="D2" s="220" t="s">
+      <c r="D2" s="222" t="s">
         <v>397</v>
       </c>
-      <c r="E2" s="220" t="s">
+      <c r="E2" s="222" t="s">
         <v>398</v>
       </c>
-      <c r="F2" s="214" t="s">
+      <c r="F2" s="219" t="s">
         <v>346</v>
       </c>
-      <c r="G2" s="215"/>
-      <c r="H2" s="216"/>
-      <c r="I2" s="214" t="s">
+      <c r="G2" s="220"/>
+      <c r="H2" s="221"/>
+      <c r="I2" s="219" t="s">
         <v>331</v>
       </c>
-      <c r="J2" s="215"/>
-      <c r="K2" s="216"/>
-      <c r="L2" s="214" t="s">
+      <c r="J2" s="220"/>
+      <c r="K2" s="221"/>
+      <c r="L2" s="219" t="s">
         <v>330</v>
       </c>
-      <c r="M2" s="215"/>
-      <c r="N2" s="216"/>
-      <c r="O2" s="214" t="s">
+      <c r="M2" s="220"/>
+      <c r="N2" s="221"/>
+      <c r="O2" s="219" t="s">
         <v>328</v>
       </c>
-      <c r="P2" s="215"/>
-      <c r="Q2" s="216"/>
-      <c r="R2" s="214" t="s">
+      <c r="P2" s="220"/>
+      <c r="Q2" s="221"/>
+      <c r="R2" s="219" t="s">
         <v>335</v>
       </c>
-      <c r="S2" s="215"/>
-      <c r="T2" s="216"/>
-      <c r="U2" s="214" t="s">
+      <c r="S2" s="220"/>
+      <c r="T2" s="221"/>
+      <c r="U2" s="219" t="s">
         <v>320</v>
       </c>
-      <c r="V2" s="215"/>
-      <c r="W2" s="216"/>
-      <c r="X2" s="214" t="s">
+      <c r="V2" s="220"/>
+      <c r="W2" s="221"/>
+      <c r="X2" s="219" t="s">
         <v>337</v>
       </c>
-      <c r="Y2" s="215"/>
-      <c r="Z2" s="216"/>
-      <c r="AA2" s="214" t="s">
+      <c r="Y2" s="220"/>
+      <c r="Z2" s="221"/>
+      <c r="AA2" s="219" t="s">
         <v>334</v>
       </c>
-      <c r="AB2" s="215"/>
-      <c r="AC2" s="216"/>
-      <c r="AD2" s="214" t="s">
+      <c r="AB2" s="220"/>
+      <c r="AC2" s="221"/>
+      <c r="AD2" s="219" t="s">
         <v>321</v>
       </c>
-      <c r="AE2" s="215"/>
-      <c r="AF2" s="216"/>
-      <c r="AG2" s="214" t="s">
+      <c r="AE2" s="220"/>
+      <c r="AF2" s="221"/>
+      <c r="AG2" s="219" t="s">
         <v>347</v>
       </c>
-      <c r="AH2" s="215"/>
-      <c r="AI2" s="216"/>
-      <c r="AJ2" s="214" t="s">
+      <c r="AH2" s="220"/>
+      <c r="AI2" s="221"/>
+      <c r="AJ2" s="219" t="s">
         <v>324</v>
       </c>
-      <c r="AK2" s="215"/>
-      <c r="AL2" s="216"/>
-      <c r="AM2" s="214" t="s">
+      <c r="AK2" s="220"/>
+      <c r="AL2" s="221"/>
+      <c r="AM2" s="219" t="s">
         <v>323</v>
       </c>
-      <c r="AN2" s="215"/>
-      <c r="AO2" s="216"/>
-      <c r="AP2" s="214" t="s">
+      <c r="AN2" s="220"/>
+      <c r="AO2" s="221"/>
+      <c r="AP2" s="219" t="s">
         <v>332</v>
       </c>
-      <c r="AQ2" s="215"/>
-      <c r="AR2" s="216"/>
-      <c r="AS2" s="214" t="s">
+      <c r="AQ2" s="220"/>
+      <c r="AR2" s="221"/>
+      <c r="AS2" s="219" t="s">
         <v>329</v>
       </c>
-      <c r="AT2" s="215"/>
-      <c r="AU2" s="216"/>
-      <c r="AV2" s="214" t="s">
+      <c r="AT2" s="220"/>
+      <c r="AU2" s="221"/>
+      <c r="AV2" s="219" t="s">
         <v>336</v>
       </c>
-      <c r="AW2" s="215"/>
-      <c r="AX2" s="216"/>
-      <c r="AY2" s="214" t="s">
+      <c r="AW2" s="220"/>
+      <c r="AX2" s="221"/>
+      <c r="AY2" s="219" t="s">
         <v>305</v>
       </c>
-      <c r="AZ2" s="215"/>
-      <c r="BA2" s="216"/>
-      <c r="BB2" s="214" t="s">
+      <c r="AZ2" s="220"/>
+      <c r="BA2" s="221"/>
+      <c r="BB2" s="219" t="s">
         <v>326</v>
       </c>
-      <c r="BC2" s="215"/>
-      <c r="BD2" s="216"/>
-      <c r="BE2" s="214" t="s">
+      <c r="BC2" s="220"/>
+      <c r="BD2" s="221"/>
+      <c r="BE2" s="219" t="s">
         <v>325</v>
       </c>
-      <c r="BF2" s="215"/>
-      <c r="BG2" s="216"/>
-      <c r="BH2" s="214" t="s">
+      <c r="BF2" s="220"/>
+      <c r="BG2" s="221"/>
+      <c r="BH2" s="219" t="s">
         <v>348</v>
       </c>
-      <c r="BI2" s="215"/>
-      <c r="BJ2" s="216"/>
-      <c r="BK2" s="214" t="s">
+      <c r="BI2" s="220"/>
+      <c r="BJ2" s="221"/>
+      <c r="BK2" s="219" t="s">
         <v>332</v>
       </c>
-      <c r="BL2" s="215"/>
-      <c r="BM2" s="216"/>
-      <c r="BN2" s="214" t="s">
+      <c r="BL2" s="220"/>
+      <c r="BM2" s="221"/>
+      <c r="BN2" s="219" t="s">
         <v>347</v>
       </c>
-      <c r="BO2" s="215"/>
-      <c r="BP2" s="216"/>
-      <c r="BQ2" s="214" t="s">
+      <c r="BO2" s="220"/>
+      <c r="BP2" s="221"/>
+      <c r="BQ2" s="219" t="s">
         <v>324</v>
       </c>
-      <c r="BR2" s="215"/>
-      <c r="BS2" s="216"/>
-      <c r="BT2" s="214" t="s">
+      <c r="BR2" s="220"/>
+      <c r="BS2" s="221"/>
+      <c r="BT2" s="219" t="s">
         <v>323</v>
       </c>
-      <c r="BU2" s="215"/>
-      <c r="BV2" s="216"/>
-      <c r="BW2" s="214" t="s">
+      <c r="BU2" s="220"/>
+      <c r="BV2" s="221"/>
+      <c r="BW2" s="219" t="s">
         <v>321</v>
       </c>
-      <c r="BX2" s="215"/>
-      <c r="BY2" s="216"/>
-      <c r="BZ2" s="214" t="s">
+      <c r="BX2" s="220"/>
+      <c r="BY2" s="221"/>
+      <c r="BZ2" s="219" t="s">
         <v>348</v>
       </c>
-      <c r="CA2" s="215"/>
-      <c r="CB2" s="216"/>
-      <c r="CC2" s="214" t="s">
+      <c r="CA2" s="220"/>
+      <c r="CB2" s="221"/>
+      <c r="CC2" s="219" t="s">
         <v>325</v>
       </c>
-      <c r="CD2" s="215"/>
-      <c r="CE2" s="216"/>
-      <c r="CF2" s="214" t="s">
+      <c r="CD2" s="220"/>
+      <c r="CE2" s="221"/>
+      <c r="CF2" s="219" t="s">
         <v>305</v>
       </c>
-      <c r="CG2" s="215"/>
-      <c r="CH2" s="216"/>
-      <c r="CI2" s="214" t="s">
+      <c r="CG2" s="220"/>
+      <c r="CH2" s="221"/>
+      <c r="CI2" s="219" t="s">
         <v>326</v>
       </c>
-      <c r="CJ2" s="215"/>
-      <c r="CK2" s="216"/>
-      <c r="CL2" s="214" t="s">
+      <c r="CJ2" s="220"/>
+      <c r="CK2" s="221"/>
+      <c r="CL2" s="219" t="s">
         <v>330</v>
       </c>
-      <c r="CM2" s="215"/>
-      <c r="CN2" s="216"/>
-      <c r="CO2" s="214" t="s">
+      <c r="CM2" s="220"/>
+      <c r="CN2" s="221"/>
+      <c r="CO2" s="219" t="s">
         <v>328</v>
       </c>
-      <c r="CP2" s="215"/>
-      <c r="CQ2" s="216"/>
-      <c r="CR2" s="214" t="s">
+      <c r="CP2" s="220"/>
+      <c r="CQ2" s="221"/>
+      <c r="CR2" s="219" t="s">
         <v>346</v>
       </c>
-      <c r="CS2" s="215"/>
-      <c r="CT2" s="216"/>
-      <c r="CU2" s="214" t="s">
+      <c r="CS2" s="220"/>
+      <c r="CT2" s="221"/>
+      <c r="CU2" s="219" t="s">
         <v>331</v>
       </c>
-      <c r="CV2" s="215"/>
-      <c r="CW2" s="216"/>
-      <c r="CX2" s="214" t="s">
+      <c r="CV2" s="220"/>
+      <c r="CW2" s="221"/>
+      <c r="CX2" s="219" t="s">
         <v>336</v>
       </c>
-      <c r="CY2" s="215"/>
-      <c r="CZ2" s="216"/>
-      <c r="DA2" s="214" t="s">
+      <c r="CY2" s="220"/>
+      <c r="CZ2" s="221"/>
+      <c r="DA2" s="219" t="s">
         <v>329</v>
       </c>
-      <c r="DB2" s="215"/>
-      <c r="DC2" s="216"/>
-      <c r="DD2" s="214" t="s">
+      <c r="DB2" s="220"/>
+      <c r="DC2" s="221"/>
+      <c r="DD2" s="219" t="s">
         <v>320</v>
       </c>
-      <c r="DE2" s="215"/>
-      <c r="DF2" s="216"/>
-      <c r="DG2" s="214" t="s">
+      <c r="DE2" s="220"/>
+      <c r="DF2" s="221"/>
+      <c r="DG2" s="219" t="s">
         <v>337</v>
       </c>
-      <c r="DH2" s="215"/>
-      <c r="DI2" s="216"/>
-      <c r="DJ2" s="214" t="s">
+      <c r="DH2" s="220"/>
+      <c r="DI2" s="221"/>
+      <c r="DJ2" s="219" t="s">
         <v>334</v>
       </c>
-      <c r="DK2" s="215"/>
-      <c r="DL2" s="216"/>
-      <c r="DM2" s="214" t="s">
+      <c r="DK2" s="220"/>
+      <c r="DL2" s="221"/>
+      <c r="DM2" s="219" t="s">
         <v>335</v>
       </c>
-      <c r="DN2" s="215"/>
-      <c r="DO2" s="216"/>
+      <c r="DN2" s="220"/>
+      <c r="DO2" s="221"/>
     </row>
     <row r="3" spans="1:119" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -38021,16 +38020,16 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="221"/>
-      <c r="D3" s="221"/>
-      <c r="E3" s="222"/>
+      <c r="C3" s="224"/>
+      <c r="D3" s="224"/>
+      <c r="E3" s="223"/>
       <c r="F3" s="160" t="s">
         <v>393</v>
       </c>
       <c r="G3" s="161" t="s">
         <v>394</v>
       </c>
-      <c r="H3" s="328" t="s">
+      <c r="H3" s="202" t="s">
         <v>395</v>
       </c>
       <c r="I3" s="160" t="s">
@@ -38048,7 +38047,7 @@
       <c r="M3" s="161" t="s">
         <v>394</v>
       </c>
-      <c r="N3" s="328" t="s">
+      <c r="N3" s="202" t="s">
         <v>395</v>
       </c>
       <c r="O3" s="160" t="s">
@@ -40034,7 +40033,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="149" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C16" s="58">
         <f t="shared" ref="C16:C37" si="4">SUM(F16,I16,L16,O16,R16,U16,X16,AA16,AD16,AG16,AJ16,AM16,AP16,AS16,AV16,AY16,BB16,BE16,BH16,BK16,BN16,BQ16,BT16,BW16,BZ16,CC16,CF16,CI16,CL16,CO16,CR16,CU16,CX16,DA16,DD16,DG16,DJ16,DM16)</f>
@@ -42928,13 +42927,13 @@
       </c>
       <c r="F37" s="146"/>
       <c r="G37" s="163"/>
-      <c r="H37" s="329"/>
+      <c r="H37" s="203"/>
       <c r="I37" s="146"/>
       <c r="J37" s="163"/>
       <c r="K37" s="147"/>
       <c r="L37" s="146"/>
       <c r="M37" s="163"/>
-      <c r="N37" s="329"/>
+      <c r="N37" s="203"/>
       <c r="O37" s="146"/>
       <c r="P37" s="163"/>
       <c r="Q37" s="147"/>
@@ -43506,69 +43505,6 @@
     </row>
   </sheetData>
   <mergeCells count="79">
-    <mergeCell ref="DM1:DO1"/>
-    <mergeCell ref="DM2:DO2"/>
-    <mergeCell ref="DA1:DC1"/>
-    <mergeCell ref="DA2:DC2"/>
-    <mergeCell ref="DD1:DF1"/>
-    <mergeCell ref="DD2:DF2"/>
-    <mergeCell ref="DG1:DI1"/>
-    <mergeCell ref="DG2:DI2"/>
-    <mergeCell ref="CU1:CW1"/>
-    <mergeCell ref="CU2:CW2"/>
-    <mergeCell ref="CX1:CZ1"/>
-    <mergeCell ref="CX2:CZ2"/>
-    <mergeCell ref="DJ1:DL1"/>
-    <mergeCell ref="DJ2:DL2"/>
-    <mergeCell ref="CL1:CN1"/>
-    <mergeCell ref="CL2:CN2"/>
-    <mergeCell ref="CO1:CQ1"/>
-    <mergeCell ref="CO2:CQ2"/>
-    <mergeCell ref="CR1:CT1"/>
-    <mergeCell ref="CR2:CT2"/>
-    <mergeCell ref="CC1:CE1"/>
-    <mergeCell ref="CC2:CE2"/>
-    <mergeCell ref="CF1:CH1"/>
-    <mergeCell ref="CF2:CH2"/>
-    <mergeCell ref="CI1:CK1"/>
-    <mergeCell ref="CI2:CK2"/>
-    <mergeCell ref="BT1:BV1"/>
-    <mergeCell ref="BT2:BV2"/>
-    <mergeCell ref="BW1:BY1"/>
-    <mergeCell ref="BW2:BY2"/>
-    <mergeCell ref="BZ1:CB1"/>
-    <mergeCell ref="BZ2:CB2"/>
-    <mergeCell ref="BK1:BM1"/>
-    <mergeCell ref="BK2:BM2"/>
-    <mergeCell ref="BN1:BP1"/>
-    <mergeCell ref="BN2:BP2"/>
-    <mergeCell ref="BQ1:BS1"/>
-    <mergeCell ref="BQ2:BS2"/>
-    <mergeCell ref="AS1:AU1"/>
-    <mergeCell ref="AS2:AU2"/>
-    <mergeCell ref="AV1:AX1"/>
-    <mergeCell ref="AV2:AX2"/>
-    <mergeCell ref="BH1:BJ1"/>
-    <mergeCell ref="BH2:BJ2"/>
-    <mergeCell ref="AY2:BA2"/>
-    <mergeCell ref="BB2:BD2"/>
-    <mergeCell ref="BE2:BG2"/>
-    <mergeCell ref="AJ1:AL1"/>
-    <mergeCell ref="AJ2:AL2"/>
-    <mergeCell ref="AM1:AO1"/>
-    <mergeCell ref="AM2:AO2"/>
-    <mergeCell ref="AP2:AR2"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
     <mergeCell ref="AD2:AF2"/>
     <mergeCell ref="AG2:AI2"/>
     <mergeCell ref="BB1:BD1"/>
@@ -43585,6 +43521,69 @@
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="X1:Z1"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="AJ1:AL1"/>
+    <mergeCell ref="AJ2:AL2"/>
+    <mergeCell ref="AM1:AO1"/>
+    <mergeCell ref="AM2:AO2"/>
+    <mergeCell ref="AP2:AR2"/>
+    <mergeCell ref="AS1:AU1"/>
+    <mergeCell ref="AS2:AU2"/>
+    <mergeCell ref="AV1:AX1"/>
+    <mergeCell ref="AV2:AX2"/>
+    <mergeCell ref="BH1:BJ1"/>
+    <mergeCell ref="BH2:BJ2"/>
+    <mergeCell ref="AY2:BA2"/>
+    <mergeCell ref="BB2:BD2"/>
+    <mergeCell ref="BE2:BG2"/>
+    <mergeCell ref="BK1:BM1"/>
+    <mergeCell ref="BK2:BM2"/>
+    <mergeCell ref="BN1:BP1"/>
+    <mergeCell ref="BN2:BP2"/>
+    <mergeCell ref="BQ1:BS1"/>
+    <mergeCell ref="BQ2:BS2"/>
+    <mergeCell ref="BT1:BV1"/>
+    <mergeCell ref="BT2:BV2"/>
+    <mergeCell ref="BW1:BY1"/>
+    <mergeCell ref="BW2:BY2"/>
+    <mergeCell ref="BZ1:CB1"/>
+    <mergeCell ref="BZ2:CB2"/>
+    <mergeCell ref="CC1:CE1"/>
+    <mergeCell ref="CC2:CE2"/>
+    <mergeCell ref="CF1:CH1"/>
+    <mergeCell ref="CF2:CH2"/>
+    <mergeCell ref="CI1:CK1"/>
+    <mergeCell ref="CI2:CK2"/>
+    <mergeCell ref="CL1:CN1"/>
+    <mergeCell ref="CL2:CN2"/>
+    <mergeCell ref="CO1:CQ1"/>
+    <mergeCell ref="CO2:CQ2"/>
+    <mergeCell ref="CR1:CT1"/>
+    <mergeCell ref="CR2:CT2"/>
+    <mergeCell ref="CU1:CW1"/>
+    <mergeCell ref="CU2:CW2"/>
+    <mergeCell ref="CX1:CZ1"/>
+    <mergeCell ref="CX2:CZ2"/>
+    <mergeCell ref="DJ1:DL1"/>
+    <mergeCell ref="DJ2:DL2"/>
+    <mergeCell ref="DM1:DO1"/>
+    <mergeCell ref="DM2:DO2"/>
+    <mergeCell ref="DA1:DC1"/>
+    <mergeCell ref="DA2:DC2"/>
+    <mergeCell ref="DD1:DF1"/>
+    <mergeCell ref="DD2:DF2"/>
+    <mergeCell ref="DG1:DI1"/>
+    <mergeCell ref="DG2:DI2"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:DO37">
     <cfRule type="cellIs" dxfId="18" priority="1" operator="between">
@@ -43620,122 +43619,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="235" t="s">
+      <c r="C1" s="234" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="235" t="s">
+      <c r="D1" s="234" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="235" t="s">
+      <c r="E1" s="234" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="226" t="s">
+      <c r="F1" s="225" t="s">
         <v>302</v>
       </c>
-      <c r="G1" s="227"/>
-      <c r="H1" s="227"/>
-      <c r="I1" s="227"/>
-      <c r="J1" s="227"/>
-      <c r="K1" s="227"/>
-      <c r="L1" s="227"/>
-      <c r="M1" s="227"/>
-      <c r="N1" s="227"/>
-      <c r="O1" s="227"/>
-      <c r="P1" s="227"/>
-      <c r="Q1" s="227"/>
-      <c r="R1" s="227"/>
-      <c r="S1" s="227"/>
-      <c r="T1" s="227"/>
-      <c r="U1" s="227"/>
-      <c r="V1" s="227"/>
-      <c r="W1" s="227"/>
-      <c r="X1" s="227"/>
-      <c r="Y1" s="227"/>
-      <c r="Z1" s="227"/>
-      <c r="AA1" s="227"/>
-      <c r="AB1" s="227"/>
-      <c r="AC1" s="228"/>
-      <c r="AD1" s="238" t="s">
+      <c r="G1" s="226"/>
+      <c r="H1" s="226"/>
+      <c r="I1" s="226"/>
+      <c r="J1" s="226"/>
+      <c r="K1" s="226"/>
+      <c r="L1" s="226"/>
+      <c r="M1" s="226"/>
+      <c r="N1" s="226"/>
+      <c r="O1" s="226"/>
+      <c r="P1" s="226"/>
+      <c r="Q1" s="226"/>
+      <c r="R1" s="226"/>
+      <c r="S1" s="226"/>
+      <c r="T1" s="226"/>
+      <c r="U1" s="226"/>
+      <c r="V1" s="226"/>
+      <c r="W1" s="226"/>
+      <c r="X1" s="226"/>
+      <c r="Y1" s="226"/>
+      <c r="Z1" s="226"/>
+      <c r="AA1" s="226"/>
+      <c r="AB1" s="226"/>
+      <c r="AC1" s="227"/>
+      <c r="AD1" s="240" t="s">
         <v>281</v>
       </c>
-      <c r="AE1" s="239"/>
-      <c r="AF1" s="239"/>
-      <c r="AG1" s="239"/>
-      <c r="AH1" s="239"/>
-      <c r="AI1" s="240"/>
-      <c r="AJ1" s="226" t="s">
+      <c r="AE1" s="241"/>
+      <c r="AF1" s="241"/>
+      <c r="AG1" s="241"/>
+      <c r="AH1" s="241"/>
+      <c r="AI1" s="242"/>
+      <c r="AJ1" s="225" t="s">
         <v>282</v>
       </c>
-      <c r="AK1" s="227"/>
-      <c r="AL1" s="227"/>
-      <c r="AM1" s="227"/>
-      <c r="AN1" s="227"/>
-      <c r="AO1" s="228"/>
-      <c r="AP1" s="229" t="s">
+      <c r="AK1" s="226"/>
+      <c r="AL1" s="226"/>
+      <c r="AM1" s="226"/>
+      <c r="AN1" s="226"/>
+      <c r="AO1" s="227"/>
+      <c r="AP1" s="228" t="s">
         <v>283</v>
       </c>
-      <c r="AQ1" s="230"/>
-      <c r="AR1" s="230"/>
-      <c r="AS1" s="230"/>
-      <c r="AT1" s="230"/>
-      <c r="AU1" s="231"/>
-      <c r="AV1" s="232" t="s">
+      <c r="AQ1" s="229"/>
+      <c r="AR1" s="229"/>
+      <c r="AS1" s="229"/>
+      <c r="AT1" s="229"/>
+      <c r="AU1" s="230"/>
+      <c r="AV1" s="231" t="s">
         <v>86</v>
       </c>
-      <c r="AW1" s="233"/>
-      <c r="AX1" s="234"/>
+      <c r="AW1" s="232"/>
+      <c r="AX1" s="233"/>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="236"/>
-      <c r="D2" s="236"/>
-      <c r="E2" s="236"/>
-      <c r="F2" s="223"/>
-      <c r="G2" s="224"/>
-      <c r="H2" s="225"/>
-      <c r="I2" s="223"/>
-      <c r="J2" s="224"/>
-      <c r="K2" s="225"/>
-      <c r="L2" s="223"/>
-      <c r="M2" s="224"/>
-      <c r="N2" s="225"/>
-      <c r="O2" s="223"/>
-      <c r="P2" s="224"/>
-      <c r="Q2" s="225"/>
-      <c r="R2" s="223"/>
-      <c r="S2" s="224"/>
-      <c r="T2" s="225"/>
-      <c r="U2" s="223"/>
-      <c r="V2" s="224"/>
-      <c r="W2" s="225"/>
-      <c r="X2" s="223"/>
-      <c r="Y2" s="224"/>
-      <c r="Z2" s="225"/>
-      <c r="AA2" s="223"/>
-      <c r="AB2" s="224"/>
-      <c r="AC2" s="224"/>
-      <c r="AD2" s="223"/>
-      <c r="AE2" s="224"/>
-      <c r="AF2" s="225"/>
-      <c r="AG2" s="223"/>
-      <c r="AH2" s="224"/>
-      <c r="AI2" s="225"/>
-      <c r="AJ2" s="223"/>
-      <c r="AK2" s="224"/>
-      <c r="AL2" s="225"/>
-      <c r="AM2" s="223"/>
-      <c r="AN2" s="224"/>
-      <c r="AO2" s="225"/>
-      <c r="AP2" s="223"/>
-      <c r="AQ2" s="224"/>
-      <c r="AR2" s="225"/>
-      <c r="AS2" s="223"/>
-      <c r="AT2" s="224"/>
-      <c r="AU2" s="225"/>
-      <c r="AV2" s="223"/>
-      <c r="AW2" s="224"/>
-      <c r="AX2" s="225"/>
+      <c r="C2" s="235"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="237" t="s">
+        <v>473</v>
+      </c>
+      <c r="G2" s="238"/>
+      <c r="H2" s="239"/>
+      <c r="I2" s="237"/>
+      <c r="J2" s="238"/>
+      <c r="K2" s="239"/>
+      <c r="L2" s="237"/>
+      <c r="M2" s="238"/>
+      <c r="N2" s="239"/>
+      <c r="O2" s="237"/>
+      <c r="P2" s="238"/>
+      <c r="Q2" s="239"/>
+      <c r="R2" s="237"/>
+      <c r="S2" s="238"/>
+      <c r="T2" s="239"/>
+      <c r="U2" s="237"/>
+      <c r="V2" s="238"/>
+      <c r="W2" s="239"/>
+      <c r="X2" s="237"/>
+      <c r="Y2" s="238"/>
+      <c r="Z2" s="239"/>
+      <c r="AA2" s="237"/>
+      <c r="AB2" s="238"/>
+      <c r="AC2" s="238"/>
+      <c r="AD2" s="237"/>
+      <c r="AE2" s="238"/>
+      <c r="AF2" s="239"/>
+      <c r="AG2" s="237"/>
+      <c r="AH2" s="238"/>
+      <c r="AI2" s="239"/>
+      <c r="AJ2" s="237"/>
+      <c r="AK2" s="238"/>
+      <c r="AL2" s="239"/>
+      <c r="AM2" s="237"/>
+      <c r="AN2" s="238"/>
+      <c r="AO2" s="239"/>
+      <c r="AP2" s="237"/>
+      <c r="AQ2" s="238"/>
+      <c r="AR2" s="239"/>
+      <c r="AS2" s="237"/>
+      <c r="AT2" s="238"/>
+      <c r="AU2" s="239"/>
+      <c r="AV2" s="237"/>
+      <c r="AW2" s="238"/>
+      <c r="AX2" s="239"/>
     </row>
     <row r="3" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -43744,9 +43745,9 @@
       <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="237"/>
-      <c r="D3" s="237"/>
-      <c r="E3" s="237"/>
+      <c r="C3" s="236"/>
+      <c r="D3" s="236"/>
+      <c r="E3" s="236"/>
       <c r="F3" s="170" t="s">
         <v>393</v>
       </c>
@@ -43892,7 +43893,7 @@
       </c>
       <c r="C4" s="58">
         <f>SUM(F4,I4,L4,O4,R4,X4,AA4,AD4,U4,AG4,AJ4,AM4,AP4,AS4,AV4)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" s="58">
         <f t="shared" ref="D4:E4" si="0">SUM(G4,J4,M4,P4,S4,Y4,AB4,AE4,V4,AH4,AK4,AN4,AQ4,AT4,AW4)</f>
@@ -43902,7 +43903,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F4" s="52"/>
+      <c r="F4" s="52">
+        <v>1</v>
+      </c>
       <c r="G4" s="36"/>
       <c r="H4" s="53"/>
       <c r="I4" s="52"/>
@@ -44087,7 +44090,7 @@
       </c>
       <c r="C7" s="58">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" s="58">
         <f t="shared" si="2"/>
@@ -44097,7 +44100,9 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F7" s="52"/>
+      <c r="F7" s="52">
+        <v>1</v>
+      </c>
       <c r="G7" s="36"/>
       <c r="H7" s="53"/>
       <c r="I7" s="52"/>
@@ -44152,7 +44157,7 @@
       </c>
       <c r="C8" s="58">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" s="58">
         <f t="shared" si="2"/>
@@ -44162,7 +44167,9 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F8" s="52"/>
+      <c r="F8" s="52">
+        <v>1</v>
+      </c>
       <c r="G8" s="36"/>
       <c r="H8" s="53"/>
       <c r="I8" s="52"/>
@@ -44217,7 +44224,7 @@
       </c>
       <c r="C9" s="58">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" s="58">
         <f t="shared" si="2"/>
@@ -44227,7 +44234,9 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F9" s="52"/>
+      <c r="F9" s="52">
+        <v>1</v>
+      </c>
       <c r="G9" s="36"/>
       <c r="H9" s="53"/>
       <c r="I9" s="52"/>
@@ -44282,7 +44291,7 @@
       </c>
       <c r="C10" s="58">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" s="58">
         <f t="shared" si="2"/>
@@ -44292,7 +44301,9 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F10" s="52"/>
+      <c r="F10" s="52">
+        <v>1</v>
+      </c>
       <c r="G10" s="36"/>
       <c r="H10" s="53"/>
       <c r="I10" s="52"/>
@@ -44347,18 +44358,22 @@
       </c>
       <c r="C11" s="58">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="58">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="58">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F11" s="52"/>
-      <c r="G11" s="36"/>
+      <c r="F11" s="52">
+        <v>1</v>
+      </c>
+      <c r="G11" s="36">
+        <v>1</v>
+      </c>
       <c r="H11" s="53"/>
       <c r="I11" s="52"/>
       <c r="J11" s="36"/>
@@ -44412,7 +44427,7 @@
       </c>
       <c r="C12" s="58">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" s="58">
         <f t="shared" si="2"/>
@@ -44422,7 +44437,9 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F12" s="52"/>
+      <c r="F12" s="52">
+        <v>1</v>
+      </c>
       <c r="G12" s="36"/>
       <c r="H12" s="53"/>
       <c r="I12" s="52"/>
@@ -44607,7 +44624,7 @@
       </c>
       <c r="C15" s="58">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" s="58">
         <f t="shared" si="2"/>
@@ -44617,7 +44634,9 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F15" s="52"/>
+      <c r="F15" s="52">
+        <v>1</v>
+      </c>
       <c r="G15" s="36"/>
       <c r="H15" s="53"/>
       <c r="I15" s="52"/>
@@ -44668,11 +44687,11 @@
         <v>15</v>
       </c>
       <c r="B16" s="149" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C16" s="58">
         <f t="shared" ref="C16:C37" si="4">SUM(F16,I16,L16,O16,R16,X16,AA16,AD16,U16,AG16,AJ16,AM16,AP16,AS16,AV16)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" s="58">
         <f t="shared" ref="D16:D37" si="5">SUM(G16,J16,M16,P16,S16,Y16,AB16,AE16,V16,AH16,AK16,AN16,AQ16,AT16,AW16)</f>
@@ -44682,7 +44701,9 @@
         <f t="shared" ref="E16:E37" si="6">SUM(H16,K16,N16,Q16,T16,Z16,AC16,AF16,W16,AI16,AL16,AO16,AR16,AU16,AX16)</f>
         <v>0</v>
       </c>
-      <c r="F16" s="52"/>
+      <c r="F16" s="52">
+        <v>1</v>
+      </c>
       <c r="G16" s="36"/>
       <c r="H16" s="53"/>
       <c r="I16" s="52"/>
@@ -44737,7 +44758,7 @@
       </c>
       <c r="C17" s="58">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" s="58">
         <f t="shared" si="5"/>
@@ -44745,11 +44766,15 @@
       </c>
       <c r="E17" s="58">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F17" s="52"/>
+        <v>1</v>
+      </c>
+      <c r="F17" s="52">
+        <v>1</v>
+      </c>
       <c r="G17" s="36"/>
-      <c r="H17" s="53"/>
+      <c r="H17" s="53">
+        <v>1</v>
+      </c>
       <c r="I17" s="52"/>
       <c r="J17" s="36"/>
       <c r="K17" s="53"/>
@@ -44802,7 +44827,7 @@
       </c>
       <c r="C18" s="58">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" s="58">
         <f t="shared" si="5"/>
@@ -44812,7 +44837,9 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F18" s="52"/>
+      <c r="F18" s="52">
+        <v>1</v>
+      </c>
       <c r="G18" s="36"/>
       <c r="H18" s="53"/>
       <c r="I18" s="52"/>
@@ -44932,7 +44959,7 @@
       </c>
       <c r="C20" s="58">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" s="58">
         <f t="shared" si="5"/>
@@ -44942,7 +44969,9 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F20" s="52"/>
+      <c r="F20" s="52">
+        <v>1</v>
+      </c>
       <c r="G20" s="36"/>
       <c r="H20" s="53"/>
       <c r="I20" s="52"/>
@@ -44997,7 +45026,7 @@
       </c>
       <c r="C21" s="58">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" s="58">
         <f t="shared" si="5"/>
@@ -45007,7 +45036,9 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F21" s="52"/>
+      <c r="F21" s="52">
+        <v>1</v>
+      </c>
       <c r="G21" s="36"/>
       <c r="H21" s="53"/>
       <c r="I21" s="52"/>
@@ -45257,7 +45288,7 @@
       </c>
       <c r="C25" s="58">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" s="58">
         <f t="shared" si="5"/>
@@ -45267,7 +45298,9 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F25" s="52"/>
+      <c r="F25" s="52">
+        <v>1</v>
+      </c>
       <c r="G25" s="36"/>
       <c r="H25" s="53"/>
       <c r="I25" s="52"/>
@@ -45322,7 +45355,7 @@
       </c>
       <c r="C26" s="58">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26" s="58">
         <f t="shared" si="5"/>
@@ -45332,7 +45365,9 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F26" s="52"/>
+      <c r="F26" s="52">
+        <v>1</v>
+      </c>
       <c r="G26" s="36"/>
       <c r="H26" s="53"/>
       <c r="I26" s="52"/>
@@ -45452,7 +45487,7 @@
       </c>
       <c r="C28" s="58">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28" s="58">
         <f t="shared" si="5"/>
@@ -45462,7 +45497,9 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="F28" s="52"/>
+      <c r="F28" s="52">
+        <v>1</v>
+      </c>
       <c r="G28" s="36"/>
       <c r="H28" s="53"/>
       <c r="I28" s="52"/>
@@ -46096,15 +46133,15 @@
     <row r="38" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F38" s="172">
         <f t="shared" ref="F38:AX38" si="8">SUM(F4:F37)</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G38" s="173">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" s="174">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" s="172">
         <f t="shared" si="8"/>
@@ -46277,6 +46314,13 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="F1:AC1"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
+    <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="AJ1:AO1"/>
     <mergeCell ref="AP1:AU1"/>
     <mergeCell ref="AV1:AX1"/>
@@ -46293,13 +46337,6 @@
     <mergeCell ref="AD1:AI1"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="I2:K2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="F1:AC1"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:AW31">
     <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
@@ -46334,70 +46371,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C1" s="235" t="s">
+      <c r="C1" s="234" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="235" t="s">
+      <c r="D1" s="234" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="235" t="s">
+      <c r="E1" s="234" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="265" t="s">
+      <c r="F1" s="274" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="266"/>
-      <c r="H1" s="267"/>
-      <c r="I1" s="268" t="s">
+      <c r="G1" s="275"/>
+      <c r="H1" s="276"/>
+      <c r="I1" s="277" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="269"/>
-      <c r="K1" s="270"/>
-      <c r="L1" s="272" t="s">
+      <c r="J1" s="278"/>
+      <c r="K1" s="279"/>
+      <c r="L1" s="244" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="273"/>
-      <c r="N1" s="274"/>
-      <c r="O1" s="275" t="s">
+      <c r="M1" s="245"/>
+      <c r="N1" s="246"/>
+      <c r="O1" s="247" t="s">
         <v>199</v>
       </c>
-      <c r="P1" s="276"/>
-      <c r="Q1" s="277"/>
-      <c r="R1" s="241" t="s">
+      <c r="P1" s="248"/>
+      <c r="Q1" s="249"/>
+      <c r="R1" s="250" t="s">
         <v>200</v>
       </c>
-      <c r="S1" s="242"/>
-      <c r="T1" s="243"/>
-      <c r="U1" s="244" t="s">
+      <c r="S1" s="251"/>
+      <c r="T1" s="252"/>
+      <c r="U1" s="253" t="s">
         <v>306</v>
       </c>
-      <c r="V1" s="245"/>
-      <c r="W1" s="246"/>
+      <c r="V1" s="254"/>
+      <c r="W1" s="255"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="236"/>
-      <c r="D2" s="236"/>
-      <c r="E2" s="236"/>
-      <c r="F2" s="247"/>
-      <c r="G2" s="248"/>
-      <c r="H2" s="249"/>
-      <c r="I2" s="262"/>
-      <c r="J2" s="263"/>
-      <c r="K2" s="264"/>
-      <c r="L2" s="259"/>
-      <c r="M2" s="260"/>
-      <c r="N2" s="261"/>
-      <c r="O2" s="256"/>
-      <c r="P2" s="257"/>
-      <c r="Q2" s="258"/>
-      <c r="R2" s="253"/>
-      <c r="S2" s="254"/>
-      <c r="T2" s="255"/>
-      <c r="U2" s="250"/>
-      <c r="V2" s="251"/>
-      <c r="W2" s="252"/>
+      <c r="C2" s="235"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="256"/>
+      <c r="G2" s="257"/>
+      <c r="H2" s="258"/>
+      <c r="I2" s="271"/>
+      <c r="J2" s="272"/>
+      <c r="K2" s="273"/>
+      <c r="L2" s="268"/>
+      <c r="M2" s="269"/>
+      <c r="N2" s="270"/>
+      <c r="O2" s="265"/>
+      <c r="P2" s="266"/>
+      <c r="Q2" s="267"/>
+      <c r="R2" s="262"/>
+      <c r="S2" s="263"/>
+      <c r="T2" s="264"/>
+      <c r="U2" s="259"/>
+      <c r="V2" s="260"/>
+      <c r="W2" s="261"/>
     </row>
     <row r="3" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -46406,9 +46443,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="271"/>
-      <c r="D3" s="271"/>
-      <c r="E3" s="271"/>
+      <c r="C3" s="243"/>
+      <c r="D3" s="243"/>
+      <c r="E3" s="243"/>
       <c r="F3" s="189" t="s">
         <v>393</v>
       </c>
@@ -46925,7 +46962,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="149" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C16" s="58">
         <f t="shared" si="2"/>
@@ -47832,11 +47869,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="O1:Q1"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="F2:H2"/>
@@ -47847,6 +47879,11 @@
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="O1:Q1"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:W31">
     <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
@@ -48126,7 +48163,7 @@
       <c r="R6" s="26"/>
       <c r="S6" s="20">
         <f>'Apps &amp; Goals 26-27'!F4</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" s="20">
         <f>'Apps &amp; Goals 26-27'!G4</f>
@@ -48138,7 +48175,7 @@
       </c>
       <c r="V6" s="26">
         <f>S6+O6</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W6" s="26">
         <f>T6+P6</f>
@@ -48705,7 +48742,7 @@
       <c r="R9" s="26"/>
       <c r="S9" s="20">
         <f>'Apps &amp; Goals 26-27'!F7</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T9" s="20">
         <f>'Apps &amp; Goals 26-27'!G7</f>
@@ -48717,7 +48754,7 @@
       </c>
       <c r="V9" s="26">
         <f t="shared" si="3"/>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W9" s="26">
         <f t="shared" si="4"/>
@@ -48898,7 +48935,7 @@
       <c r="R10" s="26"/>
       <c r="S10" s="20">
         <f>'Apps &amp; Goals 26-27'!F8</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T10" s="20">
         <f>'Apps &amp; Goals 26-27'!G8</f>
@@ -48910,7 +48947,7 @@
       </c>
       <c r="V10" s="26">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W10" s="26">
         <f t="shared" si="4"/>
@@ -49091,7 +49128,7 @@
       <c r="R11" s="26"/>
       <c r="S11" s="20">
         <f>'Apps &amp; Goals 26-27'!F9</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T11" s="20">
         <f>'Apps &amp; Goals 26-27'!G9</f>
@@ -49103,7 +49140,7 @@
       </c>
       <c r="V11" s="26">
         <f t="shared" si="3"/>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="W11" s="26">
         <f t="shared" si="4"/>
@@ -49284,7 +49321,7 @@
       <c r="R12" s="26"/>
       <c r="S12" s="20">
         <f>'Apps &amp; Goals 26-27'!F10</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T12" s="20">
         <f>'Apps &amp; Goals 26-27'!G10</f>
@@ -49296,7 +49333,7 @@
       </c>
       <c r="V12" s="26">
         <f t="shared" si="3"/>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W12" s="26">
         <f t="shared" si="4"/>
@@ -49477,11 +49514,11 @@
       <c r="R13" s="26"/>
       <c r="S13" s="20">
         <f>'Apps &amp; Goals 26-27'!F11</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T13" s="20">
         <f>'Apps &amp; Goals 26-27'!G11</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U13" s="20">
         <f>'Apps &amp; Goals 26-27'!H11</f>
@@ -49489,11 +49526,11 @@
       </c>
       <c r="V13" s="26">
         <f t="shared" si="3"/>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="W13" s="26">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X13" s="26">
         <f t="shared" si="5"/>
@@ -49670,7 +49707,7 @@
       <c r="R14" s="26"/>
       <c r="S14" s="20">
         <f>'Apps &amp; Goals 26-27'!F12</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T14" s="20">
         <f>'Apps &amp; Goals 26-27'!G12</f>
@@ -49682,7 +49719,7 @@
       </c>
       <c r="V14" s="26">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W14" s="26">
         <f t="shared" si="4"/>
@@ -50249,7 +50286,7 @@
       <c r="R17" s="26"/>
       <c r="S17" s="20">
         <f>'Apps &amp; Goals 26-27'!F15</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T17" s="20">
         <f>'Apps &amp; Goals 26-27'!G15</f>
@@ -50261,7 +50298,7 @@
       </c>
       <c r="V17" s="26">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W17" s="26">
         <f t="shared" si="4"/>
@@ -50388,7 +50425,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C18" s="25">
         <v>0</v>
@@ -50428,7 +50465,7 @@
         <v>15</v>
       </c>
       <c r="N18" s="45" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="O18" s="26">
         <v>0</v>
@@ -50442,7 +50479,7 @@
       <c r="R18" s="26"/>
       <c r="S18" s="20">
         <f>'Apps &amp; Goals 26-27'!F16</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T18" s="20">
         <f>'Apps &amp; Goals 26-27'!G16</f>
@@ -50454,7 +50491,7 @@
       </c>
       <c r="V18" s="26">
         <f t="shared" ref="V18:V39" si="18">S18+O18</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W18" s="26">
         <f t="shared" ref="W18:W39" si="19">T18+P18</f>
@@ -50465,7 +50502,7 @@
         <v>0</v>
       </c>
       <c r="Z18" s="57" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AA18" s="24">
         <v>0</v>
@@ -50502,7 +50539,7 @@
         <v>0</v>
       </c>
       <c r="AL18" s="63" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AM18" s="18">
         <v>0</v>
@@ -50539,7 +50576,7 @@
         <v>0</v>
       </c>
       <c r="AX18" s="32" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AY18" s="33">
         <v>0</v>
@@ -50635,7 +50672,7 @@
       <c r="R19" s="26"/>
       <c r="S19" s="20">
         <f>'Apps &amp; Goals 26-27'!F17</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T19" s="20">
         <f>'Apps &amp; Goals 26-27'!G17</f>
@@ -50643,11 +50680,11 @@
       </c>
       <c r="U19" s="20">
         <f>'Apps &amp; Goals 26-27'!H17</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="26">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W19" s="26">
         <f t="shared" si="19"/>
@@ -50655,7 +50692,7 @@
       </c>
       <c r="X19" s="26">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z19" s="23" t="s">
         <v>343</v>
@@ -50828,7 +50865,7 @@
       <c r="R20" s="26"/>
       <c r="S20" s="20">
         <f>'Apps &amp; Goals 26-27'!F18</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T20" s="20">
         <f>'Apps &amp; Goals 26-27'!G18</f>
@@ -50840,7 +50877,7 @@
       </c>
       <c r="V20" s="26">
         <f t="shared" si="18"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W20" s="26">
         <f t="shared" si="19"/>
@@ -51214,7 +51251,7 @@
       <c r="R22" s="26"/>
       <c r="S22" s="20">
         <f>'Apps &amp; Goals 26-27'!F20</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T22" s="20">
         <f>'Apps &amp; Goals 26-27'!G20</f>
@@ -51226,7 +51263,7 @@
       </c>
       <c r="V22" s="26">
         <f t="shared" si="18"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="W22" s="26">
         <f t="shared" si="19"/>
@@ -51407,7 +51444,7 @@
       <c r="R23" s="26"/>
       <c r="S23" s="20">
         <f>'Apps &amp; Goals 26-27'!F21</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T23" s="20">
         <f>'Apps &amp; Goals 26-27'!G21</f>
@@ -51419,7 +51456,7 @@
       </c>
       <c r="V23" s="26">
         <f t="shared" si="18"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="W23" s="26">
         <f t="shared" si="19"/>
@@ -52179,7 +52216,7 @@
       <c r="R27" s="26"/>
       <c r="S27" s="20">
         <f>'Apps &amp; Goals 26-27'!F25</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T27" s="20">
         <f>'Apps &amp; Goals 26-27'!G25</f>
@@ -52191,7 +52228,7 @@
       </c>
       <c r="V27" s="26">
         <f t="shared" si="18"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W27" s="26">
         <f t="shared" si="19"/>
@@ -52372,7 +52409,7 @@
       <c r="R28" s="26"/>
       <c r="S28" s="20">
         <f>'Apps &amp; Goals 26-27'!F26</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T28" s="20">
         <f>'Apps &amp; Goals 26-27'!G26</f>
@@ -52384,7 +52421,7 @@
       </c>
       <c r="V28" s="26">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W28" s="26">
         <f t="shared" si="19"/>
@@ -52758,7 +52795,7 @@
       <c r="R30" s="26"/>
       <c r="S30" s="20">
         <f>'Apps &amp; Goals 26-27'!F28</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T30" s="20">
         <f>'Apps &amp; Goals 26-27'!G28</f>
@@ -52770,7 +52807,7 @@
       </c>
       <c r="V30" s="26">
         <f t="shared" si="18"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="W30" s="26">
         <f t="shared" si="19"/>
@@ -54660,72 +54697,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C1" s="235" t="s">
+      <c r="C1" s="234" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="235" t="s">
+      <c r="D1" s="234" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="235" t="s">
+      <c r="E1" s="234" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="265" t="s">
+      <c r="F1" s="274" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="266"/>
-      <c r="H1" s="267"/>
-      <c r="I1" s="268" t="s">
+      <c r="G1" s="275"/>
+      <c r="H1" s="276"/>
+      <c r="I1" s="277" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="269"/>
-      <c r="K1" s="270"/>
-      <c r="L1" s="272" t="s">
+      <c r="J1" s="278"/>
+      <c r="K1" s="279"/>
+      <c r="L1" s="244" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="273"/>
-      <c r="N1" s="274"/>
-      <c r="O1" s="275" t="s">
+      <c r="M1" s="245"/>
+      <c r="N1" s="246"/>
+      <c r="O1" s="247" t="s">
         <v>199</v>
       </c>
-      <c r="P1" s="276"/>
-      <c r="Q1" s="277"/>
-      <c r="R1" s="241" t="s">
+      <c r="P1" s="248"/>
+      <c r="Q1" s="249"/>
+      <c r="R1" s="250" t="s">
         <v>200</v>
       </c>
-      <c r="S1" s="242"/>
-      <c r="T1" s="243"/>
-      <c r="U1" s="244" t="s">
+      <c r="S1" s="251"/>
+      <c r="T1" s="252"/>
+      <c r="U1" s="253" t="s">
         <v>306</v>
       </c>
-      <c r="V1" s="245"/>
-      <c r="W1" s="246"/>
+      <c r="V1" s="254"/>
+      <c r="W1" s="255"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="236"/>
-      <c r="D2" s="236"/>
-      <c r="E2" s="236"/>
-      <c r="F2" s="247" t="s">
-        <v>435</v>
-      </c>
-      <c r="G2" s="248"/>
-      <c r="H2" s="249"/>
-      <c r="I2" s="262"/>
-      <c r="J2" s="263"/>
-      <c r="K2" s="264"/>
-      <c r="L2" s="259"/>
-      <c r="M2" s="260"/>
-      <c r="N2" s="261"/>
-      <c r="O2" s="256"/>
-      <c r="P2" s="257"/>
-      <c r="Q2" s="258"/>
-      <c r="R2" s="253"/>
-      <c r="S2" s="254"/>
-      <c r="T2" s="255"/>
-      <c r="U2" s="250"/>
-      <c r="V2" s="251"/>
-      <c r="W2" s="252"/>
+      <c r="C2" s="235"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="256" t="s">
+        <v>434</v>
+      </c>
+      <c r="G2" s="257"/>
+      <c r="H2" s="258"/>
+      <c r="I2" s="271"/>
+      <c r="J2" s="272"/>
+      <c r="K2" s="273"/>
+      <c r="L2" s="268"/>
+      <c r="M2" s="269"/>
+      <c r="N2" s="270"/>
+      <c r="O2" s="265"/>
+      <c r="P2" s="266"/>
+      <c r="Q2" s="267"/>
+      <c r="R2" s="262"/>
+      <c r="S2" s="263"/>
+      <c r="T2" s="264"/>
+      <c r="U2" s="259"/>
+      <c r="V2" s="260"/>
+      <c r="W2" s="261"/>
     </row>
     <row r="3" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -54734,9 +54771,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="271"/>
-      <c r="D3" s="271"/>
-      <c r="E3" s="271"/>
+      <c r="C3" s="243"/>
+      <c r="D3" s="243"/>
+      <c r="E3" s="243"/>
       <c r="F3" s="189" t="s">
         <v>393</v>
       </c>
@@ -55253,7 +55290,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="149" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C16" s="58">
         <f t="shared" ref="C16:C37" si="2">SUM(F16,I16,L16,O16,R16,U16)</f>
@@ -56160,6 +56197,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="F2:H2"/>
@@ -56170,11 +56212,6 @@
     <mergeCell ref="U2:W2"/>
     <mergeCell ref="L1:N1"/>
     <mergeCell ref="O1:Q1"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:W31">
     <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
@@ -56202,11 +56239,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C1" s="278" t="s">
+      <c r="C1" s="280" t="s">
         <v>340</v>
       </c>
-      <c r="D1" s="279"/>
-      <c r="E1" s="279"/>
+      <c r="D1" s="281"/>
+      <c r="E1" s="281"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -56382,7 +56419,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="149" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="20"/>
@@ -56670,51 +56707,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="281" t="s">
+      <c r="C1" s="302" t="s">
         <v>202</v>
       </c>
-      <c r="D1" s="282"/>
-      <c r="E1" s="282"/>
-      <c r="F1" s="282"/>
-      <c r="G1" s="282"/>
-      <c r="H1" s="282"/>
-      <c r="I1" s="283"/>
+      <c r="D1" s="303"/>
+      <c r="E1" s="303"/>
+      <c r="F1" s="303"/>
+      <c r="G1" s="303"/>
+      <c r="H1" s="303"/>
+      <c r="I1" s="304"/>
       <c r="J1" s="114" t="s">
         <v>195</v>
       </c>
       <c r="K1" s="115" t="s">
         <v>194</v>
       </c>
-      <c r="L1" s="305" t="s">
+      <c r="L1" s="282" t="s">
         <v>287</v>
       </c>
-      <c r="M1" s="310"/>
-      <c r="N1" s="310"/>
-      <c r="O1" s="310"/>
-      <c r="P1" s="310"/>
-      <c r="Q1" s="310"/>
-      <c r="R1" s="310"/>
-      <c r="S1" s="310"/>
-      <c r="T1" s="310"/>
-      <c r="U1" s="310"/>
-      <c r="V1" s="310"/>
-      <c r="W1" s="310"/>
-      <c r="X1" s="310"/>
-      <c r="Y1" s="310"/>
-      <c r="Z1" s="310"/>
-      <c r="AA1" s="310"/>
-      <c r="AB1" s="310"/>
-      <c r="AC1" s="310"/>
-      <c r="AD1" s="310"/>
-      <c r="AE1" s="310"/>
-      <c r="AF1" s="310"/>
-      <c r="AG1" s="311"/>
-      <c r="AH1" s="305" t="s">
+      <c r="M1" s="287"/>
+      <c r="N1" s="287"/>
+      <c r="O1" s="287"/>
+      <c r="P1" s="287"/>
+      <c r="Q1" s="287"/>
+      <c r="R1" s="287"/>
+      <c r="S1" s="287"/>
+      <c r="T1" s="287"/>
+      <c r="U1" s="287"/>
+      <c r="V1" s="287"/>
+      <c r="W1" s="287"/>
+      <c r="X1" s="287"/>
+      <c r="Y1" s="287"/>
+      <c r="Z1" s="287"/>
+      <c r="AA1" s="287"/>
+      <c r="AB1" s="287"/>
+      <c r="AC1" s="287"/>
+      <c r="AD1" s="287"/>
+      <c r="AE1" s="287"/>
+      <c r="AF1" s="287"/>
+      <c r="AG1" s="288"/>
+      <c r="AH1" s="282" t="s">
         <v>175</v>
       </c>
-      <c r="AI1" s="306"/>
-      <c r="AJ1" s="306"/>
-      <c r="AK1" s="307"/>
+      <c r="AI1" s="283"/>
+      <c r="AJ1" s="283"/>
+      <c r="AK1" s="284"/>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B2" s="111"/>
@@ -61914,15 +61951,15 @@
         <f t="shared" ref="J80:J111" si="2">H80-I80</f>
         <v>2</v>
       </c>
-      <c r="K80" s="312" t="s">
-        <v>438</v>
-      </c>
-      <c r="L80" s="313"/>
-      <c r="M80" s="314"/>
+      <c r="K80" s="289" t="s">
+        <v>436</v>
+      </c>
+      <c r="L80" s="290"/>
+      <c r="M80" s="291"/>
       <c r="O80" s="133"/>
       <c r="P80" s="133"/>
-      <c r="W80" s="308"/>
-      <c r="X80" s="308"/>
+      <c r="W80" s="285"/>
+      <c r="X80" s="285"/>
       <c r="Y80" s="70" t="s">
         <v>211</v>
       </c>
@@ -61972,15 +62009,15 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K81" s="315"/>
-      <c r="L81" s="316"/>
-      <c r="M81" s="317"/>
+      <c r="K81" s="292"/>
+      <c r="L81" s="293"/>
+      <c r="M81" s="294"/>
       <c r="O81" s="133"/>
       <c r="P81" s="133"/>
-      <c r="W81" s="308" t="s">
+      <c r="W81" s="285" t="s">
         <v>209</v>
       </c>
-      <c r="X81" s="308"/>
+      <c r="X81" s="285"/>
       <c r="Y81" s="70">
         <f>COUNTIF(L3:AG40,3)</f>
         <v>481</v>
@@ -62036,17 +62073,17 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K82" s="318" t="s">
-        <v>439</v>
-      </c>
-      <c r="L82" s="319"/>
-      <c r="M82" s="320"/>
+      <c r="K82" s="295" t="s">
+        <v>437</v>
+      </c>
+      <c r="L82" s="296"/>
+      <c r="M82" s="297"/>
       <c r="O82" s="133"/>
       <c r="P82" s="133"/>
-      <c r="W82" s="308" t="s">
+      <c r="W82" s="285" t="s">
         <v>210</v>
       </c>
-      <c r="X82" s="308"/>
+      <c r="X82" s="285"/>
       <c r="Y82" s="70">
         <f>COUNTIF(K3:K40,3)+COUNTIF(J3:J15,3)</f>
         <v>25</v>
@@ -62102,17 +62139,17 @@
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="K83" s="321" t="s">
-        <v>440</v>
-      </c>
-      <c r="L83" s="322"/>
-      <c r="M83" s="323"/>
+      <c r="K83" s="298" t="s">
+        <v>438</v>
+      </c>
+      <c r="L83" s="299"/>
+      <c r="M83" s="300"/>
       <c r="O83" s="133"/>
       <c r="P83" s="133"/>
-      <c r="W83" s="309" t="s">
+      <c r="W83" s="286" t="s">
         <v>97</v>
       </c>
-      <c r="X83" s="309"/>
+      <c r="X83" s="286"/>
       <c r="Y83" s="196">
         <v>220</v>
       </c>
@@ -62165,15 +62202,15 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="K84" s="296" t="s">
+      <c r="K84" s="317" t="s">
         <v>284</v>
       </c>
-      <c r="L84" s="297"/>
-      <c r="M84" s="298"/>
+      <c r="L84" s="318"/>
+      <c r="M84" s="319"/>
       <c r="O84" s="141"/>
       <c r="P84" s="141"/>
-      <c r="W84" s="280"/>
-      <c r="X84" s="280"/>
+      <c r="W84" s="301"/>
+      <c r="X84" s="301"/>
       <c r="Y84" s="198"/>
       <c r="Z84" s="198"/>
       <c r="AA84" s="198"/>
@@ -62211,9 +62248,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K85" s="299"/>
-      <c r="L85" s="300"/>
-      <c r="M85" s="301"/>
+      <c r="K85" s="320"/>
+      <c r="L85" s="321"/>
+      <c r="M85" s="322"/>
       <c r="O85" s="141"/>
       <c r="P85" s="141"/>
     </row>
@@ -62247,9 +62284,9 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="K86" s="299"/>
-      <c r="L86" s="300"/>
-      <c r="M86" s="301"/>
+      <c r="K86" s="320"/>
+      <c r="L86" s="321"/>
+      <c r="M86" s="322"/>
       <c r="O86" s="141"/>
       <c r="P86" s="141"/>
     </row>
@@ -62283,9 +62320,9 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="K87" s="299"/>
-      <c r="L87" s="300"/>
-      <c r="M87" s="301"/>
+      <c r="K87" s="320"/>
+      <c r="L87" s="321"/>
+      <c r="M87" s="322"/>
       <c r="O87" s="141"/>
       <c r="P87" s="141"/>
     </row>
@@ -62319,9 +62356,9 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K88" s="299"/>
-      <c r="L88" s="300"/>
-      <c r="M88" s="301"/>
+      <c r="K88" s="320"/>
+      <c r="L88" s="321"/>
+      <c r="M88" s="322"/>
       <c r="O88" s="141"/>
       <c r="P88" s="141"/>
     </row>
@@ -62355,9 +62392,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K89" s="299"/>
-      <c r="L89" s="300"/>
-      <c r="M89" s="301"/>
+      <c r="K89" s="320"/>
+      <c r="L89" s="321"/>
+      <c r="M89" s="322"/>
       <c r="O89" s="141"/>
       <c r="P89" s="141"/>
     </row>
@@ -62391,9 +62428,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K90" s="299"/>
-      <c r="L90" s="300"/>
-      <c r="M90" s="301"/>
+      <c r="K90" s="320"/>
+      <c r="L90" s="321"/>
+      <c r="M90" s="322"/>
       <c r="O90" s="141"/>
       <c r="P90" s="141"/>
     </row>
@@ -62427,9 +62464,9 @@
         <f t="shared" si="2"/>
         <v>47</v>
       </c>
-      <c r="K91" s="299"/>
-      <c r="L91" s="300"/>
-      <c r="M91" s="301"/>
+      <c r="K91" s="320"/>
+      <c r="L91" s="321"/>
+      <c r="M91" s="322"/>
       <c r="O91" s="141"/>
       <c r="P91" s="141"/>
     </row>
@@ -62463,9 +62500,9 @@
         <f t="shared" si="2"/>
         <v>51</v>
       </c>
-      <c r="K92" s="299"/>
-      <c r="L92" s="300"/>
-      <c r="M92" s="301"/>
+      <c r="K92" s="320"/>
+      <c r="L92" s="321"/>
+      <c r="M92" s="322"/>
       <c r="O92" s="141"/>
       <c r="P92" s="141"/>
     </row>
@@ -62499,9 +62536,9 @@
         <f t="shared" si="2"/>
         <v>37</v>
       </c>
-      <c r="K93" s="299"/>
-      <c r="L93" s="300"/>
-      <c r="M93" s="301"/>
+      <c r="K93" s="320"/>
+      <c r="L93" s="321"/>
+      <c r="M93" s="322"/>
       <c r="O93" s="141"/>
       <c r="P93" s="141"/>
     </row>
@@ -62535,9 +62572,9 @@
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="K94" s="299"/>
-      <c r="L94" s="300"/>
-      <c r="M94" s="301"/>
+      <c r="K94" s="320"/>
+      <c r="L94" s="321"/>
+      <c r="M94" s="322"/>
       <c r="O94" s="141"/>
       <c r="P94" s="141"/>
     </row>
@@ -62571,9 +62608,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K95" s="299"/>
-      <c r="L95" s="300"/>
-      <c r="M95" s="301"/>
+      <c r="K95" s="320"/>
+      <c r="L95" s="321"/>
+      <c r="M95" s="322"/>
       <c r="O95" s="141"/>
       <c r="P95" s="141"/>
     </row>
@@ -62607,9 +62644,9 @@
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="K96" s="299"/>
-      <c r="L96" s="300"/>
-      <c r="M96" s="301"/>
+      <c r="K96" s="320"/>
+      <c r="L96" s="321"/>
+      <c r="M96" s="322"/>
       <c r="O96" s="141"/>
       <c r="P96" s="141"/>
     </row>
@@ -62643,9 +62680,9 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="K97" s="299"/>
-      <c r="L97" s="300"/>
-      <c r="M97" s="301"/>
+      <c r="K97" s="320"/>
+      <c r="L97" s="321"/>
+      <c r="M97" s="322"/>
       <c r="O97" s="141"/>
       <c r="P97" s="141"/>
     </row>
@@ -62679,9 +62716,9 @@
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="K98" s="299"/>
-      <c r="L98" s="300"/>
-      <c r="M98" s="301"/>
+      <c r="K98" s="320"/>
+      <c r="L98" s="321"/>
+      <c r="M98" s="322"/>
       <c r="O98" s="141"/>
       <c r="P98" s="141"/>
     </row>
@@ -62715,9 +62752,9 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K99" s="299"/>
-      <c r="L99" s="300"/>
-      <c r="M99" s="301"/>
+      <c r="K99" s="320"/>
+      <c r="L99" s="321"/>
+      <c r="M99" s="322"/>
       <c r="O99" s="141"/>
       <c r="P99" s="141"/>
     </row>
@@ -62751,9 +62788,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K100" s="299"/>
-      <c r="L100" s="300"/>
-      <c r="M100" s="301"/>
+      <c r="K100" s="320"/>
+      <c r="L100" s="321"/>
+      <c r="M100" s="322"/>
       <c r="O100" s="141"/>
       <c r="P100" s="141"/>
     </row>
@@ -62787,9 +62824,9 @@
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="K101" s="299"/>
-      <c r="L101" s="300"/>
-      <c r="M101" s="301"/>
+      <c r="K101" s="320"/>
+      <c r="L101" s="321"/>
+      <c r="M101" s="322"/>
       <c r="O101" s="141"/>
       <c r="P101" s="141"/>
     </row>
@@ -62823,9 +62860,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K102" s="299"/>
-      <c r="L102" s="300"/>
-      <c r="M102" s="301"/>
+      <c r="K102" s="320"/>
+      <c r="L102" s="321"/>
+      <c r="M102" s="322"/>
       <c r="O102" s="141"/>
       <c r="P102" s="141"/>
     </row>
@@ -62859,9 +62896,9 @@
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="K103" s="299"/>
-      <c r="L103" s="300"/>
-      <c r="M103" s="301"/>
+      <c r="K103" s="320"/>
+      <c r="L103" s="321"/>
+      <c r="M103" s="322"/>
       <c r="O103" s="141"/>
       <c r="P103" s="141"/>
     </row>
@@ -62895,9 +62932,9 @@
         <f t="shared" si="2"/>
         <v>33</v>
       </c>
-      <c r="K104" s="299"/>
-      <c r="L104" s="300"/>
-      <c r="M104" s="301"/>
+      <c r="K104" s="320"/>
+      <c r="L104" s="321"/>
+      <c r="M104" s="322"/>
       <c r="O104" s="141"/>
       <c r="P104" s="141"/>
     </row>
@@ -62931,9 +62968,9 @@
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="K105" s="302"/>
-      <c r="L105" s="303"/>
-      <c r="M105" s="304"/>
+      <c r="K105" s="323"/>
+      <c r="L105" s="324"/>
+      <c r="M105" s="325"/>
       <c r="O105" s="141"/>
       <c r="P105" s="141"/>
     </row>
@@ -62967,11 +63004,11 @@
         <f t="shared" si="2"/>
         <v>21</v>
       </c>
-      <c r="K106" s="293" t="s">
+      <c r="K106" s="314" t="s">
         <v>286</v>
       </c>
-      <c r="L106" s="294"/>
-      <c r="M106" s="295"/>
+      <c r="L106" s="315"/>
+      <c r="M106" s="316"/>
       <c r="O106" s="126"/>
       <c r="P106" s="126"/>
     </row>
@@ -63005,11 +63042,11 @@
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="K107" s="293" t="s">
+      <c r="K107" s="314" t="s">
         <v>288</v>
       </c>
-      <c r="L107" s="294"/>
-      <c r="M107" s="295"/>
+      <c r="L107" s="315"/>
+      <c r="M107" s="316"/>
       <c r="O107" s="126"/>
       <c r="P107" s="126"/>
     </row>
@@ -63043,11 +63080,11 @@
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="K108" s="284" t="s">
+      <c r="K108" s="305" t="s">
         <v>289</v>
       </c>
-      <c r="L108" s="285"/>
-      <c r="M108" s="286"/>
+      <c r="L108" s="306"/>
+      <c r="M108" s="307"/>
       <c r="O108" s="126"/>
       <c r="P108" s="126"/>
     </row>
@@ -63081,9 +63118,9 @@
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="K109" s="287"/>
-      <c r="L109" s="288"/>
-      <c r="M109" s="289"/>
+      <c r="K109" s="308"/>
+      <c r="L109" s="309"/>
+      <c r="M109" s="310"/>
       <c r="O109" s="126"/>
       <c r="P109" s="126"/>
     </row>
@@ -63117,9 +63154,9 @@
         <f t="shared" si="2"/>
         <v>45</v>
       </c>
-      <c r="K110" s="287"/>
-      <c r="L110" s="288"/>
-      <c r="M110" s="289"/>
+      <c r="K110" s="308"/>
+      <c r="L110" s="309"/>
+      <c r="M110" s="310"/>
       <c r="O110" s="126"/>
       <c r="P110" s="126"/>
     </row>
@@ -63153,9 +63190,9 @@
         <f t="shared" si="2"/>
         <v>62</v>
       </c>
-      <c r="K111" s="287"/>
-      <c r="L111" s="288"/>
-      <c r="M111" s="289"/>
+      <c r="K111" s="308"/>
+      <c r="L111" s="309"/>
+      <c r="M111" s="310"/>
       <c r="O111" s="126"/>
       <c r="P111" s="126"/>
     </row>
@@ -63193,9 +63230,9 @@
         <f t="shared" ref="J112:J114" si="6">H112-I112</f>
         <v>34</v>
       </c>
-      <c r="K112" s="287"/>
-      <c r="L112" s="288"/>
-      <c r="M112" s="289"/>
+      <c r="K112" s="308"/>
+      <c r="L112" s="309"/>
+      <c r="M112" s="310"/>
     </row>
     <row r="113" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="156" t="s">
@@ -63231,13 +63268,13 @@
         <f t="shared" si="6"/>
         <v>43</v>
       </c>
-      <c r="K113" s="290"/>
-      <c r="L113" s="291"/>
-      <c r="M113" s="292"/>
+      <c r="K113" s="311"/>
+      <c r="L113" s="312"/>
+      <c r="M113" s="313"/>
     </row>
     <row r="114" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" s="93" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B114" s="122"/>
       <c r="C114" s="122"/>
@@ -63273,6 +63310,12 @@
   </sheetData>
   <autoFilter ref="A79:J112" xr:uid="{9C81160F-C24B-449F-8F5A-CB622AB71070}"/>
   <mergeCells count="15">
+    <mergeCell ref="W84:X84"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="K108:M113"/>
+    <mergeCell ref="K106:M106"/>
+    <mergeCell ref="K107:M107"/>
+    <mergeCell ref="K84:M105"/>
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="W80:X80"/>
     <mergeCell ref="W81:X81"/>
@@ -63282,12 +63325,6 @@
     <mergeCell ref="K80:M81"/>
     <mergeCell ref="K82:M82"/>
     <mergeCell ref="K83:M83"/>
-    <mergeCell ref="W84:X84"/>
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="K108:M113"/>
-    <mergeCell ref="K106:M106"/>
-    <mergeCell ref="K107:M107"/>
-    <mergeCell ref="K84:M105"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <conditionalFormatting sqref="A3:A40">
@@ -63361,12 +63398,12 @@
     <col min="2" max="2" width="5.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="34" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="34" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="4.140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="22.140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="3.85546875" bestFit="1" customWidth="1"/>
@@ -63379,40 +63416,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="324" t="s">
+      <c r="A1" s="326" t="s">
+        <v>405</v>
+      </c>
+      <c r="B1" s="326"/>
+      <c r="C1" s="326"/>
+      <c r="D1" s="326"/>
+      <c r="E1" s="326"/>
+      <c r="F1" s="326" t="s">
         <v>406</v>
       </c>
-      <c r="B1" s="324"/>
-      <c r="C1" s="324"/>
-      <c r="D1" s="324"/>
-      <c r="E1" s="324"/>
-      <c r="F1" s="324" t="s">
-        <v>407</v>
-      </c>
-      <c r="G1" s="324"/>
-      <c r="H1" s="324"/>
-      <c r="I1" s="324"/>
-      <c r="J1" s="324"/>
+      <c r="G1" s="326"/>
+      <c r="H1" s="326"/>
+      <c r="I1" s="326"/>
+      <c r="J1" s="326"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2" s="324"/>
-      <c r="B2" s="324"/>
-      <c r="C2" s="324"/>
-      <c r="D2" s="324"/>
-      <c r="E2" s="324"/>
-      <c r="F2" s="324"/>
-      <c r="G2" s="324"/>
-      <c r="H2" s="324"/>
-      <c r="I2" s="324"/>
-      <c r="J2" s="324"/>
+      <c r="A2" s="326"/>
+      <c r="B2" s="326"/>
+      <c r="C2" s="326"/>
+      <c r="D2" s="326"/>
+      <c r="E2" s="326"/>
+      <c r="F2" s="326"/>
+      <c r="G2" s="326"/>
+      <c r="H2" s="326"/>
+      <c r="I2" s="326"/>
+      <c r="J2" s="326"/>
       <c r="L2" t="s">
+        <v>409</v>
+      </c>
+      <c r="M2" t="s">
         <v>410</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>411</v>
-      </c>
-      <c r="N2" t="s">
-        <v>412</v>
       </c>
       <c r="O2" t="s">
         <v>211</v>
@@ -63433,7 +63470,7 @@
         <v>139</v>
       </c>
       <c r="U2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
@@ -63456,7 +63493,7 @@
         <v>399</v>
       </c>
       <c r="G3" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H3" t="s">
         <v>401</v>
@@ -63471,7 +63508,7 @@
         <v>1</v>
       </c>
       <c r="M3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="N3" s="195">
         <v>3</v>
@@ -63500,40 +63537,40 @@
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B4" s="194">
         <v>0.875</v>
       </c>
       <c r="C4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" t="s">
+        <v>429</v>
+      </c>
+      <c r="E4" t="s">
+        <v>477</v>
+      </c>
+      <c r="F4" t="s">
+        <v>472</v>
+      </c>
+      <c r="G4" s="194" t="s">
+        <v>475</v>
+      </c>
+      <c r="H4" t="s">
         <v>6</v>
       </c>
-      <c r="D4" t="s">
-        <v>478</v>
-      </c>
-      <c r="E4" t="s">
-        <v>479</v>
-      </c>
-      <c r="F4" t="s">
-        <v>437</v>
-      </c>
-      <c r="G4" s="330" t="s">
-        <v>475</v>
-      </c>
-      <c r="H4" t="s">
-        <v>4</v>
-      </c>
       <c r="I4" t="s">
-        <v>419</v>
+        <v>473</v>
       </c>
       <c r="J4" t="s">
-        <v>404</v>
+        <v>474</v>
       </c>
       <c r="L4">
         <v>2</v>
       </c>
       <c r="M4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="N4" s="195">
         <v>3</v>
@@ -63565,7 +63602,7 @@
         <v>3</v>
       </c>
       <c r="M5" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="N5" s="195">
         <v>3</v>
@@ -63597,7 +63634,7 @@
         <v>4</v>
       </c>
       <c r="M6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="N6" s="195">
         <v>3</v>
@@ -63629,7 +63666,7 @@
         <v>5</v>
       </c>
       <c r="M7" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="N7" s="195">
         <v>3</v>
@@ -63661,7 +63698,7 @@
         <v>6</v>
       </c>
       <c r="M8" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="N8" s="195">
         <v>3</v>
@@ -63693,7 +63730,7 @@
         <v>7</v>
       </c>
       <c r="M9" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="N9" s="195">
         <v>3</v>
@@ -63725,7 +63762,7 @@
         <v>8</v>
       </c>
       <c r="M10" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N10" s="195">
         <v>3</v>
@@ -63757,7 +63794,7 @@
         <v>9</v>
       </c>
       <c r="M11" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="N11" s="195">
         <v>3</v>
@@ -63789,7 +63826,7 @@
         <v>10</v>
       </c>
       <c r="M12" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="N12" s="195">
         <v>3</v>
@@ -63821,7 +63858,7 @@
         <v>11</v>
       </c>
       <c r="M13" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="N13" s="195">
         <v>3</v>
@@ -63853,7 +63890,7 @@
         <v>12</v>
       </c>
       <c r="M14" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="N14" s="195">
         <v>3</v>
@@ -63885,7 +63922,7 @@
         <v>13</v>
       </c>
       <c r="M15" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="N15" s="195">
         <v>3</v>
@@ -63906,7 +63943,7 @@
         <v>8</v>
       </c>
       <c r="T15" s="195" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="U15" s="195">
         <v>3</v>
@@ -63917,7 +63954,7 @@
         <v>14</v>
       </c>
       <c r="M16" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="N16" s="195">
         <v>3</v>
@@ -63938,7 +63975,7 @@
         <v>8</v>
       </c>
       <c r="T16" s="195" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="U16" s="195">
         <v>3</v>
@@ -63949,7 +63986,7 @@
         <v>15</v>
       </c>
       <c r="M17" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="N17" s="195">
         <v>3</v>
@@ -63970,7 +64007,7 @@
         <v>5</v>
       </c>
       <c r="T17" s="195" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="U17" s="195">
         <v>2</v>
@@ -63981,7 +64018,7 @@
         <v>16</v>
       </c>
       <c r="M18" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="N18" s="195">
         <v>3</v>
@@ -64002,7 +64039,7 @@
         <v>3</v>
       </c>
       <c r="T18" s="195" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="U18" s="195">
         <v>2</v>
@@ -64013,7 +64050,7 @@
         <v>17</v>
       </c>
       <c r="M19" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="N19" s="195">
         <v>3</v>
@@ -64034,7 +64071,7 @@
         <v>5</v>
       </c>
       <c r="T19" s="195" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="U19" s="195">
         <v>1</v>
@@ -64045,7 +64082,7 @@
         <v>18</v>
       </c>
       <c r="M20" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="N20" s="195">
         <v>3</v>
@@ -64066,7 +64103,7 @@
         <v>5</v>
       </c>
       <c r="T20" s="195" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="U20" s="195">
         <v>1</v>
@@ -64077,7 +64114,7 @@
         <v>19</v>
       </c>
       <c r="M21" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="N21" s="195">
         <v>3</v>
@@ -64098,7 +64135,7 @@
         <v>7</v>
       </c>
       <c r="T21" s="195" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="U21" s="195">
         <v>0</v>
@@ -64109,7 +64146,7 @@
         <v>20</v>
       </c>
       <c r="M22" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="N22" s="195">
         <v>3</v>
@@ -64130,7 +64167,7 @@
         <v>5</v>
       </c>
       <c r="T22" s="195" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="U22" s="195">
         <v>0</v>
@@ -64156,19 +64193,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E1" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -64176,10 +64213,10 @@
         <v>350</v>
       </c>
       <c r="B2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C2" s="201">
-        <v>6.7</v>
+        <v>7.2</v>
       </c>
       <c r="D2">
         <v>90</v>
@@ -64187,27 +64224,27 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B3" t="s">
-        <v>455</v>
+        <v>468</v>
       </c>
       <c r="C3" s="201">
-        <v>6.4</v>
-      </c>
-      <c r="D3" t="s">
-        <v>465</v>
+        <v>6.5</v>
+      </c>
+      <c r="D3">
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B4" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="C4" s="201">
-        <v>6.9</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="D4">
         <v>90</v>
@@ -64215,13 +64252,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B5" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="C5" s="201">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="D5">
         <v>90</v>
@@ -64229,38 +64266,38 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B6" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C6" s="201">
-        <v>7.1</v>
-      </c>
-      <c r="D6">
-        <v>90</v>
+        <v>7.8</v>
+      </c>
+      <c r="D6" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B7" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="C7" s="201">
-        <v>6.3</v>
+        <v>6.8</v>
       </c>
       <c r="D7" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B8" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="C8" s="201">
         <v>8.1</v>
@@ -64268,141 +64305,135 @@
       <c r="D8">
         <v>90</v>
       </c>
-      <c r="E8" t="s">
-        <v>471</v>
-      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B9" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="C9" s="201">
         <v>9.1</v>
       </c>
-      <c r="D9" t="s">
-        <v>465</v>
+      <c r="D9">
+        <v>90</v>
       </c>
       <c r="E9" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B10" t="s">
+        <v>478</v>
+      </c>
+      <c r="C10" s="201">
+        <v>6.7</v>
+      </c>
+      <c r="D10" t="s">
         <v>461</v>
-      </c>
-      <c r="C10" s="201">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="D10">
-        <v>90</v>
-      </c>
-      <c r="E10" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B11" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="C11" s="201">
-        <v>6.5</v>
+        <v>7.4</v>
       </c>
       <c r="D11" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B12" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="C12" s="201">
-        <v>8.4</v>
+        <v>6.9</v>
       </c>
       <c r="D12" t="s">
-        <v>465</v>
-      </c>
-      <c r="E12" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B13" t="s">
-        <v>474</v>
-      </c>
-      <c r="C13" s="201"/>
+        <v>470</v>
+      </c>
+      <c r="C13" s="201">
+        <v>7</v>
+      </c>
       <c r="D13" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B14" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="C14" s="201">
-        <v>6.3</v>
+        <v>7.5</v>
       </c>
       <c r="D14" t="s">
-        <v>464</v>
+        <v>460</v>
+      </c>
+      <c r="E14" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B15" t="s">
-        <v>473</v>
+        <v>459</v>
       </c>
       <c r="C15" s="201">
-        <v>6.3</v>
+        <v>6.9</v>
       </c>
       <c r="D15" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B16" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="C16" s="201">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="D16" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B17" t="s">
-        <v>468</v>
-      </c>
-      <c r="C17" s="201">
-        <v>6.7</v>
-      </c>
+        <v>464</v>
+      </c>
+      <c r="C17" s="201"/>
       <c r="D17" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
     </row>
   </sheetData>
@@ -64429,24 +64460,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="202" t="s">
+      <c r="A1" s="204" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="325"/>
-      <c r="C1" s="326" t="s">
+      <c r="B1" s="327"/>
+      <c r="C1" s="328" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="205"/>
-      <c r="E1" s="327"/>
-      <c r="H1" s="202" t="s">
+      <c r="D1" s="210"/>
+      <c r="E1" s="329"/>
+      <c r="H1" s="204" t="s">
         <v>47</v>
       </c>
-      <c r="I1" s="325"/>
-      <c r="J1" s="326" t="s">
+      <c r="I1" s="327"/>
+      <c r="J1" s="328" t="s">
         <v>44</v>
       </c>
-      <c r="K1" s="205"/>
-      <c r="L1" s="327"/>
+      <c r="K1" s="210"/>
+      <c r="L1" s="329"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -65426,11 +65457,11 @@
       </c>
       <c r="K30" s="9">
         <f>'Apps &amp; Goals'!T10</f>
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L30" s="14">
         <f>J30/K30</f>
-        <v>0.26265822784810128</v>
+        <v>0.26182965299684541</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
@@ -65534,9 +65565,9 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="206"/>
-      <c r="G1" s="206"/>
-      <c r="H1" s="206"/>
+      <c r="F1" s="215"/>
+      <c r="G1" s="215"/>
+      <c r="H1" s="215"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -65560,38 +65591,38 @@
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="5"/>
-      <c r="E2" s="202" t="s">
+      <c r="E2" s="204" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="203"/>
-      <c r="G2" s="204"/>
+      <c r="F2" s="205"/>
+      <c r="G2" s="206"/>
       <c r="H2" s="207" t="s">
         <v>120</v>
       </c>
       <c r="I2" s="208"/>
       <c r="J2" s="209"/>
-      <c r="K2" s="202" t="s">
+      <c r="K2" s="204" t="s">
         <v>108</v>
       </c>
-      <c r="L2" s="203"/>
-      <c r="M2" s="204"/>
+      <c r="L2" s="205"/>
+      <c r="M2" s="206"/>
       <c r="N2" s="207" t="s">
         <v>110</v>
       </c>
       <c r="O2" s="208"/>
       <c r="P2" s="209"/>
-      <c r="Q2" s="202" t="s">
+      <c r="Q2" s="204" t="s">
         <v>39</v>
       </c>
-      <c r="R2" s="203"/>
-      <c r="S2" s="204"/>
-      <c r="T2" s="205" t="s">
+      <c r="R2" s="205"/>
+      <c r="S2" s="206"/>
+      <c r="T2" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="U2" s="205"/>
-      <c r="V2" s="205"/>
+      <c r="U2" s="210"/>
+      <c r="V2" s="210"/>
       <c r="Z2" s="125">
-        <v>46269</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
@@ -65658,7 +65689,7 @@
         <v>395</v>
       </c>
       <c r="W3" s="200" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
@@ -65688,7 +65719,7 @@
       </c>
       <c r="H4" s="4">
         <f>'#'!V6</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I4" s="4">
         <f>'#'!W6</f>
@@ -65736,7 +65767,7 @@
       </c>
       <c r="T4" s="2">
         <f t="shared" ref="T4:V4" si="0">SUM(E4,H4,K4,N4,Q4)</f>
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="U4" s="2">
         <f t="shared" ref="U4" si="1">SUM(F4,I4,L4,O4,R4)</f>
@@ -65946,7 +65977,7 @@
       </c>
       <c r="H7" s="4">
         <f>'#'!V9</f>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I7" s="4">
         <f>'#'!W9</f>
@@ -65994,7 +66025,7 @@
       </c>
       <c r="T7" s="2">
         <f t="shared" si="2"/>
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="U7" s="2">
         <f t="shared" si="3"/>
@@ -66032,7 +66063,7 @@
       </c>
       <c r="H8" s="4">
         <f>'#'!V10</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I8" s="4">
         <f>'#'!W10</f>
@@ -66080,7 +66111,7 @@
       </c>
       <c r="T8" s="2">
         <f t="shared" si="2"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="U8" s="2">
         <f t="shared" si="3"/>
@@ -66118,7 +66149,7 @@
       </c>
       <c r="H9" s="4">
         <f>'#'!V11</f>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I9" s="4">
         <f>'#'!W11</f>
@@ -66166,7 +66197,7 @@
       </c>
       <c r="T9" s="2">
         <f t="shared" si="2"/>
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="U9" s="2">
         <f t="shared" si="3"/>
@@ -66204,7 +66235,7 @@
       </c>
       <c r="H10" s="4">
         <f>'#'!V12</f>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I10" s="4">
         <f>'#'!W12</f>
@@ -66252,7 +66283,7 @@
       </c>
       <c r="T10" s="2">
         <f t="shared" si="2"/>
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="U10" s="2">
         <f t="shared" si="3"/>
@@ -66290,11 +66321,11 @@
       </c>
       <c r="H11" s="4">
         <f>'#'!V13</f>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I11" s="4">
         <f>'#'!W13</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J11" s="4">
         <f>'#'!X13</f>
@@ -66338,11 +66369,11 @@
       </c>
       <c r="T11" s="2">
         <f t="shared" si="2"/>
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="U11" s="2">
         <f t="shared" si="3"/>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="V11" s="2">
         <f t="shared" si="4"/>
@@ -66376,7 +66407,7 @@
       </c>
       <c r="H12" s="4">
         <f>'#'!V14</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I12" s="4">
         <f>'#'!W14</f>
@@ -66424,7 +66455,7 @@
       </c>
       <c r="T12" s="2">
         <f t="shared" si="2"/>
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="U12" s="2">
         <f t="shared" si="3"/>
@@ -66634,7 +66665,7 @@
       </c>
       <c r="H15" s="4">
         <f>'#'!V17</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I15" s="4">
         <f>'#'!W17</f>
@@ -66682,7 +66713,7 @@
       </c>
       <c r="T15" s="2">
         <f t="shared" si="2"/>
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="U15" s="2">
         <f t="shared" si="3"/>
@@ -66704,7 +66735,7 @@
         <v>352</v>
       </c>
       <c r="D16" s="149" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E16" s="6">
         <f>'#'!J18</f>
@@ -66720,7 +66751,7 @@
       </c>
       <c r="H16" s="4">
         <f>'#'!V18</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" s="4">
         <f>'#'!W18</f>
@@ -66768,7 +66799,7 @@
       </c>
       <c r="T16" s="2">
         <f t="shared" ref="T16:T37" si="5">SUM(E16,H16,K16,N16,Q16)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U16" s="2">
         <f t="shared" ref="U16:U37" si="6">SUM(F16,I16,L16,O16,R16)</f>
@@ -66806,7 +66837,7 @@
       </c>
       <c r="H17" s="4">
         <f>'#'!V19</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" s="4">
         <f>'#'!W19</f>
@@ -66814,7 +66845,7 @@
       </c>
       <c r="J17" s="4">
         <f>'#'!X19</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" s="6">
         <f>'#'!AH19</f>
@@ -66854,7 +66885,7 @@
       </c>
       <c r="T17" s="2">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U17" s="2">
         <f t="shared" si="6"/>
@@ -66862,7 +66893,7 @@
       </c>
       <c r="V17" s="2">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.25">
@@ -66892,7 +66923,7 @@
       </c>
       <c r="H18" s="4">
         <f>'#'!V20</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I18" s="4">
         <f>'#'!W20</f>
@@ -66940,7 +66971,7 @@
       </c>
       <c r="T18" s="2">
         <f t="shared" si="5"/>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="U18" s="2">
         <f t="shared" si="6"/>
@@ -67037,7 +67068,7 @@
         <v>2</v>
       </c>
       <c r="W19" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.25">
@@ -67067,7 +67098,7 @@
       </c>
       <c r="H20" s="4">
         <f>'#'!V22</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I20" s="4">
         <f>'#'!W22</f>
@@ -67115,7 +67146,7 @@
       </c>
       <c r="T20" s="2">
         <f t="shared" si="5"/>
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U20" s="2">
         <f t="shared" si="6"/>
@@ -67153,7 +67184,7 @@
       </c>
       <c r="H21" s="4">
         <f>'#'!V23</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I21" s="4">
         <f>'#'!W23</f>
@@ -67201,7 +67232,7 @@
       </c>
       <c r="T21" s="2">
         <f t="shared" si="5"/>
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="U21" s="2">
         <f t="shared" si="6"/>
@@ -67470,7 +67501,7 @@
         <v>0</v>
       </c>
       <c r="W24" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.25">
@@ -67500,7 +67531,7 @@
       </c>
       <c r="H25" s="4">
         <f>'#'!V27</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I25" s="4">
         <f>'#'!W27</f>
@@ -67548,7 +67579,7 @@
       </c>
       <c r="T25" s="2">
         <f t="shared" si="5"/>
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="U25" s="2">
         <f t="shared" si="6"/>
@@ -67586,7 +67617,7 @@
       </c>
       <c r="H26" s="4">
         <f>'#'!V28</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" s="4">
         <f>'#'!W28</f>
@@ -67634,7 +67665,7 @@
       </c>
       <c r="T26" s="2">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U26" s="2">
         <f t="shared" si="6"/>
@@ -67758,7 +67789,7 @@
       </c>
       <c r="H28" s="4">
         <f>'#'!V30</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I28" s="4">
         <f>'#'!W30</f>
@@ -67806,7 +67837,7 @@
       </c>
       <c r="T28" s="2">
         <f t="shared" si="5"/>
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="U28" s="2">
         <f t="shared" si="6"/>
@@ -68075,7 +68106,7 @@
         <v>0</v>
       </c>
       <c r="W31" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="32" spans="1:23" x14ac:dyDescent="0.25">
@@ -68250,7 +68281,7 @@
         <v>0</v>
       </c>
       <c r="W33" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.25">
@@ -68687,30 +68718,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="212" t="s">
+      <c r="D2" s="213" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="212"/>
-      <c r="F2" s="213" t="s">
+      <c r="E2" s="213"/>
+      <c r="F2" s="214" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="213"/>
-      <c r="H2" s="212" t="s">
+      <c r="G2" s="214"/>
+      <c r="H2" s="213" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="212"/>
-      <c r="J2" s="213" t="s">
+      <c r="I2" s="213"/>
+      <c r="J2" s="214" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="213"/>
-      <c r="L2" s="212" t="s">
+      <c r="K2" s="214"/>
+      <c r="L2" s="213" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="212"/>
-      <c r="N2" s="205" t="s">
+      <c r="M2" s="213"/>
+      <c r="N2" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="205"/>
+      <c r="O2" s="210"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -70707,30 +70738,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="212" t="s">
+      <c r="D2" s="213" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="212"/>
-      <c r="F2" s="213" t="s">
+      <c r="E2" s="213"/>
+      <c r="F2" s="214" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="213"/>
-      <c r="H2" s="212" t="s">
+      <c r="G2" s="214"/>
+      <c r="H2" s="213" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="212"/>
-      <c r="J2" s="213" t="s">
+      <c r="I2" s="213"/>
+      <c r="J2" s="214" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="213"/>
-      <c r="L2" s="212" t="s">
+      <c r="K2" s="214"/>
+      <c r="L2" s="213" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="212"/>
-      <c r="N2" s="205" t="s">
+      <c r="M2" s="213"/>
+      <c r="N2" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="205"/>
+      <c r="O2" s="210"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -72664,30 +72695,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="212" t="s">
+      <c r="D2" s="213" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="212"/>
-      <c r="F2" s="213" t="s">
+      <c r="E2" s="213"/>
+      <c r="F2" s="214" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="213"/>
-      <c r="H2" s="212" t="s">
+      <c r="G2" s="214"/>
+      <c r="H2" s="213" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="212"/>
-      <c r="J2" s="213" t="s">
+      <c r="I2" s="213"/>
+      <c r="J2" s="214" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="213"/>
-      <c r="L2" s="212" t="s">
+      <c r="K2" s="214"/>
+      <c r="L2" s="213" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="212"/>
-      <c r="N2" s="205" t="s">
+      <c r="M2" s="213"/>
+      <c r="N2" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="205"/>
+      <c r="O2" s="210"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -74712,30 +74743,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="212" t="s">
+      <c r="D2" s="213" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="212"/>
-      <c r="F2" s="213" t="s">
+      <c r="E2" s="213"/>
+      <c r="F2" s="214" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="213"/>
-      <c r="H2" s="212" t="s">
+      <c r="G2" s="214"/>
+      <c r="H2" s="213" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="212"/>
-      <c r="J2" s="213" t="s">
+      <c r="I2" s="213"/>
+      <c r="J2" s="214" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="213"/>
-      <c r="L2" s="212" t="s">
+      <c r="K2" s="214"/>
+      <c r="L2" s="213" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="212"/>
-      <c r="N2" s="205" t="s">
+      <c r="M2" s="213"/>
+      <c r="N2" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="205"/>
+      <c r="O2" s="210"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -76420,30 +76451,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="212" t="s">
+      <c r="C2" s="213" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="212"/>
-      <c r="E2" s="213" t="s">
+      <c r="D2" s="213"/>
+      <c r="E2" s="214" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="213"/>
-      <c r="G2" s="212" t="s">
+      <c r="F2" s="214"/>
+      <c r="G2" s="213" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="212"/>
-      <c r="I2" s="213" t="s">
+      <c r="H2" s="213"/>
+      <c r="I2" s="214" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="213"/>
-      <c r="K2" s="212" t="s">
+      <c r="J2" s="214"/>
+      <c r="K2" s="213" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="212"/>
-      <c r="M2" s="205" t="s">
+      <c r="L2" s="213"/>
+      <c r="M2" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="205"/>
+      <c r="N2" s="210"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -78205,30 +78236,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="212" t="s">
+      <c r="C2" s="213" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="212"/>
-      <c r="E2" s="213" t="s">
+      <c r="D2" s="213"/>
+      <c r="E2" s="214" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="213"/>
-      <c r="G2" s="212" t="s">
+      <c r="F2" s="214"/>
+      <c r="G2" s="213" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="212"/>
-      <c r="I2" s="213" t="s">
+      <c r="H2" s="213"/>
+      <c r="I2" s="214" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="213"/>
-      <c r="K2" s="212" t="s">
+      <c r="J2" s="214"/>
+      <c r="K2" s="213" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="212"/>
-      <c r="M2" s="205" t="s">
+      <c r="L2" s="213"/>
+      <c r="M2" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="205"/>
+      <c r="N2" s="210"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">

--- a/data/arsenal_stats.xlsx
+++ b/data/arsenal_stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bungeltd-my.sharepoint.com/personal/przemyslaw_iskra_bunge_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8311" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E05B72E1-9ECF-43E4-9295-08ACD808352C}"/>
+  <xr:revisionPtr revIDLastSave="8365" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD431384-D8BE-42A0-B75A-8AC946B83E5C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="799" firstSheet="1" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="799" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="19" state="hidden" r:id="rId1"/>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2256" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2257" uniqueCount="482">
   <si>
     <t>Arsenal FC squad statistics</t>
   </si>
@@ -1378,9 +1378,6 @@
     <t>−1</t>
   </si>
   <si>
-    <t>−4</t>
-  </si>
-  <si>
     <t>KONSA Ezri</t>
   </si>
   <si>
@@ -1486,28 +1483,10 @@
     <t>A</t>
   </si>
   <si>
-    <t>Hincapie</t>
-  </si>
-  <si>
-    <t>Gyokeres</t>
-  </si>
-  <si>
-    <t>Madueke</t>
-  </si>
-  <si>
     <t>−3</t>
   </si>
   <si>
-    <t>09.09.2026</t>
-  </si>
-  <si>
     <t>SSC Napoli</t>
-  </si>
-  <si>
-    <t>Stadio Diego Armando Maradona (A)</t>
-  </si>
-  <si>
-    <t>1-0</t>
   </si>
   <si>
     <t>12.09.2026</t>
@@ -1520,6 +1499,33 @@
   </si>
   <si>
     <t>Bruno</t>
+  </si>
+  <si>
+    <t>Calafiori</t>
+  </si>
+  <si>
+    <t>Lewis-Skelly</t>
+  </si>
+  <si>
+    <t>Timber</t>
+  </si>
+  <si>
+    <t>2-0 (W)</t>
+  </si>
+  <si>
+    <t>Ipswitch</t>
+  </si>
+  <si>
+    <t>Portman Road (A)</t>
+  </si>
+  <si>
+    <t>−2</t>
+  </si>
+  <si>
+    <t>−6</t>
+  </si>
+  <si>
+    <t>−10</t>
   </si>
 </sst>
 </file>
@@ -3080,6 +3086,15 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3089,23 +3104,23 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="54" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3143,15 +3158,6 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="28" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3159,27 +3165,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="61" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="10" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="37" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="11" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3272,67 +3257,31 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="61" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="10" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="37" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="11" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="54" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3409,6 +3358,63 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4623,7 +4629,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="32"/>
                 <c:pt idx="0">
-                  <c:v>5</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -4632,25 +4638,25 @@
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>5</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>4</c:v>
-                </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0</c:v>
@@ -4659,10 +4665,10 @@
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>5</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>4</c:v>
@@ -4671,31 +4677,31 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>4</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>5</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>4</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>5</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>3</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>5</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>0</c:v>
@@ -4707,7 +4713,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>4</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>0</c:v>
@@ -4871,7 +4877,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>4</c:v>
@@ -4919,7 +4925,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>0</c:v>
@@ -6463,7 +6469,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D109F790-1F09-405B-AFA5-DA6C0DE92235}" type="CELLRANGE">
+                    <a:fld id="{B67192A3-0B23-4ED1-984A-EF7B53097F25}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6497,7 +6503,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{AEFDBFE5-07DF-4F9E-B05D-BECF46F7AA36}" type="CELLRANGE">
+                    <a:fld id="{B846EE4C-7636-4ED0-922F-8B16A2D722AE}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6531,7 +6537,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9A3CC0EC-D1CA-42E9-96CF-075A03F56F48}" type="CELLRANGE">
+                    <a:fld id="{1FB1BAA0-EA02-4A16-91DC-29EC0349216B}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6565,7 +6571,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C82B796E-DBE7-48BC-A6BB-71704D467F70}" type="CELLRANGE">
+                    <a:fld id="{C68A256F-53DE-483A-AC43-2B499573B296}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6599,7 +6605,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{1926E432-A605-43C8-9C13-34F50B46F216}" type="CELLRANGE">
+                    <a:fld id="{F2243CF3-7D4B-4A76-84C7-57C3F7F6DD14}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6633,7 +6639,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{16357A7A-F1F2-41A9-93D8-0A123DABD418}" type="CELLRANGE">
+                    <a:fld id="{40DDA3CC-D242-4856-8EA1-2AF0C93C2FD4}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6667,7 +6673,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C5CE56F8-B006-4DC0-AA9D-B58D7670F66E}" type="CELLRANGE">
+                    <a:fld id="{A967D1FD-CB4A-44EB-BE5C-CE87BE181A31}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6701,7 +6707,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{CD18CBE0-548D-4D6A-A551-F46BE8822137}" type="CELLRANGE">
+                    <a:fld id="{B29BD653-6B52-4AD1-BA03-613A7A40DF9B}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6735,7 +6741,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{83956FB6-3A7F-4889-A43B-1D4F67ED0732}" type="CELLRANGE">
+                    <a:fld id="{DF6410AB-383F-4695-8DF2-505FAC998061}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6769,7 +6775,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{446B1998-46B8-453F-8307-A3461DA49DDD}" type="CELLRANGE">
+                    <a:fld id="{053F2BCA-BD74-43AB-B7D8-DE1989D8D45B}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6803,7 +6809,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{30937C9F-DD94-4948-87F8-D5EFF7039B90}" type="CELLRANGE">
+                    <a:fld id="{284DF3A1-1EC4-433A-A521-0158F08F948A}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6837,7 +6843,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{48A4A887-B10C-4FE4-A3B7-291C007794EE}" type="CELLRANGE">
+                    <a:fld id="{BDE88EA9-DD26-46F5-9821-303CF5C93037}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6886,7 +6892,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{B27544F2-822D-4388-B063-2452C038185F}" type="CELLRANGE">
+                    <a:fld id="{C8BDED4F-DDEA-4351-9585-CE6D13246337}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr>
                         <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
@@ -6945,7 +6951,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C6FFDFA5-FA6C-4E59-B840-9147BB498B81}" type="CELLRANGE">
+                    <a:fld id="{098E0EDC-3D5A-4AB5-B0B7-23142AF2F940}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6979,7 +6985,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6525DAAB-E3BE-4BDE-BD89-AC5B87A9A731}" type="CELLRANGE">
+                    <a:fld id="{F14D9AA0-29ED-40FA-88F0-3C3F882DF0FA}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7013,7 +7019,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7832C286-51F3-4E55-9273-6229D17C05B9}" type="CELLRANGE">
+                    <a:fld id="{C8729669-64F4-4B8C-B825-21965B1E2ED2}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7047,7 +7053,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{5805233C-FB9E-4F5C-BBCA-34CCF8E39D3D}" type="CELLRANGE">
+                    <a:fld id="{38CAB799-A096-4C26-AAE1-D14C681AFBB4}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7225,25 +7231,25 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>195</c:v>
+                  <c:v>196</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>43</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>266</c:v>
+                  <c:v>267</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>317</c:v>
+                  <c:v>318</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>239</c:v>
+                  <c:v>240</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>56</c:v>
+                  <c:v>57</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>95</c:v>
+                  <c:v>96</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>12</c:v>
@@ -7252,10 +7258,10 @@
                   <c:v>58</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>5</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>46</c:v>
@@ -7264,16 +7270,16 @@
                   <c:v>51</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>82</c:v>
+                  <c:v>83</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>116</c:v>
+                  <c:v>117</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>69</c:v>
+                  <c:v>70</c:v>
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>2</c:v>
@@ -7297,7 +7303,7 @@
                   <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>83</c:v>
+                  <c:v>84</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>46</c:v>
@@ -7524,7 +7530,7 @@
                         <c:v>24</c:v>
                       </c:pt>
                       <c:pt idx="3">
-                        <c:v>83</c:v>
+                        <c:v>84</c:v>
                       </c:pt>
                       <c:pt idx="4">
                         <c:v>46</c:v>
@@ -23230,7 +23236,7 @@
       </c>
       <c r="C4" s="6">
         <f>'Premier League'!C4</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" s="6">
         <f>'Premier League'!D4</f>
@@ -23290,7 +23296,7 @@
       </c>
       <c r="R4" s="2">
         <f>SUM(C4,F4,I4,L4,O4)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S4" s="2">
         <f t="shared" ref="S4:T4" si="0">SUM(D4,G4,J4,M4,P4)</f>
@@ -23472,7 +23478,7 @@
       </c>
       <c r="C7" s="6">
         <f>'Premier League'!C7</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" s="6">
         <f>'Premier League'!D7</f>
@@ -23532,7 +23538,7 @@
       </c>
       <c r="R7" s="2">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S7" s="2">
         <f t="shared" si="2"/>
@@ -23634,7 +23640,7 @@
       </c>
       <c r="C9" s="6">
         <f>'Premier League'!C9</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" s="6">
         <f>'Premier League'!D9</f>
@@ -23694,7 +23700,7 @@
       </c>
       <c r="R9" s="2">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S9" s="2">
         <f t="shared" si="2"/>
@@ -23715,11 +23721,11 @@
       </c>
       <c r="C10" s="6">
         <f>'Premier League'!C10</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" s="6">
         <f>'Premier League'!D10</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" s="6">
         <f>'Premier League'!E10</f>
@@ -23775,11 +23781,11 @@
       </c>
       <c r="R10" s="2">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S10" s="2">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T10" s="2">
         <f t="shared" si="3"/>
@@ -23796,7 +23802,7 @@
       </c>
       <c r="C11" s="6">
         <f>'Premier League'!C11</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" s="6">
         <f>'Premier League'!D11</f>
@@ -23856,7 +23862,7 @@
       </c>
       <c r="R11" s="2">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S11" s="2">
         <f t="shared" si="2"/>
@@ -23877,7 +23883,7 @@
       </c>
       <c r="C12" s="6">
         <f>'Premier League'!C12</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" s="6">
         <f>'Premier League'!D12</f>
@@ -23937,7 +23943,7 @@
       </c>
       <c r="R12" s="2">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S12" s="2">
         <f t="shared" si="2"/>
@@ -23958,7 +23964,7 @@
       </c>
       <c r="C13" s="6">
         <f>'Premier League'!C13</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" s="6">
         <f>'Premier League'!D13</f>
@@ -24018,7 +24024,7 @@
       </c>
       <c r="R13" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" s="2">
         <f t="shared" si="2"/>
@@ -24197,11 +24203,11 @@
         <v>15</v>
       </c>
       <c r="B16" s="149" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C16" s="6">
         <f>'Premier League'!C16</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" s="6">
         <f>'Premier League'!D16</f>
@@ -24261,7 +24267,7 @@
       </c>
       <c r="R16" s="2">
         <f t="shared" ref="R16:R37" si="4">SUM(C16,F16,I16,L16,O16)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S16" s="2">
         <f t="shared" ref="S16:S37" si="5">SUM(D16,G16,J16,M16,P16)</f>
@@ -24282,7 +24288,7 @@
       </c>
       <c r="C17" s="6">
         <f>'Premier League'!C17</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D17" s="6">
         <f>'Premier League'!D17</f>
@@ -24342,7 +24348,7 @@
       </c>
       <c r="R17" s="2">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S17" s="2">
         <f t="shared" si="5"/>
@@ -24523,7 +24529,7 @@
       </c>
       <c r="C20" s="6">
         <f>'Premier League'!C20</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D20" s="6">
         <f>'Premier League'!D20</f>
@@ -24583,7 +24589,7 @@
       </c>
       <c r="R20" s="2">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S20" s="2">
         <f t="shared" si="5"/>
@@ -24603,7 +24609,7 @@
       </c>
       <c r="C21" s="6">
         <f>'Premier League'!C21</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D21" s="6">
         <f>'Premier League'!D21</f>
@@ -24663,7 +24669,7 @@
       </c>
       <c r="R21" s="2">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S21" s="2">
         <f t="shared" si="5"/>
@@ -24765,7 +24771,7 @@
       </c>
       <c r="C23" s="6">
         <f>'Premier League'!C23</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D23" s="6">
         <f>'Premier League'!D23</f>
@@ -24825,7 +24831,7 @@
       </c>
       <c r="R23" s="2">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S23" s="2">
         <f t="shared" si="5"/>
@@ -24927,7 +24933,7 @@
       </c>
       <c r="C25" s="6">
         <f>'Premier League'!C25</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D25" s="6">
         <f>'Premier League'!D25</f>
@@ -24987,7 +24993,7 @@
       </c>
       <c r="R25" s="2">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S25" s="2">
         <f t="shared" si="5"/>
@@ -25008,11 +25014,11 @@
       </c>
       <c r="C26" s="6">
         <f>'Premier League'!C26</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" s="6">
         <f>'Premier League'!D26</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" s="6">
         <f>'Premier League'!E26</f>
@@ -25068,11 +25074,11 @@
       </c>
       <c r="R26" s="2">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S26" s="2">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T26" s="2">
         <f t="shared" si="6"/>
@@ -25169,7 +25175,7 @@
       </c>
       <c r="C28" s="6">
         <f>'Premier League'!C28</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D28" s="6">
         <f>'Premier League'!D28</f>
@@ -25177,7 +25183,7 @@
       </c>
       <c r="E28" s="6">
         <f>'Premier League'!E28</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" s="4">
         <f>Europe!C28</f>
@@ -25229,7 +25235,7 @@
       </c>
       <c r="R28" s="2">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S28" s="2">
         <f t="shared" si="5"/>
@@ -25237,7 +25243,7 @@
       </c>
       <c r="T28" s="2">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V28" s="55"/>
     </row>
@@ -25491,7 +25497,7 @@
       </c>
       <c r="C32" s="6">
         <f>'Premier League'!C32</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D32" s="6">
         <f>'Premier League'!D32</f>
@@ -25551,7 +25557,7 @@
       </c>
       <c r="R32" s="2">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S32" s="2">
         <f t="shared" si="5"/>
@@ -37619,196 +37625,196 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F1" s="216">
-        <v>1</v>
-      </c>
-      <c r="G1" s="217"/>
-      <c r="H1" s="218"/>
-      <c r="I1" s="216">
+      <c r="F1" s="219">
+        <v>1</v>
+      </c>
+      <c r="G1" s="220"/>
+      <c r="H1" s="221"/>
+      <c r="I1" s="219">
         <v>2</v>
       </c>
-      <c r="J1" s="217"/>
-      <c r="K1" s="218"/>
-      <c r="L1" s="216">
-        <v>3</v>
-      </c>
-      <c r="M1" s="217"/>
-      <c r="N1" s="218"/>
-      <c r="O1" s="216">
+      <c r="J1" s="220"/>
+      <c r="K1" s="221"/>
+      <c r="L1" s="219">
+        <v>3</v>
+      </c>
+      <c r="M1" s="220"/>
+      <c r="N1" s="221"/>
+      <c r="O1" s="219">
         <v>4</v>
       </c>
-      <c r="P1" s="217"/>
-      <c r="Q1" s="218"/>
-      <c r="R1" s="216">
+      <c r="P1" s="220"/>
+      <c r="Q1" s="221"/>
+      <c r="R1" s="219">
         <v>5</v>
       </c>
-      <c r="S1" s="217"/>
-      <c r="T1" s="218"/>
-      <c r="U1" s="216">
+      <c r="S1" s="220"/>
+      <c r="T1" s="221"/>
+      <c r="U1" s="219">
         <v>6</v>
       </c>
-      <c r="V1" s="217"/>
-      <c r="W1" s="218"/>
-      <c r="X1" s="216">
+      <c r="V1" s="220"/>
+      <c r="W1" s="221"/>
+      <c r="X1" s="219">
         <v>7</v>
       </c>
-      <c r="Y1" s="217"/>
-      <c r="Z1" s="218"/>
-      <c r="AA1" s="216">
+      <c r="Y1" s="220"/>
+      <c r="Z1" s="221"/>
+      <c r="AA1" s="219">
         <v>8</v>
       </c>
-      <c r="AB1" s="217"/>
-      <c r="AC1" s="218"/>
-      <c r="AD1" s="216">
+      <c r="AB1" s="220"/>
+      <c r="AC1" s="221"/>
+      <c r="AD1" s="219">
         <v>9</v>
       </c>
-      <c r="AE1" s="217"/>
-      <c r="AF1" s="218"/>
-      <c r="AG1" s="216">
+      <c r="AE1" s="220"/>
+      <c r="AF1" s="221"/>
+      <c r="AG1" s="219">
         <v>10</v>
       </c>
-      <c r="AH1" s="217"/>
-      <c r="AI1" s="218"/>
-      <c r="AJ1" s="216">
+      <c r="AH1" s="220"/>
+      <c r="AI1" s="221"/>
+      <c r="AJ1" s="219">
         <v>11</v>
       </c>
-      <c r="AK1" s="217"/>
-      <c r="AL1" s="218"/>
-      <c r="AM1" s="216">
+      <c r="AK1" s="220"/>
+      <c r="AL1" s="221"/>
+      <c r="AM1" s="219">
         <v>12</v>
       </c>
-      <c r="AN1" s="217"/>
-      <c r="AO1" s="218"/>
-      <c r="AP1" s="216">
+      <c r="AN1" s="220"/>
+      <c r="AO1" s="221"/>
+      <c r="AP1" s="219">
         <v>13</v>
       </c>
-      <c r="AQ1" s="217"/>
-      <c r="AR1" s="218"/>
-      <c r="AS1" s="216">
+      <c r="AQ1" s="220"/>
+      <c r="AR1" s="221"/>
+      <c r="AS1" s="219">
         <v>14</v>
       </c>
-      <c r="AT1" s="217"/>
-      <c r="AU1" s="218"/>
-      <c r="AV1" s="216">
+      <c r="AT1" s="220"/>
+      <c r="AU1" s="221"/>
+      <c r="AV1" s="219">
         <v>15</v>
       </c>
-      <c r="AW1" s="217"/>
-      <c r="AX1" s="218"/>
-      <c r="AY1" s="216">
+      <c r="AW1" s="220"/>
+      <c r="AX1" s="221"/>
+      <c r="AY1" s="219">
         <v>16</v>
       </c>
-      <c r="AZ1" s="217"/>
-      <c r="BA1" s="218"/>
-      <c r="BB1" s="216">
+      <c r="AZ1" s="220"/>
+      <c r="BA1" s="221"/>
+      <c r="BB1" s="219">
         <v>17</v>
       </c>
-      <c r="BC1" s="217"/>
-      <c r="BD1" s="218"/>
-      <c r="BE1" s="216">
+      <c r="BC1" s="220"/>
+      <c r="BD1" s="221"/>
+      <c r="BE1" s="219">
         <v>18</v>
       </c>
-      <c r="BF1" s="217"/>
-      <c r="BG1" s="218"/>
-      <c r="BH1" s="216">
+      <c r="BF1" s="220"/>
+      <c r="BG1" s="221"/>
+      <c r="BH1" s="219">
         <v>19</v>
       </c>
-      <c r="BI1" s="217"/>
-      <c r="BJ1" s="218"/>
-      <c r="BK1" s="216">
+      <c r="BI1" s="220"/>
+      <c r="BJ1" s="221"/>
+      <c r="BK1" s="219">
         <v>20</v>
       </c>
-      <c r="BL1" s="217"/>
-      <c r="BM1" s="218"/>
-      <c r="BN1" s="216">
+      <c r="BL1" s="220"/>
+      <c r="BM1" s="221"/>
+      <c r="BN1" s="219">
         <v>21</v>
       </c>
-      <c r="BO1" s="217"/>
-      <c r="BP1" s="218"/>
-      <c r="BQ1" s="216">
+      <c r="BO1" s="220"/>
+      <c r="BP1" s="221"/>
+      <c r="BQ1" s="219">
         <v>22</v>
       </c>
-      <c r="BR1" s="217"/>
-      <c r="BS1" s="218"/>
-      <c r="BT1" s="216">
+      <c r="BR1" s="220"/>
+      <c r="BS1" s="221"/>
+      <c r="BT1" s="219">
         <v>23</v>
       </c>
-      <c r="BU1" s="217"/>
-      <c r="BV1" s="218"/>
-      <c r="BW1" s="216">
+      <c r="BU1" s="220"/>
+      <c r="BV1" s="221"/>
+      <c r="BW1" s="219">
         <v>24</v>
       </c>
-      <c r="BX1" s="217"/>
-      <c r="BY1" s="218"/>
-      <c r="BZ1" s="216">
+      <c r="BX1" s="220"/>
+      <c r="BY1" s="221"/>
+      <c r="BZ1" s="219">
         <v>25</v>
       </c>
-      <c r="CA1" s="217"/>
-      <c r="CB1" s="218"/>
-      <c r="CC1" s="216">
+      <c r="CA1" s="220"/>
+      <c r="CB1" s="221"/>
+      <c r="CC1" s="219">
         <v>26</v>
       </c>
-      <c r="CD1" s="217"/>
-      <c r="CE1" s="218"/>
-      <c r="CF1" s="216">
+      <c r="CD1" s="220"/>
+      <c r="CE1" s="221"/>
+      <c r="CF1" s="219">
         <v>27</v>
       </c>
-      <c r="CG1" s="217"/>
-      <c r="CH1" s="218"/>
-      <c r="CI1" s="216">
+      <c r="CG1" s="220"/>
+      <c r="CH1" s="221"/>
+      <c r="CI1" s="219">
         <v>28</v>
       </c>
-      <c r="CJ1" s="217"/>
-      <c r="CK1" s="218"/>
-      <c r="CL1" s="216">
+      <c r="CJ1" s="220"/>
+      <c r="CK1" s="221"/>
+      <c r="CL1" s="219">
         <v>29</v>
       </c>
-      <c r="CM1" s="217"/>
-      <c r="CN1" s="218"/>
-      <c r="CO1" s="216">
+      <c r="CM1" s="220"/>
+      <c r="CN1" s="221"/>
+      <c r="CO1" s="219">
         <v>30</v>
       </c>
-      <c r="CP1" s="217"/>
-      <c r="CQ1" s="218"/>
-      <c r="CR1" s="216">
+      <c r="CP1" s="220"/>
+      <c r="CQ1" s="221"/>
+      <c r="CR1" s="219">
         <v>31</v>
       </c>
-      <c r="CS1" s="217"/>
-      <c r="CT1" s="218"/>
-      <c r="CU1" s="216">
+      <c r="CS1" s="220"/>
+      <c r="CT1" s="221"/>
+      <c r="CU1" s="219">
         <v>32</v>
       </c>
-      <c r="CV1" s="217"/>
-      <c r="CW1" s="218"/>
-      <c r="CX1" s="216">
+      <c r="CV1" s="220"/>
+      <c r="CW1" s="221"/>
+      <c r="CX1" s="219">
         <v>33</v>
       </c>
-      <c r="CY1" s="217"/>
-      <c r="CZ1" s="218"/>
-      <c r="DA1" s="216">
+      <c r="CY1" s="220"/>
+      <c r="CZ1" s="221"/>
+      <c r="DA1" s="219">
         <v>34</v>
       </c>
-      <c r="DB1" s="217"/>
-      <c r="DC1" s="218"/>
-      <c r="DD1" s="216">
+      <c r="DB1" s="220"/>
+      <c r="DC1" s="221"/>
+      <c r="DD1" s="219">
         <v>35</v>
       </c>
-      <c r="DE1" s="217"/>
-      <c r="DF1" s="218"/>
-      <c r="DG1" s="216">
+      <c r="DE1" s="220"/>
+      <c r="DF1" s="221"/>
+      <c r="DG1" s="219">
         <v>36</v>
       </c>
-      <c r="DH1" s="217"/>
-      <c r="DI1" s="218"/>
-      <c r="DJ1" s="216">
+      <c r="DH1" s="220"/>
+      <c r="DI1" s="221"/>
+      <c r="DJ1" s="219">
         <v>37</v>
       </c>
-      <c r="DK1" s="217"/>
-      <c r="DL1" s="218"/>
-      <c r="DM1" s="216">
+      <c r="DK1" s="220"/>
+      <c r="DL1" s="221"/>
+      <c r="DM1" s="219">
         <v>38</v>
       </c>
-      <c r="DN1" s="217"/>
-      <c r="DO1" s="218"/>
+      <c r="DN1" s="220"/>
+      <c r="DO1" s="221"/>
     </row>
     <row r="2" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
@@ -37822,196 +37828,196 @@
       <c r="E2" s="222" t="s">
         <v>398</v>
       </c>
-      <c r="F2" s="219" t="s">
+      <c r="F2" s="216" t="s">
         <v>346</v>
       </c>
-      <c r="G2" s="220"/>
-      <c r="H2" s="221"/>
-      <c r="I2" s="219" t="s">
+      <c r="G2" s="217"/>
+      <c r="H2" s="218"/>
+      <c r="I2" s="216" t="s">
         <v>331</v>
       </c>
-      <c r="J2" s="220"/>
-      <c r="K2" s="221"/>
-      <c r="L2" s="219" t="s">
+      <c r="J2" s="217"/>
+      <c r="K2" s="218"/>
+      <c r="L2" s="216" t="s">
         <v>330</v>
       </c>
-      <c r="M2" s="220"/>
-      <c r="N2" s="221"/>
-      <c r="O2" s="219" t="s">
+      <c r="M2" s="217"/>
+      <c r="N2" s="218"/>
+      <c r="O2" s="216" t="s">
         <v>328</v>
       </c>
-      <c r="P2" s="220"/>
-      <c r="Q2" s="221"/>
-      <c r="R2" s="219" t="s">
+      <c r="P2" s="217"/>
+      <c r="Q2" s="218"/>
+      <c r="R2" s="216" t="s">
         <v>335</v>
       </c>
-      <c r="S2" s="220"/>
-      <c r="T2" s="221"/>
-      <c r="U2" s="219" t="s">
+      <c r="S2" s="217"/>
+      <c r="T2" s="218"/>
+      <c r="U2" s="216" t="s">
         <v>320</v>
       </c>
-      <c r="V2" s="220"/>
-      <c r="W2" s="221"/>
-      <c r="X2" s="219" t="s">
+      <c r="V2" s="217"/>
+      <c r="W2" s="218"/>
+      <c r="X2" s="216" t="s">
         <v>337</v>
       </c>
-      <c r="Y2" s="220"/>
-      <c r="Z2" s="221"/>
-      <c r="AA2" s="219" t="s">
+      <c r="Y2" s="217"/>
+      <c r="Z2" s="218"/>
+      <c r="AA2" s="216" t="s">
         <v>334</v>
       </c>
-      <c r="AB2" s="220"/>
-      <c r="AC2" s="221"/>
-      <c r="AD2" s="219" t="s">
+      <c r="AB2" s="217"/>
+      <c r="AC2" s="218"/>
+      <c r="AD2" s="216" t="s">
         <v>321</v>
       </c>
-      <c r="AE2" s="220"/>
-      <c r="AF2" s="221"/>
-      <c r="AG2" s="219" t="s">
+      <c r="AE2" s="217"/>
+      <c r="AF2" s="218"/>
+      <c r="AG2" s="216" t="s">
         <v>347</v>
       </c>
-      <c r="AH2" s="220"/>
-      <c r="AI2" s="221"/>
-      <c r="AJ2" s="219" t="s">
+      <c r="AH2" s="217"/>
+      <c r="AI2" s="218"/>
+      <c r="AJ2" s="216" t="s">
         <v>324</v>
       </c>
-      <c r="AK2" s="220"/>
-      <c r="AL2" s="221"/>
-      <c r="AM2" s="219" t="s">
+      <c r="AK2" s="217"/>
+      <c r="AL2" s="218"/>
+      <c r="AM2" s="216" t="s">
         <v>323</v>
       </c>
-      <c r="AN2" s="220"/>
-      <c r="AO2" s="221"/>
-      <c r="AP2" s="219" t="s">
+      <c r="AN2" s="217"/>
+      <c r="AO2" s="218"/>
+      <c r="AP2" s="216" t="s">
         <v>332</v>
       </c>
-      <c r="AQ2" s="220"/>
-      <c r="AR2" s="221"/>
-      <c r="AS2" s="219" t="s">
+      <c r="AQ2" s="217"/>
+      <c r="AR2" s="218"/>
+      <c r="AS2" s="216" t="s">
         <v>329</v>
       </c>
-      <c r="AT2" s="220"/>
-      <c r="AU2" s="221"/>
-      <c r="AV2" s="219" t="s">
+      <c r="AT2" s="217"/>
+      <c r="AU2" s="218"/>
+      <c r="AV2" s="216" t="s">
         <v>336</v>
       </c>
-      <c r="AW2" s="220"/>
-      <c r="AX2" s="221"/>
-      <c r="AY2" s="219" t="s">
+      <c r="AW2" s="217"/>
+      <c r="AX2" s="218"/>
+      <c r="AY2" s="216" t="s">
         <v>305</v>
       </c>
-      <c r="AZ2" s="220"/>
-      <c r="BA2" s="221"/>
-      <c r="BB2" s="219" t="s">
+      <c r="AZ2" s="217"/>
+      <c r="BA2" s="218"/>
+      <c r="BB2" s="216" t="s">
         <v>326</v>
       </c>
-      <c r="BC2" s="220"/>
-      <c r="BD2" s="221"/>
-      <c r="BE2" s="219" t="s">
+      <c r="BC2" s="217"/>
+      <c r="BD2" s="218"/>
+      <c r="BE2" s="216" t="s">
         <v>325</v>
       </c>
-      <c r="BF2" s="220"/>
-      <c r="BG2" s="221"/>
-      <c r="BH2" s="219" t="s">
+      <c r="BF2" s="217"/>
+      <c r="BG2" s="218"/>
+      <c r="BH2" s="216" t="s">
         <v>348</v>
       </c>
-      <c r="BI2" s="220"/>
-      <c r="BJ2" s="221"/>
-      <c r="BK2" s="219" t="s">
+      <c r="BI2" s="217"/>
+      <c r="BJ2" s="218"/>
+      <c r="BK2" s="216" t="s">
         <v>332</v>
       </c>
-      <c r="BL2" s="220"/>
-      <c r="BM2" s="221"/>
-      <c r="BN2" s="219" t="s">
+      <c r="BL2" s="217"/>
+      <c r="BM2" s="218"/>
+      <c r="BN2" s="216" t="s">
         <v>347</v>
       </c>
-      <c r="BO2" s="220"/>
-      <c r="BP2" s="221"/>
-      <c r="BQ2" s="219" t="s">
+      <c r="BO2" s="217"/>
+      <c r="BP2" s="218"/>
+      <c r="BQ2" s="216" t="s">
         <v>324</v>
       </c>
-      <c r="BR2" s="220"/>
-      <c r="BS2" s="221"/>
-      <c r="BT2" s="219" t="s">
+      <c r="BR2" s="217"/>
+      <c r="BS2" s="218"/>
+      <c r="BT2" s="216" t="s">
         <v>323</v>
       </c>
-      <c r="BU2" s="220"/>
-      <c r="BV2" s="221"/>
-      <c r="BW2" s="219" t="s">
+      <c r="BU2" s="217"/>
+      <c r="BV2" s="218"/>
+      <c r="BW2" s="216" t="s">
         <v>321</v>
       </c>
-      <c r="BX2" s="220"/>
-      <c r="BY2" s="221"/>
-      <c r="BZ2" s="219" t="s">
+      <c r="BX2" s="217"/>
+      <c r="BY2" s="218"/>
+      <c r="BZ2" s="216" t="s">
         <v>348</v>
       </c>
-      <c r="CA2" s="220"/>
-      <c r="CB2" s="221"/>
-      <c r="CC2" s="219" t="s">
+      <c r="CA2" s="217"/>
+      <c r="CB2" s="218"/>
+      <c r="CC2" s="216" t="s">
         <v>325</v>
       </c>
-      <c r="CD2" s="220"/>
-      <c r="CE2" s="221"/>
-      <c r="CF2" s="219" t="s">
+      <c r="CD2" s="217"/>
+      <c r="CE2" s="218"/>
+      <c r="CF2" s="216" t="s">
         <v>305</v>
       </c>
-      <c r="CG2" s="220"/>
-      <c r="CH2" s="221"/>
-      <c r="CI2" s="219" t="s">
+      <c r="CG2" s="217"/>
+      <c r="CH2" s="218"/>
+      <c r="CI2" s="216" t="s">
         <v>326</v>
       </c>
-      <c r="CJ2" s="220"/>
-      <c r="CK2" s="221"/>
-      <c r="CL2" s="219" t="s">
+      <c r="CJ2" s="217"/>
+      <c r="CK2" s="218"/>
+      <c r="CL2" s="216" t="s">
         <v>330</v>
       </c>
-      <c r="CM2" s="220"/>
-      <c r="CN2" s="221"/>
-      <c r="CO2" s="219" t="s">
+      <c r="CM2" s="217"/>
+      <c r="CN2" s="218"/>
+      <c r="CO2" s="216" t="s">
         <v>328</v>
       </c>
-      <c r="CP2" s="220"/>
-      <c r="CQ2" s="221"/>
-      <c r="CR2" s="219" t="s">
+      <c r="CP2" s="217"/>
+      <c r="CQ2" s="218"/>
+      <c r="CR2" s="216" t="s">
         <v>346</v>
       </c>
-      <c r="CS2" s="220"/>
-      <c r="CT2" s="221"/>
-      <c r="CU2" s="219" t="s">
+      <c r="CS2" s="217"/>
+      <c r="CT2" s="218"/>
+      <c r="CU2" s="216" t="s">
         <v>331</v>
       </c>
-      <c r="CV2" s="220"/>
-      <c r="CW2" s="221"/>
-      <c r="CX2" s="219" t="s">
+      <c r="CV2" s="217"/>
+      <c r="CW2" s="218"/>
+      <c r="CX2" s="216" t="s">
         <v>336</v>
       </c>
-      <c r="CY2" s="220"/>
-      <c r="CZ2" s="221"/>
-      <c r="DA2" s="219" t="s">
+      <c r="CY2" s="217"/>
+      <c r="CZ2" s="218"/>
+      <c r="DA2" s="216" t="s">
         <v>329</v>
       </c>
-      <c r="DB2" s="220"/>
-      <c r="DC2" s="221"/>
-      <c r="DD2" s="219" t="s">
+      <c r="DB2" s="217"/>
+      <c r="DC2" s="218"/>
+      <c r="DD2" s="216" t="s">
         <v>320</v>
       </c>
-      <c r="DE2" s="220"/>
-      <c r="DF2" s="221"/>
-      <c r="DG2" s="219" t="s">
+      <c r="DE2" s="217"/>
+      <c r="DF2" s="218"/>
+      <c r="DG2" s="216" t="s">
         <v>337</v>
       </c>
-      <c r="DH2" s="220"/>
-      <c r="DI2" s="221"/>
-      <c r="DJ2" s="219" t="s">
+      <c r="DH2" s="217"/>
+      <c r="DI2" s="218"/>
+      <c r="DJ2" s="216" t="s">
         <v>334</v>
       </c>
-      <c r="DK2" s="220"/>
-      <c r="DL2" s="221"/>
-      <c r="DM2" s="219" t="s">
+      <c r="DK2" s="217"/>
+      <c r="DL2" s="218"/>
+      <c r="DM2" s="216" t="s">
         <v>335</v>
       </c>
-      <c r="DN2" s="220"/>
-      <c r="DO2" s="221"/>
+      <c r="DN2" s="217"/>
+      <c r="DO2" s="218"/>
     </row>
     <row r="3" spans="1:119" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -38020,9 +38026,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="224"/>
-      <c r="D3" s="224"/>
-      <c r="E3" s="223"/>
+      <c r="C3" s="223"/>
+      <c r="D3" s="223"/>
+      <c r="E3" s="224"/>
       <c r="F3" s="160" t="s">
         <v>393</v>
       </c>
@@ -38375,7 +38381,7 @@
       </c>
       <c r="C4" s="58">
         <f>SUM(F4,I4,L4,O4,R4,U4,X4,AA4,AD4,AG4,AJ4,AM4,AP4,AS4,AV4,AY4,BB4,BE4,BH4,BK4,BN4,BQ4,BT4,BW4,BZ4,CC4,CF4,CI4,CL4,CO4,CR4,CU4,CX4,DA4,DD4,DG4,DJ4,DM4)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" s="58">
         <f t="shared" ref="D4:E4" si="0">SUM(G4,J4,M4,P4,S4,V4,Y4,AB4,AE4,AH4,AK4,AN4,AQ4,AT4,AW4,AZ4,BC4,BF4,BI4,BL4,BO4,BR4,BU4,BX4,CA4,CD4,CG4,CJ4,CM4,CP4,CS4,CV4,CY4,DB4,DE4,DH4,DK4,DN4)</f>
@@ -38400,7 +38406,9 @@
       </c>
       <c r="M4" s="36"/>
       <c r="N4" s="168"/>
-      <c r="O4" s="52"/>
+      <c r="O4" s="52">
+        <v>1</v>
+      </c>
       <c r="P4" s="36"/>
       <c r="Q4" s="53"/>
       <c r="R4" s="52"/>
@@ -38787,7 +38795,7 @@
       </c>
       <c r="C7" s="58">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" s="58">
         <f t="shared" si="2"/>
@@ -38814,7 +38822,9 @@
       </c>
       <c r="M7" s="36"/>
       <c r="N7" s="168"/>
-      <c r="O7" s="52"/>
+      <c r="O7" s="52">
+        <v>1</v>
+      </c>
       <c r="P7" s="36"/>
       <c r="Q7" s="53"/>
       <c r="R7" s="52"/>
@@ -39067,7 +39077,7 @@
       </c>
       <c r="C9" s="58">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" s="58">
         <f t="shared" si="2"/>
@@ -39092,7 +39102,9 @@
       </c>
       <c r="M9" s="36"/>
       <c r="N9" s="168"/>
-      <c r="O9" s="52"/>
+      <c r="O9" s="52">
+        <v>1</v>
+      </c>
       <c r="P9" s="36"/>
       <c r="Q9" s="53"/>
       <c r="R9" s="52"/>
@@ -39207,11 +39219,11 @@
       </c>
       <c r="C10" s="58">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" s="58">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" s="51">
         <f t="shared" si="3"/>
@@ -39236,8 +39248,12 @@
       </c>
       <c r="M10" s="36"/>
       <c r="N10" s="168"/>
-      <c r="O10" s="52"/>
-      <c r="P10" s="36"/>
+      <c r="O10" s="52">
+        <v>1</v>
+      </c>
+      <c r="P10" s="36">
+        <v>1</v>
+      </c>
       <c r="Q10" s="53"/>
       <c r="R10" s="52"/>
       <c r="S10" s="36"/>
@@ -39351,7 +39367,7 @@
       </c>
       <c r="C11" s="58">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" s="58">
         <f t="shared" si="2"/>
@@ -39380,7 +39396,9 @@
         <v>1</v>
       </c>
       <c r="N11" s="168"/>
-      <c r="O11" s="52"/>
+      <c r="O11" s="52">
+        <v>1</v>
+      </c>
       <c r="P11" s="36"/>
       <c r="Q11" s="53"/>
       <c r="R11" s="52"/>
@@ -39495,7 +39513,7 @@
       </c>
       <c r="C12" s="58">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" s="58">
         <f t="shared" si="2"/>
@@ -39518,7 +39536,9 @@
       <c r="L12" s="52"/>
       <c r="M12" s="36"/>
       <c r="N12" s="168"/>
-      <c r="O12" s="52"/>
+      <c r="O12" s="52">
+        <v>1</v>
+      </c>
       <c r="P12" s="36"/>
       <c r="Q12" s="53"/>
       <c r="R12" s="52"/>
@@ -39633,7 +39653,7 @@
       </c>
       <c r="C13" s="58">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" s="58">
         <f t="shared" si="2"/>
@@ -39652,7 +39672,9 @@
       <c r="L13" s="52"/>
       <c r="M13" s="36"/>
       <c r="N13" s="168"/>
-      <c r="O13" s="52"/>
+      <c r="O13" s="52">
+        <v>1</v>
+      </c>
       <c r="P13" s="36"/>
       <c r="Q13" s="53"/>
       <c r="R13" s="52"/>
@@ -40033,11 +40055,11 @@
         <v>15</v>
       </c>
       <c r="B16" s="149" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C16" s="58">
         <f t="shared" ref="C16:C37" si="4">SUM(F16,I16,L16,O16,R16,U16,X16,AA16,AD16,AG16,AJ16,AM16,AP16,AS16,AV16,AY16,BB16,BE16,BH16,BK16,BN16,BQ16,BT16,BW16,BZ16,CC16,CF16,CI16,CL16,CO16,CR16,CU16,CX16,DA16,DD16,DG16,DJ16,DM16)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" s="58">
         <f t="shared" ref="D16:D37" si="5">SUM(G16,J16,M16,P16,S16,V16,Y16,AB16,AE16,AH16,AK16,AN16,AQ16,AT16,AW16,AZ16,BC16,BF16,BI16,BL16,BO16,BR16,BU16,BX16,CA16,CD16,CG16,CJ16,CM16,CP16,CS16,CV16,CY16,DB16,DE16,DH16,DK16,DN16)</f>
@@ -40060,7 +40082,9 @@
       </c>
       <c r="M16" s="36"/>
       <c r="N16" s="168"/>
-      <c r="O16" s="52"/>
+      <c r="O16" s="52">
+        <v>1</v>
+      </c>
       <c r="P16" s="36"/>
       <c r="Q16" s="53"/>
       <c r="R16" s="52"/>
@@ -40175,7 +40199,7 @@
       </c>
       <c r="C17" s="58">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D17" s="58">
         <f t="shared" si="5"/>
@@ -40202,7 +40226,9 @@
       <c r="N17" s="168">
         <v>1</v>
       </c>
-      <c r="O17" s="52"/>
+      <c r="O17" s="52">
+        <v>1</v>
+      </c>
       <c r="P17" s="36"/>
       <c r="Q17" s="53"/>
       <c r="R17" s="52"/>
@@ -40589,7 +40615,7 @@
       </c>
       <c r="C20" s="58">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D20" s="58">
         <f t="shared" si="5"/>
@@ -40614,7 +40640,9 @@
       </c>
       <c r="M20" s="36"/>
       <c r="N20" s="168"/>
-      <c r="O20" s="52"/>
+      <c r="O20" s="52">
+        <v>1</v>
+      </c>
       <c r="P20" s="36"/>
       <c r="Q20" s="53"/>
       <c r="R20" s="52"/>
@@ -40729,7 +40757,7 @@
       </c>
       <c r="C21" s="58">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D21" s="58">
         <f t="shared" si="5"/>
@@ -40758,7 +40786,9 @@
         <v>1</v>
       </c>
       <c r="N21" s="168"/>
-      <c r="O21" s="52"/>
+      <c r="O21" s="52">
+        <v>1</v>
+      </c>
       <c r="P21" s="36"/>
       <c r="Q21" s="53"/>
       <c r="R21" s="52"/>
@@ -41007,7 +41037,7 @@
       </c>
       <c r="C23" s="58">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D23" s="58">
         <f t="shared" si="5"/>
@@ -41036,7 +41066,9 @@
       </c>
       <c r="M23" s="36"/>
       <c r="N23" s="168"/>
-      <c r="O23" s="52"/>
+      <c r="O23" s="52">
+        <v>1</v>
+      </c>
       <c r="P23" s="36"/>
       <c r="Q23" s="53"/>
       <c r="R23" s="52"/>
@@ -41285,7 +41317,7 @@
       </c>
       <c r="C25" s="58">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D25" s="58">
         <f t="shared" si="5"/>
@@ -41310,7 +41342,9 @@
       </c>
       <c r="M25" s="36"/>
       <c r="N25" s="168"/>
-      <c r="O25" s="52"/>
+      <c r="O25" s="52">
+        <v>1</v>
+      </c>
       <c r="P25" s="36"/>
       <c r="Q25" s="53"/>
       <c r="R25" s="52"/>
@@ -41425,11 +41459,11 @@
       </c>
       <c r="C26" s="58">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" s="58">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" s="51">
         <f t="shared" si="6"/>
@@ -41446,8 +41480,12 @@
       <c r="L26" s="52"/>
       <c r="M26" s="36"/>
       <c r="N26" s="168"/>
-      <c r="O26" s="52"/>
-      <c r="P26" s="36"/>
+      <c r="O26" s="52">
+        <v>1</v>
+      </c>
+      <c r="P26" s="36">
+        <v>1</v>
+      </c>
       <c r="Q26" s="53"/>
       <c r="R26" s="52"/>
       <c r="S26" s="36"/>
@@ -41695,7 +41733,7 @@
       </c>
       <c r="C28" s="58">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D28" s="58">
         <f t="shared" si="5"/>
@@ -41703,7 +41741,7 @@
       </c>
       <c r="E28" s="51">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" s="52">
         <v>1</v>
@@ -41722,9 +41760,13 @@
       <c r="N28" s="168">
         <v>1</v>
       </c>
-      <c r="O28" s="52"/>
+      <c r="O28" s="52">
+        <v>1</v>
+      </c>
       <c r="P28" s="36"/>
-      <c r="Q28" s="53"/>
+      <c r="Q28" s="53">
+        <v>1</v>
+      </c>
       <c r="R28" s="52"/>
       <c r="S28" s="36"/>
       <c r="T28" s="53"/>
@@ -42239,7 +42281,7 @@
       </c>
       <c r="C32" s="58">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D32" s="58">
         <f t="shared" si="5"/>
@@ -42264,7 +42306,9 @@
       </c>
       <c r="M32" s="36"/>
       <c r="N32" s="168"/>
-      <c r="O32" s="52"/>
+      <c r="O32" s="52">
+        <v>1</v>
+      </c>
       <c r="P32" s="36"/>
       <c r="Q32" s="53"/>
       <c r="R32" s="52"/>
@@ -43084,15 +43128,15 @@
       </c>
       <c r="O38" s="73">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="P38" s="73">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q38" s="73">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R38" s="73">
         <f t="shared" si="8"/>
@@ -43505,6 +43549,69 @@
     </row>
   </sheetData>
   <mergeCells count="79">
+    <mergeCell ref="DM1:DO1"/>
+    <mergeCell ref="DM2:DO2"/>
+    <mergeCell ref="DA1:DC1"/>
+    <mergeCell ref="DA2:DC2"/>
+    <mergeCell ref="DD1:DF1"/>
+    <mergeCell ref="DD2:DF2"/>
+    <mergeCell ref="DG1:DI1"/>
+    <mergeCell ref="DG2:DI2"/>
+    <mergeCell ref="CU1:CW1"/>
+    <mergeCell ref="CU2:CW2"/>
+    <mergeCell ref="CX1:CZ1"/>
+    <mergeCell ref="CX2:CZ2"/>
+    <mergeCell ref="DJ1:DL1"/>
+    <mergeCell ref="DJ2:DL2"/>
+    <mergeCell ref="CL1:CN1"/>
+    <mergeCell ref="CL2:CN2"/>
+    <mergeCell ref="CO1:CQ1"/>
+    <mergeCell ref="CO2:CQ2"/>
+    <mergeCell ref="CR1:CT1"/>
+    <mergeCell ref="CR2:CT2"/>
+    <mergeCell ref="CC1:CE1"/>
+    <mergeCell ref="CC2:CE2"/>
+    <mergeCell ref="CF1:CH1"/>
+    <mergeCell ref="CF2:CH2"/>
+    <mergeCell ref="CI1:CK1"/>
+    <mergeCell ref="CI2:CK2"/>
+    <mergeCell ref="BT1:BV1"/>
+    <mergeCell ref="BT2:BV2"/>
+    <mergeCell ref="BW1:BY1"/>
+    <mergeCell ref="BW2:BY2"/>
+    <mergeCell ref="BZ1:CB1"/>
+    <mergeCell ref="BZ2:CB2"/>
+    <mergeCell ref="BK1:BM1"/>
+    <mergeCell ref="BK2:BM2"/>
+    <mergeCell ref="BN1:BP1"/>
+    <mergeCell ref="BN2:BP2"/>
+    <mergeCell ref="BQ1:BS1"/>
+    <mergeCell ref="BQ2:BS2"/>
+    <mergeCell ref="AS1:AU1"/>
+    <mergeCell ref="AS2:AU2"/>
+    <mergeCell ref="AV1:AX1"/>
+    <mergeCell ref="AV2:AX2"/>
+    <mergeCell ref="BH1:BJ1"/>
+    <mergeCell ref="BH2:BJ2"/>
+    <mergeCell ref="AY2:BA2"/>
+    <mergeCell ref="BB2:BD2"/>
+    <mergeCell ref="BE2:BG2"/>
+    <mergeCell ref="AJ1:AL1"/>
+    <mergeCell ref="AJ2:AL2"/>
+    <mergeCell ref="AM1:AO1"/>
+    <mergeCell ref="AM2:AO2"/>
+    <mergeCell ref="AP2:AR2"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
     <mergeCell ref="AD2:AF2"/>
     <mergeCell ref="AG2:AI2"/>
     <mergeCell ref="BB1:BD1"/>
@@ -43521,69 +43628,6 @@
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="X1:Z1"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="AJ1:AL1"/>
-    <mergeCell ref="AJ2:AL2"/>
-    <mergeCell ref="AM1:AO1"/>
-    <mergeCell ref="AM2:AO2"/>
-    <mergeCell ref="AP2:AR2"/>
-    <mergeCell ref="AS1:AU1"/>
-    <mergeCell ref="AS2:AU2"/>
-    <mergeCell ref="AV1:AX1"/>
-    <mergeCell ref="AV2:AX2"/>
-    <mergeCell ref="BH1:BJ1"/>
-    <mergeCell ref="BH2:BJ2"/>
-    <mergeCell ref="AY2:BA2"/>
-    <mergeCell ref="BB2:BD2"/>
-    <mergeCell ref="BE2:BG2"/>
-    <mergeCell ref="BK1:BM1"/>
-    <mergeCell ref="BK2:BM2"/>
-    <mergeCell ref="BN1:BP1"/>
-    <mergeCell ref="BN2:BP2"/>
-    <mergeCell ref="BQ1:BS1"/>
-    <mergeCell ref="BQ2:BS2"/>
-    <mergeCell ref="BT1:BV1"/>
-    <mergeCell ref="BT2:BV2"/>
-    <mergeCell ref="BW1:BY1"/>
-    <mergeCell ref="BW2:BY2"/>
-    <mergeCell ref="BZ1:CB1"/>
-    <mergeCell ref="BZ2:CB2"/>
-    <mergeCell ref="CC1:CE1"/>
-    <mergeCell ref="CC2:CE2"/>
-    <mergeCell ref="CF1:CH1"/>
-    <mergeCell ref="CF2:CH2"/>
-    <mergeCell ref="CI1:CK1"/>
-    <mergeCell ref="CI2:CK2"/>
-    <mergeCell ref="CL1:CN1"/>
-    <mergeCell ref="CL2:CN2"/>
-    <mergeCell ref="CO1:CQ1"/>
-    <mergeCell ref="CO2:CQ2"/>
-    <mergeCell ref="CR1:CT1"/>
-    <mergeCell ref="CR2:CT2"/>
-    <mergeCell ref="CU1:CW1"/>
-    <mergeCell ref="CU2:CW2"/>
-    <mergeCell ref="CX1:CZ1"/>
-    <mergeCell ref="CX2:CZ2"/>
-    <mergeCell ref="DJ1:DL1"/>
-    <mergeCell ref="DJ2:DL2"/>
-    <mergeCell ref="DM1:DO1"/>
-    <mergeCell ref="DM2:DO2"/>
-    <mergeCell ref="DA1:DC1"/>
-    <mergeCell ref="DA2:DC2"/>
-    <mergeCell ref="DD1:DF1"/>
-    <mergeCell ref="DD2:DF2"/>
-    <mergeCell ref="DG1:DI1"/>
-    <mergeCell ref="DG2:DI2"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:DO37">
     <cfRule type="cellIs" dxfId="18" priority="1" operator="between">
@@ -43619,41 +43663,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="234" t="s">
+      <c r="C1" s="237" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="234" t="s">
+      <c r="D1" s="237" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="234" t="s">
+      <c r="E1" s="237" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="225" t="s">
+      <c r="F1" s="228" t="s">
         <v>302</v>
       </c>
-      <c r="G1" s="226"/>
-      <c r="H1" s="226"/>
-      <c r="I1" s="226"/>
-      <c r="J1" s="226"/>
-      <c r="K1" s="226"/>
-      <c r="L1" s="226"/>
-      <c r="M1" s="226"/>
-      <c r="N1" s="226"/>
-      <c r="O1" s="226"/>
-      <c r="P1" s="226"/>
-      <c r="Q1" s="226"/>
-      <c r="R1" s="226"/>
-      <c r="S1" s="226"/>
-      <c r="T1" s="226"/>
-      <c r="U1" s="226"/>
-      <c r="V1" s="226"/>
-      <c r="W1" s="226"/>
-      <c r="X1" s="226"/>
-      <c r="Y1" s="226"/>
-      <c r="Z1" s="226"/>
-      <c r="AA1" s="226"/>
-      <c r="AB1" s="226"/>
-      <c r="AC1" s="227"/>
+      <c r="G1" s="229"/>
+      <c r="H1" s="229"/>
+      <c r="I1" s="229"/>
+      <c r="J1" s="229"/>
+      <c r="K1" s="229"/>
+      <c r="L1" s="229"/>
+      <c r="M1" s="229"/>
+      <c r="N1" s="229"/>
+      <c r="O1" s="229"/>
+      <c r="P1" s="229"/>
+      <c r="Q1" s="229"/>
+      <c r="R1" s="229"/>
+      <c r="S1" s="229"/>
+      <c r="T1" s="229"/>
+      <c r="U1" s="229"/>
+      <c r="V1" s="229"/>
+      <c r="W1" s="229"/>
+      <c r="X1" s="229"/>
+      <c r="Y1" s="229"/>
+      <c r="Z1" s="229"/>
+      <c r="AA1" s="229"/>
+      <c r="AB1" s="229"/>
+      <c r="AC1" s="230"/>
       <c r="AD1" s="240" t="s">
         <v>281</v>
       </c>
@@ -43662,81 +43706,81 @@
       <c r="AG1" s="241"/>
       <c r="AH1" s="241"/>
       <c r="AI1" s="242"/>
-      <c r="AJ1" s="225" t="s">
+      <c r="AJ1" s="228" t="s">
         <v>282</v>
       </c>
-      <c r="AK1" s="226"/>
-      <c r="AL1" s="226"/>
-      <c r="AM1" s="226"/>
-      <c r="AN1" s="226"/>
-      <c r="AO1" s="227"/>
-      <c r="AP1" s="228" t="s">
+      <c r="AK1" s="229"/>
+      <c r="AL1" s="229"/>
+      <c r="AM1" s="229"/>
+      <c r="AN1" s="229"/>
+      <c r="AO1" s="230"/>
+      <c r="AP1" s="231" t="s">
         <v>283</v>
       </c>
-      <c r="AQ1" s="229"/>
-      <c r="AR1" s="229"/>
-      <c r="AS1" s="229"/>
-      <c r="AT1" s="229"/>
-      <c r="AU1" s="230"/>
-      <c r="AV1" s="231" t="s">
+      <c r="AQ1" s="232"/>
+      <c r="AR1" s="232"/>
+      <c r="AS1" s="232"/>
+      <c r="AT1" s="232"/>
+      <c r="AU1" s="233"/>
+      <c r="AV1" s="234" t="s">
         <v>86</v>
       </c>
-      <c r="AW1" s="232"/>
-      <c r="AX1" s="233"/>
+      <c r="AW1" s="235"/>
+      <c r="AX1" s="236"/>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="235"/>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="237" t="s">
-        <v>473</v>
-      </c>
-      <c r="G2" s="238"/>
-      <c r="H2" s="239"/>
-      <c r="I2" s="237"/>
-      <c r="J2" s="238"/>
-      <c r="K2" s="239"/>
-      <c r="L2" s="237"/>
-      <c r="M2" s="238"/>
-      <c r="N2" s="239"/>
-      <c r="O2" s="237"/>
-      <c r="P2" s="238"/>
-      <c r="Q2" s="239"/>
-      <c r="R2" s="237"/>
-      <c r="S2" s="238"/>
-      <c r="T2" s="239"/>
-      <c r="U2" s="237"/>
-      <c r="V2" s="238"/>
-      <c r="W2" s="239"/>
-      <c r="X2" s="237"/>
-      <c r="Y2" s="238"/>
-      <c r="Z2" s="239"/>
-      <c r="AA2" s="237"/>
-      <c r="AB2" s="238"/>
-      <c r="AC2" s="238"/>
-      <c r="AD2" s="237"/>
-      <c r="AE2" s="238"/>
-      <c r="AF2" s="239"/>
-      <c r="AG2" s="237"/>
-      <c r="AH2" s="238"/>
-      <c r="AI2" s="239"/>
-      <c r="AJ2" s="237"/>
-      <c r="AK2" s="238"/>
-      <c r="AL2" s="239"/>
-      <c r="AM2" s="237"/>
-      <c r="AN2" s="238"/>
-      <c r="AO2" s="239"/>
-      <c r="AP2" s="237"/>
-      <c r="AQ2" s="238"/>
-      <c r="AR2" s="239"/>
-      <c r="AS2" s="237"/>
-      <c r="AT2" s="238"/>
-      <c r="AU2" s="239"/>
-      <c r="AV2" s="237"/>
-      <c r="AW2" s="238"/>
-      <c r="AX2" s="239"/>
+      <c r="C2" s="238"/>
+      <c r="D2" s="238"/>
+      <c r="E2" s="238"/>
+      <c r="F2" s="225" t="s">
+        <v>468</v>
+      </c>
+      <c r="G2" s="226"/>
+      <c r="H2" s="227"/>
+      <c r="I2" s="225"/>
+      <c r="J2" s="226"/>
+      <c r="K2" s="227"/>
+      <c r="L2" s="225"/>
+      <c r="M2" s="226"/>
+      <c r="N2" s="227"/>
+      <c r="O2" s="225"/>
+      <c r="P2" s="226"/>
+      <c r="Q2" s="227"/>
+      <c r="R2" s="225"/>
+      <c r="S2" s="226"/>
+      <c r="T2" s="227"/>
+      <c r="U2" s="225"/>
+      <c r="V2" s="226"/>
+      <c r="W2" s="227"/>
+      <c r="X2" s="225"/>
+      <c r="Y2" s="226"/>
+      <c r="Z2" s="227"/>
+      <c r="AA2" s="225"/>
+      <c r="AB2" s="226"/>
+      <c r="AC2" s="226"/>
+      <c r="AD2" s="225"/>
+      <c r="AE2" s="226"/>
+      <c r="AF2" s="227"/>
+      <c r="AG2" s="225"/>
+      <c r="AH2" s="226"/>
+      <c r="AI2" s="227"/>
+      <c r="AJ2" s="225"/>
+      <c r="AK2" s="226"/>
+      <c r="AL2" s="227"/>
+      <c r="AM2" s="225"/>
+      <c r="AN2" s="226"/>
+      <c r="AO2" s="227"/>
+      <c r="AP2" s="225"/>
+      <c r="AQ2" s="226"/>
+      <c r="AR2" s="227"/>
+      <c r="AS2" s="225"/>
+      <c r="AT2" s="226"/>
+      <c r="AU2" s="227"/>
+      <c r="AV2" s="225"/>
+      <c r="AW2" s="226"/>
+      <c r="AX2" s="227"/>
     </row>
     <row r="3" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -43745,9 +43789,9 @@
       <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="236"/>
-      <c r="D3" s="236"/>
-      <c r="E3" s="236"/>
+      <c r="C3" s="239"/>
+      <c r="D3" s="239"/>
+      <c r="E3" s="239"/>
       <c r="F3" s="170" t="s">
         <v>393</v>
       </c>
@@ -44687,7 +44731,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="149" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C16" s="58">
         <f t="shared" ref="C16:C37" si="4">SUM(F16,I16,L16,O16,R16,X16,AA16,AD16,U16,AG16,AJ16,AM16,AP16,AS16,AV16)</f>
@@ -46314,13 +46358,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="F1:AC1"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="AJ1:AO1"/>
     <mergeCell ref="AP1:AU1"/>
     <mergeCell ref="AV1:AX1"/>
@@ -46337,6 +46374,13 @@
     <mergeCell ref="AD1:AI1"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="I2:K2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="F1:AC1"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
+    <mergeCell ref="AA2:AC2"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:AW31">
     <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
@@ -46371,70 +46415,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C1" s="234" t="s">
+      <c r="C1" s="237" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="234" t="s">
+      <c r="D1" s="237" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="234" t="s">
+      <c r="E1" s="237" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="274" t="s">
+      <c r="F1" s="267" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="275"/>
-      <c r="H1" s="276"/>
-      <c r="I1" s="277" t="s">
+      <c r="G1" s="268"/>
+      <c r="H1" s="269"/>
+      <c r="I1" s="270" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="278"/>
-      <c r="K1" s="279"/>
-      <c r="L1" s="244" t="s">
+      <c r="J1" s="271"/>
+      <c r="K1" s="272"/>
+      <c r="L1" s="274" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="245"/>
-      <c r="N1" s="246"/>
-      <c r="O1" s="247" t="s">
+      <c r="M1" s="275"/>
+      <c r="N1" s="276"/>
+      <c r="O1" s="277" t="s">
         <v>199</v>
       </c>
-      <c r="P1" s="248"/>
-      <c r="Q1" s="249"/>
-      <c r="R1" s="250" t="s">
+      <c r="P1" s="278"/>
+      <c r="Q1" s="279"/>
+      <c r="R1" s="243" t="s">
         <v>200</v>
       </c>
-      <c r="S1" s="251"/>
-      <c r="T1" s="252"/>
-      <c r="U1" s="253" t="s">
+      <c r="S1" s="244"/>
+      <c r="T1" s="245"/>
+      <c r="U1" s="246" t="s">
         <v>306</v>
       </c>
-      <c r="V1" s="254"/>
-      <c r="W1" s="255"/>
+      <c r="V1" s="247"/>
+      <c r="W1" s="248"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="235"/>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="256"/>
-      <c r="G2" s="257"/>
-      <c r="H2" s="258"/>
-      <c r="I2" s="271"/>
-      <c r="J2" s="272"/>
-      <c r="K2" s="273"/>
-      <c r="L2" s="268"/>
-      <c r="M2" s="269"/>
-      <c r="N2" s="270"/>
-      <c r="O2" s="265"/>
-      <c r="P2" s="266"/>
-      <c r="Q2" s="267"/>
-      <c r="R2" s="262"/>
-      <c r="S2" s="263"/>
-      <c r="T2" s="264"/>
-      <c r="U2" s="259"/>
-      <c r="V2" s="260"/>
-      <c r="W2" s="261"/>
+      <c r="C2" s="238"/>
+      <c r="D2" s="238"/>
+      <c r="E2" s="238"/>
+      <c r="F2" s="249"/>
+      <c r="G2" s="250"/>
+      <c r="H2" s="251"/>
+      <c r="I2" s="264"/>
+      <c r="J2" s="265"/>
+      <c r="K2" s="266"/>
+      <c r="L2" s="261"/>
+      <c r="M2" s="262"/>
+      <c r="N2" s="263"/>
+      <c r="O2" s="258"/>
+      <c r="P2" s="259"/>
+      <c r="Q2" s="260"/>
+      <c r="R2" s="255"/>
+      <c r="S2" s="256"/>
+      <c r="T2" s="257"/>
+      <c r="U2" s="252"/>
+      <c r="V2" s="253"/>
+      <c r="W2" s="254"/>
     </row>
     <row r="3" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -46443,9 +46487,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="243"/>
-      <c r="D3" s="243"/>
-      <c r="E3" s="243"/>
+      <c r="C3" s="273"/>
+      <c r="D3" s="273"/>
+      <c r="E3" s="273"/>
       <c r="F3" s="189" t="s">
         <v>393</v>
       </c>
@@ -46962,7 +47006,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="149" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C16" s="58">
         <f t="shared" si="2"/>
@@ -47869,6 +47913,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="O1:Q1"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="F2:H2"/>
@@ -47879,11 +47928,6 @@
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="O1:Q1"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:W31">
     <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
@@ -48123,7 +48167,7 @@
       <c r="F6" s="25"/>
       <c r="G6" s="21">
         <f>'Apps &amp; Goals 26-27'!C4</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H6" s="21">
         <f>'Apps &amp; Goals 26-27'!D4</f>
@@ -48135,7 +48179,7 @@
       </c>
       <c r="J6" s="25">
         <f>G6+C6</f>
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K6" s="25">
         <f>H6+D6</f>
@@ -48702,7 +48746,7 @@
       <c r="F9" s="25"/>
       <c r="G9" s="21">
         <f>'Apps &amp; Goals 26-27'!C7</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H9" s="21">
         <f>'Apps &amp; Goals 26-27'!D7</f>
@@ -48714,7 +48758,7 @@
       </c>
       <c r="J9" s="25">
         <f t="shared" si="0"/>
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K9" s="25">
         <f t="shared" si="1"/>
@@ -49088,7 +49132,7 @@
       <c r="F11" s="25"/>
       <c r="G11" s="21">
         <f>'Apps &amp; Goals 26-27'!C9</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H11" s="21">
         <f>'Apps &amp; Goals 26-27'!D9</f>
@@ -49100,7 +49144,7 @@
       </c>
       <c r="J11" s="25">
         <f t="shared" si="0"/>
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K11" s="25">
         <f t="shared" si="1"/>
@@ -49281,11 +49325,11 @@
       <c r="F12" s="25"/>
       <c r="G12" s="21">
         <f>'Apps &amp; Goals 26-27'!C10</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H12" s="21">
         <f>'Apps &amp; Goals 26-27'!D10</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I12" s="21">
         <f>'Apps &amp; Goals 26-27'!E10</f>
@@ -49293,11 +49337,11 @@
       </c>
       <c r="J12" s="25">
         <f t="shared" si="0"/>
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K12" s="25">
         <f t="shared" si="1"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L12" s="25">
         <f t="shared" si="2"/>
@@ -49474,7 +49518,7 @@
       <c r="F13" s="25"/>
       <c r="G13" s="21">
         <f>'Apps &amp; Goals 26-27'!C11</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H13" s="21">
         <f>'Apps &amp; Goals 26-27'!D11</f>
@@ -49486,7 +49530,7 @@
       </c>
       <c r="J13" s="25">
         <f t="shared" si="0"/>
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K13" s="25">
         <f t="shared" si="1"/>
@@ -49667,7 +49711,7 @@
       <c r="F14" s="25"/>
       <c r="G14" s="21">
         <f>'Apps &amp; Goals 26-27'!C12</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H14" s="21">
         <f>'Apps &amp; Goals 26-27'!D12</f>
@@ -49679,7 +49723,7 @@
       </c>
       <c r="J14" s="25">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K14" s="25">
         <f t="shared" si="1"/>
@@ -49860,7 +49904,7 @@
       <c r="F15" s="25"/>
       <c r="G15" s="21">
         <f>'Apps &amp; Goals 26-27'!C13</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" s="21">
         <f>'Apps &amp; Goals 26-27'!D13</f>
@@ -49872,7 +49916,7 @@
       </c>
       <c r="J15" s="25">
         <f t="shared" si="0"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K15" s="25">
         <f t="shared" si="1"/>
@@ -50425,7 +50469,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C18" s="25">
         <v>0</v>
@@ -50439,7 +50483,7 @@
       <c r="F18" s="25"/>
       <c r="G18" s="21">
         <f>'Apps &amp; Goals 26-27'!C16</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H18" s="21">
         <f>'Apps &amp; Goals 26-27'!D16</f>
@@ -50451,7 +50495,7 @@
       </c>
       <c r="J18" s="25">
         <f t="shared" ref="J18:J39" si="15">G18+C18</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K18" s="25">
         <f t="shared" ref="K18:K39" si="16">H18+D18</f>
@@ -50465,7 +50509,7 @@
         <v>15</v>
       </c>
       <c r="N18" s="45" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="O18" s="26">
         <v>0</v>
@@ -50502,7 +50546,7 @@
         <v>0</v>
       </c>
       <c r="Z18" s="57" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AA18" s="24">
         <v>0</v>
@@ -50539,7 +50583,7 @@
         <v>0</v>
       </c>
       <c r="AL18" s="63" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AM18" s="18">
         <v>0</v>
@@ -50576,7 +50620,7 @@
         <v>0</v>
       </c>
       <c r="AX18" s="32" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AY18" s="33">
         <v>0</v>
@@ -50632,7 +50676,7 @@
       <c r="F19" s="25"/>
       <c r="G19" s="21">
         <f>'Apps &amp; Goals 26-27'!C17</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H19" s="21">
         <f>'Apps &amp; Goals 26-27'!D17</f>
@@ -50644,7 +50688,7 @@
       </c>
       <c r="J19" s="25">
         <f t="shared" si="15"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K19" s="25">
         <f t="shared" si="16"/>
@@ -51211,7 +51255,7 @@
       <c r="F22" s="25"/>
       <c r="G22" s="21">
         <f>'Apps &amp; Goals 26-27'!C20</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H22" s="21">
         <f>'Apps &amp; Goals 26-27'!D20</f>
@@ -51223,7 +51267,7 @@
       </c>
       <c r="J22" s="25">
         <f t="shared" si="15"/>
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K22" s="25">
         <f t="shared" si="16"/>
@@ -51404,7 +51448,7 @@
       <c r="F23" s="25"/>
       <c r="G23" s="21">
         <f>'Apps &amp; Goals 26-27'!C21</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H23" s="21">
         <f>'Apps &amp; Goals 26-27'!D21</f>
@@ -51416,7 +51460,7 @@
       </c>
       <c r="J23" s="25">
         <f t="shared" si="15"/>
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K23" s="25">
         <f t="shared" si="16"/>
@@ -51790,7 +51834,7 @@
       <c r="F25" s="25"/>
       <c r="G25" s="21">
         <f>'Apps &amp; Goals 26-27'!C23</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H25" s="21">
         <f>'Apps &amp; Goals 26-27'!D23</f>
@@ -51802,7 +51846,7 @@
       </c>
       <c r="J25" s="25">
         <f t="shared" si="15"/>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K25" s="25">
         <f t="shared" si="16"/>
@@ -52176,7 +52220,7 @@
       <c r="F27" s="25"/>
       <c r="G27" s="21">
         <f>'Apps &amp; Goals 26-27'!C25</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H27" s="21">
         <f>'Apps &amp; Goals 26-27'!D25</f>
@@ -52188,7 +52232,7 @@
       </c>
       <c r="J27" s="25">
         <f t="shared" si="15"/>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K27" s="25">
         <f t="shared" si="16"/>
@@ -52369,11 +52413,11 @@
       <c r="F28" s="25"/>
       <c r="G28" s="21">
         <f>'Apps &amp; Goals 26-27'!C26</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28" s="21">
         <f>'Apps &amp; Goals 26-27'!D26</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" s="21">
         <f>'Apps &amp; Goals 26-27'!E26</f>
@@ -52381,11 +52425,11 @@
       </c>
       <c r="J28" s="25">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K28" s="25">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="25">
         <f t="shared" si="17"/>
@@ -52755,7 +52799,7 @@
       <c r="F30" s="25"/>
       <c r="G30" s="21">
         <f>'Apps &amp; Goals 26-27'!C28</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H30" s="21">
         <f>'Apps &amp; Goals 26-27'!D28</f>
@@ -52763,11 +52807,11 @@
       </c>
       <c r="I30" s="21">
         <f>'Apps &amp; Goals 26-27'!E28</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" s="25">
         <f t="shared" si="15"/>
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K30" s="25">
         <f t="shared" si="16"/>
@@ -52775,7 +52819,7 @@
       </c>
       <c r="L30" s="25">
         <f t="shared" si="17"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M30">
         <v>41</v>
@@ -53527,7 +53571,7 @@
       <c r="F34" s="25"/>
       <c r="G34" s="21">
         <f>'Apps &amp; Goals 26-27'!C32</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H34" s="21">
         <f>'Apps &amp; Goals 26-27'!D32</f>
@@ -53539,7 +53583,7 @@
       </c>
       <c r="J34" s="25">
         <f t="shared" si="15"/>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K34" s="25">
         <f t="shared" si="16"/>
@@ -54697,72 +54741,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C1" s="234" t="s">
+      <c r="C1" s="237" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="234" t="s">
+      <c r="D1" s="237" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="234" t="s">
+      <c r="E1" s="237" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="274" t="s">
+      <c r="F1" s="267" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="275"/>
-      <c r="H1" s="276"/>
-      <c r="I1" s="277" t="s">
+      <c r="G1" s="268"/>
+      <c r="H1" s="269"/>
+      <c r="I1" s="270" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="278"/>
-      <c r="K1" s="279"/>
-      <c r="L1" s="244" t="s">
+      <c r="J1" s="271"/>
+      <c r="K1" s="272"/>
+      <c r="L1" s="274" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="245"/>
-      <c r="N1" s="246"/>
-      <c r="O1" s="247" t="s">
+      <c r="M1" s="275"/>
+      <c r="N1" s="276"/>
+      <c r="O1" s="277" t="s">
         <v>199</v>
       </c>
-      <c r="P1" s="248"/>
-      <c r="Q1" s="249"/>
-      <c r="R1" s="250" t="s">
+      <c r="P1" s="278"/>
+      <c r="Q1" s="279"/>
+      <c r="R1" s="243" t="s">
         <v>200</v>
       </c>
-      <c r="S1" s="251"/>
-      <c r="T1" s="252"/>
-      <c r="U1" s="253" t="s">
+      <c r="S1" s="244"/>
+      <c r="T1" s="245"/>
+      <c r="U1" s="246" t="s">
         <v>306</v>
       </c>
-      <c r="V1" s="254"/>
-      <c r="W1" s="255"/>
+      <c r="V1" s="247"/>
+      <c r="W1" s="248"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="235"/>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="256" t="s">
-        <v>434</v>
-      </c>
-      <c r="G2" s="257"/>
-      <c r="H2" s="258"/>
-      <c r="I2" s="271"/>
-      <c r="J2" s="272"/>
-      <c r="K2" s="273"/>
-      <c r="L2" s="268"/>
-      <c r="M2" s="269"/>
-      <c r="N2" s="270"/>
-      <c r="O2" s="265"/>
-      <c r="P2" s="266"/>
-      <c r="Q2" s="267"/>
-      <c r="R2" s="262"/>
-      <c r="S2" s="263"/>
-      <c r="T2" s="264"/>
-      <c r="U2" s="259"/>
-      <c r="V2" s="260"/>
-      <c r="W2" s="261"/>
+      <c r="C2" s="238"/>
+      <c r="D2" s="238"/>
+      <c r="E2" s="238"/>
+      <c r="F2" s="249" t="s">
+        <v>433</v>
+      </c>
+      <c r="G2" s="250"/>
+      <c r="H2" s="251"/>
+      <c r="I2" s="264"/>
+      <c r="J2" s="265"/>
+      <c r="K2" s="266"/>
+      <c r="L2" s="261"/>
+      <c r="M2" s="262"/>
+      <c r="N2" s="263"/>
+      <c r="O2" s="258"/>
+      <c r="P2" s="259"/>
+      <c r="Q2" s="260"/>
+      <c r="R2" s="255"/>
+      <c r="S2" s="256"/>
+      <c r="T2" s="257"/>
+      <c r="U2" s="252"/>
+      <c r="V2" s="253"/>
+      <c r="W2" s="254"/>
     </row>
     <row r="3" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -54771,9 +54815,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="243"/>
-      <c r="D3" s="243"/>
-      <c r="E3" s="243"/>
+      <c r="C3" s="273"/>
+      <c r="D3" s="273"/>
+      <c r="E3" s="273"/>
       <c r="F3" s="189" t="s">
         <v>393</v>
       </c>
@@ -55290,7 +55334,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="149" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C16" s="58">
         <f t="shared" ref="C16:C37" si="2">SUM(F16,I16,L16,O16,R16,U16)</f>
@@ -56197,11 +56241,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="F2:H2"/>
@@ -56212,6 +56251,11 @@
     <mergeCell ref="U2:W2"/>
     <mergeCell ref="L1:N1"/>
     <mergeCell ref="O1:Q1"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:W31">
     <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
@@ -56419,7 +56463,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="149" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="20"/>
@@ -56707,51 +56751,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="302" t="s">
+      <c r="C1" s="283" t="s">
         <v>202</v>
       </c>
-      <c r="D1" s="303"/>
-      <c r="E1" s="303"/>
-      <c r="F1" s="303"/>
-      <c r="G1" s="303"/>
-      <c r="H1" s="303"/>
-      <c r="I1" s="304"/>
+      <c r="D1" s="284"/>
+      <c r="E1" s="284"/>
+      <c r="F1" s="284"/>
+      <c r="G1" s="284"/>
+      <c r="H1" s="284"/>
+      <c r="I1" s="285"/>
       <c r="J1" s="114" t="s">
         <v>195</v>
       </c>
       <c r="K1" s="115" t="s">
         <v>194</v>
       </c>
-      <c r="L1" s="282" t="s">
+      <c r="L1" s="307" t="s">
         <v>287</v>
       </c>
-      <c r="M1" s="287"/>
-      <c r="N1" s="287"/>
-      <c r="O1" s="287"/>
-      <c r="P1" s="287"/>
-      <c r="Q1" s="287"/>
-      <c r="R1" s="287"/>
-      <c r="S1" s="287"/>
-      <c r="T1" s="287"/>
-      <c r="U1" s="287"/>
-      <c r="V1" s="287"/>
-      <c r="W1" s="287"/>
-      <c r="X1" s="287"/>
-      <c r="Y1" s="287"/>
-      <c r="Z1" s="287"/>
-      <c r="AA1" s="287"/>
-      <c r="AB1" s="287"/>
-      <c r="AC1" s="287"/>
-      <c r="AD1" s="287"/>
-      <c r="AE1" s="287"/>
-      <c r="AF1" s="287"/>
-      <c r="AG1" s="288"/>
-      <c r="AH1" s="282" t="s">
+      <c r="M1" s="312"/>
+      <c r="N1" s="312"/>
+      <c r="O1" s="312"/>
+      <c r="P1" s="312"/>
+      <c r="Q1" s="312"/>
+      <c r="R1" s="312"/>
+      <c r="S1" s="312"/>
+      <c r="T1" s="312"/>
+      <c r="U1" s="312"/>
+      <c r="V1" s="312"/>
+      <c r="W1" s="312"/>
+      <c r="X1" s="312"/>
+      <c r="Y1" s="312"/>
+      <c r="Z1" s="312"/>
+      <c r="AA1" s="312"/>
+      <c r="AB1" s="312"/>
+      <c r="AC1" s="312"/>
+      <c r="AD1" s="312"/>
+      <c r="AE1" s="312"/>
+      <c r="AF1" s="312"/>
+      <c r="AG1" s="313"/>
+      <c r="AH1" s="307" t="s">
         <v>175</v>
       </c>
-      <c r="AI1" s="283"/>
-      <c r="AJ1" s="283"/>
-      <c r="AK1" s="284"/>
+      <c r="AI1" s="308"/>
+      <c r="AJ1" s="308"/>
+      <c r="AK1" s="309"/>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B2" s="111"/>
@@ -61951,15 +61995,15 @@
         <f t="shared" ref="J80:J111" si="2">H80-I80</f>
         <v>2</v>
       </c>
-      <c r="K80" s="289" t="s">
-        <v>436</v>
-      </c>
-      <c r="L80" s="290"/>
-      <c r="M80" s="291"/>
+      <c r="K80" s="314" t="s">
+        <v>435</v>
+      </c>
+      <c r="L80" s="315"/>
+      <c r="M80" s="316"/>
       <c r="O80" s="133"/>
       <c r="P80" s="133"/>
-      <c r="W80" s="285"/>
-      <c r="X80" s="285"/>
+      <c r="W80" s="310"/>
+      <c r="X80" s="310"/>
       <c r="Y80" s="70" t="s">
         <v>211</v>
       </c>
@@ -62009,15 +62053,15 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K81" s="292"/>
-      <c r="L81" s="293"/>
-      <c r="M81" s="294"/>
+      <c r="K81" s="317"/>
+      <c r="L81" s="318"/>
+      <c r="M81" s="319"/>
       <c r="O81" s="133"/>
       <c r="P81" s="133"/>
-      <c r="W81" s="285" t="s">
+      <c r="W81" s="310" t="s">
         <v>209</v>
       </c>
-      <c r="X81" s="285"/>
+      <c r="X81" s="310"/>
       <c r="Y81" s="70">
         <f>COUNTIF(L3:AG40,3)</f>
         <v>481</v>
@@ -62073,17 +62117,17 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K82" s="295" t="s">
-        <v>437</v>
-      </c>
-      <c r="L82" s="296"/>
-      <c r="M82" s="297"/>
+      <c r="K82" s="320" t="s">
+        <v>436</v>
+      </c>
+      <c r="L82" s="321"/>
+      <c r="M82" s="322"/>
       <c r="O82" s="133"/>
       <c r="P82" s="133"/>
-      <c r="W82" s="285" t="s">
+      <c r="W82" s="310" t="s">
         <v>210</v>
       </c>
-      <c r="X82" s="285"/>
+      <c r="X82" s="310"/>
       <c r="Y82" s="70">
         <f>COUNTIF(K3:K40,3)+COUNTIF(J3:J15,3)</f>
         <v>25</v>
@@ -62139,17 +62183,17 @@
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="K83" s="298" t="s">
-        <v>438</v>
-      </c>
-      <c r="L83" s="299"/>
-      <c r="M83" s="300"/>
+      <c r="K83" s="323" t="s">
+        <v>437</v>
+      </c>
+      <c r="L83" s="324"/>
+      <c r="M83" s="325"/>
       <c r="O83" s="133"/>
       <c r="P83" s="133"/>
-      <c r="W83" s="286" t="s">
+      <c r="W83" s="311" t="s">
         <v>97</v>
       </c>
-      <c r="X83" s="286"/>
+      <c r="X83" s="311"/>
       <c r="Y83" s="196">
         <v>220</v>
       </c>
@@ -62202,15 +62246,15 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="K84" s="317" t="s">
+      <c r="K84" s="298" t="s">
         <v>284</v>
       </c>
-      <c r="L84" s="318"/>
-      <c r="M84" s="319"/>
+      <c r="L84" s="299"/>
+      <c r="M84" s="300"/>
       <c r="O84" s="141"/>
       <c r="P84" s="141"/>
-      <c r="W84" s="301"/>
-      <c r="X84" s="301"/>
+      <c r="W84" s="282"/>
+      <c r="X84" s="282"/>
       <c r="Y84" s="198"/>
       <c r="Z84" s="198"/>
       <c r="AA84" s="198"/>
@@ -62248,9 +62292,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K85" s="320"/>
-      <c r="L85" s="321"/>
-      <c r="M85" s="322"/>
+      <c r="K85" s="301"/>
+      <c r="L85" s="302"/>
+      <c r="M85" s="303"/>
       <c r="O85" s="141"/>
       <c r="P85" s="141"/>
     </row>
@@ -62284,9 +62328,9 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="K86" s="320"/>
-      <c r="L86" s="321"/>
-      <c r="M86" s="322"/>
+      <c r="K86" s="301"/>
+      <c r="L86" s="302"/>
+      <c r="M86" s="303"/>
       <c r="O86" s="141"/>
       <c r="P86" s="141"/>
     </row>
@@ -62320,9 +62364,9 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="K87" s="320"/>
-      <c r="L87" s="321"/>
-      <c r="M87" s="322"/>
+      <c r="K87" s="301"/>
+      <c r="L87" s="302"/>
+      <c r="M87" s="303"/>
       <c r="O87" s="141"/>
       <c r="P87" s="141"/>
     </row>
@@ -62356,9 +62400,9 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K88" s="320"/>
-      <c r="L88" s="321"/>
-      <c r="M88" s="322"/>
+      <c r="K88" s="301"/>
+      <c r="L88" s="302"/>
+      <c r="M88" s="303"/>
       <c r="O88" s="141"/>
       <c r="P88" s="141"/>
     </row>
@@ -62392,9 +62436,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K89" s="320"/>
-      <c r="L89" s="321"/>
-      <c r="M89" s="322"/>
+      <c r="K89" s="301"/>
+      <c r="L89" s="302"/>
+      <c r="M89" s="303"/>
       <c r="O89" s="141"/>
       <c r="P89" s="141"/>
     </row>
@@ -62428,9 +62472,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K90" s="320"/>
-      <c r="L90" s="321"/>
-      <c r="M90" s="322"/>
+      <c r="K90" s="301"/>
+      <c r="L90" s="302"/>
+      <c r="M90" s="303"/>
       <c r="O90" s="141"/>
       <c r="P90" s="141"/>
     </row>
@@ -62464,9 +62508,9 @@
         <f t="shared" si="2"/>
         <v>47</v>
       </c>
-      <c r="K91" s="320"/>
-      <c r="L91" s="321"/>
-      <c r="M91" s="322"/>
+      <c r="K91" s="301"/>
+      <c r="L91" s="302"/>
+      <c r="M91" s="303"/>
       <c r="O91" s="141"/>
       <c r="P91" s="141"/>
     </row>
@@ -62500,9 +62544,9 @@
         <f t="shared" si="2"/>
         <v>51</v>
       </c>
-      <c r="K92" s="320"/>
-      <c r="L92" s="321"/>
-      <c r="M92" s="322"/>
+      <c r="K92" s="301"/>
+      <c r="L92" s="302"/>
+      <c r="M92" s="303"/>
       <c r="O92" s="141"/>
       <c r="P92" s="141"/>
     </row>
@@ -62536,9 +62580,9 @@
         <f t="shared" si="2"/>
         <v>37</v>
       </c>
-      <c r="K93" s="320"/>
-      <c r="L93" s="321"/>
-      <c r="M93" s="322"/>
+      <c r="K93" s="301"/>
+      <c r="L93" s="302"/>
+      <c r="M93" s="303"/>
       <c r="O93" s="141"/>
       <c r="P93" s="141"/>
     </row>
@@ -62572,9 +62616,9 @@
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="K94" s="320"/>
-      <c r="L94" s="321"/>
-      <c r="M94" s="322"/>
+      <c r="K94" s="301"/>
+      <c r="L94" s="302"/>
+      <c r="M94" s="303"/>
       <c r="O94" s="141"/>
       <c r="P94" s="141"/>
     </row>
@@ -62608,9 +62652,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K95" s="320"/>
-      <c r="L95" s="321"/>
-      <c r="M95" s="322"/>
+      <c r="K95" s="301"/>
+      <c r="L95" s="302"/>
+      <c r="M95" s="303"/>
       <c r="O95" s="141"/>
       <c r="P95" s="141"/>
     </row>
@@ -62644,9 +62688,9 @@
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="K96" s="320"/>
-      <c r="L96" s="321"/>
-      <c r="M96" s="322"/>
+      <c r="K96" s="301"/>
+      <c r="L96" s="302"/>
+      <c r="M96" s="303"/>
       <c r="O96" s="141"/>
       <c r="P96" s="141"/>
     </row>
@@ -62680,9 +62724,9 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="K97" s="320"/>
-      <c r="L97" s="321"/>
-      <c r="M97" s="322"/>
+      <c r="K97" s="301"/>
+      <c r="L97" s="302"/>
+      <c r="M97" s="303"/>
       <c r="O97" s="141"/>
       <c r="P97" s="141"/>
     </row>
@@ -62716,9 +62760,9 @@
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="K98" s="320"/>
-      <c r="L98" s="321"/>
-      <c r="M98" s="322"/>
+      <c r="K98" s="301"/>
+      <c r="L98" s="302"/>
+      <c r="M98" s="303"/>
       <c r="O98" s="141"/>
       <c r="P98" s="141"/>
     </row>
@@ -62752,9 +62796,9 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K99" s="320"/>
-      <c r="L99" s="321"/>
-      <c r="M99" s="322"/>
+      <c r="K99" s="301"/>
+      <c r="L99" s="302"/>
+      <c r="M99" s="303"/>
       <c r="O99" s="141"/>
       <c r="P99" s="141"/>
     </row>
@@ -62788,9 +62832,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K100" s="320"/>
-      <c r="L100" s="321"/>
-      <c r="M100" s="322"/>
+      <c r="K100" s="301"/>
+      <c r="L100" s="302"/>
+      <c r="M100" s="303"/>
       <c r="O100" s="141"/>
       <c r="P100" s="141"/>
     </row>
@@ -62824,9 +62868,9 @@
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="K101" s="320"/>
-      <c r="L101" s="321"/>
-      <c r="M101" s="322"/>
+      <c r="K101" s="301"/>
+      <c r="L101" s="302"/>
+      <c r="M101" s="303"/>
       <c r="O101" s="141"/>
       <c r="P101" s="141"/>
     </row>
@@ -62860,9 +62904,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K102" s="320"/>
-      <c r="L102" s="321"/>
-      <c r="M102" s="322"/>
+      <c r="K102" s="301"/>
+      <c r="L102" s="302"/>
+      <c r="M102" s="303"/>
       <c r="O102" s="141"/>
       <c r="P102" s="141"/>
     </row>
@@ -62896,9 +62940,9 @@
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="K103" s="320"/>
-      <c r="L103" s="321"/>
-      <c r="M103" s="322"/>
+      <c r="K103" s="301"/>
+      <c r="L103" s="302"/>
+      <c r="M103" s="303"/>
       <c r="O103" s="141"/>
       <c r="P103" s="141"/>
     </row>
@@ -62932,9 +62976,9 @@
         <f t="shared" si="2"/>
         <v>33</v>
       </c>
-      <c r="K104" s="320"/>
-      <c r="L104" s="321"/>
-      <c r="M104" s="322"/>
+      <c r="K104" s="301"/>
+      <c r="L104" s="302"/>
+      <c r="M104" s="303"/>
       <c r="O104" s="141"/>
       <c r="P104" s="141"/>
     </row>
@@ -62968,9 +63012,9 @@
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="K105" s="323"/>
-      <c r="L105" s="324"/>
-      <c r="M105" s="325"/>
+      <c r="K105" s="304"/>
+      <c r="L105" s="305"/>
+      <c r="M105" s="306"/>
       <c r="O105" s="141"/>
       <c r="P105" s="141"/>
     </row>
@@ -63004,11 +63048,11 @@
         <f t="shared" si="2"/>
         <v>21</v>
       </c>
-      <c r="K106" s="314" t="s">
+      <c r="K106" s="295" t="s">
         <v>286</v>
       </c>
-      <c r="L106" s="315"/>
-      <c r="M106" s="316"/>
+      <c r="L106" s="296"/>
+      <c r="M106" s="297"/>
       <c r="O106" s="126"/>
       <c r="P106" s="126"/>
     </row>
@@ -63042,11 +63086,11 @@
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="K107" s="314" t="s">
+      <c r="K107" s="295" t="s">
         <v>288</v>
       </c>
-      <c r="L107" s="315"/>
-      <c r="M107" s="316"/>
+      <c r="L107" s="296"/>
+      <c r="M107" s="297"/>
       <c r="O107" s="126"/>
       <c r="P107" s="126"/>
     </row>
@@ -63080,11 +63124,11 @@
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="K108" s="305" t="s">
+      <c r="K108" s="286" t="s">
         <v>289</v>
       </c>
-      <c r="L108" s="306"/>
-      <c r="M108" s="307"/>
+      <c r="L108" s="287"/>
+      <c r="M108" s="288"/>
       <c r="O108" s="126"/>
       <c r="P108" s="126"/>
     </row>
@@ -63118,9 +63162,9 @@
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="K109" s="308"/>
-      <c r="L109" s="309"/>
-      <c r="M109" s="310"/>
+      <c r="K109" s="289"/>
+      <c r="L109" s="290"/>
+      <c r="M109" s="291"/>
       <c r="O109" s="126"/>
       <c r="P109" s="126"/>
     </row>
@@ -63154,9 +63198,9 @@
         <f t="shared" si="2"/>
         <v>45</v>
       </c>
-      <c r="K110" s="308"/>
-      <c r="L110" s="309"/>
-      <c r="M110" s="310"/>
+      <c r="K110" s="289"/>
+      <c r="L110" s="290"/>
+      <c r="M110" s="291"/>
       <c r="O110" s="126"/>
       <c r="P110" s="126"/>
     </row>
@@ -63190,9 +63234,9 @@
         <f t="shared" si="2"/>
         <v>62</v>
       </c>
-      <c r="K111" s="308"/>
-      <c r="L111" s="309"/>
-      <c r="M111" s="310"/>
+      <c r="K111" s="289"/>
+      <c r="L111" s="290"/>
+      <c r="M111" s="291"/>
       <c r="O111" s="126"/>
       <c r="P111" s="126"/>
     </row>
@@ -63230,9 +63274,9 @@
         <f t="shared" ref="J112:J114" si="6">H112-I112</f>
         <v>34</v>
       </c>
-      <c r="K112" s="308"/>
-      <c r="L112" s="309"/>
-      <c r="M112" s="310"/>
+      <c r="K112" s="289"/>
+      <c r="L112" s="290"/>
+      <c r="M112" s="291"/>
     </row>
     <row r="113" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="156" t="s">
@@ -63268,13 +63312,13 @@
         <f t="shared" si="6"/>
         <v>43</v>
       </c>
-      <c r="K113" s="311"/>
-      <c r="L113" s="312"/>
-      <c r="M113" s="313"/>
+      <c r="K113" s="292"/>
+      <c r="L113" s="293"/>
+      <c r="M113" s="294"/>
     </row>
     <row r="114" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" s="93" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B114" s="122"/>
       <c r="C114" s="122"/>
@@ -63296,26 +63340,20 @@
       </c>
       <c r="H114" s="122">
         <f>Match!R4</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I114" s="122">
         <f>Match!S4</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J114" s="122">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A79:J112" xr:uid="{9C81160F-C24B-449F-8F5A-CB622AB71070}"/>
   <mergeCells count="15">
-    <mergeCell ref="W84:X84"/>
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="K108:M113"/>
-    <mergeCell ref="K106:M106"/>
-    <mergeCell ref="K107:M107"/>
-    <mergeCell ref="K84:M105"/>
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="W80:X80"/>
     <mergeCell ref="W81:X81"/>
@@ -63325,6 +63363,12 @@
     <mergeCell ref="K80:M81"/>
     <mergeCell ref="K82:M82"/>
     <mergeCell ref="K83:M83"/>
+    <mergeCell ref="W84:X84"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="K108:M113"/>
+    <mergeCell ref="K106:M106"/>
+    <mergeCell ref="K107:M107"/>
+    <mergeCell ref="K84:M105"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <conditionalFormatting sqref="A3:A40">
@@ -63397,13 +63441,13 @@
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="34" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="4.140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="22.140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="3.85546875" bestFit="1" customWidth="1"/>
@@ -63508,13 +63552,13 @@
         <v>1</v>
       </c>
       <c r="M3" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="N3" s="195">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O3" s="195">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P3" s="195">
         <v>0</v>
@@ -63523,60 +63567,60 @@
         <v>0</v>
       </c>
       <c r="R3" s="195">
+        <v>8</v>
+      </c>
+      <c r="S3" s="195">
+        <v>1</v>
+      </c>
+      <c r="T3" s="195">
         <v>7</v>
       </c>
-      <c r="S3" s="195">
-        <v>2</v>
-      </c>
-      <c r="T3" s="195">
-        <v>5</v>
-      </c>
       <c r="U3" s="195">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="B4" s="194">
         <v>0.875</v>
       </c>
       <c r="C4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D4" t="s">
+        <v>477</v>
+      </c>
+      <c r="E4" t="s">
+        <v>478</v>
+      </c>
+      <c r="F4" t="s">
+        <v>469</v>
+      </c>
+      <c r="G4" s="194" t="s">
+        <v>476</v>
+      </c>
+      <c r="H4" t="s">
         <v>4</v>
       </c>
-      <c r="D4" t="s">
+      <c r="I4" t="s">
         <v>429</v>
       </c>
-      <c r="E4" t="s">
-        <v>477</v>
-      </c>
-      <c r="F4" t="s">
-        <v>472</v>
-      </c>
-      <c r="G4" s="194" t="s">
-        <v>475</v>
-      </c>
-      <c r="H4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I4" t="s">
-        <v>473</v>
-      </c>
       <c r="J4" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="L4">
         <v>2</v>
       </c>
       <c r="M4" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="N4" s="195">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O4" s="195">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P4" s="195">
         <v>0</v>
@@ -63585,16 +63629,16 @@
         <v>0</v>
       </c>
       <c r="R4" s="195">
+        <v>8</v>
+      </c>
+      <c r="S4" s="195">
+        <v>2</v>
+      </c>
+      <c r="T4" s="195">
         <v>6</v>
       </c>
-      <c r="S4" s="195">
-        <v>1</v>
-      </c>
-      <c r="T4" s="195">
-        <v>5</v>
-      </c>
       <c r="U4" s="195">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
@@ -63605,28 +63649,28 @@
         <v>422</v>
       </c>
       <c r="N5" s="195">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O5" s="195">
         <v>2</v>
       </c>
       <c r="P5" s="195">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q5" s="195">
         <v>0</v>
       </c>
       <c r="R5" s="195">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S5" s="195">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T5" s="195">
         <v>3</v>
       </c>
       <c r="U5" s="195">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
@@ -63634,31 +63678,31 @@
         <v>4</v>
       </c>
       <c r="M6" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="N6" s="195">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O6" s="195">
         <v>2</v>
       </c>
       <c r="P6" s="195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="195">
         <v>1</v>
       </c>
       <c r="R6" s="195">
+        <v>13</v>
+      </c>
+      <c r="S6" s="195">
+        <v>5</v>
+      </c>
+      <c r="T6" s="195">
         <v>8</v>
       </c>
-      <c r="S6" s="195">
+      <c r="U6" s="195">
         <v>7</v>
-      </c>
-      <c r="T6" s="195">
-        <v>1</v>
-      </c>
-      <c r="U6" s="195">
-        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
@@ -63666,31 +63710,31 @@
         <v>5</v>
       </c>
       <c r="M7" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="N7" s="195">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O7" s="195">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P7" s="195">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" s="195">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="S7" s="195">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="T7" s="195">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U7" s="195">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
@@ -63698,31 +63742,31 @@
         <v>6</v>
       </c>
       <c r="M8" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="N8" s="195">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O8" s="195">
         <v>1</v>
       </c>
       <c r="P8" s="195">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q8" s="195">
         <v>0</v>
       </c>
       <c r="R8" s="195">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S8" s="195">
         <v>4</v>
       </c>
       <c r="T8" s="195">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U8" s="195">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
@@ -63730,16 +63774,16 @@
         <v>7</v>
       </c>
       <c r="M9" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="N9" s="195">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O9" s="195">
         <v>1</v>
       </c>
       <c r="P9" s="195">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q9" s="195">
         <v>0</v>
@@ -63754,7 +63798,7 @@
         <v>2</v>
       </c>
       <c r="U9" s="195">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
@@ -63765,13 +63809,13 @@
         <v>420</v>
       </c>
       <c r="N10" s="195">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O10" s="195">
         <v>1</v>
       </c>
       <c r="P10" s="195">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q10" s="195">
         <v>0</v>
@@ -63786,7 +63830,7 @@
         <v>2</v>
       </c>
       <c r="U10" s="195">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
@@ -63794,31 +63838,31 @@
         <v>9</v>
       </c>
       <c r="M11" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="N11" s="195">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O11" s="195">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P11" s="195">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="195">
         <v>2</v>
       </c>
-      <c r="Q11" s="195">
-        <v>0</v>
-      </c>
       <c r="R11" s="195">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S11" s="195">
-        <v>2</v>
-      </c>
-      <c r="T11" s="195">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="T11" s="195" t="s">
+        <v>467</v>
       </c>
       <c r="U11" s="195">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
@@ -63826,7 +63870,7 @@
         <v>10</v>
       </c>
       <c r="M12" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="N12" s="195">
         <v>3</v>
@@ -63835,22 +63879,22 @@
         <v>1</v>
       </c>
       <c r="P12" s="195">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q12" s="195">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" s="195">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S12" s="195">
+        <v>4</v>
+      </c>
+      <c r="T12" s="195">
+        <v>2</v>
+      </c>
+      <c r="U12" s="195">
         <v>5</v>
-      </c>
-      <c r="T12" s="195">
-        <v>3</v>
-      </c>
-      <c r="U12" s="195">
-        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
@@ -63858,7 +63902,7 @@
         <v>11</v>
       </c>
       <c r="M13" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="N13" s="195">
         <v>3</v>
@@ -63867,22 +63911,22 @@
         <v>1</v>
       </c>
       <c r="P13" s="195">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q13" s="195">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" s="195">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="S13" s="195">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="T13" s="195">
         <v>1</v>
       </c>
       <c r="U13" s="195">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
@@ -63890,31 +63934,31 @@
         <v>12</v>
       </c>
       <c r="M14" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="N14" s="195">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O14" s="195">
         <v>1</v>
       </c>
       <c r="P14" s="195">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q14" s="195">
         <v>1</v>
       </c>
       <c r="R14" s="195">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S14" s="195">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T14" s="195">
         <v>0</v>
       </c>
       <c r="U14" s="195">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
@@ -63922,31 +63966,31 @@
         <v>13</v>
       </c>
       <c r="M15" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="N15" s="195">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O15" s="195">
         <v>1</v>
       </c>
       <c r="P15" s="195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15" s="195">
         <v>2</v>
       </c>
       <c r="R15" s="195">
+        <v>7</v>
+      </c>
+      <c r="S15" s="195">
+        <v>7</v>
+      </c>
+      <c r="T15" s="195">
+        <v>0</v>
+      </c>
+      <c r="U15" s="195">
         <v>4</v>
-      </c>
-      <c r="S15" s="195">
-        <v>8</v>
-      </c>
-      <c r="T15" s="195" t="s">
-        <v>432</v>
-      </c>
-      <c r="U15" s="195">
-        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
@@ -63954,31 +63998,31 @@
         <v>14</v>
       </c>
       <c r="M16" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="N16" s="195">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O16" s="195">
         <v>1</v>
       </c>
       <c r="P16" s="195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="195">
         <v>2</v>
       </c>
       <c r="R16" s="195">
+        <v>3</v>
+      </c>
+      <c r="S16" s="195">
+        <v>5</v>
+      </c>
+      <c r="T16" s="195" t="s">
+        <v>479</v>
+      </c>
+      <c r="U16" s="195">
         <v>4</v>
-      </c>
-      <c r="S16" s="195">
-        <v>8</v>
-      </c>
-      <c r="T16" s="195" t="s">
-        <v>432</v>
-      </c>
-      <c r="U16" s="195">
-        <v>3</v>
       </c>
     </row>
     <row r="17" spans="12:21" x14ac:dyDescent="0.25">
@@ -63989,28 +64033,28 @@
         <v>415</v>
       </c>
       <c r="N17" s="195">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O17" s="195">
         <v>0</v>
       </c>
       <c r="P17" s="195">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q17" s="195">
         <v>1</v>
       </c>
       <c r="R17" s="195">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S17" s="195">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T17" s="195" t="s">
         <v>431</v>
       </c>
       <c r="U17" s="195">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="12:21" x14ac:dyDescent="0.25">
@@ -64018,31 +64062,31 @@
         <v>16</v>
       </c>
       <c r="M18" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="N18" s="195">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O18" s="195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P18" s="195">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="195">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R18" s="195">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S18" s="195">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="T18" s="195" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="U18" s="195">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="12:21" x14ac:dyDescent="0.25">
@@ -64050,16 +64094,16 @@
         <v>17</v>
       </c>
       <c r="M19" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
       <c r="N19" s="195">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O19" s="195">
         <v>0</v>
       </c>
       <c r="P19" s="195">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q19" s="195">
         <v>2</v>
@@ -64071,10 +64115,10 @@
         <v>5</v>
       </c>
       <c r="T19" s="195" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="U19" s="195">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="12:21" x14ac:dyDescent="0.25">
@@ -64082,10 +64126,10 @@
         <v>18</v>
       </c>
       <c r="M20" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="N20" s="195">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O20" s="195">
         <v>0</v>
@@ -64094,16 +64138,16 @@
         <v>1</v>
       </c>
       <c r="Q20" s="195">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R20" s="195">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S20" s="195">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T20" s="195" t="s">
-        <v>435</v>
+        <v>467</v>
       </c>
       <c r="U20" s="195">
         <v>1</v>
@@ -64114,31 +64158,31 @@
         <v>19</v>
       </c>
       <c r="M21" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="N21" s="195">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O21" s="195">
         <v>0</v>
       </c>
       <c r="P21" s="195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q21" s="195">
         <v>3</v>
       </c>
       <c r="R21" s="195">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S21" s="195">
         <v>7</v>
       </c>
       <c r="T21" s="195" t="s">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="U21" s="195">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="12:21" x14ac:dyDescent="0.25">
@@ -64149,7 +64193,7 @@
         <v>404</v>
       </c>
       <c r="N22" s="195">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O22" s="195">
         <v>0</v>
@@ -64158,16 +64202,16 @@
         <v>0</v>
       </c>
       <c r="Q22" s="195">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R22" s="195">
         <v>0</v>
       </c>
       <c r="S22" s="195">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" s="195" t="s">
-        <v>435</v>
+        <v>481</v>
       </c>
       <c r="U22" s="195">
         <v>0</v>
@@ -64199,13 +64243,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>444</v>
+      </c>
+      <c r="D1" t="s">
         <v>445</v>
       </c>
-      <c r="D1" t="s">
-        <v>446</v>
-      </c>
       <c r="E1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -64213,227 +64257,200 @@
         <v>350</v>
       </c>
       <c r="B2" t="s">
-        <v>452</v>
-      </c>
-      <c r="C2" s="201">
-        <v>7.2</v>
-      </c>
+        <v>451</v>
+      </c>
+      <c r="C2" s="201"/>
       <c r="D2">
         <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B3" t="s">
-        <v>468</v>
-      </c>
-      <c r="C3" s="201">
-        <v>6.5</v>
-      </c>
+        <v>473</v>
+      </c>
+      <c r="C3" s="201"/>
       <c r="D3">
         <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B4" t="s">
-        <v>453</v>
-      </c>
-      <c r="C4" s="201">
-        <v>8.1999999999999993</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="C4" s="201"/>
       <c r="D4">
         <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B5" t="s">
-        <v>463</v>
-      </c>
-      <c r="C5" s="201">
-        <v>7.7</v>
-      </c>
+        <v>462</v>
+      </c>
+      <c r="C5" s="201"/>
       <c r="D5">
         <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B6" t="s">
-        <v>454</v>
-      </c>
-      <c r="C6" s="201">
-        <v>7.8</v>
-      </c>
+        <v>453</v>
+      </c>
+      <c r="C6" s="201"/>
       <c r="D6" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B7" t="s">
-        <v>462</v>
-      </c>
-      <c r="C7" s="201">
-        <v>6.8</v>
-      </c>
+        <v>474</v>
+      </c>
+      <c r="C7" s="201"/>
       <c r="D7" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B8" t="s">
-        <v>455</v>
-      </c>
-      <c r="C8" s="201">
-        <v>8.1</v>
-      </c>
-      <c r="D8">
-        <v>90</v>
+        <v>454</v>
+      </c>
+      <c r="C8" s="201"/>
+      <c r="D8" t="s">
+        <v>460</v>
+      </c>
+      <c r="E8" t="s">
+        <v>466</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B9" t="s">
-        <v>456</v>
-      </c>
-      <c r="C9" s="201">
-        <v>9.1</v>
-      </c>
-      <c r="D9">
-        <v>90</v>
-      </c>
-      <c r="E9" t="s">
-        <v>466</v>
+        <v>455</v>
+      </c>
+      <c r="C9" s="201"/>
+      <c r="D9" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B10" t="s">
-        <v>478</v>
-      </c>
-      <c r="C10" s="201">
-        <v>6.7</v>
-      </c>
+        <v>456</v>
+      </c>
+      <c r="C10" s="201"/>
       <c r="D10" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B11" t="s">
-        <v>458</v>
-      </c>
-      <c r="C11" s="201">
-        <v>7.4</v>
-      </c>
-      <c r="D11" t="s">
-        <v>461</v>
+        <v>457</v>
+      </c>
+      <c r="C11" s="201"/>
+      <c r="D11">
+        <v>90</v>
+      </c>
+      <c r="E11" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B12" t="s">
-        <v>469</v>
-      </c>
-      <c r="C12" s="201">
-        <v>6.9</v>
-      </c>
-      <c r="D12" t="s">
-        <v>461</v>
+        <v>458</v>
+      </c>
+      <c r="C12" s="201"/>
+      <c r="D12">
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="B13" t="s">
-        <v>470</v>
-      </c>
-      <c r="C13" s="201">
-        <v>7</v>
-      </c>
+        <v>475</v>
+      </c>
+      <c r="C13" s="201"/>
       <c r="D13" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B14" t="s">
-        <v>457</v>
-      </c>
-      <c r="C14" s="201">
-        <v>7.5</v>
-      </c>
+        <v>471</v>
+      </c>
+      <c r="C14" s="201"/>
       <c r="D14" t="s">
-        <v>460</v>
-      </c>
-      <c r="E14" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="B15" t="s">
+        <v>461</v>
+      </c>
+      <c r="C15" s="201"/>
+      <c r="D15" t="s">
         <v>459</v>
-      </c>
-      <c r="C15" s="201">
-        <v>6.9</v>
-      </c>
-      <c r="D15" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B16" t="s">
-        <v>479</v>
-      </c>
-      <c r="C16" s="201">
-        <v>7</v>
-      </c>
+        <v>472</v>
+      </c>
+      <c r="C16" s="201"/>
       <c r="D16" t="s">
-        <v>460</v>
+        <v>459</v>
+      </c>
+      <c r="E16" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B17" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C17" s="201"/>
       <c r="D17" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
   </sheetData>
@@ -65453,15 +65470,15 @@
       </c>
       <c r="J30" s="11">
         <f>'Apps &amp; Goals'!U10</f>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K30" s="9">
         <f>'Apps &amp; Goals'!T10</f>
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L30" s="14">
         <f>J30/K30</f>
-        <v>0.26182965299684541</v>
+        <v>0.26415094339622641</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
@@ -65622,7 +65639,7 @@
       <c r="U2" s="210"/>
       <c r="V2" s="210"/>
       <c r="Z2" s="125">
-        <v>46275</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
@@ -65689,7 +65706,7 @@
         <v>395</v>
       </c>
       <c r="W3" s="200" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
@@ -65707,7 +65724,7 @@
       </c>
       <c r="E4" s="6">
         <f>'#'!J6</f>
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F4" s="6">
         <f>'#'!K6</f>
@@ -65767,7 +65784,7 @@
       </c>
       <c r="T4" s="2">
         <f t="shared" ref="T4:V4" si="0">SUM(E4,H4,K4,N4,Q4)</f>
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="U4" s="2">
         <f t="shared" ref="U4" si="1">SUM(F4,I4,L4,O4,R4)</f>
@@ -65965,7 +65982,7 @@
       </c>
       <c r="E7" s="6">
         <f>'#'!J9</f>
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F7" s="6">
         <f>'#'!K9</f>
@@ -66025,7 +66042,7 @@
       </c>
       <c r="T7" s="2">
         <f t="shared" si="2"/>
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="U7" s="2">
         <f t="shared" si="3"/>
@@ -66137,7 +66154,7 @@
       </c>
       <c r="E9" s="6">
         <f>'#'!J11</f>
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F9" s="6">
         <f>'#'!K11</f>
@@ -66197,7 +66214,7 @@
       </c>
       <c r="T9" s="2">
         <f t="shared" si="2"/>
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="U9" s="2">
         <f t="shared" si="3"/>
@@ -66223,11 +66240,11 @@
       </c>
       <c r="E10" s="6">
         <f>'#'!J12</f>
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F10" s="6">
         <f>'#'!K12</f>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G10" s="6">
         <f>'#'!L12</f>
@@ -66283,11 +66300,11 @@
       </c>
       <c r="T10" s="2">
         <f t="shared" si="2"/>
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="U10" s="2">
         <f t="shared" si="3"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="V10" s="2">
         <f t="shared" si="4"/>
@@ -66309,7 +66326,7 @@
       </c>
       <c r="E11" s="6">
         <f>'#'!J13</f>
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F11" s="6">
         <f>'#'!K13</f>
@@ -66369,7 +66386,7 @@
       </c>
       <c r="T11" s="2">
         <f t="shared" si="2"/>
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="U11" s="2">
         <f t="shared" si="3"/>
@@ -66395,7 +66412,7 @@
       </c>
       <c r="E12" s="6">
         <f>'#'!J14</f>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F12" s="6">
         <f>'#'!K14</f>
@@ -66455,7 +66472,7 @@
       </c>
       <c r="T12" s="2">
         <f t="shared" si="2"/>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="U12" s="2">
         <f t="shared" si="3"/>
@@ -66481,7 +66498,7 @@
       </c>
       <c r="E13" s="6">
         <f>'#'!J15</f>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F13" s="6">
         <f>'#'!K15</f>
@@ -66541,7 +66558,7 @@
       </c>
       <c r="T13" s="2">
         <f t="shared" si="2"/>
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="U13" s="2">
         <f t="shared" si="3"/>
@@ -66735,11 +66752,11 @@
         <v>352</v>
       </c>
       <c r="D16" s="149" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E16" s="6">
         <f>'#'!J18</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F16" s="6">
         <f>'#'!K18</f>
@@ -66799,7 +66816,7 @@
       </c>
       <c r="T16" s="2">
         <f t="shared" ref="T16:T37" si="5">SUM(E16,H16,K16,N16,Q16)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U16" s="2">
         <f t="shared" ref="U16:U37" si="6">SUM(F16,I16,L16,O16,R16)</f>
@@ -66825,7 +66842,7 @@
       </c>
       <c r="E17" s="6">
         <f>'#'!J19</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F17" s="6">
         <f>'#'!K19</f>
@@ -66885,7 +66902,7 @@
       </c>
       <c r="T17" s="2">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U17" s="2">
         <f t="shared" si="6"/>
@@ -67068,7 +67085,7 @@
         <v>2</v>
       </c>
       <c r="W19" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.25">
@@ -67086,7 +67103,7 @@
       </c>
       <c r="E20" s="6">
         <f>'#'!J22</f>
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F20" s="6">
         <f>'#'!K22</f>
@@ -67146,7 +67163,7 @@
       </c>
       <c r="T20" s="2">
         <f t="shared" si="5"/>
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U20" s="2">
         <f t="shared" si="6"/>
@@ -67172,7 +67189,7 @@
       </c>
       <c r="E21" s="6">
         <f>'#'!J23</f>
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F21" s="6">
         <f>'#'!K23</f>
@@ -67232,7 +67249,7 @@
       </c>
       <c r="T21" s="2">
         <f t="shared" si="5"/>
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="U21" s="2">
         <f t="shared" si="6"/>
@@ -67344,7 +67361,7 @@
       </c>
       <c r="E23" s="6">
         <f>'#'!J25</f>
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F23" s="6">
         <f>'#'!K25</f>
@@ -67404,7 +67421,7 @@
       </c>
       <c r="T23" s="2">
         <f t="shared" si="5"/>
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="U23" s="2">
         <f t="shared" si="6"/>
@@ -67501,7 +67518,7 @@
         <v>0</v>
       </c>
       <c r="W24" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.25">
@@ -67519,7 +67536,7 @@
       </c>
       <c r="E25" s="6">
         <f>'#'!J27</f>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F25" s="6">
         <f>'#'!K27</f>
@@ -67579,7 +67596,7 @@
       </c>
       <c r="T25" s="2">
         <f t="shared" si="5"/>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="U25" s="2">
         <f t="shared" si="6"/>
@@ -67605,11 +67622,11 @@
       </c>
       <c r="E26" s="6">
         <f>'#'!J28</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" s="6">
         <f>'#'!K28</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" s="6">
         <f>'#'!L28</f>
@@ -67665,11 +67682,11 @@
       </c>
       <c r="T26" s="2">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U26" s="2">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V26" s="2">
         <f t="shared" si="7"/>
@@ -67777,7 +67794,7 @@
       </c>
       <c r="E28" s="6">
         <f>'#'!J30</f>
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F28" s="6">
         <f>'#'!K30</f>
@@ -67785,7 +67802,7 @@
       </c>
       <c r="G28" s="6">
         <f>'#'!L30</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H28" s="4">
         <f>'#'!V30</f>
@@ -67837,7 +67854,7 @@
       </c>
       <c r="T28" s="2">
         <f t="shared" si="5"/>
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="U28" s="2">
         <f t="shared" si="6"/>
@@ -67845,7 +67862,7 @@
       </c>
       <c r="V28" s="2">
         <f t="shared" si="7"/>
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.25">
@@ -68106,7 +68123,7 @@
         <v>0</v>
       </c>
       <c r="W31" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="32" spans="1:23" x14ac:dyDescent="0.25">
@@ -68124,7 +68141,7 @@
       </c>
       <c r="E32" s="6">
         <f>'#'!J34</f>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F32" s="6">
         <f>'#'!K34</f>
@@ -68184,7 +68201,7 @@
       </c>
       <c r="T32" s="2">
         <f t="shared" si="5"/>
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U32" s="2">
         <f t="shared" si="6"/>
@@ -68281,7 +68298,7 @@
         <v>0</v>
       </c>
       <c r="W33" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.25">

--- a/data/arsenal_stats.xlsx
+++ b/data/arsenal_stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bungeltd-my.sharepoint.com/personal/przemyslaw_iskra_bunge_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8365" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD431384-D8BE-42A0-B75A-8AC946B83E5C}"/>
+  <xr:revisionPtr revIDLastSave="8366" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24102BB1-A7B7-48A6-A680-721507145F62}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="799" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2257" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2257" uniqueCount="483">
   <si>
     <t>Arsenal FC squad statistics</t>
   </si>
@@ -1526,6 +1526,9 @@
   </si>
   <si>
     <t>−10</t>
+  </si>
+  <si>
+    <t>15.09.2026</t>
   </si>
 </sst>
 </file>
@@ -3059,6 +3062,12 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3066,9 +3075,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3083,7 +3089,13 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3095,32 +3107,14 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="54" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3158,6 +3152,15 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="28" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3165,6 +3168,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="61" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="10" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="37" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="11" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3257,31 +3281,67 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="61" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="10" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="37" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="11" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="54" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3358,63 +3418,6 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6469,7 +6472,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B67192A3-0B23-4ED1-984A-EF7B53097F25}" type="CELLRANGE">
+                    <a:fld id="{9D521208-3E63-4FC9-9B68-28E726336FAE}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6503,7 +6506,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B846EE4C-7636-4ED0-922F-8B16A2D722AE}" type="CELLRANGE">
+                    <a:fld id="{7384FCB1-74B1-44BB-8B12-A820C40A1C35}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6537,7 +6540,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{1FB1BAA0-EA02-4A16-91DC-29EC0349216B}" type="CELLRANGE">
+                    <a:fld id="{741905E0-B3A9-4E41-B782-22BB7220D4CA}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6571,7 +6574,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C68A256F-53DE-483A-AC43-2B499573B296}" type="CELLRANGE">
+                    <a:fld id="{2A06E546-FFAD-4823-8E4D-313970227B1D}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6605,7 +6608,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F2243CF3-7D4B-4A76-84C7-57C3F7F6DD14}" type="CELLRANGE">
+                    <a:fld id="{53A23186-5113-40DC-99A0-503BC2D08310}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6639,7 +6642,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{40DDA3CC-D242-4856-8EA1-2AF0C93C2FD4}" type="CELLRANGE">
+                    <a:fld id="{24A8B175-165E-4EA1-98A6-742A5BEEFFBB}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6673,7 +6676,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A967D1FD-CB4A-44EB-BE5C-CE87BE181A31}" type="CELLRANGE">
+                    <a:fld id="{7C27FA6E-1085-4E06-B2B4-8060866B5F82}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6707,7 +6710,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B29BD653-6B52-4AD1-BA03-613A7A40DF9B}" type="CELLRANGE">
+                    <a:fld id="{9AE3376A-08BA-4554-ABDA-3D29EF7DF8D6}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6741,7 +6744,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{DF6410AB-383F-4695-8DF2-505FAC998061}" type="CELLRANGE">
+                    <a:fld id="{C7689B89-9D79-47E3-8D6C-C9852BA7D5C1}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6775,7 +6778,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{053F2BCA-BD74-43AB-B7D8-DE1989D8D45B}" type="CELLRANGE">
+                    <a:fld id="{15CDE8B1-B511-4BF4-B62F-0FA2DB8FEBDD}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6809,7 +6812,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{284DF3A1-1EC4-433A-A521-0158F08F948A}" type="CELLRANGE">
+                    <a:fld id="{4647DEAF-89D1-49E4-BA50-A2A01852240A}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6843,7 +6846,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{BDE88EA9-DD26-46F5-9821-303CF5C93037}" type="CELLRANGE">
+                    <a:fld id="{0478D755-E623-4AD3-BA3F-AD74F3556FAB}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6892,7 +6895,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{C8BDED4F-DDEA-4351-9585-CE6D13246337}" type="CELLRANGE">
+                    <a:fld id="{7C294CC8-A5CF-4840-B031-0E117169ED78}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr>
                         <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
@@ -6951,7 +6954,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{098E0EDC-3D5A-4AB5-B0B7-23142AF2F940}" type="CELLRANGE">
+                    <a:fld id="{1D55FC10-3CBA-467D-B2ED-E7BA6D287039}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6985,7 +6988,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F14D9AA0-29ED-40FA-88F0-3C3F882DF0FA}" type="CELLRANGE">
+                    <a:fld id="{0925FE1F-250D-4384-BDB4-7342547D0930}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7019,7 +7022,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C8729669-64F4-4B8C-B825-21965B1E2ED2}" type="CELLRANGE">
+                    <a:fld id="{5E3DBA52-E20C-416D-978A-5367C79730F5}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7053,7 +7056,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{38CAB799-A096-4C26-AAE1-D14C681AFBB4}" type="CELLRANGE">
+                    <a:fld id="{73F596E1-F4BC-4BB9-A15E-9BBB05891E4D}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -14189,30 +14192,30 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
       <c r="B1" s="5"/>
-      <c r="C1" s="213" t="s">
+      <c r="C1" s="214" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="213"/>
-      <c r="E1" s="214" t="s">
+      <c r="D1" s="214"/>
+      <c r="E1" s="215" t="s">
         <v>120</v>
       </c>
-      <c r="F1" s="214"/>
-      <c r="G1" s="213" t="s">
+      <c r="F1" s="215"/>
+      <c r="G1" s="214" t="s">
         <v>108</v>
       </c>
-      <c r="H1" s="213"/>
-      <c r="I1" s="214" t="s">
+      <c r="H1" s="214"/>
+      <c r="I1" s="215" t="s">
         <v>110</v>
       </c>
-      <c r="J1" s="214"/>
-      <c r="K1" s="213" t="s">
+      <c r="J1" s="215"/>
+      <c r="K1" s="214" t="s">
         <v>39</v>
       </c>
-      <c r="L1" s="213"/>
-      <c r="M1" s="211" t="s">
+      <c r="L1" s="214"/>
+      <c r="M1" s="212" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="212"/>
+      <c r="N1" s="213"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -15919,30 +15922,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="213" t="s">
+      <c r="C2" s="214" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="213"/>
-      <c r="E2" s="214" t="s">
+      <c r="D2" s="214"/>
+      <c r="E2" s="215" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="214"/>
-      <c r="G2" s="213" t="s">
+      <c r="F2" s="215"/>
+      <c r="G2" s="214" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="213"/>
-      <c r="I2" s="214" t="s">
+      <c r="H2" s="214"/>
+      <c r="I2" s="215" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="214"/>
-      <c r="K2" s="213" t="s">
+      <c r="J2" s="215"/>
+      <c r="K2" s="214" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="213"/>
-      <c r="M2" s="210" t="s">
+      <c r="L2" s="214"/>
+      <c r="M2" s="207" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="210"/>
+      <c r="N2" s="207"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -17746,30 +17749,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="213" t="s">
+      <c r="C2" s="214" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="213"/>
-      <c r="E2" s="214" t="s">
+      <c r="D2" s="214"/>
+      <c r="E2" s="215" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="214"/>
-      <c r="G2" s="213" t="s">
+      <c r="F2" s="215"/>
+      <c r="G2" s="214" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="213"/>
-      <c r="I2" s="214" t="s">
+      <c r="H2" s="214"/>
+      <c r="I2" s="215" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="214"/>
-      <c r="K2" s="213" t="s">
+      <c r="J2" s="215"/>
+      <c r="K2" s="214" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="213"/>
-      <c r="M2" s="210" t="s">
+      <c r="L2" s="214"/>
+      <c r="M2" s="207" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="210"/>
+      <c r="N2" s="207"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -19436,30 +19439,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="213" t="s">
+      <c r="C2" s="214" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="213"/>
-      <c r="E2" s="214" t="s">
+      <c r="D2" s="214"/>
+      <c r="E2" s="215" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="214"/>
-      <c r="G2" s="213" t="s">
+      <c r="F2" s="215"/>
+      <c r="G2" s="214" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="213"/>
-      <c r="I2" s="214" t="s">
+      <c r="H2" s="214"/>
+      <c r="I2" s="215" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="214"/>
-      <c r="K2" s="213" t="s">
+      <c r="J2" s="215"/>
+      <c r="K2" s="214" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="213"/>
-      <c r="M2" s="210" t="s">
+      <c r="L2" s="214"/>
+      <c r="M2" s="207" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="210"/>
+      <c r="N2" s="207"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -21262,30 +21265,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="213" t="s">
+      <c r="C2" s="214" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="213"/>
-      <c r="E2" s="214" t="s">
+      <c r="D2" s="214"/>
+      <c r="E2" s="215" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="214"/>
-      <c r="G2" s="213" t="s">
+      <c r="F2" s="215"/>
+      <c r="G2" s="214" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="213"/>
-      <c r="I2" s="214" t="s">
+      <c r="H2" s="214"/>
+      <c r="I2" s="215" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="214"/>
-      <c r="K2" s="213" t="s">
+      <c r="J2" s="215"/>
+      <c r="K2" s="214" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="213"/>
-      <c r="M2" s="210" t="s">
+      <c r="L2" s="214"/>
+      <c r="M2" s="207" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="210"/>
+      <c r="N2" s="207"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -23139,31 +23142,31 @@
       </c>
       <c r="D2" s="205"/>
       <c r="E2" s="206"/>
-      <c r="F2" s="207" t="s">
+      <c r="F2" s="209" t="s">
         <v>120</v>
       </c>
-      <c r="G2" s="208"/>
-      <c r="H2" s="209"/>
+      <c r="G2" s="210"/>
+      <c r="H2" s="211"/>
       <c r="I2" s="204" t="s">
         <v>108</v>
       </c>
       <c r="J2" s="205"/>
       <c r="K2" s="206"/>
-      <c r="L2" s="207" t="s">
+      <c r="L2" s="209" t="s">
         <v>110</v>
       </c>
-      <c r="M2" s="208"/>
-      <c r="N2" s="209"/>
+      <c r="M2" s="210"/>
+      <c r="N2" s="211"/>
       <c r="O2" s="204" t="s">
         <v>39</v>
       </c>
       <c r="P2" s="205"/>
       <c r="Q2" s="206"/>
-      <c r="R2" s="210" t="s">
+      <c r="R2" s="207" t="s">
         <v>7</v>
       </c>
-      <c r="S2" s="210"/>
-      <c r="T2" s="210"/>
+      <c r="S2" s="207"/>
+      <c r="T2" s="207"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -26027,31 +26030,31 @@
       </c>
       <c r="F1" s="205"/>
       <c r="G1" s="206"/>
-      <c r="H1" s="207" t="s">
+      <c r="H1" s="209" t="s">
         <v>120</v>
       </c>
-      <c r="I1" s="208"/>
-      <c r="J1" s="209"/>
+      <c r="I1" s="210"/>
+      <c r="J1" s="211"/>
       <c r="K1" s="204" t="s">
         <v>108</v>
       </c>
       <c r="L1" s="205"/>
       <c r="M1" s="206"/>
-      <c r="N1" s="207" t="s">
+      <c r="N1" s="209" t="s">
         <v>110</v>
       </c>
-      <c r="O1" s="208"/>
-      <c r="P1" s="209"/>
+      <c r="O1" s="210"/>
+      <c r="P1" s="211"/>
       <c r="Q1" s="204" t="s">
         <v>39</v>
       </c>
       <c r="R1" s="205"/>
       <c r="S1" s="206"/>
-      <c r="T1" s="210" t="s">
+      <c r="T1" s="207" t="s">
         <v>7</v>
       </c>
-      <c r="U1" s="210"/>
-      <c r="V1" s="210"/>
+      <c r="U1" s="207"/>
+      <c r="V1" s="207"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -37625,196 +37628,196 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F1" s="219">
-        <v>1</v>
-      </c>
-      <c r="G1" s="220"/>
-      <c r="H1" s="221"/>
-      <c r="I1" s="219">
+      <c r="F1" s="216">
+        <v>1</v>
+      </c>
+      <c r="G1" s="217"/>
+      <c r="H1" s="218"/>
+      <c r="I1" s="216">
         <v>2</v>
       </c>
-      <c r="J1" s="220"/>
-      <c r="K1" s="221"/>
-      <c r="L1" s="219">
-        <v>3</v>
-      </c>
-      <c r="M1" s="220"/>
-      <c r="N1" s="221"/>
-      <c r="O1" s="219">
+      <c r="J1" s="217"/>
+      <c r="K1" s="218"/>
+      <c r="L1" s="216">
+        <v>3</v>
+      </c>
+      <c r="M1" s="217"/>
+      <c r="N1" s="218"/>
+      <c r="O1" s="216">
         <v>4</v>
       </c>
-      <c r="P1" s="220"/>
-      <c r="Q1" s="221"/>
-      <c r="R1" s="219">
+      <c r="P1" s="217"/>
+      <c r="Q1" s="218"/>
+      <c r="R1" s="216">
         <v>5</v>
       </c>
-      <c r="S1" s="220"/>
-      <c r="T1" s="221"/>
-      <c r="U1" s="219">
+      <c r="S1" s="217"/>
+      <c r="T1" s="218"/>
+      <c r="U1" s="216">
         <v>6</v>
       </c>
-      <c r="V1" s="220"/>
-      <c r="W1" s="221"/>
-      <c r="X1" s="219">
+      <c r="V1" s="217"/>
+      <c r="W1" s="218"/>
+      <c r="X1" s="216">
         <v>7</v>
       </c>
-      <c r="Y1" s="220"/>
-      <c r="Z1" s="221"/>
-      <c r="AA1" s="219">
+      <c r="Y1" s="217"/>
+      <c r="Z1" s="218"/>
+      <c r="AA1" s="216">
         <v>8</v>
       </c>
-      <c r="AB1" s="220"/>
-      <c r="AC1" s="221"/>
-      <c r="AD1" s="219">
+      <c r="AB1" s="217"/>
+      <c r="AC1" s="218"/>
+      <c r="AD1" s="216">
         <v>9</v>
       </c>
-      <c r="AE1" s="220"/>
-      <c r="AF1" s="221"/>
-      <c r="AG1" s="219">
+      <c r="AE1" s="217"/>
+      <c r="AF1" s="218"/>
+      <c r="AG1" s="216">
         <v>10</v>
       </c>
-      <c r="AH1" s="220"/>
-      <c r="AI1" s="221"/>
-      <c r="AJ1" s="219">
+      <c r="AH1" s="217"/>
+      <c r="AI1" s="218"/>
+      <c r="AJ1" s="216">
         <v>11</v>
       </c>
-      <c r="AK1" s="220"/>
-      <c r="AL1" s="221"/>
-      <c r="AM1" s="219">
+      <c r="AK1" s="217"/>
+      <c r="AL1" s="218"/>
+      <c r="AM1" s="216">
         <v>12</v>
       </c>
-      <c r="AN1" s="220"/>
-      <c r="AO1" s="221"/>
-      <c r="AP1" s="219">
+      <c r="AN1" s="217"/>
+      <c r="AO1" s="218"/>
+      <c r="AP1" s="216">
         <v>13</v>
       </c>
-      <c r="AQ1" s="220"/>
-      <c r="AR1" s="221"/>
-      <c r="AS1" s="219">
+      <c r="AQ1" s="217"/>
+      <c r="AR1" s="218"/>
+      <c r="AS1" s="216">
         <v>14</v>
       </c>
-      <c r="AT1" s="220"/>
-      <c r="AU1" s="221"/>
-      <c r="AV1" s="219">
+      <c r="AT1" s="217"/>
+      <c r="AU1" s="218"/>
+      <c r="AV1" s="216">
         <v>15</v>
       </c>
-      <c r="AW1" s="220"/>
-      <c r="AX1" s="221"/>
-      <c r="AY1" s="219">
+      <c r="AW1" s="217"/>
+      <c r="AX1" s="218"/>
+      <c r="AY1" s="216">
         <v>16</v>
       </c>
-      <c r="AZ1" s="220"/>
-      <c r="BA1" s="221"/>
-      <c r="BB1" s="219">
+      <c r="AZ1" s="217"/>
+      <c r="BA1" s="218"/>
+      <c r="BB1" s="216">
         <v>17</v>
       </c>
-      <c r="BC1" s="220"/>
-      <c r="BD1" s="221"/>
-      <c r="BE1" s="219">
+      <c r="BC1" s="217"/>
+      <c r="BD1" s="218"/>
+      <c r="BE1" s="216">
         <v>18</v>
       </c>
-      <c r="BF1" s="220"/>
-      <c r="BG1" s="221"/>
-      <c r="BH1" s="219">
+      <c r="BF1" s="217"/>
+      <c r="BG1" s="218"/>
+      <c r="BH1" s="216">
         <v>19</v>
       </c>
-      <c r="BI1" s="220"/>
-      <c r="BJ1" s="221"/>
-      <c r="BK1" s="219">
+      <c r="BI1" s="217"/>
+      <c r="BJ1" s="218"/>
+      <c r="BK1" s="216">
         <v>20</v>
       </c>
-      <c r="BL1" s="220"/>
-      <c r="BM1" s="221"/>
-      <c r="BN1" s="219">
+      <c r="BL1" s="217"/>
+      <c r="BM1" s="218"/>
+      <c r="BN1" s="216">
         <v>21</v>
       </c>
-      <c r="BO1" s="220"/>
-      <c r="BP1" s="221"/>
-      <c r="BQ1" s="219">
+      <c r="BO1" s="217"/>
+      <c r="BP1" s="218"/>
+      <c r="BQ1" s="216">
         <v>22</v>
       </c>
-      <c r="BR1" s="220"/>
-      <c r="BS1" s="221"/>
-      <c r="BT1" s="219">
+      <c r="BR1" s="217"/>
+      <c r="BS1" s="218"/>
+      <c r="BT1" s="216">
         <v>23</v>
       </c>
-      <c r="BU1" s="220"/>
-      <c r="BV1" s="221"/>
-      <c r="BW1" s="219">
+      <c r="BU1" s="217"/>
+      <c r="BV1" s="218"/>
+      <c r="BW1" s="216">
         <v>24</v>
       </c>
-      <c r="BX1" s="220"/>
-      <c r="BY1" s="221"/>
-      <c r="BZ1" s="219">
+      <c r="BX1" s="217"/>
+      <c r="BY1" s="218"/>
+      <c r="BZ1" s="216">
         <v>25</v>
       </c>
-      <c r="CA1" s="220"/>
-      <c r="CB1" s="221"/>
-      <c r="CC1" s="219">
+      <c r="CA1" s="217"/>
+      <c r="CB1" s="218"/>
+      <c r="CC1" s="216">
         <v>26</v>
       </c>
-      <c r="CD1" s="220"/>
-      <c r="CE1" s="221"/>
-      <c r="CF1" s="219">
+      <c r="CD1" s="217"/>
+      <c r="CE1" s="218"/>
+      <c r="CF1" s="216">
         <v>27</v>
       </c>
-      <c r="CG1" s="220"/>
-      <c r="CH1" s="221"/>
-      <c r="CI1" s="219">
+      <c r="CG1" s="217"/>
+      <c r="CH1" s="218"/>
+      <c r="CI1" s="216">
         <v>28</v>
       </c>
-      <c r="CJ1" s="220"/>
-      <c r="CK1" s="221"/>
-      <c r="CL1" s="219">
+      <c r="CJ1" s="217"/>
+      <c r="CK1" s="218"/>
+      <c r="CL1" s="216">
         <v>29</v>
       </c>
-      <c r="CM1" s="220"/>
-      <c r="CN1" s="221"/>
-      <c r="CO1" s="219">
+      <c r="CM1" s="217"/>
+      <c r="CN1" s="218"/>
+      <c r="CO1" s="216">
         <v>30</v>
       </c>
-      <c r="CP1" s="220"/>
-      <c r="CQ1" s="221"/>
-      <c r="CR1" s="219">
+      <c r="CP1" s="217"/>
+      <c r="CQ1" s="218"/>
+      <c r="CR1" s="216">
         <v>31</v>
       </c>
-      <c r="CS1" s="220"/>
-      <c r="CT1" s="221"/>
-      <c r="CU1" s="219">
+      <c r="CS1" s="217"/>
+      <c r="CT1" s="218"/>
+      <c r="CU1" s="216">
         <v>32</v>
       </c>
-      <c r="CV1" s="220"/>
-      <c r="CW1" s="221"/>
-      <c r="CX1" s="219">
+      <c r="CV1" s="217"/>
+      <c r="CW1" s="218"/>
+      <c r="CX1" s="216">
         <v>33</v>
       </c>
-      <c r="CY1" s="220"/>
-      <c r="CZ1" s="221"/>
-      <c r="DA1" s="219">
+      <c r="CY1" s="217"/>
+      <c r="CZ1" s="218"/>
+      <c r="DA1" s="216">
         <v>34</v>
       </c>
-      <c r="DB1" s="220"/>
-      <c r="DC1" s="221"/>
-      <c r="DD1" s="219">
+      <c r="DB1" s="217"/>
+      <c r="DC1" s="218"/>
+      <c r="DD1" s="216">
         <v>35</v>
       </c>
-      <c r="DE1" s="220"/>
-      <c r="DF1" s="221"/>
-      <c r="DG1" s="219">
+      <c r="DE1" s="217"/>
+      <c r="DF1" s="218"/>
+      <c r="DG1" s="216">
         <v>36</v>
       </c>
-      <c r="DH1" s="220"/>
-      <c r="DI1" s="221"/>
-      <c r="DJ1" s="219">
+      <c r="DH1" s="217"/>
+      <c r="DI1" s="218"/>
+      <c r="DJ1" s="216">
         <v>37</v>
       </c>
-      <c r="DK1" s="220"/>
-      <c r="DL1" s="221"/>
-      <c r="DM1" s="219">
+      <c r="DK1" s="217"/>
+      <c r="DL1" s="218"/>
+      <c r="DM1" s="216">
         <v>38</v>
       </c>
-      <c r="DN1" s="220"/>
-      <c r="DO1" s="221"/>
+      <c r="DN1" s="217"/>
+      <c r="DO1" s="218"/>
     </row>
     <row r="2" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
@@ -37828,196 +37831,196 @@
       <c r="E2" s="222" t="s">
         <v>398</v>
       </c>
-      <c r="F2" s="216" t="s">
+      <c r="F2" s="219" t="s">
         <v>346</v>
       </c>
-      <c r="G2" s="217"/>
-      <c r="H2" s="218"/>
-      <c r="I2" s="216" t="s">
+      <c r="G2" s="220"/>
+      <c r="H2" s="221"/>
+      <c r="I2" s="219" t="s">
         <v>331</v>
       </c>
-      <c r="J2" s="217"/>
-      <c r="K2" s="218"/>
-      <c r="L2" s="216" t="s">
+      <c r="J2" s="220"/>
+      <c r="K2" s="221"/>
+      <c r="L2" s="219" t="s">
         <v>330</v>
       </c>
-      <c r="M2" s="217"/>
-      <c r="N2" s="218"/>
-      <c r="O2" s="216" t="s">
+      <c r="M2" s="220"/>
+      <c r="N2" s="221"/>
+      <c r="O2" s="219" t="s">
         <v>328</v>
       </c>
-      <c r="P2" s="217"/>
-      <c r="Q2" s="218"/>
-      <c r="R2" s="216" t="s">
+      <c r="P2" s="220"/>
+      <c r="Q2" s="221"/>
+      <c r="R2" s="219" t="s">
         <v>335</v>
       </c>
-      <c r="S2" s="217"/>
-      <c r="T2" s="218"/>
-      <c r="U2" s="216" t="s">
+      <c r="S2" s="220"/>
+      <c r="T2" s="221"/>
+      <c r="U2" s="219" t="s">
         <v>320</v>
       </c>
-      <c r="V2" s="217"/>
-      <c r="W2" s="218"/>
-      <c r="X2" s="216" t="s">
+      <c r="V2" s="220"/>
+      <c r="W2" s="221"/>
+      <c r="X2" s="219" t="s">
         <v>337</v>
       </c>
-      <c r="Y2" s="217"/>
-      <c r="Z2" s="218"/>
-      <c r="AA2" s="216" t="s">
+      <c r="Y2" s="220"/>
+      <c r="Z2" s="221"/>
+      <c r="AA2" s="219" t="s">
         <v>334</v>
       </c>
-      <c r="AB2" s="217"/>
-      <c r="AC2" s="218"/>
-      <c r="AD2" s="216" t="s">
+      <c r="AB2" s="220"/>
+      <c r="AC2" s="221"/>
+      <c r="AD2" s="219" t="s">
         <v>321</v>
       </c>
-      <c r="AE2" s="217"/>
-      <c r="AF2" s="218"/>
-      <c r="AG2" s="216" t="s">
+      <c r="AE2" s="220"/>
+      <c r="AF2" s="221"/>
+      <c r="AG2" s="219" t="s">
         <v>347</v>
       </c>
-      <c r="AH2" s="217"/>
-      <c r="AI2" s="218"/>
-      <c r="AJ2" s="216" t="s">
+      <c r="AH2" s="220"/>
+      <c r="AI2" s="221"/>
+      <c r="AJ2" s="219" t="s">
         <v>324</v>
       </c>
-      <c r="AK2" s="217"/>
-      <c r="AL2" s="218"/>
-      <c r="AM2" s="216" t="s">
+      <c r="AK2" s="220"/>
+      <c r="AL2" s="221"/>
+      <c r="AM2" s="219" t="s">
         <v>323</v>
       </c>
-      <c r="AN2" s="217"/>
-      <c r="AO2" s="218"/>
-      <c r="AP2" s="216" t="s">
+      <c r="AN2" s="220"/>
+      <c r="AO2" s="221"/>
+      <c r="AP2" s="219" t="s">
         <v>332</v>
       </c>
-      <c r="AQ2" s="217"/>
-      <c r="AR2" s="218"/>
-      <c r="AS2" s="216" t="s">
+      <c r="AQ2" s="220"/>
+      <c r="AR2" s="221"/>
+      <c r="AS2" s="219" t="s">
         <v>329</v>
       </c>
-      <c r="AT2" s="217"/>
-      <c r="AU2" s="218"/>
-      <c r="AV2" s="216" t="s">
+      <c r="AT2" s="220"/>
+      <c r="AU2" s="221"/>
+      <c r="AV2" s="219" t="s">
         <v>336</v>
       </c>
-      <c r="AW2" s="217"/>
-      <c r="AX2" s="218"/>
-      <c r="AY2" s="216" t="s">
+      <c r="AW2" s="220"/>
+      <c r="AX2" s="221"/>
+      <c r="AY2" s="219" t="s">
         <v>305</v>
       </c>
-      <c r="AZ2" s="217"/>
-      <c r="BA2" s="218"/>
-      <c r="BB2" s="216" t="s">
+      <c r="AZ2" s="220"/>
+      <c r="BA2" s="221"/>
+      <c r="BB2" s="219" t="s">
         <v>326</v>
       </c>
-      <c r="BC2" s="217"/>
-      <c r="BD2" s="218"/>
-      <c r="BE2" s="216" t="s">
+      <c r="BC2" s="220"/>
+      <c r="BD2" s="221"/>
+      <c r="BE2" s="219" t="s">
         <v>325</v>
       </c>
-      <c r="BF2" s="217"/>
-      <c r="BG2" s="218"/>
-      <c r="BH2" s="216" t="s">
+      <c r="BF2" s="220"/>
+      <c r="BG2" s="221"/>
+      <c r="BH2" s="219" t="s">
         <v>348</v>
       </c>
-      <c r="BI2" s="217"/>
-      <c r="BJ2" s="218"/>
-      <c r="BK2" s="216" t="s">
+      <c r="BI2" s="220"/>
+      <c r="BJ2" s="221"/>
+      <c r="BK2" s="219" t="s">
         <v>332</v>
       </c>
-      <c r="BL2" s="217"/>
-      <c r="BM2" s="218"/>
-      <c r="BN2" s="216" t="s">
+      <c r="BL2" s="220"/>
+      <c r="BM2" s="221"/>
+      <c r="BN2" s="219" t="s">
         <v>347</v>
       </c>
-      <c r="BO2" s="217"/>
-      <c r="BP2" s="218"/>
-      <c r="BQ2" s="216" t="s">
+      <c r="BO2" s="220"/>
+      <c r="BP2" s="221"/>
+      <c r="BQ2" s="219" t="s">
         <v>324</v>
       </c>
-      <c r="BR2" s="217"/>
-      <c r="BS2" s="218"/>
-      <c r="BT2" s="216" t="s">
+      <c r="BR2" s="220"/>
+      <c r="BS2" s="221"/>
+      <c r="BT2" s="219" t="s">
         <v>323</v>
       </c>
-      <c r="BU2" s="217"/>
-      <c r="BV2" s="218"/>
-      <c r="BW2" s="216" t="s">
+      <c r="BU2" s="220"/>
+      <c r="BV2" s="221"/>
+      <c r="BW2" s="219" t="s">
         <v>321</v>
       </c>
-      <c r="BX2" s="217"/>
-      <c r="BY2" s="218"/>
-      <c r="BZ2" s="216" t="s">
+      <c r="BX2" s="220"/>
+      <c r="BY2" s="221"/>
+      <c r="BZ2" s="219" t="s">
         <v>348</v>
       </c>
-      <c r="CA2" s="217"/>
-      <c r="CB2" s="218"/>
-      <c r="CC2" s="216" t="s">
+      <c r="CA2" s="220"/>
+      <c r="CB2" s="221"/>
+      <c r="CC2" s="219" t="s">
         <v>325</v>
       </c>
-      <c r="CD2" s="217"/>
-      <c r="CE2" s="218"/>
-      <c r="CF2" s="216" t="s">
+      <c r="CD2" s="220"/>
+      <c r="CE2" s="221"/>
+      <c r="CF2" s="219" t="s">
         <v>305</v>
       </c>
-      <c r="CG2" s="217"/>
-      <c r="CH2" s="218"/>
-      <c r="CI2" s="216" t="s">
+      <c r="CG2" s="220"/>
+      <c r="CH2" s="221"/>
+      <c r="CI2" s="219" t="s">
         <v>326</v>
       </c>
-      <c r="CJ2" s="217"/>
-      <c r="CK2" s="218"/>
-      <c r="CL2" s="216" t="s">
+      <c r="CJ2" s="220"/>
+      <c r="CK2" s="221"/>
+      <c r="CL2" s="219" t="s">
         <v>330</v>
       </c>
-      <c r="CM2" s="217"/>
-      <c r="CN2" s="218"/>
-      <c r="CO2" s="216" t="s">
+      <c r="CM2" s="220"/>
+      <c r="CN2" s="221"/>
+      <c r="CO2" s="219" t="s">
         <v>328</v>
       </c>
-      <c r="CP2" s="217"/>
-      <c r="CQ2" s="218"/>
-      <c r="CR2" s="216" t="s">
+      <c r="CP2" s="220"/>
+      <c r="CQ2" s="221"/>
+      <c r="CR2" s="219" t="s">
         <v>346</v>
       </c>
-      <c r="CS2" s="217"/>
-      <c r="CT2" s="218"/>
-      <c r="CU2" s="216" t="s">
+      <c r="CS2" s="220"/>
+      <c r="CT2" s="221"/>
+      <c r="CU2" s="219" t="s">
         <v>331</v>
       </c>
-      <c r="CV2" s="217"/>
-      <c r="CW2" s="218"/>
-      <c r="CX2" s="216" t="s">
+      <c r="CV2" s="220"/>
+      <c r="CW2" s="221"/>
+      <c r="CX2" s="219" t="s">
         <v>336</v>
       </c>
-      <c r="CY2" s="217"/>
-      <c r="CZ2" s="218"/>
-      <c r="DA2" s="216" t="s">
+      <c r="CY2" s="220"/>
+      <c r="CZ2" s="221"/>
+      <c r="DA2" s="219" t="s">
         <v>329</v>
       </c>
-      <c r="DB2" s="217"/>
-      <c r="DC2" s="218"/>
-      <c r="DD2" s="216" t="s">
+      <c r="DB2" s="220"/>
+      <c r="DC2" s="221"/>
+      <c r="DD2" s="219" t="s">
         <v>320</v>
       </c>
-      <c r="DE2" s="217"/>
-      <c r="DF2" s="218"/>
-      <c r="DG2" s="216" t="s">
+      <c r="DE2" s="220"/>
+      <c r="DF2" s="221"/>
+      <c r="DG2" s="219" t="s">
         <v>337</v>
       </c>
-      <c r="DH2" s="217"/>
-      <c r="DI2" s="218"/>
-      <c r="DJ2" s="216" t="s">
+      <c r="DH2" s="220"/>
+      <c r="DI2" s="221"/>
+      <c r="DJ2" s="219" t="s">
         <v>334</v>
       </c>
-      <c r="DK2" s="217"/>
-      <c r="DL2" s="218"/>
-      <c r="DM2" s="216" t="s">
+      <c r="DK2" s="220"/>
+      <c r="DL2" s="221"/>
+      <c r="DM2" s="219" t="s">
         <v>335</v>
       </c>
-      <c r="DN2" s="217"/>
-      <c r="DO2" s="218"/>
+      <c r="DN2" s="220"/>
+      <c r="DO2" s="221"/>
     </row>
     <row r="3" spans="1:119" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -38026,9 +38029,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="223"/>
-      <c r="D3" s="223"/>
-      <c r="E3" s="224"/>
+      <c r="C3" s="224"/>
+      <c r="D3" s="224"/>
+      <c r="E3" s="223"/>
       <c r="F3" s="160" t="s">
         <v>393</v>
       </c>
@@ -43549,69 +43552,6 @@
     </row>
   </sheetData>
   <mergeCells count="79">
-    <mergeCell ref="DM1:DO1"/>
-    <mergeCell ref="DM2:DO2"/>
-    <mergeCell ref="DA1:DC1"/>
-    <mergeCell ref="DA2:DC2"/>
-    <mergeCell ref="DD1:DF1"/>
-    <mergeCell ref="DD2:DF2"/>
-    <mergeCell ref="DG1:DI1"/>
-    <mergeCell ref="DG2:DI2"/>
-    <mergeCell ref="CU1:CW1"/>
-    <mergeCell ref="CU2:CW2"/>
-    <mergeCell ref="CX1:CZ1"/>
-    <mergeCell ref="CX2:CZ2"/>
-    <mergeCell ref="DJ1:DL1"/>
-    <mergeCell ref="DJ2:DL2"/>
-    <mergeCell ref="CL1:CN1"/>
-    <mergeCell ref="CL2:CN2"/>
-    <mergeCell ref="CO1:CQ1"/>
-    <mergeCell ref="CO2:CQ2"/>
-    <mergeCell ref="CR1:CT1"/>
-    <mergeCell ref="CR2:CT2"/>
-    <mergeCell ref="CC1:CE1"/>
-    <mergeCell ref="CC2:CE2"/>
-    <mergeCell ref="CF1:CH1"/>
-    <mergeCell ref="CF2:CH2"/>
-    <mergeCell ref="CI1:CK1"/>
-    <mergeCell ref="CI2:CK2"/>
-    <mergeCell ref="BT1:BV1"/>
-    <mergeCell ref="BT2:BV2"/>
-    <mergeCell ref="BW1:BY1"/>
-    <mergeCell ref="BW2:BY2"/>
-    <mergeCell ref="BZ1:CB1"/>
-    <mergeCell ref="BZ2:CB2"/>
-    <mergeCell ref="BK1:BM1"/>
-    <mergeCell ref="BK2:BM2"/>
-    <mergeCell ref="BN1:BP1"/>
-    <mergeCell ref="BN2:BP2"/>
-    <mergeCell ref="BQ1:BS1"/>
-    <mergeCell ref="BQ2:BS2"/>
-    <mergeCell ref="AS1:AU1"/>
-    <mergeCell ref="AS2:AU2"/>
-    <mergeCell ref="AV1:AX1"/>
-    <mergeCell ref="AV2:AX2"/>
-    <mergeCell ref="BH1:BJ1"/>
-    <mergeCell ref="BH2:BJ2"/>
-    <mergeCell ref="AY2:BA2"/>
-    <mergeCell ref="BB2:BD2"/>
-    <mergeCell ref="BE2:BG2"/>
-    <mergeCell ref="AJ1:AL1"/>
-    <mergeCell ref="AJ2:AL2"/>
-    <mergeCell ref="AM1:AO1"/>
-    <mergeCell ref="AM2:AO2"/>
-    <mergeCell ref="AP2:AR2"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
     <mergeCell ref="AD2:AF2"/>
     <mergeCell ref="AG2:AI2"/>
     <mergeCell ref="BB1:BD1"/>
@@ -43628,6 +43568,69 @@
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="X1:Z1"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="AJ1:AL1"/>
+    <mergeCell ref="AJ2:AL2"/>
+    <mergeCell ref="AM1:AO1"/>
+    <mergeCell ref="AM2:AO2"/>
+    <mergeCell ref="AP2:AR2"/>
+    <mergeCell ref="AS1:AU1"/>
+    <mergeCell ref="AS2:AU2"/>
+    <mergeCell ref="AV1:AX1"/>
+    <mergeCell ref="AV2:AX2"/>
+    <mergeCell ref="BH1:BJ1"/>
+    <mergeCell ref="BH2:BJ2"/>
+    <mergeCell ref="AY2:BA2"/>
+    <mergeCell ref="BB2:BD2"/>
+    <mergeCell ref="BE2:BG2"/>
+    <mergeCell ref="BK1:BM1"/>
+    <mergeCell ref="BK2:BM2"/>
+    <mergeCell ref="BN1:BP1"/>
+    <mergeCell ref="BN2:BP2"/>
+    <mergeCell ref="BQ1:BS1"/>
+    <mergeCell ref="BQ2:BS2"/>
+    <mergeCell ref="BT1:BV1"/>
+    <mergeCell ref="BT2:BV2"/>
+    <mergeCell ref="BW1:BY1"/>
+    <mergeCell ref="BW2:BY2"/>
+    <mergeCell ref="BZ1:CB1"/>
+    <mergeCell ref="BZ2:CB2"/>
+    <mergeCell ref="CC1:CE1"/>
+    <mergeCell ref="CC2:CE2"/>
+    <mergeCell ref="CF1:CH1"/>
+    <mergeCell ref="CF2:CH2"/>
+    <mergeCell ref="CI1:CK1"/>
+    <mergeCell ref="CI2:CK2"/>
+    <mergeCell ref="CL1:CN1"/>
+    <mergeCell ref="CL2:CN2"/>
+    <mergeCell ref="CO1:CQ1"/>
+    <mergeCell ref="CO2:CQ2"/>
+    <mergeCell ref="CR1:CT1"/>
+    <mergeCell ref="CR2:CT2"/>
+    <mergeCell ref="CU1:CW1"/>
+    <mergeCell ref="CU2:CW2"/>
+    <mergeCell ref="CX1:CZ1"/>
+    <mergeCell ref="CX2:CZ2"/>
+    <mergeCell ref="DJ1:DL1"/>
+    <mergeCell ref="DJ2:DL2"/>
+    <mergeCell ref="DM1:DO1"/>
+    <mergeCell ref="DM2:DO2"/>
+    <mergeCell ref="DA1:DC1"/>
+    <mergeCell ref="DA2:DC2"/>
+    <mergeCell ref="DD1:DF1"/>
+    <mergeCell ref="DD2:DF2"/>
+    <mergeCell ref="DG1:DI1"/>
+    <mergeCell ref="DG2:DI2"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:DO37">
     <cfRule type="cellIs" dxfId="18" priority="1" operator="between">
@@ -43663,41 +43666,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="237" t="s">
+      <c r="C1" s="234" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="237" t="s">
+      <c r="D1" s="234" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="237" t="s">
+      <c r="E1" s="234" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="228" t="s">
+      <c r="F1" s="225" t="s">
         <v>302</v>
       </c>
-      <c r="G1" s="229"/>
-      <c r="H1" s="229"/>
-      <c r="I1" s="229"/>
-      <c r="J1" s="229"/>
-      <c r="K1" s="229"/>
-      <c r="L1" s="229"/>
-      <c r="M1" s="229"/>
-      <c r="N1" s="229"/>
-      <c r="O1" s="229"/>
-      <c r="P1" s="229"/>
-      <c r="Q1" s="229"/>
-      <c r="R1" s="229"/>
-      <c r="S1" s="229"/>
-      <c r="T1" s="229"/>
-      <c r="U1" s="229"/>
-      <c r="V1" s="229"/>
-      <c r="W1" s="229"/>
-      <c r="X1" s="229"/>
-      <c r="Y1" s="229"/>
-      <c r="Z1" s="229"/>
-      <c r="AA1" s="229"/>
-      <c r="AB1" s="229"/>
-      <c r="AC1" s="230"/>
+      <c r="G1" s="226"/>
+      <c r="H1" s="226"/>
+      <c r="I1" s="226"/>
+      <c r="J1" s="226"/>
+      <c r="K1" s="226"/>
+      <c r="L1" s="226"/>
+      <c r="M1" s="226"/>
+      <c r="N1" s="226"/>
+      <c r="O1" s="226"/>
+      <c r="P1" s="226"/>
+      <c r="Q1" s="226"/>
+      <c r="R1" s="226"/>
+      <c r="S1" s="226"/>
+      <c r="T1" s="226"/>
+      <c r="U1" s="226"/>
+      <c r="V1" s="226"/>
+      <c r="W1" s="226"/>
+      <c r="X1" s="226"/>
+      <c r="Y1" s="226"/>
+      <c r="Z1" s="226"/>
+      <c r="AA1" s="226"/>
+      <c r="AB1" s="226"/>
+      <c r="AC1" s="227"/>
       <c r="AD1" s="240" t="s">
         <v>281</v>
       </c>
@@ -43706,81 +43709,81 @@
       <c r="AG1" s="241"/>
       <c r="AH1" s="241"/>
       <c r="AI1" s="242"/>
-      <c r="AJ1" s="228" t="s">
+      <c r="AJ1" s="225" t="s">
         <v>282</v>
       </c>
-      <c r="AK1" s="229"/>
-      <c r="AL1" s="229"/>
-      <c r="AM1" s="229"/>
-      <c r="AN1" s="229"/>
-      <c r="AO1" s="230"/>
-      <c r="AP1" s="231" t="s">
+      <c r="AK1" s="226"/>
+      <c r="AL1" s="226"/>
+      <c r="AM1" s="226"/>
+      <c r="AN1" s="226"/>
+      <c r="AO1" s="227"/>
+      <c r="AP1" s="228" t="s">
         <v>283</v>
       </c>
-      <c r="AQ1" s="232"/>
-      <c r="AR1" s="232"/>
-      <c r="AS1" s="232"/>
-      <c r="AT1" s="232"/>
-      <c r="AU1" s="233"/>
-      <c r="AV1" s="234" t="s">
+      <c r="AQ1" s="229"/>
+      <c r="AR1" s="229"/>
+      <c r="AS1" s="229"/>
+      <c r="AT1" s="229"/>
+      <c r="AU1" s="230"/>
+      <c r="AV1" s="231" t="s">
         <v>86</v>
       </c>
-      <c r="AW1" s="235"/>
-      <c r="AX1" s="236"/>
+      <c r="AW1" s="232"/>
+      <c r="AX1" s="233"/>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="238"/>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="225" t="s">
+      <c r="C2" s="235"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="237" t="s">
         <v>468</v>
       </c>
-      <c r="G2" s="226"/>
-      <c r="H2" s="227"/>
-      <c r="I2" s="225"/>
-      <c r="J2" s="226"/>
-      <c r="K2" s="227"/>
-      <c r="L2" s="225"/>
-      <c r="M2" s="226"/>
-      <c r="N2" s="227"/>
-      <c r="O2" s="225"/>
-      <c r="P2" s="226"/>
-      <c r="Q2" s="227"/>
-      <c r="R2" s="225"/>
-      <c r="S2" s="226"/>
-      <c r="T2" s="227"/>
-      <c r="U2" s="225"/>
-      <c r="V2" s="226"/>
-      <c r="W2" s="227"/>
-      <c r="X2" s="225"/>
-      <c r="Y2" s="226"/>
-      <c r="Z2" s="227"/>
-      <c r="AA2" s="225"/>
-      <c r="AB2" s="226"/>
-      <c r="AC2" s="226"/>
-      <c r="AD2" s="225"/>
-      <c r="AE2" s="226"/>
-      <c r="AF2" s="227"/>
-      <c r="AG2" s="225"/>
-      <c r="AH2" s="226"/>
-      <c r="AI2" s="227"/>
-      <c r="AJ2" s="225"/>
-      <c r="AK2" s="226"/>
-      <c r="AL2" s="227"/>
-      <c r="AM2" s="225"/>
-      <c r="AN2" s="226"/>
-      <c r="AO2" s="227"/>
-      <c r="AP2" s="225"/>
-      <c r="AQ2" s="226"/>
-      <c r="AR2" s="227"/>
-      <c r="AS2" s="225"/>
-      <c r="AT2" s="226"/>
-      <c r="AU2" s="227"/>
-      <c r="AV2" s="225"/>
-      <c r="AW2" s="226"/>
-      <c r="AX2" s="227"/>
+      <c r="G2" s="238"/>
+      <c r="H2" s="239"/>
+      <c r="I2" s="237"/>
+      <c r="J2" s="238"/>
+      <c r="K2" s="239"/>
+      <c r="L2" s="237"/>
+      <c r="M2" s="238"/>
+      <c r="N2" s="239"/>
+      <c r="O2" s="237"/>
+      <c r="P2" s="238"/>
+      <c r="Q2" s="239"/>
+      <c r="R2" s="237"/>
+      <c r="S2" s="238"/>
+      <c r="T2" s="239"/>
+      <c r="U2" s="237"/>
+      <c r="V2" s="238"/>
+      <c r="W2" s="239"/>
+      <c r="X2" s="237"/>
+      <c r="Y2" s="238"/>
+      <c r="Z2" s="239"/>
+      <c r="AA2" s="237"/>
+      <c r="AB2" s="238"/>
+      <c r="AC2" s="238"/>
+      <c r="AD2" s="237"/>
+      <c r="AE2" s="238"/>
+      <c r="AF2" s="239"/>
+      <c r="AG2" s="237"/>
+      <c r="AH2" s="238"/>
+      <c r="AI2" s="239"/>
+      <c r="AJ2" s="237"/>
+      <c r="AK2" s="238"/>
+      <c r="AL2" s="239"/>
+      <c r="AM2" s="237"/>
+      <c r="AN2" s="238"/>
+      <c r="AO2" s="239"/>
+      <c r="AP2" s="237"/>
+      <c r="AQ2" s="238"/>
+      <c r="AR2" s="239"/>
+      <c r="AS2" s="237"/>
+      <c r="AT2" s="238"/>
+      <c r="AU2" s="239"/>
+      <c r="AV2" s="237"/>
+      <c r="AW2" s="238"/>
+      <c r="AX2" s="239"/>
     </row>
     <row r="3" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -43789,9 +43792,9 @@
       <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="239"/>
-      <c r="D3" s="239"/>
-      <c r="E3" s="239"/>
+      <c r="C3" s="236"/>
+      <c r="D3" s="236"/>
+      <c r="E3" s="236"/>
       <c r="F3" s="170" t="s">
         <v>393</v>
       </c>
@@ -46358,6 +46361,13 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="F1:AC1"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
+    <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="AJ1:AO1"/>
     <mergeCell ref="AP1:AU1"/>
     <mergeCell ref="AV1:AX1"/>
@@ -46374,13 +46384,6 @@
     <mergeCell ref="AD1:AI1"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="I2:K2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="F1:AC1"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:AW31">
     <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
@@ -46415,70 +46418,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C1" s="237" t="s">
+      <c r="C1" s="234" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="237" t="s">
+      <c r="D1" s="234" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="237" t="s">
+      <c r="E1" s="234" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="267" t="s">
+      <c r="F1" s="274" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="268"/>
-      <c r="H1" s="269"/>
-      <c r="I1" s="270" t="s">
+      <c r="G1" s="275"/>
+      <c r="H1" s="276"/>
+      <c r="I1" s="277" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="271"/>
-      <c r="K1" s="272"/>
-      <c r="L1" s="274" t="s">
+      <c r="J1" s="278"/>
+      <c r="K1" s="279"/>
+      <c r="L1" s="244" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="275"/>
-      <c r="N1" s="276"/>
-      <c r="O1" s="277" t="s">
+      <c r="M1" s="245"/>
+      <c r="N1" s="246"/>
+      <c r="O1" s="247" t="s">
         <v>199</v>
       </c>
-      <c r="P1" s="278"/>
-      <c r="Q1" s="279"/>
-      <c r="R1" s="243" t="s">
+      <c r="P1" s="248"/>
+      <c r="Q1" s="249"/>
+      <c r="R1" s="250" t="s">
         <v>200</v>
       </c>
-      <c r="S1" s="244"/>
-      <c r="T1" s="245"/>
-      <c r="U1" s="246" t="s">
+      <c r="S1" s="251"/>
+      <c r="T1" s="252"/>
+      <c r="U1" s="253" t="s">
         <v>306</v>
       </c>
-      <c r="V1" s="247"/>
-      <c r="W1" s="248"/>
+      <c r="V1" s="254"/>
+      <c r="W1" s="255"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="238"/>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="249"/>
-      <c r="G2" s="250"/>
-      <c r="H2" s="251"/>
-      <c r="I2" s="264"/>
-      <c r="J2" s="265"/>
-      <c r="K2" s="266"/>
-      <c r="L2" s="261"/>
-      <c r="M2" s="262"/>
-      <c r="N2" s="263"/>
-      <c r="O2" s="258"/>
-      <c r="P2" s="259"/>
-      <c r="Q2" s="260"/>
-      <c r="R2" s="255"/>
-      <c r="S2" s="256"/>
-      <c r="T2" s="257"/>
-      <c r="U2" s="252"/>
-      <c r="V2" s="253"/>
-      <c r="W2" s="254"/>
+      <c r="C2" s="235"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="256"/>
+      <c r="G2" s="257"/>
+      <c r="H2" s="258"/>
+      <c r="I2" s="271"/>
+      <c r="J2" s="272"/>
+      <c r="K2" s="273"/>
+      <c r="L2" s="268"/>
+      <c r="M2" s="269"/>
+      <c r="N2" s="270"/>
+      <c r="O2" s="265"/>
+      <c r="P2" s="266"/>
+      <c r="Q2" s="267"/>
+      <c r="R2" s="262"/>
+      <c r="S2" s="263"/>
+      <c r="T2" s="264"/>
+      <c r="U2" s="259"/>
+      <c r="V2" s="260"/>
+      <c r="W2" s="261"/>
     </row>
     <row r="3" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -46487,9 +46490,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="273"/>
-      <c r="D3" s="273"/>
-      <c r="E3" s="273"/>
+      <c r="C3" s="243"/>
+      <c r="D3" s="243"/>
+      <c r="E3" s="243"/>
       <c r="F3" s="189" t="s">
         <v>393</v>
       </c>
@@ -47913,11 +47916,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="O1:Q1"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="F2:H2"/>
@@ -47928,6 +47926,11 @@
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="O1:Q1"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:W31">
     <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
@@ -54741,72 +54744,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C1" s="237" t="s">
+      <c r="C1" s="234" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="237" t="s">
+      <c r="D1" s="234" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="237" t="s">
+      <c r="E1" s="234" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="267" t="s">
+      <c r="F1" s="274" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="268"/>
-      <c r="H1" s="269"/>
-      <c r="I1" s="270" t="s">
+      <c r="G1" s="275"/>
+      <c r="H1" s="276"/>
+      <c r="I1" s="277" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="271"/>
-      <c r="K1" s="272"/>
-      <c r="L1" s="274" t="s">
+      <c r="J1" s="278"/>
+      <c r="K1" s="279"/>
+      <c r="L1" s="244" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="275"/>
-      <c r="N1" s="276"/>
-      <c r="O1" s="277" t="s">
+      <c r="M1" s="245"/>
+      <c r="N1" s="246"/>
+      <c r="O1" s="247" t="s">
         <v>199</v>
       </c>
-      <c r="P1" s="278"/>
-      <c r="Q1" s="279"/>
-      <c r="R1" s="243" t="s">
+      <c r="P1" s="248"/>
+      <c r="Q1" s="249"/>
+      <c r="R1" s="250" t="s">
         <v>200</v>
       </c>
-      <c r="S1" s="244"/>
-      <c r="T1" s="245"/>
-      <c r="U1" s="246" t="s">
+      <c r="S1" s="251"/>
+      <c r="T1" s="252"/>
+      <c r="U1" s="253" t="s">
         <v>306</v>
       </c>
-      <c r="V1" s="247"/>
-      <c r="W1" s="248"/>
+      <c r="V1" s="254"/>
+      <c r="W1" s="255"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="238"/>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="249" t="s">
+      <c r="C2" s="235"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="256" t="s">
         <v>433</v>
       </c>
-      <c r="G2" s="250"/>
-      <c r="H2" s="251"/>
-      <c r="I2" s="264"/>
-      <c r="J2" s="265"/>
-      <c r="K2" s="266"/>
-      <c r="L2" s="261"/>
-      <c r="M2" s="262"/>
-      <c r="N2" s="263"/>
-      <c r="O2" s="258"/>
-      <c r="P2" s="259"/>
-      <c r="Q2" s="260"/>
-      <c r="R2" s="255"/>
-      <c r="S2" s="256"/>
-      <c r="T2" s="257"/>
-      <c r="U2" s="252"/>
-      <c r="V2" s="253"/>
-      <c r="W2" s="254"/>
+      <c r="G2" s="257"/>
+      <c r="H2" s="258"/>
+      <c r="I2" s="271"/>
+      <c r="J2" s="272"/>
+      <c r="K2" s="273"/>
+      <c r="L2" s="268"/>
+      <c r="M2" s="269"/>
+      <c r="N2" s="270"/>
+      <c r="O2" s="265"/>
+      <c r="P2" s="266"/>
+      <c r="Q2" s="267"/>
+      <c r="R2" s="262"/>
+      <c r="S2" s="263"/>
+      <c r="T2" s="264"/>
+      <c r="U2" s="259"/>
+      <c r="V2" s="260"/>
+      <c r="W2" s="261"/>
     </row>
     <row r="3" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -54815,9 +54818,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="273"/>
-      <c r="D3" s="273"/>
-      <c r="E3" s="273"/>
+      <c r="C3" s="243"/>
+      <c r="D3" s="243"/>
+      <c r="E3" s="243"/>
       <c r="F3" s="189" t="s">
         <v>393</v>
       </c>
@@ -56241,6 +56244,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="F2:H2"/>
@@ -56251,11 +56259,6 @@
     <mergeCell ref="U2:W2"/>
     <mergeCell ref="L1:N1"/>
     <mergeCell ref="O1:Q1"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:W31">
     <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
@@ -56751,51 +56754,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="283" t="s">
+      <c r="C1" s="302" t="s">
         <v>202</v>
       </c>
-      <c r="D1" s="284"/>
-      <c r="E1" s="284"/>
-      <c r="F1" s="284"/>
-      <c r="G1" s="284"/>
-      <c r="H1" s="284"/>
-      <c r="I1" s="285"/>
+      <c r="D1" s="303"/>
+      <c r="E1" s="303"/>
+      <c r="F1" s="303"/>
+      <c r="G1" s="303"/>
+      <c r="H1" s="303"/>
+      <c r="I1" s="304"/>
       <c r="J1" s="114" t="s">
         <v>195</v>
       </c>
       <c r="K1" s="115" t="s">
         <v>194</v>
       </c>
-      <c r="L1" s="307" t="s">
+      <c r="L1" s="282" t="s">
         <v>287</v>
       </c>
-      <c r="M1" s="312"/>
-      <c r="N1" s="312"/>
-      <c r="O1" s="312"/>
-      <c r="P1" s="312"/>
-      <c r="Q1" s="312"/>
-      <c r="R1" s="312"/>
-      <c r="S1" s="312"/>
-      <c r="T1" s="312"/>
-      <c r="U1" s="312"/>
-      <c r="V1" s="312"/>
-      <c r="W1" s="312"/>
-      <c r="X1" s="312"/>
-      <c r="Y1" s="312"/>
-      <c r="Z1" s="312"/>
-      <c r="AA1" s="312"/>
-      <c r="AB1" s="312"/>
-      <c r="AC1" s="312"/>
-      <c r="AD1" s="312"/>
-      <c r="AE1" s="312"/>
-      <c r="AF1" s="312"/>
-      <c r="AG1" s="313"/>
-      <c r="AH1" s="307" t="s">
+      <c r="M1" s="287"/>
+      <c r="N1" s="287"/>
+      <c r="O1" s="287"/>
+      <c r="P1" s="287"/>
+      <c r="Q1" s="287"/>
+      <c r="R1" s="287"/>
+      <c r="S1" s="287"/>
+      <c r="T1" s="287"/>
+      <c r="U1" s="287"/>
+      <c r="V1" s="287"/>
+      <c r="W1" s="287"/>
+      <c r="X1" s="287"/>
+      <c r="Y1" s="287"/>
+      <c r="Z1" s="287"/>
+      <c r="AA1" s="287"/>
+      <c r="AB1" s="287"/>
+      <c r="AC1" s="287"/>
+      <c r="AD1" s="287"/>
+      <c r="AE1" s="287"/>
+      <c r="AF1" s="287"/>
+      <c r="AG1" s="288"/>
+      <c r="AH1" s="282" t="s">
         <v>175</v>
       </c>
-      <c r="AI1" s="308"/>
-      <c r="AJ1" s="308"/>
-      <c r="AK1" s="309"/>
+      <c r="AI1" s="283"/>
+      <c r="AJ1" s="283"/>
+      <c r="AK1" s="284"/>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B2" s="111"/>
@@ -61995,15 +61998,15 @@
         <f t="shared" ref="J80:J111" si="2">H80-I80</f>
         <v>2</v>
       </c>
-      <c r="K80" s="314" t="s">
+      <c r="K80" s="289" t="s">
         <v>435</v>
       </c>
-      <c r="L80" s="315"/>
-      <c r="M80" s="316"/>
+      <c r="L80" s="290"/>
+      <c r="M80" s="291"/>
       <c r="O80" s="133"/>
       <c r="P80" s="133"/>
-      <c r="W80" s="310"/>
-      <c r="X80" s="310"/>
+      <c r="W80" s="285"/>
+      <c r="X80" s="285"/>
       <c r="Y80" s="70" t="s">
         <v>211</v>
       </c>
@@ -62053,15 +62056,15 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K81" s="317"/>
-      <c r="L81" s="318"/>
-      <c r="M81" s="319"/>
+      <c r="K81" s="292"/>
+      <c r="L81" s="293"/>
+      <c r="M81" s="294"/>
       <c r="O81" s="133"/>
       <c r="P81" s="133"/>
-      <c r="W81" s="310" t="s">
+      <c r="W81" s="285" t="s">
         <v>209</v>
       </c>
-      <c r="X81" s="310"/>
+      <c r="X81" s="285"/>
       <c r="Y81" s="70">
         <f>COUNTIF(L3:AG40,3)</f>
         <v>481</v>
@@ -62117,17 +62120,17 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K82" s="320" t="s">
+      <c r="K82" s="295" t="s">
         <v>436</v>
       </c>
-      <c r="L82" s="321"/>
-      <c r="M82" s="322"/>
+      <c r="L82" s="296"/>
+      <c r="M82" s="297"/>
       <c r="O82" s="133"/>
       <c r="P82" s="133"/>
-      <c r="W82" s="310" t="s">
+      <c r="W82" s="285" t="s">
         <v>210</v>
       </c>
-      <c r="X82" s="310"/>
+      <c r="X82" s="285"/>
       <c r="Y82" s="70">
         <f>COUNTIF(K3:K40,3)+COUNTIF(J3:J15,3)</f>
         <v>25</v>
@@ -62183,17 +62186,17 @@
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="K83" s="323" t="s">
+      <c r="K83" s="298" t="s">
         <v>437</v>
       </c>
-      <c r="L83" s="324"/>
-      <c r="M83" s="325"/>
+      <c r="L83" s="299"/>
+      <c r="M83" s="300"/>
       <c r="O83" s="133"/>
       <c r="P83" s="133"/>
-      <c r="W83" s="311" t="s">
+      <c r="W83" s="286" t="s">
         <v>97</v>
       </c>
-      <c r="X83" s="311"/>
+      <c r="X83" s="286"/>
       <c r="Y83" s="196">
         <v>220</v>
       </c>
@@ -62246,15 +62249,15 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="K84" s="298" t="s">
+      <c r="K84" s="317" t="s">
         <v>284</v>
       </c>
-      <c r="L84" s="299"/>
-      <c r="M84" s="300"/>
+      <c r="L84" s="318"/>
+      <c r="M84" s="319"/>
       <c r="O84" s="141"/>
       <c r="P84" s="141"/>
-      <c r="W84" s="282"/>
-      <c r="X84" s="282"/>
+      <c r="W84" s="301"/>
+      <c r="X84" s="301"/>
       <c r="Y84" s="198"/>
       <c r="Z84" s="198"/>
       <c r="AA84" s="198"/>
@@ -62292,9 +62295,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K85" s="301"/>
-      <c r="L85" s="302"/>
-      <c r="M85" s="303"/>
+      <c r="K85" s="320"/>
+      <c r="L85" s="321"/>
+      <c r="M85" s="322"/>
       <c r="O85" s="141"/>
       <c r="P85" s="141"/>
     </row>
@@ -62328,9 +62331,9 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="K86" s="301"/>
-      <c r="L86" s="302"/>
-      <c r="M86" s="303"/>
+      <c r="K86" s="320"/>
+      <c r="L86" s="321"/>
+      <c r="M86" s="322"/>
       <c r="O86" s="141"/>
       <c r="P86" s="141"/>
     </row>
@@ -62364,9 +62367,9 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="K87" s="301"/>
-      <c r="L87" s="302"/>
-      <c r="M87" s="303"/>
+      <c r="K87" s="320"/>
+      <c r="L87" s="321"/>
+      <c r="M87" s="322"/>
       <c r="O87" s="141"/>
       <c r="P87" s="141"/>
     </row>
@@ -62400,9 +62403,9 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K88" s="301"/>
-      <c r="L88" s="302"/>
-      <c r="M88" s="303"/>
+      <c r="K88" s="320"/>
+      <c r="L88" s="321"/>
+      <c r="M88" s="322"/>
       <c r="O88" s="141"/>
       <c r="P88" s="141"/>
     </row>
@@ -62436,9 +62439,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K89" s="301"/>
-      <c r="L89" s="302"/>
-      <c r="M89" s="303"/>
+      <c r="K89" s="320"/>
+      <c r="L89" s="321"/>
+      <c r="M89" s="322"/>
       <c r="O89" s="141"/>
       <c r="P89" s="141"/>
     </row>
@@ -62472,9 +62475,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K90" s="301"/>
-      <c r="L90" s="302"/>
-      <c r="M90" s="303"/>
+      <c r="K90" s="320"/>
+      <c r="L90" s="321"/>
+      <c r="M90" s="322"/>
       <c r="O90" s="141"/>
       <c r="P90" s="141"/>
     </row>
@@ -62508,9 +62511,9 @@
         <f t="shared" si="2"/>
         <v>47</v>
       </c>
-      <c r="K91" s="301"/>
-      <c r="L91" s="302"/>
-      <c r="M91" s="303"/>
+      <c r="K91" s="320"/>
+      <c r="L91" s="321"/>
+      <c r="M91" s="322"/>
       <c r="O91" s="141"/>
       <c r="P91" s="141"/>
     </row>
@@ -62544,9 +62547,9 @@
         <f t="shared" si="2"/>
         <v>51</v>
       </c>
-      <c r="K92" s="301"/>
-      <c r="L92" s="302"/>
-      <c r="M92" s="303"/>
+      <c r="K92" s="320"/>
+      <c r="L92" s="321"/>
+      <c r="M92" s="322"/>
       <c r="O92" s="141"/>
       <c r="P92" s="141"/>
     </row>
@@ -62580,9 +62583,9 @@
         <f t="shared" si="2"/>
         <v>37</v>
       </c>
-      <c r="K93" s="301"/>
-      <c r="L93" s="302"/>
-      <c r="M93" s="303"/>
+      <c r="K93" s="320"/>
+      <c r="L93" s="321"/>
+      <c r="M93" s="322"/>
       <c r="O93" s="141"/>
       <c r="P93" s="141"/>
     </row>
@@ -62616,9 +62619,9 @@
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="K94" s="301"/>
-      <c r="L94" s="302"/>
-      <c r="M94" s="303"/>
+      <c r="K94" s="320"/>
+      <c r="L94" s="321"/>
+      <c r="M94" s="322"/>
       <c r="O94" s="141"/>
       <c r="P94" s="141"/>
     </row>
@@ -62652,9 +62655,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K95" s="301"/>
-      <c r="L95" s="302"/>
-      <c r="M95" s="303"/>
+      <c r="K95" s="320"/>
+      <c r="L95" s="321"/>
+      <c r="M95" s="322"/>
       <c r="O95" s="141"/>
       <c r="P95" s="141"/>
     </row>
@@ -62688,9 +62691,9 @@
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="K96" s="301"/>
-      <c r="L96" s="302"/>
-      <c r="M96" s="303"/>
+      <c r="K96" s="320"/>
+      <c r="L96" s="321"/>
+      <c r="M96" s="322"/>
       <c r="O96" s="141"/>
       <c r="P96" s="141"/>
     </row>
@@ -62724,9 +62727,9 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="K97" s="301"/>
-      <c r="L97" s="302"/>
-      <c r="M97" s="303"/>
+      <c r="K97" s="320"/>
+      <c r="L97" s="321"/>
+      <c r="M97" s="322"/>
       <c r="O97" s="141"/>
       <c r="P97" s="141"/>
     </row>
@@ -62760,9 +62763,9 @@
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="K98" s="301"/>
-      <c r="L98" s="302"/>
-      <c r="M98" s="303"/>
+      <c r="K98" s="320"/>
+      <c r="L98" s="321"/>
+      <c r="M98" s="322"/>
       <c r="O98" s="141"/>
       <c r="P98" s="141"/>
     </row>
@@ -62796,9 +62799,9 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K99" s="301"/>
-      <c r="L99" s="302"/>
-      <c r="M99" s="303"/>
+      <c r="K99" s="320"/>
+      <c r="L99" s="321"/>
+      <c r="M99" s="322"/>
       <c r="O99" s="141"/>
       <c r="P99" s="141"/>
     </row>
@@ -62832,9 +62835,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K100" s="301"/>
-      <c r="L100" s="302"/>
-      <c r="M100" s="303"/>
+      <c r="K100" s="320"/>
+      <c r="L100" s="321"/>
+      <c r="M100" s="322"/>
       <c r="O100" s="141"/>
       <c r="P100" s="141"/>
     </row>
@@ -62868,9 +62871,9 @@
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="K101" s="301"/>
-      <c r="L101" s="302"/>
-      <c r="M101" s="303"/>
+      <c r="K101" s="320"/>
+      <c r="L101" s="321"/>
+      <c r="M101" s="322"/>
       <c r="O101" s="141"/>
       <c r="P101" s="141"/>
     </row>
@@ -62904,9 +62907,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K102" s="301"/>
-      <c r="L102" s="302"/>
-      <c r="M102" s="303"/>
+      <c r="K102" s="320"/>
+      <c r="L102" s="321"/>
+      <c r="M102" s="322"/>
       <c r="O102" s="141"/>
       <c r="P102" s="141"/>
     </row>
@@ -62940,9 +62943,9 @@
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="K103" s="301"/>
-      <c r="L103" s="302"/>
-      <c r="M103" s="303"/>
+      <c r="K103" s="320"/>
+      <c r="L103" s="321"/>
+      <c r="M103" s="322"/>
       <c r="O103" s="141"/>
       <c r="P103" s="141"/>
     </row>
@@ -62976,9 +62979,9 @@
         <f t="shared" si="2"/>
         <v>33</v>
       </c>
-      <c r="K104" s="301"/>
-      <c r="L104" s="302"/>
-      <c r="M104" s="303"/>
+      <c r="K104" s="320"/>
+      <c r="L104" s="321"/>
+      <c r="M104" s="322"/>
       <c r="O104" s="141"/>
       <c r="P104" s="141"/>
     </row>
@@ -63012,9 +63015,9 @@
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="K105" s="304"/>
-      <c r="L105" s="305"/>
-      <c r="M105" s="306"/>
+      <c r="K105" s="323"/>
+      <c r="L105" s="324"/>
+      <c r="M105" s="325"/>
       <c r="O105" s="141"/>
       <c r="P105" s="141"/>
     </row>
@@ -63048,11 +63051,11 @@
         <f t="shared" si="2"/>
         <v>21</v>
       </c>
-      <c r="K106" s="295" t="s">
+      <c r="K106" s="314" t="s">
         <v>286</v>
       </c>
-      <c r="L106" s="296"/>
-      <c r="M106" s="297"/>
+      <c r="L106" s="315"/>
+      <c r="M106" s="316"/>
       <c r="O106" s="126"/>
       <c r="P106" s="126"/>
     </row>
@@ -63086,11 +63089,11 @@
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="K107" s="295" t="s">
+      <c r="K107" s="314" t="s">
         <v>288</v>
       </c>
-      <c r="L107" s="296"/>
-      <c r="M107" s="297"/>
+      <c r="L107" s="315"/>
+      <c r="M107" s="316"/>
       <c r="O107" s="126"/>
       <c r="P107" s="126"/>
     </row>
@@ -63124,11 +63127,11 @@
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="K108" s="286" t="s">
+      <c r="K108" s="305" t="s">
         <v>289</v>
       </c>
-      <c r="L108" s="287"/>
-      <c r="M108" s="288"/>
+      <c r="L108" s="306"/>
+      <c r="M108" s="307"/>
       <c r="O108" s="126"/>
       <c r="P108" s="126"/>
     </row>
@@ -63162,9 +63165,9 @@
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="K109" s="289"/>
-      <c r="L109" s="290"/>
-      <c r="M109" s="291"/>
+      <c r="K109" s="308"/>
+      <c r="L109" s="309"/>
+      <c r="M109" s="310"/>
       <c r="O109" s="126"/>
       <c r="P109" s="126"/>
     </row>
@@ -63198,9 +63201,9 @@
         <f t="shared" si="2"/>
         <v>45</v>
       </c>
-      <c r="K110" s="289"/>
-      <c r="L110" s="290"/>
-      <c r="M110" s="291"/>
+      <c r="K110" s="308"/>
+      <c r="L110" s="309"/>
+      <c r="M110" s="310"/>
       <c r="O110" s="126"/>
       <c r="P110" s="126"/>
     </row>
@@ -63234,9 +63237,9 @@
         <f t="shared" si="2"/>
         <v>62</v>
       </c>
-      <c r="K111" s="289"/>
-      <c r="L111" s="290"/>
-      <c r="M111" s="291"/>
+      <c r="K111" s="308"/>
+      <c r="L111" s="309"/>
+      <c r="M111" s="310"/>
       <c r="O111" s="126"/>
       <c r="P111" s="126"/>
     </row>
@@ -63274,9 +63277,9 @@
         <f t="shared" ref="J112:J114" si="6">H112-I112</f>
         <v>34</v>
       </c>
-      <c r="K112" s="289"/>
-      <c r="L112" s="290"/>
-      <c r="M112" s="291"/>
+      <c r="K112" s="308"/>
+      <c r="L112" s="309"/>
+      <c r="M112" s="310"/>
     </row>
     <row r="113" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="156" t="s">
@@ -63312,9 +63315,9 @@
         <f t="shared" si="6"/>
         <v>43</v>
       </c>
-      <c r="K113" s="292"/>
-      <c r="L113" s="293"/>
-      <c r="M113" s="294"/>
+      <c r="K113" s="311"/>
+      <c r="L113" s="312"/>
+      <c r="M113" s="313"/>
     </row>
     <row r="114" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" s="93" t="s">
@@ -63354,6 +63357,12 @@
   </sheetData>
   <autoFilter ref="A79:J112" xr:uid="{9C81160F-C24B-449F-8F5A-CB622AB71070}"/>
   <mergeCells count="15">
+    <mergeCell ref="W84:X84"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="K108:M113"/>
+    <mergeCell ref="K106:M106"/>
+    <mergeCell ref="K107:M107"/>
+    <mergeCell ref="K84:M105"/>
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="W80:X80"/>
     <mergeCell ref="W81:X81"/>
@@ -63363,12 +63372,6 @@
     <mergeCell ref="K80:M81"/>
     <mergeCell ref="K82:M82"/>
     <mergeCell ref="K83:M83"/>
-    <mergeCell ref="W84:X84"/>
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="K108:M113"/>
-    <mergeCell ref="K106:M106"/>
-    <mergeCell ref="K107:M107"/>
-    <mergeCell ref="K84:M105"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <conditionalFormatting sqref="A3:A40">
@@ -63581,7 +63584,7 @@
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>469</v>
+        <v>482</v>
       </c>
       <c r="B4" s="194">
         <v>0.875</v>
@@ -64484,7 +64487,7 @@
       <c r="C1" s="328" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="210"/>
+      <c r="D1" s="207"/>
       <c r="E1" s="329"/>
       <c r="H1" s="204" t="s">
         <v>47</v>
@@ -64493,7 +64496,7 @@
       <c r="J1" s="328" t="s">
         <v>44</v>
       </c>
-      <c r="K1" s="210"/>
+      <c r="K1" s="207"/>
       <c r="L1" s="329"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -65582,9 +65585,9 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="215"/>
-      <c r="G1" s="215"/>
-      <c r="H1" s="215"/>
+      <c r="F1" s="208"/>
+      <c r="G1" s="208"/>
+      <c r="H1" s="208"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -65613,31 +65616,31 @@
       </c>
       <c r="F2" s="205"/>
       <c r="G2" s="206"/>
-      <c r="H2" s="207" t="s">
+      <c r="H2" s="209" t="s">
         <v>120</v>
       </c>
-      <c r="I2" s="208"/>
-      <c r="J2" s="209"/>
+      <c r="I2" s="210"/>
+      <c r="J2" s="211"/>
       <c r="K2" s="204" t="s">
         <v>108</v>
       </c>
       <c r="L2" s="205"/>
       <c r="M2" s="206"/>
-      <c r="N2" s="207" t="s">
+      <c r="N2" s="209" t="s">
         <v>110</v>
       </c>
-      <c r="O2" s="208"/>
-      <c r="P2" s="209"/>
+      <c r="O2" s="210"/>
+      <c r="P2" s="211"/>
       <c r="Q2" s="204" t="s">
         <v>39</v>
       </c>
       <c r="R2" s="205"/>
       <c r="S2" s="206"/>
-      <c r="T2" s="210" t="s">
+      <c r="T2" s="207" t="s">
         <v>7</v>
       </c>
-      <c r="U2" s="210"/>
-      <c r="V2" s="210"/>
+      <c r="U2" s="207"/>
+      <c r="V2" s="207"/>
       <c r="Z2" s="125">
         <v>46279</v>
       </c>
@@ -68735,30 +68738,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="213" t="s">
+      <c r="D2" s="214" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="213"/>
-      <c r="F2" s="214" t="s">
+      <c r="E2" s="214"/>
+      <c r="F2" s="215" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="214"/>
-      <c r="H2" s="213" t="s">
+      <c r="G2" s="215"/>
+      <c r="H2" s="214" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="213"/>
-      <c r="J2" s="214" t="s">
+      <c r="I2" s="214"/>
+      <c r="J2" s="215" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="214"/>
-      <c r="L2" s="213" t="s">
+      <c r="K2" s="215"/>
+      <c r="L2" s="214" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="213"/>
-      <c r="N2" s="210" t="s">
+      <c r="M2" s="214"/>
+      <c r="N2" s="207" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="210"/>
+      <c r="O2" s="207"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -70755,30 +70758,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="213" t="s">
+      <c r="D2" s="214" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="213"/>
-      <c r="F2" s="214" t="s">
+      <c r="E2" s="214"/>
+      <c r="F2" s="215" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="214"/>
-      <c r="H2" s="213" t="s">
+      <c r="G2" s="215"/>
+      <c r="H2" s="214" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="213"/>
-      <c r="J2" s="214" t="s">
+      <c r="I2" s="214"/>
+      <c r="J2" s="215" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="214"/>
-      <c r="L2" s="213" t="s">
+      <c r="K2" s="215"/>
+      <c r="L2" s="214" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="213"/>
-      <c r="N2" s="210" t="s">
+      <c r="M2" s="214"/>
+      <c r="N2" s="207" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="210"/>
+      <c r="O2" s="207"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -72712,30 +72715,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="213" t="s">
+      <c r="D2" s="214" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="213"/>
-      <c r="F2" s="214" t="s">
+      <c r="E2" s="214"/>
+      <c r="F2" s="215" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="214"/>
-      <c r="H2" s="213" t="s">
+      <c r="G2" s="215"/>
+      <c r="H2" s="214" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="213"/>
-      <c r="J2" s="214" t="s">
+      <c r="I2" s="214"/>
+      <c r="J2" s="215" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="214"/>
-      <c r="L2" s="213" t="s">
+      <c r="K2" s="215"/>
+      <c r="L2" s="214" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="213"/>
-      <c r="N2" s="210" t="s">
+      <c r="M2" s="214"/>
+      <c r="N2" s="207" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="210"/>
+      <c r="O2" s="207"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -74760,30 +74763,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="213" t="s">
+      <c r="D2" s="214" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="213"/>
-      <c r="F2" s="214" t="s">
+      <c r="E2" s="214"/>
+      <c r="F2" s="215" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="214"/>
-      <c r="H2" s="213" t="s">
+      <c r="G2" s="215"/>
+      <c r="H2" s="214" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="213"/>
-      <c r="J2" s="214" t="s">
+      <c r="I2" s="214"/>
+      <c r="J2" s="215" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="214"/>
-      <c r="L2" s="213" t="s">
+      <c r="K2" s="215"/>
+      <c r="L2" s="214" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="213"/>
-      <c r="N2" s="210" t="s">
+      <c r="M2" s="214"/>
+      <c r="N2" s="207" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="210"/>
+      <c r="O2" s="207"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -76468,30 +76471,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="213" t="s">
+      <c r="C2" s="214" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="213"/>
-      <c r="E2" s="214" t="s">
+      <c r="D2" s="214"/>
+      <c r="E2" s="215" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="214"/>
-      <c r="G2" s="213" t="s">
+      <c r="F2" s="215"/>
+      <c r="G2" s="214" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="213"/>
-      <c r="I2" s="214" t="s">
+      <c r="H2" s="214"/>
+      <c r="I2" s="215" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="214"/>
-      <c r="K2" s="213" t="s">
+      <c r="J2" s="215"/>
+      <c r="K2" s="214" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="213"/>
-      <c r="M2" s="210" t="s">
+      <c r="L2" s="214"/>
+      <c r="M2" s="207" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="210"/>
+      <c r="N2" s="207"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -78253,30 +78256,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="213" t="s">
+      <c r="C2" s="214" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="213"/>
-      <c r="E2" s="214" t="s">
+      <c r="D2" s="214"/>
+      <c r="E2" s="215" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="214"/>
-      <c r="G2" s="213" t="s">
+      <c r="F2" s="215"/>
+      <c r="G2" s="214" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="213"/>
-      <c r="I2" s="214" t="s">
+      <c r="H2" s="214"/>
+      <c r="I2" s="215" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="214"/>
-      <c r="K2" s="213" t="s">
+      <c r="J2" s="215"/>
+      <c r="K2" s="214" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="213"/>
-      <c r="M2" s="210" t="s">
+      <c r="L2" s="214"/>
+      <c r="M2" s="207" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="210"/>
+      <c r="N2" s="207"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">

--- a/data/arsenal_stats.xlsx
+++ b/data/arsenal_stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bungeltd-my.sharepoint.com/personal/przemyslaw_iskra_bunge_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8366" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24102BB1-A7B7-48A6-A680-721507145F62}"/>
+  <xr:revisionPtr revIDLastSave="8387" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4E88830-3FD1-4E8E-9A42-072633E2BCEE}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="799" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="799" firstSheet="1" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="19" state="hidden" r:id="rId1"/>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2257" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2264" uniqueCount="490">
   <si>
     <t>Arsenal FC squad statistics</t>
   </si>
@@ -1529,6 +1529,27 @@
   </si>
   <si>
     <t>15.09.2026</t>
+  </si>
+  <si>
+    <t>Lille</t>
+  </si>
+  <si>
+    <t>Bayern</t>
+  </si>
+  <si>
+    <t>Slavia</t>
+  </si>
+  <si>
+    <t>BVB</t>
+  </si>
+  <si>
+    <t>Real</t>
+  </si>
+  <si>
+    <t>Betis</t>
+  </si>
+  <si>
+    <t>Sabah</t>
   </si>
 </sst>
 </file>
@@ -3089,6 +3110,15 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3098,23 +3128,23 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="54" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3152,15 +3182,6 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="28" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3168,27 +3189,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="61" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="10" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="37" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="11" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3281,67 +3281,31 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="61" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="10" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="37" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="11" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="54" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3418,6 +3382,63 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6472,7 +6493,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9D521208-3E63-4FC9-9B68-28E726336FAE}" type="CELLRANGE">
+                    <a:fld id="{2F035618-6D36-417B-9A71-82371B2CC50E}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6506,7 +6527,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7384FCB1-74B1-44BB-8B12-A820C40A1C35}" type="CELLRANGE">
+                    <a:fld id="{2AD5E3CA-4761-445A-81D8-5DA62B5ADA97}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6540,7 +6561,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{741905E0-B3A9-4E41-B782-22BB7220D4CA}" type="CELLRANGE">
+                    <a:fld id="{1FDE118A-B800-46D0-9718-7D79088A7E09}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6574,7 +6595,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2A06E546-FFAD-4823-8E4D-313970227B1D}" type="CELLRANGE">
+                    <a:fld id="{AC57C183-D711-42D6-8B65-E3F2527BED6E}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6608,7 +6629,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{53A23186-5113-40DC-99A0-503BC2D08310}" type="CELLRANGE">
+                    <a:fld id="{6DC55111-0B66-4DAD-8FCA-28E00EC7FCBD}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6642,7 +6663,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{24A8B175-165E-4EA1-98A6-742A5BEEFFBB}" type="CELLRANGE">
+                    <a:fld id="{EC4932CD-FEF3-4665-8722-4BE60EBB97DD}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6676,7 +6697,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7C27FA6E-1085-4E06-B2B4-8060866B5F82}" type="CELLRANGE">
+                    <a:fld id="{A2294881-C3D1-4A1F-A951-CADE7809F313}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6710,7 +6731,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9AE3376A-08BA-4554-ABDA-3D29EF7DF8D6}" type="CELLRANGE">
+                    <a:fld id="{C2C05114-3695-4C4E-94E0-061D9301D16E}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6744,7 +6765,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C7689B89-9D79-47E3-8D6C-C9852BA7D5C1}" type="CELLRANGE">
+                    <a:fld id="{68C3B752-2EC7-4B96-900E-C7103524BE47}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6778,7 +6799,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{15CDE8B1-B511-4BF4-B62F-0FA2DB8FEBDD}" type="CELLRANGE">
+                    <a:fld id="{3C09915B-9EF9-4A2D-ADA1-1480CD934E6B}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6812,7 +6833,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{4647DEAF-89D1-49E4-BA50-A2A01852240A}" type="CELLRANGE">
+                    <a:fld id="{73660311-12BE-4C39-BDED-B5848FBB4261}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6846,7 +6867,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{0478D755-E623-4AD3-BA3F-AD74F3556FAB}" type="CELLRANGE">
+                    <a:fld id="{6501924C-828A-4B61-A822-8B2FD1F67CDC}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6895,7 +6916,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{7C294CC8-A5CF-4840-B031-0E117169ED78}" type="CELLRANGE">
+                    <a:fld id="{22C12A00-B16D-419E-936D-48212C03DED9}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr>
                         <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
@@ -6954,7 +6975,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{1D55FC10-3CBA-467D-B2ED-E7BA6D287039}" type="CELLRANGE">
+                    <a:fld id="{47DF5A90-EA4C-497A-9E82-C5224D1525B8}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6988,7 +7009,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{0925FE1F-250D-4384-BDB4-7342547D0930}" type="CELLRANGE">
+                    <a:fld id="{A31C18A6-780E-473B-8673-80845D1CCE49}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7022,7 +7043,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{5E3DBA52-E20C-416D-978A-5367C79730F5}" type="CELLRANGE">
+                    <a:fld id="{E32598A8-BFE3-4E17-9276-23EDD7D6512F}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7056,7 +7077,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{73F596E1-F4BC-4BB9-A15E-9BBB05891E4D}" type="CELLRANGE">
+                    <a:fld id="{37EF83EA-DEB5-49A9-9931-FBA9766717BB}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -37628,196 +37649,196 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F1" s="216">
-        <v>1</v>
-      </c>
-      <c r="G1" s="217"/>
-      <c r="H1" s="218"/>
-      <c r="I1" s="216">
+      <c r="F1" s="219">
+        <v>1</v>
+      </c>
+      <c r="G1" s="220"/>
+      <c r="H1" s="221"/>
+      <c r="I1" s="219">
         <v>2</v>
       </c>
-      <c r="J1" s="217"/>
-      <c r="K1" s="218"/>
-      <c r="L1" s="216">
-        <v>3</v>
-      </c>
-      <c r="M1" s="217"/>
-      <c r="N1" s="218"/>
-      <c r="O1" s="216">
+      <c r="J1" s="220"/>
+      <c r="K1" s="221"/>
+      <c r="L1" s="219">
+        <v>3</v>
+      </c>
+      <c r="M1" s="220"/>
+      <c r="N1" s="221"/>
+      <c r="O1" s="219">
         <v>4</v>
       </c>
-      <c r="P1" s="217"/>
-      <c r="Q1" s="218"/>
-      <c r="R1" s="216">
+      <c r="P1" s="220"/>
+      <c r="Q1" s="221"/>
+      <c r="R1" s="219">
         <v>5</v>
       </c>
-      <c r="S1" s="217"/>
-      <c r="T1" s="218"/>
-      <c r="U1" s="216">
+      <c r="S1" s="220"/>
+      <c r="T1" s="221"/>
+      <c r="U1" s="219">
         <v>6</v>
       </c>
-      <c r="V1" s="217"/>
-      <c r="W1" s="218"/>
-      <c r="X1" s="216">
+      <c r="V1" s="220"/>
+      <c r="W1" s="221"/>
+      <c r="X1" s="219">
         <v>7</v>
       </c>
-      <c r="Y1" s="217"/>
-      <c r="Z1" s="218"/>
-      <c r="AA1" s="216">
+      <c r="Y1" s="220"/>
+      <c r="Z1" s="221"/>
+      <c r="AA1" s="219">
         <v>8</v>
       </c>
-      <c r="AB1" s="217"/>
-      <c r="AC1" s="218"/>
-      <c r="AD1" s="216">
+      <c r="AB1" s="220"/>
+      <c r="AC1" s="221"/>
+      <c r="AD1" s="219">
         <v>9</v>
       </c>
-      <c r="AE1" s="217"/>
-      <c r="AF1" s="218"/>
-      <c r="AG1" s="216">
+      <c r="AE1" s="220"/>
+      <c r="AF1" s="221"/>
+      <c r="AG1" s="219">
         <v>10</v>
       </c>
-      <c r="AH1" s="217"/>
-      <c r="AI1" s="218"/>
-      <c r="AJ1" s="216">
+      <c r="AH1" s="220"/>
+      <c r="AI1" s="221"/>
+      <c r="AJ1" s="219">
         <v>11</v>
       </c>
-      <c r="AK1" s="217"/>
-      <c r="AL1" s="218"/>
-      <c r="AM1" s="216">
+      <c r="AK1" s="220"/>
+      <c r="AL1" s="221"/>
+      <c r="AM1" s="219">
         <v>12</v>
       </c>
-      <c r="AN1" s="217"/>
-      <c r="AO1" s="218"/>
-      <c r="AP1" s="216">
+      <c r="AN1" s="220"/>
+      <c r="AO1" s="221"/>
+      <c r="AP1" s="219">
         <v>13</v>
       </c>
-      <c r="AQ1" s="217"/>
-      <c r="AR1" s="218"/>
-      <c r="AS1" s="216">
+      <c r="AQ1" s="220"/>
+      <c r="AR1" s="221"/>
+      <c r="AS1" s="219">
         <v>14</v>
       </c>
-      <c r="AT1" s="217"/>
-      <c r="AU1" s="218"/>
-      <c r="AV1" s="216">
+      <c r="AT1" s="220"/>
+      <c r="AU1" s="221"/>
+      <c r="AV1" s="219">
         <v>15</v>
       </c>
-      <c r="AW1" s="217"/>
-      <c r="AX1" s="218"/>
-      <c r="AY1" s="216">
+      <c r="AW1" s="220"/>
+      <c r="AX1" s="221"/>
+      <c r="AY1" s="219">
         <v>16</v>
       </c>
-      <c r="AZ1" s="217"/>
-      <c r="BA1" s="218"/>
-      <c r="BB1" s="216">
+      <c r="AZ1" s="220"/>
+      <c r="BA1" s="221"/>
+      <c r="BB1" s="219">
         <v>17</v>
       </c>
-      <c r="BC1" s="217"/>
-      <c r="BD1" s="218"/>
-      <c r="BE1" s="216">
+      <c r="BC1" s="220"/>
+      <c r="BD1" s="221"/>
+      <c r="BE1" s="219">
         <v>18</v>
       </c>
-      <c r="BF1" s="217"/>
-      <c r="BG1" s="218"/>
-      <c r="BH1" s="216">
+      <c r="BF1" s="220"/>
+      <c r="BG1" s="221"/>
+      <c r="BH1" s="219">
         <v>19</v>
       </c>
-      <c r="BI1" s="217"/>
-      <c r="BJ1" s="218"/>
-      <c r="BK1" s="216">
+      <c r="BI1" s="220"/>
+      <c r="BJ1" s="221"/>
+      <c r="BK1" s="219">
         <v>20</v>
       </c>
-      <c r="BL1" s="217"/>
-      <c r="BM1" s="218"/>
-      <c r="BN1" s="216">
+      <c r="BL1" s="220"/>
+      <c r="BM1" s="221"/>
+      <c r="BN1" s="219">
         <v>21</v>
       </c>
-      <c r="BO1" s="217"/>
-      <c r="BP1" s="218"/>
-      <c r="BQ1" s="216">
+      <c r="BO1" s="220"/>
+      <c r="BP1" s="221"/>
+      <c r="BQ1" s="219">
         <v>22</v>
       </c>
-      <c r="BR1" s="217"/>
-      <c r="BS1" s="218"/>
-      <c r="BT1" s="216">
+      <c r="BR1" s="220"/>
+      <c r="BS1" s="221"/>
+      <c r="BT1" s="219">
         <v>23</v>
       </c>
-      <c r="BU1" s="217"/>
-      <c r="BV1" s="218"/>
-      <c r="BW1" s="216">
+      <c r="BU1" s="220"/>
+      <c r="BV1" s="221"/>
+      <c r="BW1" s="219">
         <v>24</v>
       </c>
-      <c r="BX1" s="217"/>
-      <c r="BY1" s="218"/>
-      <c r="BZ1" s="216">
+      <c r="BX1" s="220"/>
+      <c r="BY1" s="221"/>
+      <c r="BZ1" s="219">
         <v>25</v>
       </c>
-      <c r="CA1" s="217"/>
-      <c r="CB1" s="218"/>
-      <c r="CC1" s="216">
+      <c r="CA1" s="220"/>
+      <c r="CB1" s="221"/>
+      <c r="CC1" s="219">
         <v>26</v>
       </c>
-      <c r="CD1" s="217"/>
-      <c r="CE1" s="218"/>
-      <c r="CF1" s="216">
+      <c r="CD1" s="220"/>
+      <c r="CE1" s="221"/>
+      <c r="CF1" s="219">
         <v>27</v>
       </c>
-      <c r="CG1" s="217"/>
-      <c r="CH1" s="218"/>
-      <c r="CI1" s="216">
+      <c r="CG1" s="220"/>
+      <c r="CH1" s="221"/>
+      <c r="CI1" s="219">
         <v>28</v>
       </c>
-      <c r="CJ1" s="217"/>
-      <c r="CK1" s="218"/>
-      <c r="CL1" s="216">
+      <c r="CJ1" s="220"/>
+      <c r="CK1" s="221"/>
+      <c r="CL1" s="219">
         <v>29</v>
       </c>
-      <c r="CM1" s="217"/>
-      <c r="CN1" s="218"/>
-      <c r="CO1" s="216">
+      <c r="CM1" s="220"/>
+      <c r="CN1" s="221"/>
+      <c r="CO1" s="219">
         <v>30</v>
       </c>
-      <c r="CP1" s="217"/>
-      <c r="CQ1" s="218"/>
-      <c r="CR1" s="216">
+      <c r="CP1" s="220"/>
+      <c r="CQ1" s="221"/>
+      <c r="CR1" s="219">
         <v>31</v>
       </c>
-      <c r="CS1" s="217"/>
-      <c r="CT1" s="218"/>
-      <c r="CU1" s="216">
+      <c r="CS1" s="220"/>
+      <c r="CT1" s="221"/>
+      <c r="CU1" s="219">
         <v>32</v>
       </c>
-      <c r="CV1" s="217"/>
-      <c r="CW1" s="218"/>
-      <c r="CX1" s="216">
+      <c r="CV1" s="220"/>
+      <c r="CW1" s="221"/>
+      <c r="CX1" s="219">
         <v>33</v>
       </c>
-      <c r="CY1" s="217"/>
-      <c r="CZ1" s="218"/>
-      <c r="DA1" s="216">
+      <c r="CY1" s="220"/>
+      <c r="CZ1" s="221"/>
+      <c r="DA1" s="219">
         <v>34</v>
       </c>
-      <c r="DB1" s="217"/>
-      <c r="DC1" s="218"/>
-      <c r="DD1" s="216">
+      <c r="DB1" s="220"/>
+      <c r="DC1" s="221"/>
+      <c r="DD1" s="219">
         <v>35</v>
       </c>
-      <c r="DE1" s="217"/>
-      <c r="DF1" s="218"/>
-      <c r="DG1" s="216">
+      <c r="DE1" s="220"/>
+      <c r="DF1" s="221"/>
+      <c r="DG1" s="219">
         <v>36</v>
       </c>
-      <c r="DH1" s="217"/>
-      <c r="DI1" s="218"/>
-      <c r="DJ1" s="216">
+      <c r="DH1" s="220"/>
+      <c r="DI1" s="221"/>
+      <c r="DJ1" s="219">
         <v>37</v>
       </c>
-      <c r="DK1" s="217"/>
-      <c r="DL1" s="218"/>
-      <c r="DM1" s="216">
+      <c r="DK1" s="220"/>
+      <c r="DL1" s="221"/>
+      <c r="DM1" s="219">
         <v>38</v>
       </c>
-      <c r="DN1" s="217"/>
-      <c r="DO1" s="218"/>
+      <c r="DN1" s="220"/>
+      <c r="DO1" s="221"/>
     </row>
     <row r="2" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
@@ -37831,196 +37852,196 @@
       <c r="E2" s="222" t="s">
         <v>398</v>
       </c>
-      <c r="F2" s="219" t="s">
+      <c r="F2" s="216" t="s">
         <v>346</v>
       </c>
-      <c r="G2" s="220"/>
-      <c r="H2" s="221"/>
-      <c r="I2" s="219" t="s">
+      <c r="G2" s="217"/>
+      <c r="H2" s="218"/>
+      <c r="I2" s="216" t="s">
         <v>331</v>
       </c>
-      <c r="J2" s="220"/>
-      <c r="K2" s="221"/>
-      <c r="L2" s="219" t="s">
+      <c r="J2" s="217"/>
+      <c r="K2" s="218"/>
+      <c r="L2" s="216" t="s">
         <v>330</v>
       </c>
-      <c r="M2" s="220"/>
-      <c r="N2" s="221"/>
-      <c r="O2" s="219" t="s">
+      <c r="M2" s="217"/>
+      <c r="N2" s="218"/>
+      <c r="O2" s="216" t="s">
         <v>328</v>
       </c>
-      <c r="P2" s="220"/>
-      <c r="Q2" s="221"/>
-      <c r="R2" s="219" t="s">
+      <c r="P2" s="217"/>
+      <c r="Q2" s="218"/>
+      <c r="R2" s="216" t="s">
         <v>335</v>
       </c>
-      <c r="S2" s="220"/>
-      <c r="T2" s="221"/>
-      <c r="U2" s="219" t="s">
+      <c r="S2" s="217"/>
+      <c r="T2" s="218"/>
+      <c r="U2" s="216" t="s">
         <v>320</v>
       </c>
-      <c r="V2" s="220"/>
-      <c r="W2" s="221"/>
-      <c r="X2" s="219" t="s">
+      <c r="V2" s="217"/>
+      <c r="W2" s="218"/>
+      <c r="X2" s="216" t="s">
         <v>337</v>
       </c>
-      <c r="Y2" s="220"/>
-      <c r="Z2" s="221"/>
-      <c r="AA2" s="219" t="s">
+      <c r="Y2" s="217"/>
+      <c r="Z2" s="218"/>
+      <c r="AA2" s="216" t="s">
         <v>334</v>
       </c>
-      <c r="AB2" s="220"/>
-      <c r="AC2" s="221"/>
-      <c r="AD2" s="219" t="s">
+      <c r="AB2" s="217"/>
+      <c r="AC2" s="218"/>
+      <c r="AD2" s="216" t="s">
         <v>321</v>
       </c>
-      <c r="AE2" s="220"/>
-      <c r="AF2" s="221"/>
-      <c r="AG2" s="219" t="s">
+      <c r="AE2" s="217"/>
+      <c r="AF2" s="218"/>
+      <c r="AG2" s="216" t="s">
         <v>347</v>
       </c>
-      <c r="AH2" s="220"/>
-      <c r="AI2" s="221"/>
-      <c r="AJ2" s="219" t="s">
+      <c r="AH2" s="217"/>
+      <c r="AI2" s="218"/>
+      <c r="AJ2" s="216" t="s">
         <v>324</v>
       </c>
-      <c r="AK2" s="220"/>
-      <c r="AL2" s="221"/>
-      <c r="AM2" s="219" t="s">
+      <c r="AK2" s="217"/>
+      <c r="AL2" s="218"/>
+      <c r="AM2" s="216" t="s">
         <v>323</v>
       </c>
-      <c r="AN2" s="220"/>
-      <c r="AO2" s="221"/>
-      <c r="AP2" s="219" t="s">
+      <c r="AN2" s="217"/>
+      <c r="AO2" s="218"/>
+      <c r="AP2" s="216" t="s">
         <v>332</v>
       </c>
-      <c r="AQ2" s="220"/>
-      <c r="AR2" s="221"/>
-      <c r="AS2" s="219" t="s">
+      <c r="AQ2" s="217"/>
+      <c r="AR2" s="218"/>
+      <c r="AS2" s="216" t="s">
         <v>329</v>
       </c>
-      <c r="AT2" s="220"/>
-      <c r="AU2" s="221"/>
-      <c r="AV2" s="219" t="s">
+      <c r="AT2" s="217"/>
+      <c r="AU2" s="218"/>
+      <c r="AV2" s="216" t="s">
         <v>336</v>
       </c>
-      <c r="AW2" s="220"/>
-      <c r="AX2" s="221"/>
-      <c r="AY2" s="219" t="s">
+      <c r="AW2" s="217"/>
+      <c r="AX2" s="218"/>
+      <c r="AY2" s="216" t="s">
         <v>305</v>
       </c>
-      <c r="AZ2" s="220"/>
-      <c r="BA2" s="221"/>
-      <c r="BB2" s="219" t="s">
+      <c r="AZ2" s="217"/>
+      <c r="BA2" s="218"/>
+      <c r="BB2" s="216" t="s">
         <v>326</v>
       </c>
-      <c r="BC2" s="220"/>
-      <c r="BD2" s="221"/>
-      <c r="BE2" s="219" t="s">
+      <c r="BC2" s="217"/>
+      <c r="BD2" s="218"/>
+      <c r="BE2" s="216" t="s">
         <v>325</v>
       </c>
-      <c r="BF2" s="220"/>
-      <c r="BG2" s="221"/>
-      <c r="BH2" s="219" t="s">
+      <c r="BF2" s="217"/>
+      <c r="BG2" s="218"/>
+      <c r="BH2" s="216" t="s">
         <v>348</v>
       </c>
-      <c r="BI2" s="220"/>
-      <c r="BJ2" s="221"/>
-      <c r="BK2" s="219" t="s">
+      <c r="BI2" s="217"/>
+      <c r="BJ2" s="218"/>
+      <c r="BK2" s="216" t="s">
         <v>332</v>
       </c>
-      <c r="BL2" s="220"/>
-      <c r="BM2" s="221"/>
-      <c r="BN2" s="219" t="s">
+      <c r="BL2" s="217"/>
+      <c r="BM2" s="218"/>
+      <c r="BN2" s="216" t="s">
         <v>347</v>
       </c>
-      <c r="BO2" s="220"/>
-      <c r="BP2" s="221"/>
-      <c r="BQ2" s="219" t="s">
+      <c r="BO2" s="217"/>
+      <c r="BP2" s="218"/>
+      <c r="BQ2" s="216" t="s">
         <v>324</v>
       </c>
-      <c r="BR2" s="220"/>
-      <c r="BS2" s="221"/>
-      <c r="BT2" s="219" t="s">
+      <c r="BR2" s="217"/>
+      <c r="BS2" s="218"/>
+      <c r="BT2" s="216" t="s">
         <v>323</v>
       </c>
-      <c r="BU2" s="220"/>
-      <c r="BV2" s="221"/>
-      <c r="BW2" s="219" t="s">
+      <c r="BU2" s="217"/>
+      <c r="BV2" s="218"/>
+      <c r="BW2" s="216" t="s">
         <v>321</v>
       </c>
-      <c r="BX2" s="220"/>
-      <c r="BY2" s="221"/>
-      <c r="BZ2" s="219" t="s">
+      <c r="BX2" s="217"/>
+      <c r="BY2" s="218"/>
+      <c r="BZ2" s="216" t="s">
         <v>348</v>
       </c>
-      <c r="CA2" s="220"/>
-      <c r="CB2" s="221"/>
-      <c r="CC2" s="219" t="s">
+      <c r="CA2" s="217"/>
+      <c r="CB2" s="218"/>
+      <c r="CC2" s="216" t="s">
         <v>325</v>
       </c>
-      <c r="CD2" s="220"/>
-      <c r="CE2" s="221"/>
-      <c r="CF2" s="219" t="s">
+      <c r="CD2" s="217"/>
+      <c r="CE2" s="218"/>
+      <c r="CF2" s="216" t="s">
         <v>305</v>
       </c>
-      <c r="CG2" s="220"/>
-      <c r="CH2" s="221"/>
-      <c r="CI2" s="219" t="s">
+      <c r="CG2" s="217"/>
+      <c r="CH2" s="218"/>
+      <c r="CI2" s="216" t="s">
         <v>326</v>
       </c>
-      <c r="CJ2" s="220"/>
-      <c r="CK2" s="221"/>
-      <c r="CL2" s="219" t="s">
+      <c r="CJ2" s="217"/>
+      <c r="CK2" s="218"/>
+      <c r="CL2" s="216" t="s">
         <v>330</v>
       </c>
-      <c r="CM2" s="220"/>
-      <c r="CN2" s="221"/>
-      <c r="CO2" s="219" t="s">
+      <c r="CM2" s="217"/>
+      <c r="CN2" s="218"/>
+      <c r="CO2" s="216" t="s">
         <v>328</v>
       </c>
-      <c r="CP2" s="220"/>
-      <c r="CQ2" s="221"/>
-      <c r="CR2" s="219" t="s">
+      <c r="CP2" s="217"/>
+      <c r="CQ2" s="218"/>
+      <c r="CR2" s="216" t="s">
         <v>346</v>
       </c>
-      <c r="CS2" s="220"/>
-      <c r="CT2" s="221"/>
-      <c r="CU2" s="219" t="s">
+      <c r="CS2" s="217"/>
+      <c r="CT2" s="218"/>
+      <c r="CU2" s="216" t="s">
         <v>331</v>
       </c>
-      <c r="CV2" s="220"/>
-      <c r="CW2" s="221"/>
-      <c r="CX2" s="219" t="s">
+      <c r="CV2" s="217"/>
+      <c r="CW2" s="218"/>
+      <c r="CX2" s="216" t="s">
         <v>336</v>
       </c>
-      <c r="CY2" s="220"/>
-      <c r="CZ2" s="221"/>
-      <c r="DA2" s="219" t="s">
+      <c r="CY2" s="217"/>
+      <c r="CZ2" s="218"/>
+      <c r="DA2" s="216" t="s">
         <v>329</v>
       </c>
-      <c r="DB2" s="220"/>
-      <c r="DC2" s="221"/>
-      <c r="DD2" s="219" t="s">
+      <c r="DB2" s="217"/>
+      <c r="DC2" s="218"/>
+      <c r="DD2" s="216" t="s">
         <v>320</v>
       </c>
-      <c r="DE2" s="220"/>
-      <c r="DF2" s="221"/>
-      <c r="DG2" s="219" t="s">
+      <c r="DE2" s="217"/>
+      <c r="DF2" s="218"/>
+      <c r="DG2" s="216" t="s">
         <v>337</v>
       </c>
-      <c r="DH2" s="220"/>
-      <c r="DI2" s="221"/>
-      <c r="DJ2" s="219" t="s">
+      <c r="DH2" s="217"/>
+      <c r="DI2" s="218"/>
+      <c r="DJ2" s="216" t="s">
         <v>334</v>
       </c>
-      <c r="DK2" s="220"/>
-      <c r="DL2" s="221"/>
-      <c r="DM2" s="219" t="s">
+      <c r="DK2" s="217"/>
+      <c r="DL2" s="218"/>
+      <c r="DM2" s="216" t="s">
         <v>335</v>
       </c>
-      <c r="DN2" s="220"/>
-      <c r="DO2" s="221"/>
+      <c r="DN2" s="217"/>
+      <c r="DO2" s="218"/>
     </row>
     <row r="3" spans="1:119" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -38029,9 +38050,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="224"/>
-      <c r="D3" s="224"/>
-      <c r="E3" s="223"/>
+      <c r="C3" s="223"/>
+      <c r="D3" s="223"/>
+      <c r="E3" s="224"/>
       <c r="F3" s="160" t="s">
         <v>393</v>
       </c>
@@ -43552,6 +43573,69 @@
     </row>
   </sheetData>
   <mergeCells count="79">
+    <mergeCell ref="DM1:DO1"/>
+    <mergeCell ref="DM2:DO2"/>
+    <mergeCell ref="DA1:DC1"/>
+    <mergeCell ref="DA2:DC2"/>
+    <mergeCell ref="DD1:DF1"/>
+    <mergeCell ref="DD2:DF2"/>
+    <mergeCell ref="DG1:DI1"/>
+    <mergeCell ref="DG2:DI2"/>
+    <mergeCell ref="CU1:CW1"/>
+    <mergeCell ref="CU2:CW2"/>
+    <mergeCell ref="CX1:CZ1"/>
+    <mergeCell ref="CX2:CZ2"/>
+    <mergeCell ref="DJ1:DL1"/>
+    <mergeCell ref="DJ2:DL2"/>
+    <mergeCell ref="CL1:CN1"/>
+    <mergeCell ref="CL2:CN2"/>
+    <mergeCell ref="CO1:CQ1"/>
+    <mergeCell ref="CO2:CQ2"/>
+    <mergeCell ref="CR1:CT1"/>
+    <mergeCell ref="CR2:CT2"/>
+    <mergeCell ref="CC1:CE1"/>
+    <mergeCell ref="CC2:CE2"/>
+    <mergeCell ref="CF1:CH1"/>
+    <mergeCell ref="CF2:CH2"/>
+    <mergeCell ref="CI1:CK1"/>
+    <mergeCell ref="CI2:CK2"/>
+    <mergeCell ref="BT1:BV1"/>
+    <mergeCell ref="BT2:BV2"/>
+    <mergeCell ref="BW1:BY1"/>
+    <mergeCell ref="BW2:BY2"/>
+    <mergeCell ref="BZ1:CB1"/>
+    <mergeCell ref="BZ2:CB2"/>
+    <mergeCell ref="BK1:BM1"/>
+    <mergeCell ref="BK2:BM2"/>
+    <mergeCell ref="BN1:BP1"/>
+    <mergeCell ref="BN2:BP2"/>
+    <mergeCell ref="BQ1:BS1"/>
+    <mergeCell ref="BQ2:BS2"/>
+    <mergeCell ref="AS1:AU1"/>
+    <mergeCell ref="AS2:AU2"/>
+    <mergeCell ref="AV1:AX1"/>
+    <mergeCell ref="AV2:AX2"/>
+    <mergeCell ref="BH1:BJ1"/>
+    <mergeCell ref="BH2:BJ2"/>
+    <mergeCell ref="AY2:BA2"/>
+    <mergeCell ref="BB2:BD2"/>
+    <mergeCell ref="BE2:BG2"/>
+    <mergeCell ref="AJ1:AL1"/>
+    <mergeCell ref="AJ2:AL2"/>
+    <mergeCell ref="AM1:AO1"/>
+    <mergeCell ref="AM2:AO2"/>
+    <mergeCell ref="AP2:AR2"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
     <mergeCell ref="AD2:AF2"/>
     <mergeCell ref="AG2:AI2"/>
     <mergeCell ref="BB1:BD1"/>
@@ -43568,69 +43652,6 @@
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="X1:Z1"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="AJ1:AL1"/>
-    <mergeCell ref="AJ2:AL2"/>
-    <mergeCell ref="AM1:AO1"/>
-    <mergeCell ref="AM2:AO2"/>
-    <mergeCell ref="AP2:AR2"/>
-    <mergeCell ref="AS1:AU1"/>
-    <mergeCell ref="AS2:AU2"/>
-    <mergeCell ref="AV1:AX1"/>
-    <mergeCell ref="AV2:AX2"/>
-    <mergeCell ref="BH1:BJ1"/>
-    <mergeCell ref="BH2:BJ2"/>
-    <mergeCell ref="AY2:BA2"/>
-    <mergeCell ref="BB2:BD2"/>
-    <mergeCell ref="BE2:BG2"/>
-    <mergeCell ref="BK1:BM1"/>
-    <mergeCell ref="BK2:BM2"/>
-    <mergeCell ref="BN1:BP1"/>
-    <mergeCell ref="BN2:BP2"/>
-    <mergeCell ref="BQ1:BS1"/>
-    <mergeCell ref="BQ2:BS2"/>
-    <mergeCell ref="BT1:BV1"/>
-    <mergeCell ref="BT2:BV2"/>
-    <mergeCell ref="BW1:BY1"/>
-    <mergeCell ref="BW2:BY2"/>
-    <mergeCell ref="BZ1:CB1"/>
-    <mergeCell ref="BZ2:CB2"/>
-    <mergeCell ref="CC1:CE1"/>
-    <mergeCell ref="CC2:CE2"/>
-    <mergeCell ref="CF1:CH1"/>
-    <mergeCell ref="CF2:CH2"/>
-    <mergeCell ref="CI1:CK1"/>
-    <mergeCell ref="CI2:CK2"/>
-    <mergeCell ref="CL1:CN1"/>
-    <mergeCell ref="CL2:CN2"/>
-    <mergeCell ref="CO1:CQ1"/>
-    <mergeCell ref="CO2:CQ2"/>
-    <mergeCell ref="CR1:CT1"/>
-    <mergeCell ref="CR2:CT2"/>
-    <mergeCell ref="CU1:CW1"/>
-    <mergeCell ref="CU2:CW2"/>
-    <mergeCell ref="CX1:CZ1"/>
-    <mergeCell ref="CX2:CZ2"/>
-    <mergeCell ref="DJ1:DL1"/>
-    <mergeCell ref="DJ2:DL2"/>
-    <mergeCell ref="DM1:DO1"/>
-    <mergeCell ref="DM2:DO2"/>
-    <mergeCell ref="DA1:DC1"/>
-    <mergeCell ref="DA2:DC2"/>
-    <mergeCell ref="DD1:DF1"/>
-    <mergeCell ref="DD2:DF2"/>
-    <mergeCell ref="DG1:DI1"/>
-    <mergeCell ref="DG2:DI2"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:DO37">
     <cfRule type="cellIs" dxfId="18" priority="1" operator="between">
@@ -43666,41 +43687,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="234" t="s">
+      <c r="C1" s="237" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="234" t="s">
+      <c r="D1" s="237" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="234" t="s">
+      <c r="E1" s="237" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="225" t="s">
+      <c r="F1" s="228" t="s">
         <v>302</v>
       </c>
-      <c r="G1" s="226"/>
-      <c r="H1" s="226"/>
-      <c r="I1" s="226"/>
-      <c r="J1" s="226"/>
-      <c r="K1" s="226"/>
-      <c r="L1" s="226"/>
-      <c r="M1" s="226"/>
-      <c r="N1" s="226"/>
-      <c r="O1" s="226"/>
-      <c r="P1" s="226"/>
-      <c r="Q1" s="226"/>
-      <c r="R1" s="226"/>
-      <c r="S1" s="226"/>
-      <c r="T1" s="226"/>
-      <c r="U1" s="226"/>
-      <c r="V1" s="226"/>
-      <c r="W1" s="226"/>
-      <c r="X1" s="226"/>
-      <c r="Y1" s="226"/>
-      <c r="Z1" s="226"/>
-      <c r="AA1" s="226"/>
-      <c r="AB1" s="226"/>
-      <c r="AC1" s="227"/>
+      <c r="G1" s="229"/>
+      <c r="H1" s="229"/>
+      <c r="I1" s="229"/>
+      <c r="J1" s="229"/>
+      <c r="K1" s="229"/>
+      <c r="L1" s="229"/>
+      <c r="M1" s="229"/>
+      <c r="N1" s="229"/>
+      <c r="O1" s="229"/>
+      <c r="P1" s="229"/>
+      <c r="Q1" s="229"/>
+      <c r="R1" s="229"/>
+      <c r="S1" s="229"/>
+      <c r="T1" s="229"/>
+      <c r="U1" s="229"/>
+      <c r="V1" s="229"/>
+      <c r="W1" s="229"/>
+      <c r="X1" s="229"/>
+      <c r="Y1" s="229"/>
+      <c r="Z1" s="229"/>
+      <c r="AA1" s="229"/>
+      <c r="AB1" s="229"/>
+      <c r="AC1" s="230"/>
       <c r="AD1" s="240" t="s">
         <v>281</v>
       </c>
@@ -43709,81 +43730,95 @@
       <c r="AG1" s="241"/>
       <c r="AH1" s="241"/>
       <c r="AI1" s="242"/>
-      <c r="AJ1" s="225" t="s">
+      <c r="AJ1" s="228" t="s">
         <v>282</v>
       </c>
-      <c r="AK1" s="226"/>
-      <c r="AL1" s="226"/>
-      <c r="AM1" s="226"/>
-      <c r="AN1" s="226"/>
-      <c r="AO1" s="227"/>
-      <c r="AP1" s="228" t="s">
+      <c r="AK1" s="229"/>
+      <c r="AL1" s="229"/>
+      <c r="AM1" s="229"/>
+      <c r="AN1" s="229"/>
+      <c r="AO1" s="230"/>
+      <c r="AP1" s="231" t="s">
         <v>283</v>
       </c>
-      <c r="AQ1" s="229"/>
-      <c r="AR1" s="229"/>
-      <c r="AS1" s="229"/>
-      <c r="AT1" s="229"/>
-      <c r="AU1" s="230"/>
-      <c r="AV1" s="231" t="s">
+      <c r="AQ1" s="232"/>
+      <c r="AR1" s="232"/>
+      <c r="AS1" s="232"/>
+      <c r="AT1" s="232"/>
+      <c r="AU1" s="233"/>
+      <c r="AV1" s="234" t="s">
         <v>86</v>
       </c>
-      <c r="AW1" s="232"/>
-      <c r="AX1" s="233"/>
+      <c r="AW1" s="235"/>
+      <c r="AX1" s="236"/>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="235"/>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="237" t="s">
+      <c r="C2" s="238"/>
+      <c r="D2" s="238"/>
+      <c r="E2" s="238"/>
+      <c r="F2" s="225" t="s">
         <v>468</v>
       </c>
-      <c r="G2" s="238"/>
-      <c r="H2" s="239"/>
-      <c r="I2" s="237"/>
-      <c r="J2" s="238"/>
-      <c r="K2" s="239"/>
-      <c r="L2" s="237"/>
-      <c r="M2" s="238"/>
-      <c r="N2" s="239"/>
-      <c r="O2" s="237"/>
-      <c r="P2" s="238"/>
-      <c r="Q2" s="239"/>
-      <c r="R2" s="237"/>
-      <c r="S2" s="238"/>
-      <c r="T2" s="239"/>
-      <c r="U2" s="237"/>
-      <c r="V2" s="238"/>
-      <c r="W2" s="239"/>
-      <c r="X2" s="237"/>
-      <c r="Y2" s="238"/>
-      <c r="Z2" s="239"/>
-      <c r="AA2" s="237"/>
-      <c r="AB2" s="238"/>
-      <c r="AC2" s="238"/>
-      <c r="AD2" s="237"/>
-      <c r="AE2" s="238"/>
-      <c r="AF2" s="239"/>
-      <c r="AG2" s="237"/>
-      <c r="AH2" s="238"/>
-      <c r="AI2" s="239"/>
-      <c r="AJ2" s="237"/>
-      <c r="AK2" s="238"/>
-      <c r="AL2" s="239"/>
-      <c r="AM2" s="237"/>
-      <c r="AN2" s="238"/>
-      <c r="AO2" s="239"/>
-      <c r="AP2" s="237"/>
-      <c r="AQ2" s="238"/>
-      <c r="AR2" s="239"/>
-      <c r="AS2" s="237"/>
-      <c r="AT2" s="238"/>
-      <c r="AU2" s="239"/>
-      <c r="AV2" s="237"/>
-      <c r="AW2" s="238"/>
-      <c r="AX2" s="239"/>
+      <c r="G2" s="226"/>
+      <c r="H2" s="227"/>
+      <c r="I2" s="225" t="s">
+        <v>483</v>
+      </c>
+      <c r="J2" s="226"/>
+      <c r="K2" s="227"/>
+      <c r="L2" s="225" t="s">
+        <v>484</v>
+      </c>
+      <c r="M2" s="226"/>
+      <c r="N2" s="227"/>
+      <c r="O2" s="225" t="s">
+        <v>485</v>
+      </c>
+      <c r="P2" s="226"/>
+      <c r="Q2" s="227"/>
+      <c r="R2" s="225" t="s">
+        <v>486</v>
+      </c>
+      <c r="S2" s="226"/>
+      <c r="T2" s="227"/>
+      <c r="U2" s="225" t="s">
+        <v>487</v>
+      </c>
+      <c r="V2" s="226"/>
+      <c r="W2" s="227"/>
+      <c r="X2" s="225" t="s">
+        <v>488</v>
+      </c>
+      <c r="Y2" s="226"/>
+      <c r="Z2" s="227"/>
+      <c r="AA2" s="225" t="s">
+        <v>489</v>
+      </c>
+      <c r="AB2" s="226"/>
+      <c r="AC2" s="226"/>
+      <c r="AD2" s="225"/>
+      <c r="AE2" s="226"/>
+      <c r="AF2" s="227"/>
+      <c r="AG2" s="225"/>
+      <c r="AH2" s="226"/>
+      <c r="AI2" s="227"/>
+      <c r="AJ2" s="225"/>
+      <c r="AK2" s="226"/>
+      <c r="AL2" s="227"/>
+      <c r="AM2" s="225"/>
+      <c r="AN2" s="226"/>
+      <c r="AO2" s="227"/>
+      <c r="AP2" s="225"/>
+      <c r="AQ2" s="226"/>
+      <c r="AR2" s="227"/>
+      <c r="AS2" s="225"/>
+      <c r="AT2" s="226"/>
+      <c r="AU2" s="227"/>
+      <c r="AV2" s="225"/>
+      <c r="AW2" s="226"/>
+      <c r="AX2" s="227"/>
     </row>
     <row r="3" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -43792,9 +43827,9 @@
       <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="236"/>
-      <c r="D3" s="236"/>
-      <c r="E3" s="236"/>
+      <c r="C3" s="239"/>
+      <c r="D3" s="239"/>
+      <c r="E3" s="239"/>
       <c r="F3" s="170" t="s">
         <v>393</v>
       </c>
@@ -46361,13 +46396,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="F1:AC1"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="AJ1:AO1"/>
     <mergeCell ref="AP1:AU1"/>
     <mergeCell ref="AV1:AX1"/>
@@ -46384,6 +46412,13 @@
     <mergeCell ref="AD1:AI1"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="I2:K2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="F1:AC1"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
+    <mergeCell ref="AA2:AC2"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:AW31">
     <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
@@ -46418,70 +46453,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C1" s="234" t="s">
+      <c r="C1" s="237" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="234" t="s">
+      <c r="D1" s="237" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="234" t="s">
+      <c r="E1" s="237" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="274" t="s">
+      <c r="F1" s="267" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="275"/>
-      <c r="H1" s="276"/>
-      <c r="I1" s="277" t="s">
+      <c r="G1" s="268"/>
+      <c r="H1" s="269"/>
+      <c r="I1" s="270" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="278"/>
-      <c r="K1" s="279"/>
-      <c r="L1" s="244" t="s">
+      <c r="J1" s="271"/>
+      <c r="K1" s="272"/>
+      <c r="L1" s="274" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="245"/>
-      <c r="N1" s="246"/>
-      <c r="O1" s="247" t="s">
+      <c r="M1" s="275"/>
+      <c r="N1" s="276"/>
+      <c r="O1" s="277" t="s">
         <v>199</v>
       </c>
-      <c r="P1" s="248"/>
-      <c r="Q1" s="249"/>
-      <c r="R1" s="250" t="s">
+      <c r="P1" s="278"/>
+      <c r="Q1" s="279"/>
+      <c r="R1" s="243" t="s">
         <v>200</v>
       </c>
-      <c r="S1" s="251"/>
-      <c r="T1" s="252"/>
-      <c r="U1" s="253" t="s">
+      <c r="S1" s="244"/>
+      <c r="T1" s="245"/>
+      <c r="U1" s="246" t="s">
         <v>306</v>
       </c>
-      <c r="V1" s="254"/>
-      <c r="W1" s="255"/>
+      <c r="V1" s="247"/>
+      <c r="W1" s="248"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="235"/>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="256"/>
-      <c r="G2" s="257"/>
-      <c r="H2" s="258"/>
-      <c r="I2" s="271"/>
-      <c r="J2" s="272"/>
-      <c r="K2" s="273"/>
-      <c r="L2" s="268"/>
-      <c r="M2" s="269"/>
-      <c r="N2" s="270"/>
-      <c r="O2" s="265"/>
-      <c r="P2" s="266"/>
-      <c r="Q2" s="267"/>
-      <c r="R2" s="262"/>
-      <c r="S2" s="263"/>
-      <c r="T2" s="264"/>
-      <c r="U2" s="259"/>
-      <c r="V2" s="260"/>
-      <c r="W2" s="261"/>
+      <c r="C2" s="238"/>
+      <c r="D2" s="238"/>
+      <c r="E2" s="238"/>
+      <c r="F2" s="249"/>
+      <c r="G2" s="250"/>
+      <c r="H2" s="251"/>
+      <c r="I2" s="264"/>
+      <c r="J2" s="265"/>
+      <c r="K2" s="266"/>
+      <c r="L2" s="261"/>
+      <c r="M2" s="262"/>
+      <c r="N2" s="263"/>
+      <c r="O2" s="258"/>
+      <c r="P2" s="259"/>
+      <c r="Q2" s="260"/>
+      <c r="R2" s="255"/>
+      <c r="S2" s="256"/>
+      <c r="T2" s="257"/>
+      <c r="U2" s="252"/>
+      <c r="V2" s="253"/>
+      <c r="W2" s="254"/>
     </row>
     <row r="3" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -46490,9 +46525,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="243"/>
-      <c r="D3" s="243"/>
-      <c r="E3" s="243"/>
+      <c r="C3" s="273"/>
+      <c r="D3" s="273"/>
+      <c r="E3" s="273"/>
       <c r="F3" s="189" t="s">
         <v>393</v>
       </c>
@@ -47916,6 +47951,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="O1:Q1"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="F2:H2"/>
@@ -47926,11 +47966,6 @@
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="O1:Q1"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:W31">
     <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
@@ -54744,72 +54779,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C1" s="234" t="s">
+      <c r="C1" s="237" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="234" t="s">
+      <c r="D1" s="237" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="234" t="s">
+      <c r="E1" s="237" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="274" t="s">
+      <c r="F1" s="267" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="275"/>
-      <c r="H1" s="276"/>
-      <c r="I1" s="277" t="s">
+      <c r="G1" s="268"/>
+      <c r="H1" s="269"/>
+      <c r="I1" s="270" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="278"/>
-      <c r="K1" s="279"/>
-      <c r="L1" s="244" t="s">
+      <c r="J1" s="271"/>
+      <c r="K1" s="272"/>
+      <c r="L1" s="274" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="245"/>
-      <c r="N1" s="246"/>
-      <c r="O1" s="247" t="s">
+      <c r="M1" s="275"/>
+      <c r="N1" s="276"/>
+      <c r="O1" s="277" t="s">
         <v>199</v>
       </c>
-      <c r="P1" s="248"/>
-      <c r="Q1" s="249"/>
-      <c r="R1" s="250" t="s">
+      <c r="P1" s="278"/>
+      <c r="Q1" s="279"/>
+      <c r="R1" s="243" t="s">
         <v>200</v>
       </c>
-      <c r="S1" s="251"/>
-      <c r="T1" s="252"/>
-      <c r="U1" s="253" t="s">
+      <c r="S1" s="244"/>
+      <c r="T1" s="245"/>
+      <c r="U1" s="246" t="s">
         <v>306</v>
       </c>
-      <c r="V1" s="254"/>
-      <c r="W1" s="255"/>
+      <c r="V1" s="247"/>
+      <c r="W1" s="248"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="235"/>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="256" t="s">
+      <c r="C2" s="238"/>
+      <c r="D2" s="238"/>
+      <c r="E2" s="238"/>
+      <c r="F2" s="249" t="s">
         <v>433</v>
       </c>
-      <c r="G2" s="257"/>
-      <c r="H2" s="258"/>
-      <c r="I2" s="271"/>
-      <c r="J2" s="272"/>
-      <c r="K2" s="273"/>
-      <c r="L2" s="268"/>
-      <c r="M2" s="269"/>
-      <c r="N2" s="270"/>
-      <c r="O2" s="265"/>
-      <c r="P2" s="266"/>
-      <c r="Q2" s="267"/>
-      <c r="R2" s="262"/>
-      <c r="S2" s="263"/>
-      <c r="T2" s="264"/>
-      <c r="U2" s="259"/>
-      <c r="V2" s="260"/>
-      <c r="W2" s="261"/>
+      <c r="G2" s="250"/>
+      <c r="H2" s="251"/>
+      <c r="I2" s="264"/>
+      <c r="J2" s="265"/>
+      <c r="K2" s="266"/>
+      <c r="L2" s="261"/>
+      <c r="M2" s="262"/>
+      <c r="N2" s="263"/>
+      <c r="O2" s="258"/>
+      <c r="P2" s="259"/>
+      <c r="Q2" s="260"/>
+      <c r="R2" s="255"/>
+      <c r="S2" s="256"/>
+      <c r="T2" s="257"/>
+      <c r="U2" s="252"/>
+      <c r="V2" s="253"/>
+      <c r="W2" s="254"/>
     </row>
     <row r="3" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -54818,9 +54853,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="243"/>
-      <c r="D3" s="243"/>
-      <c r="E3" s="243"/>
+      <c r="C3" s="273"/>
+      <c r="D3" s="273"/>
+      <c r="E3" s="273"/>
       <c r="F3" s="189" t="s">
         <v>393</v>
       </c>
@@ -56244,11 +56279,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="F2:H2"/>
@@ -56259,6 +56289,11 @@
     <mergeCell ref="U2:W2"/>
     <mergeCell ref="L1:N1"/>
     <mergeCell ref="O1:Q1"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:W31">
     <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
@@ -56754,51 +56789,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="302" t="s">
+      <c r="C1" s="283" t="s">
         <v>202</v>
       </c>
-      <c r="D1" s="303"/>
-      <c r="E1" s="303"/>
-      <c r="F1" s="303"/>
-      <c r="G1" s="303"/>
-      <c r="H1" s="303"/>
-      <c r="I1" s="304"/>
+      <c r="D1" s="284"/>
+      <c r="E1" s="284"/>
+      <c r="F1" s="284"/>
+      <c r="G1" s="284"/>
+      <c r="H1" s="284"/>
+      <c r="I1" s="285"/>
       <c r="J1" s="114" t="s">
         <v>195</v>
       </c>
       <c r="K1" s="115" t="s">
         <v>194</v>
       </c>
-      <c r="L1" s="282" t="s">
+      <c r="L1" s="307" t="s">
         <v>287</v>
       </c>
-      <c r="M1" s="287"/>
-      <c r="N1" s="287"/>
-      <c r="O1" s="287"/>
-      <c r="P1" s="287"/>
-      <c r="Q1" s="287"/>
-      <c r="R1" s="287"/>
-      <c r="S1" s="287"/>
-      <c r="T1" s="287"/>
-      <c r="U1" s="287"/>
-      <c r="V1" s="287"/>
-      <c r="W1" s="287"/>
-      <c r="X1" s="287"/>
-      <c r="Y1" s="287"/>
-      <c r="Z1" s="287"/>
-      <c r="AA1" s="287"/>
-      <c r="AB1" s="287"/>
-      <c r="AC1" s="287"/>
-      <c r="AD1" s="287"/>
-      <c r="AE1" s="287"/>
-      <c r="AF1" s="287"/>
-      <c r="AG1" s="288"/>
-      <c r="AH1" s="282" t="s">
+      <c r="M1" s="312"/>
+      <c r="N1" s="312"/>
+      <c r="O1" s="312"/>
+      <c r="P1" s="312"/>
+      <c r="Q1" s="312"/>
+      <c r="R1" s="312"/>
+      <c r="S1" s="312"/>
+      <c r="T1" s="312"/>
+      <c r="U1" s="312"/>
+      <c r="V1" s="312"/>
+      <c r="W1" s="312"/>
+      <c r="X1" s="312"/>
+      <c r="Y1" s="312"/>
+      <c r="Z1" s="312"/>
+      <c r="AA1" s="312"/>
+      <c r="AB1" s="312"/>
+      <c r="AC1" s="312"/>
+      <c r="AD1" s="312"/>
+      <c r="AE1" s="312"/>
+      <c r="AF1" s="312"/>
+      <c r="AG1" s="313"/>
+      <c r="AH1" s="307" t="s">
         <v>175</v>
       </c>
-      <c r="AI1" s="283"/>
-      <c r="AJ1" s="283"/>
-      <c r="AK1" s="284"/>
+      <c r="AI1" s="308"/>
+      <c r="AJ1" s="308"/>
+      <c r="AK1" s="309"/>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B2" s="111"/>
@@ -61998,15 +62033,15 @@
         <f t="shared" ref="J80:J111" si="2">H80-I80</f>
         <v>2</v>
       </c>
-      <c r="K80" s="289" t="s">
+      <c r="K80" s="314" t="s">
         <v>435</v>
       </c>
-      <c r="L80" s="290"/>
-      <c r="M80" s="291"/>
+      <c r="L80" s="315"/>
+      <c r="M80" s="316"/>
       <c r="O80" s="133"/>
       <c r="P80" s="133"/>
-      <c r="W80" s="285"/>
-      <c r="X80" s="285"/>
+      <c r="W80" s="310"/>
+      <c r="X80" s="310"/>
       <c r="Y80" s="70" t="s">
         <v>211</v>
       </c>
@@ -62056,15 +62091,15 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K81" s="292"/>
-      <c r="L81" s="293"/>
-      <c r="M81" s="294"/>
+      <c r="K81" s="317"/>
+      <c r="L81" s="318"/>
+      <c r="M81" s="319"/>
       <c r="O81" s="133"/>
       <c r="P81" s="133"/>
-      <c r="W81" s="285" t="s">
+      <c r="W81" s="310" t="s">
         <v>209</v>
       </c>
-      <c r="X81" s="285"/>
+      <c r="X81" s="310"/>
       <c r="Y81" s="70">
         <f>COUNTIF(L3:AG40,3)</f>
         <v>481</v>
@@ -62120,17 +62155,17 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K82" s="295" t="s">
+      <c r="K82" s="320" t="s">
         <v>436</v>
       </c>
-      <c r="L82" s="296"/>
-      <c r="M82" s="297"/>
+      <c r="L82" s="321"/>
+      <c r="M82" s="322"/>
       <c r="O82" s="133"/>
       <c r="P82" s="133"/>
-      <c r="W82" s="285" t="s">
+      <c r="W82" s="310" t="s">
         <v>210</v>
       </c>
-      <c r="X82" s="285"/>
+      <c r="X82" s="310"/>
       <c r="Y82" s="70">
         <f>COUNTIF(K3:K40,3)+COUNTIF(J3:J15,3)</f>
         <v>25</v>
@@ -62186,17 +62221,17 @@
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="K83" s="298" t="s">
+      <c r="K83" s="323" t="s">
         <v>437</v>
       </c>
-      <c r="L83" s="299"/>
-      <c r="M83" s="300"/>
+      <c r="L83" s="324"/>
+      <c r="M83" s="325"/>
       <c r="O83" s="133"/>
       <c r="P83" s="133"/>
-      <c r="W83" s="286" t="s">
+      <c r="W83" s="311" t="s">
         <v>97</v>
       </c>
-      <c r="X83" s="286"/>
+      <c r="X83" s="311"/>
       <c r="Y83" s="196">
         <v>220</v>
       </c>
@@ -62249,15 +62284,15 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="K84" s="317" t="s">
+      <c r="K84" s="298" t="s">
         <v>284</v>
       </c>
-      <c r="L84" s="318"/>
-      <c r="M84" s="319"/>
+      <c r="L84" s="299"/>
+      <c r="M84" s="300"/>
       <c r="O84" s="141"/>
       <c r="P84" s="141"/>
-      <c r="W84" s="301"/>
-      <c r="X84" s="301"/>
+      <c r="W84" s="282"/>
+      <c r="X84" s="282"/>
       <c r="Y84" s="198"/>
       <c r="Z84" s="198"/>
       <c r="AA84" s="198"/>
@@ -62295,9 +62330,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K85" s="320"/>
-      <c r="L85" s="321"/>
-      <c r="M85" s="322"/>
+      <c r="K85" s="301"/>
+      <c r="L85" s="302"/>
+      <c r="M85" s="303"/>
       <c r="O85" s="141"/>
       <c r="P85" s="141"/>
     </row>
@@ -62331,9 +62366,9 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="K86" s="320"/>
-      <c r="L86" s="321"/>
-      <c r="M86" s="322"/>
+      <c r="K86" s="301"/>
+      <c r="L86" s="302"/>
+      <c r="M86" s="303"/>
       <c r="O86" s="141"/>
       <c r="P86" s="141"/>
     </row>
@@ -62367,9 +62402,9 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="K87" s="320"/>
-      <c r="L87" s="321"/>
-      <c r="M87" s="322"/>
+      <c r="K87" s="301"/>
+      <c r="L87" s="302"/>
+      <c r="M87" s="303"/>
       <c r="O87" s="141"/>
       <c r="P87" s="141"/>
     </row>
@@ -62403,9 +62438,9 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K88" s="320"/>
-      <c r="L88" s="321"/>
-      <c r="M88" s="322"/>
+      <c r="K88" s="301"/>
+      <c r="L88" s="302"/>
+      <c r="M88" s="303"/>
       <c r="O88" s="141"/>
       <c r="P88" s="141"/>
     </row>
@@ -62439,9 +62474,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K89" s="320"/>
-      <c r="L89" s="321"/>
-      <c r="M89" s="322"/>
+      <c r="K89" s="301"/>
+      <c r="L89" s="302"/>
+      <c r="M89" s="303"/>
       <c r="O89" s="141"/>
       <c r="P89" s="141"/>
     </row>
@@ -62475,9 +62510,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K90" s="320"/>
-      <c r="L90" s="321"/>
-      <c r="M90" s="322"/>
+      <c r="K90" s="301"/>
+      <c r="L90" s="302"/>
+      <c r="M90" s="303"/>
       <c r="O90" s="141"/>
       <c r="P90" s="141"/>
     </row>
@@ -62511,9 +62546,9 @@
         <f t="shared" si="2"/>
         <v>47</v>
       </c>
-      <c r="K91" s="320"/>
-      <c r="L91" s="321"/>
-      <c r="M91" s="322"/>
+      <c r="K91" s="301"/>
+      <c r="L91" s="302"/>
+      <c r="M91" s="303"/>
       <c r="O91" s="141"/>
       <c r="P91" s="141"/>
     </row>
@@ -62547,9 +62582,9 @@
         <f t="shared" si="2"/>
         <v>51</v>
       </c>
-      <c r="K92" s="320"/>
-      <c r="L92" s="321"/>
-      <c r="M92" s="322"/>
+      <c r="K92" s="301"/>
+      <c r="L92" s="302"/>
+      <c r="M92" s="303"/>
       <c r="O92" s="141"/>
       <c r="P92" s="141"/>
     </row>
@@ -62583,9 +62618,9 @@
         <f t="shared" si="2"/>
         <v>37</v>
       </c>
-      <c r="K93" s="320"/>
-      <c r="L93" s="321"/>
-      <c r="M93" s="322"/>
+      <c r="K93" s="301"/>
+      <c r="L93" s="302"/>
+      <c r="M93" s="303"/>
       <c r="O93" s="141"/>
       <c r="P93" s="141"/>
     </row>
@@ -62619,9 +62654,9 @@
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="K94" s="320"/>
-      <c r="L94" s="321"/>
-      <c r="M94" s="322"/>
+      <c r="K94" s="301"/>
+      <c r="L94" s="302"/>
+      <c r="M94" s="303"/>
       <c r="O94" s="141"/>
       <c r="P94" s="141"/>
     </row>
@@ -62655,9 +62690,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K95" s="320"/>
-      <c r="L95" s="321"/>
-      <c r="M95" s="322"/>
+      <c r="K95" s="301"/>
+      <c r="L95" s="302"/>
+      <c r="M95" s="303"/>
       <c r="O95" s="141"/>
       <c r="P95" s="141"/>
     </row>
@@ -62691,9 +62726,9 @@
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="K96" s="320"/>
-      <c r="L96" s="321"/>
-      <c r="M96" s="322"/>
+      <c r="K96" s="301"/>
+      <c r="L96" s="302"/>
+      <c r="M96" s="303"/>
       <c r="O96" s="141"/>
       <c r="P96" s="141"/>
     </row>
@@ -62727,9 +62762,9 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="K97" s="320"/>
-      <c r="L97" s="321"/>
-      <c r="M97" s="322"/>
+      <c r="K97" s="301"/>
+      <c r="L97" s="302"/>
+      <c r="M97" s="303"/>
       <c r="O97" s="141"/>
       <c r="P97" s="141"/>
     </row>
@@ -62763,9 +62798,9 @@
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="K98" s="320"/>
-      <c r="L98" s="321"/>
-      <c r="M98" s="322"/>
+      <c r="K98" s="301"/>
+      <c r="L98" s="302"/>
+      <c r="M98" s="303"/>
       <c r="O98" s="141"/>
       <c r="P98" s="141"/>
     </row>
@@ -62799,9 +62834,9 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K99" s="320"/>
-      <c r="L99" s="321"/>
-      <c r="M99" s="322"/>
+      <c r="K99" s="301"/>
+      <c r="L99" s="302"/>
+      <c r="M99" s="303"/>
       <c r="O99" s="141"/>
       <c r="P99" s="141"/>
     </row>
@@ -62835,9 +62870,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K100" s="320"/>
-      <c r="L100" s="321"/>
-      <c r="M100" s="322"/>
+      <c r="K100" s="301"/>
+      <c r="L100" s="302"/>
+      <c r="M100" s="303"/>
       <c r="O100" s="141"/>
       <c r="P100" s="141"/>
     </row>
@@ -62871,9 +62906,9 @@
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="K101" s="320"/>
-      <c r="L101" s="321"/>
-      <c r="M101" s="322"/>
+      <c r="K101" s="301"/>
+      <c r="L101" s="302"/>
+      <c r="M101" s="303"/>
       <c r="O101" s="141"/>
       <c r="P101" s="141"/>
     </row>
@@ -62907,9 +62942,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K102" s="320"/>
-      <c r="L102" s="321"/>
-      <c r="M102" s="322"/>
+      <c r="K102" s="301"/>
+      <c r="L102" s="302"/>
+      <c r="M102" s="303"/>
       <c r="O102" s="141"/>
       <c r="P102" s="141"/>
     </row>
@@ -62943,9 +62978,9 @@
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="K103" s="320"/>
-      <c r="L103" s="321"/>
-      <c r="M103" s="322"/>
+      <c r="K103" s="301"/>
+      <c r="L103" s="302"/>
+      <c r="M103" s="303"/>
       <c r="O103" s="141"/>
       <c r="P103" s="141"/>
     </row>
@@ -62979,9 +63014,9 @@
         <f t="shared" si="2"/>
         <v>33</v>
       </c>
-      <c r="K104" s="320"/>
-      <c r="L104" s="321"/>
-      <c r="M104" s="322"/>
+      <c r="K104" s="301"/>
+      <c r="L104" s="302"/>
+      <c r="M104" s="303"/>
       <c r="O104" s="141"/>
       <c r="P104" s="141"/>
     </row>
@@ -63015,9 +63050,9 @@
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="K105" s="323"/>
-      <c r="L105" s="324"/>
-      <c r="M105" s="325"/>
+      <c r="K105" s="304"/>
+      <c r="L105" s="305"/>
+      <c r="M105" s="306"/>
       <c r="O105" s="141"/>
       <c r="P105" s="141"/>
     </row>
@@ -63051,11 +63086,11 @@
         <f t="shared" si="2"/>
         <v>21</v>
       </c>
-      <c r="K106" s="314" t="s">
+      <c r="K106" s="295" t="s">
         <v>286</v>
       </c>
-      <c r="L106" s="315"/>
-      <c r="M106" s="316"/>
+      <c r="L106" s="296"/>
+      <c r="M106" s="297"/>
       <c r="O106" s="126"/>
       <c r="P106" s="126"/>
     </row>
@@ -63089,11 +63124,11 @@
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="K107" s="314" t="s">
+      <c r="K107" s="295" t="s">
         <v>288</v>
       </c>
-      <c r="L107" s="315"/>
-      <c r="M107" s="316"/>
+      <c r="L107" s="296"/>
+      <c r="M107" s="297"/>
       <c r="O107" s="126"/>
       <c r="P107" s="126"/>
     </row>
@@ -63127,11 +63162,11 @@
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="K108" s="305" t="s">
+      <c r="K108" s="286" t="s">
         <v>289</v>
       </c>
-      <c r="L108" s="306"/>
-      <c r="M108" s="307"/>
+      <c r="L108" s="287"/>
+      <c r="M108" s="288"/>
       <c r="O108" s="126"/>
       <c r="P108" s="126"/>
     </row>
@@ -63165,9 +63200,9 @@
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="K109" s="308"/>
-      <c r="L109" s="309"/>
-      <c r="M109" s="310"/>
+      <c r="K109" s="289"/>
+      <c r="L109" s="290"/>
+      <c r="M109" s="291"/>
       <c r="O109" s="126"/>
       <c r="P109" s="126"/>
     </row>
@@ -63201,9 +63236,9 @@
         <f t="shared" si="2"/>
         <v>45</v>
       </c>
-      <c r="K110" s="308"/>
-      <c r="L110" s="309"/>
-      <c r="M110" s="310"/>
+      <c r="K110" s="289"/>
+      <c r="L110" s="290"/>
+      <c r="M110" s="291"/>
       <c r="O110" s="126"/>
       <c r="P110" s="126"/>
     </row>
@@ -63237,9 +63272,9 @@
         <f t="shared" si="2"/>
         <v>62</v>
       </c>
-      <c r="K111" s="308"/>
-      <c r="L111" s="309"/>
-      <c r="M111" s="310"/>
+      <c r="K111" s="289"/>
+      <c r="L111" s="290"/>
+      <c r="M111" s="291"/>
       <c r="O111" s="126"/>
       <c r="P111" s="126"/>
     </row>
@@ -63277,9 +63312,9 @@
         <f t="shared" ref="J112:J114" si="6">H112-I112</f>
         <v>34</v>
       </c>
-      <c r="K112" s="308"/>
-      <c r="L112" s="309"/>
-      <c r="M112" s="310"/>
+      <c r="K112" s="289"/>
+      <c r="L112" s="290"/>
+      <c r="M112" s="291"/>
     </row>
     <row r="113" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="156" t="s">
@@ -63315,9 +63350,9 @@
         <f t="shared" si="6"/>
         <v>43</v>
       </c>
-      <c r="K113" s="311"/>
-      <c r="L113" s="312"/>
-      <c r="M113" s="313"/>
+      <c r="K113" s="292"/>
+      <c r="L113" s="293"/>
+      <c r="M113" s="294"/>
     </row>
     <row r="114" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" s="93" t="s">
@@ -63357,12 +63392,6 @@
   </sheetData>
   <autoFilter ref="A79:J112" xr:uid="{9C81160F-C24B-449F-8F5A-CB622AB71070}"/>
   <mergeCells count="15">
-    <mergeCell ref="W84:X84"/>
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="K108:M113"/>
-    <mergeCell ref="K106:M106"/>
-    <mergeCell ref="K107:M107"/>
-    <mergeCell ref="K84:M105"/>
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="W80:X80"/>
     <mergeCell ref="W81:X81"/>
@@ -63372,6 +63401,12 @@
     <mergeCell ref="K80:M81"/>
     <mergeCell ref="K82:M82"/>
     <mergeCell ref="K83:M83"/>
+    <mergeCell ref="W84:X84"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="K108:M113"/>
+    <mergeCell ref="K106:M106"/>
+    <mergeCell ref="K107:M107"/>
+    <mergeCell ref="K84:M105"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <conditionalFormatting sqref="A3:A40">
@@ -64262,7 +64297,9 @@
       <c r="B2" t="s">
         <v>451</v>
       </c>
-      <c r="C2" s="201"/>
+      <c r="C2" s="201">
+        <v>7.9</v>
+      </c>
       <c r="D2">
         <v>90</v>
       </c>
@@ -64274,7 +64311,9 @@
       <c r="B3" t="s">
         <v>473</v>
       </c>
-      <c r="C3" s="201"/>
+      <c r="C3" s="201">
+        <v>6.4</v>
+      </c>
       <c r="D3">
         <v>90</v>
       </c>
@@ -64286,7 +64325,9 @@
       <c r="B4" t="s">
         <v>452</v>
       </c>
-      <c r="C4" s="201"/>
+      <c r="C4" s="201">
+        <v>8.1</v>
+      </c>
       <c r="D4">
         <v>90</v>
       </c>
@@ -64298,7 +64339,9 @@
       <c r="B5" t="s">
         <v>462</v>
       </c>
-      <c r="C5" s="201"/>
+      <c r="C5" s="201">
+        <v>6.8</v>
+      </c>
       <c r="D5">
         <v>90</v>
       </c>
@@ -64310,7 +64353,9 @@
       <c r="B6" t="s">
         <v>453</v>
       </c>
-      <c r="C6" s="201"/>
+      <c r="C6" s="201">
+        <v>6.5</v>
+      </c>
       <c r="D6" t="s">
         <v>460</v>
       </c>
@@ -64322,7 +64367,9 @@
       <c r="B7" t="s">
         <v>474</v>
       </c>
-      <c r="C7" s="201"/>
+      <c r="C7" s="201">
+        <v>6.1</v>
+      </c>
       <c r="D7" t="s">
         <v>460</v>
       </c>
@@ -64334,7 +64381,9 @@
       <c r="B8" t="s">
         <v>454</v>
       </c>
-      <c r="C8" s="201"/>
+      <c r="C8" s="201">
+        <v>8.8000000000000007</v>
+      </c>
       <c r="D8" t="s">
         <v>460</v>
       </c>
@@ -64349,7 +64398,9 @@
       <c r="B9" t="s">
         <v>455</v>
       </c>
-      <c r="C9" s="201"/>
+      <c r="C9" s="201">
+        <v>7.9</v>
+      </c>
       <c r="D9" t="s">
         <v>460</v>
       </c>
@@ -64361,7 +64412,9 @@
       <c r="B10" t="s">
         <v>456</v>
       </c>
-      <c r="C10" s="201"/>
+      <c r="C10" s="201">
+        <v>6.6</v>
+      </c>
       <c r="D10" t="s">
         <v>460</v>
       </c>
@@ -64373,7 +64426,9 @@
       <c r="B11" t="s">
         <v>457</v>
       </c>
-      <c r="C11" s="201"/>
+      <c r="C11" s="201">
+        <v>7.8</v>
+      </c>
       <c r="D11">
         <v>90</v>
       </c>
@@ -64388,7 +64443,9 @@
       <c r="B12" t="s">
         <v>458</v>
       </c>
-      <c r="C12" s="201"/>
+      <c r="C12" s="201">
+        <v>6.7</v>
+      </c>
       <c r="D12">
         <v>90</v>
       </c>
@@ -64400,7 +64457,9 @@
       <c r="B13" t="s">
         <v>475</v>
       </c>
-      <c r="C13" s="201"/>
+      <c r="C13" s="201">
+        <v>6.9</v>
+      </c>
       <c r="D13" t="s">
         <v>459</v>
       </c>
@@ -64436,7 +64495,9 @@
       <c r="B16" t="s">
         <v>472</v>
       </c>
-      <c r="C16" s="201"/>
+      <c r="C16" s="201">
+        <v>7.9</v>
+      </c>
       <c r="D16" t="s">
         <v>459</v>
       </c>

--- a/data/arsenal_stats.xlsx
+++ b/data/arsenal_stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bungeltd-my.sharepoint.com/personal/przemyslaw_iskra_bunge_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8387" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4E88830-3FD1-4E8E-9A42-072633E2BCEE}"/>
+  <xr:revisionPtr revIDLastSave="8388" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2E09124-C46D-4E05-A65A-81AB73ECD1AD}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="799" firstSheet="1" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="799" firstSheet="1" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="19" state="hidden" r:id="rId1"/>
@@ -1510,9 +1510,6 @@
     <t>Timber</t>
   </si>
   <si>
-    <t>2-0 (W)</t>
-  </si>
-  <si>
     <t>Ipswitch</t>
   </si>
   <si>
@@ -1550,6 +1547,9 @@
   </si>
   <si>
     <t>Sabah</t>
+  </si>
+  <si>
+    <t>2-0</t>
   </si>
 </sst>
 </file>
@@ -3074,6 +3074,18 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3098,16 +3110,13 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3119,32 +3128,14 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="54" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3182,6 +3173,15 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="28" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3189,6 +3189,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="61" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="10" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="37" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="11" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3281,31 +3302,67 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="61" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="10" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="37" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="11" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="54" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3382,63 +3439,6 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6493,7 +6493,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2F035618-6D36-417B-9A71-82371B2CC50E}" type="CELLRANGE">
+                    <a:fld id="{BB3DF284-8977-4D0E-A388-4CA2D4E5D595}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6527,7 +6527,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2AD5E3CA-4761-445A-81D8-5DA62B5ADA97}" type="CELLRANGE">
+                    <a:fld id="{D9BEABE1-FBB5-406B-88A6-B8957D4A7E74}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6561,7 +6561,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{1FDE118A-B800-46D0-9718-7D79088A7E09}" type="CELLRANGE">
+                    <a:fld id="{D0B6C236-4C80-4E41-A6DF-21C992B43354}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6595,7 +6595,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{AC57C183-D711-42D6-8B65-E3F2527BED6E}" type="CELLRANGE">
+                    <a:fld id="{3EF0DD40-EFE4-4D7F-9C17-65795F40D894}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6629,7 +6629,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6DC55111-0B66-4DAD-8FCA-28E00EC7FCBD}" type="CELLRANGE">
+                    <a:fld id="{7FCE7825-46A3-43C2-958A-918993DD392E}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6663,7 +6663,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{EC4932CD-FEF3-4665-8722-4BE60EBB97DD}" type="CELLRANGE">
+                    <a:fld id="{F508AC7A-C0FA-4BD9-BBBF-1685F2D06A88}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6697,7 +6697,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A2294881-C3D1-4A1F-A951-CADE7809F313}" type="CELLRANGE">
+                    <a:fld id="{36068BF5-2D80-44DE-8E9B-A2DD94960B81}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6731,7 +6731,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C2C05114-3695-4C4E-94E0-061D9301D16E}" type="CELLRANGE">
+                    <a:fld id="{6996FFC1-AC10-4187-8BBB-5F27E452C914}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6765,7 +6765,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{68C3B752-2EC7-4B96-900E-C7103524BE47}" type="CELLRANGE">
+                    <a:fld id="{EE431FA8-F1C3-40D9-AEFD-FCB21E04C1C9}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6799,7 +6799,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{3C09915B-9EF9-4A2D-ADA1-1480CD934E6B}" type="CELLRANGE">
+                    <a:fld id="{E335A5E4-4730-4095-9040-D3E22236C5BC}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6833,7 +6833,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{73660311-12BE-4C39-BDED-B5848FBB4261}" type="CELLRANGE">
+                    <a:fld id="{DCE1C669-4834-4E7D-9E1B-BED3447BCAD6}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6867,7 +6867,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6501924C-828A-4B61-A822-8B2FD1F67CDC}" type="CELLRANGE">
+                    <a:fld id="{35FB4F2A-04C2-465B-9416-6CB6DD1253D0}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6916,7 +6916,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{22C12A00-B16D-419E-936D-48212C03DED9}" type="CELLRANGE">
+                    <a:fld id="{EE764AB6-4305-4828-94A8-9B95879D5F1D}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr>
                         <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
@@ -6975,7 +6975,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{47DF5A90-EA4C-497A-9E82-C5224D1525B8}" type="CELLRANGE">
+                    <a:fld id="{A040585C-2CC7-4BD0-86A4-28D6901B8367}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7009,7 +7009,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A31C18A6-780E-473B-8673-80845D1CCE49}" type="CELLRANGE">
+                    <a:fld id="{32697F90-0B0B-4B0F-9657-EF72A254F8D1}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7043,7 +7043,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E32598A8-BFE3-4E17-9276-23EDD7D6512F}" type="CELLRANGE">
+                    <a:fld id="{106266EB-0BF2-4EB4-B030-9B6FEFBD745F}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7077,7 +7077,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{37EF83EA-DEB5-49A9-9931-FBA9766717BB}" type="CELLRANGE">
+                    <a:fld id="{9AA35086-7D36-4DEA-A1C5-9D7BA6A67A60}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -14213,30 +14213,30 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
       <c r="B1" s="5"/>
-      <c r="C1" s="214" t="s">
+      <c r="C1" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="214"/>
-      <c r="E1" s="215" t="s">
+      <c r="D1" s="206"/>
+      <c r="E1" s="207" t="s">
         <v>120</v>
       </c>
-      <c r="F1" s="215"/>
-      <c r="G1" s="214" t="s">
+      <c r="F1" s="207"/>
+      <c r="G1" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="H1" s="214"/>
-      <c r="I1" s="215" t="s">
+      <c r="H1" s="206"/>
+      <c r="I1" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="J1" s="215"/>
-      <c r="K1" s="214" t="s">
+      <c r="J1" s="207"/>
+      <c r="K1" s="206" t="s">
         <v>39</v>
       </c>
-      <c r="L1" s="214"/>
-      <c r="M1" s="212" t="s">
+      <c r="L1" s="206"/>
+      <c r="M1" s="204" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="213"/>
+      <c r="N1" s="205"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -15943,30 +15943,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="214" t="s">
+      <c r="C2" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="214"/>
-      <c r="E2" s="215" t="s">
+      <c r="D2" s="206"/>
+      <c r="E2" s="207" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="215"/>
-      <c r="G2" s="214" t="s">
+      <c r="F2" s="207"/>
+      <c r="G2" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="214"/>
-      <c r="I2" s="215" t="s">
+      <c r="H2" s="206"/>
+      <c r="I2" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="215"/>
-      <c r="K2" s="214" t="s">
+      <c r="J2" s="207"/>
+      <c r="K2" s="206" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="214"/>
-      <c r="M2" s="207" t="s">
+      <c r="L2" s="206"/>
+      <c r="M2" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="207"/>
+      <c r="N2" s="211"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -17770,30 +17770,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="214" t="s">
+      <c r="C2" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="214"/>
-      <c r="E2" s="215" t="s">
+      <c r="D2" s="206"/>
+      <c r="E2" s="207" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="215"/>
-      <c r="G2" s="214" t="s">
+      <c r="F2" s="207"/>
+      <c r="G2" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="214"/>
-      <c r="I2" s="215" t="s">
+      <c r="H2" s="206"/>
+      <c r="I2" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="215"/>
-      <c r="K2" s="214" t="s">
+      <c r="J2" s="207"/>
+      <c r="K2" s="206" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="214"/>
-      <c r="M2" s="207" t="s">
+      <c r="L2" s="206"/>
+      <c r="M2" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="207"/>
+      <c r="N2" s="211"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -19460,30 +19460,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="214" t="s">
+      <c r="C2" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="214"/>
-      <c r="E2" s="215" t="s">
+      <c r="D2" s="206"/>
+      <c r="E2" s="207" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="215"/>
-      <c r="G2" s="214" t="s">
+      <c r="F2" s="207"/>
+      <c r="G2" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="214"/>
-      <c r="I2" s="215" t="s">
+      <c r="H2" s="206"/>
+      <c r="I2" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="215"/>
-      <c r="K2" s="214" t="s">
+      <c r="J2" s="207"/>
+      <c r="K2" s="206" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="214"/>
-      <c r="M2" s="207" t="s">
+      <c r="L2" s="206"/>
+      <c r="M2" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="207"/>
+      <c r="N2" s="211"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -21286,30 +21286,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="214" t="s">
+      <c r="C2" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="214"/>
-      <c r="E2" s="215" t="s">
+      <c r="D2" s="206"/>
+      <c r="E2" s="207" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="215"/>
-      <c r="G2" s="214" t="s">
+      <c r="F2" s="207"/>
+      <c r="G2" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="214"/>
-      <c r="I2" s="215" t="s">
+      <c r="H2" s="206"/>
+      <c r="I2" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="215"/>
-      <c r="K2" s="214" t="s">
+      <c r="J2" s="207"/>
+      <c r="K2" s="206" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="214"/>
-      <c r="M2" s="207" t="s">
+      <c r="L2" s="206"/>
+      <c r="M2" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="207"/>
+      <c r="N2" s="211"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -23158,36 +23158,36 @@
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="204" t="s">
+      <c r="C2" s="208" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="205"/>
-      <c r="E2" s="206"/>
-      <c r="F2" s="209" t="s">
+      <c r="D2" s="209"/>
+      <c r="E2" s="210"/>
+      <c r="F2" s="213" t="s">
         <v>120</v>
       </c>
-      <c r="G2" s="210"/>
-      <c r="H2" s="211"/>
-      <c r="I2" s="204" t="s">
+      <c r="G2" s="214"/>
+      <c r="H2" s="215"/>
+      <c r="I2" s="208" t="s">
         <v>108</v>
       </c>
-      <c r="J2" s="205"/>
-      <c r="K2" s="206"/>
-      <c r="L2" s="209" t="s">
+      <c r="J2" s="209"/>
+      <c r="K2" s="210"/>
+      <c r="L2" s="213" t="s">
         <v>110</v>
       </c>
-      <c r="M2" s="210"/>
-      <c r="N2" s="211"/>
-      <c r="O2" s="204" t="s">
+      <c r="M2" s="214"/>
+      <c r="N2" s="215"/>
+      <c r="O2" s="208" t="s">
         <v>39</v>
       </c>
-      <c r="P2" s="205"/>
-      <c r="Q2" s="206"/>
-      <c r="R2" s="207" t="s">
+      <c r="P2" s="209"/>
+      <c r="Q2" s="210"/>
+      <c r="R2" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="S2" s="207"/>
-      <c r="T2" s="207"/>
+      <c r="S2" s="211"/>
+      <c r="T2" s="211"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -26046,36 +26046,36 @@
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
       <c r="D1" s="5"/>
-      <c r="E1" s="204" t="s">
+      <c r="E1" s="208" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="205"/>
-      <c r="G1" s="206"/>
-      <c r="H1" s="209" t="s">
+      <c r="F1" s="209"/>
+      <c r="G1" s="210"/>
+      <c r="H1" s="213" t="s">
         <v>120</v>
       </c>
-      <c r="I1" s="210"/>
-      <c r="J1" s="211"/>
-      <c r="K1" s="204" t="s">
+      <c r="I1" s="214"/>
+      <c r="J1" s="215"/>
+      <c r="K1" s="208" t="s">
         <v>108</v>
       </c>
-      <c r="L1" s="205"/>
-      <c r="M1" s="206"/>
-      <c r="N1" s="209" t="s">
+      <c r="L1" s="209"/>
+      <c r="M1" s="210"/>
+      <c r="N1" s="213" t="s">
         <v>110</v>
       </c>
-      <c r="O1" s="210"/>
-      <c r="P1" s="211"/>
-      <c r="Q1" s="204" t="s">
+      <c r="O1" s="214"/>
+      <c r="P1" s="215"/>
+      <c r="Q1" s="208" t="s">
         <v>39</v>
       </c>
-      <c r="R1" s="205"/>
-      <c r="S1" s="206"/>
-      <c r="T1" s="207" t="s">
+      <c r="R1" s="209"/>
+      <c r="S1" s="210"/>
+      <c r="T1" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="U1" s="207"/>
-      <c r="V1" s="207"/>
+      <c r="U1" s="211"/>
+      <c r="V1" s="211"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -37649,196 +37649,196 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F1" s="219">
-        <v>1</v>
-      </c>
-      <c r="G1" s="220"/>
-      <c r="H1" s="221"/>
-      <c r="I1" s="219">
+      <c r="F1" s="216">
+        <v>1</v>
+      </c>
+      <c r="G1" s="217"/>
+      <c r="H1" s="218"/>
+      <c r="I1" s="216">
         <v>2</v>
       </c>
-      <c r="J1" s="220"/>
-      <c r="K1" s="221"/>
-      <c r="L1" s="219">
-        <v>3</v>
-      </c>
-      <c r="M1" s="220"/>
-      <c r="N1" s="221"/>
-      <c r="O1" s="219">
+      <c r="J1" s="217"/>
+      <c r="K1" s="218"/>
+      <c r="L1" s="216">
+        <v>3</v>
+      </c>
+      <c r="M1" s="217"/>
+      <c r="N1" s="218"/>
+      <c r="O1" s="216">
         <v>4</v>
       </c>
-      <c r="P1" s="220"/>
-      <c r="Q1" s="221"/>
-      <c r="R1" s="219">
+      <c r="P1" s="217"/>
+      <c r="Q1" s="218"/>
+      <c r="R1" s="216">
         <v>5</v>
       </c>
-      <c r="S1" s="220"/>
-      <c r="T1" s="221"/>
-      <c r="U1" s="219">
+      <c r="S1" s="217"/>
+      <c r="T1" s="218"/>
+      <c r="U1" s="216">
         <v>6</v>
       </c>
-      <c r="V1" s="220"/>
-      <c r="W1" s="221"/>
-      <c r="X1" s="219">
+      <c r="V1" s="217"/>
+      <c r="W1" s="218"/>
+      <c r="X1" s="216">
         <v>7</v>
       </c>
-      <c r="Y1" s="220"/>
-      <c r="Z1" s="221"/>
-      <c r="AA1" s="219">
+      <c r="Y1" s="217"/>
+      <c r="Z1" s="218"/>
+      <c r="AA1" s="216">
         <v>8</v>
       </c>
-      <c r="AB1" s="220"/>
-      <c r="AC1" s="221"/>
-      <c r="AD1" s="219">
+      <c r="AB1" s="217"/>
+      <c r="AC1" s="218"/>
+      <c r="AD1" s="216">
         <v>9</v>
       </c>
-      <c r="AE1" s="220"/>
-      <c r="AF1" s="221"/>
-      <c r="AG1" s="219">
+      <c r="AE1" s="217"/>
+      <c r="AF1" s="218"/>
+      <c r="AG1" s="216">
         <v>10</v>
       </c>
-      <c r="AH1" s="220"/>
-      <c r="AI1" s="221"/>
-      <c r="AJ1" s="219">
+      <c r="AH1" s="217"/>
+      <c r="AI1" s="218"/>
+      <c r="AJ1" s="216">
         <v>11</v>
       </c>
-      <c r="AK1" s="220"/>
-      <c r="AL1" s="221"/>
-      <c r="AM1" s="219">
+      <c r="AK1" s="217"/>
+      <c r="AL1" s="218"/>
+      <c r="AM1" s="216">
         <v>12</v>
       </c>
-      <c r="AN1" s="220"/>
-      <c r="AO1" s="221"/>
-      <c r="AP1" s="219">
+      <c r="AN1" s="217"/>
+      <c r="AO1" s="218"/>
+      <c r="AP1" s="216">
         <v>13</v>
       </c>
-      <c r="AQ1" s="220"/>
-      <c r="AR1" s="221"/>
-      <c r="AS1" s="219">
+      <c r="AQ1" s="217"/>
+      <c r="AR1" s="218"/>
+      <c r="AS1" s="216">
         <v>14</v>
       </c>
-      <c r="AT1" s="220"/>
-      <c r="AU1" s="221"/>
-      <c r="AV1" s="219">
+      <c r="AT1" s="217"/>
+      <c r="AU1" s="218"/>
+      <c r="AV1" s="216">
         <v>15</v>
       </c>
-      <c r="AW1" s="220"/>
-      <c r="AX1" s="221"/>
-      <c r="AY1" s="219">
+      <c r="AW1" s="217"/>
+      <c r="AX1" s="218"/>
+      <c r="AY1" s="216">
         <v>16</v>
       </c>
-      <c r="AZ1" s="220"/>
-      <c r="BA1" s="221"/>
-      <c r="BB1" s="219">
+      <c r="AZ1" s="217"/>
+      <c r="BA1" s="218"/>
+      <c r="BB1" s="216">
         <v>17</v>
       </c>
-      <c r="BC1" s="220"/>
-      <c r="BD1" s="221"/>
-      <c r="BE1" s="219">
+      <c r="BC1" s="217"/>
+      <c r="BD1" s="218"/>
+      <c r="BE1" s="216">
         <v>18</v>
       </c>
-      <c r="BF1" s="220"/>
-      <c r="BG1" s="221"/>
-      <c r="BH1" s="219">
+      <c r="BF1" s="217"/>
+      <c r="BG1" s="218"/>
+      <c r="BH1" s="216">
         <v>19</v>
       </c>
-      <c r="BI1" s="220"/>
-      <c r="BJ1" s="221"/>
-      <c r="BK1" s="219">
+      <c r="BI1" s="217"/>
+      <c r="BJ1" s="218"/>
+      <c r="BK1" s="216">
         <v>20</v>
       </c>
-      <c r="BL1" s="220"/>
-      <c r="BM1" s="221"/>
-      <c r="BN1" s="219">
+      <c r="BL1" s="217"/>
+      <c r="BM1" s="218"/>
+      <c r="BN1" s="216">
         <v>21</v>
       </c>
-      <c r="BO1" s="220"/>
-      <c r="BP1" s="221"/>
-      <c r="BQ1" s="219">
+      <c r="BO1" s="217"/>
+      <c r="BP1" s="218"/>
+      <c r="BQ1" s="216">
         <v>22</v>
       </c>
-      <c r="BR1" s="220"/>
-      <c r="BS1" s="221"/>
-      <c r="BT1" s="219">
+      <c r="BR1" s="217"/>
+      <c r="BS1" s="218"/>
+      <c r="BT1" s="216">
         <v>23</v>
       </c>
-      <c r="BU1" s="220"/>
-      <c r="BV1" s="221"/>
-      <c r="BW1" s="219">
+      <c r="BU1" s="217"/>
+      <c r="BV1" s="218"/>
+      <c r="BW1" s="216">
         <v>24</v>
       </c>
-      <c r="BX1" s="220"/>
-      <c r="BY1" s="221"/>
-      <c r="BZ1" s="219">
+      <c r="BX1" s="217"/>
+      <c r="BY1" s="218"/>
+      <c r="BZ1" s="216">
         <v>25</v>
       </c>
-      <c r="CA1" s="220"/>
-      <c r="CB1" s="221"/>
-      <c r="CC1" s="219">
+      <c r="CA1" s="217"/>
+      <c r="CB1" s="218"/>
+      <c r="CC1" s="216">
         <v>26</v>
       </c>
-      <c r="CD1" s="220"/>
-      <c r="CE1" s="221"/>
-      <c r="CF1" s="219">
+      <c r="CD1" s="217"/>
+      <c r="CE1" s="218"/>
+      <c r="CF1" s="216">
         <v>27</v>
       </c>
-      <c r="CG1" s="220"/>
-      <c r="CH1" s="221"/>
-      <c r="CI1" s="219">
+      <c r="CG1" s="217"/>
+      <c r="CH1" s="218"/>
+      <c r="CI1" s="216">
         <v>28</v>
       </c>
-      <c r="CJ1" s="220"/>
-      <c r="CK1" s="221"/>
-      <c r="CL1" s="219">
+      <c r="CJ1" s="217"/>
+      <c r="CK1" s="218"/>
+      <c r="CL1" s="216">
         <v>29</v>
       </c>
-      <c r="CM1" s="220"/>
-      <c r="CN1" s="221"/>
-      <c r="CO1" s="219">
+      <c r="CM1" s="217"/>
+      <c r="CN1" s="218"/>
+      <c r="CO1" s="216">
         <v>30</v>
       </c>
-      <c r="CP1" s="220"/>
-      <c r="CQ1" s="221"/>
-      <c r="CR1" s="219">
+      <c r="CP1" s="217"/>
+      <c r="CQ1" s="218"/>
+      <c r="CR1" s="216">
         <v>31</v>
       </c>
-      <c r="CS1" s="220"/>
-      <c r="CT1" s="221"/>
-      <c r="CU1" s="219">
+      <c r="CS1" s="217"/>
+      <c r="CT1" s="218"/>
+      <c r="CU1" s="216">
         <v>32</v>
       </c>
-      <c r="CV1" s="220"/>
-      <c r="CW1" s="221"/>
-      <c r="CX1" s="219">
+      <c r="CV1" s="217"/>
+      <c r="CW1" s="218"/>
+      <c r="CX1" s="216">
         <v>33</v>
       </c>
-      <c r="CY1" s="220"/>
-      <c r="CZ1" s="221"/>
-      <c r="DA1" s="219">
+      <c r="CY1" s="217"/>
+      <c r="CZ1" s="218"/>
+      <c r="DA1" s="216">
         <v>34</v>
       </c>
-      <c r="DB1" s="220"/>
-      <c r="DC1" s="221"/>
-      <c r="DD1" s="219">
+      <c r="DB1" s="217"/>
+      <c r="DC1" s="218"/>
+      <c r="DD1" s="216">
         <v>35</v>
       </c>
-      <c r="DE1" s="220"/>
-      <c r="DF1" s="221"/>
-      <c r="DG1" s="219">
+      <c r="DE1" s="217"/>
+      <c r="DF1" s="218"/>
+      <c r="DG1" s="216">
         <v>36</v>
       </c>
-      <c r="DH1" s="220"/>
-      <c r="DI1" s="221"/>
-      <c r="DJ1" s="219">
+      <c r="DH1" s="217"/>
+      <c r="DI1" s="218"/>
+      <c r="DJ1" s="216">
         <v>37</v>
       </c>
-      <c r="DK1" s="220"/>
-      <c r="DL1" s="221"/>
-      <c r="DM1" s="219">
+      <c r="DK1" s="217"/>
+      <c r="DL1" s="218"/>
+      <c r="DM1" s="216">
         <v>38</v>
       </c>
-      <c r="DN1" s="220"/>
-      <c r="DO1" s="221"/>
+      <c r="DN1" s="217"/>
+      <c r="DO1" s="218"/>
     </row>
     <row r="2" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
@@ -37852,196 +37852,196 @@
       <c r="E2" s="222" t="s">
         <v>398</v>
       </c>
-      <c r="F2" s="216" t="s">
+      <c r="F2" s="219" t="s">
         <v>346</v>
       </c>
-      <c r="G2" s="217"/>
-      <c r="H2" s="218"/>
-      <c r="I2" s="216" t="s">
+      <c r="G2" s="220"/>
+      <c r="H2" s="221"/>
+      <c r="I2" s="219" t="s">
         <v>331</v>
       </c>
-      <c r="J2" s="217"/>
-      <c r="K2" s="218"/>
-      <c r="L2" s="216" t="s">
+      <c r="J2" s="220"/>
+      <c r="K2" s="221"/>
+      <c r="L2" s="219" t="s">
         <v>330</v>
       </c>
-      <c r="M2" s="217"/>
-      <c r="N2" s="218"/>
-      <c r="O2" s="216" t="s">
+      <c r="M2" s="220"/>
+      <c r="N2" s="221"/>
+      <c r="O2" s="219" t="s">
         <v>328</v>
       </c>
-      <c r="P2" s="217"/>
-      <c r="Q2" s="218"/>
-      <c r="R2" s="216" t="s">
+      <c r="P2" s="220"/>
+      <c r="Q2" s="221"/>
+      <c r="R2" s="219" t="s">
         <v>335</v>
       </c>
-      <c r="S2" s="217"/>
-      <c r="T2" s="218"/>
-      <c r="U2" s="216" t="s">
+      <c r="S2" s="220"/>
+      <c r="T2" s="221"/>
+      <c r="U2" s="219" t="s">
         <v>320</v>
       </c>
-      <c r="V2" s="217"/>
-      <c r="W2" s="218"/>
-      <c r="X2" s="216" t="s">
+      <c r="V2" s="220"/>
+      <c r="W2" s="221"/>
+      <c r="X2" s="219" t="s">
         <v>337</v>
       </c>
-      <c r="Y2" s="217"/>
-      <c r="Z2" s="218"/>
-      <c r="AA2" s="216" t="s">
+      <c r="Y2" s="220"/>
+      <c r="Z2" s="221"/>
+      <c r="AA2" s="219" t="s">
         <v>334</v>
       </c>
-      <c r="AB2" s="217"/>
-      <c r="AC2" s="218"/>
-      <c r="AD2" s="216" t="s">
+      <c r="AB2" s="220"/>
+      <c r="AC2" s="221"/>
+      <c r="AD2" s="219" t="s">
         <v>321</v>
       </c>
-      <c r="AE2" s="217"/>
-      <c r="AF2" s="218"/>
-      <c r="AG2" s="216" t="s">
+      <c r="AE2" s="220"/>
+      <c r="AF2" s="221"/>
+      <c r="AG2" s="219" t="s">
         <v>347</v>
       </c>
-      <c r="AH2" s="217"/>
-      <c r="AI2" s="218"/>
-      <c r="AJ2" s="216" t="s">
+      <c r="AH2" s="220"/>
+      <c r="AI2" s="221"/>
+      <c r="AJ2" s="219" t="s">
         <v>324</v>
       </c>
-      <c r="AK2" s="217"/>
-      <c r="AL2" s="218"/>
-      <c r="AM2" s="216" t="s">
+      <c r="AK2" s="220"/>
+      <c r="AL2" s="221"/>
+      <c r="AM2" s="219" t="s">
         <v>323</v>
       </c>
-      <c r="AN2" s="217"/>
-      <c r="AO2" s="218"/>
-      <c r="AP2" s="216" t="s">
+      <c r="AN2" s="220"/>
+      <c r="AO2" s="221"/>
+      <c r="AP2" s="219" t="s">
         <v>332</v>
       </c>
-      <c r="AQ2" s="217"/>
-      <c r="AR2" s="218"/>
-      <c r="AS2" s="216" t="s">
+      <c r="AQ2" s="220"/>
+      <c r="AR2" s="221"/>
+      <c r="AS2" s="219" t="s">
         <v>329</v>
       </c>
-      <c r="AT2" s="217"/>
-      <c r="AU2" s="218"/>
-      <c r="AV2" s="216" t="s">
+      <c r="AT2" s="220"/>
+      <c r="AU2" s="221"/>
+      <c r="AV2" s="219" t="s">
         <v>336</v>
       </c>
-      <c r="AW2" s="217"/>
-      <c r="AX2" s="218"/>
-      <c r="AY2" s="216" t="s">
+      <c r="AW2" s="220"/>
+      <c r="AX2" s="221"/>
+      <c r="AY2" s="219" t="s">
         <v>305</v>
       </c>
-      <c r="AZ2" s="217"/>
-      <c r="BA2" s="218"/>
-      <c r="BB2" s="216" t="s">
+      <c r="AZ2" s="220"/>
+      <c r="BA2" s="221"/>
+      <c r="BB2" s="219" t="s">
         <v>326</v>
       </c>
-      <c r="BC2" s="217"/>
-      <c r="BD2" s="218"/>
-      <c r="BE2" s="216" t="s">
+      <c r="BC2" s="220"/>
+      <c r="BD2" s="221"/>
+      <c r="BE2" s="219" t="s">
         <v>325</v>
       </c>
-      <c r="BF2" s="217"/>
-      <c r="BG2" s="218"/>
-      <c r="BH2" s="216" t="s">
+      <c r="BF2" s="220"/>
+      <c r="BG2" s="221"/>
+      <c r="BH2" s="219" t="s">
         <v>348</v>
       </c>
-      <c r="BI2" s="217"/>
-      <c r="BJ2" s="218"/>
-      <c r="BK2" s="216" t="s">
+      <c r="BI2" s="220"/>
+      <c r="BJ2" s="221"/>
+      <c r="BK2" s="219" t="s">
         <v>332</v>
       </c>
-      <c r="BL2" s="217"/>
-      <c r="BM2" s="218"/>
-      <c r="BN2" s="216" t="s">
+      <c r="BL2" s="220"/>
+      <c r="BM2" s="221"/>
+      <c r="BN2" s="219" t="s">
         <v>347</v>
       </c>
-      <c r="BO2" s="217"/>
-      <c r="BP2" s="218"/>
-      <c r="BQ2" s="216" t="s">
+      <c r="BO2" s="220"/>
+      <c r="BP2" s="221"/>
+      <c r="BQ2" s="219" t="s">
         <v>324</v>
       </c>
-      <c r="BR2" s="217"/>
-      <c r="BS2" s="218"/>
-      <c r="BT2" s="216" t="s">
+      <c r="BR2" s="220"/>
+      <c r="BS2" s="221"/>
+      <c r="BT2" s="219" t="s">
         <v>323</v>
       </c>
-      <c r="BU2" s="217"/>
-      <c r="BV2" s="218"/>
-      <c r="BW2" s="216" t="s">
+      <c r="BU2" s="220"/>
+      <c r="BV2" s="221"/>
+      <c r="BW2" s="219" t="s">
         <v>321</v>
       </c>
-      <c r="BX2" s="217"/>
-      <c r="BY2" s="218"/>
-      <c r="BZ2" s="216" t="s">
+      <c r="BX2" s="220"/>
+      <c r="BY2" s="221"/>
+      <c r="BZ2" s="219" t="s">
         <v>348</v>
       </c>
-      <c r="CA2" s="217"/>
-      <c r="CB2" s="218"/>
-      <c r="CC2" s="216" t="s">
+      <c r="CA2" s="220"/>
+      <c r="CB2" s="221"/>
+      <c r="CC2" s="219" t="s">
         <v>325</v>
       </c>
-      <c r="CD2" s="217"/>
-      <c r="CE2" s="218"/>
-      <c r="CF2" s="216" t="s">
+      <c r="CD2" s="220"/>
+      <c r="CE2" s="221"/>
+      <c r="CF2" s="219" t="s">
         <v>305</v>
       </c>
-      <c r="CG2" s="217"/>
-      <c r="CH2" s="218"/>
-      <c r="CI2" s="216" t="s">
+      <c r="CG2" s="220"/>
+      <c r="CH2" s="221"/>
+      <c r="CI2" s="219" t="s">
         <v>326</v>
       </c>
-      <c r="CJ2" s="217"/>
-      <c r="CK2" s="218"/>
-      <c r="CL2" s="216" t="s">
+      <c r="CJ2" s="220"/>
+      <c r="CK2" s="221"/>
+      <c r="CL2" s="219" t="s">
         <v>330</v>
       </c>
-      <c r="CM2" s="217"/>
-      <c r="CN2" s="218"/>
-      <c r="CO2" s="216" t="s">
+      <c r="CM2" s="220"/>
+      <c r="CN2" s="221"/>
+      <c r="CO2" s="219" t="s">
         <v>328</v>
       </c>
-      <c r="CP2" s="217"/>
-      <c r="CQ2" s="218"/>
-      <c r="CR2" s="216" t="s">
+      <c r="CP2" s="220"/>
+      <c r="CQ2" s="221"/>
+      <c r="CR2" s="219" t="s">
         <v>346</v>
       </c>
-      <c r="CS2" s="217"/>
-      <c r="CT2" s="218"/>
-      <c r="CU2" s="216" t="s">
+      <c r="CS2" s="220"/>
+      <c r="CT2" s="221"/>
+      <c r="CU2" s="219" t="s">
         <v>331</v>
       </c>
-      <c r="CV2" s="217"/>
-      <c r="CW2" s="218"/>
-      <c r="CX2" s="216" t="s">
+      <c r="CV2" s="220"/>
+      <c r="CW2" s="221"/>
+      <c r="CX2" s="219" t="s">
         <v>336</v>
       </c>
-      <c r="CY2" s="217"/>
-      <c r="CZ2" s="218"/>
-      <c r="DA2" s="216" t="s">
+      <c r="CY2" s="220"/>
+      <c r="CZ2" s="221"/>
+      <c r="DA2" s="219" t="s">
         <v>329</v>
       </c>
-      <c r="DB2" s="217"/>
-      <c r="DC2" s="218"/>
-      <c r="DD2" s="216" t="s">
+      <c r="DB2" s="220"/>
+      <c r="DC2" s="221"/>
+      <c r="DD2" s="219" t="s">
         <v>320</v>
       </c>
-      <c r="DE2" s="217"/>
-      <c r="DF2" s="218"/>
-      <c r="DG2" s="216" t="s">
+      <c r="DE2" s="220"/>
+      <c r="DF2" s="221"/>
+      <c r="DG2" s="219" t="s">
         <v>337</v>
       </c>
-      <c r="DH2" s="217"/>
-      <c r="DI2" s="218"/>
-      <c r="DJ2" s="216" t="s">
+      <c r="DH2" s="220"/>
+      <c r="DI2" s="221"/>
+      <c r="DJ2" s="219" t="s">
         <v>334</v>
       </c>
-      <c r="DK2" s="217"/>
-      <c r="DL2" s="218"/>
-      <c r="DM2" s="216" t="s">
+      <c r="DK2" s="220"/>
+      <c r="DL2" s="221"/>
+      <c r="DM2" s="219" t="s">
         <v>335</v>
       </c>
-      <c r="DN2" s="217"/>
-      <c r="DO2" s="218"/>
+      <c r="DN2" s="220"/>
+      <c r="DO2" s="221"/>
     </row>
     <row r="3" spans="1:119" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -38050,9 +38050,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="223"/>
-      <c r="D3" s="223"/>
-      <c r="E3" s="224"/>
+      <c r="C3" s="224"/>
+      <c r="D3" s="224"/>
+      <c r="E3" s="223"/>
       <c r="F3" s="160" t="s">
         <v>393</v>
       </c>
@@ -43573,69 +43573,6 @@
     </row>
   </sheetData>
   <mergeCells count="79">
-    <mergeCell ref="DM1:DO1"/>
-    <mergeCell ref="DM2:DO2"/>
-    <mergeCell ref="DA1:DC1"/>
-    <mergeCell ref="DA2:DC2"/>
-    <mergeCell ref="DD1:DF1"/>
-    <mergeCell ref="DD2:DF2"/>
-    <mergeCell ref="DG1:DI1"/>
-    <mergeCell ref="DG2:DI2"/>
-    <mergeCell ref="CU1:CW1"/>
-    <mergeCell ref="CU2:CW2"/>
-    <mergeCell ref="CX1:CZ1"/>
-    <mergeCell ref="CX2:CZ2"/>
-    <mergeCell ref="DJ1:DL1"/>
-    <mergeCell ref="DJ2:DL2"/>
-    <mergeCell ref="CL1:CN1"/>
-    <mergeCell ref="CL2:CN2"/>
-    <mergeCell ref="CO1:CQ1"/>
-    <mergeCell ref="CO2:CQ2"/>
-    <mergeCell ref="CR1:CT1"/>
-    <mergeCell ref="CR2:CT2"/>
-    <mergeCell ref="CC1:CE1"/>
-    <mergeCell ref="CC2:CE2"/>
-    <mergeCell ref="CF1:CH1"/>
-    <mergeCell ref="CF2:CH2"/>
-    <mergeCell ref="CI1:CK1"/>
-    <mergeCell ref="CI2:CK2"/>
-    <mergeCell ref="BT1:BV1"/>
-    <mergeCell ref="BT2:BV2"/>
-    <mergeCell ref="BW1:BY1"/>
-    <mergeCell ref="BW2:BY2"/>
-    <mergeCell ref="BZ1:CB1"/>
-    <mergeCell ref="BZ2:CB2"/>
-    <mergeCell ref="BK1:BM1"/>
-    <mergeCell ref="BK2:BM2"/>
-    <mergeCell ref="BN1:BP1"/>
-    <mergeCell ref="BN2:BP2"/>
-    <mergeCell ref="BQ1:BS1"/>
-    <mergeCell ref="BQ2:BS2"/>
-    <mergeCell ref="AS1:AU1"/>
-    <mergeCell ref="AS2:AU2"/>
-    <mergeCell ref="AV1:AX1"/>
-    <mergeCell ref="AV2:AX2"/>
-    <mergeCell ref="BH1:BJ1"/>
-    <mergeCell ref="BH2:BJ2"/>
-    <mergeCell ref="AY2:BA2"/>
-    <mergeCell ref="BB2:BD2"/>
-    <mergeCell ref="BE2:BG2"/>
-    <mergeCell ref="AJ1:AL1"/>
-    <mergeCell ref="AJ2:AL2"/>
-    <mergeCell ref="AM1:AO1"/>
-    <mergeCell ref="AM2:AO2"/>
-    <mergeCell ref="AP2:AR2"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
     <mergeCell ref="AD2:AF2"/>
     <mergeCell ref="AG2:AI2"/>
     <mergeCell ref="BB1:BD1"/>
@@ -43652,6 +43589,69 @@
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="X1:Z1"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="AJ1:AL1"/>
+    <mergeCell ref="AJ2:AL2"/>
+    <mergeCell ref="AM1:AO1"/>
+    <mergeCell ref="AM2:AO2"/>
+    <mergeCell ref="AP2:AR2"/>
+    <mergeCell ref="AS1:AU1"/>
+    <mergeCell ref="AS2:AU2"/>
+    <mergeCell ref="AV1:AX1"/>
+    <mergeCell ref="AV2:AX2"/>
+    <mergeCell ref="BH1:BJ1"/>
+    <mergeCell ref="BH2:BJ2"/>
+    <mergeCell ref="AY2:BA2"/>
+    <mergeCell ref="BB2:BD2"/>
+    <mergeCell ref="BE2:BG2"/>
+    <mergeCell ref="BK1:BM1"/>
+    <mergeCell ref="BK2:BM2"/>
+    <mergeCell ref="BN1:BP1"/>
+    <mergeCell ref="BN2:BP2"/>
+    <mergeCell ref="BQ1:BS1"/>
+    <mergeCell ref="BQ2:BS2"/>
+    <mergeCell ref="BT1:BV1"/>
+    <mergeCell ref="BT2:BV2"/>
+    <mergeCell ref="BW1:BY1"/>
+    <mergeCell ref="BW2:BY2"/>
+    <mergeCell ref="BZ1:CB1"/>
+    <mergeCell ref="BZ2:CB2"/>
+    <mergeCell ref="CC1:CE1"/>
+    <mergeCell ref="CC2:CE2"/>
+    <mergeCell ref="CF1:CH1"/>
+    <mergeCell ref="CF2:CH2"/>
+    <mergeCell ref="CI1:CK1"/>
+    <mergeCell ref="CI2:CK2"/>
+    <mergeCell ref="CL1:CN1"/>
+    <mergeCell ref="CL2:CN2"/>
+    <mergeCell ref="CO1:CQ1"/>
+    <mergeCell ref="CO2:CQ2"/>
+    <mergeCell ref="CR1:CT1"/>
+    <mergeCell ref="CR2:CT2"/>
+    <mergeCell ref="CU1:CW1"/>
+    <mergeCell ref="CU2:CW2"/>
+    <mergeCell ref="CX1:CZ1"/>
+    <mergeCell ref="CX2:CZ2"/>
+    <mergeCell ref="DJ1:DL1"/>
+    <mergeCell ref="DJ2:DL2"/>
+    <mergeCell ref="DM1:DO1"/>
+    <mergeCell ref="DM2:DO2"/>
+    <mergeCell ref="DA1:DC1"/>
+    <mergeCell ref="DA2:DC2"/>
+    <mergeCell ref="DD1:DF1"/>
+    <mergeCell ref="DD2:DF2"/>
+    <mergeCell ref="DG1:DI1"/>
+    <mergeCell ref="DG2:DI2"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:DO37">
     <cfRule type="cellIs" dxfId="18" priority="1" operator="between">
@@ -43687,41 +43687,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="237" t="s">
+      <c r="C1" s="234" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="237" t="s">
+      <c r="D1" s="234" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="237" t="s">
+      <c r="E1" s="234" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="228" t="s">
+      <c r="F1" s="225" t="s">
         <v>302</v>
       </c>
-      <c r="G1" s="229"/>
-      <c r="H1" s="229"/>
-      <c r="I1" s="229"/>
-      <c r="J1" s="229"/>
-      <c r="K1" s="229"/>
-      <c r="L1" s="229"/>
-      <c r="M1" s="229"/>
-      <c r="N1" s="229"/>
-      <c r="O1" s="229"/>
-      <c r="P1" s="229"/>
-      <c r="Q1" s="229"/>
-      <c r="R1" s="229"/>
-      <c r="S1" s="229"/>
-      <c r="T1" s="229"/>
-      <c r="U1" s="229"/>
-      <c r="V1" s="229"/>
-      <c r="W1" s="229"/>
-      <c r="X1" s="229"/>
-      <c r="Y1" s="229"/>
-      <c r="Z1" s="229"/>
-      <c r="AA1" s="229"/>
-      <c r="AB1" s="229"/>
-      <c r="AC1" s="230"/>
+      <c r="G1" s="226"/>
+      <c r="H1" s="226"/>
+      <c r="I1" s="226"/>
+      <c r="J1" s="226"/>
+      <c r="K1" s="226"/>
+      <c r="L1" s="226"/>
+      <c r="M1" s="226"/>
+      <c r="N1" s="226"/>
+      <c r="O1" s="226"/>
+      <c r="P1" s="226"/>
+      <c r="Q1" s="226"/>
+      <c r="R1" s="226"/>
+      <c r="S1" s="226"/>
+      <c r="T1" s="226"/>
+      <c r="U1" s="226"/>
+      <c r="V1" s="226"/>
+      <c r="W1" s="226"/>
+      <c r="X1" s="226"/>
+      <c r="Y1" s="226"/>
+      <c r="Z1" s="226"/>
+      <c r="AA1" s="226"/>
+      <c r="AB1" s="226"/>
+      <c r="AC1" s="227"/>
       <c r="AD1" s="240" t="s">
         <v>281</v>
       </c>
@@ -43730,95 +43730,95 @@
       <c r="AG1" s="241"/>
       <c r="AH1" s="241"/>
       <c r="AI1" s="242"/>
-      <c r="AJ1" s="228" t="s">
+      <c r="AJ1" s="225" t="s">
         <v>282</v>
       </c>
-      <c r="AK1" s="229"/>
-      <c r="AL1" s="229"/>
-      <c r="AM1" s="229"/>
-      <c r="AN1" s="229"/>
-      <c r="AO1" s="230"/>
-      <c r="AP1" s="231" t="s">
+      <c r="AK1" s="226"/>
+      <c r="AL1" s="226"/>
+      <c r="AM1" s="226"/>
+      <c r="AN1" s="226"/>
+      <c r="AO1" s="227"/>
+      <c r="AP1" s="228" t="s">
         <v>283</v>
       </c>
-      <c r="AQ1" s="232"/>
-      <c r="AR1" s="232"/>
-      <c r="AS1" s="232"/>
-      <c r="AT1" s="232"/>
-      <c r="AU1" s="233"/>
-      <c r="AV1" s="234" t="s">
+      <c r="AQ1" s="229"/>
+      <c r="AR1" s="229"/>
+      <c r="AS1" s="229"/>
+      <c r="AT1" s="229"/>
+      <c r="AU1" s="230"/>
+      <c r="AV1" s="231" t="s">
         <v>86</v>
       </c>
-      <c r="AW1" s="235"/>
-      <c r="AX1" s="236"/>
+      <c r="AW1" s="232"/>
+      <c r="AX1" s="233"/>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="238"/>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="225" t="s">
+      <c r="C2" s="235"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="237" t="s">
         <v>468</v>
       </c>
-      <c r="G2" s="226"/>
-      <c r="H2" s="227"/>
-      <c r="I2" s="225" t="s">
+      <c r="G2" s="238"/>
+      <c r="H2" s="239"/>
+      <c r="I2" s="237" t="s">
+        <v>482</v>
+      </c>
+      <c r="J2" s="238"/>
+      <c r="K2" s="239"/>
+      <c r="L2" s="237" t="s">
         <v>483</v>
       </c>
-      <c r="J2" s="226"/>
-      <c r="K2" s="227"/>
-      <c r="L2" s="225" t="s">
+      <c r="M2" s="238"/>
+      <c r="N2" s="239"/>
+      <c r="O2" s="237" t="s">
         <v>484</v>
       </c>
-      <c r="M2" s="226"/>
-      <c r="N2" s="227"/>
-      <c r="O2" s="225" t="s">
+      <c r="P2" s="238"/>
+      <c r="Q2" s="239"/>
+      <c r="R2" s="237" t="s">
         <v>485</v>
       </c>
-      <c r="P2" s="226"/>
-      <c r="Q2" s="227"/>
-      <c r="R2" s="225" t="s">
+      <c r="S2" s="238"/>
+      <c r="T2" s="239"/>
+      <c r="U2" s="237" t="s">
         <v>486</v>
       </c>
-      <c r="S2" s="226"/>
-      <c r="T2" s="227"/>
-      <c r="U2" s="225" t="s">
+      <c r="V2" s="238"/>
+      <c r="W2" s="239"/>
+      <c r="X2" s="237" t="s">
         <v>487</v>
       </c>
-      <c r="V2" s="226"/>
-      <c r="W2" s="227"/>
-      <c r="X2" s="225" t="s">
+      <c r="Y2" s="238"/>
+      <c r="Z2" s="239"/>
+      <c r="AA2" s="237" t="s">
         <v>488</v>
       </c>
-      <c r="Y2" s="226"/>
-      <c r="Z2" s="227"/>
-      <c r="AA2" s="225" t="s">
-        <v>489</v>
-      </c>
-      <c r="AB2" s="226"/>
-      <c r="AC2" s="226"/>
-      <c r="AD2" s="225"/>
-      <c r="AE2" s="226"/>
-      <c r="AF2" s="227"/>
-      <c r="AG2" s="225"/>
-      <c r="AH2" s="226"/>
-      <c r="AI2" s="227"/>
-      <c r="AJ2" s="225"/>
-      <c r="AK2" s="226"/>
-      <c r="AL2" s="227"/>
-      <c r="AM2" s="225"/>
-      <c r="AN2" s="226"/>
-      <c r="AO2" s="227"/>
-      <c r="AP2" s="225"/>
-      <c r="AQ2" s="226"/>
-      <c r="AR2" s="227"/>
-      <c r="AS2" s="225"/>
-      <c r="AT2" s="226"/>
-      <c r="AU2" s="227"/>
-      <c r="AV2" s="225"/>
-      <c r="AW2" s="226"/>
-      <c r="AX2" s="227"/>
+      <c r="AB2" s="238"/>
+      <c r="AC2" s="238"/>
+      <c r="AD2" s="237"/>
+      <c r="AE2" s="238"/>
+      <c r="AF2" s="239"/>
+      <c r="AG2" s="237"/>
+      <c r="AH2" s="238"/>
+      <c r="AI2" s="239"/>
+      <c r="AJ2" s="237"/>
+      <c r="AK2" s="238"/>
+      <c r="AL2" s="239"/>
+      <c r="AM2" s="237"/>
+      <c r="AN2" s="238"/>
+      <c r="AO2" s="239"/>
+      <c r="AP2" s="237"/>
+      <c r="AQ2" s="238"/>
+      <c r="AR2" s="239"/>
+      <c r="AS2" s="237"/>
+      <c r="AT2" s="238"/>
+      <c r="AU2" s="239"/>
+      <c r="AV2" s="237"/>
+      <c r="AW2" s="238"/>
+      <c r="AX2" s="239"/>
     </row>
     <row r="3" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -43827,9 +43827,9 @@
       <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="239"/>
-      <c r="D3" s="239"/>
-      <c r="E3" s="239"/>
+      <c r="C3" s="236"/>
+      <c r="D3" s="236"/>
+      <c r="E3" s="236"/>
       <c r="F3" s="170" t="s">
         <v>393</v>
       </c>
@@ -46396,6 +46396,13 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="F1:AC1"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
+    <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="AJ1:AO1"/>
     <mergeCell ref="AP1:AU1"/>
     <mergeCell ref="AV1:AX1"/>
@@ -46412,13 +46419,6 @@
     <mergeCell ref="AD1:AI1"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="I2:K2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="F1:AC1"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:AW31">
     <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
@@ -46453,70 +46453,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C1" s="237" t="s">
+      <c r="C1" s="234" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="237" t="s">
+      <c r="D1" s="234" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="237" t="s">
+      <c r="E1" s="234" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="267" t="s">
+      <c r="F1" s="274" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="268"/>
-      <c r="H1" s="269"/>
-      <c r="I1" s="270" t="s">
+      <c r="G1" s="275"/>
+      <c r="H1" s="276"/>
+      <c r="I1" s="277" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="271"/>
-      <c r="K1" s="272"/>
-      <c r="L1" s="274" t="s">
+      <c r="J1" s="278"/>
+      <c r="K1" s="279"/>
+      <c r="L1" s="244" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="275"/>
-      <c r="N1" s="276"/>
-      <c r="O1" s="277" t="s">
+      <c r="M1" s="245"/>
+      <c r="N1" s="246"/>
+      <c r="O1" s="247" t="s">
         <v>199</v>
       </c>
-      <c r="P1" s="278"/>
-      <c r="Q1" s="279"/>
-      <c r="R1" s="243" t="s">
+      <c r="P1" s="248"/>
+      <c r="Q1" s="249"/>
+      <c r="R1" s="250" t="s">
         <v>200</v>
       </c>
-      <c r="S1" s="244"/>
-      <c r="T1" s="245"/>
-      <c r="U1" s="246" t="s">
+      <c r="S1" s="251"/>
+      <c r="T1" s="252"/>
+      <c r="U1" s="253" t="s">
         <v>306</v>
       </c>
-      <c r="V1" s="247"/>
-      <c r="W1" s="248"/>
+      <c r="V1" s="254"/>
+      <c r="W1" s="255"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="238"/>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="249"/>
-      <c r="G2" s="250"/>
-      <c r="H2" s="251"/>
-      <c r="I2" s="264"/>
-      <c r="J2" s="265"/>
-      <c r="K2" s="266"/>
-      <c r="L2" s="261"/>
-      <c r="M2" s="262"/>
-      <c r="N2" s="263"/>
-      <c r="O2" s="258"/>
-      <c r="P2" s="259"/>
-      <c r="Q2" s="260"/>
-      <c r="R2" s="255"/>
-      <c r="S2" s="256"/>
-      <c r="T2" s="257"/>
-      <c r="U2" s="252"/>
-      <c r="V2" s="253"/>
-      <c r="W2" s="254"/>
+      <c r="C2" s="235"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="256"/>
+      <c r="G2" s="257"/>
+      <c r="H2" s="258"/>
+      <c r="I2" s="271"/>
+      <c r="J2" s="272"/>
+      <c r="K2" s="273"/>
+      <c r="L2" s="268"/>
+      <c r="M2" s="269"/>
+      <c r="N2" s="270"/>
+      <c r="O2" s="265"/>
+      <c r="P2" s="266"/>
+      <c r="Q2" s="267"/>
+      <c r="R2" s="262"/>
+      <c r="S2" s="263"/>
+      <c r="T2" s="264"/>
+      <c r="U2" s="259"/>
+      <c r="V2" s="260"/>
+      <c r="W2" s="261"/>
     </row>
     <row r="3" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -46525,9 +46525,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="273"/>
-      <c r="D3" s="273"/>
-      <c r="E3" s="273"/>
+      <c r="C3" s="243"/>
+      <c r="D3" s="243"/>
+      <c r="E3" s="243"/>
       <c r="F3" s="189" t="s">
         <v>393</v>
       </c>
@@ -47951,11 +47951,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="O1:Q1"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="F2:H2"/>
@@ -47966,6 +47961,11 @@
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="O1:Q1"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:W31">
     <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
@@ -54779,72 +54779,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C1" s="237" t="s">
+      <c r="C1" s="234" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="237" t="s">
+      <c r="D1" s="234" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="237" t="s">
+      <c r="E1" s="234" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="267" t="s">
+      <c r="F1" s="274" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="268"/>
-      <c r="H1" s="269"/>
-      <c r="I1" s="270" t="s">
+      <c r="G1" s="275"/>
+      <c r="H1" s="276"/>
+      <c r="I1" s="277" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="271"/>
-      <c r="K1" s="272"/>
-      <c r="L1" s="274" t="s">
+      <c r="J1" s="278"/>
+      <c r="K1" s="279"/>
+      <c r="L1" s="244" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="275"/>
-      <c r="N1" s="276"/>
-      <c r="O1" s="277" t="s">
+      <c r="M1" s="245"/>
+      <c r="N1" s="246"/>
+      <c r="O1" s="247" t="s">
         <v>199</v>
       </c>
-      <c r="P1" s="278"/>
-      <c r="Q1" s="279"/>
-      <c r="R1" s="243" t="s">
+      <c r="P1" s="248"/>
+      <c r="Q1" s="249"/>
+      <c r="R1" s="250" t="s">
         <v>200</v>
       </c>
-      <c r="S1" s="244"/>
-      <c r="T1" s="245"/>
-      <c r="U1" s="246" t="s">
+      <c r="S1" s="251"/>
+      <c r="T1" s="252"/>
+      <c r="U1" s="253" t="s">
         <v>306</v>
       </c>
-      <c r="V1" s="247"/>
-      <c r="W1" s="248"/>
+      <c r="V1" s="254"/>
+      <c r="W1" s="255"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="238"/>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="249" t="s">
+      <c r="C2" s="235"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="256" t="s">
         <v>433</v>
       </c>
-      <c r="G2" s="250"/>
-      <c r="H2" s="251"/>
-      <c r="I2" s="264"/>
-      <c r="J2" s="265"/>
-      <c r="K2" s="266"/>
-      <c r="L2" s="261"/>
-      <c r="M2" s="262"/>
-      <c r="N2" s="263"/>
-      <c r="O2" s="258"/>
-      <c r="P2" s="259"/>
-      <c r="Q2" s="260"/>
-      <c r="R2" s="255"/>
-      <c r="S2" s="256"/>
-      <c r="T2" s="257"/>
-      <c r="U2" s="252"/>
-      <c r="V2" s="253"/>
-      <c r="W2" s="254"/>
+      <c r="G2" s="257"/>
+      <c r="H2" s="258"/>
+      <c r="I2" s="271"/>
+      <c r="J2" s="272"/>
+      <c r="K2" s="273"/>
+      <c r="L2" s="268"/>
+      <c r="M2" s="269"/>
+      <c r="N2" s="270"/>
+      <c r="O2" s="265"/>
+      <c r="P2" s="266"/>
+      <c r="Q2" s="267"/>
+      <c r="R2" s="262"/>
+      <c r="S2" s="263"/>
+      <c r="T2" s="264"/>
+      <c r="U2" s="259"/>
+      <c r="V2" s="260"/>
+      <c r="W2" s="261"/>
     </row>
     <row r="3" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -54853,9 +54853,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="273"/>
-      <c r="D3" s="273"/>
-      <c r="E3" s="273"/>
+      <c r="C3" s="243"/>
+      <c r="D3" s="243"/>
+      <c r="E3" s="243"/>
       <c r="F3" s="189" t="s">
         <v>393</v>
       </c>
@@ -56279,6 +56279,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="F2:H2"/>
@@ -56289,11 +56294,6 @@
     <mergeCell ref="U2:W2"/>
     <mergeCell ref="L1:N1"/>
     <mergeCell ref="O1:Q1"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:W31">
     <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
@@ -56789,51 +56789,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="283" t="s">
+      <c r="C1" s="302" t="s">
         <v>202</v>
       </c>
-      <c r="D1" s="284"/>
-      <c r="E1" s="284"/>
-      <c r="F1" s="284"/>
-      <c r="G1" s="284"/>
-      <c r="H1" s="284"/>
-      <c r="I1" s="285"/>
+      <c r="D1" s="303"/>
+      <c r="E1" s="303"/>
+      <c r="F1" s="303"/>
+      <c r="G1" s="303"/>
+      <c r="H1" s="303"/>
+      <c r="I1" s="304"/>
       <c r="J1" s="114" t="s">
         <v>195</v>
       </c>
       <c r="K1" s="115" t="s">
         <v>194</v>
       </c>
-      <c r="L1" s="307" t="s">
+      <c r="L1" s="282" t="s">
         <v>287</v>
       </c>
-      <c r="M1" s="312"/>
-      <c r="N1" s="312"/>
-      <c r="O1" s="312"/>
-      <c r="P1" s="312"/>
-      <c r="Q1" s="312"/>
-      <c r="R1" s="312"/>
-      <c r="S1" s="312"/>
-      <c r="T1" s="312"/>
-      <c r="U1" s="312"/>
-      <c r="V1" s="312"/>
-      <c r="W1" s="312"/>
-      <c r="X1" s="312"/>
-      <c r="Y1" s="312"/>
-      <c r="Z1" s="312"/>
-      <c r="AA1" s="312"/>
-      <c r="AB1" s="312"/>
-      <c r="AC1" s="312"/>
-      <c r="AD1" s="312"/>
-      <c r="AE1" s="312"/>
-      <c r="AF1" s="312"/>
-      <c r="AG1" s="313"/>
-      <c r="AH1" s="307" t="s">
+      <c r="M1" s="287"/>
+      <c r="N1" s="287"/>
+      <c r="O1" s="287"/>
+      <c r="P1" s="287"/>
+      <c r="Q1" s="287"/>
+      <c r="R1" s="287"/>
+      <c r="S1" s="287"/>
+      <c r="T1" s="287"/>
+      <c r="U1" s="287"/>
+      <c r="V1" s="287"/>
+      <c r="W1" s="287"/>
+      <c r="X1" s="287"/>
+      <c r="Y1" s="287"/>
+      <c r="Z1" s="287"/>
+      <c r="AA1" s="287"/>
+      <c r="AB1" s="287"/>
+      <c r="AC1" s="287"/>
+      <c r="AD1" s="287"/>
+      <c r="AE1" s="287"/>
+      <c r="AF1" s="287"/>
+      <c r="AG1" s="288"/>
+      <c r="AH1" s="282" t="s">
         <v>175</v>
       </c>
-      <c r="AI1" s="308"/>
-      <c r="AJ1" s="308"/>
-      <c r="AK1" s="309"/>
+      <c r="AI1" s="283"/>
+      <c r="AJ1" s="283"/>
+      <c r="AK1" s="284"/>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B2" s="111"/>
@@ -62033,15 +62033,15 @@
         <f t="shared" ref="J80:J111" si="2">H80-I80</f>
         <v>2</v>
       </c>
-      <c r="K80" s="314" t="s">
+      <c r="K80" s="289" t="s">
         <v>435</v>
       </c>
-      <c r="L80" s="315"/>
-      <c r="M80" s="316"/>
+      <c r="L80" s="290"/>
+      <c r="M80" s="291"/>
       <c r="O80" s="133"/>
       <c r="P80" s="133"/>
-      <c r="W80" s="310"/>
-      <c r="X80" s="310"/>
+      <c r="W80" s="285"/>
+      <c r="X80" s="285"/>
       <c r="Y80" s="70" t="s">
         <v>211</v>
       </c>
@@ -62091,15 +62091,15 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K81" s="317"/>
-      <c r="L81" s="318"/>
-      <c r="M81" s="319"/>
+      <c r="K81" s="292"/>
+      <c r="L81" s="293"/>
+      <c r="M81" s="294"/>
       <c r="O81" s="133"/>
       <c r="P81" s="133"/>
-      <c r="W81" s="310" t="s">
+      <c r="W81" s="285" t="s">
         <v>209</v>
       </c>
-      <c r="X81" s="310"/>
+      <c r="X81" s="285"/>
       <c r="Y81" s="70">
         <f>COUNTIF(L3:AG40,3)</f>
         <v>481</v>
@@ -62155,17 +62155,17 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K82" s="320" t="s">
+      <c r="K82" s="295" t="s">
         <v>436</v>
       </c>
-      <c r="L82" s="321"/>
-      <c r="M82" s="322"/>
+      <c r="L82" s="296"/>
+      <c r="M82" s="297"/>
       <c r="O82" s="133"/>
       <c r="P82" s="133"/>
-      <c r="W82" s="310" t="s">
+      <c r="W82" s="285" t="s">
         <v>210</v>
       </c>
-      <c r="X82" s="310"/>
+      <c r="X82" s="285"/>
       <c r="Y82" s="70">
         <f>COUNTIF(K3:K40,3)+COUNTIF(J3:J15,3)</f>
         <v>25</v>
@@ -62221,17 +62221,17 @@
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="K83" s="323" t="s">
+      <c r="K83" s="298" t="s">
         <v>437</v>
       </c>
-      <c r="L83" s="324"/>
-      <c r="M83" s="325"/>
+      <c r="L83" s="299"/>
+      <c r="M83" s="300"/>
       <c r="O83" s="133"/>
       <c r="P83" s="133"/>
-      <c r="W83" s="311" t="s">
+      <c r="W83" s="286" t="s">
         <v>97</v>
       </c>
-      <c r="X83" s="311"/>
+      <c r="X83" s="286"/>
       <c r="Y83" s="196">
         <v>220</v>
       </c>
@@ -62284,15 +62284,15 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="K84" s="298" t="s">
+      <c r="K84" s="317" t="s">
         <v>284</v>
       </c>
-      <c r="L84" s="299"/>
-      <c r="M84" s="300"/>
+      <c r="L84" s="318"/>
+      <c r="M84" s="319"/>
       <c r="O84" s="141"/>
       <c r="P84" s="141"/>
-      <c r="W84" s="282"/>
-      <c r="X84" s="282"/>
+      <c r="W84" s="301"/>
+      <c r="X84" s="301"/>
       <c r="Y84" s="198"/>
       <c r="Z84" s="198"/>
       <c r="AA84" s="198"/>
@@ -62330,9 +62330,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K85" s="301"/>
-      <c r="L85" s="302"/>
-      <c r="M85" s="303"/>
+      <c r="K85" s="320"/>
+      <c r="L85" s="321"/>
+      <c r="M85" s="322"/>
       <c r="O85" s="141"/>
       <c r="P85" s="141"/>
     </row>
@@ -62366,9 +62366,9 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="K86" s="301"/>
-      <c r="L86" s="302"/>
-      <c r="M86" s="303"/>
+      <c r="K86" s="320"/>
+      <c r="L86" s="321"/>
+      <c r="M86" s="322"/>
       <c r="O86" s="141"/>
       <c r="P86" s="141"/>
     </row>
@@ -62402,9 +62402,9 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="K87" s="301"/>
-      <c r="L87" s="302"/>
-      <c r="M87" s="303"/>
+      <c r="K87" s="320"/>
+      <c r="L87" s="321"/>
+      <c r="M87" s="322"/>
       <c r="O87" s="141"/>
       <c r="P87" s="141"/>
     </row>
@@ -62438,9 +62438,9 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K88" s="301"/>
-      <c r="L88" s="302"/>
-      <c r="M88" s="303"/>
+      <c r="K88" s="320"/>
+      <c r="L88" s="321"/>
+      <c r="M88" s="322"/>
       <c r="O88" s="141"/>
       <c r="P88" s="141"/>
     </row>
@@ -62474,9 +62474,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K89" s="301"/>
-      <c r="L89" s="302"/>
-      <c r="M89" s="303"/>
+      <c r="K89" s="320"/>
+      <c r="L89" s="321"/>
+      <c r="M89" s="322"/>
       <c r="O89" s="141"/>
       <c r="P89" s="141"/>
     </row>
@@ -62510,9 +62510,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K90" s="301"/>
-      <c r="L90" s="302"/>
-      <c r="M90" s="303"/>
+      <c r="K90" s="320"/>
+      <c r="L90" s="321"/>
+      <c r="M90" s="322"/>
       <c r="O90" s="141"/>
       <c r="P90" s="141"/>
     </row>
@@ -62546,9 +62546,9 @@
         <f t="shared" si="2"/>
         <v>47</v>
       </c>
-      <c r="K91" s="301"/>
-      <c r="L91" s="302"/>
-      <c r="M91" s="303"/>
+      <c r="K91" s="320"/>
+      <c r="L91" s="321"/>
+      <c r="M91" s="322"/>
       <c r="O91" s="141"/>
       <c r="P91" s="141"/>
     </row>
@@ -62582,9 +62582,9 @@
         <f t="shared" si="2"/>
         <v>51</v>
       </c>
-      <c r="K92" s="301"/>
-      <c r="L92" s="302"/>
-      <c r="M92" s="303"/>
+      <c r="K92" s="320"/>
+      <c r="L92" s="321"/>
+      <c r="M92" s="322"/>
       <c r="O92" s="141"/>
       <c r="P92" s="141"/>
     </row>
@@ -62618,9 +62618,9 @@
         <f t="shared" si="2"/>
         <v>37</v>
       </c>
-      <c r="K93" s="301"/>
-      <c r="L93" s="302"/>
-      <c r="M93" s="303"/>
+      <c r="K93" s="320"/>
+      <c r="L93" s="321"/>
+      <c r="M93" s="322"/>
       <c r="O93" s="141"/>
       <c r="P93" s="141"/>
     </row>
@@ -62654,9 +62654,9 @@
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="K94" s="301"/>
-      <c r="L94" s="302"/>
-      <c r="M94" s="303"/>
+      <c r="K94" s="320"/>
+      <c r="L94" s="321"/>
+      <c r="M94" s="322"/>
       <c r="O94" s="141"/>
       <c r="P94" s="141"/>
     </row>
@@ -62690,9 +62690,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K95" s="301"/>
-      <c r="L95" s="302"/>
-      <c r="M95" s="303"/>
+      <c r="K95" s="320"/>
+      <c r="L95" s="321"/>
+      <c r="M95" s="322"/>
       <c r="O95" s="141"/>
       <c r="P95" s="141"/>
     </row>
@@ -62726,9 +62726,9 @@
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="K96" s="301"/>
-      <c r="L96" s="302"/>
-      <c r="M96" s="303"/>
+      <c r="K96" s="320"/>
+      <c r="L96" s="321"/>
+      <c r="M96" s="322"/>
       <c r="O96" s="141"/>
       <c r="P96" s="141"/>
     </row>
@@ -62762,9 +62762,9 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="K97" s="301"/>
-      <c r="L97" s="302"/>
-      <c r="M97" s="303"/>
+      <c r="K97" s="320"/>
+      <c r="L97" s="321"/>
+      <c r="M97" s="322"/>
       <c r="O97" s="141"/>
       <c r="P97" s="141"/>
     </row>
@@ -62798,9 +62798,9 @@
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="K98" s="301"/>
-      <c r="L98" s="302"/>
-      <c r="M98" s="303"/>
+      <c r="K98" s="320"/>
+      <c r="L98" s="321"/>
+      <c r="M98" s="322"/>
       <c r="O98" s="141"/>
       <c r="P98" s="141"/>
     </row>
@@ -62834,9 +62834,9 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K99" s="301"/>
-      <c r="L99" s="302"/>
-      <c r="M99" s="303"/>
+      <c r="K99" s="320"/>
+      <c r="L99" s="321"/>
+      <c r="M99" s="322"/>
       <c r="O99" s="141"/>
       <c r="P99" s="141"/>
     </row>
@@ -62870,9 +62870,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K100" s="301"/>
-      <c r="L100" s="302"/>
-      <c r="M100" s="303"/>
+      <c r="K100" s="320"/>
+      <c r="L100" s="321"/>
+      <c r="M100" s="322"/>
       <c r="O100" s="141"/>
       <c r="P100" s="141"/>
     </row>
@@ -62906,9 +62906,9 @@
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="K101" s="301"/>
-      <c r="L101" s="302"/>
-      <c r="M101" s="303"/>
+      <c r="K101" s="320"/>
+      <c r="L101" s="321"/>
+      <c r="M101" s="322"/>
       <c r="O101" s="141"/>
       <c r="P101" s="141"/>
     </row>
@@ -62942,9 +62942,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K102" s="301"/>
-      <c r="L102" s="302"/>
-      <c r="M102" s="303"/>
+      <c r="K102" s="320"/>
+      <c r="L102" s="321"/>
+      <c r="M102" s="322"/>
       <c r="O102" s="141"/>
       <c r="P102" s="141"/>
     </row>
@@ -62978,9 +62978,9 @@
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="K103" s="301"/>
-      <c r="L103" s="302"/>
-      <c r="M103" s="303"/>
+      <c r="K103" s="320"/>
+      <c r="L103" s="321"/>
+      <c r="M103" s="322"/>
       <c r="O103" s="141"/>
       <c r="P103" s="141"/>
     </row>
@@ -63014,9 +63014,9 @@
         <f t="shared" si="2"/>
         <v>33</v>
       </c>
-      <c r="K104" s="301"/>
-      <c r="L104" s="302"/>
-      <c r="M104" s="303"/>
+      <c r="K104" s="320"/>
+      <c r="L104" s="321"/>
+      <c r="M104" s="322"/>
       <c r="O104" s="141"/>
       <c r="P104" s="141"/>
     </row>
@@ -63050,9 +63050,9 @@
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="K105" s="304"/>
-      <c r="L105" s="305"/>
-      <c r="M105" s="306"/>
+      <c r="K105" s="323"/>
+      <c r="L105" s="324"/>
+      <c r="M105" s="325"/>
       <c r="O105" s="141"/>
       <c r="P105" s="141"/>
     </row>
@@ -63086,11 +63086,11 @@
         <f t="shared" si="2"/>
         <v>21</v>
       </c>
-      <c r="K106" s="295" t="s">
+      <c r="K106" s="314" t="s">
         <v>286</v>
       </c>
-      <c r="L106" s="296"/>
-      <c r="M106" s="297"/>
+      <c r="L106" s="315"/>
+      <c r="M106" s="316"/>
       <c r="O106" s="126"/>
       <c r="P106" s="126"/>
     </row>
@@ -63124,11 +63124,11 @@
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="K107" s="295" t="s">
+      <c r="K107" s="314" t="s">
         <v>288</v>
       </c>
-      <c r="L107" s="296"/>
-      <c r="M107" s="297"/>
+      <c r="L107" s="315"/>
+      <c r="M107" s="316"/>
       <c r="O107" s="126"/>
       <c r="P107" s="126"/>
     </row>
@@ -63162,11 +63162,11 @@
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="K108" s="286" t="s">
+      <c r="K108" s="305" t="s">
         <v>289</v>
       </c>
-      <c r="L108" s="287"/>
-      <c r="M108" s="288"/>
+      <c r="L108" s="306"/>
+      <c r="M108" s="307"/>
       <c r="O108" s="126"/>
       <c r="P108" s="126"/>
     </row>
@@ -63200,9 +63200,9 @@
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="K109" s="289"/>
-      <c r="L109" s="290"/>
-      <c r="M109" s="291"/>
+      <c r="K109" s="308"/>
+      <c r="L109" s="309"/>
+      <c r="M109" s="310"/>
       <c r="O109" s="126"/>
       <c r="P109" s="126"/>
     </row>
@@ -63236,9 +63236,9 @@
         <f t="shared" si="2"/>
         <v>45</v>
       </c>
-      <c r="K110" s="289"/>
-      <c r="L110" s="290"/>
-      <c r="M110" s="291"/>
+      <c r="K110" s="308"/>
+      <c r="L110" s="309"/>
+      <c r="M110" s="310"/>
       <c r="O110" s="126"/>
       <c r="P110" s="126"/>
     </row>
@@ -63272,9 +63272,9 @@
         <f t="shared" si="2"/>
         <v>62</v>
       </c>
-      <c r="K111" s="289"/>
-      <c r="L111" s="290"/>
-      <c r="M111" s="291"/>
+      <c r="K111" s="308"/>
+      <c r="L111" s="309"/>
+      <c r="M111" s="310"/>
       <c r="O111" s="126"/>
       <c r="P111" s="126"/>
     </row>
@@ -63312,9 +63312,9 @@
         <f t="shared" ref="J112:J114" si="6">H112-I112</f>
         <v>34</v>
       </c>
-      <c r="K112" s="289"/>
-      <c r="L112" s="290"/>
-      <c r="M112" s="291"/>
+      <c r="K112" s="308"/>
+      <c r="L112" s="309"/>
+      <c r="M112" s="310"/>
     </row>
     <row r="113" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="156" t="s">
@@ -63350,9 +63350,9 @@
         <f t="shared" si="6"/>
         <v>43</v>
       </c>
-      <c r="K113" s="292"/>
-      <c r="L113" s="293"/>
-      <c r="M113" s="294"/>
+      <c r="K113" s="311"/>
+      <c r="L113" s="312"/>
+      <c r="M113" s="313"/>
     </row>
     <row r="114" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" s="93" t="s">
@@ -63392,6 +63392,12 @@
   </sheetData>
   <autoFilter ref="A79:J112" xr:uid="{9C81160F-C24B-449F-8F5A-CB622AB71070}"/>
   <mergeCells count="15">
+    <mergeCell ref="W84:X84"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="K108:M113"/>
+    <mergeCell ref="K106:M106"/>
+    <mergeCell ref="K107:M107"/>
+    <mergeCell ref="K84:M105"/>
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="W80:X80"/>
     <mergeCell ref="W81:X81"/>
@@ -63401,12 +63407,6 @@
     <mergeCell ref="K80:M81"/>
     <mergeCell ref="K82:M82"/>
     <mergeCell ref="K83:M83"/>
-    <mergeCell ref="W84:X84"/>
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="K108:M113"/>
-    <mergeCell ref="K106:M106"/>
-    <mergeCell ref="K107:M107"/>
-    <mergeCell ref="K84:M105"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <conditionalFormatting sqref="A3:A40">
@@ -63619,7 +63619,7 @@
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B4" s="194">
         <v>0.875</v>
@@ -63628,16 +63628,16 @@
         <v>110</v>
       </c>
       <c r="D4" t="s">
+        <v>476</v>
+      </c>
+      <c r="E4" t="s">
         <v>477</v>
-      </c>
-      <c r="E4" t="s">
-        <v>478</v>
       </c>
       <c r="F4" t="s">
         <v>469</v>
       </c>
       <c r="G4" s="194" t="s">
-        <v>476</v>
+        <v>489</v>
       </c>
       <c r="H4" t="s">
         <v>4</v>
@@ -64057,7 +64057,7 @@
         <v>5</v>
       </c>
       <c r="T16" s="195" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="U16" s="195">
         <v>4</v>
@@ -64217,7 +64217,7 @@
         <v>7</v>
       </c>
       <c r="T21" s="195" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="U21" s="195">
         <v>1</v>
@@ -64249,7 +64249,7 @@
         <v>10</v>
       </c>
       <c r="T22" s="195" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="U22" s="195">
         <v>0</v>
@@ -64541,23 +64541,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="204" t="s">
+      <c r="A1" s="208" t="s">
         <v>46</v>
       </c>
       <c r="B1" s="327"/>
       <c r="C1" s="328" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="207"/>
+      <c r="D1" s="211"/>
       <c r="E1" s="329"/>
-      <c r="H1" s="204" t="s">
+      <c r="H1" s="208" t="s">
         <v>47</v>
       </c>
       <c r="I1" s="327"/>
       <c r="J1" s="328" t="s">
         <v>44</v>
       </c>
-      <c r="K1" s="207"/>
+      <c r="K1" s="211"/>
       <c r="L1" s="329"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -65646,9 +65646,9 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="208"/>
-      <c r="G1" s="208"/>
-      <c r="H1" s="208"/>
+      <c r="F1" s="212"/>
+      <c r="G1" s="212"/>
+      <c r="H1" s="212"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -65672,36 +65672,36 @@
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="5"/>
-      <c r="E2" s="204" t="s">
+      <c r="E2" s="208" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="205"/>
-      <c r="G2" s="206"/>
-      <c r="H2" s="209" t="s">
+      <c r="F2" s="209"/>
+      <c r="G2" s="210"/>
+      <c r="H2" s="213" t="s">
         <v>120</v>
       </c>
-      <c r="I2" s="210"/>
-      <c r="J2" s="211"/>
-      <c r="K2" s="204" t="s">
+      <c r="I2" s="214"/>
+      <c r="J2" s="215"/>
+      <c r="K2" s="208" t="s">
         <v>108</v>
       </c>
-      <c r="L2" s="205"/>
-      <c r="M2" s="206"/>
-      <c r="N2" s="209" t="s">
+      <c r="L2" s="209"/>
+      <c r="M2" s="210"/>
+      <c r="N2" s="213" t="s">
         <v>110</v>
       </c>
-      <c r="O2" s="210"/>
-      <c r="P2" s="211"/>
-      <c r="Q2" s="204" t="s">
+      <c r="O2" s="214"/>
+      <c r="P2" s="215"/>
+      <c r="Q2" s="208" t="s">
         <v>39</v>
       </c>
-      <c r="R2" s="205"/>
-      <c r="S2" s="206"/>
-      <c r="T2" s="207" t="s">
+      <c r="R2" s="209"/>
+      <c r="S2" s="210"/>
+      <c r="T2" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="U2" s="207"/>
-      <c r="V2" s="207"/>
+      <c r="U2" s="211"/>
+      <c r="V2" s="211"/>
       <c r="Z2" s="125">
         <v>46279</v>
       </c>
@@ -68799,30 +68799,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="214" t="s">
+      <c r="D2" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="214"/>
-      <c r="F2" s="215" t="s">
+      <c r="E2" s="206"/>
+      <c r="F2" s="207" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="215"/>
-      <c r="H2" s="214" t="s">
+      <c r="G2" s="207"/>
+      <c r="H2" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="214"/>
-      <c r="J2" s="215" t="s">
+      <c r="I2" s="206"/>
+      <c r="J2" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="215"/>
-      <c r="L2" s="214" t="s">
+      <c r="K2" s="207"/>
+      <c r="L2" s="206" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="214"/>
-      <c r="N2" s="207" t="s">
+      <c r="M2" s="206"/>
+      <c r="N2" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="207"/>
+      <c r="O2" s="211"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -70819,30 +70819,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="214" t="s">
+      <c r="D2" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="214"/>
-      <c r="F2" s="215" t="s">
+      <c r="E2" s="206"/>
+      <c r="F2" s="207" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="215"/>
-      <c r="H2" s="214" t="s">
+      <c r="G2" s="207"/>
+      <c r="H2" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="214"/>
-      <c r="J2" s="215" t="s">
+      <c r="I2" s="206"/>
+      <c r="J2" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="215"/>
-      <c r="L2" s="214" t="s">
+      <c r="K2" s="207"/>
+      <c r="L2" s="206" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="214"/>
-      <c r="N2" s="207" t="s">
+      <c r="M2" s="206"/>
+      <c r="N2" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="207"/>
+      <c r="O2" s="211"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -72776,30 +72776,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="214" t="s">
+      <c r="D2" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="214"/>
-      <c r="F2" s="215" t="s">
+      <c r="E2" s="206"/>
+      <c r="F2" s="207" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="215"/>
-      <c r="H2" s="214" t="s">
+      <c r="G2" s="207"/>
+      <c r="H2" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="214"/>
-      <c r="J2" s="215" t="s">
+      <c r="I2" s="206"/>
+      <c r="J2" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="215"/>
-      <c r="L2" s="214" t="s">
+      <c r="K2" s="207"/>
+      <c r="L2" s="206" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="214"/>
-      <c r="N2" s="207" t="s">
+      <c r="M2" s="206"/>
+      <c r="N2" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="207"/>
+      <c r="O2" s="211"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -74824,30 +74824,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="214" t="s">
+      <c r="D2" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="214"/>
-      <c r="F2" s="215" t="s">
+      <c r="E2" s="206"/>
+      <c r="F2" s="207" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="215"/>
-      <c r="H2" s="214" t="s">
+      <c r="G2" s="207"/>
+      <c r="H2" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="214"/>
-      <c r="J2" s="215" t="s">
+      <c r="I2" s="206"/>
+      <c r="J2" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="215"/>
-      <c r="L2" s="214" t="s">
+      <c r="K2" s="207"/>
+      <c r="L2" s="206" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="214"/>
-      <c r="N2" s="207" t="s">
+      <c r="M2" s="206"/>
+      <c r="N2" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="207"/>
+      <c r="O2" s="211"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -76532,30 +76532,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="214" t="s">
+      <c r="C2" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="214"/>
-      <c r="E2" s="215" t="s">
+      <c r="D2" s="206"/>
+      <c r="E2" s="207" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="215"/>
-      <c r="G2" s="214" t="s">
+      <c r="F2" s="207"/>
+      <c r="G2" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="214"/>
-      <c r="I2" s="215" t="s">
+      <c r="H2" s="206"/>
+      <c r="I2" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="215"/>
-      <c r="K2" s="214" t="s">
+      <c r="J2" s="207"/>
+      <c r="K2" s="206" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="214"/>
-      <c r="M2" s="207" t="s">
+      <c r="L2" s="206"/>
+      <c r="M2" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="207"/>
+      <c r="N2" s="211"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -78317,30 +78317,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="214" t="s">
+      <c r="C2" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="214"/>
-      <c r="E2" s="215" t="s">
+      <c r="D2" s="206"/>
+      <c r="E2" s="207" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="215"/>
-      <c r="G2" s="214" t="s">
+      <c r="F2" s="207"/>
+      <c r="G2" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="214"/>
-      <c r="I2" s="215" t="s">
+      <c r="H2" s="206"/>
+      <c r="I2" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="215"/>
-      <c r="K2" s="214" t="s">
+      <c r="J2" s="207"/>
+      <c r="K2" s="206" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="214"/>
-      <c r="M2" s="207" t="s">
+      <c r="L2" s="206"/>
+      <c r="M2" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="207"/>
+      <c r="N2" s="211"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">

--- a/data/arsenal_stats.xlsx
+++ b/data/arsenal_stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bungeltd-my.sharepoint.com/personal/przemyslaw_iskra_bunge_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8388" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2E09124-C46D-4E05-A65A-81AB73ECD1AD}"/>
+  <xr:revisionPtr revIDLastSave="8392" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30DF1CB7-8C1D-4B59-A433-5989109A5895}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="799" firstSheet="1" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="799" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="19" state="hidden" r:id="rId1"/>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2264" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2262" uniqueCount="490">
   <si>
     <t>Arsenal FC squad statistics</t>
   </si>
@@ -3074,6 +3074,9 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3110,6 +3113,15 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3119,23 +3131,23 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="54" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3173,15 +3185,6 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="28" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3189,27 +3192,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="61" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="10" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="37" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="11" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3302,67 +3284,31 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="61" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="10" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="37" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="11" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="54" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3440,8 +3386,62 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6493,7 +6493,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{BB3DF284-8977-4D0E-A388-4CA2D4E5D595}" type="CELLRANGE">
+                    <a:fld id="{5D96109F-4A76-432F-A89A-18B87646FEEC}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6527,7 +6527,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D9BEABE1-FBB5-406B-88A6-B8957D4A7E74}" type="CELLRANGE">
+                    <a:fld id="{AC425F20-EDB6-42E6-8CB8-C79B16371CAB}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6561,7 +6561,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D0B6C236-4C80-4E41-A6DF-21C992B43354}" type="CELLRANGE">
+                    <a:fld id="{1068D143-79BF-4D8A-BDED-741E1C51E790}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6595,7 +6595,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{3EF0DD40-EFE4-4D7F-9C17-65795F40D894}" type="CELLRANGE">
+                    <a:fld id="{8CA1B0DF-2C6F-4331-B26D-EDB3114157A9}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6629,7 +6629,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7FCE7825-46A3-43C2-958A-918993DD392E}" type="CELLRANGE">
+                    <a:fld id="{B0D9E227-37AD-4F7D-9726-9CB678B444A6}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6663,7 +6663,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F508AC7A-C0FA-4BD9-BBBF-1685F2D06A88}" type="CELLRANGE">
+                    <a:fld id="{74EF0BCB-AD28-4391-8573-15BABAB996A9}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6697,7 +6697,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{36068BF5-2D80-44DE-8E9B-A2DD94960B81}" type="CELLRANGE">
+                    <a:fld id="{5F8A5D57-0FFE-4609-B4D3-C1EF7EE4072C}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6731,7 +6731,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6996FFC1-AC10-4187-8BBB-5F27E452C914}" type="CELLRANGE">
+                    <a:fld id="{7F848CD0-8391-4EEF-B946-8D201583075D}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6765,7 +6765,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{EE431FA8-F1C3-40D9-AEFD-FCB21E04C1C9}" type="CELLRANGE">
+                    <a:fld id="{0D0AFC80-1229-4BA5-9C79-F401B23081D8}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6799,7 +6799,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E335A5E4-4730-4095-9040-D3E22236C5BC}" type="CELLRANGE">
+                    <a:fld id="{C5B698B3-74F6-425F-94F0-F6B8048A61AE}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6833,7 +6833,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{DCE1C669-4834-4E7D-9E1B-BED3447BCAD6}" type="CELLRANGE">
+                    <a:fld id="{9A20BC0B-B1AE-40B8-B386-C748127ACEA8}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6867,7 +6867,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{35FB4F2A-04C2-465B-9416-6CB6DD1253D0}" type="CELLRANGE">
+                    <a:fld id="{3F478EFB-0FD1-40DF-9154-49D92AC831BF}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6916,7 +6916,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{EE764AB6-4305-4828-94A8-9B95879D5F1D}" type="CELLRANGE">
+                    <a:fld id="{9B49C8CC-E8DD-4F0E-AB28-B2DA9A06F46B}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr>
                         <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
@@ -6975,7 +6975,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A040585C-2CC7-4BD0-86A4-28D6901B8367}" type="CELLRANGE">
+                    <a:fld id="{57BDA9D0-27AF-48AC-BA96-D30CE82204C2}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7009,7 +7009,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{32697F90-0B0B-4B0F-9657-EF72A254F8D1}" type="CELLRANGE">
+                    <a:fld id="{DE282D94-5E23-433C-A4E7-5E90DC5F78AA}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7043,7 +7043,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{106266EB-0BF2-4EB4-B030-9B6FEFBD745F}" type="CELLRANGE">
+                    <a:fld id="{EB7844CD-AAF0-49CC-AE1D-F636752A14FE}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7077,7 +7077,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9AA35086-7D36-4DEA-A1C5-9D7BA6A67A60}" type="CELLRANGE">
+                    <a:fld id="{4A33E9F6-DD20-4C92-B191-CCAD0E64DF6B}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7884,10 +7884,10 @@
                   <c:v>1.7142857142857142</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.8235294117647058</c:v>
+                  <c:v>1.8571428571428572</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.1470588235294117</c:v>
+                  <c:v>2.1714285714285713</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>2.1176470588235294</c:v>
@@ -14213,30 +14213,30 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
       <c r="B1" s="5"/>
-      <c r="C1" s="206" t="s">
+      <c r="C1" s="207" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="206"/>
-      <c r="E1" s="207" t="s">
+      <c r="D1" s="207"/>
+      <c r="E1" s="208" t="s">
         <v>120</v>
       </c>
-      <c r="F1" s="207"/>
-      <c r="G1" s="206" t="s">
+      <c r="F1" s="208"/>
+      <c r="G1" s="207" t="s">
         <v>108</v>
       </c>
-      <c r="H1" s="206"/>
-      <c r="I1" s="207" t="s">
+      <c r="H1" s="207"/>
+      <c r="I1" s="208" t="s">
         <v>110</v>
       </c>
-      <c r="J1" s="207"/>
-      <c r="K1" s="206" t="s">
+      <c r="J1" s="208"/>
+      <c r="K1" s="207" t="s">
         <v>39</v>
       </c>
-      <c r="L1" s="206"/>
-      <c r="M1" s="204" t="s">
+      <c r="L1" s="207"/>
+      <c r="M1" s="205" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="205"/>
+      <c r="N1" s="206"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -15943,30 +15943,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="206" t="s">
+      <c r="C2" s="207" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="206"/>
-      <c r="E2" s="207" t="s">
+      <c r="D2" s="207"/>
+      <c r="E2" s="208" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="207"/>
-      <c r="G2" s="206" t="s">
+      <c r="F2" s="208"/>
+      <c r="G2" s="207" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="206"/>
-      <c r="I2" s="207" t="s">
+      <c r="H2" s="207"/>
+      <c r="I2" s="208" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="207"/>
-      <c r="K2" s="206" t="s">
+      <c r="J2" s="208"/>
+      <c r="K2" s="207" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="206"/>
-      <c r="M2" s="211" t="s">
+      <c r="L2" s="207"/>
+      <c r="M2" s="212" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="211"/>
+      <c r="N2" s="212"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -17770,30 +17770,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="206" t="s">
+      <c r="C2" s="207" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="206"/>
-      <c r="E2" s="207" t="s">
+      <c r="D2" s="207"/>
+      <c r="E2" s="208" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="207"/>
-      <c r="G2" s="206" t="s">
+      <c r="F2" s="208"/>
+      <c r="G2" s="207" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="206"/>
-      <c r="I2" s="207" t="s">
+      <c r="H2" s="207"/>
+      <c r="I2" s="208" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="207"/>
-      <c r="K2" s="206" t="s">
+      <c r="J2" s="208"/>
+      <c r="K2" s="207" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="206"/>
-      <c r="M2" s="211" t="s">
+      <c r="L2" s="207"/>
+      <c r="M2" s="212" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="211"/>
+      <c r="N2" s="212"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -19460,30 +19460,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="206" t="s">
+      <c r="C2" s="207" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="206"/>
-      <c r="E2" s="207" t="s">
+      <c r="D2" s="207"/>
+      <c r="E2" s="208" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="207"/>
-      <c r="G2" s="206" t="s">
+      <c r="F2" s="208"/>
+      <c r="G2" s="207" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="206"/>
-      <c r="I2" s="207" t="s">
+      <c r="H2" s="207"/>
+      <c r="I2" s="208" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="207"/>
-      <c r="K2" s="206" t="s">
+      <c r="J2" s="208"/>
+      <c r="K2" s="207" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="206"/>
-      <c r="M2" s="211" t="s">
+      <c r="L2" s="207"/>
+      <c r="M2" s="212" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="211"/>
+      <c r="N2" s="212"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -21286,30 +21286,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="206" t="s">
+      <c r="C2" s="207" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="206"/>
-      <c r="E2" s="207" t="s">
+      <c r="D2" s="207"/>
+      <c r="E2" s="208" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="207"/>
-      <c r="G2" s="206" t="s">
+      <c r="F2" s="208"/>
+      <c r="G2" s="207" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="206"/>
-      <c r="I2" s="207" t="s">
+      <c r="H2" s="207"/>
+      <c r="I2" s="208" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="207"/>
-      <c r="K2" s="206" t="s">
+      <c r="J2" s="208"/>
+      <c r="K2" s="207" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="206"/>
-      <c r="M2" s="211" t="s">
+      <c r="L2" s="207"/>
+      <c r="M2" s="212" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="211"/>
+      <c r="N2" s="212"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -23158,36 +23158,36 @@
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="208" t="s">
+      <c r="C2" s="209" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="209"/>
-      <c r="E2" s="210"/>
-      <c r="F2" s="213" t="s">
+      <c r="D2" s="210"/>
+      <c r="E2" s="211"/>
+      <c r="F2" s="214" t="s">
         <v>120</v>
       </c>
-      <c r="G2" s="214"/>
-      <c r="H2" s="215"/>
-      <c r="I2" s="208" t="s">
+      <c r="G2" s="215"/>
+      <c r="H2" s="216"/>
+      <c r="I2" s="209" t="s">
         <v>108</v>
       </c>
-      <c r="J2" s="209"/>
-      <c r="K2" s="210"/>
-      <c r="L2" s="213" t="s">
+      <c r="J2" s="210"/>
+      <c r="K2" s="211"/>
+      <c r="L2" s="214" t="s">
         <v>110</v>
       </c>
-      <c r="M2" s="214"/>
-      <c r="N2" s="215"/>
-      <c r="O2" s="208" t="s">
+      <c r="M2" s="215"/>
+      <c r="N2" s="216"/>
+      <c r="O2" s="209" t="s">
         <v>39</v>
       </c>
-      <c r="P2" s="209"/>
-      <c r="Q2" s="210"/>
-      <c r="R2" s="211" t="s">
+      <c r="P2" s="210"/>
+      <c r="Q2" s="211"/>
+      <c r="R2" s="212" t="s">
         <v>7</v>
       </c>
-      <c r="S2" s="211"/>
-      <c r="T2" s="211"/>
+      <c r="S2" s="212"/>
+      <c r="T2" s="212"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -26046,36 +26046,36 @@
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
       <c r="D1" s="5"/>
-      <c r="E1" s="208" t="s">
+      <c r="E1" s="209" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="209"/>
-      <c r="G1" s="210"/>
-      <c r="H1" s="213" t="s">
+      <c r="F1" s="210"/>
+      <c r="G1" s="211"/>
+      <c r="H1" s="214" t="s">
         <v>120</v>
       </c>
-      <c r="I1" s="214"/>
-      <c r="J1" s="215"/>
-      <c r="K1" s="208" t="s">
+      <c r="I1" s="215"/>
+      <c r="J1" s="216"/>
+      <c r="K1" s="209" t="s">
         <v>108</v>
       </c>
-      <c r="L1" s="209"/>
-      <c r="M1" s="210"/>
-      <c r="N1" s="213" t="s">
+      <c r="L1" s="210"/>
+      <c r="M1" s="211"/>
+      <c r="N1" s="214" t="s">
         <v>110</v>
       </c>
-      <c r="O1" s="214"/>
-      <c r="P1" s="215"/>
-      <c r="Q1" s="208" t="s">
+      <c r="O1" s="215"/>
+      <c r="P1" s="216"/>
+      <c r="Q1" s="209" t="s">
         <v>39</v>
       </c>
-      <c r="R1" s="209"/>
-      <c r="S1" s="210"/>
-      <c r="T1" s="211" t="s">
+      <c r="R1" s="210"/>
+      <c r="S1" s="211"/>
+      <c r="T1" s="212" t="s">
         <v>7</v>
       </c>
-      <c r="U1" s="211"/>
-      <c r="V1" s="211"/>
+      <c r="U1" s="212"/>
+      <c r="V1" s="212"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -37649,399 +37649,399 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F1" s="216">
-        <v>1</v>
-      </c>
-      <c r="G1" s="217"/>
-      <c r="H1" s="218"/>
-      <c r="I1" s="216">
+      <c r="F1" s="220">
+        <v>1</v>
+      </c>
+      <c r="G1" s="221"/>
+      <c r="H1" s="222"/>
+      <c r="I1" s="220">
         <v>2</v>
       </c>
-      <c r="J1" s="217"/>
-      <c r="K1" s="218"/>
-      <c r="L1" s="216">
-        <v>3</v>
-      </c>
-      <c r="M1" s="217"/>
-      <c r="N1" s="218"/>
-      <c r="O1" s="216">
+      <c r="J1" s="221"/>
+      <c r="K1" s="222"/>
+      <c r="L1" s="220">
+        <v>3</v>
+      </c>
+      <c r="M1" s="221"/>
+      <c r="N1" s="222"/>
+      <c r="O1" s="220">
         <v>4</v>
       </c>
-      <c r="P1" s="217"/>
-      <c r="Q1" s="218"/>
-      <c r="R1" s="216">
+      <c r="P1" s="221"/>
+      <c r="Q1" s="222"/>
+      <c r="R1" s="220">
         <v>5</v>
       </c>
-      <c r="S1" s="217"/>
-      <c r="T1" s="218"/>
-      <c r="U1" s="216">
+      <c r="S1" s="221"/>
+      <c r="T1" s="222"/>
+      <c r="U1" s="220">
         <v>6</v>
       </c>
-      <c r="V1" s="217"/>
-      <c r="W1" s="218"/>
-      <c r="X1" s="216">
+      <c r="V1" s="221"/>
+      <c r="W1" s="222"/>
+      <c r="X1" s="220">
         <v>7</v>
       </c>
-      <c r="Y1" s="217"/>
-      <c r="Z1" s="218"/>
-      <c r="AA1" s="216">
+      <c r="Y1" s="221"/>
+      <c r="Z1" s="222"/>
+      <c r="AA1" s="220">
         <v>8</v>
       </c>
-      <c r="AB1" s="217"/>
-      <c r="AC1" s="218"/>
-      <c r="AD1" s="216">
+      <c r="AB1" s="221"/>
+      <c r="AC1" s="222"/>
+      <c r="AD1" s="220">
         <v>9</v>
       </c>
-      <c r="AE1" s="217"/>
-      <c r="AF1" s="218"/>
-      <c r="AG1" s="216">
+      <c r="AE1" s="221"/>
+      <c r="AF1" s="222"/>
+      <c r="AG1" s="220">
         <v>10</v>
       </c>
-      <c r="AH1" s="217"/>
-      <c r="AI1" s="218"/>
-      <c r="AJ1" s="216">
+      <c r="AH1" s="221"/>
+      <c r="AI1" s="222"/>
+      <c r="AJ1" s="220">
         <v>11</v>
       </c>
-      <c r="AK1" s="217"/>
-      <c r="AL1" s="218"/>
-      <c r="AM1" s="216">
+      <c r="AK1" s="221"/>
+      <c r="AL1" s="222"/>
+      <c r="AM1" s="220">
         <v>12</v>
       </c>
-      <c r="AN1" s="217"/>
-      <c r="AO1" s="218"/>
-      <c r="AP1" s="216">
+      <c r="AN1" s="221"/>
+      <c r="AO1" s="222"/>
+      <c r="AP1" s="220">
         <v>13</v>
       </c>
-      <c r="AQ1" s="217"/>
-      <c r="AR1" s="218"/>
-      <c r="AS1" s="216">
+      <c r="AQ1" s="221"/>
+      <c r="AR1" s="222"/>
+      <c r="AS1" s="220">
         <v>14</v>
       </c>
-      <c r="AT1" s="217"/>
-      <c r="AU1" s="218"/>
-      <c r="AV1" s="216">
+      <c r="AT1" s="221"/>
+      <c r="AU1" s="222"/>
+      <c r="AV1" s="220">
         <v>15</v>
       </c>
-      <c r="AW1" s="217"/>
-      <c r="AX1" s="218"/>
-      <c r="AY1" s="216">
+      <c r="AW1" s="221"/>
+      <c r="AX1" s="222"/>
+      <c r="AY1" s="220">
         <v>16</v>
       </c>
-      <c r="AZ1" s="217"/>
-      <c r="BA1" s="218"/>
-      <c r="BB1" s="216">
+      <c r="AZ1" s="221"/>
+      <c r="BA1" s="222"/>
+      <c r="BB1" s="220">
         <v>17</v>
       </c>
-      <c r="BC1" s="217"/>
-      <c r="BD1" s="218"/>
-      <c r="BE1" s="216">
+      <c r="BC1" s="221"/>
+      <c r="BD1" s="222"/>
+      <c r="BE1" s="220">
         <v>18</v>
       </c>
-      <c r="BF1" s="217"/>
-      <c r="BG1" s="218"/>
-      <c r="BH1" s="216">
+      <c r="BF1" s="221"/>
+      <c r="BG1" s="222"/>
+      <c r="BH1" s="220">
         <v>19</v>
       </c>
-      <c r="BI1" s="217"/>
-      <c r="BJ1" s="218"/>
-      <c r="BK1" s="216">
+      <c r="BI1" s="221"/>
+      <c r="BJ1" s="222"/>
+      <c r="BK1" s="220">
         <v>20</v>
       </c>
-      <c r="BL1" s="217"/>
-      <c r="BM1" s="218"/>
-      <c r="BN1" s="216">
+      <c r="BL1" s="221"/>
+      <c r="BM1" s="222"/>
+      <c r="BN1" s="220">
         <v>21</v>
       </c>
-      <c r="BO1" s="217"/>
-      <c r="BP1" s="218"/>
-      <c r="BQ1" s="216">
+      <c r="BO1" s="221"/>
+      <c r="BP1" s="222"/>
+      <c r="BQ1" s="220">
         <v>22</v>
       </c>
-      <c r="BR1" s="217"/>
-      <c r="BS1" s="218"/>
-      <c r="BT1" s="216">
+      <c r="BR1" s="221"/>
+      <c r="BS1" s="222"/>
+      <c r="BT1" s="220">
         <v>23</v>
       </c>
-      <c r="BU1" s="217"/>
-      <c r="BV1" s="218"/>
-      <c r="BW1" s="216">
+      <c r="BU1" s="221"/>
+      <c r="BV1" s="222"/>
+      <c r="BW1" s="220">
         <v>24</v>
       </c>
-      <c r="BX1" s="217"/>
-      <c r="BY1" s="218"/>
-      <c r="BZ1" s="216">
+      <c r="BX1" s="221"/>
+      <c r="BY1" s="222"/>
+      <c r="BZ1" s="220">
         <v>25</v>
       </c>
-      <c r="CA1" s="217"/>
-      <c r="CB1" s="218"/>
-      <c r="CC1" s="216">
+      <c r="CA1" s="221"/>
+      <c r="CB1" s="222"/>
+      <c r="CC1" s="220">
         <v>26</v>
       </c>
-      <c r="CD1" s="217"/>
-      <c r="CE1" s="218"/>
-      <c r="CF1" s="216">
+      <c r="CD1" s="221"/>
+      <c r="CE1" s="222"/>
+      <c r="CF1" s="220">
         <v>27</v>
       </c>
-      <c r="CG1" s="217"/>
-      <c r="CH1" s="218"/>
-      <c r="CI1" s="216">
+      <c r="CG1" s="221"/>
+      <c r="CH1" s="222"/>
+      <c r="CI1" s="220">
         <v>28</v>
       </c>
-      <c r="CJ1" s="217"/>
-      <c r="CK1" s="218"/>
-      <c r="CL1" s="216">
+      <c r="CJ1" s="221"/>
+      <c r="CK1" s="222"/>
+      <c r="CL1" s="220">
         <v>29</v>
       </c>
-      <c r="CM1" s="217"/>
-      <c r="CN1" s="218"/>
-      <c r="CO1" s="216">
+      <c r="CM1" s="221"/>
+      <c r="CN1" s="222"/>
+      <c r="CO1" s="220">
         <v>30</v>
       </c>
-      <c r="CP1" s="217"/>
-      <c r="CQ1" s="218"/>
-      <c r="CR1" s="216">
+      <c r="CP1" s="221"/>
+      <c r="CQ1" s="222"/>
+      <c r="CR1" s="220">
         <v>31</v>
       </c>
-      <c r="CS1" s="217"/>
-      <c r="CT1" s="218"/>
-      <c r="CU1" s="216">
+      <c r="CS1" s="221"/>
+      <c r="CT1" s="222"/>
+      <c r="CU1" s="220">
         <v>32</v>
       </c>
-      <c r="CV1" s="217"/>
-      <c r="CW1" s="218"/>
-      <c r="CX1" s="216">
+      <c r="CV1" s="221"/>
+      <c r="CW1" s="222"/>
+      <c r="CX1" s="220">
         <v>33</v>
       </c>
-      <c r="CY1" s="217"/>
-      <c r="CZ1" s="218"/>
-      <c r="DA1" s="216">
+      <c r="CY1" s="221"/>
+      <c r="CZ1" s="222"/>
+      <c r="DA1" s="220">
         <v>34</v>
       </c>
-      <c r="DB1" s="217"/>
-      <c r="DC1" s="218"/>
-      <c r="DD1" s="216">
+      <c r="DB1" s="221"/>
+      <c r="DC1" s="222"/>
+      <c r="DD1" s="220">
         <v>35</v>
       </c>
-      <c r="DE1" s="217"/>
-      <c r="DF1" s="218"/>
-      <c r="DG1" s="216">
+      <c r="DE1" s="221"/>
+      <c r="DF1" s="222"/>
+      <c r="DG1" s="220">
         <v>36</v>
       </c>
-      <c r="DH1" s="217"/>
-      <c r="DI1" s="218"/>
-      <c r="DJ1" s="216">
+      <c r="DH1" s="221"/>
+      <c r="DI1" s="222"/>
+      <c r="DJ1" s="220">
         <v>37</v>
       </c>
-      <c r="DK1" s="217"/>
-      <c r="DL1" s="218"/>
-      <c r="DM1" s="216">
+      <c r="DK1" s="221"/>
+      <c r="DL1" s="222"/>
+      <c r="DM1" s="220">
         <v>38</v>
       </c>
-      <c r="DN1" s="217"/>
-      <c r="DO1" s="218"/>
+      <c r="DN1" s="221"/>
+      <c r="DO1" s="222"/>
     </row>
     <row r="2" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="222" t="s">
+      <c r="C2" s="223" t="s">
         <v>396</v>
       </c>
-      <c r="D2" s="222" t="s">
+      <c r="D2" s="223" t="s">
         <v>397</v>
       </c>
-      <c r="E2" s="222" t="s">
+      <c r="E2" s="223" t="s">
         <v>398</v>
       </c>
-      <c r="F2" s="219" t="s">
+      <c r="F2" s="217" t="s">
         <v>346</v>
       </c>
-      <c r="G2" s="220"/>
-      <c r="H2" s="221"/>
-      <c r="I2" s="219" t="s">
+      <c r="G2" s="218"/>
+      <c r="H2" s="219"/>
+      <c r="I2" s="217" t="s">
         <v>331</v>
       </c>
-      <c r="J2" s="220"/>
-      <c r="K2" s="221"/>
-      <c r="L2" s="219" t="s">
+      <c r="J2" s="218"/>
+      <c r="K2" s="219"/>
+      <c r="L2" s="217" t="s">
         <v>330</v>
       </c>
-      <c r="M2" s="220"/>
-      <c r="N2" s="221"/>
-      <c r="O2" s="219" t="s">
+      <c r="M2" s="218"/>
+      <c r="N2" s="219"/>
+      <c r="O2" s="217" t="s">
         <v>328</v>
       </c>
-      <c r="P2" s="220"/>
-      <c r="Q2" s="221"/>
-      <c r="R2" s="219" t="s">
+      <c r="P2" s="218"/>
+      <c r="Q2" s="219"/>
+      <c r="R2" s="217" t="s">
         <v>335</v>
       </c>
-      <c r="S2" s="220"/>
-      <c r="T2" s="221"/>
-      <c r="U2" s="219" t="s">
+      <c r="S2" s="218"/>
+      <c r="T2" s="219"/>
+      <c r="U2" s="217" t="s">
         <v>320</v>
       </c>
-      <c r="V2" s="220"/>
-      <c r="W2" s="221"/>
-      <c r="X2" s="219" t="s">
+      <c r="V2" s="218"/>
+      <c r="W2" s="219"/>
+      <c r="X2" s="217" t="s">
         <v>337</v>
       </c>
-      <c r="Y2" s="220"/>
-      <c r="Z2" s="221"/>
-      <c r="AA2" s="219" t="s">
+      <c r="Y2" s="218"/>
+      <c r="Z2" s="219"/>
+      <c r="AA2" s="217" t="s">
         <v>334</v>
       </c>
-      <c r="AB2" s="220"/>
-      <c r="AC2" s="221"/>
-      <c r="AD2" s="219" t="s">
+      <c r="AB2" s="218"/>
+      <c r="AC2" s="219"/>
+      <c r="AD2" s="217" t="s">
         <v>321</v>
       </c>
-      <c r="AE2" s="220"/>
-      <c r="AF2" s="221"/>
-      <c r="AG2" s="219" t="s">
+      <c r="AE2" s="218"/>
+      <c r="AF2" s="219"/>
+      <c r="AG2" s="217" t="s">
         <v>347</v>
       </c>
-      <c r="AH2" s="220"/>
-      <c r="AI2" s="221"/>
-      <c r="AJ2" s="219" t="s">
+      <c r="AH2" s="218"/>
+      <c r="AI2" s="219"/>
+      <c r="AJ2" s="217" t="s">
         <v>324</v>
       </c>
-      <c r="AK2" s="220"/>
-      <c r="AL2" s="221"/>
-      <c r="AM2" s="219" t="s">
+      <c r="AK2" s="218"/>
+      <c r="AL2" s="219"/>
+      <c r="AM2" s="217" t="s">
         <v>323</v>
       </c>
-      <c r="AN2" s="220"/>
-      <c r="AO2" s="221"/>
-      <c r="AP2" s="219" t="s">
+      <c r="AN2" s="218"/>
+      <c r="AO2" s="219"/>
+      <c r="AP2" s="217" t="s">
         <v>332</v>
       </c>
-      <c r="AQ2" s="220"/>
-      <c r="AR2" s="221"/>
-      <c r="AS2" s="219" t="s">
+      <c r="AQ2" s="218"/>
+      <c r="AR2" s="219"/>
+      <c r="AS2" s="217" t="s">
         <v>329</v>
       </c>
-      <c r="AT2" s="220"/>
-      <c r="AU2" s="221"/>
-      <c r="AV2" s="219" t="s">
+      <c r="AT2" s="218"/>
+      <c r="AU2" s="219"/>
+      <c r="AV2" s="217" t="s">
         <v>336</v>
       </c>
-      <c r="AW2" s="220"/>
-      <c r="AX2" s="221"/>
-      <c r="AY2" s="219" t="s">
+      <c r="AW2" s="218"/>
+      <c r="AX2" s="219"/>
+      <c r="AY2" s="217" t="s">
         <v>305</v>
       </c>
-      <c r="AZ2" s="220"/>
-      <c r="BA2" s="221"/>
-      <c r="BB2" s="219" t="s">
+      <c r="AZ2" s="218"/>
+      <c r="BA2" s="219"/>
+      <c r="BB2" s="217" t="s">
         <v>326</v>
       </c>
-      <c r="BC2" s="220"/>
-      <c r="BD2" s="221"/>
-      <c r="BE2" s="219" t="s">
+      <c r="BC2" s="218"/>
+      <c r="BD2" s="219"/>
+      <c r="BE2" s="217" t="s">
         <v>325</v>
       </c>
-      <c r="BF2" s="220"/>
-      <c r="BG2" s="221"/>
-      <c r="BH2" s="219" t="s">
+      <c r="BF2" s="218"/>
+      <c r="BG2" s="219"/>
+      <c r="BH2" s="217" t="s">
         <v>348</v>
       </c>
-      <c r="BI2" s="220"/>
-      <c r="BJ2" s="221"/>
-      <c r="BK2" s="219" t="s">
+      <c r="BI2" s="218"/>
+      <c r="BJ2" s="219"/>
+      <c r="BK2" s="217" t="s">
         <v>332</v>
       </c>
-      <c r="BL2" s="220"/>
-      <c r="BM2" s="221"/>
-      <c r="BN2" s="219" t="s">
+      <c r="BL2" s="218"/>
+      <c r="BM2" s="219"/>
+      <c r="BN2" s="217" t="s">
         <v>347</v>
       </c>
-      <c r="BO2" s="220"/>
-      <c r="BP2" s="221"/>
-      <c r="BQ2" s="219" t="s">
+      <c r="BO2" s="218"/>
+      <c r="BP2" s="219"/>
+      <c r="BQ2" s="217" t="s">
         <v>324</v>
       </c>
-      <c r="BR2" s="220"/>
-      <c r="BS2" s="221"/>
-      <c r="BT2" s="219" t="s">
+      <c r="BR2" s="218"/>
+      <c r="BS2" s="219"/>
+      <c r="BT2" s="217" t="s">
         <v>323</v>
       </c>
-      <c r="BU2" s="220"/>
-      <c r="BV2" s="221"/>
-      <c r="BW2" s="219" t="s">
+      <c r="BU2" s="218"/>
+      <c r="BV2" s="219"/>
+      <c r="BW2" s="217" t="s">
         <v>321</v>
       </c>
-      <c r="BX2" s="220"/>
-      <c r="BY2" s="221"/>
-      <c r="BZ2" s="219" t="s">
+      <c r="BX2" s="218"/>
+      <c r="BY2" s="219"/>
+      <c r="BZ2" s="217" t="s">
         <v>348</v>
       </c>
-      <c r="CA2" s="220"/>
-      <c r="CB2" s="221"/>
-      <c r="CC2" s="219" t="s">
+      <c r="CA2" s="218"/>
+      <c r="CB2" s="219"/>
+      <c r="CC2" s="217" t="s">
         <v>325</v>
       </c>
-      <c r="CD2" s="220"/>
-      <c r="CE2" s="221"/>
-      <c r="CF2" s="219" t="s">
+      <c r="CD2" s="218"/>
+      <c r="CE2" s="219"/>
+      <c r="CF2" s="217" t="s">
         <v>305</v>
       </c>
-      <c r="CG2" s="220"/>
-      <c r="CH2" s="221"/>
-      <c r="CI2" s="219" t="s">
+      <c r="CG2" s="218"/>
+      <c r="CH2" s="219"/>
+      <c r="CI2" s="217" t="s">
         <v>326</v>
       </c>
-      <c r="CJ2" s="220"/>
-      <c r="CK2" s="221"/>
-      <c r="CL2" s="219" t="s">
+      <c r="CJ2" s="218"/>
+      <c r="CK2" s="219"/>
+      <c r="CL2" s="217" t="s">
         <v>330</v>
       </c>
-      <c r="CM2" s="220"/>
-      <c r="CN2" s="221"/>
-      <c r="CO2" s="219" t="s">
+      <c r="CM2" s="218"/>
+      <c r="CN2" s="219"/>
+      <c r="CO2" s="217" t="s">
         <v>328</v>
       </c>
-      <c r="CP2" s="220"/>
-      <c r="CQ2" s="221"/>
-      <c r="CR2" s="219" t="s">
+      <c r="CP2" s="218"/>
+      <c r="CQ2" s="219"/>
+      <c r="CR2" s="217" t="s">
         <v>346</v>
       </c>
-      <c r="CS2" s="220"/>
-      <c r="CT2" s="221"/>
-      <c r="CU2" s="219" t="s">
+      <c r="CS2" s="218"/>
+      <c r="CT2" s="219"/>
+      <c r="CU2" s="217" t="s">
         <v>331</v>
       </c>
-      <c r="CV2" s="220"/>
-      <c r="CW2" s="221"/>
-      <c r="CX2" s="219" t="s">
+      <c r="CV2" s="218"/>
+      <c r="CW2" s="219"/>
+      <c r="CX2" s="217" t="s">
         <v>336</v>
       </c>
-      <c r="CY2" s="220"/>
-      <c r="CZ2" s="221"/>
-      <c r="DA2" s="219" t="s">
+      <c r="CY2" s="218"/>
+      <c r="CZ2" s="219"/>
+      <c r="DA2" s="217" t="s">
         <v>329</v>
       </c>
-      <c r="DB2" s="220"/>
-      <c r="DC2" s="221"/>
-      <c r="DD2" s="219" t="s">
+      <c r="DB2" s="218"/>
+      <c r="DC2" s="219"/>
+      <c r="DD2" s="217" t="s">
         <v>320</v>
       </c>
-      <c r="DE2" s="220"/>
-      <c r="DF2" s="221"/>
-      <c r="DG2" s="219" t="s">
+      <c r="DE2" s="218"/>
+      <c r="DF2" s="219"/>
+      <c r="DG2" s="217" t="s">
         <v>337</v>
       </c>
-      <c r="DH2" s="220"/>
-      <c r="DI2" s="221"/>
-      <c r="DJ2" s="219" t="s">
+      <c r="DH2" s="218"/>
+      <c r="DI2" s="219"/>
+      <c r="DJ2" s="217" t="s">
         <v>334</v>
       </c>
-      <c r="DK2" s="220"/>
-      <c r="DL2" s="221"/>
-      <c r="DM2" s="219" t="s">
+      <c r="DK2" s="218"/>
+      <c r="DL2" s="219"/>
+      <c r="DM2" s="217" t="s">
         <v>335</v>
       </c>
-      <c r="DN2" s="220"/>
-      <c r="DO2" s="221"/>
+      <c r="DN2" s="218"/>
+      <c r="DO2" s="219"/>
     </row>
     <row r="3" spans="1:119" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -38052,7 +38052,7 @@
       </c>
       <c r="C3" s="224"/>
       <c r="D3" s="224"/>
-      <c r="E3" s="223"/>
+      <c r="E3" s="225"/>
       <c r="F3" s="160" t="s">
         <v>393</v>
       </c>
@@ -43573,6 +43573,69 @@
     </row>
   </sheetData>
   <mergeCells count="79">
+    <mergeCell ref="DM1:DO1"/>
+    <mergeCell ref="DM2:DO2"/>
+    <mergeCell ref="DA1:DC1"/>
+    <mergeCell ref="DA2:DC2"/>
+    <mergeCell ref="DD1:DF1"/>
+    <mergeCell ref="DD2:DF2"/>
+    <mergeCell ref="DG1:DI1"/>
+    <mergeCell ref="DG2:DI2"/>
+    <mergeCell ref="CU1:CW1"/>
+    <mergeCell ref="CU2:CW2"/>
+    <mergeCell ref="CX1:CZ1"/>
+    <mergeCell ref="CX2:CZ2"/>
+    <mergeCell ref="DJ1:DL1"/>
+    <mergeCell ref="DJ2:DL2"/>
+    <mergeCell ref="CL1:CN1"/>
+    <mergeCell ref="CL2:CN2"/>
+    <mergeCell ref="CO1:CQ1"/>
+    <mergeCell ref="CO2:CQ2"/>
+    <mergeCell ref="CR1:CT1"/>
+    <mergeCell ref="CR2:CT2"/>
+    <mergeCell ref="CC1:CE1"/>
+    <mergeCell ref="CC2:CE2"/>
+    <mergeCell ref="CF1:CH1"/>
+    <mergeCell ref="CF2:CH2"/>
+    <mergeCell ref="CI1:CK1"/>
+    <mergeCell ref="CI2:CK2"/>
+    <mergeCell ref="BT1:BV1"/>
+    <mergeCell ref="BT2:BV2"/>
+    <mergeCell ref="BW1:BY1"/>
+    <mergeCell ref="BW2:BY2"/>
+    <mergeCell ref="BZ1:CB1"/>
+    <mergeCell ref="BZ2:CB2"/>
+    <mergeCell ref="BK1:BM1"/>
+    <mergeCell ref="BK2:BM2"/>
+    <mergeCell ref="BN1:BP1"/>
+    <mergeCell ref="BN2:BP2"/>
+    <mergeCell ref="BQ1:BS1"/>
+    <mergeCell ref="BQ2:BS2"/>
+    <mergeCell ref="AS1:AU1"/>
+    <mergeCell ref="AS2:AU2"/>
+    <mergeCell ref="AV1:AX1"/>
+    <mergeCell ref="AV2:AX2"/>
+    <mergeCell ref="BH1:BJ1"/>
+    <mergeCell ref="BH2:BJ2"/>
+    <mergeCell ref="AY2:BA2"/>
+    <mergeCell ref="BB2:BD2"/>
+    <mergeCell ref="BE2:BG2"/>
+    <mergeCell ref="AJ1:AL1"/>
+    <mergeCell ref="AJ2:AL2"/>
+    <mergeCell ref="AM1:AO1"/>
+    <mergeCell ref="AM2:AO2"/>
+    <mergeCell ref="AP2:AR2"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
     <mergeCell ref="AD2:AF2"/>
     <mergeCell ref="AG2:AI2"/>
     <mergeCell ref="BB1:BD1"/>
@@ -43589,69 +43652,6 @@
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="X1:Z1"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="AJ1:AL1"/>
-    <mergeCell ref="AJ2:AL2"/>
-    <mergeCell ref="AM1:AO1"/>
-    <mergeCell ref="AM2:AO2"/>
-    <mergeCell ref="AP2:AR2"/>
-    <mergeCell ref="AS1:AU1"/>
-    <mergeCell ref="AS2:AU2"/>
-    <mergeCell ref="AV1:AX1"/>
-    <mergeCell ref="AV2:AX2"/>
-    <mergeCell ref="BH1:BJ1"/>
-    <mergeCell ref="BH2:BJ2"/>
-    <mergeCell ref="AY2:BA2"/>
-    <mergeCell ref="BB2:BD2"/>
-    <mergeCell ref="BE2:BG2"/>
-    <mergeCell ref="BK1:BM1"/>
-    <mergeCell ref="BK2:BM2"/>
-    <mergeCell ref="BN1:BP1"/>
-    <mergeCell ref="BN2:BP2"/>
-    <mergeCell ref="BQ1:BS1"/>
-    <mergeCell ref="BQ2:BS2"/>
-    <mergeCell ref="BT1:BV1"/>
-    <mergeCell ref="BT2:BV2"/>
-    <mergeCell ref="BW1:BY1"/>
-    <mergeCell ref="BW2:BY2"/>
-    <mergeCell ref="BZ1:CB1"/>
-    <mergeCell ref="BZ2:CB2"/>
-    <mergeCell ref="CC1:CE1"/>
-    <mergeCell ref="CC2:CE2"/>
-    <mergeCell ref="CF1:CH1"/>
-    <mergeCell ref="CF2:CH2"/>
-    <mergeCell ref="CI1:CK1"/>
-    <mergeCell ref="CI2:CK2"/>
-    <mergeCell ref="CL1:CN1"/>
-    <mergeCell ref="CL2:CN2"/>
-    <mergeCell ref="CO1:CQ1"/>
-    <mergeCell ref="CO2:CQ2"/>
-    <mergeCell ref="CR1:CT1"/>
-    <mergeCell ref="CR2:CT2"/>
-    <mergeCell ref="CU1:CW1"/>
-    <mergeCell ref="CU2:CW2"/>
-    <mergeCell ref="CX1:CZ1"/>
-    <mergeCell ref="CX2:CZ2"/>
-    <mergeCell ref="DJ1:DL1"/>
-    <mergeCell ref="DJ2:DL2"/>
-    <mergeCell ref="DM1:DO1"/>
-    <mergeCell ref="DM2:DO2"/>
-    <mergeCell ref="DA1:DC1"/>
-    <mergeCell ref="DA2:DC2"/>
-    <mergeCell ref="DD1:DF1"/>
-    <mergeCell ref="DD2:DF2"/>
-    <mergeCell ref="DG1:DI1"/>
-    <mergeCell ref="DG2:DI2"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:DO37">
     <cfRule type="cellIs" dxfId="18" priority="1" operator="between">
@@ -43687,138 +43687,138 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="234" t="s">
+      <c r="C1" s="238" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="234" t="s">
+      <c r="D1" s="238" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="234" t="s">
+      <c r="E1" s="238" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="225" t="s">
+      <c r="F1" s="229" t="s">
         <v>302</v>
       </c>
-      <c r="G1" s="226"/>
-      <c r="H1" s="226"/>
-      <c r="I1" s="226"/>
-      <c r="J1" s="226"/>
-      <c r="K1" s="226"/>
-      <c r="L1" s="226"/>
-      <c r="M1" s="226"/>
-      <c r="N1" s="226"/>
-      <c r="O1" s="226"/>
-      <c r="P1" s="226"/>
-      <c r="Q1" s="226"/>
-      <c r="R1" s="226"/>
-      <c r="S1" s="226"/>
-      <c r="T1" s="226"/>
-      <c r="U1" s="226"/>
-      <c r="V1" s="226"/>
-      <c r="W1" s="226"/>
-      <c r="X1" s="226"/>
-      <c r="Y1" s="226"/>
-      <c r="Z1" s="226"/>
-      <c r="AA1" s="226"/>
-      <c r="AB1" s="226"/>
-      <c r="AC1" s="227"/>
-      <c r="AD1" s="240" t="s">
+      <c r="G1" s="230"/>
+      <c r="H1" s="230"/>
+      <c r="I1" s="230"/>
+      <c r="J1" s="230"/>
+      <c r="K1" s="230"/>
+      <c r="L1" s="230"/>
+      <c r="M1" s="230"/>
+      <c r="N1" s="230"/>
+      <c r="O1" s="230"/>
+      <c r="P1" s="230"/>
+      <c r="Q1" s="230"/>
+      <c r="R1" s="230"/>
+      <c r="S1" s="230"/>
+      <c r="T1" s="230"/>
+      <c r="U1" s="230"/>
+      <c r="V1" s="230"/>
+      <c r="W1" s="230"/>
+      <c r="X1" s="230"/>
+      <c r="Y1" s="230"/>
+      <c r="Z1" s="230"/>
+      <c r="AA1" s="230"/>
+      <c r="AB1" s="230"/>
+      <c r="AC1" s="231"/>
+      <c r="AD1" s="241" t="s">
         <v>281</v>
       </c>
-      <c r="AE1" s="241"/>
-      <c r="AF1" s="241"/>
-      <c r="AG1" s="241"/>
-      <c r="AH1" s="241"/>
-      <c r="AI1" s="242"/>
-      <c r="AJ1" s="225" t="s">
+      <c r="AE1" s="242"/>
+      <c r="AF1" s="242"/>
+      <c r="AG1" s="242"/>
+      <c r="AH1" s="242"/>
+      <c r="AI1" s="243"/>
+      <c r="AJ1" s="229" t="s">
         <v>282</v>
       </c>
-      <c r="AK1" s="226"/>
-      <c r="AL1" s="226"/>
-      <c r="AM1" s="226"/>
-      <c r="AN1" s="226"/>
-      <c r="AO1" s="227"/>
-      <c r="AP1" s="228" t="s">
+      <c r="AK1" s="230"/>
+      <c r="AL1" s="230"/>
+      <c r="AM1" s="230"/>
+      <c r="AN1" s="230"/>
+      <c r="AO1" s="231"/>
+      <c r="AP1" s="232" t="s">
         <v>283</v>
       </c>
-      <c r="AQ1" s="229"/>
-      <c r="AR1" s="229"/>
-      <c r="AS1" s="229"/>
-      <c r="AT1" s="229"/>
-      <c r="AU1" s="230"/>
-      <c r="AV1" s="231" t="s">
+      <c r="AQ1" s="233"/>
+      <c r="AR1" s="233"/>
+      <c r="AS1" s="233"/>
+      <c r="AT1" s="233"/>
+      <c r="AU1" s="234"/>
+      <c r="AV1" s="235" t="s">
         <v>86</v>
       </c>
-      <c r="AW1" s="232"/>
-      <c r="AX1" s="233"/>
+      <c r="AW1" s="236"/>
+      <c r="AX1" s="237"/>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="235"/>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="237" t="s">
+      <c r="C2" s="239"/>
+      <c r="D2" s="239"/>
+      <c r="E2" s="239"/>
+      <c r="F2" s="226" t="s">
         <v>468</v>
       </c>
-      <c r="G2" s="238"/>
-      <c r="H2" s="239"/>
-      <c r="I2" s="237" t="s">
+      <c r="G2" s="227"/>
+      <c r="H2" s="228"/>
+      <c r="I2" s="226" t="s">
         <v>482</v>
       </c>
-      <c r="J2" s="238"/>
-      <c r="K2" s="239"/>
-      <c r="L2" s="237" t="s">
+      <c r="J2" s="227"/>
+      <c r="K2" s="228"/>
+      <c r="L2" s="226" t="s">
         <v>483</v>
       </c>
-      <c r="M2" s="238"/>
-      <c r="N2" s="239"/>
-      <c r="O2" s="237" t="s">
+      <c r="M2" s="227"/>
+      <c r="N2" s="228"/>
+      <c r="O2" s="226" t="s">
         <v>484</v>
       </c>
-      <c r="P2" s="238"/>
-      <c r="Q2" s="239"/>
-      <c r="R2" s="237" t="s">
+      <c r="P2" s="227"/>
+      <c r="Q2" s="228"/>
+      <c r="R2" s="226" t="s">
         <v>485</v>
       </c>
-      <c r="S2" s="238"/>
-      <c r="T2" s="239"/>
-      <c r="U2" s="237" t="s">
+      <c r="S2" s="227"/>
+      <c r="T2" s="228"/>
+      <c r="U2" s="226" t="s">
         <v>486</v>
       </c>
-      <c r="V2" s="238"/>
-      <c r="W2" s="239"/>
-      <c r="X2" s="237" t="s">
+      <c r="V2" s="227"/>
+      <c r="W2" s="228"/>
+      <c r="X2" s="226" t="s">
         <v>487</v>
       </c>
-      <c r="Y2" s="238"/>
-      <c r="Z2" s="239"/>
-      <c r="AA2" s="237" t="s">
+      <c r="Y2" s="227"/>
+      <c r="Z2" s="228"/>
+      <c r="AA2" s="226" t="s">
         <v>488</v>
       </c>
-      <c r="AB2" s="238"/>
-      <c r="AC2" s="238"/>
-      <c r="AD2" s="237"/>
-      <c r="AE2" s="238"/>
-      <c r="AF2" s="239"/>
-      <c r="AG2" s="237"/>
-      <c r="AH2" s="238"/>
-      <c r="AI2" s="239"/>
-      <c r="AJ2" s="237"/>
-      <c r="AK2" s="238"/>
-      <c r="AL2" s="239"/>
-      <c r="AM2" s="237"/>
-      <c r="AN2" s="238"/>
-      <c r="AO2" s="239"/>
-      <c r="AP2" s="237"/>
-      <c r="AQ2" s="238"/>
-      <c r="AR2" s="239"/>
-      <c r="AS2" s="237"/>
-      <c r="AT2" s="238"/>
-      <c r="AU2" s="239"/>
-      <c r="AV2" s="237"/>
-      <c r="AW2" s="238"/>
-      <c r="AX2" s="239"/>
+      <c r="AB2" s="227"/>
+      <c r="AC2" s="227"/>
+      <c r="AD2" s="226"/>
+      <c r="AE2" s="227"/>
+      <c r="AF2" s="228"/>
+      <c r="AG2" s="226"/>
+      <c r="AH2" s="227"/>
+      <c r="AI2" s="228"/>
+      <c r="AJ2" s="226"/>
+      <c r="AK2" s="227"/>
+      <c r="AL2" s="228"/>
+      <c r="AM2" s="226"/>
+      <c r="AN2" s="227"/>
+      <c r="AO2" s="228"/>
+      <c r="AP2" s="226"/>
+      <c r="AQ2" s="227"/>
+      <c r="AR2" s="228"/>
+      <c r="AS2" s="226"/>
+      <c r="AT2" s="227"/>
+      <c r="AU2" s="228"/>
+      <c r="AV2" s="226"/>
+      <c r="AW2" s="227"/>
+      <c r="AX2" s="228"/>
     </row>
     <row r="3" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -43827,9 +43827,9 @@
       <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="236"/>
-      <c r="D3" s="236"/>
-      <c r="E3" s="236"/>
+      <c r="C3" s="240"/>
+      <c r="D3" s="240"/>
+      <c r="E3" s="240"/>
       <c r="F3" s="170" t="s">
         <v>393</v>
       </c>
@@ -46396,13 +46396,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="F1:AC1"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="AJ1:AO1"/>
     <mergeCell ref="AP1:AU1"/>
     <mergeCell ref="AV1:AX1"/>
@@ -46419,6 +46412,13 @@
     <mergeCell ref="AD1:AI1"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="I2:K2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="F1:AC1"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
+    <mergeCell ref="AA2:AC2"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:AW31">
     <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
@@ -46453,70 +46453,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C1" s="234" t="s">
+      <c r="C1" s="238" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="234" t="s">
+      <c r="D1" s="238" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="234" t="s">
+      <c r="E1" s="238" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="274" t="s">
+      <c r="F1" s="268" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="275"/>
-      <c r="H1" s="276"/>
-      <c r="I1" s="277" t="s">
+      <c r="G1" s="269"/>
+      <c r="H1" s="270"/>
+      <c r="I1" s="271" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="278"/>
-      <c r="K1" s="279"/>
-      <c r="L1" s="244" t="s">
+      <c r="J1" s="272"/>
+      <c r="K1" s="273"/>
+      <c r="L1" s="275" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="245"/>
-      <c r="N1" s="246"/>
-      <c r="O1" s="247" t="s">
+      <c r="M1" s="276"/>
+      <c r="N1" s="277"/>
+      <c r="O1" s="278" t="s">
         <v>199</v>
       </c>
-      <c r="P1" s="248"/>
-      <c r="Q1" s="249"/>
-      <c r="R1" s="250" t="s">
+      <c r="P1" s="279"/>
+      <c r="Q1" s="280"/>
+      <c r="R1" s="244" t="s">
         <v>200</v>
       </c>
-      <c r="S1" s="251"/>
-      <c r="T1" s="252"/>
-      <c r="U1" s="253" t="s">
+      <c r="S1" s="245"/>
+      <c r="T1" s="246"/>
+      <c r="U1" s="247" t="s">
         <v>306</v>
       </c>
-      <c r="V1" s="254"/>
-      <c r="W1" s="255"/>
+      <c r="V1" s="248"/>
+      <c r="W1" s="249"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="235"/>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="256"/>
-      <c r="G2" s="257"/>
-      <c r="H2" s="258"/>
-      <c r="I2" s="271"/>
-      <c r="J2" s="272"/>
-      <c r="K2" s="273"/>
-      <c r="L2" s="268"/>
-      <c r="M2" s="269"/>
-      <c r="N2" s="270"/>
-      <c r="O2" s="265"/>
-      <c r="P2" s="266"/>
-      <c r="Q2" s="267"/>
-      <c r="R2" s="262"/>
-      <c r="S2" s="263"/>
-      <c r="T2" s="264"/>
-      <c r="U2" s="259"/>
-      <c r="V2" s="260"/>
-      <c r="W2" s="261"/>
+      <c r="C2" s="239"/>
+      <c r="D2" s="239"/>
+      <c r="E2" s="239"/>
+      <c r="F2" s="250"/>
+      <c r="G2" s="251"/>
+      <c r="H2" s="252"/>
+      <c r="I2" s="265"/>
+      <c r="J2" s="266"/>
+      <c r="K2" s="267"/>
+      <c r="L2" s="262"/>
+      <c r="M2" s="263"/>
+      <c r="N2" s="264"/>
+      <c r="O2" s="259"/>
+      <c r="P2" s="260"/>
+      <c r="Q2" s="261"/>
+      <c r="R2" s="256"/>
+      <c r="S2" s="257"/>
+      <c r="T2" s="258"/>
+      <c r="U2" s="253"/>
+      <c r="V2" s="254"/>
+      <c r="W2" s="255"/>
     </row>
     <row r="3" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -46525,9 +46525,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="243"/>
-      <c r="D3" s="243"/>
-      <c r="E3" s="243"/>
+      <c r="C3" s="274"/>
+      <c r="D3" s="274"/>
+      <c r="E3" s="274"/>
       <c r="F3" s="189" t="s">
         <v>393</v>
       </c>
@@ -47951,6 +47951,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="O1:Q1"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="F2:H2"/>
@@ -47961,11 +47966,6 @@
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="O1:Q1"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:W31">
     <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
@@ -54779,72 +54779,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C1" s="234" t="s">
+      <c r="C1" s="238" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="234" t="s">
+      <c r="D1" s="238" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="234" t="s">
+      <c r="E1" s="238" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="274" t="s">
+      <c r="F1" s="268" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="275"/>
-      <c r="H1" s="276"/>
-      <c r="I1" s="277" t="s">
+      <c r="G1" s="269"/>
+      <c r="H1" s="270"/>
+      <c r="I1" s="271" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="278"/>
-      <c r="K1" s="279"/>
-      <c r="L1" s="244" t="s">
+      <c r="J1" s="272"/>
+      <c r="K1" s="273"/>
+      <c r="L1" s="275" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="245"/>
-      <c r="N1" s="246"/>
-      <c r="O1" s="247" t="s">
+      <c r="M1" s="276"/>
+      <c r="N1" s="277"/>
+      <c r="O1" s="278" t="s">
         <v>199</v>
       </c>
-      <c r="P1" s="248"/>
-      <c r="Q1" s="249"/>
-      <c r="R1" s="250" t="s">
+      <c r="P1" s="279"/>
+      <c r="Q1" s="280"/>
+      <c r="R1" s="244" t="s">
         <v>200</v>
       </c>
-      <c r="S1" s="251"/>
-      <c r="T1" s="252"/>
-      <c r="U1" s="253" t="s">
+      <c r="S1" s="245"/>
+      <c r="T1" s="246"/>
+      <c r="U1" s="247" t="s">
         <v>306</v>
       </c>
-      <c r="V1" s="254"/>
-      <c r="W1" s="255"/>
+      <c r="V1" s="248"/>
+      <c r="W1" s="249"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="235"/>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="256" t="s">
+      <c r="C2" s="239"/>
+      <c r="D2" s="239"/>
+      <c r="E2" s="239"/>
+      <c r="F2" s="250" t="s">
         <v>433</v>
       </c>
-      <c r="G2" s="257"/>
-      <c r="H2" s="258"/>
-      <c r="I2" s="271"/>
-      <c r="J2" s="272"/>
-      <c r="K2" s="273"/>
-      <c r="L2" s="268"/>
-      <c r="M2" s="269"/>
-      <c r="N2" s="270"/>
-      <c r="O2" s="265"/>
-      <c r="P2" s="266"/>
-      <c r="Q2" s="267"/>
-      <c r="R2" s="262"/>
-      <c r="S2" s="263"/>
-      <c r="T2" s="264"/>
-      <c r="U2" s="259"/>
-      <c r="V2" s="260"/>
-      <c r="W2" s="261"/>
+      <c r="G2" s="251"/>
+      <c r="H2" s="252"/>
+      <c r="I2" s="265"/>
+      <c r="J2" s="266"/>
+      <c r="K2" s="267"/>
+      <c r="L2" s="262"/>
+      <c r="M2" s="263"/>
+      <c r="N2" s="264"/>
+      <c r="O2" s="259"/>
+      <c r="P2" s="260"/>
+      <c r="Q2" s="261"/>
+      <c r="R2" s="256"/>
+      <c r="S2" s="257"/>
+      <c r="T2" s="258"/>
+      <c r="U2" s="253"/>
+      <c r="V2" s="254"/>
+      <c r="W2" s="255"/>
     </row>
     <row r="3" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -54853,9 +54853,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="243"/>
-      <c r="D3" s="243"/>
-      <c r="E3" s="243"/>
+      <c r="C3" s="274"/>
+      <c r="D3" s="274"/>
+      <c r="E3" s="274"/>
       <c r="F3" s="189" t="s">
         <v>393</v>
       </c>
@@ -56279,11 +56279,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="F2:H2"/>
@@ -56294,6 +56289,11 @@
     <mergeCell ref="U2:W2"/>
     <mergeCell ref="L1:N1"/>
     <mergeCell ref="O1:Q1"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:W31">
     <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
@@ -56321,11 +56321,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C1" s="280" t="s">
+      <c r="C1" s="281" t="s">
         <v>340</v>
       </c>
-      <c r="D1" s="281"/>
-      <c r="E1" s="281"/>
+      <c r="D1" s="282"/>
+      <c r="E1" s="282"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -56789,51 +56789,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="302" t="s">
+      <c r="C1" s="284" t="s">
         <v>202</v>
       </c>
-      <c r="D1" s="303"/>
-      <c r="E1" s="303"/>
-      <c r="F1" s="303"/>
-      <c r="G1" s="303"/>
-      <c r="H1" s="303"/>
-      <c r="I1" s="304"/>
+      <c r="D1" s="285"/>
+      <c r="E1" s="285"/>
+      <c r="F1" s="285"/>
+      <c r="G1" s="285"/>
+      <c r="H1" s="285"/>
+      <c r="I1" s="286"/>
       <c r="J1" s="114" t="s">
         <v>195</v>
       </c>
       <c r="K1" s="115" t="s">
         <v>194</v>
       </c>
-      <c r="L1" s="282" t="s">
+      <c r="L1" s="308" t="s">
         <v>287</v>
       </c>
-      <c r="M1" s="287"/>
-      <c r="N1" s="287"/>
-      <c r="O1" s="287"/>
-      <c r="P1" s="287"/>
-      <c r="Q1" s="287"/>
-      <c r="R1" s="287"/>
-      <c r="S1" s="287"/>
-      <c r="T1" s="287"/>
-      <c r="U1" s="287"/>
-      <c r="V1" s="287"/>
-      <c r="W1" s="287"/>
-      <c r="X1" s="287"/>
-      <c r="Y1" s="287"/>
-      <c r="Z1" s="287"/>
-      <c r="AA1" s="287"/>
-      <c r="AB1" s="287"/>
-      <c r="AC1" s="287"/>
-      <c r="AD1" s="287"/>
-      <c r="AE1" s="287"/>
-      <c r="AF1" s="287"/>
-      <c r="AG1" s="288"/>
-      <c r="AH1" s="282" t="s">
+      <c r="M1" s="313"/>
+      <c r="N1" s="313"/>
+      <c r="O1" s="313"/>
+      <c r="P1" s="313"/>
+      <c r="Q1" s="313"/>
+      <c r="R1" s="313"/>
+      <c r="S1" s="313"/>
+      <c r="T1" s="313"/>
+      <c r="U1" s="313"/>
+      <c r="V1" s="313"/>
+      <c r="W1" s="313"/>
+      <c r="X1" s="313"/>
+      <c r="Y1" s="313"/>
+      <c r="Z1" s="313"/>
+      <c r="AA1" s="313"/>
+      <c r="AB1" s="313"/>
+      <c r="AC1" s="313"/>
+      <c r="AD1" s="313"/>
+      <c r="AE1" s="313"/>
+      <c r="AF1" s="313"/>
+      <c r="AG1" s="314"/>
+      <c r="AH1" s="308" t="s">
         <v>175</v>
       </c>
-      <c r="AI1" s="283"/>
-      <c r="AJ1" s="283"/>
-      <c r="AK1" s="284"/>
+      <c r="AI1" s="309"/>
+      <c r="AJ1" s="309"/>
+      <c r="AK1" s="310"/>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B2" s="111"/>
@@ -57174,13 +57174,13 @@
     <row r="5" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A5" s="71">
         <f>AVERAGE(C5:AK5)</f>
-        <v>1.8235294117647058</v>
+        <v>1.8571428571428572</v>
       </c>
       <c r="B5" s="110">
         <v>3</v>
       </c>
-      <c r="C5" s="123" t="s">
-        <v>181</v>
+      <c r="C5" s="123">
+        <v>3</v>
       </c>
       <c r="D5" s="123">
         <v>0</v>
@@ -57288,13 +57288,13 @@
     <row r="6" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A6" s="71">
         <f t="shared" ref="A6:A44" si="0">AVERAGE(C6:AK6)</f>
-        <v>2.1470588235294117</v>
+        <v>2.1714285714285713</v>
       </c>
       <c r="B6" s="110">
         <v>4</v>
       </c>
-      <c r="C6" s="123" t="s">
-        <v>181</v>
+      <c r="C6" s="123">
+        <v>3</v>
       </c>
       <c r="D6" s="123">
         <v>3</v>
@@ -62033,15 +62033,15 @@
         <f t="shared" ref="J80:J111" si="2">H80-I80</f>
         <v>2</v>
       </c>
-      <c r="K80" s="289" t="s">
+      <c r="K80" s="315" t="s">
         <v>435</v>
       </c>
-      <c r="L80" s="290"/>
-      <c r="M80" s="291"/>
+      <c r="L80" s="316"/>
+      <c r="M80" s="317"/>
       <c r="O80" s="133"/>
       <c r="P80" s="133"/>
-      <c r="W80" s="285"/>
-      <c r="X80" s="285"/>
+      <c r="W80" s="311"/>
+      <c r="X80" s="311"/>
       <c r="Y80" s="70" t="s">
         <v>211</v>
       </c>
@@ -62091,15 +62091,15 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K81" s="292"/>
-      <c r="L81" s="293"/>
-      <c r="M81" s="294"/>
+      <c r="K81" s="318"/>
+      <c r="L81" s="319"/>
+      <c r="M81" s="320"/>
       <c r="O81" s="133"/>
       <c r="P81" s="133"/>
-      <c r="W81" s="285" t="s">
+      <c r="W81" s="311" t="s">
         <v>209</v>
       </c>
-      <c r="X81" s="285"/>
+      <c r="X81" s="311"/>
       <c r="Y81" s="70">
         <f>COUNTIF(L3:AG40,3)</f>
         <v>481</v>
@@ -62155,17 +62155,17 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K82" s="295" t="s">
+      <c r="K82" s="321" t="s">
         <v>436</v>
       </c>
-      <c r="L82" s="296"/>
-      <c r="M82" s="297"/>
+      <c r="L82" s="322"/>
+      <c r="M82" s="323"/>
       <c r="O82" s="133"/>
       <c r="P82" s="133"/>
-      <c r="W82" s="285" t="s">
+      <c r="W82" s="311" t="s">
         <v>210</v>
       </c>
-      <c r="X82" s="285"/>
+      <c r="X82" s="311"/>
       <c r="Y82" s="70">
         <f>COUNTIF(K3:K40,3)+COUNTIF(J3:J15,3)</f>
         <v>25</v>
@@ -62221,19 +62221,20 @@
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="K83" s="298" t="s">
+      <c r="K83" s="324" t="s">
         <v>437</v>
       </c>
-      <c r="L83" s="299"/>
-      <c r="M83" s="300"/>
+      <c r="L83" s="325"/>
+      <c r="M83" s="326"/>
       <c r="O83" s="133"/>
       <c r="P83" s="133"/>
-      <c r="W83" s="286" t="s">
+      <c r="W83" s="312" t="s">
         <v>97</v>
       </c>
-      <c r="X83" s="286"/>
+      <c r="X83" s="312"/>
       <c r="Y83" s="196">
-        <v>220</v>
+        <f>223</f>
+        <v>223</v>
       </c>
       <c r="Z83" s="196">
         <v>60</v>
@@ -62243,15 +62244,15 @@
       </c>
       <c r="AC83" s="109">
         <f>Y83/SUM($Y$83:$AA$83)</f>
-        <v>0.61971830985915488</v>
+        <v>0.62290502793296088</v>
       </c>
       <c r="AD83" s="197">
         <f t="shared" ref="AD83:AE83" si="5">Z83/SUM($Y$83:$AA$83)</f>
-        <v>0.16901408450704225</v>
+        <v>0.16759776536312848</v>
       </c>
       <c r="AE83" s="197">
         <f t="shared" si="5"/>
-        <v>0.21126760563380281</v>
+        <v>0.20949720670391062</v>
       </c>
     </row>
     <row r="84" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -62284,15 +62285,15 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="K84" s="317" t="s">
+      <c r="K84" s="299" t="s">
         <v>284</v>
       </c>
-      <c r="L84" s="318"/>
-      <c r="M84" s="319"/>
+      <c r="L84" s="300"/>
+      <c r="M84" s="301"/>
       <c r="O84" s="141"/>
       <c r="P84" s="141"/>
-      <c r="W84" s="301"/>
-      <c r="X84" s="301"/>
+      <c r="W84" s="283"/>
+      <c r="X84" s="283"/>
       <c r="Y84" s="198"/>
       <c r="Z84" s="198"/>
       <c r="AA84" s="198"/>
@@ -62330,9 +62331,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K85" s="320"/>
-      <c r="L85" s="321"/>
-      <c r="M85" s="322"/>
+      <c r="K85" s="302"/>
+      <c r="L85" s="303"/>
+      <c r="M85" s="304"/>
       <c r="O85" s="141"/>
       <c r="P85" s="141"/>
     </row>
@@ -62366,9 +62367,9 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="K86" s="320"/>
-      <c r="L86" s="321"/>
-      <c r="M86" s="322"/>
+      <c r="K86" s="302"/>
+      <c r="L86" s="303"/>
+      <c r="M86" s="304"/>
       <c r="O86" s="141"/>
       <c r="P86" s="141"/>
     </row>
@@ -62402,9 +62403,9 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="K87" s="320"/>
-      <c r="L87" s="321"/>
-      <c r="M87" s="322"/>
+      <c r="K87" s="302"/>
+      <c r="L87" s="303"/>
+      <c r="M87" s="304"/>
       <c r="O87" s="141"/>
       <c r="P87" s="141"/>
     </row>
@@ -62438,9 +62439,9 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K88" s="320"/>
-      <c r="L88" s="321"/>
-      <c r="M88" s="322"/>
+      <c r="K88" s="302"/>
+      <c r="L88" s="303"/>
+      <c r="M88" s="304"/>
       <c r="O88" s="141"/>
       <c r="P88" s="141"/>
     </row>
@@ -62474,9 +62475,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K89" s="320"/>
-      <c r="L89" s="321"/>
-      <c r="M89" s="322"/>
+      <c r="K89" s="302"/>
+      <c r="L89" s="303"/>
+      <c r="M89" s="304"/>
       <c r="O89" s="141"/>
       <c r="P89" s="141"/>
     </row>
@@ -62510,9 +62511,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K90" s="320"/>
-      <c r="L90" s="321"/>
-      <c r="M90" s="322"/>
+      <c r="K90" s="302"/>
+      <c r="L90" s="303"/>
+      <c r="M90" s="304"/>
       <c r="O90" s="141"/>
       <c r="P90" s="141"/>
     </row>
@@ -62546,9 +62547,9 @@
         <f t="shared" si="2"/>
         <v>47</v>
       </c>
-      <c r="K91" s="320"/>
-      <c r="L91" s="321"/>
-      <c r="M91" s="322"/>
+      <c r="K91" s="302"/>
+      <c r="L91" s="303"/>
+      <c r="M91" s="304"/>
       <c r="O91" s="141"/>
       <c r="P91" s="141"/>
     </row>
@@ -62582,9 +62583,9 @@
         <f t="shared" si="2"/>
         <v>51</v>
       </c>
-      <c r="K92" s="320"/>
-      <c r="L92" s="321"/>
-      <c r="M92" s="322"/>
+      <c r="K92" s="302"/>
+      <c r="L92" s="303"/>
+      <c r="M92" s="304"/>
       <c r="O92" s="141"/>
       <c r="P92" s="141"/>
     </row>
@@ -62618,9 +62619,9 @@
         <f t="shared" si="2"/>
         <v>37</v>
       </c>
-      <c r="K93" s="320"/>
-      <c r="L93" s="321"/>
-      <c r="M93" s="322"/>
+      <c r="K93" s="302"/>
+      <c r="L93" s="303"/>
+      <c r="M93" s="304"/>
       <c r="O93" s="141"/>
       <c r="P93" s="141"/>
     </row>
@@ -62654,9 +62655,9 @@
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="K94" s="320"/>
-      <c r="L94" s="321"/>
-      <c r="M94" s="322"/>
+      <c r="K94" s="302"/>
+      <c r="L94" s="303"/>
+      <c r="M94" s="304"/>
       <c r="O94" s="141"/>
       <c r="P94" s="141"/>
     </row>
@@ -62690,9 +62691,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K95" s="320"/>
-      <c r="L95" s="321"/>
-      <c r="M95" s="322"/>
+      <c r="K95" s="302"/>
+      <c r="L95" s="303"/>
+      <c r="M95" s="304"/>
       <c r="O95" s="141"/>
       <c r="P95" s="141"/>
     </row>
@@ -62726,9 +62727,9 @@
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="K96" s="320"/>
-      <c r="L96" s="321"/>
-      <c r="M96" s="322"/>
+      <c r="K96" s="302"/>
+      <c r="L96" s="303"/>
+      <c r="M96" s="304"/>
       <c r="O96" s="141"/>
       <c r="P96" s="141"/>
     </row>
@@ -62762,9 +62763,9 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="K97" s="320"/>
-      <c r="L97" s="321"/>
-      <c r="M97" s="322"/>
+      <c r="K97" s="302"/>
+      <c r="L97" s="303"/>
+      <c r="M97" s="304"/>
       <c r="O97" s="141"/>
       <c r="P97" s="141"/>
     </row>
@@ -62798,9 +62799,9 @@
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="K98" s="320"/>
-      <c r="L98" s="321"/>
-      <c r="M98" s="322"/>
+      <c r="K98" s="302"/>
+      <c r="L98" s="303"/>
+      <c r="M98" s="304"/>
       <c r="O98" s="141"/>
       <c r="P98" s="141"/>
     </row>
@@ -62834,9 +62835,9 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K99" s="320"/>
-      <c r="L99" s="321"/>
-      <c r="M99" s="322"/>
+      <c r="K99" s="302"/>
+      <c r="L99" s="303"/>
+      <c r="M99" s="304"/>
       <c r="O99" s="141"/>
       <c r="P99" s="141"/>
     </row>
@@ -62870,9 +62871,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K100" s="320"/>
-      <c r="L100" s="321"/>
-      <c r="M100" s="322"/>
+      <c r="K100" s="302"/>
+      <c r="L100" s="303"/>
+      <c r="M100" s="304"/>
       <c r="O100" s="141"/>
       <c r="P100" s="141"/>
     </row>
@@ -62906,9 +62907,9 @@
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="K101" s="320"/>
-      <c r="L101" s="321"/>
-      <c r="M101" s="322"/>
+      <c r="K101" s="302"/>
+      <c r="L101" s="303"/>
+      <c r="M101" s="304"/>
       <c r="O101" s="141"/>
       <c r="P101" s="141"/>
     </row>
@@ -62942,9 +62943,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K102" s="320"/>
-      <c r="L102" s="321"/>
-      <c r="M102" s="322"/>
+      <c r="K102" s="302"/>
+      <c r="L102" s="303"/>
+      <c r="M102" s="304"/>
       <c r="O102" s="141"/>
       <c r="P102" s="141"/>
     </row>
@@ -62978,9 +62979,9 @@
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="K103" s="320"/>
-      <c r="L103" s="321"/>
-      <c r="M103" s="322"/>
+      <c r="K103" s="302"/>
+      <c r="L103" s="303"/>
+      <c r="M103" s="304"/>
       <c r="O103" s="141"/>
       <c r="P103" s="141"/>
     </row>
@@ -63014,9 +63015,9 @@
         <f t="shared" si="2"/>
         <v>33</v>
       </c>
-      <c r="K104" s="320"/>
-      <c r="L104" s="321"/>
-      <c r="M104" s="322"/>
+      <c r="K104" s="302"/>
+      <c r="L104" s="303"/>
+      <c r="M104" s="304"/>
       <c r="O104" s="141"/>
       <c r="P104" s="141"/>
     </row>
@@ -63050,9 +63051,9 @@
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="K105" s="323"/>
-      <c r="L105" s="324"/>
-      <c r="M105" s="325"/>
+      <c r="K105" s="305"/>
+      <c r="L105" s="306"/>
+      <c r="M105" s="307"/>
       <c r="O105" s="141"/>
       <c r="P105" s="141"/>
     </row>
@@ -63086,11 +63087,11 @@
         <f t="shared" si="2"/>
         <v>21</v>
       </c>
-      <c r="K106" s="314" t="s">
+      <c r="K106" s="296" t="s">
         <v>286</v>
       </c>
-      <c r="L106" s="315"/>
-      <c r="M106" s="316"/>
+      <c r="L106" s="297"/>
+      <c r="M106" s="298"/>
       <c r="O106" s="126"/>
       <c r="P106" s="126"/>
     </row>
@@ -63124,11 +63125,11 @@
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="K107" s="314" t="s">
+      <c r="K107" s="296" t="s">
         <v>288</v>
       </c>
-      <c r="L107" s="315"/>
-      <c r="M107" s="316"/>
+      <c r="L107" s="297"/>
+      <c r="M107" s="298"/>
       <c r="O107" s="126"/>
       <c r="P107" s="126"/>
     </row>
@@ -63162,11 +63163,11 @@
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="K108" s="305" t="s">
+      <c r="K108" s="287" t="s">
         <v>289</v>
       </c>
-      <c r="L108" s="306"/>
-      <c r="M108" s="307"/>
+      <c r="L108" s="288"/>
+      <c r="M108" s="289"/>
       <c r="O108" s="126"/>
       <c r="P108" s="126"/>
     </row>
@@ -63200,9 +63201,9 @@
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="K109" s="308"/>
-      <c r="L109" s="309"/>
-      <c r="M109" s="310"/>
+      <c r="K109" s="290"/>
+      <c r="L109" s="291"/>
+      <c r="M109" s="292"/>
       <c r="O109" s="126"/>
       <c r="P109" s="126"/>
     </row>
@@ -63236,9 +63237,9 @@
         <f t="shared" si="2"/>
         <v>45</v>
       </c>
-      <c r="K110" s="308"/>
-      <c r="L110" s="309"/>
-      <c r="M110" s="310"/>
+      <c r="K110" s="290"/>
+      <c r="L110" s="291"/>
+      <c r="M110" s="292"/>
       <c r="O110" s="126"/>
       <c r="P110" s="126"/>
     </row>
@@ -63272,9 +63273,9 @@
         <f t="shared" si="2"/>
         <v>62</v>
       </c>
-      <c r="K111" s="308"/>
-      <c r="L111" s="309"/>
-      <c r="M111" s="310"/>
+      <c r="K111" s="290"/>
+      <c r="L111" s="291"/>
+      <c r="M111" s="292"/>
       <c r="O111" s="126"/>
       <c r="P111" s="126"/>
     </row>
@@ -63312,9 +63313,9 @@
         <f t="shared" ref="J112:J114" si="6">H112-I112</f>
         <v>34</v>
       </c>
-      <c r="K112" s="308"/>
-      <c r="L112" s="309"/>
-      <c r="M112" s="310"/>
+      <c r="K112" s="290"/>
+      <c r="L112" s="291"/>
+      <c r="M112" s="292"/>
     </row>
     <row r="113" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="156" t="s">
@@ -63350,9 +63351,9 @@
         <f t="shared" si="6"/>
         <v>43</v>
       </c>
-      <c r="K113" s="311"/>
-      <c r="L113" s="312"/>
-      <c r="M113" s="313"/>
+      <c r="K113" s="293"/>
+      <c r="L113" s="294"/>
+      <c r="M113" s="295"/>
     </row>
     <row r="114" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" s="93" t="s">
@@ -63362,11 +63363,11 @@
       <c r="C114" s="122"/>
       <c r="D114" s="122">
         <f>SUM(E114*3+F114)</f>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E114" s="122">
         <f>COUNTIF(C3:C41,3)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F114" s="122">
         <f>COUNTIF(C3:C41,1)</f>
@@ -63392,12 +63393,6 @@
   </sheetData>
   <autoFilter ref="A79:J112" xr:uid="{9C81160F-C24B-449F-8F5A-CB622AB71070}"/>
   <mergeCells count="15">
-    <mergeCell ref="W84:X84"/>
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="K108:M113"/>
-    <mergeCell ref="K106:M106"/>
-    <mergeCell ref="K107:M107"/>
-    <mergeCell ref="K84:M105"/>
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="W80:X80"/>
     <mergeCell ref="W81:X81"/>
@@ -63407,6 +63402,12 @@
     <mergeCell ref="K80:M81"/>
     <mergeCell ref="K82:M82"/>
     <mergeCell ref="K83:M83"/>
+    <mergeCell ref="W84:X84"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="K108:M113"/>
+    <mergeCell ref="K106:M106"/>
+    <mergeCell ref="K107:M107"/>
+    <mergeCell ref="K84:M105"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <conditionalFormatting sqref="A3:A40">
@@ -63498,32 +63499,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="326" t="s">
+      <c r="A1" s="204" t="s">
         <v>405</v>
       </c>
-      <c r="B1" s="326"/>
-      <c r="C1" s="326"/>
-      <c r="D1" s="326"/>
-      <c r="E1" s="326"/>
-      <c r="F1" s="326" t="s">
+      <c r="B1" s="204"/>
+      <c r="C1" s="204"/>
+      <c r="D1" s="204"/>
+      <c r="E1" s="204"/>
+      <c r="F1" s="204" t="s">
         <v>406</v>
       </c>
-      <c r="G1" s="326"/>
-      <c r="H1" s="326"/>
-      <c r="I1" s="326"/>
-      <c r="J1" s="326"/>
+      <c r="G1" s="204"/>
+      <c r="H1" s="204"/>
+      <c r="I1" s="204"/>
+      <c r="J1" s="204"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2" s="326"/>
-      <c r="B2" s="326"/>
-      <c r="C2" s="326"/>
-      <c r="D2" s="326"/>
-      <c r="E2" s="326"/>
-      <c r="F2" s="326"/>
-      <c r="G2" s="326"/>
-      <c r="H2" s="326"/>
-      <c r="I2" s="326"/>
-      <c r="J2" s="326"/>
+      <c r="A2" s="204"/>
+      <c r="B2" s="204"/>
+      <c r="C2" s="204"/>
+      <c r="D2" s="204"/>
+      <c r="E2" s="204"/>
+      <c r="F2" s="204"/>
+      <c r="G2" s="204"/>
+      <c r="H2" s="204"/>
+      <c r="I2" s="204"/>
+      <c r="J2" s="204"/>
       <c r="L2" t="s">
         <v>409</v>
       </c>
@@ -64541,23 +64542,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="208" t="s">
+      <c r="A1" s="209" t="s">
         <v>46</v>
       </c>
       <c r="B1" s="327"/>
       <c r="C1" s="328" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="211"/>
+      <c r="D1" s="212"/>
       <c r="E1" s="329"/>
-      <c r="H1" s="208" t="s">
+      <c r="H1" s="209" t="s">
         <v>47</v>
       </c>
       <c r="I1" s="327"/>
       <c r="J1" s="328" t="s">
         <v>44</v>
       </c>
-      <c r="K1" s="211"/>
+      <c r="K1" s="212"/>
       <c r="L1" s="329"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -65646,9 +65647,9 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="212"/>
-      <c r="G1" s="212"/>
-      <c r="H1" s="212"/>
+      <c r="F1" s="213"/>
+      <c r="G1" s="213"/>
+      <c r="H1" s="213"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -65672,36 +65673,36 @@
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="5"/>
-      <c r="E2" s="208" t="s">
+      <c r="E2" s="209" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="209"/>
-      <c r="G2" s="210"/>
-      <c r="H2" s="213" t="s">
+      <c r="F2" s="210"/>
+      <c r="G2" s="211"/>
+      <c r="H2" s="214" t="s">
         <v>120</v>
       </c>
-      <c r="I2" s="214"/>
-      <c r="J2" s="215"/>
-      <c r="K2" s="208" t="s">
+      <c r="I2" s="215"/>
+      <c r="J2" s="216"/>
+      <c r="K2" s="209" t="s">
         <v>108</v>
       </c>
-      <c r="L2" s="209"/>
-      <c r="M2" s="210"/>
-      <c r="N2" s="213" t="s">
+      <c r="L2" s="210"/>
+      <c r="M2" s="211"/>
+      <c r="N2" s="214" t="s">
         <v>110</v>
       </c>
-      <c r="O2" s="214"/>
-      <c r="P2" s="215"/>
-      <c r="Q2" s="208" t="s">
+      <c r="O2" s="215"/>
+      <c r="P2" s="216"/>
+      <c r="Q2" s="209" t="s">
         <v>39</v>
       </c>
-      <c r="R2" s="209"/>
-      <c r="S2" s="210"/>
-      <c r="T2" s="211" t="s">
+      <c r="R2" s="210"/>
+      <c r="S2" s="211"/>
+      <c r="T2" s="212" t="s">
         <v>7</v>
       </c>
-      <c r="U2" s="211"/>
-      <c r="V2" s="211"/>
+      <c r="U2" s="212"/>
+      <c r="V2" s="212"/>
       <c r="Z2" s="125">
         <v>46279</v>
       </c>
@@ -68799,30 +68800,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="206" t="s">
+      <c r="D2" s="207" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="206"/>
-      <c r="F2" s="207" t="s">
+      <c r="E2" s="207"/>
+      <c r="F2" s="208" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="207"/>
-      <c r="H2" s="206" t="s">
+      <c r="G2" s="208"/>
+      <c r="H2" s="207" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="206"/>
-      <c r="J2" s="207" t="s">
+      <c r="I2" s="207"/>
+      <c r="J2" s="208" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="207"/>
-      <c r="L2" s="206" t="s">
+      <c r="K2" s="208"/>
+      <c r="L2" s="207" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="206"/>
-      <c r="N2" s="211" t="s">
+      <c r="M2" s="207"/>
+      <c r="N2" s="212" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="211"/>
+      <c r="O2" s="212"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -70819,30 +70820,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="206" t="s">
+      <c r="D2" s="207" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="206"/>
-      <c r="F2" s="207" t="s">
+      <c r="E2" s="207"/>
+      <c r="F2" s="208" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="207"/>
-      <c r="H2" s="206" t="s">
+      <c r="G2" s="208"/>
+      <c r="H2" s="207" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="206"/>
-      <c r="J2" s="207" t="s">
+      <c r="I2" s="207"/>
+      <c r="J2" s="208" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="207"/>
-      <c r="L2" s="206" t="s">
+      <c r="K2" s="208"/>
+      <c r="L2" s="207" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="206"/>
-      <c r="N2" s="211" t="s">
+      <c r="M2" s="207"/>
+      <c r="N2" s="212" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="211"/>
+      <c r="O2" s="212"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -72776,30 +72777,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="206" t="s">
+      <c r="D2" s="207" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="206"/>
-      <c r="F2" s="207" t="s">
+      <c r="E2" s="207"/>
+      <c r="F2" s="208" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="207"/>
-      <c r="H2" s="206" t="s">
+      <c r="G2" s="208"/>
+      <c r="H2" s="207" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="206"/>
-      <c r="J2" s="207" t="s">
+      <c r="I2" s="207"/>
+      <c r="J2" s="208" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="207"/>
-      <c r="L2" s="206" t="s">
+      <c r="K2" s="208"/>
+      <c r="L2" s="207" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="206"/>
-      <c r="N2" s="211" t="s">
+      <c r="M2" s="207"/>
+      <c r="N2" s="212" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="211"/>
+      <c r="O2" s="212"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -74824,30 +74825,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="206" t="s">
+      <c r="D2" s="207" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="206"/>
-      <c r="F2" s="207" t="s">
+      <c r="E2" s="207"/>
+      <c r="F2" s="208" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="207"/>
-      <c r="H2" s="206" t="s">
+      <c r="G2" s="208"/>
+      <c r="H2" s="207" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="206"/>
-      <c r="J2" s="207" t="s">
+      <c r="I2" s="207"/>
+      <c r="J2" s="208" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="207"/>
-      <c r="L2" s="206" t="s">
+      <c r="K2" s="208"/>
+      <c r="L2" s="207" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="206"/>
-      <c r="N2" s="211" t="s">
+      <c r="M2" s="207"/>
+      <c r="N2" s="212" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="211"/>
+      <c r="O2" s="212"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -76532,30 +76533,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="206" t="s">
+      <c r="C2" s="207" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="206"/>
-      <c r="E2" s="207" t="s">
+      <c r="D2" s="207"/>
+      <c r="E2" s="208" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="207"/>
-      <c r="G2" s="206" t="s">
+      <c r="F2" s="208"/>
+      <c r="G2" s="207" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="206"/>
-      <c r="I2" s="207" t="s">
+      <c r="H2" s="207"/>
+      <c r="I2" s="208" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="207"/>
-      <c r="K2" s="206" t="s">
+      <c r="J2" s="208"/>
+      <c r="K2" s="207" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="206"/>
-      <c r="M2" s="211" t="s">
+      <c r="L2" s="207"/>
+      <c r="M2" s="212" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="211"/>
+      <c r="N2" s="212"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -78317,30 +78318,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="206" t="s">
+      <c r="C2" s="207" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="206"/>
-      <c r="E2" s="207" t="s">
+      <c r="D2" s="207"/>
+      <c r="E2" s="208" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="207"/>
-      <c r="G2" s="206" t="s">
+      <c r="F2" s="208"/>
+      <c r="G2" s="207" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="206"/>
-      <c r="I2" s="207" t="s">
+      <c r="H2" s="207"/>
+      <c r="I2" s="208" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="207"/>
-      <c r="K2" s="206" t="s">
+      <c r="J2" s="208"/>
+      <c r="K2" s="207" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="206"/>
-      <c r="M2" s="211" t="s">
+      <c r="L2" s="207"/>
+      <c r="M2" s="212" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="211"/>
+      <c r="N2" s="212"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">

--- a/data/arsenal_stats.xlsx
+++ b/data/arsenal_stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bungeltd-my.sharepoint.com/personal/przemyslaw_iskra_bunge_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8526" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3982A62C-150C-46CB-BA13-506B846A93C6}"/>
+  <xr:revisionPtr revIDLastSave="8528" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2AD9CD94-5203-48E1-B046-8EC9DACC8F89}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="799" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="799" firstSheet="1" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="19" state="hidden" r:id="rId1"/>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2278" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2278" uniqueCount="492">
   <si>
     <t>Arsenal FC squad statistics</t>
   </si>
@@ -1526,9 +1526,6 @@
   </si>
   <si>
     <t>19.09.2026</t>
-  </si>
-  <si>
-    <t>Brighton</t>
   </si>
   <si>
     <t>Amex Stadium (A)</t>
@@ -3064,6 +3061,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3100,6 +3098,15 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3109,23 +3116,23 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="54" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3163,15 +3170,6 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="28" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3179,27 +3177,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="60" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="10" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="37" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="11" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3292,67 +3269,31 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="60" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="10" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="37" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="11" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="54" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3430,6 +3371,63 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3440,7 +3438,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
@@ -6496,7 +6493,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C7EDB063-FF93-4014-AC99-7258C6F04224}" type="CELLRANGE">
+                    <a:fld id="{CC776D23-6EC0-43B2-BBBF-C7138B7FCC42}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6530,7 +6527,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{5FA0310B-9252-4177-8DB3-766B69764534}" type="CELLRANGE">
+                    <a:fld id="{BA1EA7DF-738D-4931-98BE-EA0D802F4462}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6564,7 +6561,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{CDC5A2A1-A416-4285-83D9-138BEADDCF69}" type="CELLRANGE">
+                    <a:fld id="{8B04924A-DD2C-480B-9FC2-D8036F50BB02}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6598,7 +6595,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{0D64BD0B-7F5E-432C-8ECB-44E8B4200FE5}" type="CELLRANGE">
+                    <a:fld id="{8E7934C5-6F2D-4E44-9CB0-3161FC77E946}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6632,7 +6629,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{CD5253A7-2109-46EF-B7F9-068E18500C69}" type="CELLRANGE">
+                    <a:fld id="{DF9685E5-48C8-403C-8D6C-1F759A19B6D4}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6666,7 +6663,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9A21121A-EAEF-4DDA-9EB9-E6EC812F4E8D}" type="CELLRANGE">
+                    <a:fld id="{7B85DFC7-023B-45BE-9BA5-F0EF3502E622}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6700,7 +6697,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{020B4633-EB11-4E43-9089-2F7BC748DB5B}" type="CELLRANGE">
+                    <a:fld id="{52B00131-1E14-4AC3-AA60-C8FFE2236A3D}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6734,7 +6731,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{4555740E-B9AE-47C2-8C75-BC24200109D8}" type="CELLRANGE">
+                    <a:fld id="{B4D56F95-515F-45FC-9CDC-06DDB0519B12}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6768,7 +6765,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{BBFBF747-B8AC-41AB-A955-66EBC78EE981}" type="CELLRANGE">
+                    <a:fld id="{D47F1957-F49E-4C4A-967F-DC31365B33D5}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6802,7 +6799,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{EF12D6E8-F488-4E7B-9C5B-681B752FAADA}" type="CELLRANGE">
+                    <a:fld id="{C36792FB-A187-46B9-B562-219CFE4997BF}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6836,7 +6833,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F7C1A6BD-E997-4015-BE69-85E5E4B8D4EC}" type="CELLRANGE">
+                    <a:fld id="{0303DC5A-A763-4CA2-A208-407D57DC775C}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6870,7 +6867,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A60F02E0-33C6-4E75-A3BE-8615938419B4}" type="CELLRANGE">
+                    <a:fld id="{E5A23370-79F9-4691-BDBD-7A8D62C566BC}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6919,7 +6916,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{A1DDE538-7BAE-4BD8-88F3-A5DD7EB34E79}" type="CELLRANGE">
+                    <a:fld id="{33175813-3062-4C6F-8FDE-08411AC41C6D}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr>
                         <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
@@ -6978,7 +6975,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{25DCC192-A635-4E57-8BEE-0D00A7C34986}" type="CELLRANGE">
+                    <a:fld id="{E35BDC9C-53DE-479A-9D40-15BBFE19E53D}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7012,7 +7009,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A262C22B-0C28-4EA1-948D-D119C32EBC03}" type="CELLRANGE">
+                    <a:fld id="{7FF25670-5252-4315-A1E6-9E5CCA6D4AA1}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7046,7 +7043,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{44B9E5A2-9258-4E17-843C-F86D4C899D17}" type="CELLRANGE">
+                    <a:fld id="{9D3F3147-BE4C-4865-B0DA-240B7221C309}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7080,7 +7077,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9B3B1AE0-55F4-4E8F-96DC-B478295AE178}" type="CELLRANGE">
+                    <a:fld id="{82D393B5-CEAF-447D-AE5B-B2EF98919F4A}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -14216,30 +14213,30 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
       <c r="B1" s="5"/>
-      <c r="C1" s="212" t="s">
+      <c r="C1" s="213" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="212"/>
-      <c r="E1" s="213" t="s">
+      <c r="D1" s="213"/>
+      <c r="E1" s="214" t="s">
         <v>120</v>
       </c>
-      <c r="F1" s="213"/>
-      <c r="G1" s="212" t="s">
+      <c r="F1" s="214"/>
+      <c r="G1" s="213" t="s">
         <v>108</v>
       </c>
-      <c r="H1" s="212"/>
-      <c r="I1" s="213" t="s">
+      <c r="H1" s="213"/>
+      <c r="I1" s="214" t="s">
         <v>110</v>
       </c>
-      <c r="J1" s="213"/>
-      <c r="K1" s="212" t="s">
+      <c r="J1" s="214"/>
+      <c r="K1" s="213" t="s">
         <v>39</v>
       </c>
-      <c r="L1" s="212"/>
-      <c r="M1" s="210" t="s">
+      <c r="L1" s="213"/>
+      <c r="M1" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="211"/>
+      <c r="N1" s="212"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -15946,30 +15943,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="212" t="s">
+      <c r="C2" s="213" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="212"/>
-      <c r="E2" s="213" t="s">
+      <c r="D2" s="213"/>
+      <c r="E2" s="214" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="213"/>
-      <c r="G2" s="212" t="s">
+      <c r="F2" s="214"/>
+      <c r="G2" s="213" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="212"/>
-      <c r="I2" s="213" t="s">
+      <c r="H2" s="213"/>
+      <c r="I2" s="214" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="213"/>
-      <c r="K2" s="212" t="s">
+      <c r="J2" s="214"/>
+      <c r="K2" s="213" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="212"/>
-      <c r="M2" s="205" t="s">
+      <c r="L2" s="213"/>
+      <c r="M2" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="205"/>
+      <c r="N2" s="206"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -17773,30 +17770,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="212" t="s">
+      <c r="C2" s="213" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="212"/>
-      <c r="E2" s="213" t="s">
+      <c r="D2" s="213"/>
+      <c r="E2" s="214" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="213"/>
-      <c r="G2" s="212" t="s">
+      <c r="F2" s="214"/>
+      <c r="G2" s="213" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="212"/>
-      <c r="I2" s="213" t="s">
+      <c r="H2" s="213"/>
+      <c r="I2" s="214" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="213"/>
-      <c r="K2" s="212" t="s">
+      <c r="J2" s="214"/>
+      <c r="K2" s="213" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="212"/>
-      <c r="M2" s="205" t="s">
+      <c r="L2" s="213"/>
+      <c r="M2" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="205"/>
+      <c r="N2" s="206"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -19463,30 +19460,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="212" t="s">
+      <c r="C2" s="213" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="212"/>
-      <c r="E2" s="213" t="s">
+      <c r="D2" s="213"/>
+      <c r="E2" s="214" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="213"/>
-      <c r="G2" s="212" t="s">
+      <c r="F2" s="214"/>
+      <c r="G2" s="213" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="212"/>
-      <c r="I2" s="213" t="s">
+      <c r="H2" s="213"/>
+      <c r="I2" s="214" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="213"/>
-      <c r="K2" s="212" t="s">
+      <c r="J2" s="214"/>
+      <c r="K2" s="213" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="212"/>
-      <c r="M2" s="205" t="s">
+      <c r="L2" s="213"/>
+      <c r="M2" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="205"/>
+      <c r="N2" s="206"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -21289,30 +21286,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="212" t="s">
+      <c r="C2" s="213" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="212"/>
-      <c r="E2" s="213" t="s">
+      <c r="D2" s="213"/>
+      <c r="E2" s="214" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="213"/>
-      <c r="G2" s="212" t="s">
+      <c r="F2" s="214"/>
+      <c r="G2" s="213" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="212"/>
-      <c r="I2" s="213" t="s">
+      <c r="H2" s="213"/>
+      <c r="I2" s="214" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="213"/>
-      <c r="K2" s="212" t="s">
+      <c r="J2" s="214"/>
+      <c r="K2" s="213" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="212"/>
-      <c r="M2" s="205" t="s">
+      <c r="L2" s="213"/>
+      <c r="M2" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="205"/>
+      <c r="N2" s="206"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -23161,36 +23158,36 @@
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="202" t="s">
+      <c r="C2" s="203" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="203"/>
-      <c r="E2" s="204"/>
-      <c r="F2" s="207" t="s">
+      <c r="D2" s="204"/>
+      <c r="E2" s="205"/>
+      <c r="F2" s="208" t="s">
         <v>120</v>
       </c>
-      <c r="G2" s="208"/>
-      <c r="H2" s="209"/>
-      <c r="I2" s="202" t="s">
+      <c r="G2" s="209"/>
+      <c r="H2" s="210"/>
+      <c r="I2" s="203" t="s">
         <v>108</v>
       </c>
-      <c r="J2" s="203"/>
-      <c r="K2" s="204"/>
-      <c r="L2" s="207" t="s">
+      <c r="J2" s="204"/>
+      <c r="K2" s="205"/>
+      <c r="L2" s="208" t="s">
         <v>110</v>
       </c>
-      <c r="M2" s="208"/>
-      <c r="N2" s="209"/>
-      <c r="O2" s="202" t="s">
+      <c r="M2" s="209"/>
+      <c r="N2" s="210"/>
+      <c r="O2" s="203" t="s">
         <v>39</v>
       </c>
-      <c r="P2" s="203"/>
-      <c r="Q2" s="204"/>
-      <c r="R2" s="205" t="s">
+      <c r="P2" s="204"/>
+      <c r="Q2" s="205"/>
+      <c r="R2" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="S2" s="205"/>
-      <c r="T2" s="205"/>
+      <c r="S2" s="206"/>
+      <c r="T2" s="206"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -24293,15 +24290,15 @@
         <v>0</v>
       </c>
       <c r="R16" s="2">
-        <f t="shared" ref="R16:R38" si="4">SUM(C16,F16,I16,L16,O16)</f>
+        <f t="shared" ref="R16:R28" si="4">SUM(C16,F16,I16,L16,O16)</f>
         <v>5</v>
       </c>
       <c r="S16" s="2">
-        <f t="shared" ref="S16:S38" si="5">SUM(D16,G16,J16,M16,P16)</f>
+        <f t="shared" ref="S16:S28" si="5">SUM(D16,G16,J16,M16,P16)</f>
         <v>0</v>
       </c>
       <c r="T16" s="2">
-        <f t="shared" ref="T16:T38" si="6">SUM(E16,H16,K16,N16,Q16)</f>
+        <f t="shared" ref="T16:T28" si="6">SUM(E16,H16,K16,N16,Q16)</f>
         <v>0</v>
       </c>
       <c r="V16" s="55"/>
@@ -25439,7 +25436,7 @@
         <v>45</v>
       </c>
       <c r="B31" s="148" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C31" s="6">
         <f>'Premier League'!C31</f>
@@ -26129,36 +26126,36 @@
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
       <c r="D1" s="5"/>
-      <c r="E1" s="202" t="s">
+      <c r="E1" s="203" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="203"/>
-      <c r="G1" s="204"/>
-      <c r="H1" s="207" t="s">
+      <c r="F1" s="204"/>
+      <c r="G1" s="205"/>
+      <c r="H1" s="208" t="s">
         <v>120</v>
       </c>
-      <c r="I1" s="208"/>
-      <c r="J1" s="209"/>
-      <c r="K1" s="202" t="s">
+      <c r="I1" s="209"/>
+      <c r="J1" s="210"/>
+      <c r="K1" s="203" t="s">
         <v>108</v>
       </c>
-      <c r="L1" s="203"/>
-      <c r="M1" s="204"/>
-      <c r="N1" s="207" t="s">
+      <c r="L1" s="204"/>
+      <c r="M1" s="205"/>
+      <c r="N1" s="208" t="s">
         <v>110</v>
       </c>
-      <c r="O1" s="208"/>
-      <c r="P1" s="209"/>
-      <c r="Q1" s="202" t="s">
+      <c r="O1" s="209"/>
+      <c r="P1" s="210"/>
+      <c r="Q1" s="203" t="s">
         <v>39</v>
       </c>
-      <c r="R1" s="203"/>
-      <c r="S1" s="204"/>
-      <c r="T1" s="205" t="s">
+      <c r="R1" s="204"/>
+      <c r="S1" s="205"/>
+      <c r="T1" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="U1" s="205"/>
-      <c r="V1" s="205"/>
+      <c r="U1" s="206"/>
+      <c r="V1" s="206"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -37732,399 +37729,399 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F1" s="214">
-        <v>1</v>
-      </c>
-      <c r="G1" s="215"/>
-      <c r="H1" s="216"/>
-      <c r="I1" s="214">
+      <c r="F1" s="218">
+        <v>1</v>
+      </c>
+      <c r="G1" s="219"/>
+      <c r="H1" s="220"/>
+      <c r="I1" s="218">
         <v>2</v>
       </c>
-      <c r="J1" s="215"/>
-      <c r="K1" s="216"/>
-      <c r="L1" s="214">
-        <v>3</v>
-      </c>
-      <c r="M1" s="215"/>
-      <c r="N1" s="216"/>
-      <c r="O1" s="214">
+      <c r="J1" s="219"/>
+      <c r="K1" s="220"/>
+      <c r="L1" s="218">
+        <v>3</v>
+      </c>
+      <c r="M1" s="219"/>
+      <c r="N1" s="220"/>
+      <c r="O1" s="218">
         <v>4</v>
       </c>
-      <c r="P1" s="215"/>
-      <c r="Q1" s="216"/>
-      <c r="R1" s="214">
+      <c r="P1" s="219"/>
+      <c r="Q1" s="220"/>
+      <c r="R1" s="218">
         <v>5</v>
       </c>
-      <c r="S1" s="215"/>
-      <c r="T1" s="216"/>
-      <c r="U1" s="214">
+      <c r="S1" s="219"/>
+      <c r="T1" s="220"/>
+      <c r="U1" s="218">
         <v>6</v>
       </c>
-      <c r="V1" s="215"/>
-      <c r="W1" s="216"/>
-      <c r="X1" s="214">
+      <c r="V1" s="219"/>
+      <c r="W1" s="220"/>
+      <c r="X1" s="218">
         <v>7</v>
       </c>
-      <c r="Y1" s="215"/>
-      <c r="Z1" s="216"/>
-      <c r="AA1" s="214">
+      <c r="Y1" s="219"/>
+      <c r="Z1" s="220"/>
+      <c r="AA1" s="218">
         <v>8</v>
       </c>
-      <c r="AB1" s="215"/>
-      <c r="AC1" s="216"/>
-      <c r="AD1" s="214">
+      <c r="AB1" s="219"/>
+      <c r="AC1" s="220"/>
+      <c r="AD1" s="218">
         <v>9</v>
       </c>
-      <c r="AE1" s="215"/>
-      <c r="AF1" s="216"/>
-      <c r="AG1" s="214">
+      <c r="AE1" s="219"/>
+      <c r="AF1" s="220"/>
+      <c r="AG1" s="218">
         <v>10</v>
       </c>
-      <c r="AH1" s="215"/>
-      <c r="AI1" s="216"/>
-      <c r="AJ1" s="214">
+      <c r="AH1" s="219"/>
+      <c r="AI1" s="220"/>
+      <c r="AJ1" s="218">
         <v>11</v>
       </c>
-      <c r="AK1" s="215"/>
-      <c r="AL1" s="216"/>
-      <c r="AM1" s="214">
+      <c r="AK1" s="219"/>
+      <c r="AL1" s="220"/>
+      <c r="AM1" s="218">
         <v>12</v>
       </c>
-      <c r="AN1" s="215"/>
-      <c r="AO1" s="216"/>
-      <c r="AP1" s="214">
+      <c r="AN1" s="219"/>
+      <c r="AO1" s="220"/>
+      <c r="AP1" s="218">
         <v>13</v>
       </c>
-      <c r="AQ1" s="215"/>
-      <c r="AR1" s="216"/>
-      <c r="AS1" s="214">
+      <c r="AQ1" s="219"/>
+      <c r="AR1" s="220"/>
+      <c r="AS1" s="218">
         <v>14</v>
       </c>
-      <c r="AT1" s="215"/>
-      <c r="AU1" s="216"/>
-      <c r="AV1" s="214">
+      <c r="AT1" s="219"/>
+      <c r="AU1" s="220"/>
+      <c r="AV1" s="218">
         <v>15</v>
       </c>
-      <c r="AW1" s="215"/>
-      <c r="AX1" s="216"/>
-      <c r="AY1" s="214">
+      <c r="AW1" s="219"/>
+      <c r="AX1" s="220"/>
+      <c r="AY1" s="218">
         <v>16</v>
       </c>
-      <c r="AZ1" s="215"/>
-      <c r="BA1" s="216"/>
-      <c r="BB1" s="214">
+      <c r="AZ1" s="219"/>
+      <c r="BA1" s="220"/>
+      <c r="BB1" s="218">
         <v>17</v>
       </c>
-      <c r="BC1" s="215"/>
-      <c r="BD1" s="216"/>
-      <c r="BE1" s="214">
+      <c r="BC1" s="219"/>
+      <c r="BD1" s="220"/>
+      <c r="BE1" s="218">
         <v>18</v>
       </c>
-      <c r="BF1" s="215"/>
-      <c r="BG1" s="216"/>
-      <c r="BH1" s="214">
+      <c r="BF1" s="219"/>
+      <c r="BG1" s="220"/>
+      <c r="BH1" s="218">
         <v>19</v>
       </c>
-      <c r="BI1" s="215"/>
-      <c r="BJ1" s="216"/>
-      <c r="BK1" s="214">
+      <c r="BI1" s="219"/>
+      <c r="BJ1" s="220"/>
+      <c r="BK1" s="218">
         <v>20</v>
       </c>
-      <c r="BL1" s="215"/>
-      <c r="BM1" s="216"/>
-      <c r="BN1" s="214">
+      <c r="BL1" s="219"/>
+      <c r="BM1" s="220"/>
+      <c r="BN1" s="218">
         <v>21</v>
       </c>
-      <c r="BO1" s="215"/>
-      <c r="BP1" s="216"/>
-      <c r="BQ1" s="214">
+      <c r="BO1" s="219"/>
+      <c r="BP1" s="220"/>
+      <c r="BQ1" s="218">
         <v>22</v>
       </c>
-      <c r="BR1" s="215"/>
-      <c r="BS1" s="216"/>
-      <c r="BT1" s="214">
+      <c r="BR1" s="219"/>
+      <c r="BS1" s="220"/>
+      <c r="BT1" s="218">
         <v>23</v>
       </c>
-      <c r="BU1" s="215"/>
-      <c r="BV1" s="216"/>
-      <c r="BW1" s="214">
+      <c r="BU1" s="219"/>
+      <c r="BV1" s="220"/>
+      <c r="BW1" s="218">
         <v>24</v>
       </c>
-      <c r="BX1" s="215"/>
-      <c r="BY1" s="216"/>
-      <c r="BZ1" s="214">
+      <c r="BX1" s="219"/>
+      <c r="BY1" s="220"/>
+      <c r="BZ1" s="218">
         <v>25</v>
       </c>
-      <c r="CA1" s="215"/>
-      <c r="CB1" s="216"/>
-      <c r="CC1" s="214">
+      <c r="CA1" s="219"/>
+      <c r="CB1" s="220"/>
+      <c r="CC1" s="218">
         <v>26</v>
       </c>
-      <c r="CD1" s="215"/>
-      <c r="CE1" s="216"/>
-      <c r="CF1" s="214">
+      <c r="CD1" s="219"/>
+      <c r="CE1" s="220"/>
+      <c r="CF1" s="218">
         <v>27</v>
       </c>
-      <c r="CG1" s="215"/>
-      <c r="CH1" s="216"/>
-      <c r="CI1" s="214">
+      <c r="CG1" s="219"/>
+      <c r="CH1" s="220"/>
+      <c r="CI1" s="218">
         <v>28</v>
       </c>
-      <c r="CJ1" s="215"/>
-      <c r="CK1" s="216"/>
-      <c r="CL1" s="214">
+      <c r="CJ1" s="219"/>
+      <c r="CK1" s="220"/>
+      <c r="CL1" s="218">
         <v>29</v>
       </c>
-      <c r="CM1" s="215"/>
-      <c r="CN1" s="216"/>
-      <c r="CO1" s="214">
+      <c r="CM1" s="219"/>
+      <c r="CN1" s="220"/>
+      <c r="CO1" s="218">
         <v>30</v>
       </c>
-      <c r="CP1" s="215"/>
-      <c r="CQ1" s="216"/>
-      <c r="CR1" s="214">
+      <c r="CP1" s="219"/>
+      <c r="CQ1" s="220"/>
+      <c r="CR1" s="218">
         <v>31</v>
       </c>
-      <c r="CS1" s="215"/>
-      <c r="CT1" s="216"/>
-      <c r="CU1" s="214">
+      <c r="CS1" s="219"/>
+      <c r="CT1" s="220"/>
+      <c r="CU1" s="218">
         <v>32</v>
       </c>
-      <c r="CV1" s="215"/>
-      <c r="CW1" s="216"/>
-      <c r="CX1" s="214">
+      <c r="CV1" s="219"/>
+      <c r="CW1" s="220"/>
+      <c r="CX1" s="218">
         <v>33</v>
       </c>
-      <c r="CY1" s="215"/>
-      <c r="CZ1" s="216"/>
-      <c r="DA1" s="214">
+      <c r="CY1" s="219"/>
+      <c r="CZ1" s="220"/>
+      <c r="DA1" s="218">
         <v>34</v>
       </c>
-      <c r="DB1" s="215"/>
-      <c r="DC1" s="216"/>
-      <c r="DD1" s="214">
+      <c r="DB1" s="219"/>
+      <c r="DC1" s="220"/>
+      <c r="DD1" s="218">
         <v>35</v>
       </c>
-      <c r="DE1" s="215"/>
-      <c r="DF1" s="216"/>
-      <c r="DG1" s="214">
+      <c r="DE1" s="219"/>
+      <c r="DF1" s="220"/>
+      <c r="DG1" s="218">
         <v>36</v>
       </c>
-      <c r="DH1" s="215"/>
-      <c r="DI1" s="216"/>
-      <c r="DJ1" s="214">
+      <c r="DH1" s="219"/>
+      <c r="DI1" s="220"/>
+      <c r="DJ1" s="218">
         <v>37</v>
       </c>
-      <c r="DK1" s="215"/>
-      <c r="DL1" s="216"/>
-      <c r="DM1" s="214">
+      <c r="DK1" s="219"/>
+      <c r="DL1" s="220"/>
+      <c r="DM1" s="218">
         <v>38</v>
       </c>
-      <c r="DN1" s="215"/>
-      <c r="DO1" s="216"/>
+      <c r="DN1" s="219"/>
+      <c r="DO1" s="220"/>
     </row>
     <row r="2" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="220" t="s">
+      <c r="C2" s="221" t="s">
         <v>396</v>
       </c>
-      <c r="D2" s="220" t="s">
+      <c r="D2" s="221" t="s">
         <v>397</v>
       </c>
-      <c r="E2" s="220" t="s">
+      <c r="E2" s="221" t="s">
         <v>398</v>
       </c>
-      <c r="F2" s="217" t="s">
+      <c r="F2" s="215" t="s">
         <v>346</v>
       </c>
-      <c r="G2" s="218"/>
-      <c r="H2" s="219"/>
-      <c r="I2" s="217" t="s">
+      <c r="G2" s="216"/>
+      <c r="H2" s="217"/>
+      <c r="I2" s="215" t="s">
         <v>331</v>
       </c>
-      <c r="J2" s="218"/>
-      <c r="K2" s="219"/>
-      <c r="L2" s="217" t="s">
+      <c r="J2" s="216"/>
+      <c r="K2" s="217"/>
+      <c r="L2" s="215" t="s">
         <v>330</v>
       </c>
-      <c r="M2" s="218"/>
-      <c r="N2" s="219"/>
-      <c r="O2" s="217" t="s">
+      <c r="M2" s="216"/>
+      <c r="N2" s="217"/>
+      <c r="O2" s="215" t="s">
         <v>328</v>
       </c>
-      <c r="P2" s="218"/>
-      <c r="Q2" s="219"/>
-      <c r="R2" s="217" t="s">
+      <c r="P2" s="216"/>
+      <c r="Q2" s="217"/>
+      <c r="R2" s="215" t="s">
         <v>335</v>
       </c>
-      <c r="S2" s="218"/>
-      <c r="T2" s="219"/>
-      <c r="U2" s="217" t="s">
+      <c r="S2" s="216"/>
+      <c r="T2" s="217"/>
+      <c r="U2" s="215" t="s">
         <v>320</v>
       </c>
-      <c r="V2" s="218"/>
-      <c r="W2" s="219"/>
-      <c r="X2" s="217" t="s">
+      <c r="V2" s="216"/>
+      <c r="W2" s="217"/>
+      <c r="X2" s="215" t="s">
         <v>337</v>
       </c>
-      <c r="Y2" s="218"/>
-      <c r="Z2" s="219"/>
-      <c r="AA2" s="217" t="s">
+      <c r="Y2" s="216"/>
+      <c r="Z2" s="217"/>
+      <c r="AA2" s="215" t="s">
         <v>334</v>
       </c>
-      <c r="AB2" s="218"/>
-      <c r="AC2" s="219"/>
-      <c r="AD2" s="217" t="s">
+      <c r="AB2" s="216"/>
+      <c r="AC2" s="217"/>
+      <c r="AD2" s="215" t="s">
         <v>321</v>
       </c>
-      <c r="AE2" s="218"/>
-      <c r="AF2" s="219"/>
-      <c r="AG2" s="217" t="s">
+      <c r="AE2" s="216"/>
+      <c r="AF2" s="217"/>
+      <c r="AG2" s="215" t="s">
         <v>347</v>
       </c>
-      <c r="AH2" s="218"/>
-      <c r="AI2" s="219"/>
-      <c r="AJ2" s="217" t="s">
+      <c r="AH2" s="216"/>
+      <c r="AI2" s="217"/>
+      <c r="AJ2" s="215" t="s">
         <v>324</v>
       </c>
-      <c r="AK2" s="218"/>
-      <c r="AL2" s="219"/>
-      <c r="AM2" s="217" t="s">
+      <c r="AK2" s="216"/>
+      <c r="AL2" s="217"/>
+      <c r="AM2" s="215" t="s">
         <v>323</v>
       </c>
-      <c r="AN2" s="218"/>
-      <c r="AO2" s="219"/>
-      <c r="AP2" s="217" t="s">
+      <c r="AN2" s="216"/>
+      <c r="AO2" s="217"/>
+      <c r="AP2" s="215" t="s">
         <v>332</v>
       </c>
-      <c r="AQ2" s="218"/>
-      <c r="AR2" s="219"/>
-      <c r="AS2" s="217" t="s">
+      <c r="AQ2" s="216"/>
+      <c r="AR2" s="217"/>
+      <c r="AS2" s="215" t="s">
         <v>329</v>
       </c>
-      <c r="AT2" s="218"/>
-      <c r="AU2" s="219"/>
-      <c r="AV2" s="217" t="s">
+      <c r="AT2" s="216"/>
+      <c r="AU2" s="217"/>
+      <c r="AV2" s="215" t="s">
         <v>336</v>
       </c>
-      <c r="AW2" s="218"/>
-      <c r="AX2" s="219"/>
-      <c r="AY2" s="217" t="s">
+      <c r="AW2" s="216"/>
+      <c r="AX2" s="217"/>
+      <c r="AY2" s="215" t="s">
         <v>305</v>
       </c>
-      <c r="AZ2" s="218"/>
-      <c r="BA2" s="219"/>
-      <c r="BB2" s="217" t="s">
+      <c r="AZ2" s="216"/>
+      <c r="BA2" s="217"/>
+      <c r="BB2" s="215" t="s">
         <v>326</v>
       </c>
-      <c r="BC2" s="218"/>
-      <c r="BD2" s="219"/>
-      <c r="BE2" s="217" t="s">
+      <c r="BC2" s="216"/>
+      <c r="BD2" s="217"/>
+      <c r="BE2" s="215" t="s">
         <v>325</v>
       </c>
-      <c r="BF2" s="218"/>
-      <c r="BG2" s="219"/>
-      <c r="BH2" s="217" t="s">
+      <c r="BF2" s="216"/>
+      <c r="BG2" s="217"/>
+      <c r="BH2" s="215" t="s">
         <v>348</v>
       </c>
-      <c r="BI2" s="218"/>
-      <c r="BJ2" s="219"/>
-      <c r="BK2" s="217" t="s">
+      <c r="BI2" s="216"/>
+      <c r="BJ2" s="217"/>
+      <c r="BK2" s="215" t="s">
         <v>332</v>
       </c>
-      <c r="BL2" s="218"/>
-      <c r="BM2" s="219"/>
-      <c r="BN2" s="217" t="s">
+      <c r="BL2" s="216"/>
+      <c r="BM2" s="217"/>
+      <c r="BN2" s="215" t="s">
         <v>347</v>
       </c>
-      <c r="BO2" s="218"/>
-      <c r="BP2" s="219"/>
-      <c r="BQ2" s="217" t="s">
+      <c r="BO2" s="216"/>
+      <c r="BP2" s="217"/>
+      <c r="BQ2" s="215" t="s">
         <v>324</v>
       </c>
-      <c r="BR2" s="218"/>
-      <c r="BS2" s="219"/>
-      <c r="BT2" s="217" t="s">
+      <c r="BR2" s="216"/>
+      <c r="BS2" s="217"/>
+      <c r="BT2" s="215" t="s">
         <v>323</v>
       </c>
-      <c r="BU2" s="218"/>
-      <c r="BV2" s="219"/>
-      <c r="BW2" s="217" t="s">
+      <c r="BU2" s="216"/>
+      <c r="BV2" s="217"/>
+      <c r="BW2" s="215" t="s">
         <v>321</v>
       </c>
-      <c r="BX2" s="218"/>
-      <c r="BY2" s="219"/>
-      <c r="BZ2" s="217" t="s">
+      <c r="BX2" s="216"/>
+      <c r="BY2" s="217"/>
+      <c r="BZ2" s="215" t="s">
         <v>348</v>
       </c>
-      <c r="CA2" s="218"/>
-      <c r="CB2" s="219"/>
-      <c r="CC2" s="217" t="s">
+      <c r="CA2" s="216"/>
+      <c r="CB2" s="217"/>
+      <c r="CC2" s="215" t="s">
         <v>325</v>
       </c>
-      <c r="CD2" s="218"/>
-      <c r="CE2" s="219"/>
-      <c r="CF2" s="217" t="s">
+      <c r="CD2" s="216"/>
+      <c r="CE2" s="217"/>
+      <c r="CF2" s="215" t="s">
         <v>305</v>
       </c>
-      <c r="CG2" s="218"/>
-      <c r="CH2" s="219"/>
-      <c r="CI2" s="217" t="s">
+      <c r="CG2" s="216"/>
+      <c r="CH2" s="217"/>
+      <c r="CI2" s="215" t="s">
         <v>326</v>
       </c>
-      <c r="CJ2" s="218"/>
-      <c r="CK2" s="219"/>
-      <c r="CL2" s="217" t="s">
+      <c r="CJ2" s="216"/>
+      <c r="CK2" s="217"/>
+      <c r="CL2" s="215" t="s">
         <v>330</v>
       </c>
-      <c r="CM2" s="218"/>
-      <c r="CN2" s="219"/>
-      <c r="CO2" s="217" t="s">
+      <c r="CM2" s="216"/>
+      <c r="CN2" s="217"/>
+      <c r="CO2" s="215" t="s">
         <v>328</v>
       </c>
-      <c r="CP2" s="218"/>
-      <c r="CQ2" s="219"/>
-      <c r="CR2" s="217" t="s">
+      <c r="CP2" s="216"/>
+      <c r="CQ2" s="217"/>
+      <c r="CR2" s="215" t="s">
         <v>346</v>
       </c>
-      <c r="CS2" s="218"/>
-      <c r="CT2" s="219"/>
-      <c r="CU2" s="217" t="s">
+      <c r="CS2" s="216"/>
+      <c r="CT2" s="217"/>
+      <c r="CU2" s="215" t="s">
         <v>331</v>
       </c>
-      <c r="CV2" s="218"/>
-      <c r="CW2" s="219"/>
-      <c r="CX2" s="217" t="s">
+      <c r="CV2" s="216"/>
+      <c r="CW2" s="217"/>
+      <c r="CX2" s="215" t="s">
         <v>336</v>
       </c>
-      <c r="CY2" s="218"/>
-      <c r="CZ2" s="219"/>
-      <c r="DA2" s="217" t="s">
+      <c r="CY2" s="216"/>
+      <c r="CZ2" s="217"/>
+      <c r="DA2" s="215" t="s">
         <v>329</v>
       </c>
-      <c r="DB2" s="218"/>
-      <c r="DC2" s="219"/>
-      <c r="DD2" s="217" t="s">
+      <c r="DB2" s="216"/>
+      <c r="DC2" s="217"/>
+      <c r="DD2" s="215" t="s">
         <v>320</v>
       </c>
-      <c r="DE2" s="218"/>
-      <c r="DF2" s="219"/>
-      <c r="DG2" s="217" t="s">
+      <c r="DE2" s="216"/>
+      <c r="DF2" s="217"/>
+      <c r="DG2" s="215" t="s">
         <v>337</v>
       </c>
-      <c r="DH2" s="218"/>
-      <c r="DI2" s="219"/>
-      <c r="DJ2" s="217" t="s">
+      <c r="DH2" s="216"/>
+      <c r="DI2" s="217"/>
+      <c r="DJ2" s="215" t="s">
         <v>334</v>
       </c>
-      <c r="DK2" s="218"/>
-      <c r="DL2" s="219"/>
-      <c r="DM2" s="217" t="s">
+      <c r="DK2" s="216"/>
+      <c r="DL2" s="217"/>
+      <c r="DM2" s="215" t="s">
         <v>335</v>
       </c>
-      <c r="DN2" s="218"/>
-      <c r="DO2" s="219"/>
+      <c r="DN2" s="216"/>
+      <c r="DO2" s="217"/>
     </row>
     <row r="3" spans="1:119" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -38135,7 +38132,7 @@
       </c>
       <c r="C3" s="222"/>
       <c r="D3" s="222"/>
-      <c r="E3" s="221"/>
+      <c r="E3" s="223"/>
       <c r="F3" s="160" t="s">
         <v>393</v>
       </c>
@@ -40165,15 +40162,15 @@
         <v>432</v>
       </c>
       <c r="C16" s="58">
-        <f t="shared" ref="C16:C38" si="4">SUM(F16,I16,L16,O16,R16,U16,X16,AA16,AD16,AG16,AJ16,AM16,AP16,AS16,AV16,AY16,BB16,BE16,BH16,BK16,BN16,BQ16,BT16,BW16,BZ16,CC16,CF16,CI16,CL16,CO16,CR16,CU16,CX16,DA16,DD16,DG16,DJ16,DM16)</f>
+        <f t="shared" ref="C16:C28" si="4">SUM(F16,I16,L16,O16,R16,U16,X16,AA16,AD16,AG16,AJ16,AM16,AP16,AS16,AV16,AY16,BB16,BE16,BH16,BK16,BN16,BQ16,BT16,BW16,BZ16,CC16,CF16,CI16,CL16,CO16,CR16,CU16,CX16,DA16,DD16,DG16,DJ16,DM16)</f>
         <v>3</v>
       </c>
       <c r="D16" s="58">
-        <f t="shared" ref="D16:D38" si="5">SUM(G16,J16,M16,P16,S16,V16,Y16,AB16,AE16,AH16,AK16,AN16,AQ16,AT16,AW16,AZ16,BC16,BF16,BI16,BL16,BO16,BR16,BU16,BX16,CA16,CD16,CG16,CJ16,CM16,CP16,CS16,CV16,CY16,DB16,DE16,DH16,DK16,DN16)</f>
+        <f t="shared" ref="D16:D28" si="5">SUM(G16,J16,M16,P16,S16,V16,Y16,AB16,AE16,AH16,AK16,AN16,AQ16,AT16,AW16,AZ16,BC16,BF16,BI16,BL16,BO16,BR16,BU16,BX16,CA16,CD16,CG16,CJ16,CM16,CP16,CS16,CV16,CY16,DB16,DE16,DH16,DK16,DN16)</f>
         <v>0</v>
       </c>
       <c r="E16" s="51">
-        <f t="shared" ref="E16:E38" si="6">SUM(H16,K16,N16,Q16,T16,W16,Z16,AC16,AF16,AI16,AL16,AO16,AR16,AU16,AX16,BA16,BD16,BG16,BJ16,BM16,BP16,BS16,BV16,BY16,CB16,CE16,CH16,CK16,CN16,CQ16,CT16,CW16,CZ16,DC16,DF16,DI16,DL16,DO16)</f>
+        <f t="shared" ref="E16:E28" si="6">SUM(H16,K16,N16,Q16,T16,W16,Z16,AC16,AF16,AI16,AL16,AO16,AR16,AU16,AX16,BA16,BD16,BG16,BJ16,BM16,BP16,BS16,BV16,BY16,CB16,CE16,CH16,CK16,CN16,CQ16,CT16,CW16,CZ16,DC16,DF16,DI16,DL16,DO16)</f>
         <v>0</v>
       </c>
       <c r="F16" s="52"/>
@@ -42250,7 +42247,7 @@
         <v>45</v>
       </c>
       <c r="B31" s="148" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C31" s="58">
         <f t="shared" ref="C31:C38" si="8">SUM(F31,I31,L31,O31,R31,U31,X31,AA31,AD31,AG31,AJ31,AM31,AP31,AS31,AV31,AY31,BB31,BE31,BH31,BK31,BN31,BQ31,BT31,BW31,BZ31,CC31,CF31,CI31,CL31,CO31,CR31,CU31,CX31,DA31,DD31,DG31,DJ31,DM31)</f>
@@ -43790,6 +43787,69 @@
     </row>
   </sheetData>
   <mergeCells count="79">
+    <mergeCell ref="DM1:DO1"/>
+    <mergeCell ref="DM2:DO2"/>
+    <mergeCell ref="DA1:DC1"/>
+    <mergeCell ref="DA2:DC2"/>
+    <mergeCell ref="DD1:DF1"/>
+    <mergeCell ref="DD2:DF2"/>
+    <mergeCell ref="DG1:DI1"/>
+    <mergeCell ref="DG2:DI2"/>
+    <mergeCell ref="CU1:CW1"/>
+    <mergeCell ref="CU2:CW2"/>
+    <mergeCell ref="CX1:CZ1"/>
+    <mergeCell ref="CX2:CZ2"/>
+    <mergeCell ref="DJ1:DL1"/>
+    <mergeCell ref="DJ2:DL2"/>
+    <mergeCell ref="CL1:CN1"/>
+    <mergeCell ref="CL2:CN2"/>
+    <mergeCell ref="CO1:CQ1"/>
+    <mergeCell ref="CO2:CQ2"/>
+    <mergeCell ref="CR1:CT1"/>
+    <mergeCell ref="CR2:CT2"/>
+    <mergeCell ref="CC1:CE1"/>
+    <mergeCell ref="CC2:CE2"/>
+    <mergeCell ref="CF1:CH1"/>
+    <mergeCell ref="CF2:CH2"/>
+    <mergeCell ref="CI1:CK1"/>
+    <mergeCell ref="CI2:CK2"/>
+    <mergeCell ref="BT1:BV1"/>
+    <mergeCell ref="BT2:BV2"/>
+    <mergeCell ref="BW1:BY1"/>
+    <mergeCell ref="BW2:BY2"/>
+    <mergeCell ref="BZ1:CB1"/>
+    <mergeCell ref="BZ2:CB2"/>
+    <mergeCell ref="BK1:BM1"/>
+    <mergeCell ref="BK2:BM2"/>
+    <mergeCell ref="BN1:BP1"/>
+    <mergeCell ref="BN2:BP2"/>
+    <mergeCell ref="BQ1:BS1"/>
+    <mergeCell ref="BQ2:BS2"/>
+    <mergeCell ref="AS1:AU1"/>
+    <mergeCell ref="AS2:AU2"/>
+    <mergeCell ref="AV1:AX1"/>
+    <mergeCell ref="AV2:AX2"/>
+    <mergeCell ref="BH1:BJ1"/>
+    <mergeCell ref="BH2:BJ2"/>
+    <mergeCell ref="AY2:BA2"/>
+    <mergeCell ref="BB2:BD2"/>
+    <mergeCell ref="BE2:BG2"/>
+    <mergeCell ref="AJ1:AL1"/>
+    <mergeCell ref="AJ2:AL2"/>
+    <mergeCell ref="AM1:AO1"/>
+    <mergeCell ref="AM2:AO2"/>
+    <mergeCell ref="AP2:AR2"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
     <mergeCell ref="AD2:AF2"/>
     <mergeCell ref="AG2:AI2"/>
     <mergeCell ref="BB1:BD1"/>
@@ -43806,69 +43866,6 @@
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="X1:Z1"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="AJ1:AL1"/>
-    <mergeCell ref="AJ2:AL2"/>
-    <mergeCell ref="AM1:AO1"/>
-    <mergeCell ref="AM2:AO2"/>
-    <mergeCell ref="AP2:AR2"/>
-    <mergeCell ref="AS1:AU1"/>
-    <mergeCell ref="AS2:AU2"/>
-    <mergeCell ref="AV1:AX1"/>
-    <mergeCell ref="AV2:AX2"/>
-    <mergeCell ref="BH1:BJ1"/>
-    <mergeCell ref="BH2:BJ2"/>
-    <mergeCell ref="AY2:BA2"/>
-    <mergeCell ref="BB2:BD2"/>
-    <mergeCell ref="BE2:BG2"/>
-    <mergeCell ref="BK1:BM1"/>
-    <mergeCell ref="BK2:BM2"/>
-    <mergeCell ref="BN1:BP1"/>
-    <mergeCell ref="BN2:BP2"/>
-    <mergeCell ref="BQ1:BS1"/>
-    <mergeCell ref="BQ2:BS2"/>
-    <mergeCell ref="BT1:BV1"/>
-    <mergeCell ref="BT2:BV2"/>
-    <mergeCell ref="BW1:BY1"/>
-    <mergeCell ref="BW2:BY2"/>
-    <mergeCell ref="BZ1:CB1"/>
-    <mergeCell ref="BZ2:CB2"/>
-    <mergeCell ref="CC1:CE1"/>
-    <mergeCell ref="CC2:CE2"/>
-    <mergeCell ref="CF1:CH1"/>
-    <mergeCell ref="CF2:CH2"/>
-    <mergeCell ref="CI1:CK1"/>
-    <mergeCell ref="CI2:CK2"/>
-    <mergeCell ref="CL1:CN1"/>
-    <mergeCell ref="CL2:CN2"/>
-    <mergeCell ref="CO1:CQ1"/>
-    <mergeCell ref="CO2:CQ2"/>
-    <mergeCell ref="CR1:CT1"/>
-    <mergeCell ref="CR2:CT2"/>
-    <mergeCell ref="CU1:CW1"/>
-    <mergeCell ref="CU2:CW2"/>
-    <mergeCell ref="CX1:CZ1"/>
-    <mergeCell ref="CX2:CZ2"/>
-    <mergeCell ref="DJ1:DL1"/>
-    <mergeCell ref="DJ2:DL2"/>
-    <mergeCell ref="DM1:DO1"/>
-    <mergeCell ref="DM2:DO2"/>
-    <mergeCell ref="DA1:DC1"/>
-    <mergeCell ref="DA2:DC2"/>
-    <mergeCell ref="DD1:DF1"/>
-    <mergeCell ref="DD2:DF2"/>
-    <mergeCell ref="DG1:DI1"/>
-    <mergeCell ref="DG2:DI2"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:DO38">
     <cfRule type="cellIs" dxfId="18" priority="1" operator="between">
@@ -43904,138 +43901,138 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="232" t="s">
+      <c r="C1" s="236" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="232" t="s">
+      <c r="D1" s="236" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="232" t="s">
+      <c r="E1" s="236" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="223" t="s">
+      <c r="F1" s="227" t="s">
         <v>302</v>
       </c>
-      <c r="G1" s="224"/>
-      <c r="H1" s="224"/>
-      <c r="I1" s="224"/>
-      <c r="J1" s="224"/>
-      <c r="K1" s="224"/>
-      <c r="L1" s="224"/>
-      <c r="M1" s="224"/>
-      <c r="N1" s="224"/>
-      <c r="O1" s="224"/>
-      <c r="P1" s="224"/>
-      <c r="Q1" s="224"/>
-      <c r="R1" s="224"/>
-      <c r="S1" s="224"/>
-      <c r="T1" s="224"/>
-      <c r="U1" s="224"/>
-      <c r="V1" s="224"/>
-      <c r="W1" s="224"/>
-      <c r="X1" s="224"/>
-      <c r="Y1" s="224"/>
-      <c r="Z1" s="224"/>
-      <c r="AA1" s="224"/>
-      <c r="AB1" s="224"/>
-      <c r="AC1" s="225"/>
-      <c r="AD1" s="238" t="s">
+      <c r="G1" s="228"/>
+      <c r="H1" s="228"/>
+      <c r="I1" s="228"/>
+      <c r="J1" s="228"/>
+      <c r="K1" s="228"/>
+      <c r="L1" s="228"/>
+      <c r="M1" s="228"/>
+      <c r="N1" s="228"/>
+      <c r="O1" s="228"/>
+      <c r="P1" s="228"/>
+      <c r="Q1" s="228"/>
+      <c r="R1" s="228"/>
+      <c r="S1" s="228"/>
+      <c r="T1" s="228"/>
+      <c r="U1" s="228"/>
+      <c r="V1" s="228"/>
+      <c r="W1" s="228"/>
+      <c r="X1" s="228"/>
+      <c r="Y1" s="228"/>
+      <c r="Z1" s="228"/>
+      <c r="AA1" s="228"/>
+      <c r="AB1" s="228"/>
+      <c r="AC1" s="229"/>
+      <c r="AD1" s="239" t="s">
         <v>281</v>
       </c>
-      <c r="AE1" s="239"/>
-      <c r="AF1" s="239"/>
-      <c r="AG1" s="239"/>
-      <c r="AH1" s="239"/>
-      <c r="AI1" s="240"/>
-      <c r="AJ1" s="223" t="s">
+      <c r="AE1" s="240"/>
+      <c r="AF1" s="240"/>
+      <c r="AG1" s="240"/>
+      <c r="AH1" s="240"/>
+      <c r="AI1" s="241"/>
+      <c r="AJ1" s="227" t="s">
         <v>282</v>
       </c>
-      <c r="AK1" s="224"/>
-      <c r="AL1" s="224"/>
-      <c r="AM1" s="224"/>
-      <c r="AN1" s="224"/>
-      <c r="AO1" s="225"/>
-      <c r="AP1" s="226" t="s">
+      <c r="AK1" s="228"/>
+      <c r="AL1" s="228"/>
+      <c r="AM1" s="228"/>
+      <c r="AN1" s="228"/>
+      <c r="AO1" s="229"/>
+      <c r="AP1" s="230" t="s">
         <v>283</v>
       </c>
-      <c r="AQ1" s="227"/>
-      <c r="AR1" s="227"/>
-      <c r="AS1" s="227"/>
-      <c r="AT1" s="227"/>
-      <c r="AU1" s="228"/>
-      <c r="AV1" s="229" t="s">
+      <c r="AQ1" s="231"/>
+      <c r="AR1" s="231"/>
+      <c r="AS1" s="231"/>
+      <c r="AT1" s="231"/>
+      <c r="AU1" s="232"/>
+      <c r="AV1" s="233" t="s">
         <v>86</v>
       </c>
-      <c r="AW1" s="230"/>
-      <c r="AX1" s="231"/>
+      <c r="AW1" s="234"/>
+      <c r="AX1" s="235"/>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="233"/>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="235" t="s">
+      <c r="C2" s="237"/>
+      <c r="D2" s="237"/>
+      <c r="E2" s="237"/>
+      <c r="F2" s="224" t="s">
         <v>463</v>
       </c>
-      <c r="G2" s="236"/>
-      <c r="H2" s="237"/>
-      <c r="I2" s="235" t="s">
+      <c r="G2" s="225"/>
+      <c r="H2" s="226"/>
+      <c r="I2" s="224" t="s">
         <v>473</v>
       </c>
-      <c r="J2" s="236"/>
-      <c r="K2" s="237"/>
-      <c r="L2" s="235" t="s">
+      <c r="J2" s="225"/>
+      <c r="K2" s="226"/>
+      <c r="L2" s="224" t="s">
         <v>474</v>
       </c>
-      <c r="M2" s="236"/>
-      <c r="N2" s="237"/>
-      <c r="O2" s="235" t="s">
+      <c r="M2" s="225"/>
+      <c r="N2" s="226"/>
+      <c r="O2" s="224" t="s">
         <v>475</v>
       </c>
-      <c r="P2" s="236"/>
-      <c r="Q2" s="237"/>
-      <c r="R2" s="235" t="s">
+      <c r="P2" s="225"/>
+      <c r="Q2" s="226"/>
+      <c r="R2" s="224" t="s">
         <v>476</v>
       </c>
-      <c r="S2" s="236"/>
-      <c r="T2" s="237"/>
-      <c r="U2" s="235" t="s">
+      <c r="S2" s="225"/>
+      <c r="T2" s="226"/>
+      <c r="U2" s="224" t="s">
         <v>477</v>
       </c>
-      <c r="V2" s="236"/>
-      <c r="W2" s="237"/>
-      <c r="X2" s="235" t="s">
+      <c r="V2" s="225"/>
+      <c r="W2" s="226"/>
+      <c r="X2" s="224" t="s">
         <v>478</v>
       </c>
-      <c r="Y2" s="236"/>
-      <c r="Z2" s="237"/>
-      <c r="AA2" s="235" t="s">
+      <c r="Y2" s="225"/>
+      <c r="Z2" s="226"/>
+      <c r="AA2" s="224" t="s">
         <v>479</v>
       </c>
-      <c r="AB2" s="236"/>
-      <c r="AC2" s="236"/>
-      <c r="AD2" s="235"/>
-      <c r="AE2" s="236"/>
-      <c r="AF2" s="237"/>
-      <c r="AG2" s="235"/>
-      <c r="AH2" s="236"/>
-      <c r="AI2" s="237"/>
-      <c r="AJ2" s="235"/>
-      <c r="AK2" s="236"/>
-      <c r="AL2" s="237"/>
-      <c r="AM2" s="235"/>
-      <c r="AN2" s="236"/>
-      <c r="AO2" s="237"/>
-      <c r="AP2" s="235"/>
-      <c r="AQ2" s="236"/>
-      <c r="AR2" s="237"/>
-      <c r="AS2" s="235"/>
-      <c r="AT2" s="236"/>
-      <c r="AU2" s="237"/>
-      <c r="AV2" s="235"/>
-      <c r="AW2" s="236"/>
-      <c r="AX2" s="237"/>
+      <c r="AB2" s="225"/>
+      <c r="AC2" s="225"/>
+      <c r="AD2" s="224"/>
+      <c r="AE2" s="225"/>
+      <c r="AF2" s="226"/>
+      <c r="AG2" s="224"/>
+      <c r="AH2" s="225"/>
+      <c r="AI2" s="226"/>
+      <c r="AJ2" s="224"/>
+      <c r="AK2" s="225"/>
+      <c r="AL2" s="226"/>
+      <c r="AM2" s="224"/>
+      <c r="AN2" s="225"/>
+      <c r="AO2" s="226"/>
+      <c r="AP2" s="224"/>
+      <c r="AQ2" s="225"/>
+      <c r="AR2" s="226"/>
+      <c r="AS2" s="224"/>
+      <c r="AT2" s="225"/>
+      <c r="AU2" s="226"/>
+      <c r="AV2" s="224"/>
+      <c r="AW2" s="225"/>
+      <c r="AX2" s="226"/>
     </row>
     <row r="3" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -44044,9 +44041,9 @@
       <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="234"/>
-      <c r="D3" s="234"/>
-      <c r="E3" s="234"/>
+      <c r="C3" s="238"/>
+      <c r="D3" s="238"/>
+      <c r="E3" s="238"/>
       <c r="F3" s="169" t="s">
         <v>393</v>
       </c>
@@ -44989,15 +44986,15 @@
         <v>432</v>
       </c>
       <c r="C16" s="58">
-        <f t="shared" ref="C16:C38" si="4">SUM(F16,I16,L16,O16,R16,X16,AA16,AD16,U16,AG16,AJ16,AM16,AP16,AS16,AV16)</f>
+        <f t="shared" ref="C16:C28" si="4">SUM(F16,I16,L16,O16,R16,X16,AA16,AD16,U16,AG16,AJ16,AM16,AP16,AS16,AV16)</f>
         <v>1</v>
       </c>
       <c r="D16" s="58">
-        <f t="shared" ref="D16:D38" si="5">SUM(G16,J16,M16,P16,S16,Y16,AB16,AE16,V16,AH16,AK16,AN16,AQ16,AT16,AW16)</f>
+        <f t="shared" ref="D16:D28" si="5">SUM(G16,J16,M16,P16,S16,Y16,AB16,AE16,V16,AH16,AK16,AN16,AQ16,AT16,AW16)</f>
         <v>0</v>
       </c>
       <c r="E16" s="58">
-        <f t="shared" ref="E16:E38" si="6">SUM(H16,K16,N16,Q16,T16,Z16,AC16,AF16,W16,AI16,AL16,AO16,AR16,AU16,AX16)</f>
+        <f t="shared" ref="E16:E28" si="6">SUM(H16,K16,N16,Q16,T16,Z16,AC16,AF16,W16,AI16,AL16,AO16,AR16,AU16,AX16)</f>
         <v>0</v>
       </c>
       <c r="F16" s="52">
@@ -45979,7 +45976,7 @@
         <v>45</v>
       </c>
       <c r="B31" s="148" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C31" s="58">
         <f t="shared" ref="C31:C38" si="8">SUM(F31,I31,L31,O31,R31,X31,AA31,AD31,U31,AG31,AJ31,AM31,AP31,AS31,AV31)</f>
@@ -46678,13 +46675,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="F1:AC1"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="AJ1:AO1"/>
     <mergeCell ref="AP1:AU1"/>
     <mergeCell ref="AV1:AX1"/>
@@ -46701,6 +46691,13 @@
     <mergeCell ref="AD1:AI1"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="I2:K2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="F1:AC1"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
+    <mergeCell ref="AA2:AC2"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:AW32">
     <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
@@ -46735,70 +46732,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C1" s="232" t="s">
+      <c r="C1" s="236" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="232" t="s">
+      <c r="D1" s="236" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="232" t="s">
+      <c r="E1" s="236" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="272" t="s">
+      <c r="F1" s="266" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="273"/>
-      <c r="H1" s="274"/>
-      <c r="I1" s="275" t="s">
+      <c r="G1" s="267"/>
+      <c r="H1" s="268"/>
+      <c r="I1" s="269" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="276"/>
-      <c r="K1" s="277"/>
-      <c r="L1" s="242" t="s">
+      <c r="J1" s="270"/>
+      <c r="K1" s="271"/>
+      <c r="L1" s="273" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="243"/>
-      <c r="N1" s="244"/>
-      <c r="O1" s="245" t="s">
+      <c r="M1" s="274"/>
+      <c r="N1" s="275"/>
+      <c r="O1" s="276" t="s">
         <v>199</v>
       </c>
-      <c r="P1" s="246"/>
-      <c r="Q1" s="247"/>
-      <c r="R1" s="248" t="s">
+      <c r="P1" s="277"/>
+      <c r="Q1" s="278"/>
+      <c r="R1" s="242" t="s">
         <v>200</v>
       </c>
-      <c r="S1" s="249"/>
-      <c r="T1" s="250"/>
-      <c r="U1" s="251" t="s">
+      <c r="S1" s="243"/>
+      <c r="T1" s="244"/>
+      <c r="U1" s="245" t="s">
         <v>306</v>
       </c>
-      <c r="V1" s="252"/>
-      <c r="W1" s="253"/>
+      <c r="V1" s="246"/>
+      <c r="W1" s="247"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="233"/>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="254"/>
-      <c r="G2" s="255"/>
-      <c r="H2" s="256"/>
-      <c r="I2" s="269"/>
-      <c r="J2" s="270"/>
-      <c r="K2" s="271"/>
-      <c r="L2" s="266"/>
-      <c r="M2" s="267"/>
-      <c r="N2" s="268"/>
-      <c r="O2" s="263"/>
-      <c r="P2" s="264"/>
-      <c r="Q2" s="265"/>
-      <c r="R2" s="260"/>
-      <c r="S2" s="261"/>
-      <c r="T2" s="262"/>
-      <c r="U2" s="257"/>
-      <c r="V2" s="258"/>
-      <c r="W2" s="259"/>
+      <c r="C2" s="237"/>
+      <c r="D2" s="237"/>
+      <c r="E2" s="237"/>
+      <c r="F2" s="248"/>
+      <c r="G2" s="249"/>
+      <c r="H2" s="250"/>
+      <c r="I2" s="263"/>
+      <c r="J2" s="264"/>
+      <c r="K2" s="265"/>
+      <c r="L2" s="260"/>
+      <c r="M2" s="261"/>
+      <c r="N2" s="262"/>
+      <c r="O2" s="257"/>
+      <c r="P2" s="258"/>
+      <c r="Q2" s="259"/>
+      <c r="R2" s="254"/>
+      <c r="S2" s="255"/>
+      <c r="T2" s="256"/>
+      <c r="U2" s="251"/>
+      <c r="V2" s="252"/>
+      <c r="W2" s="253"/>
     </row>
     <row r="3" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -46807,9 +46804,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="241"/>
-      <c r="D3" s="241"/>
-      <c r="E3" s="241"/>
+      <c r="C3" s="272"/>
+      <c r="D3" s="272"/>
+      <c r="E3" s="272"/>
       <c r="F3" s="188" t="s">
         <v>393</v>
       </c>
@@ -46949,15 +46946,15 @@
         <v>316</v>
       </c>
       <c r="C6" s="58">
-        <f t="shared" ref="C6:C38" si="2">SUM(F6,I6,L6,O6,R6,U6)</f>
+        <f t="shared" ref="C6:C28" si="2">SUM(F6,I6,L6,O6,R6,U6)</f>
         <v>0</v>
       </c>
       <c r="D6" s="58">
-        <f t="shared" ref="D6:D38" si="3">SUM(G6,J6,M6,P6,S6,V6)</f>
+        <f t="shared" ref="D6:D28" si="3">SUM(G6,J6,M6,P6,S6,V6)</f>
         <v>0</v>
       </c>
       <c r="E6" s="58">
-        <f t="shared" ref="E6:E38" si="4">SUM(H6,K6,N6,Q6,T6,W6)</f>
+        <f t="shared" ref="E6:E28" si="4">SUM(H6,K6,N6,Q6,T6,W6)</f>
         <v>0</v>
       </c>
       <c r="F6" s="52"/>
@@ -47896,7 +47893,7 @@
         <v>45</v>
       </c>
       <c r="B31" s="148" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C31" s="58">
         <f t="shared" ref="C31:C38" si="6">SUM(F31,I31,L31,O31,R31,U31)</f>
@@ -48271,6 +48268,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="O1:Q1"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="F2:H2"/>
@@ -48281,11 +48283,6 @@
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="O1:Q1"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:W32">
     <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
@@ -53722,7 +53719,7 @@
         <v>45</v>
       </c>
       <c r="B33" s="22" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C33" s="25">
         <v>0</v>
@@ -53762,7 +53759,7 @@
         <v>45</v>
       </c>
       <c r="N33" s="45" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="O33" s="26">
         <v>0</v>
@@ -53799,7 +53796,7 @@
         <v>0</v>
       </c>
       <c r="Z33" s="23" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="AA33" s="24">
         <v>0</v>
@@ -53836,7 +53833,7 @@
         <v>0</v>
       </c>
       <c r="AL33" s="19" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="AM33" s="18">
         <v>0</v>
@@ -53873,7 +53870,7 @@
         <v>0</v>
       </c>
       <c r="AX33" s="32" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="AY33" s="33">
         <v>0</v>
@@ -55292,72 +55289,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C1" s="232" t="s">
+      <c r="C1" s="236" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="232" t="s">
+      <c r="D1" s="236" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="232" t="s">
+      <c r="E1" s="236" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="272" t="s">
+      <c r="F1" s="266" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="273"/>
-      <c r="H1" s="274"/>
-      <c r="I1" s="275" t="s">
+      <c r="G1" s="267"/>
+      <c r="H1" s="268"/>
+      <c r="I1" s="269" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="276"/>
-      <c r="K1" s="277"/>
-      <c r="L1" s="242" t="s">
+      <c r="J1" s="270"/>
+      <c r="K1" s="271"/>
+      <c r="L1" s="273" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="243"/>
-      <c r="N1" s="244"/>
-      <c r="O1" s="245" t="s">
+      <c r="M1" s="274"/>
+      <c r="N1" s="275"/>
+      <c r="O1" s="276" t="s">
         <v>199</v>
       </c>
-      <c r="P1" s="246"/>
-      <c r="Q1" s="247"/>
-      <c r="R1" s="248" t="s">
+      <c r="P1" s="277"/>
+      <c r="Q1" s="278"/>
+      <c r="R1" s="242" t="s">
         <v>200</v>
       </c>
-      <c r="S1" s="249"/>
-      <c r="T1" s="250"/>
-      <c r="U1" s="251" t="s">
+      <c r="S1" s="243"/>
+      <c r="T1" s="244"/>
+      <c r="U1" s="245" t="s">
         <v>306</v>
       </c>
-      <c r="V1" s="252"/>
-      <c r="W1" s="253"/>
+      <c r="V1" s="246"/>
+      <c r="W1" s="247"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="233"/>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="254" t="s">
+      <c r="C2" s="237"/>
+      <c r="D2" s="237"/>
+      <c r="E2" s="237"/>
+      <c r="F2" s="248" t="s">
         <v>433</v>
       </c>
-      <c r="G2" s="255"/>
-      <c r="H2" s="256"/>
-      <c r="I2" s="269"/>
-      <c r="J2" s="270"/>
-      <c r="K2" s="271"/>
-      <c r="L2" s="266"/>
-      <c r="M2" s="267"/>
-      <c r="N2" s="268"/>
-      <c r="O2" s="263"/>
-      <c r="P2" s="264"/>
-      <c r="Q2" s="265"/>
-      <c r="R2" s="260"/>
-      <c r="S2" s="261"/>
-      <c r="T2" s="262"/>
-      <c r="U2" s="257"/>
-      <c r="V2" s="258"/>
-      <c r="W2" s="259"/>
+      <c r="G2" s="249"/>
+      <c r="H2" s="250"/>
+      <c r="I2" s="263"/>
+      <c r="J2" s="264"/>
+      <c r="K2" s="265"/>
+      <c r="L2" s="260"/>
+      <c r="M2" s="261"/>
+      <c r="N2" s="262"/>
+      <c r="O2" s="257"/>
+      <c r="P2" s="258"/>
+      <c r="Q2" s="259"/>
+      <c r="R2" s="254"/>
+      <c r="S2" s="255"/>
+      <c r="T2" s="256"/>
+      <c r="U2" s="251"/>
+      <c r="V2" s="252"/>
+      <c r="W2" s="253"/>
     </row>
     <row r="3" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -55366,9 +55363,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="241"/>
-      <c r="D3" s="241"/>
-      <c r="E3" s="241"/>
+      <c r="C3" s="272"/>
+      <c r="D3" s="272"/>
+      <c r="E3" s="272"/>
       <c r="F3" s="188" t="s">
         <v>393</v>
       </c>
@@ -55900,15 +55897,15 @@
         <v>432</v>
       </c>
       <c r="C16" s="58">
-        <f t="shared" ref="C16:C38" si="2">SUM(F16,I16,L16,O16,R16,U16)</f>
+        <f t="shared" ref="C16:C28" si="2">SUM(F16,I16,L16,O16,R16,U16)</f>
         <v>1</v>
       </c>
       <c r="D16" s="51">
-        <f t="shared" ref="D16:D38" si="3">SUM(G16,J16,M16,P16,S16,V16)</f>
+        <f t="shared" ref="D16:D28" si="3">SUM(G16,J16,M16,P16,S16,V16)</f>
         <v>0</v>
       </c>
       <c r="E16" s="58">
-        <f t="shared" ref="E16:E38" si="4">SUM(H16,K16,N16,Q16,T16,W16)</f>
+        <f t="shared" ref="E16:E28" si="4">SUM(H16,K16,N16,Q16,T16,W16)</f>
         <v>0</v>
       </c>
       <c r="F16" s="52">
@@ -56487,7 +56484,7 @@
         <v>45</v>
       </c>
       <c r="B31" s="148" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C31" s="58">
         <f t="shared" ref="C31:C38" si="6">SUM(F31,I31,L31,O31,R31,U31)</f>
@@ -56872,11 +56869,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="F2:H2"/>
@@ -56887,6 +56879,11 @@
     <mergeCell ref="U2:W2"/>
     <mergeCell ref="L1:N1"/>
     <mergeCell ref="O1:Q1"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:W32">
     <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
@@ -56914,11 +56911,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C1" s="278" t="s">
+      <c r="C1" s="279" t="s">
         <v>340</v>
       </c>
-      <c r="D1" s="279"/>
-      <c r="E1" s="279"/>
+      <c r="D1" s="280"/>
+      <c r="E1" s="280"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -57279,7 +57276,7 @@
         <v>45</v>
       </c>
       <c r="B30" s="148" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C30" s="20"/>
       <c r="D30" s="20"/>
@@ -57393,51 +57390,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="300" t="s">
+      <c r="C1" s="282" t="s">
         <v>202</v>
       </c>
-      <c r="D1" s="301"/>
-      <c r="E1" s="301"/>
-      <c r="F1" s="301"/>
-      <c r="G1" s="301"/>
-      <c r="H1" s="301"/>
-      <c r="I1" s="302"/>
+      <c r="D1" s="283"/>
+      <c r="E1" s="283"/>
+      <c r="F1" s="283"/>
+      <c r="G1" s="283"/>
+      <c r="H1" s="283"/>
+      <c r="I1" s="284"/>
       <c r="J1" s="114" t="s">
         <v>195</v>
       </c>
       <c r="K1" s="115" t="s">
         <v>194</v>
       </c>
-      <c r="L1" s="280" t="s">
+      <c r="L1" s="306" t="s">
         <v>287</v>
       </c>
-      <c r="M1" s="285"/>
-      <c r="N1" s="285"/>
-      <c r="O1" s="285"/>
-      <c r="P1" s="285"/>
-      <c r="Q1" s="285"/>
-      <c r="R1" s="285"/>
-      <c r="S1" s="285"/>
-      <c r="T1" s="285"/>
-      <c r="U1" s="285"/>
-      <c r="V1" s="285"/>
-      <c r="W1" s="285"/>
-      <c r="X1" s="285"/>
-      <c r="Y1" s="285"/>
-      <c r="Z1" s="285"/>
-      <c r="AA1" s="285"/>
-      <c r="AB1" s="285"/>
-      <c r="AC1" s="285"/>
-      <c r="AD1" s="285"/>
-      <c r="AE1" s="285"/>
-      <c r="AF1" s="285"/>
-      <c r="AG1" s="286"/>
-      <c r="AH1" s="280" t="s">
+      <c r="M1" s="311"/>
+      <c r="N1" s="311"/>
+      <c r="O1" s="311"/>
+      <c r="P1" s="311"/>
+      <c r="Q1" s="311"/>
+      <c r="R1" s="311"/>
+      <c r="S1" s="311"/>
+      <c r="T1" s="311"/>
+      <c r="U1" s="311"/>
+      <c r="V1" s="311"/>
+      <c r="W1" s="311"/>
+      <c r="X1" s="311"/>
+      <c r="Y1" s="311"/>
+      <c r="Z1" s="311"/>
+      <c r="AA1" s="311"/>
+      <c r="AB1" s="311"/>
+      <c r="AC1" s="311"/>
+      <c r="AD1" s="311"/>
+      <c r="AE1" s="311"/>
+      <c r="AF1" s="311"/>
+      <c r="AG1" s="312"/>
+      <c r="AH1" s="306" t="s">
         <v>175</v>
       </c>
-      <c r="AI1" s="281"/>
-      <c r="AJ1" s="281"/>
-      <c r="AK1" s="282"/>
+      <c r="AI1" s="307"/>
+      <c r="AJ1" s="307"/>
+      <c r="AK1" s="308"/>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B2" s="111"/>
@@ -62637,15 +62634,15 @@
         <f t="shared" ref="J80:J111" si="2">H80-I80</f>
         <v>2</v>
       </c>
-      <c r="K80" s="287" t="s">
+      <c r="K80" s="313" t="s">
         <v>435</v>
       </c>
-      <c r="L80" s="288"/>
-      <c r="M80" s="289"/>
+      <c r="L80" s="314"/>
+      <c r="M80" s="315"/>
       <c r="O80" s="133"/>
       <c r="P80" s="133"/>
-      <c r="W80" s="283"/>
-      <c r="X80" s="283"/>
+      <c r="W80" s="309"/>
+      <c r="X80" s="309"/>
       <c r="Y80" s="70" t="s">
         <v>211</v>
       </c>
@@ -62695,15 +62692,15 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K81" s="290"/>
-      <c r="L81" s="291"/>
-      <c r="M81" s="292"/>
+      <c r="K81" s="316"/>
+      <c r="L81" s="317"/>
+      <c r="M81" s="318"/>
       <c r="O81" s="133"/>
       <c r="P81" s="133"/>
-      <c r="W81" s="283" t="s">
+      <c r="W81" s="309" t="s">
         <v>209</v>
       </c>
-      <c r="X81" s="283"/>
+      <c r="X81" s="309"/>
       <c r="Y81" s="70">
         <f>COUNTIF(L3:AG40,3)</f>
         <v>481</v>
@@ -62759,17 +62756,17 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K82" s="293" t="s">
+      <c r="K82" s="319" t="s">
         <v>436</v>
       </c>
-      <c r="L82" s="294"/>
-      <c r="M82" s="295"/>
+      <c r="L82" s="320"/>
+      <c r="M82" s="321"/>
       <c r="O82" s="133"/>
       <c r="P82" s="133"/>
-      <c r="W82" s="283" t="s">
+      <c r="W82" s="309" t="s">
         <v>210</v>
       </c>
-      <c r="X82" s="283"/>
+      <c r="X82" s="309"/>
       <c r="Y82" s="70">
         <f>COUNTIF(K3:K40,3)+COUNTIF(J3:J15,3)</f>
         <v>25</v>
@@ -62825,17 +62822,17 @@
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="K83" s="296" t="s">
+      <c r="K83" s="322" t="s">
         <v>437</v>
       </c>
-      <c r="L83" s="297"/>
-      <c r="M83" s="298"/>
+      <c r="L83" s="323"/>
+      <c r="M83" s="324"/>
       <c r="O83" s="133"/>
       <c r="P83" s="133"/>
-      <c r="W83" s="284" t="s">
+      <c r="W83" s="310" t="s">
         <v>97</v>
       </c>
-      <c r="X83" s="284"/>
+      <c r="X83" s="310"/>
       <c r="Y83" s="194">
         <f>223</f>
         <v>223</v>
@@ -62889,15 +62886,15 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="K84" s="315" t="s">
+      <c r="K84" s="297" t="s">
         <v>284</v>
       </c>
-      <c r="L84" s="316"/>
-      <c r="M84" s="317"/>
+      <c r="L84" s="298"/>
+      <c r="M84" s="299"/>
       <c r="O84" s="141"/>
       <c r="P84" s="141"/>
-      <c r="W84" s="299"/>
-      <c r="X84" s="299"/>
+      <c r="W84" s="281"/>
+      <c r="X84" s="281"/>
       <c r="Y84" s="196"/>
       <c r="Z84" s="196"/>
       <c r="AA84" s="196"/>
@@ -62935,9 +62932,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K85" s="318"/>
-      <c r="L85" s="319"/>
-      <c r="M85" s="320"/>
+      <c r="K85" s="300"/>
+      <c r="L85" s="301"/>
+      <c r="M85" s="302"/>
       <c r="O85" s="141"/>
       <c r="P85" s="141"/>
     </row>
@@ -62971,9 +62968,9 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="K86" s="318"/>
-      <c r="L86" s="319"/>
-      <c r="M86" s="320"/>
+      <c r="K86" s="300"/>
+      <c r="L86" s="301"/>
+      <c r="M86" s="302"/>
       <c r="O86" s="141"/>
       <c r="P86" s="141"/>
     </row>
@@ -63007,9 +63004,9 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="K87" s="318"/>
-      <c r="L87" s="319"/>
-      <c r="M87" s="320"/>
+      <c r="K87" s="300"/>
+      <c r="L87" s="301"/>
+      <c r="M87" s="302"/>
       <c r="O87" s="141"/>
       <c r="P87" s="141"/>
     </row>
@@ -63043,9 +63040,9 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K88" s="318"/>
-      <c r="L88" s="319"/>
-      <c r="M88" s="320"/>
+      <c r="K88" s="300"/>
+      <c r="L88" s="301"/>
+      <c r="M88" s="302"/>
       <c r="O88" s="141"/>
       <c r="P88" s="141"/>
     </row>
@@ -63079,9 +63076,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K89" s="318"/>
-      <c r="L89" s="319"/>
-      <c r="M89" s="320"/>
+      <c r="K89" s="300"/>
+      <c r="L89" s="301"/>
+      <c r="M89" s="302"/>
       <c r="O89" s="141"/>
       <c r="P89" s="141"/>
     </row>
@@ -63115,9 +63112,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K90" s="318"/>
-      <c r="L90" s="319"/>
-      <c r="M90" s="320"/>
+      <c r="K90" s="300"/>
+      <c r="L90" s="301"/>
+      <c r="M90" s="302"/>
       <c r="O90" s="141"/>
       <c r="P90" s="141"/>
     </row>
@@ -63151,9 +63148,9 @@
         <f t="shared" si="2"/>
         <v>47</v>
       </c>
-      <c r="K91" s="318"/>
-      <c r="L91" s="319"/>
-      <c r="M91" s="320"/>
+      <c r="K91" s="300"/>
+      <c r="L91" s="301"/>
+      <c r="M91" s="302"/>
       <c r="O91" s="141"/>
       <c r="P91" s="141"/>
     </row>
@@ -63187,9 +63184,9 @@
         <f t="shared" si="2"/>
         <v>51</v>
       </c>
-      <c r="K92" s="318"/>
-      <c r="L92" s="319"/>
-      <c r="M92" s="320"/>
+      <c r="K92" s="300"/>
+      <c r="L92" s="301"/>
+      <c r="M92" s="302"/>
       <c r="O92" s="141"/>
       <c r="P92" s="141"/>
     </row>
@@ -63223,9 +63220,9 @@
         <f t="shared" si="2"/>
         <v>37</v>
       </c>
-      <c r="K93" s="318"/>
-      <c r="L93" s="319"/>
-      <c r="M93" s="320"/>
+      <c r="K93" s="300"/>
+      <c r="L93" s="301"/>
+      <c r="M93" s="302"/>
       <c r="O93" s="141"/>
       <c r="P93" s="141"/>
     </row>
@@ -63259,9 +63256,9 @@
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="K94" s="318"/>
-      <c r="L94" s="319"/>
-      <c r="M94" s="320"/>
+      <c r="K94" s="300"/>
+      <c r="L94" s="301"/>
+      <c r="M94" s="302"/>
       <c r="O94" s="141"/>
       <c r="P94" s="141"/>
     </row>
@@ -63295,9 +63292,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K95" s="318"/>
-      <c r="L95" s="319"/>
-      <c r="M95" s="320"/>
+      <c r="K95" s="300"/>
+      <c r="L95" s="301"/>
+      <c r="M95" s="302"/>
       <c r="O95" s="141"/>
       <c r="P95" s="141"/>
     </row>
@@ -63331,9 +63328,9 @@
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="K96" s="318"/>
-      <c r="L96" s="319"/>
-      <c r="M96" s="320"/>
+      <c r="K96" s="300"/>
+      <c r="L96" s="301"/>
+      <c r="M96" s="302"/>
       <c r="O96" s="141"/>
       <c r="P96" s="141"/>
     </row>
@@ -63367,9 +63364,9 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="K97" s="318"/>
-      <c r="L97" s="319"/>
-      <c r="M97" s="320"/>
+      <c r="K97" s="300"/>
+      <c r="L97" s="301"/>
+      <c r="M97" s="302"/>
       <c r="O97" s="141"/>
       <c r="P97" s="141"/>
     </row>
@@ -63403,9 +63400,9 @@
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="K98" s="318"/>
-      <c r="L98" s="319"/>
-      <c r="M98" s="320"/>
+      <c r="K98" s="300"/>
+      <c r="L98" s="301"/>
+      <c r="M98" s="302"/>
       <c r="O98" s="141"/>
       <c r="P98" s="141"/>
     </row>
@@ -63439,9 +63436,9 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K99" s="318"/>
-      <c r="L99" s="319"/>
-      <c r="M99" s="320"/>
+      <c r="K99" s="300"/>
+      <c r="L99" s="301"/>
+      <c r="M99" s="302"/>
       <c r="O99" s="141"/>
       <c r="P99" s="141"/>
     </row>
@@ -63475,9 +63472,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K100" s="318"/>
-      <c r="L100" s="319"/>
-      <c r="M100" s="320"/>
+      <c r="K100" s="300"/>
+      <c r="L100" s="301"/>
+      <c r="M100" s="302"/>
       <c r="O100" s="141"/>
       <c r="P100" s="141"/>
     </row>
@@ -63511,9 +63508,9 @@
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="K101" s="318"/>
-      <c r="L101" s="319"/>
-      <c r="M101" s="320"/>
+      <c r="K101" s="300"/>
+      <c r="L101" s="301"/>
+      <c r="M101" s="302"/>
       <c r="O101" s="141"/>
       <c r="P101" s="141"/>
     </row>
@@ -63547,9 +63544,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K102" s="318"/>
-      <c r="L102" s="319"/>
-      <c r="M102" s="320"/>
+      <c r="K102" s="300"/>
+      <c r="L102" s="301"/>
+      <c r="M102" s="302"/>
       <c r="O102" s="141"/>
       <c r="P102" s="141"/>
     </row>
@@ -63583,9 +63580,9 @@
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="K103" s="318"/>
-      <c r="L103" s="319"/>
-      <c r="M103" s="320"/>
+      <c r="K103" s="300"/>
+      <c r="L103" s="301"/>
+      <c r="M103" s="302"/>
       <c r="O103" s="141"/>
       <c r="P103" s="141"/>
     </row>
@@ -63619,9 +63616,9 @@
         <f t="shared" si="2"/>
         <v>33</v>
       </c>
-      <c r="K104" s="318"/>
-      <c r="L104" s="319"/>
-      <c r="M104" s="320"/>
+      <c r="K104" s="300"/>
+      <c r="L104" s="301"/>
+      <c r="M104" s="302"/>
       <c r="O104" s="141"/>
       <c r="P104" s="141"/>
     </row>
@@ -63655,9 +63652,9 @@
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="K105" s="321"/>
-      <c r="L105" s="322"/>
-      <c r="M105" s="323"/>
+      <c r="K105" s="303"/>
+      <c r="L105" s="304"/>
+      <c r="M105" s="305"/>
       <c r="O105" s="141"/>
       <c r="P105" s="141"/>
     </row>
@@ -63691,11 +63688,11 @@
         <f t="shared" si="2"/>
         <v>21</v>
       </c>
-      <c r="K106" s="312" t="s">
+      <c r="K106" s="294" t="s">
         <v>286</v>
       </c>
-      <c r="L106" s="313"/>
-      <c r="M106" s="314"/>
+      <c r="L106" s="295"/>
+      <c r="M106" s="296"/>
       <c r="O106" s="126"/>
       <c r="P106" s="126"/>
     </row>
@@ -63729,11 +63726,11 @@
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="K107" s="312" t="s">
+      <c r="K107" s="294" t="s">
         <v>288</v>
       </c>
-      <c r="L107" s="313"/>
-      <c r="M107" s="314"/>
+      <c r="L107" s="295"/>
+      <c r="M107" s="296"/>
       <c r="O107" s="126"/>
       <c r="P107" s="126"/>
     </row>
@@ -63767,11 +63764,11 @@
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="K108" s="303" t="s">
+      <c r="K108" s="285" t="s">
         <v>289</v>
       </c>
-      <c r="L108" s="304"/>
-      <c r="M108" s="305"/>
+      <c r="L108" s="286"/>
+      <c r="M108" s="287"/>
       <c r="O108" s="126"/>
       <c r="P108" s="126"/>
     </row>
@@ -63805,9 +63802,9 @@
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="K109" s="306"/>
-      <c r="L109" s="307"/>
-      <c r="M109" s="308"/>
+      <c r="K109" s="288"/>
+      <c r="L109" s="289"/>
+      <c r="M109" s="290"/>
       <c r="O109" s="126"/>
       <c r="P109" s="126"/>
     </row>
@@ -63841,9 +63838,9 @@
         <f t="shared" si="2"/>
         <v>45</v>
       </c>
-      <c r="K110" s="306"/>
-      <c r="L110" s="307"/>
-      <c r="M110" s="308"/>
+      <c r="K110" s="288"/>
+      <c r="L110" s="289"/>
+      <c r="M110" s="290"/>
       <c r="O110" s="126"/>
       <c r="P110" s="126"/>
     </row>
@@ -63877,9 +63874,9 @@
         <f t="shared" si="2"/>
         <v>62</v>
       </c>
-      <c r="K111" s="306"/>
-      <c r="L111" s="307"/>
-      <c r="M111" s="308"/>
+      <c r="K111" s="288"/>
+      <c r="L111" s="289"/>
+      <c r="M111" s="290"/>
       <c r="O111" s="126"/>
       <c r="P111" s="126"/>
     </row>
@@ -63917,9 +63914,9 @@
         <f t="shared" ref="J112:J114" si="6">H112-I112</f>
         <v>34</v>
       </c>
-      <c r="K112" s="306"/>
-      <c r="L112" s="307"/>
-      <c r="M112" s="308"/>
+      <c r="K112" s="288"/>
+      <c r="L112" s="289"/>
+      <c r="M112" s="290"/>
     </row>
     <row r="113" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="156" t="s">
@@ -63955,9 +63952,9 @@
         <f t="shared" si="6"/>
         <v>43</v>
       </c>
-      <c r="K113" s="309"/>
-      <c r="L113" s="310"/>
-      <c r="M113" s="311"/>
+      <c r="K113" s="291"/>
+      <c r="L113" s="292"/>
+      <c r="M113" s="293"/>
     </row>
     <row r="114" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" s="93" t="s">
@@ -63997,12 +63994,6 @@
   </sheetData>
   <autoFilter ref="A79:J112" xr:uid="{9C81160F-C24B-449F-8F5A-CB622AB71070}"/>
   <mergeCells count="15">
-    <mergeCell ref="W84:X84"/>
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="K108:M113"/>
-    <mergeCell ref="K106:M106"/>
-    <mergeCell ref="K107:M107"/>
-    <mergeCell ref="K84:M105"/>
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="W80:X80"/>
     <mergeCell ref="W81:X81"/>
@@ -64012,6 +64003,12 @@
     <mergeCell ref="K80:M81"/>
     <mergeCell ref="K82:M82"/>
     <mergeCell ref="K83:M83"/>
+    <mergeCell ref="W84:X84"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="K108:M113"/>
+    <mergeCell ref="K106:M106"/>
+    <mergeCell ref="K107:M107"/>
+    <mergeCell ref="K84:M105"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <conditionalFormatting sqref="A3:A40">
@@ -64084,7 +64081,7 @@
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.42578125" bestFit="1" customWidth="1"/>
@@ -64103,32 +64100,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="324" t="s">
+      <c r="A1" s="325" t="s">
         <v>405</v>
       </c>
-      <c r="B1" s="324"/>
-      <c r="C1" s="324"/>
-      <c r="D1" s="324"/>
-      <c r="E1" s="324"/>
-      <c r="F1" s="324" t="s">
+      <c r="B1" s="325"/>
+      <c r="C1" s="325"/>
+      <c r="D1" s="325"/>
+      <c r="E1" s="325"/>
+      <c r="F1" s="325" t="s">
         <v>406</v>
       </c>
-      <c r="G1" s="324"/>
-      <c r="H1" s="324"/>
-      <c r="I1" s="324"/>
-      <c r="J1" s="324"/>
+      <c r="G1" s="325"/>
+      <c r="H1" s="325"/>
+      <c r="I1" s="325"/>
+      <c r="J1" s="325"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2" s="324"/>
-      <c r="B2" s="324"/>
-      <c r="C2" s="324"/>
-      <c r="D2" s="324"/>
-      <c r="E2" s="324"/>
-      <c r="F2" s="324"/>
-      <c r="G2" s="324"/>
-      <c r="H2" s="324"/>
-      <c r="I2" s="324"/>
-      <c r="J2" s="324"/>
+      <c r="A2" s="325"/>
+      <c r="B2" s="325"/>
+      <c r="C2" s="325"/>
+      <c r="D2" s="325"/>
+      <c r="E2" s="325"/>
+      <c r="F2" s="325"/>
+      <c r="G2" s="325"/>
+      <c r="H2" s="325"/>
+      <c r="I2" s="325"/>
+      <c r="J2" s="325"/>
       <c r="L2" t="s">
         <v>409</v>
       </c>
@@ -64233,15 +64230,15 @@
         <v>4</v>
       </c>
       <c r="D4" t="s">
+        <v>417</v>
+      </c>
+      <c r="E4" t="s">
         <v>482</v>
-      </c>
-      <c r="E4" t="s">
-        <v>483</v>
       </c>
       <c r="F4" t="s">
         <v>472</v>
       </c>
-      <c r="G4" s="328" t="s">
+      <c r="G4" s="202" t="s">
         <v>480</v>
       </c>
       <c r="H4" t="s">
@@ -64900,7 +64897,7 @@
         <v>350</v>
       </c>
       <c r="B2" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C2" s="199">
         <v>6.4</v>
@@ -64942,7 +64939,7 @@
         <v>442</v>
       </c>
       <c r="B5" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C5" s="199">
         <v>7.2</v>
@@ -65004,7 +65001,7 @@
         <v>447</v>
       </c>
       <c r="B9" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C9" s="199">
         <v>8.9</v>
@@ -65013,7 +65010,7 @@
         <v>90</v>
       </c>
       <c r="E9" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -65038,7 +65035,7 @@
         <v>449</v>
       </c>
       <c r="B11" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C11" s="199">
         <v>8.6</v>
@@ -65055,7 +65052,7 @@
         <v>450</v>
       </c>
       <c r="B12" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C12" s="199">
         <v>5.8</v>
@@ -65111,7 +65108,7 @@
         <v>446</v>
       </c>
       <c r="B16" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C16" s="199">
         <v>6.6</v>
@@ -65125,7 +65122,7 @@
         <v>443</v>
       </c>
       <c r="B17" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C17" s="199"/>
       <c r="D17" t="s">
@@ -65156,24 +65153,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="202" t="s">
+      <c r="A1" s="203" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="325"/>
-      <c r="C1" s="326" t="s">
+      <c r="B1" s="326"/>
+      <c r="C1" s="327" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="205"/>
-      <c r="E1" s="327"/>
-      <c r="H1" s="202" t="s">
+      <c r="D1" s="206"/>
+      <c r="E1" s="328"/>
+      <c r="H1" s="203" t="s">
         <v>47</v>
       </c>
-      <c r="I1" s="325"/>
-      <c r="J1" s="326" t="s">
+      <c r="I1" s="326"/>
+      <c r="J1" s="327" t="s">
         <v>44</v>
       </c>
-      <c r="K1" s="205"/>
-      <c r="L1" s="327"/>
+      <c r="K1" s="206"/>
+      <c r="L1" s="328"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -66261,9 +66258,9 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="206"/>
-      <c r="G1" s="206"/>
-      <c r="H1" s="206"/>
+      <c r="F1" s="207"/>
+      <c r="G1" s="207"/>
+      <c r="H1" s="207"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -66287,36 +66284,36 @@
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="5"/>
-      <c r="E2" s="202" t="s">
+      <c r="E2" s="203" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="203"/>
-      <c r="G2" s="204"/>
-      <c r="H2" s="207" t="s">
+      <c r="F2" s="204"/>
+      <c r="G2" s="205"/>
+      <c r="H2" s="208" t="s">
         <v>120</v>
       </c>
-      <c r="I2" s="208"/>
-      <c r="J2" s="209"/>
-      <c r="K2" s="202" t="s">
+      <c r="I2" s="209"/>
+      <c r="J2" s="210"/>
+      <c r="K2" s="203" t="s">
         <v>108</v>
       </c>
-      <c r="L2" s="203"/>
-      <c r="M2" s="204"/>
-      <c r="N2" s="207" t="s">
+      <c r="L2" s="204"/>
+      <c r="M2" s="205"/>
+      <c r="N2" s="208" t="s">
         <v>110</v>
       </c>
-      <c r="O2" s="208"/>
-      <c r="P2" s="209"/>
-      <c r="Q2" s="202" t="s">
+      <c r="O2" s="209"/>
+      <c r="P2" s="210"/>
+      <c r="Q2" s="203" t="s">
         <v>39</v>
       </c>
-      <c r="R2" s="203"/>
-      <c r="S2" s="204"/>
-      <c r="T2" s="205" t="s">
+      <c r="R2" s="204"/>
+      <c r="S2" s="205"/>
+      <c r="T2" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="U2" s="205"/>
-      <c r="V2" s="205"/>
+      <c r="U2" s="206"/>
+      <c r="V2" s="206"/>
       <c r="Z2" s="125">
         <v>46280</v>
       </c>
@@ -67494,15 +67491,15 @@
         <v>0</v>
       </c>
       <c r="T16" s="2">
-        <f t="shared" ref="T16:T38" si="5">SUM(E16,H16,K16,N16,Q16)</f>
+        <f t="shared" ref="T16:T28" si="5">SUM(E16,H16,K16,N16,Q16)</f>
         <v>5</v>
       </c>
       <c r="U16" s="2">
-        <f t="shared" ref="U16:U38" si="6">SUM(F16,I16,L16,O16,R16)</f>
+        <f t="shared" ref="U16:U28" si="6">SUM(F16,I16,L16,O16,R16)</f>
         <v>0</v>
       </c>
       <c r="V16" s="2">
-        <f t="shared" ref="V16:V38" si="7">SUM(G16,J16,M16,P16,S16)</f>
+        <f t="shared" ref="V16:V28" si="7">SUM(G16,J16,M16,P16,S16)</f>
         <v>0</v>
       </c>
     </row>
@@ -68727,7 +68724,7 @@
         <v>353</v>
       </c>
       <c r="D31" s="148" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E31" s="6">
         <f>'#'!J33</f>
@@ -69500,30 +69497,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="212" t="s">
+      <c r="D2" s="213" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="212"/>
-      <c r="F2" s="213" t="s">
+      <c r="E2" s="213"/>
+      <c r="F2" s="214" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="213"/>
-      <c r="H2" s="212" t="s">
+      <c r="G2" s="214"/>
+      <c r="H2" s="213" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="212"/>
-      <c r="J2" s="213" t="s">
+      <c r="I2" s="213"/>
+      <c r="J2" s="214" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="213"/>
-      <c r="L2" s="212" t="s">
+      <c r="K2" s="214"/>
+      <c r="L2" s="213" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="212"/>
-      <c r="N2" s="205" t="s">
+      <c r="M2" s="213"/>
+      <c r="N2" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="205"/>
+      <c r="O2" s="206"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -71520,30 +71517,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="212" t="s">
+      <c r="D2" s="213" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="212"/>
-      <c r="F2" s="213" t="s">
+      <c r="E2" s="213"/>
+      <c r="F2" s="214" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="213"/>
-      <c r="H2" s="212" t="s">
+      <c r="G2" s="214"/>
+      <c r="H2" s="213" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="212"/>
-      <c r="J2" s="213" t="s">
+      <c r="I2" s="213"/>
+      <c r="J2" s="214" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="213"/>
-      <c r="L2" s="212" t="s">
+      <c r="K2" s="214"/>
+      <c r="L2" s="213" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="212"/>
-      <c r="N2" s="205" t="s">
+      <c r="M2" s="213"/>
+      <c r="N2" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="205"/>
+      <c r="O2" s="206"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -73477,30 +73474,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="212" t="s">
+      <c r="D2" s="213" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="212"/>
-      <c r="F2" s="213" t="s">
+      <c r="E2" s="213"/>
+      <c r="F2" s="214" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="213"/>
-      <c r="H2" s="212" t="s">
+      <c r="G2" s="214"/>
+      <c r="H2" s="213" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="212"/>
-      <c r="J2" s="213" t="s">
+      <c r="I2" s="213"/>
+      <c r="J2" s="214" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="213"/>
-      <c r="L2" s="212" t="s">
+      <c r="K2" s="214"/>
+      <c r="L2" s="213" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="212"/>
-      <c r="N2" s="205" t="s">
+      <c r="M2" s="213"/>
+      <c r="N2" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="205"/>
+      <c r="O2" s="206"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -75525,30 +75522,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="212" t="s">
+      <c r="D2" s="213" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="212"/>
-      <c r="F2" s="213" t="s">
+      <c r="E2" s="213"/>
+      <c r="F2" s="214" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="213"/>
-      <c r="H2" s="212" t="s">
+      <c r="G2" s="214"/>
+      <c r="H2" s="213" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="212"/>
-      <c r="J2" s="213" t="s">
+      <c r="I2" s="213"/>
+      <c r="J2" s="214" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="213"/>
-      <c r="L2" s="212" t="s">
+      <c r="K2" s="214"/>
+      <c r="L2" s="213" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="212"/>
-      <c r="N2" s="205" t="s">
+      <c r="M2" s="213"/>
+      <c r="N2" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="205"/>
+      <c r="O2" s="206"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -77233,30 +77230,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="212" t="s">
+      <c r="C2" s="213" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="212"/>
-      <c r="E2" s="213" t="s">
+      <c r="D2" s="213"/>
+      <c r="E2" s="214" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="213"/>
-      <c r="G2" s="212" t="s">
+      <c r="F2" s="214"/>
+      <c r="G2" s="213" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="212"/>
-      <c r="I2" s="213" t="s">
+      <c r="H2" s="213"/>
+      <c r="I2" s="214" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="213"/>
-      <c r="K2" s="212" t="s">
+      <c r="J2" s="214"/>
+      <c r="K2" s="213" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="212"/>
-      <c r="M2" s="205" t="s">
+      <c r="L2" s="213"/>
+      <c r="M2" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="205"/>
+      <c r="N2" s="206"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -79018,30 +79015,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="212" t="s">
+      <c r="C2" s="213" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="212"/>
-      <c r="E2" s="213" t="s">
+      <c r="D2" s="213"/>
+      <c r="E2" s="214" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="213"/>
-      <c r="G2" s="212" t="s">
+      <c r="F2" s="214"/>
+      <c r="G2" s="213" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="212"/>
-      <c r="I2" s="213" t="s">
+      <c r="H2" s="213"/>
+      <c r="I2" s="214" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="213"/>
-      <c r="K2" s="212" t="s">
+      <c r="J2" s="214"/>
+      <c r="K2" s="213" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="212"/>
-      <c r="M2" s="205" t="s">
+      <c r="L2" s="213"/>
+      <c r="M2" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="205"/>
+      <c r="N2" s="206"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">

--- a/data/arsenal_stats.xlsx
+++ b/data/arsenal_stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bungeltd-my.sharepoint.com/personal/przemyslaw_iskra_bunge_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8528" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2AD9CD94-5203-48E1-B046-8EC9DACC8F89}"/>
+  <xr:revisionPtr revIDLastSave="8609" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D7FF3B0-8F85-4157-A8D8-CA5EBBA72F55}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="799" firstSheet="1" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="799" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="19" state="hidden" r:id="rId1"/>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2278" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2274" uniqueCount="489">
   <si>
     <t>Arsenal FC squad statistics</t>
   </si>
@@ -1462,12 +1462,6 @@
     <t>Goal/Assist</t>
   </si>
   <si>
-    <t>G</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
     <t>−3</t>
   </si>
   <si>
@@ -1480,25 +1474,10 @@
     <t>Bruno</t>
   </si>
   <si>
-    <t>Lewis-Skelly</t>
-  </si>
-  <si>
-    <t>Ipswitch</t>
-  </si>
-  <si>
-    <t>Portman Road (A)</t>
-  </si>
-  <si>
     <t>−2</t>
   </si>
   <si>
     <t>−6</t>
-  </si>
-  <si>
-    <t>−10</t>
-  </si>
-  <si>
-    <t>15.09.2026</t>
   </si>
   <si>
     <t>Lille</t>
@@ -1522,9 +1501,6 @@
     <t>Sabah</t>
   </si>
   <si>
-    <t>4-2</t>
-  </si>
-  <si>
     <t>19.09.2026</t>
   </si>
   <si>
@@ -1534,28 +1510,43 @@
     <t>JULIENNE Theo</t>
   </si>
   <si>
-    <t>Kepa</t>
-  </si>
-  <si>
-    <t>Salmon</t>
-  </si>
-  <si>
     <t>Dowman</t>
-  </si>
-  <si>
-    <t>Madueke</t>
   </si>
   <si>
     <t>Gyokeres</t>
   </si>
   <si>
-    <t>Julienne</t>
+    <t>0-3</t>
   </si>
   <si>
-    <t>Ibrahim</t>
+    <t>10.10.2026</t>
   </si>
   <si>
-    <t>G;G</t>
+    <t>Emirates Stadium (H)</t>
+  </si>
+  <si>
+    <t>−4</t>
+  </si>
+  <si>
+    <t>−9</t>
+  </si>
+  <si>
+    <t>Raya</t>
+  </si>
+  <si>
+    <t>Timber</t>
+  </si>
+  <si>
+    <t>Calafiori</t>
+  </si>
+  <si>
+    <t>Rice</t>
+  </si>
+  <si>
+    <t>Saka</t>
+  </si>
+  <si>
+    <t>Havertz</t>
   </si>
 </sst>
 </file>
@@ -2672,7 +2663,7 @@
     <xf numFmtId="0" fontId="7" fillId="9" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="17" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="329">
+  <cellXfs count="328">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3061,7 +3052,21 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3086,16 +3091,13 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3107,32 +3109,14 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="54" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3170,6 +3154,15 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="28" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3177,6 +3170,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="60" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="10" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="37" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="11" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3269,107 +3283,11 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="60" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="10" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="37" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="11" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="54" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3428,8 +3346,77 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3438,6 +3425,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
@@ -4644,7 +4634,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="33"/>
                 <c:pt idx="0">
-                  <c:v>6</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -4659,31 +4649,31 @@
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>7</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>6</c:v>
-                </c:pt>
                 <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>7</c:v>
                 </c:pt>
-                <c:pt idx="8">
-                  <c:v>6</c:v>
-                </c:pt>
                 <c:pt idx="9">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>4</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>5</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>7</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>5</c:v>
@@ -4692,31 +4682,31 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>6</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>6</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>5</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>7</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>5</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>6</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>0</c:v>
@@ -4740,7 +4730,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6493,7 +6483,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{CC776D23-6EC0-43B2-BBBF-C7138B7FCC42}" type="CELLRANGE">
+                    <a:fld id="{7BC14897-0129-46CD-A73F-B1571D32917F}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6527,7 +6517,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{BA1EA7DF-738D-4931-98BE-EA0D802F4462}" type="CELLRANGE">
+                    <a:fld id="{4178F5E4-DA8C-492B-99E6-6E605E4ED344}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6561,7 +6551,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8B04924A-DD2C-480B-9FC2-D8036F50BB02}" type="CELLRANGE">
+                    <a:fld id="{641F420A-DA3E-442F-AF78-0660F7BA5D84}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6595,7 +6585,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8E7934C5-6F2D-4E44-9CB0-3161FC77E946}" type="CELLRANGE">
+                    <a:fld id="{66EE9827-6009-4444-9E84-CD86512FA6F9}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6629,7 +6619,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{DF9685E5-48C8-403C-8D6C-1F759A19B6D4}" type="CELLRANGE">
+                    <a:fld id="{E0926421-2EA9-4F6D-B77C-001F64A5EB1C}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6663,7 +6653,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7B85DFC7-023B-45BE-9BA5-F0EF3502E622}" type="CELLRANGE">
+                    <a:fld id="{876B52FC-1DAA-4E24-BFD8-9A0CF8DF73F1}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6697,7 +6687,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{52B00131-1E14-4AC3-AA60-C8FFE2236A3D}" type="CELLRANGE">
+                    <a:fld id="{6EB6174C-D0BC-4CAD-A5E0-2AF1926BBB8F}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6731,7 +6721,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B4D56F95-515F-45FC-9CDC-06DDB0519B12}" type="CELLRANGE">
+                    <a:fld id="{813790BD-6A16-4DBD-AA3A-0AF4B05C7E80}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6765,7 +6755,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D47F1957-F49E-4C4A-967F-DC31365B33D5}" type="CELLRANGE">
+                    <a:fld id="{7E9A4C21-D6BD-405D-80C6-E494D8873DD5}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6799,7 +6789,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C36792FB-A187-46B9-B562-219CFE4997BF}" type="CELLRANGE">
+                    <a:fld id="{BFF4B849-A219-48D0-A871-952A75FBF109}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6833,7 +6823,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{0303DC5A-A763-4CA2-A208-407D57DC775C}" type="CELLRANGE">
+                    <a:fld id="{1DCFCCE7-85B9-44E1-92C9-E1F2CF14F55F}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6867,7 +6857,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E5A23370-79F9-4691-BDBD-7A8D62C566BC}" type="CELLRANGE">
+                    <a:fld id="{4DDFBE4C-D4DC-4559-93FC-3599E47A5608}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6916,7 +6906,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{33175813-3062-4C6F-8FDE-08411AC41C6D}" type="CELLRANGE">
+                    <a:fld id="{9AF60094-8B4C-401D-87CC-27AEC32454E5}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr>
                         <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
@@ -6975,7 +6965,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E35BDC9C-53DE-479A-9D40-15BBFE19E53D}" type="CELLRANGE">
+                    <a:fld id="{D779D5AE-7159-49CE-BEA4-8CA46772E4D2}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7009,7 +6999,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7FF25670-5252-4315-A1E6-9E5CCA6D4AA1}" type="CELLRANGE">
+                    <a:fld id="{BE739721-2871-4B57-905E-9F3993BA9BD5}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7043,7 +7033,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9D3F3147-BE4C-4865-B0DA-240B7221C309}" type="CELLRANGE">
+                    <a:fld id="{7BBF11F2-7E34-4004-A724-7D1FD0203F4C}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7077,7 +7067,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{82D393B5-CEAF-447D-AE5B-B2EF98919F4A}" type="CELLRANGE">
+                    <a:fld id="{2BBD684D-7A55-4964-893E-FFEE60DE3101}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7261,31 +7251,31 @@
                   <c:v>43</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>268</c:v>
+                  <c:v>269</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>318</c:v>
+                  <c:v>319</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>241</c:v>
+                  <c:v>242</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>58</c:v>
+                  <c:v>59</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>96</c:v>
+                  <c:v>97</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>59</c:v>
+                  <c:v>60</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>5</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>7</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>47</c:v>
@@ -7294,16 +7284,16 @@
                   <c:v>51</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>84</c:v>
+                  <c:v>85</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>117</c:v>
+                  <c:v>118</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>70</c:v>
+                  <c:v>71</c:v>
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>2</c:v>
@@ -7890,7 +7880,7 @@
                   <c:v>2.1714285714285713</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.1176470588235294</c:v>
+                  <c:v>2.0571428571428569</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>1.8235294117647058</c:v>
@@ -14213,30 +14203,30 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
       <c r="B1" s="5"/>
-      <c r="C1" s="213" t="s">
+      <c r="C1" s="205" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="213"/>
-      <c r="E1" s="214" t="s">
+      <c r="D1" s="205"/>
+      <c r="E1" s="206" t="s">
         <v>120</v>
       </c>
-      <c r="F1" s="214"/>
-      <c r="G1" s="213" t="s">
+      <c r="F1" s="206"/>
+      <c r="G1" s="205" t="s">
         <v>108</v>
       </c>
-      <c r="H1" s="213"/>
-      <c r="I1" s="214" t="s">
+      <c r="H1" s="205"/>
+      <c r="I1" s="206" t="s">
         <v>110</v>
       </c>
-      <c r="J1" s="214"/>
-      <c r="K1" s="213" t="s">
+      <c r="J1" s="206"/>
+      <c r="K1" s="205" t="s">
         <v>39</v>
       </c>
-      <c r="L1" s="213"/>
-      <c r="M1" s="211" t="s">
+      <c r="L1" s="205"/>
+      <c r="M1" s="203" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="212"/>
+      <c r="N1" s="204"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -15943,30 +15933,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="213" t="s">
+      <c r="C2" s="205" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="213"/>
-      <c r="E2" s="214" t="s">
+      <c r="D2" s="205"/>
+      <c r="E2" s="206" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="214"/>
-      <c r="G2" s="213" t="s">
+      <c r="F2" s="206"/>
+      <c r="G2" s="205" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="213"/>
-      <c r="I2" s="214" t="s">
+      <c r="H2" s="205"/>
+      <c r="I2" s="206" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="214"/>
-      <c r="K2" s="213" t="s">
+      <c r="J2" s="206"/>
+      <c r="K2" s="205" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="213"/>
-      <c r="M2" s="206" t="s">
+      <c r="L2" s="205"/>
+      <c r="M2" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="206"/>
+      <c r="N2" s="210"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -17770,30 +17760,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="213" t="s">
+      <c r="C2" s="205" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="213"/>
-      <c r="E2" s="214" t="s">
+      <c r="D2" s="205"/>
+      <c r="E2" s="206" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="214"/>
-      <c r="G2" s="213" t="s">
+      <c r="F2" s="206"/>
+      <c r="G2" s="205" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="213"/>
-      <c r="I2" s="214" t="s">
+      <c r="H2" s="205"/>
+      <c r="I2" s="206" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="214"/>
-      <c r="K2" s="213" t="s">
+      <c r="J2" s="206"/>
+      <c r="K2" s="205" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="213"/>
-      <c r="M2" s="206" t="s">
+      <c r="L2" s="205"/>
+      <c r="M2" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="206"/>
+      <c r="N2" s="210"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -19460,30 +19450,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="213" t="s">
+      <c r="C2" s="205" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="213"/>
-      <c r="E2" s="214" t="s">
+      <c r="D2" s="205"/>
+      <c r="E2" s="206" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="214"/>
-      <c r="G2" s="213" t="s">
+      <c r="F2" s="206"/>
+      <c r="G2" s="205" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="213"/>
-      <c r="I2" s="214" t="s">
+      <c r="H2" s="205"/>
+      <c r="I2" s="206" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="214"/>
-      <c r="K2" s="213" t="s">
+      <c r="J2" s="206"/>
+      <c r="K2" s="205" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="213"/>
-      <c r="M2" s="206" t="s">
+      <c r="L2" s="205"/>
+      <c r="M2" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="206"/>
+      <c r="N2" s="210"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -21286,30 +21276,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="213" t="s">
+      <c r="C2" s="205" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="213"/>
-      <c r="E2" s="214" t="s">
+      <c r="D2" s="205"/>
+      <c r="E2" s="206" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="214"/>
-      <c r="G2" s="213" t="s">
+      <c r="F2" s="206"/>
+      <c r="G2" s="205" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="213"/>
-      <c r="I2" s="214" t="s">
+      <c r="H2" s="205"/>
+      <c r="I2" s="206" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="214"/>
-      <c r="K2" s="213" t="s">
+      <c r="J2" s="206"/>
+      <c r="K2" s="205" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="213"/>
-      <c r="M2" s="206" t="s">
+      <c r="L2" s="205"/>
+      <c r="M2" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="206"/>
+      <c r="N2" s="210"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -23158,36 +23148,36 @@
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="203" t="s">
+      <c r="C2" s="207" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="204"/>
-      <c r="E2" s="205"/>
-      <c r="F2" s="208" t="s">
+      <c r="D2" s="208"/>
+      <c r="E2" s="209"/>
+      <c r="F2" s="212" t="s">
         <v>120</v>
       </c>
-      <c r="G2" s="209"/>
-      <c r="H2" s="210"/>
-      <c r="I2" s="203" t="s">
+      <c r="G2" s="213"/>
+      <c r="H2" s="214"/>
+      <c r="I2" s="207" t="s">
         <v>108</v>
       </c>
-      <c r="J2" s="204"/>
-      <c r="K2" s="205"/>
-      <c r="L2" s="208" t="s">
+      <c r="J2" s="208"/>
+      <c r="K2" s="209"/>
+      <c r="L2" s="212" t="s">
         <v>110</v>
       </c>
-      <c r="M2" s="209"/>
-      <c r="N2" s="210"/>
-      <c r="O2" s="203" t="s">
+      <c r="M2" s="213"/>
+      <c r="N2" s="214"/>
+      <c r="O2" s="207" t="s">
         <v>39</v>
       </c>
-      <c r="P2" s="204"/>
-      <c r="Q2" s="205"/>
-      <c r="R2" s="206" t="s">
+      <c r="P2" s="208"/>
+      <c r="Q2" s="209"/>
+      <c r="R2" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="S2" s="206"/>
-      <c r="T2" s="206"/>
+      <c r="S2" s="210"/>
+      <c r="T2" s="210"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -23260,7 +23250,7 @@
       </c>
       <c r="C4" s="6">
         <f>'Premier League'!C4</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" s="6">
         <f>'Premier League'!D4</f>
@@ -23320,7 +23310,7 @@
       </c>
       <c r="R4" s="2">
         <f>SUM(C4,F4,I4,L4,O4)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S4" s="2">
         <f t="shared" ref="S4:T4" si="0">SUM(D4,G4,J4,M4,P4)</f>
@@ -23664,7 +23654,7 @@
       </c>
       <c r="C9" s="6">
         <f>'Premier League'!C9</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D9" s="6">
         <f>'Premier League'!D9</f>
@@ -23724,7 +23714,7 @@
       </c>
       <c r="R9" s="2">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S9" s="2">
         <f t="shared" si="2"/>
@@ -23745,7 +23735,7 @@
       </c>
       <c r="C10" s="6">
         <f>'Premier League'!C10</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" s="6">
         <f>'Premier League'!D10</f>
@@ -23805,7 +23795,7 @@
       </c>
       <c r="R10" s="2">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S10" s="2">
         <f t="shared" si="2"/>
@@ -23826,7 +23816,7 @@
       </c>
       <c r="C11" s="6">
         <f>'Premier League'!C11</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" s="6">
         <f>'Premier League'!D11</f>
@@ -23886,7 +23876,7 @@
       </c>
       <c r="R11" s="2">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S11" s="2">
         <f t="shared" si="2"/>
@@ -23907,7 +23897,7 @@
       </c>
       <c r="C12" s="6">
         <f>'Premier League'!C12</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" s="6">
         <f>'Premier League'!D12</f>
@@ -23967,7 +23957,7 @@
       </c>
       <c r="R12" s="2">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S12" s="2">
         <f t="shared" si="2"/>
@@ -23988,7 +23978,7 @@
       </c>
       <c r="C13" s="6">
         <f>'Premier League'!C13</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" s="6">
         <f>'Premier League'!D13</f>
@@ -24048,7 +24038,7 @@
       </c>
       <c r="R13" s="2">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S13" s="2">
         <f t="shared" si="2"/>
@@ -24150,7 +24140,7 @@
       </c>
       <c r="C15" s="6">
         <f>'Premier League'!C15</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="6">
         <f>'Premier League'!D15</f>
@@ -24210,7 +24200,7 @@
       </c>
       <c r="R15" s="2">
         <f>SUM(C15,F15,I15,L15,O15)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S15" s="2">
         <f>SUM(D15,G15,J15,M15,P15)</f>
@@ -24231,7 +24221,7 @@
       </c>
       <c r="C16" s="6">
         <f>'Premier League'!C16</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16" s="6">
         <f>'Premier League'!D16</f>
@@ -24291,7 +24281,7 @@
       </c>
       <c r="R16" s="2">
         <f t="shared" ref="R16:R28" si="4">SUM(C16,F16,I16,L16,O16)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S16" s="2">
         <f t="shared" ref="S16:S28" si="5">SUM(D16,G16,J16,M16,P16)</f>
@@ -24312,7 +24302,7 @@
       </c>
       <c r="C17" s="6">
         <f>'Premier League'!C17</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D17" s="6">
         <f>'Premier League'!D17</f>
@@ -24372,7 +24362,7 @@
       </c>
       <c r="R17" s="2">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S17" s="2">
         <f t="shared" si="5"/>
@@ -24553,7 +24543,7 @@
       </c>
       <c r="C20" s="6">
         <f>'Premier League'!C20</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D20" s="6">
         <f>'Premier League'!D20</f>
@@ -24613,7 +24603,7 @@
       </c>
       <c r="R20" s="2">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S20" s="2">
         <f t="shared" si="5"/>
@@ -24633,7 +24623,7 @@
       </c>
       <c r="C21" s="6">
         <f>'Premier League'!C21</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D21" s="6">
         <f>'Premier League'!D21</f>
@@ -24693,7 +24683,7 @@
       </c>
       <c r="R21" s="2">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S21" s="2">
         <f t="shared" si="5"/>
@@ -24795,7 +24785,7 @@
       </c>
       <c r="C23" s="6">
         <f>'Premier League'!C23</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D23" s="6">
         <f>'Premier League'!D23</f>
@@ -24855,7 +24845,7 @@
       </c>
       <c r="R23" s="2">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S23" s="2">
         <f t="shared" si="5"/>
@@ -24957,7 +24947,7 @@
       </c>
       <c r="C25" s="6">
         <f>'Premier League'!C25</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D25" s="6">
         <f>'Premier League'!D25</f>
@@ -25017,7 +25007,7 @@
       </c>
       <c r="R25" s="2">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S25" s="2">
         <f t="shared" si="5"/>
@@ -25038,7 +25028,7 @@
       </c>
       <c r="C26" s="6">
         <f>'Premier League'!C26</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D26" s="6">
         <f>'Premier League'!D26</f>
@@ -25098,7 +25088,7 @@
       </c>
       <c r="R26" s="2">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S26" s="2">
         <f t="shared" si="5"/>
@@ -25199,7 +25189,7 @@
       </c>
       <c r="C28" s="6">
         <f>'Premier League'!C28</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D28" s="6">
         <f>'Premier League'!D28</f>
@@ -25259,7 +25249,7 @@
       </c>
       <c r="R28" s="2">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S28" s="2">
         <f t="shared" si="5"/>
@@ -25436,7 +25426,7 @@
         <v>45</v>
       </c>
       <c r="B31" s="148" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="C31" s="6">
         <f>'Premier League'!C31</f>
@@ -25841,7 +25831,7 @@
       </c>
       <c r="C36" s="6">
         <f>'Premier League'!C36</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D36" s="6">
         <f>'Premier League'!D36</f>
@@ -25901,7 +25891,7 @@
       </c>
       <c r="R36" s="2">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S36" s="2">
         <f t="shared" si="9"/>
@@ -26126,36 +26116,36 @@
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
       <c r="D1" s="5"/>
-      <c r="E1" s="203" t="s">
+      <c r="E1" s="207" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="204"/>
-      <c r="G1" s="205"/>
-      <c r="H1" s="208" t="s">
+      <c r="F1" s="208"/>
+      <c r="G1" s="209"/>
+      <c r="H1" s="212" t="s">
         <v>120</v>
       </c>
-      <c r="I1" s="209"/>
-      <c r="J1" s="210"/>
-      <c r="K1" s="203" t="s">
+      <c r="I1" s="213"/>
+      <c r="J1" s="214"/>
+      <c r="K1" s="207" t="s">
         <v>108</v>
       </c>
-      <c r="L1" s="204"/>
-      <c r="M1" s="205"/>
-      <c r="N1" s="208" t="s">
+      <c r="L1" s="208"/>
+      <c r="M1" s="209"/>
+      <c r="N1" s="212" t="s">
         <v>110</v>
       </c>
-      <c r="O1" s="209"/>
-      <c r="P1" s="210"/>
-      <c r="Q1" s="203" t="s">
+      <c r="O1" s="213"/>
+      <c r="P1" s="214"/>
+      <c r="Q1" s="207" t="s">
         <v>39</v>
       </c>
-      <c r="R1" s="204"/>
-      <c r="S1" s="205"/>
-      <c r="T1" s="206" t="s">
+      <c r="R1" s="208"/>
+      <c r="S1" s="209"/>
+      <c r="T1" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="U1" s="206"/>
-      <c r="V1" s="206"/>
+      <c r="U1" s="210"/>
+      <c r="V1" s="210"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -37729,196 +37719,196 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F1" s="218">
-        <v>1</v>
-      </c>
-      <c r="G1" s="219"/>
-      <c r="H1" s="220"/>
-      <c r="I1" s="218">
+      <c r="F1" s="215">
+        <v>1</v>
+      </c>
+      <c r="G1" s="216"/>
+      <c r="H1" s="217"/>
+      <c r="I1" s="215">
         <v>2</v>
       </c>
-      <c r="J1" s="219"/>
-      <c r="K1" s="220"/>
-      <c r="L1" s="218">
-        <v>3</v>
-      </c>
-      <c r="M1" s="219"/>
-      <c r="N1" s="220"/>
-      <c r="O1" s="218">
+      <c r="J1" s="216"/>
+      <c r="K1" s="217"/>
+      <c r="L1" s="215">
+        <v>3</v>
+      </c>
+      <c r="M1" s="216"/>
+      <c r="N1" s="217"/>
+      <c r="O1" s="215">
         <v>4</v>
       </c>
-      <c r="P1" s="219"/>
-      <c r="Q1" s="220"/>
-      <c r="R1" s="218">
+      <c r="P1" s="216"/>
+      <c r="Q1" s="217"/>
+      <c r="R1" s="215">
         <v>5</v>
       </c>
-      <c r="S1" s="219"/>
-      <c r="T1" s="220"/>
-      <c r="U1" s="218">
+      <c r="S1" s="216"/>
+      <c r="T1" s="217"/>
+      <c r="U1" s="215">
         <v>6</v>
       </c>
-      <c r="V1" s="219"/>
-      <c r="W1" s="220"/>
-      <c r="X1" s="218">
+      <c r="V1" s="216"/>
+      <c r="W1" s="217"/>
+      <c r="X1" s="215">
         <v>7</v>
       </c>
-      <c r="Y1" s="219"/>
-      <c r="Z1" s="220"/>
-      <c r="AA1" s="218">
+      <c r="Y1" s="216"/>
+      <c r="Z1" s="217"/>
+      <c r="AA1" s="215">
         <v>8</v>
       </c>
-      <c r="AB1" s="219"/>
-      <c r="AC1" s="220"/>
-      <c r="AD1" s="218">
+      <c r="AB1" s="216"/>
+      <c r="AC1" s="217"/>
+      <c r="AD1" s="215">
         <v>9</v>
       </c>
-      <c r="AE1" s="219"/>
-      <c r="AF1" s="220"/>
-      <c r="AG1" s="218">
+      <c r="AE1" s="216"/>
+      <c r="AF1" s="217"/>
+      <c r="AG1" s="215">
         <v>10</v>
       </c>
-      <c r="AH1" s="219"/>
-      <c r="AI1" s="220"/>
-      <c r="AJ1" s="218">
+      <c r="AH1" s="216"/>
+      <c r="AI1" s="217"/>
+      <c r="AJ1" s="215">
         <v>11</v>
       </c>
-      <c r="AK1" s="219"/>
-      <c r="AL1" s="220"/>
-      <c r="AM1" s="218">
+      <c r="AK1" s="216"/>
+      <c r="AL1" s="217"/>
+      <c r="AM1" s="215">
         <v>12</v>
       </c>
-      <c r="AN1" s="219"/>
-      <c r="AO1" s="220"/>
-      <c r="AP1" s="218">
+      <c r="AN1" s="216"/>
+      <c r="AO1" s="217"/>
+      <c r="AP1" s="215">
         <v>13</v>
       </c>
-      <c r="AQ1" s="219"/>
-      <c r="AR1" s="220"/>
-      <c r="AS1" s="218">
+      <c r="AQ1" s="216"/>
+      <c r="AR1" s="217"/>
+      <c r="AS1" s="215">
         <v>14</v>
       </c>
-      <c r="AT1" s="219"/>
-      <c r="AU1" s="220"/>
-      <c r="AV1" s="218">
+      <c r="AT1" s="216"/>
+      <c r="AU1" s="217"/>
+      <c r="AV1" s="215">
         <v>15</v>
       </c>
-      <c r="AW1" s="219"/>
-      <c r="AX1" s="220"/>
-      <c r="AY1" s="218">
+      <c r="AW1" s="216"/>
+      <c r="AX1" s="217"/>
+      <c r="AY1" s="215">
         <v>16</v>
       </c>
-      <c r="AZ1" s="219"/>
-      <c r="BA1" s="220"/>
-      <c r="BB1" s="218">
+      <c r="AZ1" s="216"/>
+      <c r="BA1" s="217"/>
+      <c r="BB1" s="215">
         <v>17</v>
       </c>
-      <c r="BC1" s="219"/>
-      <c r="BD1" s="220"/>
-      <c r="BE1" s="218">
+      <c r="BC1" s="216"/>
+      <c r="BD1" s="217"/>
+      <c r="BE1" s="215">
         <v>18</v>
       </c>
-      <c r="BF1" s="219"/>
-      <c r="BG1" s="220"/>
-      <c r="BH1" s="218">
+      <c r="BF1" s="216"/>
+      <c r="BG1" s="217"/>
+      <c r="BH1" s="215">
         <v>19</v>
       </c>
-      <c r="BI1" s="219"/>
-      <c r="BJ1" s="220"/>
-      <c r="BK1" s="218">
+      <c r="BI1" s="216"/>
+      <c r="BJ1" s="217"/>
+      <c r="BK1" s="215">
         <v>20</v>
       </c>
-      <c r="BL1" s="219"/>
-      <c r="BM1" s="220"/>
-      <c r="BN1" s="218">
+      <c r="BL1" s="216"/>
+      <c r="BM1" s="217"/>
+      <c r="BN1" s="215">
         <v>21</v>
       </c>
-      <c r="BO1" s="219"/>
-      <c r="BP1" s="220"/>
-      <c r="BQ1" s="218">
+      <c r="BO1" s="216"/>
+      <c r="BP1" s="217"/>
+      <c r="BQ1" s="215">
         <v>22</v>
       </c>
-      <c r="BR1" s="219"/>
-      <c r="BS1" s="220"/>
-      <c r="BT1" s="218">
+      <c r="BR1" s="216"/>
+      <c r="BS1" s="217"/>
+      <c r="BT1" s="215">
         <v>23</v>
       </c>
-      <c r="BU1" s="219"/>
-      <c r="BV1" s="220"/>
-      <c r="BW1" s="218">
+      <c r="BU1" s="216"/>
+      <c r="BV1" s="217"/>
+      <c r="BW1" s="215">
         <v>24</v>
       </c>
-      <c r="BX1" s="219"/>
-      <c r="BY1" s="220"/>
-      <c r="BZ1" s="218">
+      <c r="BX1" s="216"/>
+      <c r="BY1" s="217"/>
+      <c r="BZ1" s="215">
         <v>25</v>
       </c>
-      <c r="CA1" s="219"/>
-      <c r="CB1" s="220"/>
-      <c r="CC1" s="218">
+      <c r="CA1" s="216"/>
+      <c r="CB1" s="217"/>
+      <c r="CC1" s="215">
         <v>26</v>
       </c>
-      <c r="CD1" s="219"/>
-      <c r="CE1" s="220"/>
-      <c r="CF1" s="218">
+      <c r="CD1" s="216"/>
+      <c r="CE1" s="217"/>
+      <c r="CF1" s="215">
         <v>27</v>
       </c>
-      <c r="CG1" s="219"/>
-      <c r="CH1" s="220"/>
-      <c r="CI1" s="218">
+      <c r="CG1" s="216"/>
+      <c r="CH1" s="217"/>
+      <c r="CI1" s="215">
         <v>28</v>
       </c>
-      <c r="CJ1" s="219"/>
-      <c r="CK1" s="220"/>
-      <c r="CL1" s="218">
+      <c r="CJ1" s="216"/>
+      <c r="CK1" s="217"/>
+      <c r="CL1" s="215">
         <v>29</v>
       </c>
-      <c r="CM1" s="219"/>
-      <c r="CN1" s="220"/>
-      <c r="CO1" s="218">
+      <c r="CM1" s="216"/>
+      <c r="CN1" s="217"/>
+      <c r="CO1" s="215">
         <v>30</v>
       </c>
-      <c r="CP1" s="219"/>
-      <c r="CQ1" s="220"/>
-      <c r="CR1" s="218">
+      <c r="CP1" s="216"/>
+      <c r="CQ1" s="217"/>
+      <c r="CR1" s="215">
         <v>31</v>
       </c>
-      <c r="CS1" s="219"/>
-      <c r="CT1" s="220"/>
-      <c r="CU1" s="218">
+      <c r="CS1" s="216"/>
+      <c r="CT1" s="217"/>
+      <c r="CU1" s="215">
         <v>32</v>
       </c>
-      <c r="CV1" s="219"/>
-      <c r="CW1" s="220"/>
-      <c r="CX1" s="218">
+      <c r="CV1" s="216"/>
+      <c r="CW1" s="217"/>
+      <c r="CX1" s="215">
         <v>33</v>
       </c>
-      <c r="CY1" s="219"/>
-      <c r="CZ1" s="220"/>
-      <c r="DA1" s="218">
+      <c r="CY1" s="216"/>
+      <c r="CZ1" s="217"/>
+      <c r="DA1" s="215">
         <v>34</v>
       </c>
-      <c r="DB1" s="219"/>
-      <c r="DC1" s="220"/>
-      <c r="DD1" s="218">
+      <c r="DB1" s="216"/>
+      <c r="DC1" s="217"/>
+      <c r="DD1" s="215">
         <v>35</v>
       </c>
-      <c r="DE1" s="219"/>
-      <c r="DF1" s="220"/>
-      <c r="DG1" s="218">
+      <c r="DE1" s="216"/>
+      <c r="DF1" s="217"/>
+      <c r="DG1" s="215">
         <v>36</v>
       </c>
-      <c r="DH1" s="219"/>
-      <c r="DI1" s="220"/>
-      <c r="DJ1" s="218">
+      <c r="DH1" s="216"/>
+      <c r="DI1" s="217"/>
+      <c r="DJ1" s="215">
         <v>37</v>
       </c>
-      <c r="DK1" s="219"/>
-      <c r="DL1" s="220"/>
-      <c r="DM1" s="218">
+      <c r="DK1" s="216"/>
+      <c r="DL1" s="217"/>
+      <c r="DM1" s="215">
         <v>38</v>
       </c>
-      <c r="DN1" s="219"/>
-      <c r="DO1" s="220"/>
+      <c r="DN1" s="216"/>
+      <c r="DO1" s="217"/>
     </row>
     <row r="2" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
@@ -37932,196 +37922,196 @@
       <c r="E2" s="221" t="s">
         <v>398</v>
       </c>
-      <c r="F2" s="215" t="s">
+      <c r="F2" s="218" t="s">
         <v>346</v>
       </c>
-      <c r="G2" s="216"/>
-      <c r="H2" s="217"/>
-      <c r="I2" s="215" t="s">
+      <c r="G2" s="219"/>
+      <c r="H2" s="220"/>
+      <c r="I2" s="218" t="s">
         <v>331</v>
       </c>
-      <c r="J2" s="216"/>
-      <c r="K2" s="217"/>
-      <c r="L2" s="215" t="s">
+      <c r="J2" s="219"/>
+      <c r="K2" s="220"/>
+      <c r="L2" s="218" t="s">
         <v>330</v>
       </c>
-      <c r="M2" s="216"/>
-      <c r="N2" s="217"/>
-      <c r="O2" s="215" t="s">
+      <c r="M2" s="219"/>
+      <c r="N2" s="220"/>
+      <c r="O2" s="218" t="s">
         <v>328</v>
       </c>
-      <c r="P2" s="216"/>
-      <c r="Q2" s="217"/>
-      <c r="R2" s="215" t="s">
+      <c r="P2" s="219"/>
+      <c r="Q2" s="220"/>
+      <c r="R2" s="218" t="s">
         <v>335</v>
       </c>
-      <c r="S2" s="216"/>
-      <c r="T2" s="217"/>
-      <c r="U2" s="215" t="s">
+      <c r="S2" s="219"/>
+      <c r="T2" s="220"/>
+      <c r="U2" s="218" t="s">
         <v>320</v>
       </c>
-      <c r="V2" s="216"/>
-      <c r="W2" s="217"/>
-      <c r="X2" s="215" t="s">
+      <c r="V2" s="219"/>
+      <c r="W2" s="220"/>
+      <c r="X2" s="218" t="s">
         <v>337</v>
       </c>
-      <c r="Y2" s="216"/>
-      <c r="Z2" s="217"/>
-      <c r="AA2" s="215" t="s">
+      <c r="Y2" s="219"/>
+      <c r="Z2" s="220"/>
+      <c r="AA2" s="218" t="s">
         <v>334</v>
       </c>
-      <c r="AB2" s="216"/>
-      <c r="AC2" s="217"/>
-      <c r="AD2" s="215" t="s">
+      <c r="AB2" s="219"/>
+      <c r="AC2" s="220"/>
+      <c r="AD2" s="218" t="s">
         <v>321</v>
       </c>
-      <c r="AE2" s="216"/>
-      <c r="AF2" s="217"/>
-      <c r="AG2" s="215" t="s">
+      <c r="AE2" s="219"/>
+      <c r="AF2" s="220"/>
+      <c r="AG2" s="218" t="s">
         <v>347</v>
       </c>
-      <c r="AH2" s="216"/>
-      <c r="AI2" s="217"/>
-      <c r="AJ2" s="215" t="s">
+      <c r="AH2" s="219"/>
+      <c r="AI2" s="220"/>
+      <c r="AJ2" s="218" t="s">
         <v>324</v>
       </c>
-      <c r="AK2" s="216"/>
-      <c r="AL2" s="217"/>
-      <c r="AM2" s="215" t="s">
+      <c r="AK2" s="219"/>
+      <c r="AL2" s="220"/>
+      <c r="AM2" s="218" t="s">
         <v>323</v>
       </c>
-      <c r="AN2" s="216"/>
-      <c r="AO2" s="217"/>
-      <c r="AP2" s="215" t="s">
+      <c r="AN2" s="219"/>
+      <c r="AO2" s="220"/>
+      <c r="AP2" s="218" t="s">
         <v>332</v>
       </c>
-      <c r="AQ2" s="216"/>
-      <c r="AR2" s="217"/>
-      <c r="AS2" s="215" t="s">
+      <c r="AQ2" s="219"/>
+      <c r="AR2" s="220"/>
+      <c r="AS2" s="218" t="s">
         <v>329</v>
       </c>
-      <c r="AT2" s="216"/>
-      <c r="AU2" s="217"/>
-      <c r="AV2" s="215" t="s">
+      <c r="AT2" s="219"/>
+      <c r="AU2" s="220"/>
+      <c r="AV2" s="218" t="s">
         <v>336</v>
       </c>
-      <c r="AW2" s="216"/>
-      <c r="AX2" s="217"/>
-      <c r="AY2" s="215" t="s">
+      <c r="AW2" s="219"/>
+      <c r="AX2" s="220"/>
+      <c r="AY2" s="218" t="s">
         <v>305</v>
       </c>
-      <c r="AZ2" s="216"/>
-      <c r="BA2" s="217"/>
-      <c r="BB2" s="215" t="s">
+      <c r="AZ2" s="219"/>
+      <c r="BA2" s="220"/>
+      <c r="BB2" s="218" t="s">
         <v>326</v>
       </c>
-      <c r="BC2" s="216"/>
-      <c r="BD2" s="217"/>
-      <c r="BE2" s="215" t="s">
+      <c r="BC2" s="219"/>
+      <c r="BD2" s="220"/>
+      <c r="BE2" s="218" t="s">
         <v>325</v>
       </c>
-      <c r="BF2" s="216"/>
-      <c r="BG2" s="217"/>
-      <c r="BH2" s="215" t="s">
+      <c r="BF2" s="219"/>
+      <c r="BG2" s="220"/>
+      <c r="BH2" s="218" t="s">
         <v>348</v>
       </c>
-      <c r="BI2" s="216"/>
-      <c r="BJ2" s="217"/>
-      <c r="BK2" s="215" t="s">
+      <c r="BI2" s="219"/>
+      <c r="BJ2" s="220"/>
+      <c r="BK2" s="218" t="s">
         <v>332</v>
       </c>
-      <c r="BL2" s="216"/>
-      <c r="BM2" s="217"/>
-      <c r="BN2" s="215" t="s">
+      <c r="BL2" s="219"/>
+      <c r="BM2" s="220"/>
+      <c r="BN2" s="218" t="s">
         <v>347</v>
       </c>
-      <c r="BO2" s="216"/>
-      <c r="BP2" s="217"/>
-      <c r="BQ2" s="215" t="s">
+      <c r="BO2" s="219"/>
+      <c r="BP2" s="220"/>
+      <c r="BQ2" s="218" t="s">
         <v>324</v>
       </c>
-      <c r="BR2" s="216"/>
-      <c r="BS2" s="217"/>
-      <c r="BT2" s="215" t="s">
+      <c r="BR2" s="219"/>
+      <c r="BS2" s="220"/>
+      <c r="BT2" s="218" t="s">
         <v>323</v>
       </c>
-      <c r="BU2" s="216"/>
-      <c r="BV2" s="217"/>
-      <c r="BW2" s="215" t="s">
+      <c r="BU2" s="219"/>
+      <c r="BV2" s="220"/>
+      <c r="BW2" s="218" t="s">
         <v>321</v>
       </c>
-      <c r="BX2" s="216"/>
-      <c r="BY2" s="217"/>
-      <c r="BZ2" s="215" t="s">
+      <c r="BX2" s="219"/>
+      <c r="BY2" s="220"/>
+      <c r="BZ2" s="218" t="s">
         <v>348</v>
       </c>
-      <c r="CA2" s="216"/>
-      <c r="CB2" s="217"/>
-      <c r="CC2" s="215" t="s">
+      <c r="CA2" s="219"/>
+      <c r="CB2" s="220"/>
+      <c r="CC2" s="218" t="s">
         <v>325</v>
       </c>
-      <c r="CD2" s="216"/>
-      <c r="CE2" s="217"/>
-      <c r="CF2" s="215" t="s">
+      <c r="CD2" s="219"/>
+      <c r="CE2" s="220"/>
+      <c r="CF2" s="218" t="s">
         <v>305</v>
       </c>
-      <c r="CG2" s="216"/>
-      <c r="CH2" s="217"/>
-      <c r="CI2" s="215" t="s">
+      <c r="CG2" s="219"/>
+      <c r="CH2" s="220"/>
+      <c r="CI2" s="218" t="s">
         <v>326</v>
       </c>
-      <c r="CJ2" s="216"/>
-      <c r="CK2" s="217"/>
-      <c r="CL2" s="215" t="s">
+      <c r="CJ2" s="219"/>
+      <c r="CK2" s="220"/>
+      <c r="CL2" s="218" t="s">
         <v>330</v>
       </c>
-      <c r="CM2" s="216"/>
-      <c r="CN2" s="217"/>
-      <c r="CO2" s="215" t="s">
+      <c r="CM2" s="219"/>
+      <c r="CN2" s="220"/>
+      <c r="CO2" s="218" t="s">
         <v>328</v>
       </c>
-      <c r="CP2" s="216"/>
-      <c r="CQ2" s="217"/>
-      <c r="CR2" s="215" t="s">
+      <c r="CP2" s="219"/>
+      <c r="CQ2" s="220"/>
+      <c r="CR2" s="218" t="s">
         <v>346</v>
       </c>
-      <c r="CS2" s="216"/>
-      <c r="CT2" s="217"/>
-      <c r="CU2" s="215" t="s">
+      <c r="CS2" s="219"/>
+      <c r="CT2" s="220"/>
+      <c r="CU2" s="218" t="s">
         <v>331</v>
       </c>
-      <c r="CV2" s="216"/>
-      <c r="CW2" s="217"/>
-      <c r="CX2" s="215" t="s">
+      <c r="CV2" s="219"/>
+      <c r="CW2" s="220"/>
+      <c r="CX2" s="218" t="s">
         <v>336</v>
       </c>
-      <c r="CY2" s="216"/>
-      <c r="CZ2" s="217"/>
-      <c r="DA2" s="215" t="s">
+      <c r="CY2" s="219"/>
+      <c r="CZ2" s="220"/>
+      <c r="DA2" s="218" t="s">
         <v>329</v>
       </c>
-      <c r="DB2" s="216"/>
-      <c r="DC2" s="217"/>
-      <c r="DD2" s="215" t="s">
+      <c r="DB2" s="219"/>
+      <c r="DC2" s="220"/>
+      <c r="DD2" s="218" t="s">
         <v>320</v>
       </c>
-      <c r="DE2" s="216"/>
-      <c r="DF2" s="217"/>
-      <c r="DG2" s="215" t="s">
+      <c r="DE2" s="219"/>
+      <c r="DF2" s="220"/>
+      <c r="DG2" s="218" t="s">
         <v>337</v>
       </c>
-      <c r="DH2" s="216"/>
-      <c r="DI2" s="217"/>
-      <c r="DJ2" s="215" t="s">
+      <c r="DH2" s="219"/>
+      <c r="DI2" s="220"/>
+      <c r="DJ2" s="218" t="s">
         <v>334</v>
       </c>
-      <c r="DK2" s="216"/>
-      <c r="DL2" s="217"/>
-      <c r="DM2" s="215" t="s">
+      <c r="DK2" s="219"/>
+      <c r="DL2" s="220"/>
+      <c r="DM2" s="218" t="s">
         <v>335</v>
       </c>
-      <c r="DN2" s="216"/>
-      <c r="DO2" s="217"/>
+      <c r="DN2" s="219"/>
+      <c r="DO2" s="220"/>
     </row>
     <row r="3" spans="1:119" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -38130,9 +38120,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="222"/>
-      <c r="D3" s="222"/>
-      <c r="E3" s="223"/>
+      <c r="C3" s="223"/>
+      <c r="D3" s="223"/>
+      <c r="E3" s="222"/>
       <c r="F3" s="160" t="s">
         <v>393</v>
       </c>
@@ -38485,7 +38475,7 @@
       </c>
       <c r="C4" s="58">
         <f>SUM(F4,I4,L4,O4,R4,U4,X4,AA4,AD4,AG4,AJ4,AM4,AP4,AS4,AV4,AY4,BB4,BE4,BH4,BK4,BN4,BQ4,BT4,BW4,BZ4,CC4,CF4,CI4,CL4,CO4,CR4,CU4,CX4,DA4,DD4,DG4,DJ4,DM4)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" s="58">
         <f t="shared" ref="D4:E4" si="0">SUM(G4,J4,M4,P4,S4,V4,Y4,AB4,AE4,AH4,AK4,AN4,AQ4,AT4,AW4,AZ4,BC4,BF4,BI4,BL4,BO4,BR4,BU4,BX4,CA4,CD4,CG4,CJ4,CM4,CP4,CS4,CV4,CY4,DB4,DE4,DH4,DK4,DN4)</f>
@@ -38515,7 +38505,9 @@
       </c>
       <c r="P4" s="36"/>
       <c r="Q4" s="53"/>
-      <c r="R4" s="52"/>
+      <c r="R4" s="52">
+        <v>1</v>
+      </c>
       <c r="S4" s="36"/>
       <c r="T4" s="53"/>
       <c r="U4" s="52"/>
@@ -39181,7 +39173,7 @@
       </c>
       <c r="C9" s="58">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D9" s="58">
         <f t="shared" si="2"/>
@@ -39211,7 +39203,9 @@
       </c>
       <c r="P9" s="36"/>
       <c r="Q9" s="53"/>
-      <c r="R9" s="52"/>
+      <c r="R9" s="52">
+        <v>1</v>
+      </c>
       <c r="S9" s="36"/>
       <c r="T9" s="53"/>
       <c r="U9" s="52"/>
@@ -39323,7 +39317,7 @@
       </c>
       <c r="C10" s="58">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" s="58">
         <f t="shared" si="2"/>
@@ -39359,7 +39353,9 @@
         <v>1</v>
       </c>
       <c r="Q10" s="53"/>
-      <c r="R10" s="52"/>
+      <c r="R10" s="52">
+        <v>1</v>
+      </c>
       <c r="S10" s="36"/>
       <c r="T10" s="53"/>
       <c r="U10" s="52"/>
@@ -39471,7 +39467,7 @@
       </c>
       <c r="C11" s="58">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" s="58">
         <f t="shared" si="2"/>
@@ -39505,7 +39501,9 @@
       </c>
       <c r="P11" s="36"/>
       <c r="Q11" s="53"/>
-      <c r="R11" s="52"/>
+      <c r="R11" s="52">
+        <v>1</v>
+      </c>
       <c r="S11" s="36"/>
       <c r="T11" s="53"/>
       <c r="U11" s="52"/>
@@ -39617,7 +39615,7 @@
       </c>
       <c r="C12" s="58">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" s="58">
         <f t="shared" si="2"/>
@@ -39645,7 +39643,9 @@
       </c>
       <c r="P12" s="36"/>
       <c r="Q12" s="53"/>
-      <c r="R12" s="52"/>
+      <c r="R12" s="52">
+        <v>1</v>
+      </c>
       <c r="S12" s="36"/>
       <c r="T12" s="53"/>
       <c r="U12" s="52"/>
@@ -39757,7 +39757,7 @@
       </c>
       <c r="C13" s="58">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" s="58">
         <f t="shared" si="2"/>
@@ -39781,7 +39781,9 @@
       </c>
       <c r="P13" s="36"/>
       <c r="Q13" s="53"/>
-      <c r="R13" s="52"/>
+      <c r="R13" s="52">
+        <v>1</v>
+      </c>
       <c r="S13" s="36"/>
       <c r="T13" s="53"/>
       <c r="U13" s="52"/>
@@ -40027,7 +40029,7 @@
       </c>
       <c r="C15" s="58">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="58">
         <f t="shared" si="2"/>
@@ -40051,7 +40053,9 @@
       <c r="O15" s="52"/>
       <c r="P15" s="36"/>
       <c r="Q15" s="53"/>
-      <c r="R15" s="52"/>
+      <c r="R15" s="52">
+        <v>1</v>
+      </c>
       <c r="S15" s="36"/>
       <c r="T15" s="53"/>
       <c r="U15" s="52"/>
@@ -40163,7 +40167,7 @@
       </c>
       <c r="C16" s="58">
         <f t="shared" ref="C16:C28" si="4">SUM(F16,I16,L16,O16,R16,U16,X16,AA16,AD16,AG16,AJ16,AM16,AP16,AS16,AV16,AY16,BB16,BE16,BH16,BK16,BN16,BQ16,BT16,BW16,BZ16,CC16,CF16,CI16,CL16,CO16,CR16,CU16,CX16,DA16,DD16,DG16,DJ16,DM16)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16" s="58">
         <f t="shared" ref="D16:D28" si="5">SUM(G16,J16,M16,P16,S16,V16,Y16,AB16,AE16,AH16,AK16,AN16,AQ16,AT16,AW16,AZ16,BC16,BF16,BI16,BL16,BO16,BR16,BU16,BX16,CA16,CD16,CG16,CJ16,CM16,CP16,CS16,CV16,CY16,DB16,DE16,DH16,DK16,DN16)</f>
@@ -40191,7 +40195,9 @@
       </c>
       <c r="P16" s="36"/>
       <c r="Q16" s="53"/>
-      <c r="R16" s="52"/>
+      <c r="R16" s="52">
+        <v>1</v>
+      </c>
       <c r="S16" s="36"/>
       <c r="T16" s="53"/>
       <c r="U16" s="52"/>
@@ -40303,7 +40309,7 @@
       </c>
       <c r="C17" s="58">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D17" s="58">
         <f t="shared" si="5"/>
@@ -40335,7 +40341,9 @@
       </c>
       <c r="P17" s="36"/>
       <c r="Q17" s="53"/>
-      <c r="R17" s="52"/>
+      <c r="R17" s="52">
+        <v>1</v>
+      </c>
       <c r="S17" s="36"/>
       <c r="T17" s="53"/>
       <c r="U17" s="52"/>
@@ -40719,7 +40727,7 @@
       </c>
       <c r="C20" s="58">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D20" s="58">
         <f t="shared" si="5"/>
@@ -40749,7 +40757,9 @@
       </c>
       <c r="P20" s="36"/>
       <c r="Q20" s="53"/>
-      <c r="R20" s="52"/>
+      <c r="R20" s="52">
+        <v>1</v>
+      </c>
       <c r="S20" s="36"/>
       <c r="T20" s="53"/>
       <c r="U20" s="52"/>
@@ -40861,7 +40871,7 @@
       </c>
       <c r="C21" s="58">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D21" s="58">
         <f t="shared" si="5"/>
@@ -40895,7 +40905,9 @@
       </c>
       <c r="P21" s="36"/>
       <c r="Q21" s="53"/>
-      <c r="R21" s="52"/>
+      <c r="R21" s="52">
+        <v>1</v>
+      </c>
       <c r="S21" s="36"/>
       <c r="T21" s="53"/>
       <c r="U21" s="52"/>
@@ -41141,7 +41153,7 @@
       </c>
       <c r="C23" s="58">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D23" s="58">
         <f t="shared" si="5"/>
@@ -41175,7 +41187,9 @@
       </c>
       <c r="P23" s="36"/>
       <c r="Q23" s="53"/>
-      <c r="R23" s="52"/>
+      <c r="R23" s="52">
+        <v>1</v>
+      </c>
       <c r="S23" s="36"/>
       <c r="T23" s="53"/>
       <c r="U23" s="52"/>
@@ -41421,7 +41435,7 @@
       </c>
       <c r="C25" s="58">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D25" s="58">
         <f t="shared" si="5"/>
@@ -41451,7 +41465,9 @@
       </c>
       <c r="P25" s="36"/>
       <c r="Q25" s="53"/>
-      <c r="R25" s="52"/>
+      <c r="R25" s="52">
+        <v>1</v>
+      </c>
       <c r="S25" s="36"/>
       <c r="T25" s="53"/>
       <c r="U25" s="52"/>
@@ -41563,7 +41579,7 @@
       </c>
       <c r="C26" s="58">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D26" s="58">
         <f t="shared" si="5"/>
@@ -41591,7 +41607,9 @@
         <v>1</v>
       </c>
       <c r="Q26" s="53"/>
-      <c r="R26" s="52"/>
+      <c r="R26" s="52">
+        <v>1</v>
+      </c>
       <c r="S26" s="36"/>
       <c r="T26" s="53"/>
       <c r="U26" s="52"/>
@@ -41837,7 +41855,7 @@
       </c>
       <c r="C28" s="58">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D28" s="58">
         <f t="shared" si="5"/>
@@ -41871,7 +41889,9 @@
       <c r="Q28" s="53">
         <v>1</v>
       </c>
-      <c r="R28" s="52"/>
+      <c r="R28" s="52">
+        <v>1</v>
+      </c>
       <c r="S28" s="36"/>
       <c r="T28" s="53"/>
       <c r="U28" s="52"/>
@@ -42247,7 +42267,7 @@
         <v>45</v>
       </c>
       <c r="B31" s="148" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="C31" s="58">
         <f t="shared" ref="C31:C38" si="8">SUM(F31,I31,L31,O31,R31,U31,X31,AA31,AD31,AG31,AJ31,AM31,AP31,AS31,AV31,AY31,BB31,BE31,BH31,BK31,BN31,BQ31,BT31,BW31,BZ31,CC31,CF31,CI31,CL31,CO31,CR31,CU31,CX31,DA31,DD31,DG31,DJ31,DM31)</f>
@@ -42929,7 +42949,7 @@
       </c>
       <c r="C36" s="58">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D36" s="58">
         <f t="shared" si="9"/>
@@ -42951,7 +42971,9 @@
       <c r="O36" s="52"/>
       <c r="P36" s="36"/>
       <c r="Q36" s="53"/>
-      <c r="R36" s="52"/>
+      <c r="R36" s="52">
+        <v>1</v>
+      </c>
       <c r="S36" s="36"/>
       <c r="T36" s="53"/>
       <c r="U36" s="52"/>
@@ -43378,7 +43400,7 @@
       </c>
       <c r="R39" s="73">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="S39" s="73">
         <f t="shared" si="11"/>
@@ -43787,69 +43809,6 @@
     </row>
   </sheetData>
   <mergeCells count="79">
-    <mergeCell ref="DM1:DO1"/>
-    <mergeCell ref="DM2:DO2"/>
-    <mergeCell ref="DA1:DC1"/>
-    <mergeCell ref="DA2:DC2"/>
-    <mergeCell ref="DD1:DF1"/>
-    <mergeCell ref="DD2:DF2"/>
-    <mergeCell ref="DG1:DI1"/>
-    <mergeCell ref="DG2:DI2"/>
-    <mergeCell ref="CU1:CW1"/>
-    <mergeCell ref="CU2:CW2"/>
-    <mergeCell ref="CX1:CZ1"/>
-    <mergeCell ref="CX2:CZ2"/>
-    <mergeCell ref="DJ1:DL1"/>
-    <mergeCell ref="DJ2:DL2"/>
-    <mergeCell ref="CL1:CN1"/>
-    <mergeCell ref="CL2:CN2"/>
-    <mergeCell ref="CO1:CQ1"/>
-    <mergeCell ref="CO2:CQ2"/>
-    <mergeCell ref="CR1:CT1"/>
-    <mergeCell ref="CR2:CT2"/>
-    <mergeCell ref="CC1:CE1"/>
-    <mergeCell ref="CC2:CE2"/>
-    <mergeCell ref="CF1:CH1"/>
-    <mergeCell ref="CF2:CH2"/>
-    <mergeCell ref="CI1:CK1"/>
-    <mergeCell ref="CI2:CK2"/>
-    <mergeCell ref="BT1:BV1"/>
-    <mergeCell ref="BT2:BV2"/>
-    <mergeCell ref="BW1:BY1"/>
-    <mergeCell ref="BW2:BY2"/>
-    <mergeCell ref="BZ1:CB1"/>
-    <mergeCell ref="BZ2:CB2"/>
-    <mergeCell ref="BK1:BM1"/>
-    <mergeCell ref="BK2:BM2"/>
-    <mergeCell ref="BN1:BP1"/>
-    <mergeCell ref="BN2:BP2"/>
-    <mergeCell ref="BQ1:BS1"/>
-    <mergeCell ref="BQ2:BS2"/>
-    <mergeCell ref="AS1:AU1"/>
-    <mergeCell ref="AS2:AU2"/>
-    <mergeCell ref="AV1:AX1"/>
-    <mergeCell ref="AV2:AX2"/>
-    <mergeCell ref="BH1:BJ1"/>
-    <mergeCell ref="BH2:BJ2"/>
-    <mergeCell ref="AY2:BA2"/>
-    <mergeCell ref="BB2:BD2"/>
-    <mergeCell ref="BE2:BG2"/>
-    <mergeCell ref="AJ1:AL1"/>
-    <mergeCell ref="AJ2:AL2"/>
-    <mergeCell ref="AM1:AO1"/>
-    <mergeCell ref="AM2:AO2"/>
-    <mergeCell ref="AP2:AR2"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
     <mergeCell ref="AD2:AF2"/>
     <mergeCell ref="AG2:AI2"/>
     <mergeCell ref="BB1:BD1"/>
@@ -43866,6 +43825,69 @@
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="X1:Z1"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="AJ1:AL1"/>
+    <mergeCell ref="AJ2:AL2"/>
+    <mergeCell ref="AM1:AO1"/>
+    <mergeCell ref="AM2:AO2"/>
+    <mergeCell ref="AP2:AR2"/>
+    <mergeCell ref="AS1:AU1"/>
+    <mergeCell ref="AS2:AU2"/>
+    <mergeCell ref="AV1:AX1"/>
+    <mergeCell ref="AV2:AX2"/>
+    <mergeCell ref="BH1:BJ1"/>
+    <mergeCell ref="BH2:BJ2"/>
+    <mergeCell ref="AY2:BA2"/>
+    <mergeCell ref="BB2:BD2"/>
+    <mergeCell ref="BE2:BG2"/>
+    <mergeCell ref="BK1:BM1"/>
+    <mergeCell ref="BK2:BM2"/>
+    <mergeCell ref="BN1:BP1"/>
+    <mergeCell ref="BN2:BP2"/>
+    <mergeCell ref="BQ1:BS1"/>
+    <mergeCell ref="BQ2:BS2"/>
+    <mergeCell ref="BT1:BV1"/>
+    <mergeCell ref="BT2:BV2"/>
+    <mergeCell ref="BW1:BY1"/>
+    <mergeCell ref="BW2:BY2"/>
+    <mergeCell ref="BZ1:CB1"/>
+    <mergeCell ref="BZ2:CB2"/>
+    <mergeCell ref="CC1:CE1"/>
+    <mergeCell ref="CC2:CE2"/>
+    <mergeCell ref="CF1:CH1"/>
+    <mergeCell ref="CF2:CH2"/>
+    <mergeCell ref="CI1:CK1"/>
+    <mergeCell ref="CI2:CK2"/>
+    <mergeCell ref="CL1:CN1"/>
+    <mergeCell ref="CL2:CN2"/>
+    <mergeCell ref="CO1:CQ1"/>
+    <mergeCell ref="CO2:CQ2"/>
+    <mergeCell ref="CR1:CT1"/>
+    <mergeCell ref="CR2:CT2"/>
+    <mergeCell ref="CU1:CW1"/>
+    <mergeCell ref="CU2:CW2"/>
+    <mergeCell ref="CX1:CZ1"/>
+    <mergeCell ref="CX2:CZ2"/>
+    <mergeCell ref="DJ1:DL1"/>
+    <mergeCell ref="DJ2:DL2"/>
+    <mergeCell ref="DM1:DO1"/>
+    <mergeCell ref="DM2:DO2"/>
+    <mergeCell ref="DA1:DC1"/>
+    <mergeCell ref="DA2:DC2"/>
+    <mergeCell ref="DD1:DF1"/>
+    <mergeCell ref="DD2:DF2"/>
+    <mergeCell ref="DG1:DI1"/>
+    <mergeCell ref="DG2:DI2"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:DO38">
     <cfRule type="cellIs" dxfId="18" priority="1" operator="between">
@@ -43901,41 +43923,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="236" t="s">
+      <c r="C1" s="233" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="236" t="s">
+      <c r="D1" s="233" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="236" t="s">
+      <c r="E1" s="233" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="227" t="s">
+      <c r="F1" s="224" t="s">
         <v>302</v>
       </c>
-      <c r="G1" s="228"/>
-      <c r="H1" s="228"/>
-      <c r="I1" s="228"/>
-      <c r="J1" s="228"/>
-      <c r="K1" s="228"/>
-      <c r="L1" s="228"/>
-      <c r="M1" s="228"/>
-      <c r="N1" s="228"/>
-      <c r="O1" s="228"/>
-      <c r="P1" s="228"/>
-      <c r="Q1" s="228"/>
-      <c r="R1" s="228"/>
-      <c r="S1" s="228"/>
-      <c r="T1" s="228"/>
-      <c r="U1" s="228"/>
-      <c r="V1" s="228"/>
-      <c r="W1" s="228"/>
-      <c r="X1" s="228"/>
-      <c r="Y1" s="228"/>
-      <c r="Z1" s="228"/>
-      <c r="AA1" s="228"/>
-      <c r="AB1" s="228"/>
-      <c r="AC1" s="229"/>
+      <c r="G1" s="225"/>
+      <c r="H1" s="225"/>
+      <c r="I1" s="225"/>
+      <c r="J1" s="225"/>
+      <c r="K1" s="225"/>
+      <c r="L1" s="225"/>
+      <c r="M1" s="225"/>
+      <c r="N1" s="225"/>
+      <c r="O1" s="225"/>
+      <c r="P1" s="225"/>
+      <c r="Q1" s="225"/>
+      <c r="R1" s="225"/>
+      <c r="S1" s="225"/>
+      <c r="T1" s="225"/>
+      <c r="U1" s="225"/>
+      <c r="V1" s="225"/>
+      <c r="W1" s="225"/>
+      <c r="X1" s="225"/>
+      <c r="Y1" s="225"/>
+      <c r="Z1" s="225"/>
+      <c r="AA1" s="225"/>
+      <c r="AB1" s="225"/>
+      <c r="AC1" s="226"/>
       <c r="AD1" s="239" t="s">
         <v>281</v>
       </c>
@@ -43944,95 +43966,95 @@
       <c r="AG1" s="240"/>
       <c r="AH1" s="240"/>
       <c r="AI1" s="241"/>
-      <c r="AJ1" s="227" t="s">
+      <c r="AJ1" s="224" t="s">
         <v>282</v>
       </c>
-      <c r="AK1" s="228"/>
-      <c r="AL1" s="228"/>
-      <c r="AM1" s="228"/>
-      <c r="AN1" s="228"/>
-      <c r="AO1" s="229"/>
-      <c r="AP1" s="230" t="s">
+      <c r="AK1" s="225"/>
+      <c r="AL1" s="225"/>
+      <c r="AM1" s="225"/>
+      <c r="AN1" s="225"/>
+      <c r="AO1" s="226"/>
+      <c r="AP1" s="227" t="s">
         <v>283</v>
       </c>
-      <c r="AQ1" s="231"/>
-      <c r="AR1" s="231"/>
-      <c r="AS1" s="231"/>
-      <c r="AT1" s="231"/>
-      <c r="AU1" s="232"/>
-      <c r="AV1" s="233" t="s">
+      <c r="AQ1" s="228"/>
+      <c r="AR1" s="228"/>
+      <c r="AS1" s="228"/>
+      <c r="AT1" s="228"/>
+      <c r="AU1" s="229"/>
+      <c r="AV1" s="230" t="s">
         <v>86</v>
       </c>
-      <c r="AW1" s="234"/>
-      <c r="AX1" s="235"/>
+      <c r="AW1" s="231"/>
+      <c r="AX1" s="232"/>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="237"/>
-      <c r="D2" s="237"/>
-      <c r="E2" s="237"/>
-      <c r="F2" s="224" t="s">
-        <v>463</v>
-      </c>
-      <c r="G2" s="225"/>
-      <c r="H2" s="226"/>
-      <c r="I2" s="224" t="s">
-        <v>473</v>
-      </c>
-      <c r="J2" s="225"/>
-      <c r="K2" s="226"/>
-      <c r="L2" s="224" t="s">
-        <v>474</v>
-      </c>
-      <c r="M2" s="225"/>
-      <c r="N2" s="226"/>
-      <c r="O2" s="224" t="s">
-        <v>475</v>
-      </c>
-      <c r="P2" s="225"/>
-      <c r="Q2" s="226"/>
-      <c r="R2" s="224" t="s">
-        <v>476</v>
-      </c>
-      <c r="S2" s="225"/>
-      <c r="T2" s="226"/>
-      <c r="U2" s="224" t="s">
-        <v>477</v>
-      </c>
-      <c r="V2" s="225"/>
-      <c r="W2" s="226"/>
-      <c r="X2" s="224" t="s">
-        <v>478</v>
-      </c>
-      <c r="Y2" s="225"/>
-      <c r="Z2" s="226"/>
-      <c r="AA2" s="224" t="s">
-        <v>479</v>
-      </c>
-      <c r="AB2" s="225"/>
-      <c r="AC2" s="225"/>
-      <c r="AD2" s="224"/>
-      <c r="AE2" s="225"/>
-      <c r="AF2" s="226"/>
-      <c r="AG2" s="224"/>
-      <c r="AH2" s="225"/>
-      <c r="AI2" s="226"/>
-      <c r="AJ2" s="224"/>
-      <c r="AK2" s="225"/>
-      <c r="AL2" s="226"/>
-      <c r="AM2" s="224"/>
-      <c r="AN2" s="225"/>
-      <c r="AO2" s="226"/>
-      <c r="AP2" s="224"/>
-      <c r="AQ2" s="225"/>
-      <c r="AR2" s="226"/>
-      <c r="AS2" s="224"/>
-      <c r="AT2" s="225"/>
-      <c r="AU2" s="226"/>
-      <c r="AV2" s="224"/>
-      <c r="AW2" s="225"/>
-      <c r="AX2" s="226"/>
+      <c r="C2" s="234"/>
+      <c r="D2" s="234"/>
+      <c r="E2" s="234"/>
+      <c r="F2" s="236" t="s">
+        <v>461</v>
+      </c>
+      <c r="G2" s="237"/>
+      <c r="H2" s="238"/>
+      <c r="I2" s="236" t="s">
+        <v>466</v>
+      </c>
+      <c r="J2" s="237"/>
+      <c r="K2" s="238"/>
+      <c r="L2" s="236" t="s">
+        <v>467</v>
+      </c>
+      <c r="M2" s="237"/>
+      <c r="N2" s="238"/>
+      <c r="O2" s="236" t="s">
+        <v>468</v>
+      </c>
+      <c r="P2" s="237"/>
+      <c r="Q2" s="238"/>
+      <c r="R2" s="236" t="s">
+        <v>469</v>
+      </c>
+      <c r="S2" s="237"/>
+      <c r="T2" s="238"/>
+      <c r="U2" s="236" t="s">
+        <v>470</v>
+      </c>
+      <c r="V2" s="237"/>
+      <c r="W2" s="238"/>
+      <c r="X2" s="236" t="s">
+        <v>471</v>
+      </c>
+      <c r="Y2" s="237"/>
+      <c r="Z2" s="238"/>
+      <c r="AA2" s="236" t="s">
+        <v>472</v>
+      </c>
+      <c r="AB2" s="237"/>
+      <c r="AC2" s="237"/>
+      <c r="AD2" s="236"/>
+      <c r="AE2" s="237"/>
+      <c r="AF2" s="238"/>
+      <c r="AG2" s="236"/>
+      <c r="AH2" s="237"/>
+      <c r="AI2" s="238"/>
+      <c r="AJ2" s="236"/>
+      <c r="AK2" s="237"/>
+      <c r="AL2" s="238"/>
+      <c r="AM2" s="236"/>
+      <c r="AN2" s="237"/>
+      <c r="AO2" s="238"/>
+      <c r="AP2" s="236"/>
+      <c r="AQ2" s="237"/>
+      <c r="AR2" s="238"/>
+      <c r="AS2" s="236"/>
+      <c r="AT2" s="237"/>
+      <c r="AU2" s="238"/>
+      <c r="AV2" s="236"/>
+      <c r="AW2" s="237"/>
+      <c r="AX2" s="238"/>
     </row>
     <row r="3" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -44041,9 +44063,9 @@
       <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="238"/>
-      <c r="D3" s="238"/>
-      <c r="E3" s="238"/>
+      <c r="C3" s="235"/>
+      <c r="D3" s="235"/>
+      <c r="E3" s="235"/>
       <c r="F3" s="169" t="s">
         <v>393</v>
       </c>
@@ -45976,7 +45998,7 @@
         <v>45</v>
       </c>
       <c r="B31" s="148" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="C31" s="58">
         <f t="shared" ref="C31:C38" si="8">SUM(F31,I31,L31,O31,R31,X31,AA31,AD31,U31,AG31,AJ31,AM31,AP31,AS31,AV31)</f>
@@ -46675,6 +46697,13 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="F1:AC1"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
+    <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="AJ1:AO1"/>
     <mergeCell ref="AP1:AU1"/>
     <mergeCell ref="AV1:AX1"/>
@@ -46691,13 +46720,6 @@
     <mergeCell ref="AD1:AI1"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="I2:K2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="F1:AC1"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:AW32">
     <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
@@ -46732,70 +46754,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C1" s="236" t="s">
+      <c r="C1" s="233" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="236" t="s">
+      <c r="D1" s="233" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="236" t="s">
+      <c r="E1" s="233" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="266" t="s">
+      <c r="F1" s="273" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="267"/>
-      <c r="H1" s="268"/>
-      <c r="I1" s="269" t="s">
+      <c r="G1" s="274"/>
+      <c r="H1" s="275"/>
+      <c r="I1" s="276" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="270"/>
-      <c r="K1" s="271"/>
-      <c r="L1" s="273" t="s">
+      <c r="J1" s="277"/>
+      <c r="K1" s="278"/>
+      <c r="L1" s="243" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="274"/>
-      <c r="N1" s="275"/>
-      <c r="O1" s="276" t="s">
+      <c r="M1" s="244"/>
+      <c r="N1" s="245"/>
+      <c r="O1" s="246" t="s">
         <v>199</v>
       </c>
-      <c r="P1" s="277"/>
-      <c r="Q1" s="278"/>
-      <c r="R1" s="242" t="s">
+      <c r="P1" s="247"/>
+      <c r="Q1" s="248"/>
+      <c r="R1" s="249" t="s">
         <v>200</v>
       </c>
-      <c r="S1" s="243"/>
-      <c r="T1" s="244"/>
-      <c r="U1" s="245" t="s">
+      <c r="S1" s="250"/>
+      <c r="T1" s="251"/>
+      <c r="U1" s="252" t="s">
         <v>306</v>
       </c>
-      <c r="V1" s="246"/>
-      <c r="W1" s="247"/>
+      <c r="V1" s="253"/>
+      <c r="W1" s="254"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="237"/>
-      <c r="D2" s="237"/>
-      <c r="E2" s="237"/>
-      <c r="F2" s="248"/>
-      <c r="G2" s="249"/>
-      <c r="H2" s="250"/>
-      <c r="I2" s="263"/>
-      <c r="J2" s="264"/>
-      <c r="K2" s="265"/>
-      <c r="L2" s="260"/>
-      <c r="M2" s="261"/>
-      <c r="N2" s="262"/>
-      <c r="O2" s="257"/>
-      <c r="P2" s="258"/>
-      <c r="Q2" s="259"/>
-      <c r="R2" s="254"/>
-      <c r="S2" s="255"/>
-      <c r="T2" s="256"/>
-      <c r="U2" s="251"/>
-      <c r="V2" s="252"/>
-      <c r="W2" s="253"/>
+      <c r="C2" s="234"/>
+      <c r="D2" s="234"/>
+      <c r="E2" s="234"/>
+      <c r="F2" s="255"/>
+      <c r="G2" s="256"/>
+      <c r="H2" s="257"/>
+      <c r="I2" s="270"/>
+      <c r="J2" s="271"/>
+      <c r="K2" s="272"/>
+      <c r="L2" s="267"/>
+      <c r="M2" s="268"/>
+      <c r="N2" s="269"/>
+      <c r="O2" s="264"/>
+      <c r="P2" s="265"/>
+      <c r="Q2" s="266"/>
+      <c r="R2" s="261"/>
+      <c r="S2" s="262"/>
+      <c r="T2" s="263"/>
+      <c r="U2" s="258"/>
+      <c r="V2" s="259"/>
+      <c r="W2" s="260"/>
     </row>
     <row r="3" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -46804,9 +46826,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="272"/>
-      <c r="D3" s="272"/>
-      <c r="E3" s="272"/>
+      <c r="C3" s="242"/>
+      <c r="D3" s="242"/>
+      <c r="E3" s="242"/>
       <c r="F3" s="188" t="s">
         <v>393</v>
       </c>
@@ -47893,7 +47915,7 @@
         <v>45</v>
       </c>
       <c r="B31" s="148" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="C31" s="58">
         <f t="shared" ref="C31:C38" si="6">SUM(F31,I31,L31,O31,R31,U31)</f>
@@ -48268,11 +48290,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="O1:Q1"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="F2:H2"/>
@@ -48283,6 +48300,11 @@
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="O1:Q1"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:W32">
     <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
@@ -48522,7 +48544,7 @@
       <c r="F6" s="25"/>
       <c r="G6" s="21">
         <f>'Apps &amp; Goals 26-27'!C4</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H6" s="21">
         <f>'Apps &amp; Goals 26-27'!D4</f>
@@ -48534,7 +48556,7 @@
       </c>
       <c r="J6" s="25">
         <f>G6+C6</f>
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K6" s="25">
         <f>H6+D6</f>
@@ -49487,7 +49509,7 @@
       <c r="F11" s="25"/>
       <c r="G11" s="21">
         <f>'Apps &amp; Goals 26-27'!C9</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H11" s="21">
         <f>'Apps &amp; Goals 26-27'!D9</f>
@@ -49499,7 +49521,7 @@
       </c>
       <c r="J11" s="25">
         <f t="shared" si="0"/>
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K11" s="25">
         <f t="shared" si="1"/>
@@ -49680,7 +49702,7 @@
       <c r="F12" s="25"/>
       <c r="G12" s="21">
         <f>'Apps &amp; Goals 26-27'!C10</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H12" s="21">
         <f>'Apps &amp; Goals 26-27'!D10</f>
@@ -49692,7 +49714,7 @@
       </c>
       <c r="J12" s="25">
         <f t="shared" si="0"/>
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K12" s="25">
         <f t="shared" si="1"/>
@@ -49873,7 +49895,7 @@
       <c r="F13" s="25"/>
       <c r="G13" s="21">
         <f>'Apps &amp; Goals 26-27'!C11</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H13" s="21">
         <f>'Apps &amp; Goals 26-27'!D11</f>
@@ -49885,7 +49907,7 @@
       </c>
       <c r="J13" s="25">
         <f t="shared" si="0"/>
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K13" s="25">
         <f t="shared" si="1"/>
@@ -50066,7 +50088,7 @@
       <c r="F14" s="25"/>
       <c r="G14" s="21">
         <f>'Apps &amp; Goals 26-27'!C12</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H14" s="21">
         <f>'Apps &amp; Goals 26-27'!D12</f>
@@ -50078,7 +50100,7 @@
       </c>
       <c r="J14" s="25">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K14" s="25">
         <f t="shared" si="1"/>
@@ -50259,7 +50281,7 @@
       <c r="F15" s="25"/>
       <c r="G15" s="21">
         <f>'Apps &amp; Goals 26-27'!C13</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="21">
         <f>'Apps &amp; Goals 26-27'!D13</f>
@@ -50271,7 +50293,7 @@
       </c>
       <c r="J15" s="25">
         <f t="shared" si="0"/>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K15" s="25">
         <f t="shared" si="1"/>
@@ -50645,7 +50667,7 @@
       <c r="F17" s="25"/>
       <c r="G17" s="21">
         <f>'Apps &amp; Goals 26-27'!C15</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17" s="21">
         <f>'Apps &amp; Goals 26-27'!D15</f>
@@ -50657,7 +50679,7 @@
       </c>
       <c r="J17" s="25">
         <f t="shared" si="0"/>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K17" s="25">
         <f t="shared" si="1"/>
@@ -50838,7 +50860,7 @@
       <c r="F18" s="25"/>
       <c r="G18" s="21">
         <f>'Apps &amp; Goals 26-27'!C16</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H18" s="21">
         <f>'Apps &amp; Goals 26-27'!D16</f>
@@ -50850,7 +50872,7 @@
       </c>
       <c r="J18" s="25">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K18" s="25">
         <f t="shared" si="1"/>
@@ -51031,7 +51053,7 @@
       <c r="F19" s="25"/>
       <c r="G19" s="21">
         <f>'Apps &amp; Goals 26-27'!C17</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H19" s="21">
         <f>'Apps &amp; Goals 26-27'!D17</f>
@@ -51043,7 +51065,7 @@
       </c>
       <c r="J19" s="25">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K19" s="25">
         <f t="shared" si="1"/>
@@ -51610,7 +51632,7 @@
       <c r="F22" s="25"/>
       <c r="G22" s="21">
         <f>'Apps &amp; Goals 26-27'!C20</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H22" s="21">
         <f>'Apps &amp; Goals 26-27'!D20</f>
@@ -51622,7 +51644,7 @@
       </c>
       <c r="J22" s="25">
         <f t="shared" si="0"/>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K22" s="25">
         <f t="shared" si="1"/>
@@ -51803,7 +51825,7 @@
       <c r="F23" s="25"/>
       <c r="G23" s="21">
         <f>'Apps &amp; Goals 26-27'!C21</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H23" s="21">
         <f>'Apps &amp; Goals 26-27'!D21</f>
@@ -51815,7 +51837,7 @@
       </c>
       <c r="J23" s="25">
         <f t="shared" si="0"/>
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K23" s="25">
         <f t="shared" si="1"/>
@@ -52189,7 +52211,7 @@
       <c r="F25" s="25"/>
       <c r="G25" s="21">
         <f>'Apps &amp; Goals 26-27'!C23</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H25" s="21">
         <f>'Apps &amp; Goals 26-27'!D23</f>
@@ -52201,7 +52223,7 @@
       </c>
       <c r="J25" s="25">
         <f t="shared" si="0"/>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K25" s="25">
         <f t="shared" si="1"/>
@@ -52575,7 +52597,7 @@
       <c r="F27" s="25"/>
       <c r="G27" s="21">
         <f>'Apps &amp; Goals 26-27'!C25</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H27" s="21">
         <f>'Apps &amp; Goals 26-27'!D25</f>
@@ -52587,7 +52609,7 @@
       </c>
       <c r="J27" s="25">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K27" s="25">
         <f t="shared" si="1"/>
@@ -52768,7 +52790,7 @@
       <c r="F28" s="25"/>
       <c r="G28" s="21">
         <f>'Apps &amp; Goals 26-27'!C26</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H28" s="21">
         <f>'Apps &amp; Goals 26-27'!D26</f>
@@ -52780,7 +52802,7 @@
       </c>
       <c r="J28" s="25">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K28" s="25">
         <f t="shared" si="1"/>
@@ -53154,7 +53176,7 @@
       <c r="F30" s="25"/>
       <c r="G30" s="21">
         <f>'Apps &amp; Goals 26-27'!C28</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H30" s="21">
         <f>'Apps &amp; Goals 26-27'!D28</f>
@@ -53166,7 +53188,7 @@
       </c>
       <c r="J30" s="25">
         <f t="shared" si="0"/>
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K30" s="25">
         <f t="shared" si="1"/>
@@ -53719,7 +53741,7 @@
         <v>45</v>
       </c>
       <c r="B33" s="22" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="C33" s="25">
         <v>0</v>
@@ -53759,7 +53781,7 @@
         <v>45</v>
       </c>
       <c r="N33" s="45" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="O33" s="26">
         <v>0</v>
@@ -53796,7 +53818,7 @@
         <v>0</v>
       </c>
       <c r="Z33" s="23" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="AA33" s="24">
         <v>0</v>
@@ -53833,7 +53855,7 @@
         <v>0</v>
       </c>
       <c r="AL33" s="19" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="AM33" s="18">
         <v>0</v>
@@ -53870,7 +53892,7 @@
         <v>0</v>
       </c>
       <c r="AX33" s="32" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="AY33" s="33">
         <v>0</v>
@@ -54698,7 +54720,7 @@
       <c r="F38" s="25"/>
       <c r="G38" s="21">
         <f>'Apps &amp; Goals 26-27'!C36</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" s="21">
         <f>'Apps &amp; Goals 26-27'!D36</f>
@@ -54710,7 +54732,7 @@
       </c>
       <c r="J38" s="25">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K38" s="25">
         <f t="shared" si="1"/>
@@ -55289,72 +55311,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C1" s="236" t="s">
+      <c r="C1" s="233" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="236" t="s">
+      <c r="D1" s="233" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="236" t="s">
+      <c r="E1" s="233" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="266" t="s">
+      <c r="F1" s="273" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="267"/>
-      <c r="H1" s="268"/>
-      <c r="I1" s="269" t="s">
+      <c r="G1" s="274"/>
+      <c r="H1" s="275"/>
+      <c r="I1" s="276" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="270"/>
-      <c r="K1" s="271"/>
-      <c r="L1" s="273" t="s">
+      <c r="J1" s="277"/>
+      <c r="K1" s="278"/>
+      <c r="L1" s="243" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="274"/>
-      <c r="N1" s="275"/>
-      <c r="O1" s="276" t="s">
+      <c r="M1" s="244"/>
+      <c r="N1" s="245"/>
+      <c r="O1" s="246" t="s">
         <v>199</v>
       </c>
-      <c r="P1" s="277"/>
-      <c r="Q1" s="278"/>
-      <c r="R1" s="242" t="s">
+      <c r="P1" s="247"/>
+      <c r="Q1" s="248"/>
+      <c r="R1" s="249" t="s">
         <v>200</v>
       </c>
-      <c r="S1" s="243"/>
-      <c r="T1" s="244"/>
-      <c r="U1" s="245" t="s">
+      <c r="S1" s="250"/>
+      <c r="T1" s="251"/>
+      <c r="U1" s="252" t="s">
         <v>306</v>
       </c>
-      <c r="V1" s="246"/>
-      <c r="W1" s="247"/>
+      <c r="V1" s="253"/>
+      <c r="W1" s="254"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="237"/>
-      <c r="D2" s="237"/>
-      <c r="E2" s="237"/>
-      <c r="F2" s="248" t="s">
+      <c r="C2" s="234"/>
+      <c r="D2" s="234"/>
+      <c r="E2" s="234"/>
+      <c r="F2" s="255" t="s">
         <v>433</v>
       </c>
-      <c r="G2" s="249"/>
-      <c r="H2" s="250"/>
-      <c r="I2" s="263"/>
-      <c r="J2" s="264"/>
-      <c r="K2" s="265"/>
-      <c r="L2" s="260"/>
-      <c r="M2" s="261"/>
-      <c r="N2" s="262"/>
-      <c r="O2" s="257"/>
-      <c r="P2" s="258"/>
-      <c r="Q2" s="259"/>
-      <c r="R2" s="254"/>
-      <c r="S2" s="255"/>
-      <c r="T2" s="256"/>
-      <c r="U2" s="251"/>
-      <c r="V2" s="252"/>
-      <c r="W2" s="253"/>
+      <c r="G2" s="256"/>
+      <c r="H2" s="257"/>
+      <c r="I2" s="270"/>
+      <c r="J2" s="271"/>
+      <c r="K2" s="272"/>
+      <c r="L2" s="267"/>
+      <c r="M2" s="268"/>
+      <c r="N2" s="269"/>
+      <c r="O2" s="264"/>
+      <c r="P2" s="265"/>
+      <c r="Q2" s="266"/>
+      <c r="R2" s="261"/>
+      <c r="S2" s="262"/>
+      <c r="T2" s="263"/>
+      <c r="U2" s="258"/>
+      <c r="V2" s="259"/>
+      <c r="W2" s="260"/>
     </row>
     <row r="3" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -55363,9 +55385,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="272"/>
-      <c r="D3" s="272"/>
-      <c r="E3" s="272"/>
+      <c r="C3" s="242"/>
+      <c r="D3" s="242"/>
+      <c r="E3" s="242"/>
       <c r="F3" s="188" t="s">
         <v>393</v>
       </c>
@@ -56484,7 +56506,7 @@
         <v>45</v>
       </c>
       <c r="B31" s="148" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="C31" s="58">
         <f t="shared" ref="C31:C38" si="6">SUM(F31,I31,L31,O31,R31,U31)</f>
@@ -56869,6 +56891,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="F2:H2"/>
@@ -56879,11 +56906,6 @@
     <mergeCell ref="U2:W2"/>
     <mergeCell ref="L1:N1"/>
     <mergeCell ref="O1:Q1"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:W32">
     <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
@@ -57276,7 +57298,7 @@
         <v>45</v>
       </c>
       <c r="B30" s="148" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="C30" s="20"/>
       <c r="D30" s="20"/>
@@ -57390,51 +57412,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="282" t="s">
+      <c r="C1" s="301" t="s">
         <v>202</v>
       </c>
-      <c r="D1" s="283"/>
-      <c r="E1" s="283"/>
-      <c r="F1" s="283"/>
-      <c r="G1" s="283"/>
-      <c r="H1" s="283"/>
-      <c r="I1" s="284"/>
+      <c r="D1" s="302"/>
+      <c r="E1" s="302"/>
+      <c r="F1" s="302"/>
+      <c r="G1" s="302"/>
+      <c r="H1" s="302"/>
+      <c r="I1" s="303"/>
       <c r="J1" s="114" t="s">
         <v>195</v>
       </c>
       <c r="K1" s="115" t="s">
         <v>194</v>
       </c>
-      <c r="L1" s="306" t="s">
+      <c r="L1" s="281" t="s">
         <v>287</v>
       </c>
-      <c r="M1" s="311"/>
-      <c r="N1" s="311"/>
-      <c r="O1" s="311"/>
-      <c r="P1" s="311"/>
-      <c r="Q1" s="311"/>
-      <c r="R1" s="311"/>
-      <c r="S1" s="311"/>
-      <c r="T1" s="311"/>
-      <c r="U1" s="311"/>
-      <c r="V1" s="311"/>
-      <c r="W1" s="311"/>
-      <c r="X1" s="311"/>
-      <c r="Y1" s="311"/>
-      <c r="Z1" s="311"/>
-      <c r="AA1" s="311"/>
-      <c r="AB1" s="311"/>
-      <c r="AC1" s="311"/>
-      <c r="AD1" s="311"/>
-      <c r="AE1" s="311"/>
-      <c r="AF1" s="311"/>
-      <c r="AG1" s="312"/>
-      <c r="AH1" s="306" t="s">
+      <c r="M1" s="286"/>
+      <c r="N1" s="286"/>
+      <c r="O1" s="286"/>
+      <c r="P1" s="286"/>
+      <c r="Q1" s="286"/>
+      <c r="R1" s="286"/>
+      <c r="S1" s="286"/>
+      <c r="T1" s="286"/>
+      <c r="U1" s="286"/>
+      <c r="V1" s="286"/>
+      <c r="W1" s="286"/>
+      <c r="X1" s="286"/>
+      <c r="Y1" s="286"/>
+      <c r="Z1" s="286"/>
+      <c r="AA1" s="286"/>
+      <c r="AB1" s="286"/>
+      <c r="AC1" s="286"/>
+      <c r="AD1" s="286"/>
+      <c r="AE1" s="286"/>
+      <c r="AF1" s="286"/>
+      <c r="AG1" s="287"/>
+      <c r="AH1" s="281" t="s">
         <v>175</v>
       </c>
-      <c r="AI1" s="307"/>
-      <c r="AJ1" s="307"/>
-      <c r="AK1" s="308"/>
+      <c r="AI1" s="282"/>
+      <c r="AJ1" s="282"/>
+      <c r="AK1" s="283"/>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B2" s="111"/>
@@ -58003,13 +58025,13 @@
     <row r="7" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A7" s="71">
         <f t="shared" si="0"/>
-        <v>2.1176470588235294</v>
+        <v>2.0571428571428569</v>
       </c>
       <c r="B7" s="110">
         <v>5</v>
       </c>
-      <c r="C7" s="123" t="s">
-        <v>181</v>
+      <c r="C7" s="123">
+        <v>0</v>
       </c>
       <c r="D7" s="123">
         <v>1</v>
@@ -62634,15 +62656,15 @@
         <f t="shared" ref="J80:J111" si="2">H80-I80</f>
         <v>2</v>
       </c>
-      <c r="K80" s="313" t="s">
+      <c r="K80" s="288" t="s">
         <v>435</v>
       </c>
-      <c r="L80" s="314"/>
-      <c r="M80" s="315"/>
+      <c r="L80" s="289"/>
+      <c r="M80" s="290"/>
       <c r="O80" s="133"/>
       <c r="P80" s="133"/>
-      <c r="W80" s="309"/>
-      <c r="X80" s="309"/>
+      <c r="W80" s="284"/>
+      <c r="X80" s="284"/>
       <c r="Y80" s="70" t="s">
         <v>211</v>
       </c>
@@ -62692,15 +62714,15 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K81" s="316"/>
-      <c r="L81" s="317"/>
-      <c r="M81" s="318"/>
+      <c r="K81" s="291"/>
+      <c r="L81" s="292"/>
+      <c r="M81" s="293"/>
       <c r="O81" s="133"/>
       <c r="P81" s="133"/>
-      <c r="W81" s="309" t="s">
+      <c r="W81" s="284" t="s">
         <v>209</v>
       </c>
-      <c r="X81" s="309"/>
+      <c r="X81" s="284"/>
       <c r="Y81" s="70">
         <f>COUNTIF(L3:AG40,3)</f>
         <v>481</v>
@@ -62756,17 +62778,17 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K82" s="319" t="s">
+      <c r="K82" s="294" t="s">
         <v>436</v>
       </c>
-      <c r="L82" s="320"/>
-      <c r="M82" s="321"/>
+      <c r="L82" s="295"/>
+      <c r="M82" s="296"/>
       <c r="O82" s="133"/>
       <c r="P82" s="133"/>
-      <c r="W82" s="309" t="s">
+      <c r="W82" s="284" t="s">
         <v>210</v>
       </c>
-      <c r="X82" s="309"/>
+      <c r="X82" s="284"/>
       <c r="Y82" s="70">
         <f>COUNTIF(K3:K40,3)+COUNTIF(J3:J15,3)</f>
         <v>25</v>
@@ -62822,38 +62844,37 @@
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="K83" s="322" t="s">
+      <c r="K83" s="297" t="s">
         <v>437</v>
       </c>
-      <c r="L83" s="323"/>
-      <c r="M83" s="324"/>
+      <c r="L83" s="298"/>
+      <c r="M83" s="299"/>
       <c r="O83" s="133"/>
       <c r="P83" s="133"/>
-      <c r="W83" s="310" t="s">
+      <c r="W83" s="285" t="s">
         <v>97</v>
       </c>
-      <c r="X83" s="310"/>
+      <c r="X83" s="285"/>
       <c r="Y83" s="194">
-        <f>223</f>
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Z83" s="194">
         <v>60</v>
       </c>
       <c r="AA83" s="70">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AC83" s="109">
         <f>Y83/SUM($Y$83:$AA$83)</f>
-        <v>0.62290502793296088</v>
+        <v>0.62222222222222223</v>
       </c>
       <c r="AD83" s="195">
         <f t="shared" ref="AD83:AE83" si="5">Z83/SUM($Y$83:$AA$83)</f>
-        <v>0.16759776536312848</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="AE83" s="195">
         <f t="shared" si="5"/>
-        <v>0.20949720670391062</v>
+        <v>0.21111111111111111</v>
       </c>
     </row>
     <row r="84" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -62886,15 +62907,15 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="K84" s="297" t="s">
+      <c r="K84" s="315" t="s">
         <v>284</v>
       </c>
-      <c r="L84" s="298"/>
-      <c r="M84" s="299"/>
+      <c r="L84" s="316"/>
+      <c r="M84" s="317"/>
       <c r="O84" s="141"/>
       <c r="P84" s="141"/>
-      <c r="W84" s="281"/>
-      <c r="X84" s="281"/>
+      <c r="W84" s="300"/>
+      <c r="X84" s="300"/>
       <c r="Y84" s="196"/>
       <c r="Z84" s="196"/>
       <c r="AA84" s="196"/>
@@ -62932,9 +62953,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K85" s="300"/>
-      <c r="L85" s="301"/>
-      <c r="M85" s="302"/>
+      <c r="K85" s="318"/>
+      <c r="L85" s="319"/>
+      <c r="M85" s="320"/>
       <c r="O85" s="141"/>
       <c r="P85" s="141"/>
     </row>
@@ -62968,9 +62989,9 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="K86" s="300"/>
-      <c r="L86" s="301"/>
-      <c r="M86" s="302"/>
+      <c r="K86" s="318"/>
+      <c r="L86" s="319"/>
+      <c r="M86" s="320"/>
       <c r="O86" s="141"/>
       <c r="P86" s="141"/>
     </row>
@@ -63004,9 +63025,9 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="K87" s="300"/>
-      <c r="L87" s="301"/>
-      <c r="M87" s="302"/>
+      <c r="K87" s="318"/>
+      <c r="L87" s="319"/>
+      <c r="M87" s="320"/>
       <c r="O87" s="141"/>
       <c r="P87" s="141"/>
     </row>
@@ -63040,9 +63061,9 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K88" s="300"/>
-      <c r="L88" s="301"/>
-      <c r="M88" s="302"/>
+      <c r="K88" s="318"/>
+      <c r="L88" s="319"/>
+      <c r="M88" s="320"/>
       <c r="O88" s="141"/>
       <c r="P88" s="141"/>
     </row>
@@ -63076,9 +63097,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K89" s="300"/>
-      <c r="L89" s="301"/>
-      <c r="M89" s="302"/>
+      <c r="K89" s="318"/>
+      <c r="L89" s="319"/>
+      <c r="M89" s="320"/>
       <c r="O89" s="141"/>
       <c r="P89" s="141"/>
     </row>
@@ -63112,9 +63133,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K90" s="300"/>
-      <c r="L90" s="301"/>
-      <c r="M90" s="302"/>
+      <c r="K90" s="318"/>
+      <c r="L90" s="319"/>
+      <c r="M90" s="320"/>
       <c r="O90" s="141"/>
       <c r="P90" s="141"/>
     </row>
@@ -63148,9 +63169,9 @@
         <f t="shared" si="2"/>
         <v>47</v>
       </c>
-      <c r="K91" s="300"/>
-      <c r="L91" s="301"/>
-      <c r="M91" s="302"/>
+      <c r="K91" s="318"/>
+      <c r="L91" s="319"/>
+      <c r="M91" s="320"/>
       <c r="O91" s="141"/>
       <c r="P91" s="141"/>
     </row>
@@ -63184,9 +63205,9 @@
         <f t="shared" si="2"/>
         <v>51</v>
       </c>
-      <c r="K92" s="300"/>
-      <c r="L92" s="301"/>
-      <c r="M92" s="302"/>
+      <c r="K92" s="318"/>
+      <c r="L92" s="319"/>
+      <c r="M92" s="320"/>
       <c r="O92" s="141"/>
       <c r="P92" s="141"/>
     </row>
@@ -63220,9 +63241,9 @@
         <f t="shared" si="2"/>
         <v>37</v>
       </c>
-      <c r="K93" s="300"/>
-      <c r="L93" s="301"/>
-      <c r="M93" s="302"/>
+      <c r="K93" s="318"/>
+      <c r="L93" s="319"/>
+      <c r="M93" s="320"/>
       <c r="O93" s="141"/>
       <c r="P93" s="141"/>
     </row>
@@ -63256,9 +63277,9 @@
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="K94" s="300"/>
-      <c r="L94" s="301"/>
-      <c r="M94" s="302"/>
+      <c r="K94" s="318"/>
+      <c r="L94" s="319"/>
+      <c r="M94" s="320"/>
       <c r="O94" s="141"/>
       <c r="P94" s="141"/>
     </row>
@@ -63292,9 +63313,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K95" s="300"/>
-      <c r="L95" s="301"/>
-      <c r="M95" s="302"/>
+      <c r="K95" s="318"/>
+      <c r="L95" s="319"/>
+      <c r="M95" s="320"/>
       <c r="O95" s="141"/>
       <c r="P95" s="141"/>
     </row>
@@ -63328,9 +63349,9 @@
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="K96" s="300"/>
-      <c r="L96" s="301"/>
-      <c r="M96" s="302"/>
+      <c r="K96" s="318"/>
+      <c r="L96" s="319"/>
+      <c r="M96" s="320"/>
       <c r="O96" s="141"/>
       <c r="P96" s="141"/>
     </row>
@@ -63364,9 +63385,9 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="K97" s="300"/>
-      <c r="L97" s="301"/>
-      <c r="M97" s="302"/>
+      <c r="K97" s="318"/>
+      <c r="L97" s="319"/>
+      <c r="M97" s="320"/>
       <c r="O97" s="141"/>
       <c r="P97" s="141"/>
     </row>
@@ -63400,9 +63421,9 @@
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="K98" s="300"/>
-      <c r="L98" s="301"/>
-      <c r="M98" s="302"/>
+      <c r="K98" s="318"/>
+      <c r="L98" s="319"/>
+      <c r="M98" s="320"/>
       <c r="O98" s="141"/>
       <c r="P98" s="141"/>
     </row>
@@ -63436,9 +63457,9 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K99" s="300"/>
-      <c r="L99" s="301"/>
-      <c r="M99" s="302"/>
+      <c r="K99" s="318"/>
+      <c r="L99" s="319"/>
+      <c r="M99" s="320"/>
       <c r="O99" s="141"/>
       <c r="P99" s="141"/>
     </row>
@@ -63472,9 +63493,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K100" s="300"/>
-      <c r="L100" s="301"/>
-      <c r="M100" s="302"/>
+      <c r="K100" s="318"/>
+      <c r="L100" s="319"/>
+      <c r="M100" s="320"/>
       <c r="O100" s="141"/>
       <c r="P100" s="141"/>
     </row>
@@ -63508,9 +63529,9 @@
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="K101" s="300"/>
-      <c r="L101" s="301"/>
-      <c r="M101" s="302"/>
+      <c r="K101" s="318"/>
+      <c r="L101" s="319"/>
+      <c r="M101" s="320"/>
       <c r="O101" s="141"/>
       <c r="P101" s="141"/>
     </row>
@@ -63544,9 +63565,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K102" s="300"/>
-      <c r="L102" s="301"/>
-      <c r="M102" s="302"/>
+      <c r="K102" s="318"/>
+      <c r="L102" s="319"/>
+      <c r="M102" s="320"/>
       <c r="O102" s="141"/>
       <c r="P102" s="141"/>
     </row>
@@ -63580,9 +63601,9 @@
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="K103" s="300"/>
-      <c r="L103" s="301"/>
-      <c r="M103" s="302"/>
+      <c r="K103" s="318"/>
+      <c r="L103" s="319"/>
+      <c r="M103" s="320"/>
       <c r="O103" s="141"/>
       <c r="P103" s="141"/>
     </row>
@@ -63616,9 +63637,9 @@
         <f t="shared" si="2"/>
         <v>33</v>
       </c>
-      <c r="K104" s="300"/>
-      <c r="L104" s="301"/>
-      <c r="M104" s="302"/>
+      <c r="K104" s="318"/>
+      <c r="L104" s="319"/>
+      <c r="M104" s="320"/>
       <c r="O104" s="141"/>
       <c r="P104" s="141"/>
     </row>
@@ -63652,9 +63673,9 @@
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="K105" s="303"/>
-      <c r="L105" s="304"/>
-      <c r="M105" s="305"/>
+      <c r="K105" s="321"/>
+      <c r="L105" s="322"/>
+      <c r="M105" s="323"/>
       <c r="O105" s="141"/>
       <c r="P105" s="141"/>
     </row>
@@ -63688,11 +63709,11 @@
         <f t="shared" si="2"/>
         <v>21</v>
       </c>
-      <c r="K106" s="294" t="s">
+      <c r="K106" s="312" t="s">
         <v>286</v>
       </c>
-      <c r="L106" s="295"/>
-      <c r="M106" s="296"/>
+      <c r="L106" s="313"/>
+      <c r="M106" s="314"/>
       <c r="O106" s="126"/>
       <c r="P106" s="126"/>
     </row>
@@ -63726,15 +63747,15 @@
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="K107" s="294" t="s">
+      <c r="K107" s="312" t="s">
         <v>288</v>
       </c>
-      <c r="L107" s="295"/>
-      <c r="M107" s="296"/>
+      <c r="L107" s="313"/>
+      <c r="M107" s="314"/>
       <c r="O107" s="126"/>
       <c r="P107" s="126"/>
     </row>
-    <row r="108" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="93" t="s">
         <v>201</v>
       </c>
@@ -63764,15 +63785,15 @@
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="K108" s="285" t="s">
+      <c r="K108" s="304" t="s">
         <v>289</v>
       </c>
-      <c r="L108" s="286"/>
-      <c r="M108" s="287"/>
+      <c r="L108" s="305"/>
+      <c r="M108" s="306"/>
       <c r="O108" s="126"/>
       <c r="P108" s="126"/>
     </row>
-    <row r="109" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="90" t="s">
         <v>219</v>
       </c>
@@ -63802,13 +63823,13 @@
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="K109" s="288"/>
-      <c r="L109" s="289"/>
-      <c r="M109" s="290"/>
+      <c r="K109" s="307"/>
+      <c r="L109" s="327"/>
+      <c r="M109" s="308"/>
       <c r="O109" s="126"/>
       <c r="P109" s="126"/>
     </row>
-    <row r="110" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="93" t="s">
         <v>274</v>
       </c>
@@ -63838,13 +63859,13 @@
         <f t="shared" si="2"/>
         <v>45</v>
       </c>
-      <c r="K110" s="288"/>
-      <c r="L110" s="289"/>
-      <c r="M110" s="290"/>
+      <c r="K110" s="307"/>
+      <c r="L110" s="327"/>
+      <c r="M110" s="308"/>
       <c r="O110" s="126"/>
       <c r="P110" s="126"/>
     </row>
-    <row r="111" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="90" t="s">
         <v>285</v>
       </c>
@@ -63874,13 +63895,13 @@
         <f t="shared" si="2"/>
         <v>62</v>
       </c>
-      <c r="K111" s="288"/>
-      <c r="L111" s="289"/>
-      <c r="M111" s="290"/>
+      <c r="K111" s="307"/>
+      <c r="L111" s="327"/>
+      <c r="M111" s="308"/>
       <c r="O111" s="126"/>
       <c r="P111" s="126"/>
     </row>
-    <row r="112" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="93" t="s">
         <v>310</v>
       </c>
@@ -63914,11 +63935,11 @@
         <f t="shared" ref="J112:J114" si="6">H112-I112</f>
         <v>34</v>
       </c>
-      <c r="K112" s="288"/>
-      <c r="L112" s="289"/>
-      <c r="M112" s="290"/>
-    </row>
-    <row r="113" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K112" s="307"/>
+      <c r="L112" s="327"/>
+      <c r="M112" s="308"/>
+    </row>
+    <row r="113" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="156" t="s">
         <v>311</v>
       </c>
@@ -63952,11 +63973,11 @@
         <f t="shared" si="6"/>
         <v>43</v>
       </c>
-      <c r="K113" s="291"/>
-      <c r="L113" s="292"/>
-      <c r="M113" s="293"/>
-    </row>
-    <row r="114" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="K113" s="307"/>
+      <c r="L113" s="327"/>
+      <c r="M113" s="308"/>
+    </row>
+    <row r="114" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="93" t="s">
         <v>438</v>
       </c>
@@ -63976,7 +63997,7 @@
       </c>
       <c r="G114" s="122">
         <f>COUNTIF(C3:C41,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H114" s="122">
         <f>Match!R4</f>
@@ -63984,16 +64005,25 @@
       </c>
       <c r="I114" s="122">
         <f>Match!S4</f>
-        <v>2</v>
-      </c>
-      <c r="J114" s="122">
+        <v>4</v>
+      </c>
+      <c r="J114" s="154">
         <f t="shared" si="6"/>
-        <v>6</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="K114" s="309"/>
+      <c r="L114" s="310"/>
+      <c r="M114" s="311"/>
     </row>
   </sheetData>
   <autoFilter ref="A79:J112" xr:uid="{9C81160F-C24B-449F-8F5A-CB622AB71070}"/>
   <mergeCells count="15">
+    <mergeCell ref="W84:X84"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="K106:M106"/>
+    <mergeCell ref="K107:M107"/>
+    <mergeCell ref="K84:M105"/>
+    <mergeCell ref="K108:M114"/>
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="W80:X80"/>
     <mergeCell ref="W81:X81"/>
@@ -64003,12 +64033,6 @@
     <mergeCell ref="K80:M81"/>
     <mergeCell ref="K82:M82"/>
     <mergeCell ref="K83:M83"/>
-    <mergeCell ref="W84:X84"/>
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="K108:M113"/>
-    <mergeCell ref="K106:M106"/>
-    <mergeCell ref="K107:M107"/>
-    <mergeCell ref="K84:M105"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <conditionalFormatting sqref="A3:A40">
@@ -64082,7 +64106,7 @@
     <col min="2" max="2" width="5.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19.85546875" bestFit="1" customWidth="1"/>
@@ -64100,32 +64124,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="325" t="s">
+      <c r="A1" s="202" t="s">
         <v>405</v>
       </c>
-      <c r="B1" s="325"/>
-      <c r="C1" s="325"/>
-      <c r="D1" s="325"/>
-      <c r="E1" s="325"/>
-      <c r="F1" s="325" t="s">
+      <c r="B1" s="202"/>
+      <c r="C1" s="202"/>
+      <c r="D1" s="202"/>
+      <c r="E1" s="202"/>
+      <c r="F1" s="202" t="s">
         <v>406</v>
       </c>
-      <c r="G1" s="325"/>
-      <c r="H1" s="325"/>
-      <c r="I1" s="325"/>
-      <c r="J1" s="325"/>
+      <c r="G1" s="202"/>
+      <c r="H1" s="202"/>
+      <c r="I1" s="202"/>
+      <c r="J1" s="202"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2" s="325"/>
-      <c r="B2" s="325"/>
-      <c r="C2" s="325"/>
-      <c r="D2" s="325"/>
-      <c r="E2" s="325"/>
-      <c r="F2" s="325"/>
-      <c r="G2" s="325"/>
-      <c r="H2" s="325"/>
-      <c r="I2" s="325"/>
-      <c r="J2" s="325"/>
+      <c r="A2" s="202"/>
+      <c r="B2" s="202"/>
+      <c r="C2" s="202"/>
+      <c r="D2" s="202"/>
+      <c r="E2" s="202"/>
+      <c r="F2" s="202"/>
+      <c r="G2" s="202"/>
+      <c r="H2" s="202"/>
+      <c r="I2" s="202"/>
+      <c r="J2" s="202"/>
       <c r="L2" t="s">
         <v>409</v>
       </c>
@@ -64192,13 +64216,13 @@
         <v>1</v>
       </c>
       <c r="M3" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="N3" s="193">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O3" s="193">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P3" s="193">
         <v>0</v>
@@ -64207,57 +64231,57 @@
         <v>0</v>
       </c>
       <c r="R3" s="193">
+        <v>13</v>
+      </c>
+      <c r="S3" s="193">
+        <v>5</v>
+      </c>
+      <c r="T3" s="193">
         <v>8</v>
       </c>
-      <c r="S3" s="193">
-        <v>1</v>
-      </c>
-      <c r="T3" s="193">
-        <v>7</v>
-      </c>
       <c r="U3" s="193">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B4" s="192">
-        <v>0.66666666666666663</v>
+        <v>0.5625</v>
       </c>
       <c r="C4" t="s">
         <v>4</v>
       </c>
       <c r="D4" t="s">
+        <v>424</v>
+      </c>
+      <c r="E4" t="s">
+        <v>480</v>
+      </c>
+      <c r="F4" t="s">
+        <v>473</v>
+      </c>
+      <c r="G4" s="192" t="s">
+        <v>478</v>
+      </c>
+      <c r="H4" t="s">
+        <v>4</v>
+      </c>
+      <c r="I4" t="s">
         <v>417</v>
       </c>
-      <c r="E4" t="s">
-        <v>482</v>
-      </c>
-      <c r="F4" t="s">
-        <v>472</v>
-      </c>
-      <c r="G4" s="202" t="s">
-        <v>480</v>
-      </c>
-      <c r="H4" t="s">
-        <v>110</v>
-      </c>
-      <c r="I4" t="s">
-        <v>467</v>
-      </c>
       <c r="J4" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="L4">
         <v>2</v>
       </c>
       <c r="M4" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="N4" s="193">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O4" s="193">
         <v>4</v>
@@ -64266,16 +64290,16 @@
         <v>0</v>
       </c>
       <c r="Q4" s="193">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" s="193">
         <v>8</v>
       </c>
       <c r="S4" s="193">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T4" s="193">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U4" s="193">
         <v>12</v>
@@ -64286,31 +64310,31 @@
         <v>3</v>
       </c>
       <c r="M5" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="N5" s="193">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O5" s="193">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P5" s="193">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q5" s="193">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" s="193">
+        <v>16</v>
+      </c>
+      <c r="S5" s="193">
         <v>5</v>
       </c>
-      <c r="S5" s="193">
-        <v>2</v>
-      </c>
       <c r="T5" s="193">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="U5" s="193">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
@@ -64318,31 +64342,31 @@
         <v>4</v>
       </c>
       <c r="M6" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="N6" s="193">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O6" s="193">
         <v>2</v>
       </c>
       <c r="P6" s="193">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q6" s="193">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" s="193">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="S6" s="193">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T6" s="193">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U6" s="193">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
@@ -64350,31 +64374,31 @@
         <v>5</v>
       </c>
       <c r="M7" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="N7" s="193">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O7" s="193">
         <v>2</v>
       </c>
       <c r="P7" s="193">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q7" s="193">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" s="193">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="S7" s="193">
+        <v>3</v>
+      </c>
+      <c r="T7" s="193">
+        <v>4</v>
+      </c>
+      <c r="U7" s="193">
         <v>9</v>
-      </c>
-      <c r="T7" s="193">
-        <v>1</v>
-      </c>
-      <c r="U7" s="193">
-        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
@@ -64382,13 +64406,13 @@
         <v>6</v>
       </c>
       <c r="M8" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="N8" s="193">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O8" s="193">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P8" s="193">
         <v>3</v>
@@ -64406,7 +64430,7 @@
         <v>3</v>
       </c>
       <c r="U8" s="193">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
@@ -64414,13 +64438,13 @@
         <v>7</v>
       </c>
       <c r="M9" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="N9" s="193">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O9" s="193">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P9" s="193">
         <v>3</v>
@@ -64432,13 +64456,13 @@
         <v>6</v>
       </c>
       <c r="S9" s="193">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T9" s="193">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U9" s="193">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
@@ -64446,31 +64470,31 @@
         <v>8</v>
       </c>
       <c r="M10" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="N10" s="193">
+        <v>5</v>
+      </c>
+      <c r="O10" s="193">
+        <v>2</v>
+      </c>
+      <c r="P10" s="193">
+        <v>2</v>
+      </c>
+      <c r="Q10" s="193">
+        <v>1</v>
+      </c>
+      <c r="R10" s="193">
+        <v>6</v>
+      </c>
+      <c r="S10" s="193">
         <v>4</v>
-      </c>
-      <c r="O10" s="193">
-        <v>1</v>
-      </c>
-      <c r="P10" s="193">
-        <v>3</v>
-      </c>
-      <c r="Q10" s="193">
-        <v>0</v>
-      </c>
-      <c r="R10" s="193">
-        <v>5</v>
-      </c>
-      <c r="S10" s="193">
-        <v>3</v>
       </c>
       <c r="T10" s="193">
         <v>2</v>
       </c>
       <c r="U10" s="193">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
@@ -64478,31 +64502,31 @@
         <v>9</v>
       </c>
       <c r="M11" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="N11" s="193">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O11" s="193">
         <v>2</v>
       </c>
       <c r="P11" s="193">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q11" s="193">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R11" s="193">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="S11" s="193">
-        <v>10</v>
-      </c>
-      <c r="T11" s="193" t="s">
-        <v>462</v>
+        <v>9</v>
+      </c>
+      <c r="T11" s="193">
+        <v>0</v>
       </c>
       <c r="U11" s="193">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
@@ -64510,31 +64534,31 @@
         <v>10</v>
       </c>
       <c r="M12" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="N12" s="193">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O12" s="193">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P12" s="193">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="193">
         <v>2</v>
       </c>
-      <c r="Q12" s="193">
-        <v>0</v>
-      </c>
       <c r="R12" s="193">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="S12" s="193">
-        <v>4</v>
-      </c>
-      <c r="T12" s="193">
-        <v>2</v>
+        <v>12</v>
+      </c>
+      <c r="T12" s="193" t="s">
+        <v>464</v>
       </c>
       <c r="U12" s="193">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
@@ -64542,31 +64566,31 @@
         <v>11</v>
       </c>
       <c r="M13" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="N13" s="193">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O13" s="193">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P13" s="193">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q13" s="193">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R13" s="193">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S13" s="193">
-        <v>2</v>
-      </c>
-      <c r="T13" s="193">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="T13" s="193" t="s">
+        <v>481</v>
       </c>
       <c r="U13" s="193">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
@@ -64574,10 +64598,10 @@
         <v>12</v>
       </c>
       <c r="M14" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="N14" s="193">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O14" s="193">
         <v>1</v>
@@ -64586,13 +64610,13 @@
         <v>2</v>
       </c>
       <c r="Q14" s="193">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R14" s="193">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="S14" s="193">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T14" s="193">
         <v>0</v>
@@ -64606,31 +64630,31 @@
         <v>13</v>
       </c>
       <c r="M15" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="N15" s="193">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O15" s="193">
         <v>1</v>
       </c>
       <c r="P15" s="193">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q15" s="193">
         <v>2</v>
       </c>
       <c r="R15" s="193">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="S15" s="193">
-        <v>7</v>
-      </c>
-      <c r="T15" s="193">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="T15" s="193" t="s">
+        <v>431</v>
       </c>
       <c r="U15" s="193">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
@@ -64641,7 +64665,7 @@
         <v>429</v>
       </c>
       <c r="N16" s="193">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O16" s="193">
         <v>1</v>
@@ -64650,16 +64674,16 @@
         <v>1</v>
       </c>
       <c r="Q16" s="193">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R16" s="193">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S16" s="193">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" s="193" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="U16" s="193">
         <v>4</v>
@@ -64670,31 +64694,31 @@
         <v>15</v>
       </c>
       <c r="M17" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="N17" s="193">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O17" s="193">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P17" s="193">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="193">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R17" s="193">
         <v>6</v>
       </c>
       <c r="S17" s="193">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T17" s="193" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="U17" s="193">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="12:21" x14ac:dyDescent="0.25">
@@ -64702,31 +64726,31 @@
         <v>16</v>
       </c>
       <c r="M18" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="N18" s="193">
+        <v>5</v>
+      </c>
+      <c r="O18" s="193">
+        <v>1</v>
+      </c>
+      <c r="P18" s="193">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="193">
+        <v>3</v>
+      </c>
+      <c r="R18" s="193">
         <v>4</v>
       </c>
-      <c r="O18" s="193">
-        <v>1</v>
-      </c>
-      <c r="P18" s="193">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="193">
-        <v>3</v>
-      </c>
-      <c r="R18" s="193">
-        <v>6</v>
-      </c>
       <c r="S18" s="193">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T18" s="193" t="s">
         <v>434</v>
       </c>
       <c r="U18" s="193">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="12:21" x14ac:dyDescent="0.25">
@@ -64734,31 +64758,31 @@
         <v>17</v>
       </c>
       <c r="M19" t="s">
-        <v>430</v>
+        <v>415</v>
       </c>
       <c r="N19" s="193">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O19" s="193">
         <v>0</v>
       </c>
       <c r="P19" s="193">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q19" s="193">
         <v>2</v>
       </c>
       <c r="R19" s="193">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S19" s="193">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T19" s="193" t="s">
-        <v>434</v>
+        <v>464</v>
       </c>
       <c r="U19" s="193">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="12:21" x14ac:dyDescent="0.25">
@@ -64766,31 +64790,31 @@
         <v>18</v>
       </c>
       <c r="M20" t="s">
-        <v>421</v>
+        <v>404</v>
       </c>
       <c r="N20" s="193">
+        <v>5</v>
+      </c>
+      <c r="O20" s="193">
+        <v>1</v>
+      </c>
+      <c r="P20" s="193">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="193">
         <v>4</v>
       </c>
-      <c r="O20" s="193">
-        <v>0</v>
-      </c>
-      <c r="P20" s="193">
-        <v>1</v>
-      </c>
-      <c r="Q20" s="193">
-        <v>3</v>
-      </c>
       <c r="R20" s="193">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S20" s="193">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T20" s="193" t="s">
-        <v>462</v>
+        <v>482</v>
       </c>
       <c r="U20" s="193">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="12:21" x14ac:dyDescent="0.25">
@@ -64798,31 +64822,31 @@
         <v>19</v>
       </c>
       <c r="M21" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="N21" s="193">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O21" s="193">
         <v>0</v>
       </c>
       <c r="P21" s="193">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q21" s="193">
         <v>3</v>
       </c>
       <c r="R21" s="193">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S21" s="193">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T21" s="193" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="U21" s="193">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="12:21" x14ac:dyDescent="0.25">
@@ -64830,31 +64854,31 @@
         <v>20</v>
       </c>
       <c r="M22" t="s">
-        <v>404</v>
+        <v>430</v>
       </c>
       <c r="N22" s="193">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O22" s="193">
         <v>0</v>
       </c>
       <c r="P22" s="193">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q22" s="193">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R22" s="193">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S22" s="193">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T22" s="193" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="U22" s="193">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -64897,10 +64921,10 @@
         <v>350</v>
       </c>
       <c r="B2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C2" s="199">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="D2">
         <v>90</v>
@@ -64911,10 +64935,10 @@
         <v>441</v>
       </c>
       <c r="B3" t="s">
-        <v>466</v>
+        <v>485</v>
       </c>
       <c r="C3" s="199">
-        <v>7.5</v>
+        <v>6.1</v>
       </c>
       <c r="D3">
         <v>90</v>
@@ -64928,10 +64952,10 @@
         <v>451</v>
       </c>
       <c r="C4" s="199">
-        <v>6.8</v>
-      </c>
-      <c r="D4" t="s">
-        <v>455</v>
+        <v>7</v>
+      </c>
+      <c r="D4">
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -64939,10 +64963,10 @@
         <v>442</v>
       </c>
       <c r="B5" t="s">
-        <v>485</v>
+        <v>457</v>
       </c>
       <c r="C5" s="199">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="D5">
         <v>90</v>
@@ -64953,16 +64977,13 @@
         <v>443</v>
       </c>
       <c r="B6" t="s">
-        <v>458</v>
+        <v>484</v>
       </c>
       <c r="C6" s="199">
-        <v>7.3</v>
+        <v>6.7</v>
       </c>
       <c r="D6" t="s">
         <v>455</v>
-      </c>
-      <c r="E6" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -64970,16 +64991,13 @@
         <v>446</v>
       </c>
       <c r="B7" t="s">
-        <v>456</v>
+        <v>486</v>
       </c>
       <c r="C7" s="199">
-        <v>8.3000000000000007</v>
+        <v>6.5</v>
       </c>
       <c r="D7">
         <v>90</v>
-      </c>
-      <c r="E7" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -64987,10 +65005,10 @@
         <v>446</v>
       </c>
       <c r="B8" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C8" s="199">
-        <v>7.3</v>
+        <v>5.8</v>
       </c>
       <c r="D8" t="s">
         <v>455</v>
@@ -65001,16 +65019,13 @@
         <v>447</v>
       </c>
       <c r="B9" t="s">
-        <v>486</v>
+        <v>452</v>
       </c>
       <c r="C9" s="199">
-        <v>8.9</v>
-      </c>
-      <c r="D9">
-        <v>90</v>
-      </c>
-      <c r="E9" t="s">
-        <v>491</v>
+        <v>6</v>
+      </c>
+      <c r="D9" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -65018,16 +65033,13 @@
         <v>448</v>
       </c>
       <c r="B10" t="s">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="C10" s="199">
-        <v>6.9</v>
+        <v>6.1</v>
       </c>
       <c r="D10" t="s">
         <v>455</v>
-      </c>
-      <c r="E10" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -65038,13 +65050,10 @@
         <v>487</v>
       </c>
       <c r="C11" s="199">
-        <v>8.6</v>
+        <v>6.9</v>
       </c>
       <c r="D11" t="s">
         <v>455</v>
-      </c>
-      <c r="E11" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -65055,7 +65064,7 @@
         <v>488</v>
       </c>
       <c r="C12" s="199">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="D12">
         <v>90</v>
@@ -65063,10 +65072,10 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B13" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C13" s="199">
         <v>6.5</v>
@@ -65077,13 +65086,13 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="B14" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="C14" s="199">
-        <v>6.6</v>
+        <v>6.1</v>
       </c>
       <c r="D14" t="s">
         <v>454</v>
@@ -65091,13 +65100,13 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B15" t="s">
-        <v>453</v>
+        <v>477</v>
       </c>
       <c r="C15" s="199">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="D15" t="s">
         <v>454</v>
@@ -65105,13 +65114,13 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B16" t="s">
-        <v>489</v>
+        <v>462</v>
       </c>
       <c r="C16" s="199">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="D16" t="s">
         <v>454</v>
@@ -65119,10 +65128,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="B17" t="s">
-        <v>490</v>
+        <v>476</v>
       </c>
       <c r="C17" s="199"/>
       <c r="D17" t="s">
@@ -65153,24 +65162,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="203" t="s">
+      <c r="A1" s="207" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="326"/>
-      <c r="C1" s="327" t="s">
+      <c r="B1" s="324"/>
+      <c r="C1" s="325" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="206"/>
-      <c r="E1" s="328"/>
-      <c r="H1" s="203" t="s">
+      <c r="D1" s="210"/>
+      <c r="E1" s="326"/>
+      <c r="H1" s="207" t="s">
         <v>47</v>
       </c>
-      <c r="I1" s="326"/>
-      <c r="J1" s="327" t="s">
+      <c r="I1" s="324"/>
+      <c r="J1" s="325" t="s">
         <v>44</v>
       </c>
-      <c r="K1" s="206"/>
-      <c r="L1" s="328"/>
+      <c r="K1" s="210"/>
+      <c r="L1" s="326"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -66150,11 +66159,11 @@
       </c>
       <c r="K30" s="9">
         <f>'Apps &amp; Goals'!T10</f>
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L30" s="14">
         <f>J30/K30</f>
-        <v>0.26415094339622641</v>
+        <v>0.26332288401253917</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
@@ -66258,9 +66267,9 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="207"/>
-      <c r="G1" s="207"/>
-      <c r="H1" s="207"/>
+      <c r="F1" s="211"/>
+      <c r="G1" s="211"/>
+      <c r="H1" s="211"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -66284,38 +66293,38 @@
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="5"/>
-      <c r="E2" s="203" t="s">
+      <c r="E2" s="207" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="204"/>
-      <c r="G2" s="205"/>
-      <c r="H2" s="208" t="s">
+      <c r="F2" s="208"/>
+      <c r="G2" s="209"/>
+      <c r="H2" s="212" t="s">
         <v>120</v>
       </c>
-      <c r="I2" s="209"/>
-      <c r="J2" s="210"/>
-      <c r="K2" s="203" t="s">
+      <c r="I2" s="213"/>
+      <c r="J2" s="214"/>
+      <c r="K2" s="207" t="s">
         <v>108</v>
       </c>
-      <c r="L2" s="204"/>
-      <c r="M2" s="205"/>
-      <c r="N2" s="208" t="s">
+      <c r="L2" s="208"/>
+      <c r="M2" s="209"/>
+      <c r="N2" s="212" t="s">
         <v>110</v>
       </c>
-      <c r="O2" s="209"/>
-      <c r="P2" s="210"/>
-      <c r="Q2" s="203" t="s">
+      <c r="O2" s="213"/>
+      <c r="P2" s="214"/>
+      <c r="Q2" s="207" t="s">
         <v>39</v>
       </c>
-      <c r="R2" s="204"/>
-      <c r="S2" s="205"/>
-      <c r="T2" s="206" t="s">
+      <c r="R2" s="208"/>
+      <c r="S2" s="209"/>
+      <c r="T2" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="U2" s="206"/>
-      <c r="V2" s="206"/>
+      <c r="U2" s="210"/>
+      <c r="V2" s="210"/>
       <c r="Z2" s="125">
-        <v>46280</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
@@ -66400,7 +66409,7 @@
       </c>
       <c r="E4" s="6">
         <f>'#'!J6</f>
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F4" s="6">
         <f>'#'!K6</f>
@@ -66460,7 +66469,7 @@
       </c>
       <c r="T4" s="2">
         <f t="shared" ref="T4:V4" si="0">SUM(E4,H4,K4,N4,Q4)</f>
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="U4" s="2">
         <f t="shared" ref="U4" si="1">SUM(F4,I4,L4,O4,R4)</f>
@@ -66830,7 +66839,7 @@
       </c>
       <c r="E9" s="6">
         <f>'#'!J11</f>
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F9" s="6">
         <f>'#'!K11</f>
@@ -66890,7 +66899,7 @@
       </c>
       <c r="T9" s="2">
         <f t="shared" si="2"/>
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="U9" s="2">
         <f t="shared" si="3"/>
@@ -66916,7 +66925,7 @@
       </c>
       <c r="E10" s="6">
         <f>'#'!J12</f>
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F10" s="6">
         <f>'#'!K12</f>
@@ -66976,7 +66985,7 @@
       </c>
       <c r="T10" s="2">
         <f t="shared" si="2"/>
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="U10" s="2">
         <f t="shared" si="3"/>
@@ -67002,7 +67011,7 @@
       </c>
       <c r="E11" s="6">
         <f>'#'!J13</f>
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F11" s="6">
         <f>'#'!K13</f>
@@ -67062,7 +67071,7 @@
       </c>
       <c r="T11" s="2">
         <f t="shared" si="2"/>
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="U11" s="2">
         <f t="shared" si="3"/>
@@ -67088,7 +67097,7 @@
       </c>
       <c r="E12" s="6">
         <f>'#'!J14</f>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F12" s="6">
         <f>'#'!K14</f>
@@ -67148,7 +67157,7 @@
       </c>
       <c r="T12" s="2">
         <f t="shared" si="2"/>
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U12" s="2">
         <f t="shared" si="3"/>
@@ -67174,7 +67183,7 @@
       </c>
       <c r="E13" s="6">
         <f>'#'!J15</f>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F13" s="6">
         <f>'#'!K15</f>
@@ -67234,7 +67243,7 @@
       </c>
       <c r="T13" s="2">
         <f t="shared" si="2"/>
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="U13" s="2">
         <f t="shared" si="3"/>
@@ -67346,7 +67355,7 @@
       </c>
       <c r="E15" s="6">
         <f>'#'!J17</f>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F15" s="6">
         <f>'#'!K17</f>
@@ -67406,7 +67415,7 @@
       </c>
       <c r="T15" s="2">
         <f t="shared" si="2"/>
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="U15" s="2">
         <f t="shared" si="3"/>
@@ -67432,7 +67441,7 @@
       </c>
       <c r="E16" s="6">
         <f>'#'!J18</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F16" s="6">
         <f>'#'!K18</f>
@@ -67492,7 +67501,7 @@
       </c>
       <c r="T16" s="2">
         <f t="shared" ref="T16:T28" si="5">SUM(E16,H16,K16,N16,Q16)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U16" s="2">
         <f t="shared" ref="U16:U28" si="6">SUM(F16,I16,L16,O16,R16)</f>
@@ -67518,7 +67527,7 @@
       </c>
       <c r="E17" s="6">
         <f>'#'!J19</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F17" s="6">
         <f>'#'!K19</f>
@@ -67578,7 +67587,7 @@
       </c>
       <c r="T17" s="2">
         <f t="shared" si="5"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U17" s="2">
         <f t="shared" si="6"/>
@@ -67779,7 +67788,7 @@
       </c>
       <c r="E20" s="6">
         <f>'#'!J22</f>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F20" s="6">
         <f>'#'!K22</f>
@@ -67839,7 +67848,7 @@
       </c>
       <c r="T20" s="2">
         <f t="shared" si="5"/>
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U20" s="2">
         <f t="shared" si="6"/>
@@ -67865,7 +67874,7 @@
       </c>
       <c r="E21" s="6">
         <f>'#'!J23</f>
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F21" s="6">
         <f>'#'!K23</f>
@@ -67925,7 +67934,7 @@
       </c>
       <c r="T21" s="2">
         <f t="shared" si="5"/>
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="U21" s="2">
         <f t="shared" si="6"/>
@@ -68037,7 +68046,7 @@
       </c>
       <c r="E23" s="6">
         <f>'#'!J25</f>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F23" s="6">
         <f>'#'!K25</f>
@@ -68097,7 +68106,7 @@
       </c>
       <c r="T23" s="2">
         <f t="shared" si="5"/>
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="U23" s="2">
         <f t="shared" si="6"/>
@@ -68212,7 +68221,7 @@
       </c>
       <c r="E25" s="6">
         <f>'#'!J27</f>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F25" s="6">
         <f>'#'!K27</f>
@@ -68272,7 +68281,7 @@
       </c>
       <c r="T25" s="2">
         <f t="shared" si="5"/>
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U25" s="2">
         <f t="shared" si="6"/>
@@ -68298,7 +68307,7 @@
       </c>
       <c r="E26" s="6">
         <f>'#'!J28</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F26" s="6">
         <f>'#'!K28</f>
@@ -68358,7 +68367,7 @@
       </c>
       <c r="T26" s="2">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U26" s="2">
         <f t="shared" si="6"/>
@@ -68470,7 +68479,7 @@
       </c>
       <c r="E28" s="6">
         <f>'#'!J30</f>
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F28" s="6">
         <f>'#'!K30</f>
@@ -68530,7 +68539,7 @@
       </c>
       <c r="T28" s="2">
         <f t="shared" si="5"/>
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="U28" s="2">
         <f t="shared" si="6"/>
@@ -68724,7 +68733,7 @@
         <v>353</v>
       </c>
       <c r="D31" s="148" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="E31" s="6">
         <f>'#'!J33</f>
@@ -69164,7 +69173,7 @@
       </c>
       <c r="E36" s="6">
         <f>'#'!J38</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F36" s="6">
         <f>'#'!K38</f>
@@ -69224,7 +69233,7 @@
       </c>
       <c r="T36" s="2">
         <f t="shared" si="9"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="U36" s="2">
         <f t="shared" si="10"/>
@@ -69497,30 +69506,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="213" t="s">
+      <c r="D2" s="205" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="213"/>
-      <c r="F2" s="214" t="s">
+      <c r="E2" s="205"/>
+      <c r="F2" s="206" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="214"/>
-      <c r="H2" s="213" t="s">
+      <c r="G2" s="206"/>
+      <c r="H2" s="205" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="213"/>
-      <c r="J2" s="214" t="s">
+      <c r="I2" s="205"/>
+      <c r="J2" s="206" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="214"/>
-      <c r="L2" s="213" t="s">
+      <c r="K2" s="206"/>
+      <c r="L2" s="205" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="213"/>
-      <c r="N2" s="206" t="s">
+      <c r="M2" s="205"/>
+      <c r="N2" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="206"/>
+      <c r="O2" s="210"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -71517,30 +71526,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="213" t="s">
+      <c r="D2" s="205" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="213"/>
-      <c r="F2" s="214" t="s">
+      <c r="E2" s="205"/>
+      <c r="F2" s="206" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="214"/>
-      <c r="H2" s="213" t="s">
+      <c r="G2" s="206"/>
+      <c r="H2" s="205" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="213"/>
-      <c r="J2" s="214" t="s">
+      <c r="I2" s="205"/>
+      <c r="J2" s="206" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="214"/>
-      <c r="L2" s="213" t="s">
+      <c r="K2" s="206"/>
+      <c r="L2" s="205" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="213"/>
-      <c r="N2" s="206" t="s">
+      <c r="M2" s="205"/>
+      <c r="N2" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="206"/>
+      <c r="O2" s="210"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -73474,30 +73483,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="213" t="s">
+      <c r="D2" s="205" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="213"/>
-      <c r="F2" s="214" t="s">
+      <c r="E2" s="205"/>
+      <c r="F2" s="206" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="214"/>
-      <c r="H2" s="213" t="s">
+      <c r="G2" s="206"/>
+      <c r="H2" s="205" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="213"/>
-      <c r="J2" s="214" t="s">
+      <c r="I2" s="205"/>
+      <c r="J2" s="206" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="214"/>
-      <c r="L2" s="213" t="s">
+      <c r="K2" s="206"/>
+      <c r="L2" s="205" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="213"/>
-      <c r="N2" s="206" t="s">
+      <c r="M2" s="205"/>
+      <c r="N2" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="206"/>
+      <c r="O2" s="210"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -75522,30 +75531,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="213" t="s">
+      <c r="D2" s="205" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="213"/>
-      <c r="F2" s="214" t="s">
+      <c r="E2" s="205"/>
+      <c r="F2" s="206" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="214"/>
-      <c r="H2" s="213" t="s">
+      <c r="G2" s="206"/>
+      <c r="H2" s="205" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="213"/>
-      <c r="J2" s="214" t="s">
+      <c r="I2" s="205"/>
+      <c r="J2" s="206" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="214"/>
-      <c r="L2" s="213" t="s">
+      <c r="K2" s="206"/>
+      <c r="L2" s="205" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="213"/>
-      <c r="N2" s="206" t="s">
+      <c r="M2" s="205"/>
+      <c r="N2" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="206"/>
+      <c r="O2" s="210"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -77230,30 +77239,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="213" t="s">
+      <c r="C2" s="205" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="213"/>
-      <c r="E2" s="214" t="s">
+      <c r="D2" s="205"/>
+      <c r="E2" s="206" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="214"/>
-      <c r="G2" s="213" t="s">
+      <c r="F2" s="206"/>
+      <c r="G2" s="205" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="213"/>
-      <c r="I2" s="214" t="s">
+      <c r="H2" s="205"/>
+      <c r="I2" s="206" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="214"/>
-      <c r="K2" s="213" t="s">
+      <c r="J2" s="206"/>
+      <c r="K2" s="205" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="213"/>
-      <c r="M2" s="206" t="s">
+      <c r="L2" s="205"/>
+      <c r="M2" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="206"/>
+      <c r="N2" s="210"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -79015,30 +79024,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="213" t="s">
+      <c r="C2" s="205" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="213"/>
-      <c r="E2" s="214" t="s">
+      <c r="D2" s="205"/>
+      <c r="E2" s="206" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="214"/>
-      <c r="G2" s="213" t="s">
+      <c r="F2" s="206"/>
+      <c r="G2" s="205" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="213"/>
-      <c r="I2" s="214" t="s">
+      <c r="H2" s="205"/>
+      <c r="I2" s="206" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="214"/>
-      <c r="K2" s="213" t="s">
+      <c r="J2" s="206"/>
+      <c r="K2" s="205" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="213"/>
-      <c r="M2" s="206" t="s">
+      <c r="L2" s="205"/>
+      <c r="M2" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="206"/>
+      <c r="N2" s="210"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">

--- a/data/arsenal_stats.xlsx
+++ b/data/arsenal_stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bungeltd-my.sharepoint.com/personal/przemyslaw_iskra_bunge_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8609" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D7FF3B0-8F85-4157-A8D8-CA5EBBA72F55}"/>
+  <xr:revisionPtr revIDLastSave="8660" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F13D3A70-3713-471D-BA9C-0CF41389DE5B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="799" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2274" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2277" uniqueCount="488">
   <si>
     <t>Arsenal FC squad statistics</t>
   </si>
@@ -1375,9 +1375,6 @@
     <t>Tottenham Hotspur</t>
   </si>
   <si>
-    <t>−1</t>
-  </si>
-  <si>
     <t>KONSA Ezri</t>
   </si>
   <si>
@@ -1441,9 +1438,6 @@
     <t>Odegaard</t>
   </si>
   <si>
-    <t>Tzolis</t>
-  </si>
-  <si>
     <t>Sub</t>
   </si>
   <si>
@@ -1456,9 +1450,6 @@
     <t>Konsa</t>
   </si>
   <si>
-    <t>Zubimendi</t>
-  </si>
-  <si>
     <t>Goal/Assist</t>
   </si>
   <si>
@@ -1468,13 +1459,7 @@
     <t>SSC Napoli</t>
   </si>
   <si>
-    <t>Eze</t>
-  </si>
-  <si>
     <t>Bruno</t>
-  </si>
-  <si>
-    <t>−2</t>
   </si>
   <si>
     <t>−6</t>
@@ -1501,22 +1486,10 @@
     <t>Sabah</t>
   </si>
   <si>
-    <t>19.09.2026</t>
-  </si>
-  <si>
-    <t>Amex Stadium (A)</t>
-  </si>
-  <si>
     <t>JULIENNE Theo</t>
   </si>
   <si>
-    <t>Dowman</t>
-  </si>
-  <si>
     <t>Gyokeres</t>
-  </si>
-  <si>
-    <t>0-3</t>
   </si>
   <si>
     <t>10.10.2026</t>
@@ -1547,6 +1520,30 @@
   </si>
   <si>
     <t>Havertz</t>
+  </si>
+  <si>
+    <t>2-1</t>
+  </si>
+  <si>
+    <t>13.10.2026</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>White</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Lewis-Skelly</t>
+  </si>
+  <si>
+    <t>Madueke</t>
+  </si>
+  <si>
+    <t>Hincapie</t>
   </si>
 </sst>
 </file>
@@ -2663,7 +2660,7 @@
     <xf numFmtId="0" fontId="7" fillId="9" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="17" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="328">
+  <cellXfs count="329">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3052,21 +3049,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3091,13 +3073,16 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3109,14 +3094,32 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="54" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3154,15 +3157,6 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="28" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3170,27 +3164,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="60" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="10" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="37" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="11" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3283,10 +3256,106 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="60" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="10" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="37" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="11" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="54" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3346,77 +3415,8 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3425,9 +3425,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
@@ -4634,7 +4632,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="33"/>
                 <c:pt idx="0">
-                  <c:v>7</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -4643,55 +4641,55 @@
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>8</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
-                </c:pt>
                 <c:pt idx="7">
-                  <c:v>8</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>5</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>6</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>5</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>7</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>7</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>6</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>0</c:v>
@@ -4700,13 +4698,13 @@
                   <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>6</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>7</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>0</c:v>
@@ -4721,7 +4719,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>6</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>0</c:v>
@@ -4927,7 +4925,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>0</c:v>
@@ -4936,7 +4934,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>0</c:v>
@@ -6483,7 +6481,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7BC14897-0129-46CD-A73F-B1571D32917F}" type="CELLRANGE">
+                    <a:fld id="{20595F00-0B75-4A4F-A893-9330259D7299}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6517,7 +6515,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{4178F5E4-DA8C-492B-99E6-6E605E4ED344}" type="CELLRANGE">
+                    <a:fld id="{56043E37-011C-4457-8B49-3C0E8BDF360E}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6551,7 +6549,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{641F420A-DA3E-442F-AF78-0660F7BA5D84}" type="CELLRANGE">
+                    <a:fld id="{A06AD215-DA47-41F3-8EC1-ECEA4C77A108}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6585,7 +6583,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{66EE9827-6009-4444-9E84-CD86512FA6F9}" type="CELLRANGE">
+                    <a:fld id="{8B37CCAE-B9CB-46C3-ADB9-526406B7DB32}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6619,7 +6617,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E0926421-2EA9-4F6D-B77C-001F64A5EB1C}" type="CELLRANGE">
+                    <a:fld id="{020919F7-F801-4709-97A1-8D26A712D9AE}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6653,7 +6651,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{876B52FC-1DAA-4E24-BFD8-9A0CF8DF73F1}" type="CELLRANGE">
+                    <a:fld id="{FFF2D78D-4DC5-4101-80AB-DB7B4C5966C3}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6687,7 +6685,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6EB6174C-D0BC-4CAD-A5E0-2AF1926BBB8F}" type="CELLRANGE">
+                    <a:fld id="{A4E5032B-69B0-4F5C-9B26-312259075FD2}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6721,7 +6719,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{813790BD-6A16-4DBD-AA3A-0AF4B05C7E80}" type="CELLRANGE">
+                    <a:fld id="{F85034E7-E76F-496E-A6B4-6FB9CB08BFBB}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6755,7 +6753,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7E9A4C21-D6BD-405D-80C6-E494D8873DD5}" type="CELLRANGE">
+                    <a:fld id="{09CDCC49-A929-4FA6-9AFA-4ECB84B5847B}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6789,7 +6787,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{BFF4B849-A219-48D0-A871-952A75FBF109}" type="CELLRANGE">
+                    <a:fld id="{BDEA372C-FBF9-4AAD-94D2-EBAB609A61B9}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6823,7 +6821,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{1DCFCCE7-85B9-44E1-92C9-E1F2CF14F55F}" type="CELLRANGE">
+                    <a:fld id="{B20D9E29-D58F-43AB-901A-ED9E422FA096}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6857,7 +6855,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{4DDFBE4C-D4DC-4559-93FC-3599E47A5608}" type="CELLRANGE">
+                    <a:fld id="{5AA3BA7B-48DB-4F22-9644-D4D68816E8E3}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6906,7 +6904,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{9AF60094-8B4C-401D-87CC-27AEC32454E5}" type="CELLRANGE">
+                    <a:fld id="{DA9C5508-EF0B-48BD-91C1-6CAD40FDFF7C}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr>
                         <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
@@ -6965,7 +6963,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D779D5AE-7159-49CE-BEA4-8CA46772E4D2}" type="CELLRANGE">
+                    <a:fld id="{8174E073-8A5C-4E02-88E3-7B2489DC77C1}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6999,7 +6997,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{BE739721-2871-4B57-905E-9F3993BA9BD5}" type="CELLRANGE">
+                    <a:fld id="{8A0D8CA5-F683-4E04-9EEA-F8D004088AD9}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7033,7 +7031,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7BBF11F2-7E34-4004-A724-7D1FD0203F4C}" type="CELLRANGE">
+                    <a:fld id="{710D97AE-4A50-4CEB-A2C7-89DD376D9EE0}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7067,7 +7065,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2BBD684D-7A55-4964-893E-FFEE60DE3101}" type="CELLRANGE">
+                    <a:fld id="{C9C941AC-8B6F-4DFA-9532-00F47C4D15BC}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7245,55 +7243,55 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>196</c:v>
+                  <c:v>197</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>43</c:v>
+                  <c:v>44</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>269</c:v>
+                  <c:v>270</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>319</c:v>
+                  <c:v>320</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>242</c:v>
+                  <c:v>243</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>59</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>97</c:v>
+                  <c:v>98</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>60</c:v>
+                  <c:v>61</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>6</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>47</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>51</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>85</c:v>
+                  <c:v>86</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>118</c:v>
+                  <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>71</c:v>
+                  <c:v>72</c:v>
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>2</c:v>
@@ -7356,7 +7354,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>5</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>0</c:v>
@@ -7583,7 +7581,7 @@
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="16">
-                        <c:v>5</c:v>
+                        <c:v>6</c:v>
                       </c:pt>
                       <c:pt idx="17">
                         <c:v>0</c:v>
@@ -14203,30 +14201,30 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
       <c r="B1" s="5"/>
-      <c r="C1" s="205" t="s">
+      <c r="C1" s="212" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="205"/>
-      <c r="E1" s="206" t="s">
+      <c r="D1" s="212"/>
+      <c r="E1" s="213" t="s">
         <v>120</v>
       </c>
-      <c r="F1" s="206"/>
-      <c r="G1" s="205" t="s">
+      <c r="F1" s="213"/>
+      <c r="G1" s="212" t="s">
         <v>108</v>
       </c>
-      <c r="H1" s="205"/>
-      <c r="I1" s="206" t="s">
+      <c r="H1" s="212"/>
+      <c r="I1" s="213" t="s">
         <v>110</v>
       </c>
-      <c r="J1" s="206"/>
-      <c r="K1" s="205" t="s">
+      <c r="J1" s="213"/>
+      <c r="K1" s="212" t="s">
         <v>39</v>
       </c>
-      <c r="L1" s="205"/>
-      <c r="M1" s="203" t="s">
+      <c r="L1" s="212"/>
+      <c r="M1" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="204"/>
+      <c r="N1" s="211"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -15933,30 +15931,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="205" t="s">
+      <c r="C2" s="212" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="205"/>
-      <c r="E2" s="206" t="s">
+      <c r="D2" s="212"/>
+      <c r="E2" s="213" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="206"/>
-      <c r="G2" s="205" t="s">
+      <c r="F2" s="213"/>
+      <c r="G2" s="212" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="205"/>
-      <c r="I2" s="206" t="s">
+      <c r="H2" s="212"/>
+      <c r="I2" s="213" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="206"/>
-      <c r="K2" s="205" t="s">
+      <c r="J2" s="213"/>
+      <c r="K2" s="212" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="205"/>
-      <c r="M2" s="210" t="s">
+      <c r="L2" s="212"/>
+      <c r="M2" s="205" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="210"/>
+      <c r="N2" s="205"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -17760,30 +17758,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="205" t="s">
+      <c r="C2" s="212" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="205"/>
-      <c r="E2" s="206" t="s">
+      <c r="D2" s="212"/>
+      <c r="E2" s="213" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="206"/>
-      <c r="G2" s="205" t="s">
+      <c r="F2" s="213"/>
+      <c r="G2" s="212" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="205"/>
-      <c r="I2" s="206" t="s">
+      <c r="H2" s="212"/>
+      <c r="I2" s="213" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="206"/>
-      <c r="K2" s="205" t="s">
+      <c r="J2" s="213"/>
+      <c r="K2" s="212" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="205"/>
-      <c r="M2" s="210" t="s">
+      <c r="L2" s="212"/>
+      <c r="M2" s="205" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="210"/>
+      <c r="N2" s="205"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -19450,30 +19448,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="205" t="s">
+      <c r="C2" s="212" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="205"/>
-      <c r="E2" s="206" t="s">
+      <c r="D2" s="212"/>
+      <c r="E2" s="213" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="206"/>
-      <c r="G2" s="205" t="s">
+      <c r="F2" s="213"/>
+      <c r="G2" s="212" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="205"/>
-      <c r="I2" s="206" t="s">
+      <c r="H2" s="212"/>
+      <c r="I2" s="213" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="206"/>
-      <c r="K2" s="205" t="s">
+      <c r="J2" s="213"/>
+      <c r="K2" s="212" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="205"/>
-      <c r="M2" s="210" t="s">
+      <c r="L2" s="212"/>
+      <c r="M2" s="205" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="210"/>
+      <c r="N2" s="205"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -21276,30 +21274,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="205" t="s">
+      <c r="C2" s="212" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="205"/>
-      <c r="E2" s="206" t="s">
+      <c r="D2" s="212"/>
+      <c r="E2" s="213" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="206"/>
-      <c r="G2" s="205" t="s">
+      <c r="F2" s="213"/>
+      <c r="G2" s="212" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="205"/>
-      <c r="I2" s="206" t="s">
+      <c r="H2" s="212"/>
+      <c r="I2" s="213" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="206"/>
-      <c r="K2" s="205" t="s">
+      <c r="J2" s="213"/>
+      <c r="K2" s="212" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="205"/>
-      <c r="M2" s="210" t="s">
+      <c r="L2" s="212"/>
+      <c r="M2" s="205" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="210"/>
+      <c r="N2" s="205"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -23148,36 +23146,36 @@
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="207" t="s">
+      <c r="C2" s="202" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="208"/>
-      <c r="E2" s="209"/>
-      <c r="F2" s="212" t="s">
+      <c r="D2" s="203"/>
+      <c r="E2" s="204"/>
+      <c r="F2" s="207" t="s">
         <v>120</v>
       </c>
-      <c r="G2" s="213"/>
-      <c r="H2" s="214"/>
-      <c r="I2" s="207" t="s">
+      <c r="G2" s="208"/>
+      <c r="H2" s="209"/>
+      <c r="I2" s="202" t="s">
         <v>108</v>
       </c>
-      <c r="J2" s="208"/>
-      <c r="K2" s="209"/>
-      <c r="L2" s="212" t="s">
+      <c r="J2" s="203"/>
+      <c r="K2" s="204"/>
+      <c r="L2" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="M2" s="213"/>
-      <c r="N2" s="214"/>
-      <c r="O2" s="207" t="s">
+      <c r="M2" s="208"/>
+      <c r="N2" s="209"/>
+      <c r="O2" s="202" t="s">
         <v>39</v>
       </c>
-      <c r="P2" s="208"/>
-      <c r="Q2" s="209"/>
-      <c r="R2" s="210" t="s">
+      <c r="P2" s="203"/>
+      <c r="Q2" s="204"/>
+      <c r="R2" s="205" t="s">
         <v>7</v>
       </c>
-      <c r="S2" s="210"/>
-      <c r="T2" s="210"/>
+      <c r="S2" s="205"/>
+      <c r="T2" s="205"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -23250,7 +23248,7 @@
       </c>
       <c r="C4" s="6">
         <f>'Premier League'!C4</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" s="6">
         <f>'Premier League'!D4</f>
@@ -23310,7 +23308,7 @@
       </c>
       <c r="R4" s="2">
         <f>SUM(C4,F4,I4,L4,O4)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S4" s="2">
         <f t="shared" ref="S4:T4" si="0">SUM(D4,G4,J4,M4,P4)</f>
@@ -23492,7 +23490,7 @@
       </c>
       <c r="C7" s="6">
         <f>'Premier League'!C7</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7" s="6">
         <f>'Premier League'!D7</f>
@@ -23500,7 +23498,7 @@
       </c>
       <c r="E7" s="6">
         <f>'Premier League'!E7</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="4">
         <f>Europe!C7</f>
@@ -23552,7 +23550,7 @@
       </c>
       <c r="R7" s="2">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S7" s="2">
         <f t="shared" si="2"/>
@@ -23560,7 +23558,7 @@
       </c>
       <c r="T7" s="2">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V7" s="55"/>
     </row>
@@ -23573,7 +23571,7 @@
       </c>
       <c r="C8" s="6">
         <f>'Premier League'!C8</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" s="6">
         <f>'Premier League'!D8</f>
@@ -23633,7 +23631,7 @@
       </c>
       <c r="R8" s="2">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S8" s="2">
         <f t="shared" si="2"/>
@@ -23654,7 +23652,7 @@
       </c>
       <c r="C9" s="6">
         <f>'Premier League'!C9</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" s="6">
         <f>'Premier League'!D9</f>
@@ -23714,7 +23712,7 @@
       </c>
       <c r="R9" s="2">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S9" s="2">
         <f t="shared" si="2"/>
@@ -23735,7 +23733,7 @@
       </c>
       <c r="C10" s="6">
         <f>'Premier League'!C10</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10" s="6">
         <f>'Premier League'!D10</f>
@@ -23795,7 +23793,7 @@
       </c>
       <c r="R10" s="2">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S10" s="2">
         <f t="shared" si="2"/>
@@ -23816,7 +23814,7 @@
       </c>
       <c r="C11" s="6">
         <f>'Premier League'!C11</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D11" s="6">
         <f>'Premier League'!D11</f>
@@ -23876,7 +23874,7 @@
       </c>
       <c r="R11" s="2">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S11" s="2">
         <f t="shared" si="2"/>
@@ -23978,7 +23976,7 @@
       </c>
       <c r="C13" s="6">
         <f>'Premier League'!C13</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" s="6">
         <f>'Premier League'!D13</f>
@@ -24038,7 +24036,7 @@
       </c>
       <c r="R13" s="2">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S13" s="2">
         <f t="shared" si="2"/>
@@ -24140,7 +24138,7 @@
       </c>
       <c r="C15" s="6">
         <f>'Premier League'!C15</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" s="6">
         <f>'Premier League'!D15</f>
@@ -24200,7 +24198,7 @@
       </c>
       <c r="R15" s="2">
         <f>SUM(C15,F15,I15,L15,O15)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S15" s="2">
         <f>SUM(D15,G15,J15,M15,P15)</f>
@@ -24217,11 +24215,11 @@
         <v>15</v>
       </c>
       <c r="B16" s="149" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C16" s="6">
         <f>'Premier League'!C16</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" s="6">
         <f>'Premier League'!D16</f>
@@ -24281,7 +24279,7 @@
       </c>
       <c r="R16" s="2">
         <f t="shared" ref="R16:R28" si="4">SUM(C16,F16,I16,L16,O16)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S16" s="2">
         <f t="shared" ref="S16:S28" si="5">SUM(D16,G16,J16,M16,P16)</f>
@@ -24383,7 +24381,7 @@
       </c>
       <c r="C18" s="6">
         <f>'Premier League'!C18</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" s="6">
         <f>'Premier League'!D18</f>
@@ -24443,7 +24441,7 @@
       </c>
       <c r="R18" s="2">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S18" s="2">
         <f t="shared" si="5"/>
@@ -24543,7 +24541,7 @@
       </c>
       <c r="C20" s="6">
         <f>'Premier League'!C20</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D20" s="6">
         <f>'Premier League'!D20</f>
@@ -24603,7 +24601,7 @@
       </c>
       <c r="R20" s="2">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S20" s="2">
         <f t="shared" si="5"/>
@@ -24623,7 +24621,7 @@
       </c>
       <c r="C21" s="6">
         <f>'Premier League'!C21</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D21" s="6">
         <f>'Premier League'!D21</f>
@@ -24683,7 +24681,7 @@
       </c>
       <c r="R21" s="2">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S21" s="2">
         <f t="shared" si="5"/>
@@ -24785,11 +24783,11 @@
       </c>
       <c r="C23" s="6">
         <f>'Premier League'!C23</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D23" s="6">
         <f>'Premier League'!D23</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="6">
         <f>'Premier League'!E23</f>
@@ -24845,11 +24843,11 @@
       </c>
       <c r="R23" s="2">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S23" s="2">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T23" s="2">
         <f t="shared" si="6"/>
@@ -25028,11 +25026,11 @@
       </c>
       <c r="C26" s="6">
         <f>'Premier League'!C26</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D26" s="6">
         <f>'Premier League'!D26</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" s="6">
         <f>'Premier League'!E26</f>
@@ -25088,11 +25086,11 @@
       </c>
       <c r="R26" s="2">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S26" s="2">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T26" s="2">
         <f t="shared" si="6"/>
@@ -25189,7 +25187,7 @@
       </c>
       <c r="C28" s="6">
         <f>'Premier League'!C28</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D28" s="6">
         <f>'Premier League'!D28</f>
@@ -25197,7 +25195,7 @@
       </c>
       <c r="E28" s="6">
         <f>'Premier League'!E28</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F28" s="4">
         <f>Europe!C28</f>
@@ -25249,7 +25247,7 @@
       </c>
       <c r="R28" s="2">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S28" s="2">
         <f t="shared" si="5"/>
@@ -25257,7 +25255,7 @@
       </c>
       <c r="T28" s="2">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V28" s="55"/>
     </row>
@@ -25426,7 +25424,7 @@
         <v>45</v>
       </c>
       <c r="B31" s="148" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="C31" s="6">
         <f>'Premier League'!C31</f>
@@ -25591,7 +25589,7 @@
       </c>
       <c r="C33" s="6">
         <f>'Premier League'!C33</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D33" s="6">
         <f>'Premier League'!D33</f>
@@ -25651,7 +25649,7 @@
       </c>
       <c r="R33" s="2">
         <f t="shared" si="8"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S33" s="2">
         <f t="shared" si="9"/>
@@ -26116,36 +26114,36 @@
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
       <c r="D1" s="5"/>
-      <c r="E1" s="207" t="s">
+      <c r="E1" s="202" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="208"/>
-      <c r="G1" s="209"/>
-      <c r="H1" s="212" t="s">
+      <c r="F1" s="203"/>
+      <c r="G1" s="204"/>
+      <c r="H1" s="207" t="s">
         <v>120</v>
       </c>
-      <c r="I1" s="213"/>
-      <c r="J1" s="214"/>
-      <c r="K1" s="207" t="s">
+      <c r="I1" s="208"/>
+      <c r="J1" s="209"/>
+      <c r="K1" s="202" t="s">
         <v>108</v>
       </c>
-      <c r="L1" s="208"/>
-      <c r="M1" s="209"/>
-      <c r="N1" s="212" t="s">
+      <c r="L1" s="203"/>
+      <c r="M1" s="204"/>
+      <c r="N1" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="O1" s="213"/>
-      <c r="P1" s="214"/>
-      <c r="Q1" s="207" t="s">
+      <c r="O1" s="208"/>
+      <c r="P1" s="209"/>
+      <c r="Q1" s="202" t="s">
         <v>39</v>
       </c>
-      <c r="R1" s="208"/>
-      <c r="S1" s="209"/>
-      <c r="T1" s="210" t="s">
+      <c r="R1" s="203"/>
+      <c r="S1" s="204"/>
+      <c r="T1" s="205" t="s">
         <v>7</v>
       </c>
-      <c r="U1" s="210"/>
-      <c r="V1" s="210"/>
+      <c r="U1" s="205"/>
+      <c r="V1" s="205"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -37719,399 +37717,399 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F1" s="215">
-        <v>1</v>
-      </c>
-      <c r="G1" s="216"/>
-      <c r="H1" s="217"/>
-      <c r="I1" s="215">
+      <c r="F1" s="217">
+        <v>1</v>
+      </c>
+      <c r="G1" s="218"/>
+      <c r="H1" s="219"/>
+      <c r="I1" s="217">
         <v>2</v>
       </c>
-      <c r="J1" s="216"/>
-      <c r="K1" s="217"/>
-      <c r="L1" s="215">
-        <v>3</v>
-      </c>
-      <c r="M1" s="216"/>
-      <c r="N1" s="217"/>
-      <c r="O1" s="215">
+      <c r="J1" s="218"/>
+      <c r="K1" s="219"/>
+      <c r="L1" s="217">
+        <v>3</v>
+      </c>
+      <c r="M1" s="218"/>
+      <c r="N1" s="219"/>
+      <c r="O1" s="217">
         <v>4</v>
       </c>
-      <c r="P1" s="216"/>
-      <c r="Q1" s="217"/>
-      <c r="R1" s="215">
+      <c r="P1" s="218"/>
+      <c r="Q1" s="219"/>
+      <c r="R1" s="217">
         <v>5</v>
       </c>
-      <c r="S1" s="216"/>
-      <c r="T1" s="217"/>
-      <c r="U1" s="215">
+      <c r="S1" s="218"/>
+      <c r="T1" s="219"/>
+      <c r="U1" s="217">
         <v>6</v>
       </c>
-      <c r="V1" s="216"/>
-      <c r="W1" s="217"/>
-      <c r="X1" s="215">
+      <c r="V1" s="218"/>
+      <c r="W1" s="219"/>
+      <c r="X1" s="217">
         <v>7</v>
       </c>
-      <c r="Y1" s="216"/>
-      <c r="Z1" s="217"/>
-      <c r="AA1" s="215">
+      <c r="Y1" s="218"/>
+      <c r="Z1" s="219"/>
+      <c r="AA1" s="217">
         <v>8</v>
       </c>
-      <c r="AB1" s="216"/>
-      <c r="AC1" s="217"/>
-      <c r="AD1" s="215">
+      <c r="AB1" s="218"/>
+      <c r="AC1" s="219"/>
+      <c r="AD1" s="217">
         <v>9</v>
       </c>
-      <c r="AE1" s="216"/>
-      <c r="AF1" s="217"/>
-      <c r="AG1" s="215">
+      <c r="AE1" s="218"/>
+      <c r="AF1" s="219"/>
+      <c r="AG1" s="217">
         <v>10</v>
       </c>
-      <c r="AH1" s="216"/>
-      <c r="AI1" s="217"/>
-      <c r="AJ1" s="215">
+      <c r="AH1" s="218"/>
+      <c r="AI1" s="219"/>
+      <c r="AJ1" s="217">
         <v>11</v>
       </c>
-      <c r="AK1" s="216"/>
-      <c r="AL1" s="217"/>
-      <c r="AM1" s="215">
+      <c r="AK1" s="218"/>
+      <c r="AL1" s="219"/>
+      <c r="AM1" s="217">
         <v>12</v>
       </c>
-      <c r="AN1" s="216"/>
-      <c r="AO1" s="217"/>
-      <c r="AP1" s="215">
+      <c r="AN1" s="218"/>
+      <c r="AO1" s="219"/>
+      <c r="AP1" s="217">
         <v>13</v>
       </c>
-      <c r="AQ1" s="216"/>
-      <c r="AR1" s="217"/>
-      <c r="AS1" s="215">
+      <c r="AQ1" s="218"/>
+      <c r="AR1" s="219"/>
+      <c r="AS1" s="217">
         <v>14</v>
       </c>
-      <c r="AT1" s="216"/>
-      <c r="AU1" s="217"/>
-      <c r="AV1" s="215">
+      <c r="AT1" s="218"/>
+      <c r="AU1" s="219"/>
+      <c r="AV1" s="217">
         <v>15</v>
       </c>
-      <c r="AW1" s="216"/>
-      <c r="AX1" s="217"/>
-      <c r="AY1" s="215">
+      <c r="AW1" s="218"/>
+      <c r="AX1" s="219"/>
+      <c r="AY1" s="217">
         <v>16</v>
       </c>
-      <c r="AZ1" s="216"/>
-      <c r="BA1" s="217"/>
-      <c r="BB1" s="215">
+      <c r="AZ1" s="218"/>
+      <c r="BA1" s="219"/>
+      <c r="BB1" s="217">
         <v>17</v>
       </c>
-      <c r="BC1" s="216"/>
-      <c r="BD1" s="217"/>
-      <c r="BE1" s="215">
+      <c r="BC1" s="218"/>
+      <c r="BD1" s="219"/>
+      <c r="BE1" s="217">
         <v>18</v>
       </c>
-      <c r="BF1" s="216"/>
-      <c r="BG1" s="217"/>
-      <c r="BH1" s="215">
+      <c r="BF1" s="218"/>
+      <c r="BG1" s="219"/>
+      <c r="BH1" s="217">
         <v>19</v>
       </c>
-      <c r="BI1" s="216"/>
-      <c r="BJ1" s="217"/>
-      <c r="BK1" s="215">
+      <c r="BI1" s="218"/>
+      <c r="BJ1" s="219"/>
+      <c r="BK1" s="217">
         <v>20</v>
       </c>
-      <c r="BL1" s="216"/>
-      <c r="BM1" s="217"/>
-      <c r="BN1" s="215">
+      <c r="BL1" s="218"/>
+      <c r="BM1" s="219"/>
+      <c r="BN1" s="217">
         <v>21</v>
       </c>
-      <c r="BO1" s="216"/>
-      <c r="BP1" s="217"/>
-      <c r="BQ1" s="215">
+      <c r="BO1" s="218"/>
+      <c r="BP1" s="219"/>
+      <c r="BQ1" s="217">
         <v>22</v>
       </c>
-      <c r="BR1" s="216"/>
-      <c r="BS1" s="217"/>
-      <c r="BT1" s="215">
+      <c r="BR1" s="218"/>
+      <c r="BS1" s="219"/>
+      <c r="BT1" s="217">
         <v>23</v>
       </c>
-      <c r="BU1" s="216"/>
-      <c r="BV1" s="217"/>
-      <c r="BW1" s="215">
+      <c r="BU1" s="218"/>
+      <c r="BV1" s="219"/>
+      <c r="BW1" s="217">
         <v>24</v>
       </c>
-      <c r="BX1" s="216"/>
-      <c r="BY1" s="217"/>
-      <c r="BZ1" s="215">
+      <c r="BX1" s="218"/>
+      <c r="BY1" s="219"/>
+      <c r="BZ1" s="217">
         <v>25</v>
       </c>
-      <c r="CA1" s="216"/>
-      <c r="CB1" s="217"/>
-      <c r="CC1" s="215">
+      <c r="CA1" s="218"/>
+      <c r="CB1" s="219"/>
+      <c r="CC1" s="217">
         <v>26</v>
       </c>
-      <c r="CD1" s="216"/>
-      <c r="CE1" s="217"/>
-      <c r="CF1" s="215">
+      <c r="CD1" s="218"/>
+      <c r="CE1" s="219"/>
+      <c r="CF1" s="217">
         <v>27</v>
       </c>
-      <c r="CG1" s="216"/>
-      <c r="CH1" s="217"/>
-      <c r="CI1" s="215">
+      <c r="CG1" s="218"/>
+      <c r="CH1" s="219"/>
+      <c r="CI1" s="217">
         <v>28</v>
       </c>
-      <c r="CJ1" s="216"/>
-      <c r="CK1" s="217"/>
-      <c r="CL1" s="215">
+      <c r="CJ1" s="218"/>
+      <c r="CK1" s="219"/>
+      <c r="CL1" s="217">
         <v>29</v>
       </c>
-      <c r="CM1" s="216"/>
-      <c r="CN1" s="217"/>
-      <c r="CO1" s="215">
+      <c r="CM1" s="218"/>
+      <c r="CN1" s="219"/>
+      <c r="CO1" s="217">
         <v>30</v>
       </c>
-      <c r="CP1" s="216"/>
-      <c r="CQ1" s="217"/>
-      <c r="CR1" s="215">
+      <c r="CP1" s="218"/>
+      <c r="CQ1" s="219"/>
+      <c r="CR1" s="217">
         <v>31</v>
       </c>
-      <c r="CS1" s="216"/>
-      <c r="CT1" s="217"/>
-      <c r="CU1" s="215">
+      <c r="CS1" s="218"/>
+      <c r="CT1" s="219"/>
+      <c r="CU1" s="217">
         <v>32</v>
       </c>
-      <c r="CV1" s="216"/>
-      <c r="CW1" s="217"/>
-      <c r="CX1" s="215">
+      <c r="CV1" s="218"/>
+      <c r="CW1" s="219"/>
+      <c r="CX1" s="217">
         <v>33</v>
       </c>
-      <c r="CY1" s="216"/>
-      <c r="CZ1" s="217"/>
-      <c r="DA1" s="215">
+      <c r="CY1" s="218"/>
+      <c r="CZ1" s="219"/>
+      <c r="DA1" s="217">
         <v>34</v>
       </c>
-      <c r="DB1" s="216"/>
-      <c r="DC1" s="217"/>
-      <c r="DD1" s="215">
+      <c r="DB1" s="218"/>
+      <c r="DC1" s="219"/>
+      <c r="DD1" s="217">
         <v>35</v>
       </c>
-      <c r="DE1" s="216"/>
-      <c r="DF1" s="217"/>
-      <c r="DG1" s="215">
+      <c r="DE1" s="218"/>
+      <c r="DF1" s="219"/>
+      <c r="DG1" s="217">
         <v>36</v>
       </c>
-      <c r="DH1" s="216"/>
-      <c r="DI1" s="217"/>
-      <c r="DJ1" s="215">
+      <c r="DH1" s="218"/>
+      <c r="DI1" s="219"/>
+      <c r="DJ1" s="217">
         <v>37</v>
       </c>
-      <c r="DK1" s="216"/>
-      <c r="DL1" s="217"/>
-      <c r="DM1" s="215">
+      <c r="DK1" s="218"/>
+      <c r="DL1" s="219"/>
+      <c r="DM1" s="217">
         <v>38</v>
       </c>
-      <c r="DN1" s="216"/>
-      <c r="DO1" s="217"/>
+      <c r="DN1" s="218"/>
+      <c r="DO1" s="219"/>
     </row>
     <row r="2" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="221" t="s">
+      <c r="C2" s="220" t="s">
         <v>396</v>
       </c>
-      <c r="D2" s="221" t="s">
+      <c r="D2" s="220" t="s">
         <v>397</v>
       </c>
-      <c r="E2" s="221" t="s">
+      <c r="E2" s="220" t="s">
         <v>398</v>
       </c>
-      <c r="F2" s="218" t="s">
+      <c r="F2" s="214" t="s">
         <v>346</v>
       </c>
-      <c r="G2" s="219"/>
-      <c r="H2" s="220"/>
-      <c r="I2" s="218" t="s">
+      <c r="G2" s="215"/>
+      <c r="H2" s="216"/>
+      <c r="I2" s="214" t="s">
         <v>331</v>
       </c>
-      <c r="J2" s="219"/>
-      <c r="K2" s="220"/>
-      <c r="L2" s="218" t="s">
+      <c r="J2" s="215"/>
+      <c r="K2" s="216"/>
+      <c r="L2" s="214" t="s">
         <v>330</v>
       </c>
-      <c r="M2" s="219"/>
-      <c r="N2" s="220"/>
-      <c r="O2" s="218" t="s">
+      <c r="M2" s="215"/>
+      <c r="N2" s="216"/>
+      <c r="O2" s="214" t="s">
         <v>328</v>
       </c>
-      <c r="P2" s="219"/>
-      <c r="Q2" s="220"/>
-      <c r="R2" s="218" t="s">
+      <c r="P2" s="215"/>
+      <c r="Q2" s="216"/>
+      <c r="R2" s="214" t="s">
         <v>335</v>
       </c>
-      <c r="S2" s="219"/>
-      <c r="T2" s="220"/>
-      <c r="U2" s="218" t="s">
+      <c r="S2" s="215"/>
+      <c r="T2" s="216"/>
+      <c r="U2" s="214" t="s">
         <v>320</v>
       </c>
-      <c r="V2" s="219"/>
-      <c r="W2" s="220"/>
-      <c r="X2" s="218" t="s">
+      <c r="V2" s="215"/>
+      <c r="W2" s="216"/>
+      <c r="X2" s="214" t="s">
         <v>337</v>
       </c>
-      <c r="Y2" s="219"/>
-      <c r="Z2" s="220"/>
-      <c r="AA2" s="218" t="s">
+      <c r="Y2" s="215"/>
+      <c r="Z2" s="216"/>
+      <c r="AA2" s="214" t="s">
         <v>334</v>
       </c>
-      <c r="AB2" s="219"/>
-      <c r="AC2" s="220"/>
-      <c r="AD2" s="218" t="s">
+      <c r="AB2" s="215"/>
+      <c r="AC2" s="216"/>
+      <c r="AD2" s="214" t="s">
         <v>321</v>
       </c>
-      <c r="AE2" s="219"/>
-      <c r="AF2" s="220"/>
-      <c r="AG2" s="218" t="s">
+      <c r="AE2" s="215"/>
+      <c r="AF2" s="216"/>
+      <c r="AG2" s="214" t="s">
         <v>347</v>
       </c>
-      <c r="AH2" s="219"/>
-      <c r="AI2" s="220"/>
-      <c r="AJ2" s="218" t="s">
+      <c r="AH2" s="215"/>
+      <c r="AI2" s="216"/>
+      <c r="AJ2" s="214" t="s">
         <v>324</v>
       </c>
-      <c r="AK2" s="219"/>
-      <c r="AL2" s="220"/>
-      <c r="AM2" s="218" t="s">
+      <c r="AK2" s="215"/>
+      <c r="AL2" s="216"/>
+      <c r="AM2" s="214" t="s">
         <v>323</v>
       </c>
-      <c r="AN2" s="219"/>
-      <c r="AO2" s="220"/>
-      <c r="AP2" s="218" t="s">
+      <c r="AN2" s="215"/>
+      <c r="AO2" s="216"/>
+      <c r="AP2" s="214" t="s">
         <v>332</v>
       </c>
-      <c r="AQ2" s="219"/>
-      <c r="AR2" s="220"/>
-      <c r="AS2" s="218" t="s">
+      <c r="AQ2" s="215"/>
+      <c r="AR2" s="216"/>
+      <c r="AS2" s="214" t="s">
         <v>329</v>
       </c>
-      <c r="AT2" s="219"/>
-      <c r="AU2" s="220"/>
-      <c r="AV2" s="218" t="s">
+      <c r="AT2" s="215"/>
+      <c r="AU2" s="216"/>
+      <c r="AV2" s="214" t="s">
         <v>336</v>
       </c>
-      <c r="AW2" s="219"/>
-      <c r="AX2" s="220"/>
-      <c r="AY2" s="218" t="s">
+      <c r="AW2" s="215"/>
+      <c r="AX2" s="216"/>
+      <c r="AY2" s="214" t="s">
         <v>305</v>
       </c>
-      <c r="AZ2" s="219"/>
-      <c r="BA2" s="220"/>
-      <c r="BB2" s="218" t="s">
+      <c r="AZ2" s="215"/>
+      <c r="BA2" s="216"/>
+      <c r="BB2" s="214" t="s">
         <v>326</v>
       </c>
-      <c r="BC2" s="219"/>
-      <c r="BD2" s="220"/>
-      <c r="BE2" s="218" t="s">
+      <c r="BC2" s="215"/>
+      <c r="BD2" s="216"/>
+      <c r="BE2" s="214" t="s">
         <v>325</v>
       </c>
-      <c r="BF2" s="219"/>
-      <c r="BG2" s="220"/>
-      <c r="BH2" s="218" t="s">
+      <c r="BF2" s="215"/>
+      <c r="BG2" s="216"/>
+      <c r="BH2" s="214" t="s">
         <v>348</v>
       </c>
-      <c r="BI2" s="219"/>
-      <c r="BJ2" s="220"/>
-      <c r="BK2" s="218" t="s">
+      <c r="BI2" s="215"/>
+      <c r="BJ2" s="216"/>
+      <c r="BK2" s="214" t="s">
         <v>332</v>
       </c>
-      <c r="BL2" s="219"/>
-      <c r="BM2" s="220"/>
-      <c r="BN2" s="218" t="s">
+      <c r="BL2" s="215"/>
+      <c r="BM2" s="216"/>
+      <c r="BN2" s="214" t="s">
         <v>347</v>
       </c>
-      <c r="BO2" s="219"/>
-      <c r="BP2" s="220"/>
-      <c r="BQ2" s="218" t="s">
+      <c r="BO2" s="215"/>
+      <c r="BP2" s="216"/>
+      <c r="BQ2" s="214" t="s">
         <v>324</v>
       </c>
-      <c r="BR2" s="219"/>
-      <c r="BS2" s="220"/>
-      <c r="BT2" s="218" t="s">
+      <c r="BR2" s="215"/>
+      <c r="BS2" s="216"/>
+      <c r="BT2" s="214" t="s">
         <v>323</v>
       </c>
-      <c r="BU2" s="219"/>
-      <c r="BV2" s="220"/>
-      <c r="BW2" s="218" t="s">
+      <c r="BU2" s="215"/>
+      <c r="BV2" s="216"/>
+      <c r="BW2" s="214" t="s">
         <v>321</v>
       </c>
-      <c r="BX2" s="219"/>
-      <c r="BY2" s="220"/>
-      <c r="BZ2" s="218" t="s">
+      <c r="BX2" s="215"/>
+      <c r="BY2" s="216"/>
+      <c r="BZ2" s="214" t="s">
         <v>348</v>
       </c>
-      <c r="CA2" s="219"/>
-      <c r="CB2" s="220"/>
-      <c r="CC2" s="218" t="s">
+      <c r="CA2" s="215"/>
+      <c r="CB2" s="216"/>
+      <c r="CC2" s="214" t="s">
         <v>325</v>
       </c>
-      <c r="CD2" s="219"/>
-      <c r="CE2" s="220"/>
-      <c r="CF2" s="218" t="s">
+      <c r="CD2" s="215"/>
+      <c r="CE2" s="216"/>
+      <c r="CF2" s="214" t="s">
         <v>305</v>
       </c>
-      <c r="CG2" s="219"/>
-      <c r="CH2" s="220"/>
-      <c r="CI2" s="218" t="s">
+      <c r="CG2" s="215"/>
+      <c r="CH2" s="216"/>
+      <c r="CI2" s="214" t="s">
         <v>326</v>
       </c>
-      <c r="CJ2" s="219"/>
-      <c r="CK2" s="220"/>
-      <c r="CL2" s="218" t="s">
+      <c r="CJ2" s="215"/>
+      <c r="CK2" s="216"/>
+      <c r="CL2" s="214" t="s">
         <v>330</v>
       </c>
-      <c r="CM2" s="219"/>
-      <c r="CN2" s="220"/>
-      <c r="CO2" s="218" t="s">
+      <c r="CM2" s="215"/>
+      <c r="CN2" s="216"/>
+      <c r="CO2" s="214" t="s">
         <v>328</v>
       </c>
-      <c r="CP2" s="219"/>
-      <c r="CQ2" s="220"/>
-      <c r="CR2" s="218" t="s">
+      <c r="CP2" s="215"/>
+      <c r="CQ2" s="216"/>
+      <c r="CR2" s="214" t="s">
         <v>346</v>
       </c>
-      <c r="CS2" s="219"/>
-      <c r="CT2" s="220"/>
-      <c r="CU2" s="218" t="s">
+      <c r="CS2" s="215"/>
+      <c r="CT2" s="216"/>
+      <c r="CU2" s="214" t="s">
         <v>331</v>
       </c>
-      <c r="CV2" s="219"/>
-      <c r="CW2" s="220"/>
-      <c r="CX2" s="218" t="s">
+      <c r="CV2" s="215"/>
+      <c r="CW2" s="216"/>
+      <c r="CX2" s="214" t="s">
         <v>336</v>
       </c>
-      <c r="CY2" s="219"/>
-      <c r="CZ2" s="220"/>
-      <c r="DA2" s="218" t="s">
+      <c r="CY2" s="215"/>
+      <c r="CZ2" s="216"/>
+      <c r="DA2" s="214" t="s">
         <v>329</v>
       </c>
-      <c r="DB2" s="219"/>
-      <c r="DC2" s="220"/>
-      <c r="DD2" s="218" t="s">
+      <c r="DB2" s="215"/>
+      <c r="DC2" s="216"/>
+      <c r="DD2" s="214" t="s">
         <v>320</v>
       </c>
-      <c r="DE2" s="219"/>
-      <c r="DF2" s="220"/>
-      <c r="DG2" s="218" t="s">
+      <c r="DE2" s="215"/>
+      <c r="DF2" s="216"/>
+      <c r="DG2" s="214" t="s">
         <v>337</v>
       </c>
-      <c r="DH2" s="219"/>
-      <c r="DI2" s="220"/>
-      <c r="DJ2" s="218" t="s">
+      <c r="DH2" s="215"/>
+      <c r="DI2" s="216"/>
+      <c r="DJ2" s="214" t="s">
         <v>334</v>
       </c>
-      <c r="DK2" s="219"/>
-      <c r="DL2" s="220"/>
-      <c r="DM2" s="218" t="s">
+      <c r="DK2" s="215"/>
+      <c r="DL2" s="216"/>
+      <c r="DM2" s="214" t="s">
         <v>335</v>
       </c>
-      <c r="DN2" s="219"/>
-      <c r="DO2" s="220"/>
+      <c r="DN2" s="215"/>
+      <c r="DO2" s="216"/>
     </row>
     <row r="3" spans="1:119" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -38120,8 +38118,8 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="223"/>
-      <c r="D3" s="223"/>
+      <c r="C3" s="221"/>
+      <c r="D3" s="221"/>
       <c r="E3" s="222"/>
       <c r="F3" s="160" t="s">
         <v>393</v>
@@ -38475,7 +38473,7 @@
       </c>
       <c r="C4" s="58">
         <f>SUM(F4,I4,L4,O4,R4,U4,X4,AA4,AD4,AG4,AJ4,AM4,AP4,AS4,AV4,AY4,BB4,BE4,BH4,BK4,BN4,BQ4,BT4,BW4,BZ4,CC4,CF4,CI4,CL4,CO4,CR4,CU4,CX4,DA4,DD4,DG4,DJ4,DM4)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" s="58">
         <f t="shared" ref="D4:E4" si="0">SUM(G4,J4,M4,P4,S4,V4,Y4,AB4,AE4,AH4,AK4,AN4,AQ4,AT4,AW4,AZ4,BC4,BF4,BI4,BL4,BO4,BR4,BU4,BX4,CA4,CD4,CG4,CJ4,CM4,CP4,CS4,CV4,CY4,DB4,DE4,DH4,DK4,DN4)</f>
@@ -38510,7 +38508,9 @@
       </c>
       <c r="S4" s="36"/>
       <c r="T4" s="53"/>
-      <c r="U4" s="52"/>
+      <c r="U4" s="52">
+        <v>1</v>
+      </c>
       <c r="V4" s="36"/>
       <c r="W4" s="53"/>
       <c r="X4" s="52"/>
@@ -38891,7 +38891,7 @@
       </c>
       <c r="C7" s="58">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7" s="58">
         <f t="shared" si="2"/>
@@ -38899,7 +38899,7 @@
       </c>
       <c r="E7" s="51">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="52">
         <v>1</v>
@@ -38926,9 +38926,13 @@
       <c r="R7" s="52"/>
       <c r="S7" s="36"/>
       <c r="T7" s="53"/>
-      <c r="U7" s="52"/>
+      <c r="U7" s="52">
+        <v>1</v>
+      </c>
       <c r="V7" s="36"/>
-      <c r="W7" s="53"/>
+      <c r="W7" s="53">
+        <v>1</v>
+      </c>
       <c r="X7" s="52"/>
       <c r="Y7" s="36"/>
       <c r="Z7" s="53"/>
@@ -39035,7 +39039,7 @@
       </c>
       <c r="C8" s="58">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" s="58">
         <f t="shared" si="2"/>
@@ -39064,7 +39068,9 @@
       <c r="R8" s="52"/>
       <c r="S8" s="36"/>
       <c r="T8" s="53"/>
-      <c r="U8" s="52"/>
+      <c r="U8" s="52">
+        <v>1</v>
+      </c>
       <c r="V8" s="36"/>
       <c r="W8" s="53"/>
       <c r="X8" s="52"/>
@@ -39173,7 +39179,7 @@
       </c>
       <c r="C9" s="58">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" s="58">
         <f t="shared" si="2"/>
@@ -39208,7 +39214,9 @@
       </c>
       <c r="S9" s="36"/>
       <c r="T9" s="53"/>
-      <c r="U9" s="52"/>
+      <c r="U9" s="52">
+        <v>1</v>
+      </c>
       <c r="V9" s="36"/>
       <c r="W9" s="53"/>
       <c r="X9" s="52"/>
@@ -39317,7 +39325,7 @@
       </c>
       <c r="C10" s="58">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10" s="58">
         <f t="shared" si="2"/>
@@ -39358,7 +39366,9 @@
       </c>
       <c r="S10" s="36"/>
       <c r="T10" s="53"/>
-      <c r="U10" s="52"/>
+      <c r="U10" s="52">
+        <v>1</v>
+      </c>
       <c r="V10" s="36"/>
       <c r="W10" s="53"/>
       <c r="X10" s="52"/>
@@ -39467,7 +39477,7 @@
       </c>
       <c r="C11" s="58">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D11" s="58">
         <f t="shared" si="2"/>
@@ -39506,7 +39516,9 @@
       </c>
       <c r="S11" s="36"/>
       <c r="T11" s="53"/>
-      <c r="U11" s="52"/>
+      <c r="U11" s="52">
+        <v>1</v>
+      </c>
       <c r="V11" s="36"/>
       <c r="W11" s="53"/>
       <c r="X11" s="52"/>
@@ -39757,7 +39769,7 @@
       </c>
       <c r="C13" s="58">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" s="58">
         <f t="shared" si="2"/>
@@ -39786,7 +39798,9 @@
       </c>
       <c r="S13" s="36"/>
       <c r="T13" s="53"/>
-      <c r="U13" s="52"/>
+      <c r="U13" s="52">
+        <v>1</v>
+      </c>
       <c r="V13" s="36"/>
       <c r="W13" s="53"/>
       <c r="X13" s="52"/>
@@ -40029,7 +40043,7 @@
       </c>
       <c r="C15" s="58">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" s="58">
         <f t="shared" si="2"/>
@@ -40058,7 +40072,9 @@
       </c>
       <c r="S15" s="36"/>
       <c r="T15" s="53"/>
-      <c r="U15" s="52"/>
+      <c r="U15" s="52">
+        <v>1</v>
+      </c>
       <c r="V15" s="36"/>
       <c r="W15" s="53"/>
       <c r="X15" s="52"/>
@@ -40163,11 +40179,11 @@
         <v>15</v>
       </c>
       <c r="B16" s="149" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C16" s="58">
         <f t="shared" ref="C16:C28" si="4">SUM(F16,I16,L16,O16,R16,U16,X16,AA16,AD16,AG16,AJ16,AM16,AP16,AS16,AV16,AY16,BB16,BE16,BH16,BK16,BN16,BQ16,BT16,BW16,BZ16,CC16,CF16,CI16,CL16,CO16,CR16,CU16,CX16,DA16,DD16,DG16,DJ16,DM16)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" s="58">
         <f t="shared" ref="D16:D28" si="5">SUM(G16,J16,M16,P16,S16,V16,Y16,AB16,AE16,AH16,AK16,AN16,AQ16,AT16,AW16,AZ16,BC16,BF16,BI16,BL16,BO16,BR16,BU16,BX16,CA16,CD16,CG16,CJ16,CM16,CP16,CS16,CV16,CY16,DB16,DE16,DH16,DK16,DN16)</f>
@@ -40200,7 +40216,9 @@
       </c>
       <c r="S16" s="36"/>
       <c r="T16" s="53"/>
-      <c r="U16" s="52"/>
+      <c r="U16" s="52">
+        <v>1</v>
+      </c>
       <c r="V16" s="36"/>
       <c r="W16" s="53"/>
       <c r="X16" s="52"/>
@@ -40455,7 +40473,7 @@
       </c>
       <c r="C18" s="58">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" s="58">
         <f t="shared" si="5"/>
@@ -40484,7 +40502,9 @@
       <c r="R18" s="52"/>
       <c r="S18" s="36"/>
       <c r="T18" s="53"/>
-      <c r="U18" s="52"/>
+      <c r="U18" s="52">
+        <v>1</v>
+      </c>
       <c r="V18" s="36"/>
       <c r="W18" s="53"/>
       <c r="X18" s="52"/>
@@ -40727,7 +40747,7 @@
       </c>
       <c r="C20" s="58">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D20" s="58">
         <f t="shared" si="5"/>
@@ -40762,7 +40782,9 @@
       </c>
       <c r="S20" s="36"/>
       <c r="T20" s="53"/>
-      <c r="U20" s="52"/>
+      <c r="U20" s="52">
+        <v>1</v>
+      </c>
       <c r="V20" s="36"/>
       <c r="W20" s="53"/>
       <c r="X20" s="52"/>
@@ -40871,7 +40893,7 @@
       </c>
       <c r="C21" s="58">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D21" s="58">
         <f t="shared" si="5"/>
@@ -40910,7 +40932,9 @@
       </c>
       <c r="S21" s="36"/>
       <c r="T21" s="53"/>
-      <c r="U21" s="52"/>
+      <c r="U21" s="52">
+        <v>1</v>
+      </c>
       <c r="V21" s="36"/>
       <c r="W21" s="53"/>
       <c r="X21" s="52"/>
@@ -41153,11 +41177,11 @@
       </c>
       <c r="C23" s="58">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D23" s="58">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="51">
         <f t="shared" si="6"/>
@@ -41192,8 +41216,12 @@
       </c>
       <c r="S23" s="36"/>
       <c r="T23" s="53"/>
-      <c r="U23" s="52"/>
-      <c r="V23" s="36"/>
+      <c r="U23" s="52">
+        <v>1</v>
+      </c>
+      <c r="V23" s="36">
+        <v>1</v>
+      </c>
       <c r="W23" s="53"/>
       <c r="X23" s="52"/>
       <c r="Y23" s="36"/>
@@ -41579,11 +41607,11 @@
       </c>
       <c r="C26" s="58">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D26" s="58">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" s="51">
         <f t="shared" si="6"/>
@@ -41612,8 +41640,12 @@
       </c>
       <c r="S26" s="36"/>
       <c r="T26" s="53"/>
-      <c r="U26" s="52"/>
-      <c r="V26" s="36"/>
+      <c r="U26" s="52">
+        <v>1</v>
+      </c>
+      <c r="V26" s="36">
+        <v>1</v>
+      </c>
       <c r="W26" s="53"/>
       <c r="X26" s="52"/>
       <c r="Y26" s="36"/>
@@ -41855,7 +41887,7 @@
       </c>
       <c r="C28" s="58">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D28" s="58">
         <f t="shared" si="5"/>
@@ -41863,7 +41895,7 @@
       </c>
       <c r="E28" s="51">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F28" s="52">
         <v>1</v>
@@ -41894,9 +41926,13 @@
       </c>
       <c r="S28" s="36"/>
       <c r="T28" s="53"/>
-      <c r="U28" s="52"/>
+      <c r="U28" s="52">
+        <v>1</v>
+      </c>
       <c r="V28" s="36"/>
-      <c r="W28" s="53"/>
+      <c r="W28" s="53">
+        <v>1</v>
+      </c>
       <c r="X28" s="52"/>
       <c r="Y28" s="36"/>
       <c r="Z28" s="53"/>
@@ -42267,7 +42303,7 @@
         <v>45</v>
       </c>
       <c r="B31" s="148" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="C31" s="58">
         <f t="shared" ref="C31:C38" si="8">SUM(F31,I31,L31,O31,R31,U31,X31,AA31,AD31,AG31,AJ31,AM31,AP31,AS31,AV31,AY31,BB31,BE31,BH31,BK31,BN31,BQ31,BT31,BW31,BZ31,CC31,CF31,CI31,CL31,CO31,CR31,CU31,CX31,DA31,DD31,DG31,DJ31,DM31)</f>
@@ -42539,7 +42575,7 @@
       </c>
       <c r="C33" s="58">
         <f t="shared" si="8"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D33" s="58">
         <f t="shared" si="9"/>
@@ -42572,7 +42608,9 @@
       <c r="R33" s="52"/>
       <c r="S33" s="36"/>
       <c r="T33" s="53"/>
-      <c r="U33" s="52"/>
+      <c r="U33" s="52">
+        <v>1</v>
+      </c>
       <c r="V33" s="36"/>
       <c r="W33" s="53"/>
       <c r="X33" s="52"/>
@@ -43412,15 +43450,15 @@
       </c>
       <c r="U39" s="73">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="V39" s="73">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W39" s="73">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X39" s="73">
         <f t="shared" si="11"/>
@@ -43809,6 +43847,69 @@
     </row>
   </sheetData>
   <mergeCells count="79">
+    <mergeCell ref="DM1:DO1"/>
+    <mergeCell ref="DM2:DO2"/>
+    <mergeCell ref="DA1:DC1"/>
+    <mergeCell ref="DA2:DC2"/>
+    <mergeCell ref="DD1:DF1"/>
+    <mergeCell ref="DD2:DF2"/>
+    <mergeCell ref="DG1:DI1"/>
+    <mergeCell ref="DG2:DI2"/>
+    <mergeCell ref="CU1:CW1"/>
+    <mergeCell ref="CU2:CW2"/>
+    <mergeCell ref="CX1:CZ1"/>
+    <mergeCell ref="CX2:CZ2"/>
+    <mergeCell ref="DJ1:DL1"/>
+    <mergeCell ref="DJ2:DL2"/>
+    <mergeCell ref="CL1:CN1"/>
+    <mergeCell ref="CL2:CN2"/>
+    <mergeCell ref="CO1:CQ1"/>
+    <mergeCell ref="CO2:CQ2"/>
+    <mergeCell ref="CR1:CT1"/>
+    <mergeCell ref="CR2:CT2"/>
+    <mergeCell ref="CC1:CE1"/>
+    <mergeCell ref="CC2:CE2"/>
+    <mergeCell ref="CF1:CH1"/>
+    <mergeCell ref="CF2:CH2"/>
+    <mergeCell ref="CI1:CK1"/>
+    <mergeCell ref="CI2:CK2"/>
+    <mergeCell ref="BT1:BV1"/>
+    <mergeCell ref="BT2:BV2"/>
+    <mergeCell ref="BW1:BY1"/>
+    <mergeCell ref="BW2:BY2"/>
+    <mergeCell ref="BZ1:CB1"/>
+    <mergeCell ref="BZ2:CB2"/>
+    <mergeCell ref="BK1:BM1"/>
+    <mergeCell ref="BK2:BM2"/>
+    <mergeCell ref="BN1:BP1"/>
+    <mergeCell ref="BN2:BP2"/>
+    <mergeCell ref="BQ1:BS1"/>
+    <mergeCell ref="BQ2:BS2"/>
+    <mergeCell ref="AS1:AU1"/>
+    <mergeCell ref="AS2:AU2"/>
+    <mergeCell ref="AV1:AX1"/>
+    <mergeCell ref="AV2:AX2"/>
+    <mergeCell ref="BH1:BJ1"/>
+    <mergeCell ref="BH2:BJ2"/>
+    <mergeCell ref="AY2:BA2"/>
+    <mergeCell ref="BB2:BD2"/>
+    <mergeCell ref="BE2:BG2"/>
+    <mergeCell ref="AJ1:AL1"/>
+    <mergeCell ref="AJ2:AL2"/>
+    <mergeCell ref="AM1:AO1"/>
+    <mergeCell ref="AM2:AO2"/>
+    <mergeCell ref="AP2:AR2"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
     <mergeCell ref="AD2:AF2"/>
     <mergeCell ref="AG2:AI2"/>
     <mergeCell ref="BB1:BD1"/>
@@ -43825,69 +43926,6 @@
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="X1:Z1"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="AJ1:AL1"/>
-    <mergeCell ref="AJ2:AL2"/>
-    <mergeCell ref="AM1:AO1"/>
-    <mergeCell ref="AM2:AO2"/>
-    <mergeCell ref="AP2:AR2"/>
-    <mergeCell ref="AS1:AU1"/>
-    <mergeCell ref="AS2:AU2"/>
-    <mergeCell ref="AV1:AX1"/>
-    <mergeCell ref="AV2:AX2"/>
-    <mergeCell ref="BH1:BJ1"/>
-    <mergeCell ref="BH2:BJ2"/>
-    <mergeCell ref="AY2:BA2"/>
-    <mergeCell ref="BB2:BD2"/>
-    <mergeCell ref="BE2:BG2"/>
-    <mergeCell ref="BK1:BM1"/>
-    <mergeCell ref="BK2:BM2"/>
-    <mergeCell ref="BN1:BP1"/>
-    <mergeCell ref="BN2:BP2"/>
-    <mergeCell ref="BQ1:BS1"/>
-    <mergeCell ref="BQ2:BS2"/>
-    <mergeCell ref="BT1:BV1"/>
-    <mergeCell ref="BT2:BV2"/>
-    <mergeCell ref="BW1:BY1"/>
-    <mergeCell ref="BW2:BY2"/>
-    <mergeCell ref="BZ1:CB1"/>
-    <mergeCell ref="BZ2:CB2"/>
-    <mergeCell ref="CC1:CE1"/>
-    <mergeCell ref="CC2:CE2"/>
-    <mergeCell ref="CF1:CH1"/>
-    <mergeCell ref="CF2:CH2"/>
-    <mergeCell ref="CI1:CK1"/>
-    <mergeCell ref="CI2:CK2"/>
-    <mergeCell ref="CL1:CN1"/>
-    <mergeCell ref="CL2:CN2"/>
-    <mergeCell ref="CO1:CQ1"/>
-    <mergeCell ref="CO2:CQ2"/>
-    <mergeCell ref="CR1:CT1"/>
-    <mergeCell ref="CR2:CT2"/>
-    <mergeCell ref="CU1:CW1"/>
-    <mergeCell ref="CU2:CW2"/>
-    <mergeCell ref="CX1:CZ1"/>
-    <mergeCell ref="CX2:CZ2"/>
-    <mergeCell ref="DJ1:DL1"/>
-    <mergeCell ref="DJ2:DL2"/>
-    <mergeCell ref="DM1:DO1"/>
-    <mergeCell ref="DM2:DO2"/>
-    <mergeCell ref="DA1:DC1"/>
-    <mergeCell ref="DA2:DC2"/>
-    <mergeCell ref="DD1:DF1"/>
-    <mergeCell ref="DD2:DF2"/>
-    <mergeCell ref="DG1:DI1"/>
-    <mergeCell ref="DG2:DI2"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:DO38">
     <cfRule type="cellIs" dxfId="18" priority="1" operator="between">
@@ -43923,138 +43961,138 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="233" t="s">
+      <c r="C1" s="235" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="233" t="s">
+      <c r="D1" s="235" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="233" t="s">
+      <c r="E1" s="235" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="224" t="s">
+      <c r="F1" s="226" t="s">
         <v>302</v>
       </c>
-      <c r="G1" s="225"/>
-      <c r="H1" s="225"/>
-      <c r="I1" s="225"/>
-      <c r="J1" s="225"/>
-      <c r="K1" s="225"/>
-      <c r="L1" s="225"/>
-      <c r="M1" s="225"/>
-      <c r="N1" s="225"/>
-      <c r="O1" s="225"/>
-      <c r="P1" s="225"/>
-      <c r="Q1" s="225"/>
-      <c r="R1" s="225"/>
-      <c r="S1" s="225"/>
-      <c r="T1" s="225"/>
-      <c r="U1" s="225"/>
-      <c r="V1" s="225"/>
-      <c r="W1" s="225"/>
-      <c r="X1" s="225"/>
-      <c r="Y1" s="225"/>
-      <c r="Z1" s="225"/>
-      <c r="AA1" s="225"/>
-      <c r="AB1" s="225"/>
-      <c r="AC1" s="226"/>
-      <c r="AD1" s="239" t="s">
+      <c r="G1" s="227"/>
+      <c r="H1" s="227"/>
+      <c r="I1" s="227"/>
+      <c r="J1" s="227"/>
+      <c r="K1" s="227"/>
+      <c r="L1" s="227"/>
+      <c r="M1" s="227"/>
+      <c r="N1" s="227"/>
+      <c r="O1" s="227"/>
+      <c r="P1" s="227"/>
+      <c r="Q1" s="227"/>
+      <c r="R1" s="227"/>
+      <c r="S1" s="227"/>
+      <c r="T1" s="227"/>
+      <c r="U1" s="227"/>
+      <c r="V1" s="227"/>
+      <c r="W1" s="227"/>
+      <c r="X1" s="227"/>
+      <c r="Y1" s="227"/>
+      <c r="Z1" s="227"/>
+      <c r="AA1" s="227"/>
+      <c r="AB1" s="227"/>
+      <c r="AC1" s="228"/>
+      <c r="AD1" s="238" t="s">
         <v>281</v>
       </c>
-      <c r="AE1" s="240"/>
-      <c r="AF1" s="240"/>
-      <c r="AG1" s="240"/>
-      <c r="AH1" s="240"/>
-      <c r="AI1" s="241"/>
-      <c r="AJ1" s="224" t="s">
+      <c r="AE1" s="239"/>
+      <c r="AF1" s="239"/>
+      <c r="AG1" s="239"/>
+      <c r="AH1" s="239"/>
+      <c r="AI1" s="240"/>
+      <c r="AJ1" s="226" t="s">
         <v>282</v>
       </c>
-      <c r="AK1" s="225"/>
-      <c r="AL1" s="225"/>
-      <c r="AM1" s="225"/>
-      <c r="AN1" s="225"/>
-      <c r="AO1" s="226"/>
-      <c r="AP1" s="227" t="s">
+      <c r="AK1" s="227"/>
+      <c r="AL1" s="227"/>
+      <c r="AM1" s="227"/>
+      <c r="AN1" s="227"/>
+      <c r="AO1" s="228"/>
+      <c r="AP1" s="229" t="s">
         <v>283</v>
       </c>
-      <c r="AQ1" s="228"/>
-      <c r="AR1" s="228"/>
-      <c r="AS1" s="228"/>
-      <c r="AT1" s="228"/>
-      <c r="AU1" s="229"/>
-      <c r="AV1" s="230" t="s">
+      <c r="AQ1" s="230"/>
+      <c r="AR1" s="230"/>
+      <c r="AS1" s="230"/>
+      <c r="AT1" s="230"/>
+      <c r="AU1" s="231"/>
+      <c r="AV1" s="232" t="s">
         <v>86</v>
       </c>
-      <c r="AW1" s="231"/>
-      <c r="AX1" s="232"/>
+      <c r="AW1" s="233"/>
+      <c r="AX1" s="234"/>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="234"/>
-      <c r="D2" s="234"/>
-      <c r="E2" s="234"/>
-      <c r="F2" s="236" t="s">
+      <c r="C2" s="236"/>
+      <c r="D2" s="236"/>
+      <c r="E2" s="236"/>
+      <c r="F2" s="223" t="s">
+        <v>458</v>
+      </c>
+      <c r="G2" s="224"/>
+      <c r="H2" s="225"/>
+      <c r="I2" s="223" t="s">
         <v>461</v>
       </c>
-      <c r="G2" s="237"/>
-      <c r="H2" s="238"/>
-      <c r="I2" s="236" t="s">
+      <c r="J2" s="224"/>
+      <c r="K2" s="225"/>
+      <c r="L2" s="223" t="s">
+        <v>462</v>
+      </c>
+      <c r="M2" s="224"/>
+      <c r="N2" s="225"/>
+      <c r="O2" s="223" t="s">
+        <v>463</v>
+      </c>
+      <c r="P2" s="224"/>
+      <c r="Q2" s="225"/>
+      <c r="R2" s="223" t="s">
+        <v>464</v>
+      </c>
+      <c r="S2" s="224"/>
+      <c r="T2" s="225"/>
+      <c r="U2" s="223" t="s">
+        <v>465</v>
+      </c>
+      <c r="V2" s="224"/>
+      <c r="W2" s="225"/>
+      <c r="X2" s="223" t="s">
         <v>466</v>
       </c>
-      <c r="J2" s="237"/>
-      <c r="K2" s="238"/>
-      <c r="L2" s="236" t="s">
+      <c r="Y2" s="224"/>
+      <c r="Z2" s="225"/>
+      <c r="AA2" s="223" t="s">
         <v>467</v>
       </c>
-      <c r="M2" s="237"/>
-      <c r="N2" s="238"/>
-      <c r="O2" s="236" t="s">
-        <v>468</v>
-      </c>
-      <c r="P2" s="237"/>
-      <c r="Q2" s="238"/>
-      <c r="R2" s="236" t="s">
-        <v>469</v>
-      </c>
-      <c r="S2" s="237"/>
-      <c r="T2" s="238"/>
-      <c r="U2" s="236" t="s">
-        <v>470</v>
-      </c>
-      <c r="V2" s="237"/>
-      <c r="W2" s="238"/>
-      <c r="X2" s="236" t="s">
-        <v>471</v>
-      </c>
-      <c r="Y2" s="237"/>
-      <c r="Z2" s="238"/>
-      <c r="AA2" s="236" t="s">
-        <v>472</v>
-      </c>
-      <c r="AB2" s="237"/>
-      <c r="AC2" s="237"/>
-      <c r="AD2" s="236"/>
-      <c r="AE2" s="237"/>
-      <c r="AF2" s="238"/>
-      <c r="AG2" s="236"/>
-      <c r="AH2" s="237"/>
-      <c r="AI2" s="238"/>
-      <c r="AJ2" s="236"/>
-      <c r="AK2" s="237"/>
-      <c r="AL2" s="238"/>
-      <c r="AM2" s="236"/>
-      <c r="AN2" s="237"/>
-      <c r="AO2" s="238"/>
-      <c r="AP2" s="236"/>
-      <c r="AQ2" s="237"/>
-      <c r="AR2" s="238"/>
-      <c r="AS2" s="236"/>
-      <c r="AT2" s="237"/>
-      <c r="AU2" s="238"/>
-      <c r="AV2" s="236"/>
-      <c r="AW2" s="237"/>
-      <c r="AX2" s="238"/>
+      <c r="AB2" s="224"/>
+      <c r="AC2" s="224"/>
+      <c r="AD2" s="223"/>
+      <c r="AE2" s="224"/>
+      <c r="AF2" s="225"/>
+      <c r="AG2" s="223"/>
+      <c r="AH2" s="224"/>
+      <c r="AI2" s="225"/>
+      <c r="AJ2" s="223"/>
+      <c r="AK2" s="224"/>
+      <c r="AL2" s="225"/>
+      <c r="AM2" s="223"/>
+      <c r="AN2" s="224"/>
+      <c r="AO2" s="225"/>
+      <c r="AP2" s="223"/>
+      <c r="AQ2" s="224"/>
+      <c r="AR2" s="225"/>
+      <c r="AS2" s="223"/>
+      <c r="AT2" s="224"/>
+      <c r="AU2" s="225"/>
+      <c r="AV2" s="223"/>
+      <c r="AW2" s="224"/>
+      <c r="AX2" s="225"/>
     </row>
     <row r="3" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -44063,9 +44101,9 @@
       <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="235"/>
-      <c r="D3" s="235"/>
-      <c r="E3" s="235"/>
+      <c r="C3" s="237"/>
+      <c r="D3" s="237"/>
+      <c r="E3" s="237"/>
       <c r="F3" s="169" t="s">
         <v>393</v>
       </c>
@@ -45005,7 +45043,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="149" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C16" s="58">
         <f t="shared" ref="C16:C28" si="4">SUM(F16,I16,L16,O16,R16,X16,AA16,AD16,U16,AG16,AJ16,AM16,AP16,AS16,AV16)</f>
@@ -45998,7 +46036,7 @@
         <v>45</v>
       </c>
       <c r="B31" s="148" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="C31" s="58">
         <f t="shared" ref="C31:C38" si="8">SUM(F31,I31,L31,O31,R31,X31,AA31,AD31,U31,AG31,AJ31,AM31,AP31,AS31,AV31)</f>
@@ -46697,13 +46735,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="F1:AC1"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="AJ1:AO1"/>
     <mergeCell ref="AP1:AU1"/>
     <mergeCell ref="AV1:AX1"/>
@@ -46720,6 +46751,13 @@
     <mergeCell ref="AD1:AI1"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="I2:K2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="F1:AC1"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
+    <mergeCell ref="AA2:AC2"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:AW32">
     <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
@@ -46754,70 +46792,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C1" s="233" t="s">
+      <c r="C1" s="235" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="233" t="s">
+      <c r="D1" s="235" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="233" t="s">
+      <c r="E1" s="235" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="273" t="s">
+      <c r="F1" s="265" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="274"/>
-      <c r="H1" s="275"/>
-      <c r="I1" s="276" t="s">
+      <c r="G1" s="266"/>
+      <c r="H1" s="267"/>
+      <c r="I1" s="268" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="277"/>
-      <c r="K1" s="278"/>
-      <c r="L1" s="243" t="s">
+      <c r="J1" s="269"/>
+      <c r="K1" s="270"/>
+      <c r="L1" s="272" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="244"/>
-      <c r="N1" s="245"/>
-      <c r="O1" s="246" t="s">
+      <c r="M1" s="273"/>
+      <c r="N1" s="274"/>
+      <c r="O1" s="275" t="s">
         <v>199</v>
       </c>
-      <c r="P1" s="247"/>
-      <c r="Q1" s="248"/>
-      <c r="R1" s="249" t="s">
+      <c r="P1" s="276"/>
+      <c r="Q1" s="277"/>
+      <c r="R1" s="241" t="s">
         <v>200</v>
       </c>
-      <c r="S1" s="250"/>
-      <c r="T1" s="251"/>
-      <c r="U1" s="252" t="s">
+      <c r="S1" s="242"/>
+      <c r="T1" s="243"/>
+      <c r="U1" s="244" t="s">
         <v>306</v>
       </c>
-      <c r="V1" s="253"/>
-      <c r="W1" s="254"/>
+      <c r="V1" s="245"/>
+      <c r="W1" s="246"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="234"/>
-      <c r="D2" s="234"/>
-      <c r="E2" s="234"/>
-      <c r="F2" s="255"/>
-      <c r="G2" s="256"/>
-      <c r="H2" s="257"/>
-      <c r="I2" s="270"/>
-      <c r="J2" s="271"/>
-      <c r="K2" s="272"/>
-      <c r="L2" s="267"/>
-      <c r="M2" s="268"/>
-      <c r="N2" s="269"/>
-      <c r="O2" s="264"/>
-      <c r="P2" s="265"/>
-      <c r="Q2" s="266"/>
-      <c r="R2" s="261"/>
-      <c r="S2" s="262"/>
-      <c r="T2" s="263"/>
-      <c r="U2" s="258"/>
-      <c r="V2" s="259"/>
-      <c r="W2" s="260"/>
+      <c r="C2" s="236"/>
+      <c r="D2" s="236"/>
+      <c r="E2" s="236"/>
+      <c r="F2" s="247"/>
+      <c r="G2" s="248"/>
+      <c r="H2" s="249"/>
+      <c r="I2" s="262"/>
+      <c r="J2" s="263"/>
+      <c r="K2" s="264"/>
+      <c r="L2" s="259"/>
+      <c r="M2" s="260"/>
+      <c r="N2" s="261"/>
+      <c r="O2" s="256"/>
+      <c r="P2" s="257"/>
+      <c r="Q2" s="258"/>
+      <c r="R2" s="253"/>
+      <c r="S2" s="254"/>
+      <c r="T2" s="255"/>
+      <c r="U2" s="250"/>
+      <c r="V2" s="251"/>
+      <c r="W2" s="252"/>
     </row>
     <row r="3" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -46826,9 +46864,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="242"/>
-      <c r="D3" s="242"/>
-      <c r="E3" s="242"/>
+      <c r="C3" s="271"/>
+      <c r="D3" s="271"/>
+      <c r="E3" s="271"/>
       <c r="F3" s="188" t="s">
         <v>393</v>
       </c>
@@ -47345,7 +47383,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="149" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C16" s="58">
         <f t="shared" si="2"/>
@@ -47915,7 +47953,7 @@
         <v>45</v>
       </c>
       <c r="B31" s="148" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="C31" s="58">
         <f t="shared" ref="C31:C38" si="6">SUM(F31,I31,L31,O31,R31,U31)</f>
@@ -48290,6 +48328,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="O1:Q1"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="F2:H2"/>
@@ -48300,11 +48343,6 @@
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="O1:Q1"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:W32">
     <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
@@ -48544,7 +48582,7 @@
       <c r="F6" s="25"/>
       <c r="G6" s="21">
         <f>'Apps &amp; Goals 26-27'!C4</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H6" s="21">
         <f>'Apps &amp; Goals 26-27'!D4</f>
@@ -48556,7 +48594,7 @@
       </c>
       <c r="J6" s="25">
         <f>G6+C6</f>
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K6" s="25">
         <f>H6+D6</f>
@@ -49123,7 +49161,7 @@
       <c r="F9" s="25"/>
       <c r="G9" s="21">
         <f>'Apps &amp; Goals 26-27'!C7</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H9" s="21">
         <f>'Apps &amp; Goals 26-27'!D7</f>
@@ -49131,11 +49169,11 @@
       </c>
       <c r="I9" s="21">
         <f>'Apps &amp; Goals 26-27'!E7</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J9" s="25">
         <f t="shared" si="0"/>
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K9" s="25">
         <f t="shared" si="1"/>
@@ -49143,7 +49181,7 @@
       </c>
       <c r="L9" s="25">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M9">
         <v>4</v>
@@ -49316,7 +49354,7 @@
       <c r="F10" s="25"/>
       <c r="G10" s="21">
         <f>'Apps &amp; Goals 26-27'!C8</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H10" s="21">
         <f>'Apps &amp; Goals 26-27'!D8</f>
@@ -49328,7 +49366,7 @@
       </c>
       <c r="J10" s="25">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K10" s="25">
         <f t="shared" si="1"/>
@@ -49509,7 +49547,7 @@
       <c r="F11" s="25"/>
       <c r="G11" s="21">
         <f>'Apps &amp; Goals 26-27'!C9</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H11" s="21">
         <f>'Apps &amp; Goals 26-27'!D9</f>
@@ -49521,7 +49559,7 @@
       </c>
       <c r="J11" s="25">
         <f t="shared" si="0"/>
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K11" s="25">
         <f t="shared" si="1"/>
@@ -49702,7 +49740,7 @@
       <c r="F12" s="25"/>
       <c r="G12" s="21">
         <f>'Apps &amp; Goals 26-27'!C10</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H12" s="21">
         <f>'Apps &amp; Goals 26-27'!D10</f>
@@ -49714,7 +49752,7 @@
       </c>
       <c r="J12" s="25">
         <f t="shared" si="0"/>
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K12" s="25">
         <f t="shared" si="1"/>
@@ -49895,7 +49933,7 @@
       <c r="F13" s="25"/>
       <c r="G13" s="21">
         <f>'Apps &amp; Goals 26-27'!C11</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H13" s="21">
         <f>'Apps &amp; Goals 26-27'!D11</f>
@@ -49907,7 +49945,7 @@
       </c>
       <c r="J13" s="25">
         <f t="shared" si="0"/>
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K13" s="25">
         <f t="shared" si="1"/>
@@ -50281,7 +50319,7 @@
       <c r="F15" s="25"/>
       <c r="G15" s="21">
         <f>'Apps &amp; Goals 26-27'!C13</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="21">
         <f>'Apps &amp; Goals 26-27'!D13</f>
@@ -50293,7 +50331,7 @@
       </c>
       <c r="J15" s="25">
         <f t="shared" si="0"/>
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K15" s="25">
         <f t="shared" si="1"/>
@@ -50667,7 +50705,7 @@
       <c r="F17" s="25"/>
       <c r="G17" s="21">
         <f>'Apps &amp; Goals 26-27'!C15</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H17" s="21">
         <f>'Apps &amp; Goals 26-27'!D15</f>
@@ -50679,7 +50717,7 @@
       </c>
       <c r="J17" s="25">
         <f t="shared" si="0"/>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K17" s="25">
         <f t="shared" si="1"/>
@@ -50846,7 +50884,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C18" s="25">
         <v>0</v>
@@ -50860,7 +50898,7 @@
       <c r="F18" s="25"/>
       <c r="G18" s="21">
         <f>'Apps &amp; Goals 26-27'!C16</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H18" s="21">
         <f>'Apps &amp; Goals 26-27'!D16</f>
@@ -50872,7 +50910,7 @@
       </c>
       <c r="J18" s="25">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K18" s="25">
         <f t="shared" si="1"/>
@@ -50886,7 +50924,7 @@
         <v>15</v>
       </c>
       <c r="N18" s="45" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="O18" s="26">
         <v>0</v>
@@ -50923,7 +50961,7 @@
         <v>0</v>
       </c>
       <c r="Z18" s="57" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AA18" s="24">
         <v>0</v>
@@ -50960,7 +50998,7 @@
         <v>0</v>
       </c>
       <c r="AL18" s="63" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AM18" s="18">
         <v>0</v>
@@ -50997,7 +51035,7 @@
         <v>0</v>
       </c>
       <c r="AX18" s="32" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AY18" s="33">
         <v>0</v>
@@ -51246,7 +51284,7 @@
       <c r="F20" s="25"/>
       <c r="G20" s="21">
         <f>'Apps &amp; Goals 26-27'!C18</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H20" s="21">
         <f>'Apps &amp; Goals 26-27'!D18</f>
@@ -51258,7 +51296,7 @@
       </c>
       <c r="J20" s="25">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K20" s="25">
         <f t="shared" si="1"/>
@@ -51632,7 +51670,7 @@
       <c r="F22" s="25"/>
       <c r="G22" s="21">
         <f>'Apps &amp; Goals 26-27'!C20</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H22" s="21">
         <f>'Apps &amp; Goals 26-27'!D20</f>
@@ -51644,7 +51682,7 @@
       </c>
       <c r="J22" s="25">
         <f t="shared" si="0"/>
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K22" s="25">
         <f t="shared" si="1"/>
@@ -51825,7 +51863,7 @@
       <c r="F23" s="25"/>
       <c r="G23" s="21">
         <f>'Apps &amp; Goals 26-27'!C21</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H23" s="21">
         <f>'Apps &amp; Goals 26-27'!D21</f>
@@ -51837,7 +51875,7 @@
       </c>
       <c r="J23" s="25">
         <f t="shared" si="0"/>
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K23" s="25">
         <f t="shared" si="1"/>
@@ -52211,11 +52249,11 @@
       <c r="F25" s="25"/>
       <c r="G25" s="21">
         <f>'Apps &amp; Goals 26-27'!C23</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H25" s="21">
         <f>'Apps &amp; Goals 26-27'!D23</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" s="21">
         <f>'Apps &amp; Goals 26-27'!E23</f>
@@ -52223,11 +52261,11 @@
       </c>
       <c r="J25" s="25">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K25" s="25">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L25" s="25">
         <f t="shared" si="2"/>
@@ -52790,11 +52828,11 @@
       <c r="F28" s="25"/>
       <c r="G28" s="21">
         <f>'Apps &amp; Goals 26-27'!C26</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H28" s="21">
         <f>'Apps &amp; Goals 26-27'!D26</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I28" s="21">
         <f>'Apps &amp; Goals 26-27'!E26</f>
@@ -52802,11 +52840,11 @@
       </c>
       <c r="J28" s="25">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K28" s="25">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L28" s="25">
         <f t="shared" si="2"/>
@@ -53176,7 +53214,7 @@
       <c r="F30" s="25"/>
       <c r="G30" s="21">
         <f>'Apps &amp; Goals 26-27'!C28</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H30" s="21">
         <f>'Apps &amp; Goals 26-27'!D28</f>
@@ -53184,11 +53222,11 @@
       </c>
       <c r="I30" s="21">
         <f>'Apps &amp; Goals 26-27'!E28</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J30" s="25">
         <f t="shared" si="0"/>
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K30" s="25">
         <f t="shared" si="1"/>
@@ -53196,7 +53234,7 @@
       </c>
       <c r="L30" s="25">
         <f t="shared" si="2"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M30">
         <v>41</v>
@@ -53741,7 +53779,7 @@
         <v>45</v>
       </c>
       <c r="B33" s="22" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="C33" s="25">
         <v>0</v>
@@ -53781,7 +53819,7 @@
         <v>45</v>
       </c>
       <c r="N33" s="45" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="O33" s="26">
         <v>0</v>
@@ -53818,7 +53856,7 @@
         <v>0</v>
       </c>
       <c r="Z33" s="23" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="AA33" s="24">
         <v>0</v>
@@ -53855,7 +53893,7 @@
         <v>0</v>
       </c>
       <c r="AL33" s="19" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="AM33" s="18">
         <v>0</v>
@@ -53892,7 +53930,7 @@
         <v>0</v>
       </c>
       <c r="AX33" s="32" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="AY33" s="33">
         <v>0</v>
@@ -54141,7 +54179,7 @@
       <c r="F35" s="25"/>
       <c r="G35" s="21">
         <f>'Apps &amp; Goals 26-27'!C33</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H35" s="21">
         <f>'Apps &amp; Goals 26-27'!D33</f>
@@ -54153,7 +54191,7 @@
       </c>
       <c r="J35" s="25">
         <f t="shared" si="0"/>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K35" s="25">
         <f t="shared" si="1"/>
@@ -55311,72 +55349,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C1" s="233" t="s">
+      <c r="C1" s="235" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="233" t="s">
+      <c r="D1" s="235" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="233" t="s">
+      <c r="E1" s="235" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="273" t="s">
+      <c r="F1" s="265" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="274"/>
-      <c r="H1" s="275"/>
-      <c r="I1" s="276" t="s">
+      <c r="G1" s="266"/>
+      <c r="H1" s="267"/>
+      <c r="I1" s="268" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="277"/>
-      <c r="K1" s="278"/>
-      <c r="L1" s="243" t="s">
+      <c r="J1" s="269"/>
+      <c r="K1" s="270"/>
+      <c r="L1" s="272" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="244"/>
-      <c r="N1" s="245"/>
-      <c r="O1" s="246" t="s">
+      <c r="M1" s="273"/>
+      <c r="N1" s="274"/>
+      <c r="O1" s="275" t="s">
         <v>199</v>
       </c>
-      <c r="P1" s="247"/>
-      <c r="Q1" s="248"/>
-      <c r="R1" s="249" t="s">
+      <c r="P1" s="276"/>
+      <c r="Q1" s="277"/>
+      <c r="R1" s="241" t="s">
         <v>200</v>
       </c>
-      <c r="S1" s="250"/>
-      <c r="T1" s="251"/>
-      <c r="U1" s="252" t="s">
+      <c r="S1" s="242"/>
+      <c r="T1" s="243"/>
+      <c r="U1" s="244" t="s">
         <v>306</v>
       </c>
-      <c r="V1" s="253"/>
-      <c r="W1" s="254"/>
+      <c r="V1" s="245"/>
+      <c r="W1" s="246"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="234"/>
-      <c r="D2" s="234"/>
-      <c r="E2" s="234"/>
-      <c r="F2" s="255" t="s">
-        <v>433</v>
-      </c>
-      <c r="G2" s="256"/>
-      <c r="H2" s="257"/>
-      <c r="I2" s="270"/>
-      <c r="J2" s="271"/>
-      <c r="K2" s="272"/>
-      <c r="L2" s="267"/>
-      <c r="M2" s="268"/>
-      <c r="N2" s="269"/>
-      <c r="O2" s="264"/>
-      <c r="P2" s="265"/>
-      <c r="Q2" s="266"/>
-      <c r="R2" s="261"/>
-      <c r="S2" s="262"/>
-      <c r="T2" s="263"/>
-      <c r="U2" s="258"/>
-      <c r="V2" s="259"/>
-      <c r="W2" s="260"/>
+      <c r="C2" s="236"/>
+      <c r="D2" s="236"/>
+      <c r="E2" s="236"/>
+      <c r="F2" s="247" t="s">
+        <v>432</v>
+      </c>
+      <c r="G2" s="248"/>
+      <c r="H2" s="249"/>
+      <c r="I2" s="262"/>
+      <c r="J2" s="263"/>
+      <c r="K2" s="264"/>
+      <c r="L2" s="259"/>
+      <c r="M2" s="260"/>
+      <c r="N2" s="261"/>
+      <c r="O2" s="256"/>
+      <c r="P2" s="257"/>
+      <c r="Q2" s="258"/>
+      <c r="R2" s="253"/>
+      <c r="S2" s="254"/>
+      <c r="T2" s="255"/>
+      <c r="U2" s="250"/>
+      <c r="V2" s="251"/>
+      <c r="W2" s="252"/>
     </row>
     <row r="3" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -55385,9 +55423,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="242"/>
-      <c r="D3" s="242"/>
-      <c r="E3" s="242"/>
+      <c r="C3" s="271"/>
+      <c r="D3" s="271"/>
+      <c r="E3" s="271"/>
       <c r="F3" s="188" t="s">
         <v>393</v>
       </c>
@@ -55916,7 +55954,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="149" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C16" s="58">
         <f t="shared" ref="C16:C28" si="2">SUM(F16,I16,L16,O16,R16,U16)</f>
@@ -56506,7 +56544,7 @@
         <v>45</v>
       </c>
       <c r="B31" s="148" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="C31" s="58">
         <f t="shared" ref="C31:C38" si="6">SUM(F31,I31,L31,O31,R31,U31)</f>
@@ -56891,11 +56929,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="F2:H2"/>
@@ -56906,6 +56939,11 @@
     <mergeCell ref="U2:W2"/>
     <mergeCell ref="L1:N1"/>
     <mergeCell ref="O1:Q1"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:W32">
     <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
@@ -56933,11 +56971,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C1" s="279" t="s">
+      <c r="C1" s="278" t="s">
         <v>340</v>
       </c>
-      <c r="D1" s="280"/>
-      <c r="E1" s="280"/>
+      <c r="D1" s="279"/>
+      <c r="E1" s="279"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -57113,7 +57151,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="149" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="20"/>
@@ -57298,7 +57336,7 @@
         <v>45</v>
       </c>
       <c r="B30" s="148" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="C30" s="20"/>
       <c r="D30" s="20"/>
@@ -57412,51 +57450,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="301" t="s">
+      <c r="C1" s="281" t="s">
         <v>202</v>
       </c>
-      <c r="D1" s="302"/>
-      <c r="E1" s="302"/>
-      <c r="F1" s="302"/>
-      <c r="G1" s="302"/>
-      <c r="H1" s="302"/>
-      <c r="I1" s="303"/>
+      <c r="D1" s="282"/>
+      <c r="E1" s="282"/>
+      <c r="F1" s="282"/>
+      <c r="G1" s="282"/>
+      <c r="H1" s="282"/>
+      <c r="I1" s="283"/>
       <c r="J1" s="114" t="s">
         <v>195</v>
       </c>
       <c r="K1" s="115" t="s">
         <v>194</v>
       </c>
-      <c r="L1" s="281" t="s">
+      <c r="L1" s="305" t="s">
         <v>287</v>
       </c>
-      <c r="M1" s="286"/>
-      <c r="N1" s="286"/>
-      <c r="O1" s="286"/>
-      <c r="P1" s="286"/>
-      <c r="Q1" s="286"/>
-      <c r="R1" s="286"/>
-      <c r="S1" s="286"/>
-      <c r="T1" s="286"/>
-      <c r="U1" s="286"/>
-      <c r="V1" s="286"/>
-      <c r="W1" s="286"/>
-      <c r="X1" s="286"/>
-      <c r="Y1" s="286"/>
-      <c r="Z1" s="286"/>
-      <c r="AA1" s="286"/>
-      <c r="AB1" s="286"/>
-      <c r="AC1" s="286"/>
-      <c r="AD1" s="286"/>
-      <c r="AE1" s="286"/>
-      <c r="AF1" s="286"/>
-      <c r="AG1" s="287"/>
-      <c r="AH1" s="281" t="s">
+      <c r="M1" s="310"/>
+      <c r="N1" s="310"/>
+      <c r="O1" s="310"/>
+      <c r="P1" s="310"/>
+      <c r="Q1" s="310"/>
+      <c r="R1" s="310"/>
+      <c r="S1" s="310"/>
+      <c r="T1" s="310"/>
+      <c r="U1" s="310"/>
+      <c r="V1" s="310"/>
+      <c r="W1" s="310"/>
+      <c r="X1" s="310"/>
+      <c r="Y1" s="310"/>
+      <c r="Z1" s="310"/>
+      <c r="AA1" s="310"/>
+      <c r="AB1" s="310"/>
+      <c r="AC1" s="310"/>
+      <c r="AD1" s="310"/>
+      <c r="AE1" s="310"/>
+      <c r="AF1" s="310"/>
+      <c r="AG1" s="311"/>
+      <c r="AH1" s="305" t="s">
         <v>175</v>
       </c>
-      <c r="AI1" s="282"/>
-      <c r="AJ1" s="282"/>
-      <c r="AK1" s="283"/>
+      <c r="AI1" s="306"/>
+      <c r="AJ1" s="306"/>
+      <c r="AK1" s="307"/>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B2" s="111"/>
@@ -62656,15 +62694,15 @@
         <f t="shared" ref="J80:J111" si="2">H80-I80</f>
         <v>2</v>
       </c>
-      <c r="K80" s="288" t="s">
-        <v>435</v>
-      </c>
-      <c r="L80" s="289"/>
-      <c r="M80" s="290"/>
+      <c r="K80" s="312" t="s">
+        <v>434</v>
+      </c>
+      <c r="L80" s="313"/>
+      <c r="M80" s="314"/>
       <c r="O80" s="133"/>
       <c r="P80" s="133"/>
-      <c r="W80" s="284"/>
-      <c r="X80" s="284"/>
+      <c r="W80" s="308"/>
+      <c r="X80" s="308"/>
       <c r="Y80" s="70" t="s">
         <v>211</v>
       </c>
@@ -62714,15 +62752,15 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K81" s="291"/>
-      <c r="L81" s="292"/>
-      <c r="M81" s="293"/>
+      <c r="K81" s="315"/>
+      <c r="L81" s="316"/>
+      <c r="M81" s="317"/>
       <c r="O81" s="133"/>
       <c r="P81" s="133"/>
-      <c r="W81" s="284" t="s">
+      <c r="W81" s="308" t="s">
         <v>209</v>
       </c>
-      <c r="X81" s="284"/>
+      <c r="X81" s="308"/>
       <c r="Y81" s="70">
         <f>COUNTIF(L3:AG40,3)</f>
         <v>481</v>
@@ -62778,17 +62816,17 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K82" s="294" t="s">
-        <v>436</v>
-      </c>
-      <c r="L82" s="295"/>
-      <c r="M82" s="296"/>
+      <c r="K82" s="318" t="s">
+        <v>435</v>
+      </c>
+      <c r="L82" s="319"/>
+      <c r="M82" s="320"/>
       <c r="O82" s="133"/>
       <c r="P82" s="133"/>
-      <c r="W82" s="284" t="s">
+      <c r="W82" s="308" t="s">
         <v>210</v>
       </c>
-      <c r="X82" s="284"/>
+      <c r="X82" s="308"/>
       <c r="Y82" s="70">
         <f>COUNTIF(K3:K40,3)+COUNTIF(J3:J15,3)</f>
         <v>25</v>
@@ -62844,17 +62882,17 @@
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="K83" s="297" t="s">
-        <v>437</v>
-      </c>
-      <c r="L83" s="298"/>
-      <c r="M83" s="299"/>
+      <c r="K83" s="321" t="s">
+        <v>436</v>
+      </c>
+      <c r="L83" s="322"/>
+      <c r="M83" s="323"/>
       <c r="O83" s="133"/>
       <c r="P83" s="133"/>
-      <c r="W83" s="285" t="s">
+      <c r="W83" s="309" t="s">
         <v>97</v>
       </c>
-      <c r="X83" s="285"/>
+      <c r="X83" s="309"/>
       <c r="Y83" s="194">
         <v>224</v>
       </c>
@@ -62907,15 +62945,15 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="K84" s="315" t="s">
+      <c r="K84" s="287" t="s">
         <v>284</v>
       </c>
-      <c r="L84" s="316"/>
-      <c r="M84" s="317"/>
+      <c r="L84" s="288"/>
+      <c r="M84" s="289"/>
       <c r="O84" s="141"/>
       <c r="P84" s="141"/>
-      <c r="W84" s="300"/>
-      <c r="X84" s="300"/>
+      <c r="W84" s="280"/>
+      <c r="X84" s="280"/>
       <c r="Y84" s="196"/>
       <c r="Z84" s="196"/>
       <c r="AA84" s="196"/>
@@ -62953,9 +62991,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K85" s="318"/>
-      <c r="L85" s="319"/>
-      <c r="M85" s="320"/>
+      <c r="K85" s="290"/>
+      <c r="L85" s="291"/>
+      <c r="M85" s="292"/>
       <c r="O85" s="141"/>
       <c r="P85" s="141"/>
     </row>
@@ -62989,9 +63027,9 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="K86" s="318"/>
-      <c r="L86" s="319"/>
-      <c r="M86" s="320"/>
+      <c r="K86" s="290"/>
+      <c r="L86" s="291"/>
+      <c r="M86" s="292"/>
       <c r="O86" s="141"/>
       <c r="P86" s="141"/>
     </row>
@@ -63025,9 +63063,9 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="K87" s="318"/>
-      <c r="L87" s="319"/>
-      <c r="M87" s="320"/>
+      <c r="K87" s="290"/>
+      <c r="L87" s="291"/>
+      <c r="M87" s="292"/>
       <c r="O87" s="141"/>
       <c r="P87" s="141"/>
     </row>
@@ -63061,9 +63099,9 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K88" s="318"/>
-      <c r="L88" s="319"/>
-      <c r="M88" s="320"/>
+      <c r="K88" s="290"/>
+      <c r="L88" s="291"/>
+      <c r="M88" s="292"/>
       <c r="O88" s="141"/>
       <c r="P88" s="141"/>
     </row>
@@ -63097,9 +63135,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K89" s="318"/>
-      <c r="L89" s="319"/>
-      <c r="M89" s="320"/>
+      <c r="K89" s="290"/>
+      <c r="L89" s="291"/>
+      <c r="M89" s="292"/>
       <c r="O89" s="141"/>
       <c r="P89" s="141"/>
     </row>
@@ -63133,9 +63171,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K90" s="318"/>
-      <c r="L90" s="319"/>
-      <c r="M90" s="320"/>
+      <c r="K90" s="290"/>
+      <c r="L90" s="291"/>
+      <c r="M90" s="292"/>
       <c r="O90" s="141"/>
       <c r="P90" s="141"/>
     </row>
@@ -63169,9 +63207,9 @@
         <f t="shared" si="2"/>
         <v>47</v>
       </c>
-      <c r="K91" s="318"/>
-      <c r="L91" s="319"/>
-      <c r="M91" s="320"/>
+      <c r="K91" s="290"/>
+      <c r="L91" s="291"/>
+      <c r="M91" s="292"/>
       <c r="O91" s="141"/>
       <c r="P91" s="141"/>
     </row>
@@ -63205,9 +63243,9 @@
         <f t="shared" si="2"/>
         <v>51</v>
       </c>
-      <c r="K92" s="318"/>
-      <c r="L92" s="319"/>
-      <c r="M92" s="320"/>
+      <c r="K92" s="290"/>
+      <c r="L92" s="291"/>
+      <c r="M92" s="292"/>
       <c r="O92" s="141"/>
       <c r="P92" s="141"/>
     </row>
@@ -63241,9 +63279,9 @@
         <f t="shared" si="2"/>
         <v>37</v>
       </c>
-      <c r="K93" s="318"/>
-      <c r="L93" s="319"/>
-      <c r="M93" s="320"/>
+      <c r="K93" s="290"/>
+      <c r="L93" s="291"/>
+      <c r="M93" s="292"/>
       <c r="O93" s="141"/>
       <c r="P93" s="141"/>
     </row>
@@ -63277,9 +63315,9 @@
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="K94" s="318"/>
-      <c r="L94" s="319"/>
-      <c r="M94" s="320"/>
+      <c r="K94" s="290"/>
+      <c r="L94" s="291"/>
+      <c r="M94" s="292"/>
       <c r="O94" s="141"/>
       <c r="P94" s="141"/>
     </row>
@@ -63313,9 +63351,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K95" s="318"/>
-      <c r="L95" s="319"/>
-      <c r="M95" s="320"/>
+      <c r="K95" s="290"/>
+      <c r="L95" s="291"/>
+      <c r="M95" s="292"/>
       <c r="O95" s="141"/>
       <c r="P95" s="141"/>
     </row>
@@ -63349,9 +63387,9 @@
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="K96" s="318"/>
-      <c r="L96" s="319"/>
-      <c r="M96" s="320"/>
+      <c r="K96" s="290"/>
+      <c r="L96" s="291"/>
+      <c r="M96" s="292"/>
       <c r="O96" s="141"/>
       <c r="P96" s="141"/>
     </row>
@@ -63385,9 +63423,9 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="K97" s="318"/>
-      <c r="L97" s="319"/>
-      <c r="M97" s="320"/>
+      <c r="K97" s="290"/>
+      <c r="L97" s="291"/>
+      <c r="M97" s="292"/>
       <c r="O97" s="141"/>
       <c r="P97" s="141"/>
     </row>
@@ -63421,9 +63459,9 @@
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="K98" s="318"/>
-      <c r="L98" s="319"/>
-      <c r="M98" s="320"/>
+      <c r="K98" s="290"/>
+      <c r="L98" s="291"/>
+      <c r="M98" s="292"/>
       <c r="O98" s="141"/>
       <c r="P98" s="141"/>
     </row>
@@ -63457,9 +63495,9 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K99" s="318"/>
-      <c r="L99" s="319"/>
-      <c r="M99" s="320"/>
+      <c r="K99" s="290"/>
+      <c r="L99" s="291"/>
+      <c r="M99" s="292"/>
       <c r="O99" s="141"/>
       <c r="P99" s="141"/>
     </row>
@@ -63493,9 +63531,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K100" s="318"/>
-      <c r="L100" s="319"/>
-      <c r="M100" s="320"/>
+      <c r="K100" s="290"/>
+      <c r="L100" s="291"/>
+      <c r="M100" s="292"/>
       <c r="O100" s="141"/>
       <c r="P100" s="141"/>
     </row>
@@ -63529,9 +63567,9 @@
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="K101" s="318"/>
-      <c r="L101" s="319"/>
-      <c r="M101" s="320"/>
+      <c r="K101" s="290"/>
+      <c r="L101" s="291"/>
+      <c r="M101" s="292"/>
       <c r="O101" s="141"/>
       <c r="P101" s="141"/>
     </row>
@@ -63565,9 +63603,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K102" s="318"/>
-      <c r="L102" s="319"/>
-      <c r="M102" s="320"/>
+      <c r="K102" s="290"/>
+      <c r="L102" s="291"/>
+      <c r="M102" s="292"/>
       <c r="O102" s="141"/>
       <c r="P102" s="141"/>
     </row>
@@ -63601,9 +63639,9 @@
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="K103" s="318"/>
-      <c r="L103" s="319"/>
-      <c r="M103" s="320"/>
+      <c r="K103" s="290"/>
+      <c r="L103" s="291"/>
+      <c r="M103" s="292"/>
       <c r="O103" s="141"/>
       <c r="P103" s="141"/>
     </row>
@@ -63637,9 +63675,9 @@
         <f t="shared" si="2"/>
         <v>33</v>
       </c>
-      <c r="K104" s="318"/>
-      <c r="L104" s="319"/>
-      <c r="M104" s="320"/>
+      <c r="K104" s="290"/>
+      <c r="L104" s="291"/>
+      <c r="M104" s="292"/>
       <c r="O104" s="141"/>
       <c r="P104" s="141"/>
     </row>
@@ -63673,9 +63711,9 @@
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="K105" s="321"/>
-      <c r="L105" s="322"/>
-      <c r="M105" s="323"/>
+      <c r="K105" s="293"/>
+      <c r="L105" s="294"/>
+      <c r="M105" s="295"/>
       <c r="O105" s="141"/>
       <c r="P105" s="141"/>
     </row>
@@ -63709,11 +63747,11 @@
         <f t="shared" si="2"/>
         <v>21</v>
       </c>
-      <c r="K106" s="312" t="s">
+      <c r="K106" s="284" t="s">
         <v>286</v>
       </c>
-      <c r="L106" s="313"/>
-      <c r="M106" s="314"/>
+      <c r="L106" s="285"/>
+      <c r="M106" s="286"/>
       <c r="O106" s="126"/>
       <c r="P106" s="126"/>
     </row>
@@ -63747,11 +63785,11 @@
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="K107" s="312" t="s">
+      <c r="K107" s="284" t="s">
         <v>288</v>
       </c>
-      <c r="L107" s="313"/>
-      <c r="M107" s="314"/>
+      <c r="L107" s="285"/>
+      <c r="M107" s="286"/>
       <c r="O107" s="126"/>
       <c r="P107" s="126"/>
     </row>
@@ -63785,11 +63823,11 @@
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="K108" s="304" t="s">
+      <c r="K108" s="296" t="s">
         <v>289</v>
       </c>
-      <c r="L108" s="305"/>
-      <c r="M108" s="306"/>
+      <c r="L108" s="297"/>
+      <c r="M108" s="298"/>
       <c r="O108" s="126"/>
       <c r="P108" s="126"/>
     </row>
@@ -63823,9 +63861,9 @@
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="K109" s="307"/>
-      <c r="L109" s="327"/>
-      <c r="M109" s="308"/>
+      <c r="K109" s="299"/>
+      <c r="L109" s="300"/>
+      <c r="M109" s="301"/>
       <c r="O109" s="126"/>
       <c r="P109" s="126"/>
     </row>
@@ -63859,9 +63897,9 @@
         <f t="shared" si="2"/>
         <v>45</v>
       </c>
-      <c r="K110" s="307"/>
-      <c r="L110" s="327"/>
-      <c r="M110" s="308"/>
+      <c r="K110" s="299"/>
+      <c r="L110" s="300"/>
+      <c r="M110" s="301"/>
       <c r="O110" s="126"/>
       <c r="P110" s="126"/>
     </row>
@@ -63895,9 +63933,9 @@
         <f t="shared" si="2"/>
         <v>62</v>
       </c>
-      <c r="K111" s="307"/>
-      <c r="L111" s="327"/>
-      <c r="M111" s="308"/>
+      <c r="K111" s="299"/>
+      <c r="L111" s="300"/>
+      <c r="M111" s="301"/>
       <c r="O111" s="126"/>
       <c r="P111" s="126"/>
     </row>
@@ -63935,9 +63973,9 @@
         <f t="shared" ref="J112:J114" si="6">H112-I112</f>
         <v>34</v>
       </c>
-      <c r="K112" s="307"/>
-      <c r="L112" s="327"/>
-      <c r="M112" s="308"/>
+      <c r="K112" s="299"/>
+      <c r="L112" s="300"/>
+      <c r="M112" s="301"/>
     </row>
     <row r="113" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="156" t="s">
@@ -63973,13 +64011,13 @@
         <f t="shared" si="6"/>
         <v>43</v>
       </c>
-      <c r="K113" s="307"/>
-      <c r="L113" s="327"/>
-      <c r="M113" s="308"/>
+      <c r="K113" s="299"/>
+      <c r="L113" s="300"/>
+      <c r="M113" s="301"/>
     </row>
     <row r="114" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="93" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B114" s="122"/>
       <c r="C114" s="122"/>
@@ -64001,28 +64039,23 @@
       </c>
       <c r="H114" s="122">
         <f>Match!R4</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I114" s="122">
         <f>Match!S4</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J114" s="154">
         <f t="shared" si="6"/>
-        <v>4</v>
-      </c>
-      <c r="K114" s="309"/>
-      <c r="L114" s="310"/>
-      <c r="M114" s="311"/>
+        <v>5</v>
+      </c>
+      <c r="K114" s="302"/>
+      <c r="L114" s="303"/>
+      <c r="M114" s="304"/>
     </row>
   </sheetData>
   <autoFilter ref="A79:J112" xr:uid="{9C81160F-C24B-449F-8F5A-CB622AB71070}"/>
   <mergeCells count="15">
-    <mergeCell ref="W84:X84"/>
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="K106:M106"/>
-    <mergeCell ref="K107:M107"/>
-    <mergeCell ref="K84:M105"/>
     <mergeCell ref="K108:M114"/>
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="W80:X80"/>
@@ -64033,6 +64066,11 @@
     <mergeCell ref="K80:M81"/>
     <mergeCell ref="K82:M82"/>
     <mergeCell ref="K83:M83"/>
+    <mergeCell ref="W84:X84"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="K106:M106"/>
+    <mergeCell ref="K107:M107"/>
+    <mergeCell ref="K84:M105"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <conditionalFormatting sqref="A3:A40">
@@ -64124,32 +64162,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="202" t="s">
+      <c r="A1" s="324" t="s">
         <v>405</v>
       </c>
-      <c r="B1" s="202"/>
-      <c r="C1" s="202"/>
-      <c r="D1" s="202"/>
-      <c r="E1" s="202"/>
-      <c r="F1" s="202" t="s">
+      <c r="B1" s="324"/>
+      <c r="C1" s="324"/>
+      <c r="D1" s="324"/>
+      <c r="E1" s="324"/>
+      <c r="F1" s="324" t="s">
         <v>406</v>
       </c>
-      <c r="G1" s="202"/>
-      <c r="H1" s="202"/>
-      <c r="I1" s="202"/>
-      <c r="J1" s="202"/>
+      <c r="G1" s="324"/>
+      <c r="H1" s="324"/>
+      <c r="I1" s="324"/>
+      <c r="J1" s="324"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2" s="202"/>
-      <c r="B2" s="202"/>
-      <c r="C2" s="202"/>
-      <c r="D2" s="202"/>
-      <c r="E2" s="202"/>
-      <c r="F2" s="202"/>
-      <c r="G2" s="202"/>
-      <c r="H2" s="202"/>
-      <c r="I2" s="202"/>
-      <c r="J2" s="202"/>
+      <c r="A2" s="324"/>
+      <c r="B2" s="324"/>
+      <c r="C2" s="324"/>
+      <c r="D2" s="324"/>
+      <c r="E2" s="324"/>
+      <c r="F2" s="324"/>
+      <c r="G2" s="324"/>
+      <c r="H2" s="324"/>
+      <c r="I2" s="324"/>
+      <c r="J2" s="324"/>
       <c r="L2" t="s">
         <v>409</v>
       </c>
@@ -64219,10 +64257,10 @@
         <v>408</v>
       </c>
       <c r="N3" s="193">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O3" s="193">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P3" s="193">
         <v>0</v>
@@ -64231,48 +64269,48 @@
         <v>0</v>
       </c>
       <c r="R3" s="193">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="S3" s="193">
         <v>5</v>
       </c>
       <c r="T3" s="193">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="U3" s="193">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B4" s="192">
-        <v>0.5625</v>
+        <v>0.875</v>
       </c>
       <c r="C4" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>424</v>
+        <v>461</v>
       </c>
       <c r="E4" t="s">
+        <v>471</v>
+      </c>
+      <c r="F4" t="s">
+        <v>470</v>
+      </c>
+      <c r="G4" s="328" t="s">
         <v>480</v>
-      </c>
-      <c r="F4" t="s">
-        <v>473</v>
-      </c>
-      <c r="G4" s="192" t="s">
-        <v>478</v>
       </c>
       <c r="H4" t="s">
         <v>4</v>
       </c>
       <c r="I4" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="J4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="L4">
         <v>2</v>
@@ -64281,11 +64319,11 @@
         <v>413</v>
       </c>
       <c r="N4" s="193">
+        <v>6</v>
+      </c>
+      <c r="O4" s="193">
         <v>5</v>
       </c>
-      <c r="O4" s="193">
-        <v>4</v>
-      </c>
       <c r="P4" s="193">
         <v>0</v>
       </c>
@@ -64293,16 +64331,16 @@
         <v>1</v>
       </c>
       <c r="R4" s="193">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S4" s="193">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T4" s="193">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U4" s="193">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
@@ -64313,10 +64351,10 @@
         <v>417</v>
       </c>
       <c r="N5" s="193">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O5" s="193">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P5" s="193">
         <v>1</v>
@@ -64325,16 +64363,16 @@
         <v>1</v>
       </c>
       <c r="R5" s="193">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="S5" s="193">
         <v>5</v>
       </c>
       <c r="T5" s="193">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="U5" s="193">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
@@ -64345,28 +64383,28 @@
         <v>416</v>
       </c>
       <c r="N6" s="193">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O6" s="193">
         <v>2</v>
       </c>
       <c r="P6" s="193">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q6" s="193">
         <v>0</v>
       </c>
       <c r="R6" s="193">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="S6" s="193">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T6" s="193">
         <v>6</v>
       </c>
       <c r="U6" s="193">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
@@ -64374,31 +64412,31 @@
         <v>5</v>
       </c>
       <c r="M7" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="N7" s="193">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O7" s="193">
         <v>2</v>
       </c>
       <c r="P7" s="193">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q7" s="193">
         <v>0</v>
       </c>
       <c r="R7" s="193">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S7" s="193">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T7" s="193">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U7" s="193">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
@@ -64406,31 +64444,31 @@
         <v>6</v>
       </c>
       <c r="M8" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="N8" s="193">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O8" s="193">
+        <v>3</v>
+      </c>
+      <c r="P8" s="193">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="193">
         <v>2</v>
       </c>
-      <c r="P8" s="193">
-        <v>3</v>
-      </c>
-      <c r="Q8" s="193">
-        <v>0</v>
-      </c>
       <c r="R8" s="193">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="S8" s="193">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T8" s="193">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U8" s="193">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
@@ -64438,10 +64476,10 @@
         <v>7</v>
       </c>
       <c r="M9" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="N9" s="193">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O9" s="193">
         <v>2</v>
@@ -64450,13 +64488,13 @@
         <v>3</v>
       </c>
       <c r="Q9" s="193">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" s="193">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S9" s="193">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T9" s="193">
         <v>3</v>
@@ -64473,28 +64511,28 @@
         <v>422</v>
       </c>
       <c r="N10" s="193">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O10" s="193">
         <v>2</v>
       </c>
       <c r="P10" s="193">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q10" s="193">
         <v>1</v>
       </c>
       <c r="R10" s="193">
+        <v>8</v>
+      </c>
+      <c r="S10" s="193">
         <v>6</v>
-      </c>
-      <c r="S10" s="193">
-        <v>4</v>
       </c>
       <c r="T10" s="193">
         <v>2</v>
       </c>
       <c r="U10" s="193">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
@@ -64502,31 +64540,31 @@
         <v>9</v>
       </c>
       <c r="M11" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="N11" s="193">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O11" s="193">
         <v>2</v>
       </c>
       <c r="P11" s="193">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q11" s="193">
         <v>1</v>
       </c>
       <c r="R11" s="193">
+        <v>7</v>
+      </c>
+      <c r="S11" s="193">
+        <v>7</v>
+      </c>
+      <c r="T11" s="193">
+        <v>0</v>
+      </c>
+      <c r="U11" s="193">
         <v>9</v>
-      </c>
-      <c r="S11" s="193">
-        <v>9</v>
-      </c>
-      <c r="T11" s="193">
-        <v>0</v>
-      </c>
-      <c r="U11" s="193">
-        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
@@ -64534,31 +64572,31 @@
         <v>10</v>
       </c>
       <c r="M12" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="N12" s="193">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O12" s="193">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P12" s="193">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q12" s="193">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R12" s="193">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S12" s="193">
         <v>12</v>
       </c>
       <c r="T12" s="193" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="U12" s="193">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
@@ -64566,7 +64604,7 @@
         <v>11</v>
       </c>
       <c r="M13" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="N13" s="193">
         <v>5</v>
@@ -64575,22 +64613,22 @@
         <v>2</v>
       </c>
       <c r="P13" s="193">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q13" s="193">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R13" s="193">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="S13" s="193">
-        <v>11</v>
-      </c>
-      <c r="T13" s="193" t="s">
-        <v>481</v>
+        <v>9</v>
+      </c>
+      <c r="T13" s="193">
+        <v>0</v>
       </c>
       <c r="U13" s="193">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
@@ -64598,31 +64636,31 @@
         <v>12</v>
       </c>
       <c r="M14" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="N14" s="193">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O14" s="193">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P14" s="193">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q14" s="193">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R14" s="193">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S14" s="193">
-        <v>8</v>
-      </c>
-      <c r="T14" s="193">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="T14" s="193" t="s">
+        <v>457</v>
       </c>
       <c r="U14" s="193">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
@@ -64630,31 +64668,31 @@
         <v>13</v>
       </c>
       <c r="M15" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="N15" s="193">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O15" s="193">
         <v>1</v>
       </c>
       <c r="P15" s="193">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q15" s="193">
         <v>2</v>
       </c>
       <c r="R15" s="193">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="S15" s="193">
-        <v>5</v>
-      </c>
-      <c r="T15" s="193" t="s">
-        <v>431</v>
+        <v>9</v>
+      </c>
+      <c r="T15" s="193">
+        <v>0</v>
       </c>
       <c r="U15" s="193">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
@@ -64662,31 +64700,31 @@
         <v>14</v>
       </c>
       <c r="M16" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="N16" s="193">
+        <v>6</v>
+      </c>
+      <c r="O16" s="193">
+        <v>1</v>
+      </c>
+      <c r="P16" s="193">
+        <v>2</v>
+      </c>
+      <c r="Q16" s="193">
+        <v>3</v>
+      </c>
+      <c r="R16" s="193">
         <v>5</v>
       </c>
-      <c r="O16" s="193">
-        <v>1</v>
-      </c>
-      <c r="P16" s="193">
-        <v>1</v>
-      </c>
-      <c r="Q16" s="193">
-        <v>3</v>
-      </c>
-      <c r="R16" s="193">
-        <v>6</v>
-      </c>
       <c r="S16" s="193">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T16" s="193" t="s">
-        <v>481</v>
+        <v>457</v>
       </c>
       <c r="U16" s="193">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="12:21" x14ac:dyDescent="0.25">
@@ -64694,16 +64732,16 @@
         <v>15</v>
       </c>
       <c r="M17" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="N17" s="193">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O17" s="193">
         <v>1</v>
       </c>
       <c r="P17" s="193">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q17" s="193">
         <v>3</v>
@@ -64715,10 +64753,10 @@
         <v>11</v>
       </c>
       <c r="T17" s="193" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="U17" s="193">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="12:21" x14ac:dyDescent="0.25">
@@ -64726,10 +64764,10 @@
         <v>16</v>
       </c>
       <c r="M18" t="s">
-        <v>414</v>
+        <v>429</v>
       </c>
       <c r="N18" s="193">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O18" s="193">
         <v>1</v>
@@ -64738,16 +64776,16 @@
         <v>1</v>
       </c>
       <c r="Q18" s="193">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R18" s="193">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S18" s="193">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T18" s="193" t="s">
-        <v>434</v>
+        <v>460</v>
       </c>
       <c r="U18" s="193">
         <v>4</v>
@@ -64761,7 +64799,7 @@
         <v>415</v>
       </c>
       <c r="N19" s="193">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O19" s="193">
         <v>0</v>
@@ -64770,16 +64808,16 @@
         <v>3</v>
       </c>
       <c r="Q19" s="193">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R19" s="193">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S19" s="193">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T19" s="193" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="U19" s="193">
         <v>3</v>
@@ -64790,28 +64828,28 @@
         <v>18</v>
       </c>
       <c r="M20" t="s">
-        <v>404</v>
+        <v>430</v>
       </c>
       <c r="N20" s="193">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O20" s="193">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P20" s="193">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q20" s="193">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R20" s="193">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S20" s="193">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T20" s="193" t="s">
-        <v>482</v>
+        <v>460</v>
       </c>
       <c r="U20" s="193">
         <v>3</v>
@@ -64822,31 +64860,31 @@
         <v>19</v>
       </c>
       <c r="M21" t="s">
-        <v>421</v>
+        <v>404</v>
       </c>
       <c r="N21" s="193">
         <v>5</v>
       </c>
       <c r="O21" s="193">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P21" s="193">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="193">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R21" s="193">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S21" s="193">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T21" s="193" t="s">
-        <v>460</v>
+        <v>473</v>
       </c>
       <c r="U21" s="193">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="12:21" x14ac:dyDescent="0.25">
@@ -64854,10 +64892,10 @@
         <v>20</v>
       </c>
       <c r="M22" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="N22" s="193">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O22" s="193">
         <v>0</v>
@@ -64866,16 +64904,16 @@
         <v>2</v>
       </c>
       <c r="Q22" s="193">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R22" s="193">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S22" s="193">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T22" s="193" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="U22" s="193">
         <v>2</v>
@@ -64907,13 +64945,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>443</v>
+      </c>
+      <c r="D1" t="s">
         <v>444</v>
       </c>
-      <c r="D1" t="s">
-        <v>445</v>
-      </c>
       <c r="E1" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -64921,221 +64959,203 @@
         <v>350</v>
       </c>
       <c r="B2" t="s">
-        <v>483</v>
-      </c>
-      <c r="C2" s="199">
-        <v>5.9</v>
-      </c>
+        <v>474</v>
+      </c>
+      <c r="C2" s="199"/>
       <c r="D2">
         <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B3" t="s">
-        <v>485</v>
-      </c>
-      <c r="C3" s="199">
-        <v>6.1</v>
-      </c>
-      <c r="D3">
-        <v>90</v>
+        <v>476</v>
+      </c>
+      <c r="C3" s="199"/>
+      <c r="D3" t="s">
+        <v>453</v>
+      </c>
+      <c r="E3" t="s">
+        <v>482</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B4" t="s">
-        <v>451</v>
-      </c>
-      <c r="C4" s="199">
-        <v>7</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="C4" s="199"/>
       <c r="D4">
         <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B5" t="s">
-        <v>457</v>
-      </c>
-      <c r="C5" s="199">
-        <v>6</v>
-      </c>
+        <v>455</v>
+      </c>
+      <c r="C5" s="199"/>
       <c r="D5">
         <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B6" t="s">
+        <v>483</v>
+      </c>
+      <c r="C6" s="199"/>
+      <c r="D6" t="s">
+        <v>453</v>
+      </c>
+      <c r="E6" t="s">
         <v>484</v>
-      </c>
-      <c r="C6" s="199">
-        <v>6.7</v>
-      </c>
-      <c r="D6" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B7" t="s">
-        <v>486</v>
-      </c>
-      <c r="C7" s="199">
-        <v>6.5</v>
-      </c>
+        <v>477</v>
+      </c>
+      <c r="C7" s="199"/>
       <c r="D7">
         <v>90</v>
       </c>
+      <c r="E7" t="s">
+        <v>484</v>
+      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B8" t="s">
-        <v>463</v>
-      </c>
-      <c r="C8" s="199">
-        <v>5.8</v>
-      </c>
+        <v>485</v>
+      </c>
+      <c r="C8" s="199"/>
       <c r="D8" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B9" t="s">
-        <v>452</v>
-      </c>
-      <c r="C9" s="199">
-        <v>6</v>
-      </c>
+        <v>451</v>
+      </c>
+      <c r="C9" s="199"/>
       <c r="D9" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B10" t="s">
-        <v>453</v>
-      </c>
-      <c r="C10" s="199">
-        <v>6.1</v>
-      </c>
-      <c r="D10" t="s">
-        <v>455</v>
+        <v>486</v>
+      </c>
+      <c r="C10" s="199"/>
+      <c r="D10">
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B11" t="s">
-        <v>487</v>
-      </c>
-      <c r="C11" s="199">
-        <v>6.9</v>
-      </c>
-      <c r="D11" t="s">
-        <v>455</v>
+        <v>478</v>
+      </c>
+      <c r="C11" s="199"/>
+      <c r="D11">
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B12" t="s">
-        <v>488</v>
-      </c>
-      <c r="C12" s="199">
-        <v>6.6</v>
-      </c>
-      <c r="D12">
-        <v>90</v>
+        <v>479</v>
+      </c>
+      <c r="C12" s="199"/>
+      <c r="D12" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B13" t="s">
-        <v>458</v>
-      </c>
-      <c r="C13" s="199">
-        <v>6.5</v>
-      </c>
+        <v>475</v>
+      </c>
+      <c r="C13" s="199"/>
       <c r="D13" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B14" t="s">
-        <v>456</v>
-      </c>
-      <c r="C14" s="199">
-        <v>6.1</v>
-      </c>
+        <v>459</v>
+      </c>
+      <c r="C14" s="199"/>
       <c r="D14" t="s">
-        <v>454</v>
+        <v>452</v>
+      </c>
+      <c r="E14" t="s">
+        <v>482</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B15" t="s">
-        <v>477</v>
-      </c>
-      <c r="C15" s="199">
-        <v>6.8</v>
-      </c>
+        <v>469</v>
+      </c>
+      <c r="C15" s="199"/>
       <c r="D15" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B16" t="s">
-        <v>462</v>
-      </c>
-      <c r="C16" s="199">
-        <v>6.5</v>
-      </c>
+        <v>454</v>
+      </c>
+      <c r="C16" s="199"/>
       <c r="D16" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="B17" t="s">
-        <v>476</v>
+        <v>487</v>
       </c>
       <c r="C17" s="199"/>
       <c r="D17" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
   </sheetData>
@@ -65162,24 +65182,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="207" t="s">
+      <c r="A1" s="202" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="324"/>
-      <c r="C1" s="325" t="s">
+      <c r="B1" s="325"/>
+      <c r="C1" s="326" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="210"/>
-      <c r="E1" s="326"/>
-      <c r="H1" s="207" t="s">
+      <c r="D1" s="205"/>
+      <c r="E1" s="327"/>
+      <c r="H1" s="202" t="s">
         <v>47</v>
       </c>
-      <c r="I1" s="324"/>
-      <c r="J1" s="325" t="s">
+      <c r="I1" s="325"/>
+      <c r="J1" s="326" t="s">
         <v>44</v>
       </c>
-      <c r="K1" s="210"/>
-      <c r="L1" s="326"/>
+      <c r="K1" s="205"/>
+      <c r="L1" s="327"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -66159,11 +66179,11 @@
       </c>
       <c r="K30" s="9">
         <f>'Apps &amp; Goals'!T10</f>
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L30" s="14">
         <f>J30/K30</f>
-        <v>0.26332288401253917</v>
+        <v>0.26250000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
@@ -66267,9 +66287,9 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="211"/>
-      <c r="G1" s="211"/>
-      <c r="H1" s="211"/>
+      <c r="F1" s="206"/>
+      <c r="G1" s="206"/>
+      <c r="H1" s="206"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -66293,38 +66313,38 @@
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="5"/>
-      <c r="E2" s="207" t="s">
+      <c r="E2" s="202" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="208"/>
-      <c r="G2" s="209"/>
-      <c r="H2" s="212" t="s">
+      <c r="F2" s="203"/>
+      <c r="G2" s="204"/>
+      <c r="H2" s="207" t="s">
         <v>120</v>
       </c>
-      <c r="I2" s="213"/>
-      <c r="J2" s="214"/>
-      <c r="K2" s="207" t="s">
+      <c r="I2" s="208"/>
+      <c r="J2" s="209"/>
+      <c r="K2" s="202" t="s">
         <v>108</v>
       </c>
-      <c r="L2" s="208"/>
-      <c r="M2" s="209"/>
-      <c r="N2" s="212" t="s">
+      <c r="L2" s="203"/>
+      <c r="M2" s="204"/>
+      <c r="N2" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="O2" s="213"/>
-      <c r="P2" s="214"/>
-      <c r="Q2" s="207" t="s">
+      <c r="O2" s="208"/>
+      <c r="P2" s="209"/>
+      <c r="Q2" s="202" t="s">
         <v>39</v>
       </c>
-      <c r="R2" s="208"/>
-      <c r="S2" s="209"/>
-      <c r="T2" s="210" t="s">
+      <c r="R2" s="203"/>
+      <c r="S2" s="204"/>
+      <c r="T2" s="205" t="s">
         <v>7</v>
       </c>
-      <c r="U2" s="210"/>
-      <c r="V2" s="210"/>
+      <c r="U2" s="205"/>
+      <c r="V2" s="205"/>
       <c r="Z2" s="125">
-        <v>46286</v>
+        <v>46307</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
@@ -66391,7 +66411,7 @@
         <v>395</v>
       </c>
       <c r="W3" s="198" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
@@ -66409,7 +66429,7 @@
       </c>
       <c r="E4" s="6">
         <f>'#'!J6</f>
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F4" s="6">
         <f>'#'!K6</f>
@@ -66469,7 +66489,7 @@
       </c>
       <c r="T4" s="2">
         <f t="shared" ref="T4:V4" si="0">SUM(E4,H4,K4,N4,Q4)</f>
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="U4" s="2">
         <f t="shared" ref="U4" si="1">SUM(F4,I4,L4,O4,R4)</f>
@@ -66667,7 +66687,7 @@
       </c>
       <c r="E7" s="6">
         <f>'#'!J9</f>
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F7" s="6">
         <f>'#'!K9</f>
@@ -66675,7 +66695,7 @@
       </c>
       <c r="G7" s="6">
         <f>'#'!L9</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H7" s="4">
         <f>'#'!V9</f>
@@ -66727,7 +66747,7 @@
       </c>
       <c r="T7" s="2">
         <f t="shared" si="2"/>
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="U7" s="2">
         <f t="shared" si="3"/>
@@ -66735,7 +66755,7 @@
       </c>
       <c r="V7" s="2">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
@@ -66753,7 +66773,7 @@
       </c>
       <c r="E8" s="6">
         <f>'#'!J10</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F8" s="6">
         <f>'#'!K10</f>
@@ -66813,7 +66833,7 @@
       </c>
       <c r="T8" s="2">
         <f t="shared" si="2"/>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="U8" s="2">
         <f t="shared" si="3"/>
@@ -66839,7 +66859,7 @@
       </c>
       <c r="E9" s="6">
         <f>'#'!J11</f>
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F9" s="6">
         <f>'#'!K11</f>
@@ -66899,7 +66919,7 @@
       </c>
       <c r="T9" s="2">
         <f t="shared" si="2"/>
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="U9" s="2">
         <f t="shared" si="3"/>
@@ -66925,7 +66945,7 @@
       </c>
       <c r="E10" s="6">
         <f>'#'!J12</f>
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F10" s="6">
         <f>'#'!K12</f>
@@ -66985,7 +67005,7 @@
       </c>
       <c r="T10" s="2">
         <f t="shared" si="2"/>
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="U10" s="2">
         <f t="shared" si="3"/>
@@ -67011,7 +67031,7 @@
       </c>
       <c r="E11" s="6">
         <f>'#'!J13</f>
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F11" s="6">
         <f>'#'!K13</f>
@@ -67071,7 +67091,7 @@
       </c>
       <c r="T11" s="2">
         <f t="shared" si="2"/>
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="U11" s="2">
         <f t="shared" si="3"/>
@@ -67183,7 +67203,7 @@
       </c>
       <c r="E13" s="6">
         <f>'#'!J15</f>
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F13" s="6">
         <f>'#'!K15</f>
@@ -67243,7 +67263,7 @@
       </c>
       <c r="T13" s="2">
         <f t="shared" si="2"/>
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="U13" s="2">
         <f t="shared" si="3"/>
@@ -67355,7 +67375,7 @@
       </c>
       <c r="E15" s="6">
         <f>'#'!J17</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F15" s="6">
         <f>'#'!K17</f>
@@ -67415,7 +67435,7 @@
       </c>
       <c r="T15" s="2">
         <f t="shared" si="2"/>
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="U15" s="2">
         <f t="shared" si="3"/>
@@ -67437,11 +67457,11 @@
         <v>352</v>
       </c>
       <c r="D16" s="149" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E16" s="6">
         <f>'#'!J18</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F16" s="6">
         <f>'#'!K18</f>
@@ -67501,7 +67521,7 @@
       </c>
       <c r="T16" s="2">
         <f t="shared" ref="T16:T28" si="5">SUM(E16,H16,K16,N16,Q16)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U16" s="2">
         <f t="shared" ref="U16:U28" si="6">SUM(F16,I16,L16,O16,R16)</f>
@@ -67613,7 +67633,7 @@
       </c>
       <c r="E18" s="6">
         <f>'#'!J20</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F18" s="6">
         <f>'#'!K20</f>
@@ -67673,7 +67693,7 @@
       </c>
       <c r="T18" s="2">
         <f t="shared" si="5"/>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U18" s="2">
         <f t="shared" si="6"/>
@@ -67770,7 +67790,7 @@
         <v>2</v>
       </c>
       <c r="W19" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.25">
@@ -67788,7 +67808,7 @@
       </c>
       <c r="E20" s="6">
         <f>'#'!J22</f>
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F20" s="6">
         <f>'#'!K22</f>
@@ -67848,7 +67868,7 @@
       </c>
       <c r="T20" s="2">
         <f t="shared" si="5"/>
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="U20" s="2">
         <f t="shared" si="6"/>
@@ -67874,7 +67894,7 @@
       </c>
       <c r="E21" s="6">
         <f>'#'!J23</f>
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F21" s="6">
         <f>'#'!K23</f>
@@ -67934,7 +67954,7 @@
       </c>
       <c r="T21" s="2">
         <f t="shared" si="5"/>
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="U21" s="2">
         <f t="shared" si="6"/>
@@ -68046,11 +68066,11 @@
       </c>
       <c r="E23" s="6">
         <f>'#'!J25</f>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F23" s="6">
         <f>'#'!K25</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G23" s="6">
         <f>'#'!L25</f>
@@ -68106,11 +68126,11 @@
       </c>
       <c r="T23" s="2">
         <f t="shared" si="5"/>
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="U23" s="2">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V23" s="2">
         <f t="shared" si="7"/>
@@ -68203,7 +68223,7 @@
         <v>0</v>
       </c>
       <c r="W24" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.25">
@@ -68307,11 +68327,11 @@
       </c>
       <c r="E26" s="6">
         <f>'#'!J28</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F26" s="6">
         <f>'#'!K28</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G26" s="6">
         <f>'#'!L28</f>
@@ -68367,11 +68387,11 @@
       </c>
       <c r="T26" s="2">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U26" s="2">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V26" s="2">
         <f t="shared" si="7"/>
@@ -68479,7 +68499,7 @@
       </c>
       <c r="E28" s="6">
         <f>'#'!J30</f>
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F28" s="6">
         <f>'#'!K30</f>
@@ -68487,7 +68507,7 @@
       </c>
       <c r="G28" s="6">
         <f>'#'!L30</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H28" s="4">
         <f>'#'!V30</f>
@@ -68539,7 +68559,7 @@
       </c>
       <c r="T28" s="2">
         <f t="shared" si="5"/>
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="U28" s="2">
         <f t="shared" si="6"/>
@@ -68547,7 +68567,7 @@
       </c>
       <c r="V28" s="2">
         <f t="shared" si="7"/>
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.25">
@@ -68733,7 +68753,7 @@
         <v>353</v>
       </c>
       <c r="D31" s="148" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="E31" s="6">
         <f>'#'!J33</f>
@@ -68894,7 +68914,7 @@
         <v>0</v>
       </c>
       <c r="W32" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="33" spans="1:23" x14ac:dyDescent="0.25">
@@ -68912,7 +68932,7 @@
       </c>
       <c r="E33" s="6">
         <f>'#'!J35</f>
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F33" s="6">
         <f>'#'!K35</f>
@@ -68972,7 +68992,7 @@
       </c>
       <c r="T33" s="2">
         <f t="shared" si="9"/>
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U33" s="2">
         <f t="shared" si="10"/>
@@ -69069,7 +69089,7 @@
         <v>0</v>
       </c>
       <c r="W34" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="35" spans="1:23" x14ac:dyDescent="0.25">
@@ -69506,30 +69526,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="205" t="s">
+      <c r="D2" s="212" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="205"/>
-      <c r="F2" s="206" t="s">
+      <c r="E2" s="212"/>
+      <c r="F2" s="213" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="206"/>
-      <c r="H2" s="205" t="s">
+      <c r="G2" s="213"/>
+      <c r="H2" s="212" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="205"/>
-      <c r="J2" s="206" t="s">
+      <c r="I2" s="212"/>
+      <c r="J2" s="213" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="206"/>
-      <c r="L2" s="205" t="s">
+      <c r="K2" s="213"/>
+      <c r="L2" s="212" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="205"/>
-      <c r="N2" s="210" t="s">
+      <c r="M2" s="212"/>
+      <c r="N2" s="205" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="210"/>
+      <c r="O2" s="205"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -71526,30 +71546,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="205" t="s">
+      <c r="D2" s="212" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="205"/>
-      <c r="F2" s="206" t="s">
+      <c r="E2" s="212"/>
+      <c r="F2" s="213" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="206"/>
-      <c r="H2" s="205" t="s">
+      <c r="G2" s="213"/>
+      <c r="H2" s="212" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="205"/>
-      <c r="J2" s="206" t="s">
+      <c r="I2" s="212"/>
+      <c r="J2" s="213" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="206"/>
-      <c r="L2" s="205" t="s">
+      <c r="K2" s="213"/>
+      <c r="L2" s="212" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="205"/>
-      <c r="N2" s="210" t="s">
+      <c r="M2" s="212"/>
+      <c r="N2" s="205" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="210"/>
+      <c r="O2" s="205"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -73483,30 +73503,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="205" t="s">
+      <c r="D2" s="212" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="205"/>
-      <c r="F2" s="206" t="s">
+      <c r="E2" s="212"/>
+      <c r="F2" s="213" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="206"/>
-      <c r="H2" s="205" t="s">
+      <c r="G2" s="213"/>
+      <c r="H2" s="212" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="205"/>
-      <c r="J2" s="206" t="s">
+      <c r="I2" s="212"/>
+      <c r="J2" s="213" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="206"/>
-      <c r="L2" s="205" t="s">
+      <c r="K2" s="213"/>
+      <c r="L2" s="212" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="205"/>
-      <c r="N2" s="210" t="s">
+      <c r="M2" s="212"/>
+      <c r="N2" s="205" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="210"/>
+      <c r="O2" s="205"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -75531,30 +75551,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="205" t="s">
+      <c r="D2" s="212" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="205"/>
-      <c r="F2" s="206" t="s">
+      <c r="E2" s="212"/>
+      <c r="F2" s="213" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="206"/>
-      <c r="H2" s="205" t="s">
+      <c r="G2" s="213"/>
+      <c r="H2" s="212" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="205"/>
-      <c r="J2" s="206" t="s">
+      <c r="I2" s="212"/>
+      <c r="J2" s="213" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="206"/>
-      <c r="L2" s="205" t="s">
+      <c r="K2" s="213"/>
+      <c r="L2" s="212" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="205"/>
-      <c r="N2" s="210" t="s">
+      <c r="M2" s="212"/>
+      <c r="N2" s="205" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="210"/>
+      <c r="O2" s="205"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -77239,30 +77259,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="205" t="s">
+      <c r="C2" s="212" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="205"/>
-      <c r="E2" s="206" t="s">
+      <c r="D2" s="212"/>
+      <c r="E2" s="213" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="206"/>
-      <c r="G2" s="205" t="s">
+      <c r="F2" s="213"/>
+      <c r="G2" s="212" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="205"/>
-      <c r="I2" s="206" t="s">
+      <c r="H2" s="212"/>
+      <c r="I2" s="213" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="206"/>
-      <c r="K2" s="205" t="s">
+      <c r="J2" s="213"/>
+      <c r="K2" s="212" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="205"/>
-      <c r="M2" s="210" t="s">
+      <c r="L2" s="212"/>
+      <c r="M2" s="205" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="210"/>
+      <c r="N2" s="205"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -79024,30 +79044,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="205" t="s">
+      <c r="C2" s="212" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="205"/>
-      <c r="E2" s="206" t="s">
+      <c r="D2" s="212"/>
+      <c r="E2" s="213" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="206"/>
-      <c r="G2" s="205" t="s">
+      <c r="F2" s="213"/>
+      <c r="G2" s="212" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="205"/>
-      <c r="I2" s="206" t="s">
+      <c r="H2" s="212"/>
+      <c r="I2" s="213" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="206"/>
-      <c r="K2" s="205" t="s">
+      <c r="J2" s="213"/>
+      <c r="K2" s="212" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="205"/>
-      <c r="M2" s="210" t="s">
+      <c r="L2" s="212"/>
+      <c r="M2" s="205" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="210"/>
+      <c r="N2" s="205"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">

--- a/data/arsenal_stats.xlsx
+++ b/data/arsenal_stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bungeltd-my.sharepoint.com/personal/przemyslaw_iskra_bunge_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8660" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F13D3A70-3713-471D-BA9C-0CF41389DE5B}"/>
+  <xr:revisionPtr revIDLastSave="8661" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0DAF3CF0-C3FB-4FDC-AA35-4AF0BAFBADDE}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="799" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="799" firstSheet="1" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="19" state="hidden" r:id="rId1"/>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2277" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2277" uniqueCount="489">
   <si>
     <t>Arsenal FC squad statistics</t>
   </si>
@@ -1544,6 +1544,9 @@
   </si>
   <si>
     <t>Hincapie</t>
+  </si>
+  <si>
+    <t>Lille OSC</t>
   </si>
 </sst>
 </file>
@@ -3049,6 +3052,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3085,6 +3089,15 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3094,32 +3107,14 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="54" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3157,6 +3152,15 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="28" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3164,6 +3168,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="60" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="10" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="37" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="11" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3256,80 +3281,11 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="60" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="10" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="37" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="11" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="54" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3415,6 +3371,54 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3425,7 +3429,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
@@ -6481,7 +6484,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{20595F00-0B75-4A4F-A893-9330259D7299}" type="CELLRANGE">
+                    <a:fld id="{1EECF14B-3885-4F6B-90AF-7109EA3999EC}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6515,7 +6518,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{56043E37-011C-4457-8B49-3C0E8BDF360E}" type="CELLRANGE">
+                    <a:fld id="{55440238-1EA6-449F-95FD-41D6F20F2F2C}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6549,7 +6552,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A06AD215-DA47-41F3-8EC1-ECEA4C77A108}" type="CELLRANGE">
+                    <a:fld id="{DC5EB162-82C8-4FE6-99E2-D1A9EC6ECBD6}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6583,7 +6586,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8B37CCAE-B9CB-46C3-ADB9-526406B7DB32}" type="CELLRANGE">
+                    <a:fld id="{E20E35AB-3D12-46D5-8A5B-D36059947323}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6617,7 +6620,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{020919F7-F801-4709-97A1-8D26A712D9AE}" type="CELLRANGE">
+                    <a:fld id="{8D82C366-00D5-4F7B-BBB0-AAFE50F3E731}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6651,7 +6654,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{FFF2D78D-4DC5-4101-80AB-DB7B4C5966C3}" type="CELLRANGE">
+                    <a:fld id="{E698677A-7B5B-4B4F-AB9D-88BFB8B9DA8C}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6685,7 +6688,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A4E5032B-69B0-4F5C-9B26-312259075FD2}" type="CELLRANGE">
+                    <a:fld id="{ABD7D148-1811-4C35-B163-EAEDEA51CBBE}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6719,7 +6722,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F85034E7-E76F-496E-A6B4-6FB9CB08BFBB}" type="CELLRANGE">
+                    <a:fld id="{5C36AFAD-9C4A-4F19-9D64-1216E85D883A}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6753,7 +6756,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{09CDCC49-A929-4FA6-9AFA-4ECB84B5847B}" type="CELLRANGE">
+                    <a:fld id="{167F2A7B-B394-48AC-A2EA-98AFA254036D}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6787,7 +6790,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{BDEA372C-FBF9-4AAD-94D2-EBAB609A61B9}" type="CELLRANGE">
+                    <a:fld id="{E2093DFE-F9D7-4AD5-A4BE-A3F826B605A9}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6821,7 +6824,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B20D9E29-D58F-43AB-901A-ED9E422FA096}" type="CELLRANGE">
+                    <a:fld id="{24F5BAB3-AA0E-43DD-8716-3EE9E9181131}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6855,7 +6858,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{5AA3BA7B-48DB-4F22-9644-D4D68816E8E3}" type="CELLRANGE">
+                    <a:fld id="{43B2D4D7-96A7-4D83-A4A9-AEDA00B3B488}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6904,7 +6907,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{DA9C5508-EF0B-48BD-91C1-6CAD40FDFF7C}" type="CELLRANGE">
+                    <a:fld id="{33EC7F9C-080C-48A8-9E63-5D3B0EDCB5AB}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr>
                         <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
@@ -6963,7 +6966,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8174E073-8A5C-4E02-88E3-7B2489DC77C1}" type="CELLRANGE">
+                    <a:fld id="{09A250CC-138B-40B4-AFCD-ED0C0C187D0A}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6997,7 +7000,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8A0D8CA5-F683-4E04-9EEA-F8D004088AD9}" type="CELLRANGE">
+                    <a:fld id="{8F698416-DF55-41EC-953E-FE8124265B61}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7031,7 +7034,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{710D97AE-4A50-4CEB-A2C7-89DD376D9EE0}" type="CELLRANGE">
+                    <a:fld id="{FC7E52A3-AB5F-408F-9C7B-F61639121BE0}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7065,7 +7068,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C9C941AC-8B6F-4DFA-9532-00F47C4D15BC}" type="CELLRANGE">
+                    <a:fld id="{C852397F-1368-4D58-9F11-C695055A8B9A}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -14201,30 +14204,30 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
       <c r="B1" s="5"/>
-      <c r="C1" s="212" t="s">
+      <c r="C1" s="213" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="212"/>
-      <c r="E1" s="213" t="s">
+      <c r="D1" s="213"/>
+      <c r="E1" s="214" t="s">
         <v>120</v>
       </c>
-      <c r="F1" s="213"/>
-      <c r="G1" s="212" t="s">
+      <c r="F1" s="214"/>
+      <c r="G1" s="213" t="s">
         <v>108</v>
       </c>
-      <c r="H1" s="212"/>
-      <c r="I1" s="213" t="s">
+      <c r="H1" s="213"/>
+      <c r="I1" s="214" t="s">
         <v>110</v>
       </c>
-      <c r="J1" s="213"/>
-      <c r="K1" s="212" t="s">
+      <c r="J1" s="214"/>
+      <c r="K1" s="213" t="s">
         <v>39</v>
       </c>
-      <c r="L1" s="212"/>
-      <c r="M1" s="210" t="s">
+      <c r="L1" s="213"/>
+      <c r="M1" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="211"/>
+      <c r="N1" s="212"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -15931,30 +15934,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="212" t="s">
+      <c r="C2" s="213" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="212"/>
-      <c r="E2" s="213" t="s">
+      <c r="D2" s="213"/>
+      <c r="E2" s="214" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="213"/>
-      <c r="G2" s="212" t="s">
+      <c r="F2" s="214"/>
+      <c r="G2" s="213" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="212"/>
-      <c r="I2" s="213" t="s">
+      <c r="H2" s="213"/>
+      <c r="I2" s="214" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="213"/>
-      <c r="K2" s="212" t="s">
+      <c r="J2" s="214"/>
+      <c r="K2" s="213" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="212"/>
-      <c r="M2" s="205" t="s">
+      <c r="L2" s="213"/>
+      <c r="M2" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="205"/>
+      <c r="N2" s="206"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -17758,30 +17761,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="212" t="s">
+      <c r="C2" s="213" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="212"/>
-      <c r="E2" s="213" t="s">
+      <c r="D2" s="213"/>
+      <c r="E2" s="214" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="213"/>
-      <c r="G2" s="212" t="s">
+      <c r="F2" s="214"/>
+      <c r="G2" s="213" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="212"/>
-      <c r="I2" s="213" t="s">
+      <c r="H2" s="213"/>
+      <c r="I2" s="214" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="213"/>
-      <c r="K2" s="212" t="s">
+      <c r="J2" s="214"/>
+      <c r="K2" s="213" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="212"/>
-      <c r="M2" s="205" t="s">
+      <c r="L2" s="213"/>
+      <c r="M2" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="205"/>
+      <c r="N2" s="206"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -19448,30 +19451,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="212" t="s">
+      <c r="C2" s="213" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="212"/>
-      <c r="E2" s="213" t="s">
+      <c r="D2" s="213"/>
+      <c r="E2" s="214" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="213"/>
-      <c r="G2" s="212" t="s">
+      <c r="F2" s="214"/>
+      <c r="G2" s="213" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="212"/>
-      <c r="I2" s="213" t="s">
+      <c r="H2" s="213"/>
+      <c r="I2" s="214" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="213"/>
-      <c r="K2" s="212" t="s">
+      <c r="J2" s="214"/>
+      <c r="K2" s="213" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="212"/>
-      <c r="M2" s="205" t="s">
+      <c r="L2" s="213"/>
+      <c r="M2" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="205"/>
+      <c r="N2" s="206"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -21274,30 +21277,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="212" t="s">
+      <c r="C2" s="213" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="212"/>
-      <c r="E2" s="213" t="s">
+      <c r="D2" s="213"/>
+      <c r="E2" s="214" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="213"/>
-      <c r="G2" s="212" t="s">
+      <c r="F2" s="214"/>
+      <c r="G2" s="213" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="212"/>
-      <c r="I2" s="213" t="s">
+      <c r="H2" s="213"/>
+      <c r="I2" s="214" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="213"/>
-      <c r="K2" s="212" t="s">
+      <c r="J2" s="214"/>
+      <c r="K2" s="213" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="212"/>
-      <c r="M2" s="205" t="s">
+      <c r="L2" s="213"/>
+      <c r="M2" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="205"/>
+      <c r="N2" s="206"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -23146,36 +23149,36 @@
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="202" t="s">
+      <c r="C2" s="203" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="203"/>
-      <c r="E2" s="204"/>
-      <c r="F2" s="207" t="s">
+      <c r="D2" s="204"/>
+      <c r="E2" s="205"/>
+      <c r="F2" s="208" t="s">
         <v>120</v>
       </c>
-      <c r="G2" s="208"/>
-      <c r="H2" s="209"/>
-      <c r="I2" s="202" t="s">
+      <c r="G2" s="209"/>
+      <c r="H2" s="210"/>
+      <c r="I2" s="203" t="s">
         <v>108</v>
       </c>
-      <c r="J2" s="203"/>
-      <c r="K2" s="204"/>
-      <c r="L2" s="207" t="s">
+      <c r="J2" s="204"/>
+      <c r="K2" s="205"/>
+      <c r="L2" s="208" t="s">
         <v>110</v>
       </c>
-      <c r="M2" s="208"/>
-      <c r="N2" s="209"/>
-      <c r="O2" s="202" t="s">
+      <c r="M2" s="209"/>
+      <c r="N2" s="210"/>
+      <c r="O2" s="203" t="s">
         <v>39</v>
       </c>
-      <c r="P2" s="203"/>
-      <c r="Q2" s="204"/>
-      <c r="R2" s="205" t="s">
+      <c r="P2" s="204"/>
+      <c r="Q2" s="205"/>
+      <c r="R2" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="S2" s="205"/>
-      <c r="T2" s="205"/>
+      <c r="S2" s="206"/>
+      <c r="T2" s="206"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -26114,36 +26117,36 @@
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
       <c r="D1" s="5"/>
-      <c r="E1" s="202" t="s">
+      <c r="E1" s="203" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="203"/>
-      <c r="G1" s="204"/>
-      <c r="H1" s="207" t="s">
+      <c r="F1" s="204"/>
+      <c r="G1" s="205"/>
+      <c r="H1" s="208" t="s">
         <v>120</v>
       </c>
-      <c r="I1" s="208"/>
-      <c r="J1" s="209"/>
-      <c r="K1" s="202" t="s">
+      <c r="I1" s="209"/>
+      <c r="J1" s="210"/>
+      <c r="K1" s="203" t="s">
         <v>108</v>
       </c>
-      <c r="L1" s="203"/>
-      <c r="M1" s="204"/>
-      <c r="N1" s="207" t="s">
+      <c r="L1" s="204"/>
+      <c r="M1" s="205"/>
+      <c r="N1" s="208" t="s">
         <v>110</v>
       </c>
-      <c r="O1" s="208"/>
-      <c r="P1" s="209"/>
-      <c r="Q1" s="202" t="s">
+      <c r="O1" s="209"/>
+      <c r="P1" s="210"/>
+      <c r="Q1" s="203" t="s">
         <v>39</v>
       </c>
-      <c r="R1" s="203"/>
-      <c r="S1" s="204"/>
-      <c r="T1" s="205" t="s">
+      <c r="R1" s="204"/>
+      <c r="S1" s="205"/>
+      <c r="T1" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="U1" s="205"/>
-      <c r="V1" s="205"/>
+      <c r="U1" s="206"/>
+      <c r="V1" s="206"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -37717,399 +37720,399 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F1" s="217">
-        <v>1</v>
-      </c>
-      <c r="G1" s="218"/>
-      <c r="H1" s="219"/>
-      <c r="I1" s="217">
+      <c r="F1" s="215">
+        <v>1</v>
+      </c>
+      <c r="G1" s="216"/>
+      <c r="H1" s="217"/>
+      <c r="I1" s="215">
         <v>2</v>
       </c>
-      <c r="J1" s="218"/>
-      <c r="K1" s="219"/>
-      <c r="L1" s="217">
-        <v>3</v>
-      </c>
-      <c r="M1" s="218"/>
-      <c r="N1" s="219"/>
-      <c r="O1" s="217">
+      <c r="J1" s="216"/>
+      <c r="K1" s="217"/>
+      <c r="L1" s="215">
+        <v>3</v>
+      </c>
+      <c r="M1" s="216"/>
+      <c r="N1" s="217"/>
+      <c r="O1" s="215">
         <v>4</v>
       </c>
-      <c r="P1" s="218"/>
-      <c r="Q1" s="219"/>
-      <c r="R1" s="217">
+      <c r="P1" s="216"/>
+      <c r="Q1" s="217"/>
+      <c r="R1" s="215">
         <v>5</v>
       </c>
-      <c r="S1" s="218"/>
-      <c r="T1" s="219"/>
-      <c r="U1" s="217">
+      <c r="S1" s="216"/>
+      <c r="T1" s="217"/>
+      <c r="U1" s="215">
         <v>6</v>
       </c>
-      <c r="V1" s="218"/>
-      <c r="W1" s="219"/>
-      <c r="X1" s="217">
+      <c r="V1" s="216"/>
+      <c r="W1" s="217"/>
+      <c r="X1" s="215">
         <v>7</v>
       </c>
-      <c r="Y1" s="218"/>
-      <c r="Z1" s="219"/>
-      <c r="AA1" s="217">
+      <c r="Y1" s="216"/>
+      <c r="Z1" s="217"/>
+      <c r="AA1" s="215">
         <v>8</v>
       </c>
-      <c r="AB1" s="218"/>
-      <c r="AC1" s="219"/>
-      <c r="AD1" s="217">
+      <c r="AB1" s="216"/>
+      <c r="AC1" s="217"/>
+      <c r="AD1" s="215">
         <v>9</v>
       </c>
-      <c r="AE1" s="218"/>
-      <c r="AF1" s="219"/>
-      <c r="AG1" s="217">
+      <c r="AE1" s="216"/>
+      <c r="AF1" s="217"/>
+      <c r="AG1" s="215">
         <v>10</v>
       </c>
-      <c r="AH1" s="218"/>
-      <c r="AI1" s="219"/>
-      <c r="AJ1" s="217">
+      <c r="AH1" s="216"/>
+      <c r="AI1" s="217"/>
+      <c r="AJ1" s="215">
         <v>11</v>
       </c>
-      <c r="AK1" s="218"/>
-      <c r="AL1" s="219"/>
-      <c r="AM1" s="217">
+      <c r="AK1" s="216"/>
+      <c r="AL1" s="217"/>
+      <c r="AM1" s="215">
         <v>12</v>
       </c>
-      <c r="AN1" s="218"/>
-      <c r="AO1" s="219"/>
-      <c r="AP1" s="217">
+      <c r="AN1" s="216"/>
+      <c r="AO1" s="217"/>
+      <c r="AP1" s="215">
         <v>13</v>
       </c>
-      <c r="AQ1" s="218"/>
-      <c r="AR1" s="219"/>
-      <c r="AS1" s="217">
+      <c r="AQ1" s="216"/>
+      <c r="AR1" s="217"/>
+      <c r="AS1" s="215">
         <v>14</v>
       </c>
-      <c r="AT1" s="218"/>
-      <c r="AU1" s="219"/>
-      <c r="AV1" s="217">
+      <c r="AT1" s="216"/>
+      <c r="AU1" s="217"/>
+      <c r="AV1" s="215">
         <v>15</v>
       </c>
-      <c r="AW1" s="218"/>
-      <c r="AX1" s="219"/>
-      <c r="AY1" s="217">
+      <c r="AW1" s="216"/>
+      <c r="AX1" s="217"/>
+      <c r="AY1" s="215">
         <v>16</v>
       </c>
-      <c r="AZ1" s="218"/>
-      <c r="BA1" s="219"/>
-      <c r="BB1" s="217">
+      <c r="AZ1" s="216"/>
+      <c r="BA1" s="217"/>
+      <c r="BB1" s="215">
         <v>17</v>
       </c>
-      <c r="BC1" s="218"/>
-      <c r="BD1" s="219"/>
-      <c r="BE1" s="217">
+      <c r="BC1" s="216"/>
+      <c r="BD1" s="217"/>
+      <c r="BE1" s="215">
         <v>18</v>
       </c>
-      <c r="BF1" s="218"/>
-      <c r="BG1" s="219"/>
-      <c r="BH1" s="217">
+      <c r="BF1" s="216"/>
+      <c r="BG1" s="217"/>
+      <c r="BH1" s="215">
         <v>19</v>
       </c>
-      <c r="BI1" s="218"/>
-      <c r="BJ1" s="219"/>
-      <c r="BK1" s="217">
+      <c r="BI1" s="216"/>
+      <c r="BJ1" s="217"/>
+      <c r="BK1" s="215">
         <v>20</v>
       </c>
-      <c r="BL1" s="218"/>
-      <c r="BM1" s="219"/>
-      <c r="BN1" s="217">
+      <c r="BL1" s="216"/>
+      <c r="BM1" s="217"/>
+      <c r="BN1" s="215">
         <v>21</v>
       </c>
-      <c r="BO1" s="218"/>
-      <c r="BP1" s="219"/>
-      <c r="BQ1" s="217">
+      <c r="BO1" s="216"/>
+      <c r="BP1" s="217"/>
+      <c r="BQ1" s="215">
         <v>22</v>
       </c>
-      <c r="BR1" s="218"/>
-      <c r="BS1" s="219"/>
-      <c r="BT1" s="217">
+      <c r="BR1" s="216"/>
+      <c r="BS1" s="217"/>
+      <c r="BT1" s="215">
         <v>23</v>
       </c>
-      <c r="BU1" s="218"/>
-      <c r="BV1" s="219"/>
-      <c r="BW1" s="217">
+      <c r="BU1" s="216"/>
+      <c r="BV1" s="217"/>
+      <c r="BW1" s="215">
         <v>24</v>
       </c>
-      <c r="BX1" s="218"/>
-      <c r="BY1" s="219"/>
-      <c r="BZ1" s="217">
+      <c r="BX1" s="216"/>
+      <c r="BY1" s="217"/>
+      <c r="BZ1" s="215">
         <v>25</v>
       </c>
-      <c r="CA1" s="218"/>
-      <c r="CB1" s="219"/>
-      <c r="CC1" s="217">
+      <c r="CA1" s="216"/>
+      <c r="CB1" s="217"/>
+      <c r="CC1" s="215">
         <v>26</v>
       </c>
-      <c r="CD1" s="218"/>
-      <c r="CE1" s="219"/>
-      <c r="CF1" s="217">
+      <c r="CD1" s="216"/>
+      <c r="CE1" s="217"/>
+      <c r="CF1" s="215">
         <v>27</v>
       </c>
-      <c r="CG1" s="218"/>
-      <c r="CH1" s="219"/>
-      <c r="CI1" s="217">
+      <c r="CG1" s="216"/>
+      <c r="CH1" s="217"/>
+      <c r="CI1" s="215">
         <v>28</v>
       </c>
-      <c r="CJ1" s="218"/>
-      <c r="CK1" s="219"/>
-      <c r="CL1" s="217">
+      <c r="CJ1" s="216"/>
+      <c r="CK1" s="217"/>
+      <c r="CL1" s="215">
         <v>29</v>
       </c>
-      <c r="CM1" s="218"/>
-      <c r="CN1" s="219"/>
-      <c r="CO1" s="217">
+      <c r="CM1" s="216"/>
+      <c r="CN1" s="217"/>
+      <c r="CO1" s="215">
         <v>30</v>
       </c>
-      <c r="CP1" s="218"/>
-      <c r="CQ1" s="219"/>
-      <c r="CR1" s="217">
+      <c r="CP1" s="216"/>
+      <c r="CQ1" s="217"/>
+      <c r="CR1" s="215">
         <v>31</v>
       </c>
-      <c r="CS1" s="218"/>
-      <c r="CT1" s="219"/>
-      <c r="CU1" s="217">
+      <c r="CS1" s="216"/>
+      <c r="CT1" s="217"/>
+      <c r="CU1" s="215">
         <v>32</v>
       </c>
-      <c r="CV1" s="218"/>
-      <c r="CW1" s="219"/>
-      <c r="CX1" s="217">
+      <c r="CV1" s="216"/>
+      <c r="CW1" s="217"/>
+      <c r="CX1" s="215">
         <v>33</v>
       </c>
-      <c r="CY1" s="218"/>
-      <c r="CZ1" s="219"/>
-      <c r="DA1" s="217">
+      <c r="CY1" s="216"/>
+      <c r="CZ1" s="217"/>
+      <c r="DA1" s="215">
         <v>34</v>
       </c>
-      <c r="DB1" s="218"/>
-      <c r="DC1" s="219"/>
-      <c r="DD1" s="217">
+      <c r="DB1" s="216"/>
+      <c r="DC1" s="217"/>
+      <c r="DD1" s="215">
         <v>35</v>
       </c>
-      <c r="DE1" s="218"/>
-      <c r="DF1" s="219"/>
-      <c r="DG1" s="217">
+      <c r="DE1" s="216"/>
+      <c r="DF1" s="217"/>
+      <c r="DG1" s="215">
         <v>36</v>
       </c>
-      <c r="DH1" s="218"/>
-      <c r="DI1" s="219"/>
-      <c r="DJ1" s="217">
+      <c r="DH1" s="216"/>
+      <c r="DI1" s="217"/>
+      <c r="DJ1" s="215">
         <v>37</v>
       </c>
-      <c r="DK1" s="218"/>
-      <c r="DL1" s="219"/>
-      <c r="DM1" s="217">
+      <c r="DK1" s="216"/>
+      <c r="DL1" s="217"/>
+      <c r="DM1" s="215">
         <v>38</v>
       </c>
-      <c r="DN1" s="218"/>
-      <c r="DO1" s="219"/>
+      <c r="DN1" s="216"/>
+      <c r="DO1" s="217"/>
     </row>
     <row r="2" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="220" t="s">
+      <c r="C2" s="221" t="s">
         <v>396</v>
       </c>
-      <c r="D2" s="220" t="s">
+      <c r="D2" s="221" t="s">
         <v>397</v>
       </c>
-      <c r="E2" s="220" t="s">
+      <c r="E2" s="221" t="s">
         <v>398</v>
       </c>
-      <c r="F2" s="214" t="s">
+      <c r="F2" s="218" t="s">
         <v>346</v>
       </c>
-      <c r="G2" s="215"/>
-      <c r="H2" s="216"/>
-      <c r="I2" s="214" t="s">
+      <c r="G2" s="219"/>
+      <c r="H2" s="220"/>
+      <c r="I2" s="218" t="s">
         <v>331</v>
       </c>
-      <c r="J2" s="215"/>
-      <c r="K2" s="216"/>
-      <c r="L2" s="214" t="s">
+      <c r="J2" s="219"/>
+      <c r="K2" s="220"/>
+      <c r="L2" s="218" t="s">
         <v>330</v>
       </c>
-      <c r="M2" s="215"/>
-      <c r="N2" s="216"/>
-      <c r="O2" s="214" t="s">
+      <c r="M2" s="219"/>
+      <c r="N2" s="220"/>
+      <c r="O2" s="218" t="s">
         <v>328</v>
       </c>
-      <c r="P2" s="215"/>
-      <c r="Q2" s="216"/>
-      <c r="R2" s="214" t="s">
+      <c r="P2" s="219"/>
+      <c r="Q2" s="220"/>
+      <c r="R2" s="218" t="s">
         <v>335</v>
       </c>
-      <c r="S2" s="215"/>
-      <c r="T2" s="216"/>
-      <c r="U2" s="214" t="s">
+      <c r="S2" s="219"/>
+      <c r="T2" s="220"/>
+      <c r="U2" s="218" t="s">
         <v>320</v>
       </c>
-      <c r="V2" s="215"/>
-      <c r="W2" s="216"/>
-      <c r="X2" s="214" t="s">
+      <c r="V2" s="219"/>
+      <c r="W2" s="220"/>
+      <c r="X2" s="218" t="s">
         <v>337</v>
       </c>
-      <c r="Y2" s="215"/>
-      <c r="Z2" s="216"/>
-      <c r="AA2" s="214" t="s">
+      <c r="Y2" s="219"/>
+      <c r="Z2" s="220"/>
+      <c r="AA2" s="218" t="s">
         <v>334</v>
       </c>
-      <c r="AB2" s="215"/>
-      <c r="AC2" s="216"/>
-      <c r="AD2" s="214" t="s">
+      <c r="AB2" s="219"/>
+      <c r="AC2" s="220"/>
+      <c r="AD2" s="218" t="s">
         <v>321</v>
       </c>
-      <c r="AE2" s="215"/>
-      <c r="AF2" s="216"/>
-      <c r="AG2" s="214" t="s">
+      <c r="AE2" s="219"/>
+      <c r="AF2" s="220"/>
+      <c r="AG2" s="218" t="s">
         <v>347</v>
       </c>
-      <c r="AH2" s="215"/>
-      <c r="AI2" s="216"/>
-      <c r="AJ2" s="214" t="s">
+      <c r="AH2" s="219"/>
+      <c r="AI2" s="220"/>
+      <c r="AJ2" s="218" t="s">
         <v>324</v>
       </c>
-      <c r="AK2" s="215"/>
-      <c r="AL2" s="216"/>
-      <c r="AM2" s="214" t="s">
+      <c r="AK2" s="219"/>
+      <c r="AL2" s="220"/>
+      <c r="AM2" s="218" t="s">
         <v>323</v>
       </c>
-      <c r="AN2" s="215"/>
-      <c r="AO2" s="216"/>
-      <c r="AP2" s="214" t="s">
+      <c r="AN2" s="219"/>
+      <c r="AO2" s="220"/>
+      <c r="AP2" s="218" t="s">
         <v>332</v>
       </c>
-      <c r="AQ2" s="215"/>
-      <c r="AR2" s="216"/>
-      <c r="AS2" s="214" t="s">
+      <c r="AQ2" s="219"/>
+      <c r="AR2" s="220"/>
+      <c r="AS2" s="218" t="s">
         <v>329</v>
       </c>
-      <c r="AT2" s="215"/>
-      <c r="AU2" s="216"/>
-      <c r="AV2" s="214" t="s">
+      <c r="AT2" s="219"/>
+      <c r="AU2" s="220"/>
+      <c r="AV2" s="218" t="s">
         <v>336</v>
       </c>
-      <c r="AW2" s="215"/>
-      <c r="AX2" s="216"/>
-      <c r="AY2" s="214" t="s">
+      <c r="AW2" s="219"/>
+      <c r="AX2" s="220"/>
+      <c r="AY2" s="218" t="s">
         <v>305</v>
       </c>
-      <c r="AZ2" s="215"/>
-      <c r="BA2" s="216"/>
-      <c r="BB2" s="214" t="s">
+      <c r="AZ2" s="219"/>
+      <c r="BA2" s="220"/>
+      <c r="BB2" s="218" t="s">
         <v>326</v>
       </c>
-      <c r="BC2" s="215"/>
-      <c r="BD2" s="216"/>
-      <c r="BE2" s="214" t="s">
+      <c r="BC2" s="219"/>
+      <c r="BD2" s="220"/>
+      <c r="BE2" s="218" t="s">
         <v>325</v>
       </c>
-      <c r="BF2" s="215"/>
-      <c r="BG2" s="216"/>
-      <c r="BH2" s="214" t="s">
+      <c r="BF2" s="219"/>
+      <c r="BG2" s="220"/>
+      <c r="BH2" s="218" t="s">
         <v>348</v>
       </c>
-      <c r="BI2" s="215"/>
-      <c r="BJ2" s="216"/>
-      <c r="BK2" s="214" t="s">
+      <c r="BI2" s="219"/>
+      <c r="BJ2" s="220"/>
+      <c r="BK2" s="218" t="s">
         <v>332</v>
       </c>
-      <c r="BL2" s="215"/>
-      <c r="BM2" s="216"/>
-      <c r="BN2" s="214" t="s">
+      <c r="BL2" s="219"/>
+      <c r="BM2" s="220"/>
+      <c r="BN2" s="218" t="s">
         <v>347</v>
       </c>
-      <c r="BO2" s="215"/>
-      <c r="BP2" s="216"/>
-      <c r="BQ2" s="214" t="s">
+      <c r="BO2" s="219"/>
+      <c r="BP2" s="220"/>
+      <c r="BQ2" s="218" t="s">
         <v>324</v>
       </c>
-      <c r="BR2" s="215"/>
-      <c r="BS2" s="216"/>
-      <c r="BT2" s="214" t="s">
+      <c r="BR2" s="219"/>
+      <c r="BS2" s="220"/>
+      <c r="BT2" s="218" t="s">
         <v>323</v>
       </c>
-      <c r="BU2" s="215"/>
-      <c r="BV2" s="216"/>
-      <c r="BW2" s="214" t="s">
+      <c r="BU2" s="219"/>
+      <c r="BV2" s="220"/>
+      <c r="BW2" s="218" t="s">
         <v>321</v>
       </c>
-      <c r="BX2" s="215"/>
-      <c r="BY2" s="216"/>
-      <c r="BZ2" s="214" t="s">
+      <c r="BX2" s="219"/>
+      <c r="BY2" s="220"/>
+      <c r="BZ2" s="218" t="s">
         <v>348</v>
       </c>
-      <c r="CA2" s="215"/>
-      <c r="CB2" s="216"/>
-      <c r="CC2" s="214" t="s">
+      <c r="CA2" s="219"/>
+      <c r="CB2" s="220"/>
+      <c r="CC2" s="218" t="s">
         <v>325</v>
       </c>
-      <c r="CD2" s="215"/>
-      <c r="CE2" s="216"/>
-      <c r="CF2" s="214" t="s">
+      <c r="CD2" s="219"/>
+      <c r="CE2" s="220"/>
+      <c r="CF2" s="218" t="s">
         <v>305</v>
       </c>
-      <c r="CG2" s="215"/>
-      <c r="CH2" s="216"/>
-      <c r="CI2" s="214" t="s">
+      <c r="CG2" s="219"/>
+      <c r="CH2" s="220"/>
+      <c r="CI2" s="218" t="s">
         <v>326</v>
       </c>
-      <c r="CJ2" s="215"/>
-      <c r="CK2" s="216"/>
-      <c r="CL2" s="214" t="s">
+      <c r="CJ2" s="219"/>
+      <c r="CK2" s="220"/>
+      <c r="CL2" s="218" t="s">
         <v>330</v>
       </c>
-      <c r="CM2" s="215"/>
-      <c r="CN2" s="216"/>
-      <c r="CO2" s="214" t="s">
+      <c r="CM2" s="219"/>
+      <c r="CN2" s="220"/>
+      <c r="CO2" s="218" t="s">
         <v>328</v>
       </c>
-      <c r="CP2" s="215"/>
-      <c r="CQ2" s="216"/>
-      <c r="CR2" s="214" t="s">
+      <c r="CP2" s="219"/>
+      <c r="CQ2" s="220"/>
+      <c r="CR2" s="218" t="s">
         <v>346</v>
       </c>
-      <c r="CS2" s="215"/>
-      <c r="CT2" s="216"/>
-      <c r="CU2" s="214" t="s">
+      <c r="CS2" s="219"/>
+      <c r="CT2" s="220"/>
+      <c r="CU2" s="218" t="s">
         <v>331</v>
       </c>
-      <c r="CV2" s="215"/>
-      <c r="CW2" s="216"/>
-      <c r="CX2" s="214" t="s">
+      <c r="CV2" s="219"/>
+      <c r="CW2" s="220"/>
+      <c r="CX2" s="218" t="s">
         <v>336</v>
       </c>
-      <c r="CY2" s="215"/>
-      <c r="CZ2" s="216"/>
-      <c r="DA2" s="214" t="s">
+      <c r="CY2" s="219"/>
+      <c r="CZ2" s="220"/>
+      <c r="DA2" s="218" t="s">
         <v>329</v>
       </c>
-      <c r="DB2" s="215"/>
-      <c r="DC2" s="216"/>
-      <c r="DD2" s="214" t="s">
+      <c r="DB2" s="219"/>
+      <c r="DC2" s="220"/>
+      <c r="DD2" s="218" t="s">
         <v>320</v>
       </c>
-      <c r="DE2" s="215"/>
-      <c r="DF2" s="216"/>
-      <c r="DG2" s="214" t="s">
+      <c r="DE2" s="219"/>
+      <c r="DF2" s="220"/>
+      <c r="DG2" s="218" t="s">
         <v>337</v>
       </c>
-      <c r="DH2" s="215"/>
-      <c r="DI2" s="216"/>
-      <c r="DJ2" s="214" t="s">
+      <c r="DH2" s="219"/>
+      <c r="DI2" s="220"/>
+      <c r="DJ2" s="218" t="s">
         <v>334</v>
       </c>
-      <c r="DK2" s="215"/>
-      <c r="DL2" s="216"/>
-      <c r="DM2" s="214" t="s">
+      <c r="DK2" s="219"/>
+      <c r="DL2" s="220"/>
+      <c r="DM2" s="218" t="s">
         <v>335</v>
       </c>
-      <c r="DN2" s="215"/>
-      <c r="DO2" s="216"/>
+      <c r="DN2" s="219"/>
+      <c r="DO2" s="220"/>
     </row>
     <row r="3" spans="1:119" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -38118,8 +38121,8 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="221"/>
-      <c r="D3" s="221"/>
+      <c r="C3" s="223"/>
+      <c r="D3" s="223"/>
       <c r="E3" s="222"/>
       <c r="F3" s="160" t="s">
         <v>393</v>
@@ -43847,69 +43850,6 @@
     </row>
   </sheetData>
   <mergeCells count="79">
-    <mergeCell ref="DM1:DO1"/>
-    <mergeCell ref="DM2:DO2"/>
-    <mergeCell ref="DA1:DC1"/>
-    <mergeCell ref="DA2:DC2"/>
-    <mergeCell ref="DD1:DF1"/>
-    <mergeCell ref="DD2:DF2"/>
-    <mergeCell ref="DG1:DI1"/>
-    <mergeCell ref="DG2:DI2"/>
-    <mergeCell ref="CU1:CW1"/>
-    <mergeCell ref="CU2:CW2"/>
-    <mergeCell ref="CX1:CZ1"/>
-    <mergeCell ref="CX2:CZ2"/>
-    <mergeCell ref="DJ1:DL1"/>
-    <mergeCell ref="DJ2:DL2"/>
-    <mergeCell ref="CL1:CN1"/>
-    <mergeCell ref="CL2:CN2"/>
-    <mergeCell ref="CO1:CQ1"/>
-    <mergeCell ref="CO2:CQ2"/>
-    <mergeCell ref="CR1:CT1"/>
-    <mergeCell ref="CR2:CT2"/>
-    <mergeCell ref="CC1:CE1"/>
-    <mergeCell ref="CC2:CE2"/>
-    <mergeCell ref="CF1:CH1"/>
-    <mergeCell ref="CF2:CH2"/>
-    <mergeCell ref="CI1:CK1"/>
-    <mergeCell ref="CI2:CK2"/>
-    <mergeCell ref="BT1:BV1"/>
-    <mergeCell ref="BT2:BV2"/>
-    <mergeCell ref="BW1:BY1"/>
-    <mergeCell ref="BW2:BY2"/>
-    <mergeCell ref="BZ1:CB1"/>
-    <mergeCell ref="BZ2:CB2"/>
-    <mergeCell ref="BK1:BM1"/>
-    <mergeCell ref="BK2:BM2"/>
-    <mergeCell ref="BN1:BP1"/>
-    <mergeCell ref="BN2:BP2"/>
-    <mergeCell ref="BQ1:BS1"/>
-    <mergeCell ref="BQ2:BS2"/>
-    <mergeCell ref="AS1:AU1"/>
-    <mergeCell ref="AS2:AU2"/>
-    <mergeCell ref="AV1:AX1"/>
-    <mergeCell ref="AV2:AX2"/>
-    <mergeCell ref="BH1:BJ1"/>
-    <mergeCell ref="BH2:BJ2"/>
-    <mergeCell ref="AY2:BA2"/>
-    <mergeCell ref="BB2:BD2"/>
-    <mergeCell ref="BE2:BG2"/>
-    <mergeCell ref="AJ1:AL1"/>
-    <mergeCell ref="AJ2:AL2"/>
-    <mergeCell ref="AM1:AO1"/>
-    <mergeCell ref="AM2:AO2"/>
-    <mergeCell ref="AP2:AR2"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
     <mergeCell ref="AD2:AF2"/>
     <mergeCell ref="AG2:AI2"/>
     <mergeCell ref="BB1:BD1"/>
@@ -43926,6 +43866,69 @@
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="X1:Z1"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="AJ1:AL1"/>
+    <mergeCell ref="AJ2:AL2"/>
+    <mergeCell ref="AM1:AO1"/>
+    <mergeCell ref="AM2:AO2"/>
+    <mergeCell ref="AP2:AR2"/>
+    <mergeCell ref="AS1:AU1"/>
+    <mergeCell ref="AS2:AU2"/>
+    <mergeCell ref="AV1:AX1"/>
+    <mergeCell ref="AV2:AX2"/>
+    <mergeCell ref="BH1:BJ1"/>
+    <mergeCell ref="BH2:BJ2"/>
+    <mergeCell ref="AY2:BA2"/>
+    <mergeCell ref="BB2:BD2"/>
+    <mergeCell ref="BE2:BG2"/>
+    <mergeCell ref="BK1:BM1"/>
+    <mergeCell ref="BK2:BM2"/>
+    <mergeCell ref="BN1:BP1"/>
+    <mergeCell ref="BN2:BP2"/>
+    <mergeCell ref="BQ1:BS1"/>
+    <mergeCell ref="BQ2:BS2"/>
+    <mergeCell ref="BT1:BV1"/>
+    <mergeCell ref="BT2:BV2"/>
+    <mergeCell ref="BW1:BY1"/>
+    <mergeCell ref="BW2:BY2"/>
+    <mergeCell ref="BZ1:CB1"/>
+    <mergeCell ref="BZ2:CB2"/>
+    <mergeCell ref="CC1:CE1"/>
+    <mergeCell ref="CC2:CE2"/>
+    <mergeCell ref="CF1:CH1"/>
+    <mergeCell ref="CF2:CH2"/>
+    <mergeCell ref="CI1:CK1"/>
+    <mergeCell ref="CI2:CK2"/>
+    <mergeCell ref="CL1:CN1"/>
+    <mergeCell ref="CL2:CN2"/>
+    <mergeCell ref="CO1:CQ1"/>
+    <mergeCell ref="CO2:CQ2"/>
+    <mergeCell ref="CR1:CT1"/>
+    <mergeCell ref="CR2:CT2"/>
+    <mergeCell ref="CU1:CW1"/>
+    <mergeCell ref="CU2:CW2"/>
+    <mergeCell ref="CX1:CZ1"/>
+    <mergeCell ref="CX2:CZ2"/>
+    <mergeCell ref="DJ1:DL1"/>
+    <mergeCell ref="DJ2:DL2"/>
+    <mergeCell ref="DM1:DO1"/>
+    <mergeCell ref="DM2:DO2"/>
+    <mergeCell ref="DA1:DC1"/>
+    <mergeCell ref="DA2:DC2"/>
+    <mergeCell ref="DD1:DF1"/>
+    <mergeCell ref="DD2:DF2"/>
+    <mergeCell ref="DG1:DI1"/>
+    <mergeCell ref="DG2:DI2"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:DO38">
     <cfRule type="cellIs" dxfId="18" priority="1" operator="between">
@@ -43961,138 +43964,138 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="235" t="s">
+      <c r="C1" s="233" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="235" t="s">
+      <c r="D1" s="233" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="235" t="s">
+      <c r="E1" s="233" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="226" t="s">
+      <c r="F1" s="224" t="s">
         <v>302</v>
       </c>
-      <c r="G1" s="227"/>
-      <c r="H1" s="227"/>
-      <c r="I1" s="227"/>
-      <c r="J1" s="227"/>
-      <c r="K1" s="227"/>
-      <c r="L1" s="227"/>
-      <c r="M1" s="227"/>
-      <c r="N1" s="227"/>
-      <c r="O1" s="227"/>
-      <c r="P1" s="227"/>
-      <c r="Q1" s="227"/>
-      <c r="R1" s="227"/>
-      <c r="S1" s="227"/>
-      <c r="T1" s="227"/>
-      <c r="U1" s="227"/>
-      <c r="V1" s="227"/>
-      <c r="W1" s="227"/>
-      <c r="X1" s="227"/>
-      <c r="Y1" s="227"/>
-      <c r="Z1" s="227"/>
-      <c r="AA1" s="227"/>
-      <c r="AB1" s="227"/>
-      <c r="AC1" s="228"/>
-      <c r="AD1" s="238" t="s">
+      <c r="G1" s="225"/>
+      <c r="H1" s="225"/>
+      <c r="I1" s="225"/>
+      <c r="J1" s="225"/>
+      <c r="K1" s="225"/>
+      <c r="L1" s="225"/>
+      <c r="M1" s="225"/>
+      <c r="N1" s="225"/>
+      <c r="O1" s="225"/>
+      <c r="P1" s="225"/>
+      <c r="Q1" s="225"/>
+      <c r="R1" s="225"/>
+      <c r="S1" s="225"/>
+      <c r="T1" s="225"/>
+      <c r="U1" s="225"/>
+      <c r="V1" s="225"/>
+      <c r="W1" s="225"/>
+      <c r="X1" s="225"/>
+      <c r="Y1" s="225"/>
+      <c r="Z1" s="225"/>
+      <c r="AA1" s="225"/>
+      <c r="AB1" s="225"/>
+      <c r="AC1" s="226"/>
+      <c r="AD1" s="239" t="s">
         <v>281</v>
       </c>
-      <c r="AE1" s="239"/>
-      <c r="AF1" s="239"/>
-      <c r="AG1" s="239"/>
-      <c r="AH1" s="239"/>
-      <c r="AI1" s="240"/>
-      <c r="AJ1" s="226" t="s">
+      <c r="AE1" s="240"/>
+      <c r="AF1" s="240"/>
+      <c r="AG1" s="240"/>
+      <c r="AH1" s="240"/>
+      <c r="AI1" s="241"/>
+      <c r="AJ1" s="224" t="s">
         <v>282</v>
       </c>
-      <c r="AK1" s="227"/>
-      <c r="AL1" s="227"/>
-      <c r="AM1" s="227"/>
-      <c r="AN1" s="227"/>
-      <c r="AO1" s="228"/>
-      <c r="AP1" s="229" t="s">
+      <c r="AK1" s="225"/>
+      <c r="AL1" s="225"/>
+      <c r="AM1" s="225"/>
+      <c r="AN1" s="225"/>
+      <c r="AO1" s="226"/>
+      <c r="AP1" s="227" t="s">
         <v>283</v>
       </c>
-      <c r="AQ1" s="230"/>
-      <c r="AR1" s="230"/>
-      <c r="AS1" s="230"/>
-      <c r="AT1" s="230"/>
-      <c r="AU1" s="231"/>
-      <c r="AV1" s="232" t="s">
+      <c r="AQ1" s="228"/>
+      <c r="AR1" s="228"/>
+      <c r="AS1" s="228"/>
+      <c r="AT1" s="228"/>
+      <c r="AU1" s="229"/>
+      <c r="AV1" s="230" t="s">
         <v>86</v>
       </c>
-      <c r="AW1" s="233"/>
-      <c r="AX1" s="234"/>
+      <c r="AW1" s="231"/>
+      <c r="AX1" s="232"/>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="236"/>
-      <c r="D2" s="236"/>
-      <c r="E2" s="236"/>
-      <c r="F2" s="223" t="s">
+      <c r="C2" s="234"/>
+      <c r="D2" s="234"/>
+      <c r="E2" s="234"/>
+      <c r="F2" s="236" t="s">
         <v>458</v>
       </c>
-      <c r="G2" s="224"/>
-      <c r="H2" s="225"/>
-      <c r="I2" s="223" t="s">
+      <c r="G2" s="237"/>
+      <c r="H2" s="238"/>
+      <c r="I2" s="236" t="s">
         <v>461</v>
       </c>
-      <c r="J2" s="224"/>
-      <c r="K2" s="225"/>
-      <c r="L2" s="223" t="s">
+      <c r="J2" s="237"/>
+      <c r="K2" s="238"/>
+      <c r="L2" s="236" t="s">
         <v>462</v>
       </c>
-      <c r="M2" s="224"/>
-      <c r="N2" s="225"/>
-      <c r="O2" s="223" t="s">
+      <c r="M2" s="237"/>
+      <c r="N2" s="238"/>
+      <c r="O2" s="236" t="s">
         <v>463</v>
       </c>
-      <c r="P2" s="224"/>
-      <c r="Q2" s="225"/>
-      <c r="R2" s="223" t="s">
+      <c r="P2" s="237"/>
+      <c r="Q2" s="238"/>
+      <c r="R2" s="236" t="s">
         <v>464</v>
       </c>
-      <c r="S2" s="224"/>
-      <c r="T2" s="225"/>
-      <c r="U2" s="223" t="s">
+      <c r="S2" s="237"/>
+      <c r="T2" s="238"/>
+      <c r="U2" s="236" t="s">
         <v>465</v>
       </c>
-      <c r="V2" s="224"/>
-      <c r="W2" s="225"/>
-      <c r="X2" s="223" t="s">
+      <c r="V2" s="237"/>
+      <c r="W2" s="238"/>
+      <c r="X2" s="236" t="s">
         <v>466</v>
       </c>
-      <c r="Y2" s="224"/>
-      <c r="Z2" s="225"/>
-      <c r="AA2" s="223" t="s">
+      <c r="Y2" s="237"/>
+      <c r="Z2" s="238"/>
+      <c r="AA2" s="236" t="s">
         <v>467</v>
       </c>
-      <c r="AB2" s="224"/>
-      <c r="AC2" s="224"/>
-      <c r="AD2" s="223"/>
-      <c r="AE2" s="224"/>
-      <c r="AF2" s="225"/>
-      <c r="AG2" s="223"/>
-      <c r="AH2" s="224"/>
-      <c r="AI2" s="225"/>
-      <c r="AJ2" s="223"/>
-      <c r="AK2" s="224"/>
-      <c r="AL2" s="225"/>
-      <c r="AM2" s="223"/>
-      <c r="AN2" s="224"/>
-      <c r="AO2" s="225"/>
-      <c r="AP2" s="223"/>
-      <c r="AQ2" s="224"/>
-      <c r="AR2" s="225"/>
-      <c r="AS2" s="223"/>
-      <c r="AT2" s="224"/>
-      <c r="AU2" s="225"/>
-      <c r="AV2" s="223"/>
-      <c r="AW2" s="224"/>
-      <c r="AX2" s="225"/>
+      <c r="AB2" s="237"/>
+      <c r="AC2" s="237"/>
+      <c r="AD2" s="236"/>
+      <c r="AE2" s="237"/>
+      <c r="AF2" s="238"/>
+      <c r="AG2" s="236"/>
+      <c r="AH2" s="237"/>
+      <c r="AI2" s="238"/>
+      <c r="AJ2" s="236"/>
+      <c r="AK2" s="237"/>
+      <c r="AL2" s="238"/>
+      <c r="AM2" s="236"/>
+      <c r="AN2" s="237"/>
+      <c r="AO2" s="238"/>
+      <c r="AP2" s="236"/>
+      <c r="AQ2" s="237"/>
+      <c r="AR2" s="238"/>
+      <c r="AS2" s="236"/>
+      <c r="AT2" s="237"/>
+      <c r="AU2" s="238"/>
+      <c r="AV2" s="236"/>
+      <c r="AW2" s="237"/>
+      <c r="AX2" s="238"/>
     </row>
     <row r="3" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -44101,9 +44104,9 @@
       <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="237"/>
-      <c r="D3" s="237"/>
-      <c r="E3" s="237"/>
+      <c r="C3" s="235"/>
+      <c r="D3" s="235"/>
+      <c r="E3" s="235"/>
       <c r="F3" s="169" t="s">
         <v>393</v>
       </c>
@@ -46735,6 +46738,13 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="F1:AC1"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
+    <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="AJ1:AO1"/>
     <mergeCell ref="AP1:AU1"/>
     <mergeCell ref="AV1:AX1"/>
@@ -46751,13 +46761,6 @@
     <mergeCell ref="AD1:AI1"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="I2:K2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="F1:AC1"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:AW32">
     <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
@@ -46792,70 +46795,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C1" s="235" t="s">
+      <c r="C1" s="233" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="235" t="s">
+      <c r="D1" s="233" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="235" t="s">
+      <c r="E1" s="233" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="265" t="s">
+      <c r="F1" s="273" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="266"/>
-      <c r="H1" s="267"/>
-      <c r="I1" s="268" t="s">
+      <c r="G1" s="274"/>
+      <c r="H1" s="275"/>
+      <c r="I1" s="276" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="269"/>
-      <c r="K1" s="270"/>
-      <c r="L1" s="272" t="s">
+      <c r="J1" s="277"/>
+      <c r="K1" s="278"/>
+      <c r="L1" s="243" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="273"/>
-      <c r="N1" s="274"/>
-      <c r="O1" s="275" t="s">
+      <c r="M1" s="244"/>
+      <c r="N1" s="245"/>
+      <c r="O1" s="246" t="s">
         <v>199</v>
       </c>
-      <c r="P1" s="276"/>
-      <c r="Q1" s="277"/>
-      <c r="R1" s="241" t="s">
+      <c r="P1" s="247"/>
+      <c r="Q1" s="248"/>
+      <c r="R1" s="249" t="s">
         <v>200</v>
       </c>
-      <c r="S1" s="242"/>
-      <c r="T1" s="243"/>
-      <c r="U1" s="244" t="s">
+      <c r="S1" s="250"/>
+      <c r="T1" s="251"/>
+      <c r="U1" s="252" t="s">
         <v>306</v>
       </c>
-      <c r="V1" s="245"/>
-      <c r="W1" s="246"/>
+      <c r="V1" s="253"/>
+      <c r="W1" s="254"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="236"/>
-      <c r="D2" s="236"/>
-      <c r="E2" s="236"/>
-      <c r="F2" s="247"/>
-      <c r="G2" s="248"/>
-      <c r="H2" s="249"/>
-      <c r="I2" s="262"/>
-      <c r="J2" s="263"/>
-      <c r="K2" s="264"/>
-      <c r="L2" s="259"/>
-      <c r="M2" s="260"/>
-      <c r="N2" s="261"/>
-      <c r="O2" s="256"/>
-      <c r="P2" s="257"/>
-      <c r="Q2" s="258"/>
-      <c r="R2" s="253"/>
-      <c r="S2" s="254"/>
-      <c r="T2" s="255"/>
-      <c r="U2" s="250"/>
-      <c r="V2" s="251"/>
-      <c r="W2" s="252"/>
+      <c r="C2" s="234"/>
+      <c r="D2" s="234"/>
+      <c r="E2" s="234"/>
+      <c r="F2" s="255"/>
+      <c r="G2" s="256"/>
+      <c r="H2" s="257"/>
+      <c r="I2" s="270"/>
+      <c r="J2" s="271"/>
+      <c r="K2" s="272"/>
+      <c r="L2" s="267"/>
+      <c r="M2" s="268"/>
+      <c r="N2" s="269"/>
+      <c r="O2" s="264"/>
+      <c r="P2" s="265"/>
+      <c r="Q2" s="266"/>
+      <c r="R2" s="261"/>
+      <c r="S2" s="262"/>
+      <c r="T2" s="263"/>
+      <c r="U2" s="258"/>
+      <c r="V2" s="259"/>
+      <c r="W2" s="260"/>
     </row>
     <row r="3" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -46864,9 +46867,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="271"/>
-      <c r="D3" s="271"/>
-      <c r="E3" s="271"/>
+      <c r="C3" s="242"/>
+      <c r="D3" s="242"/>
+      <c r="E3" s="242"/>
       <c r="F3" s="188" t="s">
         <v>393</v>
       </c>
@@ -48328,11 +48331,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="O1:Q1"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="F2:H2"/>
@@ -48343,6 +48341,11 @@
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="O1:Q1"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:W32">
     <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
@@ -55349,72 +55352,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C1" s="235" t="s">
+      <c r="C1" s="233" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="235" t="s">
+      <c r="D1" s="233" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="235" t="s">
+      <c r="E1" s="233" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="265" t="s">
+      <c r="F1" s="273" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="266"/>
-      <c r="H1" s="267"/>
-      <c r="I1" s="268" t="s">
+      <c r="G1" s="274"/>
+      <c r="H1" s="275"/>
+      <c r="I1" s="276" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="269"/>
-      <c r="K1" s="270"/>
-      <c r="L1" s="272" t="s">
+      <c r="J1" s="277"/>
+      <c r="K1" s="278"/>
+      <c r="L1" s="243" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="273"/>
-      <c r="N1" s="274"/>
-      <c r="O1" s="275" t="s">
+      <c r="M1" s="244"/>
+      <c r="N1" s="245"/>
+      <c r="O1" s="246" t="s">
         <v>199</v>
       </c>
-      <c r="P1" s="276"/>
-      <c r="Q1" s="277"/>
-      <c r="R1" s="241" t="s">
+      <c r="P1" s="247"/>
+      <c r="Q1" s="248"/>
+      <c r="R1" s="249" t="s">
         <v>200</v>
       </c>
-      <c r="S1" s="242"/>
-      <c r="T1" s="243"/>
-      <c r="U1" s="244" t="s">
+      <c r="S1" s="250"/>
+      <c r="T1" s="251"/>
+      <c r="U1" s="252" t="s">
         <v>306</v>
       </c>
-      <c r="V1" s="245"/>
-      <c r="W1" s="246"/>
+      <c r="V1" s="253"/>
+      <c r="W1" s="254"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="236"/>
-      <c r="D2" s="236"/>
-      <c r="E2" s="236"/>
-      <c r="F2" s="247" t="s">
+      <c r="C2" s="234"/>
+      <c r="D2" s="234"/>
+      <c r="E2" s="234"/>
+      <c r="F2" s="255" t="s">
         <v>432</v>
       </c>
-      <c r="G2" s="248"/>
-      <c r="H2" s="249"/>
-      <c r="I2" s="262"/>
-      <c r="J2" s="263"/>
-      <c r="K2" s="264"/>
-      <c r="L2" s="259"/>
-      <c r="M2" s="260"/>
-      <c r="N2" s="261"/>
-      <c r="O2" s="256"/>
-      <c r="P2" s="257"/>
-      <c r="Q2" s="258"/>
-      <c r="R2" s="253"/>
-      <c r="S2" s="254"/>
-      <c r="T2" s="255"/>
-      <c r="U2" s="250"/>
-      <c r="V2" s="251"/>
-      <c r="W2" s="252"/>
+      <c r="G2" s="256"/>
+      <c r="H2" s="257"/>
+      <c r="I2" s="270"/>
+      <c r="J2" s="271"/>
+      <c r="K2" s="272"/>
+      <c r="L2" s="267"/>
+      <c r="M2" s="268"/>
+      <c r="N2" s="269"/>
+      <c r="O2" s="264"/>
+      <c r="P2" s="265"/>
+      <c r="Q2" s="266"/>
+      <c r="R2" s="261"/>
+      <c r="S2" s="262"/>
+      <c r="T2" s="263"/>
+      <c r="U2" s="258"/>
+      <c r="V2" s="259"/>
+      <c r="W2" s="260"/>
     </row>
     <row r="3" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -55423,9 +55426,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="271"/>
-      <c r="D3" s="271"/>
-      <c r="E3" s="271"/>
+      <c r="C3" s="242"/>
+      <c r="D3" s="242"/>
+      <c r="E3" s="242"/>
       <c r="F3" s="188" t="s">
         <v>393</v>
       </c>
@@ -56929,6 +56932,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="F2:H2"/>
@@ -56939,11 +56947,6 @@
     <mergeCell ref="U2:W2"/>
     <mergeCell ref="L1:N1"/>
     <mergeCell ref="O1:Q1"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:W32">
     <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
@@ -56971,11 +56974,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C1" s="278" t="s">
+      <c r="C1" s="279" t="s">
         <v>340</v>
       </c>
-      <c r="D1" s="279"/>
-      <c r="E1" s="279"/>
+      <c r="D1" s="280"/>
+      <c r="E1" s="280"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -57450,51 +57453,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="281" t="s">
+      <c r="C1" s="310" t="s">
         <v>202</v>
       </c>
-      <c r="D1" s="282"/>
-      <c r="E1" s="282"/>
-      <c r="F1" s="282"/>
-      <c r="G1" s="282"/>
-      <c r="H1" s="282"/>
-      <c r="I1" s="283"/>
+      <c r="D1" s="311"/>
+      <c r="E1" s="311"/>
+      <c r="F1" s="311"/>
+      <c r="G1" s="311"/>
+      <c r="H1" s="311"/>
+      <c r="I1" s="312"/>
       <c r="J1" s="114" t="s">
         <v>195</v>
       </c>
       <c r="K1" s="115" t="s">
         <v>194</v>
       </c>
-      <c r="L1" s="305" t="s">
+      <c r="L1" s="290" t="s">
         <v>287</v>
       </c>
-      <c r="M1" s="310"/>
-      <c r="N1" s="310"/>
-      <c r="O1" s="310"/>
-      <c r="P1" s="310"/>
-      <c r="Q1" s="310"/>
-      <c r="R1" s="310"/>
-      <c r="S1" s="310"/>
-      <c r="T1" s="310"/>
-      <c r="U1" s="310"/>
-      <c r="V1" s="310"/>
-      <c r="W1" s="310"/>
-      <c r="X1" s="310"/>
-      <c r="Y1" s="310"/>
-      <c r="Z1" s="310"/>
-      <c r="AA1" s="310"/>
-      <c r="AB1" s="310"/>
-      <c r="AC1" s="310"/>
-      <c r="AD1" s="310"/>
-      <c r="AE1" s="310"/>
-      <c r="AF1" s="310"/>
-      <c r="AG1" s="311"/>
-      <c r="AH1" s="305" t="s">
+      <c r="M1" s="295"/>
+      <c r="N1" s="295"/>
+      <c r="O1" s="295"/>
+      <c r="P1" s="295"/>
+      <c r="Q1" s="295"/>
+      <c r="R1" s="295"/>
+      <c r="S1" s="295"/>
+      <c r="T1" s="295"/>
+      <c r="U1" s="295"/>
+      <c r="V1" s="295"/>
+      <c r="W1" s="295"/>
+      <c r="X1" s="295"/>
+      <c r="Y1" s="295"/>
+      <c r="Z1" s="295"/>
+      <c r="AA1" s="295"/>
+      <c r="AB1" s="295"/>
+      <c r="AC1" s="295"/>
+      <c r="AD1" s="295"/>
+      <c r="AE1" s="295"/>
+      <c r="AF1" s="295"/>
+      <c r="AG1" s="296"/>
+      <c r="AH1" s="290" t="s">
         <v>175</v>
       </c>
-      <c r="AI1" s="306"/>
-      <c r="AJ1" s="306"/>
-      <c r="AK1" s="307"/>
+      <c r="AI1" s="291"/>
+      <c r="AJ1" s="291"/>
+      <c r="AK1" s="292"/>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B2" s="111"/>
@@ -62694,15 +62697,15 @@
         <f t="shared" ref="J80:J111" si="2">H80-I80</f>
         <v>2</v>
       </c>
-      <c r="K80" s="312" t="s">
+      <c r="K80" s="297" t="s">
         <v>434</v>
       </c>
-      <c r="L80" s="313"/>
-      <c r="M80" s="314"/>
+      <c r="L80" s="298"/>
+      <c r="M80" s="299"/>
       <c r="O80" s="133"/>
       <c r="P80" s="133"/>
-      <c r="W80" s="308"/>
-      <c r="X80" s="308"/>
+      <c r="W80" s="293"/>
+      <c r="X80" s="293"/>
       <c r="Y80" s="70" t="s">
         <v>211</v>
       </c>
@@ -62752,15 +62755,15 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K81" s="315"/>
-      <c r="L81" s="316"/>
-      <c r="M81" s="317"/>
+      <c r="K81" s="300"/>
+      <c r="L81" s="301"/>
+      <c r="M81" s="302"/>
       <c r="O81" s="133"/>
       <c r="P81" s="133"/>
-      <c r="W81" s="308" t="s">
+      <c r="W81" s="293" t="s">
         <v>209</v>
       </c>
-      <c r="X81" s="308"/>
+      <c r="X81" s="293"/>
       <c r="Y81" s="70">
         <f>COUNTIF(L3:AG40,3)</f>
         <v>481</v>
@@ -62816,17 +62819,17 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K82" s="318" t="s">
+      <c r="K82" s="303" t="s">
         <v>435</v>
       </c>
-      <c r="L82" s="319"/>
-      <c r="M82" s="320"/>
+      <c r="L82" s="304"/>
+      <c r="M82" s="305"/>
       <c r="O82" s="133"/>
       <c r="P82" s="133"/>
-      <c r="W82" s="308" t="s">
+      <c r="W82" s="293" t="s">
         <v>210</v>
       </c>
-      <c r="X82" s="308"/>
+      <c r="X82" s="293"/>
       <c r="Y82" s="70">
         <f>COUNTIF(K3:K40,3)+COUNTIF(J3:J15,3)</f>
         <v>25</v>
@@ -62882,17 +62885,17 @@
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="K83" s="321" t="s">
+      <c r="K83" s="306" t="s">
         <v>436</v>
       </c>
-      <c r="L83" s="322"/>
-      <c r="M83" s="323"/>
+      <c r="L83" s="307"/>
+      <c r="M83" s="308"/>
       <c r="O83" s="133"/>
       <c r="P83" s="133"/>
-      <c r="W83" s="309" t="s">
+      <c r="W83" s="294" t="s">
         <v>97</v>
       </c>
-      <c r="X83" s="309"/>
+      <c r="X83" s="294"/>
       <c r="Y83" s="194">
         <v>224</v>
       </c>
@@ -62945,15 +62948,15 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="K84" s="287" t="s">
+      <c r="K84" s="316" t="s">
         <v>284</v>
       </c>
-      <c r="L84" s="288"/>
-      <c r="M84" s="289"/>
+      <c r="L84" s="317"/>
+      <c r="M84" s="318"/>
       <c r="O84" s="141"/>
       <c r="P84" s="141"/>
-      <c r="W84" s="280"/>
-      <c r="X84" s="280"/>
+      <c r="W84" s="309"/>
+      <c r="X84" s="309"/>
       <c r="Y84" s="196"/>
       <c r="Z84" s="196"/>
       <c r="AA84" s="196"/>
@@ -62991,9 +62994,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K85" s="290"/>
-      <c r="L85" s="291"/>
-      <c r="M85" s="292"/>
+      <c r="K85" s="319"/>
+      <c r="L85" s="320"/>
+      <c r="M85" s="321"/>
       <c r="O85" s="141"/>
       <c r="P85" s="141"/>
     </row>
@@ -63027,9 +63030,9 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="K86" s="290"/>
-      <c r="L86" s="291"/>
-      <c r="M86" s="292"/>
+      <c r="K86" s="319"/>
+      <c r="L86" s="320"/>
+      <c r="M86" s="321"/>
       <c r="O86" s="141"/>
       <c r="P86" s="141"/>
     </row>
@@ -63063,9 +63066,9 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="K87" s="290"/>
-      <c r="L87" s="291"/>
-      <c r="M87" s="292"/>
+      <c r="K87" s="319"/>
+      <c r="L87" s="320"/>
+      <c r="M87" s="321"/>
       <c r="O87" s="141"/>
       <c r="P87" s="141"/>
     </row>
@@ -63099,9 +63102,9 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K88" s="290"/>
-      <c r="L88" s="291"/>
-      <c r="M88" s="292"/>
+      <c r="K88" s="319"/>
+      <c r="L88" s="320"/>
+      <c r="M88" s="321"/>
       <c r="O88" s="141"/>
       <c r="P88" s="141"/>
     </row>
@@ -63135,9 +63138,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K89" s="290"/>
-      <c r="L89" s="291"/>
-      <c r="M89" s="292"/>
+      <c r="K89" s="319"/>
+      <c r="L89" s="320"/>
+      <c r="M89" s="321"/>
       <c r="O89" s="141"/>
       <c r="P89" s="141"/>
     </row>
@@ -63171,9 +63174,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K90" s="290"/>
-      <c r="L90" s="291"/>
-      <c r="M90" s="292"/>
+      <c r="K90" s="319"/>
+      <c r="L90" s="320"/>
+      <c r="M90" s="321"/>
       <c r="O90" s="141"/>
       <c r="P90" s="141"/>
     </row>
@@ -63207,9 +63210,9 @@
         <f t="shared" si="2"/>
         <v>47</v>
       </c>
-      <c r="K91" s="290"/>
-      <c r="L91" s="291"/>
-      <c r="M91" s="292"/>
+      <c r="K91" s="319"/>
+      <c r="L91" s="320"/>
+      <c r="M91" s="321"/>
       <c r="O91" s="141"/>
       <c r="P91" s="141"/>
     </row>
@@ -63243,9 +63246,9 @@
         <f t="shared" si="2"/>
         <v>51</v>
       </c>
-      <c r="K92" s="290"/>
-      <c r="L92" s="291"/>
-      <c r="M92" s="292"/>
+      <c r="K92" s="319"/>
+      <c r="L92" s="320"/>
+      <c r="M92" s="321"/>
       <c r="O92" s="141"/>
       <c r="P92" s="141"/>
     </row>
@@ -63279,9 +63282,9 @@
         <f t="shared" si="2"/>
         <v>37</v>
       </c>
-      <c r="K93" s="290"/>
-      <c r="L93" s="291"/>
-      <c r="M93" s="292"/>
+      <c r="K93" s="319"/>
+      <c r="L93" s="320"/>
+      <c r="M93" s="321"/>
       <c r="O93" s="141"/>
       <c r="P93" s="141"/>
     </row>
@@ -63315,9 +63318,9 @@
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="K94" s="290"/>
-      <c r="L94" s="291"/>
-      <c r="M94" s="292"/>
+      <c r="K94" s="319"/>
+      <c r="L94" s="320"/>
+      <c r="M94" s="321"/>
       <c r="O94" s="141"/>
       <c r="P94" s="141"/>
     </row>
@@ -63351,9 +63354,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K95" s="290"/>
-      <c r="L95" s="291"/>
-      <c r="M95" s="292"/>
+      <c r="K95" s="319"/>
+      <c r="L95" s="320"/>
+      <c r="M95" s="321"/>
       <c r="O95" s="141"/>
       <c r="P95" s="141"/>
     </row>
@@ -63387,9 +63390,9 @@
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="K96" s="290"/>
-      <c r="L96" s="291"/>
-      <c r="M96" s="292"/>
+      <c r="K96" s="319"/>
+      <c r="L96" s="320"/>
+      <c r="M96" s="321"/>
       <c r="O96" s="141"/>
       <c r="P96" s="141"/>
     </row>
@@ -63423,9 +63426,9 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="K97" s="290"/>
-      <c r="L97" s="291"/>
-      <c r="M97" s="292"/>
+      <c r="K97" s="319"/>
+      <c r="L97" s="320"/>
+      <c r="M97" s="321"/>
       <c r="O97" s="141"/>
       <c r="P97" s="141"/>
     </row>
@@ -63459,9 +63462,9 @@
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="K98" s="290"/>
-      <c r="L98" s="291"/>
-      <c r="M98" s="292"/>
+      <c r="K98" s="319"/>
+      <c r="L98" s="320"/>
+      <c r="M98" s="321"/>
       <c r="O98" s="141"/>
       <c r="P98" s="141"/>
     </row>
@@ -63495,9 +63498,9 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K99" s="290"/>
-      <c r="L99" s="291"/>
-      <c r="M99" s="292"/>
+      <c r="K99" s="319"/>
+      <c r="L99" s="320"/>
+      <c r="M99" s="321"/>
       <c r="O99" s="141"/>
       <c r="P99" s="141"/>
     </row>
@@ -63531,9 +63534,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K100" s="290"/>
-      <c r="L100" s="291"/>
-      <c r="M100" s="292"/>
+      <c r="K100" s="319"/>
+      <c r="L100" s="320"/>
+      <c r="M100" s="321"/>
       <c r="O100" s="141"/>
       <c r="P100" s="141"/>
     </row>
@@ -63567,9 +63570,9 @@
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="K101" s="290"/>
-      <c r="L101" s="291"/>
-      <c r="M101" s="292"/>
+      <c r="K101" s="319"/>
+      <c r="L101" s="320"/>
+      <c r="M101" s="321"/>
       <c r="O101" s="141"/>
       <c r="P101" s="141"/>
     </row>
@@ -63603,9 +63606,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K102" s="290"/>
-      <c r="L102" s="291"/>
-      <c r="M102" s="292"/>
+      <c r="K102" s="319"/>
+      <c r="L102" s="320"/>
+      <c r="M102" s="321"/>
       <c r="O102" s="141"/>
       <c r="P102" s="141"/>
     </row>
@@ -63639,9 +63642,9 @@
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="K103" s="290"/>
-      <c r="L103" s="291"/>
-      <c r="M103" s="292"/>
+      <c r="K103" s="319"/>
+      <c r="L103" s="320"/>
+      <c r="M103" s="321"/>
       <c r="O103" s="141"/>
       <c r="P103" s="141"/>
     </row>
@@ -63675,9 +63678,9 @@
         <f t="shared" si="2"/>
         <v>33</v>
       </c>
-      <c r="K104" s="290"/>
-      <c r="L104" s="291"/>
-      <c r="M104" s="292"/>
+      <c r="K104" s="319"/>
+      <c r="L104" s="320"/>
+      <c r="M104" s="321"/>
       <c r="O104" s="141"/>
       <c r="P104" s="141"/>
     </row>
@@ -63711,9 +63714,9 @@
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="K105" s="293"/>
-      <c r="L105" s="294"/>
-      <c r="M105" s="295"/>
+      <c r="K105" s="322"/>
+      <c r="L105" s="323"/>
+      <c r="M105" s="324"/>
       <c r="O105" s="141"/>
       <c r="P105" s="141"/>
     </row>
@@ -63747,11 +63750,11 @@
         <f t="shared" si="2"/>
         <v>21</v>
       </c>
-      <c r="K106" s="284" t="s">
+      <c r="K106" s="313" t="s">
         <v>286</v>
       </c>
-      <c r="L106" s="285"/>
-      <c r="M106" s="286"/>
+      <c r="L106" s="314"/>
+      <c r="M106" s="315"/>
       <c r="O106" s="126"/>
       <c r="P106" s="126"/>
     </row>
@@ -63785,11 +63788,11 @@
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="K107" s="284" t="s">
+      <c r="K107" s="313" t="s">
         <v>288</v>
       </c>
-      <c r="L107" s="285"/>
-      <c r="M107" s="286"/>
+      <c r="L107" s="314"/>
+      <c r="M107" s="315"/>
       <c r="O107" s="126"/>
       <c r="P107" s="126"/>
     </row>
@@ -63823,11 +63826,11 @@
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="K108" s="296" t="s">
+      <c r="K108" s="281" t="s">
         <v>289</v>
       </c>
-      <c r="L108" s="297"/>
-      <c r="M108" s="298"/>
+      <c r="L108" s="282"/>
+      <c r="M108" s="283"/>
       <c r="O108" s="126"/>
       <c r="P108" s="126"/>
     </row>
@@ -63861,9 +63864,9 @@
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="K109" s="299"/>
-      <c r="L109" s="300"/>
-      <c r="M109" s="301"/>
+      <c r="K109" s="284"/>
+      <c r="L109" s="285"/>
+      <c r="M109" s="286"/>
       <c r="O109" s="126"/>
       <c r="P109" s="126"/>
     </row>
@@ -63897,9 +63900,9 @@
         <f t="shared" si="2"/>
         <v>45</v>
       </c>
-      <c r="K110" s="299"/>
-      <c r="L110" s="300"/>
-      <c r="M110" s="301"/>
+      <c r="K110" s="284"/>
+      <c r="L110" s="285"/>
+      <c r="M110" s="286"/>
       <c r="O110" s="126"/>
       <c r="P110" s="126"/>
     </row>
@@ -63933,9 +63936,9 @@
         <f t="shared" si="2"/>
         <v>62</v>
       </c>
-      <c r="K111" s="299"/>
-      <c r="L111" s="300"/>
-      <c r="M111" s="301"/>
+      <c r="K111" s="284"/>
+      <c r="L111" s="285"/>
+      <c r="M111" s="286"/>
       <c r="O111" s="126"/>
       <c r="P111" s="126"/>
     </row>
@@ -63973,9 +63976,9 @@
         <f t="shared" ref="J112:J114" si="6">H112-I112</f>
         <v>34</v>
       </c>
-      <c r="K112" s="299"/>
-      <c r="L112" s="300"/>
-      <c r="M112" s="301"/>
+      <c r="K112" s="284"/>
+      <c r="L112" s="285"/>
+      <c r="M112" s="286"/>
     </row>
     <row r="113" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="156" t="s">
@@ -64011,9 +64014,9 @@
         <f t="shared" si="6"/>
         <v>43</v>
       </c>
-      <c r="K113" s="299"/>
-      <c r="L113" s="300"/>
-      <c r="M113" s="301"/>
+      <c r="K113" s="284"/>
+      <c r="L113" s="285"/>
+      <c r="M113" s="286"/>
     </row>
     <row r="114" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="93" t="s">
@@ -64049,13 +64052,17 @@
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="K114" s="302"/>
-      <c r="L114" s="303"/>
-      <c r="M114" s="304"/>
+      <c r="K114" s="287"/>
+      <c r="L114" s="288"/>
+      <c r="M114" s="289"/>
     </row>
   </sheetData>
   <autoFilter ref="A79:J112" xr:uid="{9C81160F-C24B-449F-8F5A-CB622AB71070}"/>
   <mergeCells count="15">
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="K106:M106"/>
+    <mergeCell ref="K107:M107"/>
+    <mergeCell ref="K84:M105"/>
     <mergeCell ref="K108:M114"/>
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="W80:X80"/>
@@ -64067,10 +64074,6 @@
     <mergeCell ref="K82:M82"/>
     <mergeCell ref="K83:M83"/>
     <mergeCell ref="W84:X84"/>
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="K106:M106"/>
-    <mergeCell ref="K107:M107"/>
-    <mergeCell ref="K84:M105"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <conditionalFormatting sqref="A3:A40">
@@ -64162,32 +64165,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="324" t="s">
+      <c r="A1" s="325" t="s">
         <v>405</v>
       </c>
-      <c r="B1" s="324"/>
-      <c r="C1" s="324"/>
-      <c r="D1" s="324"/>
-      <c r="E1" s="324"/>
-      <c r="F1" s="324" t="s">
+      <c r="B1" s="325"/>
+      <c r="C1" s="325"/>
+      <c r="D1" s="325"/>
+      <c r="E1" s="325"/>
+      <c r="F1" s="325" t="s">
         <v>406</v>
       </c>
-      <c r="G1" s="324"/>
-      <c r="H1" s="324"/>
-      <c r="I1" s="324"/>
-      <c r="J1" s="324"/>
+      <c r="G1" s="325"/>
+      <c r="H1" s="325"/>
+      <c r="I1" s="325"/>
+      <c r="J1" s="325"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2" s="324"/>
-      <c r="B2" s="324"/>
-      <c r="C2" s="324"/>
-      <c r="D2" s="324"/>
-      <c r="E2" s="324"/>
-      <c r="F2" s="324"/>
-      <c r="G2" s="324"/>
-      <c r="H2" s="324"/>
-      <c r="I2" s="324"/>
-      <c r="J2" s="324"/>
+      <c r="A2" s="325"/>
+      <c r="B2" s="325"/>
+      <c r="C2" s="325"/>
+      <c r="D2" s="325"/>
+      <c r="E2" s="325"/>
+      <c r="F2" s="325"/>
+      <c r="G2" s="325"/>
+      <c r="H2" s="325"/>
+      <c r="I2" s="325"/>
+      <c r="J2" s="325"/>
       <c r="L2" t="s">
         <v>409</v>
       </c>
@@ -64292,7 +64295,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>461</v>
+        <v>488</v>
       </c>
       <c r="E4" t="s">
         <v>471</v>
@@ -64300,7 +64303,7 @@
       <c r="F4" t="s">
         <v>470</v>
       </c>
-      <c r="G4" s="328" t="s">
+      <c r="G4" s="202" t="s">
         <v>480</v>
       </c>
       <c r="H4" t="s">
@@ -65182,24 +65185,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="202" t="s">
+      <c r="A1" s="203" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="325"/>
-      <c r="C1" s="326" t="s">
+      <c r="B1" s="326"/>
+      <c r="C1" s="327" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="205"/>
-      <c r="E1" s="327"/>
-      <c r="H1" s="202" t="s">
+      <c r="D1" s="206"/>
+      <c r="E1" s="328"/>
+      <c r="H1" s="203" t="s">
         <v>47</v>
       </c>
-      <c r="I1" s="325"/>
-      <c r="J1" s="326" t="s">
+      <c r="I1" s="326"/>
+      <c r="J1" s="327" t="s">
         <v>44</v>
       </c>
-      <c r="K1" s="205"/>
-      <c r="L1" s="327"/>
+      <c r="K1" s="206"/>
+      <c r="L1" s="328"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -66287,9 +66290,9 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="206"/>
-      <c r="G1" s="206"/>
-      <c r="H1" s="206"/>
+      <c r="F1" s="207"/>
+      <c r="G1" s="207"/>
+      <c r="H1" s="207"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -66313,36 +66316,36 @@
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="5"/>
-      <c r="E2" s="202" t="s">
+      <c r="E2" s="203" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="203"/>
-      <c r="G2" s="204"/>
-      <c r="H2" s="207" t="s">
+      <c r="F2" s="204"/>
+      <c r="G2" s="205"/>
+      <c r="H2" s="208" t="s">
         <v>120</v>
       </c>
-      <c r="I2" s="208"/>
-      <c r="J2" s="209"/>
-      <c r="K2" s="202" t="s">
+      <c r="I2" s="209"/>
+      <c r="J2" s="210"/>
+      <c r="K2" s="203" t="s">
         <v>108</v>
       </c>
-      <c r="L2" s="203"/>
-      <c r="M2" s="204"/>
-      <c r="N2" s="207" t="s">
+      <c r="L2" s="204"/>
+      <c r="M2" s="205"/>
+      <c r="N2" s="208" t="s">
         <v>110</v>
       </c>
-      <c r="O2" s="208"/>
-      <c r="P2" s="209"/>
-      <c r="Q2" s="202" t="s">
+      <c r="O2" s="209"/>
+      <c r="P2" s="210"/>
+      <c r="Q2" s="203" t="s">
         <v>39</v>
       </c>
-      <c r="R2" s="203"/>
-      <c r="S2" s="204"/>
-      <c r="T2" s="205" t="s">
+      <c r="R2" s="204"/>
+      <c r="S2" s="205"/>
+      <c r="T2" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="U2" s="205"/>
-      <c r="V2" s="205"/>
+      <c r="U2" s="206"/>
+      <c r="V2" s="206"/>
       <c r="Z2" s="125">
         <v>46307</v>
       </c>
@@ -69526,30 +69529,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="212" t="s">
+      <c r="D2" s="213" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="212"/>
-      <c r="F2" s="213" t="s">
+      <c r="E2" s="213"/>
+      <c r="F2" s="214" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="213"/>
-      <c r="H2" s="212" t="s">
+      <c r="G2" s="214"/>
+      <c r="H2" s="213" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="212"/>
-      <c r="J2" s="213" t="s">
+      <c r="I2" s="213"/>
+      <c r="J2" s="214" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="213"/>
-      <c r="L2" s="212" t="s">
+      <c r="K2" s="214"/>
+      <c r="L2" s="213" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="212"/>
-      <c r="N2" s="205" t="s">
+      <c r="M2" s="213"/>
+      <c r="N2" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="205"/>
+      <c r="O2" s="206"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -71546,30 +71549,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="212" t="s">
+      <c r="D2" s="213" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="212"/>
-      <c r="F2" s="213" t="s">
+      <c r="E2" s="213"/>
+      <c r="F2" s="214" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="213"/>
-      <c r="H2" s="212" t="s">
+      <c r="G2" s="214"/>
+      <c r="H2" s="213" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="212"/>
-      <c r="J2" s="213" t="s">
+      <c r="I2" s="213"/>
+      <c r="J2" s="214" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="213"/>
-      <c r="L2" s="212" t="s">
+      <c r="K2" s="214"/>
+      <c r="L2" s="213" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="212"/>
-      <c r="N2" s="205" t="s">
+      <c r="M2" s="213"/>
+      <c r="N2" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="205"/>
+      <c r="O2" s="206"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -73503,30 +73506,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="212" t="s">
+      <c r="D2" s="213" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="212"/>
-      <c r="F2" s="213" t="s">
+      <c r="E2" s="213"/>
+      <c r="F2" s="214" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="213"/>
-      <c r="H2" s="212" t="s">
+      <c r="G2" s="214"/>
+      <c r="H2" s="213" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="212"/>
-      <c r="J2" s="213" t="s">
+      <c r="I2" s="213"/>
+      <c r="J2" s="214" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="213"/>
-      <c r="L2" s="212" t="s">
+      <c r="K2" s="214"/>
+      <c r="L2" s="213" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="212"/>
-      <c r="N2" s="205" t="s">
+      <c r="M2" s="213"/>
+      <c r="N2" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="205"/>
+      <c r="O2" s="206"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -75551,30 +75554,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="212" t="s">
+      <c r="D2" s="213" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="212"/>
-      <c r="F2" s="213" t="s">
+      <c r="E2" s="213"/>
+      <c r="F2" s="214" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="213"/>
-      <c r="H2" s="212" t="s">
+      <c r="G2" s="214"/>
+      <c r="H2" s="213" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="212"/>
-      <c r="J2" s="213" t="s">
+      <c r="I2" s="213"/>
+      <c r="J2" s="214" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="213"/>
-      <c r="L2" s="212" t="s">
+      <c r="K2" s="214"/>
+      <c r="L2" s="213" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="212"/>
-      <c r="N2" s="205" t="s">
+      <c r="M2" s="213"/>
+      <c r="N2" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="205"/>
+      <c r="O2" s="206"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -77259,30 +77262,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="212" t="s">
+      <c r="C2" s="213" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="212"/>
-      <c r="E2" s="213" t="s">
+      <c r="D2" s="213"/>
+      <c r="E2" s="214" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="213"/>
-      <c r="G2" s="212" t="s">
+      <c r="F2" s="214"/>
+      <c r="G2" s="213" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="212"/>
-      <c r="I2" s="213" t="s">
+      <c r="H2" s="213"/>
+      <c r="I2" s="214" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="213"/>
-      <c r="K2" s="212" t="s">
+      <c r="J2" s="214"/>
+      <c r="K2" s="213" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="212"/>
-      <c r="M2" s="205" t="s">
+      <c r="L2" s="213"/>
+      <c r="M2" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="205"/>
+      <c r="N2" s="206"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -79044,30 +79047,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="212" t="s">
+      <c r="C2" s="213" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="212"/>
-      <c r="E2" s="213" t="s">
+      <c r="D2" s="213"/>
+      <c r="E2" s="214" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="213"/>
-      <c r="G2" s="212" t="s">
+      <c r="F2" s="214"/>
+      <c r="G2" s="213" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="212"/>
-      <c r="I2" s="213" t="s">
+      <c r="H2" s="213"/>
+      <c r="I2" s="214" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="213"/>
-      <c r="K2" s="212" t="s">
+      <c r="J2" s="214"/>
+      <c r="K2" s="213" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="212"/>
-      <c r="M2" s="205" t="s">
+      <c r="L2" s="213"/>
+      <c r="M2" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="205"/>
+      <c r="N2" s="206"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">

--- a/data/arsenal_stats.xlsx
+++ b/data/arsenal_stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bungeltd-my.sharepoint.com/personal/przemyslaw_iskra_bunge_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8661" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0DAF3CF0-C3FB-4FDC-AA35-4AF0BAFBADDE}"/>
+  <xr:revisionPtr revIDLastSave="8679" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D61A02A5-AEDC-4FD6-A8F7-53E285334E56}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="799" firstSheet="1" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="799" firstSheet="1" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="19" state="hidden" r:id="rId1"/>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2277" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2279" uniqueCount="489">
   <si>
     <t>Arsenal FC squad statistics</t>
   </si>
@@ -3053,6 +3053,21 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3077,17 +3092,14 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3098,23 +3110,23 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="54" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3152,15 +3164,6 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="28" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3168,27 +3171,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="60" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="10" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="37" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="11" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3281,11 +3263,77 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="60" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="10" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="37" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="11" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="54" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3372,54 +3420,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -6484,7 +6484,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{1EECF14B-3885-4F6B-90AF-7109EA3999EC}" type="CELLRANGE">
+                    <a:fld id="{4786A9F6-9CE2-484D-863A-8D9EEF6C9A67}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6518,7 +6518,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{55440238-1EA6-449F-95FD-41D6F20F2F2C}" type="CELLRANGE">
+                    <a:fld id="{48D528F4-52B6-43FB-B985-444B268D58BD}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6552,7 +6552,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{DC5EB162-82C8-4FE6-99E2-D1A9EC6ECBD6}" type="CELLRANGE">
+                    <a:fld id="{7F6110BB-0686-4710-8543-05D273F98E06}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6586,7 +6586,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E20E35AB-3D12-46D5-8A5B-D36059947323}" type="CELLRANGE">
+                    <a:fld id="{F57E0001-B673-4275-BE5C-2974F37E38E8}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6620,7 +6620,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8D82C366-00D5-4F7B-BBB0-AAFE50F3E731}" type="CELLRANGE">
+                    <a:fld id="{57908D16-A707-4FE1-ADB6-B4F0E3F32071}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6654,7 +6654,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E698677A-7B5B-4B4F-AB9D-88BFB8B9DA8C}" type="CELLRANGE">
+                    <a:fld id="{FA12F139-FE87-427D-8C87-6CEE96D7F7DF}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6688,7 +6688,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{ABD7D148-1811-4C35-B163-EAEDEA51CBBE}" type="CELLRANGE">
+                    <a:fld id="{6F1FCFC3-8621-4C67-A866-DCEE2172C714}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6722,7 +6722,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{5C36AFAD-9C4A-4F19-9D64-1216E85D883A}" type="CELLRANGE">
+                    <a:fld id="{4B220D83-9BA5-4B8C-9BCE-7BB8BD5AE44F}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6756,7 +6756,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{167F2A7B-B394-48AC-A2EA-98AFA254036D}" type="CELLRANGE">
+                    <a:fld id="{661CC650-0950-4B66-B1AA-BFC9FB667972}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6790,7 +6790,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E2093DFE-F9D7-4AD5-A4BE-A3F826B605A9}" type="CELLRANGE">
+                    <a:fld id="{7688C2B5-EFE9-4361-9292-45503FC402FF}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6824,7 +6824,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{24F5BAB3-AA0E-43DD-8716-3EE9E9181131}" type="CELLRANGE">
+                    <a:fld id="{00818CA7-1E43-4113-B9FD-BB649D6DFB34}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6858,7 +6858,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{43B2D4D7-96A7-4D83-A4A9-AEDA00B3B488}" type="CELLRANGE">
+                    <a:fld id="{175B0745-5ACD-48C8-874B-B0C7CFFE957B}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6907,7 +6907,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{33EC7F9C-080C-48A8-9E63-5D3B0EDCB5AB}" type="CELLRANGE">
+                    <a:fld id="{7B637FCC-7019-4663-8F1C-EB7408FF9339}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr>
                         <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
@@ -6966,7 +6966,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{09A250CC-138B-40B4-AFCD-ED0C0C187D0A}" type="CELLRANGE">
+                    <a:fld id="{8A134787-70AA-437E-A8F9-A7DE1CC54D34}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7000,7 +7000,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8F698416-DF55-41EC-953E-FE8124265B61}" type="CELLRANGE">
+                    <a:fld id="{629F6D06-AE65-415A-813A-ACE26C3BF65E}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7034,7 +7034,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{FC7E52A3-AB5F-408F-9C7B-F61639121BE0}" type="CELLRANGE">
+                    <a:fld id="{9B6A8264-1166-4DB6-AA0B-5188D7E72867}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7068,7 +7068,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C852397F-1368-4D58-9F11-C695055A8B9A}" type="CELLRANGE">
+                    <a:fld id="{1003B611-C38E-4DF6-B027-4DBF581516E1}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -14204,30 +14204,30 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
       <c r="B1" s="5"/>
-      <c r="C1" s="213" t="s">
+      <c r="C1" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="213"/>
-      <c r="E1" s="214" t="s">
+      <c r="D1" s="206"/>
+      <c r="E1" s="207" t="s">
         <v>120</v>
       </c>
-      <c r="F1" s="214"/>
-      <c r="G1" s="213" t="s">
+      <c r="F1" s="207"/>
+      <c r="G1" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="H1" s="213"/>
-      <c r="I1" s="214" t="s">
+      <c r="H1" s="206"/>
+      <c r="I1" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="J1" s="214"/>
-      <c r="K1" s="213" t="s">
+      <c r="J1" s="207"/>
+      <c r="K1" s="206" t="s">
         <v>39</v>
       </c>
-      <c r="L1" s="213"/>
-      <c r="M1" s="211" t="s">
+      <c r="L1" s="206"/>
+      <c r="M1" s="204" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="212"/>
+      <c r="N1" s="205"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -15934,30 +15934,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="213" t="s">
+      <c r="C2" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="213"/>
-      <c r="E2" s="214" t="s">
+      <c r="D2" s="206"/>
+      <c r="E2" s="207" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="214"/>
-      <c r="G2" s="213" t="s">
+      <c r="F2" s="207"/>
+      <c r="G2" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="213"/>
-      <c r="I2" s="214" t="s">
+      <c r="H2" s="206"/>
+      <c r="I2" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="214"/>
-      <c r="K2" s="213" t="s">
+      <c r="J2" s="207"/>
+      <c r="K2" s="206" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="213"/>
-      <c r="M2" s="206" t="s">
+      <c r="L2" s="206"/>
+      <c r="M2" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="206"/>
+      <c r="N2" s="211"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -17761,30 +17761,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="213" t="s">
+      <c r="C2" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="213"/>
-      <c r="E2" s="214" t="s">
+      <c r="D2" s="206"/>
+      <c r="E2" s="207" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="214"/>
-      <c r="G2" s="213" t="s">
+      <c r="F2" s="207"/>
+      <c r="G2" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="213"/>
-      <c r="I2" s="214" t="s">
+      <c r="H2" s="206"/>
+      <c r="I2" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="214"/>
-      <c r="K2" s="213" t="s">
+      <c r="J2" s="207"/>
+      <c r="K2" s="206" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="213"/>
-      <c r="M2" s="206" t="s">
+      <c r="L2" s="206"/>
+      <c r="M2" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="206"/>
+      <c r="N2" s="211"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -19451,30 +19451,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="213" t="s">
+      <c r="C2" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="213"/>
-      <c r="E2" s="214" t="s">
+      <c r="D2" s="206"/>
+      <c r="E2" s="207" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="214"/>
-      <c r="G2" s="213" t="s">
+      <c r="F2" s="207"/>
+      <c r="G2" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="213"/>
-      <c r="I2" s="214" t="s">
+      <c r="H2" s="206"/>
+      <c r="I2" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="214"/>
-      <c r="K2" s="213" t="s">
+      <c r="J2" s="207"/>
+      <c r="K2" s="206" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="213"/>
-      <c r="M2" s="206" t="s">
+      <c r="L2" s="206"/>
+      <c r="M2" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="206"/>
+      <c r="N2" s="211"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -21277,30 +21277,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="213" t="s">
+      <c r="C2" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="213"/>
-      <c r="E2" s="214" t="s">
+      <c r="D2" s="206"/>
+      <c r="E2" s="207" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="214"/>
-      <c r="G2" s="213" t="s">
+      <c r="F2" s="207"/>
+      <c r="G2" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="213"/>
-      <c r="I2" s="214" t="s">
+      <c r="H2" s="206"/>
+      <c r="I2" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="214"/>
-      <c r="K2" s="213" t="s">
+      <c r="J2" s="207"/>
+      <c r="K2" s="206" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="213"/>
-      <c r="M2" s="206" t="s">
+      <c r="L2" s="206"/>
+      <c r="M2" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="206"/>
+      <c r="N2" s="211"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -23149,36 +23149,36 @@
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="203" t="s">
+      <c r="C2" s="208" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="204"/>
-      <c r="E2" s="205"/>
-      <c r="F2" s="208" t="s">
+      <c r="D2" s="209"/>
+      <c r="E2" s="210"/>
+      <c r="F2" s="213" t="s">
         <v>120</v>
       </c>
-      <c r="G2" s="209"/>
-      <c r="H2" s="210"/>
-      <c r="I2" s="203" t="s">
+      <c r="G2" s="214"/>
+      <c r="H2" s="215"/>
+      <c r="I2" s="208" t="s">
         <v>108</v>
       </c>
-      <c r="J2" s="204"/>
-      <c r="K2" s="205"/>
-      <c r="L2" s="208" t="s">
+      <c r="J2" s="209"/>
+      <c r="K2" s="210"/>
+      <c r="L2" s="213" t="s">
         <v>110</v>
       </c>
-      <c r="M2" s="209"/>
-      <c r="N2" s="210"/>
-      <c r="O2" s="203" t="s">
+      <c r="M2" s="214"/>
+      <c r="N2" s="215"/>
+      <c r="O2" s="208" t="s">
         <v>39</v>
       </c>
-      <c r="P2" s="204"/>
-      <c r="Q2" s="205"/>
-      <c r="R2" s="206" t="s">
+      <c r="P2" s="209"/>
+      <c r="Q2" s="210"/>
+      <c r="R2" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="S2" s="206"/>
-      <c r="T2" s="206"/>
+      <c r="S2" s="211"/>
+      <c r="T2" s="211"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -26117,36 +26117,36 @@
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
       <c r="D1" s="5"/>
-      <c r="E1" s="203" t="s">
+      <c r="E1" s="208" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="204"/>
-      <c r="G1" s="205"/>
-      <c r="H1" s="208" t="s">
+      <c r="F1" s="209"/>
+      <c r="G1" s="210"/>
+      <c r="H1" s="213" t="s">
         <v>120</v>
       </c>
-      <c r="I1" s="209"/>
-      <c r="J1" s="210"/>
-      <c r="K1" s="203" t="s">
+      <c r="I1" s="214"/>
+      <c r="J1" s="215"/>
+      <c r="K1" s="208" t="s">
         <v>108</v>
       </c>
-      <c r="L1" s="204"/>
-      <c r="M1" s="205"/>
-      <c r="N1" s="208" t="s">
+      <c r="L1" s="209"/>
+      <c r="M1" s="210"/>
+      <c r="N1" s="213" t="s">
         <v>110</v>
       </c>
-      <c r="O1" s="209"/>
-      <c r="P1" s="210"/>
-      <c r="Q1" s="203" t="s">
+      <c r="O1" s="214"/>
+      <c r="P1" s="215"/>
+      <c r="Q1" s="208" t="s">
         <v>39</v>
       </c>
-      <c r="R1" s="204"/>
-      <c r="S1" s="205"/>
-      <c r="T1" s="206" t="s">
+      <c r="R1" s="209"/>
+      <c r="S1" s="210"/>
+      <c r="T1" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="U1" s="206"/>
-      <c r="V1" s="206"/>
+      <c r="U1" s="211"/>
+      <c r="V1" s="211"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -37720,399 +37720,399 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F1" s="215">
-        <v>1</v>
-      </c>
-      <c r="G1" s="216"/>
-      <c r="H1" s="217"/>
-      <c r="I1" s="215">
+      <c r="F1" s="219">
+        <v>1</v>
+      </c>
+      <c r="G1" s="220"/>
+      <c r="H1" s="221"/>
+      <c r="I1" s="219">
         <v>2</v>
       </c>
-      <c r="J1" s="216"/>
-      <c r="K1" s="217"/>
-      <c r="L1" s="215">
-        <v>3</v>
-      </c>
-      <c r="M1" s="216"/>
-      <c r="N1" s="217"/>
-      <c r="O1" s="215">
+      <c r="J1" s="220"/>
+      <c r="K1" s="221"/>
+      <c r="L1" s="219">
+        <v>3</v>
+      </c>
+      <c r="M1" s="220"/>
+      <c r="N1" s="221"/>
+      <c r="O1" s="219">
         <v>4</v>
       </c>
-      <c r="P1" s="216"/>
-      <c r="Q1" s="217"/>
-      <c r="R1" s="215">
+      <c r="P1" s="220"/>
+      <c r="Q1" s="221"/>
+      <c r="R1" s="219">
         <v>5</v>
       </c>
-      <c r="S1" s="216"/>
-      <c r="T1" s="217"/>
-      <c r="U1" s="215">
+      <c r="S1" s="220"/>
+      <c r="T1" s="221"/>
+      <c r="U1" s="219">
         <v>6</v>
       </c>
-      <c r="V1" s="216"/>
-      <c r="W1" s="217"/>
-      <c r="X1" s="215">
+      <c r="V1" s="220"/>
+      <c r="W1" s="221"/>
+      <c r="X1" s="219">
         <v>7</v>
       </c>
-      <c r="Y1" s="216"/>
-      <c r="Z1" s="217"/>
-      <c r="AA1" s="215">
+      <c r="Y1" s="220"/>
+      <c r="Z1" s="221"/>
+      <c r="AA1" s="219">
         <v>8</v>
       </c>
-      <c r="AB1" s="216"/>
-      <c r="AC1" s="217"/>
-      <c r="AD1" s="215">
+      <c r="AB1" s="220"/>
+      <c r="AC1" s="221"/>
+      <c r="AD1" s="219">
         <v>9</v>
       </c>
-      <c r="AE1" s="216"/>
-      <c r="AF1" s="217"/>
-      <c r="AG1" s="215">
+      <c r="AE1" s="220"/>
+      <c r="AF1" s="221"/>
+      <c r="AG1" s="219">
         <v>10</v>
       </c>
-      <c r="AH1" s="216"/>
-      <c r="AI1" s="217"/>
-      <c r="AJ1" s="215">
+      <c r="AH1" s="220"/>
+      <c r="AI1" s="221"/>
+      <c r="AJ1" s="219">
         <v>11</v>
       </c>
-      <c r="AK1" s="216"/>
-      <c r="AL1" s="217"/>
-      <c r="AM1" s="215">
+      <c r="AK1" s="220"/>
+      <c r="AL1" s="221"/>
+      <c r="AM1" s="219">
         <v>12</v>
       </c>
-      <c r="AN1" s="216"/>
-      <c r="AO1" s="217"/>
-      <c r="AP1" s="215">
+      <c r="AN1" s="220"/>
+      <c r="AO1" s="221"/>
+      <c r="AP1" s="219">
         <v>13</v>
       </c>
-      <c r="AQ1" s="216"/>
-      <c r="AR1" s="217"/>
-      <c r="AS1" s="215">
+      <c r="AQ1" s="220"/>
+      <c r="AR1" s="221"/>
+      <c r="AS1" s="219">
         <v>14</v>
       </c>
-      <c r="AT1" s="216"/>
-      <c r="AU1" s="217"/>
-      <c r="AV1" s="215">
+      <c r="AT1" s="220"/>
+      <c r="AU1" s="221"/>
+      <c r="AV1" s="219">
         <v>15</v>
       </c>
-      <c r="AW1" s="216"/>
-      <c r="AX1" s="217"/>
-      <c r="AY1" s="215">
+      <c r="AW1" s="220"/>
+      <c r="AX1" s="221"/>
+      <c r="AY1" s="219">
         <v>16</v>
       </c>
-      <c r="AZ1" s="216"/>
-      <c r="BA1" s="217"/>
-      <c r="BB1" s="215">
+      <c r="AZ1" s="220"/>
+      <c r="BA1" s="221"/>
+      <c r="BB1" s="219">
         <v>17</v>
       </c>
-      <c r="BC1" s="216"/>
-      <c r="BD1" s="217"/>
-      <c r="BE1" s="215">
+      <c r="BC1" s="220"/>
+      <c r="BD1" s="221"/>
+      <c r="BE1" s="219">
         <v>18</v>
       </c>
-      <c r="BF1" s="216"/>
-      <c r="BG1" s="217"/>
-      <c r="BH1" s="215">
+      <c r="BF1" s="220"/>
+      <c r="BG1" s="221"/>
+      <c r="BH1" s="219">
         <v>19</v>
       </c>
-      <c r="BI1" s="216"/>
-      <c r="BJ1" s="217"/>
-      <c r="BK1" s="215">
+      <c r="BI1" s="220"/>
+      <c r="BJ1" s="221"/>
+      <c r="BK1" s="219">
         <v>20</v>
       </c>
-      <c r="BL1" s="216"/>
-      <c r="BM1" s="217"/>
-      <c r="BN1" s="215">
+      <c r="BL1" s="220"/>
+      <c r="BM1" s="221"/>
+      <c r="BN1" s="219">
         <v>21</v>
       </c>
-      <c r="BO1" s="216"/>
-      <c r="BP1" s="217"/>
-      <c r="BQ1" s="215">
+      <c r="BO1" s="220"/>
+      <c r="BP1" s="221"/>
+      <c r="BQ1" s="219">
         <v>22</v>
       </c>
-      <c r="BR1" s="216"/>
-      <c r="BS1" s="217"/>
-      <c r="BT1" s="215">
+      <c r="BR1" s="220"/>
+      <c r="BS1" s="221"/>
+      <c r="BT1" s="219">
         <v>23</v>
       </c>
-      <c r="BU1" s="216"/>
-      <c r="BV1" s="217"/>
-      <c r="BW1" s="215">
+      <c r="BU1" s="220"/>
+      <c r="BV1" s="221"/>
+      <c r="BW1" s="219">
         <v>24</v>
       </c>
-      <c r="BX1" s="216"/>
-      <c r="BY1" s="217"/>
-      <c r="BZ1" s="215">
+      <c r="BX1" s="220"/>
+      <c r="BY1" s="221"/>
+      <c r="BZ1" s="219">
         <v>25</v>
       </c>
-      <c r="CA1" s="216"/>
-      <c r="CB1" s="217"/>
-      <c r="CC1" s="215">
+      <c r="CA1" s="220"/>
+      <c r="CB1" s="221"/>
+      <c r="CC1" s="219">
         <v>26</v>
       </c>
-      <c r="CD1" s="216"/>
-      <c r="CE1" s="217"/>
-      <c r="CF1" s="215">
+      <c r="CD1" s="220"/>
+      <c r="CE1" s="221"/>
+      <c r="CF1" s="219">
         <v>27</v>
       </c>
-      <c r="CG1" s="216"/>
-      <c r="CH1" s="217"/>
-      <c r="CI1" s="215">
+      <c r="CG1" s="220"/>
+      <c r="CH1" s="221"/>
+      <c r="CI1" s="219">
         <v>28</v>
       </c>
-      <c r="CJ1" s="216"/>
-      <c r="CK1" s="217"/>
-      <c r="CL1" s="215">
+      <c r="CJ1" s="220"/>
+      <c r="CK1" s="221"/>
+      <c r="CL1" s="219">
         <v>29</v>
       </c>
-      <c r="CM1" s="216"/>
-      <c r="CN1" s="217"/>
-      <c r="CO1" s="215">
+      <c r="CM1" s="220"/>
+      <c r="CN1" s="221"/>
+      <c r="CO1" s="219">
         <v>30</v>
       </c>
-      <c r="CP1" s="216"/>
-      <c r="CQ1" s="217"/>
-      <c r="CR1" s="215">
+      <c r="CP1" s="220"/>
+      <c r="CQ1" s="221"/>
+      <c r="CR1" s="219">
         <v>31</v>
       </c>
-      <c r="CS1" s="216"/>
-      <c r="CT1" s="217"/>
-      <c r="CU1" s="215">
+      <c r="CS1" s="220"/>
+      <c r="CT1" s="221"/>
+      <c r="CU1" s="219">
         <v>32</v>
       </c>
-      <c r="CV1" s="216"/>
-      <c r="CW1" s="217"/>
-      <c r="CX1" s="215">
+      <c r="CV1" s="220"/>
+      <c r="CW1" s="221"/>
+      <c r="CX1" s="219">
         <v>33</v>
       </c>
-      <c r="CY1" s="216"/>
-      <c r="CZ1" s="217"/>
-      <c r="DA1" s="215">
+      <c r="CY1" s="220"/>
+      <c r="CZ1" s="221"/>
+      <c r="DA1" s="219">
         <v>34</v>
       </c>
-      <c r="DB1" s="216"/>
-      <c r="DC1" s="217"/>
-      <c r="DD1" s="215">
+      <c r="DB1" s="220"/>
+      <c r="DC1" s="221"/>
+      <c r="DD1" s="219">
         <v>35</v>
       </c>
-      <c r="DE1" s="216"/>
-      <c r="DF1" s="217"/>
-      <c r="DG1" s="215">
+      <c r="DE1" s="220"/>
+      <c r="DF1" s="221"/>
+      <c r="DG1" s="219">
         <v>36</v>
       </c>
-      <c r="DH1" s="216"/>
-      <c r="DI1" s="217"/>
-      <c r="DJ1" s="215">
+      <c r="DH1" s="220"/>
+      <c r="DI1" s="221"/>
+      <c r="DJ1" s="219">
         <v>37</v>
       </c>
-      <c r="DK1" s="216"/>
-      <c r="DL1" s="217"/>
-      <c r="DM1" s="215">
+      <c r="DK1" s="220"/>
+      <c r="DL1" s="221"/>
+      <c r="DM1" s="219">
         <v>38</v>
       </c>
-      <c r="DN1" s="216"/>
-      <c r="DO1" s="217"/>
+      <c r="DN1" s="220"/>
+      <c r="DO1" s="221"/>
     </row>
     <row r="2" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="221" t="s">
+      <c r="C2" s="222" t="s">
         <v>396</v>
       </c>
-      <c r="D2" s="221" t="s">
+      <c r="D2" s="222" t="s">
         <v>397</v>
       </c>
-      <c r="E2" s="221" t="s">
+      <c r="E2" s="222" t="s">
         <v>398</v>
       </c>
-      <c r="F2" s="218" t="s">
+      <c r="F2" s="216" t="s">
         <v>346</v>
       </c>
-      <c r="G2" s="219"/>
-      <c r="H2" s="220"/>
-      <c r="I2" s="218" t="s">
+      <c r="G2" s="217"/>
+      <c r="H2" s="218"/>
+      <c r="I2" s="216" t="s">
         <v>331</v>
       </c>
-      <c r="J2" s="219"/>
-      <c r="K2" s="220"/>
-      <c r="L2" s="218" t="s">
+      <c r="J2" s="217"/>
+      <c r="K2" s="218"/>
+      <c r="L2" s="216" t="s">
         <v>330</v>
       </c>
-      <c r="M2" s="219"/>
-      <c r="N2" s="220"/>
-      <c r="O2" s="218" t="s">
+      <c r="M2" s="217"/>
+      <c r="N2" s="218"/>
+      <c r="O2" s="216" t="s">
         <v>328</v>
       </c>
-      <c r="P2" s="219"/>
-      <c r="Q2" s="220"/>
-      <c r="R2" s="218" t="s">
+      <c r="P2" s="217"/>
+      <c r="Q2" s="218"/>
+      <c r="R2" s="216" t="s">
         <v>335</v>
       </c>
-      <c r="S2" s="219"/>
-      <c r="T2" s="220"/>
-      <c r="U2" s="218" t="s">
+      <c r="S2" s="217"/>
+      <c r="T2" s="218"/>
+      <c r="U2" s="216" t="s">
         <v>320</v>
       </c>
-      <c r="V2" s="219"/>
-      <c r="W2" s="220"/>
-      <c r="X2" s="218" t="s">
+      <c r="V2" s="217"/>
+      <c r="W2" s="218"/>
+      <c r="X2" s="216" t="s">
         <v>337</v>
       </c>
-      <c r="Y2" s="219"/>
-      <c r="Z2" s="220"/>
-      <c r="AA2" s="218" t="s">
+      <c r="Y2" s="217"/>
+      <c r="Z2" s="218"/>
+      <c r="AA2" s="216" t="s">
         <v>334</v>
       </c>
-      <c r="AB2" s="219"/>
-      <c r="AC2" s="220"/>
-      <c r="AD2" s="218" t="s">
+      <c r="AB2" s="217"/>
+      <c r="AC2" s="218"/>
+      <c r="AD2" s="216" t="s">
         <v>321</v>
       </c>
-      <c r="AE2" s="219"/>
-      <c r="AF2" s="220"/>
-      <c r="AG2" s="218" t="s">
+      <c r="AE2" s="217"/>
+      <c r="AF2" s="218"/>
+      <c r="AG2" s="216" t="s">
         <v>347</v>
       </c>
-      <c r="AH2" s="219"/>
-      <c r="AI2" s="220"/>
-      <c r="AJ2" s="218" t="s">
+      <c r="AH2" s="217"/>
+      <c r="AI2" s="218"/>
+      <c r="AJ2" s="216" t="s">
         <v>324</v>
       </c>
-      <c r="AK2" s="219"/>
-      <c r="AL2" s="220"/>
-      <c r="AM2" s="218" t="s">
+      <c r="AK2" s="217"/>
+      <c r="AL2" s="218"/>
+      <c r="AM2" s="216" t="s">
         <v>323</v>
       </c>
-      <c r="AN2" s="219"/>
-      <c r="AO2" s="220"/>
-      <c r="AP2" s="218" t="s">
+      <c r="AN2" s="217"/>
+      <c r="AO2" s="218"/>
+      <c r="AP2" s="216" t="s">
         <v>332</v>
       </c>
-      <c r="AQ2" s="219"/>
-      <c r="AR2" s="220"/>
-      <c r="AS2" s="218" t="s">
+      <c r="AQ2" s="217"/>
+      <c r="AR2" s="218"/>
+      <c r="AS2" s="216" t="s">
         <v>329</v>
       </c>
-      <c r="AT2" s="219"/>
-      <c r="AU2" s="220"/>
-      <c r="AV2" s="218" t="s">
+      <c r="AT2" s="217"/>
+      <c r="AU2" s="218"/>
+      <c r="AV2" s="216" t="s">
         <v>336</v>
       </c>
-      <c r="AW2" s="219"/>
-      <c r="AX2" s="220"/>
-      <c r="AY2" s="218" t="s">
+      <c r="AW2" s="217"/>
+      <c r="AX2" s="218"/>
+      <c r="AY2" s="216" t="s">
         <v>305</v>
       </c>
-      <c r="AZ2" s="219"/>
-      <c r="BA2" s="220"/>
-      <c r="BB2" s="218" t="s">
+      <c r="AZ2" s="217"/>
+      <c r="BA2" s="218"/>
+      <c r="BB2" s="216" t="s">
         <v>326</v>
       </c>
-      <c r="BC2" s="219"/>
-      <c r="BD2" s="220"/>
-      <c r="BE2" s="218" t="s">
+      <c r="BC2" s="217"/>
+      <c r="BD2" s="218"/>
+      <c r="BE2" s="216" t="s">
         <v>325</v>
       </c>
-      <c r="BF2" s="219"/>
-      <c r="BG2" s="220"/>
-      <c r="BH2" s="218" t="s">
+      <c r="BF2" s="217"/>
+      <c r="BG2" s="218"/>
+      <c r="BH2" s="216" t="s">
         <v>348</v>
       </c>
-      <c r="BI2" s="219"/>
-      <c r="BJ2" s="220"/>
-      <c r="BK2" s="218" t="s">
+      <c r="BI2" s="217"/>
+      <c r="BJ2" s="218"/>
+      <c r="BK2" s="216" t="s">
         <v>332</v>
       </c>
-      <c r="BL2" s="219"/>
-      <c r="BM2" s="220"/>
-      <c r="BN2" s="218" t="s">
+      <c r="BL2" s="217"/>
+      <c r="BM2" s="218"/>
+      <c r="BN2" s="216" t="s">
         <v>347</v>
       </c>
-      <c r="BO2" s="219"/>
-      <c r="BP2" s="220"/>
-      <c r="BQ2" s="218" t="s">
+      <c r="BO2" s="217"/>
+      <c r="BP2" s="218"/>
+      <c r="BQ2" s="216" t="s">
         <v>324</v>
       </c>
-      <c r="BR2" s="219"/>
-      <c r="BS2" s="220"/>
-      <c r="BT2" s="218" t="s">
+      <c r="BR2" s="217"/>
+      <c r="BS2" s="218"/>
+      <c r="BT2" s="216" t="s">
         <v>323</v>
       </c>
-      <c r="BU2" s="219"/>
-      <c r="BV2" s="220"/>
-      <c r="BW2" s="218" t="s">
+      <c r="BU2" s="217"/>
+      <c r="BV2" s="218"/>
+      <c r="BW2" s="216" t="s">
         <v>321</v>
       </c>
-      <c r="BX2" s="219"/>
-      <c r="BY2" s="220"/>
-      <c r="BZ2" s="218" t="s">
+      <c r="BX2" s="217"/>
+      <c r="BY2" s="218"/>
+      <c r="BZ2" s="216" t="s">
         <v>348</v>
       </c>
-      <c r="CA2" s="219"/>
-      <c r="CB2" s="220"/>
-      <c r="CC2" s="218" t="s">
+      <c r="CA2" s="217"/>
+      <c r="CB2" s="218"/>
+      <c r="CC2" s="216" t="s">
         <v>325</v>
       </c>
-      <c r="CD2" s="219"/>
-      <c r="CE2" s="220"/>
-      <c r="CF2" s="218" t="s">
+      <c r="CD2" s="217"/>
+      <c r="CE2" s="218"/>
+      <c r="CF2" s="216" t="s">
         <v>305</v>
       </c>
-      <c r="CG2" s="219"/>
-      <c r="CH2" s="220"/>
-      <c r="CI2" s="218" t="s">
+      <c r="CG2" s="217"/>
+      <c r="CH2" s="218"/>
+      <c r="CI2" s="216" t="s">
         <v>326</v>
       </c>
-      <c r="CJ2" s="219"/>
-      <c r="CK2" s="220"/>
-      <c r="CL2" s="218" t="s">
+      <c r="CJ2" s="217"/>
+      <c r="CK2" s="218"/>
+      <c r="CL2" s="216" t="s">
         <v>330</v>
       </c>
-      <c r="CM2" s="219"/>
-      <c r="CN2" s="220"/>
-      <c r="CO2" s="218" t="s">
+      <c r="CM2" s="217"/>
+      <c r="CN2" s="218"/>
+      <c r="CO2" s="216" t="s">
         <v>328</v>
       </c>
-      <c r="CP2" s="219"/>
-      <c r="CQ2" s="220"/>
-      <c r="CR2" s="218" t="s">
+      <c r="CP2" s="217"/>
+      <c r="CQ2" s="218"/>
+      <c r="CR2" s="216" t="s">
         <v>346</v>
       </c>
-      <c r="CS2" s="219"/>
-      <c r="CT2" s="220"/>
-      <c r="CU2" s="218" t="s">
+      <c r="CS2" s="217"/>
+      <c r="CT2" s="218"/>
+      <c r="CU2" s="216" t="s">
         <v>331</v>
       </c>
-      <c r="CV2" s="219"/>
-      <c r="CW2" s="220"/>
-      <c r="CX2" s="218" t="s">
+      <c r="CV2" s="217"/>
+      <c r="CW2" s="218"/>
+      <c r="CX2" s="216" t="s">
         <v>336</v>
       </c>
-      <c r="CY2" s="219"/>
-      <c r="CZ2" s="220"/>
-      <c r="DA2" s="218" t="s">
+      <c r="CY2" s="217"/>
+      <c r="CZ2" s="218"/>
+      <c r="DA2" s="216" t="s">
         <v>329</v>
       </c>
-      <c r="DB2" s="219"/>
-      <c r="DC2" s="220"/>
-      <c r="DD2" s="218" t="s">
+      <c r="DB2" s="217"/>
+      <c r="DC2" s="218"/>
+      <c r="DD2" s="216" t="s">
         <v>320</v>
       </c>
-      <c r="DE2" s="219"/>
-      <c r="DF2" s="220"/>
-      <c r="DG2" s="218" t="s">
+      <c r="DE2" s="217"/>
+      <c r="DF2" s="218"/>
+      <c r="DG2" s="216" t="s">
         <v>337</v>
       </c>
-      <c r="DH2" s="219"/>
-      <c r="DI2" s="220"/>
-      <c r="DJ2" s="218" t="s">
+      <c r="DH2" s="217"/>
+      <c r="DI2" s="218"/>
+      <c r="DJ2" s="216" t="s">
         <v>334</v>
       </c>
-      <c r="DK2" s="219"/>
-      <c r="DL2" s="220"/>
-      <c r="DM2" s="218" t="s">
+      <c r="DK2" s="217"/>
+      <c r="DL2" s="218"/>
+      <c r="DM2" s="216" t="s">
         <v>335</v>
       </c>
-      <c r="DN2" s="219"/>
-      <c r="DO2" s="220"/>
+      <c r="DN2" s="217"/>
+      <c r="DO2" s="218"/>
     </row>
     <row r="3" spans="1:119" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -38123,7 +38123,7 @@
       </c>
       <c r="C3" s="223"/>
       <c r="D3" s="223"/>
-      <c r="E3" s="222"/>
+      <c r="E3" s="224"/>
       <c r="F3" s="160" t="s">
         <v>393</v>
       </c>
@@ -43850,6 +43850,69 @@
     </row>
   </sheetData>
   <mergeCells count="79">
+    <mergeCell ref="DM1:DO1"/>
+    <mergeCell ref="DM2:DO2"/>
+    <mergeCell ref="DA1:DC1"/>
+    <mergeCell ref="DA2:DC2"/>
+    <mergeCell ref="DD1:DF1"/>
+    <mergeCell ref="DD2:DF2"/>
+    <mergeCell ref="DG1:DI1"/>
+    <mergeCell ref="DG2:DI2"/>
+    <mergeCell ref="CU1:CW1"/>
+    <mergeCell ref="CU2:CW2"/>
+    <mergeCell ref="CX1:CZ1"/>
+    <mergeCell ref="CX2:CZ2"/>
+    <mergeCell ref="DJ1:DL1"/>
+    <mergeCell ref="DJ2:DL2"/>
+    <mergeCell ref="CL1:CN1"/>
+    <mergeCell ref="CL2:CN2"/>
+    <mergeCell ref="CO1:CQ1"/>
+    <mergeCell ref="CO2:CQ2"/>
+    <mergeCell ref="CR1:CT1"/>
+    <mergeCell ref="CR2:CT2"/>
+    <mergeCell ref="CC1:CE1"/>
+    <mergeCell ref="CC2:CE2"/>
+    <mergeCell ref="CF1:CH1"/>
+    <mergeCell ref="CF2:CH2"/>
+    <mergeCell ref="CI1:CK1"/>
+    <mergeCell ref="CI2:CK2"/>
+    <mergeCell ref="BT1:BV1"/>
+    <mergeCell ref="BT2:BV2"/>
+    <mergeCell ref="BW1:BY1"/>
+    <mergeCell ref="BW2:BY2"/>
+    <mergeCell ref="BZ1:CB1"/>
+    <mergeCell ref="BZ2:CB2"/>
+    <mergeCell ref="BK1:BM1"/>
+    <mergeCell ref="BK2:BM2"/>
+    <mergeCell ref="BN1:BP1"/>
+    <mergeCell ref="BN2:BP2"/>
+    <mergeCell ref="BQ1:BS1"/>
+    <mergeCell ref="BQ2:BS2"/>
+    <mergeCell ref="AS1:AU1"/>
+    <mergeCell ref="AS2:AU2"/>
+    <mergeCell ref="AV1:AX1"/>
+    <mergeCell ref="AV2:AX2"/>
+    <mergeCell ref="BH1:BJ1"/>
+    <mergeCell ref="BH2:BJ2"/>
+    <mergeCell ref="AY2:BA2"/>
+    <mergeCell ref="BB2:BD2"/>
+    <mergeCell ref="BE2:BG2"/>
+    <mergeCell ref="AJ1:AL1"/>
+    <mergeCell ref="AJ2:AL2"/>
+    <mergeCell ref="AM1:AO1"/>
+    <mergeCell ref="AM2:AO2"/>
+    <mergeCell ref="AP2:AR2"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
     <mergeCell ref="AD2:AF2"/>
     <mergeCell ref="AG2:AI2"/>
     <mergeCell ref="BB1:BD1"/>
@@ -43866,69 +43929,6 @@
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="X1:Z1"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="AJ1:AL1"/>
-    <mergeCell ref="AJ2:AL2"/>
-    <mergeCell ref="AM1:AO1"/>
-    <mergeCell ref="AM2:AO2"/>
-    <mergeCell ref="AP2:AR2"/>
-    <mergeCell ref="AS1:AU1"/>
-    <mergeCell ref="AS2:AU2"/>
-    <mergeCell ref="AV1:AX1"/>
-    <mergeCell ref="AV2:AX2"/>
-    <mergeCell ref="BH1:BJ1"/>
-    <mergeCell ref="BH2:BJ2"/>
-    <mergeCell ref="AY2:BA2"/>
-    <mergeCell ref="BB2:BD2"/>
-    <mergeCell ref="BE2:BG2"/>
-    <mergeCell ref="BK1:BM1"/>
-    <mergeCell ref="BK2:BM2"/>
-    <mergeCell ref="BN1:BP1"/>
-    <mergeCell ref="BN2:BP2"/>
-    <mergeCell ref="BQ1:BS1"/>
-    <mergeCell ref="BQ2:BS2"/>
-    <mergeCell ref="BT1:BV1"/>
-    <mergeCell ref="BT2:BV2"/>
-    <mergeCell ref="BW1:BY1"/>
-    <mergeCell ref="BW2:BY2"/>
-    <mergeCell ref="BZ1:CB1"/>
-    <mergeCell ref="BZ2:CB2"/>
-    <mergeCell ref="CC1:CE1"/>
-    <mergeCell ref="CC2:CE2"/>
-    <mergeCell ref="CF1:CH1"/>
-    <mergeCell ref="CF2:CH2"/>
-    <mergeCell ref="CI1:CK1"/>
-    <mergeCell ref="CI2:CK2"/>
-    <mergeCell ref="CL1:CN1"/>
-    <mergeCell ref="CL2:CN2"/>
-    <mergeCell ref="CO1:CQ1"/>
-    <mergeCell ref="CO2:CQ2"/>
-    <mergeCell ref="CR1:CT1"/>
-    <mergeCell ref="CR2:CT2"/>
-    <mergeCell ref="CU1:CW1"/>
-    <mergeCell ref="CU2:CW2"/>
-    <mergeCell ref="CX1:CZ1"/>
-    <mergeCell ref="CX2:CZ2"/>
-    <mergeCell ref="DJ1:DL1"/>
-    <mergeCell ref="DJ2:DL2"/>
-    <mergeCell ref="DM1:DO1"/>
-    <mergeCell ref="DM2:DO2"/>
-    <mergeCell ref="DA1:DC1"/>
-    <mergeCell ref="DA2:DC2"/>
-    <mergeCell ref="DD1:DF1"/>
-    <mergeCell ref="DD2:DF2"/>
-    <mergeCell ref="DG1:DI1"/>
-    <mergeCell ref="DG2:DI2"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:DO38">
     <cfRule type="cellIs" dxfId="18" priority="1" operator="between">
@@ -43964,138 +43964,138 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="233" t="s">
+      <c r="C1" s="237" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="233" t="s">
+      <c r="D1" s="237" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="233" t="s">
+      <c r="E1" s="237" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="224" t="s">
+      <c r="F1" s="228" t="s">
         <v>302</v>
       </c>
-      <c r="G1" s="225"/>
-      <c r="H1" s="225"/>
-      <c r="I1" s="225"/>
-      <c r="J1" s="225"/>
-      <c r="K1" s="225"/>
-      <c r="L1" s="225"/>
-      <c r="M1" s="225"/>
-      <c r="N1" s="225"/>
-      <c r="O1" s="225"/>
-      <c r="P1" s="225"/>
-      <c r="Q1" s="225"/>
-      <c r="R1" s="225"/>
-      <c r="S1" s="225"/>
-      <c r="T1" s="225"/>
-      <c r="U1" s="225"/>
-      <c r="V1" s="225"/>
-      <c r="W1" s="225"/>
-      <c r="X1" s="225"/>
-      <c r="Y1" s="225"/>
-      <c r="Z1" s="225"/>
-      <c r="AA1" s="225"/>
-      <c r="AB1" s="225"/>
-      <c r="AC1" s="226"/>
-      <c r="AD1" s="239" t="s">
+      <c r="G1" s="229"/>
+      <c r="H1" s="229"/>
+      <c r="I1" s="229"/>
+      <c r="J1" s="229"/>
+      <c r="K1" s="229"/>
+      <c r="L1" s="229"/>
+      <c r="M1" s="229"/>
+      <c r="N1" s="229"/>
+      <c r="O1" s="229"/>
+      <c r="P1" s="229"/>
+      <c r="Q1" s="229"/>
+      <c r="R1" s="229"/>
+      <c r="S1" s="229"/>
+      <c r="T1" s="229"/>
+      <c r="U1" s="229"/>
+      <c r="V1" s="229"/>
+      <c r="W1" s="229"/>
+      <c r="X1" s="229"/>
+      <c r="Y1" s="229"/>
+      <c r="Z1" s="229"/>
+      <c r="AA1" s="229"/>
+      <c r="AB1" s="229"/>
+      <c r="AC1" s="230"/>
+      <c r="AD1" s="240" t="s">
         <v>281</v>
       </c>
-      <c r="AE1" s="240"/>
-      <c r="AF1" s="240"/>
-      <c r="AG1" s="240"/>
-      <c r="AH1" s="240"/>
-      <c r="AI1" s="241"/>
-      <c r="AJ1" s="224" t="s">
+      <c r="AE1" s="241"/>
+      <c r="AF1" s="241"/>
+      <c r="AG1" s="241"/>
+      <c r="AH1" s="241"/>
+      <c r="AI1" s="242"/>
+      <c r="AJ1" s="228" t="s">
         <v>282</v>
       </c>
-      <c r="AK1" s="225"/>
-      <c r="AL1" s="225"/>
-      <c r="AM1" s="225"/>
-      <c r="AN1" s="225"/>
-      <c r="AO1" s="226"/>
-      <c r="AP1" s="227" t="s">
+      <c r="AK1" s="229"/>
+      <c r="AL1" s="229"/>
+      <c r="AM1" s="229"/>
+      <c r="AN1" s="229"/>
+      <c r="AO1" s="230"/>
+      <c r="AP1" s="231" t="s">
         <v>283</v>
       </c>
-      <c r="AQ1" s="228"/>
-      <c r="AR1" s="228"/>
-      <c r="AS1" s="228"/>
-      <c r="AT1" s="228"/>
-      <c r="AU1" s="229"/>
-      <c r="AV1" s="230" t="s">
+      <c r="AQ1" s="232"/>
+      <c r="AR1" s="232"/>
+      <c r="AS1" s="232"/>
+      <c r="AT1" s="232"/>
+      <c r="AU1" s="233"/>
+      <c r="AV1" s="234" t="s">
         <v>86</v>
       </c>
-      <c r="AW1" s="231"/>
-      <c r="AX1" s="232"/>
+      <c r="AW1" s="235"/>
+      <c r="AX1" s="236"/>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="234"/>
-      <c r="D2" s="234"/>
-      <c r="E2" s="234"/>
-      <c r="F2" s="236" t="s">
+      <c r="C2" s="238"/>
+      <c r="D2" s="238"/>
+      <c r="E2" s="238"/>
+      <c r="F2" s="225" t="s">
         <v>458</v>
       </c>
-      <c r="G2" s="237"/>
-      <c r="H2" s="238"/>
-      <c r="I2" s="236" t="s">
+      <c r="G2" s="226"/>
+      <c r="H2" s="227"/>
+      <c r="I2" s="225" t="s">
         <v>461</v>
       </c>
-      <c r="J2" s="237"/>
-      <c r="K2" s="238"/>
-      <c r="L2" s="236" t="s">
+      <c r="J2" s="226"/>
+      <c r="K2" s="227"/>
+      <c r="L2" s="225" t="s">
         <v>462</v>
       </c>
-      <c r="M2" s="237"/>
-      <c r="N2" s="238"/>
-      <c r="O2" s="236" t="s">
+      <c r="M2" s="226"/>
+      <c r="N2" s="227"/>
+      <c r="O2" s="225" t="s">
         <v>463</v>
       </c>
-      <c r="P2" s="237"/>
-      <c r="Q2" s="238"/>
-      <c r="R2" s="236" t="s">
+      <c r="P2" s="226"/>
+      <c r="Q2" s="227"/>
+      <c r="R2" s="225" t="s">
         <v>464</v>
       </c>
-      <c r="S2" s="237"/>
-      <c r="T2" s="238"/>
-      <c r="U2" s="236" t="s">
+      <c r="S2" s="226"/>
+      <c r="T2" s="227"/>
+      <c r="U2" s="225" t="s">
         <v>465</v>
       </c>
-      <c r="V2" s="237"/>
-      <c r="W2" s="238"/>
-      <c r="X2" s="236" t="s">
+      <c r="V2" s="226"/>
+      <c r="W2" s="227"/>
+      <c r="X2" s="225" t="s">
         <v>466</v>
       </c>
-      <c r="Y2" s="237"/>
-      <c r="Z2" s="238"/>
-      <c r="AA2" s="236" t="s">
+      <c r="Y2" s="226"/>
+      <c r="Z2" s="227"/>
+      <c r="AA2" s="225" t="s">
         <v>467</v>
       </c>
-      <c r="AB2" s="237"/>
-      <c r="AC2" s="237"/>
-      <c r="AD2" s="236"/>
-      <c r="AE2" s="237"/>
-      <c r="AF2" s="238"/>
-      <c r="AG2" s="236"/>
-      <c r="AH2" s="237"/>
-      <c r="AI2" s="238"/>
-      <c r="AJ2" s="236"/>
-      <c r="AK2" s="237"/>
-      <c r="AL2" s="238"/>
-      <c r="AM2" s="236"/>
-      <c r="AN2" s="237"/>
-      <c r="AO2" s="238"/>
-      <c r="AP2" s="236"/>
-      <c r="AQ2" s="237"/>
-      <c r="AR2" s="238"/>
-      <c r="AS2" s="236"/>
-      <c r="AT2" s="237"/>
-      <c r="AU2" s="238"/>
-      <c r="AV2" s="236"/>
-      <c r="AW2" s="237"/>
-      <c r="AX2" s="238"/>
+      <c r="AB2" s="226"/>
+      <c r="AC2" s="226"/>
+      <c r="AD2" s="225"/>
+      <c r="AE2" s="226"/>
+      <c r="AF2" s="227"/>
+      <c r="AG2" s="225"/>
+      <c r="AH2" s="226"/>
+      <c r="AI2" s="227"/>
+      <c r="AJ2" s="225"/>
+      <c r="AK2" s="226"/>
+      <c r="AL2" s="227"/>
+      <c r="AM2" s="225"/>
+      <c r="AN2" s="226"/>
+      <c r="AO2" s="227"/>
+      <c r="AP2" s="225"/>
+      <c r="AQ2" s="226"/>
+      <c r="AR2" s="227"/>
+      <c r="AS2" s="225"/>
+      <c r="AT2" s="226"/>
+      <c r="AU2" s="227"/>
+      <c r="AV2" s="225"/>
+      <c r="AW2" s="226"/>
+      <c r="AX2" s="227"/>
     </row>
     <row r="3" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -44104,9 +44104,9 @@
       <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="235"/>
-      <c r="D3" s="235"/>
-      <c r="E3" s="235"/>
+      <c r="C3" s="239"/>
+      <c r="D3" s="239"/>
+      <c r="E3" s="239"/>
       <c r="F3" s="169" t="s">
         <v>393</v>
       </c>
@@ -46738,13 +46738,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="F1:AC1"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="AJ1:AO1"/>
     <mergeCell ref="AP1:AU1"/>
     <mergeCell ref="AV1:AX1"/>
@@ -46761,6 +46754,13 @@
     <mergeCell ref="AD1:AI1"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="I2:K2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="F1:AC1"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
+    <mergeCell ref="AA2:AC2"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:AW32">
     <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
@@ -46795,70 +46795,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C1" s="233" t="s">
+      <c r="C1" s="237" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="233" t="s">
+      <c r="D1" s="237" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="233" t="s">
+      <c r="E1" s="237" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="273" t="s">
+      <c r="F1" s="267" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="274"/>
-      <c r="H1" s="275"/>
-      <c r="I1" s="276" t="s">
+      <c r="G1" s="268"/>
+      <c r="H1" s="269"/>
+      <c r="I1" s="270" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="277"/>
-      <c r="K1" s="278"/>
-      <c r="L1" s="243" t="s">
+      <c r="J1" s="271"/>
+      <c r="K1" s="272"/>
+      <c r="L1" s="274" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="244"/>
-      <c r="N1" s="245"/>
-      <c r="O1" s="246" t="s">
+      <c r="M1" s="275"/>
+      <c r="N1" s="276"/>
+      <c r="O1" s="277" t="s">
         <v>199</v>
       </c>
-      <c r="P1" s="247"/>
-      <c r="Q1" s="248"/>
-      <c r="R1" s="249" t="s">
+      <c r="P1" s="278"/>
+      <c r="Q1" s="279"/>
+      <c r="R1" s="243" t="s">
         <v>200</v>
       </c>
-      <c r="S1" s="250"/>
-      <c r="T1" s="251"/>
-      <c r="U1" s="252" t="s">
+      <c r="S1" s="244"/>
+      <c r="T1" s="245"/>
+      <c r="U1" s="246" t="s">
         <v>306</v>
       </c>
-      <c r="V1" s="253"/>
-      <c r="W1" s="254"/>
+      <c r="V1" s="247"/>
+      <c r="W1" s="248"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="234"/>
-      <c r="D2" s="234"/>
-      <c r="E2" s="234"/>
-      <c r="F2" s="255"/>
-      <c r="G2" s="256"/>
-      <c r="H2" s="257"/>
-      <c r="I2" s="270"/>
-      <c r="J2" s="271"/>
-      <c r="K2" s="272"/>
-      <c r="L2" s="267"/>
-      <c r="M2" s="268"/>
-      <c r="N2" s="269"/>
-      <c r="O2" s="264"/>
-      <c r="P2" s="265"/>
-      <c r="Q2" s="266"/>
-      <c r="R2" s="261"/>
-      <c r="S2" s="262"/>
-      <c r="T2" s="263"/>
-      <c r="U2" s="258"/>
-      <c r="V2" s="259"/>
-      <c r="W2" s="260"/>
+      <c r="C2" s="238"/>
+      <c r="D2" s="238"/>
+      <c r="E2" s="238"/>
+      <c r="F2" s="249"/>
+      <c r="G2" s="250"/>
+      <c r="H2" s="251"/>
+      <c r="I2" s="264"/>
+      <c r="J2" s="265"/>
+      <c r="K2" s="266"/>
+      <c r="L2" s="261"/>
+      <c r="M2" s="262"/>
+      <c r="N2" s="263"/>
+      <c r="O2" s="258"/>
+      <c r="P2" s="259"/>
+      <c r="Q2" s="260"/>
+      <c r="R2" s="255"/>
+      <c r="S2" s="256"/>
+      <c r="T2" s="257"/>
+      <c r="U2" s="252"/>
+      <c r="V2" s="253"/>
+      <c r="W2" s="254"/>
     </row>
     <row r="3" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -46867,9 +46867,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="242"/>
-      <c r="D3" s="242"/>
-      <c r="E3" s="242"/>
+      <c r="C3" s="273"/>
+      <c r="D3" s="273"/>
+      <c r="E3" s="273"/>
       <c r="F3" s="188" t="s">
         <v>393</v>
       </c>
@@ -48331,6 +48331,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="O1:Q1"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="F2:H2"/>
@@ -48341,11 +48346,6 @@
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="O1:Q1"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:W32">
     <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
@@ -55352,72 +55352,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C1" s="233" t="s">
+      <c r="C1" s="237" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="233" t="s">
+      <c r="D1" s="237" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="233" t="s">
+      <c r="E1" s="237" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="273" t="s">
+      <c r="F1" s="267" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="274"/>
-      <c r="H1" s="275"/>
-      <c r="I1" s="276" t="s">
+      <c r="G1" s="268"/>
+      <c r="H1" s="269"/>
+      <c r="I1" s="270" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="277"/>
-      <c r="K1" s="278"/>
-      <c r="L1" s="243" t="s">
+      <c r="J1" s="271"/>
+      <c r="K1" s="272"/>
+      <c r="L1" s="274" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="244"/>
-      <c r="N1" s="245"/>
-      <c r="O1" s="246" t="s">
+      <c r="M1" s="275"/>
+      <c r="N1" s="276"/>
+      <c r="O1" s="277" t="s">
         <v>199</v>
       </c>
-      <c r="P1" s="247"/>
-      <c r="Q1" s="248"/>
-      <c r="R1" s="249" t="s">
+      <c r="P1" s="278"/>
+      <c r="Q1" s="279"/>
+      <c r="R1" s="243" t="s">
         <v>200</v>
       </c>
-      <c r="S1" s="250"/>
-      <c r="T1" s="251"/>
-      <c r="U1" s="252" t="s">
+      <c r="S1" s="244"/>
+      <c r="T1" s="245"/>
+      <c r="U1" s="246" t="s">
         <v>306</v>
       </c>
-      <c r="V1" s="253"/>
-      <c r="W1" s="254"/>
+      <c r="V1" s="247"/>
+      <c r="W1" s="248"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="234"/>
-      <c r="D2" s="234"/>
-      <c r="E2" s="234"/>
-      <c r="F2" s="255" t="s">
+      <c r="C2" s="238"/>
+      <c r="D2" s="238"/>
+      <c r="E2" s="238"/>
+      <c r="F2" s="249" t="s">
         <v>432</v>
       </c>
-      <c r="G2" s="256"/>
-      <c r="H2" s="257"/>
-      <c r="I2" s="270"/>
-      <c r="J2" s="271"/>
-      <c r="K2" s="272"/>
-      <c r="L2" s="267"/>
-      <c r="M2" s="268"/>
-      <c r="N2" s="269"/>
-      <c r="O2" s="264"/>
-      <c r="P2" s="265"/>
-      <c r="Q2" s="266"/>
-      <c r="R2" s="261"/>
-      <c r="S2" s="262"/>
-      <c r="T2" s="263"/>
-      <c r="U2" s="258"/>
-      <c r="V2" s="259"/>
-      <c r="W2" s="260"/>
+      <c r="G2" s="250"/>
+      <c r="H2" s="251"/>
+      <c r="I2" s="264"/>
+      <c r="J2" s="265"/>
+      <c r="K2" s="266"/>
+      <c r="L2" s="261"/>
+      <c r="M2" s="262"/>
+      <c r="N2" s="263"/>
+      <c r="O2" s="258"/>
+      <c r="P2" s="259"/>
+      <c r="Q2" s="260"/>
+      <c r="R2" s="255"/>
+      <c r="S2" s="256"/>
+      <c r="T2" s="257"/>
+      <c r="U2" s="252"/>
+      <c r="V2" s="253"/>
+      <c r="W2" s="254"/>
     </row>
     <row r="3" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -55426,9 +55426,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="242"/>
-      <c r="D3" s="242"/>
-      <c r="E3" s="242"/>
+      <c r="C3" s="273"/>
+      <c r="D3" s="273"/>
+      <c r="E3" s="273"/>
       <c r="F3" s="188" t="s">
         <v>393</v>
       </c>
@@ -56932,11 +56932,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="F2:H2"/>
@@ -56947,6 +56942,11 @@
     <mergeCell ref="U2:W2"/>
     <mergeCell ref="L1:N1"/>
     <mergeCell ref="O1:Q1"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:W32">
     <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
@@ -56974,11 +56974,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C1" s="279" t="s">
+      <c r="C1" s="280" t="s">
         <v>340</v>
       </c>
-      <c r="D1" s="280"/>
-      <c r="E1" s="280"/>
+      <c r="D1" s="281"/>
+      <c r="E1" s="281"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -57453,51 +57453,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="310" t="s">
+      <c r="C1" s="282" t="s">
         <v>202</v>
       </c>
-      <c r="D1" s="311"/>
-      <c r="E1" s="311"/>
-      <c r="F1" s="311"/>
-      <c r="G1" s="311"/>
-      <c r="H1" s="311"/>
-      <c r="I1" s="312"/>
+      <c r="D1" s="283"/>
+      <c r="E1" s="283"/>
+      <c r="F1" s="283"/>
+      <c r="G1" s="283"/>
+      <c r="H1" s="283"/>
+      <c r="I1" s="284"/>
       <c r="J1" s="114" t="s">
         <v>195</v>
       </c>
       <c r="K1" s="115" t="s">
         <v>194</v>
       </c>
-      <c r="L1" s="290" t="s">
+      <c r="L1" s="306" t="s">
         <v>287</v>
       </c>
-      <c r="M1" s="295"/>
-      <c r="N1" s="295"/>
-      <c r="O1" s="295"/>
-      <c r="P1" s="295"/>
-      <c r="Q1" s="295"/>
-      <c r="R1" s="295"/>
-      <c r="S1" s="295"/>
-      <c r="T1" s="295"/>
-      <c r="U1" s="295"/>
-      <c r="V1" s="295"/>
-      <c r="W1" s="295"/>
-      <c r="X1" s="295"/>
-      <c r="Y1" s="295"/>
-      <c r="Z1" s="295"/>
-      <c r="AA1" s="295"/>
-      <c r="AB1" s="295"/>
-      <c r="AC1" s="295"/>
-      <c r="AD1" s="295"/>
-      <c r="AE1" s="295"/>
-      <c r="AF1" s="295"/>
-      <c r="AG1" s="296"/>
-      <c r="AH1" s="290" t="s">
+      <c r="M1" s="311"/>
+      <c r="N1" s="311"/>
+      <c r="O1" s="311"/>
+      <c r="P1" s="311"/>
+      <c r="Q1" s="311"/>
+      <c r="R1" s="311"/>
+      <c r="S1" s="311"/>
+      <c r="T1" s="311"/>
+      <c r="U1" s="311"/>
+      <c r="V1" s="311"/>
+      <c r="W1" s="311"/>
+      <c r="X1" s="311"/>
+      <c r="Y1" s="311"/>
+      <c r="Z1" s="311"/>
+      <c r="AA1" s="311"/>
+      <c r="AB1" s="311"/>
+      <c r="AC1" s="311"/>
+      <c r="AD1" s="311"/>
+      <c r="AE1" s="311"/>
+      <c r="AF1" s="311"/>
+      <c r="AG1" s="312"/>
+      <c r="AH1" s="306" t="s">
         <v>175</v>
       </c>
-      <c r="AI1" s="291"/>
-      <c r="AJ1" s="291"/>
-      <c r="AK1" s="292"/>
+      <c r="AI1" s="307"/>
+      <c r="AJ1" s="307"/>
+      <c r="AK1" s="308"/>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B2" s="111"/>
@@ -62697,15 +62697,15 @@
         <f t="shared" ref="J80:J111" si="2">H80-I80</f>
         <v>2</v>
       </c>
-      <c r="K80" s="297" t="s">
+      <c r="K80" s="313" t="s">
         <v>434</v>
       </c>
-      <c r="L80" s="298"/>
-      <c r="M80" s="299"/>
+      <c r="L80" s="314"/>
+      <c r="M80" s="315"/>
       <c r="O80" s="133"/>
       <c r="P80" s="133"/>
-      <c r="W80" s="293"/>
-      <c r="X80" s="293"/>
+      <c r="W80" s="309"/>
+      <c r="X80" s="309"/>
       <c r="Y80" s="70" t="s">
         <v>211</v>
       </c>
@@ -62755,15 +62755,15 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K81" s="300"/>
-      <c r="L81" s="301"/>
-      <c r="M81" s="302"/>
+      <c r="K81" s="316"/>
+      <c r="L81" s="317"/>
+      <c r="M81" s="318"/>
       <c r="O81" s="133"/>
       <c r="P81" s="133"/>
-      <c r="W81" s="293" t="s">
+      <c r="W81" s="309" t="s">
         <v>209</v>
       </c>
-      <c r="X81" s="293"/>
+      <c r="X81" s="309"/>
       <c r="Y81" s="70">
         <f>COUNTIF(L3:AG40,3)</f>
         <v>481</v>
@@ -62819,17 +62819,17 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K82" s="303" t="s">
+      <c r="K82" s="319" t="s">
         <v>435</v>
       </c>
-      <c r="L82" s="304"/>
-      <c r="M82" s="305"/>
+      <c r="L82" s="320"/>
+      <c r="M82" s="321"/>
       <c r="O82" s="133"/>
       <c r="P82" s="133"/>
-      <c r="W82" s="293" t="s">
+      <c r="W82" s="309" t="s">
         <v>210</v>
       </c>
-      <c r="X82" s="293"/>
+      <c r="X82" s="309"/>
       <c r="Y82" s="70">
         <f>COUNTIF(K3:K40,3)+COUNTIF(J3:J15,3)</f>
         <v>25</v>
@@ -62885,17 +62885,17 @@
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="K83" s="306" t="s">
+      <c r="K83" s="322" t="s">
         <v>436</v>
       </c>
-      <c r="L83" s="307"/>
-      <c r="M83" s="308"/>
+      <c r="L83" s="323"/>
+      <c r="M83" s="324"/>
       <c r="O83" s="133"/>
       <c r="P83" s="133"/>
-      <c r="W83" s="294" t="s">
+      <c r="W83" s="310" t="s">
         <v>97</v>
       </c>
-      <c r="X83" s="294"/>
+      <c r="X83" s="310"/>
       <c r="Y83" s="194">
         <v>224</v>
       </c>
@@ -62948,15 +62948,15 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="K84" s="316" t="s">
+      <c r="K84" s="288" t="s">
         <v>284</v>
       </c>
-      <c r="L84" s="317"/>
-      <c r="M84" s="318"/>
+      <c r="L84" s="289"/>
+      <c r="M84" s="290"/>
       <c r="O84" s="141"/>
       <c r="P84" s="141"/>
-      <c r="W84" s="309"/>
-      <c r="X84" s="309"/>
+      <c r="W84" s="325"/>
+      <c r="X84" s="325"/>
       <c r="Y84" s="196"/>
       <c r="Z84" s="196"/>
       <c r="AA84" s="196"/>
@@ -62994,9 +62994,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K85" s="319"/>
-      <c r="L85" s="320"/>
-      <c r="M85" s="321"/>
+      <c r="K85" s="291"/>
+      <c r="L85" s="292"/>
+      <c r="M85" s="293"/>
       <c r="O85" s="141"/>
       <c r="P85" s="141"/>
     </row>
@@ -63030,9 +63030,9 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="K86" s="319"/>
-      <c r="L86" s="320"/>
-      <c r="M86" s="321"/>
+      <c r="K86" s="291"/>
+      <c r="L86" s="292"/>
+      <c r="M86" s="293"/>
       <c r="O86" s="141"/>
       <c r="P86" s="141"/>
     </row>
@@ -63066,9 +63066,9 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="K87" s="319"/>
-      <c r="L87" s="320"/>
-      <c r="M87" s="321"/>
+      <c r="K87" s="291"/>
+      <c r="L87" s="292"/>
+      <c r="M87" s="293"/>
       <c r="O87" s="141"/>
       <c r="P87" s="141"/>
     </row>
@@ -63102,9 +63102,9 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K88" s="319"/>
-      <c r="L88" s="320"/>
-      <c r="M88" s="321"/>
+      <c r="K88" s="291"/>
+      <c r="L88" s="292"/>
+      <c r="M88" s="293"/>
       <c r="O88" s="141"/>
       <c r="P88" s="141"/>
     </row>
@@ -63138,9 +63138,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K89" s="319"/>
-      <c r="L89" s="320"/>
-      <c r="M89" s="321"/>
+      <c r="K89" s="291"/>
+      <c r="L89" s="292"/>
+      <c r="M89" s="293"/>
       <c r="O89" s="141"/>
       <c r="P89" s="141"/>
     </row>
@@ -63174,9 +63174,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K90" s="319"/>
-      <c r="L90" s="320"/>
-      <c r="M90" s="321"/>
+      <c r="K90" s="291"/>
+      <c r="L90" s="292"/>
+      <c r="M90" s="293"/>
       <c r="O90" s="141"/>
       <c r="P90" s="141"/>
     </row>
@@ -63210,9 +63210,9 @@
         <f t="shared" si="2"/>
         <v>47</v>
       </c>
-      <c r="K91" s="319"/>
-      <c r="L91" s="320"/>
-      <c r="M91" s="321"/>
+      <c r="K91" s="291"/>
+      <c r="L91" s="292"/>
+      <c r="M91" s="293"/>
       <c r="O91" s="141"/>
       <c r="P91" s="141"/>
     </row>
@@ -63246,9 +63246,9 @@
         <f t="shared" si="2"/>
         <v>51</v>
       </c>
-      <c r="K92" s="319"/>
-      <c r="L92" s="320"/>
-      <c r="M92" s="321"/>
+      <c r="K92" s="291"/>
+      <c r="L92" s="292"/>
+      <c r="M92" s="293"/>
       <c r="O92" s="141"/>
       <c r="P92" s="141"/>
     </row>
@@ -63282,9 +63282,9 @@
         <f t="shared" si="2"/>
         <v>37</v>
       </c>
-      <c r="K93" s="319"/>
-      <c r="L93" s="320"/>
-      <c r="M93" s="321"/>
+      <c r="K93" s="291"/>
+      <c r="L93" s="292"/>
+      <c r="M93" s="293"/>
       <c r="O93" s="141"/>
       <c r="P93" s="141"/>
     </row>
@@ -63318,9 +63318,9 @@
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="K94" s="319"/>
-      <c r="L94" s="320"/>
-      <c r="M94" s="321"/>
+      <c r="K94" s="291"/>
+      <c r="L94" s="292"/>
+      <c r="M94" s="293"/>
       <c r="O94" s="141"/>
       <c r="P94" s="141"/>
     </row>
@@ -63354,9 +63354,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K95" s="319"/>
-      <c r="L95" s="320"/>
-      <c r="M95" s="321"/>
+      <c r="K95" s="291"/>
+      <c r="L95" s="292"/>
+      <c r="M95" s="293"/>
       <c r="O95" s="141"/>
       <c r="P95" s="141"/>
     </row>
@@ -63390,9 +63390,9 @@
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="K96" s="319"/>
-      <c r="L96" s="320"/>
-      <c r="M96" s="321"/>
+      <c r="K96" s="291"/>
+      <c r="L96" s="292"/>
+      <c r="M96" s="293"/>
       <c r="O96" s="141"/>
       <c r="P96" s="141"/>
     </row>
@@ -63426,9 +63426,9 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="K97" s="319"/>
-      <c r="L97" s="320"/>
-      <c r="M97" s="321"/>
+      <c r="K97" s="291"/>
+      <c r="L97" s="292"/>
+      <c r="M97" s="293"/>
       <c r="O97" s="141"/>
       <c r="P97" s="141"/>
     </row>
@@ -63462,9 +63462,9 @@
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="K98" s="319"/>
-      <c r="L98" s="320"/>
-      <c r="M98" s="321"/>
+      <c r="K98" s="291"/>
+      <c r="L98" s="292"/>
+      <c r="M98" s="293"/>
       <c r="O98" s="141"/>
       <c r="P98" s="141"/>
     </row>
@@ -63498,9 +63498,9 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K99" s="319"/>
-      <c r="L99" s="320"/>
-      <c r="M99" s="321"/>
+      <c r="K99" s="291"/>
+      <c r="L99" s="292"/>
+      <c r="M99" s="293"/>
       <c r="O99" s="141"/>
       <c r="P99" s="141"/>
     </row>
@@ -63534,9 +63534,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K100" s="319"/>
-      <c r="L100" s="320"/>
-      <c r="M100" s="321"/>
+      <c r="K100" s="291"/>
+      <c r="L100" s="292"/>
+      <c r="M100" s="293"/>
       <c r="O100" s="141"/>
       <c r="P100" s="141"/>
     </row>
@@ -63570,9 +63570,9 @@
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="K101" s="319"/>
-      <c r="L101" s="320"/>
-      <c r="M101" s="321"/>
+      <c r="K101" s="291"/>
+      <c r="L101" s="292"/>
+      <c r="M101" s="293"/>
       <c r="O101" s="141"/>
       <c r="P101" s="141"/>
     </row>
@@ -63606,9 +63606,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K102" s="319"/>
-      <c r="L102" s="320"/>
-      <c r="M102" s="321"/>
+      <c r="K102" s="291"/>
+      <c r="L102" s="292"/>
+      <c r="M102" s="293"/>
       <c r="O102" s="141"/>
       <c r="P102" s="141"/>
     </row>
@@ -63642,9 +63642,9 @@
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="K103" s="319"/>
-      <c r="L103" s="320"/>
-      <c r="M103" s="321"/>
+      <c r="K103" s="291"/>
+      <c r="L103" s="292"/>
+      <c r="M103" s="293"/>
       <c r="O103" s="141"/>
       <c r="P103" s="141"/>
     </row>
@@ -63678,9 +63678,9 @@
         <f t="shared" si="2"/>
         <v>33</v>
       </c>
-      <c r="K104" s="319"/>
-      <c r="L104" s="320"/>
-      <c r="M104" s="321"/>
+      <c r="K104" s="291"/>
+      <c r="L104" s="292"/>
+      <c r="M104" s="293"/>
       <c r="O104" s="141"/>
       <c r="P104" s="141"/>
     </row>
@@ -63714,9 +63714,9 @@
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="K105" s="322"/>
-      <c r="L105" s="323"/>
-      <c r="M105" s="324"/>
+      <c r="K105" s="294"/>
+      <c r="L105" s="295"/>
+      <c r="M105" s="296"/>
       <c r="O105" s="141"/>
       <c r="P105" s="141"/>
     </row>
@@ -63750,11 +63750,11 @@
         <f t="shared" si="2"/>
         <v>21</v>
       </c>
-      <c r="K106" s="313" t="s">
+      <c r="K106" s="285" t="s">
         <v>286</v>
       </c>
-      <c r="L106" s="314"/>
-      <c r="M106" s="315"/>
+      <c r="L106" s="286"/>
+      <c r="M106" s="287"/>
       <c r="O106" s="126"/>
       <c r="P106" s="126"/>
     </row>
@@ -63788,11 +63788,11 @@
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="K107" s="313" t="s">
+      <c r="K107" s="285" t="s">
         <v>288</v>
       </c>
-      <c r="L107" s="314"/>
-      <c r="M107" s="315"/>
+      <c r="L107" s="286"/>
+      <c r="M107" s="287"/>
       <c r="O107" s="126"/>
       <c r="P107" s="126"/>
     </row>
@@ -63826,11 +63826,11 @@
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="K108" s="281" t="s">
+      <c r="K108" s="297" t="s">
         <v>289</v>
       </c>
-      <c r="L108" s="282"/>
-      <c r="M108" s="283"/>
+      <c r="L108" s="298"/>
+      <c r="M108" s="299"/>
       <c r="O108" s="126"/>
       <c r="P108" s="126"/>
     </row>
@@ -63864,9 +63864,9 @@
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="K109" s="284"/>
-      <c r="L109" s="285"/>
-      <c r="M109" s="286"/>
+      <c r="K109" s="300"/>
+      <c r="L109" s="301"/>
+      <c r="M109" s="302"/>
       <c r="O109" s="126"/>
       <c r="P109" s="126"/>
     </row>
@@ -63900,9 +63900,9 @@
         <f t="shared" si="2"/>
         <v>45</v>
       </c>
-      <c r="K110" s="284"/>
-      <c r="L110" s="285"/>
-      <c r="M110" s="286"/>
+      <c r="K110" s="300"/>
+      <c r="L110" s="301"/>
+      <c r="M110" s="302"/>
       <c r="O110" s="126"/>
       <c r="P110" s="126"/>
     </row>
@@ -63936,9 +63936,9 @@
         <f t="shared" si="2"/>
         <v>62</v>
       </c>
-      <c r="K111" s="284"/>
-      <c r="L111" s="285"/>
-      <c r="M111" s="286"/>
+      <c r="K111" s="300"/>
+      <c r="L111" s="301"/>
+      <c r="M111" s="302"/>
       <c r="O111" s="126"/>
       <c r="P111" s="126"/>
     </row>
@@ -63976,9 +63976,9 @@
         <f t="shared" ref="J112:J114" si="6">H112-I112</f>
         <v>34</v>
       </c>
-      <c r="K112" s="284"/>
-      <c r="L112" s="285"/>
-      <c r="M112" s="286"/>
+      <c r="K112" s="300"/>
+      <c r="L112" s="301"/>
+      <c r="M112" s="302"/>
     </row>
     <row r="113" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="156" t="s">
@@ -64014,9 +64014,9 @@
         <f t="shared" si="6"/>
         <v>43</v>
       </c>
-      <c r="K113" s="284"/>
-      <c r="L113" s="285"/>
-      <c r="M113" s="286"/>
+      <c r="K113" s="300"/>
+      <c r="L113" s="301"/>
+      <c r="M113" s="302"/>
     </row>
     <row r="114" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="93" t="s">
@@ -64052,18 +64052,14 @@
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="K114" s="287"/>
-      <c r="L114" s="288"/>
-      <c r="M114" s="289"/>
+      <c r="K114" s="303"/>
+      <c r="L114" s="304"/>
+      <c r="M114" s="305"/>
     </row>
   </sheetData>
   <autoFilter ref="A79:J112" xr:uid="{9C81160F-C24B-449F-8F5A-CB622AB71070}"/>
   <mergeCells count="15">
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="K106:M106"/>
-    <mergeCell ref="K107:M107"/>
-    <mergeCell ref="K84:M105"/>
-    <mergeCell ref="K108:M114"/>
+    <mergeCell ref="W84:X84"/>
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="W80:X80"/>
     <mergeCell ref="W81:X81"/>
@@ -64073,7 +64069,11 @@
     <mergeCell ref="K80:M81"/>
     <mergeCell ref="K82:M82"/>
     <mergeCell ref="K83:M83"/>
-    <mergeCell ref="W84:X84"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="K106:M106"/>
+    <mergeCell ref="K107:M107"/>
+    <mergeCell ref="K84:M105"/>
+    <mergeCell ref="K108:M114"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <conditionalFormatting sqref="A3:A40">
@@ -64165,32 +64165,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="325" t="s">
+      <c r="A1" s="203" t="s">
         <v>405</v>
       </c>
-      <c r="B1" s="325"/>
-      <c r="C1" s="325"/>
-      <c r="D1" s="325"/>
-      <c r="E1" s="325"/>
-      <c r="F1" s="325" t="s">
+      <c r="B1" s="203"/>
+      <c r="C1" s="203"/>
+      <c r="D1" s="203"/>
+      <c r="E1" s="203"/>
+      <c r="F1" s="203" t="s">
         <v>406</v>
       </c>
-      <c r="G1" s="325"/>
-      <c r="H1" s="325"/>
-      <c r="I1" s="325"/>
-      <c r="J1" s="325"/>
+      <c r="G1" s="203"/>
+      <c r="H1" s="203"/>
+      <c r="I1" s="203"/>
+      <c r="J1" s="203"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2" s="325"/>
-      <c r="B2" s="325"/>
-      <c r="C2" s="325"/>
-      <c r="D2" s="325"/>
-      <c r="E2" s="325"/>
-      <c r="F2" s="325"/>
-      <c r="G2" s="325"/>
-      <c r="H2" s="325"/>
-      <c r="I2" s="325"/>
-      <c r="J2" s="325"/>
+      <c r="A2" s="203"/>
+      <c r="B2" s="203"/>
+      <c r="C2" s="203"/>
+      <c r="D2" s="203"/>
+      <c r="E2" s="203"/>
+      <c r="F2" s="203"/>
+      <c r="G2" s="203"/>
+      <c r="H2" s="203"/>
+      <c r="I2" s="203"/>
+      <c r="J2" s="203"/>
       <c r="L2" t="s">
         <v>409</v>
       </c>
@@ -64964,7 +64964,9 @@
       <c r="B2" t="s">
         <v>474</v>
       </c>
-      <c r="C2" s="199"/>
+      <c r="C2" s="199">
+        <v>7.6</v>
+      </c>
       <c r="D2">
         <v>90</v>
       </c>
@@ -64976,7 +64978,9 @@
       <c r="B3" t="s">
         <v>476</v>
       </c>
-      <c r="C3" s="199"/>
+      <c r="C3" s="199">
+        <v>7.6</v>
+      </c>
       <c r="D3" t="s">
         <v>453</v>
       </c>
@@ -64991,7 +64995,9 @@
       <c r="B4" t="s">
         <v>450</v>
       </c>
-      <c r="C4" s="199"/>
+      <c r="C4" s="199">
+        <v>6.3</v>
+      </c>
       <c r="D4">
         <v>90</v>
       </c>
@@ -65003,7 +65009,9 @@
       <c r="B5" t="s">
         <v>455</v>
       </c>
-      <c r="C5" s="199"/>
+      <c r="C5" s="199">
+        <v>7.4</v>
+      </c>
       <c r="D5">
         <v>90</v>
       </c>
@@ -65015,7 +65023,9 @@
       <c r="B6" t="s">
         <v>483</v>
       </c>
-      <c r="C6" s="199"/>
+      <c r="C6" s="199">
+        <v>7.7</v>
+      </c>
       <c r="D6" t="s">
         <v>453</v>
       </c>
@@ -65030,7 +65040,9 @@
       <c r="B7" t="s">
         <v>477</v>
       </c>
-      <c r="C7" s="199"/>
+      <c r="C7" s="199">
+        <v>7.5</v>
+      </c>
       <c r="D7">
         <v>90</v>
       </c>
@@ -65045,7 +65057,9 @@
       <c r="B8" t="s">
         <v>485</v>
       </c>
-      <c r="C8" s="199"/>
+      <c r="C8" s="199">
+        <v>7.2</v>
+      </c>
       <c r="D8" t="s">
         <v>453</v>
       </c>
@@ -65057,7 +65071,9 @@
       <c r="B9" t="s">
         <v>451</v>
       </c>
-      <c r="C9" s="199"/>
+      <c r="C9" s="199">
+        <v>7.1</v>
+      </c>
       <c r="D9" t="s">
         <v>453</v>
       </c>
@@ -65069,7 +65085,9 @@
       <c r="B10" t="s">
         <v>486</v>
       </c>
-      <c r="C10" s="199"/>
+      <c r="C10" s="199">
+        <v>8.1</v>
+      </c>
       <c r="D10">
         <v>90</v>
       </c>
@@ -65081,7 +65099,9 @@
       <c r="B11" t="s">
         <v>478</v>
       </c>
-      <c r="C11" s="199"/>
+      <c r="C11" s="199">
+        <v>6.8</v>
+      </c>
       <c r="D11">
         <v>90</v>
       </c>
@@ -65093,7 +65113,9 @@
       <c r="B12" t="s">
         <v>479</v>
       </c>
-      <c r="C12" s="199"/>
+      <c r="C12" s="199">
+        <v>6.4</v>
+      </c>
       <c r="D12" t="s">
         <v>453</v>
       </c>
@@ -65105,7 +65127,9 @@
       <c r="B13" t="s">
         <v>475</v>
       </c>
-      <c r="C13" s="199"/>
+      <c r="C13" s="199">
+        <v>6.6</v>
+      </c>
       <c r="D13" t="s">
         <v>452</v>
       </c>
@@ -65117,7 +65141,9 @@
       <c r="B14" t="s">
         <v>459</v>
       </c>
-      <c r="C14" s="199"/>
+      <c r="C14" s="199">
+        <v>8.1999999999999993</v>
+      </c>
       <c r="D14" t="s">
         <v>452</v>
       </c>
@@ -65132,7 +65158,9 @@
       <c r="B15" t="s">
         <v>469</v>
       </c>
-      <c r="C15" s="199"/>
+      <c r="C15" s="199">
+        <v>7.1</v>
+      </c>
       <c r="D15" t="s">
         <v>452</v>
       </c>
@@ -65144,7 +65172,9 @@
       <c r="B16" t="s">
         <v>454</v>
       </c>
-      <c r="C16" s="199"/>
+      <c r="C16" s="199" t="s">
+        <v>166</v>
+      </c>
       <c r="D16" t="s">
         <v>452</v>
       </c>
@@ -65156,7 +65186,9 @@
       <c r="B17" t="s">
         <v>487</v>
       </c>
-      <c r="C17" s="199"/>
+      <c r="C17" s="199" t="s">
+        <v>166</v>
+      </c>
       <c r="D17" t="s">
         <v>452</v>
       </c>
@@ -65185,23 +65217,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="203" t="s">
+      <c r="A1" s="208" t="s">
         <v>46</v>
       </c>
       <c r="B1" s="326"/>
       <c r="C1" s="327" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="206"/>
+      <c r="D1" s="211"/>
       <c r="E1" s="328"/>
-      <c r="H1" s="203" t="s">
+      <c r="H1" s="208" t="s">
         <v>47</v>
       </c>
       <c r="I1" s="326"/>
       <c r="J1" s="327" t="s">
         <v>44</v>
       </c>
-      <c r="K1" s="206"/>
+      <c r="K1" s="211"/>
       <c r="L1" s="328"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -66290,9 +66322,9 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="207"/>
-      <c r="G1" s="207"/>
-      <c r="H1" s="207"/>
+      <c r="F1" s="212"/>
+      <c r="G1" s="212"/>
+      <c r="H1" s="212"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -66316,36 +66348,36 @@
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="5"/>
-      <c r="E2" s="203" t="s">
+      <c r="E2" s="208" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="204"/>
-      <c r="G2" s="205"/>
-      <c r="H2" s="208" t="s">
+      <c r="F2" s="209"/>
+      <c r="G2" s="210"/>
+      <c r="H2" s="213" t="s">
         <v>120</v>
       </c>
-      <c r="I2" s="209"/>
-      <c r="J2" s="210"/>
-      <c r="K2" s="203" t="s">
+      <c r="I2" s="214"/>
+      <c r="J2" s="215"/>
+      <c r="K2" s="208" t="s">
         <v>108</v>
       </c>
-      <c r="L2" s="204"/>
-      <c r="M2" s="205"/>
-      <c r="N2" s="208" t="s">
+      <c r="L2" s="209"/>
+      <c r="M2" s="210"/>
+      <c r="N2" s="213" t="s">
         <v>110</v>
       </c>
-      <c r="O2" s="209"/>
-      <c r="P2" s="210"/>
-      <c r="Q2" s="203" t="s">
+      <c r="O2" s="214"/>
+      <c r="P2" s="215"/>
+      <c r="Q2" s="208" t="s">
         <v>39</v>
       </c>
-      <c r="R2" s="204"/>
-      <c r="S2" s="205"/>
-      <c r="T2" s="206" t="s">
+      <c r="R2" s="209"/>
+      <c r="S2" s="210"/>
+      <c r="T2" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="U2" s="206"/>
-      <c r="V2" s="206"/>
+      <c r="U2" s="211"/>
+      <c r="V2" s="211"/>
       <c r="Z2" s="125">
         <v>46307</v>
       </c>
@@ -69529,30 +69561,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="213" t="s">
+      <c r="D2" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="213"/>
-      <c r="F2" s="214" t="s">
+      <c r="E2" s="206"/>
+      <c r="F2" s="207" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="214"/>
-      <c r="H2" s="213" t="s">
+      <c r="G2" s="207"/>
+      <c r="H2" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="213"/>
-      <c r="J2" s="214" t="s">
+      <c r="I2" s="206"/>
+      <c r="J2" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="214"/>
-      <c r="L2" s="213" t="s">
+      <c r="K2" s="207"/>
+      <c r="L2" s="206" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="213"/>
-      <c r="N2" s="206" t="s">
+      <c r="M2" s="206"/>
+      <c r="N2" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="206"/>
+      <c r="O2" s="211"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -71549,30 +71581,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="213" t="s">
+      <c r="D2" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="213"/>
-      <c r="F2" s="214" t="s">
+      <c r="E2" s="206"/>
+      <c r="F2" s="207" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="214"/>
-      <c r="H2" s="213" t="s">
+      <c r="G2" s="207"/>
+      <c r="H2" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="213"/>
-      <c r="J2" s="214" t="s">
+      <c r="I2" s="206"/>
+      <c r="J2" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="214"/>
-      <c r="L2" s="213" t="s">
+      <c r="K2" s="207"/>
+      <c r="L2" s="206" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="213"/>
-      <c r="N2" s="206" t="s">
+      <c r="M2" s="206"/>
+      <c r="N2" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="206"/>
+      <c r="O2" s="211"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -73506,30 +73538,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="213" t="s">
+      <c r="D2" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="213"/>
-      <c r="F2" s="214" t="s">
+      <c r="E2" s="206"/>
+      <c r="F2" s="207" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="214"/>
-      <c r="H2" s="213" t="s">
+      <c r="G2" s="207"/>
+      <c r="H2" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="213"/>
-      <c r="J2" s="214" t="s">
+      <c r="I2" s="206"/>
+      <c r="J2" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="214"/>
-      <c r="L2" s="213" t="s">
+      <c r="K2" s="207"/>
+      <c r="L2" s="206" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="213"/>
-      <c r="N2" s="206" t="s">
+      <c r="M2" s="206"/>
+      <c r="N2" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="206"/>
+      <c r="O2" s="211"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -75554,30 +75586,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="213" t="s">
+      <c r="D2" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="213"/>
-      <c r="F2" s="214" t="s">
+      <c r="E2" s="206"/>
+      <c r="F2" s="207" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="214"/>
-      <c r="H2" s="213" t="s">
+      <c r="G2" s="207"/>
+      <c r="H2" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="213"/>
-      <c r="J2" s="214" t="s">
+      <c r="I2" s="206"/>
+      <c r="J2" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="214"/>
-      <c r="L2" s="213" t="s">
+      <c r="K2" s="207"/>
+      <c r="L2" s="206" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="213"/>
-      <c r="N2" s="206" t="s">
+      <c r="M2" s="206"/>
+      <c r="N2" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="206"/>
+      <c r="O2" s="211"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -77262,30 +77294,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="213" t="s">
+      <c r="C2" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="213"/>
-      <c r="E2" s="214" t="s">
+      <c r="D2" s="206"/>
+      <c r="E2" s="207" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="214"/>
-      <c r="G2" s="213" t="s">
+      <c r="F2" s="207"/>
+      <c r="G2" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="213"/>
-      <c r="I2" s="214" t="s">
+      <c r="H2" s="206"/>
+      <c r="I2" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="214"/>
-      <c r="K2" s="213" t="s">
+      <c r="J2" s="207"/>
+      <c r="K2" s="206" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="213"/>
-      <c r="M2" s="206" t="s">
+      <c r="L2" s="206"/>
+      <c r="M2" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="206"/>
+      <c r="N2" s="211"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -79047,30 +79079,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="213" t="s">
+      <c r="C2" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="213"/>
-      <c r="E2" s="214" t="s">
+      <c r="D2" s="206"/>
+      <c r="E2" s="207" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="214"/>
-      <c r="G2" s="213" t="s">
+      <c r="F2" s="207"/>
+      <c r="G2" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="213"/>
-      <c r="I2" s="214" t="s">
+      <c r="H2" s="206"/>
+      <c r="I2" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="214"/>
-      <c r="K2" s="213" t="s">
+      <c r="J2" s="207"/>
+      <c r="K2" s="206" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="213"/>
-      <c r="M2" s="206" t="s">
+      <c r="L2" s="206"/>
+      <c r="M2" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="206"/>
+      <c r="N2" s="211"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">

--- a/data/arsenal_stats.xlsx
+++ b/data/arsenal_stats.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bungeltd-my.sharepoint.com/personal/przemyslaw_iskra_bunge_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8679" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D61A02A5-AEDC-4FD6-A8F7-53E285334E56}"/>
+  <xr:revisionPtr revIDLastSave="8762" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{791A5D5F-B7B4-466B-8D0B-7FC2C84CC851}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="799" firstSheet="1" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="799" firstSheet="1" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="19" state="hidden" r:id="rId1"/>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2279" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2269" uniqueCount="489">
   <si>
     <t>Arsenal FC squad statistics</t>
   </si>
@@ -1492,12 +1492,6 @@
     <t>Gyokeres</t>
   </si>
   <si>
-    <t>10.10.2026</t>
-  </si>
-  <si>
-    <t>Emirates Stadium (H)</t>
-  </si>
-  <si>
     <t>−4</t>
   </si>
   <si>
@@ -1522,12 +1516,6 @@
     <t>Havertz</t>
   </si>
   <si>
-    <t>2-1</t>
-  </si>
-  <si>
-    <t>13.10.2026</t>
-  </si>
-  <si>
     <t>G</t>
   </si>
   <si>
@@ -1537,16 +1525,28 @@
     <t>A</t>
   </si>
   <si>
-    <t>Lewis-Skelly</t>
-  </si>
-  <si>
     <t>Madueke</t>
   </si>
   <si>
-    <t>Hincapie</t>
+    <t>Eze</t>
   </si>
   <si>
-    <t>Lille OSC</t>
+    <t>18.10.2026</t>
+  </si>
+  <si>
+    <t>1-0</t>
+  </si>
+  <si>
+    <t>Nottingham</t>
+  </si>
+  <si>
+    <t>City Ground (A)</t>
+  </si>
+  <si>
+    <t>21.10.2026</t>
+  </si>
+  <si>
+    <t>Allianz Arena (A)</t>
   </si>
 </sst>
 </file>
@@ -3053,9 +3053,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3092,6 +3089,15 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3101,32 +3107,14 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="54" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3164,6 +3152,15 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="28" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3171,6 +3168,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="60" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="10" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="37" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="11" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3263,31 +3281,70 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="60" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="10" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="37" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="11" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="54" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3362,64 +3419,7 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -4635,7 +4635,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="33"/>
                 <c:pt idx="0">
-                  <c:v>8</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -4644,55 +4644,55 @@
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>9</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>7</c:v>
-                </c:pt>
                 <c:pt idx="9">
-                  <c:v>3</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>6</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>7</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>6</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>8</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>8</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>7</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>0</c:v>
@@ -4701,13 +4701,13 @@
                   <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>7</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>8</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>0</c:v>
@@ -4722,7 +4722,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>7</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>0</c:v>
@@ -4731,7 +4731,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>2</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4889,16 +4889,16 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>0</c:v>
@@ -4913,7 +4913,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>0</c:v>
@@ -6484,7 +6484,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{4786A9F6-9CE2-484D-863A-8D9EEF6C9A67}" type="CELLRANGE">
+                    <a:fld id="{8669909C-91B4-4AE5-9E3F-1DDCB7E9AA04}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6518,7 +6518,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{48D528F4-52B6-43FB-B985-444B268D58BD}" type="CELLRANGE">
+                    <a:fld id="{44986CE5-0DA0-427C-AFE1-3732BF3C4699}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6552,7 +6552,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7F6110BB-0686-4710-8543-05D273F98E06}" type="CELLRANGE">
+                    <a:fld id="{B20F27BD-30CB-424B-A149-952149474756}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6586,7 +6586,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F57E0001-B673-4275-BE5C-2974F37E38E8}" type="CELLRANGE">
+                    <a:fld id="{A9B3CE18-A5DF-4656-87F7-DBEB2987FDA0}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6620,7 +6620,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{57908D16-A707-4FE1-ADB6-B4F0E3F32071}" type="CELLRANGE">
+                    <a:fld id="{343831B2-23F4-4226-8AD6-B7438F9B313B}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6654,7 +6654,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{FA12F139-FE87-427D-8C87-6CEE96D7F7DF}" type="CELLRANGE">
+                    <a:fld id="{815DF824-7F75-4E9D-9936-304E39B08B3C}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6688,7 +6688,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6F1FCFC3-8621-4C67-A866-DCEE2172C714}" type="CELLRANGE">
+                    <a:fld id="{0D69B8E7-9C90-4079-9660-8C4BA3979F1C}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6722,7 +6722,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{4B220D83-9BA5-4B8C-9BCE-7BB8BD5AE44F}" type="CELLRANGE">
+                    <a:fld id="{118E26D6-514C-406B-A504-85E44911D652}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6756,7 +6756,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{661CC650-0950-4B66-B1AA-BFC9FB667972}" type="CELLRANGE">
+                    <a:fld id="{8E128C8A-A1B5-4E6D-9984-A9F60D700F1B}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6790,7 +6790,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7688C2B5-EFE9-4361-9292-45503FC402FF}" type="CELLRANGE">
+                    <a:fld id="{44D87958-CA84-4BBB-8723-C1FA9C3BA8B5}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6824,7 +6824,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{00818CA7-1E43-4113-B9FD-BB649D6DFB34}" type="CELLRANGE">
+                    <a:fld id="{464D4944-7B1C-4709-A94E-C95F28708490}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6858,7 +6858,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{175B0745-5ACD-48C8-874B-B0C7CFFE957B}" type="CELLRANGE">
+                    <a:fld id="{0DA59A05-C7C1-4F39-910D-CAAADF619DC2}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6907,7 +6907,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{7B637FCC-7019-4663-8F1C-EB7408FF9339}" type="CELLRANGE">
+                    <a:fld id="{B12B0083-3852-4228-9266-3EDAF8B50255}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr>
                         <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
@@ -6966,7 +6966,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8A134787-70AA-437E-A8F9-A7DE1CC54D34}" type="CELLRANGE">
+                    <a:fld id="{06318371-67C6-4F36-82C0-31B16AB6AA38}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7000,7 +7000,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{629F6D06-AE65-415A-813A-ACE26C3BF65E}" type="CELLRANGE">
+                    <a:fld id="{C77EA08B-8225-4B3F-9C78-DE17EBB1BED4}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7034,7 +7034,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9B6A8264-1166-4DB6-AA0B-5188D7E72867}" type="CELLRANGE">
+                    <a:fld id="{799C1FE3-6F05-41A3-AC49-8FEAD5BAC7D7}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7068,7 +7068,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{1003B611-C38E-4DF6-B027-4DBF581516E1}" type="CELLRANGE">
+                    <a:fld id="{27713E53-9E79-43AF-B3F6-E86D21419CE9}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7246,55 +7246,55 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>197</c:v>
+                  <c:v>199</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>44</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>270</c:v>
+                  <c:v>272</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>320</c:v>
+                  <c:v>322</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>243</c:v>
+                  <c:v>245</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>59</c:v>
+                  <c:v>61</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>98</c:v>
+                  <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>61</c:v>
+                  <c:v>63</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>7</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>48</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>51</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>86</c:v>
+                  <c:v>88</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>119</c:v>
+                  <c:v>121</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>72</c:v>
+                  <c:v>73</c:v>
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>2</c:v>
@@ -7318,16 +7318,16 @@
                   <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>84</c:v>
+                  <c:v>85</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>46</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>10</c:v>
+                  <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>6</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0</c:v>
@@ -7342,7 +7342,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>9</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>10</c:v>
@@ -7545,16 +7545,16 @@
                         <c:v>24</c:v>
                       </c:pt>
                       <c:pt idx="3">
-                        <c:v>84</c:v>
+                        <c:v>85</c:v>
                       </c:pt>
                       <c:pt idx="4">
                         <c:v>46</c:v>
                       </c:pt>
                       <c:pt idx="5">
-                        <c:v>10</c:v>
+                        <c:v>11</c:v>
                       </c:pt>
                       <c:pt idx="6">
-                        <c:v>6</c:v>
+                        <c:v>7</c:v>
                       </c:pt>
                       <c:pt idx="7">
                         <c:v>0</c:v>
@@ -7569,7 +7569,7 @@
                         <c:v>0</c:v>
                       </c:pt>
                       <c:pt idx="11">
-                        <c:v>9</c:v>
+                        <c:v>10</c:v>
                       </c:pt>
                       <c:pt idx="12">
                         <c:v>10</c:v>
@@ -7884,10 +7884,10 @@
                   <c:v>2.0571428571428569</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.8235294117647058</c:v>
+                  <c:v>1.8571428571428572</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.2647058823529411</c:v>
+                  <c:v>2.2857142857142856</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>2.0882352941176472</c:v>
@@ -13895,6 +13895,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Motyw pakietu Office">
   <a:themeElements>
@@ -14204,30 +14208,30 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
       <c r="B1" s="5"/>
-      <c r="C1" s="206" t="s">
+      <c r="C1" s="205" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="206"/>
-      <c r="E1" s="207" t="s">
+      <c r="D1" s="205"/>
+      <c r="E1" s="206" t="s">
         <v>120</v>
       </c>
-      <c r="F1" s="207"/>
-      <c r="G1" s="206" t="s">
+      <c r="F1" s="206"/>
+      <c r="G1" s="205" t="s">
         <v>108</v>
       </c>
-      <c r="H1" s="206"/>
-      <c r="I1" s="207" t="s">
+      <c r="H1" s="205"/>
+      <c r="I1" s="206" t="s">
         <v>110</v>
       </c>
-      <c r="J1" s="207"/>
-      <c r="K1" s="206" t="s">
+      <c r="J1" s="206"/>
+      <c r="K1" s="205" t="s">
         <v>39</v>
       </c>
-      <c r="L1" s="206"/>
-      <c r="M1" s="204" t="s">
+      <c r="L1" s="205"/>
+      <c r="M1" s="203" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="205"/>
+      <c r="N1" s="204"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -15934,30 +15938,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="206" t="s">
+      <c r="C2" s="205" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="206"/>
-      <c r="E2" s="207" t="s">
+      <c r="D2" s="205"/>
+      <c r="E2" s="206" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="207"/>
-      <c r="G2" s="206" t="s">
+      <c r="F2" s="206"/>
+      <c r="G2" s="205" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="206"/>
-      <c r="I2" s="207" t="s">
+      <c r="H2" s="205"/>
+      <c r="I2" s="206" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="207"/>
-      <c r="K2" s="206" t="s">
+      <c r="J2" s="206"/>
+      <c r="K2" s="205" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="206"/>
-      <c r="M2" s="211" t="s">
+      <c r="L2" s="205"/>
+      <c r="M2" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="211"/>
+      <c r="N2" s="210"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -17761,30 +17765,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="206" t="s">
+      <c r="C2" s="205" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="206"/>
-      <c r="E2" s="207" t="s">
+      <c r="D2" s="205"/>
+      <c r="E2" s="206" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="207"/>
-      <c r="G2" s="206" t="s">
+      <c r="F2" s="206"/>
+      <c r="G2" s="205" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="206"/>
-      <c r="I2" s="207" t="s">
+      <c r="H2" s="205"/>
+      <c r="I2" s="206" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="207"/>
-      <c r="K2" s="206" t="s">
+      <c r="J2" s="206"/>
+      <c r="K2" s="205" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="206"/>
-      <c r="M2" s="211" t="s">
+      <c r="L2" s="205"/>
+      <c r="M2" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="211"/>
+      <c r="N2" s="210"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -19451,30 +19455,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="206" t="s">
+      <c r="C2" s="205" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="206"/>
-      <c r="E2" s="207" t="s">
+      <c r="D2" s="205"/>
+      <c r="E2" s="206" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="207"/>
-      <c r="G2" s="206" t="s">
+      <c r="F2" s="206"/>
+      <c r="G2" s="205" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="206"/>
-      <c r="I2" s="207" t="s">
+      <c r="H2" s="205"/>
+      <c r="I2" s="206" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="207"/>
-      <c r="K2" s="206" t="s">
+      <c r="J2" s="206"/>
+      <c r="K2" s="205" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="206"/>
-      <c r="M2" s="211" t="s">
+      <c r="L2" s="205"/>
+      <c r="M2" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="211"/>
+      <c r="N2" s="210"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -21277,30 +21281,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="206" t="s">
+      <c r="C2" s="205" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="206"/>
-      <c r="E2" s="207" t="s">
+      <c r="D2" s="205"/>
+      <c r="E2" s="206" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="207"/>
-      <c r="G2" s="206" t="s">
+      <c r="F2" s="206"/>
+      <c r="G2" s="205" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="206"/>
-      <c r="I2" s="207" t="s">
+      <c r="H2" s="205"/>
+      <c r="I2" s="206" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="207"/>
-      <c r="K2" s="206" t="s">
+      <c r="J2" s="206"/>
+      <c r="K2" s="205" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="206"/>
-      <c r="M2" s="211" t="s">
+      <c r="L2" s="205"/>
+      <c r="M2" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="211"/>
+      <c r="N2" s="210"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -23149,36 +23153,36 @@
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="208" t="s">
+      <c r="C2" s="207" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="209"/>
-      <c r="E2" s="210"/>
-      <c r="F2" s="213" t="s">
+      <c r="D2" s="208"/>
+      <c r="E2" s="209"/>
+      <c r="F2" s="212" t="s">
         <v>120</v>
       </c>
-      <c r="G2" s="214"/>
-      <c r="H2" s="215"/>
-      <c r="I2" s="208" t="s">
+      <c r="G2" s="213"/>
+      <c r="H2" s="214"/>
+      <c r="I2" s="207" t="s">
         <v>108</v>
       </c>
-      <c r="J2" s="209"/>
-      <c r="K2" s="210"/>
-      <c r="L2" s="213" t="s">
+      <c r="J2" s="208"/>
+      <c r="K2" s="209"/>
+      <c r="L2" s="212" t="s">
         <v>110</v>
       </c>
-      <c r="M2" s="214"/>
-      <c r="N2" s="215"/>
-      <c r="O2" s="208" t="s">
+      <c r="M2" s="213"/>
+      <c r="N2" s="214"/>
+      <c r="O2" s="207" t="s">
         <v>39</v>
       </c>
-      <c r="P2" s="209"/>
-      <c r="Q2" s="210"/>
-      <c r="R2" s="211" t="s">
+      <c r="P2" s="208"/>
+      <c r="Q2" s="209"/>
+      <c r="R2" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="S2" s="211"/>
-      <c r="T2" s="211"/>
+      <c r="S2" s="210"/>
+      <c r="T2" s="210"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -23251,7 +23255,7 @@
       </c>
       <c r="C4" s="6">
         <f>'Premier League'!C4</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" s="6">
         <f>'Premier League'!D4</f>
@@ -23263,7 +23267,7 @@
       </c>
       <c r="F4" s="4">
         <f>Europe!C4</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" s="4">
         <f>Europe!D4</f>
@@ -23311,7 +23315,7 @@
       </c>
       <c r="R4" s="2">
         <f>SUM(C4,F4,I4,L4,O4)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S4" s="2">
         <f t="shared" ref="S4:T4" si="0">SUM(D4,G4,J4,M4,P4)</f>
@@ -23493,7 +23497,7 @@
       </c>
       <c r="C7" s="6">
         <f>'Premier League'!C7</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" s="6">
         <f>'Premier League'!D7</f>
@@ -23505,7 +23509,7 @@
       </c>
       <c r="F7" s="4">
         <f>Europe!C7</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" s="4">
         <f>Europe!D7</f>
@@ -23553,7 +23557,7 @@
       </c>
       <c r="R7" s="2">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="S7" s="2">
         <f t="shared" si="2"/>
@@ -23655,7 +23659,7 @@
       </c>
       <c r="C9" s="6">
         <f>'Premier League'!C9</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" s="6">
         <f>'Premier League'!D9</f>
@@ -23667,7 +23671,7 @@
       </c>
       <c r="F9" s="4">
         <f>Europe!C9</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" s="4">
         <f>Europe!D9</f>
@@ -23715,7 +23719,7 @@
       </c>
       <c r="R9" s="2">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="S9" s="2">
         <f t="shared" si="2"/>
@@ -23736,7 +23740,7 @@
       </c>
       <c r="C10" s="6">
         <f>'Premier League'!C10</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" s="6">
         <f>'Premier League'!D10</f>
@@ -23748,15 +23752,15 @@
       </c>
       <c r="F10" s="4">
         <f>Europe!C10</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" s="4">
         <f>Europe!D10</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" s="4">
         <f>Europe!E10</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" s="6">
         <f>'FA Cup'!C10</f>
@@ -23796,15 +23800,15 @@
       </c>
       <c r="R10" s="2">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S10" s="2">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T10" s="2">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" s="55"/>
     </row>
@@ -23817,7 +23821,7 @@
       </c>
       <c r="C11" s="6">
         <f>'Premier League'!C11</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" s="6">
         <f>'Premier League'!D11</f>
@@ -23829,7 +23833,7 @@
       </c>
       <c r="F11" s="4">
         <f>Europe!C11</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" s="4">
         <f>Europe!D11</f>
@@ -23877,7 +23881,7 @@
       </c>
       <c r="R11" s="2">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="S11" s="2">
         <f t="shared" si="2"/>
@@ -23898,7 +23902,7 @@
       </c>
       <c r="C12" s="6">
         <f>'Premier League'!C12</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D12" s="6">
         <f>'Premier League'!D12</f>
@@ -23910,11 +23914,11 @@
       </c>
       <c r="F12" s="4">
         <f>Europe!C12</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" s="4">
         <f>Europe!D12</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" s="4">
         <f>Europe!E12</f>
@@ -23958,11 +23962,11 @@
       </c>
       <c r="R12" s="2">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="S12" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T12" s="2">
         <f t="shared" si="3"/>
@@ -23979,7 +23983,7 @@
       </c>
       <c r="C13" s="6">
         <f>'Premier League'!C13</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" s="6">
         <f>'Premier League'!D13</f>
@@ -23991,11 +23995,11 @@
       </c>
       <c r="F13" s="4">
         <f>Europe!C13</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" s="4">
         <f>Europe!D13</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" s="4">
         <f>Europe!E13</f>
@@ -24039,11 +24043,11 @@
       </c>
       <c r="R13" s="2">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S13" s="2">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T13" s="2">
         <f t="shared" si="3"/>
@@ -24141,7 +24145,7 @@
       </c>
       <c r="C15" s="6">
         <f>'Premier League'!C15</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" s="6">
         <f>'Premier League'!D15</f>
@@ -24153,7 +24157,7 @@
       </c>
       <c r="F15" s="4">
         <f>Europe!C15</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="4">
         <f>Europe!D15</f>
@@ -24201,7 +24205,7 @@
       </c>
       <c r="R15" s="2">
         <f>SUM(C15,F15,I15,L15,O15)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S15" s="2">
         <f>SUM(D15,G15,J15,M15,P15)</f>
@@ -24222,7 +24226,7 @@
       </c>
       <c r="C16" s="6">
         <f>'Premier League'!C16</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D16" s="6">
         <f>'Premier League'!D16</f>
@@ -24234,7 +24238,7 @@
       </c>
       <c r="F16" s="4">
         <f>Europe!C16</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16" s="4">
         <f>Europe!D16</f>
@@ -24282,7 +24286,7 @@
       </c>
       <c r="R16" s="2">
         <f t="shared" ref="R16:R28" si="4">SUM(C16,F16,I16,L16,O16)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="S16" s="2">
         <f t="shared" ref="S16:S28" si="5">SUM(D16,G16,J16,M16,P16)</f>
@@ -24384,11 +24388,11 @@
       </c>
       <c r="C18" s="6">
         <f>'Premier League'!C18</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18" s="6">
         <f>'Premier League'!D18</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" s="6">
         <f>'Premier League'!E18</f>
@@ -24396,7 +24400,7 @@
       </c>
       <c r="F18" s="4">
         <f>Europe!C18</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G18" s="4">
         <f>Europe!D18</f>
@@ -24404,7 +24408,7 @@
       </c>
       <c r="H18" s="4">
         <f>Europe!E18</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" s="6">
         <f>'FA Cup'!C18</f>
@@ -24444,15 +24448,15 @@
       </c>
       <c r="R18" s="2">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S18" s="2">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T18" s="2">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.25">
@@ -24544,7 +24548,7 @@
       </c>
       <c r="C20" s="6">
         <f>'Premier League'!C20</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D20" s="6">
         <f>'Premier League'!D20</f>
@@ -24556,7 +24560,7 @@
       </c>
       <c r="F20" s="4">
         <f>Europe!C20</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20" s="4">
         <f>Europe!D20</f>
@@ -24604,7 +24608,7 @@
       </c>
       <c r="R20" s="2">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S20" s="2">
         <f t="shared" si="5"/>
@@ -24624,7 +24628,7 @@
       </c>
       <c r="C21" s="6">
         <f>'Premier League'!C21</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D21" s="6">
         <f>'Premier League'!D21</f>
@@ -24636,7 +24640,7 @@
       </c>
       <c r="F21" s="4">
         <f>Europe!C21</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G21" s="4">
         <f>Europe!D21</f>
@@ -24644,7 +24648,7 @@
       </c>
       <c r="H21" s="4">
         <f>Europe!E21</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" s="6">
         <f>'FA Cup'!C21</f>
@@ -24684,7 +24688,7 @@
       </c>
       <c r="R21" s="2">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S21" s="2">
         <f t="shared" si="5"/>
@@ -24692,7 +24696,7 @@
       </c>
       <c r="T21" s="2">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="55"/>
     </row>
@@ -24786,7 +24790,7 @@
       </c>
       <c r="C23" s="6">
         <f>'Premier League'!C23</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D23" s="6">
         <f>'Premier League'!D23</f>
@@ -24846,7 +24850,7 @@
       </c>
       <c r="R23" s="2">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S23" s="2">
         <f t="shared" si="5"/>
@@ -25029,7 +25033,7 @@
       </c>
       <c r="C26" s="6">
         <f>'Premier League'!C26</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D26" s="6">
         <f>'Premier League'!D26</f>
@@ -25041,7 +25045,7 @@
       </c>
       <c r="F26" s="4">
         <f>Europe!C26</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G26" s="4">
         <f>Europe!D26</f>
@@ -25089,7 +25093,7 @@
       </c>
       <c r="R26" s="2">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="S26" s="2">
         <f t="shared" si="5"/>
@@ -25190,7 +25194,7 @@
       </c>
       <c r="C28" s="6">
         <f>'Premier League'!C28</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D28" s="6">
         <f>'Premier League'!D28</f>
@@ -25198,11 +25202,11 @@
       </c>
       <c r="E28" s="6">
         <f>'Premier League'!E28</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F28" s="4">
         <f>Europe!C28</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="4">
         <f>Europe!D28</f>
@@ -25250,7 +25254,7 @@
       </c>
       <c r="R28" s="2">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S28" s="2">
         <f t="shared" si="5"/>
@@ -25258,7 +25262,7 @@
       </c>
       <c r="T28" s="2">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V28" s="55"/>
     </row>
@@ -25604,7 +25608,7 @@
       </c>
       <c r="F33" s="4">
         <f>Europe!C33</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" s="4">
         <f>Europe!D33</f>
@@ -25652,7 +25656,7 @@
       </c>
       <c r="R33" s="2">
         <f t="shared" si="8"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S33" s="2">
         <f t="shared" si="9"/>
@@ -25844,7 +25848,7 @@
       </c>
       <c r="F36" s="4">
         <f>Europe!C36</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" s="4">
         <f>Europe!D36</f>
@@ -25892,7 +25896,7 @@
       </c>
       <c r="R36" s="2">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S36" s="2">
         <f t="shared" si="9"/>
@@ -26117,36 +26121,36 @@
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
       <c r="D1" s="5"/>
-      <c r="E1" s="208" t="s">
+      <c r="E1" s="207" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="209"/>
-      <c r="G1" s="210"/>
-      <c r="H1" s="213" t="s">
+      <c r="F1" s="208"/>
+      <c r="G1" s="209"/>
+      <c r="H1" s="212" t="s">
         <v>120</v>
       </c>
-      <c r="I1" s="214"/>
-      <c r="J1" s="215"/>
-      <c r="K1" s="208" t="s">
+      <c r="I1" s="213"/>
+      <c r="J1" s="214"/>
+      <c r="K1" s="207" t="s">
         <v>108</v>
       </c>
-      <c r="L1" s="209"/>
-      <c r="M1" s="210"/>
-      <c r="N1" s="213" t="s">
+      <c r="L1" s="208"/>
+      <c r="M1" s="209"/>
+      <c r="N1" s="212" t="s">
         <v>110</v>
       </c>
-      <c r="O1" s="214"/>
-      <c r="P1" s="215"/>
-      <c r="Q1" s="208" t="s">
+      <c r="O1" s="213"/>
+      <c r="P1" s="214"/>
+      <c r="Q1" s="207" t="s">
         <v>39</v>
       </c>
-      <c r="R1" s="209"/>
-      <c r="S1" s="210"/>
-      <c r="T1" s="211" t="s">
+      <c r="R1" s="208"/>
+      <c r="S1" s="209"/>
+      <c r="T1" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="U1" s="211"/>
-      <c r="V1" s="211"/>
+      <c r="U1" s="210"/>
+      <c r="V1" s="210"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -37720,399 +37724,399 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F1" s="219">
-        <v>1</v>
-      </c>
-      <c r="G1" s="220"/>
-      <c r="H1" s="221"/>
-      <c r="I1" s="219">
+      <c r="F1" s="215">
+        <v>1</v>
+      </c>
+      <c r="G1" s="216"/>
+      <c r="H1" s="217"/>
+      <c r="I1" s="215">
         <v>2</v>
       </c>
-      <c r="J1" s="220"/>
-      <c r="K1" s="221"/>
-      <c r="L1" s="219">
-        <v>3</v>
-      </c>
-      <c r="M1" s="220"/>
-      <c r="N1" s="221"/>
-      <c r="O1" s="219">
+      <c r="J1" s="216"/>
+      <c r="K1" s="217"/>
+      <c r="L1" s="215">
+        <v>3</v>
+      </c>
+      <c r="M1" s="216"/>
+      <c r="N1" s="217"/>
+      <c r="O1" s="215">
         <v>4</v>
       </c>
-      <c r="P1" s="220"/>
-      <c r="Q1" s="221"/>
-      <c r="R1" s="219">
+      <c r="P1" s="216"/>
+      <c r="Q1" s="217"/>
+      <c r="R1" s="215">
         <v>5</v>
       </c>
-      <c r="S1" s="220"/>
-      <c r="T1" s="221"/>
-      <c r="U1" s="219">
+      <c r="S1" s="216"/>
+      <c r="T1" s="217"/>
+      <c r="U1" s="215">
         <v>6</v>
       </c>
-      <c r="V1" s="220"/>
-      <c r="W1" s="221"/>
-      <c r="X1" s="219">
+      <c r="V1" s="216"/>
+      <c r="W1" s="217"/>
+      <c r="X1" s="215">
         <v>7</v>
       </c>
-      <c r="Y1" s="220"/>
-      <c r="Z1" s="221"/>
-      <c r="AA1" s="219">
+      <c r="Y1" s="216"/>
+      <c r="Z1" s="217"/>
+      <c r="AA1" s="215">
         <v>8</v>
       </c>
-      <c r="AB1" s="220"/>
-      <c r="AC1" s="221"/>
-      <c r="AD1" s="219">
+      <c r="AB1" s="216"/>
+      <c r="AC1" s="217"/>
+      <c r="AD1" s="215">
         <v>9</v>
       </c>
-      <c r="AE1" s="220"/>
-      <c r="AF1" s="221"/>
-      <c r="AG1" s="219">
+      <c r="AE1" s="216"/>
+      <c r="AF1" s="217"/>
+      <c r="AG1" s="215">
         <v>10</v>
       </c>
-      <c r="AH1" s="220"/>
-      <c r="AI1" s="221"/>
-      <c r="AJ1" s="219">
+      <c r="AH1" s="216"/>
+      <c r="AI1" s="217"/>
+      <c r="AJ1" s="215">
         <v>11</v>
       </c>
-      <c r="AK1" s="220"/>
-      <c r="AL1" s="221"/>
-      <c r="AM1" s="219">
+      <c r="AK1" s="216"/>
+      <c r="AL1" s="217"/>
+      <c r="AM1" s="215">
         <v>12</v>
       </c>
-      <c r="AN1" s="220"/>
-      <c r="AO1" s="221"/>
-      <c r="AP1" s="219">
+      <c r="AN1" s="216"/>
+      <c r="AO1" s="217"/>
+      <c r="AP1" s="215">
         <v>13</v>
       </c>
-      <c r="AQ1" s="220"/>
-      <c r="AR1" s="221"/>
-      <c r="AS1" s="219">
+      <c r="AQ1" s="216"/>
+      <c r="AR1" s="217"/>
+      <c r="AS1" s="215">
         <v>14</v>
       </c>
-      <c r="AT1" s="220"/>
-      <c r="AU1" s="221"/>
-      <c r="AV1" s="219">
+      <c r="AT1" s="216"/>
+      <c r="AU1" s="217"/>
+      <c r="AV1" s="215">
         <v>15</v>
       </c>
-      <c r="AW1" s="220"/>
-      <c r="AX1" s="221"/>
-      <c r="AY1" s="219">
+      <c r="AW1" s="216"/>
+      <c r="AX1" s="217"/>
+      <c r="AY1" s="215">
         <v>16</v>
       </c>
-      <c r="AZ1" s="220"/>
-      <c r="BA1" s="221"/>
-      <c r="BB1" s="219">
+      <c r="AZ1" s="216"/>
+      <c r="BA1" s="217"/>
+      <c r="BB1" s="215">
         <v>17</v>
       </c>
-      <c r="BC1" s="220"/>
-      <c r="BD1" s="221"/>
-      <c r="BE1" s="219">
+      <c r="BC1" s="216"/>
+      <c r="BD1" s="217"/>
+      <c r="BE1" s="215">
         <v>18</v>
       </c>
-      <c r="BF1" s="220"/>
-      <c r="BG1" s="221"/>
-      <c r="BH1" s="219">
+      <c r="BF1" s="216"/>
+      <c r="BG1" s="217"/>
+      <c r="BH1" s="215">
         <v>19</v>
       </c>
-      <c r="BI1" s="220"/>
-      <c r="BJ1" s="221"/>
-      <c r="BK1" s="219">
+      <c r="BI1" s="216"/>
+      <c r="BJ1" s="217"/>
+      <c r="BK1" s="215">
         <v>20</v>
       </c>
-      <c r="BL1" s="220"/>
-      <c r="BM1" s="221"/>
-      <c r="BN1" s="219">
+      <c r="BL1" s="216"/>
+      <c r="BM1" s="217"/>
+      <c r="BN1" s="215">
         <v>21</v>
       </c>
-      <c r="BO1" s="220"/>
-      <c r="BP1" s="221"/>
-      <c r="BQ1" s="219">
+      <c r="BO1" s="216"/>
+      <c r="BP1" s="217"/>
+      <c r="BQ1" s="215">
         <v>22</v>
       </c>
-      <c r="BR1" s="220"/>
-      <c r="BS1" s="221"/>
-      <c r="BT1" s="219">
+      <c r="BR1" s="216"/>
+      <c r="BS1" s="217"/>
+      <c r="BT1" s="215">
         <v>23</v>
       </c>
-      <c r="BU1" s="220"/>
-      <c r="BV1" s="221"/>
-      <c r="BW1" s="219">
+      <c r="BU1" s="216"/>
+      <c r="BV1" s="217"/>
+      <c r="BW1" s="215">
         <v>24</v>
       </c>
-      <c r="BX1" s="220"/>
-      <c r="BY1" s="221"/>
-      <c r="BZ1" s="219">
+      <c r="BX1" s="216"/>
+      <c r="BY1" s="217"/>
+      <c r="BZ1" s="215">
         <v>25</v>
       </c>
-      <c r="CA1" s="220"/>
-      <c r="CB1" s="221"/>
-      <c r="CC1" s="219">
+      <c r="CA1" s="216"/>
+      <c r="CB1" s="217"/>
+      <c r="CC1" s="215">
         <v>26</v>
       </c>
-      <c r="CD1" s="220"/>
-      <c r="CE1" s="221"/>
-      <c r="CF1" s="219">
+      <c r="CD1" s="216"/>
+      <c r="CE1" s="217"/>
+      <c r="CF1" s="215">
         <v>27</v>
       </c>
-      <c r="CG1" s="220"/>
-      <c r="CH1" s="221"/>
-      <c r="CI1" s="219">
+      <c r="CG1" s="216"/>
+      <c r="CH1" s="217"/>
+      <c r="CI1" s="215">
         <v>28</v>
       </c>
-      <c r="CJ1" s="220"/>
-      <c r="CK1" s="221"/>
-      <c r="CL1" s="219">
+      <c r="CJ1" s="216"/>
+      <c r="CK1" s="217"/>
+      <c r="CL1" s="215">
         <v>29</v>
       </c>
-      <c r="CM1" s="220"/>
-      <c r="CN1" s="221"/>
-      <c r="CO1" s="219">
+      <c r="CM1" s="216"/>
+      <c r="CN1" s="217"/>
+      <c r="CO1" s="215">
         <v>30</v>
       </c>
-      <c r="CP1" s="220"/>
-      <c r="CQ1" s="221"/>
-      <c r="CR1" s="219">
+      <c r="CP1" s="216"/>
+      <c r="CQ1" s="217"/>
+      <c r="CR1" s="215">
         <v>31</v>
       </c>
-      <c r="CS1" s="220"/>
-      <c r="CT1" s="221"/>
-      <c r="CU1" s="219">
+      <c r="CS1" s="216"/>
+      <c r="CT1" s="217"/>
+      <c r="CU1" s="215">
         <v>32</v>
       </c>
-      <c r="CV1" s="220"/>
-      <c r="CW1" s="221"/>
-      <c r="CX1" s="219">
+      <c r="CV1" s="216"/>
+      <c r="CW1" s="217"/>
+      <c r="CX1" s="215">
         <v>33</v>
       </c>
-      <c r="CY1" s="220"/>
-      <c r="CZ1" s="221"/>
-      <c r="DA1" s="219">
+      <c r="CY1" s="216"/>
+      <c r="CZ1" s="217"/>
+      <c r="DA1" s="215">
         <v>34</v>
       </c>
-      <c r="DB1" s="220"/>
-      <c r="DC1" s="221"/>
-      <c r="DD1" s="219">
+      <c r="DB1" s="216"/>
+      <c r="DC1" s="217"/>
+      <c r="DD1" s="215">
         <v>35</v>
       </c>
-      <c r="DE1" s="220"/>
-      <c r="DF1" s="221"/>
-      <c r="DG1" s="219">
+      <c r="DE1" s="216"/>
+      <c r="DF1" s="217"/>
+      <c r="DG1" s="215">
         <v>36</v>
       </c>
-      <c r="DH1" s="220"/>
-      <c r="DI1" s="221"/>
-      <c r="DJ1" s="219">
+      <c r="DH1" s="216"/>
+      <c r="DI1" s="217"/>
+      <c r="DJ1" s="215">
         <v>37</v>
       </c>
-      <c r="DK1" s="220"/>
-      <c r="DL1" s="221"/>
-      <c r="DM1" s="219">
+      <c r="DK1" s="216"/>
+      <c r="DL1" s="217"/>
+      <c r="DM1" s="215">
         <v>38</v>
       </c>
-      <c r="DN1" s="220"/>
-      <c r="DO1" s="221"/>
+      <c r="DN1" s="216"/>
+      <c r="DO1" s="217"/>
     </row>
     <row r="2" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="222" t="s">
+      <c r="C2" s="221" t="s">
         <v>396</v>
       </c>
-      <c r="D2" s="222" t="s">
+      <c r="D2" s="221" t="s">
         <v>397</v>
       </c>
-      <c r="E2" s="222" t="s">
+      <c r="E2" s="221" t="s">
         <v>398</v>
       </c>
-      <c r="F2" s="216" t="s">
+      <c r="F2" s="218" t="s">
         <v>346</v>
       </c>
-      <c r="G2" s="217"/>
-      <c r="H2" s="218"/>
-      <c r="I2" s="216" t="s">
+      <c r="G2" s="219"/>
+      <c r="H2" s="220"/>
+      <c r="I2" s="218" t="s">
         <v>331</v>
       </c>
-      <c r="J2" s="217"/>
-      <c r="K2" s="218"/>
-      <c r="L2" s="216" t="s">
+      <c r="J2" s="219"/>
+      <c r="K2" s="220"/>
+      <c r="L2" s="218" t="s">
         <v>330</v>
       </c>
-      <c r="M2" s="217"/>
-      <c r="N2" s="218"/>
-      <c r="O2" s="216" t="s">
+      <c r="M2" s="219"/>
+      <c r="N2" s="220"/>
+      <c r="O2" s="218" t="s">
         <v>328</v>
       </c>
-      <c r="P2" s="217"/>
-      <c r="Q2" s="218"/>
-      <c r="R2" s="216" t="s">
+      <c r="P2" s="219"/>
+      <c r="Q2" s="220"/>
+      <c r="R2" s="218" t="s">
         <v>335</v>
       </c>
-      <c r="S2" s="217"/>
-      <c r="T2" s="218"/>
-      <c r="U2" s="216" t="s">
+      <c r="S2" s="219"/>
+      <c r="T2" s="220"/>
+      <c r="U2" s="218" t="s">
         <v>320</v>
       </c>
-      <c r="V2" s="217"/>
-      <c r="W2" s="218"/>
-      <c r="X2" s="216" t="s">
+      <c r="V2" s="219"/>
+      <c r="W2" s="220"/>
+      <c r="X2" s="218" t="s">
         <v>337</v>
       </c>
-      <c r="Y2" s="217"/>
-      <c r="Z2" s="218"/>
-      <c r="AA2" s="216" t="s">
+      <c r="Y2" s="219"/>
+      <c r="Z2" s="220"/>
+      <c r="AA2" s="218" t="s">
         <v>334</v>
       </c>
-      <c r="AB2" s="217"/>
-      <c r="AC2" s="218"/>
-      <c r="AD2" s="216" t="s">
+      <c r="AB2" s="219"/>
+      <c r="AC2" s="220"/>
+      <c r="AD2" s="218" t="s">
         <v>321</v>
       </c>
-      <c r="AE2" s="217"/>
-      <c r="AF2" s="218"/>
-      <c r="AG2" s="216" t="s">
+      <c r="AE2" s="219"/>
+      <c r="AF2" s="220"/>
+      <c r="AG2" s="218" t="s">
         <v>347</v>
       </c>
-      <c r="AH2" s="217"/>
-      <c r="AI2" s="218"/>
-      <c r="AJ2" s="216" t="s">
+      <c r="AH2" s="219"/>
+      <c r="AI2" s="220"/>
+      <c r="AJ2" s="218" t="s">
         <v>324</v>
       </c>
-      <c r="AK2" s="217"/>
-      <c r="AL2" s="218"/>
-      <c r="AM2" s="216" t="s">
+      <c r="AK2" s="219"/>
+      <c r="AL2" s="220"/>
+      <c r="AM2" s="218" t="s">
         <v>323</v>
       </c>
-      <c r="AN2" s="217"/>
-      <c r="AO2" s="218"/>
-      <c r="AP2" s="216" t="s">
+      <c r="AN2" s="219"/>
+      <c r="AO2" s="220"/>
+      <c r="AP2" s="218" t="s">
         <v>332</v>
       </c>
-      <c r="AQ2" s="217"/>
-      <c r="AR2" s="218"/>
-      <c r="AS2" s="216" t="s">
+      <c r="AQ2" s="219"/>
+      <c r="AR2" s="220"/>
+      <c r="AS2" s="218" t="s">
         <v>329</v>
       </c>
-      <c r="AT2" s="217"/>
-      <c r="AU2" s="218"/>
-      <c r="AV2" s="216" t="s">
+      <c r="AT2" s="219"/>
+      <c r="AU2" s="220"/>
+      <c r="AV2" s="218" t="s">
         <v>336</v>
       </c>
-      <c r="AW2" s="217"/>
-      <c r="AX2" s="218"/>
-      <c r="AY2" s="216" t="s">
+      <c r="AW2" s="219"/>
+      <c r="AX2" s="220"/>
+      <c r="AY2" s="218" t="s">
         <v>305</v>
       </c>
-      <c r="AZ2" s="217"/>
-      <c r="BA2" s="218"/>
-      <c r="BB2" s="216" t="s">
+      <c r="AZ2" s="219"/>
+      <c r="BA2" s="220"/>
+      <c r="BB2" s="218" t="s">
         <v>326</v>
       </c>
-      <c r="BC2" s="217"/>
-      <c r="BD2" s="218"/>
-      <c r="BE2" s="216" t="s">
+      <c r="BC2" s="219"/>
+      <c r="BD2" s="220"/>
+      <c r="BE2" s="218" t="s">
         <v>325</v>
       </c>
-      <c r="BF2" s="217"/>
-      <c r="BG2" s="218"/>
-      <c r="BH2" s="216" t="s">
+      <c r="BF2" s="219"/>
+      <c r="BG2" s="220"/>
+      <c r="BH2" s="218" t="s">
         <v>348</v>
       </c>
-      <c r="BI2" s="217"/>
-      <c r="BJ2" s="218"/>
-      <c r="BK2" s="216" t="s">
+      <c r="BI2" s="219"/>
+      <c r="BJ2" s="220"/>
+      <c r="BK2" s="218" t="s">
         <v>332</v>
       </c>
-      <c r="BL2" s="217"/>
-      <c r="BM2" s="218"/>
-      <c r="BN2" s="216" t="s">
+      <c r="BL2" s="219"/>
+      <c r="BM2" s="220"/>
+      <c r="BN2" s="218" t="s">
         <v>347</v>
       </c>
-      <c r="BO2" s="217"/>
-      <c r="BP2" s="218"/>
-      <c r="BQ2" s="216" t="s">
+      <c r="BO2" s="219"/>
+      <c r="BP2" s="220"/>
+      <c r="BQ2" s="218" t="s">
         <v>324</v>
       </c>
-      <c r="BR2" s="217"/>
-      <c r="BS2" s="218"/>
-      <c r="BT2" s="216" t="s">
+      <c r="BR2" s="219"/>
+      <c r="BS2" s="220"/>
+      <c r="BT2" s="218" t="s">
         <v>323</v>
       </c>
-      <c r="BU2" s="217"/>
-      <c r="BV2" s="218"/>
-      <c r="BW2" s="216" t="s">
+      <c r="BU2" s="219"/>
+      <c r="BV2" s="220"/>
+      <c r="BW2" s="218" t="s">
         <v>321</v>
       </c>
-      <c r="BX2" s="217"/>
-      <c r="BY2" s="218"/>
-      <c r="BZ2" s="216" t="s">
+      <c r="BX2" s="219"/>
+      <c r="BY2" s="220"/>
+      <c r="BZ2" s="218" t="s">
         <v>348</v>
       </c>
-      <c r="CA2" s="217"/>
-      <c r="CB2" s="218"/>
-      <c r="CC2" s="216" t="s">
+      <c r="CA2" s="219"/>
+      <c r="CB2" s="220"/>
+      <c r="CC2" s="218" t="s">
         <v>325</v>
       </c>
-      <c r="CD2" s="217"/>
-      <c r="CE2" s="218"/>
-      <c r="CF2" s="216" t="s">
+      <c r="CD2" s="219"/>
+      <c r="CE2" s="220"/>
+      <c r="CF2" s="218" t="s">
         <v>305</v>
       </c>
-      <c r="CG2" s="217"/>
-      <c r="CH2" s="218"/>
-      <c r="CI2" s="216" t="s">
+      <c r="CG2" s="219"/>
+      <c r="CH2" s="220"/>
+      <c r="CI2" s="218" t="s">
         <v>326</v>
       </c>
-      <c r="CJ2" s="217"/>
-      <c r="CK2" s="218"/>
-      <c r="CL2" s="216" t="s">
+      <c r="CJ2" s="219"/>
+      <c r="CK2" s="220"/>
+      <c r="CL2" s="218" t="s">
         <v>330</v>
       </c>
-      <c r="CM2" s="217"/>
-      <c r="CN2" s="218"/>
-      <c r="CO2" s="216" t="s">
+      <c r="CM2" s="219"/>
+      <c r="CN2" s="220"/>
+      <c r="CO2" s="218" t="s">
         <v>328</v>
       </c>
-      <c r="CP2" s="217"/>
-      <c r="CQ2" s="218"/>
-      <c r="CR2" s="216" t="s">
+      <c r="CP2" s="219"/>
+      <c r="CQ2" s="220"/>
+      <c r="CR2" s="218" t="s">
         <v>346</v>
       </c>
-      <c r="CS2" s="217"/>
-      <c r="CT2" s="218"/>
-      <c r="CU2" s="216" t="s">
+      <c r="CS2" s="219"/>
+      <c r="CT2" s="220"/>
+      <c r="CU2" s="218" t="s">
         <v>331</v>
       </c>
-      <c r="CV2" s="217"/>
-      <c r="CW2" s="218"/>
-      <c r="CX2" s="216" t="s">
+      <c r="CV2" s="219"/>
+      <c r="CW2" s="220"/>
+      <c r="CX2" s="218" t="s">
         <v>336</v>
       </c>
-      <c r="CY2" s="217"/>
-      <c r="CZ2" s="218"/>
-      <c r="DA2" s="216" t="s">
+      <c r="CY2" s="219"/>
+      <c r="CZ2" s="220"/>
+      <c r="DA2" s="218" t="s">
         <v>329</v>
       </c>
-      <c r="DB2" s="217"/>
-      <c r="DC2" s="218"/>
-      <c r="DD2" s="216" t="s">
+      <c r="DB2" s="219"/>
+      <c r="DC2" s="220"/>
+      <c r="DD2" s="218" t="s">
         <v>320</v>
       </c>
-      <c r="DE2" s="217"/>
-      <c r="DF2" s="218"/>
-      <c r="DG2" s="216" t="s">
+      <c r="DE2" s="219"/>
+      <c r="DF2" s="220"/>
+      <c r="DG2" s="218" t="s">
         <v>337</v>
       </c>
-      <c r="DH2" s="217"/>
-      <c r="DI2" s="218"/>
-      <c r="DJ2" s="216" t="s">
+      <c r="DH2" s="219"/>
+      <c r="DI2" s="220"/>
+      <c r="DJ2" s="218" t="s">
         <v>334</v>
       </c>
-      <c r="DK2" s="217"/>
-      <c r="DL2" s="218"/>
-      <c r="DM2" s="216" t="s">
+      <c r="DK2" s="219"/>
+      <c r="DL2" s="220"/>
+      <c r="DM2" s="218" t="s">
         <v>335</v>
       </c>
-      <c r="DN2" s="217"/>
-      <c r="DO2" s="218"/>
+      <c r="DN2" s="219"/>
+      <c r="DO2" s="220"/>
     </row>
     <row r="3" spans="1:119" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -38123,7 +38127,7 @@
       </c>
       <c r="C3" s="223"/>
       <c r="D3" s="223"/>
-      <c r="E3" s="224"/>
+      <c r="E3" s="222"/>
       <c r="F3" s="160" t="s">
         <v>393</v>
       </c>
@@ -38476,7 +38480,7 @@
       </c>
       <c r="C4" s="58">
         <f>SUM(F4,I4,L4,O4,R4,U4,X4,AA4,AD4,AG4,AJ4,AM4,AP4,AS4,AV4,AY4,BB4,BE4,BH4,BK4,BN4,BQ4,BT4,BW4,BZ4,CC4,CF4,CI4,CL4,CO4,CR4,CU4,CX4,DA4,DD4,DG4,DJ4,DM4)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" s="58">
         <f t="shared" ref="D4:E4" si="0">SUM(G4,J4,M4,P4,S4,V4,Y4,AB4,AE4,AH4,AK4,AN4,AQ4,AT4,AW4,AZ4,BC4,BF4,BI4,BL4,BO4,BR4,BU4,BX4,CA4,CD4,CG4,CJ4,CM4,CP4,CS4,CV4,CY4,DB4,DE4,DH4,DK4,DN4)</f>
@@ -38516,7 +38520,9 @@
       </c>
       <c r="V4" s="36"/>
       <c r="W4" s="53"/>
-      <c r="X4" s="52"/>
+      <c r="X4" s="52">
+        <v>1</v>
+      </c>
       <c r="Y4" s="36"/>
       <c r="Z4" s="53"/>
       <c r="AA4" s="52"/>
@@ -38894,7 +38900,7 @@
       </c>
       <c r="C7" s="58">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" s="58">
         <f t="shared" si="2"/>
@@ -38936,7 +38942,9 @@
       <c r="W7" s="53">
         <v>1</v>
       </c>
-      <c r="X7" s="52"/>
+      <c r="X7" s="52">
+        <v>1</v>
+      </c>
       <c r="Y7" s="36"/>
       <c r="Z7" s="53"/>
       <c r="AA7" s="52"/>
@@ -39182,7 +39190,7 @@
       </c>
       <c r="C9" s="58">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" s="58">
         <f t="shared" si="2"/>
@@ -39222,7 +39230,9 @@
       </c>
       <c r="V9" s="36"/>
       <c r="W9" s="53"/>
-      <c r="X9" s="52"/>
+      <c r="X9" s="52">
+        <v>1</v>
+      </c>
       <c r="Y9" s="36"/>
       <c r="Z9" s="53"/>
       <c r="AA9" s="52"/>
@@ -39328,7 +39338,7 @@
       </c>
       <c r="C10" s="58">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" s="58">
         <f t="shared" si="2"/>
@@ -39374,7 +39384,9 @@
       </c>
       <c r="V10" s="36"/>
       <c r="W10" s="53"/>
-      <c r="X10" s="52"/>
+      <c r="X10" s="52">
+        <v>1</v>
+      </c>
       <c r="Y10" s="36"/>
       <c r="Z10" s="53"/>
       <c r="AA10" s="52"/>
@@ -39480,7 +39492,7 @@
       </c>
       <c r="C11" s="58">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" s="58">
         <f t="shared" si="2"/>
@@ -39524,7 +39536,9 @@
       </c>
       <c r="V11" s="36"/>
       <c r="W11" s="53"/>
-      <c r="X11" s="52"/>
+      <c r="X11" s="52">
+        <v>1</v>
+      </c>
       <c r="Y11" s="36"/>
       <c r="Z11" s="53"/>
       <c r="AA11" s="52"/>
@@ -39630,7 +39644,7 @@
       </c>
       <c r="C12" s="58">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D12" s="58">
         <f t="shared" si="2"/>
@@ -39666,7 +39680,9 @@
       <c r="U12" s="52"/>
       <c r="V12" s="36"/>
       <c r="W12" s="53"/>
-      <c r="X12" s="52"/>
+      <c r="X12" s="52">
+        <v>1</v>
+      </c>
       <c r="Y12" s="36"/>
       <c r="Z12" s="53"/>
       <c r="AA12" s="52"/>
@@ -39772,7 +39788,7 @@
       </c>
       <c r="C13" s="58">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" s="58">
         <f t="shared" si="2"/>
@@ -39806,7 +39822,9 @@
       </c>
       <c r="V13" s="36"/>
       <c r="W13" s="53"/>
-      <c r="X13" s="52"/>
+      <c r="X13" s="52">
+        <v>1</v>
+      </c>
       <c r="Y13" s="36"/>
       <c r="Z13" s="53"/>
       <c r="AA13" s="52"/>
@@ -40046,7 +40064,7 @@
       </c>
       <c r="C15" s="58">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" s="58">
         <f t="shared" si="2"/>
@@ -40080,7 +40098,9 @@
       </c>
       <c r="V15" s="36"/>
       <c r="W15" s="53"/>
-      <c r="X15" s="52"/>
+      <c r="X15" s="52">
+        <v>1</v>
+      </c>
       <c r="Y15" s="36"/>
       <c r="Z15" s="53"/>
       <c r="AA15" s="52"/>
@@ -40186,7 +40206,7 @@
       </c>
       <c r="C16" s="58">
         <f t="shared" ref="C16:C28" si="4">SUM(F16,I16,L16,O16,R16,U16,X16,AA16,AD16,AG16,AJ16,AM16,AP16,AS16,AV16,AY16,BB16,BE16,BH16,BK16,BN16,BQ16,BT16,BW16,BZ16,CC16,CF16,CI16,CL16,CO16,CR16,CU16,CX16,DA16,DD16,DG16,DJ16,DM16)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D16" s="58">
         <f t="shared" ref="D16:D28" si="5">SUM(G16,J16,M16,P16,S16,V16,Y16,AB16,AE16,AH16,AK16,AN16,AQ16,AT16,AW16,AZ16,BC16,BF16,BI16,BL16,BO16,BR16,BU16,BX16,CA16,CD16,CG16,CJ16,CM16,CP16,CS16,CV16,CY16,DB16,DE16,DH16,DK16,DN16)</f>
@@ -40224,7 +40244,9 @@
       </c>
       <c r="V16" s="36"/>
       <c r="W16" s="53"/>
-      <c r="X16" s="52"/>
+      <c r="X16" s="52">
+        <v>1</v>
+      </c>
       <c r="Y16" s="36"/>
       <c r="Z16" s="53"/>
       <c r="AA16" s="52"/>
@@ -40476,11 +40498,11 @@
       </c>
       <c r="C18" s="58">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18" s="58">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" s="51">
         <f t="shared" si="6"/>
@@ -40510,8 +40532,12 @@
       </c>
       <c r="V18" s="36"/>
       <c r="W18" s="53"/>
-      <c r="X18" s="52"/>
-      <c r="Y18" s="36"/>
+      <c r="X18" s="52">
+        <v>1</v>
+      </c>
+      <c r="Y18" s="36">
+        <v>1</v>
+      </c>
       <c r="Z18" s="53"/>
       <c r="AA18" s="52"/>
       <c r="AB18" s="36"/>
@@ -40750,7 +40776,7 @@
       </c>
       <c r="C20" s="58">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D20" s="58">
         <f t="shared" si="5"/>
@@ -40790,7 +40816,9 @@
       </c>
       <c r="V20" s="36"/>
       <c r="W20" s="53"/>
-      <c r="X20" s="52"/>
+      <c r="X20" s="52">
+        <v>1</v>
+      </c>
       <c r="Y20" s="36"/>
       <c r="Z20" s="53"/>
       <c r="AA20" s="52"/>
@@ -40896,7 +40924,7 @@
       </c>
       <c r="C21" s="58">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D21" s="58">
         <f t="shared" si="5"/>
@@ -40940,7 +40968,9 @@
       </c>
       <c r="V21" s="36"/>
       <c r="W21" s="53"/>
-      <c r="X21" s="52"/>
+      <c r="X21" s="52">
+        <v>1</v>
+      </c>
       <c r="Y21" s="36"/>
       <c r="Z21" s="53"/>
       <c r="AA21" s="52"/>
@@ -41180,7 +41210,7 @@
       </c>
       <c r="C23" s="58">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D23" s="58">
         <f t="shared" si="5"/>
@@ -41226,7 +41256,9 @@
         <v>1</v>
       </c>
       <c r="W23" s="53"/>
-      <c r="X23" s="52"/>
+      <c r="X23" s="52">
+        <v>1</v>
+      </c>
       <c r="Y23" s="36"/>
       <c r="Z23" s="53"/>
       <c r="AA23" s="52"/>
@@ -41610,7 +41642,7 @@
       </c>
       <c r="C26" s="58">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D26" s="58">
         <f t="shared" si="5"/>
@@ -41650,7 +41682,9 @@
         <v>1</v>
       </c>
       <c r="W26" s="53"/>
-      <c r="X26" s="52"/>
+      <c r="X26" s="52">
+        <v>1</v>
+      </c>
       <c r="Y26" s="36"/>
       <c r="Z26" s="53"/>
       <c r="AA26" s="52"/>
@@ -41890,7 +41924,7 @@
       </c>
       <c r="C28" s="58">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D28" s="58">
         <f t="shared" si="5"/>
@@ -41898,7 +41932,7 @@
       </c>
       <c r="E28" s="51">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F28" s="52">
         <v>1</v>
@@ -41936,9 +41970,13 @@
       <c r="W28" s="53">
         <v>1</v>
       </c>
-      <c r="X28" s="52"/>
+      <c r="X28" s="52">
+        <v>1</v>
+      </c>
       <c r="Y28" s="36"/>
-      <c r="Z28" s="53"/>
+      <c r="Z28" s="53">
+        <v>1</v>
+      </c>
       <c r="AA28" s="52"/>
       <c r="AB28" s="36"/>
       <c r="AC28" s="53"/>
@@ -43465,15 +43503,15 @@
       </c>
       <c r="X39" s="73">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Y39" s="73">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z39" s="73">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA39" s="73">
         <f t="shared" si="11"/>
@@ -43850,69 +43888,6 @@
     </row>
   </sheetData>
   <mergeCells count="79">
-    <mergeCell ref="DM1:DO1"/>
-    <mergeCell ref="DM2:DO2"/>
-    <mergeCell ref="DA1:DC1"/>
-    <mergeCell ref="DA2:DC2"/>
-    <mergeCell ref="DD1:DF1"/>
-    <mergeCell ref="DD2:DF2"/>
-    <mergeCell ref="DG1:DI1"/>
-    <mergeCell ref="DG2:DI2"/>
-    <mergeCell ref="CU1:CW1"/>
-    <mergeCell ref="CU2:CW2"/>
-    <mergeCell ref="CX1:CZ1"/>
-    <mergeCell ref="CX2:CZ2"/>
-    <mergeCell ref="DJ1:DL1"/>
-    <mergeCell ref="DJ2:DL2"/>
-    <mergeCell ref="CL1:CN1"/>
-    <mergeCell ref="CL2:CN2"/>
-    <mergeCell ref="CO1:CQ1"/>
-    <mergeCell ref="CO2:CQ2"/>
-    <mergeCell ref="CR1:CT1"/>
-    <mergeCell ref="CR2:CT2"/>
-    <mergeCell ref="CC1:CE1"/>
-    <mergeCell ref="CC2:CE2"/>
-    <mergeCell ref="CF1:CH1"/>
-    <mergeCell ref="CF2:CH2"/>
-    <mergeCell ref="CI1:CK1"/>
-    <mergeCell ref="CI2:CK2"/>
-    <mergeCell ref="BT1:BV1"/>
-    <mergeCell ref="BT2:BV2"/>
-    <mergeCell ref="BW1:BY1"/>
-    <mergeCell ref="BW2:BY2"/>
-    <mergeCell ref="BZ1:CB1"/>
-    <mergeCell ref="BZ2:CB2"/>
-    <mergeCell ref="BK1:BM1"/>
-    <mergeCell ref="BK2:BM2"/>
-    <mergeCell ref="BN1:BP1"/>
-    <mergeCell ref="BN2:BP2"/>
-    <mergeCell ref="BQ1:BS1"/>
-    <mergeCell ref="BQ2:BS2"/>
-    <mergeCell ref="AS1:AU1"/>
-    <mergeCell ref="AS2:AU2"/>
-    <mergeCell ref="AV1:AX1"/>
-    <mergeCell ref="AV2:AX2"/>
-    <mergeCell ref="BH1:BJ1"/>
-    <mergeCell ref="BH2:BJ2"/>
-    <mergeCell ref="AY2:BA2"/>
-    <mergeCell ref="BB2:BD2"/>
-    <mergeCell ref="BE2:BG2"/>
-    <mergeCell ref="AJ1:AL1"/>
-    <mergeCell ref="AJ2:AL2"/>
-    <mergeCell ref="AM1:AO1"/>
-    <mergeCell ref="AM2:AO2"/>
-    <mergeCell ref="AP2:AR2"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
     <mergeCell ref="AD2:AF2"/>
     <mergeCell ref="AG2:AI2"/>
     <mergeCell ref="BB1:BD1"/>
@@ -43929,6 +43904,69 @@
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="X1:Z1"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="AJ1:AL1"/>
+    <mergeCell ref="AJ2:AL2"/>
+    <mergeCell ref="AM1:AO1"/>
+    <mergeCell ref="AM2:AO2"/>
+    <mergeCell ref="AP2:AR2"/>
+    <mergeCell ref="AS1:AU1"/>
+    <mergeCell ref="AS2:AU2"/>
+    <mergeCell ref="AV1:AX1"/>
+    <mergeCell ref="AV2:AX2"/>
+    <mergeCell ref="BH1:BJ1"/>
+    <mergeCell ref="BH2:BJ2"/>
+    <mergeCell ref="AY2:BA2"/>
+    <mergeCell ref="BB2:BD2"/>
+    <mergeCell ref="BE2:BG2"/>
+    <mergeCell ref="BK1:BM1"/>
+    <mergeCell ref="BK2:BM2"/>
+    <mergeCell ref="BN1:BP1"/>
+    <mergeCell ref="BN2:BP2"/>
+    <mergeCell ref="BQ1:BS1"/>
+    <mergeCell ref="BQ2:BS2"/>
+    <mergeCell ref="BT1:BV1"/>
+    <mergeCell ref="BT2:BV2"/>
+    <mergeCell ref="BW1:BY1"/>
+    <mergeCell ref="BW2:BY2"/>
+    <mergeCell ref="BZ1:CB1"/>
+    <mergeCell ref="BZ2:CB2"/>
+    <mergeCell ref="CC1:CE1"/>
+    <mergeCell ref="CC2:CE2"/>
+    <mergeCell ref="CF1:CH1"/>
+    <mergeCell ref="CF2:CH2"/>
+    <mergeCell ref="CI1:CK1"/>
+    <mergeCell ref="CI2:CK2"/>
+    <mergeCell ref="CL1:CN1"/>
+    <mergeCell ref="CL2:CN2"/>
+    <mergeCell ref="CO1:CQ1"/>
+    <mergeCell ref="CO2:CQ2"/>
+    <mergeCell ref="CR1:CT1"/>
+    <mergeCell ref="CR2:CT2"/>
+    <mergeCell ref="CU1:CW1"/>
+    <mergeCell ref="CU2:CW2"/>
+    <mergeCell ref="CX1:CZ1"/>
+    <mergeCell ref="CX2:CZ2"/>
+    <mergeCell ref="DJ1:DL1"/>
+    <mergeCell ref="DJ2:DL2"/>
+    <mergeCell ref="DM1:DO1"/>
+    <mergeCell ref="DM2:DO2"/>
+    <mergeCell ref="DA1:DC1"/>
+    <mergeCell ref="DA2:DC2"/>
+    <mergeCell ref="DD1:DF1"/>
+    <mergeCell ref="DD2:DF2"/>
+    <mergeCell ref="DG1:DI1"/>
+    <mergeCell ref="DG2:DI2"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:DO38">
     <cfRule type="cellIs" dxfId="18" priority="1" operator="between">
@@ -43964,138 +44002,138 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="237" t="s">
+      <c r="C1" s="233" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="237" t="s">
+      <c r="D1" s="233" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="237" t="s">
+      <c r="E1" s="233" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="228" t="s">
+      <c r="F1" s="224" t="s">
         <v>302</v>
       </c>
-      <c r="G1" s="229"/>
-      <c r="H1" s="229"/>
-      <c r="I1" s="229"/>
-      <c r="J1" s="229"/>
-      <c r="K1" s="229"/>
-      <c r="L1" s="229"/>
-      <c r="M1" s="229"/>
-      <c r="N1" s="229"/>
-      <c r="O1" s="229"/>
-      <c r="P1" s="229"/>
-      <c r="Q1" s="229"/>
-      <c r="R1" s="229"/>
-      <c r="S1" s="229"/>
-      <c r="T1" s="229"/>
-      <c r="U1" s="229"/>
-      <c r="V1" s="229"/>
-      <c r="W1" s="229"/>
-      <c r="X1" s="229"/>
-      <c r="Y1" s="229"/>
-      <c r="Z1" s="229"/>
-      <c r="AA1" s="229"/>
-      <c r="AB1" s="229"/>
-      <c r="AC1" s="230"/>
-      <c r="AD1" s="240" t="s">
+      <c r="G1" s="225"/>
+      <c r="H1" s="225"/>
+      <c r="I1" s="225"/>
+      <c r="J1" s="225"/>
+      <c r="K1" s="225"/>
+      <c r="L1" s="225"/>
+      <c r="M1" s="225"/>
+      <c r="N1" s="225"/>
+      <c r="O1" s="225"/>
+      <c r="P1" s="225"/>
+      <c r="Q1" s="225"/>
+      <c r="R1" s="225"/>
+      <c r="S1" s="225"/>
+      <c r="T1" s="225"/>
+      <c r="U1" s="225"/>
+      <c r="V1" s="225"/>
+      <c r="W1" s="225"/>
+      <c r="X1" s="225"/>
+      <c r="Y1" s="225"/>
+      <c r="Z1" s="225"/>
+      <c r="AA1" s="225"/>
+      <c r="AB1" s="225"/>
+      <c r="AC1" s="226"/>
+      <c r="AD1" s="239" t="s">
         <v>281</v>
       </c>
-      <c r="AE1" s="241"/>
-      <c r="AF1" s="241"/>
-      <c r="AG1" s="241"/>
-      <c r="AH1" s="241"/>
-      <c r="AI1" s="242"/>
-      <c r="AJ1" s="228" t="s">
+      <c r="AE1" s="240"/>
+      <c r="AF1" s="240"/>
+      <c r="AG1" s="240"/>
+      <c r="AH1" s="240"/>
+      <c r="AI1" s="241"/>
+      <c r="AJ1" s="224" t="s">
         <v>282</v>
       </c>
-      <c r="AK1" s="229"/>
-      <c r="AL1" s="229"/>
-      <c r="AM1" s="229"/>
-      <c r="AN1" s="229"/>
-      <c r="AO1" s="230"/>
-      <c r="AP1" s="231" t="s">
+      <c r="AK1" s="225"/>
+      <c r="AL1" s="225"/>
+      <c r="AM1" s="225"/>
+      <c r="AN1" s="225"/>
+      <c r="AO1" s="226"/>
+      <c r="AP1" s="227" t="s">
         <v>283</v>
       </c>
-      <c r="AQ1" s="232"/>
-      <c r="AR1" s="232"/>
-      <c r="AS1" s="232"/>
-      <c r="AT1" s="232"/>
-      <c r="AU1" s="233"/>
-      <c r="AV1" s="234" t="s">
+      <c r="AQ1" s="228"/>
+      <c r="AR1" s="228"/>
+      <c r="AS1" s="228"/>
+      <c r="AT1" s="228"/>
+      <c r="AU1" s="229"/>
+      <c r="AV1" s="230" t="s">
         <v>86</v>
       </c>
-      <c r="AW1" s="235"/>
-      <c r="AX1" s="236"/>
+      <c r="AW1" s="231"/>
+      <c r="AX1" s="232"/>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="238"/>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="225" t="s">
+      <c r="C2" s="234"/>
+      <c r="D2" s="234"/>
+      <c r="E2" s="234"/>
+      <c r="F2" s="236" t="s">
         <v>458</v>
       </c>
-      <c r="G2" s="226"/>
-      <c r="H2" s="227"/>
-      <c r="I2" s="225" t="s">
+      <c r="G2" s="237"/>
+      <c r="H2" s="238"/>
+      <c r="I2" s="236" t="s">
         <v>461</v>
       </c>
-      <c r="J2" s="226"/>
-      <c r="K2" s="227"/>
-      <c r="L2" s="225" t="s">
+      <c r="J2" s="237"/>
+      <c r="K2" s="238"/>
+      <c r="L2" s="236" t="s">
         <v>462</v>
       </c>
-      <c r="M2" s="226"/>
-      <c r="N2" s="227"/>
-      <c r="O2" s="225" t="s">
+      <c r="M2" s="237"/>
+      <c r="N2" s="238"/>
+      <c r="O2" s="236" t="s">
         <v>463</v>
       </c>
-      <c r="P2" s="226"/>
-      <c r="Q2" s="227"/>
-      <c r="R2" s="225" t="s">
+      <c r="P2" s="237"/>
+      <c r="Q2" s="238"/>
+      <c r="R2" s="236" t="s">
         <v>464</v>
       </c>
-      <c r="S2" s="226"/>
-      <c r="T2" s="227"/>
-      <c r="U2" s="225" t="s">
+      <c r="S2" s="237"/>
+      <c r="T2" s="238"/>
+      <c r="U2" s="236" t="s">
         <v>465</v>
       </c>
-      <c r="V2" s="226"/>
-      <c r="W2" s="227"/>
-      <c r="X2" s="225" t="s">
+      <c r="V2" s="237"/>
+      <c r="W2" s="238"/>
+      <c r="X2" s="236" t="s">
         <v>466</v>
       </c>
-      <c r="Y2" s="226"/>
-      <c r="Z2" s="227"/>
-      <c r="AA2" s="225" t="s">
+      <c r="Y2" s="237"/>
+      <c r="Z2" s="238"/>
+      <c r="AA2" s="236" t="s">
         <v>467</v>
       </c>
-      <c r="AB2" s="226"/>
-      <c r="AC2" s="226"/>
-      <c r="AD2" s="225"/>
-      <c r="AE2" s="226"/>
-      <c r="AF2" s="227"/>
-      <c r="AG2" s="225"/>
-      <c r="AH2" s="226"/>
-      <c r="AI2" s="227"/>
-      <c r="AJ2" s="225"/>
-      <c r="AK2" s="226"/>
-      <c r="AL2" s="227"/>
-      <c r="AM2" s="225"/>
-      <c r="AN2" s="226"/>
-      <c r="AO2" s="227"/>
-      <c r="AP2" s="225"/>
-      <c r="AQ2" s="226"/>
-      <c r="AR2" s="227"/>
-      <c r="AS2" s="225"/>
-      <c r="AT2" s="226"/>
-      <c r="AU2" s="227"/>
-      <c r="AV2" s="225"/>
-      <c r="AW2" s="226"/>
-      <c r="AX2" s="227"/>
+      <c r="AB2" s="237"/>
+      <c r="AC2" s="237"/>
+      <c r="AD2" s="236"/>
+      <c r="AE2" s="237"/>
+      <c r="AF2" s="238"/>
+      <c r="AG2" s="236"/>
+      <c r="AH2" s="237"/>
+      <c r="AI2" s="238"/>
+      <c r="AJ2" s="236"/>
+      <c r="AK2" s="237"/>
+      <c r="AL2" s="238"/>
+      <c r="AM2" s="236"/>
+      <c r="AN2" s="237"/>
+      <c r="AO2" s="238"/>
+      <c r="AP2" s="236"/>
+      <c r="AQ2" s="237"/>
+      <c r="AR2" s="238"/>
+      <c r="AS2" s="236"/>
+      <c r="AT2" s="237"/>
+      <c r="AU2" s="238"/>
+      <c r="AV2" s="236"/>
+      <c r="AW2" s="237"/>
+      <c r="AX2" s="238"/>
     </row>
     <row r="3" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -44104,9 +44142,9 @@
       <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="239"/>
-      <c r="D3" s="239"/>
-      <c r="E3" s="239"/>
+      <c r="C3" s="235"/>
+      <c r="D3" s="235"/>
+      <c r="E3" s="235"/>
       <c r="F3" s="169" t="s">
         <v>393</v>
       </c>
@@ -44252,7 +44290,7 @@
       </c>
       <c r="C4" s="58">
         <f>SUM(F4,I4,L4,O4,R4,X4,AA4,AD4,U4,AG4,AJ4,AM4,AP4,AS4,AV4)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="58">
         <f t="shared" ref="D4:E4" si="0">SUM(G4,J4,M4,P4,S4,Y4,AB4,AE4,V4,AH4,AK4,AN4,AQ4,AT4,AW4)</f>
@@ -44267,7 +44305,9 @@
       </c>
       <c r="G4" s="36"/>
       <c r="H4" s="53"/>
-      <c r="I4" s="52"/>
+      <c r="I4" s="52">
+        <v>1</v>
+      </c>
       <c r="J4" s="36"/>
       <c r="K4" s="53"/>
       <c r="L4" s="52"/>
@@ -44449,7 +44489,7 @@
       </c>
       <c r="C7" s="58">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" s="58">
         <f t="shared" si="2"/>
@@ -44464,7 +44504,9 @@
       </c>
       <c r="G7" s="36"/>
       <c r="H7" s="53"/>
-      <c r="I7" s="52"/>
+      <c r="I7" s="52">
+        <v>1</v>
+      </c>
       <c r="J7" s="36"/>
       <c r="K7" s="53"/>
       <c r="L7" s="52"/>
@@ -44583,7 +44625,7 @@
       </c>
       <c r="C9" s="58">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" s="58">
         <f t="shared" si="2"/>
@@ -44598,7 +44640,9 @@
       </c>
       <c r="G9" s="36"/>
       <c r="H9" s="53"/>
-      <c r="I9" s="52"/>
+      <c r="I9" s="52">
+        <v>1</v>
+      </c>
       <c r="J9" s="36"/>
       <c r="K9" s="53"/>
       <c r="L9" s="52"/>
@@ -44650,24 +44694,30 @@
       </c>
       <c r="C10" s="58">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" s="58">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="52">
         <v>1</v>
       </c>
       <c r="G10" s="36"/>
       <c r="H10" s="53"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="36"/>
-      <c r="K10" s="53"/>
+      <c r="I10" s="52">
+        <v>1</v>
+      </c>
+      <c r="J10" s="36">
+        <v>1</v>
+      </c>
+      <c r="K10" s="53">
+        <v>1</v>
+      </c>
       <c r="L10" s="52"/>
       <c r="M10" s="36"/>
       <c r="N10" s="53"/>
@@ -44717,7 +44767,7 @@
       </c>
       <c r="C11" s="58">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" s="58">
         <f t="shared" si="2"/>
@@ -44734,7 +44784,9 @@
         <v>1</v>
       </c>
       <c r="H11" s="53"/>
-      <c r="I11" s="52"/>
+      <c r="I11" s="52">
+        <v>1</v>
+      </c>
       <c r="J11" s="36"/>
       <c r="K11" s="53"/>
       <c r="L11" s="52"/>
@@ -44786,11 +44838,11 @@
       </c>
       <c r="C12" s="58">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" s="58">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="58">
         <f t="shared" si="3"/>
@@ -44801,8 +44853,12 @@
       </c>
       <c r="G12" s="36"/>
       <c r="H12" s="53"/>
-      <c r="I12" s="52"/>
-      <c r="J12" s="36"/>
+      <c r="I12" s="52">
+        <v>1</v>
+      </c>
+      <c r="J12" s="36">
+        <v>1</v>
+      </c>
       <c r="K12" s="53"/>
       <c r="L12" s="52"/>
       <c r="M12" s="36"/>
@@ -44853,11 +44909,11 @@
       </c>
       <c r="C13" s="58">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" s="58">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" s="58">
         <f t="shared" si="3"/>
@@ -44866,8 +44922,12 @@
       <c r="F13" s="52"/>
       <c r="G13" s="36"/>
       <c r="H13" s="53"/>
-      <c r="I13" s="52"/>
-      <c r="J13" s="36"/>
+      <c r="I13" s="52">
+        <v>1</v>
+      </c>
+      <c r="J13" s="36">
+        <v>1</v>
+      </c>
       <c r="K13" s="53"/>
       <c r="L13" s="52"/>
       <c r="M13" s="36"/>
@@ -44983,7 +45043,7 @@
       </c>
       <c r="C15" s="58">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="58">
         <f t="shared" si="2"/>
@@ -44998,7 +45058,9 @@
       </c>
       <c r="G15" s="36"/>
       <c r="H15" s="53"/>
-      <c r="I15" s="52"/>
+      <c r="I15" s="52">
+        <v>1</v>
+      </c>
       <c r="J15" s="36"/>
       <c r="K15" s="53"/>
       <c r="L15" s="52"/>
@@ -45050,7 +45112,7 @@
       </c>
       <c r="C16" s="58">
         <f t="shared" ref="C16:C28" si="4">SUM(F16,I16,L16,O16,R16,X16,AA16,AD16,U16,AG16,AJ16,AM16,AP16,AS16,AV16)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="58">
         <f t="shared" ref="D16:D28" si="5">SUM(G16,J16,M16,P16,S16,Y16,AB16,AE16,V16,AH16,AK16,AN16,AQ16,AT16,AW16)</f>
@@ -45065,7 +45127,9 @@
       </c>
       <c r="G16" s="36"/>
       <c r="H16" s="53"/>
-      <c r="I16" s="52"/>
+      <c r="I16" s="52">
+        <v>1</v>
+      </c>
       <c r="J16" s="36"/>
       <c r="K16" s="53"/>
       <c r="L16" s="52"/>
@@ -45186,7 +45250,7 @@
       </c>
       <c r="C18" s="58">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="58">
         <f t="shared" si="5"/>
@@ -45194,16 +45258,20 @@
       </c>
       <c r="E18" s="58">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" s="52">
         <v>1</v>
       </c>
       <c r="G18" s="36"/>
       <c r="H18" s="53"/>
-      <c r="I18" s="52"/>
+      <c r="I18" s="52">
+        <v>1</v>
+      </c>
       <c r="J18" s="36"/>
-      <c r="K18" s="53"/>
+      <c r="K18" s="53">
+        <v>1</v>
+      </c>
       <c r="L18" s="52"/>
       <c r="M18" s="36"/>
       <c r="N18" s="53"/>
@@ -45318,7 +45386,7 @@
       </c>
       <c r="C20" s="58">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" s="58">
         <f t="shared" si="5"/>
@@ -45333,7 +45401,9 @@
       </c>
       <c r="G20" s="36"/>
       <c r="H20" s="53"/>
-      <c r="I20" s="52"/>
+      <c r="I20" s="52">
+        <v>1</v>
+      </c>
       <c r="J20" s="36"/>
       <c r="K20" s="53"/>
       <c r="L20" s="52"/>
@@ -45385,7 +45455,7 @@
       </c>
       <c r="C21" s="58">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" s="58">
         <f t="shared" si="5"/>
@@ -45393,16 +45463,20 @@
       </c>
       <c r="E21" s="58">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" s="52">
         <v>1</v>
       </c>
       <c r="G21" s="36"/>
       <c r="H21" s="53"/>
-      <c r="I21" s="52"/>
+      <c r="I21" s="52">
+        <v>1</v>
+      </c>
       <c r="J21" s="36"/>
-      <c r="K21" s="53"/>
+      <c r="K21" s="53">
+        <v>1</v>
+      </c>
       <c r="L21" s="52"/>
       <c r="M21" s="36"/>
       <c r="N21" s="53"/>
@@ -45714,7 +45788,7 @@
       </c>
       <c r="C26" s="58">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" s="58">
         <f t="shared" si="5"/>
@@ -45729,7 +45803,9 @@
       </c>
       <c r="G26" s="36"/>
       <c r="H26" s="53"/>
-      <c r="I26" s="52"/>
+      <c r="I26" s="52">
+        <v>1</v>
+      </c>
       <c r="J26" s="36"/>
       <c r="K26" s="53"/>
       <c r="L26" s="52"/>
@@ -45846,7 +45922,7 @@
       </c>
       <c r="C28" s="58">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" s="58">
         <f t="shared" si="5"/>
@@ -45861,7 +45937,9 @@
       </c>
       <c r="G28" s="36"/>
       <c r="H28" s="53"/>
-      <c r="I28" s="52"/>
+      <c r="I28" s="52">
+        <v>1</v>
+      </c>
       <c r="J28" s="36"/>
       <c r="K28" s="53"/>
       <c r="L28" s="52"/>
@@ -46173,7 +46251,7 @@
       </c>
       <c r="C33" s="58">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D33" s="58">
         <f t="shared" si="9"/>
@@ -46186,7 +46264,9 @@
       <c r="F33" s="49"/>
       <c r="G33" s="165"/>
       <c r="H33" s="50"/>
-      <c r="I33" s="49"/>
+      <c r="I33" s="49">
+        <v>1</v>
+      </c>
       <c r="J33" s="165"/>
       <c r="K33" s="50"/>
       <c r="L33" s="49"/>
@@ -46368,7 +46448,7 @@
       </c>
       <c r="C36" s="58">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D36" s="58">
         <f t="shared" si="9"/>
@@ -46381,7 +46461,9 @@
       <c r="F36" s="49"/>
       <c r="G36" s="165"/>
       <c r="H36" s="50"/>
-      <c r="I36" s="49"/>
+      <c r="I36" s="49">
+        <v>1</v>
+      </c>
       <c r="J36" s="165"/>
       <c r="K36" s="50"/>
       <c r="L36" s="49"/>
@@ -46569,15 +46651,15 @@
       </c>
       <c r="I39" s="171">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J39" s="172">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K39" s="173">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L39" s="171">
         <f t="shared" si="11"/>
@@ -46738,6 +46820,13 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="F1:AC1"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
+    <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="AJ1:AO1"/>
     <mergeCell ref="AP1:AU1"/>
     <mergeCell ref="AV1:AX1"/>
@@ -46754,13 +46843,6 @@
     <mergeCell ref="AD1:AI1"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="I2:K2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="F1:AC1"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:AW32">
     <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
@@ -46795,70 +46877,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C1" s="237" t="s">
+      <c r="C1" s="233" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="237" t="s">
+      <c r="D1" s="233" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="237" t="s">
+      <c r="E1" s="233" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="267" t="s">
+      <c r="F1" s="273" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="268"/>
-      <c r="H1" s="269"/>
-      <c r="I1" s="270" t="s">
+      <c r="G1" s="274"/>
+      <c r="H1" s="275"/>
+      <c r="I1" s="276" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="271"/>
-      <c r="K1" s="272"/>
-      <c r="L1" s="274" t="s">
+      <c r="J1" s="277"/>
+      <c r="K1" s="278"/>
+      <c r="L1" s="243" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="275"/>
-      <c r="N1" s="276"/>
-      <c r="O1" s="277" t="s">
+      <c r="M1" s="244"/>
+      <c r="N1" s="245"/>
+      <c r="O1" s="246" t="s">
         <v>199</v>
       </c>
-      <c r="P1" s="278"/>
-      <c r="Q1" s="279"/>
-      <c r="R1" s="243" t="s">
+      <c r="P1" s="247"/>
+      <c r="Q1" s="248"/>
+      <c r="R1" s="249" t="s">
         <v>200</v>
       </c>
-      <c r="S1" s="244"/>
-      <c r="T1" s="245"/>
-      <c r="U1" s="246" t="s">
+      <c r="S1" s="250"/>
+      <c r="T1" s="251"/>
+      <c r="U1" s="252" t="s">
         <v>306</v>
       </c>
-      <c r="V1" s="247"/>
-      <c r="W1" s="248"/>
+      <c r="V1" s="253"/>
+      <c r="W1" s="254"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="238"/>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="249"/>
-      <c r="G2" s="250"/>
-      <c r="H2" s="251"/>
-      <c r="I2" s="264"/>
-      <c r="J2" s="265"/>
-      <c r="K2" s="266"/>
-      <c r="L2" s="261"/>
-      <c r="M2" s="262"/>
-      <c r="N2" s="263"/>
-      <c r="O2" s="258"/>
-      <c r="P2" s="259"/>
-      <c r="Q2" s="260"/>
-      <c r="R2" s="255"/>
-      <c r="S2" s="256"/>
-      <c r="T2" s="257"/>
-      <c r="U2" s="252"/>
-      <c r="V2" s="253"/>
-      <c r="W2" s="254"/>
+      <c r="C2" s="234"/>
+      <c r="D2" s="234"/>
+      <c r="E2" s="234"/>
+      <c r="F2" s="255"/>
+      <c r="G2" s="256"/>
+      <c r="H2" s="257"/>
+      <c r="I2" s="270"/>
+      <c r="J2" s="271"/>
+      <c r="K2" s="272"/>
+      <c r="L2" s="267"/>
+      <c r="M2" s="268"/>
+      <c r="N2" s="269"/>
+      <c r="O2" s="264"/>
+      <c r="P2" s="265"/>
+      <c r="Q2" s="266"/>
+      <c r="R2" s="261"/>
+      <c r="S2" s="262"/>
+      <c r="T2" s="263"/>
+      <c r="U2" s="258"/>
+      <c r="V2" s="259"/>
+      <c r="W2" s="260"/>
     </row>
     <row r="3" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -46867,9 +46949,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="273"/>
-      <c r="D3" s="273"/>
-      <c r="E3" s="273"/>
+      <c r="C3" s="242"/>
+      <c r="D3" s="242"/>
+      <c r="E3" s="242"/>
       <c r="F3" s="188" t="s">
         <v>393</v>
       </c>
@@ -48331,11 +48413,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="O1:Q1"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="F2:H2"/>
@@ -48346,6 +48423,11 @@
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="O1:Q1"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:W32">
     <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
@@ -48585,7 +48667,7 @@
       <c r="F6" s="25"/>
       <c r="G6" s="21">
         <f>'Apps &amp; Goals 26-27'!C4</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H6" s="21">
         <f>'Apps &amp; Goals 26-27'!D4</f>
@@ -48597,7 +48679,7 @@
       </c>
       <c r="J6" s="25">
         <f>G6+C6</f>
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K6" s="25">
         <f>H6+D6</f>
@@ -48625,7 +48707,7 @@
       <c r="R6" s="26"/>
       <c r="S6" s="20">
         <f>'Apps &amp; Goals 26-27'!F4</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T6" s="20">
         <f>'Apps &amp; Goals 26-27'!G4</f>
@@ -48637,7 +48719,7 @@
       </c>
       <c r="V6" s="26">
         <f>S6+O6</f>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W6" s="26">
         <f>T6+P6</f>
@@ -49164,7 +49246,7 @@
       <c r="F9" s="25"/>
       <c r="G9" s="21">
         <f>'Apps &amp; Goals 26-27'!C7</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H9" s="21">
         <f>'Apps &amp; Goals 26-27'!D7</f>
@@ -49176,7 +49258,7 @@
       </c>
       <c r="J9" s="25">
         <f t="shared" si="0"/>
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K9" s="25">
         <f t="shared" si="1"/>
@@ -49204,7 +49286,7 @@
       <c r="R9" s="26"/>
       <c r="S9" s="20">
         <f>'Apps &amp; Goals 26-27'!F7</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T9" s="20">
         <f>'Apps &amp; Goals 26-27'!G7</f>
@@ -49216,7 +49298,7 @@
       </c>
       <c r="V9" s="26">
         <f t="shared" si="3"/>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="W9" s="26">
         <f t="shared" si="4"/>
@@ -49550,7 +49632,7 @@
       <c r="F11" s="25"/>
       <c r="G11" s="21">
         <f>'Apps &amp; Goals 26-27'!C9</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H11" s="21">
         <f>'Apps &amp; Goals 26-27'!D9</f>
@@ -49562,7 +49644,7 @@
       </c>
       <c r="J11" s="25">
         <f t="shared" si="0"/>
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K11" s="25">
         <f t="shared" si="1"/>
@@ -49590,7 +49672,7 @@
       <c r="R11" s="26"/>
       <c r="S11" s="20">
         <f>'Apps &amp; Goals 26-27'!F9</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T11" s="20">
         <f>'Apps &amp; Goals 26-27'!G9</f>
@@ -49602,7 +49684,7 @@
       </c>
       <c r="V11" s="26">
         <f t="shared" si="3"/>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="W11" s="26">
         <f t="shared" si="4"/>
@@ -49743,7 +49825,7 @@
       <c r="F12" s="25"/>
       <c r="G12" s="21">
         <f>'Apps &amp; Goals 26-27'!C10</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H12" s="21">
         <f>'Apps &amp; Goals 26-27'!D10</f>
@@ -49755,7 +49837,7 @@
       </c>
       <c r="J12" s="25">
         <f t="shared" si="0"/>
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K12" s="25">
         <f t="shared" si="1"/>
@@ -49783,27 +49865,27 @@
       <c r="R12" s="26"/>
       <c r="S12" s="20">
         <f>'Apps &amp; Goals 26-27'!F10</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T12" s="20">
         <f>'Apps &amp; Goals 26-27'!G10</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U12" s="20">
         <f>'Apps &amp; Goals 26-27'!H10</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12" s="26">
         <f t="shared" si="3"/>
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="W12" s="26">
         <f t="shared" si="4"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="X12" s="26">
         <f t="shared" si="5"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z12" s="57" t="s">
         <v>180</v>
@@ -49936,7 +50018,7 @@
       <c r="F13" s="25"/>
       <c r="G13" s="21">
         <f>'Apps &amp; Goals 26-27'!C11</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H13" s="21">
         <f>'Apps &amp; Goals 26-27'!D11</f>
@@ -49948,7 +50030,7 @@
       </c>
       <c r="J13" s="25">
         <f t="shared" si="0"/>
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K13" s="25">
         <f t="shared" si="1"/>
@@ -49976,7 +50058,7 @@
       <c r="R13" s="26"/>
       <c r="S13" s="20">
         <f>'Apps &amp; Goals 26-27'!F11</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T13" s="20">
         <f>'Apps &amp; Goals 26-27'!G11</f>
@@ -49988,7 +50070,7 @@
       </c>
       <c r="V13" s="26">
         <f t="shared" si="3"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="W13" s="26">
         <f t="shared" si="4"/>
@@ -50129,7 +50211,7 @@
       <c r="F14" s="25"/>
       <c r="G14" s="21">
         <f>'Apps &amp; Goals 26-27'!C12</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H14" s="21">
         <f>'Apps &amp; Goals 26-27'!D12</f>
@@ -50141,7 +50223,7 @@
       </c>
       <c r="J14" s="25">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K14" s="25">
         <f t="shared" si="1"/>
@@ -50169,11 +50251,11 @@
       <c r="R14" s="26"/>
       <c r="S14" s="20">
         <f>'Apps &amp; Goals 26-27'!F12</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T14" s="20">
         <f>'Apps &amp; Goals 26-27'!G12</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U14" s="20">
         <f>'Apps &amp; Goals 26-27'!H12</f>
@@ -50181,11 +50263,11 @@
       </c>
       <c r="V14" s="26">
         <f t="shared" si="3"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="W14" s="26">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X14" s="26">
         <f t="shared" si="5"/>
@@ -50322,7 +50404,7 @@
       <c r="F15" s="25"/>
       <c r="G15" s="21">
         <f>'Apps &amp; Goals 26-27'!C13</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H15" s="21">
         <f>'Apps &amp; Goals 26-27'!D13</f>
@@ -50334,7 +50416,7 @@
       </c>
       <c r="J15" s="25">
         <f t="shared" si="0"/>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K15" s="25">
         <f t="shared" si="1"/>
@@ -50362,11 +50444,11 @@
       <c r="R15" s="26"/>
       <c r="S15" s="20">
         <f>'Apps &amp; Goals 26-27'!F13</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T15" s="20">
         <f>'Apps &amp; Goals 26-27'!G13</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U15" s="20">
         <f>'Apps &amp; Goals 26-27'!H13</f>
@@ -50374,11 +50456,11 @@
       </c>
       <c r="V15" s="26">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="W15" s="26">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X15" s="26">
         <f t="shared" si="5"/>
@@ -50708,7 +50790,7 @@
       <c r="F17" s="25"/>
       <c r="G17" s="21">
         <f>'Apps &amp; Goals 26-27'!C15</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H17" s="21">
         <f>'Apps &amp; Goals 26-27'!D15</f>
@@ -50720,7 +50802,7 @@
       </c>
       <c r="J17" s="25">
         <f t="shared" si="0"/>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K17" s="25">
         <f t="shared" si="1"/>
@@ -50748,7 +50830,7 @@
       <c r="R17" s="26"/>
       <c r="S17" s="20">
         <f>'Apps &amp; Goals 26-27'!F15</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T17" s="20">
         <f>'Apps &amp; Goals 26-27'!G15</f>
@@ -50760,7 +50842,7 @@
       </c>
       <c r="V17" s="26">
         <f t="shared" si="3"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="W17" s="26">
         <f t="shared" si="4"/>
@@ -50901,7 +50983,7 @@
       <c r="F18" s="25"/>
       <c r="G18" s="21">
         <f>'Apps &amp; Goals 26-27'!C16</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H18" s="21">
         <f>'Apps &amp; Goals 26-27'!D16</f>
@@ -50913,7 +50995,7 @@
       </c>
       <c r="J18" s="25">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K18" s="25">
         <f t="shared" si="1"/>
@@ -50941,7 +51023,7 @@
       <c r="R18" s="26"/>
       <c r="S18" s="20">
         <f>'Apps &amp; Goals 26-27'!F16</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T18" s="20">
         <f>'Apps &amp; Goals 26-27'!G16</f>
@@ -50953,7 +51035,7 @@
       </c>
       <c r="V18" s="26">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W18" s="26">
         <f t="shared" si="4"/>
@@ -51287,11 +51369,11 @@
       <c r="F20" s="25"/>
       <c r="G20" s="21">
         <f>'Apps &amp; Goals 26-27'!C18</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H20" s="21">
         <f>'Apps &amp; Goals 26-27'!D18</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" s="21">
         <f>'Apps &amp; Goals 26-27'!E18</f>
@@ -51299,11 +51381,11 @@
       </c>
       <c r="J20" s="25">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K20" s="25">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L20" s="25">
         <f t="shared" si="2"/>
@@ -51327,7 +51409,7 @@
       <c r="R20" s="26"/>
       <c r="S20" s="20">
         <f>'Apps &amp; Goals 26-27'!F18</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T20" s="20">
         <f>'Apps &amp; Goals 26-27'!G18</f>
@@ -51335,11 +51417,11 @@
       </c>
       <c r="U20" s="20">
         <f>'Apps &amp; Goals 26-27'!H18</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="26">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W20" s="26">
         <f t="shared" si="4"/>
@@ -51347,7 +51429,7 @@
       </c>
       <c r="X20" s="26">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z20" s="23" t="s">
         <v>315</v>
@@ -51673,7 +51755,7 @@
       <c r="F22" s="25"/>
       <c r="G22" s="21">
         <f>'Apps &amp; Goals 26-27'!C20</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H22" s="21">
         <f>'Apps &amp; Goals 26-27'!D20</f>
@@ -51685,7 +51767,7 @@
       </c>
       <c r="J22" s="25">
         <f t="shared" si="0"/>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K22" s="25">
         <f t="shared" si="1"/>
@@ -51713,7 +51795,7 @@
       <c r="R22" s="26"/>
       <c r="S22" s="20">
         <f>'Apps &amp; Goals 26-27'!F20</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T22" s="20">
         <f>'Apps &amp; Goals 26-27'!G20</f>
@@ -51725,7 +51807,7 @@
       </c>
       <c r="V22" s="26">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W22" s="26">
         <f t="shared" si="4"/>
@@ -51866,7 +51948,7 @@
       <c r="F23" s="25"/>
       <c r="G23" s="21">
         <f>'Apps &amp; Goals 26-27'!C21</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H23" s="21">
         <f>'Apps &amp; Goals 26-27'!D21</f>
@@ -51878,7 +51960,7 @@
       </c>
       <c r="J23" s="25">
         <f t="shared" si="0"/>
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K23" s="25">
         <f t="shared" si="1"/>
@@ -51906,7 +51988,7 @@
       <c r="R23" s="26"/>
       <c r="S23" s="20">
         <f>'Apps &amp; Goals 26-27'!F21</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T23" s="20">
         <f>'Apps &amp; Goals 26-27'!G21</f>
@@ -51914,11 +51996,11 @@
       </c>
       <c r="U23" s="20">
         <f>'Apps &amp; Goals 26-27'!H21</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="26">
         <f t="shared" si="3"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W23" s="26">
         <f t="shared" si="4"/>
@@ -51926,7 +52008,7 @@
       </c>
       <c r="X23" s="26">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z23" s="57" t="s">
         <v>275</v>
@@ -52252,7 +52334,7 @@
       <c r="F25" s="25"/>
       <c r="G25" s="21">
         <f>'Apps &amp; Goals 26-27'!C23</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H25" s="21">
         <f>'Apps &amp; Goals 26-27'!D23</f>
@@ -52264,7 +52346,7 @@
       </c>
       <c r="J25" s="25">
         <f t="shared" si="0"/>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K25" s="25">
         <f t="shared" si="1"/>
@@ -52831,7 +52913,7 @@
       <c r="F28" s="25"/>
       <c r="G28" s="21">
         <f>'Apps &amp; Goals 26-27'!C26</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H28" s="21">
         <f>'Apps &amp; Goals 26-27'!D26</f>
@@ -52843,7 +52925,7 @@
       </c>
       <c r="J28" s="25">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K28" s="25">
         <f t="shared" si="1"/>
@@ -52871,7 +52953,7 @@
       <c r="R28" s="26"/>
       <c r="S28" s="20">
         <f>'Apps &amp; Goals 26-27'!F26</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T28" s="20">
         <f>'Apps &amp; Goals 26-27'!G26</f>
@@ -52883,7 +52965,7 @@
       </c>
       <c r="V28" s="26">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W28" s="26">
         <f t="shared" si="4"/>
@@ -53217,7 +53299,7 @@
       <c r="F30" s="25"/>
       <c r="G30" s="21">
         <f>'Apps &amp; Goals 26-27'!C28</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H30" s="21">
         <f>'Apps &amp; Goals 26-27'!D28</f>
@@ -53225,11 +53307,11 @@
       </c>
       <c r="I30" s="21">
         <f>'Apps &amp; Goals 26-27'!E28</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J30" s="25">
         <f t="shared" si="0"/>
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K30" s="25">
         <f t="shared" si="1"/>
@@ -53237,7 +53319,7 @@
       </c>
       <c r="L30" s="25">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M30">
         <v>41</v>
@@ -53257,7 +53339,7 @@
       <c r="R30" s="26"/>
       <c r="S30" s="20">
         <f>'Apps &amp; Goals 26-27'!F28</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T30" s="20">
         <f>'Apps &amp; Goals 26-27'!G28</f>
@@ -53269,7 +53351,7 @@
       </c>
       <c r="V30" s="26">
         <f t="shared" si="3"/>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W30" s="26">
         <f t="shared" si="4"/>
@@ -54222,7 +54304,7 @@
       <c r="R35" s="26"/>
       <c r="S35" s="20">
         <f>'Apps &amp; Goals 26-27'!F33</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T35" s="20">
         <f>'Apps &amp; Goals 26-27'!G33</f>
@@ -54234,7 +54316,7 @@
       </c>
       <c r="V35" s="26">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W35" s="26">
         <f t="shared" si="4"/>
@@ -54801,7 +54883,7 @@
       <c r="R38" s="26"/>
       <c r="S38" s="20">
         <f>'Apps &amp; Goals 26-27'!F36</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T38" s="20">
         <f>'Apps &amp; Goals 26-27'!G36</f>
@@ -54813,7 +54895,7 @@
       </c>
       <c r="V38" s="26">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W38" s="26">
         <f t="shared" si="4"/>
@@ -55352,72 +55434,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C1" s="237" t="s">
+      <c r="C1" s="233" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="237" t="s">
+      <c r="D1" s="233" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="237" t="s">
+      <c r="E1" s="233" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="267" t="s">
+      <c r="F1" s="273" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="268"/>
-      <c r="H1" s="269"/>
-      <c r="I1" s="270" t="s">
+      <c r="G1" s="274"/>
+      <c r="H1" s="275"/>
+      <c r="I1" s="276" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="271"/>
-      <c r="K1" s="272"/>
-      <c r="L1" s="274" t="s">
+      <c r="J1" s="277"/>
+      <c r="K1" s="278"/>
+      <c r="L1" s="243" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="275"/>
-      <c r="N1" s="276"/>
-      <c r="O1" s="277" t="s">
+      <c r="M1" s="244"/>
+      <c r="N1" s="245"/>
+      <c r="O1" s="246" t="s">
         <v>199</v>
       </c>
-      <c r="P1" s="278"/>
-      <c r="Q1" s="279"/>
-      <c r="R1" s="243" t="s">
+      <c r="P1" s="247"/>
+      <c r="Q1" s="248"/>
+      <c r="R1" s="249" t="s">
         <v>200</v>
       </c>
-      <c r="S1" s="244"/>
-      <c r="T1" s="245"/>
-      <c r="U1" s="246" t="s">
+      <c r="S1" s="250"/>
+      <c r="T1" s="251"/>
+      <c r="U1" s="252" t="s">
         <v>306</v>
       </c>
-      <c r="V1" s="247"/>
-      <c r="W1" s="248"/>
+      <c r="V1" s="253"/>
+      <c r="W1" s="254"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="238"/>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="249" t="s">
+      <c r="C2" s="234"/>
+      <c r="D2" s="234"/>
+      <c r="E2" s="234"/>
+      <c r="F2" s="255" t="s">
         <v>432</v>
       </c>
-      <c r="G2" s="250"/>
-      <c r="H2" s="251"/>
-      <c r="I2" s="264"/>
-      <c r="J2" s="265"/>
-      <c r="K2" s="266"/>
-      <c r="L2" s="261"/>
-      <c r="M2" s="262"/>
-      <c r="N2" s="263"/>
-      <c r="O2" s="258"/>
-      <c r="P2" s="259"/>
-      <c r="Q2" s="260"/>
-      <c r="R2" s="255"/>
-      <c r="S2" s="256"/>
-      <c r="T2" s="257"/>
-      <c r="U2" s="252"/>
-      <c r="V2" s="253"/>
-      <c r="W2" s="254"/>
+      <c r="G2" s="256"/>
+      <c r="H2" s="257"/>
+      <c r="I2" s="270"/>
+      <c r="J2" s="271"/>
+      <c r="K2" s="272"/>
+      <c r="L2" s="267"/>
+      <c r="M2" s="268"/>
+      <c r="N2" s="269"/>
+      <c r="O2" s="264"/>
+      <c r="P2" s="265"/>
+      <c r="Q2" s="266"/>
+      <c r="R2" s="261"/>
+      <c r="S2" s="262"/>
+      <c r="T2" s="263"/>
+      <c r="U2" s="258"/>
+      <c r="V2" s="259"/>
+      <c r="W2" s="260"/>
     </row>
     <row r="3" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -55426,9 +55508,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="273"/>
-      <c r="D3" s="273"/>
-      <c r="E3" s="273"/>
+      <c r="C3" s="242"/>
+      <c r="D3" s="242"/>
+      <c r="E3" s="242"/>
       <c r="F3" s="188" t="s">
         <v>393</v>
       </c>
@@ -56932,6 +57014,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="F2:H2"/>
@@ -56942,11 +57029,6 @@
     <mergeCell ref="U2:W2"/>
     <mergeCell ref="L1:N1"/>
     <mergeCell ref="O1:Q1"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:W32">
     <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
@@ -56974,11 +57056,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C1" s="280" t="s">
+      <c r="C1" s="279" t="s">
         <v>340</v>
       </c>
-      <c r="D1" s="281"/>
-      <c r="E1" s="281"/>
+      <c r="D1" s="280"/>
+      <c r="E1" s="280"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -57453,51 +57535,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="282" t="s">
+      <c r="C1" s="301" t="s">
         <v>202</v>
       </c>
-      <c r="D1" s="283"/>
-      <c r="E1" s="283"/>
-      <c r="F1" s="283"/>
-      <c r="G1" s="283"/>
-      <c r="H1" s="283"/>
-      <c r="I1" s="284"/>
+      <c r="D1" s="302"/>
+      <c r="E1" s="302"/>
+      <c r="F1" s="302"/>
+      <c r="G1" s="302"/>
+      <c r="H1" s="302"/>
+      <c r="I1" s="303"/>
       <c r="J1" s="114" t="s">
         <v>195</v>
       </c>
       <c r="K1" s="115" t="s">
         <v>194</v>
       </c>
-      <c r="L1" s="306" t="s">
+      <c r="L1" s="282" t="s">
         <v>287</v>
       </c>
-      <c r="M1" s="311"/>
-      <c r="N1" s="311"/>
-      <c r="O1" s="311"/>
-      <c r="P1" s="311"/>
-      <c r="Q1" s="311"/>
-      <c r="R1" s="311"/>
-      <c r="S1" s="311"/>
-      <c r="T1" s="311"/>
-      <c r="U1" s="311"/>
-      <c r="V1" s="311"/>
-      <c r="W1" s="311"/>
-      <c r="X1" s="311"/>
-      <c r="Y1" s="311"/>
-      <c r="Z1" s="311"/>
-      <c r="AA1" s="311"/>
-      <c r="AB1" s="311"/>
-      <c r="AC1" s="311"/>
-      <c r="AD1" s="311"/>
-      <c r="AE1" s="311"/>
-      <c r="AF1" s="311"/>
-      <c r="AG1" s="312"/>
-      <c r="AH1" s="306" t="s">
+      <c r="M1" s="287"/>
+      <c r="N1" s="287"/>
+      <c r="O1" s="287"/>
+      <c r="P1" s="287"/>
+      <c r="Q1" s="287"/>
+      <c r="R1" s="287"/>
+      <c r="S1" s="287"/>
+      <c r="T1" s="287"/>
+      <c r="U1" s="287"/>
+      <c r="V1" s="287"/>
+      <c r="W1" s="287"/>
+      <c r="X1" s="287"/>
+      <c r="Y1" s="287"/>
+      <c r="Z1" s="287"/>
+      <c r="AA1" s="287"/>
+      <c r="AB1" s="287"/>
+      <c r="AC1" s="287"/>
+      <c r="AD1" s="287"/>
+      <c r="AE1" s="287"/>
+      <c r="AF1" s="287"/>
+      <c r="AG1" s="288"/>
+      <c r="AH1" s="282" t="s">
         <v>175</v>
       </c>
-      <c r="AI1" s="307"/>
-      <c r="AJ1" s="307"/>
-      <c r="AK1" s="308"/>
+      <c r="AI1" s="283"/>
+      <c r="AJ1" s="283"/>
+      <c r="AK1" s="284"/>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B2" s="111"/>
@@ -58180,13 +58262,13 @@
     <row r="8" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A8" s="71">
         <f t="shared" si="0"/>
-        <v>1.8235294117647058</v>
+        <v>1.8571428571428572</v>
       </c>
       <c r="B8" s="110">
         <v>6</v>
       </c>
-      <c r="C8" s="123" t="s">
-        <v>181</v>
+      <c r="C8" s="123">
+        <v>3</v>
       </c>
       <c r="D8" s="123">
         <v>3</v>
@@ -58294,13 +58376,13 @@
     <row r="9" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A9" s="71">
         <f t="shared" si="0"/>
-        <v>2.2647058823529411</v>
+        <v>2.2857142857142856</v>
       </c>
       <c r="B9" s="110">
         <v>7</v>
       </c>
-      <c r="C9" s="123" t="s">
-        <v>181</v>
+      <c r="C9" s="123">
+        <v>3</v>
       </c>
       <c r="D9" s="123">
         <v>3</v>
@@ -62697,15 +62779,15 @@
         <f t="shared" ref="J80:J111" si="2">H80-I80</f>
         <v>2</v>
       </c>
-      <c r="K80" s="313" t="s">
+      <c r="K80" s="289" t="s">
         <v>434</v>
       </c>
-      <c r="L80" s="314"/>
-      <c r="M80" s="315"/>
+      <c r="L80" s="290"/>
+      <c r="M80" s="291"/>
       <c r="O80" s="133"/>
       <c r="P80" s="133"/>
-      <c r="W80" s="309"/>
-      <c r="X80" s="309"/>
+      <c r="W80" s="285"/>
+      <c r="X80" s="285"/>
       <c r="Y80" s="70" t="s">
         <v>211</v>
       </c>
@@ -62755,15 +62837,15 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K81" s="316"/>
-      <c r="L81" s="317"/>
-      <c r="M81" s="318"/>
+      <c r="K81" s="292"/>
+      <c r="L81" s="293"/>
+      <c r="M81" s="294"/>
       <c r="O81" s="133"/>
       <c r="P81" s="133"/>
-      <c r="W81" s="309" t="s">
+      <c r="W81" s="285" t="s">
         <v>209</v>
       </c>
-      <c r="X81" s="309"/>
+      <c r="X81" s="285"/>
       <c r="Y81" s="70">
         <f>COUNTIF(L3:AG40,3)</f>
         <v>481</v>
@@ -62819,17 +62901,17 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K82" s="319" t="s">
+      <c r="K82" s="295" t="s">
         <v>435</v>
       </c>
-      <c r="L82" s="320"/>
-      <c r="M82" s="321"/>
+      <c r="L82" s="296"/>
+      <c r="M82" s="297"/>
       <c r="O82" s="133"/>
       <c r="P82" s="133"/>
-      <c r="W82" s="309" t="s">
+      <c r="W82" s="285" t="s">
         <v>210</v>
       </c>
-      <c r="X82" s="309"/>
+      <c r="X82" s="285"/>
       <c r="Y82" s="70">
         <f>COUNTIF(K3:K40,3)+COUNTIF(J3:J15,3)</f>
         <v>25</v>
@@ -62885,17 +62967,17 @@
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="K83" s="322" t="s">
+      <c r="K83" s="298" t="s">
         <v>436</v>
       </c>
-      <c r="L83" s="323"/>
-      <c r="M83" s="324"/>
+      <c r="L83" s="299"/>
+      <c r="M83" s="300"/>
       <c r="O83" s="133"/>
       <c r="P83" s="133"/>
-      <c r="W83" s="310" t="s">
+      <c r="W83" s="286" t="s">
         <v>97</v>
       </c>
-      <c r="X83" s="310"/>
+      <c r="X83" s="286"/>
       <c r="Y83" s="194">
         <v>224</v>
       </c>
@@ -62948,15 +63030,15 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="K84" s="288" t="s">
+      <c r="K84" s="307" t="s">
         <v>284</v>
       </c>
-      <c r="L84" s="289"/>
-      <c r="M84" s="290"/>
+      <c r="L84" s="308"/>
+      <c r="M84" s="309"/>
       <c r="O84" s="141"/>
       <c r="P84" s="141"/>
-      <c r="W84" s="325"/>
-      <c r="X84" s="325"/>
+      <c r="W84" s="281"/>
+      <c r="X84" s="281"/>
       <c r="Y84" s="196"/>
       <c r="Z84" s="196"/>
       <c r="AA84" s="196"/>
@@ -62994,9 +63076,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K85" s="291"/>
-      <c r="L85" s="292"/>
-      <c r="M85" s="293"/>
+      <c r="K85" s="310"/>
+      <c r="L85" s="311"/>
+      <c r="M85" s="312"/>
       <c r="O85" s="141"/>
       <c r="P85" s="141"/>
     </row>
@@ -63030,9 +63112,9 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="K86" s="291"/>
-      <c r="L86" s="292"/>
-      <c r="M86" s="293"/>
+      <c r="K86" s="310"/>
+      <c r="L86" s="311"/>
+      <c r="M86" s="312"/>
       <c r="O86" s="141"/>
       <c r="P86" s="141"/>
     </row>
@@ -63066,9 +63148,9 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="K87" s="291"/>
-      <c r="L87" s="292"/>
-      <c r="M87" s="293"/>
+      <c r="K87" s="310"/>
+      <c r="L87" s="311"/>
+      <c r="M87" s="312"/>
       <c r="O87" s="141"/>
       <c r="P87" s="141"/>
     </row>
@@ -63102,9 +63184,9 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K88" s="291"/>
-      <c r="L88" s="292"/>
-      <c r="M88" s="293"/>
+      <c r="K88" s="310"/>
+      <c r="L88" s="311"/>
+      <c r="M88" s="312"/>
       <c r="O88" s="141"/>
       <c r="P88" s="141"/>
     </row>
@@ -63138,9 +63220,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K89" s="291"/>
-      <c r="L89" s="292"/>
-      <c r="M89" s="293"/>
+      <c r="K89" s="310"/>
+      <c r="L89" s="311"/>
+      <c r="M89" s="312"/>
       <c r="O89" s="141"/>
       <c r="P89" s="141"/>
     </row>
@@ -63174,9 +63256,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K90" s="291"/>
-      <c r="L90" s="292"/>
-      <c r="M90" s="293"/>
+      <c r="K90" s="310"/>
+      <c r="L90" s="311"/>
+      <c r="M90" s="312"/>
       <c r="O90" s="141"/>
       <c r="P90" s="141"/>
     </row>
@@ -63210,9 +63292,9 @@
         <f t="shared" si="2"/>
         <v>47</v>
       </c>
-      <c r="K91" s="291"/>
-      <c r="L91" s="292"/>
-      <c r="M91" s="293"/>
+      <c r="K91" s="310"/>
+      <c r="L91" s="311"/>
+      <c r="M91" s="312"/>
       <c r="O91" s="141"/>
       <c r="P91" s="141"/>
     </row>
@@ -63246,9 +63328,9 @@
         <f t="shared" si="2"/>
         <v>51</v>
       </c>
-      <c r="K92" s="291"/>
-      <c r="L92" s="292"/>
-      <c r="M92" s="293"/>
+      <c r="K92" s="310"/>
+      <c r="L92" s="311"/>
+      <c r="M92" s="312"/>
       <c r="O92" s="141"/>
       <c r="P92" s="141"/>
     </row>
@@ -63282,9 +63364,9 @@
         <f t="shared" si="2"/>
         <v>37</v>
       </c>
-      <c r="K93" s="291"/>
-      <c r="L93" s="292"/>
-      <c r="M93" s="293"/>
+      <c r="K93" s="310"/>
+      <c r="L93" s="311"/>
+      <c r="M93" s="312"/>
       <c r="O93" s="141"/>
       <c r="P93" s="141"/>
     </row>
@@ -63318,9 +63400,9 @@
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="K94" s="291"/>
-      <c r="L94" s="292"/>
-      <c r="M94" s="293"/>
+      <c r="K94" s="310"/>
+      <c r="L94" s="311"/>
+      <c r="M94" s="312"/>
       <c r="O94" s="141"/>
       <c r="P94" s="141"/>
     </row>
@@ -63354,9 +63436,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K95" s="291"/>
-      <c r="L95" s="292"/>
-      <c r="M95" s="293"/>
+      <c r="K95" s="310"/>
+      <c r="L95" s="311"/>
+      <c r="M95" s="312"/>
       <c r="O95" s="141"/>
       <c r="P95" s="141"/>
     </row>
@@ -63390,9 +63472,9 @@
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="K96" s="291"/>
-      <c r="L96" s="292"/>
-      <c r="M96" s="293"/>
+      <c r="K96" s="310"/>
+      <c r="L96" s="311"/>
+      <c r="M96" s="312"/>
       <c r="O96" s="141"/>
       <c r="P96" s="141"/>
     </row>
@@ -63426,9 +63508,9 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="K97" s="291"/>
-      <c r="L97" s="292"/>
-      <c r="M97" s="293"/>
+      <c r="K97" s="310"/>
+      <c r="L97" s="311"/>
+      <c r="M97" s="312"/>
       <c r="O97" s="141"/>
       <c r="P97" s="141"/>
     </row>
@@ -63462,9 +63544,9 @@
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="K98" s="291"/>
-      <c r="L98" s="292"/>
-      <c r="M98" s="293"/>
+      <c r="K98" s="310"/>
+      <c r="L98" s="311"/>
+      <c r="M98" s="312"/>
       <c r="O98" s="141"/>
       <c r="P98" s="141"/>
     </row>
@@ -63498,9 +63580,9 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K99" s="291"/>
-      <c r="L99" s="292"/>
-      <c r="M99" s="293"/>
+      <c r="K99" s="310"/>
+      <c r="L99" s="311"/>
+      <c r="M99" s="312"/>
       <c r="O99" s="141"/>
       <c r="P99" s="141"/>
     </row>
@@ -63534,9 +63616,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K100" s="291"/>
-      <c r="L100" s="292"/>
-      <c r="M100" s="293"/>
+      <c r="K100" s="310"/>
+      <c r="L100" s="311"/>
+      <c r="M100" s="312"/>
       <c r="O100" s="141"/>
       <c r="P100" s="141"/>
     </row>
@@ -63570,9 +63652,9 @@
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="K101" s="291"/>
-      <c r="L101" s="292"/>
-      <c r="M101" s="293"/>
+      <c r="K101" s="310"/>
+      <c r="L101" s="311"/>
+      <c r="M101" s="312"/>
       <c r="O101" s="141"/>
       <c r="P101" s="141"/>
     </row>
@@ -63606,9 +63688,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K102" s="291"/>
-      <c r="L102" s="292"/>
-      <c r="M102" s="293"/>
+      <c r="K102" s="310"/>
+      <c r="L102" s="311"/>
+      <c r="M102" s="312"/>
       <c r="O102" s="141"/>
       <c r="P102" s="141"/>
     </row>
@@ -63642,9 +63724,9 @@
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="K103" s="291"/>
-      <c r="L103" s="292"/>
-      <c r="M103" s="293"/>
+      <c r="K103" s="310"/>
+      <c r="L103" s="311"/>
+      <c r="M103" s="312"/>
       <c r="O103" s="141"/>
       <c r="P103" s="141"/>
     </row>
@@ -63678,9 +63760,9 @@
         <f t="shared" si="2"/>
         <v>33</v>
       </c>
-      <c r="K104" s="291"/>
-      <c r="L104" s="292"/>
-      <c r="M104" s="293"/>
+      <c r="K104" s="310"/>
+      <c r="L104" s="311"/>
+      <c r="M104" s="312"/>
       <c r="O104" s="141"/>
       <c r="P104" s="141"/>
     </row>
@@ -63714,9 +63796,9 @@
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="K105" s="294"/>
-      <c r="L105" s="295"/>
-      <c r="M105" s="296"/>
+      <c r="K105" s="313"/>
+      <c r="L105" s="314"/>
+      <c r="M105" s="315"/>
       <c r="O105" s="141"/>
       <c r="P105" s="141"/>
     </row>
@@ -63750,11 +63832,11 @@
         <f t="shared" si="2"/>
         <v>21</v>
       </c>
-      <c r="K106" s="285" t="s">
+      <c r="K106" s="304" t="s">
         <v>286</v>
       </c>
-      <c r="L106" s="286"/>
-      <c r="M106" s="287"/>
+      <c r="L106" s="305"/>
+      <c r="M106" s="306"/>
       <c r="O106" s="126"/>
       <c r="P106" s="126"/>
     </row>
@@ -63788,11 +63870,11 @@
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="K107" s="285" t="s">
+      <c r="K107" s="304" t="s">
         <v>288</v>
       </c>
-      <c r="L107" s="286"/>
-      <c r="M107" s="287"/>
+      <c r="L107" s="305"/>
+      <c r="M107" s="306"/>
       <c r="O107" s="126"/>
       <c r="P107" s="126"/>
     </row>
@@ -63826,11 +63908,11 @@
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="K108" s="297" t="s">
+      <c r="K108" s="316" t="s">
         <v>289</v>
       </c>
-      <c r="L108" s="298"/>
-      <c r="M108" s="299"/>
+      <c r="L108" s="317"/>
+      <c r="M108" s="318"/>
       <c r="O108" s="126"/>
       <c r="P108" s="126"/>
     </row>
@@ -63864,9 +63946,9 @@
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="K109" s="300"/>
-      <c r="L109" s="301"/>
-      <c r="M109" s="302"/>
+      <c r="K109" s="319"/>
+      <c r="L109" s="320"/>
+      <c r="M109" s="321"/>
       <c r="O109" s="126"/>
       <c r="P109" s="126"/>
     </row>
@@ -63900,9 +63982,9 @@
         <f t="shared" si="2"/>
         <v>45</v>
       </c>
-      <c r="K110" s="300"/>
-      <c r="L110" s="301"/>
-      <c r="M110" s="302"/>
+      <c r="K110" s="319"/>
+      <c r="L110" s="320"/>
+      <c r="M110" s="321"/>
       <c r="O110" s="126"/>
       <c r="P110" s="126"/>
     </row>
@@ -63936,9 +64018,9 @@
         <f t="shared" si="2"/>
         <v>62</v>
       </c>
-      <c r="K111" s="300"/>
-      <c r="L111" s="301"/>
-      <c r="M111" s="302"/>
+      <c r="K111" s="319"/>
+      <c r="L111" s="320"/>
+      <c r="M111" s="321"/>
       <c r="O111" s="126"/>
       <c r="P111" s="126"/>
     </row>
@@ -63976,9 +64058,9 @@
         <f t="shared" ref="J112:J114" si="6">H112-I112</f>
         <v>34</v>
       </c>
-      <c r="K112" s="300"/>
-      <c r="L112" s="301"/>
-      <c r="M112" s="302"/>
+      <c r="K112" s="319"/>
+      <c r="L112" s="320"/>
+      <c r="M112" s="321"/>
     </row>
     <row r="113" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="156" t="s">
@@ -64014,9 +64096,9 @@
         <f t="shared" si="6"/>
         <v>43</v>
       </c>
-      <c r="K113" s="300"/>
-      <c r="L113" s="301"/>
-      <c r="M113" s="302"/>
+      <c r="K113" s="319"/>
+      <c r="L113" s="320"/>
+      <c r="M113" s="321"/>
     </row>
     <row r="114" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="93" t="s">
@@ -64026,11 +64108,11 @@
       <c r="C114" s="122"/>
       <c r="D114" s="122">
         <f>SUM(E114*3+F114)</f>
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E114" s="122">
         <f>COUNTIF(C3:C41,3)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F114" s="122">
         <f>COUNTIF(C3:C41,1)</f>
@@ -64052,13 +64134,18 @@
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="K114" s="303"/>
-      <c r="L114" s="304"/>
-      <c r="M114" s="305"/>
+      <c r="K114" s="322"/>
+      <c r="L114" s="323"/>
+      <c r="M114" s="324"/>
     </row>
   </sheetData>
   <autoFilter ref="A79:J112" xr:uid="{9C81160F-C24B-449F-8F5A-CB622AB71070}"/>
   <mergeCells count="15">
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="K106:M106"/>
+    <mergeCell ref="K107:M107"/>
+    <mergeCell ref="K84:M105"/>
+    <mergeCell ref="K108:M114"/>
     <mergeCell ref="W84:X84"/>
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="W80:X80"/>
@@ -64069,11 +64156,6 @@
     <mergeCell ref="K80:M81"/>
     <mergeCell ref="K82:M82"/>
     <mergeCell ref="K83:M83"/>
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="K106:M106"/>
-    <mergeCell ref="K107:M107"/>
-    <mergeCell ref="K84:M105"/>
-    <mergeCell ref="K108:M114"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <conditionalFormatting sqref="A3:A40">
@@ -64165,32 +64247,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="203" t="s">
+      <c r="A1" s="325" t="s">
         <v>405</v>
       </c>
-      <c r="B1" s="203"/>
-      <c r="C1" s="203"/>
-      <c r="D1" s="203"/>
-      <c r="E1" s="203"/>
-      <c r="F1" s="203" t="s">
+      <c r="B1" s="325"/>
+      <c r="C1" s="325"/>
+      <c r="D1" s="325"/>
+      <c r="E1" s="325"/>
+      <c r="F1" s="325" t="s">
         <v>406</v>
       </c>
-      <c r="G1" s="203"/>
-      <c r="H1" s="203"/>
-      <c r="I1" s="203"/>
-      <c r="J1" s="203"/>
+      <c r="G1" s="325"/>
+      <c r="H1" s="325"/>
+      <c r="I1" s="325"/>
+      <c r="J1" s="325"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2" s="203"/>
-      <c r="B2" s="203"/>
-      <c r="C2" s="203"/>
-      <c r="D2" s="203"/>
-      <c r="E2" s="203"/>
-      <c r="F2" s="203"/>
-      <c r="G2" s="203"/>
-      <c r="H2" s="203"/>
-      <c r="I2" s="203"/>
-      <c r="J2" s="203"/>
+      <c r="A2" s="325"/>
+      <c r="B2" s="325"/>
+      <c r="C2" s="325"/>
+      <c r="D2" s="325"/>
+      <c r="E2" s="325"/>
+      <c r="F2" s="325"/>
+      <c r="G2" s="325"/>
+      <c r="H2" s="325"/>
+      <c r="I2" s="325"/>
+      <c r="J2" s="325"/>
       <c r="L2" t="s">
         <v>409</v>
       </c>
@@ -64286,7 +64368,7 @@
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="B4" s="192">
         <v>0.875</v>
@@ -64295,25 +64377,25 @@
         <v>6</v>
       </c>
       <c r="D4" t="s">
+        <v>462</v>
+      </c>
+      <c r="E4" t="s">
         <v>488</v>
       </c>
-      <c r="E4" t="s">
-        <v>471</v>
-      </c>
       <c r="F4" t="s">
-        <v>470</v>
+        <v>483</v>
       </c>
       <c r="G4" s="202" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="H4" t="s">
         <v>4</v>
       </c>
       <c r="I4" t="s">
-        <v>424</v>
+        <v>485</v>
       </c>
       <c r="J4" t="s">
-        <v>471</v>
+        <v>486</v>
       </c>
       <c r="L4">
         <v>2</v>
@@ -64884,7 +64966,7 @@
         <v>10</v>
       </c>
       <c r="T21" s="193" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="U21" s="193">
         <v>3</v>
@@ -64916,7 +64998,7 @@
         <v>10</v>
       </c>
       <c r="T22" s="193" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="U22" s="193">
         <v>2</v>
@@ -64934,7 +65016,7 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44DFF815-59E5-49DB-A710-CC57B82C1BDD}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
@@ -64962,10 +65044,10 @@
         <v>350</v>
       </c>
       <c r="B2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C2" s="199">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="D2">
         <v>90</v>
@@ -64976,16 +65058,13 @@
         <v>440</v>
       </c>
       <c r="B3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C3" s="199">
-        <v>7.6</v>
-      </c>
-      <c r="D3" t="s">
-        <v>453</v>
-      </c>
-      <c r="E3" t="s">
-        <v>482</v>
+        <v>6.7</v>
+      </c>
+      <c r="D3">
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -64996,7 +65075,7 @@
         <v>450</v>
       </c>
       <c r="C4" s="199">
-        <v>6.3</v>
+        <v>8</v>
       </c>
       <c r="D4">
         <v>90</v>
@@ -65010,7 +65089,7 @@
         <v>455</v>
       </c>
       <c r="C5" s="199">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="D5">
         <v>90</v>
@@ -65021,16 +65100,13 @@
         <v>442</v>
       </c>
       <c r="B6" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="C6" s="199">
-        <v>7.7</v>
+        <v>6.7</v>
       </c>
       <c r="D6" t="s">
         <v>453</v>
-      </c>
-      <c r="E6" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -65038,16 +65114,16 @@
         <v>445</v>
       </c>
       <c r="B7" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C7" s="199">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="D7">
         <v>90</v>
       </c>
       <c r="E7" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -65055,10 +65131,10 @@
         <v>445</v>
       </c>
       <c r="B8" t="s">
-        <v>485</v>
+        <v>459</v>
       </c>
       <c r="C8" s="199">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="D8" t="s">
         <v>453</v>
@@ -65072,10 +65148,10 @@
         <v>451</v>
       </c>
       <c r="C9" s="199">
-        <v>7.1</v>
-      </c>
-      <c r="D9" t="s">
-        <v>453</v>
+        <v>7.5</v>
+      </c>
+      <c r="D9">
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -65083,13 +65159,13 @@
         <v>447</v>
       </c>
       <c r="B10" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="C10" s="199">
-        <v>8.1</v>
-      </c>
-      <c r="D10">
-        <v>90</v>
+        <v>6.4</v>
+      </c>
+      <c r="D10" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -65097,10 +65173,10 @@
         <v>448</v>
       </c>
       <c r="B11" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C11" s="199">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="D11">
         <v>90</v>
@@ -65111,10 +65187,10 @@
         <v>449</v>
       </c>
       <c r="B12" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C12" s="199">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="D12" t="s">
         <v>453</v>
@@ -65125,10 +65201,10 @@
         <v>442</v>
       </c>
       <c r="B13" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C13" s="199">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="D13" t="s">
         <v>452</v>
@@ -65139,16 +65215,13 @@
         <v>445</v>
       </c>
       <c r="B14" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="C14" s="199">
-        <v>8.1999999999999993</v>
+        <v>6.8</v>
       </c>
       <c r="D14" t="s">
         <v>452</v>
-      </c>
-      <c r="E14" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -65159,7 +65232,7 @@
         <v>469</v>
       </c>
       <c r="C15" s="199">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="D15" t="s">
         <v>452</v>
@@ -65167,30 +65240,19 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B16" t="s">
-        <v>454</v>
-      </c>
-      <c r="C16" s="199" t="s">
-        <v>166</v>
+        <v>481</v>
+      </c>
+      <c r="C16" s="199">
+        <v>6.8</v>
       </c>
       <c r="D16" t="s">
         <v>452</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>440</v>
-      </c>
-      <c r="B17" t="s">
-        <v>487</v>
-      </c>
-      <c r="C17" s="199" t="s">
-        <v>166</v>
-      </c>
-      <c r="D17" t="s">
-        <v>452</v>
+      <c r="E16" t="s">
+        <v>478</v>
       </c>
     </row>
   </sheetData>
@@ -65217,23 +65279,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="208" t="s">
+      <c r="A1" s="207" t="s">
         <v>46</v>
       </c>
       <c r="B1" s="326"/>
       <c r="C1" s="327" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="211"/>
+      <c r="D1" s="210"/>
       <c r="E1" s="328"/>
-      <c r="H1" s="208" t="s">
+      <c r="H1" s="207" t="s">
         <v>47</v>
       </c>
       <c r="I1" s="326"/>
       <c r="J1" s="327" t="s">
         <v>44</v>
       </c>
-      <c r="K1" s="211"/>
+      <c r="K1" s="210"/>
       <c r="L1" s="328"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -66210,15 +66272,15 @@
       </c>
       <c r="J30" s="11">
         <f>'Apps &amp; Goals'!U10</f>
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K30" s="9">
         <f>'Apps &amp; Goals'!T10</f>
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L30" s="14">
         <f>J30/K30</f>
-        <v>0.26250000000000001</v>
+        <v>0.2639751552795031</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
@@ -66322,9 +66384,9 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="212"/>
-      <c r="G1" s="212"/>
-      <c r="H1" s="212"/>
+      <c r="F1" s="211"/>
+      <c r="G1" s="211"/>
+      <c r="H1" s="211"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -66348,38 +66410,38 @@
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="5"/>
-      <c r="E2" s="208" t="s">
+      <c r="E2" s="207" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="209"/>
-      <c r="G2" s="210"/>
-      <c r="H2" s="213" t="s">
+      <c r="F2" s="208"/>
+      <c r="G2" s="209"/>
+      <c r="H2" s="212" t="s">
         <v>120</v>
       </c>
-      <c r="I2" s="214"/>
-      <c r="J2" s="215"/>
-      <c r="K2" s="208" t="s">
+      <c r="I2" s="213"/>
+      <c r="J2" s="214"/>
+      <c r="K2" s="207" t="s">
         <v>108</v>
       </c>
-      <c r="L2" s="209"/>
-      <c r="M2" s="210"/>
-      <c r="N2" s="213" t="s">
+      <c r="L2" s="208"/>
+      <c r="M2" s="209"/>
+      <c r="N2" s="212" t="s">
         <v>110</v>
       </c>
-      <c r="O2" s="214"/>
-      <c r="P2" s="215"/>
-      <c r="Q2" s="208" t="s">
+      <c r="O2" s="213"/>
+      <c r="P2" s="214"/>
+      <c r="Q2" s="207" t="s">
         <v>39</v>
       </c>
-      <c r="R2" s="209"/>
-      <c r="S2" s="210"/>
-      <c r="T2" s="211" t="s">
+      <c r="R2" s="208"/>
+      <c r="S2" s="209"/>
+      <c r="T2" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="U2" s="211"/>
-      <c r="V2" s="211"/>
+      <c r="U2" s="210"/>
+      <c r="V2" s="210"/>
       <c r="Z2" s="125">
-        <v>46307</v>
+        <v>46314</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
@@ -66464,7 +66526,7 @@
       </c>
       <c r="E4" s="6">
         <f>'#'!J6</f>
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F4" s="6">
         <f>'#'!K6</f>
@@ -66476,7 +66538,7 @@
       </c>
       <c r="H4" s="4">
         <f>'#'!V6</f>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I4" s="4">
         <f>'#'!W6</f>
@@ -66524,7 +66586,7 @@
       </c>
       <c r="T4" s="2">
         <f t="shared" ref="T4:V4" si="0">SUM(E4,H4,K4,N4,Q4)</f>
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="U4" s="2">
         <f t="shared" ref="U4" si="1">SUM(F4,I4,L4,O4,R4)</f>
@@ -66722,7 +66784,7 @@
       </c>
       <c r="E7" s="6">
         <f>'#'!J9</f>
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F7" s="6">
         <f>'#'!K9</f>
@@ -66734,7 +66796,7 @@
       </c>
       <c r="H7" s="4">
         <f>'#'!V9</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I7" s="4">
         <f>'#'!W9</f>
@@ -66782,7 +66844,7 @@
       </c>
       <c r="T7" s="2">
         <f t="shared" si="2"/>
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="U7" s="2">
         <f t="shared" si="3"/>
@@ -66894,7 +66956,7 @@
       </c>
       <c r="E9" s="6">
         <f>'#'!J11</f>
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F9" s="6">
         <f>'#'!K11</f>
@@ -66906,7 +66968,7 @@
       </c>
       <c r="H9" s="4">
         <f>'#'!V11</f>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I9" s="4">
         <f>'#'!W11</f>
@@ -66954,7 +67016,7 @@
       </c>
       <c r="T9" s="2">
         <f t="shared" si="2"/>
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="U9" s="2">
         <f t="shared" si="3"/>
@@ -66980,7 +67042,7 @@
       </c>
       <c r="E10" s="6">
         <f>'#'!J12</f>
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F10" s="6">
         <f>'#'!K12</f>
@@ -66992,15 +67054,15 @@
       </c>
       <c r="H10" s="4">
         <f>'#'!V12</f>
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I10" s="4">
         <f>'#'!W12</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J10" s="4">
         <f>'#'!X12</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K10" s="6">
         <f>'#'!AH12</f>
@@ -67040,15 +67102,15 @@
       </c>
       <c r="T10" s="2">
         <f t="shared" si="2"/>
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="U10" s="2">
         <f t="shared" si="3"/>
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V10" s="2">
         <f t="shared" si="4"/>
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
@@ -67066,7 +67128,7 @@
       </c>
       <c r="E11" s="6">
         <f>'#'!J13</f>
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F11" s="6">
         <f>'#'!K13</f>
@@ -67078,7 +67140,7 @@
       </c>
       <c r="H11" s="4">
         <f>'#'!V13</f>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I11" s="4">
         <f>'#'!W13</f>
@@ -67126,7 +67188,7 @@
       </c>
       <c r="T11" s="2">
         <f t="shared" si="2"/>
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="U11" s="2">
         <f t="shared" si="3"/>
@@ -67152,7 +67214,7 @@
       </c>
       <c r="E12" s="6">
         <f>'#'!J14</f>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F12" s="6">
         <f>'#'!K14</f>
@@ -67164,11 +67226,11 @@
       </c>
       <c r="H12" s="4">
         <f>'#'!V14</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I12" s="4">
         <f>'#'!W14</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J12" s="4">
         <f>'#'!X14</f>
@@ -67212,11 +67274,11 @@
       </c>
       <c r="T12" s="2">
         <f t="shared" si="2"/>
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="U12" s="2">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V12" s="2">
         <f t="shared" si="4"/>
@@ -67238,7 +67300,7 @@
       </c>
       <c r="E13" s="6">
         <f>'#'!J15</f>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F13" s="6">
         <f>'#'!K15</f>
@@ -67250,11 +67312,11 @@
       </c>
       <c r="H13" s="4">
         <f>'#'!V15</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I13" s="4">
         <f>'#'!W15</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J13" s="4">
         <f>'#'!X15</f>
@@ -67298,11 +67360,11 @@
       </c>
       <c r="T13" s="2">
         <f t="shared" si="2"/>
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="U13" s="2">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V13" s="2">
         <f t="shared" si="4"/>
@@ -67410,7 +67472,7 @@
       </c>
       <c r="E15" s="6">
         <f>'#'!J17</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F15" s="6">
         <f>'#'!K17</f>
@@ -67422,7 +67484,7 @@
       </c>
       <c r="H15" s="4">
         <f>'#'!V17</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I15" s="4">
         <f>'#'!W17</f>
@@ -67470,7 +67532,7 @@
       </c>
       <c r="T15" s="2">
         <f t="shared" si="2"/>
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="U15" s="2">
         <f t="shared" si="3"/>
@@ -67496,7 +67558,7 @@
       </c>
       <c r="E16" s="6">
         <f>'#'!J18</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F16" s="6">
         <f>'#'!K18</f>
@@ -67508,7 +67570,7 @@
       </c>
       <c r="H16" s="4">
         <f>'#'!V18</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16" s="4">
         <f>'#'!W18</f>
@@ -67556,7 +67618,7 @@
       </c>
       <c r="T16" s="2">
         <f t="shared" ref="T16:T28" si="5">SUM(E16,H16,K16,N16,Q16)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U16" s="2">
         <f t="shared" ref="U16:U28" si="6">SUM(F16,I16,L16,O16,R16)</f>
@@ -67668,11 +67730,11 @@
       </c>
       <c r="E18" s="6">
         <f>'#'!J20</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F18" s="6">
         <f>'#'!K20</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G18" s="6">
         <f>'#'!L20</f>
@@ -67680,7 +67742,7 @@
       </c>
       <c r="H18" s="4">
         <f>'#'!V20</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I18" s="4">
         <f>'#'!W20</f>
@@ -67688,7 +67750,7 @@
       </c>
       <c r="J18" s="4">
         <f>'#'!X20</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" s="6">
         <f>'#'!AH20</f>
@@ -67728,15 +67790,15 @@
       </c>
       <c r="T18" s="2">
         <f t="shared" si="5"/>
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="U18" s="2">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V18" s="2">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.25">
@@ -67843,7 +67905,7 @@
       </c>
       <c r="E20" s="6">
         <f>'#'!J22</f>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F20" s="6">
         <f>'#'!K22</f>
@@ -67855,7 +67917,7 @@
       </c>
       <c r="H20" s="4">
         <f>'#'!V22</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I20" s="4">
         <f>'#'!W22</f>
@@ -67903,7 +67965,7 @@
       </c>
       <c r="T20" s="2">
         <f t="shared" si="5"/>
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="U20" s="2">
         <f t="shared" si="6"/>
@@ -67929,7 +67991,7 @@
       </c>
       <c r="E21" s="6">
         <f>'#'!J23</f>
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F21" s="6">
         <f>'#'!K23</f>
@@ -67941,7 +68003,7 @@
       </c>
       <c r="H21" s="4">
         <f>'#'!V23</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I21" s="4">
         <f>'#'!W23</f>
@@ -67949,7 +68011,7 @@
       </c>
       <c r="J21" s="4">
         <f>'#'!X23</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K21" s="6">
         <f>'#'!AH23</f>
@@ -67989,7 +68051,7 @@
       </c>
       <c r="T21" s="2">
         <f t="shared" si="5"/>
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="U21" s="2">
         <f t="shared" si="6"/>
@@ -67997,7 +68059,7 @@
       </c>
       <c r="V21" s="2">
         <f t="shared" si="7"/>
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.25">
@@ -68101,7 +68163,7 @@
       </c>
       <c r="E23" s="6">
         <f>'#'!J25</f>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F23" s="6">
         <f>'#'!K25</f>
@@ -68161,7 +68223,7 @@
       </c>
       <c r="T23" s="2">
         <f t="shared" si="5"/>
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="U23" s="2">
         <f t="shared" si="6"/>
@@ -68362,7 +68424,7 @@
       </c>
       <c r="E26" s="6">
         <f>'#'!J28</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F26" s="6">
         <f>'#'!K28</f>
@@ -68374,7 +68436,7 @@
       </c>
       <c r="H26" s="4">
         <f>'#'!V28</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I26" s="4">
         <f>'#'!W28</f>
@@ -68422,7 +68484,7 @@
       </c>
       <c r="T26" s="2">
         <f t="shared" si="5"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U26" s="2">
         <f t="shared" si="6"/>
@@ -68534,7 +68596,7 @@
       </c>
       <c r="E28" s="6">
         <f>'#'!J30</f>
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F28" s="6">
         <f>'#'!K30</f>
@@ -68542,11 +68604,11 @@
       </c>
       <c r="G28" s="6">
         <f>'#'!L30</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H28" s="4">
         <f>'#'!V30</f>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I28" s="4">
         <f>'#'!W30</f>
@@ -68594,7 +68656,7 @@
       </c>
       <c r="T28" s="2">
         <f t="shared" si="5"/>
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="U28" s="2">
         <f t="shared" si="6"/>
@@ -68602,7 +68664,7 @@
       </c>
       <c r="V28" s="2">
         <f t="shared" si="7"/>
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.25">
@@ -68979,7 +69041,7 @@
       </c>
       <c r="H33" s="4">
         <f>'#'!V35</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I33" s="4">
         <f>'#'!W35</f>
@@ -69027,7 +69089,7 @@
       </c>
       <c r="T33" s="2">
         <f t="shared" si="9"/>
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U33" s="2">
         <f t="shared" si="10"/>
@@ -69240,7 +69302,7 @@
       </c>
       <c r="H36" s="4">
         <f>'#'!V38</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I36" s="4">
         <f>'#'!W38</f>
@@ -69288,7 +69350,7 @@
       </c>
       <c r="T36" s="2">
         <f t="shared" si="9"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U36" s="2">
         <f t="shared" si="10"/>
@@ -69561,30 +69623,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="206" t="s">
+      <c r="D2" s="205" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="206"/>
-      <c r="F2" s="207" t="s">
+      <c r="E2" s="205"/>
+      <c r="F2" s="206" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="207"/>
-      <c r="H2" s="206" t="s">
+      <c r="G2" s="206"/>
+      <c r="H2" s="205" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="206"/>
-      <c r="J2" s="207" t="s">
+      <c r="I2" s="205"/>
+      <c r="J2" s="206" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="207"/>
-      <c r="L2" s="206" t="s">
+      <c r="K2" s="206"/>
+      <c r="L2" s="205" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="206"/>
-      <c r="N2" s="211" t="s">
+      <c r="M2" s="205"/>
+      <c r="N2" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="211"/>
+      <c r="O2" s="210"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -71581,30 +71643,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="206" t="s">
+      <c r="D2" s="205" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="206"/>
-      <c r="F2" s="207" t="s">
+      <c r="E2" s="205"/>
+      <c r="F2" s="206" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="207"/>
-      <c r="H2" s="206" t="s">
+      <c r="G2" s="206"/>
+      <c r="H2" s="205" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="206"/>
-      <c r="J2" s="207" t="s">
+      <c r="I2" s="205"/>
+      <c r="J2" s="206" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="207"/>
-      <c r="L2" s="206" t="s">
+      <c r="K2" s="206"/>
+      <c r="L2" s="205" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="206"/>
-      <c r="N2" s="211" t="s">
+      <c r="M2" s="205"/>
+      <c r="N2" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="211"/>
+      <c r="O2" s="210"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -73538,30 +73600,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="206" t="s">
+      <c r="D2" s="205" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="206"/>
-      <c r="F2" s="207" t="s">
+      <c r="E2" s="205"/>
+      <c r="F2" s="206" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="207"/>
-      <c r="H2" s="206" t="s">
+      <c r="G2" s="206"/>
+      <c r="H2" s="205" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="206"/>
-      <c r="J2" s="207" t="s">
+      <c r="I2" s="205"/>
+      <c r="J2" s="206" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="207"/>
-      <c r="L2" s="206" t="s">
+      <c r="K2" s="206"/>
+      <c r="L2" s="205" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="206"/>
-      <c r="N2" s="211" t="s">
+      <c r="M2" s="205"/>
+      <c r="N2" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="211"/>
+      <c r="O2" s="210"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -75586,30 +75648,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="206" t="s">
+      <c r="D2" s="205" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="206"/>
-      <c r="F2" s="207" t="s">
+      <c r="E2" s="205"/>
+      <c r="F2" s="206" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="207"/>
-      <c r="H2" s="206" t="s">
+      <c r="G2" s="206"/>
+      <c r="H2" s="205" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="206"/>
-      <c r="J2" s="207" t="s">
+      <c r="I2" s="205"/>
+      <c r="J2" s="206" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="207"/>
-      <c r="L2" s="206" t="s">
+      <c r="K2" s="206"/>
+      <c r="L2" s="205" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="206"/>
-      <c r="N2" s="211" t="s">
+      <c r="M2" s="205"/>
+      <c r="N2" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="211"/>
+      <c r="O2" s="210"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -77294,30 +77356,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="206" t="s">
+      <c r="C2" s="205" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="206"/>
-      <c r="E2" s="207" t="s">
+      <c r="D2" s="205"/>
+      <c r="E2" s="206" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="207"/>
-      <c r="G2" s="206" t="s">
+      <c r="F2" s="206"/>
+      <c r="G2" s="205" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="206"/>
-      <c r="I2" s="207" t="s">
+      <c r="H2" s="205"/>
+      <c r="I2" s="206" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="207"/>
-      <c r="K2" s="206" t="s">
+      <c r="J2" s="206"/>
+      <c r="K2" s="205" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="206"/>
-      <c r="M2" s="211" t="s">
+      <c r="L2" s="205"/>
+      <c r="M2" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="211"/>
+      <c r="N2" s="210"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -79079,30 +79141,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="206" t="s">
+      <c r="C2" s="205" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="206"/>
-      <c r="E2" s="207" t="s">
+      <c r="D2" s="205"/>
+      <c r="E2" s="206" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="207"/>
-      <c r="G2" s="206" t="s">
+      <c r="F2" s="206"/>
+      <c r="G2" s="205" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="206"/>
-      <c r="I2" s="207" t="s">
+      <c r="H2" s="205"/>
+      <c r="I2" s="206" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="207"/>
-      <c r="K2" s="206" t="s">
+      <c r="J2" s="206"/>
+      <c r="K2" s="205" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="206"/>
-      <c r="M2" s="211" t="s">
+      <c r="L2" s="205"/>
+      <c r="M2" s="210" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="211"/>
+      <c r="N2" s="210"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">

--- a/data/arsenal_stats.xlsx
+++ b/data/arsenal_stats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bungeltd-my.sharepoint.com/personal/przemyslaw_iskra_bunge_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8762" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{791A5D5F-B7B4-466B-8D0B-7FC2C84CC851}"/>
+  <xr:revisionPtr revIDLastSave="8764" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F68ABC9-AC17-43C1-A976-ADE063C185F3}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="799" firstSheet="1" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1537,9 +1537,6 @@
     <t>1-0</t>
   </si>
   <si>
-    <t>Nottingham</t>
-  </si>
-  <si>
     <t>City Ground (A)</t>
   </si>
   <si>
@@ -1547,6 +1544,9 @@
   </si>
   <si>
     <t>Allianz Arena (A)</t>
+  </si>
+  <si>
+    <t>Bayern Munich</t>
   </si>
 </sst>
 </file>
@@ -3053,6 +3053,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3089,6 +3092,15 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3098,23 +3110,23 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="54" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3152,15 +3164,6 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="28" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3168,27 +3171,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="60" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="10" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="37" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="11" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3281,70 +3263,31 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="60" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="10" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="37" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="11" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="54" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3419,8 +3362,65 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6484,7 +6484,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8669909C-91B4-4AE5-9E3F-1DDCB7E9AA04}" type="CELLRANGE">
+                    <a:fld id="{12EEBCA2-A950-4545-80D7-3DB270419853}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6518,7 +6518,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{44986CE5-0DA0-427C-AFE1-3732BF3C4699}" type="CELLRANGE">
+                    <a:fld id="{C1812816-BCDD-4802-A683-BF2508616593}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6552,7 +6552,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B20F27BD-30CB-424B-A149-952149474756}" type="CELLRANGE">
+                    <a:fld id="{549C1BAF-016C-4329-BE87-2CA208F446AE}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6586,7 +6586,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A9B3CE18-A5DF-4656-87F7-DBEB2987FDA0}" type="CELLRANGE">
+                    <a:fld id="{74AA0544-8240-4E1C-872C-1A74A2520CAF}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6620,7 +6620,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{343831B2-23F4-4226-8AD6-B7438F9B313B}" type="CELLRANGE">
+                    <a:fld id="{CD0715D4-6E79-405D-92F4-5075EBB7BBB8}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6654,7 +6654,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{815DF824-7F75-4E9D-9936-304E39B08B3C}" type="CELLRANGE">
+                    <a:fld id="{5DE2B6E8-B8CF-4AA1-9C11-2D8B644F1A16}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6688,7 +6688,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{0D69B8E7-9C90-4079-9660-8C4BA3979F1C}" type="CELLRANGE">
+                    <a:fld id="{695847D1-572D-4F8E-A00A-75836C83662C}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6722,7 +6722,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{118E26D6-514C-406B-A504-85E44911D652}" type="CELLRANGE">
+                    <a:fld id="{E5FBB9A9-60FB-426B-83C8-98381CCE1DA1}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6756,7 +6756,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8E128C8A-A1B5-4E6D-9984-A9F60D700F1B}" type="CELLRANGE">
+                    <a:fld id="{89259CF9-8DAF-4F8C-82A5-F4F2E0AF4738}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6790,7 +6790,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{44D87958-CA84-4BBB-8723-C1FA9C3BA8B5}" type="CELLRANGE">
+                    <a:fld id="{05B628D6-3679-4884-A7F5-E8A1A1B297F9}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6824,7 +6824,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{464D4944-7B1C-4709-A94E-C95F28708490}" type="CELLRANGE">
+                    <a:fld id="{3C09ADE4-0597-406F-8A57-50213A1D0C9B}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6858,7 +6858,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{0DA59A05-C7C1-4F39-910D-CAAADF619DC2}" type="CELLRANGE">
+                    <a:fld id="{2ADF03FE-D28B-4C94-B22C-89235311B37F}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6907,7 +6907,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{B12B0083-3852-4228-9266-3EDAF8B50255}" type="CELLRANGE">
+                    <a:fld id="{A7CC240D-9CC9-457E-9889-859CD5BB481A}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr>
                         <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
@@ -6966,7 +6966,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{06318371-67C6-4F36-82C0-31B16AB6AA38}" type="CELLRANGE">
+                    <a:fld id="{E8E7377F-E99D-451E-80E4-0775D263448C}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7000,7 +7000,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C77EA08B-8225-4B3F-9C78-DE17EBB1BED4}" type="CELLRANGE">
+                    <a:fld id="{AF98B625-E84C-409F-A122-2025114DC99D}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7034,7 +7034,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{799C1FE3-6F05-41A3-AC49-8FEAD5BAC7D7}" type="CELLRANGE">
+                    <a:fld id="{48DA96F2-01C1-45AE-B277-1A4548CC3995}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7068,7 +7068,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{27713E53-9E79-43AF-B3F6-E86D21419CE9}" type="CELLRANGE">
+                    <a:fld id="{F46EA80E-47FC-4EEA-A194-4306343E9CEC}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13895,10 +13895,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Motyw pakietu Office">
   <a:themeElements>
@@ -14208,30 +14204,30 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
       <c r="B1" s="5"/>
-      <c r="C1" s="205" t="s">
+      <c r="C1" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="205"/>
-      <c r="E1" s="206" t="s">
+      <c r="D1" s="206"/>
+      <c r="E1" s="207" t="s">
         <v>120</v>
       </c>
-      <c r="F1" s="206"/>
-      <c r="G1" s="205" t="s">
+      <c r="F1" s="207"/>
+      <c r="G1" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="H1" s="205"/>
-      <c r="I1" s="206" t="s">
+      <c r="H1" s="206"/>
+      <c r="I1" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="J1" s="206"/>
-      <c r="K1" s="205" t="s">
+      <c r="J1" s="207"/>
+      <c r="K1" s="206" t="s">
         <v>39</v>
       </c>
-      <c r="L1" s="205"/>
-      <c r="M1" s="203" t="s">
+      <c r="L1" s="206"/>
+      <c r="M1" s="204" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="204"/>
+      <c r="N1" s="205"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -15938,30 +15934,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="205" t="s">
+      <c r="C2" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="205"/>
-      <c r="E2" s="206" t="s">
+      <c r="D2" s="206"/>
+      <c r="E2" s="207" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="206"/>
-      <c r="G2" s="205" t="s">
+      <c r="F2" s="207"/>
+      <c r="G2" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="205"/>
-      <c r="I2" s="206" t="s">
+      <c r="H2" s="206"/>
+      <c r="I2" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="206"/>
-      <c r="K2" s="205" t="s">
+      <c r="J2" s="207"/>
+      <c r="K2" s="206" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="205"/>
-      <c r="M2" s="210" t="s">
+      <c r="L2" s="206"/>
+      <c r="M2" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="210"/>
+      <c r="N2" s="211"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -17765,30 +17761,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="205" t="s">
+      <c r="C2" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="205"/>
-      <c r="E2" s="206" t="s">
+      <c r="D2" s="206"/>
+      <c r="E2" s="207" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="206"/>
-      <c r="G2" s="205" t="s">
+      <c r="F2" s="207"/>
+      <c r="G2" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="205"/>
-      <c r="I2" s="206" t="s">
+      <c r="H2" s="206"/>
+      <c r="I2" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="206"/>
-      <c r="K2" s="205" t="s">
+      <c r="J2" s="207"/>
+      <c r="K2" s="206" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="205"/>
-      <c r="M2" s="210" t="s">
+      <c r="L2" s="206"/>
+      <c r="M2" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="210"/>
+      <c r="N2" s="211"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -19455,30 +19451,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="205" t="s">
+      <c r="C2" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="205"/>
-      <c r="E2" s="206" t="s">
+      <c r="D2" s="206"/>
+      <c r="E2" s="207" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="206"/>
-      <c r="G2" s="205" t="s">
+      <c r="F2" s="207"/>
+      <c r="G2" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="205"/>
-      <c r="I2" s="206" t="s">
+      <c r="H2" s="206"/>
+      <c r="I2" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="206"/>
-      <c r="K2" s="205" t="s">
+      <c r="J2" s="207"/>
+      <c r="K2" s="206" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="205"/>
-      <c r="M2" s="210" t="s">
+      <c r="L2" s="206"/>
+      <c r="M2" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="210"/>
+      <c r="N2" s="211"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -21281,30 +21277,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="205" t="s">
+      <c r="C2" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="205"/>
-      <c r="E2" s="206" t="s">
+      <c r="D2" s="206"/>
+      <c r="E2" s="207" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="206"/>
-      <c r="G2" s="205" t="s">
+      <c r="F2" s="207"/>
+      <c r="G2" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="205"/>
-      <c r="I2" s="206" t="s">
+      <c r="H2" s="206"/>
+      <c r="I2" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="206"/>
-      <c r="K2" s="205" t="s">
+      <c r="J2" s="207"/>
+      <c r="K2" s="206" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="205"/>
-      <c r="M2" s="210" t="s">
+      <c r="L2" s="206"/>
+      <c r="M2" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="210"/>
+      <c r="N2" s="211"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -23153,36 +23149,36 @@
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="207" t="s">
+      <c r="C2" s="208" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="208"/>
-      <c r="E2" s="209"/>
-      <c r="F2" s="212" t="s">
+      <c r="D2" s="209"/>
+      <c r="E2" s="210"/>
+      <c r="F2" s="213" t="s">
         <v>120</v>
       </c>
-      <c r="G2" s="213"/>
-      <c r="H2" s="214"/>
-      <c r="I2" s="207" t="s">
+      <c r="G2" s="214"/>
+      <c r="H2" s="215"/>
+      <c r="I2" s="208" t="s">
         <v>108</v>
       </c>
-      <c r="J2" s="208"/>
-      <c r="K2" s="209"/>
-      <c r="L2" s="212" t="s">
+      <c r="J2" s="209"/>
+      <c r="K2" s="210"/>
+      <c r="L2" s="213" t="s">
         <v>110</v>
       </c>
-      <c r="M2" s="213"/>
-      <c r="N2" s="214"/>
-      <c r="O2" s="207" t="s">
+      <c r="M2" s="214"/>
+      <c r="N2" s="215"/>
+      <c r="O2" s="208" t="s">
         <v>39</v>
       </c>
-      <c r="P2" s="208"/>
-      <c r="Q2" s="209"/>
-      <c r="R2" s="210" t="s">
+      <c r="P2" s="209"/>
+      <c r="Q2" s="210"/>
+      <c r="R2" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="S2" s="210"/>
-      <c r="T2" s="210"/>
+      <c r="S2" s="211"/>
+      <c r="T2" s="211"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -26121,36 +26117,36 @@
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
       <c r="D1" s="5"/>
-      <c r="E1" s="207" t="s">
+      <c r="E1" s="208" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="208"/>
-      <c r="G1" s="209"/>
-      <c r="H1" s="212" t="s">
+      <c r="F1" s="209"/>
+      <c r="G1" s="210"/>
+      <c r="H1" s="213" t="s">
         <v>120</v>
       </c>
-      <c r="I1" s="213"/>
-      <c r="J1" s="214"/>
-      <c r="K1" s="207" t="s">
+      <c r="I1" s="214"/>
+      <c r="J1" s="215"/>
+      <c r="K1" s="208" t="s">
         <v>108</v>
       </c>
-      <c r="L1" s="208"/>
-      <c r="M1" s="209"/>
-      <c r="N1" s="212" t="s">
+      <c r="L1" s="209"/>
+      <c r="M1" s="210"/>
+      <c r="N1" s="213" t="s">
         <v>110</v>
       </c>
-      <c r="O1" s="213"/>
-      <c r="P1" s="214"/>
-      <c r="Q1" s="207" t="s">
+      <c r="O1" s="214"/>
+      <c r="P1" s="215"/>
+      <c r="Q1" s="208" t="s">
         <v>39</v>
       </c>
-      <c r="R1" s="208"/>
-      <c r="S1" s="209"/>
-      <c r="T1" s="210" t="s">
+      <c r="R1" s="209"/>
+      <c r="S1" s="210"/>
+      <c r="T1" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="U1" s="210"/>
-      <c r="V1" s="210"/>
+      <c r="U1" s="211"/>
+      <c r="V1" s="211"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -37724,399 +37720,399 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F1" s="215">
-        <v>1</v>
-      </c>
-      <c r="G1" s="216"/>
-      <c r="H1" s="217"/>
-      <c r="I1" s="215">
+      <c r="F1" s="219">
+        <v>1</v>
+      </c>
+      <c r="G1" s="220"/>
+      <c r="H1" s="221"/>
+      <c r="I1" s="219">
         <v>2</v>
       </c>
-      <c r="J1" s="216"/>
-      <c r="K1" s="217"/>
-      <c r="L1" s="215">
-        <v>3</v>
-      </c>
-      <c r="M1" s="216"/>
-      <c r="N1" s="217"/>
-      <c r="O1" s="215">
+      <c r="J1" s="220"/>
+      <c r="K1" s="221"/>
+      <c r="L1" s="219">
+        <v>3</v>
+      </c>
+      <c r="M1" s="220"/>
+      <c r="N1" s="221"/>
+      <c r="O1" s="219">
         <v>4</v>
       </c>
-      <c r="P1" s="216"/>
-      <c r="Q1" s="217"/>
-      <c r="R1" s="215">
+      <c r="P1" s="220"/>
+      <c r="Q1" s="221"/>
+      <c r="R1" s="219">
         <v>5</v>
       </c>
-      <c r="S1" s="216"/>
-      <c r="T1" s="217"/>
-      <c r="U1" s="215">
+      <c r="S1" s="220"/>
+      <c r="T1" s="221"/>
+      <c r="U1" s="219">
         <v>6</v>
       </c>
-      <c r="V1" s="216"/>
-      <c r="W1" s="217"/>
-      <c r="X1" s="215">
+      <c r="V1" s="220"/>
+      <c r="W1" s="221"/>
+      <c r="X1" s="219">
         <v>7</v>
       </c>
-      <c r="Y1" s="216"/>
-      <c r="Z1" s="217"/>
-      <c r="AA1" s="215">
+      <c r="Y1" s="220"/>
+      <c r="Z1" s="221"/>
+      <c r="AA1" s="219">
         <v>8</v>
       </c>
-      <c r="AB1" s="216"/>
-      <c r="AC1" s="217"/>
-      <c r="AD1" s="215">
+      <c r="AB1" s="220"/>
+      <c r="AC1" s="221"/>
+      <c r="AD1" s="219">
         <v>9</v>
       </c>
-      <c r="AE1" s="216"/>
-      <c r="AF1" s="217"/>
-      <c r="AG1" s="215">
+      <c r="AE1" s="220"/>
+      <c r="AF1" s="221"/>
+      <c r="AG1" s="219">
         <v>10</v>
       </c>
-      <c r="AH1" s="216"/>
-      <c r="AI1" s="217"/>
-      <c r="AJ1" s="215">
+      <c r="AH1" s="220"/>
+      <c r="AI1" s="221"/>
+      <c r="AJ1" s="219">
         <v>11</v>
       </c>
-      <c r="AK1" s="216"/>
-      <c r="AL1" s="217"/>
-      <c r="AM1" s="215">
+      <c r="AK1" s="220"/>
+      <c r="AL1" s="221"/>
+      <c r="AM1" s="219">
         <v>12</v>
       </c>
-      <c r="AN1" s="216"/>
-      <c r="AO1" s="217"/>
-      <c r="AP1" s="215">
+      <c r="AN1" s="220"/>
+      <c r="AO1" s="221"/>
+      <c r="AP1" s="219">
         <v>13</v>
       </c>
-      <c r="AQ1" s="216"/>
-      <c r="AR1" s="217"/>
-      <c r="AS1" s="215">
+      <c r="AQ1" s="220"/>
+      <c r="AR1" s="221"/>
+      <c r="AS1" s="219">
         <v>14</v>
       </c>
-      <c r="AT1" s="216"/>
-      <c r="AU1" s="217"/>
-      <c r="AV1" s="215">
+      <c r="AT1" s="220"/>
+      <c r="AU1" s="221"/>
+      <c r="AV1" s="219">
         <v>15</v>
       </c>
-      <c r="AW1" s="216"/>
-      <c r="AX1" s="217"/>
-      <c r="AY1" s="215">
+      <c r="AW1" s="220"/>
+      <c r="AX1" s="221"/>
+      <c r="AY1" s="219">
         <v>16</v>
       </c>
-      <c r="AZ1" s="216"/>
-      <c r="BA1" s="217"/>
-      <c r="BB1" s="215">
+      <c r="AZ1" s="220"/>
+      <c r="BA1" s="221"/>
+      <c r="BB1" s="219">
         <v>17</v>
       </c>
-      <c r="BC1" s="216"/>
-      <c r="BD1" s="217"/>
-      <c r="BE1" s="215">
+      <c r="BC1" s="220"/>
+      <c r="BD1" s="221"/>
+      <c r="BE1" s="219">
         <v>18</v>
       </c>
-      <c r="BF1" s="216"/>
-      <c r="BG1" s="217"/>
-      <c r="BH1" s="215">
+      <c r="BF1" s="220"/>
+      <c r="BG1" s="221"/>
+      <c r="BH1" s="219">
         <v>19</v>
       </c>
-      <c r="BI1" s="216"/>
-      <c r="BJ1" s="217"/>
-      <c r="BK1" s="215">
+      <c r="BI1" s="220"/>
+      <c r="BJ1" s="221"/>
+      <c r="BK1" s="219">
         <v>20</v>
       </c>
-      <c r="BL1" s="216"/>
-      <c r="BM1" s="217"/>
-      <c r="BN1" s="215">
+      <c r="BL1" s="220"/>
+      <c r="BM1" s="221"/>
+      <c r="BN1" s="219">
         <v>21</v>
       </c>
-      <c r="BO1" s="216"/>
-      <c r="BP1" s="217"/>
-      <c r="BQ1" s="215">
+      <c r="BO1" s="220"/>
+      <c r="BP1" s="221"/>
+      <c r="BQ1" s="219">
         <v>22</v>
       </c>
-      <c r="BR1" s="216"/>
-      <c r="BS1" s="217"/>
-      <c r="BT1" s="215">
+      <c r="BR1" s="220"/>
+      <c r="BS1" s="221"/>
+      <c r="BT1" s="219">
         <v>23</v>
       </c>
-      <c r="BU1" s="216"/>
-      <c r="BV1" s="217"/>
-      <c r="BW1" s="215">
+      <c r="BU1" s="220"/>
+      <c r="BV1" s="221"/>
+      <c r="BW1" s="219">
         <v>24</v>
       </c>
-      <c r="BX1" s="216"/>
-      <c r="BY1" s="217"/>
-      <c r="BZ1" s="215">
+      <c r="BX1" s="220"/>
+      <c r="BY1" s="221"/>
+      <c r="BZ1" s="219">
         <v>25</v>
       </c>
-      <c r="CA1" s="216"/>
-      <c r="CB1" s="217"/>
-      <c r="CC1" s="215">
+      <c r="CA1" s="220"/>
+      <c r="CB1" s="221"/>
+      <c r="CC1" s="219">
         <v>26</v>
       </c>
-      <c r="CD1" s="216"/>
-      <c r="CE1" s="217"/>
-      <c r="CF1" s="215">
+      <c r="CD1" s="220"/>
+      <c r="CE1" s="221"/>
+      <c r="CF1" s="219">
         <v>27</v>
       </c>
-      <c r="CG1" s="216"/>
-      <c r="CH1" s="217"/>
-      <c r="CI1" s="215">
+      <c r="CG1" s="220"/>
+      <c r="CH1" s="221"/>
+      <c r="CI1" s="219">
         <v>28</v>
       </c>
-      <c r="CJ1" s="216"/>
-      <c r="CK1" s="217"/>
-      <c r="CL1" s="215">
+      <c r="CJ1" s="220"/>
+      <c r="CK1" s="221"/>
+      <c r="CL1" s="219">
         <v>29</v>
       </c>
-      <c r="CM1" s="216"/>
-      <c r="CN1" s="217"/>
-      <c r="CO1" s="215">
+      <c r="CM1" s="220"/>
+      <c r="CN1" s="221"/>
+      <c r="CO1" s="219">
         <v>30</v>
       </c>
-      <c r="CP1" s="216"/>
-      <c r="CQ1" s="217"/>
-      <c r="CR1" s="215">
+      <c r="CP1" s="220"/>
+      <c r="CQ1" s="221"/>
+      <c r="CR1" s="219">
         <v>31</v>
       </c>
-      <c r="CS1" s="216"/>
-      <c r="CT1" s="217"/>
-      <c r="CU1" s="215">
+      <c r="CS1" s="220"/>
+      <c r="CT1" s="221"/>
+      <c r="CU1" s="219">
         <v>32</v>
       </c>
-      <c r="CV1" s="216"/>
-      <c r="CW1" s="217"/>
-      <c r="CX1" s="215">
+      <c r="CV1" s="220"/>
+      <c r="CW1" s="221"/>
+      <c r="CX1" s="219">
         <v>33</v>
       </c>
-      <c r="CY1" s="216"/>
-      <c r="CZ1" s="217"/>
-      <c r="DA1" s="215">
+      <c r="CY1" s="220"/>
+      <c r="CZ1" s="221"/>
+      <c r="DA1" s="219">
         <v>34</v>
       </c>
-      <c r="DB1" s="216"/>
-      <c r="DC1" s="217"/>
-      <c r="DD1" s="215">
+      <c r="DB1" s="220"/>
+      <c r="DC1" s="221"/>
+      <c r="DD1" s="219">
         <v>35</v>
       </c>
-      <c r="DE1" s="216"/>
-      <c r="DF1" s="217"/>
-      <c r="DG1" s="215">
+      <c r="DE1" s="220"/>
+      <c r="DF1" s="221"/>
+      <c r="DG1" s="219">
         <v>36</v>
       </c>
-      <c r="DH1" s="216"/>
-      <c r="DI1" s="217"/>
-      <c r="DJ1" s="215">
+      <c r="DH1" s="220"/>
+      <c r="DI1" s="221"/>
+      <c r="DJ1" s="219">
         <v>37</v>
       </c>
-      <c r="DK1" s="216"/>
-      <c r="DL1" s="217"/>
-      <c r="DM1" s="215">
+      <c r="DK1" s="220"/>
+      <c r="DL1" s="221"/>
+      <c r="DM1" s="219">
         <v>38</v>
       </c>
-      <c r="DN1" s="216"/>
-      <c r="DO1" s="217"/>
+      <c r="DN1" s="220"/>
+      <c r="DO1" s="221"/>
     </row>
     <row r="2" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="221" t="s">
+      <c r="C2" s="222" t="s">
         <v>396</v>
       </c>
-      <c r="D2" s="221" t="s">
+      <c r="D2" s="222" t="s">
         <v>397</v>
       </c>
-      <c r="E2" s="221" t="s">
+      <c r="E2" s="222" t="s">
         <v>398</v>
       </c>
-      <c r="F2" s="218" t="s">
+      <c r="F2" s="216" t="s">
         <v>346</v>
       </c>
-      <c r="G2" s="219"/>
-      <c r="H2" s="220"/>
-      <c r="I2" s="218" t="s">
+      <c r="G2" s="217"/>
+      <c r="H2" s="218"/>
+      <c r="I2" s="216" t="s">
         <v>331</v>
       </c>
-      <c r="J2" s="219"/>
-      <c r="K2" s="220"/>
-      <c r="L2" s="218" t="s">
+      <c r="J2" s="217"/>
+      <c r="K2" s="218"/>
+      <c r="L2" s="216" t="s">
         <v>330</v>
       </c>
-      <c r="M2" s="219"/>
-      <c r="N2" s="220"/>
-      <c r="O2" s="218" t="s">
+      <c r="M2" s="217"/>
+      <c r="N2" s="218"/>
+      <c r="O2" s="216" t="s">
         <v>328</v>
       </c>
-      <c r="P2" s="219"/>
-      <c r="Q2" s="220"/>
-      <c r="R2" s="218" t="s">
+      <c r="P2" s="217"/>
+      <c r="Q2" s="218"/>
+      <c r="R2" s="216" t="s">
         <v>335</v>
       </c>
-      <c r="S2" s="219"/>
-      <c r="T2" s="220"/>
-      <c r="U2" s="218" t="s">
+      <c r="S2" s="217"/>
+      <c r="T2" s="218"/>
+      <c r="U2" s="216" t="s">
         <v>320</v>
       </c>
-      <c r="V2" s="219"/>
-      <c r="W2" s="220"/>
-      <c r="X2" s="218" t="s">
+      <c r="V2" s="217"/>
+      <c r="W2" s="218"/>
+      <c r="X2" s="216" t="s">
         <v>337</v>
       </c>
-      <c r="Y2" s="219"/>
-      <c r="Z2" s="220"/>
-      <c r="AA2" s="218" t="s">
+      <c r="Y2" s="217"/>
+      <c r="Z2" s="218"/>
+      <c r="AA2" s="216" t="s">
         <v>334</v>
       </c>
-      <c r="AB2" s="219"/>
-      <c r="AC2" s="220"/>
-      <c r="AD2" s="218" t="s">
+      <c r="AB2" s="217"/>
+      <c r="AC2" s="218"/>
+      <c r="AD2" s="216" t="s">
         <v>321</v>
       </c>
-      <c r="AE2" s="219"/>
-      <c r="AF2" s="220"/>
-      <c r="AG2" s="218" t="s">
+      <c r="AE2" s="217"/>
+      <c r="AF2" s="218"/>
+      <c r="AG2" s="216" t="s">
         <v>347</v>
       </c>
-      <c r="AH2" s="219"/>
-      <c r="AI2" s="220"/>
-      <c r="AJ2" s="218" t="s">
+      <c r="AH2" s="217"/>
+      <c r="AI2" s="218"/>
+      <c r="AJ2" s="216" t="s">
         <v>324</v>
       </c>
-      <c r="AK2" s="219"/>
-      <c r="AL2" s="220"/>
-      <c r="AM2" s="218" t="s">
+      <c r="AK2" s="217"/>
+      <c r="AL2" s="218"/>
+      <c r="AM2" s="216" t="s">
         <v>323</v>
       </c>
-      <c r="AN2" s="219"/>
-      <c r="AO2" s="220"/>
-      <c r="AP2" s="218" t="s">
+      <c r="AN2" s="217"/>
+      <c r="AO2" s="218"/>
+      <c r="AP2" s="216" t="s">
         <v>332</v>
       </c>
-      <c r="AQ2" s="219"/>
-      <c r="AR2" s="220"/>
-      <c r="AS2" s="218" t="s">
+      <c r="AQ2" s="217"/>
+      <c r="AR2" s="218"/>
+      <c r="AS2" s="216" t="s">
         <v>329</v>
       </c>
-      <c r="AT2" s="219"/>
-      <c r="AU2" s="220"/>
-      <c r="AV2" s="218" t="s">
+      <c r="AT2" s="217"/>
+      <c r="AU2" s="218"/>
+      <c r="AV2" s="216" t="s">
         <v>336</v>
       </c>
-      <c r="AW2" s="219"/>
-      <c r="AX2" s="220"/>
-      <c r="AY2" s="218" t="s">
+      <c r="AW2" s="217"/>
+      <c r="AX2" s="218"/>
+      <c r="AY2" s="216" t="s">
         <v>305</v>
       </c>
-      <c r="AZ2" s="219"/>
-      <c r="BA2" s="220"/>
-      <c r="BB2" s="218" t="s">
+      <c r="AZ2" s="217"/>
+      <c r="BA2" s="218"/>
+      <c r="BB2" s="216" t="s">
         <v>326</v>
       </c>
-      <c r="BC2" s="219"/>
-      <c r="BD2" s="220"/>
-      <c r="BE2" s="218" t="s">
+      <c r="BC2" s="217"/>
+      <c r="BD2" s="218"/>
+      <c r="BE2" s="216" t="s">
         <v>325</v>
       </c>
-      <c r="BF2" s="219"/>
-      <c r="BG2" s="220"/>
-      <c r="BH2" s="218" t="s">
+      <c r="BF2" s="217"/>
+      <c r="BG2" s="218"/>
+      <c r="BH2" s="216" t="s">
         <v>348</v>
       </c>
-      <c r="BI2" s="219"/>
-      <c r="BJ2" s="220"/>
-      <c r="BK2" s="218" t="s">
+      <c r="BI2" s="217"/>
+      <c r="BJ2" s="218"/>
+      <c r="BK2" s="216" t="s">
         <v>332</v>
       </c>
-      <c r="BL2" s="219"/>
-      <c r="BM2" s="220"/>
-      <c r="BN2" s="218" t="s">
+      <c r="BL2" s="217"/>
+      <c r="BM2" s="218"/>
+      <c r="BN2" s="216" t="s">
         <v>347</v>
       </c>
-      <c r="BO2" s="219"/>
-      <c r="BP2" s="220"/>
-      <c r="BQ2" s="218" t="s">
+      <c r="BO2" s="217"/>
+      <c r="BP2" s="218"/>
+      <c r="BQ2" s="216" t="s">
         <v>324</v>
       </c>
-      <c r="BR2" s="219"/>
-      <c r="BS2" s="220"/>
-      <c r="BT2" s="218" t="s">
+      <c r="BR2" s="217"/>
+      <c r="BS2" s="218"/>
+      <c r="BT2" s="216" t="s">
         <v>323</v>
       </c>
-      <c r="BU2" s="219"/>
-      <c r="BV2" s="220"/>
-      <c r="BW2" s="218" t="s">
+      <c r="BU2" s="217"/>
+      <c r="BV2" s="218"/>
+      <c r="BW2" s="216" t="s">
         <v>321</v>
       </c>
-      <c r="BX2" s="219"/>
-      <c r="BY2" s="220"/>
-      <c r="BZ2" s="218" t="s">
+      <c r="BX2" s="217"/>
+      <c r="BY2" s="218"/>
+      <c r="BZ2" s="216" t="s">
         <v>348</v>
       </c>
-      <c r="CA2" s="219"/>
-      <c r="CB2" s="220"/>
-      <c r="CC2" s="218" t="s">
+      <c r="CA2" s="217"/>
+      <c r="CB2" s="218"/>
+      <c r="CC2" s="216" t="s">
         <v>325</v>
       </c>
-      <c r="CD2" s="219"/>
-      <c r="CE2" s="220"/>
-      <c r="CF2" s="218" t="s">
+      <c r="CD2" s="217"/>
+      <c r="CE2" s="218"/>
+      <c r="CF2" s="216" t="s">
         <v>305</v>
       </c>
-      <c r="CG2" s="219"/>
-      <c r="CH2" s="220"/>
-      <c r="CI2" s="218" t="s">
+      <c r="CG2" s="217"/>
+      <c r="CH2" s="218"/>
+      <c r="CI2" s="216" t="s">
         <v>326</v>
       </c>
-      <c r="CJ2" s="219"/>
-      <c r="CK2" s="220"/>
-      <c r="CL2" s="218" t="s">
+      <c r="CJ2" s="217"/>
+      <c r="CK2" s="218"/>
+      <c r="CL2" s="216" t="s">
         <v>330</v>
       </c>
-      <c r="CM2" s="219"/>
-      <c r="CN2" s="220"/>
-      <c r="CO2" s="218" t="s">
+      <c r="CM2" s="217"/>
+      <c r="CN2" s="218"/>
+      <c r="CO2" s="216" t="s">
         <v>328</v>
       </c>
-      <c r="CP2" s="219"/>
-      <c r="CQ2" s="220"/>
-      <c r="CR2" s="218" t="s">
+      <c r="CP2" s="217"/>
+      <c r="CQ2" s="218"/>
+      <c r="CR2" s="216" t="s">
         <v>346</v>
       </c>
-      <c r="CS2" s="219"/>
-      <c r="CT2" s="220"/>
-      <c r="CU2" s="218" t="s">
+      <c r="CS2" s="217"/>
+      <c r="CT2" s="218"/>
+      <c r="CU2" s="216" t="s">
         <v>331</v>
       </c>
-      <c r="CV2" s="219"/>
-      <c r="CW2" s="220"/>
-      <c r="CX2" s="218" t="s">
+      <c r="CV2" s="217"/>
+      <c r="CW2" s="218"/>
+      <c r="CX2" s="216" t="s">
         <v>336</v>
       </c>
-      <c r="CY2" s="219"/>
-      <c r="CZ2" s="220"/>
-      <c r="DA2" s="218" t="s">
+      <c r="CY2" s="217"/>
+      <c r="CZ2" s="218"/>
+      <c r="DA2" s="216" t="s">
         <v>329</v>
       </c>
-      <c r="DB2" s="219"/>
-      <c r="DC2" s="220"/>
-      <c r="DD2" s="218" t="s">
+      <c r="DB2" s="217"/>
+      <c r="DC2" s="218"/>
+      <c r="DD2" s="216" t="s">
         <v>320</v>
       </c>
-      <c r="DE2" s="219"/>
-      <c r="DF2" s="220"/>
-      <c r="DG2" s="218" t="s">
+      <c r="DE2" s="217"/>
+      <c r="DF2" s="218"/>
+      <c r="DG2" s="216" t="s">
         <v>337</v>
       </c>
-      <c r="DH2" s="219"/>
-      <c r="DI2" s="220"/>
-      <c r="DJ2" s="218" t="s">
+      <c r="DH2" s="217"/>
+      <c r="DI2" s="218"/>
+      <c r="DJ2" s="216" t="s">
         <v>334</v>
       </c>
-      <c r="DK2" s="219"/>
-      <c r="DL2" s="220"/>
-      <c r="DM2" s="218" t="s">
+      <c r="DK2" s="217"/>
+      <c r="DL2" s="218"/>
+      <c r="DM2" s="216" t="s">
         <v>335</v>
       </c>
-      <c r="DN2" s="219"/>
-      <c r="DO2" s="220"/>
+      <c r="DN2" s="217"/>
+      <c r="DO2" s="218"/>
     </row>
     <row r="3" spans="1:119" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -38127,7 +38123,7 @@
       </c>
       <c r="C3" s="223"/>
       <c r="D3" s="223"/>
-      <c r="E3" s="222"/>
+      <c r="E3" s="224"/>
       <c r="F3" s="160" t="s">
         <v>393</v>
       </c>
@@ -43888,6 +43884,69 @@
     </row>
   </sheetData>
   <mergeCells count="79">
+    <mergeCell ref="DM1:DO1"/>
+    <mergeCell ref="DM2:DO2"/>
+    <mergeCell ref="DA1:DC1"/>
+    <mergeCell ref="DA2:DC2"/>
+    <mergeCell ref="DD1:DF1"/>
+    <mergeCell ref="DD2:DF2"/>
+    <mergeCell ref="DG1:DI1"/>
+    <mergeCell ref="DG2:DI2"/>
+    <mergeCell ref="CU1:CW1"/>
+    <mergeCell ref="CU2:CW2"/>
+    <mergeCell ref="CX1:CZ1"/>
+    <mergeCell ref="CX2:CZ2"/>
+    <mergeCell ref="DJ1:DL1"/>
+    <mergeCell ref="DJ2:DL2"/>
+    <mergeCell ref="CL1:CN1"/>
+    <mergeCell ref="CL2:CN2"/>
+    <mergeCell ref="CO1:CQ1"/>
+    <mergeCell ref="CO2:CQ2"/>
+    <mergeCell ref="CR1:CT1"/>
+    <mergeCell ref="CR2:CT2"/>
+    <mergeCell ref="CC1:CE1"/>
+    <mergeCell ref="CC2:CE2"/>
+    <mergeCell ref="CF1:CH1"/>
+    <mergeCell ref="CF2:CH2"/>
+    <mergeCell ref="CI1:CK1"/>
+    <mergeCell ref="CI2:CK2"/>
+    <mergeCell ref="BT1:BV1"/>
+    <mergeCell ref="BT2:BV2"/>
+    <mergeCell ref="BW1:BY1"/>
+    <mergeCell ref="BW2:BY2"/>
+    <mergeCell ref="BZ1:CB1"/>
+    <mergeCell ref="BZ2:CB2"/>
+    <mergeCell ref="BK1:BM1"/>
+    <mergeCell ref="BK2:BM2"/>
+    <mergeCell ref="BN1:BP1"/>
+    <mergeCell ref="BN2:BP2"/>
+    <mergeCell ref="BQ1:BS1"/>
+    <mergeCell ref="BQ2:BS2"/>
+    <mergeCell ref="AS1:AU1"/>
+    <mergeCell ref="AS2:AU2"/>
+    <mergeCell ref="AV1:AX1"/>
+    <mergeCell ref="AV2:AX2"/>
+    <mergeCell ref="BH1:BJ1"/>
+    <mergeCell ref="BH2:BJ2"/>
+    <mergeCell ref="AY2:BA2"/>
+    <mergeCell ref="BB2:BD2"/>
+    <mergeCell ref="BE2:BG2"/>
+    <mergeCell ref="AJ1:AL1"/>
+    <mergeCell ref="AJ2:AL2"/>
+    <mergeCell ref="AM1:AO1"/>
+    <mergeCell ref="AM2:AO2"/>
+    <mergeCell ref="AP2:AR2"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
     <mergeCell ref="AD2:AF2"/>
     <mergeCell ref="AG2:AI2"/>
     <mergeCell ref="BB1:BD1"/>
@@ -43904,69 +43963,6 @@
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="X1:Z1"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="AJ1:AL1"/>
-    <mergeCell ref="AJ2:AL2"/>
-    <mergeCell ref="AM1:AO1"/>
-    <mergeCell ref="AM2:AO2"/>
-    <mergeCell ref="AP2:AR2"/>
-    <mergeCell ref="AS1:AU1"/>
-    <mergeCell ref="AS2:AU2"/>
-    <mergeCell ref="AV1:AX1"/>
-    <mergeCell ref="AV2:AX2"/>
-    <mergeCell ref="BH1:BJ1"/>
-    <mergeCell ref="BH2:BJ2"/>
-    <mergeCell ref="AY2:BA2"/>
-    <mergeCell ref="BB2:BD2"/>
-    <mergeCell ref="BE2:BG2"/>
-    <mergeCell ref="BK1:BM1"/>
-    <mergeCell ref="BK2:BM2"/>
-    <mergeCell ref="BN1:BP1"/>
-    <mergeCell ref="BN2:BP2"/>
-    <mergeCell ref="BQ1:BS1"/>
-    <mergeCell ref="BQ2:BS2"/>
-    <mergeCell ref="BT1:BV1"/>
-    <mergeCell ref="BT2:BV2"/>
-    <mergeCell ref="BW1:BY1"/>
-    <mergeCell ref="BW2:BY2"/>
-    <mergeCell ref="BZ1:CB1"/>
-    <mergeCell ref="BZ2:CB2"/>
-    <mergeCell ref="CC1:CE1"/>
-    <mergeCell ref="CC2:CE2"/>
-    <mergeCell ref="CF1:CH1"/>
-    <mergeCell ref="CF2:CH2"/>
-    <mergeCell ref="CI1:CK1"/>
-    <mergeCell ref="CI2:CK2"/>
-    <mergeCell ref="CL1:CN1"/>
-    <mergeCell ref="CL2:CN2"/>
-    <mergeCell ref="CO1:CQ1"/>
-    <mergeCell ref="CO2:CQ2"/>
-    <mergeCell ref="CR1:CT1"/>
-    <mergeCell ref="CR2:CT2"/>
-    <mergeCell ref="CU1:CW1"/>
-    <mergeCell ref="CU2:CW2"/>
-    <mergeCell ref="CX1:CZ1"/>
-    <mergeCell ref="CX2:CZ2"/>
-    <mergeCell ref="DJ1:DL1"/>
-    <mergeCell ref="DJ2:DL2"/>
-    <mergeCell ref="DM1:DO1"/>
-    <mergeCell ref="DM2:DO2"/>
-    <mergeCell ref="DA1:DC1"/>
-    <mergeCell ref="DA2:DC2"/>
-    <mergeCell ref="DD1:DF1"/>
-    <mergeCell ref="DD2:DF2"/>
-    <mergeCell ref="DG1:DI1"/>
-    <mergeCell ref="DG2:DI2"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:DO38">
     <cfRule type="cellIs" dxfId="18" priority="1" operator="between">
@@ -44002,138 +43998,138 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="233" t="s">
+      <c r="C1" s="237" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="233" t="s">
+      <c r="D1" s="237" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="233" t="s">
+      <c r="E1" s="237" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="224" t="s">
+      <c r="F1" s="228" t="s">
         <v>302</v>
       </c>
-      <c r="G1" s="225"/>
-      <c r="H1" s="225"/>
-      <c r="I1" s="225"/>
-      <c r="J1" s="225"/>
-      <c r="K1" s="225"/>
-      <c r="L1" s="225"/>
-      <c r="M1" s="225"/>
-      <c r="N1" s="225"/>
-      <c r="O1" s="225"/>
-      <c r="P1" s="225"/>
-      <c r="Q1" s="225"/>
-      <c r="R1" s="225"/>
-      <c r="S1" s="225"/>
-      <c r="T1" s="225"/>
-      <c r="U1" s="225"/>
-      <c r="V1" s="225"/>
-      <c r="W1" s="225"/>
-      <c r="X1" s="225"/>
-      <c r="Y1" s="225"/>
-      <c r="Z1" s="225"/>
-      <c r="AA1" s="225"/>
-      <c r="AB1" s="225"/>
-      <c r="AC1" s="226"/>
-      <c r="AD1" s="239" t="s">
+      <c r="G1" s="229"/>
+      <c r="H1" s="229"/>
+      <c r="I1" s="229"/>
+      <c r="J1" s="229"/>
+      <c r="K1" s="229"/>
+      <c r="L1" s="229"/>
+      <c r="M1" s="229"/>
+      <c r="N1" s="229"/>
+      <c r="O1" s="229"/>
+      <c r="P1" s="229"/>
+      <c r="Q1" s="229"/>
+      <c r="R1" s="229"/>
+      <c r="S1" s="229"/>
+      <c r="T1" s="229"/>
+      <c r="U1" s="229"/>
+      <c r="V1" s="229"/>
+      <c r="W1" s="229"/>
+      <c r="X1" s="229"/>
+      <c r="Y1" s="229"/>
+      <c r="Z1" s="229"/>
+      <c r="AA1" s="229"/>
+      <c r="AB1" s="229"/>
+      <c r="AC1" s="230"/>
+      <c r="AD1" s="240" t="s">
         <v>281</v>
       </c>
-      <c r="AE1" s="240"/>
-      <c r="AF1" s="240"/>
-      <c r="AG1" s="240"/>
-      <c r="AH1" s="240"/>
-      <c r="AI1" s="241"/>
-      <c r="AJ1" s="224" t="s">
+      <c r="AE1" s="241"/>
+      <c r="AF1" s="241"/>
+      <c r="AG1" s="241"/>
+      <c r="AH1" s="241"/>
+      <c r="AI1" s="242"/>
+      <c r="AJ1" s="228" t="s">
         <v>282</v>
       </c>
-      <c r="AK1" s="225"/>
-      <c r="AL1" s="225"/>
-      <c r="AM1" s="225"/>
-      <c r="AN1" s="225"/>
-      <c r="AO1" s="226"/>
-      <c r="AP1" s="227" t="s">
+      <c r="AK1" s="229"/>
+      <c r="AL1" s="229"/>
+      <c r="AM1" s="229"/>
+      <c r="AN1" s="229"/>
+      <c r="AO1" s="230"/>
+      <c r="AP1" s="231" t="s">
         <v>283</v>
       </c>
-      <c r="AQ1" s="228"/>
-      <c r="AR1" s="228"/>
-      <c r="AS1" s="228"/>
-      <c r="AT1" s="228"/>
-      <c r="AU1" s="229"/>
-      <c r="AV1" s="230" t="s">
+      <c r="AQ1" s="232"/>
+      <c r="AR1" s="232"/>
+      <c r="AS1" s="232"/>
+      <c r="AT1" s="232"/>
+      <c r="AU1" s="233"/>
+      <c r="AV1" s="234" t="s">
         <v>86</v>
       </c>
-      <c r="AW1" s="231"/>
-      <c r="AX1" s="232"/>
+      <c r="AW1" s="235"/>
+      <c r="AX1" s="236"/>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="234"/>
-      <c r="D2" s="234"/>
-      <c r="E2" s="234"/>
-      <c r="F2" s="236" t="s">
+      <c r="C2" s="238"/>
+      <c r="D2" s="238"/>
+      <c r="E2" s="238"/>
+      <c r="F2" s="225" t="s">
         <v>458</v>
       </c>
-      <c r="G2" s="237"/>
-      <c r="H2" s="238"/>
-      <c r="I2" s="236" t="s">
+      <c r="G2" s="226"/>
+      <c r="H2" s="227"/>
+      <c r="I2" s="225" t="s">
         <v>461</v>
       </c>
-      <c r="J2" s="237"/>
-      <c r="K2" s="238"/>
-      <c r="L2" s="236" t="s">
+      <c r="J2" s="226"/>
+      <c r="K2" s="227"/>
+      <c r="L2" s="225" t="s">
         <v>462</v>
       </c>
-      <c r="M2" s="237"/>
-      <c r="N2" s="238"/>
-      <c r="O2" s="236" t="s">
+      <c r="M2" s="226"/>
+      <c r="N2" s="227"/>
+      <c r="O2" s="225" t="s">
         <v>463</v>
       </c>
-      <c r="P2" s="237"/>
-      <c r="Q2" s="238"/>
-      <c r="R2" s="236" t="s">
+      <c r="P2" s="226"/>
+      <c r="Q2" s="227"/>
+      <c r="R2" s="225" t="s">
         <v>464</v>
       </c>
-      <c r="S2" s="237"/>
-      <c r="T2" s="238"/>
-      <c r="U2" s="236" t="s">
+      <c r="S2" s="226"/>
+      <c r="T2" s="227"/>
+      <c r="U2" s="225" t="s">
         <v>465</v>
       </c>
-      <c r="V2" s="237"/>
-      <c r="W2" s="238"/>
-      <c r="X2" s="236" t="s">
+      <c r="V2" s="226"/>
+      <c r="W2" s="227"/>
+      <c r="X2" s="225" t="s">
         <v>466</v>
       </c>
-      <c r="Y2" s="237"/>
-      <c r="Z2" s="238"/>
-      <c r="AA2" s="236" t="s">
+      <c r="Y2" s="226"/>
+      <c r="Z2" s="227"/>
+      <c r="AA2" s="225" t="s">
         <v>467</v>
       </c>
-      <c r="AB2" s="237"/>
-      <c r="AC2" s="237"/>
-      <c r="AD2" s="236"/>
-      <c r="AE2" s="237"/>
-      <c r="AF2" s="238"/>
-      <c r="AG2" s="236"/>
-      <c r="AH2" s="237"/>
-      <c r="AI2" s="238"/>
-      <c r="AJ2" s="236"/>
-      <c r="AK2" s="237"/>
-      <c r="AL2" s="238"/>
-      <c r="AM2" s="236"/>
-      <c r="AN2" s="237"/>
-      <c r="AO2" s="238"/>
-      <c r="AP2" s="236"/>
-      <c r="AQ2" s="237"/>
-      <c r="AR2" s="238"/>
-      <c r="AS2" s="236"/>
-      <c r="AT2" s="237"/>
-      <c r="AU2" s="238"/>
-      <c r="AV2" s="236"/>
-      <c r="AW2" s="237"/>
-      <c r="AX2" s="238"/>
+      <c r="AB2" s="226"/>
+      <c r="AC2" s="226"/>
+      <c r="AD2" s="225"/>
+      <c r="AE2" s="226"/>
+      <c r="AF2" s="227"/>
+      <c r="AG2" s="225"/>
+      <c r="AH2" s="226"/>
+      <c r="AI2" s="227"/>
+      <c r="AJ2" s="225"/>
+      <c r="AK2" s="226"/>
+      <c r="AL2" s="227"/>
+      <c r="AM2" s="225"/>
+      <c r="AN2" s="226"/>
+      <c r="AO2" s="227"/>
+      <c r="AP2" s="225"/>
+      <c r="AQ2" s="226"/>
+      <c r="AR2" s="227"/>
+      <c r="AS2" s="225"/>
+      <c r="AT2" s="226"/>
+      <c r="AU2" s="227"/>
+      <c r="AV2" s="225"/>
+      <c r="AW2" s="226"/>
+      <c r="AX2" s="227"/>
     </row>
     <row r="3" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -44142,9 +44138,9 @@
       <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="235"/>
-      <c r="D3" s="235"/>
-      <c r="E3" s="235"/>
+      <c r="C3" s="239"/>
+      <c r="D3" s="239"/>
+      <c r="E3" s="239"/>
       <c r="F3" s="169" t="s">
         <v>393</v>
       </c>
@@ -46820,13 +46816,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="F1:AC1"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="AJ1:AO1"/>
     <mergeCell ref="AP1:AU1"/>
     <mergeCell ref="AV1:AX1"/>
@@ -46843,6 +46832,13 @@
     <mergeCell ref="AD1:AI1"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="I2:K2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="F1:AC1"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
+    <mergeCell ref="AA2:AC2"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:AW32">
     <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
@@ -46877,70 +46873,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C1" s="233" t="s">
+      <c r="C1" s="237" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="233" t="s">
+      <c r="D1" s="237" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="233" t="s">
+      <c r="E1" s="237" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="273" t="s">
+      <c r="F1" s="267" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="274"/>
-      <c r="H1" s="275"/>
-      <c r="I1" s="276" t="s">
+      <c r="G1" s="268"/>
+      <c r="H1" s="269"/>
+      <c r="I1" s="270" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="277"/>
-      <c r="K1" s="278"/>
-      <c r="L1" s="243" t="s">
+      <c r="J1" s="271"/>
+      <c r="K1" s="272"/>
+      <c r="L1" s="274" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="244"/>
-      <c r="N1" s="245"/>
-      <c r="O1" s="246" t="s">
+      <c r="M1" s="275"/>
+      <c r="N1" s="276"/>
+      <c r="O1" s="277" t="s">
         <v>199</v>
       </c>
-      <c r="P1" s="247"/>
-      <c r="Q1" s="248"/>
-      <c r="R1" s="249" t="s">
+      <c r="P1" s="278"/>
+      <c r="Q1" s="279"/>
+      <c r="R1" s="243" t="s">
         <v>200</v>
       </c>
-      <c r="S1" s="250"/>
-      <c r="T1" s="251"/>
-      <c r="U1" s="252" t="s">
+      <c r="S1" s="244"/>
+      <c r="T1" s="245"/>
+      <c r="U1" s="246" t="s">
         <v>306</v>
       </c>
-      <c r="V1" s="253"/>
-      <c r="W1" s="254"/>
+      <c r="V1" s="247"/>
+      <c r="W1" s="248"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="234"/>
-      <c r="D2" s="234"/>
-      <c r="E2" s="234"/>
-      <c r="F2" s="255"/>
-      <c r="G2" s="256"/>
-      <c r="H2" s="257"/>
-      <c r="I2" s="270"/>
-      <c r="J2" s="271"/>
-      <c r="K2" s="272"/>
-      <c r="L2" s="267"/>
-      <c r="M2" s="268"/>
-      <c r="N2" s="269"/>
-      <c r="O2" s="264"/>
-      <c r="P2" s="265"/>
-      <c r="Q2" s="266"/>
-      <c r="R2" s="261"/>
-      <c r="S2" s="262"/>
-      <c r="T2" s="263"/>
-      <c r="U2" s="258"/>
-      <c r="V2" s="259"/>
-      <c r="W2" s="260"/>
+      <c r="C2" s="238"/>
+      <c r="D2" s="238"/>
+      <c r="E2" s="238"/>
+      <c r="F2" s="249"/>
+      <c r="G2" s="250"/>
+      <c r="H2" s="251"/>
+      <c r="I2" s="264"/>
+      <c r="J2" s="265"/>
+      <c r="K2" s="266"/>
+      <c r="L2" s="261"/>
+      <c r="M2" s="262"/>
+      <c r="N2" s="263"/>
+      <c r="O2" s="258"/>
+      <c r="P2" s="259"/>
+      <c r="Q2" s="260"/>
+      <c r="R2" s="255"/>
+      <c r="S2" s="256"/>
+      <c r="T2" s="257"/>
+      <c r="U2" s="252"/>
+      <c r="V2" s="253"/>
+      <c r="W2" s="254"/>
     </row>
     <row r="3" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -46949,9 +46945,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="242"/>
-      <c r="D3" s="242"/>
-      <c r="E3" s="242"/>
+      <c r="C3" s="273"/>
+      <c r="D3" s="273"/>
+      <c r="E3" s="273"/>
       <c r="F3" s="188" t="s">
         <v>393</v>
       </c>
@@ -48413,6 +48409,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="O1:Q1"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="F2:H2"/>
@@ -48423,11 +48424,6 @@
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="O1:Q1"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:W32">
     <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
@@ -55434,72 +55430,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C1" s="233" t="s">
+      <c r="C1" s="237" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="233" t="s">
+      <c r="D1" s="237" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="233" t="s">
+      <c r="E1" s="237" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="273" t="s">
+      <c r="F1" s="267" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="274"/>
-      <c r="H1" s="275"/>
-      <c r="I1" s="276" t="s">
+      <c r="G1" s="268"/>
+      <c r="H1" s="269"/>
+      <c r="I1" s="270" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="277"/>
-      <c r="K1" s="278"/>
-      <c r="L1" s="243" t="s">
+      <c r="J1" s="271"/>
+      <c r="K1" s="272"/>
+      <c r="L1" s="274" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="244"/>
-      <c r="N1" s="245"/>
-      <c r="O1" s="246" t="s">
+      <c r="M1" s="275"/>
+      <c r="N1" s="276"/>
+      <c r="O1" s="277" t="s">
         <v>199</v>
       </c>
-      <c r="P1" s="247"/>
-      <c r="Q1" s="248"/>
-      <c r="R1" s="249" t="s">
+      <c r="P1" s="278"/>
+      <c r="Q1" s="279"/>
+      <c r="R1" s="243" t="s">
         <v>200</v>
       </c>
-      <c r="S1" s="250"/>
-      <c r="T1" s="251"/>
-      <c r="U1" s="252" t="s">
+      <c r="S1" s="244"/>
+      <c r="T1" s="245"/>
+      <c r="U1" s="246" t="s">
         <v>306</v>
       </c>
-      <c r="V1" s="253"/>
-      <c r="W1" s="254"/>
+      <c r="V1" s="247"/>
+      <c r="W1" s="248"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="234"/>
-      <c r="D2" s="234"/>
-      <c r="E2" s="234"/>
-      <c r="F2" s="255" t="s">
+      <c r="C2" s="238"/>
+      <c r="D2" s="238"/>
+      <c r="E2" s="238"/>
+      <c r="F2" s="249" t="s">
         <v>432</v>
       </c>
-      <c r="G2" s="256"/>
-      <c r="H2" s="257"/>
-      <c r="I2" s="270"/>
-      <c r="J2" s="271"/>
-      <c r="K2" s="272"/>
-      <c r="L2" s="267"/>
-      <c r="M2" s="268"/>
-      <c r="N2" s="269"/>
-      <c r="O2" s="264"/>
-      <c r="P2" s="265"/>
-      <c r="Q2" s="266"/>
-      <c r="R2" s="261"/>
-      <c r="S2" s="262"/>
-      <c r="T2" s="263"/>
-      <c r="U2" s="258"/>
-      <c r="V2" s="259"/>
-      <c r="W2" s="260"/>
+      <c r="G2" s="250"/>
+      <c r="H2" s="251"/>
+      <c r="I2" s="264"/>
+      <c r="J2" s="265"/>
+      <c r="K2" s="266"/>
+      <c r="L2" s="261"/>
+      <c r="M2" s="262"/>
+      <c r="N2" s="263"/>
+      <c r="O2" s="258"/>
+      <c r="P2" s="259"/>
+      <c r="Q2" s="260"/>
+      <c r="R2" s="255"/>
+      <c r="S2" s="256"/>
+      <c r="T2" s="257"/>
+      <c r="U2" s="252"/>
+      <c r="V2" s="253"/>
+      <c r="W2" s="254"/>
     </row>
     <row r="3" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -55508,9 +55504,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="242"/>
-      <c r="D3" s="242"/>
-      <c r="E3" s="242"/>
+      <c r="C3" s="273"/>
+      <c r="D3" s="273"/>
+      <c r="E3" s="273"/>
       <c r="F3" s="188" t="s">
         <v>393</v>
       </c>
@@ -57014,11 +57010,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="F2:H2"/>
@@ -57029,6 +57020,11 @@
     <mergeCell ref="U2:W2"/>
     <mergeCell ref="L1:N1"/>
     <mergeCell ref="O1:Q1"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:W32">
     <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
@@ -57056,11 +57052,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C1" s="279" t="s">
+      <c r="C1" s="280" t="s">
         <v>340</v>
       </c>
-      <c r="D1" s="280"/>
-      <c r="E1" s="280"/>
+      <c r="D1" s="281"/>
+      <c r="E1" s="281"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -57535,51 +57531,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="301" t="s">
+      <c r="C1" s="282" t="s">
         <v>202</v>
       </c>
-      <c r="D1" s="302"/>
-      <c r="E1" s="302"/>
-      <c r="F1" s="302"/>
-      <c r="G1" s="302"/>
-      <c r="H1" s="302"/>
-      <c r="I1" s="303"/>
+      <c r="D1" s="283"/>
+      <c r="E1" s="283"/>
+      <c r="F1" s="283"/>
+      <c r="G1" s="283"/>
+      <c r="H1" s="283"/>
+      <c r="I1" s="284"/>
       <c r="J1" s="114" t="s">
         <v>195</v>
       </c>
       <c r="K1" s="115" t="s">
         <v>194</v>
       </c>
-      <c r="L1" s="282" t="s">
+      <c r="L1" s="307" t="s">
         <v>287</v>
       </c>
-      <c r="M1" s="287"/>
-      <c r="N1" s="287"/>
-      <c r="O1" s="287"/>
-      <c r="P1" s="287"/>
-      <c r="Q1" s="287"/>
-      <c r="R1" s="287"/>
-      <c r="S1" s="287"/>
-      <c r="T1" s="287"/>
-      <c r="U1" s="287"/>
-      <c r="V1" s="287"/>
-      <c r="W1" s="287"/>
-      <c r="X1" s="287"/>
-      <c r="Y1" s="287"/>
-      <c r="Z1" s="287"/>
-      <c r="AA1" s="287"/>
-      <c r="AB1" s="287"/>
-      <c r="AC1" s="287"/>
-      <c r="AD1" s="287"/>
-      <c r="AE1" s="287"/>
-      <c r="AF1" s="287"/>
-      <c r="AG1" s="288"/>
-      <c r="AH1" s="282" t="s">
+      <c r="M1" s="312"/>
+      <c r="N1" s="312"/>
+      <c r="O1" s="312"/>
+      <c r="P1" s="312"/>
+      <c r="Q1" s="312"/>
+      <c r="R1" s="312"/>
+      <c r="S1" s="312"/>
+      <c r="T1" s="312"/>
+      <c r="U1" s="312"/>
+      <c r="V1" s="312"/>
+      <c r="W1" s="312"/>
+      <c r="X1" s="312"/>
+      <c r="Y1" s="312"/>
+      <c r="Z1" s="312"/>
+      <c r="AA1" s="312"/>
+      <c r="AB1" s="312"/>
+      <c r="AC1" s="312"/>
+      <c r="AD1" s="312"/>
+      <c r="AE1" s="312"/>
+      <c r="AF1" s="312"/>
+      <c r="AG1" s="313"/>
+      <c r="AH1" s="307" t="s">
         <v>175</v>
       </c>
-      <c r="AI1" s="283"/>
-      <c r="AJ1" s="283"/>
-      <c r="AK1" s="284"/>
+      <c r="AI1" s="308"/>
+      <c r="AJ1" s="308"/>
+      <c r="AK1" s="309"/>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B2" s="111"/>
@@ -62779,15 +62775,15 @@
         <f t="shared" ref="J80:J111" si="2">H80-I80</f>
         <v>2</v>
       </c>
-      <c r="K80" s="289" t="s">
+      <c r="K80" s="314" t="s">
         <v>434</v>
       </c>
-      <c r="L80" s="290"/>
-      <c r="M80" s="291"/>
+      <c r="L80" s="315"/>
+      <c r="M80" s="316"/>
       <c r="O80" s="133"/>
       <c r="P80" s="133"/>
-      <c r="W80" s="285"/>
-      <c r="X80" s="285"/>
+      <c r="W80" s="310"/>
+      <c r="X80" s="310"/>
       <c r="Y80" s="70" t="s">
         <v>211</v>
       </c>
@@ -62837,15 +62833,15 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K81" s="292"/>
-      <c r="L81" s="293"/>
-      <c r="M81" s="294"/>
+      <c r="K81" s="317"/>
+      <c r="L81" s="318"/>
+      <c r="M81" s="319"/>
       <c r="O81" s="133"/>
       <c r="P81" s="133"/>
-      <c r="W81" s="285" t="s">
+      <c r="W81" s="310" t="s">
         <v>209</v>
       </c>
-      <c r="X81" s="285"/>
+      <c r="X81" s="310"/>
       <c r="Y81" s="70">
         <f>COUNTIF(L3:AG40,3)</f>
         <v>481</v>
@@ -62901,17 +62897,17 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K82" s="295" t="s">
+      <c r="K82" s="320" t="s">
         <v>435</v>
       </c>
-      <c r="L82" s="296"/>
-      <c r="M82" s="297"/>
+      <c r="L82" s="321"/>
+      <c r="M82" s="322"/>
       <c r="O82" s="133"/>
       <c r="P82" s="133"/>
-      <c r="W82" s="285" t="s">
+      <c r="W82" s="310" t="s">
         <v>210</v>
       </c>
-      <c r="X82" s="285"/>
+      <c r="X82" s="310"/>
       <c r="Y82" s="70">
         <f>COUNTIF(K3:K40,3)+COUNTIF(J3:J15,3)</f>
         <v>25</v>
@@ -62967,17 +62963,17 @@
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="K83" s="298" t="s">
+      <c r="K83" s="323" t="s">
         <v>436</v>
       </c>
-      <c r="L83" s="299"/>
-      <c r="M83" s="300"/>
+      <c r="L83" s="324"/>
+      <c r="M83" s="325"/>
       <c r="O83" s="133"/>
       <c r="P83" s="133"/>
-      <c r="W83" s="286" t="s">
+      <c r="W83" s="311" t="s">
         <v>97</v>
       </c>
-      <c r="X83" s="286"/>
+      <c r="X83" s="311"/>
       <c r="Y83" s="194">
         <v>224</v>
       </c>
@@ -63030,15 +63026,15 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="K84" s="307" t="s">
+      <c r="K84" s="288" t="s">
         <v>284</v>
       </c>
-      <c r="L84" s="308"/>
-      <c r="M84" s="309"/>
+      <c r="L84" s="289"/>
+      <c r="M84" s="290"/>
       <c r="O84" s="141"/>
       <c r="P84" s="141"/>
-      <c r="W84" s="281"/>
-      <c r="X84" s="281"/>
+      <c r="W84" s="306"/>
+      <c r="X84" s="306"/>
       <c r="Y84" s="196"/>
       <c r="Z84" s="196"/>
       <c r="AA84" s="196"/>
@@ -63076,9 +63072,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K85" s="310"/>
-      <c r="L85" s="311"/>
-      <c r="M85" s="312"/>
+      <c r="K85" s="291"/>
+      <c r="L85" s="292"/>
+      <c r="M85" s="293"/>
       <c r="O85" s="141"/>
       <c r="P85" s="141"/>
     </row>
@@ -63112,9 +63108,9 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="K86" s="310"/>
-      <c r="L86" s="311"/>
-      <c r="M86" s="312"/>
+      <c r="K86" s="291"/>
+      <c r="L86" s="292"/>
+      <c r="M86" s="293"/>
       <c r="O86" s="141"/>
       <c r="P86" s="141"/>
     </row>
@@ -63148,9 +63144,9 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="K87" s="310"/>
-      <c r="L87" s="311"/>
-      <c r="M87" s="312"/>
+      <c r="K87" s="291"/>
+      <c r="L87" s="292"/>
+      <c r="M87" s="293"/>
       <c r="O87" s="141"/>
       <c r="P87" s="141"/>
     </row>
@@ -63184,9 +63180,9 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K88" s="310"/>
-      <c r="L88" s="311"/>
-      <c r="M88" s="312"/>
+      <c r="K88" s="291"/>
+      <c r="L88" s="292"/>
+      <c r="M88" s="293"/>
       <c r="O88" s="141"/>
       <c r="P88" s="141"/>
     </row>
@@ -63220,9 +63216,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K89" s="310"/>
-      <c r="L89" s="311"/>
-      <c r="M89" s="312"/>
+      <c r="K89" s="291"/>
+      <c r="L89" s="292"/>
+      <c r="M89" s="293"/>
       <c r="O89" s="141"/>
       <c r="P89" s="141"/>
     </row>
@@ -63256,9 +63252,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K90" s="310"/>
-      <c r="L90" s="311"/>
-      <c r="M90" s="312"/>
+      <c r="K90" s="291"/>
+      <c r="L90" s="292"/>
+      <c r="M90" s="293"/>
       <c r="O90" s="141"/>
       <c r="P90" s="141"/>
     </row>
@@ -63292,9 +63288,9 @@
         <f t="shared" si="2"/>
         <v>47</v>
       </c>
-      <c r="K91" s="310"/>
-      <c r="L91" s="311"/>
-      <c r="M91" s="312"/>
+      <c r="K91" s="291"/>
+      <c r="L91" s="292"/>
+      <c r="M91" s="293"/>
       <c r="O91" s="141"/>
       <c r="P91" s="141"/>
     </row>
@@ -63328,9 +63324,9 @@
         <f t="shared" si="2"/>
         <v>51</v>
       </c>
-      <c r="K92" s="310"/>
-      <c r="L92" s="311"/>
-      <c r="M92" s="312"/>
+      <c r="K92" s="291"/>
+      <c r="L92" s="292"/>
+      <c r="M92" s="293"/>
       <c r="O92" s="141"/>
       <c r="P92" s="141"/>
     </row>
@@ -63364,9 +63360,9 @@
         <f t="shared" si="2"/>
         <v>37</v>
       </c>
-      <c r="K93" s="310"/>
-      <c r="L93" s="311"/>
-      <c r="M93" s="312"/>
+      <c r="K93" s="291"/>
+      <c r="L93" s="292"/>
+      <c r="M93" s="293"/>
       <c r="O93" s="141"/>
       <c r="P93" s="141"/>
     </row>
@@ -63400,9 +63396,9 @@
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="K94" s="310"/>
-      <c r="L94" s="311"/>
-      <c r="M94" s="312"/>
+      <c r="K94" s="291"/>
+      <c r="L94" s="292"/>
+      <c r="M94" s="293"/>
       <c r="O94" s="141"/>
       <c r="P94" s="141"/>
     </row>
@@ -63436,9 +63432,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K95" s="310"/>
-      <c r="L95" s="311"/>
-      <c r="M95" s="312"/>
+      <c r="K95" s="291"/>
+      <c r="L95" s="292"/>
+      <c r="M95" s="293"/>
       <c r="O95" s="141"/>
       <c r="P95" s="141"/>
     </row>
@@ -63472,9 +63468,9 @@
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="K96" s="310"/>
-      <c r="L96" s="311"/>
-      <c r="M96" s="312"/>
+      <c r="K96" s="291"/>
+      <c r="L96" s="292"/>
+      <c r="M96" s="293"/>
       <c r="O96" s="141"/>
       <c r="P96" s="141"/>
     </row>
@@ -63508,9 +63504,9 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="K97" s="310"/>
-      <c r="L97" s="311"/>
-      <c r="M97" s="312"/>
+      <c r="K97" s="291"/>
+      <c r="L97" s="292"/>
+      <c r="M97" s="293"/>
       <c r="O97" s="141"/>
       <c r="P97" s="141"/>
     </row>
@@ -63544,9 +63540,9 @@
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="K98" s="310"/>
-      <c r="L98" s="311"/>
-      <c r="M98" s="312"/>
+      <c r="K98" s="291"/>
+      <c r="L98" s="292"/>
+      <c r="M98" s="293"/>
       <c r="O98" s="141"/>
       <c r="P98" s="141"/>
     </row>
@@ -63580,9 +63576,9 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K99" s="310"/>
-      <c r="L99" s="311"/>
-      <c r="M99" s="312"/>
+      <c r="K99" s="291"/>
+      <c r="L99" s="292"/>
+      <c r="M99" s="293"/>
       <c r="O99" s="141"/>
       <c r="P99" s="141"/>
     </row>
@@ -63616,9 +63612,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K100" s="310"/>
-      <c r="L100" s="311"/>
-      <c r="M100" s="312"/>
+      <c r="K100" s="291"/>
+      <c r="L100" s="292"/>
+      <c r="M100" s="293"/>
       <c r="O100" s="141"/>
       <c r="P100" s="141"/>
     </row>
@@ -63652,9 +63648,9 @@
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="K101" s="310"/>
-      <c r="L101" s="311"/>
-      <c r="M101" s="312"/>
+      <c r="K101" s="291"/>
+      <c r="L101" s="292"/>
+      <c r="M101" s="293"/>
       <c r="O101" s="141"/>
       <c r="P101" s="141"/>
     </row>
@@ -63688,9 +63684,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K102" s="310"/>
-      <c r="L102" s="311"/>
-      <c r="M102" s="312"/>
+      <c r="K102" s="291"/>
+      <c r="L102" s="292"/>
+      <c r="M102" s="293"/>
       <c r="O102" s="141"/>
       <c r="P102" s="141"/>
     </row>
@@ -63724,9 +63720,9 @@
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="K103" s="310"/>
-      <c r="L103" s="311"/>
-      <c r="M103" s="312"/>
+      <c r="K103" s="291"/>
+      <c r="L103" s="292"/>
+      <c r="M103" s="293"/>
       <c r="O103" s="141"/>
       <c r="P103" s="141"/>
     </row>
@@ -63760,9 +63756,9 @@
         <f t="shared" si="2"/>
         <v>33</v>
       </c>
-      <c r="K104" s="310"/>
-      <c r="L104" s="311"/>
-      <c r="M104" s="312"/>
+      <c r="K104" s="291"/>
+      <c r="L104" s="292"/>
+      <c r="M104" s="293"/>
       <c r="O104" s="141"/>
       <c r="P104" s="141"/>
     </row>
@@ -63796,9 +63792,9 @@
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="K105" s="313"/>
-      <c r="L105" s="314"/>
-      <c r="M105" s="315"/>
+      <c r="K105" s="294"/>
+      <c r="L105" s="295"/>
+      <c r="M105" s="296"/>
       <c r="O105" s="141"/>
       <c r="P105" s="141"/>
     </row>
@@ -63832,11 +63828,11 @@
         <f t="shared" si="2"/>
         <v>21</v>
       </c>
-      <c r="K106" s="304" t="s">
+      <c r="K106" s="285" t="s">
         <v>286</v>
       </c>
-      <c r="L106" s="305"/>
-      <c r="M106" s="306"/>
+      <c r="L106" s="286"/>
+      <c r="M106" s="287"/>
       <c r="O106" s="126"/>
       <c r="P106" s="126"/>
     </row>
@@ -63870,11 +63866,11 @@
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="K107" s="304" t="s">
+      <c r="K107" s="285" t="s">
         <v>288</v>
       </c>
-      <c r="L107" s="305"/>
-      <c r="M107" s="306"/>
+      <c r="L107" s="286"/>
+      <c r="M107" s="287"/>
       <c r="O107" s="126"/>
       <c r="P107" s="126"/>
     </row>
@@ -63908,11 +63904,11 @@
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="K108" s="316" t="s">
+      <c r="K108" s="297" t="s">
         <v>289</v>
       </c>
-      <c r="L108" s="317"/>
-      <c r="M108" s="318"/>
+      <c r="L108" s="298"/>
+      <c r="M108" s="299"/>
       <c r="O108" s="126"/>
       <c r="P108" s="126"/>
     </row>
@@ -63946,9 +63942,9 @@
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="K109" s="319"/>
-      <c r="L109" s="320"/>
-      <c r="M109" s="321"/>
+      <c r="K109" s="300"/>
+      <c r="L109" s="301"/>
+      <c r="M109" s="302"/>
       <c r="O109" s="126"/>
       <c r="P109" s="126"/>
     </row>
@@ -63982,9 +63978,9 @@
         <f t="shared" si="2"/>
         <v>45</v>
       </c>
-      <c r="K110" s="319"/>
-      <c r="L110" s="320"/>
-      <c r="M110" s="321"/>
+      <c r="K110" s="300"/>
+      <c r="L110" s="301"/>
+      <c r="M110" s="302"/>
       <c r="O110" s="126"/>
       <c r="P110" s="126"/>
     </row>
@@ -64018,9 +64014,9 @@
         <f t="shared" si="2"/>
         <v>62</v>
       </c>
-      <c r="K111" s="319"/>
-      <c r="L111" s="320"/>
-      <c r="M111" s="321"/>
+      <c r="K111" s="300"/>
+      <c r="L111" s="301"/>
+      <c r="M111" s="302"/>
       <c r="O111" s="126"/>
       <c r="P111" s="126"/>
     </row>
@@ -64058,9 +64054,9 @@
         <f t="shared" ref="J112:J114" si="6">H112-I112</f>
         <v>34</v>
       </c>
-      <c r="K112" s="319"/>
-      <c r="L112" s="320"/>
-      <c r="M112" s="321"/>
+      <c r="K112" s="300"/>
+      <c r="L112" s="301"/>
+      <c r="M112" s="302"/>
     </row>
     <row r="113" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="156" t="s">
@@ -64096,9 +64092,9 @@
         <f t="shared" si="6"/>
         <v>43</v>
       </c>
-      <c r="K113" s="319"/>
-      <c r="L113" s="320"/>
-      <c r="M113" s="321"/>
+      <c r="K113" s="300"/>
+      <c r="L113" s="301"/>
+      <c r="M113" s="302"/>
     </row>
     <row r="114" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="93" t="s">
@@ -64134,18 +64130,13 @@
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="K114" s="322"/>
-      <c r="L114" s="323"/>
-      <c r="M114" s="324"/>
+      <c r="K114" s="303"/>
+      <c r="L114" s="304"/>
+      <c r="M114" s="305"/>
     </row>
   </sheetData>
   <autoFilter ref="A79:J112" xr:uid="{9C81160F-C24B-449F-8F5A-CB622AB71070}"/>
   <mergeCells count="15">
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="K106:M106"/>
-    <mergeCell ref="K107:M107"/>
-    <mergeCell ref="K84:M105"/>
-    <mergeCell ref="K108:M114"/>
     <mergeCell ref="W84:X84"/>
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="W80:X80"/>
@@ -64156,6 +64147,11 @@
     <mergeCell ref="K80:M81"/>
     <mergeCell ref="K82:M82"/>
     <mergeCell ref="K83:M83"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="K106:M106"/>
+    <mergeCell ref="K107:M107"/>
+    <mergeCell ref="K84:M105"/>
+    <mergeCell ref="K108:M114"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <conditionalFormatting sqref="A3:A40">
@@ -64247,32 +64243,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="325" t="s">
+      <c r="A1" s="203" t="s">
         <v>405</v>
       </c>
-      <c r="B1" s="325"/>
-      <c r="C1" s="325"/>
-      <c r="D1" s="325"/>
-      <c r="E1" s="325"/>
-      <c r="F1" s="325" t="s">
+      <c r="B1" s="203"/>
+      <c r="C1" s="203"/>
+      <c r="D1" s="203"/>
+      <c r="E1" s="203"/>
+      <c r="F1" s="203" t="s">
         <v>406</v>
       </c>
-      <c r="G1" s="325"/>
-      <c r="H1" s="325"/>
-      <c r="I1" s="325"/>
-      <c r="J1" s="325"/>
+      <c r="G1" s="203"/>
+      <c r="H1" s="203"/>
+      <c r="I1" s="203"/>
+      <c r="J1" s="203"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2" s="325"/>
-      <c r="B2" s="325"/>
-      <c r="C2" s="325"/>
-      <c r="D2" s="325"/>
-      <c r="E2" s="325"/>
-      <c r="F2" s="325"/>
-      <c r="G2" s="325"/>
-      <c r="H2" s="325"/>
-      <c r="I2" s="325"/>
-      <c r="J2" s="325"/>
+      <c r="A2" s="203"/>
+      <c r="B2" s="203"/>
+      <c r="C2" s="203"/>
+      <c r="D2" s="203"/>
+      <c r="E2" s="203"/>
+      <c r="F2" s="203"/>
+      <c r="G2" s="203"/>
+      <c r="H2" s="203"/>
+      <c r="I2" s="203"/>
+      <c r="J2" s="203"/>
       <c r="L2" t="s">
         <v>409</v>
       </c>
@@ -64368,7 +64364,7 @@
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B4" s="192">
         <v>0.875</v>
@@ -64377,10 +64373,10 @@
         <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>462</v>
+        <v>488</v>
       </c>
       <c r="E4" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F4" t="s">
         <v>483</v>
@@ -64392,10 +64388,10 @@
         <v>4</v>
       </c>
       <c r="I4" t="s">
+        <v>428</v>
+      </c>
+      <c r="J4" t="s">
         <v>485</v>
-      </c>
-      <c r="J4" t="s">
-        <v>486</v>
       </c>
       <c r="L4">
         <v>2</v>
@@ -65279,23 +65275,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="207" t="s">
+      <c r="A1" s="208" t="s">
         <v>46</v>
       </c>
       <c r="B1" s="326"/>
       <c r="C1" s="327" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="210"/>
+      <c r="D1" s="211"/>
       <c r="E1" s="328"/>
-      <c r="H1" s="207" t="s">
+      <c r="H1" s="208" t="s">
         <v>47</v>
       </c>
       <c r="I1" s="326"/>
       <c r="J1" s="327" t="s">
         <v>44</v>
       </c>
-      <c r="K1" s="210"/>
+      <c r="K1" s="211"/>
       <c r="L1" s="328"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -66384,9 +66380,9 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="211"/>
-      <c r="G1" s="211"/>
-      <c r="H1" s="211"/>
+      <c r="F1" s="212"/>
+      <c r="G1" s="212"/>
+      <c r="H1" s="212"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -66410,36 +66406,36 @@
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="5"/>
-      <c r="E2" s="207" t="s">
+      <c r="E2" s="208" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="208"/>
-      <c r="G2" s="209"/>
-      <c r="H2" s="212" t="s">
+      <c r="F2" s="209"/>
+      <c r="G2" s="210"/>
+      <c r="H2" s="213" t="s">
         <v>120</v>
       </c>
-      <c r="I2" s="213"/>
-      <c r="J2" s="214"/>
-      <c r="K2" s="207" t="s">
+      <c r="I2" s="214"/>
+      <c r="J2" s="215"/>
+      <c r="K2" s="208" t="s">
         <v>108</v>
       </c>
-      <c r="L2" s="208"/>
-      <c r="M2" s="209"/>
-      <c r="N2" s="212" t="s">
+      <c r="L2" s="209"/>
+      <c r="M2" s="210"/>
+      <c r="N2" s="213" t="s">
         <v>110</v>
       </c>
-      <c r="O2" s="213"/>
-      <c r="P2" s="214"/>
-      <c r="Q2" s="207" t="s">
+      <c r="O2" s="214"/>
+      <c r="P2" s="215"/>
+      <c r="Q2" s="208" t="s">
         <v>39</v>
       </c>
-      <c r="R2" s="208"/>
-      <c r="S2" s="209"/>
-      <c r="T2" s="210" t="s">
+      <c r="R2" s="209"/>
+      <c r="S2" s="210"/>
+      <c r="T2" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="U2" s="210"/>
-      <c r="V2" s="210"/>
+      <c r="U2" s="211"/>
+      <c r="V2" s="211"/>
       <c r="Z2" s="125">
         <v>46314</v>
       </c>
@@ -69623,30 +69619,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="205" t="s">
+      <c r="D2" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="205"/>
-      <c r="F2" s="206" t="s">
+      <c r="E2" s="206"/>
+      <c r="F2" s="207" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="206"/>
-      <c r="H2" s="205" t="s">
+      <c r="G2" s="207"/>
+      <c r="H2" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="205"/>
-      <c r="J2" s="206" t="s">
+      <c r="I2" s="206"/>
+      <c r="J2" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="206"/>
-      <c r="L2" s="205" t="s">
+      <c r="K2" s="207"/>
+      <c r="L2" s="206" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="205"/>
-      <c r="N2" s="210" t="s">
+      <c r="M2" s="206"/>
+      <c r="N2" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="210"/>
+      <c r="O2" s="211"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -71643,30 +71639,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="205" t="s">
+      <c r="D2" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="205"/>
-      <c r="F2" s="206" t="s">
+      <c r="E2" s="206"/>
+      <c r="F2" s="207" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="206"/>
-      <c r="H2" s="205" t="s">
+      <c r="G2" s="207"/>
+      <c r="H2" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="205"/>
-      <c r="J2" s="206" t="s">
+      <c r="I2" s="206"/>
+      <c r="J2" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="206"/>
-      <c r="L2" s="205" t="s">
+      <c r="K2" s="207"/>
+      <c r="L2" s="206" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="205"/>
-      <c r="N2" s="210" t="s">
+      <c r="M2" s="206"/>
+      <c r="N2" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="210"/>
+      <c r="O2" s="211"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -73600,30 +73596,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="205" t="s">
+      <c r="D2" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="205"/>
-      <c r="F2" s="206" t="s">
+      <c r="E2" s="206"/>
+      <c r="F2" s="207" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="206"/>
-      <c r="H2" s="205" t="s">
+      <c r="G2" s="207"/>
+      <c r="H2" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="205"/>
-      <c r="J2" s="206" t="s">
+      <c r="I2" s="206"/>
+      <c r="J2" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="206"/>
-      <c r="L2" s="205" t="s">
+      <c r="K2" s="207"/>
+      <c r="L2" s="206" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="205"/>
-      <c r="N2" s="210" t="s">
+      <c r="M2" s="206"/>
+      <c r="N2" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="210"/>
+      <c r="O2" s="211"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -75648,30 +75644,30 @@
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
-      <c r="D2" s="205" t="s">
+      <c r="D2" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="205"/>
-      <c r="F2" s="206" t="s">
+      <c r="E2" s="206"/>
+      <c r="F2" s="207" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="206"/>
-      <c r="H2" s="205" t="s">
+      <c r="G2" s="207"/>
+      <c r="H2" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="205"/>
-      <c r="J2" s="206" t="s">
+      <c r="I2" s="206"/>
+      <c r="J2" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="K2" s="206"/>
-      <c r="L2" s="205" t="s">
+      <c r="K2" s="207"/>
+      <c r="L2" s="206" t="s">
         <v>39</v>
       </c>
-      <c r="M2" s="205"/>
-      <c r="N2" s="210" t="s">
+      <c r="M2" s="206"/>
+      <c r="N2" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="210"/>
+      <c r="O2" s="211"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -77356,30 +77352,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="205" t="s">
+      <c r="C2" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="205"/>
-      <c r="E2" s="206" t="s">
+      <c r="D2" s="206"/>
+      <c r="E2" s="207" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="206"/>
-      <c r="G2" s="205" t="s">
+      <c r="F2" s="207"/>
+      <c r="G2" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="205"/>
-      <c r="I2" s="206" t="s">
+      <c r="H2" s="206"/>
+      <c r="I2" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="206"/>
-      <c r="K2" s="205" t="s">
+      <c r="J2" s="207"/>
+      <c r="K2" s="206" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="205"/>
-      <c r="M2" s="210" t="s">
+      <c r="L2" s="206"/>
+      <c r="M2" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="210"/>
+      <c r="N2" s="211"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -79141,30 +79137,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="205" t="s">
+      <c r="C2" s="206" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="205"/>
-      <c r="E2" s="206" t="s">
+      <c r="D2" s="206"/>
+      <c r="E2" s="207" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="206"/>
-      <c r="G2" s="205" t="s">
+      <c r="F2" s="207"/>
+      <c r="G2" s="206" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="205"/>
-      <c r="I2" s="206" t="s">
+      <c r="H2" s="206"/>
+      <c r="I2" s="207" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="206"/>
-      <c r="K2" s="205" t="s">
+      <c r="J2" s="207"/>
+      <c r="K2" s="206" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="205"/>
-      <c r="M2" s="210" t="s">
+      <c r="L2" s="206"/>
+      <c r="M2" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="210"/>
+      <c r="N2" s="211"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">

--- a/data/arsenal_stats.xlsx
+++ b/data/arsenal_stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bungeltd-my.sharepoint.com/personal/przemyslaw_iskra_bunge_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8764" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F68ABC9-AC17-43C1-A976-ADE063C185F3}"/>
+  <xr:revisionPtr revIDLastSave="8828" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{349CB5C9-7605-476C-A4E3-07D50A0C4E97}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="799" firstSheet="1" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="799" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="19" state="hidden" r:id="rId1"/>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2269" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2271" uniqueCount="489">
   <si>
     <t>Arsenal FC squad statistics</t>
   </si>
@@ -1519,9 +1519,6 @@
     <t>G</t>
   </si>
   <si>
-    <t>White</t>
-  </si>
-  <si>
     <t>A</t>
   </si>
   <si>
@@ -1531,15 +1528,6 @@
     <t>Eze</t>
   </si>
   <si>
-    <t>18.10.2026</t>
-  </si>
-  <si>
-    <t>1-0</t>
-  </si>
-  <si>
-    <t>City Ground (A)</t>
-  </si>
-  <si>
     <t>21.10.2026</t>
   </si>
   <si>
@@ -1547,6 +1535,18 @@
   </si>
   <si>
     <t>Bayern Munich</t>
+  </si>
+  <si>
+    <t>2-2</t>
+  </si>
+  <si>
+    <t>24.10.2026</t>
+  </si>
+  <si>
+    <t>Emirates Stadium (H)</t>
+  </si>
+  <si>
+    <t>Lewis-Skelly</t>
   </si>
 </sst>
 </file>
@@ -3092,6 +3092,15 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3101,32 +3110,14 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="54" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3164,6 +3155,15 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="28" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3171,6 +3171,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="60" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="10" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="37" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="11" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3263,31 +3284,70 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="60" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="10" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="37" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="11" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="54" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3360,66 +3420,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -4635,7 +4635,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="33"/>
                 <c:pt idx="0">
-                  <c:v>10</c:v>
+                  <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -4650,49 +4650,49 @@
                   <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>11</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>10</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9</c:v>
-                </c:pt>
                 <c:pt idx="9">
-                  <c:v>5</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>8</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>9</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>8</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>10</c:v>
+                  <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>10</c:v>
+                  <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>8</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>0</c:v>
@@ -4701,13 +4701,13 @@
                   <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>9</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>10</c:v>
+                  <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>0</c:v>
@@ -4722,7 +4722,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>8</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>0</c:v>
@@ -4895,7 +4895,7 @@
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>1</c:v>
@@ -4943,7 +4943,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>0</c:v>
@@ -6484,7 +6484,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{12EEBCA2-A950-4545-80D7-3DB270419853}" type="CELLRANGE">
+                    <a:fld id="{C3F69A78-597A-4B61-A53F-37C534451298}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6518,7 +6518,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C1812816-BCDD-4802-A683-BF2508616593}" type="CELLRANGE">
+                    <a:fld id="{4A5BC353-34AF-4387-9748-548EE3AA67E4}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6552,7 +6552,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{549C1BAF-016C-4329-BE87-2CA208F446AE}" type="CELLRANGE">
+                    <a:fld id="{9C9A2F4C-CBB8-4F5B-B64C-25160BEC71BF}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6586,7 +6586,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{74AA0544-8240-4E1C-872C-1A74A2520CAF}" type="CELLRANGE">
+                    <a:fld id="{5C127597-DB84-498B-B02F-9D6149647BDA}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6620,7 +6620,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{CD0715D4-6E79-405D-92F4-5075EBB7BBB8}" type="CELLRANGE">
+                    <a:fld id="{F799D473-7896-4A64-A2B7-ADE4C51872CF}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6654,7 +6654,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{5DE2B6E8-B8CF-4AA1-9C11-2D8B644F1A16}" type="CELLRANGE">
+                    <a:fld id="{F5293035-5F1F-4E90-A001-CEDF0463FF1C}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6688,7 +6688,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{695847D1-572D-4F8E-A00A-75836C83662C}" type="CELLRANGE">
+                    <a:fld id="{CEE01B22-9206-4C5E-9727-13B886FBD8A0}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6722,7 +6722,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E5FBB9A9-60FB-426B-83C8-98381CCE1DA1}" type="CELLRANGE">
+                    <a:fld id="{54E7DC27-CC6A-495F-A62F-97DB0D9ED9AE}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6756,7 +6756,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{89259CF9-8DAF-4F8C-82A5-F4F2E0AF4738}" type="CELLRANGE">
+                    <a:fld id="{4B5C21A5-AC62-437D-B644-72F97AC045AA}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6790,7 +6790,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{05B628D6-3679-4884-A7F5-E8A1A1B297F9}" type="CELLRANGE">
+                    <a:fld id="{AD91FAAB-00B3-4F7C-B6A8-A7744A655FD6}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6824,7 +6824,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{3C09ADE4-0597-406F-8A57-50213A1D0C9B}" type="CELLRANGE">
+                    <a:fld id="{3F42F5EA-5E46-4060-908C-3670EA2F7FC9}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6858,7 +6858,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2ADF03FE-D28B-4C94-B22C-89235311B37F}" type="CELLRANGE">
+                    <a:fld id="{5241F2FA-E345-45DB-8E6E-1A8DF2267E06}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6907,7 +6907,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{A7CC240D-9CC9-457E-9889-859CD5BB481A}" type="CELLRANGE">
+                    <a:fld id="{17C29309-C308-4D52-BE12-531910DE70DC}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr>
                         <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
@@ -6966,7 +6966,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E8E7377F-E99D-451E-80E4-0775D263448C}" type="CELLRANGE">
+                    <a:fld id="{D12C8347-F3BC-468B-9973-316C769735C5}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7000,7 +7000,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{AF98B625-E84C-409F-A122-2025114DC99D}" type="CELLRANGE">
+                    <a:fld id="{99870CFE-0B48-4691-BA61-C90F14E67A18}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7034,7 +7034,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{48DA96F2-01C1-45AE-B277-1A4548CC3995}" type="CELLRANGE">
+                    <a:fld id="{4CDEED84-7315-4A2B-8300-113E6A7463BA}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7068,7 +7068,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F46EA80E-47FC-4EEA-A194-4306343E9CEC}" type="CELLRANGE">
+                    <a:fld id="{C6C497EA-C79F-4C6F-B2D9-B649AA1F663D}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7252,49 +7252,49 @@
                   <c:v>44</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>272</c:v>
+                  <c:v>273</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>322</c:v>
+                  <c:v>323</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>245</c:v>
+                  <c:v>246</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>61</c:v>
+                  <c:v>62</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>100</c:v>
+                  <c:v>101</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>63</c:v>
+                  <c:v>64</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>9</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>50</c:v>
+                  <c:v>51</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>51</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>88</c:v>
+                  <c:v>89</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>121</c:v>
+                  <c:v>122</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>73</c:v>
+                  <c:v>74</c:v>
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>2</c:v>
@@ -7324,7 +7324,7 @@
                   <c:v>46</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>11</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>7</c:v>
@@ -7551,7 +7551,7 @@
                         <c:v>46</c:v>
                       </c:pt>
                       <c:pt idx="5">
-                        <c:v>11</c:v>
+                        <c:v>12</c:v>
                       </c:pt>
                       <c:pt idx="6">
                         <c:v>7</c:v>
@@ -13895,6 +13895,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Motyw pakietu Office">
   <a:themeElements>
@@ -23263,7 +23267,7 @@
       </c>
       <c r="F4" s="4">
         <f>Europe!C4</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G4" s="4">
         <f>Europe!D4</f>
@@ -23311,7 +23315,7 @@
       </c>
       <c r="R4" s="2">
         <f>SUM(C4,F4,I4,L4,O4)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S4" s="2">
         <f t="shared" ref="S4:T4" si="0">SUM(D4,G4,J4,M4,P4)</f>
@@ -23667,7 +23671,7 @@
       </c>
       <c r="F9" s="4">
         <f>Europe!C9</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G9" s="4">
         <f>Europe!D9</f>
@@ -23715,7 +23719,7 @@
       </c>
       <c r="R9" s="2">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="S9" s="2">
         <f t="shared" si="2"/>
@@ -23748,7 +23752,7 @@
       </c>
       <c r="F10" s="4">
         <f>Europe!C10</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G10" s="4">
         <f>Europe!D10</f>
@@ -23796,7 +23800,7 @@
       </c>
       <c r="R10" s="2">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S10" s="2">
         <f t="shared" si="2"/>
@@ -23829,7 +23833,7 @@
       </c>
       <c r="F11" s="4">
         <f>Europe!C11</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G11" s="4">
         <f>Europe!D11</f>
@@ -23837,7 +23841,7 @@
       </c>
       <c r="H11" s="4">
         <f>Europe!E11</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" s="6">
         <f>'FA Cup'!C11</f>
@@ -23877,7 +23881,7 @@
       </c>
       <c r="R11" s="2">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="S11" s="2">
         <f t="shared" si="2"/>
@@ -23885,7 +23889,7 @@
       </c>
       <c r="T11" s="2">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="55"/>
     </row>
@@ -23910,11 +23914,11 @@
       </c>
       <c r="F12" s="4">
         <f>Europe!C12</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G12" s="4">
         <f>Europe!D12</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" s="4">
         <f>Europe!E12</f>
@@ -23958,11 +23962,11 @@
       </c>
       <c r="R12" s="2">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S12" s="2">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T12" s="2">
         <f t="shared" si="3"/>
@@ -23991,7 +23995,7 @@
       </c>
       <c r="F13" s="4">
         <f>Europe!C13</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G13" s="4">
         <f>Europe!D13</f>
@@ -24039,7 +24043,7 @@
       </c>
       <c r="R13" s="2">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S13" s="2">
         <f t="shared" si="2"/>
@@ -24153,7 +24157,7 @@
       </c>
       <c r="F15" s="4">
         <f>Europe!C15</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="4">
         <f>Europe!D15</f>
@@ -24161,7 +24165,7 @@
       </c>
       <c r="H15" s="4">
         <f>Europe!E15</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" s="6">
         <f>'FA Cup'!C15</f>
@@ -24201,7 +24205,7 @@
       </c>
       <c r="R15" s="2">
         <f>SUM(C15,F15,I15,L15,O15)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S15" s="2">
         <f>SUM(D15,G15,J15,M15,P15)</f>
@@ -24209,7 +24213,7 @@
       </c>
       <c r="T15" s="2">
         <f>SUM(E15,H15,K15,N15,Q15)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="55"/>
     </row>
@@ -24234,7 +24238,7 @@
       </c>
       <c r="F16" s="4">
         <f>Europe!C16</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G16" s="4">
         <f>Europe!D16</f>
@@ -24282,7 +24286,7 @@
       </c>
       <c r="R16" s="2">
         <f t="shared" ref="R16:R28" si="4">SUM(C16,F16,I16,L16,O16)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S16" s="2">
         <f t="shared" ref="S16:S28" si="5">SUM(D16,G16,J16,M16,P16)</f>
@@ -24396,7 +24400,7 @@
       </c>
       <c r="F18" s="4">
         <f>Europe!C18</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G18" s="4">
         <f>Europe!D18</f>
@@ -24444,7 +24448,7 @@
       </c>
       <c r="R18" s="2">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S18" s="2">
         <f t="shared" si="5"/>
@@ -24556,7 +24560,7 @@
       </c>
       <c r="F20" s="4">
         <f>Europe!C20</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20" s="4">
         <f>Europe!D20</f>
@@ -24604,7 +24608,7 @@
       </c>
       <c r="R20" s="2">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S20" s="2">
         <f t="shared" si="5"/>
@@ -24636,7 +24640,7 @@
       </c>
       <c r="F21" s="4">
         <f>Europe!C21</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G21" s="4">
         <f>Europe!D21</f>
@@ -24684,7 +24688,7 @@
       </c>
       <c r="R21" s="2">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S21" s="2">
         <f t="shared" si="5"/>
@@ -24798,7 +24802,7 @@
       </c>
       <c r="F23" s="4">
         <f>Europe!C23</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" s="4">
         <f>Europe!D23</f>
@@ -24846,7 +24850,7 @@
       </c>
       <c r="R23" s="2">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S23" s="2">
         <f t="shared" si="5"/>
@@ -25041,7 +25045,7 @@
       </c>
       <c r="F26" s="4">
         <f>Europe!C26</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G26" s="4">
         <f>Europe!D26</f>
@@ -25089,7 +25093,7 @@
       </c>
       <c r="R26" s="2">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S26" s="2">
         <f t="shared" si="5"/>
@@ -25202,11 +25206,11 @@
       </c>
       <c r="F28" s="4">
         <f>Europe!C28</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G28" s="4">
         <f>Europe!D28</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" s="4">
         <f>Europe!E28</f>
@@ -25250,11 +25254,11 @@
       </c>
       <c r="R28" s="2">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S28" s="2">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T28" s="2">
         <f t="shared" si="6"/>
@@ -25604,7 +25608,7 @@
       </c>
       <c r="F33" s="4">
         <f>Europe!C33</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" s="4">
         <f>Europe!D33</f>
@@ -25652,7 +25656,7 @@
       </c>
       <c r="R33" s="2">
         <f t="shared" si="8"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S33" s="2">
         <f t="shared" si="9"/>
@@ -37720,196 +37724,196 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F1" s="219">
-        <v>1</v>
-      </c>
-      <c r="G1" s="220"/>
-      <c r="H1" s="221"/>
-      <c r="I1" s="219">
+      <c r="F1" s="216">
+        <v>1</v>
+      </c>
+      <c r="G1" s="217"/>
+      <c r="H1" s="218"/>
+      <c r="I1" s="216">
         <v>2</v>
       </c>
-      <c r="J1" s="220"/>
-      <c r="K1" s="221"/>
-      <c r="L1" s="219">
-        <v>3</v>
-      </c>
-      <c r="M1" s="220"/>
-      <c r="N1" s="221"/>
-      <c r="O1" s="219">
+      <c r="J1" s="217"/>
+      <c r="K1" s="218"/>
+      <c r="L1" s="216">
+        <v>3</v>
+      </c>
+      <c r="M1" s="217"/>
+      <c r="N1" s="218"/>
+      <c r="O1" s="216">
         <v>4</v>
       </c>
-      <c r="P1" s="220"/>
-      <c r="Q1" s="221"/>
-      <c r="R1" s="219">
+      <c r="P1" s="217"/>
+      <c r="Q1" s="218"/>
+      <c r="R1" s="216">
         <v>5</v>
       </c>
-      <c r="S1" s="220"/>
-      <c r="T1" s="221"/>
-      <c r="U1" s="219">
+      <c r="S1" s="217"/>
+      <c r="T1" s="218"/>
+      <c r="U1" s="216">
         <v>6</v>
       </c>
-      <c r="V1" s="220"/>
-      <c r="W1" s="221"/>
-      <c r="X1" s="219">
+      <c r="V1" s="217"/>
+      <c r="W1" s="218"/>
+      <c r="X1" s="216">
         <v>7</v>
       </c>
-      <c r="Y1" s="220"/>
-      <c r="Z1" s="221"/>
-      <c r="AA1" s="219">
+      <c r="Y1" s="217"/>
+      <c r="Z1" s="218"/>
+      <c r="AA1" s="216">
         <v>8</v>
       </c>
-      <c r="AB1" s="220"/>
-      <c r="AC1" s="221"/>
-      <c r="AD1" s="219">
+      <c r="AB1" s="217"/>
+      <c r="AC1" s="218"/>
+      <c r="AD1" s="216">
         <v>9</v>
       </c>
-      <c r="AE1" s="220"/>
-      <c r="AF1" s="221"/>
-      <c r="AG1" s="219">
+      <c r="AE1" s="217"/>
+      <c r="AF1" s="218"/>
+      <c r="AG1" s="216">
         <v>10</v>
       </c>
-      <c r="AH1" s="220"/>
-      <c r="AI1" s="221"/>
-      <c r="AJ1" s="219">
+      <c r="AH1" s="217"/>
+      <c r="AI1" s="218"/>
+      <c r="AJ1" s="216">
         <v>11</v>
       </c>
-      <c r="AK1" s="220"/>
-      <c r="AL1" s="221"/>
-      <c r="AM1" s="219">
+      <c r="AK1" s="217"/>
+      <c r="AL1" s="218"/>
+      <c r="AM1" s="216">
         <v>12</v>
       </c>
-      <c r="AN1" s="220"/>
-      <c r="AO1" s="221"/>
-      <c r="AP1" s="219">
+      <c r="AN1" s="217"/>
+      <c r="AO1" s="218"/>
+      <c r="AP1" s="216">
         <v>13</v>
       </c>
-      <c r="AQ1" s="220"/>
-      <c r="AR1" s="221"/>
-      <c r="AS1" s="219">
+      <c r="AQ1" s="217"/>
+      <c r="AR1" s="218"/>
+      <c r="AS1" s="216">
         <v>14</v>
       </c>
-      <c r="AT1" s="220"/>
-      <c r="AU1" s="221"/>
-      <c r="AV1" s="219">
+      <c r="AT1" s="217"/>
+      <c r="AU1" s="218"/>
+      <c r="AV1" s="216">
         <v>15</v>
       </c>
-      <c r="AW1" s="220"/>
-      <c r="AX1" s="221"/>
-      <c r="AY1" s="219">
+      <c r="AW1" s="217"/>
+      <c r="AX1" s="218"/>
+      <c r="AY1" s="216">
         <v>16</v>
       </c>
-      <c r="AZ1" s="220"/>
-      <c r="BA1" s="221"/>
-      <c r="BB1" s="219">
+      <c r="AZ1" s="217"/>
+      <c r="BA1" s="218"/>
+      <c r="BB1" s="216">
         <v>17</v>
       </c>
-      <c r="BC1" s="220"/>
-      <c r="BD1" s="221"/>
-      <c r="BE1" s="219">
+      <c r="BC1" s="217"/>
+      <c r="BD1" s="218"/>
+      <c r="BE1" s="216">
         <v>18</v>
       </c>
-      <c r="BF1" s="220"/>
-      <c r="BG1" s="221"/>
-      <c r="BH1" s="219">
+      <c r="BF1" s="217"/>
+      <c r="BG1" s="218"/>
+      <c r="BH1" s="216">
         <v>19</v>
       </c>
-      <c r="BI1" s="220"/>
-      <c r="BJ1" s="221"/>
-      <c r="BK1" s="219">
+      <c r="BI1" s="217"/>
+      <c r="BJ1" s="218"/>
+      <c r="BK1" s="216">
         <v>20</v>
       </c>
-      <c r="BL1" s="220"/>
-      <c r="BM1" s="221"/>
-      <c r="BN1" s="219">
+      <c r="BL1" s="217"/>
+      <c r="BM1" s="218"/>
+      <c r="BN1" s="216">
         <v>21</v>
       </c>
-      <c r="BO1" s="220"/>
-      <c r="BP1" s="221"/>
-      <c r="BQ1" s="219">
+      <c r="BO1" s="217"/>
+      <c r="BP1" s="218"/>
+      <c r="BQ1" s="216">
         <v>22</v>
       </c>
-      <c r="BR1" s="220"/>
-      <c r="BS1" s="221"/>
-      <c r="BT1" s="219">
+      <c r="BR1" s="217"/>
+      <c r="BS1" s="218"/>
+      <c r="BT1" s="216">
         <v>23</v>
       </c>
-      <c r="BU1" s="220"/>
-      <c r="BV1" s="221"/>
-      <c r="BW1" s="219">
+      <c r="BU1" s="217"/>
+      <c r="BV1" s="218"/>
+      <c r="BW1" s="216">
         <v>24</v>
       </c>
-      <c r="BX1" s="220"/>
-      <c r="BY1" s="221"/>
-      <c r="BZ1" s="219">
+      <c r="BX1" s="217"/>
+      <c r="BY1" s="218"/>
+      <c r="BZ1" s="216">
         <v>25</v>
       </c>
-      <c r="CA1" s="220"/>
-      <c r="CB1" s="221"/>
-      <c r="CC1" s="219">
+      <c r="CA1" s="217"/>
+      <c r="CB1" s="218"/>
+      <c r="CC1" s="216">
         <v>26</v>
       </c>
-      <c r="CD1" s="220"/>
-      <c r="CE1" s="221"/>
-      <c r="CF1" s="219">
+      <c r="CD1" s="217"/>
+      <c r="CE1" s="218"/>
+      <c r="CF1" s="216">
         <v>27</v>
       </c>
-      <c r="CG1" s="220"/>
-      <c r="CH1" s="221"/>
-      <c r="CI1" s="219">
+      <c r="CG1" s="217"/>
+      <c r="CH1" s="218"/>
+      <c r="CI1" s="216">
         <v>28</v>
       </c>
-      <c r="CJ1" s="220"/>
-      <c r="CK1" s="221"/>
-      <c r="CL1" s="219">
+      <c r="CJ1" s="217"/>
+      <c r="CK1" s="218"/>
+      <c r="CL1" s="216">
         <v>29</v>
       </c>
-      <c r="CM1" s="220"/>
-      <c r="CN1" s="221"/>
-      <c r="CO1" s="219">
+      <c r="CM1" s="217"/>
+      <c r="CN1" s="218"/>
+      <c r="CO1" s="216">
         <v>30</v>
       </c>
-      <c r="CP1" s="220"/>
-      <c r="CQ1" s="221"/>
-      <c r="CR1" s="219">
+      <c r="CP1" s="217"/>
+      <c r="CQ1" s="218"/>
+      <c r="CR1" s="216">
         <v>31</v>
       </c>
-      <c r="CS1" s="220"/>
-      <c r="CT1" s="221"/>
-      <c r="CU1" s="219">
+      <c r="CS1" s="217"/>
+      <c r="CT1" s="218"/>
+      <c r="CU1" s="216">
         <v>32</v>
       </c>
-      <c r="CV1" s="220"/>
-      <c r="CW1" s="221"/>
-      <c r="CX1" s="219">
+      <c r="CV1" s="217"/>
+      <c r="CW1" s="218"/>
+      <c r="CX1" s="216">
         <v>33</v>
       </c>
-      <c r="CY1" s="220"/>
-      <c r="CZ1" s="221"/>
-      <c r="DA1" s="219">
+      <c r="CY1" s="217"/>
+      <c r="CZ1" s="218"/>
+      <c r="DA1" s="216">
         <v>34</v>
       </c>
-      <c r="DB1" s="220"/>
-      <c r="DC1" s="221"/>
-      <c r="DD1" s="219">
+      <c r="DB1" s="217"/>
+      <c r="DC1" s="218"/>
+      <c r="DD1" s="216">
         <v>35</v>
       </c>
-      <c r="DE1" s="220"/>
-      <c r="DF1" s="221"/>
-      <c r="DG1" s="219">
+      <c r="DE1" s="217"/>
+      <c r="DF1" s="218"/>
+      <c r="DG1" s="216">
         <v>36</v>
       </c>
-      <c r="DH1" s="220"/>
-      <c r="DI1" s="221"/>
-      <c r="DJ1" s="219">
+      <c r="DH1" s="217"/>
+      <c r="DI1" s="218"/>
+      <c r="DJ1" s="216">
         <v>37</v>
       </c>
-      <c r="DK1" s="220"/>
-      <c r="DL1" s="221"/>
-      <c r="DM1" s="219">
+      <c r="DK1" s="217"/>
+      <c r="DL1" s="218"/>
+      <c r="DM1" s="216">
         <v>38</v>
       </c>
-      <c r="DN1" s="220"/>
-      <c r="DO1" s="221"/>
+      <c r="DN1" s="217"/>
+      <c r="DO1" s="218"/>
     </row>
     <row r="2" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
@@ -37923,196 +37927,196 @@
       <c r="E2" s="222" t="s">
         <v>398</v>
       </c>
-      <c r="F2" s="216" t="s">
+      <c r="F2" s="219" t="s">
         <v>346</v>
       </c>
-      <c r="G2" s="217"/>
-      <c r="H2" s="218"/>
-      <c r="I2" s="216" t="s">
+      <c r="G2" s="220"/>
+      <c r="H2" s="221"/>
+      <c r="I2" s="219" t="s">
         <v>331</v>
       </c>
-      <c r="J2" s="217"/>
-      <c r="K2" s="218"/>
-      <c r="L2" s="216" t="s">
+      <c r="J2" s="220"/>
+      <c r="K2" s="221"/>
+      <c r="L2" s="219" t="s">
         <v>330</v>
       </c>
-      <c r="M2" s="217"/>
-      <c r="N2" s="218"/>
-      <c r="O2" s="216" t="s">
+      <c r="M2" s="220"/>
+      <c r="N2" s="221"/>
+      <c r="O2" s="219" t="s">
         <v>328</v>
       </c>
-      <c r="P2" s="217"/>
-      <c r="Q2" s="218"/>
-      <c r="R2" s="216" t="s">
+      <c r="P2" s="220"/>
+      <c r="Q2" s="221"/>
+      <c r="R2" s="219" t="s">
         <v>335</v>
       </c>
-      <c r="S2" s="217"/>
-      <c r="T2" s="218"/>
-      <c r="U2" s="216" t="s">
+      <c r="S2" s="220"/>
+      <c r="T2" s="221"/>
+      <c r="U2" s="219" t="s">
         <v>320</v>
       </c>
-      <c r="V2" s="217"/>
-      <c r="W2" s="218"/>
-      <c r="X2" s="216" t="s">
+      <c r="V2" s="220"/>
+      <c r="W2" s="221"/>
+      <c r="X2" s="219" t="s">
         <v>337</v>
       </c>
-      <c r="Y2" s="217"/>
-      <c r="Z2" s="218"/>
-      <c r="AA2" s="216" t="s">
+      <c r="Y2" s="220"/>
+      <c r="Z2" s="221"/>
+      <c r="AA2" s="219" t="s">
         <v>334</v>
       </c>
-      <c r="AB2" s="217"/>
-      <c r="AC2" s="218"/>
-      <c r="AD2" s="216" t="s">
+      <c r="AB2" s="220"/>
+      <c r="AC2" s="221"/>
+      <c r="AD2" s="219" t="s">
         <v>321</v>
       </c>
-      <c r="AE2" s="217"/>
-      <c r="AF2" s="218"/>
-      <c r="AG2" s="216" t="s">
+      <c r="AE2" s="220"/>
+      <c r="AF2" s="221"/>
+      <c r="AG2" s="219" t="s">
         <v>347</v>
       </c>
-      <c r="AH2" s="217"/>
-      <c r="AI2" s="218"/>
-      <c r="AJ2" s="216" t="s">
+      <c r="AH2" s="220"/>
+      <c r="AI2" s="221"/>
+      <c r="AJ2" s="219" t="s">
         <v>324</v>
       </c>
-      <c r="AK2" s="217"/>
-      <c r="AL2" s="218"/>
-      <c r="AM2" s="216" t="s">
+      <c r="AK2" s="220"/>
+      <c r="AL2" s="221"/>
+      <c r="AM2" s="219" t="s">
         <v>323</v>
       </c>
-      <c r="AN2" s="217"/>
-      <c r="AO2" s="218"/>
-      <c r="AP2" s="216" t="s">
+      <c r="AN2" s="220"/>
+      <c r="AO2" s="221"/>
+      <c r="AP2" s="219" t="s">
         <v>332</v>
       </c>
-      <c r="AQ2" s="217"/>
-      <c r="AR2" s="218"/>
-      <c r="AS2" s="216" t="s">
+      <c r="AQ2" s="220"/>
+      <c r="AR2" s="221"/>
+      <c r="AS2" s="219" t="s">
         <v>329</v>
       </c>
-      <c r="AT2" s="217"/>
-      <c r="AU2" s="218"/>
-      <c r="AV2" s="216" t="s">
+      <c r="AT2" s="220"/>
+      <c r="AU2" s="221"/>
+      <c r="AV2" s="219" t="s">
         <v>336</v>
       </c>
-      <c r="AW2" s="217"/>
-      <c r="AX2" s="218"/>
-      <c r="AY2" s="216" t="s">
+      <c r="AW2" s="220"/>
+      <c r="AX2" s="221"/>
+      <c r="AY2" s="219" t="s">
         <v>305</v>
       </c>
-      <c r="AZ2" s="217"/>
-      <c r="BA2" s="218"/>
-      <c r="BB2" s="216" t="s">
+      <c r="AZ2" s="220"/>
+      <c r="BA2" s="221"/>
+      <c r="BB2" s="219" t="s">
         <v>326</v>
       </c>
-      <c r="BC2" s="217"/>
-      <c r="BD2" s="218"/>
-      <c r="BE2" s="216" t="s">
+      <c r="BC2" s="220"/>
+      <c r="BD2" s="221"/>
+      <c r="BE2" s="219" t="s">
         <v>325</v>
       </c>
-      <c r="BF2" s="217"/>
-      <c r="BG2" s="218"/>
-      <c r="BH2" s="216" t="s">
+      <c r="BF2" s="220"/>
+      <c r="BG2" s="221"/>
+      <c r="BH2" s="219" t="s">
         <v>348</v>
       </c>
-      <c r="BI2" s="217"/>
-      <c r="BJ2" s="218"/>
-      <c r="BK2" s="216" t="s">
+      <c r="BI2" s="220"/>
+      <c r="BJ2" s="221"/>
+      <c r="BK2" s="219" t="s">
         <v>332</v>
       </c>
-      <c r="BL2" s="217"/>
-      <c r="BM2" s="218"/>
-      <c r="BN2" s="216" t="s">
+      <c r="BL2" s="220"/>
+      <c r="BM2" s="221"/>
+      <c r="BN2" s="219" t="s">
         <v>347</v>
       </c>
-      <c r="BO2" s="217"/>
-      <c r="BP2" s="218"/>
-      <c r="BQ2" s="216" t="s">
+      <c r="BO2" s="220"/>
+      <c r="BP2" s="221"/>
+      <c r="BQ2" s="219" t="s">
         <v>324</v>
       </c>
-      <c r="BR2" s="217"/>
-      <c r="BS2" s="218"/>
-      <c r="BT2" s="216" t="s">
+      <c r="BR2" s="220"/>
+      <c r="BS2" s="221"/>
+      <c r="BT2" s="219" t="s">
         <v>323</v>
       </c>
-      <c r="BU2" s="217"/>
-      <c r="BV2" s="218"/>
-      <c r="BW2" s="216" t="s">
+      <c r="BU2" s="220"/>
+      <c r="BV2" s="221"/>
+      <c r="BW2" s="219" t="s">
         <v>321</v>
       </c>
-      <c r="BX2" s="217"/>
-      <c r="BY2" s="218"/>
-      <c r="BZ2" s="216" t="s">
+      <c r="BX2" s="220"/>
+      <c r="BY2" s="221"/>
+      <c r="BZ2" s="219" t="s">
         <v>348</v>
       </c>
-      <c r="CA2" s="217"/>
-      <c r="CB2" s="218"/>
-      <c r="CC2" s="216" t="s">
+      <c r="CA2" s="220"/>
+      <c r="CB2" s="221"/>
+      <c r="CC2" s="219" t="s">
         <v>325</v>
       </c>
-      <c r="CD2" s="217"/>
-      <c r="CE2" s="218"/>
-      <c r="CF2" s="216" t="s">
+      <c r="CD2" s="220"/>
+      <c r="CE2" s="221"/>
+      <c r="CF2" s="219" t="s">
         <v>305</v>
       </c>
-      <c r="CG2" s="217"/>
-      <c r="CH2" s="218"/>
-      <c r="CI2" s="216" t="s">
+      <c r="CG2" s="220"/>
+      <c r="CH2" s="221"/>
+      <c r="CI2" s="219" t="s">
         <v>326</v>
       </c>
-      <c r="CJ2" s="217"/>
-      <c r="CK2" s="218"/>
-      <c r="CL2" s="216" t="s">
+      <c r="CJ2" s="220"/>
+      <c r="CK2" s="221"/>
+      <c r="CL2" s="219" t="s">
         <v>330</v>
       </c>
-      <c r="CM2" s="217"/>
-      <c r="CN2" s="218"/>
-      <c r="CO2" s="216" t="s">
+      <c r="CM2" s="220"/>
+      <c r="CN2" s="221"/>
+      <c r="CO2" s="219" t="s">
         <v>328</v>
       </c>
-      <c r="CP2" s="217"/>
-      <c r="CQ2" s="218"/>
-      <c r="CR2" s="216" t="s">
+      <c r="CP2" s="220"/>
+      <c r="CQ2" s="221"/>
+      <c r="CR2" s="219" t="s">
         <v>346</v>
       </c>
-      <c r="CS2" s="217"/>
-      <c r="CT2" s="218"/>
-      <c r="CU2" s="216" t="s">
+      <c r="CS2" s="220"/>
+      <c r="CT2" s="221"/>
+      <c r="CU2" s="219" t="s">
         <v>331</v>
       </c>
-      <c r="CV2" s="217"/>
-      <c r="CW2" s="218"/>
-      <c r="CX2" s="216" t="s">
+      <c r="CV2" s="220"/>
+      <c r="CW2" s="221"/>
+      <c r="CX2" s="219" t="s">
         <v>336</v>
       </c>
-      <c r="CY2" s="217"/>
-      <c r="CZ2" s="218"/>
-      <c r="DA2" s="216" t="s">
+      <c r="CY2" s="220"/>
+      <c r="CZ2" s="221"/>
+      <c r="DA2" s="219" t="s">
         <v>329</v>
       </c>
-      <c r="DB2" s="217"/>
-      <c r="DC2" s="218"/>
-      <c r="DD2" s="216" t="s">
+      <c r="DB2" s="220"/>
+      <c r="DC2" s="221"/>
+      <c r="DD2" s="219" t="s">
         <v>320</v>
       </c>
-      <c r="DE2" s="217"/>
-      <c r="DF2" s="218"/>
-      <c r="DG2" s="216" t="s">
+      <c r="DE2" s="220"/>
+      <c r="DF2" s="221"/>
+      <c r="DG2" s="219" t="s">
         <v>337</v>
       </c>
-      <c r="DH2" s="217"/>
-      <c r="DI2" s="218"/>
-      <c r="DJ2" s="216" t="s">
+      <c r="DH2" s="220"/>
+      <c r="DI2" s="221"/>
+      <c r="DJ2" s="219" t="s">
         <v>334</v>
       </c>
-      <c r="DK2" s="217"/>
-      <c r="DL2" s="218"/>
-      <c r="DM2" s="216" t="s">
+      <c r="DK2" s="220"/>
+      <c r="DL2" s="221"/>
+      <c r="DM2" s="219" t="s">
         <v>335</v>
       </c>
-      <c r="DN2" s="217"/>
-      <c r="DO2" s="218"/>
+      <c r="DN2" s="220"/>
+      <c r="DO2" s="221"/>
     </row>
     <row r="3" spans="1:119" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -38121,9 +38125,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="223"/>
-      <c r="D3" s="223"/>
-      <c r="E3" s="224"/>
+      <c r="C3" s="224"/>
+      <c r="D3" s="224"/>
+      <c r="E3" s="223"/>
       <c r="F3" s="160" t="s">
         <v>393</v>
       </c>
@@ -43884,69 +43888,6 @@
     </row>
   </sheetData>
   <mergeCells count="79">
-    <mergeCell ref="DM1:DO1"/>
-    <mergeCell ref="DM2:DO2"/>
-    <mergeCell ref="DA1:DC1"/>
-    <mergeCell ref="DA2:DC2"/>
-    <mergeCell ref="DD1:DF1"/>
-    <mergeCell ref="DD2:DF2"/>
-    <mergeCell ref="DG1:DI1"/>
-    <mergeCell ref="DG2:DI2"/>
-    <mergeCell ref="CU1:CW1"/>
-    <mergeCell ref="CU2:CW2"/>
-    <mergeCell ref="CX1:CZ1"/>
-    <mergeCell ref="CX2:CZ2"/>
-    <mergeCell ref="DJ1:DL1"/>
-    <mergeCell ref="DJ2:DL2"/>
-    <mergeCell ref="CL1:CN1"/>
-    <mergeCell ref="CL2:CN2"/>
-    <mergeCell ref="CO1:CQ1"/>
-    <mergeCell ref="CO2:CQ2"/>
-    <mergeCell ref="CR1:CT1"/>
-    <mergeCell ref="CR2:CT2"/>
-    <mergeCell ref="CC1:CE1"/>
-    <mergeCell ref="CC2:CE2"/>
-    <mergeCell ref="CF1:CH1"/>
-    <mergeCell ref="CF2:CH2"/>
-    <mergeCell ref="CI1:CK1"/>
-    <mergeCell ref="CI2:CK2"/>
-    <mergeCell ref="BT1:BV1"/>
-    <mergeCell ref="BT2:BV2"/>
-    <mergeCell ref="BW1:BY1"/>
-    <mergeCell ref="BW2:BY2"/>
-    <mergeCell ref="BZ1:CB1"/>
-    <mergeCell ref="BZ2:CB2"/>
-    <mergeCell ref="BK1:BM1"/>
-    <mergeCell ref="BK2:BM2"/>
-    <mergeCell ref="BN1:BP1"/>
-    <mergeCell ref="BN2:BP2"/>
-    <mergeCell ref="BQ1:BS1"/>
-    <mergeCell ref="BQ2:BS2"/>
-    <mergeCell ref="AS1:AU1"/>
-    <mergeCell ref="AS2:AU2"/>
-    <mergeCell ref="AV1:AX1"/>
-    <mergeCell ref="AV2:AX2"/>
-    <mergeCell ref="BH1:BJ1"/>
-    <mergeCell ref="BH2:BJ2"/>
-    <mergeCell ref="AY2:BA2"/>
-    <mergeCell ref="BB2:BD2"/>
-    <mergeCell ref="BE2:BG2"/>
-    <mergeCell ref="AJ1:AL1"/>
-    <mergeCell ref="AJ2:AL2"/>
-    <mergeCell ref="AM1:AO1"/>
-    <mergeCell ref="AM2:AO2"/>
-    <mergeCell ref="AP2:AR2"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
     <mergeCell ref="AD2:AF2"/>
     <mergeCell ref="AG2:AI2"/>
     <mergeCell ref="BB1:BD1"/>
@@ -43963,6 +43904,69 @@
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="X1:Z1"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="AJ1:AL1"/>
+    <mergeCell ref="AJ2:AL2"/>
+    <mergeCell ref="AM1:AO1"/>
+    <mergeCell ref="AM2:AO2"/>
+    <mergeCell ref="AP2:AR2"/>
+    <mergeCell ref="AS1:AU1"/>
+    <mergeCell ref="AS2:AU2"/>
+    <mergeCell ref="AV1:AX1"/>
+    <mergeCell ref="AV2:AX2"/>
+    <mergeCell ref="BH1:BJ1"/>
+    <mergeCell ref="BH2:BJ2"/>
+    <mergeCell ref="AY2:BA2"/>
+    <mergeCell ref="BB2:BD2"/>
+    <mergeCell ref="BE2:BG2"/>
+    <mergeCell ref="BK1:BM1"/>
+    <mergeCell ref="BK2:BM2"/>
+    <mergeCell ref="BN1:BP1"/>
+    <mergeCell ref="BN2:BP2"/>
+    <mergeCell ref="BQ1:BS1"/>
+    <mergeCell ref="BQ2:BS2"/>
+    <mergeCell ref="BT1:BV1"/>
+    <mergeCell ref="BT2:BV2"/>
+    <mergeCell ref="BW1:BY1"/>
+    <mergeCell ref="BW2:BY2"/>
+    <mergeCell ref="BZ1:CB1"/>
+    <mergeCell ref="BZ2:CB2"/>
+    <mergeCell ref="CC1:CE1"/>
+    <mergeCell ref="CC2:CE2"/>
+    <mergeCell ref="CF1:CH1"/>
+    <mergeCell ref="CF2:CH2"/>
+    <mergeCell ref="CI1:CK1"/>
+    <mergeCell ref="CI2:CK2"/>
+    <mergeCell ref="CL1:CN1"/>
+    <mergeCell ref="CL2:CN2"/>
+    <mergeCell ref="CO1:CQ1"/>
+    <mergeCell ref="CO2:CQ2"/>
+    <mergeCell ref="CR1:CT1"/>
+    <mergeCell ref="CR2:CT2"/>
+    <mergeCell ref="CU1:CW1"/>
+    <mergeCell ref="CU2:CW2"/>
+    <mergeCell ref="CX1:CZ1"/>
+    <mergeCell ref="CX2:CZ2"/>
+    <mergeCell ref="DJ1:DL1"/>
+    <mergeCell ref="DJ2:DL2"/>
+    <mergeCell ref="DM1:DO1"/>
+    <mergeCell ref="DM2:DO2"/>
+    <mergeCell ref="DA1:DC1"/>
+    <mergeCell ref="DA2:DC2"/>
+    <mergeCell ref="DD1:DF1"/>
+    <mergeCell ref="DD2:DF2"/>
+    <mergeCell ref="DG1:DI1"/>
+    <mergeCell ref="DG2:DI2"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:DO38">
     <cfRule type="cellIs" dxfId="18" priority="1" operator="between">
@@ -43998,41 +44002,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="237" t="s">
+      <c r="C1" s="234" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="237" t="s">
+      <c r="D1" s="234" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="237" t="s">
+      <c r="E1" s="234" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="228" t="s">
+      <c r="F1" s="225" t="s">
         <v>302</v>
       </c>
-      <c r="G1" s="229"/>
-      <c r="H1" s="229"/>
-      <c r="I1" s="229"/>
-      <c r="J1" s="229"/>
-      <c r="K1" s="229"/>
-      <c r="L1" s="229"/>
-      <c r="M1" s="229"/>
-      <c r="N1" s="229"/>
-      <c r="O1" s="229"/>
-      <c r="P1" s="229"/>
-      <c r="Q1" s="229"/>
-      <c r="R1" s="229"/>
-      <c r="S1" s="229"/>
-      <c r="T1" s="229"/>
-      <c r="U1" s="229"/>
-      <c r="V1" s="229"/>
-      <c r="W1" s="229"/>
-      <c r="X1" s="229"/>
-      <c r="Y1" s="229"/>
-      <c r="Z1" s="229"/>
-      <c r="AA1" s="229"/>
-      <c r="AB1" s="229"/>
-      <c r="AC1" s="230"/>
+      <c r="G1" s="226"/>
+      <c r="H1" s="226"/>
+      <c r="I1" s="226"/>
+      <c r="J1" s="226"/>
+      <c r="K1" s="226"/>
+      <c r="L1" s="226"/>
+      <c r="M1" s="226"/>
+      <c r="N1" s="226"/>
+      <c r="O1" s="226"/>
+      <c r="P1" s="226"/>
+      <c r="Q1" s="226"/>
+      <c r="R1" s="226"/>
+      <c r="S1" s="226"/>
+      <c r="T1" s="226"/>
+      <c r="U1" s="226"/>
+      <c r="V1" s="226"/>
+      <c r="W1" s="226"/>
+      <c r="X1" s="226"/>
+      <c r="Y1" s="226"/>
+      <c r="Z1" s="226"/>
+      <c r="AA1" s="226"/>
+      <c r="AB1" s="226"/>
+      <c r="AC1" s="227"/>
       <c r="AD1" s="240" t="s">
         <v>281</v>
       </c>
@@ -44041,95 +44045,95 @@
       <c r="AG1" s="241"/>
       <c r="AH1" s="241"/>
       <c r="AI1" s="242"/>
-      <c r="AJ1" s="228" t="s">
+      <c r="AJ1" s="225" t="s">
         <v>282</v>
       </c>
-      <c r="AK1" s="229"/>
-      <c r="AL1" s="229"/>
-      <c r="AM1" s="229"/>
-      <c r="AN1" s="229"/>
-      <c r="AO1" s="230"/>
-      <c r="AP1" s="231" t="s">
+      <c r="AK1" s="226"/>
+      <c r="AL1" s="226"/>
+      <c r="AM1" s="226"/>
+      <c r="AN1" s="226"/>
+      <c r="AO1" s="227"/>
+      <c r="AP1" s="228" t="s">
         <v>283</v>
       </c>
-      <c r="AQ1" s="232"/>
-      <c r="AR1" s="232"/>
-      <c r="AS1" s="232"/>
-      <c r="AT1" s="232"/>
-      <c r="AU1" s="233"/>
-      <c r="AV1" s="234" t="s">
+      <c r="AQ1" s="229"/>
+      <c r="AR1" s="229"/>
+      <c r="AS1" s="229"/>
+      <c r="AT1" s="229"/>
+      <c r="AU1" s="230"/>
+      <c r="AV1" s="231" t="s">
         <v>86</v>
       </c>
-      <c r="AW1" s="235"/>
-      <c r="AX1" s="236"/>
+      <c r="AW1" s="232"/>
+      <c r="AX1" s="233"/>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="238"/>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="225" t="s">
+      <c r="C2" s="235"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="237" t="s">
         <v>458</v>
       </c>
-      <c r="G2" s="226"/>
-      <c r="H2" s="227"/>
-      <c r="I2" s="225" t="s">
+      <c r="G2" s="238"/>
+      <c r="H2" s="239"/>
+      <c r="I2" s="237" t="s">
         <v>461</v>
       </c>
-      <c r="J2" s="226"/>
-      <c r="K2" s="227"/>
-      <c r="L2" s="225" t="s">
+      <c r="J2" s="238"/>
+      <c r="K2" s="239"/>
+      <c r="L2" s="237" t="s">
         <v>462</v>
       </c>
-      <c r="M2" s="226"/>
-      <c r="N2" s="227"/>
-      <c r="O2" s="225" t="s">
+      <c r="M2" s="238"/>
+      <c r="N2" s="239"/>
+      <c r="O2" s="237" t="s">
         <v>463</v>
       </c>
-      <c r="P2" s="226"/>
-      <c r="Q2" s="227"/>
-      <c r="R2" s="225" t="s">
+      <c r="P2" s="238"/>
+      <c r="Q2" s="239"/>
+      <c r="R2" s="237" t="s">
         <v>464</v>
       </c>
-      <c r="S2" s="226"/>
-      <c r="T2" s="227"/>
-      <c r="U2" s="225" t="s">
+      <c r="S2" s="238"/>
+      <c r="T2" s="239"/>
+      <c r="U2" s="237" t="s">
         <v>465</v>
       </c>
-      <c r="V2" s="226"/>
-      <c r="W2" s="227"/>
-      <c r="X2" s="225" t="s">
+      <c r="V2" s="238"/>
+      <c r="W2" s="239"/>
+      <c r="X2" s="237" t="s">
         <v>466</v>
       </c>
-      <c r="Y2" s="226"/>
-      <c r="Z2" s="227"/>
-      <c r="AA2" s="225" t="s">
+      <c r="Y2" s="238"/>
+      <c r="Z2" s="239"/>
+      <c r="AA2" s="237" t="s">
         <v>467</v>
       </c>
-      <c r="AB2" s="226"/>
-      <c r="AC2" s="226"/>
-      <c r="AD2" s="225"/>
-      <c r="AE2" s="226"/>
-      <c r="AF2" s="227"/>
-      <c r="AG2" s="225"/>
-      <c r="AH2" s="226"/>
-      <c r="AI2" s="227"/>
-      <c r="AJ2" s="225"/>
-      <c r="AK2" s="226"/>
-      <c r="AL2" s="227"/>
-      <c r="AM2" s="225"/>
-      <c r="AN2" s="226"/>
-      <c r="AO2" s="227"/>
-      <c r="AP2" s="225"/>
-      <c r="AQ2" s="226"/>
-      <c r="AR2" s="227"/>
-      <c r="AS2" s="225"/>
-      <c r="AT2" s="226"/>
-      <c r="AU2" s="227"/>
-      <c r="AV2" s="225"/>
-      <c r="AW2" s="226"/>
-      <c r="AX2" s="227"/>
+      <c r="AB2" s="238"/>
+      <c r="AC2" s="238"/>
+      <c r="AD2" s="237"/>
+      <c r="AE2" s="238"/>
+      <c r="AF2" s="239"/>
+      <c r="AG2" s="237"/>
+      <c r="AH2" s="238"/>
+      <c r="AI2" s="239"/>
+      <c r="AJ2" s="237"/>
+      <c r="AK2" s="238"/>
+      <c r="AL2" s="239"/>
+      <c r="AM2" s="237"/>
+      <c r="AN2" s="238"/>
+      <c r="AO2" s="239"/>
+      <c r="AP2" s="237"/>
+      <c r="AQ2" s="238"/>
+      <c r="AR2" s="239"/>
+      <c r="AS2" s="237"/>
+      <c r="AT2" s="238"/>
+      <c r="AU2" s="239"/>
+      <c r="AV2" s="237"/>
+      <c r="AW2" s="238"/>
+      <c r="AX2" s="239"/>
     </row>
     <row r="3" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -44138,9 +44142,9 @@
       <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="239"/>
-      <c r="D3" s="239"/>
-      <c r="E3" s="239"/>
+      <c r="C3" s="236"/>
+      <c r="D3" s="236"/>
+      <c r="E3" s="236"/>
       <c r="F3" s="169" t="s">
         <v>393</v>
       </c>
@@ -44286,7 +44290,7 @@
       </c>
       <c r="C4" s="58">
         <f>SUM(F4,I4,L4,O4,R4,X4,AA4,AD4,U4,AG4,AJ4,AM4,AP4,AS4,AV4)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="58">
         <f t="shared" ref="D4:E4" si="0">SUM(G4,J4,M4,P4,S4,Y4,AB4,AE4,V4,AH4,AK4,AN4,AQ4,AT4,AW4)</f>
@@ -44306,7 +44310,9 @@
       </c>
       <c r="J4" s="36"/>
       <c r="K4" s="53"/>
-      <c r="L4" s="52"/>
+      <c r="L4" s="52">
+        <v>1</v>
+      </c>
       <c r="M4" s="36"/>
       <c r="N4" s="53"/>
       <c r="O4" s="52"/>
@@ -44621,7 +44627,7 @@
       </c>
       <c r="C9" s="58">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" s="58">
         <f t="shared" si="2"/>
@@ -44641,7 +44647,9 @@
       </c>
       <c r="J9" s="36"/>
       <c r="K9" s="53"/>
-      <c r="L9" s="52"/>
+      <c r="L9" s="52">
+        <v>1</v>
+      </c>
       <c r="M9" s="36"/>
       <c r="N9" s="53"/>
       <c r="O9" s="52"/>
@@ -44690,7 +44698,7 @@
       </c>
       <c r="C10" s="58">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" s="58">
         <f t="shared" si="2"/>
@@ -44714,7 +44722,9 @@
       <c r="K10" s="53">
         <v>1</v>
       </c>
-      <c r="L10" s="52"/>
+      <c r="L10" s="52">
+        <v>1</v>
+      </c>
       <c r="M10" s="36"/>
       <c r="N10" s="53"/>
       <c r="O10" s="52"/>
@@ -44763,7 +44773,7 @@
       </c>
       <c r="C11" s="58">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" s="58">
         <f t="shared" si="2"/>
@@ -44771,7 +44781,7 @@
       </c>
       <c r="E11" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="52">
         <v>1</v>
@@ -44785,9 +44795,13 @@
       </c>
       <c r="J11" s="36"/>
       <c r="K11" s="53"/>
-      <c r="L11" s="52"/>
+      <c r="L11" s="52">
+        <v>1</v>
+      </c>
       <c r="M11" s="36"/>
-      <c r="N11" s="53"/>
+      <c r="N11" s="53">
+        <v>1</v>
+      </c>
       <c r="O11" s="52"/>
       <c r="P11" s="36"/>
       <c r="Q11" s="53"/>
@@ -44834,11 +44848,11 @@
       </c>
       <c r="C12" s="58">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" s="58">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" s="58">
         <f t="shared" si="3"/>
@@ -44856,8 +44870,12 @@
         <v>1</v>
       </c>
       <c r="K12" s="53"/>
-      <c r="L12" s="52"/>
-      <c r="M12" s="36"/>
+      <c r="L12" s="52">
+        <v>1</v>
+      </c>
+      <c r="M12" s="36">
+        <v>1</v>
+      </c>
       <c r="N12" s="53"/>
       <c r="O12" s="52"/>
       <c r="P12" s="36"/>
@@ -44905,7 +44923,7 @@
       </c>
       <c r="C13" s="58">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" s="58">
         <f t="shared" si="2"/>
@@ -44925,7 +44943,9 @@
         <v>1</v>
       </c>
       <c r="K13" s="53"/>
-      <c r="L13" s="52"/>
+      <c r="L13" s="52">
+        <v>1</v>
+      </c>
       <c r="M13" s="36"/>
       <c r="N13" s="53"/>
       <c r="O13" s="52"/>
@@ -45039,7 +45059,7 @@
       </c>
       <c r="C15" s="58">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" s="58">
         <f t="shared" si="2"/>
@@ -45047,7 +45067,7 @@
       </c>
       <c r="E15" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="52">
         <v>1</v>
@@ -45059,9 +45079,13 @@
       </c>
       <c r="J15" s="36"/>
       <c r="K15" s="53"/>
-      <c r="L15" s="52"/>
+      <c r="L15" s="52">
+        <v>1</v>
+      </c>
       <c r="M15" s="36"/>
-      <c r="N15" s="53"/>
+      <c r="N15" s="53">
+        <v>1</v>
+      </c>
       <c r="O15" s="52"/>
       <c r="P15" s="36"/>
       <c r="Q15" s="53"/>
@@ -45108,7 +45132,7 @@
       </c>
       <c r="C16" s="58">
         <f t="shared" ref="C16:C28" si="4">SUM(F16,I16,L16,O16,R16,X16,AA16,AD16,U16,AG16,AJ16,AM16,AP16,AS16,AV16)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" s="58">
         <f t="shared" ref="D16:D28" si="5">SUM(G16,J16,M16,P16,S16,Y16,AB16,AE16,V16,AH16,AK16,AN16,AQ16,AT16,AW16)</f>
@@ -45128,7 +45152,9 @@
       </c>
       <c r="J16" s="36"/>
       <c r="K16" s="53"/>
-      <c r="L16" s="52"/>
+      <c r="L16" s="52">
+        <v>1</v>
+      </c>
       <c r="M16" s="36"/>
       <c r="N16" s="53"/>
       <c r="O16" s="52"/>
@@ -45246,7 +45272,7 @@
       </c>
       <c r="C18" s="58">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" s="58">
         <f t="shared" si="5"/>
@@ -45268,7 +45294,9 @@
       <c r="K18" s="53">
         <v>1</v>
       </c>
-      <c r="L18" s="52"/>
+      <c r="L18" s="52">
+        <v>1</v>
+      </c>
       <c r="M18" s="36"/>
       <c r="N18" s="53"/>
       <c r="O18" s="52"/>
@@ -45382,7 +45410,7 @@
       </c>
       <c r="C20" s="58">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" s="58">
         <f t="shared" si="5"/>
@@ -45402,7 +45430,9 @@
       </c>
       <c r="J20" s="36"/>
       <c r="K20" s="53"/>
-      <c r="L20" s="52"/>
+      <c r="L20" s="52">
+        <v>1</v>
+      </c>
       <c r="M20" s="36"/>
       <c r="N20" s="53"/>
       <c r="O20" s="52"/>
@@ -45451,7 +45481,7 @@
       </c>
       <c r="C21" s="58">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D21" s="58">
         <f t="shared" si="5"/>
@@ -45473,7 +45503,9 @@
       <c r="K21" s="53">
         <v>1</v>
       </c>
-      <c r="L21" s="52"/>
+      <c r="L21" s="52">
+        <v>1</v>
+      </c>
       <c r="M21" s="36"/>
       <c r="N21" s="53"/>
       <c r="O21" s="52"/>
@@ -45587,7 +45619,7 @@
       </c>
       <c r="C23" s="58">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" s="58">
         <f t="shared" si="5"/>
@@ -45603,7 +45635,9 @@
       <c r="I23" s="52"/>
       <c r="J23" s="36"/>
       <c r="K23" s="53"/>
-      <c r="L23" s="52"/>
+      <c r="L23" s="52">
+        <v>1</v>
+      </c>
       <c r="M23" s="36"/>
       <c r="N23" s="53"/>
       <c r="O23" s="52"/>
@@ -45784,7 +45818,7 @@
       </c>
       <c r="C26" s="58">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D26" s="58">
         <f t="shared" si="5"/>
@@ -45804,7 +45838,9 @@
       </c>
       <c r="J26" s="36"/>
       <c r="K26" s="53"/>
-      <c r="L26" s="52"/>
+      <c r="L26" s="52">
+        <v>1</v>
+      </c>
       <c r="M26" s="36"/>
       <c r="N26" s="53"/>
       <c r="O26" s="52"/>
@@ -45918,11 +45954,11 @@
       </c>
       <c r="C28" s="58">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D28" s="58">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" s="58">
         <f t="shared" si="6"/>
@@ -45938,8 +45974,12 @@
       </c>
       <c r="J28" s="36"/>
       <c r="K28" s="53"/>
-      <c r="L28" s="52"/>
-      <c r="M28" s="36"/>
+      <c r="L28" s="52">
+        <v>1</v>
+      </c>
+      <c r="M28" s="36">
+        <v>1</v>
+      </c>
       <c r="N28" s="53"/>
       <c r="O28" s="52"/>
       <c r="P28" s="36"/>
@@ -46247,7 +46287,7 @@
       </c>
       <c r="C33" s="58">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" s="58">
         <f t="shared" si="9"/>
@@ -46265,7 +46305,9 @@
       </c>
       <c r="J33" s="165"/>
       <c r="K33" s="50"/>
-      <c r="L33" s="49"/>
+      <c r="L33" s="49">
+        <v>1</v>
+      </c>
       <c r="M33" s="165"/>
       <c r="N33" s="50"/>
       <c r="O33" s="49"/>
@@ -46659,15 +46701,15 @@
       </c>
       <c r="L39" s="171">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M39" s="172">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N39" s="173">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O39" s="171">
         <f t="shared" si="11"/>
@@ -46816,6 +46858,13 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="F1:AC1"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
+    <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="AJ1:AO1"/>
     <mergeCell ref="AP1:AU1"/>
     <mergeCell ref="AV1:AX1"/>
@@ -46832,13 +46881,6 @@
     <mergeCell ref="AD1:AI1"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="I2:K2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="F1:AC1"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:AW32">
     <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
@@ -46873,70 +46915,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C1" s="237" t="s">
+      <c r="C1" s="234" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="237" t="s">
+      <c r="D1" s="234" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="237" t="s">
+      <c r="E1" s="234" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="267" t="s">
+      <c r="F1" s="274" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="268"/>
-      <c r="H1" s="269"/>
-      <c r="I1" s="270" t="s">
+      <c r="G1" s="275"/>
+      <c r="H1" s="276"/>
+      <c r="I1" s="277" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="271"/>
-      <c r="K1" s="272"/>
-      <c r="L1" s="274" t="s">
+      <c r="J1" s="278"/>
+      <c r="K1" s="279"/>
+      <c r="L1" s="244" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="275"/>
-      <c r="N1" s="276"/>
-      <c r="O1" s="277" t="s">
+      <c r="M1" s="245"/>
+      <c r="N1" s="246"/>
+      <c r="O1" s="247" t="s">
         <v>199</v>
       </c>
-      <c r="P1" s="278"/>
-      <c r="Q1" s="279"/>
-      <c r="R1" s="243" t="s">
+      <c r="P1" s="248"/>
+      <c r="Q1" s="249"/>
+      <c r="R1" s="250" t="s">
         <v>200</v>
       </c>
-      <c r="S1" s="244"/>
-      <c r="T1" s="245"/>
-      <c r="U1" s="246" t="s">
+      <c r="S1" s="251"/>
+      <c r="T1" s="252"/>
+      <c r="U1" s="253" t="s">
         <v>306</v>
       </c>
-      <c r="V1" s="247"/>
-      <c r="W1" s="248"/>
+      <c r="V1" s="254"/>
+      <c r="W1" s="255"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="238"/>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="249"/>
-      <c r="G2" s="250"/>
-      <c r="H2" s="251"/>
-      <c r="I2" s="264"/>
-      <c r="J2" s="265"/>
-      <c r="K2" s="266"/>
-      <c r="L2" s="261"/>
-      <c r="M2" s="262"/>
-      <c r="N2" s="263"/>
-      <c r="O2" s="258"/>
-      <c r="P2" s="259"/>
-      <c r="Q2" s="260"/>
-      <c r="R2" s="255"/>
-      <c r="S2" s="256"/>
-      <c r="T2" s="257"/>
-      <c r="U2" s="252"/>
-      <c r="V2" s="253"/>
-      <c r="W2" s="254"/>
+      <c r="C2" s="235"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="256"/>
+      <c r="G2" s="257"/>
+      <c r="H2" s="258"/>
+      <c r="I2" s="271"/>
+      <c r="J2" s="272"/>
+      <c r="K2" s="273"/>
+      <c r="L2" s="268"/>
+      <c r="M2" s="269"/>
+      <c r="N2" s="270"/>
+      <c r="O2" s="265"/>
+      <c r="P2" s="266"/>
+      <c r="Q2" s="267"/>
+      <c r="R2" s="262"/>
+      <c r="S2" s="263"/>
+      <c r="T2" s="264"/>
+      <c r="U2" s="259"/>
+      <c r="V2" s="260"/>
+      <c r="W2" s="261"/>
     </row>
     <row r="3" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -46945,9 +46987,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="273"/>
-      <c r="D3" s="273"/>
-      <c r="E3" s="273"/>
+      <c r="C3" s="243"/>
+      <c r="D3" s="243"/>
+      <c r="E3" s="243"/>
       <c r="F3" s="188" t="s">
         <v>393</v>
       </c>
@@ -48409,11 +48451,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="O1:Q1"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="F2:H2"/>
@@ -48424,6 +48461,11 @@
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="O1:Q1"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:W32">
     <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
@@ -48703,7 +48745,7 @@
       <c r="R6" s="26"/>
       <c r="S6" s="20">
         <f>'Apps &amp; Goals 26-27'!F4</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T6" s="20">
         <f>'Apps &amp; Goals 26-27'!G4</f>
@@ -48715,7 +48757,7 @@
       </c>
       <c r="V6" s="26">
         <f>S6+O6</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="W6" s="26">
         <f>T6+P6</f>
@@ -49668,7 +49710,7 @@
       <c r="R11" s="26"/>
       <c r="S11" s="20">
         <f>'Apps &amp; Goals 26-27'!F9</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T11" s="20">
         <f>'Apps &amp; Goals 26-27'!G9</f>
@@ -49680,7 +49722,7 @@
       </c>
       <c r="V11" s="26">
         <f t="shared" si="3"/>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="W11" s="26">
         <f t="shared" si="4"/>
@@ -49861,7 +49903,7 @@
       <c r="R12" s="26"/>
       <c r="S12" s="20">
         <f>'Apps &amp; Goals 26-27'!F10</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T12" s="20">
         <f>'Apps &amp; Goals 26-27'!G10</f>
@@ -49873,7 +49915,7 @@
       </c>
       <c r="V12" s="26">
         <f t="shared" si="3"/>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="W12" s="26">
         <f t="shared" si="4"/>
@@ -50054,7 +50096,7 @@
       <c r="R13" s="26"/>
       <c r="S13" s="20">
         <f>'Apps &amp; Goals 26-27'!F11</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T13" s="20">
         <f>'Apps &amp; Goals 26-27'!G11</f>
@@ -50062,11 +50104,11 @@
       </c>
       <c r="U13" s="20">
         <f>'Apps &amp; Goals 26-27'!H11</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="26">
         <f t="shared" si="3"/>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="W13" s="26">
         <f t="shared" si="4"/>
@@ -50074,7 +50116,7 @@
       </c>
       <c r="X13" s="26">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z13" s="23" t="s">
         <v>218</v>
@@ -50247,11 +50289,11 @@
       <c r="R14" s="26"/>
       <c r="S14" s="20">
         <f>'Apps &amp; Goals 26-27'!F12</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T14" s="20">
         <f>'Apps &amp; Goals 26-27'!G12</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U14" s="20">
         <f>'Apps &amp; Goals 26-27'!H12</f>
@@ -50259,11 +50301,11 @@
       </c>
       <c r="V14" s="26">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W14" s="26">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X14" s="26">
         <f t="shared" si="5"/>
@@ -50440,7 +50482,7 @@
       <c r="R15" s="26"/>
       <c r="S15" s="20">
         <f>'Apps &amp; Goals 26-27'!F13</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T15" s="20">
         <f>'Apps &amp; Goals 26-27'!G13</f>
@@ -50452,7 +50494,7 @@
       </c>
       <c r="V15" s="26">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W15" s="26">
         <f t="shared" si="4"/>
@@ -50826,7 +50868,7 @@
       <c r="R17" s="26"/>
       <c r="S17" s="20">
         <f>'Apps &amp; Goals 26-27'!F15</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T17" s="20">
         <f>'Apps &amp; Goals 26-27'!G15</f>
@@ -50834,11 +50876,11 @@
       </c>
       <c r="U17" s="20">
         <f>'Apps &amp; Goals 26-27'!H15</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="26">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W17" s="26">
         <f t="shared" si="4"/>
@@ -50846,7 +50888,7 @@
       </c>
       <c r="X17" s="26">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z17" s="57" t="s">
         <v>317</v>
@@ -51019,7 +51061,7 @@
       <c r="R18" s="26"/>
       <c r="S18" s="20">
         <f>'Apps &amp; Goals 26-27'!F16</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T18" s="20">
         <f>'Apps &amp; Goals 26-27'!G16</f>
@@ -51031,7 +51073,7 @@
       </c>
       <c r="V18" s="26">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W18" s="26">
         <f t="shared" si="4"/>
@@ -51405,7 +51447,7 @@
       <c r="R20" s="26"/>
       <c r="S20" s="20">
         <f>'Apps &amp; Goals 26-27'!F18</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T20" s="20">
         <f>'Apps &amp; Goals 26-27'!G18</f>
@@ -51417,7 +51459,7 @@
       </c>
       <c r="V20" s="26">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W20" s="26">
         <f t="shared" si="4"/>
@@ -51791,7 +51833,7 @@
       <c r="R22" s="26"/>
       <c r="S22" s="20">
         <f>'Apps &amp; Goals 26-27'!F20</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T22" s="20">
         <f>'Apps &amp; Goals 26-27'!G20</f>
@@ -51803,7 +51845,7 @@
       </c>
       <c r="V22" s="26">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="W22" s="26">
         <f t="shared" si="4"/>
@@ -51984,7 +52026,7 @@
       <c r="R23" s="26"/>
       <c r="S23" s="20">
         <f>'Apps &amp; Goals 26-27'!F21</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T23" s="20">
         <f>'Apps &amp; Goals 26-27'!G21</f>
@@ -51996,7 +52038,7 @@
       </c>
       <c r="V23" s="26">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="W23" s="26">
         <f t="shared" si="4"/>
@@ -52370,7 +52412,7 @@
       <c r="R25" s="26"/>
       <c r="S25" s="20">
         <f>'Apps &amp; Goals 26-27'!F23</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T25" s="20">
         <f>'Apps &amp; Goals 26-27'!G23</f>
@@ -52382,7 +52424,7 @@
       </c>
       <c r="V25" s="26">
         <f t="shared" si="3"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="W25" s="26">
         <f t="shared" si="4"/>
@@ -52949,7 +52991,7 @@
       <c r="R28" s="26"/>
       <c r="S28" s="20">
         <f>'Apps &amp; Goals 26-27'!F26</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T28" s="20">
         <f>'Apps &amp; Goals 26-27'!G26</f>
@@ -52961,7 +53003,7 @@
       </c>
       <c r="V28" s="26">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W28" s="26">
         <f t="shared" si="4"/>
@@ -53335,11 +53377,11 @@
       <c r="R30" s="26"/>
       <c r="S30" s="20">
         <f>'Apps &amp; Goals 26-27'!F28</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T30" s="20">
         <f>'Apps &amp; Goals 26-27'!G28</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U30" s="20">
         <f>'Apps &amp; Goals 26-27'!H28</f>
@@ -53347,11 +53389,11 @@
       </c>
       <c r="V30" s="26">
         <f t="shared" si="3"/>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="W30" s="26">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X30" s="26">
         <f t="shared" si="5"/>
@@ -54300,7 +54342,7 @@
       <c r="R35" s="26"/>
       <c r="S35" s="20">
         <f>'Apps &amp; Goals 26-27'!F33</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T35" s="20">
         <f>'Apps &amp; Goals 26-27'!G33</f>
@@ -54312,7 +54354,7 @@
       </c>
       <c r="V35" s="26">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="W35" s="26">
         <f t="shared" si="4"/>
@@ -55430,72 +55472,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C1" s="237" t="s">
+      <c r="C1" s="234" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="237" t="s">
+      <c r="D1" s="234" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="237" t="s">
+      <c r="E1" s="234" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="267" t="s">
+      <c r="F1" s="274" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="268"/>
-      <c r="H1" s="269"/>
-      <c r="I1" s="270" t="s">
+      <c r="G1" s="275"/>
+      <c r="H1" s="276"/>
+      <c r="I1" s="277" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="271"/>
-      <c r="K1" s="272"/>
-      <c r="L1" s="274" t="s">
+      <c r="J1" s="278"/>
+      <c r="K1" s="279"/>
+      <c r="L1" s="244" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="275"/>
-      <c r="N1" s="276"/>
-      <c r="O1" s="277" t="s">
+      <c r="M1" s="245"/>
+      <c r="N1" s="246"/>
+      <c r="O1" s="247" t="s">
         <v>199</v>
       </c>
-      <c r="P1" s="278"/>
-      <c r="Q1" s="279"/>
-      <c r="R1" s="243" t="s">
+      <c r="P1" s="248"/>
+      <c r="Q1" s="249"/>
+      <c r="R1" s="250" t="s">
         <v>200</v>
       </c>
-      <c r="S1" s="244"/>
-      <c r="T1" s="245"/>
-      <c r="U1" s="246" t="s">
+      <c r="S1" s="251"/>
+      <c r="T1" s="252"/>
+      <c r="U1" s="253" t="s">
         <v>306</v>
       </c>
-      <c r="V1" s="247"/>
-      <c r="W1" s="248"/>
+      <c r="V1" s="254"/>
+      <c r="W1" s="255"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="238"/>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="249" t="s">
+      <c r="C2" s="235"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="256" t="s">
         <v>432</v>
       </c>
-      <c r="G2" s="250"/>
-      <c r="H2" s="251"/>
-      <c r="I2" s="264"/>
-      <c r="J2" s="265"/>
-      <c r="K2" s="266"/>
-      <c r="L2" s="261"/>
-      <c r="M2" s="262"/>
-      <c r="N2" s="263"/>
-      <c r="O2" s="258"/>
-      <c r="P2" s="259"/>
-      <c r="Q2" s="260"/>
-      <c r="R2" s="255"/>
-      <c r="S2" s="256"/>
-      <c r="T2" s="257"/>
-      <c r="U2" s="252"/>
-      <c r="V2" s="253"/>
-      <c r="W2" s="254"/>
+      <c r="G2" s="257"/>
+      <c r="H2" s="258"/>
+      <c r="I2" s="271"/>
+      <c r="J2" s="272"/>
+      <c r="K2" s="273"/>
+      <c r="L2" s="268"/>
+      <c r="M2" s="269"/>
+      <c r="N2" s="270"/>
+      <c r="O2" s="265"/>
+      <c r="P2" s="266"/>
+      <c r="Q2" s="267"/>
+      <c r="R2" s="262"/>
+      <c r="S2" s="263"/>
+      <c r="T2" s="264"/>
+      <c r="U2" s="259"/>
+      <c r="V2" s="260"/>
+      <c r="W2" s="261"/>
     </row>
     <row r="3" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -55504,9 +55546,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="273"/>
-      <c r="D3" s="273"/>
-      <c r="E3" s="273"/>
+      <c r="C3" s="243"/>
+      <c r="D3" s="243"/>
+      <c r="E3" s="243"/>
       <c r="F3" s="188" t="s">
         <v>393</v>
       </c>
@@ -57010,6 +57052,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="F2:H2"/>
@@ -57020,11 +57067,6 @@
     <mergeCell ref="U2:W2"/>
     <mergeCell ref="L1:N1"/>
     <mergeCell ref="O1:Q1"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:W32">
     <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
@@ -57531,51 +57573,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="282" t="s">
+      <c r="C1" s="302" t="s">
         <v>202</v>
       </c>
-      <c r="D1" s="283"/>
-      <c r="E1" s="283"/>
-      <c r="F1" s="283"/>
-      <c r="G1" s="283"/>
-      <c r="H1" s="283"/>
-      <c r="I1" s="284"/>
+      <c r="D1" s="303"/>
+      <c r="E1" s="303"/>
+      <c r="F1" s="303"/>
+      <c r="G1" s="303"/>
+      <c r="H1" s="303"/>
+      <c r="I1" s="304"/>
       <c r="J1" s="114" t="s">
         <v>195</v>
       </c>
       <c r="K1" s="115" t="s">
         <v>194</v>
       </c>
-      <c r="L1" s="307" t="s">
+      <c r="L1" s="283" t="s">
         <v>287</v>
       </c>
-      <c r="M1" s="312"/>
-      <c r="N1" s="312"/>
-      <c r="O1" s="312"/>
-      <c r="P1" s="312"/>
-      <c r="Q1" s="312"/>
-      <c r="R1" s="312"/>
-      <c r="S1" s="312"/>
-      <c r="T1" s="312"/>
-      <c r="U1" s="312"/>
-      <c r="V1" s="312"/>
-      <c r="W1" s="312"/>
-      <c r="X1" s="312"/>
-      <c r="Y1" s="312"/>
-      <c r="Z1" s="312"/>
-      <c r="AA1" s="312"/>
-      <c r="AB1" s="312"/>
-      <c r="AC1" s="312"/>
-      <c r="AD1" s="312"/>
-      <c r="AE1" s="312"/>
-      <c r="AF1" s="312"/>
-      <c r="AG1" s="313"/>
-      <c r="AH1" s="307" t="s">
+      <c r="M1" s="288"/>
+      <c r="N1" s="288"/>
+      <c r="O1" s="288"/>
+      <c r="P1" s="288"/>
+      <c r="Q1" s="288"/>
+      <c r="R1" s="288"/>
+      <c r="S1" s="288"/>
+      <c r="T1" s="288"/>
+      <c r="U1" s="288"/>
+      <c r="V1" s="288"/>
+      <c r="W1" s="288"/>
+      <c r="X1" s="288"/>
+      <c r="Y1" s="288"/>
+      <c r="Z1" s="288"/>
+      <c r="AA1" s="288"/>
+      <c r="AB1" s="288"/>
+      <c r="AC1" s="288"/>
+      <c r="AD1" s="288"/>
+      <c r="AE1" s="288"/>
+      <c r="AF1" s="288"/>
+      <c r="AG1" s="289"/>
+      <c r="AH1" s="283" t="s">
         <v>175</v>
       </c>
-      <c r="AI1" s="308"/>
-      <c r="AJ1" s="308"/>
-      <c r="AK1" s="309"/>
+      <c r="AI1" s="284"/>
+      <c r="AJ1" s="284"/>
+      <c r="AK1" s="285"/>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B2" s="111"/>
@@ -62775,15 +62817,15 @@
         <f t="shared" ref="J80:J111" si="2">H80-I80</f>
         <v>2</v>
       </c>
-      <c r="K80" s="314" t="s">
+      <c r="K80" s="290" t="s">
         <v>434</v>
       </c>
-      <c r="L80" s="315"/>
-      <c r="M80" s="316"/>
+      <c r="L80" s="291"/>
+      <c r="M80" s="292"/>
       <c r="O80" s="133"/>
       <c r="P80" s="133"/>
-      <c r="W80" s="310"/>
-      <c r="X80" s="310"/>
+      <c r="W80" s="286"/>
+      <c r="X80" s="286"/>
       <c r="Y80" s="70" t="s">
         <v>211</v>
       </c>
@@ -62833,15 +62875,15 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K81" s="317"/>
-      <c r="L81" s="318"/>
-      <c r="M81" s="319"/>
+      <c r="K81" s="293"/>
+      <c r="L81" s="294"/>
+      <c r="M81" s="295"/>
       <c r="O81" s="133"/>
       <c r="P81" s="133"/>
-      <c r="W81" s="310" t="s">
+      <c r="W81" s="286" t="s">
         <v>209</v>
       </c>
-      <c r="X81" s="310"/>
+      <c r="X81" s="286"/>
       <c r="Y81" s="70">
         <f>COUNTIF(L3:AG40,3)</f>
         <v>481</v>
@@ -62897,17 +62939,17 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K82" s="320" t="s">
+      <c r="K82" s="296" t="s">
         <v>435</v>
       </c>
-      <c r="L82" s="321"/>
-      <c r="M82" s="322"/>
+      <c r="L82" s="297"/>
+      <c r="M82" s="298"/>
       <c r="O82" s="133"/>
       <c r="P82" s="133"/>
-      <c r="W82" s="310" t="s">
+      <c r="W82" s="286" t="s">
         <v>210</v>
       </c>
-      <c r="X82" s="310"/>
+      <c r="X82" s="286"/>
       <c r="Y82" s="70">
         <f>COUNTIF(K3:K40,3)+COUNTIF(J3:J15,3)</f>
         <v>25</v>
@@ -62963,37 +63005,37 @@
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="K83" s="323" t="s">
+      <c r="K83" s="299" t="s">
         <v>436</v>
       </c>
-      <c r="L83" s="324"/>
-      <c r="M83" s="325"/>
+      <c r="L83" s="300"/>
+      <c r="M83" s="301"/>
       <c r="O83" s="133"/>
       <c r="P83" s="133"/>
-      <c r="W83" s="311" t="s">
+      <c r="W83" s="287" t="s">
         <v>97</v>
       </c>
-      <c r="X83" s="311"/>
+      <c r="X83" s="287"/>
       <c r="Y83" s="194">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Z83" s="194">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AA83" s="70">
         <v>76</v>
       </c>
       <c r="AC83" s="109">
         <f>Y83/SUM($Y$83:$AA$83)</f>
-        <v>0.62222222222222223</v>
+        <v>0.62362637362637363</v>
       </c>
       <c r="AD83" s="195">
         <f t="shared" ref="AD83:AE83" si="5">Z83/SUM($Y$83:$AA$83)</f>
-        <v>0.16666666666666666</v>
+        <v>0.16758241758241757</v>
       </c>
       <c r="AE83" s="195">
         <f t="shared" si="5"/>
-        <v>0.21111111111111111</v>
+        <v>0.2087912087912088</v>
       </c>
     </row>
     <row r="84" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -63026,15 +63068,15 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="K84" s="288" t="s">
+      <c r="K84" s="308" t="s">
         <v>284</v>
       </c>
-      <c r="L84" s="289"/>
-      <c r="M84" s="290"/>
+      <c r="L84" s="309"/>
+      <c r="M84" s="310"/>
       <c r="O84" s="141"/>
       <c r="P84" s="141"/>
-      <c r="W84" s="306"/>
-      <c r="X84" s="306"/>
+      <c r="W84" s="282"/>
+      <c r="X84" s="282"/>
       <c r="Y84" s="196"/>
       <c r="Z84" s="196"/>
       <c r="AA84" s="196"/>
@@ -63072,9 +63114,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K85" s="291"/>
-      <c r="L85" s="292"/>
-      <c r="M85" s="293"/>
+      <c r="K85" s="311"/>
+      <c r="L85" s="312"/>
+      <c r="M85" s="313"/>
       <c r="O85" s="141"/>
       <c r="P85" s="141"/>
     </row>
@@ -63108,9 +63150,9 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="K86" s="291"/>
-      <c r="L86" s="292"/>
-      <c r="M86" s="293"/>
+      <c r="K86" s="311"/>
+      <c r="L86" s="312"/>
+      <c r="M86" s="313"/>
       <c r="O86" s="141"/>
       <c r="P86" s="141"/>
     </row>
@@ -63144,9 +63186,9 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="K87" s="291"/>
-      <c r="L87" s="292"/>
-      <c r="M87" s="293"/>
+      <c r="K87" s="311"/>
+      <c r="L87" s="312"/>
+      <c r="M87" s="313"/>
       <c r="O87" s="141"/>
       <c r="P87" s="141"/>
     </row>
@@ -63180,9 +63222,9 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K88" s="291"/>
-      <c r="L88" s="292"/>
-      <c r="M88" s="293"/>
+      <c r="K88" s="311"/>
+      <c r="L88" s="312"/>
+      <c r="M88" s="313"/>
       <c r="O88" s="141"/>
       <c r="P88" s="141"/>
     </row>
@@ -63216,9 +63258,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K89" s="291"/>
-      <c r="L89" s="292"/>
-      <c r="M89" s="293"/>
+      <c r="K89" s="311"/>
+      <c r="L89" s="312"/>
+      <c r="M89" s="313"/>
       <c r="O89" s="141"/>
       <c r="P89" s="141"/>
     </row>
@@ -63252,9 +63294,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K90" s="291"/>
-      <c r="L90" s="292"/>
-      <c r="M90" s="293"/>
+      <c r="K90" s="311"/>
+      <c r="L90" s="312"/>
+      <c r="M90" s="313"/>
       <c r="O90" s="141"/>
       <c r="P90" s="141"/>
     </row>
@@ -63288,9 +63330,9 @@
         <f t="shared" si="2"/>
         <v>47</v>
       </c>
-      <c r="K91" s="291"/>
-      <c r="L91" s="292"/>
-      <c r="M91" s="293"/>
+      <c r="K91" s="311"/>
+      <c r="L91" s="312"/>
+      <c r="M91" s="313"/>
       <c r="O91" s="141"/>
       <c r="P91" s="141"/>
     </row>
@@ -63324,9 +63366,9 @@
         <f t="shared" si="2"/>
         <v>51</v>
       </c>
-      <c r="K92" s="291"/>
-      <c r="L92" s="292"/>
-      <c r="M92" s="293"/>
+      <c r="K92" s="311"/>
+      <c r="L92" s="312"/>
+      <c r="M92" s="313"/>
       <c r="O92" s="141"/>
       <c r="P92" s="141"/>
     </row>
@@ -63360,9 +63402,9 @@
         <f t="shared" si="2"/>
         <v>37</v>
       </c>
-      <c r="K93" s="291"/>
-      <c r="L93" s="292"/>
-      <c r="M93" s="293"/>
+      <c r="K93" s="311"/>
+      <c r="L93" s="312"/>
+      <c r="M93" s="313"/>
       <c r="O93" s="141"/>
       <c r="P93" s="141"/>
     </row>
@@ -63396,9 +63438,9 @@
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="K94" s="291"/>
-      <c r="L94" s="292"/>
-      <c r="M94" s="293"/>
+      <c r="K94" s="311"/>
+      <c r="L94" s="312"/>
+      <c r="M94" s="313"/>
       <c r="O94" s="141"/>
       <c r="P94" s="141"/>
     </row>
@@ -63432,9 +63474,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K95" s="291"/>
-      <c r="L95" s="292"/>
-      <c r="M95" s="293"/>
+      <c r="K95" s="311"/>
+      <c r="L95" s="312"/>
+      <c r="M95" s="313"/>
       <c r="O95" s="141"/>
       <c r="P95" s="141"/>
     </row>
@@ -63468,9 +63510,9 @@
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="K96" s="291"/>
-      <c r="L96" s="292"/>
-      <c r="M96" s="293"/>
+      <c r="K96" s="311"/>
+      <c r="L96" s="312"/>
+      <c r="M96" s="313"/>
       <c r="O96" s="141"/>
       <c r="P96" s="141"/>
     </row>
@@ -63504,9 +63546,9 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="K97" s="291"/>
-      <c r="L97" s="292"/>
-      <c r="M97" s="293"/>
+      <c r="K97" s="311"/>
+      <c r="L97" s="312"/>
+      <c r="M97" s="313"/>
       <c r="O97" s="141"/>
       <c r="P97" s="141"/>
     </row>
@@ -63540,9 +63582,9 @@
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="K98" s="291"/>
-      <c r="L98" s="292"/>
-      <c r="M98" s="293"/>
+      <c r="K98" s="311"/>
+      <c r="L98" s="312"/>
+      <c r="M98" s="313"/>
       <c r="O98" s="141"/>
       <c r="P98" s="141"/>
     </row>
@@ -63576,9 +63618,9 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K99" s="291"/>
-      <c r="L99" s="292"/>
-      <c r="M99" s="293"/>
+      <c r="K99" s="311"/>
+      <c r="L99" s="312"/>
+      <c r="M99" s="313"/>
       <c r="O99" s="141"/>
       <c r="P99" s="141"/>
     </row>
@@ -63612,9 +63654,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K100" s="291"/>
-      <c r="L100" s="292"/>
-      <c r="M100" s="293"/>
+      <c r="K100" s="311"/>
+      <c r="L100" s="312"/>
+      <c r="M100" s="313"/>
       <c r="O100" s="141"/>
       <c r="P100" s="141"/>
     </row>
@@ -63648,9 +63690,9 @@
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="K101" s="291"/>
-      <c r="L101" s="292"/>
-      <c r="M101" s="293"/>
+      <c r="K101" s="311"/>
+      <c r="L101" s="312"/>
+      <c r="M101" s="313"/>
       <c r="O101" s="141"/>
       <c r="P101" s="141"/>
     </row>
@@ -63684,9 +63726,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K102" s="291"/>
-      <c r="L102" s="292"/>
-      <c r="M102" s="293"/>
+      <c r="K102" s="311"/>
+      <c r="L102" s="312"/>
+      <c r="M102" s="313"/>
       <c r="O102" s="141"/>
       <c r="P102" s="141"/>
     </row>
@@ -63720,9 +63762,9 @@
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="K103" s="291"/>
-      <c r="L103" s="292"/>
-      <c r="M103" s="293"/>
+      <c r="K103" s="311"/>
+      <c r="L103" s="312"/>
+      <c r="M103" s="313"/>
       <c r="O103" s="141"/>
       <c r="P103" s="141"/>
     </row>
@@ -63756,9 +63798,9 @@
         <f t="shared" si="2"/>
         <v>33</v>
       </c>
-      <c r="K104" s="291"/>
-      <c r="L104" s="292"/>
-      <c r="M104" s="293"/>
+      <c r="K104" s="311"/>
+      <c r="L104" s="312"/>
+      <c r="M104" s="313"/>
       <c r="O104" s="141"/>
       <c r="P104" s="141"/>
     </row>
@@ -63792,9 +63834,9 @@
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="K105" s="294"/>
-      <c r="L105" s="295"/>
-      <c r="M105" s="296"/>
+      <c r="K105" s="314"/>
+      <c r="L105" s="315"/>
+      <c r="M105" s="316"/>
       <c r="O105" s="141"/>
       <c r="P105" s="141"/>
     </row>
@@ -63828,11 +63870,11 @@
         <f t="shared" si="2"/>
         <v>21</v>
       </c>
-      <c r="K106" s="285" t="s">
+      <c r="K106" s="305" t="s">
         <v>286</v>
       </c>
-      <c r="L106" s="286"/>
-      <c r="M106" s="287"/>
+      <c r="L106" s="306"/>
+      <c r="M106" s="307"/>
       <c r="O106" s="126"/>
       <c r="P106" s="126"/>
     </row>
@@ -63866,11 +63908,11 @@
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="K107" s="285" t="s">
+      <c r="K107" s="305" t="s">
         <v>288</v>
       </c>
-      <c r="L107" s="286"/>
-      <c r="M107" s="287"/>
+      <c r="L107" s="306"/>
+      <c r="M107" s="307"/>
       <c r="O107" s="126"/>
       <c r="P107" s="126"/>
     </row>
@@ -63904,11 +63946,11 @@
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="K108" s="297" t="s">
+      <c r="K108" s="317" t="s">
         <v>289</v>
       </c>
-      <c r="L108" s="298"/>
-      <c r="M108" s="299"/>
+      <c r="L108" s="318"/>
+      <c r="M108" s="319"/>
       <c r="O108" s="126"/>
       <c r="P108" s="126"/>
     </row>
@@ -63942,9 +63984,9 @@
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="K109" s="300"/>
-      <c r="L109" s="301"/>
-      <c r="M109" s="302"/>
+      <c r="K109" s="320"/>
+      <c r="L109" s="321"/>
+      <c r="M109" s="322"/>
       <c r="O109" s="126"/>
       <c r="P109" s="126"/>
     </row>
@@ -63978,9 +64020,9 @@
         <f t="shared" si="2"/>
         <v>45</v>
       </c>
-      <c r="K110" s="300"/>
-      <c r="L110" s="301"/>
-      <c r="M110" s="302"/>
+      <c r="K110" s="320"/>
+      <c r="L110" s="321"/>
+      <c r="M110" s="322"/>
       <c r="O110" s="126"/>
       <c r="P110" s="126"/>
     </row>
@@ -64014,9 +64056,9 @@
         <f t="shared" si="2"/>
         <v>62</v>
       </c>
-      <c r="K111" s="300"/>
-      <c r="L111" s="301"/>
-      <c r="M111" s="302"/>
+      <c r="K111" s="320"/>
+      <c r="L111" s="321"/>
+      <c r="M111" s="322"/>
       <c r="O111" s="126"/>
       <c r="P111" s="126"/>
     </row>
@@ -64054,9 +64096,9 @@
         <f t="shared" ref="J112:J114" si="6">H112-I112</f>
         <v>34</v>
       </c>
-      <c r="K112" s="300"/>
-      <c r="L112" s="301"/>
-      <c r="M112" s="302"/>
+      <c r="K112" s="320"/>
+      <c r="L112" s="321"/>
+      <c r="M112" s="322"/>
     </row>
     <row r="113" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="156" t="s">
@@ -64092,9 +64134,9 @@
         <f t="shared" si="6"/>
         <v>43</v>
       </c>
-      <c r="K113" s="300"/>
-      <c r="L113" s="301"/>
-      <c r="M113" s="302"/>
+      <c r="K113" s="320"/>
+      <c r="L113" s="321"/>
+      <c r="M113" s="322"/>
     </row>
     <row r="114" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="93" t="s">
@@ -64130,13 +64172,18 @@
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="K114" s="303"/>
-      <c r="L114" s="304"/>
-      <c r="M114" s="305"/>
+      <c r="K114" s="323"/>
+      <c r="L114" s="324"/>
+      <c r="M114" s="325"/>
     </row>
   </sheetData>
   <autoFilter ref="A79:J112" xr:uid="{9C81160F-C24B-449F-8F5A-CB622AB71070}"/>
   <mergeCells count="15">
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="K106:M106"/>
+    <mergeCell ref="K107:M107"/>
+    <mergeCell ref="K84:M105"/>
+    <mergeCell ref="K108:M114"/>
     <mergeCell ref="W84:X84"/>
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="W80:X80"/>
@@ -64147,11 +64194,6 @@
     <mergeCell ref="K80:M81"/>
     <mergeCell ref="K82:M82"/>
     <mergeCell ref="K83:M83"/>
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="K106:M106"/>
-    <mergeCell ref="K107:M107"/>
-    <mergeCell ref="K84:M105"/>
-    <mergeCell ref="K108:M114"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <conditionalFormatting sqref="A3:A40">
@@ -64367,31 +64409,31 @@
         <v>486</v>
       </c>
       <c r="B4" s="192">
-        <v>0.875</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>488</v>
+        <v>420</v>
       </c>
       <c r="E4" t="s">
         <v>487</v>
       </c>
       <c r="F4" t="s">
+        <v>482</v>
+      </c>
+      <c r="G4" s="202" t="s">
+        <v>485</v>
+      </c>
+      <c r="H4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I4" t="s">
+        <v>484</v>
+      </c>
+      <c r="J4" t="s">
         <v>483</v>
-      </c>
-      <c r="G4" s="202" t="s">
-        <v>484</v>
-      </c>
-      <c r="H4" t="s">
-        <v>4</v>
-      </c>
-      <c r="I4" t="s">
-        <v>428</v>
-      </c>
-      <c r="J4" t="s">
-        <v>485</v>
       </c>
       <c r="L4">
         <v>2</v>
@@ -65057,7 +65099,7 @@
         <v>474</v>
       </c>
       <c r="C3" s="199">
-        <v>6.7</v>
+        <v>6.1</v>
       </c>
       <c r="D3">
         <v>90</v>
@@ -65071,7 +65113,7 @@
         <v>450</v>
       </c>
       <c r="C4" s="199">
-        <v>8</v>
+        <v>6.1</v>
       </c>
       <c r="D4">
         <v>90</v>
@@ -65085,7 +65127,7 @@
         <v>455</v>
       </c>
       <c r="C5" s="199">
-        <v>7.3</v>
+        <v>6.2</v>
       </c>
       <c r="D5">
         <v>90</v>
@@ -65096,13 +65138,13 @@
         <v>442</v>
       </c>
       <c r="B6" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="C6" s="199">
-        <v>6.7</v>
-      </c>
-      <c r="D6" t="s">
-        <v>453</v>
+        <v>5.6</v>
+      </c>
+      <c r="D6">
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -65113,13 +65155,13 @@
         <v>475</v>
       </c>
       <c r="C7" s="199">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="D7">
         <v>90</v>
       </c>
       <c r="E7" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -65130,7 +65172,7 @@
         <v>459</v>
       </c>
       <c r="C8" s="199">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="D8" t="s">
         <v>453</v>
@@ -65144,10 +65186,13 @@
         <v>451</v>
       </c>
       <c r="C9" s="199">
-        <v>7.5</v>
-      </c>
-      <c r="D9">
-        <v>90</v>
+        <v>7.9</v>
+      </c>
+      <c r="D9" t="s">
+        <v>453</v>
+      </c>
+      <c r="E9" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -65155,13 +65200,13 @@
         <v>447</v>
       </c>
       <c r="B10" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C10" s="199">
-        <v>6.4</v>
-      </c>
-      <c r="D10" t="s">
-        <v>453</v>
+        <v>6.5</v>
+      </c>
+      <c r="D10">
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -65171,11 +65216,9 @@
       <c r="B11" t="s">
         <v>476</v>
       </c>
-      <c r="C11" s="199">
-        <v>7</v>
-      </c>
-      <c r="D11">
-        <v>90</v>
+      <c r="C11" s="199"/>
+      <c r="D11" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -65197,10 +65240,10 @@
         <v>442</v>
       </c>
       <c r="B13" t="s">
-        <v>473</v>
+        <v>488</v>
       </c>
       <c r="C13" s="199">
-        <v>7</v>
+        <v>6.1</v>
       </c>
       <c r="D13" t="s">
         <v>452</v>
@@ -65213,9 +65256,7 @@
       <c r="B14" t="s">
         <v>454</v>
       </c>
-      <c r="C14" s="199">
-        <v>6.8</v>
-      </c>
+      <c r="C14" s="199"/>
       <c r="D14" t="s">
         <v>452</v>
       </c>
@@ -65228,10 +65269,13 @@
         <v>469</v>
       </c>
       <c r="C15" s="199">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="D15" t="s">
         <v>452</v>
+      </c>
+      <c r="E15" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -65242,7 +65286,7 @@
         <v>481</v>
       </c>
       <c r="C16" s="199">
-        <v>6.8</v>
+        <v>7.9</v>
       </c>
       <c r="D16" t="s">
         <v>452</v>
@@ -66272,11 +66316,11 @@
       </c>
       <c r="K30" s="9">
         <f>'Apps &amp; Goals'!T10</f>
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L30" s="14">
         <f>J30/K30</f>
-        <v>0.2639751552795031</v>
+        <v>0.26315789473684209</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
@@ -66437,7 +66481,7 @@
       <c r="U2" s="211"/>
       <c r="V2" s="211"/>
       <c r="Z2" s="125">
-        <v>46314</v>
+        <v>46317</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
@@ -66534,7 +66578,7 @@
       </c>
       <c r="H4" s="4">
         <f>'#'!V6</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I4" s="4">
         <f>'#'!W6</f>
@@ -66582,7 +66626,7 @@
       </c>
       <c r="T4" s="2">
         <f t="shared" ref="T4:V4" si="0">SUM(E4,H4,K4,N4,Q4)</f>
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="U4" s="2">
         <f t="shared" ref="U4" si="1">SUM(F4,I4,L4,O4,R4)</f>
@@ -66964,7 +67008,7 @@
       </c>
       <c r="H9" s="4">
         <f>'#'!V11</f>
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I9" s="4">
         <f>'#'!W11</f>
@@ -67012,7 +67056,7 @@
       </c>
       <c r="T9" s="2">
         <f t="shared" si="2"/>
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="U9" s="2">
         <f t="shared" si="3"/>
@@ -67050,7 +67094,7 @@
       </c>
       <c r="H10" s="4">
         <f>'#'!V12</f>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I10" s="4">
         <f>'#'!W12</f>
@@ -67098,7 +67142,7 @@
       </c>
       <c r="T10" s="2">
         <f t="shared" si="2"/>
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="U10" s="2">
         <f t="shared" si="3"/>
@@ -67136,7 +67180,7 @@
       </c>
       <c r="H11" s="4">
         <f>'#'!V13</f>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I11" s="4">
         <f>'#'!W13</f>
@@ -67144,7 +67188,7 @@
       </c>
       <c r="J11" s="4">
         <f>'#'!X13</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K11" s="6">
         <f>'#'!AH13</f>
@@ -67184,7 +67228,7 @@
       </c>
       <c r="T11" s="2">
         <f t="shared" si="2"/>
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="U11" s="2">
         <f t="shared" si="3"/>
@@ -67192,7 +67236,7 @@
       </c>
       <c r="V11" s="2">
         <f t="shared" si="4"/>
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
@@ -67222,11 +67266,11 @@
       </c>
       <c r="H12" s="4">
         <f>'#'!V14</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I12" s="4">
         <f>'#'!W14</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J12" s="4">
         <f>'#'!X14</f>
@@ -67270,11 +67314,11 @@
       </c>
       <c r="T12" s="2">
         <f t="shared" si="2"/>
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="U12" s="2">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V12" s="2">
         <f t="shared" si="4"/>
@@ -67308,7 +67352,7 @@
       </c>
       <c r="H13" s="4">
         <f>'#'!V15</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I13" s="4">
         <f>'#'!W15</f>
@@ -67356,7 +67400,7 @@
       </c>
       <c r="T13" s="2">
         <f t="shared" si="2"/>
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="U13" s="2">
         <f t="shared" si="3"/>
@@ -67480,7 +67524,7 @@
       </c>
       <c r="H15" s="4">
         <f>'#'!V17</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I15" s="4">
         <f>'#'!W17</f>
@@ -67488,7 +67532,7 @@
       </c>
       <c r="J15" s="4">
         <f>'#'!X17</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K15" s="6">
         <f>'#'!AH17</f>
@@ -67528,7 +67572,7 @@
       </c>
       <c r="T15" s="2">
         <f t="shared" si="2"/>
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="U15" s="2">
         <f t="shared" si="3"/>
@@ -67536,7 +67580,7 @@
       </c>
       <c r="V15" s="2">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">
@@ -67566,7 +67610,7 @@
       </c>
       <c r="H16" s="4">
         <f>'#'!V18</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I16" s="4">
         <f>'#'!W18</f>
@@ -67614,7 +67658,7 @@
       </c>
       <c r="T16" s="2">
         <f t="shared" ref="T16:T28" si="5">SUM(E16,H16,K16,N16,Q16)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U16" s="2">
         <f t="shared" ref="U16:U28" si="6">SUM(F16,I16,L16,O16,R16)</f>
@@ -67738,7 +67782,7 @@
       </c>
       <c r="H18" s="4">
         <f>'#'!V20</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I18" s="4">
         <f>'#'!W20</f>
@@ -67786,7 +67830,7 @@
       </c>
       <c r="T18" s="2">
         <f t="shared" si="5"/>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="U18" s="2">
         <f t="shared" si="6"/>
@@ -67913,7 +67957,7 @@
       </c>
       <c r="H20" s="4">
         <f>'#'!V22</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I20" s="4">
         <f>'#'!W22</f>
@@ -67961,7 +68005,7 @@
       </c>
       <c r="T20" s="2">
         <f t="shared" si="5"/>
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="U20" s="2">
         <f t="shared" si="6"/>
@@ -67999,7 +68043,7 @@
       </c>
       <c r="H21" s="4">
         <f>'#'!V23</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I21" s="4">
         <f>'#'!W23</f>
@@ -68047,7 +68091,7 @@
       </c>
       <c r="T21" s="2">
         <f t="shared" si="5"/>
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="U21" s="2">
         <f t="shared" si="6"/>
@@ -68171,7 +68215,7 @@
       </c>
       <c r="H23" s="4">
         <f>'#'!V25</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I23" s="4">
         <f>'#'!W25</f>
@@ -68219,7 +68263,7 @@
       </c>
       <c r="T23" s="2">
         <f t="shared" si="5"/>
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="U23" s="2">
         <f t="shared" si="6"/>
@@ -68432,7 +68476,7 @@
       </c>
       <c r="H26" s="4">
         <f>'#'!V28</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I26" s="4">
         <f>'#'!W28</f>
@@ -68480,7 +68524,7 @@
       </c>
       <c r="T26" s="2">
         <f t="shared" si="5"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U26" s="2">
         <f t="shared" si="6"/>
@@ -68604,11 +68648,11 @@
       </c>
       <c r="H28" s="4">
         <f>'#'!V30</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I28" s="4">
         <f>'#'!W30</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J28" s="4">
         <f>'#'!X30</f>
@@ -68652,11 +68696,11 @@
       </c>
       <c r="T28" s="2">
         <f t="shared" si="5"/>
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="U28" s="2">
         <f t="shared" si="6"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="V28" s="2">
         <f t="shared" si="7"/>
@@ -69037,7 +69081,7 @@
       </c>
       <c r="H33" s="4">
         <f>'#'!V35</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I33" s="4">
         <f>'#'!W35</f>
@@ -69085,7 +69129,7 @@
       </c>
       <c r="T33" s="2">
         <f t="shared" si="9"/>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U33" s="2">
         <f t="shared" si="10"/>

--- a/data/arsenal_stats.xlsx
+++ b/data/arsenal_stats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bungeltd-my.sharepoint.com/personal/przemyslaw_iskra_bunge_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8828" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{349CB5C9-7605-476C-A4E3-07D50A0C4E97}"/>
+  <xr:revisionPtr revIDLastSave="8830" documentId="13_ncr:1_{662DAA9A-C5C7-8346-85AE-B86E329139C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4E8BE79-060F-468D-B184-7DA361D18E92}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="799" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="799" firstSheet="1" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="19" state="hidden" r:id="rId1"/>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2271" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2272" uniqueCount="487">
   <si>
     <t>Arsenal FC squad statistics</t>
   </si>
@@ -1381,9 +1381,6 @@
     <t>Ipswitch Town</t>
   </si>
   <si>
-    <t>−5</t>
-  </si>
-  <si>
     <t>GEORGE GRAHAM</t>
   </si>
   <si>
@@ -1462,9 +1459,6 @@
     <t>Bruno</t>
   </si>
   <si>
-    <t>−6</t>
-  </si>
-  <si>
     <t>Lille</t>
   </si>
   <si>
@@ -1493,9 +1487,6 @@
   </si>
   <si>
     <t>−4</t>
-  </si>
-  <si>
-    <t>−9</t>
   </si>
   <si>
     <t>Raya</t>
@@ -1547,6 +1538,9 @@
   </si>
   <si>
     <t>Lewis-Skelly</t>
+  </si>
+  <si>
+    <t>−8</t>
   </si>
 </sst>
 </file>
@@ -3053,21 +3047,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3092,13 +3071,16 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3110,14 +3092,32 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="19" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="54" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="27" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3155,15 +3155,6 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="28" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3171,27 +3162,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="10" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="60" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="10" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="37" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="15" fillId="0" borderId="11" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3284,70 +3254,31 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="60" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="10" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="37" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="15" fillId="0" borderId="11" xfId="6" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="54" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3421,6 +3352,69 @@
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6484,7 +6478,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C3F69A78-597A-4B61-A53F-37C534451298}" type="CELLRANGE">
+                    <a:fld id="{F03B3B20-96CB-41AB-81C7-ED2BBAA84080}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6518,7 +6512,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{4A5BC353-34AF-4387-9748-548EE3AA67E4}" type="CELLRANGE">
+                    <a:fld id="{36785554-18E5-4C58-8019-4CBFBD95613A}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6552,7 +6546,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9C9A2F4C-CBB8-4F5B-B64C-25160BEC71BF}" type="CELLRANGE">
+                    <a:fld id="{F357BAAF-79A7-4862-96E9-844ECBC1E507}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6586,7 +6580,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{5C127597-DB84-498B-B02F-9D6149647BDA}" type="CELLRANGE">
+                    <a:fld id="{03989932-3D58-426A-B514-F77C296BEFCE}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6620,7 +6614,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F799D473-7896-4A64-A2B7-ADE4C51872CF}" type="CELLRANGE">
+                    <a:fld id="{903AFDFC-13AF-47D7-AB47-239E859E5BDF}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6654,7 +6648,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F5293035-5F1F-4E90-A001-CEDF0463FF1C}" type="CELLRANGE">
+                    <a:fld id="{0C6EB1B0-132F-46CA-AE62-B462D38CD38A}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6688,7 +6682,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{CEE01B22-9206-4C5E-9727-13B886FBD8A0}" type="CELLRANGE">
+                    <a:fld id="{E2EB67FF-0592-4AEF-AC23-69228F484A6F}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6722,7 +6716,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{54E7DC27-CC6A-495F-A62F-97DB0D9ED9AE}" type="CELLRANGE">
+                    <a:fld id="{DA1FD8CB-28D5-4BDC-8F06-253F05753E9A}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6756,7 +6750,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{4B5C21A5-AC62-437D-B644-72F97AC045AA}" type="CELLRANGE">
+                    <a:fld id="{148B38BE-DAA3-43F0-A1CE-354DC5237854}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6790,7 +6784,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{AD91FAAB-00B3-4F7C-B6A8-A7744A655FD6}" type="CELLRANGE">
+                    <a:fld id="{9FE67F1D-D06C-4D91-8DD2-1DF3CC0308B3}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6824,7 +6818,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{3F42F5EA-5E46-4060-908C-3670EA2F7FC9}" type="CELLRANGE">
+                    <a:fld id="{B587D341-5BD8-4BE6-9A0C-9C504395D86F}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6858,7 +6852,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{5241F2FA-E345-45DB-8E6E-1A8DF2267E06}" type="CELLRANGE">
+                    <a:fld id="{901458BD-2209-413A-B148-7FA8BA076EAD}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6907,7 +6901,7 @@
                         <a:cs typeface="+mn-cs"/>
                       </a:defRPr>
                     </a:pPr>
-                    <a:fld id="{17C29309-C308-4D52-BE12-531910DE70DC}" type="CELLRANGE">
+                    <a:fld id="{1337EC61-0050-4BEB-854C-2E14F003002F}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr>
                         <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
@@ -6966,7 +6960,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D12C8347-F3BC-468B-9973-316C769735C5}" type="CELLRANGE">
+                    <a:fld id="{D5ABAB5A-7F43-4F0C-A22A-F0A4D99C4B9E}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7000,7 +6994,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{99870CFE-0B48-4691-BA61-C90F14E67A18}" type="CELLRANGE">
+                    <a:fld id="{E507F86C-C233-4554-815E-FFA3B1158B56}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7034,7 +7028,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{4CDEED84-7315-4A2B-8300-113E6A7463BA}" type="CELLRANGE">
+                    <a:fld id="{B12B4D92-1634-4AE3-B328-FB8FFC3E3FEB}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -7068,7 +7062,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C6C497EA-C79F-4C6F-B2D9-B649AA1F663D}" type="CELLRANGE">
+                    <a:fld id="{EA1DFFE7-ABA3-4435-9C35-96367A834B84}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -13895,10 +13889,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Motyw pakietu Office">
   <a:themeElements>
@@ -14208,30 +14198,30 @@
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="3"/>
       <c r="B1" s="5"/>
-      <c r="C1" s="206" t="s">
+      <c r="C1" s="213" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="206"/>
-      <c r="E1" s="207" t="s">
+      <c r="D1" s="213"/>
+      <c r="E1" s="214" t="s">
         <v>120</v>
       </c>
-      <c r="F1" s="207"/>
-      <c r="G1" s="206" t="s">
+      <c r="F1" s="214"/>
+      <c r="G1" s="213" t="s">
         <v>108</v>
       </c>
-      <c r="H1" s="206"/>
-      <c r="I1" s="207" t="s">
+      <c r="H1" s="213"/>
+      <c r="I1" s="214" t="s">
         <v>110</v>
       </c>
-      <c r="J1" s="207"/>
-      <c r="K1" s="206" t="s">
+      <c r="J1" s="214"/>
+      <c r="K1" s="213" t="s">
         <v>39</v>
       </c>
-      <c r="L1" s="206"/>
-      <c r="M1" s="204" t="s">
+      <c r="L1" s="213"/>
+      <c r="M1" s="211" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="205"/>
+      <c r="N1" s="212"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -15938,30 +15928,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="206" t="s">
+      <c r="C2" s="213" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="206"/>
-      <c r="E2" s="207" t="s">
+      <c r="D2" s="213"/>
+      <c r="E2" s="214" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="207"/>
-      <c r="G2" s="206" t="s">
+      <c r="F2" s="214"/>
+      <c r="G2" s="213" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="206"/>
-      <c r="I2" s="207" t="s">
+      <c r="H2" s="213"/>
+      <c r="I2" s="214" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="207"/>
-      <c r="K2" s="206" t="s">
+      <c r="J2" s="214"/>
+      <c r="K2" s="213" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="206"/>
-      <c r="M2" s="211" t="s">
+      <c r="L2" s="213"/>
+      <c r="M2" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="211"/>
+      <c r="N2" s="206"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -17765,30 +17755,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="206" t="s">
+      <c r="C2" s="213" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="206"/>
-      <c r="E2" s="207" t="s">
+      <c r="D2" s="213"/>
+      <c r="E2" s="214" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="207"/>
-      <c r="G2" s="206" t="s">
+      <c r="F2" s="214"/>
+      <c r="G2" s="213" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="206"/>
-      <c r="I2" s="207" t="s">
+      <c r="H2" s="213"/>
+      <c r="I2" s="214" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="207"/>
-      <c r="K2" s="206" t="s">
+      <c r="J2" s="214"/>
+      <c r="K2" s="213" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="206"/>
-      <c r="M2" s="211" t="s">
+      <c r="L2" s="213"/>
+      <c r="M2" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="211"/>
+      <c r="N2" s="206"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -19455,30 +19445,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="206" t="s">
+      <c r="C2" s="213" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="206"/>
-      <c r="E2" s="207" t="s">
+      <c r="D2" s="213"/>
+      <c r="E2" s="214" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="207"/>
-      <c r="G2" s="206" t="s">
+      <c r="F2" s="214"/>
+      <c r="G2" s="213" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="206"/>
-      <c r="I2" s="207" t="s">
+      <c r="H2" s="213"/>
+      <c r="I2" s="214" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="207"/>
-      <c r="K2" s="206" t="s">
+      <c r="J2" s="214"/>
+      <c r="K2" s="213" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="206"/>
-      <c r="M2" s="211" t="s">
+      <c r="L2" s="213"/>
+      <c r="M2" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="211"/>
+      <c r="N2" s="206"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -21281,30 +21271,30 @@
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="206" t="s">
+      <c r="C2" s="213" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="206"/>
-      <c r="E2" s="207" t="s">
+      <c r="D2" s="213"/>
+      <c r="E2" s="214" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="207"/>
-      <c r="G2" s="206" t="s">
+      <c r="F2" s="214"/>
+      <c r="G2" s="213" t="s">
         <v>108</v>
       </c>
-      <c r="H2" s="206"/>
-      <c r="I2" s="207" t="s">
+      <c r="H2" s="213"/>
+      <c r="I2" s="214" t="s">
         <v>110</v>
       </c>
-      <c r="J2" s="207"/>
-      <c r="K2" s="206" t="s">
+      <c r="J2" s="214"/>
+      <c r="K2" s="213" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="206"/>
-      <c r="M2" s="211" t="s">
+      <c r="L2" s="213"/>
+      <c r="M2" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="211"/>
+      <c r="N2" s="206"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -23153,36 +23143,36 @@
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="208" t="s">
+      <c r="C2" s="203" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="209"/>
-      <c r="E2" s="210"/>
-      <c r="F2" s="213" t="s">
+      <c r="D2" s="204"/>
+      <c r="E2" s="205"/>
+      <c r="F2" s="208" t="s">
         <v>120</v>
       </c>
-      <c r="G2" s="214"/>
-      <c r="H2" s="215"/>
-      <c r="I2" s="208" t="s">
+      <c r="G2" s="209"/>
+      <c r="H2" s="210"/>
+      <c r="I2" s="203" t="s">
         <v>108</v>
       </c>
-      <c r="J2" s="209"/>
-      <c r="K2" s="210"/>
-      <c r="L2" s="213" t="s">
+      <c r="J2" s="204"/>
+      <c r="K2" s="205"/>
+      <c r="L2" s="208" t="s">
         <v>110</v>
       </c>
-      <c r="M2" s="214"/>
-      <c r="N2" s="215"/>
-      <c r="O2" s="208" t="s">
+      <c r="M2" s="209"/>
+      <c r="N2" s="210"/>
+      <c r="O2" s="203" t="s">
         <v>39</v>
       </c>
-      <c r="P2" s="209"/>
-      <c r="Q2" s="210"/>
-      <c r="R2" s="211" t="s">
+      <c r="P2" s="204"/>
+      <c r="Q2" s="205"/>
+      <c r="R2" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="S2" s="211"/>
-      <c r="T2" s="211"/>
+      <c r="S2" s="206"/>
+      <c r="T2" s="206"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -25431,7 +25421,7 @@
         <v>45</v>
       </c>
       <c r="B31" s="148" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C31" s="6">
         <f>'Premier League'!C31</f>
@@ -26121,36 +26111,36 @@
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
       <c r="D1" s="5"/>
-      <c r="E1" s="208" t="s">
+      <c r="E1" s="203" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="209"/>
-      <c r="G1" s="210"/>
-      <c r="H1" s="213" t="s">
+      <c r="F1" s="204"/>
+      <c r="G1" s="205"/>
+      <c r="H1" s="208" t="s">
         <v>120</v>
       </c>
-      <c r="I1" s="214"/>
-      <c r="J1" s="215"/>
-      <c r="K1" s="208" t="s">
+      <c r="I1" s="209"/>
+      <c r="J1" s="210"/>
+      <c r="K1" s="203" t="s">
         <v>108</v>
       </c>
-      <c r="L1" s="209"/>
-      <c r="M1" s="210"/>
-      <c r="N1" s="213" t="s">
+      <c r="L1" s="204"/>
+      <c r="M1" s="205"/>
+      <c r="N1" s="208" t="s">
         <v>110</v>
       </c>
-      <c r="O1" s="214"/>
-      <c r="P1" s="215"/>
-      <c r="Q1" s="208" t="s">
+      <c r="O1" s="209"/>
+      <c r="P1" s="210"/>
+      <c r="Q1" s="203" t="s">
         <v>39</v>
       </c>
-      <c r="R1" s="209"/>
-      <c r="S1" s="210"/>
-      <c r="T1" s="211" t="s">
+      <c r="R1" s="204"/>
+      <c r="S1" s="205"/>
+      <c r="T1" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="U1" s="211"/>
-      <c r="V1" s="211"/>
+      <c r="U1" s="206"/>
+      <c r="V1" s="206"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -37724,399 +37714,399 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F1" s="216">
-        <v>1</v>
-      </c>
-      <c r="G1" s="217"/>
-      <c r="H1" s="218"/>
-      <c r="I1" s="216">
+      <c r="F1" s="218">
+        <v>1</v>
+      </c>
+      <c r="G1" s="219"/>
+      <c r="H1" s="220"/>
+      <c r="I1" s="218">
         <v>2</v>
       </c>
-      <c r="J1" s="217"/>
-      <c r="K1" s="218"/>
-      <c r="L1" s="216">
-        <v>3</v>
-      </c>
-      <c r="M1" s="217"/>
-      <c r="N1" s="218"/>
-      <c r="O1" s="216">
+      <c r="J1" s="219"/>
+      <c r="K1" s="220"/>
+      <c r="L1" s="218">
+        <v>3</v>
+      </c>
+      <c r="M1" s="219"/>
+      <c r="N1" s="220"/>
+      <c r="O1" s="218">
         <v>4</v>
       </c>
-      <c r="P1" s="217"/>
-      <c r="Q1" s="218"/>
-      <c r="R1" s="216">
+      <c r="P1" s="219"/>
+      <c r="Q1" s="220"/>
+      <c r="R1" s="218">
         <v>5</v>
       </c>
-      <c r="S1" s="217"/>
-      <c r="T1" s="218"/>
-      <c r="U1" s="216">
+      <c r="S1" s="219"/>
+      <c r="T1" s="220"/>
+      <c r="U1" s="218">
         <v>6</v>
       </c>
-      <c r="V1" s="217"/>
-      <c r="W1" s="218"/>
-      <c r="X1" s="216">
+      <c r="V1" s="219"/>
+      <c r="W1" s="220"/>
+      <c r="X1" s="218">
         <v>7</v>
       </c>
-      <c r="Y1" s="217"/>
-      <c r="Z1" s="218"/>
-      <c r="AA1" s="216">
+      <c r="Y1" s="219"/>
+      <c r="Z1" s="220"/>
+      <c r="AA1" s="218">
         <v>8</v>
       </c>
-      <c r="AB1" s="217"/>
-      <c r="AC1" s="218"/>
-      <c r="AD1" s="216">
+      <c r="AB1" s="219"/>
+      <c r="AC1" s="220"/>
+      <c r="AD1" s="218">
         <v>9</v>
       </c>
-      <c r="AE1" s="217"/>
-      <c r="AF1" s="218"/>
-      <c r="AG1" s="216">
+      <c r="AE1" s="219"/>
+      <c r="AF1" s="220"/>
+      <c r="AG1" s="218">
         <v>10</v>
       </c>
-      <c r="AH1" s="217"/>
-      <c r="AI1" s="218"/>
-      <c r="AJ1" s="216">
+      <c r="AH1" s="219"/>
+      <c r="AI1" s="220"/>
+      <c r="AJ1" s="218">
         <v>11</v>
       </c>
-      <c r="AK1" s="217"/>
-      <c r="AL1" s="218"/>
-      <c r="AM1" s="216">
+      <c r="AK1" s="219"/>
+      <c r="AL1" s="220"/>
+      <c r="AM1" s="218">
         <v>12</v>
       </c>
-      <c r="AN1" s="217"/>
-      <c r="AO1" s="218"/>
-      <c r="AP1" s="216">
+      <c r="AN1" s="219"/>
+      <c r="AO1" s="220"/>
+      <c r="AP1" s="218">
         <v>13</v>
       </c>
-      <c r="AQ1" s="217"/>
-      <c r="AR1" s="218"/>
-      <c r="AS1" s="216">
+      <c r="AQ1" s="219"/>
+      <c r="AR1" s="220"/>
+      <c r="AS1" s="218">
         <v>14</v>
       </c>
-      <c r="AT1" s="217"/>
-      <c r="AU1" s="218"/>
-      <c r="AV1" s="216">
+      <c r="AT1" s="219"/>
+      <c r="AU1" s="220"/>
+      <c r="AV1" s="218">
         <v>15</v>
       </c>
-      <c r="AW1" s="217"/>
-      <c r="AX1" s="218"/>
-      <c r="AY1" s="216">
+      <c r="AW1" s="219"/>
+      <c r="AX1" s="220"/>
+      <c r="AY1" s="218">
         <v>16</v>
       </c>
-      <c r="AZ1" s="217"/>
-      <c r="BA1" s="218"/>
-      <c r="BB1" s="216">
+      <c r="AZ1" s="219"/>
+      <c r="BA1" s="220"/>
+      <c r="BB1" s="218">
         <v>17</v>
       </c>
-      <c r="BC1" s="217"/>
-      <c r="BD1" s="218"/>
-      <c r="BE1" s="216">
+      <c r="BC1" s="219"/>
+      <c r="BD1" s="220"/>
+      <c r="BE1" s="218">
         <v>18</v>
       </c>
-      <c r="BF1" s="217"/>
-      <c r="BG1" s="218"/>
-      <c r="BH1" s="216">
+      <c r="BF1" s="219"/>
+      <c r="BG1" s="220"/>
+      <c r="BH1" s="218">
         <v>19</v>
       </c>
-      <c r="BI1" s="217"/>
-      <c r="BJ1" s="218"/>
-      <c r="BK1" s="216">
+      <c r="BI1" s="219"/>
+      <c r="BJ1" s="220"/>
+      <c r="BK1" s="218">
         <v>20</v>
       </c>
-      <c r="BL1" s="217"/>
-      <c r="BM1" s="218"/>
-      <c r="BN1" s="216">
+      <c r="BL1" s="219"/>
+      <c r="BM1" s="220"/>
+      <c r="BN1" s="218">
         <v>21</v>
       </c>
-      <c r="BO1" s="217"/>
-      <c r="BP1" s="218"/>
-      <c r="BQ1" s="216">
+      <c r="BO1" s="219"/>
+      <c r="BP1" s="220"/>
+      <c r="BQ1" s="218">
         <v>22</v>
       </c>
-      <c r="BR1" s="217"/>
-      <c r="BS1" s="218"/>
-      <c r="BT1" s="216">
+      <c r="BR1" s="219"/>
+      <c r="BS1" s="220"/>
+      <c r="BT1" s="218">
         <v>23</v>
       </c>
-      <c r="BU1" s="217"/>
-      <c r="BV1" s="218"/>
-      <c r="BW1" s="216">
+      <c r="BU1" s="219"/>
+      <c r="BV1" s="220"/>
+      <c r="BW1" s="218">
         <v>24</v>
       </c>
-      <c r="BX1" s="217"/>
-      <c r="BY1" s="218"/>
-      <c r="BZ1" s="216">
+      <c r="BX1" s="219"/>
+      <c r="BY1" s="220"/>
+      <c r="BZ1" s="218">
         <v>25</v>
       </c>
-      <c r="CA1" s="217"/>
-      <c r="CB1" s="218"/>
-      <c r="CC1" s="216">
+      <c r="CA1" s="219"/>
+      <c r="CB1" s="220"/>
+      <c r="CC1" s="218">
         <v>26</v>
       </c>
-      <c r="CD1" s="217"/>
-      <c r="CE1" s="218"/>
-      <c r="CF1" s="216">
+      <c r="CD1" s="219"/>
+      <c r="CE1" s="220"/>
+      <c r="CF1" s="218">
         <v>27</v>
       </c>
-      <c r="CG1" s="217"/>
-      <c r="CH1" s="218"/>
-      <c r="CI1" s="216">
+      <c r="CG1" s="219"/>
+      <c r="CH1" s="220"/>
+      <c r="CI1" s="218">
         <v>28</v>
       </c>
-      <c r="CJ1" s="217"/>
-      <c r="CK1" s="218"/>
-      <c r="CL1" s="216">
+      <c r="CJ1" s="219"/>
+      <c r="CK1" s="220"/>
+      <c r="CL1" s="218">
         <v>29</v>
       </c>
-      <c r="CM1" s="217"/>
-      <c r="CN1" s="218"/>
-      <c r="CO1" s="216">
+      <c r="CM1" s="219"/>
+      <c r="CN1" s="220"/>
+      <c r="CO1" s="218">
         <v>30</v>
       </c>
-      <c r="CP1" s="217"/>
-      <c r="CQ1" s="218"/>
-      <c r="CR1" s="216">
+      <c r="CP1" s="219"/>
+      <c r="CQ1" s="220"/>
+      <c r="CR1" s="218">
         <v>31</v>
       </c>
-      <c r="CS1" s="217"/>
-      <c r="CT1" s="218"/>
-      <c r="CU1" s="216">
+      <c r="CS1" s="219"/>
+      <c r="CT1" s="220"/>
+      <c r="CU1" s="218">
         <v>32</v>
       </c>
-      <c r="CV1" s="217"/>
-      <c r="CW1" s="218"/>
-      <c r="CX1" s="216">
+      <c r="CV1" s="219"/>
+      <c r="CW1" s="220"/>
+      <c r="CX1" s="218">
         <v>33</v>
       </c>
-      <c r="CY1" s="217"/>
-      <c r="CZ1" s="218"/>
-      <c r="DA1" s="216">
+      <c r="CY1" s="219"/>
+      <c r="CZ1" s="220"/>
+      <c r="DA1" s="218">
         <v>34</v>
       </c>
-      <c r="DB1" s="217"/>
-      <c r="DC1" s="218"/>
-      <c r="DD1" s="216">
+      <c r="DB1" s="219"/>
+      <c r="DC1" s="220"/>
+      <c r="DD1" s="218">
         <v>35</v>
       </c>
-      <c r="DE1" s="217"/>
-      <c r="DF1" s="218"/>
-      <c r="DG1" s="216">
+      <c r="DE1" s="219"/>
+      <c r="DF1" s="220"/>
+      <c r="DG1" s="218">
         <v>36</v>
       </c>
-      <c r="DH1" s="217"/>
-      <c r="DI1" s="218"/>
-      <c r="DJ1" s="216">
+      <c r="DH1" s="219"/>
+      <c r="DI1" s="220"/>
+      <c r="DJ1" s="218">
         <v>37</v>
       </c>
-      <c r="DK1" s="217"/>
-      <c r="DL1" s="218"/>
-      <c r="DM1" s="216">
+      <c r="DK1" s="219"/>
+      <c r="DL1" s="220"/>
+      <c r="DM1" s="218">
         <v>38</v>
       </c>
-      <c r="DN1" s="217"/>
-      <c r="DO1" s="218"/>
+      <c r="DN1" s="219"/>
+      <c r="DO1" s="220"/>
     </row>
     <row r="2" spans="1:119" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="222" t="s">
+      <c r="C2" s="221" t="s">
         <v>396</v>
       </c>
-      <c r="D2" s="222" t="s">
+      <c r="D2" s="221" t="s">
         <v>397</v>
       </c>
-      <c r="E2" s="222" t="s">
+      <c r="E2" s="221" t="s">
         <v>398</v>
       </c>
-      <c r="F2" s="219" t="s">
+      <c r="F2" s="215" t="s">
         <v>346</v>
       </c>
-      <c r="G2" s="220"/>
-      <c r="H2" s="221"/>
-      <c r="I2" s="219" t="s">
+      <c r="G2" s="216"/>
+      <c r="H2" s="217"/>
+      <c r="I2" s="215" t="s">
         <v>331</v>
       </c>
-      <c r="J2" s="220"/>
-      <c r="K2" s="221"/>
-      <c r="L2" s="219" t="s">
+      <c r="J2" s="216"/>
+      <c r="K2" s="217"/>
+      <c r="L2" s="215" t="s">
         <v>330</v>
       </c>
-      <c r="M2" s="220"/>
-      <c r="N2" s="221"/>
-      <c r="O2" s="219" t="s">
+      <c r="M2" s="216"/>
+      <c r="N2" s="217"/>
+      <c r="O2" s="215" t="s">
         <v>328</v>
       </c>
-      <c r="P2" s="220"/>
-      <c r="Q2" s="221"/>
-      <c r="R2" s="219" t="s">
+      <c r="P2" s="216"/>
+      <c r="Q2" s="217"/>
+      <c r="R2" s="215" t="s">
         <v>335</v>
       </c>
-      <c r="S2" s="220"/>
-      <c r="T2" s="221"/>
-      <c r="U2" s="219" t="s">
+      <c r="S2" s="216"/>
+      <c r="T2" s="217"/>
+      <c r="U2" s="215" t="s">
         <v>320</v>
       </c>
-      <c r="V2" s="220"/>
-      <c r="W2" s="221"/>
-      <c r="X2" s="219" t="s">
+      <c r="V2" s="216"/>
+      <c r="W2" s="217"/>
+      <c r="X2" s="215" t="s">
         <v>337</v>
       </c>
-      <c r="Y2" s="220"/>
-      <c r="Z2" s="221"/>
-      <c r="AA2" s="219" t="s">
+      <c r="Y2" s="216"/>
+      <c r="Z2" s="217"/>
+      <c r="AA2" s="215" t="s">
         <v>334</v>
       </c>
-      <c r="AB2" s="220"/>
-      <c r="AC2" s="221"/>
-      <c r="AD2" s="219" t="s">
+      <c r="AB2" s="216"/>
+      <c r="AC2" s="217"/>
+      <c r="AD2" s="215" t="s">
         <v>321</v>
       </c>
-      <c r="AE2" s="220"/>
-      <c r="AF2" s="221"/>
-      <c r="AG2" s="219" t="s">
+      <c r="AE2" s="216"/>
+      <c r="AF2" s="217"/>
+      <c r="AG2" s="215" t="s">
         <v>347</v>
       </c>
-      <c r="AH2" s="220"/>
-      <c r="AI2" s="221"/>
-      <c r="AJ2" s="219" t="s">
+      <c r="AH2" s="216"/>
+      <c r="AI2" s="217"/>
+      <c r="AJ2" s="215" t="s">
         <v>324</v>
       </c>
-      <c r="AK2" s="220"/>
-      <c r="AL2" s="221"/>
-      <c r="AM2" s="219" t="s">
+      <c r="AK2" s="216"/>
+      <c r="AL2" s="217"/>
+      <c r="AM2" s="215" t="s">
         <v>323</v>
       </c>
-      <c r="AN2" s="220"/>
-      <c r="AO2" s="221"/>
-      <c r="AP2" s="219" t="s">
+      <c r="AN2" s="216"/>
+      <c r="AO2" s="217"/>
+      <c r="AP2" s="215" t="s">
         <v>332</v>
       </c>
-      <c r="AQ2" s="220"/>
-      <c r="AR2" s="221"/>
-      <c r="AS2" s="219" t="s">
+      <c r="AQ2" s="216"/>
+      <c r="AR2" s="217"/>
+      <c r="AS2" s="215" t="s">
         <v>329</v>
       </c>
-      <c r="AT2" s="220"/>
-      <c r="AU2" s="221"/>
-      <c r="AV2" s="219" t="s">
+      <c r="AT2" s="216"/>
+      <c r="AU2" s="217"/>
+      <c r="AV2" s="215" t="s">
         <v>336</v>
       </c>
-      <c r="AW2" s="220"/>
-      <c r="AX2" s="221"/>
-      <c r="AY2" s="219" t="s">
+      <c r="AW2" s="216"/>
+      <c r="AX2" s="217"/>
+      <c r="AY2" s="215" t="s">
         <v>305</v>
       </c>
-      <c r="AZ2" s="220"/>
-      <c r="BA2" s="221"/>
-      <c r="BB2" s="219" t="s">
+      <c r="AZ2" s="216"/>
+      <c r="BA2" s="217"/>
+      <c r="BB2" s="215" t="s">
         <v>326</v>
       </c>
-      <c r="BC2" s="220"/>
-      <c r="BD2" s="221"/>
-      <c r="BE2" s="219" t="s">
+      <c r="BC2" s="216"/>
+      <c r="BD2" s="217"/>
+      <c r="BE2" s="215" t="s">
         <v>325</v>
       </c>
-      <c r="BF2" s="220"/>
-      <c r="BG2" s="221"/>
-      <c r="BH2" s="219" t="s">
+      <c r="BF2" s="216"/>
+      <c r="BG2" s="217"/>
+      <c r="BH2" s="215" t="s">
         <v>348</v>
       </c>
-      <c r="BI2" s="220"/>
-      <c r="BJ2" s="221"/>
-      <c r="BK2" s="219" t="s">
+      <c r="BI2" s="216"/>
+      <c r="BJ2" s="217"/>
+      <c r="BK2" s="215" t="s">
         <v>332</v>
       </c>
-      <c r="BL2" s="220"/>
-      <c r="BM2" s="221"/>
-      <c r="BN2" s="219" t="s">
+      <c r="BL2" s="216"/>
+      <c r="BM2" s="217"/>
+      <c r="BN2" s="215" t="s">
         <v>347</v>
       </c>
-      <c r="BO2" s="220"/>
-      <c r="BP2" s="221"/>
-      <c r="BQ2" s="219" t="s">
+      <c r="BO2" s="216"/>
+      <c r="BP2" s="217"/>
+      <c r="BQ2" s="215" t="s">
         <v>324</v>
       </c>
-      <c r="BR2" s="220"/>
-      <c r="BS2" s="221"/>
-      <c r="BT2" s="219" t="s">
+      <c r="BR2" s="216"/>
+      <c r="BS2" s="217"/>
+      <c r="BT2" s="215" t="s">
         <v>323</v>
       </c>
-      <c r="BU2" s="220"/>
-      <c r="BV2" s="221"/>
-      <c r="BW2" s="219" t="s">
+      <c r="BU2" s="216"/>
+      <c r="BV2" s="217"/>
+      <c r="BW2" s="215" t="s">
         <v>321</v>
       </c>
-      <c r="BX2" s="220"/>
-      <c r="BY2" s="221"/>
-      <c r="BZ2" s="219" t="s">
+      <c r="BX2" s="216"/>
+      <c r="BY2" s="217"/>
+      <c r="BZ2" s="215" t="s">
         <v>348</v>
       </c>
-      <c r="CA2" s="220"/>
-      <c r="CB2" s="221"/>
-      <c r="CC2" s="219" t="s">
+      <c r="CA2" s="216"/>
+      <c r="CB2" s="217"/>
+      <c r="CC2" s="215" t="s">
         <v>325</v>
       </c>
-      <c r="CD2" s="220"/>
-      <c r="CE2" s="221"/>
-      <c r="CF2" s="219" t="s">
+      <c r="CD2" s="216"/>
+      <c r="CE2" s="217"/>
+      <c r="CF2" s="215" t="s">
         <v>305</v>
       </c>
-      <c r="CG2" s="220"/>
-      <c r="CH2" s="221"/>
-      <c r="CI2" s="219" t="s">
+      <c r="CG2" s="216"/>
+      <c r="CH2" s="217"/>
+      <c r="CI2" s="215" t="s">
         <v>326</v>
       </c>
-      <c r="CJ2" s="220"/>
-      <c r="CK2" s="221"/>
-      <c r="CL2" s="219" t="s">
+      <c r="CJ2" s="216"/>
+      <c r="CK2" s="217"/>
+      <c r="CL2" s="215" t="s">
         <v>330</v>
       </c>
-      <c r="CM2" s="220"/>
-      <c r="CN2" s="221"/>
-      <c r="CO2" s="219" t="s">
+      <c r="CM2" s="216"/>
+      <c r="CN2" s="217"/>
+      <c r="CO2" s="215" t="s">
         <v>328</v>
       </c>
-      <c r="CP2" s="220"/>
-      <c r="CQ2" s="221"/>
-      <c r="CR2" s="219" t="s">
+      <c r="CP2" s="216"/>
+      <c r="CQ2" s="217"/>
+      <c r="CR2" s="215" t="s">
         <v>346</v>
       </c>
-      <c r="CS2" s="220"/>
-      <c r="CT2" s="221"/>
-      <c r="CU2" s="219" t="s">
+      <c r="CS2" s="216"/>
+      <c r="CT2" s="217"/>
+      <c r="CU2" s="215" t="s">
         <v>331</v>
       </c>
-      <c r="CV2" s="220"/>
-      <c r="CW2" s="221"/>
-      <c r="CX2" s="219" t="s">
+      <c r="CV2" s="216"/>
+      <c r="CW2" s="217"/>
+      <c r="CX2" s="215" t="s">
         <v>336</v>
       </c>
-      <c r="CY2" s="220"/>
-      <c r="CZ2" s="221"/>
-      <c r="DA2" s="219" t="s">
+      <c r="CY2" s="216"/>
+      <c r="CZ2" s="217"/>
+      <c r="DA2" s="215" t="s">
         <v>329</v>
       </c>
-      <c r="DB2" s="220"/>
-      <c r="DC2" s="221"/>
-      <c r="DD2" s="219" t="s">
+      <c r="DB2" s="216"/>
+      <c r="DC2" s="217"/>
+      <c r="DD2" s="215" t="s">
         <v>320</v>
       </c>
-      <c r="DE2" s="220"/>
-      <c r="DF2" s="221"/>
-      <c r="DG2" s="219" t="s">
+      <c r="DE2" s="216"/>
+      <c r="DF2" s="217"/>
+      <c r="DG2" s="215" t="s">
         <v>337</v>
       </c>
-      <c r="DH2" s="220"/>
-      <c r="DI2" s="221"/>
-      <c r="DJ2" s="219" t="s">
+      <c r="DH2" s="216"/>
+      <c r="DI2" s="217"/>
+      <c r="DJ2" s="215" t="s">
         <v>334</v>
       </c>
-      <c r="DK2" s="220"/>
-      <c r="DL2" s="221"/>
-      <c r="DM2" s="219" t="s">
+      <c r="DK2" s="216"/>
+      <c r="DL2" s="217"/>
+      <c r="DM2" s="215" t="s">
         <v>335</v>
       </c>
-      <c r="DN2" s="220"/>
-      <c r="DO2" s="221"/>
+      <c r="DN2" s="216"/>
+      <c r="DO2" s="217"/>
     </row>
     <row r="3" spans="1:119" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -38125,8 +38115,8 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="224"/>
-      <c r="D3" s="224"/>
+      <c r="C3" s="222"/>
+      <c r="D3" s="222"/>
       <c r="E3" s="223"/>
       <c r="F3" s="160" t="s">
         <v>393</v>
@@ -42344,7 +42334,7 @@
         <v>45</v>
       </c>
       <c r="B31" s="148" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C31" s="58">
         <f t="shared" ref="C31:C38" si="8">SUM(F31,I31,L31,O31,R31,U31,X31,AA31,AD31,AG31,AJ31,AM31,AP31,AS31,AV31,AY31,BB31,BE31,BH31,BK31,BN31,BQ31,BT31,BW31,BZ31,CC31,CF31,CI31,CL31,CO31,CR31,CU31,CX31,DA31,DD31,DG31,DJ31,DM31)</f>
@@ -43888,6 +43878,69 @@
     </row>
   </sheetData>
   <mergeCells count="79">
+    <mergeCell ref="DM1:DO1"/>
+    <mergeCell ref="DM2:DO2"/>
+    <mergeCell ref="DA1:DC1"/>
+    <mergeCell ref="DA2:DC2"/>
+    <mergeCell ref="DD1:DF1"/>
+    <mergeCell ref="DD2:DF2"/>
+    <mergeCell ref="DG1:DI1"/>
+    <mergeCell ref="DG2:DI2"/>
+    <mergeCell ref="CU1:CW1"/>
+    <mergeCell ref="CU2:CW2"/>
+    <mergeCell ref="CX1:CZ1"/>
+    <mergeCell ref="CX2:CZ2"/>
+    <mergeCell ref="DJ1:DL1"/>
+    <mergeCell ref="DJ2:DL2"/>
+    <mergeCell ref="CL1:CN1"/>
+    <mergeCell ref="CL2:CN2"/>
+    <mergeCell ref="CO1:CQ1"/>
+    <mergeCell ref="CO2:CQ2"/>
+    <mergeCell ref="CR1:CT1"/>
+    <mergeCell ref="CR2:CT2"/>
+    <mergeCell ref="CC1:CE1"/>
+    <mergeCell ref="CC2:CE2"/>
+    <mergeCell ref="CF1:CH1"/>
+    <mergeCell ref="CF2:CH2"/>
+    <mergeCell ref="CI1:CK1"/>
+    <mergeCell ref="CI2:CK2"/>
+    <mergeCell ref="BT1:BV1"/>
+    <mergeCell ref="BT2:BV2"/>
+    <mergeCell ref="BW1:BY1"/>
+    <mergeCell ref="BW2:BY2"/>
+    <mergeCell ref="BZ1:CB1"/>
+    <mergeCell ref="BZ2:CB2"/>
+    <mergeCell ref="BK1:BM1"/>
+    <mergeCell ref="BK2:BM2"/>
+    <mergeCell ref="BN1:BP1"/>
+    <mergeCell ref="BN2:BP2"/>
+    <mergeCell ref="BQ1:BS1"/>
+    <mergeCell ref="BQ2:BS2"/>
+    <mergeCell ref="AS1:AU1"/>
+    <mergeCell ref="AS2:AU2"/>
+    <mergeCell ref="AV1:AX1"/>
+    <mergeCell ref="AV2:AX2"/>
+    <mergeCell ref="BH1:BJ1"/>
+    <mergeCell ref="BH2:BJ2"/>
+    <mergeCell ref="AY2:BA2"/>
+    <mergeCell ref="BB2:BD2"/>
+    <mergeCell ref="BE2:BG2"/>
+    <mergeCell ref="AJ1:AL1"/>
+    <mergeCell ref="AJ2:AL2"/>
+    <mergeCell ref="AM1:AO1"/>
+    <mergeCell ref="AM2:AO2"/>
+    <mergeCell ref="AP2:AR2"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
     <mergeCell ref="AD2:AF2"/>
     <mergeCell ref="AG2:AI2"/>
     <mergeCell ref="BB1:BD1"/>
@@ -43904,69 +43957,6 @@
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="X1:Z1"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="AJ1:AL1"/>
-    <mergeCell ref="AJ2:AL2"/>
-    <mergeCell ref="AM1:AO1"/>
-    <mergeCell ref="AM2:AO2"/>
-    <mergeCell ref="AP2:AR2"/>
-    <mergeCell ref="AS1:AU1"/>
-    <mergeCell ref="AS2:AU2"/>
-    <mergeCell ref="AV1:AX1"/>
-    <mergeCell ref="AV2:AX2"/>
-    <mergeCell ref="BH1:BJ1"/>
-    <mergeCell ref="BH2:BJ2"/>
-    <mergeCell ref="AY2:BA2"/>
-    <mergeCell ref="BB2:BD2"/>
-    <mergeCell ref="BE2:BG2"/>
-    <mergeCell ref="BK1:BM1"/>
-    <mergeCell ref="BK2:BM2"/>
-    <mergeCell ref="BN1:BP1"/>
-    <mergeCell ref="BN2:BP2"/>
-    <mergeCell ref="BQ1:BS1"/>
-    <mergeCell ref="BQ2:BS2"/>
-    <mergeCell ref="BT1:BV1"/>
-    <mergeCell ref="BT2:BV2"/>
-    <mergeCell ref="BW1:BY1"/>
-    <mergeCell ref="BW2:BY2"/>
-    <mergeCell ref="BZ1:CB1"/>
-    <mergeCell ref="BZ2:CB2"/>
-    <mergeCell ref="CC1:CE1"/>
-    <mergeCell ref="CC2:CE2"/>
-    <mergeCell ref="CF1:CH1"/>
-    <mergeCell ref="CF2:CH2"/>
-    <mergeCell ref="CI1:CK1"/>
-    <mergeCell ref="CI2:CK2"/>
-    <mergeCell ref="CL1:CN1"/>
-    <mergeCell ref="CL2:CN2"/>
-    <mergeCell ref="CO1:CQ1"/>
-    <mergeCell ref="CO2:CQ2"/>
-    <mergeCell ref="CR1:CT1"/>
-    <mergeCell ref="CR2:CT2"/>
-    <mergeCell ref="CU1:CW1"/>
-    <mergeCell ref="CU2:CW2"/>
-    <mergeCell ref="CX1:CZ1"/>
-    <mergeCell ref="CX2:CZ2"/>
-    <mergeCell ref="DJ1:DL1"/>
-    <mergeCell ref="DJ2:DL2"/>
-    <mergeCell ref="DM1:DO1"/>
-    <mergeCell ref="DM2:DO2"/>
-    <mergeCell ref="DA1:DC1"/>
-    <mergeCell ref="DA2:DC2"/>
-    <mergeCell ref="DD1:DF1"/>
-    <mergeCell ref="DD2:DF2"/>
-    <mergeCell ref="DG1:DI1"/>
-    <mergeCell ref="DG2:DI2"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:DO38">
     <cfRule type="cellIs" dxfId="18" priority="1" operator="between">
@@ -44002,138 +43992,138 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="234" t="s">
+      <c r="C1" s="236" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="234" t="s">
+      <c r="D1" s="236" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="234" t="s">
+      <c r="E1" s="236" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="225" t="s">
+      <c r="F1" s="227" t="s">
         <v>302</v>
       </c>
-      <c r="G1" s="226"/>
-      <c r="H1" s="226"/>
-      <c r="I1" s="226"/>
-      <c r="J1" s="226"/>
-      <c r="K1" s="226"/>
-      <c r="L1" s="226"/>
-      <c r="M1" s="226"/>
-      <c r="N1" s="226"/>
-      <c r="O1" s="226"/>
-      <c r="P1" s="226"/>
-      <c r="Q1" s="226"/>
-      <c r="R1" s="226"/>
-      <c r="S1" s="226"/>
-      <c r="T1" s="226"/>
-      <c r="U1" s="226"/>
-      <c r="V1" s="226"/>
-      <c r="W1" s="226"/>
-      <c r="X1" s="226"/>
-      <c r="Y1" s="226"/>
-      <c r="Z1" s="226"/>
-      <c r="AA1" s="226"/>
-      <c r="AB1" s="226"/>
-      <c r="AC1" s="227"/>
-      <c r="AD1" s="240" t="s">
+      <c r="G1" s="228"/>
+      <c r="H1" s="228"/>
+      <c r="I1" s="228"/>
+      <c r="J1" s="228"/>
+      <c r="K1" s="228"/>
+      <c r="L1" s="228"/>
+      <c r="M1" s="228"/>
+      <c r="N1" s="228"/>
+      <c r="O1" s="228"/>
+      <c r="P1" s="228"/>
+      <c r="Q1" s="228"/>
+      <c r="R1" s="228"/>
+      <c r="S1" s="228"/>
+      <c r="T1" s="228"/>
+      <c r="U1" s="228"/>
+      <c r="V1" s="228"/>
+      <c r="W1" s="228"/>
+      <c r="X1" s="228"/>
+      <c r="Y1" s="228"/>
+      <c r="Z1" s="228"/>
+      <c r="AA1" s="228"/>
+      <c r="AB1" s="228"/>
+      <c r="AC1" s="229"/>
+      <c r="AD1" s="239" t="s">
         <v>281</v>
       </c>
-      <c r="AE1" s="241"/>
-      <c r="AF1" s="241"/>
-      <c r="AG1" s="241"/>
-      <c r="AH1" s="241"/>
-      <c r="AI1" s="242"/>
-      <c r="AJ1" s="225" t="s">
+      <c r="AE1" s="240"/>
+      <c r="AF1" s="240"/>
+      <c r="AG1" s="240"/>
+      <c r="AH1" s="240"/>
+      <c r="AI1" s="241"/>
+      <c r="AJ1" s="227" t="s">
         <v>282</v>
       </c>
-      <c r="AK1" s="226"/>
-      <c r="AL1" s="226"/>
-      <c r="AM1" s="226"/>
-      <c r="AN1" s="226"/>
-      <c r="AO1" s="227"/>
-      <c r="AP1" s="228" t="s">
+      <c r="AK1" s="228"/>
+      <c r="AL1" s="228"/>
+      <c r="AM1" s="228"/>
+      <c r="AN1" s="228"/>
+      <c r="AO1" s="229"/>
+      <c r="AP1" s="230" t="s">
         <v>283</v>
       </c>
-      <c r="AQ1" s="229"/>
-      <c r="AR1" s="229"/>
-      <c r="AS1" s="229"/>
-      <c r="AT1" s="229"/>
-      <c r="AU1" s="230"/>
-      <c r="AV1" s="231" t="s">
+      <c r="AQ1" s="231"/>
+      <c r="AR1" s="231"/>
+      <c r="AS1" s="231"/>
+      <c r="AT1" s="231"/>
+      <c r="AU1" s="232"/>
+      <c r="AV1" s="233" t="s">
         <v>86</v>
       </c>
-      <c r="AW1" s="232"/>
-      <c r="AX1" s="233"/>
+      <c r="AW1" s="234"/>
+      <c r="AX1" s="235"/>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="235"/>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="237" t="s">
-        <v>458</v>
-      </c>
-      <c r="G2" s="238"/>
-      <c r="H2" s="239"/>
-      <c r="I2" s="237" t="s">
+      <c r="C2" s="237"/>
+      <c r="D2" s="237"/>
+      <c r="E2" s="237"/>
+      <c r="F2" s="224" t="s">
+        <v>457</v>
+      </c>
+      <c r="G2" s="225"/>
+      <c r="H2" s="226"/>
+      <c r="I2" s="224" t="s">
+        <v>459</v>
+      </c>
+      <c r="J2" s="225"/>
+      <c r="K2" s="226"/>
+      <c r="L2" s="224" t="s">
+        <v>460</v>
+      </c>
+      <c r="M2" s="225"/>
+      <c r="N2" s="226"/>
+      <c r="O2" s="224" t="s">
         <v>461</v>
       </c>
-      <c r="J2" s="238"/>
-      <c r="K2" s="239"/>
-      <c r="L2" s="237" t="s">
+      <c r="P2" s="225"/>
+      <c r="Q2" s="226"/>
+      <c r="R2" s="224" t="s">
         <v>462</v>
       </c>
-      <c r="M2" s="238"/>
-      <c r="N2" s="239"/>
-      <c r="O2" s="237" t="s">
+      <c r="S2" s="225"/>
+      <c r="T2" s="226"/>
+      <c r="U2" s="224" t="s">
         <v>463</v>
       </c>
-      <c r="P2" s="238"/>
-      <c r="Q2" s="239"/>
-      <c r="R2" s="237" t="s">
+      <c r="V2" s="225"/>
+      <c r="W2" s="226"/>
+      <c r="X2" s="224" t="s">
         <v>464</v>
       </c>
-      <c r="S2" s="238"/>
-      <c r="T2" s="239"/>
-      <c r="U2" s="237" t="s">
+      <c r="Y2" s="225"/>
+      <c r="Z2" s="226"/>
+      <c r="AA2" s="224" t="s">
         <v>465</v>
       </c>
-      <c r="V2" s="238"/>
-      <c r="W2" s="239"/>
-      <c r="X2" s="237" t="s">
-        <v>466</v>
-      </c>
-      <c r="Y2" s="238"/>
-      <c r="Z2" s="239"/>
-      <c r="AA2" s="237" t="s">
-        <v>467</v>
-      </c>
-      <c r="AB2" s="238"/>
-      <c r="AC2" s="238"/>
-      <c r="AD2" s="237"/>
-      <c r="AE2" s="238"/>
-      <c r="AF2" s="239"/>
-      <c r="AG2" s="237"/>
-      <c r="AH2" s="238"/>
-      <c r="AI2" s="239"/>
-      <c r="AJ2" s="237"/>
-      <c r="AK2" s="238"/>
-      <c r="AL2" s="239"/>
-      <c r="AM2" s="237"/>
-      <c r="AN2" s="238"/>
-      <c r="AO2" s="239"/>
-      <c r="AP2" s="237"/>
-      <c r="AQ2" s="238"/>
-      <c r="AR2" s="239"/>
-      <c r="AS2" s="237"/>
-      <c r="AT2" s="238"/>
-      <c r="AU2" s="239"/>
-      <c r="AV2" s="237"/>
-      <c r="AW2" s="238"/>
-      <c r="AX2" s="239"/>
+      <c r="AB2" s="225"/>
+      <c r="AC2" s="225"/>
+      <c r="AD2" s="224"/>
+      <c r="AE2" s="225"/>
+      <c r="AF2" s="226"/>
+      <c r="AG2" s="224"/>
+      <c r="AH2" s="225"/>
+      <c r="AI2" s="226"/>
+      <c r="AJ2" s="224"/>
+      <c r="AK2" s="225"/>
+      <c r="AL2" s="226"/>
+      <c r="AM2" s="224"/>
+      <c r="AN2" s="225"/>
+      <c r="AO2" s="226"/>
+      <c r="AP2" s="224"/>
+      <c r="AQ2" s="225"/>
+      <c r="AR2" s="226"/>
+      <c r="AS2" s="224"/>
+      <c r="AT2" s="225"/>
+      <c r="AU2" s="226"/>
+      <c r="AV2" s="224"/>
+      <c r="AW2" s="225"/>
+      <c r="AX2" s="226"/>
     </row>
     <row r="3" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -44142,9 +44132,9 @@
       <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="236"/>
-      <c r="D3" s="236"/>
-      <c r="E3" s="236"/>
+      <c r="C3" s="238"/>
+      <c r="D3" s="238"/>
+      <c r="E3" s="238"/>
       <c r="F3" s="169" t="s">
         <v>393</v>
       </c>
@@ -46153,7 +46143,7 @@
         <v>45</v>
       </c>
       <c r="B31" s="148" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C31" s="58">
         <f t="shared" ref="C31:C38" si="8">SUM(F31,I31,L31,O31,R31,X31,AA31,AD31,U31,AG31,AJ31,AM31,AP31,AS31,AV31)</f>
@@ -46858,13 +46848,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="F1:AC1"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="U2:W2"/>
-    <mergeCell ref="X2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="AJ1:AO1"/>
     <mergeCell ref="AP1:AU1"/>
     <mergeCell ref="AV1:AX1"/>
@@ -46881,6 +46864,13 @@
     <mergeCell ref="AD1:AI1"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="I2:K2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="F1:AC1"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:W2"/>
+    <mergeCell ref="X2:Z2"/>
+    <mergeCell ref="AA2:AC2"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:AW32">
     <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
@@ -46915,70 +46905,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C1" s="234" t="s">
+      <c r="C1" s="236" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="234" t="s">
+      <c r="D1" s="236" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="234" t="s">
+      <c r="E1" s="236" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="274" t="s">
+      <c r="F1" s="266" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="275"/>
-      <c r="H1" s="276"/>
-      <c r="I1" s="277" t="s">
+      <c r="G1" s="267"/>
+      <c r="H1" s="268"/>
+      <c r="I1" s="269" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="278"/>
-      <c r="K1" s="279"/>
-      <c r="L1" s="244" t="s">
+      <c r="J1" s="270"/>
+      <c r="K1" s="271"/>
+      <c r="L1" s="273" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="245"/>
-      <c r="N1" s="246"/>
-      <c r="O1" s="247" t="s">
+      <c r="M1" s="274"/>
+      <c r="N1" s="275"/>
+      <c r="O1" s="276" t="s">
         <v>199</v>
       </c>
-      <c r="P1" s="248"/>
-      <c r="Q1" s="249"/>
-      <c r="R1" s="250" t="s">
+      <c r="P1" s="277"/>
+      <c r="Q1" s="278"/>
+      <c r="R1" s="242" t="s">
         <v>200</v>
       </c>
-      <c r="S1" s="251"/>
-      <c r="T1" s="252"/>
-      <c r="U1" s="253" t="s">
+      <c r="S1" s="243"/>
+      <c r="T1" s="244"/>
+      <c r="U1" s="245" t="s">
         <v>306</v>
       </c>
-      <c r="V1" s="254"/>
-      <c r="W1" s="255"/>
+      <c r="V1" s="246"/>
+      <c r="W1" s="247"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
-      <c r="C2" s="235"/>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="256"/>
-      <c r="G2" s="257"/>
-      <c r="H2" s="258"/>
-      <c r="I2" s="271"/>
-      <c r="J2" s="272"/>
-      <c r="K2" s="273"/>
-      <c r="L2" s="268"/>
-      <c r="M2" s="269"/>
-      <c r="N2" s="270"/>
-      <c r="O2" s="265"/>
-      <c r="P2" s="266"/>
-      <c r="Q2" s="267"/>
-      <c r="R2" s="262"/>
-      <c r="S2" s="263"/>
-      <c r="T2" s="264"/>
-      <c r="U2" s="259"/>
-      <c r="V2" s="260"/>
-      <c r="W2" s="261"/>
+      <c r="C2" s="237"/>
+      <c r="D2" s="237"/>
+      <c r="E2" s="237"/>
+      <c r="F2" s="248"/>
+      <c r="G2" s="249"/>
+      <c r="H2" s="250"/>
+      <c r="I2" s="263"/>
+      <c r="J2" s="264"/>
+      <c r="K2" s="265"/>
+      <c r="L2" s="260"/>
+      <c r="M2" s="261"/>
+      <c r="N2" s="262"/>
+      <c r="O2" s="257"/>
+      <c r="P2" s="258"/>
+      <c r="Q2" s="259"/>
+      <c r="R2" s="254"/>
+      <c r="S2" s="255"/>
+      <c r="T2" s="256"/>
+      <c r="U2" s="251"/>
+      <c r="V2" s="252"/>
+      <c r="W2" s="253"/>
     </row>
     <row r="3" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -46987,9 +46977,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="243"/>
-      <c r="D3" s="243"/>
-      <c r="E3" s="243"/>
+      <c r="C3" s="272"/>
+      <c r="D3" s="272"/>
+      <c r="E3" s="272"/>
       <c r="F3" s="188" t="s">
         <v>393</v>
       </c>
@@ -48076,7 +48066,7 @@
         <v>45</v>
       </c>
       <c r="B31" s="148" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C31" s="58">
         <f t="shared" ref="C31:C38" si="6">SUM(F31,I31,L31,O31,R31,U31)</f>
@@ -48451,6 +48441,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="O1:Q1"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="F2:H2"/>
@@ -48461,11 +48456,6 @@
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="O1:Q1"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:W32">
     <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
@@ -53902,7 +53892,7 @@
         <v>45</v>
       </c>
       <c r="B33" s="22" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C33" s="25">
         <v>0</v>
@@ -53942,7 +53932,7 @@
         <v>45</v>
       </c>
       <c r="N33" s="45" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="O33" s="26">
         <v>0</v>
@@ -53979,7 +53969,7 @@
         <v>0</v>
       </c>
       <c r="Z33" s="23" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="AA33" s="24">
         <v>0</v>
@@ -54016,7 +54006,7 @@
         <v>0</v>
       </c>
       <c r="AL33" s="19" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="AM33" s="18">
         <v>0</v>
@@ -54053,7 +54043,7 @@
         <v>0</v>
       </c>
       <c r="AX33" s="32" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="AY33" s="33">
         <v>0</v>
@@ -55472,72 +55462,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="C1" s="234" t="s">
+      <c r="C1" s="236" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="234" t="s">
+      <c r="D1" s="236" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="234" t="s">
+      <c r="E1" s="236" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="274" t="s">
+      <c r="F1" s="266" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="275"/>
-      <c r="H1" s="276"/>
-      <c r="I1" s="277" t="s">
+      <c r="G1" s="267"/>
+      <c r="H1" s="268"/>
+      <c r="I1" s="269" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="278"/>
-      <c r="K1" s="279"/>
-      <c r="L1" s="244" t="s">
+      <c r="J1" s="270"/>
+      <c r="K1" s="271"/>
+      <c r="L1" s="273" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="245"/>
-      <c r="N1" s="246"/>
-      <c r="O1" s="247" t="s">
+      <c r="M1" s="274"/>
+      <c r="N1" s="275"/>
+      <c r="O1" s="276" t="s">
         <v>199</v>
       </c>
-      <c r="P1" s="248"/>
-      <c r="Q1" s="249"/>
-      <c r="R1" s="250" t="s">
+      <c r="P1" s="277"/>
+      <c r="Q1" s="278"/>
+      <c r="R1" s="242" t="s">
         <v>200</v>
       </c>
-      <c r="S1" s="251"/>
-      <c r="T1" s="252"/>
-      <c r="U1" s="253" t="s">
+      <c r="S1" s="243"/>
+      <c r="T1" s="244"/>
+      <c r="U1" s="245" t="s">
         <v>306</v>
       </c>
-      <c r="V1" s="254"/>
-      <c r="W1" s="255"/>
+      <c r="V1" s="246"/>
+      <c r="W1" s="247"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="17"/>
-      <c r="C2" s="235"/>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="256" t="s">
+      <c r="C2" s="237"/>
+      <c r="D2" s="237"/>
+      <c r="E2" s="237"/>
+      <c r="F2" s="248" t="s">
         <v>432</v>
       </c>
-      <c r="G2" s="257"/>
-      <c r="H2" s="258"/>
-      <c r="I2" s="271"/>
-      <c r="J2" s="272"/>
-      <c r="K2" s="273"/>
-      <c r="L2" s="268"/>
-      <c r="M2" s="269"/>
-      <c r="N2" s="270"/>
-      <c r="O2" s="265"/>
-      <c r="P2" s="266"/>
-      <c r="Q2" s="267"/>
-      <c r="R2" s="262"/>
-      <c r="S2" s="263"/>
-      <c r="T2" s="264"/>
-      <c r="U2" s="259"/>
-      <c r="V2" s="260"/>
-      <c r="W2" s="261"/>
+      <c r="G2" s="249"/>
+      <c r="H2" s="250"/>
+      <c r="I2" s="263"/>
+      <c r="J2" s="264"/>
+      <c r="K2" s="265"/>
+      <c r="L2" s="260"/>
+      <c r="M2" s="261"/>
+      <c r="N2" s="262"/>
+      <c r="O2" s="257"/>
+      <c r="P2" s="258"/>
+      <c r="Q2" s="259"/>
+      <c r="R2" s="254"/>
+      <c r="S2" s="255"/>
+      <c r="T2" s="256"/>
+      <c r="U2" s="251"/>
+      <c r="V2" s="252"/>
+      <c r="W2" s="253"/>
     </row>
     <row r="3" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -55546,9 +55536,9 @@
       <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="243"/>
-      <c r="D3" s="243"/>
-      <c r="E3" s="243"/>
+      <c r="C3" s="272"/>
+      <c r="D3" s="272"/>
+      <c r="E3" s="272"/>
       <c r="F3" s="188" t="s">
         <v>393</v>
       </c>
@@ -56667,7 +56657,7 @@
         <v>45</v>
       </c>
       <c r="B31" s="148" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C31" s="58">
         <f t="shared" ref="C31:C38" si="6">SUM(F31,I31,L31,O31,R31,U31)</f>
@@ -57052,11 +57042,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="F2:H2"/>
@@ -57067,6 +57052,11 @@
     <mergeCell ref="U2:W2"/>
     <mergeCell ref="L1:N1"/>
     <mergeCell ref="O1:Q1"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:W32">
     <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
@@ -57094,11 +57084,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C1" s="280" t="s">
+      <c r="C1" s="279" t="s">
         <v>340</v>
       </c>
-      <c r="D1" s="281"/>
-      <c r="E1" s="281"/>
+      <c r="D1" s="280"/>
+      <c r="E1" s="280"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -57459,7 +57449,7 @@
         <v>45</v>
       </c>
       <c r="B30" s="148" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C30" s="20"/>
       <c r="D30" s="20"/>
@@ -57573,51 +57563,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C1" s="302" t="s">
+      <c r="C1" s="281" t="s">
         <v>202</v>
       </c>
-      <c r="D1" s="303"/>
-      <c r="E1" s="303"/>
-      <c r="F1" s="303"/>
-      <c r="G1" s="303"/>
-      <c r="H1" s="303"/>
-      <c r="I1" s="304"/>
+      <c r="D1" s="282"/>
+      <c r="E1" s="282"/>
+      <c r="F1" s="282"/>
+      <c r="G1" s="282"/>
+      <c r="H1" s="282"/>
+      <c r="I1" s="283"/>
       <c r="J1" s="114" t="s">
         <v>195</v>
       </c>
       <c r="K1" s="115" t="s">
         <v>194</v>
       </c>
-      <c r="L1" s="283" t="s">
+      <c r="L1" s="306" t="s">
         <v>287</v>
       </c>
-      <c r="M1" s="288"/>
-      <c r="N1" s="288"/>
-      <c r="O1" s="288"/>
-      <c r="P1" s="288"/>
-      <c r="Q1" s="288"/>
-      <c r="R1" s="288"/>
-      <c r="S1" s="288"/>
-      <c r="T1" s="288"/>
-      <c r="U1" s="288"/>
-      <c r="V1" s="288"/>
-      <c r="W1" s="288"/>
-      <c r="X1" s="288"/>
-      <c r="Y1" s="288"/>
-      <c r="Z1" s="288"/>
-      <c r="AA1" s="288"/>
-      <c r="AB1" s="288"/>
-      <c r="AC1" s="288"/>
-      <c r="AD1" s="288"/>
-      <c r="AE1" s="288"/>
-      <c r="AF1" s="288"/>
-      <c r="AG1" s="289"/>
-      <c r="AH1" s="283" t="s">
+      <c r="M1" s="311"/>
+      <c r="N1" s="311"/>
+      <c r="O1" s="311"/>
+      <c r="P1" s="311"/>
+      <c r="Q1" s="311"/>
+      <c r="R1" s="311"/>
+      <c r="S1" s="311"/>
+      <c r="T1" s="311"/>
+      <c r="U1" s="311"/>
+      <c r="V1" s="311"/>
+      <c r="W1" s="311"/>
+      <c r="X1" s="311"/>
+      <c r="Y1" s="311"/>
+      <c r="Z1" s="311"/>
+      <c r="AA1" s="311"/>
+      <c r="AB1" s="311"/>
+      <c r="AC1" s="311"/>
+      <c r="AD1" s="311"/>
+      <c r="AE1" s="311"/>
+      <c r="AF1" s="311"/>
+      <c r="AG1" s="312"/>
+      <c r="AH1" s="306" t="s">
         <v>175</v>
       </c>
-      <c r="AI1" s="284"/>
-      <c r="AJ1" s="284"/>
-      <c r="AK1" s="285"/>
+      <c r="AI1" s="307"/>
+      <c r="AJ1" s="307"/>
+      <c r="AK1" s="308"/>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B2" s="111"/>
@@ -62817,15 +62807,15 @@
         <f t="shared" ref="J80:J111" si="2">H80-I80</f>
         <v>2</v>
       </c>
-      <c r="K80" s="290" t="s">
-        <v>434</v>
-      </c>
-      <c r="L80" s="291"/>
-      <c r="M80" s="292"/>
+      <c r="K80" s="313" t="s">
+        <v>433</v>
+      </c>
+      <c r="L80" s="314"/>
+      <c r="M80" s="315"/>
       <c r="O80" s="133"/>
       <c r="P80" s="133"/>
-      <c r="W80" s="286"/>
-      <c r="X80" s="286"/>
+      <c r="W80" s="309"/>
+      <c r="X80" s="309"/>
       <c r="Y80" s="70" t="s">
         <v>211</v>
       </c>
@@ -62875,15 +62865,15 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K81" s="293"/>
-      <c r="L81" s="294"/>
-      <c r="M81" s="295"/>
+      <c r="K81" s="316"/>
+      <c r="L81" s="317"/>
+      <c r="M81" s="318"/>
       <c r="O81" s="133"/>
       <c r="P81" s="133"/>
-      <c r="W81" s="286" t="s">
+      <c r="W81" s="309" t="s">
         <v>209</v>
       </c>
-      <c r="X81" s="286"/>
+      <c r="X81" s="309"/>
       <c r="Y81" s="70">
         <f>COUNTIF(L3:AG40,3)</f>
         <v>481</v>
@@ -62939,17 +62929,17 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="K82" s="296" t="s">
-        <v>435</v>
-      </c>
-      <c r="L82" s="297"/>
-      <c r="M82" s="298"/>
+      <c r="K82" s="319" t="s">
+        <v>434</v>
+      </c>
+      <c r="L82" s="320"/>
+      <c r="M82" s="321"/>
       <c r="O82" s="133"/>
       <c r="P82" s="133"/>
-      <c r="W82" s="286" t="s">
+      <c r="W82" s="309" t="s">
         <v>210</v>
       </c>
-      <c r="X82" s="286"/>
+      <c r="X82" s="309"/>
       <c r="Y82" s="70">
         <f>COUNTIF(K3:K40,3)+COUNTIF(J3:J15,3)</f>
         <v>25</v>
@@ -63005,17 +62995,17 @@
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="K83" s="299" t="s">
-        <v>436</v>
-      </c>
-      <c r="L83" s="300"/>
-      <c r="M83" s="301"/>
+      <c r="K83" s="322" t="s">
+        <v>435</v>
+      </c>
+      <c r="L83" s="323"/>
+      <c r="M83" s="324"/>
       <c r="O83" s="133"/>
       <c r="P83" s="133"/>
-      <c r="W83" s="287" t="s">
+      <c r="W83" s="310" t="s">
         <v>97</v>
       </c>
-      <c r="X83" s="287"/>
+      <c r="X83" s="310"/>
       <c r="Y83" s="194">
         <v>227</v>
       </c>
@@ -63068,15 +63058,15 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="K84" s="308" t="s">
+      <c r="K84" s="287" t="s">
         <v>284</v>
       </c>
-      <c r="L84" s="309"/>
-      <c r="M84" s="310"/>
+      <c r="L84" s="288"/>
+      <c r="M84" s="289"/>
       <c r="O84" s="141"/>
       <c r="P84" s="141"/>
-      <c r="W84" s="282"/>
-      <c r="X84" s="282"/>
+      <c r="W84" s="305"/>
+      <c r="X84" s="305"/>
       <c r="Y84" s="196"/>
       <c r="Z84" s="196"/>
       <c r="AA84" s="196"/>
@@ -63114,9 +63104,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K85" s="311"/>
-      <c r="L85" s="312"/>
-      <c r="M85" s="313"/>
+      <c r="K85" s="290"/>
+      <c r="L85" s="291"/>
+      <c r="M85" s="292"/>
       <c r="O85" s="141"/>
       <c r="P85" s="141"/>
     </row>
@@ -63150,9 +63140,9 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="K86" s="311"/>
-      <c r="L86" s="312"/>
-      <c r="M86" s="313"/>
+      <c r="K86" s="290"/>
+      <c r="L86" s="291"/>
+      <c r="M86" s="292"/>
       <c r="O86" s="141"/>
       <c r="P86" s="141"/>
     </row>
@@ -63186,9 +63176,9 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="K87" s="311"/>
-      <c r="L87" s="312"/>
-      <c r="M87" s="313"/>
+      <c r="K87" s="290"/>
+      <c r="L87" s="291"/>
+      <c r="M87" s="292"/>
       <c r="O87" s="141"/>
       <c r="P87" s="141"/>
     </row>
@@ -63222,9 +63212,9 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K88" s="311"/>
-      <c r="L88" s="312"/>
-      <c r="M88" s="313"/>
+      <c r="K88" s="290"/>
+      <c r="L88" s="291"/>
+      <c r="M88" s="292"/>
       <c r="O88" s="141"/>
       <c r="P88" s="141"/>
     </row>
@@ -63258,9 +63248,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K89" s="311"/>
-      <c r="L89" s="312"/>
-      <c r="M89" s="313"/>
+      <c r="K89" s="290"/>
+      <c r="L89" s="291"/>
+      <c r="M89" s="292"/>
       <c r="O89" s="141"/>
       <c r="P89" s="141"/>
     </row>
@@ -63294,9 +63284,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K90" s="311"/>
-      <c r="L90" s="312"/>
-      <c r="M90" s="313"/>
+      <c r="K90" s="290"/>
+      <c r="L90" s="291"/>
+      <c r="M90" s="292"/>
       <c r="O90" s="141"/>
       <c r="P90" s="141"/>
     </row>
@@ -63330,9 +63320,9 @@
         <f t="shared" si="2"/>
         <v>47</v>
       </c>
-      <c r="K91" s="311"/>
-      <c r="L91" s="312"/>
-      <c r="M91" s="313"/>
+      <c r="K91" s="290"/>
+      <c r="L91" s="291"/>
+      <c r="M91" s="292"/>
       <c r="O91" s="141"/>
       <c r="P91" s="141"/>
     </row>
@@ -63366,9 +63356,9 @@
         <f t="shared" si="2"/>
         <v>51</v>
       </c>
-      <c r="K92" s="311"/>
-      <c r="L92" s="312"/>
-      <c r="M92" s="313"/>
+      <c r="K92" s="290"/>
+      <c r="L92" s="291"/>
+      <c r="M92" s="292"/>
       <c r="O92" s="141"/>
       <c r="P92" s="141"/>
     </row>
@@ -63402,9 +63392,9 @@
         <f t="shared" si="2"/>
         <v>37</v>
       </c>
-      <c r="K93" s="311"/>
-      <c r="L93" s="312"/>
-      <c r="M93" s="313"/>
+      <c r="K93" s="290"/>
+      <c r="L93" s="291"/>
+      <c r="M93" s="292"/>
       <c r="O93" s="141"/>
       <c r="P93" s="141"/>
     </row>
@@ -63438,9 +63428,9 @@
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="K94" s="311"/>
-      <c r="L94" s="312"/>
-      <c r="M94" s="313"/>
+      <c r="K94" s="290"/>
+      <c r="L94" s="291"/>
+      <c r="M94" s="292"/>
       <c r="O94" s="141"/>
       <c r="P94" s="141"/>
     </row>
@@ -63474,9 +63464,9 @@
         <f t="shared" si="2"/>
         <v>43</v>
       </c>
-      <c r="K95" s="311"/>
-      <c r="L95" s="312"/>
-      <c r="M95" s="313"/>
+      <c r="K95" s="290"/>
+      <c r="L95" s="291"/>
+      <c r="M95" s="292"/>
       <c r="O95" s="141"/>
       <c r="P95" s="141"/>
     </row>
@@ -63510,9 +63500,9 @@
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="K96" s="311"/>
-      <c r="L96" s="312"/>
-      <c r="M96" s="313"/>
+      <c r="K96" s="290"/>
+      <c r="L96" s="291"/>
+      <c r="M96" s="292"/>
       <c r="O96" s="141"/>
       <c r="P96" s="141"/>
     </row>
@@ -63546,9 +63536,9 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="K97" s="311"/>
-      <c r="L97" s="312"/>
-      <c r="M97" s="313"/>
+      <c r="K97" s="290"/>
+      <c r="L97" s="291"/>
+      <c r="M97" s="292"/>
       <c r="O97" s="141"/>
       <c r="P97" s="141"/>
     </row>
@@ -63582,9 +63572,9 @@
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="K98" s="311"/>
-      <c r="L98" s="312"/>
-      <c r="M98" s="313"/>
+      <c r="K98" s="290"/>
+      <c r="L98" s="291"/>
+      <c r="M98" s="292"/>
       <c r="O98" s="141"/>
       <c r="P98" s="141"/>
     </row>
@@ -63618,9 +63608,9 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="K99" s="311"/>
-      <c r="L99" s="312"/>
-      <c r="M99" s="313"/>
+      <c r="K99" s="290"/>
+      <c r="L99" s="291"/>
+      <c r="M99" s="292"/>
       <c r="O99" s="141"/>
       <c r="P99" s="141"/>
     </row>
@@ -63654,9 +63644,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K100" s="311"/>
-      <c r="L100" s="312"/>
-      <c r="M100" s="313"/>
+      <c r="K100" s="290"/>
+      <c r="L100" s="291"/>
+      <c r="M100" s="292"/>
       <c r="O100" s="141"/>
       <c r="P100" s="141"/>
     </row>
@@ -63690,9 +63680,9 @@
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="K101" s="311"/>
-      <c r="L101" s="312"/>
-      <c r="M101" s="313"/>
+      <c r="K101" s="290"/>
+      <c r="L101" s="291"/>
+      <c r="M101" s="292"/>
       <c r="O101" s="141"/>
       <c r="P101" s="141"/>
     </row>
@@ -63726,9 +63716,9 @@
         <f t="shared" si="2"/>
         <v>35</v>
       </c>
-      <c r="K102" s="311"/>
-      <c r="L102" s="312"/>
-      <c r="M102" s="313"/>
+      <c r="K102" s="290"/>
+      <c r="L102" s="291"/>
+      <c r="M102" s="292"/>
       <c r="O102" s="141"/>
       <c r="P102" s="141"/>
     </row>
@@ -63762,9 +63752,9 @@
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="K103" s="311"/>
-      <c r="L103" s="312"/>
-      <c r="M103" s="313"/>
+      <c r="K103" s="290"/>
+      <c r="L103" s="291"/>
+      <c r="M103" s="292"/>
       <c r="O103" s="141"/>
       <c r="P103" s="141"/>
     </row>
@@ -63798,9 +63788,9 @@
         <f t="shared" si="2"/>
         <v>33</v>
       </c>
-      <c r="K104" s="311"/>
-      <c r="L104" s="312"/>
-      <c r="M104" s="313"/>
+      <c r="K104" s="290"/>
+      <c r="L104" s="291"/>
+      <c r="M104" s="292"/>
       <c r="O104" s="141"/>
       <c r="P104" s="141"/>
     </row>
@@ -63834,9 +63824,9 @@
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="K105" s="314"/>
-      <c r="L105" s="315"/>
-      <c r="M105" s="316"/>
+      <c r="K105" s="293"/>
+      <c r="L105" s="294"/>
+      <c r="M105" s="295"/>
       <c r="O105" s="141"/>
       <c r="P105" s="141"/>
     </row>
@@ -63870,11 +63860,11 @@
         <f t="shared" si="2"/>
         <v>21</v>
       </c>
-      <c r="K106" s="305" t="s">
+      <c r="K106" s="284" t="s">
         <v>286</v>
       </c>
-      <c r="L106" s="306"/>
-      <c r="M106" s="307"/>
+      <c r="L106" s="285"/>
+      <c r="M106" s="286"/>
       <c r="O106" s="126"/>
       <c r="P106" s="126"/>
     </row>
@@ -63908,11 +63898,11 @@
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="K107" s="305" t="s">
+      <c r="K107" s="284" t="s">
         <v>288</v>
       </c>
-      <c r="L107" s="306"/>
-      <c r="M107" s="307"/>
+      <c r="L107" s="285"/>
+      <c r="M107" s="286"/>
       <c r="O107" s="126"/>
       <c r="P107" s="126"/>
     </row>
@@ -63946,11 +63936,11 @@
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="K108" s="317" t="s">
+      <c r="K108" s="296" t="s">
         <v>289</v>
       </c>
-      <c r="L108" s="318"/>
-      <c r="M108" s="319"/>
+      <c r="L108" s="297"/>
+      <c r="M108" s="298"/>
       <c r="O108" s="126"/>
       <c r="P108" s="126"/>
     </row>
@@ -63984,9 +63974,9 @@
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="K109" s="320"/>
-      <c r="L109" s="321"/>
-      <c r="M109" s="322"/>
+      <c r="K109" s="299"/>
+      <c r="L109" s="300"/>
+      <c r="M109" s="301"/>
       <c r="O109" s="126"/>
       <c r="P109" s="126"/>
     </row>
@@ -64020,9 +64010,9 @@
         <f t="shared" si="2"/>
         <v>45</v>
       </c>
-      <c r="K110" s="320"/>
-      <c r="L110" s="321"/>
-      <c r="M110" s="322"/>
+      <c r="K110" s="299"/>
+      <c r="L110" s="300"/>
+      <c r="M110" s="301"/>
       <c r="O110" s="126"/>
       <c r="P110" s="126"/>
     </row>
@@ -64056,9 +64046,9 @@
         <f t="shared" si="2"/>
         <v>62</v>
       </c>
-      <c r="K111" s="320"/>
-      <c r="L111" s="321"/>
-      <c r="M111" s="322"/>
+      <c r="K111" s="299"/>
+      <c r="L111" s="300"/>
+      <c r="M111" s="301"/>
       <c r="O111" s="126"/>
       <c r="P111" s="126"/>
     </row>
@@ -64096,9 +64086,9 @@
         <f t="shared" ref="J112:J114" si="6">H112-I112</f>
         <v>34</v>
       </c>
-      <c r="K112" s="320"/>
-      <c r="L112" s="321"/>
-      <c r="M112" s="322"/>
+      <c r="K112" s="299"/>
+      <c r="L112" s="300"/>
+      <c r="M112" s="301"/>
     </row>
     <row r="113" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="156" t="s">
@@ -64134,13 +64124,13 @@
         <f t="shared" si="6"/>
         <v>43</v>
       </c>
-      <c r="K113" s="320"/>
-      <c r="L113" s="321"/>
-      <c r="M113" s="322"/>
+      <c r="K113" s="299"/>
+      <c r="L113" s="300"/>
+      <c r="M113" s="301"/>
     </row>
     <row r="114" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="93" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B114" s="122"/>
       <c r="C114" s="122"/>
@@ -64162,7 +64152,7 @@
       </c>
       <c r="H114" s="122">
         <f>Match!R4</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I114" s="122">
         <f>Match!S4</f>
@@ -64170,20 +64160,15 @@
       </c>
       <c r="J114" s="154">
         <f t="shared" si="6"/>
-        <v>5</v>
-      </c>
-      <c r="K114" s="323"/>
-      <c r="L114" s="324"/>
-      <c r="M114" s="325"/>
+        <v>6</v>
+      </c>
+      <c r="K114" s="302"/>
+      <c r="L114" s="303"/>
+      <c r="M114" s="304"/>
     </row>
   </sheetData>
   <autoFilter ref="A79:J112" xr:uid="{9C81160F-C24B-449F-8F5A-CB622AB71070}"/>
   <mergeCells count="15">
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="K106:M106"/>
-    <mergeCell ref="K107:M107"/>
-    <mergeCell ref="K84:M105"/>
-    <mergeCell ref="K108:M114"/>
     <mergeCell ref="W84:X84"/>
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="W80:X80"/>
@@ -64194,6 +64179,11 @@
     <mergeCell ref="K80:M81"/>
     <mergeCell ref="K82:M82"/>
     <mergeCell ref="K83:M83"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="K106:M106"/>
+    <mergeCell ref="K107:M107"/>
+    <mergeCell ref="K84:M105"/>
+    <mergeCell ref="K108:M114"/>
   </mergeCells>
   <phoneticPr fontId="23" type="noConversion"/>
   <conditionalFormatting sqref="A3:A40">
@@ -64285,32 +64275,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="203" t="s">
+      <c r="A1" s="325" t="s">
         <v>405</v>
       </c>
-      <c r="B1" s="203"/>
-      <c r="C1" s="203"/>
-      <c r="D1" s="203"/>
-      <c r="E1" s="203"/>
-      <c r="F1" s="203" t="s">
+      <c r="B1" s="325"/>
+      <c r="C1" s="325"/>
+      <c r="D1" s="325"/>
+      <c r="E1" s="325"/>
+      <c r="F1" s="325" t="s">
         <v>406</v>
       </c>
-      <c r="G1" s="203"/>
-      <c r="H1" s="203"/>
-      <c r="I1" s="203"/>
-      <c r="J1" s="203"/>
+      <c r="G1" s="325"/>
+      <c r="H1" s="325"/>
+      <c r="I1" s="325"/>
+      <c r="J1" s="325"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2" s="203"/>
-      <c r="B2" s="203"/>
-      <c r="C2" s="203"/>
-      <c r="D2" s="203"/>
-      <c r="E2" s="203"/>
-      <c r="F2" s="203"/>
-      <c r="G2" s="203"/>
-      <c r="H2" s="203"/>
-      <c r="I2" s="203"/>
-      <c r="J2" s="203"/>
+      <c r="A2" s="325"/>
+      <c r="B2" s="325"/>
+      <c r="C2" s="325"/>
+      <c r="D2" s="325"/>
+      <c r="E2" s="325"/>
+      <c r="F2" s="325"/>
+      <c r="G2" s="325"/>
+      <c r="H2" s="325"/>
+      <c r="I2" s="325"/>
+      <c r="J2" s="325"/>
       <c r="L2" t="s">
         <v>409</v>
       </c>
@@ -64380,10 +64370,10 @@
         <v>408</v>
       </c>
       <c r="N3" s="193">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O3" s="193">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P3" s="193">
         <v>0</v>
@@ -64392,21 +64382,21 @@
         <v>0</v>
       </c>
       <c r="R3" s="193">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="S3" s="193">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T3" s="193">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U3" s="193">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B4" s="192">
         <v>0.66666666666666663</v>
@@ -64418,22 +64408,22 @@
         <v>420</v>
       </c>
       <c r="E4" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="F4" t="s">
+        <v>479</v>
+      </c>
+      <c r="G4" s="202" t="s">
         <v>482</v>
-      </c>
-      <c r="G4" s="202" t="s">
-        <v>485</v>
       </c>
       <c r="H4" t="s">
         <v>6</v>
       </c>
       <c r="I4" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="J4" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="L4">
         <v>2</v>
@@ -64442,11 +64432,11 @@
         <v>413</v>
       </c>
       <c r="N4" s="193">
+        <v>7</v>
+      </c>
+      <c r="O4" s="193">
         <v>6</v>
       </c>
-      <c r="O4" s="193">
-        <v>5</v>
-      </c>
       <c r="P4" s="193">
         <v>0</v>
       </c>
@@ -64454,16 +64444,16 @@
         <v>1</v>
       </c>
       <c r="R4" s="193">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S4" s="193">
         <v>5</v>
       </c>
       <c r="T4" s="193">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U4" s="193">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
@@ -64474,10 +64464,10 @@
         <v>417</v>
       </c>
       <c r="N5" s="193">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O5" s="193">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P5" s="193">
         <v>1</v>
@@ -64486,16 +64476,16 @@
         <v>1</v>
       </c>
       <c r="R5" s="193">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="S5" s="193">
         <v>5</v>
       </c>
       <c r="T5" s="193">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="U5" s="193">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
@@ -64503,31 +64493,31 @@
         <v>4</v>
       </c>
       <c r="M6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="N6" s="193">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O6" s="193">
+        <v>4</v>
+      </c>
+      <c r="P6" s="193">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="193">
         <v>2</v>
       </c>
-      <c r="P6" s="193">
+      <c r="R6" s="193">
+        <v>17</v>
+      </c>
+      <c r="S6" s="193">
+        <v>13</v>
+      </c>
+      <c r="T6" s="193">
         <v>4</v>
       </c>
-      <c r="Q6" s="193">
-        <v>0</v>
-      </c>
-      <c r="R6" s="193">
-        <v>12</v>
-      </c>
-      <c r="S6" s="193">
-        <v>6</v>
-      </c>
-      <c r="T6" s="193">
-        <v>6</v>
-      </c>
       <c r="U6" s="193">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
@@ -64535,31 +64525,31 @@
         <v>5</v>
       </c>
       <c r="M7" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="N7" s="193">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O7" s="193">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P7" s="193">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q7" s="193">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" s="193">
+        <v>9</v>
+      </c>
+      <c r="S7" s="193">
         <v>8</v>
       </c>
-      <c r="S7" s="193">
-        <v>5</v>
-      </c>
       <c r="T7" s="193">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U7" s="193">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
@@ -64567,28 +64557,28 @@
         <v>6</v>
       </c>
       <c r="M8" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="N8" s="193">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O8" s="193">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P8" s="193">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q8" s="193">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R8" s="193">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="S8" s="193">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T8" s="193">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U8" s="193">
         <v>10</v>
@@ -64602,28 +64592,28 @@
         <v>424</v>
       </c>
       <c r="N9" s="193">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O9" s="193">
         <v>2</v>
       </c>
       <c r="P9" s="193">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q9" s="193">
         <v>1</v>
       </c>
       <c r="R9" s="193">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S9" s="193">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T9" s="193">
         <v>3</v>
       </c>
       <c r="U9" s="193">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
@@ -64631,16 +64621,16 @@
         <v>8</v>
       </c>
       <c r="M10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="N10" s="193">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O10" s="193">
         <v>2</v>
       </c>
       <c r="P10" s="193">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q10" s="193">
         <v>1</v>
@@ -64649,13 +64639,13 @@
         <v>8</v>
       </c>
       <c r="S10" s="193">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T10" s="193">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U10" s="193">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
@@ -64663,10 +64653,10 @@
         <v>9</v>
       </c>
       <c r="M11" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="N11" s="193">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O11" s="193">
         <v>2</v>
@@ -64675,16 +64665,16 @@
         <v>3</v>
       </c>
       <c r="Q11" s="193">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R11" s="193">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S11" s="193">
         <v>7</v>
       </c>
       <c r="T11" s="193">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U11" s="193">
         <v>9</v>
@@ -64698,7 +64688,7 @@
         <v>423</v>
       </c>
       <c r="N12" s="193">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O12" s="193">
         <v>3</v>
@@ -64707,16 +64697,16 @@
         <v>0</v>
       </c>
       <c r="Q12" s="193">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R12" s="193">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="S12" s="193">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T12" s="193" t="s">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="U12" s="193">
         <v>9</v>
@@ -64730,7 +64720,7 @@
         <v>427</v>
       </c>
       <c r="N13" s="193">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O13" s="193">
         <v>2</v>
@@ -64739,16 +64729,16 @@
         <v>2</v>
       </c>
       <c r="Q13" s="193">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R13" s="193">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S13" s="193">
-        <v>9</v>
-      </c>
-      <c r="T13" s="193">
-        <v>0</v>
+        <v>14</v>
+      </c>
+      <c r="T13" s="193" t="s">
+        <v>468</v>
       </c>
       <c r="U13" s="193">
         <v>8</v>
@@ -64759,31 +64749,31 @@
         <v>12</v>
       </c>
       <c r="M14" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="N14" s="193">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O14" s="193">
         <v>2</v>
       </c>
       <c r="P14" s="193">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q14" s="193">
         <v>3</v>
       </c>
       <c r="R14" s="193">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S14" s="193">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T14" s="193" t="s">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="U14" s="193">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
@@ -64794,28 +64784,28 @@
         <v>426</v>
       </c>
       <c r="N15" s="193">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O15" s="193">
         <v>1</v>
       </c>
       <c r="P15" s="193">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q15" s="193">
         <v>2</v>
       </c>
       <c r="R15" s="193">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S15" s="193">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T15" s="193">
         <v>0</v>
       </c>
       <c r="U15" s="193">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
@@ -64823,31 +64813,31 @@
         <v>14</v>
       </c>
       <c r="M16" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="N16" s="193">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O16" s="193">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P16" s="193">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="193">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R16" s="193">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="S16" s="193">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="T16" s="193" t="s">
-        <v>457</v>
+        <v>486</v>
       </c>
       <c r="U16" s="193">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="12:21" x14ac:dyDescent="0.25">
@@ -64855,31 +64845,31 @@
         <v>15</v>
       </c>
       <c r="M17" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N17" s="193">
+        <v>7</v>
+      </c>
+      <c r="O17" s="193">
+        <v>1</v>
+      </c>
+      <c r="P17" s="193">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="193">
+        <v>3</v>
+      </c>
+      <c r="R17" s="193">
+        <v>9</v>
+      </c>
+      <c r="S17" s="193">
+        <v>13</v>
+      </c>
+      <c r="T17" s="193" t="s">
+        <v>468</v>
+      </c>
+      <c r="U17" s="193">
         <v>6</v>
-      </c>
-      <c r="O17" s="193">
-        <v>1</v>
-      </c>
-      <c r="P17" s="193">
-        <v>2</v>
-      </c>
-      <c r="Q17" s="193">
-        <v>3</v>
-      </c>
-      <c r="R17" s="193">
-        <v>6</v>
-      </c>
-      <c r="S17" s="193">
-        <v>11</v>
-      </c>
-      <c r="T17" s="193" t="s">
-        <v>433</v>
-      </c>
-      <c r="U17" s="193">
-        <v>5</v>
       </c>
     </row>
     <row r="18" spans="12:21" x14ac:dyDescent="0.25">
@@ -64887,31 +64877,31 @@
         <v>16</v>
       </c>
       <c r="M18" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N18" s="193">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O18" s="193">
         <v>1</v>
       </c>
       <c r="P18" s="193">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q18" s="193">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R18" s="193">
         <v>6</v>
       </c>
       <c r="S18" s="193">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T18" s="193" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="U18" s="193">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="12:21" x14ac:dyDescent="0.25">
@@ -64919,31 +64909,31 @@
         <v>17</v>
       </c>
       <c r="M19" t="s">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="N19" s="193">
+        <v>7</v>
+      </c>
+      <c r="O19" s="193">
+        <v>2</v>
+      </c>
+      <c r="P19" s="193">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="193">
+        <v>5</v>
+      </c>
+      <c r="R19" s="193">
         <v>6</v>
       </c>
-      <c r="O19" s="193">
-        <v>0</v>
-      </c>
-      <c r="P19" s="193">
-        <v>3</v>
-      </c>
-      <c r="Q19" s="193">
-        <v>3</v>
-      </c>
-      <c r="R19" s="193">
-        <v>7</v>
-      </c>
       <c r="S19" s="193">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T19" s="193" t="s">
-        <v>460</v>
+        <v>486</v>
       </c>
       <c r="U19" s="193">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="12:21" x14ac:dyDescent="0.25">
@@ -64951,31 +64941,31 @@
         <v>18</v>
       </c>
       <c r="M20" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="N20" s="193">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O20" s="193">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P20" s="193">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q20" s="193">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R20" s="193">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S20" s="193">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T20" s="193" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="U20" s="193">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="12:21" x14ac:dyDescent="0.25">
@@ -64983,31 +64973,31 @@
         <v>19</v>
       </c>
       <c r="M21" t="s">
-        <v>404</v>
+        <v>428</v>
       </c>
       <c r="N21" s="193">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O21" s="193">
         <v>1</v>
       </c>
       <c r="P21" s="193">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q21" s="193">
         <v>4</v>
       </c>
       <c r="R21" s="193">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S21" s="193">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T21" s="193" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="U21" s="193">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="12:21" x14ac:dyDescent="0.25">
@@ -65015,31 +65005,31 @@
         <v>20</v>
       </c>
       <c r="M22" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="N22" s="193">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O22" s="193">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P22" s="193">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q22" s="193">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R22" s="193">
         <v>6</v>
       </c>
       <c r="S22" s="193">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T22" s="193" t="s">
-        <v>470</v>
+        <v>486</v>
       </c>
       <c r="U22" s="193">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -65068,13 +65058,13 @@
         <v>1</v>
    